--- a/public/data/住宅公寓口碑汇总.xlsx
+++ b/public/data/住宅公寓口碑汇总.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口碑汇总" sheetId="1" r:id="R94256486cd52457e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口碑汇总" sheetId="1" r:id="R2efacbacf86149b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -252,41 +252,44 @@
         <x:v>北京市海淀区东北旺西路8号院</x:v>
       </x:c>
       <x:c r="E2" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F2" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G2" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H2" t="n">
         <x:v>8.5</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>2011年高品质社区，绿化率高且紧邻软件园，租金较高但通勤极佳，适合高预算人群。</x:v>
+        <x:v>品质极佳且紧邻软件园，隔音好环境优，虽缺乏大型商场但通勤便利，非常适合网易员工。</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 7800元/月；+4.71% * 二室 9350元/月；-1.07% * 三室 14761元/月；+1.62% * 四室 22000元/月；月租金 涨跌幅 * 1.香炉营头条33号院10637元/月；小区名称 月租金 涨跌幅 * 1.东旭园6408元/月；-1.26% ↓ * 2.东馨园5495元/月；-0.81% ↓ * 3.苗圃家属楼5628元/月</x:v>
+        <x:v>由亿城山水开发，2012年交房，装修标准3800元/㎡</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v># 亿城西山公馆租房,上地亿城西山公馆房屋出租价格,亿城西山公馆整租合租房价-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;上地小区 &gt;亿城西山公馆&gt;亿城西山公馆租房 亿城西山公馆 * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 # 亿城西山公馆 * 物业类型：公寓住宅 * 竣工时间：2011 * 总户数：726 * 容积数：1.92 * 建筑类型：多层、高层 * 统一供暖：否 * 停车位：200（1:0.28） * 车位管理费：暂无数据 * 小区地址：东北旺西路8号 * 幼儿园：暂无数据 * 小学：北京市东北旺中心小学 * 初中：暂无数据 * 权属类别：商品房住宅 * 产权年限：暂无数据 * 总建面积：暂无数据 * 绿化率：46% * 所属商圈：上地 * 物业公司：远洋物业服务游侠公司 * 物业费：3.60元/平米/月 * 开发商：北京亿城房地产开发有限公司 * 电梯：未知 亿城西山公馆租金趋势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 7800元/月+4.71% * 二室 9350元/月-1.07% * 三室 14761元/月+1.62% * 四室 22000元/月 0.00% * 四室以上 0元/月+0.00% 亿城西山公馆出租房源 * 全部 * 整租 * 合租 * 个人 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 * 暂无数据 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 附近小区房屋出租 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 同区域房屋出租 * 全部 * 安选 * VR看房 * 视频看房 * 9200 元整租 四季青 曙光花园望山园 2室1厅 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租白石桥大柳树甲17号院2室1厅 2室1厅 / 64.0㎡ 推荐理由： 精装修 * 1800 元永旺家园一区全女生合租次卧出租价格1800可 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 2300 元16号线 永旺家园 原始主卧 万象汇 软件园 百度 网易 3室1厅 / 16㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 * 9200 元整租 四季青 曙光花园望山园 2室1厅 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租白石桥大柳树甲17号院2室1厅 2室1厅 / 64.0㎡ 推荐理由： 精装修 * 1800 元永旺家园一区全女生合租次卧出租价格1800可 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 2300 元16号线 永旺家园 原始主卧 万象汇 软件园 百度 网易 3室1厅 / 16㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 * 6600 元南北通透 近魏公村地铁 全家具家电 看房方便 2室1厅 / 53.89㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 7600 元五棵松新兴年代中楼层2居室 2室1厅 / 92.84㎡ 推荐理由： 邻地铁 精装修 * 9800 元双榆树双榆树西里中楼层3居室 3室1厅 / 70.23㎡ 推荐理由： 邻地铁 * 6992 元定慧寺恩济庄46号院高楼层2居室 2室1厅 / 86.87㎡ 推荐理由： 邻地铁 押一付一 * 7500 元2室1厅 景和园 企业力荐诚意出租随时看房 2室1厅 / 74.0㎡ 推荐理由： 邻地铁 * 5200 元紫竹桥 广源大厦 可 可月付 豪柏大厦 人济山庄 1室1厅 / 38.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 * 14000 元南北通透 3室2厅 乐府江南 3室2厅 / 140.13㎡ 推荐理由： 邻地铁 * 4200 元正南 1室1厅 温泉凯盛家园(一区) 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 * 6175 元白石桥钢铁研究院中楼层2居室 2室1厅 / 50.1㎡ 推荐理由： 精装修 * 4200 元民水民电 西三旗万象汇对面 东升科技园 民水民电 朝南一居室 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 * 6300 元整租西直门交大东路34号院1室1厅 1室1厅 / 45.4㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 4000 元月付，0押，海淀西五环中关村三小精装带电梯两居出租随时看 2室1厅 / 78㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 12500 元精装三居室采光好 清华北大 华清嘉园 近五道口地铁站13号线 3室1厅 / 141.90㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 9000 元整租定慧寺定慧北里3室2厅 3室2厅 / 103.46㎡ 推荐理由： 邻地铁 精装修 * 4050 元民水民电 西三旗万象汇对面 东升科技园 可月付 无中介无杂费 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 ## 亿城西山公馆相关小区推荐 ## 同价位小区推荐 * 小区名称 月租金 涨跌幅 * 1.香炉营头条33号院10637元/月 0.58% ↑ ## 附近小区推荐 * 小区名称 月租金 涨跌幅 * 1.东旭园6408元/月-1.26% ↓ * 2.东馨园5495元/月-0.81% ↓ * 3.苗圃家属楼5628元/月 1.10% ↑ * 4.八维一公寓1556元/月-3.23% ↓ * 5.唐家岭路55号院2500元/月- ## 同区域小区推荐 * 小区名称 月租金 涨跌幅 * 1.翠湖别墅15750元/月 0.00% ↑ * 2.龙翔路8号院6450元/月- * 3.气象局宿舍8110元/月 7.79% ↑ * 4.阜成路6号院10000元/月- * 5.鑫德嘉园10907元/月 0.09% ↑ ## 同城小区推荐 * 小区名称 月租金 涨跌幅 * 1.远洋万和城(C区)30900元/月-15.57% ↓ * 2.翠湖别墅15750元/月 0.00% ↑ * 3.东坝河甲2号院3250元/月-1.81% ↓ * 4.鹿鸣苑5266元/月 1.90% ↑ * 5.永定河孔雀城剑桥郡(八期)-- ## 亿城西山公馆附近经纪人 * 王莉娟 北京永泰伟业房地产经纪有限公司 * 赵瑞涛 北京永泰伟业房地产经纪有限公司 * 张利丹 北京麦田房产经纪有限公司 * 夏宁 北京永泰伟业房地产经纪有限公司 * 张寅 北京信富住房租赁有限公司 * 邢倩 北京永泰伟业房地产经纪有限公司 * 高鸿岩 北京麦田房产经纪有限公司 * 刘贺 北京麦田房产经纪有限公司 * 戚永乐 北京信富住房租赁有限公司 * 李兵 北京永泰伟业房地产经纪有限公司 * 王嘉宇 北京我爱我家房地产经纪有限公司 * 芦伟霞 北京永泰伟业房地产经纪有限公司 ## 亿城西山公馆问答 * 问 租房能落户吗？；中介费一般只收一次，一般是一个月的租金为中介费 * 问【沿湖南区】 要看短租房 * 沉默： 您好，小区有短租的房子，您可以联系我带您看房 * 问 租房都要注意什么 * cNoFvjD： 需要注意是业主直租还是中介公司的房源，看清租赁合同、租金、押金、付款方式、退租要求、水电燃气上个租户是否结清，房屋的家电家具做好物业交割。；北京吉屋网提供北京亿城西山公馆二手房出售信息、亿城西山公馆二手房价格，包括及时更新北京亿城西山公馆二手房房源、价格走势、户型图、业主论坛、生活配套。；# 亿城西山公馆_北京亿城西山公馆小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_亿城西山公馆 更新于 2026-06-01 10:46:29 [](https://bj.jiwu.com/tu/5867584.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867585.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867586.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867587.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867588.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867589.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867590.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867591.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867592.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867593.html "亿城西山公馆实景图图片") # 亿城西山公馆 别名：亿城西山公馆 加入本地买房群 关注 _北京 - 海淀 - 海淀东北旺西路8号中关村软件园_ 发地址到手机 参考均价 _77213 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2012_ 小区户数 _676户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-18群（356） * 大家觉得这里未来发展怎么样？；加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(5)3室(5) 全部户型 [](https://bj.jiwu.com/huxing/887531.html "亿城西山公馆2室2厅2卫109㎡户型图")2室2厅2卫 109㎡咨询户型房源 [](https://bj.jiwu.com/huxing/887532.html "亿城西山公馆3室2厅2卫131㎡户型图")3室2厅2卫 131㎡咨询户型房源 [](https://bj.jiwu.com/huxing/887533.html "亿城西山公馆2室2厅2卫113㎡户型图")2室2厅2卫 113㎡咨询户型房源 小区评测报告 ？</x:v>
+        <x:v>房屋由亿城山水开发，2012年交房，装修标准3800元/㎡，采用双层玻璃，隔音效果较好；；户型以一梯两户为主，有南北通透、东西通透户型，包括69平左右1室、77-78平左右2室、150平左右3室；；物业实行专业管理，小区绿化率高，环境好；</x:v>
       </x:c>
       <x:c r="L2" t="str">
-        <x:v># 亿城西山公馆租房,上地亿城西山公馆房屋出租价格,亿城西山公馆整租合租房价-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;上地小区 &gt;亿城西山公馆&gt;亿城西山公馆租房 亿城西山公馆 * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 # 亿城西山公馆 * 物业类型：公寓住宅 * 竣工时间：2011 * 总户数：726 * 容积数：1.92 * 建筑类型：多层、高层 * 统一供暖：否 * 停车位：200（1:0.28） * 车位管理费：暂无数据 * 小区地址：东北旺西路8号 * 幼儿园：暂无数据 * 小学：北京市东北旺中心小学 * 初中：暂无数据 * 权属类别：商品房住宅 * 产权年限：暂无数据 * 总建面积：暂无数据 * 绿化率：46% * 所属商圈：上地 * 物业公司：远洋物业服务游侠公司 * 物业费：3.60元/平米/月 * 开发商：北京亿城房地产开发有限公司 * 电梯：未知 亿城西山公馆租金趋势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 7800元/月+4.71% * 二室 9350元/月-1.07% * 三室 14761元/月+1.62% * 四室 22000元/月 0.00% * 四室以上 0元/月+0.00% 亿城西山公馆出租房源 * 全部 * 整租 * 合租 * 个人 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 * 暂无数据 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 附近小区房屋出租 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 同区域房屋出租 * 全部 * 安选 * VR看房 * 视频看房 * 9200 元整租 四季青 曙光花园望山园 2室1厅 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租白石桥大柳树甲17号院2室1厅 2室1厅 / 64.0㎡ 推荐理由： 精装修 * 1800 元永旺家园一区全女生合租次卧出租价格1800可 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 2300 元16号线 永旺家园 原始主卧 万象汇 软件园 百度 网易 3室1厅 / 16㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 * 9200 元整租 四季青 曙光花园望山园 2室1厅 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租白石桥大柳树甲17号院2室1厅 2室1厅 / 64.0㎡ 推荐理由： 精装修 * 1800 元永旺家园一区全女生合租次卧出租价格1800可 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 2300 元16号线 永旺家园 原始主卧 万象汇 软件园 百度 网易 3室1厅 / 16㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 * 6600 元南北通透 近魏公村地铁 全家具家电 看房方便 2室1厅 / 53.89㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 7600 元五棵松新兴年代中楼层2居室 2室1厅 / 92.84㎡ 推荐理由： 邻地铁 精装修 * 9800 元双榆树双榆树西里中楼层3居室 3室1厅 / 70.23㎡ 推荐理由： 邻地铁 * 6992 元定慧寺恩济庄46号院高楼层2居室 2室1厅 / 86.87㎡ 推荐理由： 邻地铁 押一付一 * 7500 元2室1厅 景和园 企业力荐诚意出租随时看房 2室1厅 / 74.0㎡ 推荐理由： 邻地铁 * 5200 元紫竹桥 广源大厦 可 可月付 豪柏大厦 人济山庄 1室1厅 / 38.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 * 14000 元南北通透 3室2厅 乐府江南 3室2厅 / 140.13㎡ 推荐理由： 邻地铁 * 4200 元正南 1室1厅 温泉凯盛家园(一区) 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 * 6175 元白石桥钢铁研究院中楼层2居室 2室1厅 / 50.1㎡ 推荐理由： 精装修 * 4200 元民水民电 西三旗万象汇对面 东升科技园 民水民电 朝南一居室 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 * 6300 元整租西直门交大东路34号院1室1厅 1室1厅 / 45.4㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 4000 元月付，0押，海淀西五环中关村三小精装带电梯两居出租随时看 2室1厅 / 78㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 12500 元精装三居室采光好 清华北大 华清嘉园 近五道口地铁站13号线 3室1厅 / 141.90㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 9000 元整租定慧寺定慧北里3室2厅 3室2厅 / 103.46㎡ 推荐理由： 邻地铁 精装修 * 4050 元民水民电 西三旗万象汇对面 东升科技园 可月付 无中介无杂费 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 ## 亿城西山公馆相关小区推荐 ## 同价位小区推荐 * 小区名称 月租金 涨跌幅 * 1.香炉营头条33号院10637元/月 0.58% ↑ ## 附近小区推荐 * 小区名称 月租金 涨跌幅 * 1.东旭园6408元/月-1.26% ↓ * 2.东馨园5495元/月-0.81% ↓ * 3.苗圃家属楼5628元/月 1.10% ↑ * 4.八维一公寓1556元/月-3.23% ↓ * 5.唐家岭路55号院2500元/月- ## 同区域小区推荐 * 小区名称 月租金 涨跌幅 * 1.翠湖别墅15750元/月 0.00% ↑ * 2.龙翔路8号院6450元/月- * 3.气象局宿舍8110元/月 7.79% ↑ * 4.阜成路6号院10000元/月- * 5.鑫德嘉园10907元/月 0.09% ↑ ## 同城小区推荐 * 小区名称 月租金 涨跌幅 * 1.远洋万和城(C区)30900元/月-15.57% ↓ * 2.翠湖别墅15750元/月 0.00% ↑ * 3.东坝河甲2号院3250元/月-1.81% ↓ * 4.鹿鸣苑5266元/月 1.90% ↑ * 5.永定河孔雀城剑桥郡(八期)-- ## 亿城西山公馆附近经纪人 * 王莉娟 北京永泰伟业房地产经纪有限公司 * 赵瑞涛 北京永泰伟业房地产经纪有限公司 * 张利丹 北京麦田房产经纪有限公司 * 夏宁 北京永泰伟业房地产经纪有限公司 * 张寅 北京信富住房租赁有限公司 * 邢倩 北京永泰伟业房地产经纪有限公司 * 高鸿岩 北京麦田房产经纪有限公司 * 刘贺 北京麦田房产经纪有限公司 * 戚永乐 北京信富住房租赁有限公司 * 李兵 北京永泰伟业房地产经纪有限公司 * 王嘉宇 北京我爱我家房地产经纪有限公司 * 芦伟霞 北京永泰伟业房地产经纪有限公司 ## 亿城西山公馆问答 * 问 租房能落户吗？；* 郭飞洋： 1.找和业主直签的房子 2.*签约合同，并写上业主和租户需要承担的费用 3.看业主身份证和房本 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 宁国租房 * 宁德租房 * 汕尾租房 * 六盘水租房 * 定西租房 * 三亚租房 * 睢县租房 * 十堰租房 * 孝感租房 * 常宁租房 * 馆陶租房 * 启东租房 * 响水租房 * 大连租房 * 开原租房 * 邹城租房 * 大竹租房 * 丽江租房 * 义乌租房 * 诸暨租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 东旭园租房 * 东馨园租房 * 苗圃家属楼租房 * 八维一公寓租房 * 唐家岭路55号院租房 * 唐家岭路57号院租房 * 万德嘉园(一区)租房 * 万德嘉园(二区)租房 * 上地八街7号院2号楼租房 * 辉煌国际公寓租房 * 菊花盛苑租房 * 菊园租房 * 四方大厦租房 * 柳浪家园北里租房 * 马连洼北路1号院租房 * 竹园小区租房 * 柳浪家园东里租房 * 百草园社区租房 * 裕和嘉园租房 * 亿城西山华府珑园租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 三室户租房 * 家电齐全租房 * 带网络合租房 * 特别干净出租 * 带书房合租房 * 带安保出租 * 带密码门锁出租 * 毕业生出租 * 一层租房 * 个人合租房 * 超值合租房 * 廉价租房 * 青年公寓合租房 * 自建房合租房 * 抢手租房 * 朝西出租 * loft复式租房 * 朝西北租房 * 地铁口附近租房 * 篮球场附近出租 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?；北京吉屋网提供北京亿城西山公馆二手房出售信息、亿城西山公馆二手房价格，包括及时更新北京亿城西山公馆二手房房源、价格走势、户型图、业主论坛、生活配套。；# 亿城西山公馆_北京亿城西山公馆小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_亿城西山公馆 更新于 2026-06-01 10:46:29 [](https://bj.jiwu.com/tu/5867584.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867585.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867586.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867587.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867588.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867589.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867590.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867591.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867592.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867593.html "亿城西山公馆实景图图片") # 亿城西山公馆 别名：亿城西山公馆 加入本地买房群 关注 _北京 - 海淀 - 海淀东北旺西路8号中关村软件园_ 发地址到手机 参考均价 _77213 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2012_ 小区户数 _676户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-18群（356） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?</x:v>
+        <x:v>通勤方面，距18号线上地软件园步行约839米，昌平线西二旗步行约1850米，周边有东北旺南路等公交站；；生活便利度较高，楼下有便利店、甜点店，南侧有市政公园，周边有千禧百旺生活超市、农贸市场，附近有仁德堂药店、北京三院，餐饮配套丰富，紧邻中关村软件园；；暂无明确差评风险，需注意部分房源中介费需一个月租金，部分报道中提到小区在软件园内部，相对独立，大型商业配套不足。；暂无明确差评风险，需注意部分房源中介费需一个月租金，部分报道中提到小区在软件园内部，相对独立，大型商业配套不足</x:v>
       </x:c>
       <x:c r="M2" t="str">
-        <x:v>* 郭飞洋： 1.找和业主直签的房子 2.*签约合同，并写上业主和租户需要承担的费用 3.看业主身份证和房本 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 宁国租房 * 宁德租房 * 汕尾租房 * 六盘水租房 * 定西租房 * 三亚租房 * 睢县租房 * 十堰租房 * 孝感租房 * 常宁租房 * 馆陶租房 * 启东租房 * 响水租房 * 大连租房 * 开原租房 * 邹城租房 * 大竹租房 * 丽江租房 * 义乌租房 * 诸暨租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 东旭园租房 * 东馨园租房 * 苗圃家属楼租房 * 八维一公寓租房 * 唐家岭路55号院租房 * 唐家岭路57号院租房 * 万德嘉园(一区)租房 * 万德嘉园(二区)租房 * 上地八街7号院2号楼租房 * 辉煌国际公寓租房 * 菊花盛苑租房 * 菊园租房 * 四方大厦租房 * 柳浪家园北里租房 * 马连洼北路1号院租房 * 竹园小区租房 * 柳浪家园东里租房 * 百草园社区租房 * 裕和嘉园租房 * 亿城西山华府珑园租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 三室户租房 * 家电齐全租房 * 带网络合租房 * 特别干净出租 * 带书房合租房 * 带安保出租 * 带密码门锁出租 * 毕业生出租 * 一层租房 * 个人合租房 * 超值合租房 * 廉价租房 * 青年公寓合租房 * 自建房合租房 * 抢手租房 * 朝西出租 * loft复式租房 * 朝西北租房 * 地铁口附近租房 * 篮球场附近出租 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?</x:v>
+        <x:v>暂无明确差评风险，需注意部分房源中介费需一个月租金，部分报道中提到小区在软件园内部，相对独立，大型商业配套不足。；暂无明确差评风险，需注意部分房源中介费需一个月租金，部分报道中提到小区在软件园内部，相对独立，大型商业配套不足</x:v>
       </x:c>
       <x:c r="N2" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 7800元/月；+4.71% * 二室 9350元/月；-1.07% * 三室 14761元/月；+1.62% * 四室 22000元/月；月租金 涨跌幅 * 1.香炉营头条33号院10637元/月；小区名称 月租金 涨跌幅 * 1.东旭园6408元/月；-1.26% ↓ * 2.东馨园5495元/月；-0.81% ↓ * 3.苗圃家属楼5628元/月；房屋质量/户型线索：# 亿城西山公馆租房,上地亿城西山公馆房屋出租价格,亿城西山公馆整租合租房价-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;上地小区 &gt;亿城西山公馆&gt;亿城西山公馆租房 亿城西山公馆 * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 # 亿城西山公馆 * 物业类型：公寓住宅 * 竣工时间：2011 * 总户数：726 * 容积数：1.92 * 建筑类型：多层、高层 * 统一供暖：否 * 停车位：200（1:0.28） * 车位管理费：暂无数据 * 小区地址：东北旺西路8号 * 幼儿园：暂无数据 * 小学：北京市东北旺中心小学 * 初中：暂无数据 * 权属类别：商品房住宅 * 产权年限：暂无数据 * 总建面积：暂无数据 * 绿化率：46% * 所属商圈：上地 * 物业公司：远洋物业服务游侠公司 * 物业费：3.60元/平米/月 * 开发商：北京亿城房地产开发有限公司 * 电梯：未知 亿城西山公馆租金趋势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 7800元/月+4.71% * 二室 9350元/月-1.07% * 三室 14761元/月+1.62% * 四室 22000元/月 0.00% * 四室以上 0元/月+0.00% 亿城西山公馆出租房源 * 全部 * 整租 * 合租 * 个人 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 * 暂无数据 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 附近小区房屋出租 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 同区域房屋出租 * 全部 * 安选 * VR看房 * 视频看房 * 9200 元整租 四季青 曙光花园望山园 2室1厅 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租白石桥大柳树甲17号院2室1厅 2室1厅 / 64.0㎡ 推荐理由： 精装修 * 1800 元永旺家园一区全女生合租次卧出租价格1800可 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 2300 元16号线 永旺家园 原始主卧 万象汇 软件园 百度 网易 3室1厅 / 16㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 * 9200 元整租 四季青 曙光花园望山园 2室1厅 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租白石桥大柳树甲17号院2室1厅 2室1厅 / 64.0㎡ 推荐理由： 精装修 * 1800 元永旺家园一区全女生合租次卧出租价格1800可 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 2300 元16号线 永旺家园 原始主卧 万象汇 软件园 百度 网易 3室1厅 / 16㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 * 6600 元南北通透 近魏公村地铁 全家具家电 看房方便 2室1厅 / 53.89㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 7600 元五棵松新兴年代中楼层2居室 2室1厅 / 92.84㎡ 推荐理由： 邻地铁 精装修 * 9800 元双榆树双榆树西里中楼层3居室 3室1厅 / 70.23㎡ 推荐理由： 邻地铁 * 6992 元定慧寺恩济庄46号院高楼层2居室 2室1厅 / 86.87㎡ 推荐理由： 邻地铁 押一付一 * 7500 元2室1厅 景和园 企业力荐诚意出租随时看房 2室1厅 / 74.0㎡ 推荐理由： 邻地铁 * 5200 元紫竹桥 广源大厦 可 可月付 豪柏大厦 人济山庄 1室1厅 / 38.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 * 14000 元南北通透 3室2厅 乐府江南 3室2厅 / 140.13㎡ 推荐理由： 邻地铁 * 4200 元正南 1室1厅 温泉凯盛家园(一区) 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 * 6175 元白石桥钢铁研究院中楼层2居室 2室1厅 / 50.1㎡ 推荐理由： 精装修 * 4200 元民水民电 西三旗万象汇对面 东升科技园 民水民电 朝南一居室 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 * 6300 元整租西直门交大东路34号院1室1厅 1室1厅 / 45.4㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 4000 元月付，0押，海淀西五环中关村三小精装带电梯两居出租随时看 2室1厅 / 78㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 12500 元精装三居室采光好 清华北大 华清嘉园 近五道口地铁站13号线 3室1厅 / 141.90㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 9000 元整租定慧寺定慧北里3室2厅 3室2厅 / 103.46㎡ 推荐理由： 邻地铁 精装修 * 4050 元民水民电 西三旗万象汇对面 东升科技园 可月付 无中介无杂费 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 ## 亿城西山公馆相关小区推荐 ## 同价位小区推荐 * 小区名称 月租金 涨跌幅 * 1.香炉营头条33号院10637元/月 0.58% ↑ ## 附近小区推荐 * 小区名称 月租金 涨跌幅 * 1.东旭园6408元/月-1.26% ↓ * 2.东馨园5495元/月-0.81% ↓ * 3.苗圃家属楼5628元/月 1.10% ↑ * 4.八维一公寓1556元/月-3.23% ↓ * 5.唐家岭路55号院2500元/月- ## 同区域小区推荐 * 小区名称 月租金 涨跌幅 * 1.翠湖别墅15750元/月 0.00% ↑ * 2.龙翔路8号院6450元/月- * 3.气象局宿舍8110元/月 7.79% ↑ * 4.阜成路6号院10000元/月- * 5.鑫德嘉园10907元/月 0.09% ↑ ## 同城小区推荐 * 小区名称 月租金 涨跌幅 * 1.远洋万和城(C区)30900元/月-15.57% ↓ * 2.翠湖别墅15750元/月 0.00% ↑ * 3.东坝河甲2号院3250元/月-1.81% ↓ * 4.鹿鸣苑5266元/月 1.90% ↑ * 5.永定河孔雀城剑桥郡(八期)-- ## 亿城西山公馆附近经纪人 * 王莉娟 北京永泰伟业房地产经纪有限公司 * 赵瑞涛 北京永泰伟业房地产经纪有限公司 * 张利丹 北京麦田房产经纪有限公司 * 夏宁 北京永泰伟业房地产经纪有限公司 * 张寅 北京信富住房租赁有限公司 * 邢倩 北京永泰伟业房地产经纪有限公司 * 高鸿岩 北京麦田房产经纪有限公司 * 刘贺 北京麦田房产经纪有限公司 * 戚永乐 北京信富住房租赁有限公司 * 李兵 北京永泰伟业房地产经纪有限公司 * 王嘉宇 北京我爱我家房地产经纪有限公司 * 芦伟霞 北京永泰伟业房地产经纪有限公司 ## 亿城西山公馆问答 * 问 租房能落户吗？；中介费一般只收一次，一般是一个月的租金为中介费 * 问【沿湖南区】 要看短租房 * 沉默： 您好，小区有短租的房子，您可以联系我带您看房 * 问 租房都要注意什么 * cNoFvjD： 需要注意是业主直租还是中介公司的房源，看清租赁合同、租金、押金、付款方式、退租要求、水电燃气上个租户是否结清，房屋的家电家具做好物业交割。；北京吉屋网提供北京亿城西山公馆二手房出售信息、亿城西山公馆二手房价格，包括及时更新北京亿城西山公馆二手房房源、价格走势、户型图、业主论坛、生活配套。；# 亿城西山公馆_北京亿城西山公馆小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_亿城西山公馆 更新于 2026-06-01 10:46:29 [](https://bj.jiwu.com/tu/5867584.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867585.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867586.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867587.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867588.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867589.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867590.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867591.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867592.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867593.html "亿城西山公馆实景图图片") # 亿城西山公馆 别名：亿城西山公馆 加入本地买房群 关注 _北京 - 海淀 - 海淀东北旺西路8号中关村软件园_ 发地址到手机 参考均价 _77213 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2012_ 小区户数 _676户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-18群（356） * 大家觉得这里未来发展怎么样？；加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(5)3室(5) 全部户型 [](https://bj.jiwu.com/huxing/887531.html "亿城西山公馆2室2厅2卫109㎡户型图")2室2厅2卫 109㎡咨询户型房源 [](https://bj.jiwu.com/huxing/887532.html "亿城西山公馆3室2厅2卫131㎡户型图")3室2厅2卫 131㎡咨询户型房源 [](https://bj.jiwu.com/huxing/887533.html "亿城西山公馆2室2厅2卫113㎡户型图")2室2厅2卫 113㎡咨询户型房源 小区评测报告 ？；生活便利线索：# 亿城西山公馆租房,上地亿城西山公馆房屋出租价格,亿城西山公馆整租合租房价-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;上地小区 &gt;亿城西山公馆&gt;亿城西山公馆租房 亿城西山公馆 * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 # 亿城西山公馆 * 物业类型：公寓住宅 * 竣工时间：2011 * 总户数：726 * 容积数：1.92 * 建筑类型：多层、高层 * 统一供暖：否 * 停车位：200（1:0.28） * 车位管理费：暂无数据 * 小区地址：东北旺西路8号 * 幼儿园：暂无数据 * 小学：北京市东北旺中心小学 * 初中：暂无数据 * 权属类别：商品房住宅 * 产权年限：暂无数据 * 总建面积：暂无数据 * 绿化率：46% * 所属商圈：上地 * 物业公司：远洋物业服务游侠公司 * 物业费：3.60元/平米/月 * 开发商：北京亿城房地产开发有限公司 * 电梯：未知 亿城西山公馆租金趋势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 7800元/月+4.71% * 二室 9350元/月-1.07% * 三室 14761元/月+1.62% * 四室 22000元/月 0.00% * 四室以上 0元/月+0.00% 亿城西山公馆出租房源 * 全部 * 整租 * 合租 * 个人 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 * 暂无数据 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 附近小区房屋出租 * 9000 元西山公馆 精装两居室 配置齐全 业主签约 可长租 可约看房 2室1厅 / 77.70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元亿城西山公馆 2室1厅1卫 2室1厅 / 77.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7800 元整租 西北旺 西山公馆 1室1厅 1室1厅 / 68.93㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 7800 元1室1厅 亿城西山公馆 1室1厅 / 69.78㎡ 推荐理由： 独卫一居 邻地铁 * 14500 元亿城西山公馆 精装大三居 业主自住初次出租 家具齐全随时看房 3室2厅 / 150㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 9000 元近地铁 亿城西山公馆 全南精装两居 实房拍摄 配置齐全业主签 2室2厅 / 78.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 14000 元南北通透 3室1厅 亿城西山公馆 3室1厅 / 151.0㎡ 推荐理由： 邻地铁 * 10000 元0押金月付 马连洼西北旺中关村软件园西山公馆出租精装两居 2室1厅 / 110.2㎡ 推荐理由： 可短租 邻地铁 配套齐全 精装修 有阳台 首次出租 同区域房屋出租 * 全部 * 安选 * VR看房 * 视频看房 * 9200 元整租 四季青 曙光花园望山园 2室1厅 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租白石桥大柳树甲17号院2室1厅 2室1厅 / 64.0㎡ 推荐理由： 精装修 * 1800 元永旺家园一区全女生合租次卧出租价格1800可 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 2300 元16号线 永旺家园 原始主卧 万象汇 软件园 百度 网易 3室1厅 / 16㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 * 9200 元整租 四季青 曙光花园望山园 2室1厅 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租白石桥大柳树甲17号院2室1厅 2室1厅 / 64.0㎡ 推荐理由： 精装修 * 1800 元永旺家园一区全女生合租次卧出租价格1800可 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 2300 元16号线 永旺家园 原始主卧 万象汇 软件园 百度 网易 3室1厅 / 16㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 * 6600 元南北通透 近魏公村地铁 全家具家电 看房方便 2室1厅 / 53.89㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 7600 元五棵松新兴年代中楼层2居室 2室1厅 / 92.84㎡ 推荐理由： 邻地铁 精装修 * 9800 元双榆树双榆树西里中楼层3居室 3室1厅 / 70.23㎡ 推荐理由： 邻地铁 * 6992 元定慧寺恩济庄46号院高楼层2居室 2室1厅 / 86.87㎡ 推荐理由： 邻地铁 押一付一 * 7500 元2室1厅 景和园 企业力荐诚意出租随时看房 2室1厅 / 74.0㎡ 推荐理由： 邻地铁 * 5200 元紫竹桥 广源大厦 可 可月付 豪柏大厦 人济山庄 1室1厅 / 38.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 * 14000 元南北通透 3室2厅 乐府江南 3室2厅 / 140.13㎡ 推荐理由： 邻地铁 * 4200 元正南 1室1厅 温泉凯盛家园(一区) 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 * 6175 元白石桥钢铁研究院中楼层2居室 2室1厅 / 50.1㎡ 推荐理由： 精装修 * 4200 元民水民电 西三旗万象汇对面 东升科技园 民水民电 朝南一居室 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 * 6300 元整租西直门交大东路34号院1室1厅 1室1厅 / 45.4㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 4000 元月付，0押，海淀西五环中关村三小精装带电梯两居出租随时看 2室1厅 / 78㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 12500 元精装三居室采光好 清华北大 华清嘉园 近五道口地铁站13号线 3室1厅 / 141.90㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 9000 元整租定慧寺定慧北里3室2厅 3室2厅 / 103.46㎡ 推荐理由： 邻地铁 精装修 * 4050 元民水民电 西三旗万象汇对面 东升科技园 可月付 无中介无杂费 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 ## 亿城西山公馆相关小区推荐 ## 同价位小区推荐 * 小区名称 月租金 涨跌幅 * 1.香炉营头条33号院10637元/月 0.58% ↑ ## 附近小区推荐 * 小区名称 月租金 涨跌幅 * 1.东旭园6408元/月-1.26% ↓ * 2.东馨园5495元/月-0.81% ↓ * 3.苗圃家属楼5628元/月 1.10% ↑ * 4.八维一公寓1556元/月-3.23% ↓ * 5.唐家岭路55号院2500元/月- ## 同区域小区推荐 * 小区名称 月租金 涨跌幅 * 1.翠湖别墅15750元/月 0.00% ↑ * 2.龙翔路8号院6450元/月- * 3.气象局宿舍8110元/月 7.79% ↑ * 4.阜成路6号院10000元/月- * 5.鑫德嘉园10907元/月 0.09% ↑ ## 同城小区推荐 * 小区名称 月租金 涨跌幅 * 1.远洋万和城(C区)30900元/月-15.57% ↓ * 2.翠湖别墅15750元/月 0.00% ↑ * 3.东坝河甲2号院3250元/月-1.81% ↓ * 4.鹿鸣苑5266元/月 1.90% ↑ * 5.永定河孔雀城剑桥郡(八期)-- ## 亿城西山公馆附近经纪人 * 王莉娟 北京永泰伟业房地产经纪有限公司 * 赵瑞涛 北京永泰伟业房地产经纪有限公司 * 张利丹 北京麦田房产经纪有限公司 * 夏宁 北京永泰伟业房地产经纪有限公司 * 张寅 北京信富住房租赁有限公司 * 邢倩 北京永泰伟业房地产经纪有限公司 * 高鸿岩 北京麦田房产经纪有限公司 * 刘贺 北京麦田房产经纪有限公司 * 戚永乐 北京信富住房租赁有限公司 * 李兵 北京永泰伟业房地产经纪有限公司 * 王嘉宇 北京我爱我家房地产经纪有限公司 * 芦伟霞 北京永泰伟业房地产经纪有限公司 ## 亿城西山公馆问答 * 问 租房能落户吗？；* 郭飞洋： 1.找和业主直签的房子 2.*签约合同，并写上业主和租户需要承担的费用 3.看业主身份证和房本 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 宁国租房 * 宁德租房 * 汕尾租房 * 六盘水租房 * 定西租房 * 三亚租房 * 睢县租房 * 十堰租房 * 孝感租房 * 常宁租房 * 馆陶租房 * 启东租房 * 响水租房 * 大连租房 * 开原租房 * 邹城租房 * 大竹租房 * 丽江租房 * 义乌租房 * 诸暨租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 东旭园租房 * 东馨园租房 * 苗圃家属楼租房 * 八维一公寓租房 * 唐家岭路55号院租房 * 唐家岭路57号院租房 * 万德嘉园(一区)租房 * 万德嘉园(二区)租房 * 上地八街7号院2号楼租房 * 辉煌国际公寓租房 * 菊花盛苑租房 * 菊园租房 * 四方大厦租房 * 柳浪家园北里租房 * 马连洼北路1号院租房 * 竹园小区租房 * 柳浪家园东里租房 * 百草园社区租房 * 裕和嘉园租房 * 亿城西山华府珑园租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 三室户租房 * 家电齐全租房 * 带网络合租房 * 特别干净出租 * 带书房合租房 * 带安保出租 * 带密码门锁出租 * 毕业生出租 * 一层租房 * 个人合租房 * 超值合租房 * 廉价租房 * 青年公寓合租房 * 自建房合租房 * 抢手租房 * 朝西出租 * loft复式租房 * 朝西北租房 * 地铁口附近租房 * 篮球场附近出租 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?；北京吉屋网提供北京亿城西山公馆二手房出售信息、亿城西山公馆二手房价格，包括及时更新北京亿城西山公馆二手房房源、价格走势、户型图、业主论坛、生活配套。；# 亿城西山公馆_北京亿城西山公馆小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_亿城西山公馆 更新于 2026-06-01 10:46:29 [](https://bj.jiwu.com/tu/5867584.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867585.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867586.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867587.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867588.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867589.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867590.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867591.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867592.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867593.html "亿城西山公馆实景图图片") # 亿城西山公馆 别名：亿城西山公馆 加入本地买房群 关注 _北京 - 海淀 - 海淀东北旺西路8号中关村软件园_ 发地址到手机 参考均价 _77213 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2012_ 小区户数 _676户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-18群（356） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；风险线索：* 郭飞洋： 1.找和业主直签的房子 2.*签约合同，并写上业主和租户需要承担的费用 3.看业主身份证和房本 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 宁国租房 * 宁德租房 * 汕尾租房 * 六盘水租房 * 定西租房 * 三亚租房 * 睢县租房 * 十堰租房 * 孝感租房 * 常宁租房 * 馆陶租房 * 启东租房 * 响水租房 * 大连租房 * 开原租房 * 邹城租房 * 大竹租房 * 丽江租房 * 义乌租房 * 诸暨租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 东旭园租房 * 东馨园租房 * 苗圃家属楼租房 * 八维一公寓租房 * 唐家岭路55号院租房 * 唐家岭路57号院租房 * 万德嘉园(一区)租房 * 万德嘉园(二区)租房 * 上地八街7号院2号楼租房 * 辉煌国际公寓租房 * 菊花盛苑租房 * 菊园租房 * 四方大厦租房 * 柳浪家园北里租房 * 马连洼北路1号院租房 * 竹园小区租房 * 柳浪家园东里租房 * 百草园社区租房 * 裕和嘉园租房 * 亿城西山华府珑园租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 三室户租房 * 家电齐全租房 * 带网络合租房 * 特别干净出租 * 带书房合租房 * 带安保出租 * 带密码门锁出租 * 毕业生出租 * 一层租房 * 个人合租房 * 超值合租房 * 廉价租房 * 青年公寓合租房 * 自建房合租房 * 抢手租房 * 朝西出租 * loft复式租房 * 朝西北租房 * 地铁口附近租房 * 篮球场附近出租 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：由亿城山水开发，2012年交房，装修标准3800元/㎡；房屋质量/户型线索：房屋由亿城山水开发，2012年交房，装修标准3800元/㎡，采用双层玻璃，隔音效果较好；；户型以一梯两户为主，有南北通透、东西通透户型，包括69平左右1室、77-78平左右2室、150平左右3室；；物业实行专业管理，小区绿化率高，环境好；；生活便利线索：通勤方面，距18号线上地软件园步行约839米，昌平线西二旗步行约1850米，周边有东北旺南路等公交站；；生活便利度较高，楼下有便利店、甜点店，南侧有市政公园，周边有千禧百旺生活超市、农贸市场，附近有仁德堂药店、北京三院，餐饮配套丰富，紧邻中关村软件园；；暂无明确差评风险，需注意部分房源中介费需一个月租金，部分报道中提到小区在软件园内部，相对独立，大型商业配套不足。；暂无明确差评风险，需注意部分房源中介费需一个月租金，部分报道中提到小区在软件园内部，相对独立，大型商业配套不足；风险线索：暂无明确差评风险，需注意部分房源中介费需一个月租金，部分报道中提到小区在软件园内部，相对独立，大型商业配套不足。；暂无明确差评风险，需注意部分房源中介费需一个月租金，部分报道中提到小区在软件园内部，相对独立，大型商业配套不足</x:v>
       </x:c>
       <x:c r="O2" t="str">
-        <x:v>1. 亿城西山公馆租房,上地亿城西山公馆房屋出租价格,亿城西山公馆整租合租房价-北京58同城 http://mob.58.com/zfxq/bj-sy100403405/
-2. 亿城西山公馆_北京亿城西山公馆小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/55072.html
-3. 西山公馆房价怎么样？ 北京西山公馆房源|户型图|小区车位|交通地址详情分析 https://m.ke.com/news/bj/xiaoqu/1111042959484.html
-4. 【北京亿城西山公馆小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010653307.htm
-5. 亿城西山公馆房价, 亿城西山公馆亿城西山公馆房价走势图, 亿城西山公馆价格均价多少钱-安居客 https://m.anjuke.com/bj/trendency/community/457833/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4599360411100171-3/
+2. http://m.anjuke.com/bj/rent/4585296133823490-3/
+3. http://m.anjuke.com/bj/rent/4591549969345549-3/
+4. http://m.anjuke.com/bj/rent/4599418089726976-3/
+5. http://m.anjuke.com/bj/rent/4595721672666125-3/
+6. http://m.anjuke.com/bj/community/457833/jiedu-4138002/
+7. 1室1厅 亿城西山公馆 http://m.anjuke.com/bj/rent/4599360411100171-3/
+8. 亿城西山公馆怎么样，好不好_中介房产经纪人:李志颖对亿城西山公馆的评价-北京安居客 http://m.anjuke.com/bj/community/457833/jiedu-4138002/</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -303,41 +306,40 @@
         <x:v>北京市海淀区旺科东路</x:v>
       </x:c>
       <x:c r="E3" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F3" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G3" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H3" t="n">
-        <x:v>4.5</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>搜索证据存在严重的地理位置泛化错误，混入大量房山数据，真实租赁信息极度不透明。</x:v>
-      </x:c>
-      <x:c r="J3" t="str">
-        <x:v>21500 元/月；12000 元/月；交通便利周边配套齐采光好 2500 元/月；10200 元/月；交通便利周边配套齐采光好 1700 元/月；旺-颐和山庄 交通便利周边配套齐采光好 1200 元/月；2400 元/月；2600 元/月</x:v>
-      </x:c>
+        <x:v>2020年新房品质高，人车分流环境好，但需注意区分产业园办公空间与住宅房源。</x:v>
+      </x:c>
+      <x:c r="J3" t="str"/>
       <x:c r="K3" t="str">
-        <x:v>长阳半岛2号院 这个小区主打两居室 三居室 一居室一般都在一层 是属于变异户型 套数比较少 目前在租的一居室没有 租金一般在4500左右 * 陈耀忠： 您好，长阳半岛2号院的租金基本在3800-55000元之间。；# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：西北旺公寓出租条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486950500_1.htm) 4室2厅百旺茉莉园2期 整租|4室2厅|251㎡|朝南北 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。；12000 元/月 [](http://www.fang.com/chuzu/3_486520660_1.htm) 4室3厅保利西山林语别墅 整租|4室3厅|458㎡|朝南 海淀-西北旺-保利西山林语别墅 24600 元/月 [](http://www.fang.com/chuzu/3_486520654_1.htm) 1室1厅保利西山林语3期 整租|1室1厅|48㎡|朝南 海淀-西北旺-保利西山林语 4500 元/月 [](http://www.fang.com/chuzu/3_486952149_1.htm) 2室1厅保利西山林语3期 整租|2室1厅|91㎡|朝南北 海淀-西北旺-保利西山林语 5900 元/月 [](http://www.fang.com/chuzu/3_486918756_1.htm) 2室1厅保利西山林语2期 整租|2室1厅|96㎡|朝南北 海淀-西北旺-保利西山林语 6500 元/月 [](http://www.fang.com/chuzu/3_486843512_1.htm) 2室1厅保利西山林语3期 整租|2室1厅|91㎡|朝南北 海淀-西北旺-保利西山林语 5300 元/月 [](http://www.fang.com/chuzu/3_486952150_1.htm) 2室1厅保利西山林语2期 整租|2室1厅|85㎡|朝南北 海淀-西北旺-保利西山林语 5300 元/月 [](http://www.fang.com/chuzu/3_486951513_1.htm) 南北通透百旺新城冬晴园2室1厅精装修 整租|2室1厅|82㎡|朝南北 海淀-西北旺-百旺新城冬晴园 距16号线西北旺站约1193米。；5600 元/月 [](http://www.fang.com/chuzu/3_486918752_1.htm) 2室1厅保利西山林语3期 整租|2室1厅|91㎡|朝南北 海淀-西北旺-保利西山林语 5900 元/月 [](http://www.fang.com/chuzu/3_486950359_1.htm) 南北通透百旺新城夏霖园3室1厅精装修 整租|3室1厅|96㎡|朝南北 海淀-西北旺-百旺新城夏霖园 距16号线西北旺站约879米。</x:v>
+        <x:v>住宅类房源部分提到：冷泉村住房的房源精装修、户型采光好、隔音好；；另有房东直租的大两居为2020年底新房，2020年8月完成精装，户型南北通透，小区安静不临街，有电梯，人车分流，环境优美，配套运动设施；；产业园区类房源装修维护好、物业管理到位；</x:v>
       </x:c>
       <x:c r="L3" t="str">
-        <x:v>* 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * [](https://bj.zf.58.com/) * [](https://bj.zf.58.com/zz/xibeiwang/) * [](https://bj.zf.58.com/hz/xibeiwang/) * [](https://bj.zf.58.com/gr/xibeiwang/) * [](https://bj.58.com/pinpaigongyu/) * [](https://bj.58.com/xq/) * [](https://bj.zf.58.com/zujin/) * 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 ## 西北旺租房房产中介 * 张帅 北京相寓住房租赁有限公司 * 康涛 怡家（北京）住房租赁有限公司 * 李玲芳 北京正义东南房地产经纪有限公司 * 任琦 北京相寓住房租赁有限公司 * 陈永胜 北京德佑嘉业住房租赁有限公司 * 王春媛 北京泊邻美寓住房租赁有限公司 * 范金辉 北京相寓住房租赁有限公司 * 于意然 北京爱玛家房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 王万漳 北京麦田房产经纪有限公司 ## 租房房产问答 * 问 现在年底租房子便宜不 * Kair： 您好，我是我爱我家钱立智，很荣幸为您服务，年底租房客户群体较少，市场属于买方市场，供大于求，房价相对要便宜一些，过了年很多外来人员都有租房需求，供求关系发生变化，价格会有所上涨，具体情况欢迎垂询，期待您的来电，买好房，找立志！；* 侯丽霞： 您好，看您在的小区，租房可以上租房周边的幼儿园。；* 于娟： 你好，地方不同，政策不同，需要看当地政策来决定 * 艾尼卡尔江·阿布都拉： 您好，租房是可以上您所租的房子周边的幼儿园的。；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：西北旺公寓出租条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486950500_1.htm) 4室2厅百旺茉莉园2期 整租|4室2厅|251㎡|朝南北 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。；12000 元/月 [](http://www.fang.com/chuzu/3_486625663_1.htm) 立水桥地铁 茉莉园精装主卧独卫 19平朝西 四家两卫 合租主卧|3户合租|19㎡|朝南 海淀-西北旺-茉莉园 距16号线西北旺站约349米。</x:v>
-      </x:c>
-      <x:c r="M3" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>西北旺东路10号院（注意：部分搜索结果显示，该院区部分房源为产业园区类，380平整租月租金约3.31万元，另有周边相近区域住宅类租房如冷泉村住房，1室0厅1卫25平月租1800元，1室1厅1卫35平月租2200元，1室1厅1卫30平平房月租1800元）；；另有房东直租的大两居为2020年底新房，2020年8月完成精装，户型南北通透，小区安静不临街，有电梯，人车分流，环境优美，配套运动设施；；周边有商场、超市、菜市场、药店、幼儿园，临近地铁16号线西北旺站，通勤方便，可直达中关村、西二旗等互联网企业聚集地；</x:v>
+      </x:c>
+      <x:c r="M3" t="str"/>
       <x:c r="N3" t="str">
-        <x:v>价格线索：21500 元/月；12000 元/月；交通便利周边配套齐采光好 2500 元/月；10200 元/月；交通便利周边配套齐采光好 1700 元/月；旺-颐和山庄 交通便利周边配套齐采光好 1200 元/月；2400 元/月；2600 元/月；房屋质量/户型线索：长阳半岛2号院 这个小区主打两居室 三居室 一居室一般都在一层 是属于变异户型 套数比较少 目前在租的一居室没有 租金一般在4500左右 * 陈耀忠： 您好，长阳半岛2号院的租金基本在3800-55000元之间。；# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：西北旺公寓出租条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486950500_1.htm) 4室2厅百旺茉莉园2期 整租|4室2厅|251㎡|朝南北 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。；12000 元/月 [](http://www.fang.com/chuzu/3_486520660_1.htm) 4室3厅保利西山林语别墅 整租|4室3厅|458㎡|朝南 海淀-西北旺-保利西山林语别墅 24600 元/月 [](http://www.fang.com/chuzu/3_486520654_1.htm) 1室1厅保利西山林语3期 整租|1室1厅|48㎡|朝南 海淀-西北旺-保利西山林语 4500 元/月 [](http://www.fang.com/chuzu/3_486952149_1.htm) 2室1厅保利西山林语3期 整租|2室1厅|91㎡|朝南北 海淀-西北旺-保利西山林语 5900 元/月 [](http://www.fang.com/chuzu/3_486918756_1.htm) 2室1厅保利西山林语2期 整租|2室1厅|96㎡|朝南北 海淀-西北旺-保利西山林语 6500 元/月 [](http://www.fang.com/chuzu/3_486843512_1.htm) 2室1厅保利西山林语3期 整租|2室1厅|91㎡|朝南北 海淀-西北旺-保利西山林语 5300 元/月 [](http://www.fang.com/chuzu/3_486952150_1.htm) 2室1厅保利西山林语2期 整租|2室1厅|85㎡|朝南北 海淀-西北旺-保利西山林语 5300 元/月 [](http://www.fang.com/chuzu/3_486951513_1.htm) 南北通透百旺新城冬晴园2室1厅精装修 整租|2室1厅|82㎡|朝南北 海淀-西北旺-百旺新城冬晴园 距16号线西北旺站约1193米。；5600 元/月 [](http://www.fang.com/chuzu/3_486918752_1.htm) 2室1厅保利西山林语3期 整租|2室1厅|91㎡|朝南北 海淀-西北旺-保利西山林语 5900 元/月 [](http://www.fang.com/chuzu/3_486950359_1.htm) 南北通透百旺新城夏霖园3室1厅精装修 整租|3室1厅|96㎡|朝南北 海淀-西北旺-百旺新城夏霖园 距16号线西北旺站约879米。；生活便利线索：* 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * [](https://bj.zf.58.com/) * [](https://bj.zf.58.com/zz/xibeiwang/) * [](https://bj.zf.58.com/hz/xibeiwang/) * [](https://bj.zf.58.com/gr/xibeiwang/) * [](https://bj.58.com/pinpaigongyu/) * [](https://bj.58.com/xq/) * [](https://bj.zf.58.com/zujin/) * 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 ## 西北旺租房房产中介 * 张帅 北京相寓住房租赁有限公司 * 康涛 怡家（北京）住房租赁有限公司 * 李玲芳 北京正义东南房地产经纪有限公司 * 任琦 北京相寓住房租赁有限公司 * 陈永胜 北京德佑嘉业住房租赁有限公司 * 王春媛 北京泊邻美寓住房租赁有限公司 * 范金辉 北京相寓住房租赁有限公司 * 于意然 北京爱玛家房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 王万漳 北京麦田房产经纪有限公司 ## 租房房产问答 * 问 现在年底租房子便宜不 * Kair： 您好，我是我爱我家钱立智，很荣幸为您服务，年底租房客户群体较少，市场属于买方市场，供大于求，房价相对要便宜一些，过了年很多外来人员都有租房需求，供求关系发生变化，价格会有所上涨，具体情况欢迎垂询，期待您的来电，买好房，找立志！；* 侯丽霞： 您好，看您在的小区，租房可以上租房周边的幼儿园。；* 于娟： 你好，地方不同，政策不同，需要看当地政策来决定 * 艾尼卡尔江·阿布都拉： 您好，租房是可以上您所租的房子周边的幼儿园的。；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：西北旺公寓出租条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486950500_1.htm) 4室2厅百旺茉莉园2期 整租|4室2厅|251㎡|朝南北 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。；12000 元/月 [](http://www.fang.com/chuzu/3_486625663_1.htm) 立水桥地铁 茉莉园精装主卧独卫 19平朝西 四家两卫 合租主卧|3户合租|19㎡|朝南 海淀-西北旺-茉莉园 距16号线西北旺站约349米。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>房屋质量/户型线索：住宅类房源部分提到：冷泉村住房的房源精装修、户型采光好、隔音好；；另有房东直租的大两居为2020年底新房，2020年8月完成精装，户型南北通透，小区安静不临街，有电梯，人车分流，环境优美，配套运动设施；；产业园区类房源装修维护好、物业管理到位；；生活便利线索：西北旺东路10号院（注意：部分搜索结果显示，该院区部分房源为产业园区类，380平整租月租金约3.31万元，另有周边相近区域住宅类租房如冷泉村住房，1室0厅1卫25平月租1800元，1室1厅1卫35平月租2200元，1室1厅1卫30平平房月租1800元）；；另有房东直租的大两居为2020年底新房，2020年8月完成精装，户型南北通透，小区安静不临街，有电梯，人车分流，环境优美，配套运动设施；；周边有商场、超市、菜市场、药店、幼儿园，临近地铁16号线西北旺站，通勤方便，可直达中关村、西二旗等互联网企业聚集地；</x:v>
       </x:c>
       <x:c r="O3" t="str">
-        <x:v>1. 西北旺房屋出租信息_北京海淀西北旺出租房源信息-58出租网 http://mob.58.com/zf/cz/cz-xibeiwang/
-2. 【北京租房网_北京租房信息|房屋出租】- 房天下 http://www.fang.com/houses/zf_252240bj/
-3. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-4. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://m.36kr.com/p/1721780568065
-5. 百度地图 https://map.baidu.com/mobile/webapp/search/search/qt=s&amp;wd=%E5%8C%97%E4%BA%AC%E5%8C%97%E4%BA%AC%E5%B8%82%E6%B5%B7%E6%B7%80%E5%8C%BA%E5%8C%97%E4%BA%AC%E5%B8%82%E6%B5%B7%E6%B7%80%E5%8C%BA%E8%A5%BF%E5%8C%97%E6%97%BA%E4%B8%9C%E8%B7%AF10%E5%8F%B7%E9%99%A2%E4%B8%9C%E5%8C%BA1%E5%8F%B7%E6%A5%BC/&amp;vt=map</x:v>
+        <x:v>1. https://m.58.com/bj/zhaozu/82376094584155x.shtml
+2. http://m.anjuke.com/ch/rent/4601519520099329-3/
+3. http://m.anjuke.com/bj/rent/4581070293050371-3/
+4. https://www.douban.com/group/topic/342059161/?_spm_id=MTMwMzEwNTQy
+5. http://m.anjuke.com/bj/rent/4543318725782531-3/
+6. 出租上地西二旗200平380平500平精装有班车 https://m.58.com/bj/zhaozu/82376094584155x.shtml
+7. 整租 西北旺 近地铁 0中介 隔音好 采光好 http://m.anjuke.com/ch/rent/4601519520099329-3/
+8. 整租 西北旺 近地铁 0中介 隔音好 采光好 http://m.anjuke.com/bj/rent/4601519520099329-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -354,40 +356,42 @@
         <x:v>北京市海淀区西北旺东路与软件园南街交叉路口往西约100米</x:v>
       </x:c>
       <x:c r="E4" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G4" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H4" t="n">
-        <x:v>7.2</x:v>
+        <x:v>5.8</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>顶级低密度豪宅社区，环境与物业极佳，但以大户型为主且租金门槛极高，适合高管改善。</x:v>
-      </x:c>
-      <x:c r="J4" t="str">
-        <x:v>026-04-06 | 1763万 | 97383元/㎡；026-03-04 | 1699万 | 85123元/㎡；026-02-04 | 1949万 | 83505元/㎡；3室2厅2卫丨190㎡丨南北丨低楼层丨 136300元/㎡；3室2厅2卫丨182㎡丨南北丨中楼层丨 137500元/㎡；000_ 元/m² 西山壹号院，小区价格98287元/㎡</x:v>
-      </x:c>
+        <x:v>豪宅定位，租金极高且多为大户型，临路房源有噪音风险，适合高预算且对空间有要求的租客。</x:v>
+      </x:c>
+      <x:c r="J4" t="str"/>
       <x:c r="K4" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **93727** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑1.51% 贷款计算器 * 二手房源 82套 * 最近成交 122套 * 楼栋总数 42栋 * 房屋总数 1000户 * 建筑类型 板楼 * 建筑年代 2011年建成 * 小区位置 圆明园西路药用植物园北侧地图 * 物业公司 北京高力国际物业服务有限公司 * 开发商 北京融创恒基地产有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 王福兴 评分：5.0 从业信息卡 百科 闪电回复 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 韩建宽 评分：4.9 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 层高3.4米精装南北三居有车位储藏室管家服务 3室2厅 200.81㎡**1860**万 * #### 西山壹号院北区4室2厅南北 4室2厅 201.36㎡**1890**万 * #### 西山壹号院南区层高3.4米视野好看房方便 3室2厅 200.81㎡**1799**万 * #### 新增西山壹号院下跃四居室钥匙房源功德寺 4室3厅 438.35㎡**3650**万 ### 西山壹号院成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 181.14㎡ | 2026-04-06 | 1763万 | 97383元/㎡ | 市场信息 | | 199.71㎡ | 2026-03-04 | 1699万 | 85123元/㎡ | 市场信息 | | 233.40㎡ | 2026-02-04 | 1949万 | 83505元/㎡ | 市场信息 | 查看全部成交 ### 西山壹号院价格走势 ### 西山壹号院房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 西山壹号院 海淀·马连洼**93728** 元/㎡ * #### 芳怡园 海淀·马连洼**69034** 元/㎡ * #### 五矿万科如园 海淀·马连洼**102964** 元/㎡ * #### 百旺新城景和园 海淀·西北旺**66305** 元/㎡ * #### 润千秋佳苑 海淀·马连洼**73885** 元/㎡ ### 相关资讯 * 小区资讯北京西山壹号院怎么样?；西山壹号院地址均价户型优势解读2021-09-22 * 小区资讯本月买房,你一定不能错过这份西山壹号院1月房价报告!；北京吉屋网提供北京西山壹号院二手房出售信息、西山壹号院二手房价格，包括��时更新北京西山壹号院二手房房源、价格走势、户型图、业主论坛、生活配套。；# 西山壹号院_北京西山壹号院小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_西山壹号院 更新于 2026-06-01 10:46:26 [](https://bj.jiwu.com/tu/11888128.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888129.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888130.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888131.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888132.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888133.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888134.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888135.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888136.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888137.html "西山壹号院实景图图片") # 西山壹号院 别名：西山壹号院 加入本地买房群 关注 _北京 - 海淀 - 海淀圆明园西路药用植物园北侧_ 发地址到手机 参考均价 _98287 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2011_ 小区户数 _1052户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-55群（346） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？</x:v>
+        <x:v>3室2厅月租约21000-25000元，4室2厅月租约25000-42000元，户型面积多为181㎡及以上的大户型；；2011年建成，房龄约15年；；装修多为精装修；；房屋品质较高，外立面采用德国进口莱姆石；；部分临近永丰路楼栋有噪音影响（隔音问题）；</x:v>
       </x:c>
       <x:c r="L4" t="str">
-        <x:v>北京吉屋网提供北京西山壹号院二手房出售信息、西山壹号院二手房价格，包括��时更新北京西山壹号院二手房房源、价格走势、户型图、业主论坛、生活配套。；# 西山壹号院_北京西山壹号院小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_西山壹号院 更新于 2026-06-01 10:46:26 [](https://bj.jiwu.com/tu/11888128.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888129.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888130.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888131.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888132.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888133.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888134.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888135.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888136.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888137.html "西山壹号院实景图图片") # 西山壹号院 别名：西山壹号院 加入本地买房群 关注 _北京 - 海淀 - 海淀圆明园西路药用植物园北侧_ 发地址到手机 参考均价 _98287 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2011_ 小区户数 _1052户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-55群（346） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；加入群聊 二手房源全部房源 * [](https://bj.jiwu.com/esf/37333136.html "南北观山三居， 南北大间距、精装修、近地铁看房随时")南北观山三居， 南北大间距、精装修、近地铁看房随时 2590万 3室2厅2卫丨190㎡丨南北丨低楼层丨 136300元/㎡ 西山壹号院 | 海淀 - 西北旺 | 2011年建 * [](https://bj.jiwu.com/esf/37333137.html "西山壹号院 南区精装三居 带车位 诚意出售 可拎包入住")西山壹号院 南区精装三居 带车位 诚意出售 可拎包入住 2500万 3室2厅2卫丨182㎡丨南北丨中楼层丨 137500元/㎡ 西山壹号院 | 海淀 - 西北旺 | 2011年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 3室(4) 全部户型 [](https://bj.jiwu.com/huxing/969549.html "西山壹号院3室2厅2卫180㎡户型图")3室2厅2卫 180㎡咨询户型房源 [](https://bj.jiwu.com/huxing/969551.html "西山壹号院3室2厅3卫199㎡户型图")3室2厅3卫 199㎡咨询户型房源 [](https://bj.jiwu.com/huxing/969553.html "西山壹号院3室3厅2卫235㎡户型图")3室3厅2卫 235㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；答 西山壹号院的容积率1.5，绿化率45.0，环境优雅，非常适宜居住生活。</x:v>
+        <x:v>地铁16号线马连洼站步行约866-1200米；；公交便利，周边有多个公交站；；商业配套不够成熟，日常购物稍不便；；小区内有会所（含游泳、健身）、儿童游乐区等配套；；餐饮方面小区内部或周边有一定资源；</x:v>
       </x:c>
       <x:c r="M4" t="str">
-        <x:v>如果遇到停车难的问题，也有西山壹号院的物业快速协调。</x:v>
+        <x:v>部分临近永丰路楼栋有噪音影响（隔音问题）；；部分临近永丰路楼栋有噪音（隔音不足）；</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>价格线索：026-04-06 | 1763万 | 97383元/㎡；026-03-04 | 1699万 | 85123元/㎡；026-02-04 | 1949万 | 83505元/㎡；3室2厅2卫丨190㎡丨南北丨低楼层丨 136300元/㎡；3室2厅2卫丨182㎡丨南北丨中楼层丨 137500元/㎡；000_ 元/m² 西山壹号院，小区价格98287元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **93727** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑1.51% 贷款计算器 * 二手房源 82套 * 最近成交 122套 * 楼栋总数 42栋 * 房屋总数 1000户 * 建筑类型 板楼 * 建筑年代 2011年建成 * 小区位置 圆明园西路药用植物园北侧地图 * 物业公司 北京高力国际物业服务有限公司 * 开发商 北京融创恒基地产有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 王福兴 评分：5.0 从业信息卡 百科 闪电回复 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 韩建宽 评分：4.9 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 层高3.4米精装南北三居有车位储藏室管家服务 3室2厅 200.81㎡**1860**万 * #### 西山壹号院北区4室2厅南北 4室2厅 201.36㎡**1890**万 * #### 西山壹号院南区层高3.4米视野好看房方便 3室2厅 200.81㎡**1799**万 * #### 新增西山壹号院下跃四居室钥匙房源功德寺 4室3厅 438.35㎡**3650**万 ### 西山壹号院成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 181.14㎡ | 2026-04-06 | 1763万 | 97383元/㎡ | 市场信息 | | 199.71㎡ | 2026-03-04 | 1699万 | 85123元/㎡ | 市场信息 | | 233.40㎡ | 2026-02-04 | 1949万 | 83505元/㎡ | 市场信息 | 查看全部成交 ### 西山壹号院价格走势 ### 西山壹号院房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 西山壹号院 海淀·马连洼**93728** 元/㎡ * #### 芳怡园 海淀·马连洼**69034** 元/㎡ * #### 五矿万科如园 海淀·马连洼**102964** 元/㎡ * #### 百旺新城景和园 海淀·西北旺**66305** 元/㎡ * #### 润千秋佳苑 海淀·马连洼**73885** 元/㎡ ### 相关资讯 * 小区资讯北京西山壹号院怎么样?；西山壹号院地址均价户型优势解读2021-09-22 * 小区资讯本月买房,你一定不能错过这份西山壹号院1月房价报告!；北京吉屋网提供北京西山壹号院二手房出售信息、西山壹号院二手房价格，包括��时更新北京西山壹号院二手房房源、价格走势、户型图、业主论坛、生活配套。；# 西山壹号院_北京西山壹号院小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_西山壹号院 更新于 2026-06-01 10:46:26 [](https://bj.jiwu.com/tu/11888128.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888129.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888130.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888131.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888132.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888133.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888134.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888135.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888136.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888137.html "西山壹号院实景图图片") # 西山壹号院 别名：西山壹号院 加入本地买房群 关注 _北京 - 海淀 - 海淀圆明园西路药用植物园北侧_ 发地址到手机 参考均价 _98287 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2011_ 小区户数 _1052户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-55群（346） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；生活便利线索：北京吉屋网提供北京西山壹号院二手房出售信息、西山壹号院二手房价格，包括��时更新北京西山壹号院二手房房源、价格走势、户型图、业主论坛、生活配套。；# 西山壹号院_北京西山壹号院小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_西山壹号院 更新于 2026-06-01 10:46:26 [](https://bj.jiwu.com/tu/11888128.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888129.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888130.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888131.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888132.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888133.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888134.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888135.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888136.html "西山壹号院实景图图片")[](https://bj.jiwu.com/tu/11888137.html "西山壹号院实景图图片") # 西山壹号院 别名：西山壹号院 加入本地买房群 关注 _北京 - 海淀 - 海淀圆明园西路药用植物园北侧_ 发地址到手机 参考均价 _98287 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2011_ 小区户数 _1052户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-55群（346） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；加入群聊 二手房源全部房源 * [](https://bj.jiwu.com/esf/37333136.html "南北观山三居， 南北大间距、精装修、近地铁看房随时")南北观山三居， 南北大间距、精装修、近地铁看房随时 2590万 3室2厅2卫丨190㎡丨南北丨低楼层丨 136300元/㎡ 西山壹号院 | 海淀 - 西北旺 | 2011年建 * [](https://bj.jiwu.com/esf/37333137.html "西山壹号院 南区精装三居 带车位 诚意出售 可拎包入住")西山壹号院 南区精装三居 带车位 诚意出售 可拎包入住 2500万 3室2厅2卫丨182㎡丨南北丨中楼层丨 137500元/㎡ 西山壹号院 | 海淀 - 西北旺 | 2011年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 3室(4) 全部户型 [](https://bj.jiwu.com/huxing/969549.html "西山壹号院3室2厅2卫180㎡户型图")3室2厅2卫 180㎡咨询户型房源 [](https://bj.jiwu.com/huxing/969551.html "西山壹号院3室2厅3卫199㎡户型图")3室2厅3卫 199㎡咨询户型房源 [](https://bj.jiwu.com/huxing/969553.html "西山壹号院3室3厅2卫235㎡户型图")3室3厅2卫 235㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；答 西山壹号院的容积率1.5，绿化率45.0，环境优雅，非常适宜居住生活。；风险线索：如果遇到停车难的问题，也有西山壹号院的物业快速协调。</x:v>
+        <x:v>房屋质量/户型线索：3室2厅月租约21000-25000元，4室2厅月租约25000-42000元，户型面积多为181㎡及以上的大户型；；2011年建成，房龄约15年；；装修多为精装修；；房屋品质较高，外立面采用德国进口莱姆石；；部分临近永丰路楼栋有噪音影响（隔音问题）；；生活便利线索：地铁16号线马连洼站步行约866-1200米；；公交便利，周边有多个公交站；；商业配套不够成熟，日常购物稍不便；；小区内有会所（含游泳、健身）、儿童游乐区等配套；；餐饮方面小区内部或周边有一定资源；；风险线索：部分临近永丰路楼栋有噪音影响（隔音问题）；；部分临近永丰路楼栋有噪音（隔音不足）；</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>1. 【北京西山壹号院小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010682751.htm
-2. 西山壹号院_北京西山壹号院小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/55020.html
-3. 西北旺西山壹号院(北区)附近租合租房子,西北旺附近租房价格,三室两厅合租-北京58同城 http://mob.58.com/zfxq/bj-sy100511126/fujinchuzu/
-4. 解读西山壹号院热销之谜 https://m.bjnews.com.cn/detail/155145396414637.html</x:v>
+        <x:v>1. https://mob.58.com/esfxq/bj-s2190846/ceping/
+2. http://m.anjuke.com/bj/community/342443/jiedu/
+3. https://m.anjuke.com/bj/fednr/342443/gonglue?is_title_transparent=1
+4. 西山壹号院(北区) https://mob.58.com/esfxq/bj-s2190846/ceping/
+5. 重庆华岩新城通勤痛点终结者？幸福·西山壹号院真实测评 https://m.fang.com/note/cq_2441629.html
+6. 西山壹号院(南区)优点、不足，西山壹号院(南区)怎么样，西山壹号院(南区)周边房产中介经纪人评价-北京安居客 http://m.anjuke.com/bj/community/342443/jiedu/
+7. 西山壹号院(南区) https://m.anjuke.com/bj/fednr/342443/gonglue?is_title_transparent=1
+8. 重庆西区买房避坑指南：幸福·西山壹号院竟是双面人？ https://m.fang.com/note/cq_2441630.html</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -404,41 +408,40 @@
         <x:v>海淀区圆明园西路药用植物园北侧</x:v>
       </x:c>
       <x:c r="E5" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G5" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H5" t="n">
-        <x:v>7</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="I5" t="str">
-        <x:v>高端改善型社区北区，品质卓越且靠近地铁，但房源多为大户型，普通员工租住压力大。</x:v>
-      </x:c>
-      <x:c r="J5" t="str">
-        <x:v>026-04-06 | 1763万 | 97383元/㎡；026-03-04 | 1699万 | 85123元/㎡；026-02-04 | 1949万 | 83505元/㎡；2厅二手房 199.19㎡ 2700万 135549元/㎡；2厅二手房 181.84㎡ 2399万 131930元/㎡；3室2厅2卫丨190㎡丨南北丨低楼层丨 136300元/㎡；3室2厅2卫丨182㎡丨南北丨中楼层丨 137500元/㎡；000_ 元/m² 西山壹号院，小区价格98287元/㎡</x:v>
-      </x:c>
+        <x:v>豪华大户型为主，租金昂贵且距离地铁较远，生活配套尚可，性价比对普通员工而言较低。</x:v>
+      </x:c>
+      <x:c r="J5" t="str"/>
       <x:c r="K5" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **93727** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑1.51% 贷款计算器 * 二手房源 82套 * 最近成交 122套 * 楼栋总数 42栋 * 房屋总数 1000户 * 建筑类型 板楼 * 建筑年代 2011年建成 * 小区位置 圆明园西路药用植物园北侧地图 * 物业公司 北京高力国际物业服务有限公司 * 开发商 北京融创恒基地产有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 王福兴 评分：5.0 从业信息卡 百科 闪电回复 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 韩建宽 评分：4.9 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 层高3.4米精装南北三居有车位储藏室管家服务 3室2厅 200.81㎡**1860**万 * #### 西山壹号院北区4室2厅南北 4室2厅 201.36㎡**1890**万 * #### 西山壹号院南区层高3.4米视野好看房方便 3室2厅 200.81㎡**1799**万 * #### 新增西山壹号院下跃四居室钥匙房源功德寺 4室3厅 438.35㎡**3650**万 ### 西山壹号院成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 181.14㎡ | 2026-04-06 | 1763万 | 97383元/㎡ | 市场信息 | | 199.71㎡ | 2026-03-04 | 1699万 | 85123元/㎡ | 市场信息 | | 233.40㎡ | 2026-02-04 | 1949万 | 83505元/㎡ | 市场信息 | 查看全部成交 ### 西山壹号院价格走势 ### 西山壹号院房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 西山壹号院 海淀·马连洼**93728** 元/㎡ * #### 芳怡园 海淀·马连洼**69034** 元/㎡ * #### 五矿万科如园 海淀·马连洼**102964** 元/㎡ * #### 百旺新城景和园 海淀·西北旺**66305** 元/㎡ * #### 润千秋佳苑 海淀·马连洼**73885** 元/㎡ ### 相关资讯 * 小区资讯北京西山壹号院怎么样?；西山壹号院地址均价户型优势解读2021-09-22 * 小区资讯本月买房,你一定不能错过这份西山壹号院1月房价报告!；北京西山壹号院南区房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下西山壹号院南区房价、房源、户型、环境、交通等周边配套的相关问题！</x:v>
+        <x:v>豪华装修房源价格更高，如398平米精装4居月租40000元。；房龄约2011年建成；；物业为天津融创物业管理有限公司北京分公司（或高力国际，需注意信息差异）；；户型为板楼南北通透；；装修多为豪华装修或普通装修；</x:v>
       </x:c>
       <x:c r="L5" t="str">
-        <x:v>北京西山壹号院南区房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下西山壹号院南区房价、房源、户型、环境、交通等周边配套的相关问题！；### 西山壹号院南区交通状况如何？；专143路 西山壹号院南区附近地铁：地铁16号线 ### 西山壹号院南区周边配套 **幼儿园：**海淀区海育幼儿园、西山为明幼儿园、海淀区小星星双语艺术幼儿园、亿城蓝天幼儿园、北京红缨幼儿园(马连洼北路)、北京明耀国际幼儿园、儿童之家潜能开发课程实验幼儿园 **中小学：**中关村第二小学(百旺校区)、中关村第二小学(西山分校) **大学：**中国农业大学(西校区)、中国医学科学院北京协和医学院(北区)、中国农业大学西校区和园 **商场：**西北旺万象汇、中发百旺商城 **医院：**北京大学第三医院(海淀北部院区)、马连洼社区卫生服务中心、东北旺中心卫生院、中国农业大学西区社区卫生服务中心、海淀区青龙桥社区卫生服务中心兰园社区卫生服务站、海淀区青龙桥社区卫生服务中心兰园社区卫生服务站、联想总部社区卫生服务站、兰园社区卫生服务站中医馆、海淀区农大西区紫苑社区卫生服务站 **邮局：**邮件中心 **银行：**中国工商银行(马连洼支行)、中国工商银行(北京百旺新城支行)、中信银行(西山壹号院支行)、中国农业银行(北京西北旺支行)、北京银行(北京永丰支行)、招商银行(圆明园西路支行)、中国银行信息科技运营中心、中国农业银行(北京茉莉园支行)、北京银行(中关村软件园支行)、北京农商银行(百旺分理处) **其他：** ### 西山壹号院南区二手房源推荐 #### 推荐房源1：西山壹号院南区 3室2厅二手房 199.19㎡ 2700万 135549元/㎡ 新上房源 西山壹号院南区 南北通透三居 精装修自住。；房源|户型图|小区车位|交通地址详情分析！</x:v>
-      </x:c>
-      <x:c r="M5" t="str">
-        <x:v>如果遇到停车难的问题，也有西山壹号院的物业快速协调。</x:v>
-      </x:c>
+        <x:v>地铁：16、18号线马连洼站步行约1600米；；商超：周边有美廉美超市(百旺店)、中发百旺商城、超市发等；；医院：嘉和百旺医疗美容门诊部、马连洼社区卫生服务站等；；交通：临近圆明园西路，周边公交站较多；；餐饮：周边配套餐饮资源待明确（搜索结果未详细提及）。</x:v>
+      </x:c>
+      <x:c r="M5" t="str"/>
       <x:c r="N5" t="str">
-        <x:v>价格线索：026-04-06 | 1763万 | 97383元/㎡；026-03-04 | 1699万 | 85123元/㎡；026-02-04 | 1949万 | 83505元/㎡；2厅二手房 199.19㎡ 2700万 135549元/㎡；2厅二手房 181.84㎡ 2399万 131930元/㎡；3室2厅2卫丨190㎡丨南北丨低楼层丨 136300元/㎡；3室2厅2卫丨182㎡丨南北丨中楼层丨 137500元/㎡；000_ 元/m² 西山壹号院，小区价格98287元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **93727** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑1.51% 贷款计算器 * 二手房源 82套 * 最近成交 122套 * 楼栋总数 42栋 * 房屋总数 1000户 * 建筑类型 板楼 * 建筑年代 2011年建成 * 小区位置 圆明园西路药用植物园北侧地图 * 物业公司 北京高力国际物业服务有限公司 * 开发商 北京融创恒基地产有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 王福兴 评分：5.0 从业信息卡 百科 闪电回复 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 韩建宽 评分：4.9 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 层高3.4米精装南北三居有车位储藏室管家服务 3室2厅 200.81㎡**1860**万 * #### 西山壹号院北区4室2厅南北 4室2厅 201.36㎡**1890**万 * #### 西山壹号院南区层高3.4米视野好看房方便 3室2厅 200.81㎡**1799**万 * #### 新增西山壹号院下跃四居室钥匙房源功德寺 4室3厅 438.35㎡**3650**万 ### 西山壹号院成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 181.14㎡ | 2026-04-06 | 1763万 | 97383元/㎡ | 市场信息 | | 199.71㎡ | 2026-03-04 | 1699万 | 85123元/㎡ | 市场信息 | | 233.40㎡ | 2026-02-04 | 1949万 | 83505元/㎡ | 市场信息 | 查看全部成交 ### 西山壹号院价格走势 ### 西山壹号院房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 西山壹号院 海淀·马连洼**93728** 元/㎡ * #### 芳怡园 海淀·马连洼**69034** 元/㎡ * #### 五矿万科如园 海淀·马连洼**102964** 元/㎡ * #### 百旺新城景和园 海淀·西北旺**66305** 元/㎡ * #### 润千秋佳苑 海淀·马连洼**73885** 元/㎡ ### 相关资讯 * 小区资讯北京西山壹号院怎么样?；西山壹号院地址均价户型优势解读2021-09-22 * 小区资讯本月买房,你一定不能错过这份西山壹号院1月房价报告!；北京西山壹号院南区房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下西山壹号院南区房价、房源、户型、环境、交通等周边配套的相关问题！；生活便利线索：北京西山壹号院南区房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下西山壹号院南区房价、房源、户型、环境、交通等周边配套的相关问题！；### 西山壹号院南区交通状况如何？；专143路 西山壹号院南区附近地铁：地铁16号线 ### 西山壹号院南区周边配套 **幼儿园：**海淀区海育幼儿园、西山为明幼儿园、海淀区小星星双语艺术幼儿园、亿城蓝天幼儿园、北京红缨幼儿园(马连洼北路)、北京明耀国际幼儿园、儿童之家潜能开发课程实验幼儿园 **中小学：**中关村第二小学(百旺校区)、中关村第二小学(西山分校) **大学：**中国农业大学(西校区)、中国医学科学院北京协和医学院(北区)、中国农业大学西校区和园 **商场：**西北旺万象汇、中发百旺商城 **医院：**北京大学第三医院(海淀北部院区)、马连洼社区卫生服务中心、东北旺中心卫生院、中国农业大学西区社区卫生服务中心、海淀区青龙桥社区卫生服务中心兰园社区卫生服务站、海淀区青龙桥社区卫生服务中心兰园社区卫生服务站、联想总部社区卫生服务站、兰园社区卫生服务站中医馆、海淀区农大西区紫苑社区卫生服务站 **邮局：**邮件中心 **银行：**中国工商银行(马连洼支行)、中国工商银行(北京百旺新城支行)、中信银行(西山壹号院支行)、中国农业银行(北京西北旺支行)、北京银行(北京永丰支行)、招商银行(圆明园西路支行)、中国银行信息科技运营中心、中国农业银行(北京茉莉园支行)、北京银行(中关村软件园支行)、北京农商银行(百旺分理处) **其他：** ### 西山壹号院南区二手房源推荐 #### 推荐房源1：西山壹号院南区 3室2厅二手房 199.19㎡ 2700万 135549元/㎡ 新上房源 西山壹号院南区 南北通透三居 精装修自住。；房源|户型图|小区车位|交通地址详情分析！；风险线索：如果遇到停车难的问题，也有西山壹号院的物业快速协调。</x:v>
+        <x:v>房屋质量/户型线索：豪华装修房源价格更高，如398平米精装4居月租40000元。；房龄约2011年建成；；物业为天津融创物业管理有限公司北京分公司（或高力国际，需注意信息差异）；；户型为板楼南北通透；；装修多为豪华装修或普通装修；；生活便利线索：地铁：16、18号线马连洼站步行约1600米；；商超：周边有美廉美超市(百旺店)、中发百旺商城、超市发等；；医院：嘉和百旺医疗美容门诊部、马连洼社区卫生服务站等；；交通：临近圆明园西路，周边公交站较多；；餐饮：周边配套餐饮资源待明确（搜索结果未详细提及）。</x:v>
       </x:c>
       <x:c r="O5" t="str">
-        <x:v>1. 【北京西山壹号院小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010682751.htm
-2. 西山壹号院南区房价怎么样？ 北京西山壹号院南区房源|户型图|小区车位|交通地址详情分析 https://m.ke.com/news/bj/xiaoqu/1111041084751.html
-3. 西山壹号院_北京西山壹号院小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/55020.html
-4. 西北旺西山壹号院(北区)附近租合租房子,西北旺附近租房价格,三室两厅合租-北京58同城 https://bj.zf.58.com/zfxq/sy100511126/fujinchuzu/
-5. 解读西山壹号院热销之谜 https://m.bjnews.com.cn/detail/155145396414637.html</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4571521089985541-3/
+2. http://m.anjuke.com/bj/rent/4577025162372109-3/
+3. https://m.5i5j.com/bj/xq_news/239100.html
+4. https://m.jiwu.com/bj/xqjd/55020.html
+5. 西山壹号院北区精装4居4卫带车位出租看房有密码只租一家人长租 http://m.anjuke.com/bj/rent/4571521089985541-3/
+6. 南北通透 5室2厅 西山壹号院(北区) http://m.anjuke.com/bj/rent/4577025162372109-3/
+7. 西山壹号院怎么样?北京西山壹号院房价|房源|地址|户型图|周边配套详情 https://m.5i5j.com/bj/xq_news/239100.html
+8. 南北通透 4室2厅 西山壹号院(北区) http://m.anjuke.com/bj/rent/4569654266031113-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -455,37 +458,44 @@
         <x:v>北京市海淀区百草西路与神农路交叉口西北450米路北</x:v>
       </x:c>
       <x:c r="E6" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F6" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G6" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H6" t="n">
-        <x:v>7</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I6" t="str">
-        <x:v>南区物业管理水平极高，生活配套成熟，但租赁市场以高端整租为主，合租性价比低。</x:v>
+        <x:v>顶级豪宅社区，环境优美且紧邻软件园，但租金极高，仅适合高预算人群。</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>026-04-06 | 1763万 | 97383元/㎡；026-03-04 | 1699万 | 85123元/㎡；026-02-04 | 1949万 | 83505元/㎡；2厅二手房 199.19㎡ 2700万 135549元/㎡；2厅二手房 181.84㎡ 2399万 131930元/㎡</x:v>
+        <x:v>租房价格：整租3室2厅约18000元/月；，4室2厅约35000元/月；，5室2厅5卫约47000元/月；，5室3厅34000-60000元/月</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **93727** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑1.51% 贷款计算器 * 二手房源 82套 * 最近成交 122套 * 楼栋总数 42栋 * 房屋总数 1000户 * 建筑类型 板楼 * 建筑年代 2011年建成 * 小区位置 圆明园西路药用植物园北侧地图 * 物业公司 北京高力国际物业服务有限公司 * 开发商 北京融创恒基地产有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 王福兴 评分：5.0 从业信息卡 百科 闪电回复 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 韩建宽 评分：4.9 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 层高3.4米精装南北三居有车位储藏室管家服务 3室2厅 200.81㎡**1860**万 * #### 西山壹号院北区4室2厅南北 4室2厅 201.36㎡**1890**万 * #### 西山壹号院南区层高3.4米视野好看房方便 3室2厅 200.81㎡**1799**万 * #### 新增西山壹号院下跃四居室钥匙房源功德寺 4室3厅 438.35㎡**3650**万 ### 西山壹号院成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 181.14㎡ | 2026-04-06 | 1763万 | 97383元/㎡ | 市场信息 | | 199.71㎡ | 2026-03-04 | 1699万 | 85123元/㎡ | 市场信息 | | 233.40㎡ | 2026-02-04 | 1949万 | 83505元/㎡ | 市场信息 | 查看全部成交 ### 西山壹号院价格走势 ### 西山壹号院房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 西山壹号院 海淀·马连洼**93728** 元/㎡ * #### 芳怡园 海淀·马连洼**69034** 元/㎡ * #### 五矿万科如园 海淀·马连洼**102964** 元/㎡ * #### 百旺新城景和园 海淀·西北旺**66305** 元/㎡ * #### 润千秋佳苑 海淀·马连洼**73885** 元/㎡ ### 相关资讯 * 小区资讯北京西山壹号院怎么样?；西山壹号院地址均价户型优势解读2021-09-22 * 小区资讯本月买房,你一定不能错过这份西山壹号院1月房价报告!；北京西山壹号院南区房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下西山壹号院南区房价、房源、户型、环境、交通等周边配套的相关问题！</x:v>
+        <x:v>租房价格：整租3室2厅约18000元/月，4室2厅约35000元/月，5室2厅5卫约47000元/月，5室3厅34000-60000元/月不等，付款方式多为押一付三或押一付半年，部分房源包物业取暖费用。；房子质量：2011年建成，物业为天津融创物业管理有限公司北京分公司；；户型多为南北通透，以大平层为主（如3室、4室、5室），采光和通风较好；；装修有普通装修、精装修、豪华装修；；物业方面部分房源包物业，小区有低容积率、高绿化、安静舒适、有停车位的特点；</x:v>
       </x:c>
       <x:c r="L6" t="str">
-        <x:v>北京西山壹号院南区房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下西山壹号院南区房价、房源、户型、环境、交通等周边配套的相关问题！；### 西山壹号院南区交通状况如何？；专143路 西山壹号院南区附近地铁：地铁16号线 ### 西山壹号院南区周边配套 **幼儿园：**海淀区海育幼儿园、西山为明幼儿园、海淀区小星星双语艺术幼儿园、亿城蓝天幼儿园、北京红缨幼儿园(马连洼北路)、北京明耀国际幼儿园、儿童之家潜能开发课程实验幼儿园 **中小学：**中关村第二小学(百旺校区)、中关村第二小学(西山分校) **大学：**中国农业大学(西校区)、中国医学科学院北京协和医学院(北区)、中国农业大学西校区和园 **商场：**西北旺万象汇、中发百旺商城 **医院：**北京大学第三医院(海淀北部院区)、马连洼社区卫生服务中心、东北旺中心卫生院、中国农业大学西区社区卫生服务中心、海淀区青龙桥社区卫生服务中心兰园社区卫生服务站、海淀区青龙桥社区卫生服务中心兰园社区卫生服务站、联想总部社区卫生服务站、兰园社区卫生服务站中医馆、海淀区农大西区紫苑社区卫生服务站 **邮局：**邮件中心 **银行：**中国工商银行(马连洼支行)、中国工商银行(北京百旺新城支行)、中信银行(西山壹号院支行)、中国农业银行(北京西北旺支行)、北京银行(北京永丰支行)、招商银行(圆明园西路支行)、中国银行信息科技运营中心、中国农业银行(北京茉莉园支行)、北京银行(中关村软件园支行)、北京农商银行(百旺分理处) **其他：** ### 西山壹号院南区二手房源推荐 #### 推荐房源1：西山壹号院南区 3室2厅二手房 199.19㎡ 2700万 135549元/㎡ 新上房源 西山壹号院南区 南北通透三居 精装修自住。；房源|户型图|小区车位|交通地址详情分析！</x:v>
-      </x:c>
-      <x:c r="M6" t="str"/>
+        <x:v>生活便利程度：距离16号线马连洼站约1662-1851米，18号线马连洼站等；；周边有西北旺万象汇（约1298米）、中发百旺商城，世纪华联超市等商超；；餐饮配套未详细提及，通勤依赖地铁，距离软件园较近（如百度科技园约761米）。</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>未发现其他明确租房差评风险。</x:v>
+      </x:c>
       <x:c r="N6" t="str">
-        <x:v>价格线索：026-04-06 | 1763万 | 97383元/㎡；026-03-04 | 1699万 | 85123元/㎡；026-02-04 | 1949万 | 83505元/㎡；2厅二手房 199.19㎡ 2700万 135549元/㎡；2厅二手房 181.84㎡ 2399万 131930元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) [](https://esf.fang.com/loupan/1010682751/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **93727** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑1.51% 贷款计算器 * 二手房源 82套 * 最近成交 122套 * 楼栋总数 42栋 * 房屋总数 1000户 * 建筑类型 板楼 * 建筑年代 2011年建成 * 小区位置 圆明园西路药用植物园北侧地图 * 物业公司 北京高力国际物业服务有限公司 * 开发商 北京融创恒基地产有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 王福兴 评分：5.0 从业信息卡 百科 闪电回复 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 韩建宽 评分：4.9 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 层高3.4米精装南北三居有车位储藏室管家服务 3室2厅 200.81㎡**1860**万 * #### 西山壹号院北区4室2厅南北 4室2厅 201.36㎡**1890**万 * #### 西山壹号院南区层高3.4米视野好看房方便 3室2厅 200.81㎡**1799**万 * #### 新增西山壹号院下跃四居室钥匙房源功德寺 4室3厅 438.35㎡**3650**万 ### 西山壹号院成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 181.14㎡ | 2026-04-06 | 1763万 | 97383元/㎡ | 市场信息 | | 199.71㎡ | 2026-03-04 | 1699万 | 85123元/㎡ | 市场信息 | | 233.40㎡ | 2026-02-04 | 1949万 | 83505元/㎡ | 市场信息 | 查看全部成交 ### 西山壹号院价格走势 ### 西山壹号院房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 西山壹号院 海淀·马连洼**93728** 元/㎡ * #### 芳怡园 海淀·马连洼**69034** 元/㎡ * #### 五矿万科如园 海淀·马连洼**102964** 元/㎡ * #### 百旺新城景和园 海淀·西北旺**66305** 元/㎡ * #### 润千秋佳苑 海淀·马连洼**73885** 元/㎡ ### 相关资讯 * 小区资讯北京西山壹号院怎么样?；西山壹号院地址均价户型优势解读2021-09-22 * 小区资讯本月买房,你一定不能错过这份西山壹号院1月房价报告!；北京西山壹号院南区房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下西山壹号院南区房价、房源、户型、环境、交通等周边配套的相关问题！；生活便利线索：北京西山壹号院南区房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下西山壹号院南区房价、房源、户型、环境、交通等周边配套的相关问题！；### 西山壹号院南区交通状况如何？；专143路 西山壹号院南区附近地铁：地铁16号线 ### 西山壹号院南区周边配套 **幼儿园：**海淀区海育幼儿园、西山为明幼儿园、海淀区小星星双语艺术幼儿园、亿城蓝天幼儿园、北京红缨幼儿园(马连洼北路)、北京明耀国际幼儿园、儿童之家潜能开发课程实验幼儿园 **中小学：**中关村第二小学(百旺校区)、中关村第二小学(西山分校) **大学：**中国农业大学(西校区)、中国医学科学院北京协和医学院(北区)、中国农业大学西校区和园 **商场：**西北旺万象汇、中发百旺商城 **医院：**北京大学第三医院(海淀北部院区)、马连洼社区卫生服务中心、东北旺中心卫生院、中国农业大学西区社区卫生服务中心、海淀区青龙桥社区卫生服务中心兰园社区卫生服务站、海淀区青龙桥社区卫生服务中心兰园社区卫生服务站、联想总部社区卫生服务站、兰园社区卫生服务站中医馆、海淀区农大西区紫苑社区卫生服务站 **邮局：**邮件中心 **银行：**中国工商银行(马连洼支行)、中国工商银行(北京百旺新城支行)、中信银行(西山壹号院支行)、中国农业银行(北京西北旺支行)、北京银行(北京永丰支行)、招商银行(圆明园西路支行)、中国银行信息科技运营中心、中国农业银行(北京茉莉园支行)、北京银行(中关村软件园支行)、北京农商银行(百旺分理处) **其他：** ### 西山壹号院南区二手房源推荐 #### 推荐房源1：西山壹号院南区 3室2厅二手房 199.19㎡ 2700万 135549元/㎡ 新上房源 西山壹号院南区 南北通透三居 精装修自住。；房源|户型图|小区车位|交通地址详情分析！</x:v>
+        <x:v>价格线索：租房价格：整租3室2厅约18000元/月；，4室2厅约35000元/月；，5室2厅5卫约47000元/月；，5室3厅34000-60000元/月；房屋质量/户型线索：租房价格：整租3室2厅约18000元/月，4室2厅约35000元/月，5室2厅5卫约47000元/月，5室3厅34000-60000元/月不等，付款方式多为押一付三或押一付半年，部分房源包物业取暖费用。；房子质量：2011年建成，物业为天津融创物业管理有限公司北京分公司；；户型多为南北通透，以大平层为主（如3室、4室、5室），采光和通风较好；；装修有普通装修、精装修、豪华装修；；物业方面部分房源包物业，小区有低容积率、高绿化、安静舒适、有停车位的特点；；生活便利线索：生活便利程度：距离16号线马连洼站约1662-1851米，18号线马连洼站等；；周边有西北旺万象汇（约1298米）、中发百旺商城，世纪华联超市等商超；；餐饮配套未详细提及，通勤依赖地铁，距离软件园较近（如百度科技园约761米）。；风险线索：未发现其他明确租房差评风险。</x:v>
       </x:c>
       <x:c r="O6" t="str">
-        <x:v>1. 【北京西山壹号院小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010682751.htm
-2. 西山壹号院南区房价怎么样？ 北京西山壹号院南区房源|户型图|小区车位|交通地址详情分析 https://m.ke.com/news/bj/xiaoqu/1111041084751.html
-3. 西北旺西山壹号院(北区)附近租合租房子,西北旺附近租房价格,三室两厅合租-北京58同城 https://bj.zf.58.com/zfxq/sy100511126/fujinchuzu/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4590076421086209-3/
+2. http://m.anjuke.com/bj/rent/4578787107466241-3/
+3. https://bj.zu.anjuke.com/fangyuan/4142155694660618
+4. https://m.lianjia.com/news/cq/xiaoqu/1111041084751.html
+5. 南北通透 3室2厅 西山壹号院(南区) http://m.anjuke.com/bj/rent/4590076421086209-3/
+6. 豪宅 西山壹号院精装修大平层 看房随时 http://m.anjuke.com/bj/rent/4578787107466241-3/
+7. 【多图】西山壹号院(南区)，西北旺租房，西山壹号院 5室出租 业主直签 有车位 万象汇 地铁 软件园，海淀租房 https://bj.zu.anjuke.com/fangyuan/4142155694660618
+8. 我是房子跟单人~ 价格可谈 看房随时 西山壹号院(南区) http://m.anjuke.com/bj/rent/2796407096400907-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -502,41 +512,42 @@
         <x:v>北京市海淀区中关村软件园二期西北旺东路10号院东区</x:v>
       </x:c>
       <x:c r="E7" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G7" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H7" t="n">
-        <x:v>4</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="I7" t="str">
-        <x:v>网页证据存在明显的跨区域泛化错误，有效租赁信息匮乏且价格线索混乱，评分保守。</x:v>
+        <x:v>地理位置极佳且租金低廉，但具体房屋质量证据较模糊，建议实地考察风险。</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>12000 元/月；58000 元/月；80000 元/月；55000 元/月；65000 元/月；90000 元/月；85000 元/月；180000 元/月</x:v>
+        <x:v>甲店主卧）的1室1厅整租价格约2200-2800元/月；，合租主卧约1600元/月</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>长阳半岛2号院 这个小区主打两居室 三居室 一居室一般都在一层 是属于变异户型 套数比较少 目前在租的一居室没有 租金一般在4500左右 * 陈耀忠： 您好，长阳半岛2号院的租金基本在3800-55000元之间。；# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀租房价格条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486910069_1.htm) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 距12号线蓝靛厂站约379米。；75000 元/月 [](http://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；138000 元/月 [](http://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。</x:v>
+        <x:v>未找到西北旺东路10号院东区19的房子质量（隔音、户型、房龄、装修、物业）的相关详细评价，仅同区域提及部分房源为精装修，小区有保安24小时值班，部分房源提供免费维修服务，但不确定是否适用于该目标地址。</x:v>
       </x:c>
       <x:c r="L7" t="str">
-        <x:v>* 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * [](https://bj.zf.58.com/) * [](https://bj.zf.58.com/zz/xibeiwang/) * [](https://bj.zf.58.com/hz/xibeiwang/) * [](https://bj.zf.58.com/gr/xibeiwang/) * [](https://bj.58.com/pinpaigongyu/) * [](https://bj.58.com/xq/) * [](https://bj.zf.58.com/zujin/) * 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 ## 西北旺租房房产中介 * 张帅 北京相寓住房租赁有限公司 * 康涛 怡家（北京）住房租赁有限公司 * 李玲芳 北京正义东南房地产经纪有限公司 * 任琦 北京相寓住房租赁有限公司 * 陈永胜 北京德佑嘉业住房租赁有限公司 * 王春媛 北京泊邻美寓住房租赁有限公司 * 范金辉 北京相寓住房租赁有限公司 * 于意然 北京爱玛家房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 王万漳 北京麦田房产经纪有限公司 ## 租房房产问答 * 问 现在年底租房子便宜不 * Kair： 您好，我是我爱我家钱立智，很荣幸为您服务，年底租房客户群体较少，市场属于买方市场，供大于求，房价相对要便宜一些，过了年很多外来人员都有租房需求，供求关系发生变化，价格会有所上涨，具体情况欢迎垂询，期待您的来电，买好房，找立志！；* 侯丽霞： 您好，看您在的小区，租房可以上租房周边的幼儿园。；* 于娟： 你好，地方不同，政策不同，需要看当地政策来决定 * 艾尼卡尔江·阿布都拉： 您好，租房是可以上您所租的房子周边的幼儿园的。；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀租房价格条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486910069_1.htm) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 距12号线蓝靛厂站约379米。；交通便利南北通透 18000 元/月 [](http://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。</x:v>
-      </x:c>
-      <x:c r="M7" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>未直接获取西北旺东路10号院东区19的具体租房价格，同区域西北旺周边（如冷泉村住房、亮甲店主卧）的1室1厅整租价格约2200-2800元/月，合租主卧约1600元/月，该区域同类型房源价格大致参考此区间。；该地址位于中关村软件园二期周边，临近西北旺地铁站及公交站，周边有便利店、饭店等，办公生活配套较完善，属于西北旺西北旺东路周边的生活便利区域，但具体商超、医院等细节未明确。</x:v>
+      </x:c>
+      <x:c r="M7" t="str"/>
       <x:c r="N7" t="str">
-        <x:v>价格线索：12000 元/月；58000 元/月；80000 元/月；55000 元/月；65000 元/月；90000 元/月；85000 元/月；180000 元/月；房屋质量/户型线索：长阳半岛2号院 这个小区主打两居室 三居室 一居室一般都在一层 是属于变异户型 套数比较少 目前在租的一居室没有 租金一般在4500左右 * 陈耀忠： 您好，长阳半岛2号院的租金基本在3800-55000元之间。；# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀租房价格条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486910069_1.htm) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 距12号线蓝靛厂站约379米。；75000 元/月 [](http://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；138000 元/月 [](http://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；生活便利线索：* 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * [](https://bj.zf.58.com/) * [](https://bj.zf.58.com/zz/xibeiwang/) * [](https://bj.zf.58.com/hz/xibeiwang/) * [](https://bj.zf.58.com/gr/xibeiwang/) * [](https://bj.58.com/pinpaigongyu/) * [](https://bj.58.com/xq/) * [](https://bj.zf.58.com/zujin/) * 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 ## 西北旺租房房产中介 * 张帅 北京相寓住房租赁有限公司 * 康涛 怡家（北京）住房租赁有限公司 * 李玲芳 北京正义东南房地产经纪有限公司 * 任琦 北京相寓住房租赁有限公司 * 陈永胜 北京德佑嘉业住房租赁有限公司 * 王春媛 北京泊邻美寓住房租赁有限公司 * 范金辉 北京相寓住房租赁有限公司 * 于意然 北京爱玛家房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 王万漳 北京麦田房产经纪有限公司 ## 租房房产问答 * 问 现在年底租房子便宜不 * Kair： 您好，我是我爱我家钱立智，很荣幸为您服务，年底租房客户群体较少，市场属于买方市场，供大于求，房价相对要便宜一些，过了年很多外来人员都有租房需求，供求关系发生变化，价格会有所上涨，具体情况欢迎垂询，期待您的来电，买好房，找立志！；* 侯丽霞： 您好，看您在的小区，租房可以上租房周边的幼儿园。；* 于娟： 你好，地方不同，政策不同，需要看当地政策来决定 * 艾尼卡尔江·阿布都拉： 您好，租房是可以上您所租的房子周边的幼儿园的。；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀租房价格条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486910069_1.htm) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 距12号线蓝靛厂站约379米。；交通便利南北通透 18000 元/月 [](http://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：甲店主卧）的1室1厅整租价格约2200-2800元/月；，合租主卧约1600元/月；房屋质量/户型线索：未找到西北旺东路10号院东区19的房子质量（隔音、户型、房龄、装修、物业）的相关详细评价，仅同区域提及部分房源为精装修，小区有保安24小时值班，部分房源提供免费维修服务，但不确定是否适用于该目标地址。；生活便利线索：未直接获取西北旺东路10号院东区19的具体租房价格，同区域西北旺周边（如冷泉村住房、亮甲店主卧）的1室1厅整租价格约2200-2800元/月，合租主卧约1600元/月，该区域同类型房源价格大致参考此区间。；该地址位于中关村软件园二期周边，临近西北旺地铁站及公交站，周边有便利店、饭店等，办公生活配套较完善，属于西北旺西北旺东路周边的生活便利区域，但具体商超、医院等细节未明确。</x:v>
       </x:c>
       <x:c r="O7" t="str">
-        <x:v>1. 西北旺房屋出租信息_北京海淀西北旺出租房源信息-58出租网 https://bj.zf.58.com/cz/xibeiwang/
-2. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-3. 【北京租房网_北京租房信息|房屋出租】- 房天下 http://www.fang.com/houses/zf_254250bj/
-4. 百度地图 https://map.baidu.com/mobile/webapp/search/search/qt=s&amp;wd=%E5%8C%97%E4%BA%AC%E5%8C%97%E4%BA%AC%E5%B8%82%E6%B5%B7%E6%B7%80%E5%8C%BA%E5%8C%97%E4%BA%AC%E5%B8%82%E6%B5%B7%E6%B7%80%E5%8C%BA%E8%A5%BF%E5%8C%97%E6%97%BA%E4%B8%9C%E8%B7%AF10%E5%8F%B7%E9%99%A2%E4%B8%9C%E5%8C%BA1%E5%8F%B7%E6%A5%BC/&amp;vt=map
-5. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4542770423211022-3/
+2. https://m.58.com/bj/zhaozu/82376094584155x.shtml
+3. http://m.anjuke.com/dongyang/rent/4469160742611980-3/
+4. http://m.anjuke.com/bj/rent/4547064957854733-3/
+5. http://m.anjuke.com/ch/rent/4518818290377730-3/
+6. https://m.map.360.cn/site/detail/c1ecf709b622d2a3
+7. 近公交站 西北旺站 交通便利 户型方正 0中介费 干净采光好 http://m.anjuke.com/bj/rent/4542770423211022-3/
+8. 出租上地西二旗200平380平500平精装有班车 https://m.58.com/bj/zhaozu/82376094584155x.shtml</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -553,41 +564,44 @@
         <x:v>北京市海淀区东北旺中路199号附近</x:v>
       </x:c>
       <x:c r="E8" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F8" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G8" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H8" t="n">
-        <x:v>6.5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I8" t="str">
-        <x:v>地理位置优越的老旧家属院，租金相对亲民，但证据混杂了其他区域，居住品质上限较低。</x:v>
+        <x:v>租金适中且提及隔音良好，生活配套成熟，是性价比极高的务实通勤选择。</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>南北通透采光好独门独卫 18000 元/月；交通便利周边配套齐全装全配 70000 元/月；交通便利周边配套齐全装全配 130000 元/月；各庄-丽景嘉苑 交通便利独门独卫采光好 4500 元/月；各庄-丽景嘉苑 交通便利独门独卫采光好 3500 元/月；它-旭辉丽舍 交通便利周边配套齐采光好 2000 元/月；21500 元/月；可注册办公首次出租南北通透 6000 元/月</x:v>
+        <x:v>月租5200-6000元/月</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v># 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：东北旺租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_472516191_1.htm) 能容纳20多人的客厅。；可注册办公首次出租南北通透 6000 元/月 [](http://www.fang.com/chuzu/3_486941141_1.htm) 北洼西里2室1厅精装修 整租|2室1厅|77㎡|朝东南 海淀-紫竹桥-北洼西里 距6号线慈寿寺站约1043米。；首次出租南北通透 3600 元/月 [](http://www.fang.com/chuzu/3_486521908_1.htm) 宝星华庭 3室2卫2厅 142.5平精装修 2000 整租|3室2厅|142㎡|朝东西 朝阳-望京-宝星华庭 交通便利周边配套齐独门独卫 25000 元/月 [](http://www.fang.com/chuzu/3_486846916_1.htm) 南北通透星河湾5室2厅精装修 整租|5室2厅|268㎡|朝南北 朝阳-朝青-星河湾 距6号线青年路站约865米。；35000 元/月 [](http://www.fang.com/chuzu/3_486861582_1.htm) 南北通透星河湾5室2厅豪华装修 整租|5室2厅|346㎡|朝南北 朝阳-朝青-星河湾 距6号线青年路站约865米。</x:v>
+        <x:v>月租5200-6000元/月，户型多为2室1厅1卫，面积53-55平米，精装修，押一付三，中介费为一个月租金；；房龄约2001年；；装修为精装修；；有提到卧室隔音效果好；；物业相关未详细提及，但房源介绍中说小区治安好；</x:v>
       </x:c>
       <x:c r="L8" t="str">
-        <x:v>) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：东北旺租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_472516191_1.htm) 能容纳20多人的客厅。；交通便利周边配套齐全装全配 70000 元/月 [](http://www.fang.com/chuzu/3_468102180_1.htm) 东城 北京站 王府井东单精装独栋四合院会所出租带kt 整租|5室1厅|350㎡|朝南北 东城-东单-船板胡同 距2号线崇文门站约448米。；交通便利周边配套齐全装全配 130000 元/月 [](http://www.fang.com/chuzu/3_486654240_1.htm) 地铁7号线郎辛庄站 丽景嘉苑 二居88平4500元 整租|2室1厅|88㎡|朝南 朝阳-豆各庄-丽景嘉苑 交通便利独门独卫采光好 4500 元/月 [](http://www.fang.com/chuzu/3_486654223_1.htm) 地铁7号线郎辛庄站 丽景嘉苑 一居70平3500元 整租|1室1厅|70㎡|朝南 朝阳-豆各庄-丽景嘉苑 交通便利独门独卫采光好 3500 元/月 [](http://www.fang.com/chuzu/3_484703554_1.htm) 房东直租 通州宋庄 旭辉丽舍一居室出租 整租|1室1厅|51㎡|朝东北 通州-通州其它-旭辉丽舍 交通便利周边配套齐采光好 2000 元/月 [](http://www.fang.com/chuzu/3_486950500_1.htm) 4室2厅百旺茉莉园2期 整租|4室2厅|251㎡|朝南北 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。；21500 元/月 [](http://www.fang.com/chuzu/3_486875501_1.htm) 4号线西红门地铁 荟聚东兴海家园月苑 3室1厅 11 整租|3室1厅|112㎡|朝北 大兴-西红门-兴海家园月苑 距4号线大兴线西红门站约841米。；首次出租南北通透 4300 元/月 [](http://www.fang.com/chuzu/3_486905632_1.htm) 4号线西红门地铁整租·西红门荟聚宜家东侧 兴海家园日 整租|2室1厅|78㎡|朝南北 大兴-西红门-兴海家园日苑 距4号线大兴线西红门站约841米。</x:v>
+        <x:v>周边有超市、餐馆、医院，生活设施齐全；；交通出行方便，多路公交经过，适合通勤；</x:v>
       </x:c>
       <x:c r="M8" t="str">
-        <x:v>[](http://house.hexun.com/2020-07-04/201654129.html) 日本的“奇葩”婚俗，女性需要做到3件事 频 道 新闻股票基金黄金 外汇期货保险银行 理财债券互金评论 交 易 [](http://licaike.hexun.com/) 财经客户端 举报/投诉/意见反馈 - 联系我们 - 关于我们 - 广告服务 和讯网违法和不良信息/涉未成年人有害信息举报电话：010-65880240 客服电话：010-85650688 传真：010-85650844 邮箱：yhts#staff.hexun.com(发送时#改为@) 本站郑重声明：和讯网 北京和讯在线信息咨询服务有限公司所载文章、数据仅供参考，投资有风险，选择需谨慎。</x:v>
+        <x:v>未发现明确同名误命中或负面差评信息，暂未收集到风险相关内容。；未发现明确同名误命中或负面差评信息，暂未收集到风险相关内容</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>价格线索：南北通透采光好独门独卫 18000 元/月；交通便利周边配套齐全装全配 70000 元/月；交通便利周边配套齐全装全配 130000 元/月；各庄-丽景嘉苑 交通便利独门独卫采光好 4500 元/月；各庄-丽景嘉苑 交通便利独门独卫采光好 3500 元/月；它-旭辉丽舍 交通便利周边配套齐采光好 2000 元/月；21500 元/月；可注册办公首次出租南北通透 6000 元/月；房屋质量/户型线索：# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：东北旺租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_472516191_1.htm) 能容纳20多人的客厅。；可注册办公首次出租南北通透 6000 元/月 [](http://www.fang.com/chuzu/3_486941141_1.htm) 北洼西里2室1厅精装修 整租|2室1厅|77㎡|朝东南 海淀-紫竹桥-北洼西里 距6号线慈寿寺站约1043米。；首次出租南北通透 3600 元/月 [](http://www.fang.com/chuzu/3_486521908_1.htm) 宝星华庭 3室2卫2厅 142.5平精装修 2000 整租|3室2厅|142㎡|朝东西 朝阳-望京-宝星华庭 交通便利周边配套齐独门独卫 25000 元/月 [](http://www.fang.com/chuzu/3_486846916_1.htm) 南北通透星河湾5室2厅精装修 整租|5室2厅|268㎡|朝南北 朝阳-朝青-星河湾 距6号线青年路站约865米。；35000 元/月 [](http://www.fang.com/chuzu/3_486861582_1.htm) 南北通透星河湾5室2厅豪华装修 整租|5室2厅|346㎡|朝南北 朝阳-朝青-星河湾 距6号线青年路站约865米。；生活便利线索：) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：东北旺租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_472516191_1.htm) 能容纳20多人的客厅。；交通便利周边配套齐全装全配 70000 元/月 [](http://www.fang.com/chuzu/3_468102180_1.htm) 东城 北京站 王府井东单精装独栋四合院会所出租带kt 整租|5室1厅|350㎡|朝南北 东城-东单-船板胡同 距2号线崇文门站约448米。；交通便利周边配套齐全装全配 130000 元/月 [](http://www.fang.com/chuzu/3_486654240_1.htm) 地铁7号线郎辛庄站 丽景嘉苑 二居88平4500元 整租|2室1厅|88㎡|朝南 朝阳-豆各庄-丽景嘉苑 交通便利独门独卫采光好 4500 元/月 [](http://www.fang.com/chuzu/3_486654223_1.htm) 地铁7号线郎辛庄站 丽景嘉苑 一居70平3500元 整租|1室1厅|70㎡|朝南 朝阳-豆各庄-丽景嘉苑 交通便利独门独卫采光好 3500 元/月 [](http://www.fang.com/chuzu/3_484703554_1.htm) 房东直租 通州宋庄 旭辉丽舍一居室出租 整租|1室1厅|51㎡|朝东北 通州-通州其它-旭辉丽舍 交通便利周边配套齐采光好 2000 元/月 [](http://www.fang.com/chuzu/3_486950500_1.htm) 4室2厅百旺茉莉园2期 整租|4室2厅|251㎡|朝南北 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。；21500 元/月 [](http://www.fang.com/chuzu/3_486875501_1.htm) 4号线西红门地铁 荟聚东兴海家园月苑 3室1厅 11 整租|3室1厅|112㎡|朝北 大兴-西红门-兴海家园月苑 距4号线大兴线西红门站约841米。；首次出租南北通透 4300 元/月 [](http://www.fang.com/chuzu/3_486905632_1.htm) 4号线西红门地铁整租·西红门荟聚宜家东侧 兴海家园日 整租|2室1厅|78㎡|朝南北 大兴-西红门-兴海家园日苑 距4号线大兴线西红门站约841米。；风险线索：[](http://house.hexun.com/2020-07-04/201654129.html) 日本的“奇葩”婚俗，女性需要做到3件事 频 道 新闻股票基金黄金 外汇期货保险银行 理财债券互金评论 交 易 [](http://licaike.hexun.com/) 财经客户端 举报/投诉/意见反馈 - 联系我们 - 关于我们 - 广告服务 和讯网违法和不良信息/涉未成年人有害信息举报电话：010-65880240 客服电话：010-85650688 传真：010-85650844 邮箱：yhts#staff.hexun.com(发送时#改为@) 本站郑重声明：和讯网 北京和讯在线信息咨询服务有限公司所载文章、数据仅供参考，投资有风险，选择需谨慎。</x:v>
+        <x:v>价格线索：月租5200-6000元/月；房屋质量/户型线索：月租5200-6000元/月，户型多为2室1厅1卫，面积53-55平米，精装修，押一付三，中介费为一个月租金；；房龄约2001年；；装修为精装修；；有提到卧室隔音效果好；；物业相关未详细提及，但房源介绍中说小区治安好；；生活便利线索：周边有超市、餐馆、医院，生活设施齐全；；交通出行方便，多路公交经过，适合通勤；；风险线索：未发现明确同名误命中或负面差评信息，暂未收集到风险相关内容。；未发现明确同名误命中或负面差评信息，暂未收集到风险相关内容</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>1. 【北京租房网_北京租房信息|房屋出租】- 房天下 http://www.fang.com/houses/zf_253029bj/
-2. 西北旺房屋出租信息_北京海淀西北旺出租房源信息-58出租网 https://bj.zf.58.com/cz/xibeiwang/
-3.  https://www.ziroom.com/xiaoqu/1111040862977.html
-4. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-5. 深圳翻身二手房房价_深圳翻身二手房出售信息网-深圳中原找房 https://sz.centanet.com/ershoufang/fanshen/q7q32q5/</x:v>
+        <x:v>1. http://m.anjuke.com/dongyang/rent/4550389414126594-3/
+2. http://m.anjuke.com/bj/rent/4568773179550733-3/
+3. http://m.anjuke.com/ch/rent/4358919451012107-3/
+4. 东北旺 苗圃宿舍家属楼 精装两居 价格可谈 随时入住稳定长租 http://m.anjuke.com/dongyang/rent/4550389414126594-3/
+5. 东北旺 苗圃家属院 精装两居 跟业主签约 低楼层 配套全长租 http://m.anjuke.com/bj/rent/4568773179550733-3/
+6. 东北旺 苗圃家属楼 精装两居 跟业主签约 实房实图 配套全齐 http://m.anjuke.com/ch/rent/4358919451012107-3/
+7. 东北旺 苗圃家属院 南向两居 集中供暖 配置齐全 价格可谈 http://m.anjuke.com/ch/rent/4550051287131137-3/
+8. 东北旺 苗圃家属院 精装两居 实房实图 跟业主签约 稳定长租 http://m.anjuke.com/dongyang/rent/4561628593941510-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -604,37 +618,44 @@
         <x:v>北京市海淀区德馨路与西北旺二街交叉路口往西北约170米</x:v>
       </x:c>
       <x:c r="E9" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G9" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H9" t="n">
-        <x:v>9.2</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I9" t="str">
-        <x:v>紧邻网易及万象汇，租金适中且生活配套极佳，是软件园员工性价比极高的租住首选。</x:v>
+        <x:v>物业负责且居住氛围好，配套完善，虽租金稍高但综合居住品质较为理想。</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>1室1厅二手房 50.06㎡ 320万 63924元/㎡；1室1厅二手房 54.55㎡ 320万 58662元/㎡</x:v>
+        <x:v>合租次卧约2800-2860元/月；（15平左右），整租1室约6600元/月；，2室约8000元/月</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>北京芳怡园房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下芳怡园房价、房源、户型、环境、交通等周边配套的相关问题！；### 芳怡园小区简介 芳怡园于2000年建成建成；；这个户型只有拐弯单元有一户，户型并不多。；[](https://m.ke.com/bj/ershoufang/101131632491.html) 户型方正，正规一室一厅，布局合理，出入方便，比较实用，同户型小区只有8户。</x:v>
+        <x:v>房龄未明确，装修多为精装修，物业评价负责、小区安保完善；；未提及明显隔音问题，房屋保养较好，合住室友多为上班族/学生，整体居住氛围融洽；</x:v>
       </x:c>
       <x:c r="L9" t="str">
-        <x:v>* ### 西北旺万象汇 腾讯 百度科技园 联想总部 网易 芳怡园次卧 3室1厅 合租次卧 36天前 海淀 - 芳怡园 交通便利 周边配套齐 采光好 全装全配 _1800_ 元/月 * ### 网易腾讯 百度 软件园 让芳怡园 主卧阳台 可集中供暖 3室1厅 合租主卧 202天前 海淀 - 芳怡园 南北通透 采光好 周边配套齐 _2500_ 元/月 * ### 16号线西北旺 中关村软件园 万象汇 中发百旺 芳怡园一居室 1室1厅 整租 34天前 海淀 - 芳怡园 交通便利 周边配套齐 采光好 全装全配 _6500_ 元/月 * ### 16号线西北旺 百望山 中关村软件园 豆神教育 万象汇旁边 3室1厅 合租次卧 36天前 海淀 - 芳怡园 交通便利 周边配套齐 采光好 全装全配 _2000_ 元/月 * ### 软件园二期 芳怡园小区 开间 挨着 百度 网易 新浪 腾讯 1室1厅 整租 202天前 海淀 - 芳怡园 周边配套齐 交通便利 采光好 _5880_ 元/月 * 实时更新 ### 6月北京高性价比个人房源 尽在房天下APP 立即打开 * ### 西北旺 中关村软件园 快手万家灯火 百度腾讯网易 芳怡园开间 1室1厅 整租 5天前 海淀 - 芳怡园 交通便利 周边配套齐 采光好 独门独卫 _5000_ 元/月。；北京芳怡园房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下芳怡园房价、房源、户型、环境、交通等周边配套的相关问题！；### 芳怡园交通状况如何？；专143路 芳怡园附近地铁：地铁16号线 ### 芳怡园周边配套 **幼儿园：**海淀区海育幼儿园、北京本然森林幼儿园、北京市海淀区海育幼儿园(科学城北区分园)、西山为明幼儿园、海育幼儿园永靓分园、锦绣明天森林幼儿园、北京明耀国际幼儿园 **中小学：**中关村第二小学(百旺校区) **大学：**中国医学科学院北京协和医学院(北区) **商场：**西北旺万象汇 **医院：**北京大学第三医院(海淀北部院区)、北京市海淀区妇幼保健院(北部院区)、马连洼社区卫生服务中心、东北旺中心卫生院、联想总部社区卫生服务站、北京大学第三医院(海淀北部院区)-静脉用药调配中心 **邮局：**邮件中心、西北旺邮政支局揽投部 **银行：**中国工商银行(北京百旺新城支行)、中信银行(西山壹号院支行)、中国农业银行(北京西北旺支行)、北京银行(北京永丰支行)、中国银行信息科技运营中心、中国农业银行(北京茉莉园支行)、北京农商银行(百旺分理处)、中信银行24小时自助银行(西山壹号院支行)、中国农业银行24小时自助银行(北京茉莉园支行)、中国工商银行24小时自助银行服务(百旺新城支行) **其他：** ### 芳怡园二手房源推荐 #### 推荐房源1：芳怡园 1室1厅二手房 50.06㎡ 320万 63924元/㎡ 芳怡园中间层西向一居室 电梯直通车库 看房随时。</x:v>
-      </x:c>
-      <x:c r="M9" t="str"/>
+        <x:v>周边有商场、商超、餐饮，临近软件园等产业园；；小区绿化率高，停车便利，交通和生活配套较完善；</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>部分信息来自租房中介，未发现同名误命中情况，未明确大额风险差评，无相关负面记录。；部分信息来自租房中介，未发现同名误命中情况，未明确大额风险差评，无相关负面记录</x:v>
+      </x:c>
       <x:c r="N9" t="str">
-        <x:v>价格线索：1室1厅二手房 50.06㎡ 320万 63924元/㎡；1室1厅二手房 54.55㎡ 320万 58662元/㎡；房屋质量/户型线索：北京芳怡园房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下芳怡园房价、房源、户型、环境、交通等周边配套的相关问题！；### 芳怡园小区简介 芳怡园于2000年建成建成；；这个户型只有拐弯单元有一户，户型并不多。；[](https://m.ke.com/bj/ershoufang/101131632491.html) 户型方正，正规一室一厅，布局合理，出入方便，比较实用，同户型小区只有8户。；生活便利线索：* ### 西北旺万象汇 腾讯 百度科技园 联想总部 网易 芳怡园次卧 3室1厅 合租次卧 36天前 海淀 - 芳怡园 交通便利 周边配套齐 采光好 全装全配 _1800_ 元/月 * ### 网易腾讯 百度 软件园 让芳怡园 主卧阳台 可集中供暖 3室1厅 合租主卧 202天前 海淀 - 芳怡园 南北通透 采光好 周边配套齐 _2500_ 元/月 * ### 16号线西北旺 中关村软件园 万象汇 中发百旺 芳怡园一居室 1室1厅 整租 34天前 海淀 - 芳怡园 交通便利 周边配套齐 采光好 全装全配 _6500_ 元/月 * ### 16号线西北旺 百望山 中关村软件园 豆神教育 万象汇旁边 3室1厅 合租次卧 36天前 海淀 - 芳怡园 交通便利 周边配套齐 采光好 全装全配 _2000_ 元/月 * ### 软件园二期 芳怡园小区 开间 挨着 百度 网易 新浪 腾讯 1室1厅 整租 202天前 海淀 - 芳怡园 周边配套齐 交通便利 采光好 _5880_ 元/月 * 实时更新 ### 6月北京高性价比个人房源 尽在房天下APP 立即打开 * ### 西北旺 中关村软件园 快手万家灯火 百度腾讯网易 芳怡园开间 1室1厅 整租 5天前 海淀 - 芳怡园 交通便利 周边配套齐 采光好 独门独卫 _5000_ 元/月。；北京芳怡园房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下芳怡园房价、房源、户型、环境、交通等周边配套的相关问题！；### 芳怡园交通状况如何？；专143路 芳怡园附近地铁：地铁16号线 ### 芳怡园周边配套 **幼儿园：**海淀区海育幼儿园、北京本然森林幼儿园、北京市海淀区海育幼儿园(科学城北区分园)、西山为明幼儿园、海育幼儿园永靓分园、锦绣明天森林幼儿园、北京明耀国际幼儿园 **中小学：**中关村第二小学(百旺校区) **大学：**中国医学科学院北京协和医学院(北区) **商场：**西北旺万象汇 **医院：**北京大学第三医院(海淀北部院区)、北京市海淀区妇幼保健院(北部院区)、马连洼社区卫生服务中心、东北旺中心卫生院、联想总部社区卫生服务站、北京大学第三医院(海淀北部院区)-静脉用药调配中心 **邮局：**邮件中心、西北旺邮政支局揽投部 **银行：**中国工商银行(北京百旺新城支行)、中信银行(西山壹号院支行)、中国农业银行(北京西北旺支行)、北京银行(北京永丰支行)、中国银行信息科技运营中心、中国农业银行(北京茉莉园支行)、北京农商银行(百旺分理处)、中信银行24小时自助银行(西山壹号院支行)、中国农业银行24小时自助银行(北京茉莉园支行)、中国工商银行24小时自助银行服务(百旺新城支行) **其他：** ### 芳怡园二手房源推荐 #### 推荐房源1：芳怡园 1室1厅二手房 50.06㎡ 320万 63924元/㎡ 芳怡园中间层西向一居室 电梯直通车库 看房随时。</x:v>
+        <x:v>价格线索：合租次卧约2800-2860元/月；（15平左右），整租1室约6600元/月；，2室约8000元/月；房屋质量/户型线索：房龄未明确，装修多为精装修，物业评价负责、小区安保完善；；未提及明显隔音问题，房屋保养较好，合住室友多为上班族/学生，整体居住氛围融洽；；生活便利线索：周边有商场、商超、餐饮，临近软件园等产业园；；小区绿化率高，停车便利，交通和生活配套较完善；；风险线索：部分信息来自租房中介，未发现同名误命中情况，未明确大额风险差评，无相关负面记录。；部分信息来自租房中介，未发现同名误命中情况，未明确大额风险差评，无相关负面记录</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>1. 【芳怡园租房子_北京海淀芳怡园租房信息】北京手机房天下 https://m.fang.com/zf/bj_xm1010127929/
-2. 芳怡园房价怎么样？ 北京芳怡园房源|户型图|小区车位|交通地址详情分析 https://m.ke.com/news/bj/xiaoqu/11000000000539.html
-3. 芳怡园最新房价_北京海淀区-中国房价行情 https://m.creprice.cn/community/0211969194.html?city=bj</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4575704389934089-3/
+2. http://m.anjuke.com/bj/rent/4518997916949510-3/
+3. http://m.anjuke.com/bj/rent/4582779459132416-3/
+4. http://m.anjuke.com/bj/rent/4582796763098114-3/
+5. https://bj.zu.anjuke.com/fangyuan/3574616985148428
+6. http://m.anjuke.com/bj/rent/3811285970805773-3/
+7. 芳怡园朝南次卧全女生合租 男生想租也有同户型 软件园 万象汇 http://m.anjuke.com/bj/rent/4575704389934089-3/
+8. 芳怡园精装修朝南主卧临近中关村产业园西北旺地铁站度小满腾讯 http://m.anjuke.com/bj/rent/4518997916949510-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -651,39 +672,40 @@
         <x:v>北京市海淀区西二旗西路29号</x:v>
       </x:c>
       <x:c r="E10" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F10" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G10" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H10" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="I10" t="str">
-        <x:v>离网易极近，租金在西二旗区域较具性价比，户型选择多，生活配套成熟。</x:v>
+        <x:v>步行至西二旗站仅10分钟，通勤极便，生活配套成熟，但房龄偏老且车位管理混乱。</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>70000_ 元/m² 智学苑，小区价格51518元/㎡；三室 * 四室 * 四室以上 * 一室 5300元/月；+1.92% * 二室 6600元/月；-4.35% * 三室 11500元/月；+4.55% * 四室 21000元/月；+0.00% * 四室以上 36000元/月；小区名称 月租金 涨跌幅 * 1.智学苑5500元/月； 0.00% * 2.领秀新硅谷AB区5500元/月</x:v>
+        <x:v>1室1厅约5500元/月；，2室1厅约5700-7300元/月；，3室1厅约8700元/月；，142㎡三居两卫约9870元/月</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>北京吉屋网提供北京智学苑二手房出售信息、智学苑二手房价格，包括及时更新北京智学苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 智学苑_北京智学苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_智学苑 更新于 2026-06-01 10:52:22 [](https://bj.jiwu.com/tu/4228062.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228063.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228064.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228065.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228066.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228067.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228068.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228069.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228070.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228071.html "智学苑实景图图片") # 智学苑 别名：智学苑 加入本地买房群 关注 _北京 - 海淀 - 西二旗西路29号_ 发地址到手机 参考均价 _51518 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1848_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-27群（384） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(2)3室(3) 全部户型 [](https://bj.jiwu.com/huxing/677286.html "智学苑2室1厅1卫81㎡户型图")2室1厅1卫 81㎡咨询户型房源 [](https://bj.jiwu.com/huxing/677287.html "智学苑2室2厅2卫114㎡户型图")2室2厅2卫 114㎡咨询户型房源 [](https://bj.jiwu.com/huxing/677288.html "智学苑1室1厅1卫55㎡户型图")1室1厅1卫 55㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；而且智学苑的绿化率高，绿化覆盖面积大，环境十分舒适安静。</x:v>
+        <x:v>房龄1998年建成；；有加装隔音窗，夜晚噪音小，隔音效果较好；；户型南北通透，设计合理；；部分房源精装修，部分简单装修；；物业方面停车位混乱，固定车位被霸占，怨声载道；</x:v>
       </x:c>
       <x:c r="L10" t="str">
-        <x:v>北京吉屋网提供北京智学苑二手房出售信息、智学苑二手房价格，包括及时更新北京智学苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 智学苑_北京智学苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_智学苑 更新于 2026-06-01 10:52:22 [](https://bj.jiwu.com/tu/4228062.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228063.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228064.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228065.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228066.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228067.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228068.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228069.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228070.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228071.html "智学苑实景图图片") # 智学苑 别名：智学苑 加入本地买房群 关注 _北京 - 海淀 - 西二旗西路29号_ 发地址到手机 参考均价 _51518 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1848_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-27群（384） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(2)3室(3) 全部户型 [](https://bj.jiwu.com/huxing/677286.html "智学苑2室1厅1卫81㎡户型图")2室1厅1卫 81㎡咨询户型房源 [](https://bj.jiwu.com/huxing/677287.html "智学苑2室2厅2卫114㎡户型图")2室2厅2卫 114㎡咨询户型房源 [](https://bj.jiwu.com/huxing/677288.html "智学苑1室1厅1卫55㎡户型图")1室1厅1卫 55㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?</x:v>
+        <x:v>距离西二旗地铁站步行不到10分钟，昌平线、13号线等可达；；周边有超市发、711、便利蜂等商超，益民市场买菜方便；；周边饭馆多，生活气息浓厚；；距离小米、快手等企业较近，通勤便利；</x:v>
       </x:c>
       <x:c r="M10" t="str">
-        <x:v>手机版： 西二旗租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 云浮租房网 * 崇左租房网 * 保亭租房网 * 周口租房网 * 公主岭租房网 * 莱阳租房网 * 神木租房网 * 大理租房网 * 楚雄租房网 * 余姚租房网 * 北京周边租房网 * 大兴租房网 * 昌平租房网 * 西城租房网 * 朝阳租房网 * 海淀租房网 * 东城租房网 * 顺义租房网 * 门头沟租房网 * 平谷租房网 * 白广路租房网 * 百万庄租房网 * 白纸坊租房网 * 菜市口租房网 * 长椿街租房网 * 车公庄租房网 * 大栅栏租房网 * 德胜门租房网 * 地安门租房网 * 阜成门租房网 * 复兴门租房网 * 保定租房网 * 百善租房网 * 滨河路租房网 * 安定门租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * CBD租房网 * 磁各庄租房网 * 江门租房 * 长葛租房 * 醴陵租房 * 宣威租房 * 嘉善租房 * 江门出租 * 长葛出租 * 醴陵出租 * 宣威出租 * 嘉善出租 * 江门整租房 * 长葛整租房 * 醴陵整租房 * 宣威整租房 * 嘉善整租房 * 江门合租房 * 长葛合租房 * 醴陵合租房 * 宣威合租房 * 嘉善合租房 * 江门个人 * 长葛个人 * 醴陵个人 * 宣威个人 * 嘉善个人 * 北京周边租房 * 大兴租房 * 昌平租房 * 西城租房 * 朝阳租房 * 北京周边出租 * 大兴出租 * 昌平出租 * 西城出租 * 朝阳出租 * 北京周边整租房 * 大兴整租房 * 昌平整租房 * 西城整租房 * 朝阳整租房 * 北京周边合租房 * 大兴合租房 * 昌平合租房 * 西城合租房 * 朝阳合租房 * 北京一室一厅租房 * 北京一室两厅租房 * 北京四室两厅租房 * 北京简单装修租房 * 北京800元左右租房 * 北京25平米租房 * 北京50平米租房 * 北京60平米租房 * 北京110平米租房 * 北京130平米租房 * 北京160平米租房 * 北京复式租房 * 北京大平层租房 * 北京交通便利租房 * 北京新小区租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?</x:v>
+        <x:v>有加装隔音窗，夜晚噪音小，隔音效果较好；</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>价格线索：70000_ 元/m² 智学苑，小区价格51518元/㎡；三室 * 四室 * 四室以上 * 一室 5300元/月；+1.92% * 二室 6600元/月；-4.35% * 三室 11500元/月；+4.55% * 四室 21000元/月；+0.00% * 四室以上 36000元/月；小区名称 月租金 涨跌幅 * 1.智学苑5500元/月； 0.00% * 2.领秀新硅谷AB区5500元/月；房屋质量/户型线索：北京吉屋网提供北京智学苑二手房出售信息、智学苑二手房价格，包括及时更新北京智学苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 智学苑_北京智学苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_智学苑 更新于 2026-06-01 10:52:22 [](https://bj.jiwu.com/tu/4228062.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228063.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228064.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228065.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228066.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228067.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228068.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228069.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228070.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228071.html "智学苑实景图图片") # 智学苑 别名：智学苑 加入本地买房群 关注 _北京 - 海淀 - 西二旗西路29号_ 发地址到手机 参考均价 _51518 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1848_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-27群（384） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(2)3室(3) 全部户型 [](https://bj.jiwu.com/huxing/677286.html "智学苑2室1厅1卫81㎡户型图")2室1厅1卫 81㎡咨询户型房源 [](https://bj.jiwu.com/huxing/677287.html "智学苑2室2厅2卫114㎡户型图")2室2厅2卫 114㎡咨询户型房源 [](https://bj.jiwu.com/huxing/677288.html "智学苑1室1厅1卫55㎡户型图")1室1厅1卫 55㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；而且智学苑的绿化率高，绿化覆盖面积大，环境十分舒适安静。；生活便利线索：北京吉屋网提供北京智学苑二手房出售信息、智学苑二手房价格，包括及时更新北京智学苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 智学苑_北京智学苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_智学苑 更新于 2026-06-01 10:52:22 [](https://bj.jiwu.com/tu/4228062.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228063.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228064.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228065.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228066.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228067.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228068.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228069.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228070.html "智学苑实景图图片")[](https://bj.jiwu.com/tu/4228071.html "智学苑实景图图片") # 智学苑 别名：智学苑 加入本地买房群 关注 _北京 - 海淀 - 西二旗西路29号_ 发地址到手机 参考均价 _51518 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1848_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-27群（384） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(2)3室(3) 全部户型 [](https://bj.jiwu.com/huxing/677286.html "智学苑2室1厅1卫81㎡户型图")2室1厅1卫 81㎡咨询户型房源 [](https://bj.jiwu.com/huxing/677287.html "智学苑2室2厅2卫114㎡户型图")2室2厅2卫 114㎡咨询户型房源 [](https://bj.jiwu.com/huxing/677288.html "智学苑1室1厅1卫55㎡户型图")1室1厅1卫 55㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；风险线索：手机版： 西二旗租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 云浮租房网 * 崇左租房网 * 保亭租房网 * 周口租房网 * 公主岭租房网 * 莱阳租房网 * 神木租房网 * 大理租房网 * 楚雄租房网 * 余姚租房网 * 北京周边租房网 * 大兴租房网 * 昌平租房网 * 西城租房网 * 朝阳租房网 * 海淀租房网 * 东城租房网 * 顺义租房网 * 门头沟租房网 * 平谷租房网 * 白广路租房网 * 百万庄租房网 * 白纸坊租房网 * 菜市口租房网 * 长椿街租房网 * 车公庄租房网 * 大栅栏租房网 * 德胜门租房网 * 地安门租房网 * 阜成门租房网 * 复兴门租房网 * 保定租房网 * 百善租房网 * 滨河路租房网 * 安定门租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * CBD租房网 * 磁各庄租房网 * 江门租房 * 长葛租房 * 醴陵租房 * 宣威租房 * 嘉善租房 * 江门出租 * 长葛出租 * 醴陵出租 * 宣威出租 * 嘉善出租 * 江门整租房 * 长葛整租房 * 醴陵整租房 * 宣威整租房 * 嘉善整租房 * 江门合租房 * 长葛合租房 * 醴陵合租房 * 宣威合租房 * 嘉善合租房 * 江门个人 * 长葛个人 * 醴陵个人 * 宣威个人 * 嘉善个人 * 北京周边租房 * 大兴租房 * 昌平租房 * 西城租房 * 朝阳租房 * 北京周边出租 * 大兴出租 * 昌平出租 * 西城出租 * 朝阳出租 * 北京周边整租房 * 大兴整租房 * 昌平整租房 * 西城整租房 * 朝阳整租房 * 北京周边合租房 * 大兴合租房 * 昌平合租房 * 西城合租房 * 朝阳合租房 * 北京一室一厅租房 * 北京一室两厅租房 * 北京四室两厅租房 * 北京简单装修租房 * 北京800元左右租房 * 北京25平米租房 * 北京50平米租房 * 北京60平米租房 * 北京110平米租房 * 北京130平米租房 * 北京160平米租房 * 北京复式租房 * 北京大平层租房 * 北京交通便利租房 * 北京新小区租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：1室1厅约5500元/月；，2室1厅约5700-7300元/月；，3室1厅约8700元/月；，142㎡三居两卫约9870元/月；房屋质量/户型线索：房龄1998年建成；；有加装隔音窗，夜晚噪音小，隔音效果较好；；户型南北通透，设计合理；；部分房源精装修，部分简单装修；；物业方面停车位混乱，固定车位被霸占，怨声载道；；生活便利线索：距离西二旗地铁站步行不到10分钟，昌平线、13号线等可达；；周边有超市发、711、便利蜂等商超，益民市场买菜方便；；周边饭馆多，生活气息浓厚；；距离小米、快手等企业较近，通勤便利；；风险线索：有加装隔音窗，夜晚噪音小，隔音效果较好；</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>1. 智学苑_北京智学苑小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/166846.html
-2. 西二旗租房_北京海淀西二旗租房信息|西二旗租房价格信息-58租房网 http://mob.58.com/zf/bj-xierqi/
-3. 讨论精选（豆瓣） https://m.douban.com/group/hdzufang/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4606476587129860-3/
+2. https://m.xflapp.com/owner-comment-list/6587274137750733069
+3. 出租西二旗地铁小米快手附近智学苑小区一套142平米的三居两卫 http://m.anjuke.com/bj/rent/4606476587129860-3/
+4. 智学苑 海淀西二旗| 在售房源34套 63815 元/平 https://m.xflapp.com/owner-comment-list/6587274137750733069</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -700,40 +722,44 @@
         <x:v>北京市海淀区后厂村路66号</x:v>
       </x:c>
       <x:c r="E11" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G11" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H11" t="n">
-        <x:v>7.2</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="I11" t="str">
-        <x:v>配套齐全且交通便利，但涉及公租房性质，普通租赁房源需核实供应量。</x:v>
+        <x:v>房龄较新且居住密度适中，租金性价比高，配套完善，但部分楼栋无电梯且距地铁稍远。</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>【北京海淀区房屋出租5000-8000223元/月；# 【北京海淀区房屋出租5000-8000223元/月；* 关键字：海淀区房屋出租5000-8000223元/月；8500 元/月；-双泉嘉苑 周边配套齐独门独卫交通便利 8800 元/月；8900 元/月；交通便利周边配套齐全装全配 8930 元/月；9000 元/月</x:v>
+        <x:v>整租一居约5800元/月；、二居约6000元/月；、合租主卧约4240元/月</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v># 《燕保 ·汇鸿家园等 25 个公租房项 # 目情况简介》 目录 一、燕保 ·汇鸿家园 公租房项目基本情况介绍 ............................................................. 5 （一）基本信息 ................................................................................................. 5 （二）项目配套情况 ........................................................................................... 5 （三） 本次配租主要户型详细信息 ....................................................................... 6 二、熙悦尚郡公租房项目基本情况介绍 ....................................................................... 9 （一） 基本信息 ................................................................................................. 9 （二） 项目配套情况 ........................................................................................... 9 （三）本次配租主要户型详细信息 ..................................................................... 10 三、燕保 ·双桥家园 项目 基本情况介绍 ..................................................................... 11 （一）基本信息 ............................................................................................... 11 （二）项目配套情况 ........................................................................................ 11 （三）本次配租主要户型详细信息 ..................................................................... 12 四、怡景园项目基本情况介绍 .................................................................................. 14 （一） 基本信息 ............................................................................................... 14 （二） 项目配套情况 ........................................................................................ 14 （三） 本次配租主要户型详细信息 ..................................................................... 15 五、燕保 ·北焦家园项目基本情况介绍 ..................................................................... 17 （一）基本信息 ............................................................................................... 17 （二）项目配套情况 ........................................................................................ 17 （三） 本次配租主要户型详细信息 ................................................................... 18 六、燕保 ·常营家园 公租房项目基本情况介绍 ........................................................... 22 （一）基本信息 ............................................................................................... 22 （二）项目配套情况 ........................................................................................ 22 （三）户型详细信息 ........................................................................................ 23 七、管庄北二里 公租房项目基本情况介绍 ................................................................. 25 （一）基本信息 ............................................................................................... 25 （二）项目配套情况 ........................................................................................ 25 （三） 本次配租主要户型 详细信息 ..................................................................... 25 八、燕保 ·马泉营家园 项目基本情况 ........................................................................ 27 （一）基本信息 ............................................................................................... 27 （二）项目配套情况 ........................................................................................ 27 （三）本次配租主要户型 详细信息 ..................................................................... 28 九、瑞湾家园 项目基本情况 ..................................................................................... 31 （一）基本信息 ............................................................................................... 31 （二）项目配套情况 ........................................................................................ 31 （三）本次配租 主要户型详细信息 ..................................................................... 32 十、燕保 ·辛店家园 项目基本情况 ........................................................................... 33 （一）基本信息 ............................................................................................... 33 （二）项目配套情况 ........................................................................................ 33 （三）本次配租 主要户型详细信息 ..................................................................... 34 十一、燕保 ·温泉家园公租房项目情况简介 .............................................................. 35 （一）基本信息 ............................................................................................... 35 （二）项目配套情况 ........................................................................................ 35 （三）本次配租主要户型详细信息 ..................................................................... 36 十二、苏家坨 项目基本情况 ..................................................................................... 37 （一）基本信息 ............................................................................................... 37 （二）项目配套情况 ........................................................................................ 37 （三）本次配租 主要户型详细信息 ..................................................................... 38 十三、三嘉信苑 公租房项目基本情况介绍 ................................................................. 39 （一） 基本信息 ............................................................................................... 39 （二） 项目配套情况 ........................................................................................ 39 （三） 本次配租 主要 户型详细信息 ..................................................................... 40 十四、台湖银河湾（东区） 项目 基本情况 ................................................................. 41 （一）基本信息 ............................................................................................... 41 （二）项目配套情况 ........................................................................................ 41 （三）本次配租主要户型 详细信息 ..................................................................... 42 十五、台湖银河湾（西区） 项目 基本情况 ................................................................. 44 （一）基本信息 ............................................................................................... 44 （二）项目配套情况 ........................................................................................ 44 （三）本���配租主要户型 详细信息 ..................................................................... 45 十六、缇香雅园 项目基本情况 .................................................................................. 46 （一）基本信息 ............................................................................................... 46 （二）项目配套情况 ........................................................................................ 46 （三）本次配租主要户型 详细信息 ..................................................................... 47 十七、燕保 ·马驹桥家园 项目简介 ........................................................................... 52 （一）基本信息 ............................................................................................... 52 （二）项目配套情况 ........................................................................................ 52 （三）本次配租主要户型 详细信息 ..................................................................... 53 十八、拾景园 项目基本情况 ..................................................................................... 59 （一）基本信息 ............................................................................................... 59 （二）项目配套情况 ........................................................................................ 59 （三）本次配租主要户型 详细信息 ..................................................................... 60 十九、盛达嘉园 项目基本情况 .................................................................................. 62 （一）基本信息 ............................................................................................... 62 （二）项目配套情况 ........................................................................................ 62 （三）本次配租主要户型 详细信息 ..................................................................... 63 二十、璟秀欣苑 项目基本情况 .................................................................................. 66 （一）基本信息 ............................................................................................... 66 （二）项目配套情况 ........................................................................................ 66 （三）本次配租主要户型 详细信息 ..................................................................... 67 二十一、通州光机电 项目基本情况 ...............................................。；# 【北京海淀区房屋出租5000-8000223元/月租房信息_房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀区房屋出租5000-8000223元/月条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://fang.com/chuzu/3_486508934_1.htm) 2室2厅世纪城三期烟树园 整租|2室2厅|84㎡|朝西南 海淀-世纪城-世纪城三期烟树园 距12号线蓝靛厂站约643米。；9000 元/月 [](https://fang.com/chuzu/3_475596192_1.htm) 龙湖唐宁ONE 1室 配套齐全 精装修 电梯房 整租|1室0厅|46㎡|朝北 海淀-五道口-龙湖唐宁ONE 距13号线五道口站约548米。；9500 元/月 [](https://fang.com/chuzu/3_486588776_1.htm) 南北通透郦城2室2厅精装修 整租|2室2厅|100㎡|朝南北 海淀-四季青-郦城 距12号线蓝靛厂站约1158米。</x:v>
+        <x:v>房龄约16年（2008年建成），部分楼栋无电梯（仅1、2号楼有电梯）；；户型南北通透方正，采光通风较好；；精装修房源配置齐全，简装修房源基础；；物业为北京阳光物业公司，物业费0.8元/㎡·月，评价提及物业一般；；房屋顶层带阁楼，不漏水，一层不潮，楼间距30米，居住密度适中（容积率1.8）；</x:v>
       </x:c>
       <x:c r="L11" t="str">
-        <x:v># 《燕保 ·汇鸿家园等 25 个公租房项 # 目情况简介》 目录 一、燕保 ·汇鸿家园 公租房项目基本情况介绍 ............................................................. 5 （一）基本信息 ................................................................................................. 5 （二）项目配套情况 ........................................................................................... 5 （三） 本次配租主要户型详细信息 ....................................................................... 6 二、熙悦尚郡公租房项目基本情况介绍 ....................................................................... 9 （一） 基本信息 ................................................................................................. 9 （二） 项目配套情况 ........................................................................................... 9 （三）本次配租主要户型详细信息 ..................................................................... 10 三、燕保 ·双桥家园 项目 基本情况介绍 ..................................................................... 11 （一）基本信息 ............................................................................................... 11 （二）项目配套情况 ........................................................................................ 11 （三）本次配租主要户型详细信息 ..................................................................... 12 四、怡景园项目基本情况介绍 .................................................................................. 14 （一） 基本信息 ............................................................................................... 14 （二） 项目配套情况 ........................................................................................ 14 （三） 本次配租主要户型详细信息 ..................................................................... 15 五、燕保 ·北焦家园项目基本情况介绍 ..................................................................... 17 （一）基本信息 ............................................................................................... 17 （二）项目配套情况 ........................................................................................ 17 （三） 本次配租主要户型详细信息 ................................................................... 18 六、燕保 ·常营家园 公租房项目基本情况介绍 ........................................................... 22 （一）基本信息 ............................................................................................... 22 （二）项目配套情况 ........................................................................................ 22 （三）户型详细信息 ........................................................................................ 23 七、管庄北二里 公租房项目基本情况介绍 ................................................................. 25 （一）基本信息 ............................................................................................... 25 （二）项目配套情况 ........................................................................................ 25 （三） 本次配租主要户型 详细信息 ..................................................................... 25 八、燕保 ·马泉营家园 项目基本情况 ........................................................................ 27 （一）基本信息 ............................................................................................... 27 （二）项目配套情况 ........................................................................................ 27 （三）本次配租主要户型 详细信息 ..................................................................... 28 九、瑞湾家园 项目基本情况 ..................................................................................... 31 （一）基本信息 ............................................................................................... 31 （二）项目配套情况 ........................................................................................ 31 （三）本次配租 主要户型详细信息 ..................................................................... 32 十、燕保 ·辛店家园 项目基本情况 ........................................................................... 33 （一）基本信息 ............................................................................................... 33 （二）项目配套情况 ........................................................................................ 33 （三）本次配租 主要户型详细信息 ..................................................................... 34 十一、燕保 ·温泉家园公租房项目情况简介 .............................................................. 35 （一）基本信息 ............................................................................................... 35 （二）项目配套情况 ........................................................................................ 35 （三）本次配租主要户型详细信息 ..................................................................... 36 十二、苏家坨 项目基本情况 ..................................................................................... 37 （一）基本信息 ............................................................................................... 37 （二）项目配套情况 ........................................................................................ 37 （三）本次配租 主要户型详细信息 ..................................................................... 38 十三、三嘉信苑 公租房项目基本情况介绍 ................................................................. 39 （一） 基本信息 ............................................................................................... 39 （二） 项目配套情况 ........................................................................................ 39 （三） 本次配租 主要 户型详细信息 ..................................................................... 40 十四、台湖银河湾（东区） 项目 基本情况 ................................................................. 41 （一）基本信息 ............................................................................................... 41 （二）项目配套情况 ........................................................................................ 41 （三）本次配租主要户型 详细信息 ..................................................................... 42 十五、台湖银河湾（西区） 项目 基本情况 ................................................................. 44 （一）基本信息 ............................................................................................... 44 （二）项目配套情况 ........................................................................................ 44 （三）本���配租主要户型 详细信息 ..................................................................... 45 十六、缇香雅园 项目基本情况 .................................................................................. 46 （一）基本信息 ............................................................................................... 46 （二）项目配套情况 ........................................................................................ 46 （三）本次配租主要户型 详细信息 ..................................................................... 47 十七、燕保 ·马驹桥家园 项目简介 ........................................................................... 52 （一）基本信息 ............................................................................................... 52 （二）项目配套情况 ........................................................................................ 52 （三）本次配租主要户型 详细信息 ..................................................................... 53 十八、拾景园 项目基本情况 ..................................................................................... 59 （一）基本信息 ............................................................................................... 59 （二）项目配套情况 ........................................................................................ 59 （三）本次配租主要户型 详细信息 ..................................................................... 60 十九、盛达嘉园 项目基本情况 .................................................................................. 62 （一）基本信息 ............................................................................................... 62 （二）项目配套情况 ........................................................................................ 62 （三）本次配租主要户型 详细信息 ..................................................................... 63 二十、璟秀欣苑 项目基本情况 .................................................................................. 66 （一）基本信息 ............................................................................................... 66 （二）项目配套情况 ........................................................................................ 66 （三）本次配租主要户型 详细信息 ..................................................................... 67 二十一、通州光机电 项目基本情况 ...............................................。；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀区房屋出租5000-8000223元/月条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://fang.com/chuzu/3_486508934_1.htm) 2室2厅世纪城三期烟树园 整租|2室2厅|84㎡|朝西南 海淀-世纪城-世纪城三期烟树园 距12号线蓝靛厂站约643米。；8500 元/月 [](https://fang.com/chuzu/3_486480546_1.htm) 学院路 新辰里附近 双泉嘉苑 两居室出租 配套齐全 整租|2室1厅|85㎡|朝南 海淀-学院路-双泉嘉苑 周边配套齐独门独卫交通便利 8800 元/月 [](https://fang.com/chuzu/3_486696643_1.htm) 整租·甘家口·建设部大院·2室·1厅 整租|2室1厅|72㎡|朝南北 海淀-增光路-建设部大院 距16号线二里沟站约453米。；交通便利周边配套齐全装全配 8930 元/月 [](https://fang.com/chuzu/3_486941180_1.htm) 3室1厅人济山庄一期 整租|3室1厅|195㎡|朝东 海淀-紫竹桥-人济山庄 距16号线万寿寺站约780米。；9000 元/月 [](https://fang.com/chuzu/3_485198288_1.htm) 五道口 华联购物中心旁 暂安处 80多平三居出租 可 整租|3室1厅|81㎡|朝南北 海淀-五道口-暂安处 距13号线五道口站约455米。</x:v>
+        <x:v>通勤：距16号线西北旺站约800-1193米，步行可达，周边公交站多（如963、982等）；；商超：北门有生鲜、果蔬等日常超市，周边有百旺商场；；医院：周边有309医院、上地医院、北医三院；；餐饮：周边有蜀食轩、滇蜀美食广场等各类餐饮；</x:v>
       </x:c>
       <x:c r="M11" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?</x:v>
+        <x:v>房屋顶层带阁楼，不漏水，一层不潮，楼间距30米，居住密度适中（容积率1.8）；</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>价格线索：【北京海淀区房屋出租5000-8000223元/月；# 【北京海淀区房屋出租5000-8000223元/月；* 关键字：海淀区房屋出租5000-8000223元/月；8500 元/月；-双泉嘉苑 周边配套齐独门独卫交通便利 8800 元/月；8900 元/月；交通便利周边配套齐全装全配 8930 元/月；9000 元/月；房屋质量/户型线索：# 《燕保 ·汇鸿家园等 25 个公租房项 # 目情况简介》 目录 一、燕保 ·汇鸿家园 公租房项目基本情况介绍 ............................................................. 5 （一）基本信息 ................................................................................................. 5 （二）项目配套情况 ........................................................................................... 5 （三） 本次配租主要户型详细信息 ....................................................................... 6 二、熙悦尚郡公租房项目基本情况介绍 ....................................................................... 9 （一） 基本信息 ................................................................................................. 9 （二） 项目配套情况 ........................................................................................... 9 （三）本次配租主要户型详细信息 ..................................................................... 10 三、燕保 ·双桥家园 项目 基本情况介绍 ..................................................................... 11 （一）基本信息 ............................................................................................... 11 （二）项目配套情况 ........................................................................................ 11 （三）本次配租主要户型详细信息 ..................................................................... 12 四、怡景园项目基本情况介绍 .................................................................................. 14 （一） 基本信息 ............................................................................................... 14 （二） 项目配套情况 ........................................................................................ 14 （三） 本次配租主要户型详细信息 ..................................................................... 15 五、燕保 ·北焦家园项目基本情况介绍 ..................................................................... 17 （一）基本信息 ............................................................................................... 17 （二）项目配套情况 ........................................................................................ 17 （三） 本次配租主要户型详细信息 ................................................................... 18 六、燕保 ·常营家园 公租房项目基本情况介绍 ........................................................... 22 （一）基本信息 ............................................................................................... 22 （二）项目配套情况 ........................................................................................ 22 （三）户型详细信息 ........................................................................................ 23 七、管庄北二里 公租房项目基本情况介绍 ................................................................. 25 （一）基本信息 ............................................................................................... 25 （二）项目配套情况 ........................................................................................ 25 （三） 本次配租主要户型 详细信息 ..................................................................... 25 八、燕保 ·马泉营家园 项目基本情况 ........................................................................ 27 （一）基本信息 ............................................................................................... 27 （二）项目配套情况 ........................................................................................ 27 （三）本次配租主要户型 详细信息 ..................................................................... 28 九、瑞湾家园 项目基本情况 ..................................................................................... 31 （一）基本信息 ............................................................................................... 31 （二）项目配套情况 ........................................................................................ 31 （三）本次配租 主要户型详细信息 ..................................................................... 32 十、燕保 ·辛店家园 项目基本情况 ........................................................................... 33 （一）基本信息 ............................................................................................... 33 （二）项目配套情况 ........................................................................................ 33 （三）本次配租 主要户型详细信息 ..................................................................... 34 十一、燕保 ·温泉家园公租房项目情况简介 .............................................................. 35 （一）基本信息 ............................................................................................... 35 （二）项目配套情况 ........................................................................................ 35 （三）本次配租主要户型详细信息 ..................................................................... 36 十二、苏家坨 项目基本情况 ..................................................................................... 37 （一）基本信息 ............................................................................................... 37 （二）项目配套情况 ........................................................................................ 37 （三）本次配租 主要户型详细信息 ..................................................................... 38 十三、三嘉信苑 公租房项目基本情况介绍 ................................................................. 39 （一） 基本信息 ............................................................................................... 39 （二） 项目配套情况 ........................................................................................ 39 （三） 本次配租 主要 户型详细信息 ..................................................................... 40 十四、台湖银河湾（东区） 项目 基本情况 ................................................................. 41 （一）基本信息 ............................................................................................... 41 （二）项目配套情况 ........................................................................................ 41 （三）本次配租主要户型 详细信息 ..................................................................... 42 十五、台湖银河湾（西区） 项目 基本情况 ................................................................. 44 （一）基本信息 ............................................................................................... 44 （二）项目配套情况 ........................................................................................ 44 （三）本���配租主要户型 详细信息 ..................................................................... 45 十六、缇香雅园 项目基本情况 .................................................................................. 46 （一）基本信息 ............................................................................................... 46 （二）项目配套情况 ........................................................................................ 46 （三）本次配租主要户型 详细信息 ..................................................................... 47 十七、燕保 ·马驹桥家园 项目简介 ........................................................................... 52 （一）基本信息 ............................................................................................... 52 （二）项目配套情况 ........................................................................................ 52 （三）本次配租主要户型 详细信息 ..................................................................... 53 十八、拾景园 项目基本情况 ..................................................................................... 59 （一）基本信息 ............................................................................................... 59 （二）项目配套情况 ........................................................................................ 59 （三）本次配租主要户型 详细信息 ..................................................................... 60 十九、盛达嘉园 项目基本情况 .................................................................................. 62 （一）基本信息 ............................................................................................... 62 （二）项目配套情况 ........................................................................................ 62 （三）本次配租主要户型 详细信息 ..................................................................... 63 二十、璟秀欣苑 项目基本情况 .................................................................................. 66 （一）基本信息 ............................................................................................... 66 （二）项目配套情况 ........................................................................................ 66 （三）本次配租主要户型 详细信息 ..................................................................... 67 二十一、通州光机电 项目基本情况 ...............................................。；# 【北京海淀区房屋出租5000-8000223元/月租房信息_房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀区房屋出租5000-8000223元/月条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://fang.com/chuzu/3_486508934_1.htm) 2室2厅世纪城三期烟树园 整租|2室2厅|84㎡|朝西南 海淀-世纪城-世纪城三期烟树园 距12号线蓝靛厂站约643米。；9000 元/月 [](https://fang.com/chuzu/3_475596192_1.htm) 龙湖唐宁ONE 1室 配套齐全 精装修 电梯房 整租|1室0厅|46㎡|朝北 海淀-五道口-龙湖唐宁ONE 距13号线五道口站约548米。；9500 元/月 [](https://fang.com/chuzu/3_486588776_1.htm) 南北通透郦城2室2厅精装修 整租|2室2厅|100㎡|朝南北 海淀-四季青-郦城 距12号线蓝靛厂站约1158米。；生活便利线索：# 《燕保 ·汇鸿家园等 25 个公租房项 # 目情况简介》 目录 一、燕保 ·汇鸿家园 公租房项目基本情况介绍 ............................................................. 5 （一）基本信息 ................................................................................................. 5 （二）项目配套情况 ........................................................................................... 5 （三） 本次配租主要户型详细信息 ....................................................................... 6 二、熙悦尚郡公租房项目基本情况介绍 ....................................................................... 9 （一） 基本信息 ................................................................................................. 9 （二） 项目配套情况 ........................................................................................... 9 （三）本次配租主要户型详细信息 ..................................................................... 10 三、燕保 ·双桥家园 项目 基本情况介绍 ..................................................................... 11 （一）基本信息 ............................................................................................... 11 （二）项目配套情况 ........................................................................................ 11 （三）本次配租主要户型详细信息 ..................................................................... 12 四、怡景园项目基本情况介绍 .................................................................................. 14 （一） 基本信息 ............................................................................................... 14 （二） 项目配套情况 ........................................................................................ 14 （三） 本次配租主要户型详细信息 ..................................................................... 15 五、燕保 ·北焦家园项目基本情况介绍 ..................................................................... 17 （一）基本信息 ............................................................................................... 17 （二）项目配套情况 ........................................................................................ 17 （三） 本次配租主要户型详细信息 ................................................................... 18 六、燕保 ·常营家园 公租房项目基本情况介绍 ........................................................... 22 （一）基本信息 ............................................................................................... 22 （二）项目配套情况 ........................................................................................ 22 （三）户型详细信息 ........................................................................................ 23 七、管庄北二里 公租房项目基本情况介绍 ................................................................. 25 （一）基本信息 ............................................................................................... 25 （二）项目配套情况 ........................................................................................ 25 （三） 本次配租主要户型 详细信息 ..................................................................... 25 八、燕保 ·马泉营家园 项目基本情况 ........................................................................ 27 （一）基本信息 ............................................................................................... 27 （二）项目配套情况 ........................................................................................ 27 （三）本次配租主要户型 详细信息 ..................................................................... 28 九、瑞湾家园 项目基本情况 ..................................................................................... 31 （一）基本信息 ............................................................................................... 31 （二）项目配套情况 ........................................................................................ 31 （三）本次配租 主要户型详细信息 ..................................................................... 32 十、燕保 ·辛店家园 项目基本情况 ........................................................................... 33 （一）基本信息 ............................................................................................... 33 （二）项目配套情况 ........................................................................................ 33 （三）本次配租 主要户型详细信息 ..................................................................... 34 十一、燕保 ·温泉家园公租房项目情况简介 .............................................................. 35 （一）基本信息 ............................................................................................... 35 （二）项目配套情况 ........................................................................................ 35 （三）本次配租主要户型详细信息 ..................................................................... 36 十二、苏家坨 项目基本情况 ..................................................................................... 37 （一）基本信息 ............................................................................................... 37 （二）项目配套情况 ........................................................................................ 37 （三）本次配租 主要户型详细信息 ..................................................................... 38 十三、三嘉信苑 公租房项目基本情况介绍 ................................................................. 39 （一） 基本信息 ............................................................................................... 39 （二） 项目配套情况 ........................................................................................ 39 （三） 本次配租 主要 户型详细信息 ..................................................................... 40 十四、台湖银河湾（东区） 项目 基本情况 ................................................................. 41 （一）基本信息 ............................................................................................... 41 （二）项目配套情况 ........................................................................................ 41 （三）本次配租主要户型 详细信息 ..................................................................... 42 十五、台湖银河湾（西区） 项目 基本情况 ................................................................. 44 （一）基本信息 ............................................................................................... 44 （二）项目配套情况 ........................................................................................ 44 （三）本���配租主要户型 详细信息 ..................................................................... 45 十六、缇香雅园 项目基本情况 .................................................................................. 46 （一）基本信息 ............................................................................................... 46 （二）项目配套情况 ........................................................................................ 46 （三）本次配租主要户型 详细信息 ..................................................................... 47 十七、燕保 ·马驹桥家园 项目简介 ........................................................................... 52 （一）基本信息 ............................................................................................... 52 （二）项目配套情况 ........................................................................................ 52 （三）本次配租主要户型 详细信息 ..................................................................... 53 十八、拾景园 项目基本情况 ..................................................................................... 59 （一）基本信息 ............................................................................................... 59 （二）项目配套情况 ........................................................................................ 59 （三）本次配租主要户型 详细信息 ..................................................................... 60 十九、盛达嘉园 项目基本情况 .................................................................................. 62 （一）基本信息 ............................................................................................... 62 （二）项目配套情况 ........................................................................................ 62 （三）本次配租主要户型 详细信息 ..................................................................... 63 二十、璟秀欣苑 项目基本情况 .................................................................................. 66 （一）基本信息 ............................................................................................... 66 （二）项目配套情况 ........................................................................................ 66 （三）本次配租主要户型 详细信息 ..................................................................... 67 二十一、通州光机电 项目基本情况 ...............................................。；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀区房屋出租5000-8000223元/月条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://fang.com/chuzu/3_486508934_1.htm) 2室2厅世纪城三期烟树园 整租|2室2厅|84㎡|朝西南 海淀-世纪城-世纪城三期烟树园 距12号线蓝靛厂站约643米。；8500 元/月 [](https://fang.com/chuzu/3_486480546_1.htm) 学院路 新辰里附近 双泉嘉苑 两居室出租 配套齐全 整租|2室1厅|85㎡|朝南 海淀-学院路-双泉嘉苑 周边配套齐独门独卫交通便利 8800 元/月 [](https://fang.com/chuzu/3_486696643_1.htm) 整租·甘家口·建设部大院·2室·1厅 整租|2室1厅|72㎡|朝南北 海淀-增光路-建设部大院 距16号线二里沟站约453米。；交通便利周边配套齐全装全配 8930 元/月 [](https://fang.com/chuzu/3_486941180_1.htm) 3室1厅人济山庄一期 整租|3室1厅|195㎡|朝东 海淀-紫竹桥-人济山庄 距16号线万寿寺站约780米。；9000 元/月 [](https://fang.com/chuzu/3_485198288_1.htm) 五道口 华联购物中心旁 暂安处 80多平三居出租 可 整租|3室1厅|81㎡|朝南北 海淀-五道口-暂安处 距13号线五道口站约455米。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：整租一居约5800元/月；、二居约6000元/月；、合租主卧约4240元/月；房屋质量/户型线索：房龄约16年（2008年建成），部分楼栋无电梯（仅1、2号楼有电梯）；；户型南北通透方正，采光通风较好；；精装修房源配置齐全，简装修房源基础；；物业为北京阳光物业公司，物业费0.8元/㎡·月，评价提及物业一般；；房屋顶层带阁楼，不漏水，一层不潮，楼间距30米，居住密度适中（容积率1.8）；；生活便利线索：通勤：距16号线西北旺站约800-1193米，步行可达，周边公交站多（如963、982等）；；商超：北门有生鲜、果蔬等日常超市，周边有百旺商场；；医院：周边有309医院、上地医院、北医三院；；餐饮：周边有蜀食轩、滇蜀美食广场等各类餐饮；；风险线索：房屋顶层带阁楼，不漏水，一层不潮，楼间距30米，居住密度适中（容积率1.8）；</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>1. 海淀区苏家坨公租房项目基本情况介绍 https://www.bjdch.gov.cn/zwgk/jgdh/qzfzcbmdh/fgj/bzxzffp/202511/P020251117576266490220.pdf
-2. 【北京海淀区房屋出租5000-8000223元/月租房信息_房屋出租】- 房天下 https://fang.com/houses/zf_252999bj/c25000-d28000223,4,-h34-i33/
-3. 冬晴园租房 - 北京租房网 https://m.zufun.cn/bj/property/47512
-4. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 http://mob.58.com/zf/wh-haidian/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4129705946078223-3/
+2. https://esf.fang.com/loupan/1010664537/strategy.htm
+3. http://m.anjuke.com/ch/rent/4476379661413388-3/
+4. http://m.fang.com/esf/bj/3_486613583.html
+5. http://m.anjuke.com/ch/rent/4554479851203596-3/
+6. http://m.anjuke.com/bj/community/850677/jiedu/
+7. 冬晴园 2室出租 业主直签 价格便宜 随时住 邻后厂村路 http://m.anjuke.com/bj/rent/4129705946078223-3/
+8. 2026北京百旺新城冬晴园小区，配套指南，买房攻略 https://esf.fang.com/loupan/1010664537/strategy.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -750,39 +776,42 @@
         <x:v>北京市海淀区东北旺路与东北旺中路交叉口(东北旺路38号)</x:v>
       </x:c>
       <x:c r="E12" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F12" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G12" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H12" t="n">
-        <x:v>6.8</x:v>
+        <x:v>7.4</x:v>
       </x:c>
       <x:c r="I12" t="str">
-        <x:v>海淀老牌社区，生活便利，但网页证据多为二手房售价，租金参考性略弱。</x:v>
+        <x:v>紧邻软件园通勤优势极大，环境安静安全，但1992年房龄很老且为无电梯步梯房。</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>2026-02-09 | 301万 | 44090元/㎡；2025-12-25 | 206万 | 36332元/㎡；万 2室1厅1卫丨68㎡丨南北丨顶层丨 80500元/㎡；万 3室1厅1卫丨82㎡丨南北丨顶层丨 94700元/㎡；05000_ 元/m² 东馨园，小区价格65653元/㎡</x:v>
+        <x:v>整租月租：1室1厅5100-6400元/月；，2室1厅5100-8000元/月；，合租单间1700-2500元/月</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **55654** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓1.96% 贷款计算器 * 二手房源 2套 * 最近成交 181套 * 楼栋总数 12栋 * 房屋总数 728户 * 建筑类型 板楼 * 建筑年代 1998年建成 * 小区位置 东北旺路与东北旺中路交叉口(东北旺路38号)地图 * 物业公司 北京东居物业管理有限公司 * 开发商 无开发商 #### 推荐经纪人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 王立新 评分：4.6 从业信息卡 百科 闪电回复 ##### 张波 评分：4.6 从业信息卡 百科 闪电回复 ##### 韩岗 评分：4.1 从业信息卡 百科 ### 东馨园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 68.27㎡ | 2026-02-09 | 301万 | 44090元/㎡ | 市场信息 | | 62.20㎡ | 2026-01-11 | -- | -- | 市场信息 | | 56.70㎡ | 2025-12-25 | 206万 | 36332元/㎡ | 市场信息 | 查看全部成交 ### 东馨园价格走势 ### 东馨园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 东馨园 海淀·马连洼**55655** 元/㎡ * #### 东旭园 海淀·马连洼**55817** 元/㎡ * #### 亿城西山公馆 海淀·上地**75374** 元/㎡ * #### 和樾玉鸣 海淀·马连洼**108704** 元/㎡ * #### 和樾望云 海淀·马连洼**111075** 元/㎡ ### 相关资讯 * 小区资讯北京东馨园怎么样?；北京海淀区馨瑞嘉园公租房项目介绍(位置+租金+户型图)。；北京吉屋网提供北京东馨园二手房出售信息、东馨园二手房价格，包括及时更新北京东馨园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 东馨园_北京东馨园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_东馨园 更新于 2026-06-01 10:55:13 [](https://bj.jiwu.com/tu/4232937.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722662.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722663.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722664.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722665.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722666.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722667.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722668.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722669.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722670.html "东馨园实景图图片") # 东馨园 别名：东馨园 加入本地买房群 关注 _北京 - 海淀 - 东北旺中路_ 发地址到手机 参考均价 _65653 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1260_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-73群（472） * 大家觉得这里未来发展怎么样？</x:v>
+        <x:v>租房价格整体受户型、面积影响，精装修房源月租略高于同户型基础装修房源；；房龄约1992年，步梯房共6层；；装修多为精装修（部分简单装修）；；隔音方面宣传卧室不紧挨，隔音效果好；；物业安保24小时巡视，小区环境安静绿化好；</x:v>
       </x:c>
       <x:c r="L12" t="str">
-        <x:v>北京吉屋网提供北京东馨园二手房出售信息、东馨园二手房价格，包括及时更新北京东馨园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 东馨园_北京东馨园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_东馨园 更新于 2026-06-01 10:55:13 [](https://bj.jiwu.com/tu/4232937.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722662.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722663.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722664.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722665.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722666.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722667.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722668.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722669.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722670.html "东馨园实景图图片") # 东馨园 别名：东馨园 加入本地买房群 关注 _北京 - 海淀 - 东北旺中路_ 发地址到手机 参考均价 _65653 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1260_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-73群（472） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；东馨园的位置在东北旺中路，交通便利。；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等东馨园小区信息，关注吉屋北京东馨园！</x:v>
+        <x:v>通勤：紧邻18号线上地软件园站（步行约569米）、东北旺站（约1659米），多路公交直达；；商超：周边有鹏旺果蔬生鲜超市、供销社便民超市，距中发百旺商城1.8公里；；生活配套：周边餐饮丰富，有超市、绿地公园等，居住人群多为软件园白领；；医院、银行等配套较齐全；</x:v>
       </x:c>
       <x:c r="M12" t="str"/>
       <x:c r="N12" t="str">
-        <x:v>价格线索：2026-02-09 | 301万 | 44090元/㎡；2025-12-25 | 206万 | 36332元/㎡；万 2室1厅1卫丨68㎡丨南北丨顶层丨 80500元/㎡；万 3室1厅1卫丨82㎡丨南北丨顶层丨 94700元/㎡；05000_ 元/m² 东馨园，小区价格65653元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **55654** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓1.96% 贷款计算器 * 二手房源 2套 * 最近成交 181套 * 楼栋总数 12栋 * 房屋总数 728户 * 建筑类型 板楼 * 建筑年代 1998年建成 * 小区位置 东北旺路与东北旺中路交叉口(东北旺路38号)地图 * 物业公司 北京东居物业管理有限公司 * 开发商 无开发商 #### 推荐经纪人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 王立新 评分：4.6 从业信息卡 百科 闪电回复 ##### 张波 评分：4.6 从业信息卡 百科 闪电回复 ##### 韩岗 评分：4.1 从业信息卡 百科 ### 东馨园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 68.27㎡ | 2026-02-09 | 301万 | 44090元/㎡ | 市场信息 | | 62.20㎡ | 2026-01-11 | -- | -- | 市场信息 | | 56.70㎡ | 2025-12-25 | 206万 | 36332元/㎡ | 市场信息 | 查看全部成交 ### 东馨园价格走势 ### 东馨园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 东馨园 海淀·马连洼**55655** 元/㎡ * #### 东旭园 海淀·马连洼**55817** 元/㎡ * #### 亿城西山公馆 海淀·上地**75374** 元/㎡ * #### 和樾玉鸣 海淀·马连洼**108704** 元/㎡ * #### 和樾望云 海淀·马连洼**111075** 元/㎡ ### 相关资讯 * 小区资讯北京东馨园怎么样?；北京海淀区馨瑞嘉园公租房项目介绍(位置+租金+户型图)。；北京吉屋网提供北京东馨园二手房出售信息、东馨园二手房价格，包括及时更新北京东馨园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 东馨园_北京东馨园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_东馨园 更新于 2026-06-01 10:55:13 [](https://bj.jiwu.com/tu/4232937.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722662.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722663.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722664.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722665.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722666.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722667.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722668.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722669.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722670.html "东馨园实景图图片") # 东馨园 别名：东馨园 加入本地买房群 关注 _北京 - 海淀 - 东北旺中路_ 发地址到手机 参考均价 _65653 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1260_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-73群（472） * 大家觉得这里未来发展怎么样？；生活便利线索：北京吉屋网提供北京东馨园二手房出售信息、东馨园二手房价格，包括及时更新北京东馨园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 东馨园_北京东馨园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_东馨园 更新于 2026-06-01 10:55:13 [](https://bj.jiwu.com/tu/4232937.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722662.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722663.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722664.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722665.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722666.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722667.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722668.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722669.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722670.html "东馨园实景图图片") # 东馨园 别名：东馨园 加入本地买房群 关注 _北京 - 海淀 - 东北旺中路_ 发地址到手机 参考均价 _65653 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1260_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-73群（472） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；东馨园的位置在东北旺中路，交通便利。；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等东馨园小区信息，关注吉屋北京东馨园！</x:v>
+        <x:v>价格线索：整租月租：1室1厅5100-6400元/月；，2室1厅5100-8000元/月；，合租单间1700-2500元/月；房屋质量/户型线索：租房价格整体受户型、面积影响，精装修房源月租略高于同户型基础装修房源；；房龄约1992年，步梯房共6层；；装修多为精装修（部分简单装修）；；隔音方面宣传卧室不紧挨，隔音效果好；；物业安保24小时巡视，小区环境安静绿化好；；生活便利线索：通勤：紧邻18号线上地软件园站（步行约569米）、东北旺站（约1659米），多路公交直达；；商超：周边有鹏旺果蔬生鲜超市、供销社便民超市，距中发百旺商城1.8公里；；生活配套：周边餐饮丰富，有超市、绿地公园等，居住人群多为软件园白领；；医院、银行等配套较齐全；</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>1. 【北京东馨园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010215647.htm
-2.  https://www.bjdch.gov.cn/zwgk/jgdh/qzfzcbmdh/fgj/bzxzffp/202511/P020251117576266490220.pdf
-3. 北京海淀区馨瑞嘉园公租房项目介绍(位置+租金+户型图) http://bj.bendibao.com/zffw/20231115/353686.shtm
-4. 东馨园_北京东馨园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/170106.html
-5. 东馨园二手房,2室1厅 东馨园,房源位于东北旺中路-幸福里 https://fangchan.snssdk.com/ershoufang/bj-7473992157500080191.html</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/3076822915408899-3/
+2. http://m.anjuke.com/dongyang/rent/4598003578297352-3/
+3. http://m.anjuke.com/bj/rent/4605026638736399-3/
+4. http://m.anjuke.com/bj/rent/4367579693686790-3/
+5. 东馨园 真实 实图实价 杜绝虚假 无 可月付短签 http://m.anjuke.com/bj/rent/3076822915408899-3/
+6. 0押金月付 上地西北旺中关村软件园东馨园全南精装两居室 http://m.anjuke.com/dongyang/rent/4598003578297352-3/
+7. 东馨园 真实 无中 一屋一人 可月付短签 单间独开整 http://m.anjuke.com/bj/rent/2960192883942413-3/
+8. 东馨园 东旭园 万德嘉园 软件园 百度 科技园 华联 急租 http://m.anjuke.com/bj/rent/4605026638736399-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -799,7 +828,7 @@
         <x:v>东北旺西路8号院</x:v>
       </x:c>
       <x:c r="E13" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F13" t="n">
         <x:v>9</x:v>
@@ -808,30 +837,33 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H13" t="n">
-        <x:v>9.2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I13" t="str">
-        <x:v>位于软件园核心区，步行通勤极佳，租金水平合理，是网易员工的首选之一。</x:v>
+        <x:v>缺乏该小区具体的质量与配套信息，现有数据疑似泛化或误导，证据不足建议保守考虑。</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5000元/月；+0.00% * 二室 7300元/月；+0.00% * 三室 10700元/月；+16.30% * 四室 15000元/月；+0.00% * 四室以上 33500元/月；55000 元/月；12000 元/月；65000 元/月</x:v>
+        <x:v>尚东数字居等）的租房信息，价格在800-3500元/月</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v># 尚东数字谷_海淀_北京写字楼网 北京写字楼-办公室出租-出售信息平台-北京写字楼出租网 [](http://www.bgxzl.net/) * 首页 * 租写字楼 * 装修设计 * 楼市资讯 * 委托找房 * 投放房源 * 关于我们 010-53680119 登录 | 微信 [](http://www.bgxzl.net/) 首页`&gt;`海淀`&gt;` 尚东数字谷 项目首页 基本信息 空置房源 建筑指标 硬件设施 周边配套 详细信息 楼盘相册 10分钟步行圈 **尚东数字谷** 物业类型：写字楼 租售形式：出租 地铁线路：13号线,16号线 城市城区：海淀 最新报价：**4元/天/平米** 物业位置：软件园二号路 3010 18518099987 **楼盘详情** **空置房源** * 租售形式 出租面积(㎡)日租金(元/㎡)月租金(万元)**操作** * [](http://www.bgxzl.net/detail.php?；id=33996)**1600㎡****4元/㎡/天****19.47万元/月****查看房源** **基本信息** 物业类型 写字楼 物业评级 所属商圈 海淀 付款方式 面议 环线位置 北五环 基本租期 1年 **建筑指标** 开间面积 100-2000㎡ 绿化率 0.0 **硬件配套** **详细信息** 数字山谷是北京写字楼租赁市场中比较具有人文气息和时代文化的一座大厦，数字山谷写字楼坐落于北京海淀区核心地区，是中关村软件园区内一座涵盖各类高档写字楼与多种商业形态于一体的现代化写字楼，可以说数字山谷写字楼是“中国软件园”内最具特色的写字楼，也是属于中关村软件园二期工程重要之一。；* 王福海： 您好，可以的，可以不带家具北京易合房产怀柔顶秀美泉店王福海很高兴为您回答 希望能帮到您 * 张波： 小区物业可以不带家具，家电，具体跟房主沟通就可以 * 问 可以一次签三至六年的租房合同吗 * NTHfhN： 签租赁合同的具体日期长短，需要和业主协商。；58同城北京租房网，为您提供北京上地租房信息，包括上地房屋出租信息、上地合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。；基本信息 业态： 写字楼 权属性质： 综合用地 物业费：25元/月/平米(租金已含) 代理公司：北京���工厂投资管理公司 外立面形式：玻璃幕墙 建筑结构：框架结构 免租期：具体客户具体谈判 建筑指标 总建筑面积：80000.0平米 总层数：7层 建筑高度：20.5米 标准层层高：3.9米 标准层净高：2.8米 楼板承重：200.0 Kg/平米 平面布局 标准层面积：2500.0平米 主力户型（开间面积）：1700.0平米 窗户是否可开：可开 柱距： 8.4米 承重柱位置：贴边加中间 进深：10.0米 核心筒布局：单侧筒式 有无黑房间/面积多少： 无黑房间平米 硬件配套 电梯品牌：广州日立 数量 客梯：16部 消防梯：16部 荷载人数：13人/梯 空调品牌：开立 中央空调制式：两管制 是否分区可控： 否 电力总容量： 5000.0千瓦 单方电力： 120.0瓦/平米 车位： 100 个(地上) 325 个(地下) 梯速： 1.0米/秒 (客梯) 平均每层容量：30000.0 千瓦 开发商租赁部电话：010-82826882 20150306有一个单层面积2500平米的出租、一个独栋7800平方米单层面积1650最少租两层、一个独栋12221平方米，出租价格6.32元。</x:v>
+        <x:v>未查询到目标小区的住宅质量相关信息，搜索结果多为其他小区，提及的房子质量（如精装修、配套全、采光好等）均不属于目标小区。</x:v>
       </x:c>
       <x:c r="L13" t="str">
-        <x:v># 尚东数字谷_海淀_北京写字楼网 北京写字楼-办公室出租-出售信息平台-北京写字楼出租网 [](http://www.bgxzl.net/) * 首页 * 租写字楼 * 装修设计 * 楼市资讯 * 委托找房 * 投放房源 * 关于我们 010-53680119 登录 | 微信 [](http://www.bgxzl.net/) 首页`&gt;`海淀`&gt;` 尚东数字谷 项目首页 基本信息 空置房源 建筑指标 硬件设施 周边配套 详细信息 楼盘相册 10分钟步行圈 **尚东数字谷** 物业类型：写字楼 租售形式：出租 地铁线路：13号线,16号线 城市城区：海淀 最新报价：**4元/天/平米** 物业位置：软件园二号路 3010 18518099987 **楼盘详情** **空置房源** * 租售形式 出租面积(㎡)日租金(元/㎡)月租金(万元)**操作** * [](http://www.bgxzl.net/detail.php?；id=33996)**1600㎡****4元/㎡/天****19.47万元/月****查看房源** **基本信息** 物业类型 写字楼 物业评级 所属商圈 海淀 付款方式 面议 环线位置 北五环 基本租期 1年 **建筑指标** 开间面积 100-2000㎡ 绿化率 0.0 **硬件配套** **详细信息** 数字山谷是北京写字楼租赁市场中比较具有人文气息和时代文化的一座大厦，数字山谷写字楼坐落于北京海淀区核心地区，是中关村软件园区内一座涵盖各类高档写字楼与多种商业形态于一体的现代化写字楼，可以说数字山谷写字楼是“中国软件园”内最具特色的写字楼，也是属于中关村软件园二期工程重要之一。；地铁13号线西二旗站。；id=4257) **同价位楼盘 &gt;** **同商圈楼盘 &gt;** **同区域楼盘 &gt;** **关注我们** #### **10分钟步行圈** 地铁/公交站 约 14 2465 1 个站点 周边暂检索不到地铁和公交站 * 上地软件园 * 上地软件园地铁站-A口 * 上地软件园地铁站-B口 * 上地软件园地铁站-C口 * 地铁18号线中关村软件园站东南口 * 软件园西区 * 东北旺西 * 地铁上地软件园站 * 地铁上地软件园站 * 数学山谷 在地图显示 快餐 约 20 4989 家快餐 周边暂检索不到快餐 * 肯德基 * 川湘菜刀削面 * 吉野家 * 金牌黄焖鸡烤肉拌饭 * 常玖岐山面肉夹馍 在地图显示 餐厅 约 9 2777 家餐厅 周边暂检索不到餐厅 * 莫家菜·全国非遗·扬州三头宴 * 椒塘四川风味馆 * 环宇大厦餐厅 * 海盗虾饭 * 祥和友湖南菜 在地图显示 银行 约 4 958 家银行 周边暂检索不到银行 * 中国建设银行 * 招商银行 * 24小时自助银行服务 * 中国民生银行 在地图显示 酒店 约 0 0 个酒店 周边暂检索不到酒店 在地图显示 ## 交通地图 * 地铁/公交 * 快餐 * 餐厅 * 银行 * 酒店 shadow 出口 [](http://map.baidu.com/?；* 陈帆帆： 可以自己发布，也可以找中介带客户，还可以托管给代理公司 * 姜红丹： 你好，可以挂在网上拿着产权证进行识别认证，五八会自动推送房源代理 * 李义强： 中介门店登记下 让中介公司帮忙出租 或者自己拍些照片 挂58网 * 谭帅鹏： 可以看一下周边房产公司，免费登记，一定要整租，找个好租户，中介公司也一定要找好，小公司不找 * 问 在这个平台出租房屋，靠谱吗？</x:v>
+        <x:v>未查询到目标小区的住宅质量相关信息，搜索结果多为其他小区，提及的房子质量（如精装修、配套全、采光好等）均不属于目标小区。；未查询到目标小区的生活便利程度相关信息，搜索结果中其他同名小区提及的通勤、商超等均与目标小区无关。</x:v>
       </x:c>
       <x:c r="M13" t="str"/>
       <x:c r="N13" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5000元/月；+0.00% * 二室 7300元/月；+0.00% * 三室 10700元/月；+16.30% * 四室 15000元/月；+0.00% * 四室以上 33500元/月；55000 元/月；12000 元/月；65000 元/月；房屋质量/户型线索：# 尚东数字谷_海淀_北京写字楼网 北京写字楼-办公室出租-出售信息平台-北京写字楼出租网 [](http://www.bgxzl.net/) * 首页 * 租写字楼 * 装修设计 * 楼市资讯 * 委托找房 * 投放房源 * 关于我们 010-53680119 登录 | 微信 [](http://www.bgxzl.net/) 首页`&gt;`海淀`&gt;` 尚东数字谷 项目首页 基本信息 空置房源 建筑指标 硬件设施 周边配套 详细信息 楼盘相册 10分钟步行圈 **尚东数字谷** 物业类型：写字楼 租售形式：出租 地铁线路：13号线,16号线 城市城区：海淀 最新报价：**4元/天/平米** 物业位置：软件园二号路 3010 18518099987 **楼盘详情** **空置房源** * 租售形式 出租面积(㎡)日租金(元/㎡)月租金(万元)**操作** * [](http://www.bgxzl.net/detail.php?；id=33996)**1600㎡****4元/㎡/天****19.47万元/月****查看房源** **基本信息** 物业类型 写字楼 物业评级 所属商圈 海淀 付款方式 面议 环线位置 北五环 基本租期 1年 **建筑指标** 开间面积 100-2000㎡ 绿化率 0.0 **硬件配套** **详细信息** 数字山谷是北京写字楼租赁市场中比较具有人文气息和时代文化的一座大厦，数字山谷写字楼坐落于北京海淀区核心地区，是中关村软件园区内一座涵盖各类高档写字楼与多种商业形态于一体的现代化写字楼，可以说数字山谷写字楼是“中国软件园”内最具特色的写字楼，也是属于中关村软件园二期工程重要之一。；* 王福海： 您好，可以的，可以不带家具北京易合房产怀柔顶秀美泉店王福海很高兴为您回答 希望能帮到您 * 张波： 小区物业可以不带家具，家电，具体跟房主沟通就可以 * 问 可以一次签三至六年的租房合同吗 * NTHfhN： 签租赁合同的具体日期长短，需要和业主协商。；58同城北京租房网，为您提供北京上地租房信息，包括上地房屋出租信息、上地合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。；基本信息 业态： 写字楼 权属性质： 综合用地 物业费：25元/月/平米(租金已含) 代理公司：北京���工厂投资管理公司 外立面形式：玻璃幕墙 建筑结构：框架结构 免租期：具体客户具体谈判 建筑指标 总建筑面积：80000.0平米 总层数：7层 建筑高度：20.5米 标准层层高：3.9米 标准层净高：2.8米 楼板承重：200.0 Kg/平米 平面布局 标准层面积：2500.0平米 主力户型（开间面积）：1700.0平米 窗户是否可开：可开 柱距： 8.4米 承重柱位置：贴边加中间 进深：10.0米 核心筒布局：单侧筒式 有无黑房间/面积多少： 无黑房间平米 硬件配套 电梯品牌：广州日立 数量 客梯：16部 消防梯：16部 荷载人数：13人/梯 空调品牌：开立 中央空调制式：两管制 是否分区可控： 否 电力总容量： 5000.0千瓦 单方电力： 120.0瓦/平米 车位： 100 个(地上) 325 个(地下) 梯速： 1.0米/秒 (客梯) 平均每层容量：30000.0 千瓦 开发商租赁部电话：010-82826882 20150306有一个单层面积2500平米的出租、一个独栋7800平方米单层面积1650最少租两层、一个独栋12221平方米，出租价格6.32元。；生活便利线索：# 尚东数字谷_海淀_北京写字楼网 北京写字楼-办公室出租-出售信息平台-北京写字楼出租网 [](http://www.bgxzl.net/) * 首页 * 租写字楼 * 装修设计 * 楼市资讯 * 委托找房 * 投放房源 * 关于我们 010-53680119 登录 | 微信 [](http://www.bgxzl.net/) 首页`&gt;`海淀`&gt;` 尚东数字谷 项目首页 基本信息 空置房源 建筑指标 硬件设施 周边配套 详细信息 楼盘相册 10分钟步行圈 **尚东数字谷** 物业类型：写字楼 租售形式：出租 地铁线路：13号线,16号线 城市城区：海淀 最新报价：**4元/天/平米** 物业位置：软件园二号路 3010 18518099987 **楼盘详情** **空置房源** * 租售形式 出租面积(㎡)日租金(元/㎡)月租金(万元)**操作** * [](http://www.bgxzl.net/detail.php?；id=33996)**1600㎡****4元/㎡/天****19.47万元/月****查看房源** **基本信息** 物业类型 写字楼 物业评级 所属商圈 海淀 付款方式 面议 环线位置 北五环 基本租期 1年 **建筑指标** 开间面积 100-2000㎡ 绿化率 0.0 **硬件配套** **详细信息** 数字山谷是北京写字楼租赁市场中比较具有人文气息和时代文化的一座大厦，数字山谷写字楼坐落于北京海淀区核心地区，是中关村软件园区内一座涵盖各类高档写字楼与多种商业形态于一体的现代化写字楼，可以说数字山谷写字楼是“中国软件园”内最具特色的写字楼，也是属于中关村软件园二期工程重要之一。；地铁13号线西二旗站。；id=4257) **同价位楼盘 &gt;** **同商圈楼盘 &gt;** **同区域楼盘 &gt;** **关注我们** #### **10分钟步行圈** 地铁/公交站 约 14 2465 1 个站点 周边暂检索不到地铁和公交站 * 上地软件园 * 上地软件园地铁站-A口 * 上地软件园地铁站-B口 * 上地软件园地铁站-C口 * 地铁18号线中关村软件园站东南口 * 软件园西区 * 东北旺西 * 地铁上地软件园站 * 地铁上地软件园站 * 数学山谷 在地图显示 快餐 约 20 4989 家快餐 周边暂检索不到快餐 * 肯德基 * 川湘菜刀削面 * 吉野家 * 金牌黄焖鸡烤肉拌饭 * 常玖岐山面肉夹馍 在地图显示 餐厅 约 9 2777 家餐厅 周边暂检索不到餐厅 * 莫家菜·全国非遗·扬州三头宴 * 椒塘四川风味馆 * 环宇大厦餐厅 * 海盗虾饭 * 祥和友湖南菜 在地图显示 银行 约 4 958 家银行 周边暂检索不到银行 * 中国建设银行 * 招商银行 * 24小时自助银行服务 * 中国民生银行 在地图显示 酒店 约 0 0 个酒店 周边暂检索不到酒店 在地图显示 ## 交通地图 * 地铁/公交 * 快餐 * 餐厅 * 银行 * 酒店 shadow 出口 [](http://map.baidu.com/?；* 陈帆帆： 可以自己发布，也可以找中介带客户，还可以托管给代理公司 * 姜红丹： 你好，可以挂在网上拿着产权证进行识别认证，五八会自动推送房源代理 * 李义强： 中介门店登记下 让中介公司帮忙出租 或者自己拍些照片 挂58网 * 谭帅鹏： 可以看一下周边房产公司，免费登记，一定要整租，找个好租户，中介公司也一定要找好，小公司不找 * 问 在这个平台出租房屋，靠谱吗？</x:v>
+        <x:v>价格线索：尚东数字居等）的租房信息，价格在800-3500元/月；房屋质量/户型线索：未查询到目标小区的住宅质量相关信息，搜索结果多为其他小区，提及的房子质量（如精装修、配套全、采光好等）均不属于目标小区。；生活便利线索：未查询到目标小区的住宅质量相关信息，搜索结果多为其他小区，提及的房子质量（如精装修、配套全、采光好等）均不属于目标小区。；未查询到目标小区的生活便利程度相关信息，搜索结果中其他同名小区提及的通勤、商超等均与目标小区无关。</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>1. 海淀区 - 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/amp6amp4ama0/
-2. 尚东数字谷_海淀_北京写字楼网 北京写字楼-办公室出租-出售信息平台-北京写字楼出租网 http://www.bgxzl.net/goods.php?id=4257
-3. 上地租房_北京海淀上地租房信息|上地租房价格信息-58租房网 https://mob.58.com/zf/bj-shangdi/
-4. 尚东数字山谷-写字楼出租出售价格欢迎您 https://sdszsg.bj-sydc.com/
-5. 【北京租房网_北京租房信息|房屋出租】- 房天下 http://www.fang.com/houses/zf_253028bj/</x:v>
+        <x:v>1. http://m.anjuke.com/rz/rent/4593902922357764-2/
+2. http://m.anjuke.com/rz/rent/4415752886281218-3/
+3. http://m.anjuke.com/ch/rent/4546018333891597-3/
+4. https://rz.zu.anjuke.com/fangyuan/4415752886281218
+5. http://m.anjuke.com/gz/rent/4292232373591044-3/
+6. http://m.anjuke.com/gz/rent/4582392008745991-3/
+7. http://m.anjuke.com/bj/xzl/zu/7399164189/?houseid=4503088887913485
+8. http://m.anjuke.com/suz/rent/4539815429385230-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -848,41 +880,44 @@
         <x:v>北京市海淀区马连洼街道马连洼北路与圆明园西路交叉口东南角</x:v>
       </x:c>
       <x:c r="E14" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F14" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G14" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H14" t="n">
-        <x:v>7.2</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I14" t="str">
-        <x:v>紧邻马连洼地铁站，通勤网易极便，虽房龄较老且小户型多，但生活配套成熟。</x:v>
+        <x:v>离马连洼站极近，精装房源且环境安静，租金在同地段具竞争力，生活配套成熟。</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>东馨园 1998年竣工 距离1644m 56908 元/㎡；OMA 2008年竣工 距离3917m 62225 元/㎡；冬晴园 2008年竣工 距离2157m 66100 元/㎡；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；光明胡同 可注册办公首次出租南北通透 180000 元/月</x:v>
+        <x:v>区兰园小区租房月租：1室1厅约5200-5700元/月；，2室1厅约6000元/月</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>去APP体验 # 兰园小区 海淀 马连洼 圆明园西路 * 16号线等 * 五六环之间 * 小户型居多 * 配套齐全 收藏 56175 _元/㎡_ 6月挂牌均价23 _套_ 在售房源180 _套_ 在租房源 估价 6.9 小区评分 地段交通 8.2 生活配套 6.0 居住品质 6.0 小区评测 小区距离马连洼地铁站较近，居民轨交出行便利；；小区于1999年建成，房龄较老；；查看完整评测 基本信息查看更多 * 竣工时间 1997年 * 物业类型 住宅 * 所属商圈 马连洼 * 开发商 上海凯邦实业有限公司 * 物业公司 实创物业管理公司 基础信息 * 小区名称 兰园小区 * 物业类型 住宅 * 竣工时间 1997年 * 绿化率 30.0% * 容积率 1.90 * 建筑面积 暂无 * 总户数 1724户 * 小区地址 圆明园西路 * 所属商圈 马连洼 物业信息 * 停车位 0 * 物业费 0.90元/平米/月 * 物业公司 实创物业管理公司 * 开发商 上海凯邦实业有限公司 小区概况 兰园小区位于海淀区马连洼板块，于1999年建成，房龄较老。；小区楼栋共26栋左右，占地面积约100000㎡，建筑面积约180000㎡，容积率1.9左右，小区户型面积有51㎡-97㎡左右的1-3居室。；完成 周边配套 兰园小区 圆明园西路 地铁 公交 学校 餐饮 购物 二手房 租房 出门地铁，精装修三居，南北通透，明厨明卫，看房随时 马连洼 兰园小区 560 万 3室1厅 90.54㎡ 马连洼地铁旁，南北精装修，看房方便，前后无遮挡 马连洼 兰园小区 499 万 3室1厅 81.11㎡ 新增！</x:v>
+        <x:v>海淀区兰园小区租房月租：1室1厅约5200-5700元/月，2室1厅约6000元/月，均为精装修，押一付三，中介费1个月租金。；房子质量：房龄较低，装修为精装修；；户型以1室1厅、2室1厅为主，朝向多为南或南北通透；；物业未明确提及具体评价，但小区绿化率高，环境安静舒适；；隔音方面，搜索结果中暂无针对该小区隔音的明确评价（注意：义乌、杭州同名兰园小区有提到隔音好，但非目标小区）。</x:v>
       </x:c>
       <x:c r="L14" t="str">
-        <x:v>安居客小区频道，提供兰园小区二手房,平均房价56175元/平米,找兰园小区二手房，兰园小区租房，兰园小区房价走势、实景图、房型图、周边交通配套信息就上安居客。；去APP体验 # 兰园小区 海淀 马连洼 圆明园西路 * 16号线等 * 五六环之间 * 小户型居多 * 配套齐全 收藏 56175 _元/㎡_ 6月挂牌均价23 _套_ 在售房源180 _套_ 在租房源 估价 6.9 小区评分 地段交通 8.2 生活配套 6.0 居住品质 6.0 小区评测 小区距离马连洼地铁站较近，居民轨交出行便利；；小区距离马连洼地铁站约273m，地铁16号线途经该站点，居民轨交出行便利；；距离百旺家苑公交站约571m，518路、651路、932路等公交在该站点停靠，居民乘坐公交出行较为便利；；完成 周边配套 兰园小区 圆明园西路 地铁 公交 学校 餐饮 购物 二手房 租房 出门地铁，精装修三居，南北通透，明厨明卫，看房随时 马连洼 兰园小区 560 万 3室1厅 90.54㎡ 马连洼地铁旁，南北精装修，看房方便，前后无遮挡 马连洼 兰园小区 499 万 3室1厅 81.11㎡ 新增！</x:v>
+        <x:v>生活便利程度：地铁方面，步行至16号线马连洼站约247-407米，通勤便利；；商超有天喜百旺超市、中发百旺商城等；；医院有解放军总医院第八医学中心；；餐饮配套丰富，周边餐饮选择多；</x:v>
       </x:c>
       <x:c r="M14" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可��册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。；手机版： 新发地租房信息 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安溪租房网 * 桂林租房网 * 黔东南租房网 * 海口租房网 * 钟祥租房网 * 常德租房网 * 抚顺租房网 * 呼伦贝尔租房网 * 大同租房网 * 阿坝租房网 * 丰台租房网 * 西城租房网 * 密云租房网 * 朝阳租房网 * 门头沟租房网 * 北京周边租房网 * 延庆租房网 * 大兴租房网 * 房山租房网 * 怀柔租房网 * 不老屯租房网 * 密云城区租房网 * 密云水库别墅区租房网 * 密云周边租房网 * 溪翁庄租房网 * 城子街道租房网 * 大峪租房网 * 东辛房租房网 * 军庄租房网 * 龙泉租房网 * 门头沟周边租房网 * 保定租房网 * 八达岭租房网 * 渤海镇租房网 * 白广路租房网 * 磁各庄租房网 * 北大地租房网 * CBD租房网 * 长阳租房网 * 梧州租房 * 杞县租房 * 邵阳租房 * 黄骅租房 * 淮安租房 * 梧州出租 * 杞县出租 * 邵阳出租 * 黄骅出租 * 淮安出租 * 梧州整租房 * 杞县整租房 * 邵阳整租房 * 黄骅整租房 * 淮安整租房 * 梧州合租房 * 杞县合租房 * 邵阳合租房 * 黄骅合租房 * 淮安合租房 * 梧州个人 * 杞县个人 * 邵阳个人 * 黄骅个人 * 淮安个人 * 丰台租房 * 西城租房 * 密云租房 * 朝阳租房 * 门头沟租房 * 丰台出租 * 西城出租 * 密云出租 * 朝阳出租 * 门头沟出租 * 丰台整租房 * 西城整租房 * 密云整租房 * 朝阳整租房 * 门头沟整租房 * 丰台合租房 * 西城合租房 * 密云合租房 * 朝阳合租房 * 门头沟合租房 * 北京别墅租房 * 北京公寓租房 * 北京公租房租房 * 北京500元左右租房 * 北京10平米租房 * 北京50平米租房 * 北京60平米租房 * 北京120平米租房 * 北京150平米租房 * 北京交通便利租房 * 北京商场附近租房 * 北京公园附近租房 * 北京拎包入住租房 * 北京幼儿园附近租房 * 北京小学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?</x:v>
+        <x:v>未发现该小区明确的租房风险或差评信息。</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>价格线索：东馨园 1998年竣工 距离1644m 56908 元/㎡；OMA 2008年竣工 距离3917m 62225 元/㎡；冬晴园 2008年竣工 距离2157m 66100 元/㎡；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；光明胡同 可注册办公首次出租南北通透 180000 元/月；房屋质量/户型线索：去APP体验 # 兰园小区 海淀 马连洼 圆明园西路 * 16号线等 * 五六环之间 * 小户型居多 * 配套齐全 收藏 56175 _元/㎡_ 6月挂牌均价23 _套_ 在售房源180 _套_ 在租房源 估价 6.9 小区评分 地段交通 8.2 生活配套 6.0 居住品质 6.0 小区评测 小区距离马连洼地铁站较近，居民轨交出行便利；；小区于1999年建成，房龄较老；；查看完整评测 基本信息查看更多 * 竣工时间 1997年 * 物业类型 住宅 * 所属商圈 马连洼 * 开发商 上海凯邦实业有限公司 * 物业公司 实创物业管理公司 基础信息 * 小区名称 兰园小区 * 物业类型 住宅 * 竣工时间 1997年 * 绿化率 30.0% * 容积率 1.90 * 建筑面积 暂无 * 总户数 1724户 * 小区地址 圆明园西路 * 所属商圈 马连洼 物业信息 * 停车位 0 * 物业费 0.90元/平米/月 * 物业公司 实创物业管理公司 * 开发商 上海凯邦实业有限公司 小区概况 兰园小区位于海淀区马连洼板块，于1999年建成，房龄较老。；小区楼栋共26栋左右，占地面积约100000㎡，建筑面积约180000㎡，容积率1.9左右，小区户型面积有51㎡-97㎡左右的1-3居室。；完成 周边配套 兰园小区 圆明园西路 地铁 公交 学校 餐饮 购物 二手房 租房 出门地铁，精装修三居，南北通透，明厨明卫，看房随时 马连洼 兰园小区 560 万 3室1厅 90.54㎡ 马连洼地铁旁，南北精装修，看房方便，前后无遮挡 马连洼 兰园小区 499 万 3室1厅 81.11㎡ 新增！；生活便利线索：安居客小区频道，提供兰园小区二手房,平均房价56175元/平米,找兰园小区二手房，兰园小区租房，兰园小区房价走势、实景图、房型图、周边交通配套信息就上安居客。；去APP体验 # 兰园小区 海淀 马连洼 圆明园西路 * 16号线等 * 五六环之间 * 小户型居多 * 配套齐全 收藏 56175 _元/㎡_ 6月挂牌均价23 _套_ 在售房源180 _套_ 在租房源 估价 6.9 小区评分 地段交通 8.2 生活配套 6.0 居住品质 6.0 小区评测 小区距离马连洼地铁站较近，居民轨交出行便利；；小区距离马连洼地铁站约273m，地铁16号线途经该站点，居民轨交出行便利；；距离百旺家苑公交站约571m，518路、651路、932路等公交在该站点停靠，居民乘坐公交出行较为便利；；完成 周边配套 兰园小区 圆明园西路 地铁 公交 学校 餐饮 购物 二手房 租房 出门地铁，精装修三居，南北通透，明厨明卫，看房随时 马连洼 兰园小区 560 万 3室1厅 90.54㎡ 马连洼地铁旁，南北精装修，看房方便，前后无遮挡 马连洼 兰园小区 499 万 3室1厅 81.11㎡ 新增！；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可��册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。；手机版： 新发地租房信息 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安溪租房网 * 桂林租房网 * 黔东南租房网 * 海口租房网 * 钟祥租房网 * 常德租房网 * 抚顺租房网 * 呼伦贝尔租房网 * 大同租房网 * 阿坝租房网 * 丰台租房网 * 西城租房网 * 密云租房网 * 朝阳租房网 * 门头沟租房网 * 北京周边租房网 * 延庆租房网 * 大兴租房网 * 房山租房网 * 怀柔租房网 * 不老屯租房网 * 密云城区租房网 * 密云水库别墅区租房网 * 密云周边租房网 * 溪翁庄租房网 * 城子街道租房网 * 大峪租房网 * 东辛房租房网 * 军庄租房网 * 龙泉租房网 * 门头沟周边租房网 * 保定租房网 * 八达岭租房网 * 渤海镇租房网 * 白广路租房网 * 磁各庄租房网 * 北大地租房网 * CBD租房网 * 长阳租房网 * 梧州租房 * 杞县租房 * 邵阳租房 * 黄骅租房 * 淮安租房 * 梧州出租 * 杞县出租 * 邵阳出租 * 黄骅出租 * 淮安出租 * 梧州整租房 * 杞县整租房 * 邵阳整租房 * 黄骅整租房 * 淮安整租房 * 梧州合租房 * 杞县合租房 * 邵阳合租房 * 黄骅合租房 * 淮安合租房 * 梧州个人 * 杞县个人 * 邵阳个人 * 黄骅个人 * 淮安个人 * 丰台租房 * 西城租房 * 密云租房 * 朝阳租房 * 门头沟租房 * 丰台出租 * 西城出租 * 密云出租 * 朝阳出租 * 门头沟出租 * 丰台整租房 * 西城整租房 * 密云整租房 * 朝阳整租房 * 门头沟整租房 * 丰台合租房 * 西城合租房 * 密云合租房 * 朝阳合租房 * 门头沟合租房 * 北京别墅租房 * 北京公寓租房 * 北京公租房租房 * 北京500元左右租房 * 北京10平米租房 * 北京50平米租房 * 北京60平米租房 * 北京120平米租房 * 北京150平米租房 * 北京交通便利租房 * 北京商场附近租房 * 北京公园附近租房 * 北京拎包入住租房 * 北京幼儿园附近租房 * 北京小学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：区兰园小区租房月租：1室1厅约5200-5700元/月；，2室1厅约6000元/月；房屋质量/户型线索：海淀区兰园小区租房月租：1室1厅约5200-5700元/月，2室1厅约6000元/月，均为精装修，押一付三，中介费1个月租金。；房子质量：房龄较低，装修为精装修；；户型以1室1厅、2室1厅为主，朝向多为南或南北通透；；物业未明确提及具体评价，但小区绿化率高，环境安静舒适；；隔音方面，搜索结果中暂无针对该小区隔音的明确评价（注意：义乌、杭州同名兰园小区有提到隔音好，但非目标小区）。；生活便利线索：生活便利程度：地铁方面，步行至16号线马连洼站约247-407米，通勤便利；；商超有天喜百旺超市、中发百旺商城等；；医院有解放军总医院第八医学中心；；餐饮配套丰富，周边餐饮选择多；；风险线索：未发现该小区明确的租房风险或差评信息。</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>1. 兰园小区,圆明园西路-北京兰园小区二手房、租房、房价-北京安居客 https://m.anjuke.com/bj/community/849661/
-2. 【北京kok官方体育app下载iossoo8.top租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kwkok%E5%AE%98%E6%96%B9%E4%BD%93%E8%82%B2app%E4%B8%8B%E8%BD%BDiossoo8.top?37%20target=_blank
-3. 來自【591租金行情】 https://rent.591.com.tw/market/community?community_id=15193&amp;pattern=four-bedroom-plus&amp;itm_source=rent&amp;itm_medium=detail&amp;itm_campaign=market_trend
-4. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-5. 新发地房屋出租信息_北京丰台新发地出租房源信息-58出租网 http://mob.58.com/zf/hz/cz-xinfadi/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4585267493772291-3/
+2. http://m.anjuke.com/ch/rent/4569831888462858-3/
+3. http://m.anjuke.com/bj/rent/4568757887362048-3/
+4. 急租！兰园温馨一居 干净整洁 通勤方便 价格可谈 http://m.anjuke.com/bj/rent/4585267493772291-3/
+5. 16号线药植所马连洼地铁边兰园小区精装全南向大一居出租 http://m.anjuke.com/ch/rent/4569831888462858-3/
+6. 绿城义乌兰园优点、不足，绿城义乌兰园怎么样，绿城义乌兰园周边房产中介经纪人评价-义乌安居客 http://m.anjuke.com/yw/community/1315371/jiedu/
+7. 租金可谈 马连洼地铁站 兰园二层2居出租 南北双阳台 可长租 http://m.anjuke.com/bj/rent/4568757887362048-3/
+8. 绿城兰园(商住楼)优点、不足，绿城兰园(商住楼)怎么样，绿城兰园(商住楼)周边房产中介经纪人评价-杭州安居客 http://m.anjuke.com/hz/community/880190/jiedu/</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -899,40 +934,42 @@
         <x:v>北京市海淀区后厂村路102号</x:v>
       </x:c>
       <x:c r="E15" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F15" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G15" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H15" t="n">
-        <x:v>4</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I15" t="str">
-        <x:v>缺乏该小区针对性的有效信息，搜索结果多为无关的高端住宅，建议实地考察。</x:v>
+        <x:v>紧邻大厂园区，通勤极便，物业管理规范，适合在后厂村工作的租客合租或整租。</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；光明胡同 可注册办公首次出租南北通透 180000 元/月；簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月；东四三条 可注册办公首次出租南北通透 300000 元/月；后小井胡同 可注册办公首次出租南北通透 60000 元/月</x:v>
+        <x:v>海淀区景和园租房：合租（20平）2500元/月；整租（90平）8000元/月</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；) 北京房产网&gt;北京租房网&gt; 北京160平米租房&gt; 海淀160平米租房&gt; 四季青160平米租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * 拖市 * 蒋场 * 胡市 * 佛子山 * 麻洋 * 干驿 * 渔薪 * 皂市 * 天门周边 * 云阳 * 丰都 * 彭水 * 忠县 * 秀山 * 黔江 * 武隆 * 巫山 * 石柱 * 酉阳 * 城口 * 巫溪 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 * W * 万福隆 # 为您找到以下 "160平米" 租房房源 该条件下房源较少，为您推荐： * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 4600 元马家堡嘉园二里高楼层2居室 2室1厅 / 56.92㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 1000 元大兴 1室1厅1卫 1室1厅 / 25㎡ 推荐理由： * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 6600 元我爱我家相寓 西直门交大东路19号院高楼层2居室 2室1厅 / 53.2㎡ 推荐理由： 邻地铁 精装修 * 2500 元温都水城 朝南大复式押一付一 TBD云集中心 平西府地铁站 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元我爱我家相寓 安贞安贞里二区高楼层3居室次卧1 3室1厅 / 12.0㎡ 推荐理由： 邻地铁 精装修 * 2500 元惠新西街中直5号院高楼层3居室次卧2 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 1868 元宋家庄榴景秀苑低楼层3居室次卧1 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 * 5700 元我爱我家相寓 石佛营东风苑小区低楼层1居室 1室1厅 / 55.12㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 8500 元(可以搬家保洁)（周边方便）（业主人好）（高层） 1室1厅 / 76.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1300 元出租南邵地铁站500米合租北次，随时入住看房 3室0厅 / 15㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4100 元我爱我家相寓 角门角门东里低楼层1居室 1室1厅 / 40.8㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4800 元整租龙泽新龙城二期1室1厅 1室1厅 / 54.43㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元幸福时光(通州) 2室1厅1卫 2室1厅 / 89.96㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 5800 元整租木樨地白云观南里2室1厅 2室1厅 / 53.3㎡ 推荐理由： 邻地铁 精装修 * 2400 元实拍 次渠京东班车 民水民电 物业直签0中介费 一二三居都有 1室1厅 / 50㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5900 元新出，丽新嘉园东区 南向一居随时入住 1室1厅 / 65㎡ 推荐理由： 独卫一居 邻��铁 精装修 随时看房 * 8800 元正南 1室1厅 金石美苑 1室1厅 / 72.0㎡ 推荐理由： 独卫一居 邻地铁 * 5600 元整租马家堡福海棠2室1厅 2室1厅 / 74.29㎡ 推荐理由： 精装修 * 5500 元整租北工大松榆东里1室1厅 1室1厅 / 63.88㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 6175 元我爱我家相寓 东大桥芳草地西街中楼层2居室 2室1厅 / 47.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 1000 元西山口村住房 1室0厅1卫 1室0厅 / 25㎡ 推荐理由： 邻地铁 押一付一 * 3000 元我爱我家相寓 惠新西街安苑里中楼层3居室主卧 3室1厅 / 18.0㎡ 推荐理由： 邻地铁 * 2300 元中关村壹号 用友 中关村软件园永旺家园主卧出租价格2300 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 南北通透 * 6800 元整租回龙观国仕汇3室1厅 3室1厅 / 120.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 2100 元北京城建北京密码(东区) 2室1厅1卫 2室1厅 / 57㎡ 推荐理由： 配套齐全 * 800 元辛力庄村住房 1室0厅1卫 1室0厅 / 20㎡ 推荐理由： 押一付一 配套齐全 精装修 首次出租 * 4600 元急租成寿寺地铁口恒悦城南向大开间家电齐全随时看房 1室0厅 / 48㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 5500 元整租劲松劲松八区2室1厅 2室1厅 / 69.28㎡ 推荐理由： 邻地铁 配套齐全 精装修 # 四季青租房房产中介 * 康涛 怡家（北京）住房租赁有限公司 * 于成 北京首嘉房住房租赁有限公司 * 田田 北京天通伟业房地产经纪有限公司 * 初金波 北京麦田房产经纪有限公司 * 周建宇 北京云帆温居住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 王英辉 北京金城阜业房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 常利 北京中世禾房地产经纪有限公司 * 姚景昱 北京欢颜住房租赁有限公司 ## 租房房产问答 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；* 初娟娟： 您好密云这边租房子物业费和暖气费都需要自己交，物业费2.36元每平米 * 问 租房能办居住证吗 * 9mD9xD9： 你好，租房可以办理居住证。</x:v>
+        <x:v>海淀区景和园租房：合租（20平）2500元/月（押一付一，0佣金，民水民电，包物业取暖）；；海淀区景和园：房龄相关未明确，装修为精装修，户型方正/南北通透；；物业方面有全天保安巡逻，维修/保洁有专人负责；；隔音信息未提及，物业费包含在租金中；</x:v>
       </x:c>
       <x:c r="L15" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；) 北京房产网&gt;北京租房网&gt; 北京160平米租房&gt; 海淀160平米租房&gt; 四季青160平米租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * 拖市 * 蒋场 * 胡市 * 佛子山 * 麻洋 * 干驿 * 渔薪 * 皂市 * 天门周边 * 云阳 * 丰都 * 彭水 * 忠县 * 秀山 * 黔江 * 武隆 * 巫山 * 石柱 * 酉阳 * 城口 * 巫溪 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 * W * 万福隆 # 为您找到以下 "160平米" 租房房源 该条件下房源较少，为您推荐： * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 4600 元马家堡嘉园二里高楼层2居室 2室1厅 / 56.92㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 1000 元大兴 1室1厅1卫 1室1厅 / 25㎡ 推荐理由： * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 6600 元我爱我家相寓 西直门交大东路19号院高楼层2居室 2室1厅 / 53.2㎡ 推荐理由： 邻地铁 精装修 * 2500 元温都水城 朝南大复式押一付一 TBD云集中心 平西府地铁站 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元我爱我家相寓 安贞安贞里二区高楼层3居室次卧1 3室1厅 / 12.0㎡ 推荐理由： 邻地铁 精装修 * 2500 元惠新西街中直5号院高楼层3居室次卧2 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 1868 元宋家庄榴景秀苑低楼层3居室次卧1 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 * 5700 元我爱我家相寓 石佛营东风苑小区低楼层1居室 1室1厅 / 55.12㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 8500 元(可以搬家保洁)（周边方便）（业主人好）（高层） 1室1厅 / 76.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1300 元出租南邵地铁站500米合租北次，随时入住看房 3室0厅 / 15㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4100 元我爱我家相寓 角门角门东里低楼层1居室 1室1厅 / 40.8㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4800 元整租龙泽新龙城二期1室1厅 1室1厅 / 54.43㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元幸福时光(通州) 2室1厅1卫 2室1厅 / 89.96㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 5800 元整租木樨地白云观南里2室1厅 2室1厅 / 53.3㎡ 推荐理由： 邻地铁 精装修 * 2400 元实拍 次渠京东班车 民水民电 物业直签0中介费 一二三居都有 1室1厅 / 50㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5900 元新出，丽新嘉园东区 南向一居随时入住 1室1厅 / 65㎡ 推荐理由： 独卫一居 邻��铁 精装修 随时看房 * 8800 元正南 1室1厅 金石美苑 1室1厅 / 72.0㎡ 推荐理由： 独卫一居 邻地铁 * 5600 元整租马家堡福海棠2室1厅 2室1厅 / 74.29㎡ 推荐理由： 精装修 * 5500 元整租北工大松榆东里1室1厅 1室1厅 / 63.88㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 6175 元我爱我家相寓 东大桥芳草地西街中楼层2居室 2室1厅 / 47.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 1000 元西山口村住房 1室0厅1卫 1室0厅 / 25㎡ 推荐理由： 邻地铁 押一付一 * 3000 元我爱我家相寓 惠新西街安苑里中楼层3居室主卧 3室1厅 / 18.0㎡ 推荐理由： 邻地铁 * 2300 元中关村壹号 用友 中关村软件园永旺家园主卧出租价格2300 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 南北通透 * 6800 元整租回龙观国仕汇3室1厅 3室1厅 / 120.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 2100 元北京城建北京密码(东区) 2室1厅1卫 2室1厅 / 57㎡ 推荐理由： 配套齐全 * 800 元辛力庄村住房 1室0厅1卫 1室0厅 / 20㎡ 推荐理由： 押一付一 配套齐全 精装修 首次出租 * 4600 元急租成寿寺地铁口恒悦城南向大开间家电齐全随时看房 1室0厅 / 48㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 5500 元整租劲松劲松八区2室1厅 2室1厅 / 69.28㎡ 推荐理由： 邻地铁 配套齐全 精装修 # 四季青租房房产中介 * 康涛 怡家（北京）住房租赁有限公司 * 于成 北京首嘉房住房租赁有限公司 * 田田 北京天通伟业房地产经纪有限公司 * 初金波 北京麦田房产经纪有限公司 * 周建宇 北京云帆温居住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 王英辉 北京金城阜业房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 常利 北京中世禾房地产经纪有限公司 * 姚景昱 北京欢颜住房租赁有限公司 ## 租房房产问答 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；手机版： 四季青160平米租房 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安阳租房网 * 肇东租房网 * 张家界租房网 * 长岭租房网 * 微山租房网 * 东平租房网 * 太原租房网 * 定边租房网 * 昆明租房网 * 怒江租房网 * 西城租房网 * 怀柔租房网 * 朝阳租房网 * 门头沟租房网 * 平谷租房网 * 海淀租房网 * 大兴租房网 * 房山租房网 * 通州租房网 * 昌平租房网 * CBD租房网 * 安慧桥租房网 * 安贞租房网 * 奥林匹克公园租房网 * 百子湾租房网 * 八里庄租房网 * 北沙滩租房网 * 北苑租房网 * 常营租房网 * 朝青板块租房网 * 朝外大街租房网 * 磁各庄租房网 * 八里桥租房网 * 渤海镇租房网 * 安宁庄租房网 * 滨河路租房网 * 城子街道租房网 * 长阳租房网 * 百善租房网 * 白广路租房网 * 巢湖租房 * 嘉峪关租房 * 平顶山租房 * 沧州租房 * 阿克苏租房 * 巢湖出租 * 嘉峪关出租 * 平顶山出租 * 沧州出租 * 阿克苏出租 * 巢湖整租房 * 嘉峪关整租房 * 平顶山整租房 * 沧州整租房 * 阿克苏整租房 * 巢湖合租房 * 嘉峪关合租房 * 平顶山合租房 * 沧州合租房 * 阿克苏合租房 * 巢湖个人 * 嘉峪关个人 * 平顶山个人 * 沧州个人 * 阿克苏个人 * 西城租房 * 怀柔租房 * 朝阳租房 * 门头沟租房 * 平谷租房 * 西城出租 * 怀柔出租 * 朝阳出租 * 门头沟出租 * 平谷出租 * 西城整租房 * 怀柔整租房 * 朝阳整租房 * 门头沟整租房 * 平谷整租房 * 西城合租房 * 怀柔合租房 * 朝阳合租房 * 门头沟合租房 * 平谷合租房 * 北京一室一厅租房 * 北京两室一厅租房 * 北京两室一卫租房 * 北京四室两厅租房 * 北京五室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京190平米租房 * 北京商场附近租房 * 北京学校附近租房 * 北京新小区租房 * 北京幼儿园附近租房 * 北京小学附近租房 * 北京大学附近租房 * 北京整租租房。</x:v>
-      </x:c>
-      <x:c r="M15" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>海淀区景和园：临近16号线西北旺站（步行715米），周边有公交；；距百度科技园、联想总部近，通勤便利；；有超市便利店满足日常；；周边有公园，医疗未明确提及；</x:v>
+      </x:c>
+      <x:c r="M15" t="str"/>
       <x:c r="N15" t="str">
-        <x:v>价格线索：-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；光明胡同 可注册办公首次出租南北通透 180000 元/月；簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月；东四三条 可注册办公首次出租南北通透 300000 元/月；后小井胡同 可注册办公首次出租南北通透 60000 元/月；房屋质量/户型线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；) 北京房产网&gt;北京租房网&gt; 北京160平米租房&gt; 海淀160平米租房&gt; 四季青160平米租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * 拖市 * 蒋场 * 胡市 * 佛子山 * 麻洋 * 干驿 * 渔薪 * 皂市 * 天门周边 * 云阳 * 丰都 * 彭水 * 忠县 * 秀山 * 黔江 * 武隆 * 巫山 * 石柱 * 酉阳 * 城口 * 巫溪 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 * W * 万福隆 # 为您找到以下 "160平米" 租房房源 该条件下房源较少，为您推荐： * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 4600 元马家堡嘉园二里高楼层2居室 2室1厅 / 56.92㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 1000 元大兴 1室1厅1卫 1室1厅 / 25㎡ 推荐理由： * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 6600 元我爱我家相寓 西直门交大东路19号院高楼层2居室 2室1厅 / 53.2㎡ 推荐理由： 邻地铁 精装修 * 2500 元温都水城 朝南大复式押一付一 TBD云集中心 平西府地铁站 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元我爱我家相寓 安贞安贞里二区高楼层3居室次卧1 3室1厅 / 12.0㎡ 推荐理由： 邻地铁 精装修 * 2500 元惠新西街中直5号院高楼层3居室次卧2 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 1868 元宋家庄榴景秀苑低楼层3居室次卧1 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 * 5700 元我爱我家相寓 石佛营东风苑小区低楼层1居室 1室1厅 / 55.12㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 8500 元(可以搬家保洁)（周边方便）（业主人好）（高层） 1室1厅 / 76.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1300 元出租南邵地铁站500米合租北次，随时入住看房 3室0厅 / 15㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4100 元我爱我家相寓 角门角门东里低楼层1居室 1室1厅 / 40.8㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4800 元整租龙泽新龙城二期1室1厅 1室1厅 / 54.43㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元幸福时光(通州) 2室1厅1卫 2室1厅 / 89.96㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 5800 元整租木樨地白云观南里2室1厅 2室1厅 / 53.3㎡ 推荐理由： 邻地铁 精装修 * 2400 元实拍 次渠京东班车 民水民电 物业直签0中介费 一二三居都有 1室1厅 / 50㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5900 元新出，丽新嘉园东区 南向一居随时入住 1室1厅 / 65㎡ 推荐理由： 独卫一居 邻��铁 精装修 随时看房 * 8800 元正南 1室1厅 金石美苑 1室1厅 / 72.0㎡ 推荐理由： 独卫一居 邻地铁 * 5600 元整租马家堡福海棠2室1厅 2室1厅 / 74.29㎡ 推荐理由： 精装修 * 5500 元整租北工大松榆东里1室1厅 1室1厅 / 63.88㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 6175 元我爱我家相寓 东大桥芳草地西街中楼层2居室 2室1厅 / 47.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 1000 元西山口村住房 1室0厅1卫 1室0厅 / 25㎡ 推荐理由： 邻地铁 押一付一 * 3000 元我爱我家相寓 惠新西街安苑里中楼层3居室主卧 3室1厅 / 18.0㎡ 推荐理由： 邻地铁 * 2300 元中关村壹号 用友 中关村软件园永旺家园主卧出租价格2300 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 南北通透 * 6800 元整租回龙观国仕汇3室1厅 3室1厅 / 120.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 2100 元北京城建北京密码(东区) 2室1厅1卫 2室1厅 / 57㎡ 推荐理由： 配套齐全 * 800 元辛力庄村住房 1室0厅1卫 1室0厅 / 20㎡ 推荐理由： 押一付一 配套齐全 精装修 首次出租 * 4600 元急租成寿寺地铁口恒悦城南向大开间家电齐全随时看房 1室0厅 / 48㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 5500 元整租劲松劲松八区2室1厅 2室1厅 / 69.28㎡ 推荐理由： 邻地铁 配套齐全 精装修 # 四季青租房房产中介 * 康涛 怡家（北京）住房租赁有限公司 * 于成 北京首嘉房住房租赁有限公司 * 田田 北京天通伟业房地产经纪有限公司 * 初金波 北京麦田房产经纪有限公司 * 周建宇 北京云帆温居住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 王英辉 北京金城阜业房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 常利 北京中世禾房地产经纪有限公司 * 姚景昱 北京欢颜住房租赁有限公司 ## 租房房产问答 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；* 初娟娟： 您好密云这边租房子物业费和暖气费都需要自己交，物业费2.36元每平米 * 问 租房能办居住证吗 * 9mD9xD9： 你好，租房可以办理居住证。；生活便利线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；) 北京房产网&gt;北京租房网&gt; 北京160平米租房&gt; 海淀160平米租房&gt; 四季青160平米租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * 拖市 * 蒋场 * 胡市 * 佛子山 * 麻洋 * 干驿 * 渔薪 * 皂市 * 天门周边 * 云阳 * 丰都 * 彭水 * 忠县 * 秀山 * 黔江 * 武隆 * 巫山 * 石柱 * 酉阳 * 城口 * 巫溪 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 * W * 万福隆 # 为您找到以下 "160平米" 租房房源 该条件下房源较少，为您推荐： * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 4600 元马家堡嘉园二里高楼层2居室 2室1厅 / 56.92㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 1000 元大兴 1室1厅1卫 1室1厅 / 25㎡ 推荐理由： * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 6600 元我爱我家相寓 西直门交大东路19号院高楼层2居室 2室1厅 / 53.2㎡ 推荐理由： 邻地铁 精装修 * 2500 元温都水城 朝南大复式押一付一 TBD云集中心 平西府地铁站 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元我爱我家相寓 安贞安贞里二区高楼层3居室次卧1 3室1厅 / 12.0㎡ 推荐理由： 邻地铁 精装修 * 2500 元惠新西街中直5号院高楼层3居室次卧2 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 1868 元宋家庄榴景秀苑低楼层3居室次卧1 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 * 5700 元我爱我家相寓 石佛营东风苑小区低楼层1居室 1室1厅 / 55.12㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 8500 元(可以搬家保洁)（周边方便）（业主人好）（高层） 1室1厅 / 76.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1300 元出租南邵地铁站500米合租北次，随时入住看房 3室0厅 / 15㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4100 元我爱我家相寓 角门角门东里低楼层1居室 1室1厅 / 40.8㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4800 元整租龙泽新龙城二期1室1厅 1室1厅 / 54.43㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元幸福时光(通州) 2室1厅1卫 2室1厅 / 89.96㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 5800 元整租木樨地白云观南里2室1厅 2室1厅 / 53.3㎡ 推荐理由： 邻地铁 精装修 * 2400 元实拍 次渠京东班车 民水民电 物业直签0中介费 一二三居都有 1室1厅 / 50㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5900 元新出，丽新嘉园东区 南向一居随时入住 1室1厅 / 65㎡ 推荐理由： 独卫一居 邻��铁 精装修 随时看房 * 8800 元正南 1室1厅 金石美苑 1室1厅 / 72.0㎡ 推荐理由： 独卫一居 邻地铁 * 5600 元整租马家堡福海棠2室1厅 2室1厅 / 74.29㎡ 推荐理由： 精装修 * 5500 元整租北工大松榆东里1室1厅 1室1厅 / 63.88㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 6175 元我爱我家相寓 东大桥芳草地西街中楼层2居室 2室1厅 / 47.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 1000 元西山口村住房 1室0厅1卫 1室0厅 / 25㎡ 推荐理由： 邻地铁 押一付一 * 3000 元我爱我家相寓 惠新西街安苑里中楼层3居室主卧 3室1厅 / 18.0㎡ 推荐理由： 邻地铁 * 2300 元中关村壹号 用友 中关村软件园永旺家园主卧出租价格2300 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 南北通透 * 6800 元整租回龙观国仕汇3室1厅 3室1厅 / 120.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 2100 元北京城建北京密码(东区) 2室1厅1卫 2室1厅 / 57㎡ 推荐理由： 配套齐全 * 800 元辛力庄村住房 1室0厅1卫 1室0厅 / 20㎡ 推荐理由： 押一付一 配套齐全 精装修 首次出租 * 4600 元急租成寿寺地铁口恒悦城南向大开间家电齐全随时看房 1室0厅 / 48㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 5500 元整租劲松劲松八区2室1厅 2室1厅 / 69.28㎡ 推荐理由： 邻地铁 配套齐全 精装修 # 四季青租房房产中介 * 康涛 怡家（北京）住房租赁有限公司 * 于成 北京首嘉房住房租赁有限公司 * 田田 北京天通伟业房地产经纪有限公司 * 初金波 北京麦田房产经纪有限公司 * 周建宇 北京云帆温居住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 王英辉 北京金城阜业房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 常利 北京中世禾房地产经纪有限公司 * 姚景昱 北京欢颜住房租赁有限公司 ## 租房房产问答 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；手机版： 四季青160平米租房 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安阳租房网 * 肇东租房网 * 张家界租房网 * 长岭租房网 * 微山租房网 * 东平租房网 * 太原租房网 * 定边租房网 * 昆明租房网 * 怒江租房网 * 西城租房网 * 怀柔租房网 * 朝阳租房网 * 门头沟租房网 * 平谷租房网 * 海淀租房网 * 大兴租房网 * 房山租房网 * 通州租房网 * 昌平租房网 * CBD租房网 * 安慧桥租房网 * 安贞租房网 * 奥林匹克公园租房网 * 百子湾租房网 * 八里庄租房网 * 北沙滩租房网 * 北苑租房网 * 常营租房网 * 朝青板块租房网 * 朝外大街租房网 * 磁各庄租房网 * 八里桥租房网 * 渤海镇租房网 * 安宁庄租房网 * 滨河路租房网 * 城子街道租房网 * 长阳租房网 * 百善租房网 * 白广路租房网 * 巢湖租房 * 嘉峪关租房 * 平顶山租房 * 沧州租房 * 阿克苏租房 * 巢湖出租 * 嘉峪关出租 * 平顶山出租 * 沧州出租 * 阿克苏出租 * 巢湖整租房 * 嘉峪关整租房 * 平顶山整租房 * 沧州整租房 * 阿克苏整租房 * 巢湖合租房 * 嘉峪关合租房 * 平顶山合租房 * 沧州合租房 * 阿克苏合租房 * 巢湖个人 * 嘉峪关个人 * 平顶山个人 * 沧州个人 * 阿克苏个人 * 西城租房 * 怀柔租房 * 朝阳租房 * 门头沟租房 * 平谷租房 * 西城出租 * 怀柔出租 * 朝阳出租 * 门头沟出租 * 平谷出租 * 西城整租房 * 怀柔整租房 * 朝阳整租房 * 门头沟整租房 * 平谷整租房 * 西城合租房 * 怀柔合租房 * 朝阳合租房 * 门头沟合租房 * 平谷合租房 * 北京一室一厅租房 * 北京两室一厅租房 * 北京两室一卫租房 * 北京四室两厅租房 * 北京五室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京190平米租房 * 北京商场附近租房 * 北京学校附近租房 * 北京新小区租房 * 北京幼儿园附近租房 * 北京小学附近租房 * 北京大学附近租房 * 北京整租租房。；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：海淀区景和园租房：合租（20平）2500元/月；整租（90平）8000元/月；房屋质量/户型线索：海淀区景和园租房：合租（20平）2500元/月（押一付一，0佣金，民水民电，包物业取暖）；；海淀区景和园：房龄相关未明确，装修为精装修，户型方正/南北通透；；物业方面有全天保安巡逻，维修/保洁有专人负责；；隔音信息未提及，物业费包含在租金中；；生活便利线索：海淀区景和园：临近16号线西北旺站（步行715米），周边有公交；；距百度科技园、联想总部近，通勤便利；；有超市便利店满足日常；；周边有公园，医疗未明确提及；</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>1. 【北京pa视讯wa48.cc租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kwPA%E8%A7%86%E8%AE%AFwa48.cc?196%20target=_blank
-2. 四季青160平米租房_北京海淀四季青160平米房屋出租-北京58同城 http://mob.58.com/zf/tm/ssc-48/sijiqinghd/
-3. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-4. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml</x:v>
+        <x:v>1. https://bj.zu.anjuke.com/fangyuan/3440494560894977
+2. http://m.anjuke.com/bj/rent/4561883669830669-3
+3. http://m.anjuke.com/bj/rent/4591387059151872-3
+4. 实图实价景和园 干净整洁 后厂村路 百度科技园 联想总部月付 https://bj.zu.anjuke.com/fangyuan/3440494560894977
+5. 整租 东坝南金隅景和园六区全南两居室 电梯房集中供暖 随时看 http://m.anjuke.com/bj/rent/4605294028610562-3/
+6. 后厂村路景和园 主卧阳台 联想大厦 网易 百度科技园 http://m.anjuke.com/bj/rent/4561883669830669-3/
+7. 朝阳 东坝南3号线 金隅佳品 景和园七区北向次卧现房出租 http://m.anjuke.com/bj/rent/4603597746611207-3/
+8. 西北旺地铁站 后厂村景和园精装三居 业主人好说话 干净整洁 http://m.anjuke.com/bj/rent/4591387059151872-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -949,39 +986,43 @@
         <x:v>北京市海淀区马连洼街道西北旺东路9号</x:v>
       </x:c>
       <x:c r="E16" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F16" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G16" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H16" t="n">
-        <x:v>4</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I16" t="str">
-        <x:v>现有证据被大量无关豪宅信息干扰，缺乏真实租金与品质参考，评分较为保守。</x:v>
+        <x:v>房龄适中且绿化好，邻近万象汇商圈，生活便利度高，是后厂村周边的稳健选择。</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；胡同小区 可注册办公首次出租南北通透 250000 元/月；刹海四合院 可注册办公首次出租南北通透 83333 元/月；镇江胡同 可注册办公首次出租南北通透 140000 元/月；07㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月</x:v>
+        <x:v>整租：1室5300-5800元/月；、2室6800-7500元/月；、3室7500-8000元/月；合租单间约3500元/月</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 ) 南北通透国锐金嵿5室2厅精装修 整租|5室2厅|277㎡|朝南北 大兴-亦庄-国锐金嵿 30000 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 携程酒店-北京春晖园温泉度假酒店预订-北京春晖园温泉度假酒店价格、点评、电话、地址查询-【携程旅行手机版】   房型 点评 亮点 设施 周边 政策 6 月 3 日 - 6 月 4 日 共1晚 1 󱠲 1 󱠱 0 󱠰 亲子酒店 酒店设有小黄鸭等主题儿童房、陪伴您的宝宝快乐成长、宝宝乐园的海洋球池、蹦床世界嗨翻一整天 详情 酒店设有小黄鸭等主题儿童房、陪伴您的宝宝快乐成长、宝宝乐园的海洋球池、蹦床世界嗨翻一整天 详情  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中 住客好评 房间挺大，设备挺好，人员服务也很热情，吃的略小贵，但是可以接受，厨艺很好，环境也不错，游乐园挺大的，推荐 1860085****2026年05月入住  查看更多 封面 精选 点评 相册  北京春晖园温泉度假酒店 2014年装修 儿童乐园 私密性好 免费停车场 室内温泉 湖景别墅 蹦床体验 管家服务 复式loft房 泳池 设施 政策  4.5 很好 1711条 “庭院里的私汤温泉泡起来舒适惬意” 距未来科学城北地铁站驾车4.1公里,约11分钟 | 顺义区高丽营镇于庄 地图 今天 6 月 3 日 - 明天 6 月 4 日 共1晚 间数人数 1 󱠲 1 󱠱 0 󱠰 酒店套餐 含早餐 立即确认 大床房 双床房 免费取消 可订 在线付款 闪住 免费Wi-Fi上网 免费有线宽带 筛选 筛选 本店销量No.1 5 度假私汤双床房 󱮔 2张1.2米单人床 50㎡ 2人入住 1-5层 6RX5KR-BRSBSW 无早餐 不可取消 含玩乐活动  温泉会单人门票 2份/天+宝宝乐园亲子票（一大一小） 1份/天+两池私汤 1份/天 立即确认 登录看低价 I95D01-BRSBSU 2份早餐 不可取消 含玩乐活动  温泉会单人门票 2份/天+宝宝乐园亲子票（一大一小） 1份/天+两池私汤 1份/天 立即确认 登录看低价 查看其他4个价格 󰠾 14 Bduck小黄鸭主题房 󱮕 1张2.4米特大床 50㎡ 2人入住 5层 7 度假私汤大床房 󱮕 1张2.4米特大床 50㎡ 2人入住 5层 7 小熊尼奥AR魔法屋 󱮕 1张2.4米特大床 50㎡ 2人入住 1-5层 5 度假私汤复式大床套房 󱮕 1张1.8米大床 75㎡ 1室1厅1卫 2人入住 6层 5 度假私汤复式双床套房 󱮕 2张1.2米单人床 75㎡ 1室1厅1卫 2人入住 6层 13 湖畔园景私汤房 󱮕 1张1.8米大床 50㎡ 2人入住 1层 11 湖畔露台私汤房 󱮕 1张1.8米大床 50㎡ 2人入住 1层 庭院景 露台 7 度假复式私汤家庭房 󱮕 1张1.8米大床 及 1张1.2米单人床 75㎡ 4人入住 6层 11 汤泉麻雀豪华套房 󱮕 1张1.8米大床 100㎡ 1室1厅2卫 2人入住 2-6层 查看其他3个房型󰠾 住客点评 4.5 很好 1711条 4.5 卫 生 4.6 环 境 4.5 服 务 4.4 设 施 由AI生成 环境 342 : 酒店环境优雅，周围景色宜人，特别是春天樱花盛开时，适合老人和亲子游。；整体环境安静，空气清新，是放松度假的好去处。</x:v>
+        <x:v>房龄约2003-2005年；；精装修为主，有电梯（部分楼层）；；物业为北京旺达家兴物业公司；；小区绿化率高、环境舒适，部分房源提到自住保养好，但未明确提及隔音情况；；户型多为南北通透或南向板楼/塔楼；</x:v>
       </x:c>
       <x:c r="L16" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；携程旅行为您提供北京春晖园温泉度假酒店预订及价格查询，涵盖北京春晖园温泉度假酒店电话、服务设施、地址交通及周边酒店信息，真实详细的北京春晖园温泉度假酒店点评、酒店图片信息，使您入住北京春晖园温泉度假酒店更放心更省心。；# 携程酒店-北京春晖园温泉度假酒店预订-北京春晖园温泉度假酒店价格、点评、电话、地址查询-【携程旅行手机版】   房型 点评 亮点 设施 周边 政策 6 月 3 日 - 6 月 4 日 共1晚 1 󱠲 1 󱠱 0 󱠰 亲子酒店 酒店设有小黄鸭等主题儿童房、陪伴您的宝宝快乐成长、宝宝乐园的海洋球池、蹦床世界嗨翻一整天 详情 酒店设有小黄鸭等主题儿童房、陪伴您的宝宝快乐成长、宝宝乐园的海洋球池、蹦床世界嗨翻一整天 详情  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中 住客好评 房间挺大，设备挺好，人员服务也很热情，吃的略小贵，但是可以接受，厨艺很好，环境也不错，游乐园挺大的，推荐 1860085****2026年05月入住  查看更多 封面 精选 点评 相册  北京春晖园温泉度假酒店 2014年装修 儿童乐园 私密性好 免费停车场 室内温泉 湖景别墅 蹦床体验 管家服务 复式loft房 泳池 设施 政策  4.5 很好 1711条 “庭院里的私汤温泉泡起来舒适惬意” 距未来科学城北地铁站驾车4.1公里,约11分钟 | 顺义区高丽营镇于庄 地图 今天 6 月 3 日 - 明天 6 月 4 日 共1晚 间数人数 1 󱠲 1 󱠱 0 󱠰 酒店套餐 含早餐 立即确认 大床房 双床房 免费取消 可订 在线付款 闪住 免费Wi-Fi上网 免费有线宽带 筛选 筛选 本店销量No.1 5 度假私汤双床房 󱮔 2张1.2米单人床 50㎡ 2人入住 1-5层 6RX5KR-BRSBSW 无早餐 不可取消 含玩乐活动  温泉会单人门票 2份/天+宝宝乐园亲子票（一大一小） 1份/天+两池私汤 1份/天 立即确认 登录看低价 I95D01-BRSBSU 2份早餐 不可取消 含玩乐活动  温泉会单人门票 2份/天+宝宝乐园亲子票（一大一小） 1份/天+两池私汤 1份/天 立即确认 登录看低价 查看其他4个价格 󰠾 14 Bduck小黄鸭主题房 󱮕 1张2.4米特大床 50㎡ 2人入住 5层 7 度假私汤大床房 󱮕 1张2.4米特大床 50㎡ 2人入住 5层 7 小熊尼奥AR魔法屋 󱮕 1张2.4米特大床 50㎡ 2人入住 1-5层 5 度假私汤复式大床套房 󱮕 1张1.8米大床 75㎡ 1室1厅1卫 2人入住 6层 5 度假私汤复式双床套房 󱮕 2张1.2米单人床 75㎡ 1室1厅1卫 2人入住 6层 13 湖畔园景私汤房 󱮕 1张1.8米大床 50㎡ 2人入住 1层 11 湖畔露台私汤房 󱮕 1张1.8米大床 50㎡ 2人入住 1层 庭院景 露台 7 度假复式私汤家庭房 󱮕 1张1.8米大床 及 1张1.2米单人床 75㎡ 4人入住 6层 11 汤泉麻雀豪华套房 󱮕 1张1.8米大床 100㎡ 1室1厅2卫 2人入住 2-6层 查看其他3个房型󰠾 住客点评 4.5 很好 1711条 4.5 卫 生 4.6 环 境 4.5 服 务 4.4 设 施 由AI生成 环境 342 : 酒店环境优雅，周围景色宜人，特别是春天樱花盛开时，适合老人和亲子游。</x:v>
+        <x:v>生活：周边有红阳阳超市、宜城生活超市，西北旺万象汇约772米；；餐饮、休闲有配套，临近中关村公园等；</x:v>
       </x:c>
       <x:c r="M16" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；在京郊的温泉主题酒店中，“春晖园”虽然春晖园略微有些老旧，但绝对是口碑最靠前的地方~ 🏨酒店：北京春晖园温泉度假酒店 📍地址：顺义高丽营镇于庄，建议自驾前往 💰价位：夏季基础房型600元，冬季基础房型1200元 我们入住过两次，一次是夏季，一次是冬季（因为抢到了便宜的房券，哈哈），正好入住的还是不同房型，来跟大家分享一下两次的入住体验（差异很大……🤔）~ 🔻夏季入住的复式大床房 也许因为夏季是淡季，我们预订的大床标间，结果被莫名其妙的升房啦，哈哈😄 复式房间的整体感觉要比最基础的房间洋气、时尚很多，贴近年轻人的审美~📷也很好看 楼上是床区域🛏️，自动窗帘遮光效果和隔音效果超棒~ 🔻冬季入住的普通标间房 今年抢到了春晖园近乎五折的房券，冬季周末750元能住个春晖园非常难得~ 双床标间比想象的大很多，还有腿部按摩椅（虽然要扫码支付）；</x:v>
+        <x:v>无明确差评或同名误命中信息，仅提示交易前需核实房源信息，部分房源信息已过期需注意。；无明确差评或同名误命中信息，仅提示交易前需核实房源信息，部分房源信息已过期需注意</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>价格线索：-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；胡同小区 可注册办公首次出租南北通透 250000 元/月；刹海四合院 可注册办公首次出租南北通透 83333 元/月；镇江胡同 可注册办公首次出租南北通透 140000 元/月；07㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月；房屋质量/户型线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 ) 南北通透国锐金嵿5室2厅精装修 整租|5室2厅|277㎡|朝南北 大兴-亦庄-国锐金嵿 30000 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 携程酒店-北京春晖园温泉度假酒店预订-北京春晖园温泉度假酒店价格、点评、电话、地址查询-【携程旅行手机版】   房型 点评 亮点 设施 周边 政策 6 月 3 日 - 6 月 4 日 共1晚 1 󱠲 1 󱠱 0 󱠰 亲子酒店 酒店设有小黄鸭等主题儿童房、陪伴您的宝宝快乐成长、宝宝乐园的海洋球池、蹦床世界嗨翻一整天 详情 酒店设有小黄鸭等主题儿童房、陪伴您的宝宝快乐成长、宝宝乐园的海洋球池、蹦床世界嗨翻一整天 详情  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中 住客好评 房间挺大，设备挺好，人员服务也很热情，吃的略小贵，但是可以接受，厨艺很好，环境也不错，游乐园挺大的，推荐 1860085****2026年05月入住  查看更多 封面 精选 点评 相册  北京春晖园温泉度假酒店 2014年装修 儿童乐园 私密性好 免费停车场 室内温泉 湖景别墅 蹦床体验 管家服务 复式loft房 泳池 设施 政策  4.5 很好 1711条 “庭院里的私汤温泉泡起来舒适惬意” 距未来科学城北地铁站驾车4.1公里,约11分钟 | 顺义区高丽营镇于庄 地图 今天 6 月 3 日 - 明天 6 月 4 日 共1晚 间数人数 1 󱠲 1 󱠱 0 󱠰 酒店套餐 含早餐 立即确认 大床房 双床房 免费取消 可订 在线付款 闪住 免费Wi-Fi上网 免费有线宽带 筛选 筛选 本店销量No.1 5 度假私汤双床房 󱮔 2张1.2米单人床 50㎡ 2人入住 1-5层 6RX5KR-BRSBSW 无早餐 不可取消 含玩乐活动  温泉会单人门票 2份/天+宝宝乐园亲子票（一大一小） 1份/天+两池私汤 1份/天 立即确认 登录看低价 I95D01-BRSBSU 2份早餐 不可取消 含玩乐活动  温泉会单人门票 2份/天+宝宝乐园亲子票（一大一小） 1份/天+两池私汤 1份/天 立即确认 登录看低价 查看其他4个价格 󰠾 14 Bduck小黄鸭主题房 󱮕 1张2.4米特大床 50㎡ 2人入住 5层 7 度假私汤大床房 󱮕 1张2.4米特大床 50㎡ 2人入住 5层 7 小熊尼奥AR魔法屋 󱮕 1张2.4米特大床 50㎡ 2人入住 1-5层 5 度假私汤复式大床套房 󱮕 1张1.8米大床 75㎡ 1室1厅1卫 2人入住 6层 5 度假私汤复式双床套房 󱮕 2张1.2米单人床 75㎡ 1室1厅1卫 2人入住 6层 13 湖畔园景私汤房 󱮕 1张1.8米大床 50㎡ 2人入住 1层 11 湖畔露台私汤房 󱮕 1张1.8米大床 50㎡ 2人入住 1层 庭院景 露台 7 度假复式私汤家庭房 󱮕 1张1.8米大床 及 1张1.2米单人床 75㎡ 4人入住 6层 11 汤泉麻雀豪华套房 󱮕 1张1.8米大床 100㎡ 1室1厅2卫 2人入住 2-6层 查看其他3个房型󰠾 住客点评 4.5 很好 1711条 4.5 卫 生 4.6 环 境 4.5 服 务 4.4 设 施 由AI生成 环境 342 : 酒店环境优雅，周围景色宜人，特别是春天樱花盛开时，适合老人和亲子游。；整体环境安静，空气清新，是放松度假的好去处。；生活便利线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；携程旅行为您提供北京春晖园温泉度假酒店预订及价格查询，涵盖北京春晖园温泉度假酒店电话、服务设施、地址交通及周边酒店信息，真实详细的北京春晖园温泉度假酒店点评、酒店图片信息，使您入住北京春晖园温泉度假酒店更放心更省心。；# 携程酒店-北京春晖园温泉度假酒店预订-北京春晖园温泉度假酒店价格、点评、电话、地址查询-【携程旅行手机版】   房型 点评 亮点 设施 周边 政策 6 月 3 日 - 6 月 4 日 共1晚 1 󱠲 1 󱠱 0 󱠰 亲子酒店 酒店设有小黄鸭等主题儿童房、陪伴您的宝宝快乐成长、宝宝乐园的海洋球池、蹦床世界嗨翻一整天 详情 酒店设有小黄鸭等主题儿童房、陪伴您的宝宝快乐成长、宝宝乐园的海洋球池、蹦床世界嗨翻一整天 详情  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中  图片加载中 住客好评 房间挺大，设备挺好，人员服务也很热情，吃的略小贵，但是可以接受，厨艺很好，环境也不错，游乐园挺大的，推荐 1860085****2026年05月入住  查看更多 封面 精选 点评 相册  北京春晖园温泉度假酒店 2014年装修 儿童乐园 私密性好 免费停车场 室内温泉 湖景别墅 蹦床体验 管家服务 复式loft房 泳池 设施 政策  4.5 很好 1711条 “庭院里的私汤温泉泡起来舒适惬意” 距未来科学城北地铁站驾车4.1公里,约11分钟 | 顺义区高丽营镇于庄 地图 今天 6 月 3 日 - 明天 6 月 4 日 共1晚 间数人数 1 󱠲 1 󱠱 0 󱠰 酒店套餐 含早餐 立即确认 大床房 双床房 免费取消 可订 在线付款 闪住 免费Wi-Fi上网 免费有线宽带 筛选 筛选 本店销量No.1 5 度假私汤双床房 󱮔 2张1.2米单人床 50㎡ 2人入住 1-5层 6RX5KR-BRSBSW 无早餐 不可取消 含玩乐活动  温泉会单人门票 2份/天+宝宝乐园亲子票（一大一小） 1份/天+两池私汤 1份/天 立即确认 登录看低价 I95D01-BRSBSU 2份早餐 不可取消 含玩乐活动  温泉会单人门票 2份/天+宝宝乐园亲子票（一大一小） 1份/天+两池私汤 1份/天 立即确认 登录看低价 查看其他4个价格 󰠾 14 Bduck小黄鸭主题房 󱮕 1张2.4米特大床 50㎡ 2人入住 5层 7 度假私汤大床房 󱮕 1张2.4米特大床 50㎡ 2人入住 5层 7 小熊尼奥AR魔法屋 󱮕 1张2.4米特大床 50㎡ 2人入住 1-5层 5 度假私汤复式大床套房 󱮕 1张1.8米大床 75㎡ 1室1厅1卫 2人入住 6层 5 度假私汤复式双床套房 󱮕 2张1.2米单人床 75㎡ 1室1厅1卫 2人入住 6层 13 湖畔园景私汤房 󱮕 1张1.8米大床 50㎡ 2人入住 1层 11 湖畔露台私汤房 󱮕 1张1.8米大床 50㎡ 2人入住 1层 庭院景 露台 7 度假复式私汤家庭房 󱮕 1张1.8米大床 及 1张1.2米单人床 75㎡ 4人入住 6层 11 汤泉麻雀豪华套房 󱮕 1张1.8米大床 100㎡ 1室1厅2卫 2人入住 2-6层 查看其他3个房型󰠾 住客点评 4.5 很好 1711条 4.5 卫 生 4.6 环 境 4.5 服 务 4.4 设 施 由AI生成 环境 342 : 酒店环境优雅，周围景色宜人，特别是春天樱花盛开时，适合老人和亲子游。；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；在京郊的温泉主题酒店中，“春晖园”虽然春晖园略微有些老旧，但绝对是口碑最靠前的地方~ 🏨酒店：北京春晖园温泉度假酒店 📍地址：顺义高丽营镇于庄，建议自驾前往 💰价位：夏季基础房型600元，冬季基础房型1200元 我们入住过两次，一次是夏季，一次是冬季（因为抢到了便宜的房券，哈哈），正好入住的还是不同房型，来跟大家分享一下两次的入住体验（差异很大……🤔）~ 🔻夏季入住的复式大床房 也许因为夏季是淡季，我们预订的大床标间，结果被莫名其妙的升房啦，哈哈😄 复式房间的整体感觉要比最基础的房间洋气、时尚很多，贴近年轻人的审美~📷也很好看 楼上是床区域🛏️，自动窗帘遮光效果和隔音效果超棒~ 🔻冬季入住的普通标间房 今年抢到了春晖园近乎五折的房券，冬季周末750元能住个春晖园非常难得~ 双床标间比想象的大很多，还有腿部按摩椅（虽然要扫码支付）；</x:v>
+        <x:v>价格线索：整租：1室5300-5800元/月；、2室6800-7500元/月；、3室7500-8000元/月；合租单间约3500元/月；房屋质量/户型线索：房龄约2003-2005年；；精装修为主，有电梯（部分楼层）；；物业为北京旺达家兴物业公司；；小区绿化率高、环境舒适，部分房源提到自住保养好，但未明确提及隔音情况；；户型多为南北通透或南向板楼/塔楼；；生活便利线索：生活：周边有红阳阳超市、宜城生活超市，西北旺万象汇约772米；；餐饮、休闲有配套，临近中关村公园等；；风险线索：无明确差评或同名误命中信息，仅提示交易前需核实房源信息，部分房源信息已过期需注意。；无明确差评或同名误命中信息，仅提示交易前需核实房源信息，部分房源信息已过期需注意</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>1. 【北京b体育appv0x.cn租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kwB%E4%BD%93%E8%82%B2Appv0x.cn?15%20target=_blank
-2. 携程酒店-北京春晖园温泉度假酒店预订-北京春晖园温泉度假酒店价格、点评、电话、地址查询-【携程旅行手机版】 https://m.ctrip.com/html5/hotel/hoteldetail/435777.html
-3. China best holiday homes | HolidayHomes https://www.holidayhomes.com/china/</x:v>
+        <x:v>1. https://bj.zu.anjuke.com/fangyuan/3103156154228743
+2. http://m.anjuke.com/bj/rent/4603882202455047-3/
+3. http://m.anjuke.com/bj/rent/4580010439728135-3/
+4. 马连洼春晖园2室1厅 https://bj.zu.anjuke.com/fangyuan/3103156154228743
+5. 春晖园 独立卫浴，带阳台， 精装修 采光好 http://m.anjuke.com/bj/rent/4603882202455047-3/
+6. 春晖园一居 园区正中间 中间楼层 全南向 自住保养好 诚售 https://m.5i5j.com/bj/ershoufang/504482603.html
+7. 春晖园 2室出租 业主直签 电梯房 精装修 采光视野非常好 http://m.anjuke.com/bj/rent/4580010439728135-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -998,38 +1039,40 @@
         <x:v>北京市海淀区马连洼街道兴隆庄乙1号</x:v>
       </x:c>
       <x:c r="E17" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F17" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G17" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H17" t="n">
-        <x:v>7.8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="I17" t="str">
-        <x:v>距离马连洼站仅约200米，通勤优势极大，绿化与户型较好，是网易员工的优质选择。</x:v>
-      </x:c>
-      <x:c r="J17" t="str">
-        <x:v>2026-01-04 | 285万 | 50718元/㎡；025-11-04 | 1236万 | 75138元/㎡</x:v>
-      </x:c>
+        <x:v>建筑质量优异且地铁近在咫尺，但大户型租金较高，车位紧张且低层可能受噪音影响。</x:v>
+      </x:c>
+      <x:c r="J17" t="str"/>
       <x:c r="K17" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 ### 润千秋佳苑主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010088440/photo/?；视频 图片 382 ## 润千秋佳苑 海淀 马连洼 永丰路 * 16号线 * 五六环之间 * 户型丰富 * 绿化好 * 配套齐全 收藏 78253 _元/㎡_ 6月挂牌均价7 _套_ 在售房源44 _套_ 在租房源 估价 6.9 小区评分 地段交通 8.3 生活配套 6.0 居住品质 6.0 小区评测 距离小区最近的地铁站是马连洼，约204米；；查看完整评测 基本信息查看更多 * 竣工时间 2006年 * 物业类型 住宅 * 所属商圈 马连洼 * 开发商 华岳原林投资(北京)有限公司 * 物业公司 北京市均豪物业管理股份有限公司 周边配套 润千秋佳苑 永丰路 地铁 公交 学校 餐饮 购物 二手房 租房 观山大复式）客厅挑高6m 中间位置双地铁价格可谈满五一 马连洼 润千秋佳苑 1460 万 5室2厅 277.2㎡ 新增 地铁电梯房两居室 中高层 有 马连洼 润千秋佳苑 649 万 2室1厅 82.31㎡ 新增！；84个回答 * 【润千秋佳苑】 这个小区哪个户型比较好？</x:v>
+        <x:v>整租房源中，2室1厅月租约8300-8400元，3室2厅月租约12000元，具体随户型、装修、面积略有浮动；；房龄约2004-2007年建成，获长城建设奖，建筑质量可抗8级地震；；隔音和防水中等，部分房源装修为精装修；；物业方面有提到物业服务好，车位比1:1但略紧张；</x:v>
       </x:c>
       <x:c r="L17" t="str">
-        <x:v>安居客小区频道，提供润千秋佳苑二手房,平均房价78253元/平米,找润千秋佳苑二手房，润千秋佳苑租房，润千秋佳苑房价走势、实景图、房型图、周边交通配套信息就上安居客。；视频 图片 382 ## 润千秋佳苑 海淀 马连洼 永丰路 * 16号线 * 五六环之间 * 户型丰富 * 绿化好 * 配套齐全 收藏 78253 _元/㎡_ 6月挂牌均价7 _套_ 在售房源44 _套_ 在租房源 估价 6.9 小区评分 地段交通 8.3 生活配套 6.0 居住品质 6.0 小区评测 距离小区最近的地铁站是马连洼，约204米；；交通配套越好，出行就越方便，房产也越保值。；周边学校越多，对应小区配套的学校越好，上学越方便。；学校配套综合考虑配套数量、距离、学校等级等因素。</x:v>
+        <x:v>通勤便利，距离16号线马连洼站约168-300米；；生活配套：南门500米内有中发百旺商城、美廉美超市，1千米内有农行等金融机构，2000米左右有309医院，餐饮购物等日常需求可满足；；车位紧张，部分住户反映距离地铁近陌生人较多可能带来嘈杂问题；；有提及配套不算特别成熟，内部绿化虽高但部分认为欠缺。；有提及配套不算特别成熟，内部绿化虽高但部分认为欠缺</x:v>
       </x:c>
       <x:c r="M17" t="str"/>
       <x:c r="N17" t="str">
-        <x:v>价格线索：2026-01-04 | 285万 | 50718元/㎡；025-11-04 | 1236万 | 75138元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) [](https://esf.fang.com/loupan/1010088440/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 ### 润千秋佳苑主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010088440/photo/?；视频 图片 382 ## 润千秋佳苑 海淀 马连洼 永丰路 * 16号线 * 五六环之间 * 户型丰富 * 绿化好 * 配套齐全 收藏 78253 _元/㎡_ 6月挂牌均价7 _套_ 在售房源44 _套_ 在租房源 估价 6.9 小区评分 地段交通 8.3 生活配套 6.0 居住品质 6.0 小区评测 距离小区最近的地铁站是马连洼，约204米；；查看完整评测 基本信息查看更多 * 竣工时间 2006年 * 物业类型 住宅 * 所属商圈 马连洼 * 开发商 华岳原林投资(北京)有限公司 * 物业公司 北京市均豪物业管理股份有限公司 周边配套 润千秋佳苑 永丰路 地铁 公交 学校 餐饮 购物 二手房 租房 观山大复式）客厅挑高6m 中间位置双地铁价格可谈满五一 马连洼 润千秋佳苑 1460 万 5室2厅 277.2㎡ 新增 地铁电梯房两居室 中高层 有 马连洼 润千秋佳苑 649 万 2室1厅 82.31㎡ 新增！；84个回答 * 【润千秋佳苑】 这个小区哪个户型比较好？；生活便利线索：安居客小区频道，提供润千秋佳苑二手房,平均房价78253元/平米,找润千秋佳苑二手房，润千秋佳苑租房，润千秋佳苑房价走势、实景图、房型图、周边交通配套信息就上安居客。；视频 图片 382 ## 润千秋佳苑 海淀 马连洼 永丰路 * 16号线 * 五六环之间 * 户型丰富 * 绿化好 * 配套齐全 收藏 78253 _元/㎡_ 6月挂牌均价7 _套_ 在售房源44 _套_ 在租房源 估价 6.9 小区评分 地段交通 8.3 生活配套 6.0 居住品质 6.0 小区评测 距离小区最近的地铁站是马连洼，约204米；；交通配套越好，出行就越方便，房产也越保值。；周边学校越多，对应小区配套的学校越好，上学越方便。；学校配套综合考虑配套数量、距离、学校等级等因素。</x:v>
+        <x:v>房屋质量/户型线索：整租房源中，2室1厅月租约8300-8400元，3室2厅月租约12000元，具体随户型、装修、面积略有浮动；；房龄约2004-2007年建成，获长城建设奖，建筑质量可抗8级地震；；隔音和防水中等，部分房源装修为精装修；；物业方面有提到物业服务好，车位比1:1但略紧张；；生活便利线索：通勤便利，距离16号线马连洼站约168-300米；；生活配套：南门500米内有中发百旺商城、美廉美超市，1千米内有农行等金融机构，2000米左右有309医院，餐饮购物等日常需求可满足；；车位紧张，部分住户反映距离地铁近陌生人较多可能带来嘈杂问题；；有提及配套不算特别成熟，内部绿化虽高但部分认为欠缺。；有提及配套不算特别成熟，内部绿化虽高但部分认为欠缺</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>1. 【北京润千秋佳苑小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010088440.htm
-2. 润千秋佳苑,永丰路-北京润千秋佳苑二手房、租房、房价-北京安居客 https://m.anjuke.com/bj/community/52275/
-3. 润千秋佳苑 https://baike.baidu.com/item/%E6%B6%A6%E5%8D%83%E7%A7%8B%E4%BD%B3%E8%8B%91/10078608
-4. 润千秋佳苑最新房价_北京海淀区-中国房价行情 https://m.creprice.cn/community/pa00023335hd209.html?city=bj</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4597918925446156-3/
+2. http://m.anjuke.com/bj/rent/4604115567799304-3/
+3. http://m.anjuke.com/bj/community/52275/jiedu/
+4. http://m.anjuke.com/bj/community/52275/jiedu/p2/
+5. 2室1厅 润千秋佳苑 http://m.anjuke.com/bj/rent/4597918925446156-3/
+6. 润千秋佳苑精装两居出租 家具全齐 看房方便 实图拍摄稳定长租 http://m.anjuke.com/bj/rent/4604115567799304-3/
+7. 润千秋佳苑优点、不足，润千秋佳苑怎么样，润千秋佳苑周边房产中介经纪人评价-北京安居客 http://m.anjuke.com/bj/community/52275/jiedu/
+8. 2室2厅 润千秋佳苑 http://m.anjuke.com/bj/rent/4598057913670670-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1046,41 +1089,44 @@
         <x:v>北京市海淀区西路8号院</x:v>
       </x:c>
       <x:c r="E18" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F18" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G18" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H18" t="n">
-        <x:v>7.2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I18" t="str">
-        <x:v>紧邻网易大厦，租金相对适中，但网页证据多为泛化信息，房屋具体质量及隔音待考。</x:v>
+        <x:v>临近软件园通勤便利，但部分低价房源信息疑似不实，且步行至地铁站距离较远。</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
+        <x:v>（含周边同区域房源）租房价格：整租一居约1500元/月；散式公寓、30-32.6㎡），整租两居约9999元/月；110㎡、精装修），合租主卧（20㎡）约3200元/月</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂��庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；58同城北京租房网，为您提供北京海淀租房信息，包括海淀房屋出租信息、海淀合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。</x:v>
+        <x:v>东北旺西路8号院（含周边同区域房源）租房价格：整租一居约1500元/月（分散式公寓、30-32.6㎡），整租两居约9999元/月（110㎡、精装修），合租主卧（20㎡）约3200元/月。；房屋质量：部分房源为精装修（如1室1厅配科勒家电、智能控制），房龄信息未明确提及；；未找到明确隔音、户型瑕疵及物业负面反馈相关内容。</x:v>
       </x:c>
       <x:c r="L18" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂��庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。</x:v>
+        <x:v>东北旺西路8号院（含周边同区域房源）租房价格：整租一居约1500元/月（分散式公寓、30-32.6㎡），整租两居约9999元/月（110㎡、精装修），合租主卧（20㎡）约3200元/月。；生活便利程度：临近18号线东北旺站（步行约1200-1655米）、13号线/昌平线西二旗站（步行约1743-1974米）；；周边有中发百旺商城、仓储折扣超市，还有健身房、咖啡厅等配套，临近软件园、科技园，通勤便利，餐饮配套完善。</x:v>
       </x:c>
       <x:c r="M18" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?；3.**周边限制与政策：** 了解园区或所在区域对于**特定研发活动（如生物实验、化学合成、噪音振动测试）** 有无特殊规定或限制。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未明确发现针对东北旺西路8号院本身的租房风险或差评信息。</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂��庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；58同城北京租房网，为您提供北京海淀租房信息，包括海淀房屋出租信息、海淀合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。；生活便利线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂��庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](http://helps.58.com/train/detail?；3.**周边限制与政策：** 了解园区或所在区域对于**特定研发活动（如生物实验、化学合成、噪音振动测试）** 有无特殊规定或限制。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：（含周边同区域房源）租房价格：整租一居约1500元/月；散式公寓、30-32.6㎡），整租两居约9999元/月；110㎡、精装修），合租主卧（20㎡）约3200元/月；房屋质量/户型线索：东北旺西路8号院（含周边同区域房源）租房价格：整租一居约1500元/月（分散式公寓、30-32.6㎡），整租两居约9999元/月（110㎡、精装修），合租主卧（20㎡）约3200元/月。；房屋质量：部分房源为精装修（如1室1厅配科勒家电、智能控制），房龄信息未明确提及；；未找到明确隔音、户型瑕疵及物业负面反馈相关内容。；生活便利线索：东北旺西路8号院（含周边同区域房源）租房价格：整租一居约1500元/月（分散式公寓、30-32.6㎡），整租两居约9999元/月（110㎡、精装修），合租主卧（20㎡）约3200元/月。；生活便利程度：临近18号线东北旺站（步行约1200-1655米）、13号线/昌平线西二旗站（步行约1743-1974米）；；周边有中发百旺商城、仓储折扣超市，还有健身房、咖啡厅等配套，临近软件园、科技园，通勤便利，餐饮配套完善。；风险线索：未明确发现针对东北旺西路8号院本身的租房风险或差评信息。</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>1. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 http://mob.58.com/zf/cd-haidian/
-2. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_253028bj/
-3. 北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment
-4. 讨论精选（豆瓣） https://www.douban.com/group/explore
-5. 「2026年北京海淀独栋研发楼出租怎么选？企房房严选东北旺南路好房/办公楼出租」- 写字楼租房网 https://bj-sydc.com/article.php?id=43712</x:v>
+        <x:v>1. https://m.58.com/bj/zufang/84302388292059x.shtml
+2. http://m.anjuke.com/dongyang/rent/4577247395879939-3/
+3. http://m.anjuke.com/bj/rent/4568578093540365-3/
+4. http://m.anjuke.com/bj/rent/4568337772407816-3/
+5. http://m.anjuke.com/bj/rent/4480798369033218-3/
+6. 软件园 亿城西山公馆空房两居 有电梯 长租 https://m.58.com/bj/zufang/84302388292059x.shtml
+7. 无中介费 押一付一 近地铁站 交通便利 配套齐全 http://m.anjuke.com/dongyang/rent/4577247395879939-3/
+8. 18号线东北旺八百米 小米 百度 网易 快手 腾讯大厂房补内 http://m.anjuke.com/bj/rent/4568578093540365-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1097,41 +1143,44 @@
         <x:v>北京市海淀区马连洼街道</x:v>
       </x:c>
       <x:c r="E19" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F19" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G19" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H19" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I19" t="str">
-        <x:v>价格亲民但房龄偏老，存在隔音差、无客厅及违建等明显质量缺陷，需谨慎选择。</x:v>
+        <x:v>典型的老旧成熟社区，虽无电梯但胜在离地铁近、生活便利，适合预算有限的租客。</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>2026-03-28 | 381万 | 43222元/㎡；2026-03-18 | 285万 | 44854元/㎡；2026-01-06 | 295万 | 39572元/㎡；000_ 元/m² 百草园社区，小区价格72583元/㎡；三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月</x:v>
+        <x:v>月租约5890-8700元/月；，1室1厅约6000元/月；，2室1厅约6500-8000元/月；，3室1厅约5890-8700元/月</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 * 户型 * 价格 * #### 百草园 2室1厅 北 南 2室1厅 63.54㎡**360**万 * #### 马连洼 · 百草园 · 2室 · 1厅 2室1厅 87.97㎡**625**万 * #### 百草园2室1厅南北 2室1厅 87.97㎡**540**万 * #### 百草园三居室,低楼层,南向,户型可方正了,实用 3室2厅 69.3㎡**460**万 ### 百草园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 88.38㎡ | 2026-03-28 | 381万 | 43222元/㎡ | 市场信息 | | 63.54㎡ | 2026-03-18 | 285万 | 44854元/㎡ | 市场信息 | | 74.80㎡ | 2026-01-06 | 295万 | 39572元/㎡ | 市场信息 | 查看全部成交 ### 百草园价格走势 ### 百草园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 百草园 海淀·马连洼**67788** 元/㎡ * #### 西山华府别墅 海淀·马连洼**待定** * #### 西山华府 海淀·马连洼**90430** 元/㎡ * #### 马连洼兰园 海淀·马连洼**60105** 元/㎡ * #### 马连洼竹园 海淀·马连洼**54689** 元/㎡ ### 相关资讯 * 小区资讯北京百草园怎么样?；北京吉屋网提供北京百草园社区二手房出售信息、百草园社区二手房价格，包括及时更新北京百草园社区二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百草园社区_北京百草园社区小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百草园社区 更新于 2026-06-01 10:50:39 [](https://bj.jiwu.com/tu/3480166.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480167.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480168.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480169.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480170.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480171.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480172.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480173.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480174.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480175.html "百草园社区实景图图片") # 百草园社区 别名：百草园小区 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路128号_ 发地址到手机 参考均价 _72583 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _948_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-42群（327） * 大家觉得这里未来发展怎么样？；加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(1)3室(1) 全部户型 [](https://bj.jiwu.com/huxing/661736.html "百草园社区3室1厅1卫114㎡户型图")3室1厅1卫 114㎡咨询户型房源 [](https://bj.jiwu.com/huxing/661737.html "百草园社区2室1厅1卫90㎡户型图")2室1厅1卫 90㎡咨询户型房源 [](https://bj.jiwu.com/huxing/661738.html "百草园社区1室1厅1卫户型图")1室1厅1卫咨询户型房源 小区评测报告 ？</x:v>
+        <x:v>小区1995年建成，多为低层（6层）无电梯；；装修分简单装修和精装修；；户型多南北通透，采光较好；；暂未发现明确隔音、物业差评提及；</x:v>
       </x:c>
       <x:c r="L19" t="str">
-        <x:v>百草园房价地段交通配套分析2022-04-04 * 小区资讯马连洼租房,百草园最新房源报告!；北京吉屋网提供北京百草园社区二手房出售信息、百草园社区二手房价格，包括及时更新北京百草园社区二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百草园社区_北京百草园社区小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百草园社区 更新于 2026-06-01 10:50:39 [](https://bj.jiwu.com/tu/3480166.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480167.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480168.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480169.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480170.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480171.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480172.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480173.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480174.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480175.html "百草园社区实景图图片") # 百草园社区 别名：百草园小区 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路128号_ 发地址到手机 参考均价 _72583 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _948_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-42群（327） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；百草园社区是一个园林品牌社区，管理严格，配套设施齐全，交通购物便利，小区环境优美。</x:v>
+        <x:v>配套有集中供暖，房屋设施（家电、厨房等）基本齐全；；交通：邻近18号线/16号线马连洼站（步行约627-677米），近马连洼西站（步行约286米）；；商超：距离中发百旺商城约755米，周边有便民果蔬店、农大超市；；医疗：附近有北京八珍堂中医医院（约1678米）；；环境：绿化率高，周边有公园，生活便利；</x:v>
       </x:c>
       <x:c r="M19" t="str">
-        <x:v>在北京城区的老房子住了20多年，“70多平方米小三居，没客厅，隔音差，朝向也不好。；不仅如此，小区内违建成风，公共区域被私人‘圈占’，导致居民停车难、出行难，活动空间受限。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>暂未发现明确隔音、物业差评提及；；无明确其他风险/差评记录。；无明确其他风险/差评记录</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>价格线索：2026-03-28 | 381万 | 43222元/㎡；2026-03-18 | 285万 | 44854元/㎡；2026-01-06 | 295万 | 39572元/㎡；000_ 元/m² 百草园社区，小区价格72583元/㎡；三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) [](https://esf.fang.com/loupan/1010544065/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 * 户型 * 价格 * #### 百草园 2室1厅 北 南 2室1厅 63.54㎡**360**万 * #### 马连洼 · 百草园 · 2室 · 1厅 2室1厅 87.97㎡**625**万 * #### 百草园2室1厅南北 2室1厅 87.97㎡**540**万 * #### 百草园三居室,低楼层,南向,户型可方正了,实用 3室2厅 69.3㎡**460**万 ### 百草园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 88.38㎡ | 2026-03-28 | 381万 | 43222元/㎡ | 市场信息 | | 63.54㎡ | 2026-03-18 | 285万 | 44854元/㎡ | 市场信息 | | 74.80㎡ | 2026-01-06 | 295万 | 39572元/㎡ | 市场信息 | 查看全部成交 ### 百草园价格走势 ### 百草园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 百草园 海淀·马连洼**67788** 元/㎡ * #### 西山华府别墅 海淀·马连洼**待定** * #### 西山华府 海淀·马连洼**90430** 元/㎡ * #### 马连洼兰园 海淀·马连洼**60105** 元/㎡ * #### 马连洼竹园 海淀·马连洼**54689** 元/㎡ ### 相关资讯 * 小区资讯北京百草园怎么样?；北京吉屋网提供北京百草园社区二手房出售信息、百草园社区二手房价格，包括及时更新北京百草园社区二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百草园社区_北京百草园社区小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百草园社区 更新于 2026-06-01 10:50:39 [](https://bj.jiwu.com/tu/3480166.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480167.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480168.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480169.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480170.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480171.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480172.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480173.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480174.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480175.html "百草园社区实景图图片") # 百草园社区 别名：百草园小区 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路128号_ 发地址到手机 参考均价 _72583 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _948_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-42群（327） * 大家觉得这里未来发展怎么样？；加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(1)3室(1) 全部户型 [](https://bj.jiwu.com/huxing/661736.html "百草园社区3室1厅1卫114㎡户型图")3室1厅1卫 114㎡咨询户型房源 [](https://bj.jiwu.com/huxing/661737.html "百草园社区2室1厅1卫90㎡户型图")2室1厅1卫 90㎡咨询户型房源 [](https://bj.jiwu.com/huxing/661738.html "百草园社区1室1厅1卫户型图")1室1厅1卫咨询户型房源 小区评测报告 ？；生活便利线索：百草园房价地段交通配套分析2022-04-04 * 小区资讯马连洼租房,百草园最新房源报告!；北京吉屋网提供北京百草园社区二手房出售信息、百草园社区二手房价格，包括及时更新北京百草园社区二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百草园社区_北京百草园社区小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百草园社区 更新于 2026-06-01 10:50:39 [](https://bj.jiwu.com/tu/3480166.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480167.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480168.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480169.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480170.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480171.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480172.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480173.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480174.html "百草园社区实景图图片")[](https://bj.jiwu.com/tu/3480175.html "百草园社区实景图图片") # 百草园社区 别名：百草园小区 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路128号_ 发地址到手机 参考均价 _72583 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _948_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-42群（327） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；百草园社区是一个园林品牌社区，管理严格，配套设施齐全，交通购物便利，小区环境优美。；风险线索：在北京城区的老房子住了20多年，“70多平方米小三居，没客厅，隔音差，朝向也不好。；不仅如此，小区内违建成风，公共区域被私人‘圈占’，导致居民停车难、出行难，活动空间受限。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：月租约5890-8700元/月；，1室1厅约6000元/月；，2室1厅约6500-8000元/月；，3室1厅约5890-8700元/月；房屋质量/户型线索：小区1995年建成，多为低层（6层）无电梯；；装修分简单装修和精装修；；户型多南北通透，采光较好；；暂未发现明确隔音、物业差评提及；；生活便利线索：配套有集中供暖，房屋设施（家电、厨房等）基本齐全；；交通：邻近18号线/16号线马连洼站（步行约627-677米），近马连洼西站（步行约286米）；；商超：距离中发百旺商城约755米，周边有便民果蔬店、农大超市；；医疗：附近有北京八珍堂中医医院（约1678米）；；环境：绿化率高，周边有公园，生活便利；；风险线索：暂未发现明确隔音、物业差评提及；；无明确其他风险/差评记录。；无明确其他风险/差评记录</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>1. 【北京百草园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010544065.htm
-2. 百草园社区_北京百草园社区小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/150260.html
-3. 我们的美丽城市 我们的宜居家园（产经观察） https://paper.people.com.cn/rmrb/pc/content/202507/23/content_30089825.html
-4. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-5. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. http://m.anjuke.com/ch/rent/4572053450957824-3/
+2. http://m.anjuke.com/bj/rent/4589832269702148-3/
+3. http://m.anjuke.com/bj/rent/4583915300051974-3/
+4. http://m.anjuke.com/dongyang/rent/4589729874893826-3/
+5. 急租好价 百草园正规一室一厅 干净整洁通勤便捷 http://m.anjuke.com/ch/rent/4572053450957824-3/
+6. 马连洼 百草园社区 南北通透 低楼层 采光好 2室1厅1卫 http://m.anjuke.com/bj/rent/4589832269702148-3/
+7. 百草园社区 2室2厅1卫 低楼层6500 集中供暖 家电齐全 http://m.anjuke.com/bj/rent/4583915300051974-3/
+8. 马连洼 百草园社区 两卧朝南 低楼层 出门地铁 可长租 http://m.anjuke.com/dongyang/rent/4589729874893826-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1148,38 +1197,44 @@
         <x:v>北京市海淀区农大南路43号</x:v>
       </x:c>
       <x:c r="E20" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F20" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G20" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H20" t="n">
-        <x:v>8.2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>高品质大型社区，环境优越且配套完善，适合预算较高、追求大户型居住体验的租客。</x:v>
+        <x:v>社区环境优美且物业专业，户型采光佳，适合对居住品质有要求、预算较充足的人群。</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>026-02-06 | 1141万 | 73111元/㎡；025-12-21 | 1095万 | 70541元/㎡；025-11-27 | 1292万 | 81263元/㎡；万 5室1厅3卫丨235㎡丨南丨顶层丨 88699元/㎡； 3室2厅2卫丨151㎡丨南北丨底层丨 104000元/㎡；3室2厅2卫丨132㎡丨南北丨中楼层丨 115300元/㎡；6000_ 元/m² 博雅西园，小区价格80308元/㎡</x:v>
+        <x:v>合租主卧3800元/月；，整租2室2厅约9200元/月；，2室1厅约9200元/月；，3室1厅约9900元/月；，3室2厅约12300-15100元/月</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 * 户型 * 价格 * #### 树村博雅西园满五年电梯全明格局集中供暖采光好 3室2厅 151.0㎡**1240**万 * #### 上地树村马连洼不临街,南北通透,有平台可观景 2室1厅 79.34㎡**667**万 * #### 博雅西园顶层三居室拎包入住带充电车位 3室2厅 151.37㎡**1200**万 * #### 博雅西园2室1厅南北 2室1厅 78.42㎡**740**万 ### 博雅西园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 156.20㎡ | 2026-02-06 | 1141万 | 73111元/㎡ | 市场信息 | | 155.37㎡ | 2025-12-21 | 1095万 | 70541元/㎡ | 市场信息 | | 158.99㎡ | 2025-11-27 | 1292万 | 81263元/㎡ | 市场信息 | 查看全部成交 ### 博雅西园价格走势 ### 博雅西园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 博雅西园 海淀·马连洼**83932** 元/㎡ * #### 部队家属院 海淀·马连洼**35786** 元/㎡ * #### 万树园 海淀·马连洼**74950** 元/㎡ * #### 紫成嘉园 海淀·马连洼**80926** 元/㎡ * #### 紫城嘉园 海淀·马连洼**80765** 元/㎡ ### 相关资讯 * 小区资讯北京博雅西园怎么样?；北京吉屋网提供北京博雅西园二手房出售信息、博雅西园二手房价格，包括及时更新北京博雅西园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 博雅西园_北京博雅西园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_博雅西园 更新于 2026-06-01 10:52:42 [](https://bj.jiwu.com/tu/4300116.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300117.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300118.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300119.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300120.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300121.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300122.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300123.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300124.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300125.html "博雅西园实景图图片") # 博雅西园 别名：博雅西园 加入本地买房群 关注 _北京 - 海淀 - 农大南路_ 发地址到手机 参考均价 _80308 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2005_ 小区户数 _1258户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-95群（365） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；加入群聊 二手房源全部房源 * [](https://bj.jiwu.com/esf/37351696.html "农大南路，博雅西园大复试，五室全朝南，全明格局，精装修")农大南路，博雅西园大复试，五室全朝南，全明格局，精装修 2088万 5室1厅3卫丨235㎡丨南丨顶层丨 88699元/㎡ 博雅西园 | 海淀 - | 2005年建 * [](https://bj.jiwu.com/esf/37351697.html "博雅西园一层3居室，南北通透，诚意出售")博雅西园一层3居室，南北通透，诚意出售 1570万 3室2厅2卫丨151㎡丨南北丨底层丨 104000元/㎡ 博雅西园 | 海淀 - | 2005年建 * [](https://bj.jiwu.com/esf/37351698.html "马连洼博雅西园3室2厅 中间层，有电梯，位置安静，看房方便")马连洼博雅西园3室2厅 中间层，有电梯，位置安静，看房方便 1520万 3室2厅2卫丨132㎡丨南北丨中楼层丨 115300元/㎡ 博雅西园 | 海淀 - | 2005年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(3)3室(1)4室(1) 全部户型 [](https://bj.jiwu.com/huxing/678731.html "博雅西园2室1厅1卫118㎡户型图")2室1厅1卫 118㎡咨询户型房源 [](https://bj.jiwu.com/huxing/678732.html "博雅西园4室2厅2卫157㎡户型图")4室2厅2卫 157㎡咨询户型房源 [](https://bj.jiwu.com/huxing/678733.html "博雅西园3室2厅2卫156㎡户型图")3室2厅2卫 156㎡咨询户型房源 小区评测报告 ？</x:v>
+        <x:v>租金含物业费部分房源，需额外支付中介费（约1个月租金），押一付三为主，部分可押一付半年。；房龄约2005年，房屋类型为普通住宅板楼，绿化约42%；；装修有精装、豪华装修；；物业为北京瑞赢酒店物业管理有限公司，物业费2.4元/㎡·月，部分房源包物业取暖；；户型以方正、明卫为主，采光通风较好；</x:v>
       </x:c>
       <x:c r="L20" t="str">
-        <x:v>北京吉屋网提供北京博雅西园二手房出售信息、博雅西园二手房价格，包括及时更新北京博雅西园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 博雅西园_北京博雅西园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_博雅西园 更新于 2026-06-01 10:52:42 [](https://bj.jiwu.com/tu/4300116.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300117.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300118.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300119.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300120.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300121.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300122.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300123.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300124.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300125.html "博雅西园实景图图片") # 博雅西园 别名：博雅西园 加入本地买房群 关注 _北京 - 海淀 - 农大南路_ 发地址到手机 参考均价 _80308 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2005_ 小区户数 _1258户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-95群（365） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等博雅西园小区信息，关注吉屋北京博雅西园！；* 买房交流 * 找房小程序 * 返回顶部 * 关于吉屋 * 公司新闻 * 联系我们 * 加入我们 * 服务声明 * 服务热线：0755-26404403 * 网站地图 周边买房 * 北京买房 北京新房 * 房山新房 * 顺义新房 * 昌平新房 * 大兴新房 * 北京周边新房 * 平谷新房 * 海淀新房 * 丰台新房 * 门头沟新房 * 朝阳新房 * 延庆新房 * 密云新房 * 石景山新房 * 通州新房 * 怀柔新房 * 西城新房 * 东城新房 * 怀来新房 * 其他新房 * 崇礼新房 * 海滨新房 * 亦庄经开区新房 周边房价 * 房山房价 * 顺义房价 * 昌平房价 * 大兴房价 * 北京周边房价 * 平谷房价 * 海淀房价 * 丰台房价 * 门头沟房价 * 朝阳房价 * 延庆房价 * 密云房价 * 石景山房价 * 通州房价 * 怀柔房价 * 西城房价 * 东城房价 * 怀来房价 * 其他房价 * 崇礼房价 * 海滨房价 * 亦庄经开区房价 深圳市吉屋网络技术有限公司 粤ICP备11045667号粤公网安备 44030502001914号增值电信业务经营许可证房地产经纪机构备案工商网监中国电子认证服务产业联盟 免责声明：楼盘信息来源开发商、第三方平台，本站旨在为用户提供更多信息服务，最终以政府部门登记备案为准，请蓮慎核查。</x:v>
-      </x:c>
-      <x:c r="M20" t="str"/>
+        <x:v>距离16号线农大南路站步行约1175-1178米，周边有北京华联BHG Mall、中发百旺商城、幸福荣耀生活超市等商超；；餐饮资源较丰富，周边有园区配套及商业餐饮；；通勤主要依赖16号线地铁及公交；</x:v>
+      </x:c>
+      <x:c r="M20" t="str">
+        <x:v>未发现明确针对租房的差评或高风险信息，部分房源中介费较高（1个月租金），需注意房源真实性核实（多为中介发布）。</x:v>
+      </x:c>
       <x:c r="N20" t="str">
-        <x:v>价格线索：026-02-06 | 1141万 | 73111元/㎡；025-12-21 | 1095万 | 70541元/㎡；025-11-27 | 1292万 | 81263元/㎡；万 5室1厅3卫丨235㎡丨南丨顶层丨 88699元/㎡； 3室2厅2卫丨151㎡丨南北丨底层丨 104000元/㎡；3室2厅2卫丨132㎡丨南北丨中楼层丨 115300元/㎡；6000_ 元/m² 博雅西园，小区价格80308元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) [](https://esf.fang.com/loupan/1010025998/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 * 户型 * 价格 * #### 树村博雅西园满五年电梯全明格局集中供暖采光好 3室2厅 151.0㎡**1240**万 * #### 上地树村马连洼不临街,南北通透,有平台可观景 2室1厅 79.34㎡**667**万 * #### 博雅西园顶层三居室拎包入住带充电车位 3室2厅 151.37㎡**1200**万 * #### 博雅西园2室1厅南北 2室1厅 78.42㎡**740**万 ### 博雅西园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 156.20㎡ | 2026-02-06 | 1141万 | 73111元/㎡ | 市场信息 | | 155.37㎡ | 2025-12-21 | 1095万 | 70541元/㎡ | 市场信息 | | 158.99㎡ | 2025-11-27 | 1292万 | 81263元/㎡ | 市场信息 | 查看全部成交 ### 博雅西园价格走势 ### 博雅西园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 博雅西园 海淀·马连洼**83932** 元/㎡ * #### 部队家属院 海淀·马连洼**35786** 元/㎡ * #### 万树园 海淀·马连洼**74950** 元/㎡ * #### 紫成嘉园 海淀·马连洼**80926** 元/㎡ * #### 紫城嘉园 海淀·马连洼**80765** 元/㎡ ### 相关资讯 * 小区资讯北京博雅西园怎么样?；北京吉屋网提供北京博雅西园二手房出售信息、博雅西园二手房价格，包括及时更新北京博雅西园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 博雅西园_北京博雅西园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_博雅西园 更新于 2026-06-01 10:52:42 [](https://bj.jiwu.com/tu/4300116.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300117.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300118.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300119.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300120.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300121.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300122.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300123.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300124.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300125.html "博雅西园实景图图片") # 博雅西园 别名：博雅西园 加入本地买房群 关注 _北京 - 海淀 - 农大南路_ 发地址到手机 参考均价 _80308 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2005_ 小区户数 _1258户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-95群（365） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；加入群聊 二手房源全部房源 * [](https://bj.jiwu.com/esf/37351696.html "农大南路，博雅西园大复试，五室全朝南，全明格局，精装修")农大南路，博雅西园大复试，五室全朝南，全明格局，精装修 2088万 5室1厅3卫丨235㎡丨南丨顶层丨 88699元/㎡ 博雅西园 | 海淀 - | 2005年建 * [](https://bj.jiwu.com/esf/37351697.html "博雅西园一层3居室，南北通透，诚意出售")博雅西园一层3居室，南北通透，诚意出售 1570万 3室2厅2卫丨151㎡丨南北丨底层丨 104000元/㎡ 博雅西园 | 海淀 - | 2005年建 * [](https://bj.jiwu.com/esf/37351698.html "马连洼博雅西园3室2厅 中间层，有电梯，位置安静，看房方便")马连洼博雅西园3室2厅 中间层，有电梯，位置安静，看房方便 1520万 3室2厅2卫丨132㎡丨南北丨中楼层丨 115300元/㎡ 博雅西园 | 海淀 - | 2005年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(3)3室(1)4室(1) 全部户型 [](https://bj.jiwu.com/huxing/678731.html "博雅西园2室1厅1卫118㎡户型图")2室1厅1卫 118㎡咨询户型房源 [](https://bj.jiwu.com/huxing/678732.html "博雅西园4室2厅2卫157㎡户型图")4室2厅2卫 157㎡咨询户型房源 [](https://bj.jiwu.com/huxing/678733.html "博雅西园3室2厅2卫156㎡户型图")3室2厅2卫 156㎡咨询户型房源 小区评测报告 ？；生活便利线索：北京吉屋网提供北京博雅西园二手房出售信息、博雅西园二手房价格，包括及时更新北京博雅西园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 博雅西园_北京博雅西园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_博雅西园 更新于 2026-06-01 10:52:42 [](https://bj.jiwu.com/tu/4300116.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300117.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300118.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300119.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300120.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300121.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300122.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300123.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300124.html "博雅西园实景图图片")[](https://bj.jiwu.com/tu/4300125.html "博雅西园实景图图片") # 博雅西园 别名：博雅西园 加入本地买房群 关注 _北京 - 海淀 - 农大南路_ 发地址到手机 参考均价 _80308 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2005_ 小区户数 _1258户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-95群（365） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等博雅西园小区信息，关注吉屋北京博雅西园！；* 买房交流 * 找房小程序 * 返回顶部 * 关于吉屋 * 公司新闻 * 联系我们 * 加入我们 * 服务声明 * 服务热线：0755-26404403 * 网站地图 周边买房 * 北京买房 北京新房 * 房山新房 * 顺义新房 * 昌平新房 * 大兴新房 * 北京周边新房 * 平谷新房 * 海淀新房 * 丰台新房 * 门头沟新房 * 朝阳新房 * 延庆新房 * 密云新房 * 石景山新房 * 通州新房 * 怀柔新房 * 西城新房 * 东城新房 * 怀来新房 * 其他新房 * 崇礼新房 * 海滨新房 * 亦庄经开区新房 周边房价 * 房山房价 * 顺义房价 * 昌平房价 * 大兴房价 * 北京周边房价 * 平谷房价 * 海淀房价 * 丰台房价 * 门头沟房价 * 朝阳房价 * 延庆房价 * 密云房价 * 石景山房价 * 通州房价 * 怀柔房价 * 西城房价 * 东城房价 * 怀来房价 * 其他房价 * 崇礼房价 * 海滨房价 * 亦庄经开区房价 深圳市吉屋网络技术有限公司 粤ICP备11045667号粤公网安备 44030502001914号增值电信业务经营许可证房地产经纪机构备案工商网监中国电子认证服务产业联盟 免责声明：楼盘信息来源开发商、第三方平台，本站旨在为用户提供更多信息服务，最终以政府部门登记备案为准，请蓮慎核查。</x:v>
+        <x:v>价格线索：合租主卧3800元/月；，整租2室2厅约9200元/月；，2室1厅约9200元/月；，3室1厅约9900元/月；，3室2厅约12300-15100元/月；房屋质量/户型线索：租金含物业费部分房源，需额外支付中介费（约1个月租金），押一付三为主，部分可押一付半年。；房龄约2005年，房屋类型为普通住宅板楼，绿化约42%；；装修有精装、豪华装修；；物业为北京瑞赢酒店物业管理有限公司，物业费2.4元/㎡·月，部分房源包物业取暖；；户型以方正、明卫为主，采光通风较好；；生活便利线索：距离16号线农大南路站步行约1175-1178米，周边有北京华联BHG Mall、中发百旺商城、幸福荣耀生活超市等商超；；餐饮资源较丰富，周边有园区配套及商业餐饮；；通勤主要依赖16号线地铁及公交；；风险线索：未发现明确针对租房的差评或高风险信息，部分房源中介费较高（1个月租金），需注意房源真实性核实（多为中介发布）。</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>1. 【北京博雅西园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010025998.htm
-2. 博雅西园_北京博雅西园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/167094.html
-3. 博雅西园 https://baike.baidu.com/item/%E5%8D%9A%E9%9B%85%E8%A5%BF%E5%9B%AD/3699296
-4. 博雅西园最新房价_北京海淀区-中国房价行情 https://m.creprice.cn/community/pa00025756hd666.html?city=bj</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4582815231339535-3/
+2. http://m.anjuke.com/bj/rent/4500748479521805-3/
+3. http://m.anjuke.com/bj/rent/4418593967741966-3/
+4. http://m.anjuke.com/bj/rent/3055344267058180-3/
+5. https://bj.zu.anjuke.com/fangyuan/4188003497975816
+6. https://boyaxiyuan.fang.com/?ztzh_uuid=wap_news42776414
+7. 农大南路农大西校区百度科技园博雅西园精装主卧两家合租业主签约 http://m.anjuke.com/bj/rent/4582815231339535-3/
+8. 整租博雅西园2室2厅 可 http://m.anjuke.com/bj/rent/4500748479521805-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1196,41 +1251,44 @@
         <x:v>北京市海淀区马连洼南路8号</x:v>
       </x:c>
       <x:c r="E21" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F21" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G21" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H21" t="n">
-        <x:v>7.9</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>万科物业加持，房龄相对较新且临近地铁，属于品质与便利兼具的高端租住选择。</x:v>
+        <x:v>高品质人车分流社区，物业管理严密且环境安静，配套成熟，是该区域的优质改善选择。</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡； 上地 2014年竣工 距离3293m 74659 元/㎡；西二旗 2009年竣工 距离2708m 82732 元/㎡； 上地 2004年竣工 距离2550m 69075 元/㎡；00_ 元/m² 亿城西山公馆，小区价格77213元/㎡；采暖 装 修： 毛坯 车 位 费： 地上150元/月；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月</x:v>
+        <x:v>1室1厅，约40-60㎡）月租5300-6000元/月；，大户型（5室2厅）月租32000元/月；，4室2厅178.12㎡房源月租19000元/月；，商铺600㎡月租9万/月</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **90429** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.9% 贷款计算器 * 二手房源 92套 * 最近成交 141套 * 楼栋总数 48栋 * 房屋总数 1606户 * 建筑类型 板楼 * 建筑年代 2011年建成 * 小区位置 马连洼北路与竹园中街交汇处南行150米路两侧地图 * 物业公司 北京亿城物业管理有限公司 * 开发商 北京亿城山水房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 王智慧 评分：4.9 从业信息卡 闪电回复 ##### 徐强 评分：4.9 从业信息卡 百科 闪电回复 ### 西山华府主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010257223/photo/?；from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡ 6月挂牌均价 0.03% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 一层50平园子）全南2居 中间位置 满五年价格可谈双地铁 马连洼 亿城西山华府珑园 846 万 2室2厅 93.51㎡ 万科物业推荐好房 马连洼西山华府一居出售 带电梯 大阳台 马连洼 亿城西山华府珑园 540 万 1室1厅 59.42㎡ 必看好房）马连洼品质2居 带明卫满五一 不临街中高层 双地铁 马连洼 亿城西山华府珑园 1080 万 2室2厅 120.84㎡ 海淀双卫两居 一梯两户 中间位置 车储 万科物业 马连洼 亿城西山华府珑园 1150 万 2室2厅 121.52㎡ 必卖好房）单本全明3居 一车一储 满五年 价格可谈双地铁 马连洼 亿城西山华府珑园 1498 万 3室2厅 177.47㎡ 必看高层）挑高4.2M 一车一储 方正4居 视野开阔价格可谈 马连洼 亿城西山华府珑园 1600 万 4室2厅 176.36㎡ ### 本小区租房推荐查看更多 ### 西山华府 177四居 全齐 马连洼地铁口 人大附中 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 马连洼双地铁 西山华府 一层院子 人大附中 农业大学 马连洼 亿城西山华府珑园 整租 16/18号线 朝南 _11000_ 元/月 2室2厅 93.5㎡ ### 陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 178.8㎡ ### 新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 新增 出租 带车位 集中供暖 家具家电齐全 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 177㎡ ### 万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 178.1㎡ ### 周边热门小区查看更多 * 347 上林溪 海淀 上地 2014年竣工 距离3293m 74659 元/㎡24套在售 小区评测 近地铁 近学校 13号线 五六环之间 户型丰富 配套齐全 7.1 分 * 421 领秀新硅谷AB区 海淀 西二旗 2009年竣工 距离2708m 82732 元/㎡15套在售 小区评测 近地铁 近学校 昌平线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 6.9 分 * 3 当代城市家园 海淀 上地 2004年竣工 距离2550m 69075 元/㎡19套在售 小区评测 近地铁 近学校 13号线等 五六环之间 绿化好 配套齐全 7.2 分 小区单页 国奥村(西区)今日家园广渠金茂府(北区)朱雀门小区景泰嘉园远洋山水(北区)天鹅湾(北区)首城国际丽都壹号凤凰城(一期二期四期)望京花园西区华清嘉园御汤山东区芍药居北里小区华纺易城一栋洋房星河湾畅园山水文园东园万象新天家园翠微北里 本板块小区大全 褐石园今日家园碧桐园颐源居同泽园西里北坞嘉园南里上地佳园翠微南里四季香山雪梨澳乡(别墅)京泉馨苑东里西山美墅馆(别墅)美丽园智学苑香山艺墅交大嘉园尚峰尚水水云居万泉新新家园翠湖别墅 小区二手房 国奥村(西区)二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售朱雀门小区二手房出售景泰嘉园二手房出售远洋山水(北区)二手房出售天鹅湾(北区)二手房出售首城国际二手房出售丽都壹号二手房出售凤凰城(一期二期四期)二手房出售望京花园西区二手房出售华清嘉园二手房出售御汤山东区二手房出售芍药居北里小区二手房出售华纺易城二手房出售一栋洋房二手房出售星河湾畅园二手房出售山水文园东园二手房出售万象新天家园二手房出售翠微北里二手房出售 小区房价 国奥村(西区)房价走势今日家园房价走势广渠金茂府(北区)房价走势朱雀门小区房价走势景泰嘉园房价走势远洋山水(北区)房价走势天鹅湾(北区)房价走势首城国际房价走势丽都壹号房价走势凤凰城(一期二期四期)房价走势望京花园西区房价走势华清嘉园房价走势御汤山东区房价走势芍药居北里小区房价走势华纺易城房价走势一栋洋房房价走势星河湾畅园房价走势山水文园东园房价走势万象新天家园房价走势翠微北里房价走势 推荐小区价格 百环家园二手房出售紫金长安二手房出售华业东方玫瑰二手房出售首邑溪谷二手房出售新城国际二手房出售金色漫香苑二手房出售美丽园二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售中海紫御公馆二手房出售保利西山林语二手房出售新怡家园二手房出售平乐园小区二手房出售太阳公元(北区)二手房出售珠光逸景(二号院)二手房出售国奥村(东区)二手房出售保利百合花园二手房出售远洋天地二手房出售望京西园三区二手房出售 二手房商圈 海运仓二手房万泉河二手房延庆周边二手房八大处二手房皂君庙二手房麦子店二手房韩村河二手房东辛房二手房紫竹桥二手房媒体村二手房地安门二手房常营二手房通州周边二手房西二旗二手房密云城区二手房潭柘寺二手房新发地二手房五里店二手房保定二手房潞苑二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价亿城西山华府珑园小区亿城西山华府珑园二手房亿城西山华府珑园租房亿城西山华府珑园户型图亿城西山华府珑园周边配置亿城西山华府珑园亿城西山华府珑园实景图亿城西山华府珑园经纪人亿城西山华府珑园房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;亿城西山华府珑园 安居客小区频道，为您提供北京亿城西山华府珑园2009年房价趋势、走势图，亿城西山华府珑园二手房均价价格信息， 及时查询亿城西山华府珑园房价走势、了解亿城西山华府珑园房价上涨还是下跌，预测亿城西山华府珑园房价暴跌暴涨，亿城西山华府珑园房价多少钱一平米？；北京吉屋网提供北京亿城西山公馆二手房出售信息、亿城西山公馆二手房价格，包括及时更新北京亿城西山公馆二手房房源、价格走势、户型图、业主论坛、生活配套。；# 亿城西山公馆_北京亿城西山公馆小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_亿城西山公馆 更新于 2026-06-01 10:46:29 [](https://bj.jiwu.com/tu/5867584.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867585.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867586.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867587.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867588.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867589.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867590.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867591.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867592.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867593.html "亿城西山公馆实景图图片") # 亿城西山公馆 别名：亿城西山公馆 加入本地买房群 关注 _北京 - 海淀 - 海淀东北旺西路8号中关村软件园_ 发地址到手机 参考均价 _77213 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2012_ 小区户数 _676户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-18群（356） * 大家觉得这里未来发展怎么样？</x:v>
+        <x:v>小户型（1室1厅，约40-60㎡）月租5300-6000元/月，大户型（5室2厅）月租32000元/月，4室2厅178.12㎡房源月租19000元/月，商铺600㎡月租9万/月；；2006-2008年建成，开发商亿城山水，物业优质，实行24小时保安巡逻、专业管理；；户型多为板楼，一梯一户/两户，人车分流，绿化率高，居家较清静；；部分房源为精装修，房屋配套较全；；用户未提及隔音相关评价，无明确负面质量反馈；</x:v>
       </x:c>
       <x:c r="L21" t="str">
-        <x:v>from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡ 6月挂牌均价 0.03% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 一层50平园子）全南2居 中间位置 满五年价格可谈双地铁 马连洼 亿城西山华府珑园 846 万 2室2厅 93.51㎡ 万科物业推荐好房 马连洼西山华府一居出售 带电梯 大阳台 马连洼 亿城西山华府珑园 540 万 1室1厅 59.42㎡ 必看好房）马连洼品质2居 带明卫满五一 不临街中高层 双地铁 马连洼 亿城西山华府珑园 1080 万 2室2厅 120.84㎡ 海淀双卫两居 一梯两户 中间位置 车储 万科物业 马连洼 亿城西山华府珑园 1150 万 2室2厅 121.52㎡ 必卖好房）单本全明3居 一车一储 满五年 价格可谈双地铁 马连洼 亿城西山华府珑园 1498 万 3室2厅 177.47㎡ 必看高层）挑高4.2M 一车一储 方正4居 视野开阔价格可谈 马连洼 亿城西山华府珑园 1600 万 4室2厅 176.36㎡ ### 本小区租房推荐查看更多 ### 西山华府 177四居 全齐 马连洼地铁口 人大附中 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 马连洼双地铁 西山华府 一层院子 人大附中 农业大学 马连洼 亿城西山华府珑园 整租 16/18号线 朝南 _11000_ 元/月 2室2厅 93.5㎡ ### 陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 178.8㎡ ### 新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 新增 出租 带车位 集中供暖 家具家电齐全 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 177㎡ ### 万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 178.1㎡ ### 周边热门小区查看更多 * 347 上林溪 海淀 上地 2014年竣工 距离3293m 74659 元/㎡24套在售 小区评测 近地铁 近学校 13号线 五六环之间 户型丰富 配套齐全 7.1 分 * 421 领秀新硅谷AB区 海淀 西二旗 2009年竣工 距离2708m 82732 元/㎡15套在售 小区评测 近地铁 近学校 昌平线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 6.9 分 * 3 当代城市家园 海淀 上地 2004年竣工 距离2550m 69075 元/㎡19套在售 小区评测 近地铁 近学校 13号线等 五六环之间 绿化好 配套齐全 7.2 分 小区单页 国奥村(西区)今日家园广渠金茂府(北区)朱雀门小区景泰嘉园远洋山水(北区)天鹅湾(北区)首城国际丽都壹号凤凰城(一期二期四期)望京花园西区华清嘉园御汤山东区芍药居北里小区华纺易城一栋洋房星河湾畅园山水文园东园万象新天家园翠微北里 本板块小区大全 褐石园今日家园碧桐园颐源居同泽园西里北坞嘉园南里上地佳园翠微南里四季香山雪梨澳乡(别墅)京泉馨苑东里西山美墅馆(别墅)美丽园智学苑香山艺墅交大嘉园尚峰尚水水云居万泉新新家园翠湖别墅 小区二手房 国奥村(西区)二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售朱雀门小区二手房出售景泰嘉园二手房出售远洋山水(北区)二手房出售天鹅湾(北区)二手房出售首城国际二手房出售丽都壹号二手房出售凤凰城(一期二期四期)二手房出售望京花园西区二手房出售华清嘉园二手房出售御汤山东区二手房出售芍药居北里小区二手房出售华纺易城二手房出售一栋洋房二手房出售星河湾畅园二手房出售山水文园东园二手房出售万象新天家园二手房出售翠微北里二手房出售 小区房价 国奥村(西区)房价走势今日家园房价走势广渠金茂府(北区)房价走势朱雀门小区房价走势景泰嘉园房价走势远洋山水(北区)房价走势天鹅湾(北区)房价走势首城国际房价走势丽都壹号房价走势凤凰城(一期二期四期)房价走势望京花园西区房价走势华清嘉园房价走势御汤山东区房价走势芍药居北里小区房价走势华纺易城房价走势一栋洋房房价走势星河湾畅园房价走势山水文园东园房价走势万象新天家园房价走势翠微北里房价走势 推荐小区价格 百环家园二手房出售紫金长安二手房出售华业东方玫瑰二手房出售首邑溪谷二手房出售新城国际二手房出售金色漫香苑二手房出售美丽园二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售中海紫御公馆二手房出售保利西山林语二手房出售新怡家园二手房出售平乐园小区二手房出售太阳公元(北区)二手房出售珠光逸景(二号院)二手房出售国奥村(东区)二手房出售保利百合花园二手房出售远洋天地二手房出售望京西园三区二手房出售 二手房商圈 海运仓二手房万泉河二手房延庆周边二手房八大处二手房皂君庙二手房麦子店二手房韩村河二手房东辛房二手房紫竹桥二手房媒体村二手房地安门二手房常营二手房通州周边二手房西二旗二手房密云城区二手房潭柘寺二手房新发地二手房五里店二手房保定二手房潞苑二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价亿城西山华府珑园小区亿城西山华府珑园二手房亿城西山华府珑园租房亿城西山华府珑园户型图亿城西山华府珑园周边配置亿城西山华府珑园亿城西山华府珑园实景图亿城西山华府珑园经纪人亿城西山华府珑园房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;亿城西山华府珑园 安居客小区频道，为您提供北京亿城西山华府珑园2009年房价趋势、走势图，亿城西山华府珑园二手房均价价格信息， 及时查询亿城西山华府珑园房价走势、了解亿城西山华府珑园房价上涨还是下跌，预测亿城西山华府珑园房价暴跌暴涨，亿城西山华府珑园房价多少钱一平米？；北京吉屋网提供北京亿城西山公馆二手房出售信息、亿城西山公馆二手房价格，包括及时更新北京亿城西山公馆二手房房源、价格走势、户型图、业主论坛、生活配套。；# 亿城西山公馆_北京亿城西山公馆小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_亿城西山公馆 更新于 2026-06-01 10:46:29 [](https://bj.jiwu.com/tu/5867584.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867585.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867586.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867587.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867588.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867589.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867590.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867591.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867592.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867593.html "亿城西山公馆实景图图片") # 亿城西山公馆 别名：亿城西山公馆 加入本地买房群 关注 _北京 - 海淀 - 海淀东北旺西路8号中关村软件园_ 发地址到手机 参考均价 _77213 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2012_ 小区户数 _676户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-18群（356） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；答 选购亿城西山公馆的房子要注意第一，首先看亿城西山公馆的地理位置，亿城西山公馆的地处位于海淀东北旺西路8号中关村软件园交通便利。</x:v>
+        <x:v>部分房源为精装修，房屋配套较全；；地铁方面，16号线马连洼站步行约732-939米，18号线马连洼站步行约887米；；周边有新北门诊部、西苑医院等医疗资源；；商超有金源Shopping Mal、新中关等，餐饮配套丰富；；日常购物、通勤便利，周边配套成熟；</x:v>
       </x:c>
       <x:c r="M21" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。</x:v>
+        <x:v>商铺出租需注意业态限制（如部分要求餐饮行业需明确是否可明火等），无明确重大差评风险。；商铺出租需注意业态限制（如部分要求餐饮行业需明确是否可明火等），无明确重大差评风险</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>价格线索：录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡； 上地 2014年竣工 距离3293m 74659 元/㎡；西二旗 2009年竣工 距离2708m 82732 元/㎡； 上地 2004年竣工 距离2550m 69075 元/㎡；00_ 元/m² 亿城西山公馆，小区价格77213元/㎡；采暖 装 修： 毛坯 车 位 费： 地上150元/月；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) [](https://esf.fang.com/loupan/1010257223/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **90429** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.9% 贷款计算器 * 二手房源 92套 * 最近成交 141套 * 楼栋总数 48栋 * 房屋总数 1606户 * 建筑类型 板楼 * 建筑年代 2011年建成 * 小区位置 马连洼北路与竹园中街交汇处南行150米路两侧地图 * 物业公司 北京亿城物业管理有限公司 * 开发商 北京亿城山水房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 王智慧 评分：4.9 从业信息卡 闪电回复 ##### 徐强 评分：4.9 从业信息卡 百科 闪电回复 ### 西山华府主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010257223/photo/?；from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡ 6月挂牌均价 0.03% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 一层50平园子）全南2居 中间位置 满五年价格可谈双地铁 马连洼 亿城西山华府珑园 846 万 2室2厅 93.51㎡ 万科物业推荐好房 马连洼西山华府一居出售 带电梯 大阳台 马连洼 亿城西山华府珑园 540 万 1室1厅 59.42㎡ 必看好房）马连洼品质2居 带明卫满五一 不临街中高层 双地铁 马连洼 亿城西山华府珑园 1080 万 2室2厅 120.84㎡ 海淀双卫两居 一梯两户 中间位置 车储 万科物业 马连洼 亿城西山华府珑园 1150 万 2室2厅 121.52㎡ 必卖好房）单本全明3居 一车一储 满五年 价格可谈双地铁 马连洼 亿城西山华府珑园 1498 万 3室2厅 177.47㎡ 必看高层）挑高4.2M 一车一储 方正4居 视野开阔价格可谈 马连洼 亿城西山华府珑园 1600 万 4室2厅 176.36㎡ ### 本小区租房推荐查看更多 ### 西山华府 177四居 全齐 马连洼地铁口 人大附中 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 马连洼双地铁 西山华府 一层院子 人大附中 农业大学 马连洼 亿城西山华府珑园 整租 16/18号线 朝南 _11000_ 元/月 2室2厅 93.5㎡ ### 陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 178.8㎡ ### 新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 新增 出租 带车位 集中供暖 家具家电齐全 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 177㎡ ### 万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 178.1㎡ ### 周边热门小区查看更多 * 347 上林溪 海淀 上地 2014年竣工 距离3293m 74659 元/㎡24套在售 小区评测 近地铁 近学校 13号线 五六环之间 户型丰富 配套齐全 7.1 分 * 421 领秀新硅谷AB区 海淀 西二旗 2009年竣工 距离2708m 82732 元/㎡15套在售 小区评测 近地铁 近学校 昌平线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 6.9 分 * 3 当代城市家园 海淀 上地 2004年竣工 距离2550m 69075 元/㎡19套在售 小区评测 近地铁 近学校 13号线等 五六环之间 绿化好 配套齐全 7.2 分 小区单页 国奥村(西区)今日家园广渠金茂府(北区)朱雀门小区景泰嘉园远洋山水(北区)天鹅湾(北区)首城国际丽都壹号凤凰城(一期二期四期)望京花园西区华清嘉园御汤山东区芍药居北里小区华纺易城一栋洋房星河湾畅园山水文园东园万象新天家园翠微北里 本板块小区大全 褐石园今日家园碧桐园颐源居同泽园西里北坞嘉园南里上地佳园翠微南里四季香山雪梨澳乡(别墅)京泉馨苑东里西山美墅馆(别墅)美丽园智学苑香山艺墅交大嘉园尚峰尚水水云居万泉新新家园翠湖别墅 小区二手房 国奥村(西区)二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售朱雀门小区二手房出售景泰嘉园二手房出售远洋山水(北区)二手房出售天鹅湾(北区)二手房出售首城国际二手房出售丽都壹号二手房出售凤凰城(一期二期四期)二手房出售望京花园西区二手房出售华清嘉园二手房出售御汤山东区二手房出售芍药居北里小区二手房出售华纺易城二手房出售一栋洋房二手房出售星河湾畅园二手房出售山水文园东园二手房出售万象新天家园二手房出售翠微北里二手房出售 小区房价 国奥村(西区)房价走势今日家园房价走势广渠金茂府(北区)房价走势朱雀门小区房价走势景泰嘉园房价走势远洋山水(北区)房价走势天鹅湾(北区)房价走势首城国际房价走势丽都壹号房价走势凤凰城(一期二期四期)房价走势望京花园西区房价走势华清嘉园房价走势御汤山东区房价走势芍药居北里小区房价走势华纺易城房价走势一栋洋房房价走势星河湾畅园房价走势山水文园东园房价走势万象新天家园房价走势翠微北里房价走势 推荐小区价格 百环家园二手房出售紫金长安二手房出售华业东方玫瑰二手房出售首邑溪谷二手房出售新城国际二手房出售金色漫香苑二手房出售美丽园二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售中海紫御公馆二手房出售保利西山林语二手房出售新怡家园二手房出售平乐园小区二手房出售太阳公元(北区)二手房出售珠光逸景(二号院)二手房出售国奥村(东区)二手房出售保利百合花园二手房出售远洋天地二手房出售望京西园三区二手房出售 二手房商圈 海运仓二手房万泉河二手房延庆周边二手房八大处二手房皂君庙二手房麦子店二手房韩村河二手房东辛房二手房紫竹桥二手房媒体村二手房地安门二手房常营二手房通州周边二手房西二旗二手房密云城区二手房潭柘寺二手房新发地二手房五里店二手房保定二手房潞苑二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价亿城西山华府珑园小区亿城西山华府珑园二手房亿城西山华府珑园租房亿城西山华府珑园户型图亿城西山华府珑园周边配置亿城西山华府珑园亿城西山华府珑园实景图亿城西山华府珑园经纪人亿城西山华府珑园房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;亿城西山华府珑园 安居客小区频道，为您提供北京亿城西山华府珑园2009年房价趋势、走势图，亿城西山华府珑园二手房均价价格信息， 及时查询亿城西山华府珑园房价走势、了解亿城西山华府珑园房价上涨还是下跌，预测亿城西山华府珑园房价暴跌暴涨，亿城西山华府珑园房价多少钱一平米？；北京吉屋网提供北京亿城西山公馆二手房出售信息、亿城西山公馆二手房价格，包括及时更新北京亿城西山公馆二手房房源、价格走势、户型图、业主论坛、生活配套。；# 亿城西山公馆_北京亿城西山公馆小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_亿城西山公馆 更新于 2026-06-01 10:46:29 [](https://bj.jiwu.com/tu/5867584.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867585.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867586.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867587.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867588.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867589.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867590.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867591.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867592.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867593.html "亿城西山公馆实景图图片") # 亿城西山公馆 别名：亿城西山公馆 加入本地买房群 关注 _北京 - 海淀 - 海淀东北旺西路8号中关村软件园_ 发地址到手机 参考均价 _77213 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2012_ 小区户数 _676户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-18群（356） * 大家觉得这里未来发展怎么样？；生活便利线索：from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡ 6月挂牌均价 0.03% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 一层50平园子）全南2居 中间位置 满五年价格可谈双地铁 马连洼 亿城西山华府珑园 846 万 2室2厅 93.51㎡ 万科物业推荐好房 马连洼西山华府一居出售 带电梯 大阳台 马连洼 亿城西山华府珑园 540 万 1室1厅 59.42㎡ 必看好房）马连洼品质2居 带明卫满五一 不临街中高层 双地铁 马连洼 亿城西山华府珑园 1080 万 2室2厅 120.84㎡ 海淀双卫两居 一梯两户 中间位置 车储 万科物业 马连洼 亿城西山华府珑园 1150 万 2室2厅 121.52㎡ 必卖好房）单本全明3居 一车一储 满五年 价格可谈双地铁 马连洼 亿城西山华府珑园 1498 万 3室2厅 177.47㎡ 必看高层）挑高4.2M 一车一储 方正4居 视野开阔价格可谈 马连洼 亿城西山华府珑园 1600 万 4室2厅 176.36㎡ ### 本小区租房推荐查看更多 ### 西山华府 177四居 全齐 马连洼地铁口 人大附中 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 马连洼双地铁 西山华府 一层院子 人大附中 农业大学 马连洼 亿城西山华府珑园 整租 16/18号线 朝南 _11000_ 元/月 2室2厅 93.5㎡ ### 陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 178.8㎡ ### 新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 新增 出租 带车位 集中供暖 家具家电齐全 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 177㎡ ### 万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 178.1㎡ ### 周边热门小区查看更多 * 347 上林溪 海淀 上地 2014年竣工 距离3293m 74659 元/㎡24套在售 小区评测 近地铁 近学校 13号线 五六环之间 户型丰富 配套齐全 7.1 分 * 421 领秀新硅谷AB区 海淀 西二旗 2009年竣工 距离2708m 82732 元/㎡15套在售 小区评测 近地铁 近学校 昌平线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 6.9 分 * 3 当代城市家园 海淀 上地 2004年竣工 距离2550m 69075 元/㎡19套在售 小区评测 近地铁 近学校 13号线等 五六环之间 绿化好 配套齐全 7.2 分 小区单页 国奥村(西区)今日家园广渠金茂府(北区)朱雀门小区景泰嘉园远洋山水(北区)天鹅湾(北区)首城国际丽都壹号凤凰城(一期二期四期)望京花园西区华清嘉园御汤山东区芍药居北里小区华纺易城一栋洋房星河湾畅园山水文园东园万象新天家园翠微北里 本板块小区大全 褐石园今日家园碧桐园颐源居同泽园西里北坞嘉园南里上地佳园翠微南里四季香山雪梨澳乡(别墅)京泉馨苑东里西山美墅馆(别墅)美丽园智学苑香山艺墅交大嘉园尚峰尚水水云居万泉新新家园翠湖别墅 小区二手房 国奥村(西区)二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售朱雀门小区二手房出售景泰嘉园二手房出售远洋山水(北区)二手房出售天鹅湾(北区)二手房出售首城国际二手房出售丽都壹号二手房出售凤凰城(一期二期四期)二手房出售望京花园西区二手房出售华清嘉园二手房出售御汤山东区二手房出售芍药居北里小区二手房出售华纺易城二手房出售一栋洋房二手房出售星河湾畅园二手房出售山水文园东园二手房出售万象新天家园二手房出售翠微北里二手房出售 小区房价 国奥村(西区)房价走势今日家园房价走势广渠金茂府(北区)房价走势朱雀门小区房价走势景泰嘉园房价走势远洋山水(北区)房价走势天鹅湾(北区)房价走势首城国际房价走势丽都壹号房价走势凤凰城(一期二期四期)房价走势望京花园西区房价走势华清嘉园房价走势御汤山东区房价走势芍药居北里小区房价走势华纺易城房价走势一栋洋房房价走势星河湾畅园房价走势山水文园东园房价走势万象新天家园房价走势翠微北里房价走势 推荐小区价格 百环家园二手房出售紫金长安二手房出售华业东方玫瑰二手房出售首邑溪谷二手房出售新城国际二手房出售金色漫香苑二手房出售美丽园二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售中海紫御公馆二手房出售保利西山林语二手房出售新怡家园二手房出售平乐园小区二手房出售太阳公元(北区)二手房出售珠光逸景(二号院)二手房出售国奥村(东区)二手房出售保利百合花园二手房出售远洋天地二手房出售望京西园三区二手房出售 二手房商圈 海运仓二手房万泉河二手房延庆周边二手房八大处二手房皂君庙二手房麦子店二手房韩村河二手房东辛房二手房紫竹桥二手房媒体村二手房地安门二手房常营二手房通州周边二手房西二旗二手房密云城区二手房潭柘寺二手房新发地二手房五里店二手房保定二手房潞苑二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价亿城西山华府珑园小区亿城西山华府珑园二手房亿城西山华府珑园租房亿城西山华府珑园户型图亿城西山华府珑园周边配置亿城西山华府珑园亿城西山华府珑园实景图亿城西山华府珑园经纪人亿城西山华府珑园房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;亿城西山华府珑园 安居客小区频道，为您提供北京亿城西山华府珑园2009年房价趋势、走势图，亿城西山华府珑园二手房均价价格信息， 及时查询亿城西山华府珑园房价走势、了解亿城西山华府珑园房价上涨还是下跌，预测亿城西山华府珑园房价暴跌暴涨，亿城西山华府珑园房价多少钱一平米？；北京吉屋网提供北京亿城西山公馆二手房出售信息、亿城西山公馆二手房价格，包括及时更新北京亿城西山公馆二手房房源、价格走势、户型图、业主论坛、生活配套。；# 亿城西山公馆_北京亿城西山公馆小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_亿城西山公馆 更新于 2026-06-01 10:46:29 [](https://bj.jiwu.com/tu/5867584.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867585.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867586.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867587.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867588.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867589.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867590.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867591.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867592.html "亿城西山公馆实景图图片")[](https://bj.jiwu.com/tu/5867593.html "亿城西山公馆实景图图片") # 亿城西山公馆 别名：亿城西山公馆 加入本地买房群 关注 _北京 - 海淀 - 海淀东北旺西路8号中关村软件园_ 发地址到手机 参考均价 _77213 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2012_ 小区户数 _676户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-18群（356） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；答 选购亿城西山公馆的房子要注意第一，首先看亿城西山公馆的地理位置，亿城西山公馆的地处位于海淀东北旺西路8号中关村软件园交通便利。；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。</x:v>
+        <x:v>价格线索：1室1厅，约40-60㎡）月租5300-6000元/月；，大户型（5室2厅）月租32000元/月；，4室2厅178.12㎡房源月租19000元/月；，商铺600㎡月租9万/月；房屋质量/户型线索：小户型（1室1厅，约40-60㎡）月租5300-6000元/月，大户型（5室2厅）月租32000元/月，4室2厅178.12㎡房源月租19000元/月，商铺600㎡月租9万/月；；2006-2008年建成，开发商亿城山水，物业优质，实行24小时保安巡逻、专业管理；；户型多为板楼，一梯一户/两户，人车分流，绿化率高，居家较清静；；部分房源为精装修，房屋配套较全；；用户未提及隔音相关评价，无明确负面质量反馈；；生活便利线索：部分房源为精装修，房屋配套较全；；地铁方面，16号线马连洼站步行约732-939米，18号线马连洼站步行约887米；；周边有新北门诊部、西苑医院等医疗资源；；商超有金源Shopping Mal、新中关等，餐饮配套丰富；；日常购物、通勤便利，周边配套成熟；；风险线索：商铺出租需注意业态限制（如部分要求餐饮行业需明确是否可明火等），无明确重大差评风险。；商铺出租需注意业态限制（如部分要求餐饮行业需明确是否可明火等），无明确重大差评风险</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>1. 【北京西山华府小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010257223.htm
-2. 亿城西山华府珑园房价, 亿城西山华府珑园亿城西山华府珑园房价走势图, 亿城西山华府珑园价格均价多少钱-安居客 https://m.anjuke.com/bj/trendency/community/851045/
-3. 亿城西山公馆_北京亿城西山公馆小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/55072.html
-4. 亿城西山华府 https://baike.baidu.com/item/%E4%BA%BF%E5%9F%8E%E8%A5%BF%E5%B1%B1%E5%8D%8E%E5%BA%9C/5176873
-5. 【北京欧亿登录入口soo8.top租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kw%E6%AC%A7%E4%BA%BF%E7%99%BB%E5%BD%95%E5%85%A5%E5%8F%A3soo8.top?425%20target=_blank</x:v>
+        <x:v>1. https://bj.esf.fang.com/loupan/1010257223/strategy.htm
+2. https://map.360.cn/site/detail/1f00a77117ef3186
+3. http://m.anjuke.com/bj/rent/4527674915331085-3/
+4. http://m.anjuke.com/bj/rent/4605485220703241-3/
+5. 2026北京西山华府小区，配套指南，买房攻略 https://bj.esf.fang.com/loupan/1010257223/strategy.htm
+6. 亿城西山华府 https://map.360.cn/site/detail/1f00a77117ef3186
+7. 西山华府 精装一居室 实图拍摄 价格可聊 和业主签约 可长租 http://m.anjuke.com/bj/rent/4527674915331085-3/
+8. 亿城西山华府怎么样 https://www.kupet.cn/read-1773826583a35540208.html</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1247,39 +1305,42 @@
         <x:v>北京市海淀区西北旺东路威凯西北旺镇辛店A地块东侧约40米</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F22" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G22" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H22" t="n">
-        <x:v>6.5</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="I22" t="str">
-        <x:v>紧邻网易但租金极高，属于顶级豪宅区，需注意早晚高峰严重的交通拥堵问题。</x:v>
+        <x:v>缺乏具体小区质量信息，多为周边参考数据，胜在靠近软件园且通勤便利。</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>55000 元/月；12000 元/月；65000 元/月；58000 元/月；180000 元/月；138000 元/月；75000 元/月；80000 元/月</x:v>
+        <x:v>周边类似西北旺后厂村合租价格约2000-2500元/月；，整租约4000-5800元/月</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v># 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；58000 元/月 [](https://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；30000 元/月 [](https://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；22000 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。</x:v>
+        <x:v>未找到该小区（后厂村路61号院）明确的隔音、房龄、物业等质量信息，周边同区域小区普遍为精装修，物业安保相对完善；</x:v>
       </x:c>
       <x:c r="L22" t="str">
-        <x:v>) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；交通便利南北通透 18000 元/月 [](https://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；采光好周边配套齐 21800 元/月 [](https://www.fang.com/chuzu/3_486903096_1.htm) 清华大学双清苑 附小陪读 全新精装南北三居室 首次出 整租|3室2厅|122㎡|朝南北 海淀-学院路-双清苑 距昌平线学知园站约1157米。；交通便利周边配套齐采光好 20000 元/月 [](https://www.fang.com/chuzu/3_486864130_1.htm) 20套起看 万柳书院万城华府 2居南北通透 有车位有 整租|2室2厅|116㎡|朝南北 海淀-万柳-万城华府龙园 距10号线火器营站约436米。；交通便利周边配套齐首次出租 3000 元/月 [](https://www.fang.com/chuzu/3_481166418_1.htm) 西直门凯德茂。</x:v>
-      </x:c>
-      <x:c r="M22" t="str">
-        <x:v>交通拥堵严重，早晚高峰是痛点。</x:v>
-      </x:c>
+        <x:v>暂未找到「后厂村路61号院」直接相关的租房价格，周边类似西北旺后厂村合租价格约2000-2500元/月，整租约4000-5800元/月（仅供参考）；；未找到该小区（后厂村路61号院）明确的隔音、房龄、物业等质量信息，周边同区域小区普遍为精装修，物业安保相对完善；；未找到该小区直接的通勤、地铁、商超等便利信息，周边后厂村区域靠近16号线西北旺站，通勤至软件园便利，有商业配套（参考周边小区）；</x:v>
+      </x:c>
+      <x:c r="M22" t="str"/>
       <x:c r="N22" t="str">
-        <x:v>价格线索：55000 元/月；12000 元/月；65000 元/月；58000 元/月；180000 元/月；138000 元/月；75000 元/月；80000 元/月；房屋质量/户型线索：# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；58000 元/月 [](https://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；30000 元/月 [](https://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；22000 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。；生活便利线索：) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；交通便利南北通透 18000 元/月 [](https://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；采光好周边配套齐 21800 元/月 [](https://www.fang.com/chuzu/3_486903096_1.htm) 清华大学双清苑 附小陪读 全新精装南北三居室 首次出 整租|3室2厅|122㎡|朝南北 海淀-学院路-双清苑 距昌平线学知园站约1157米。；交通便利周边配套齐采光好 20000 元/月 [](https://www.fang.com/chuzu/3_486864130_1.htm) 20套起看 万柳书院万城华府 2居南北通透 有车位有 整租|2室2厅|116㎡|朝南北 海淀-万柳-万城华府龙园 距10号线火器营站约436米。；交通便利周边配套齐首次出租 3000 元/月 [](https://www.fang.com/chuzu/3_481166418_1.htm) 西直门凯德茂。；风险线索：交通拥堵严重，早晚高峰是痛点。</x:v>
+        <x:v>价格线索：周边类似西北旺后厂村合租价格约2000-2500元/月；，整租约4000-5800元/月；房屋质量/户型线索：未找到该小区（后厂村路61号院）明确的隔音、房龄、物业等质量信息，周边同区域小区普遍为精装修，物业安保相对完善；；生活便利线索：暂未找到「后厂村路61号院」直接相关的租房价格，周边类似西北旺后厂村合租价格约2000-2500元/月，整租约4000-5800元/月（仅供参考）；；未找到该小区（后厂村路61号院）明确的隔音、房龄、物业等质量信息，周边同区域小区普遍为精装修，物业安保相对完善；；未找到该小区直接的通勤、地铁、商超等便利信息，周边后厂村区域靠近16号线西北旺站，通勤至软件园便利，有商业配套（参考周边小区）；</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>1. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_253028bj/
-2. 「海淀后厂村路附近独栋写字楼出租，企房房怎么找靠谱？/办公楼出租」- 写字楼租房网 https://bj-sydc.com/article.php?id=46249
-3. 讨论精选（豆瓣） https://www.douban.com/group/explore</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4605536645356553-3/
+2. https://bj.zu.anjuke.com/fangyuan/4397393908870158
+3. http://m.anjuke.com/ch/rent/4543257953475590-3/
+4. 无中介 可月付 紧邻新澄海 后厂村路 百度 快手 上地软件园 http://m.anjuke.com/bj/rent/4605536645356553-3/
+5. 田村半壁店61号院丨精装南北低价两居出租丨家电齐全随时看房 https://bj.zu.anjuke.com/fangyuan/4397393908870158
+6. 西北旺后厂村 随时可以看房精装修 配置齐全 http://m.anjuke.com/ch/rent/4543257953475590-3/
+7. 首月减免步行后厂村网易大楼新浪大厦腾讯总部联想总部百度大厦 http://m.anjuke.com/bj/rent/4537454348643343-3/
+8. 北京海淀后厂村房东直租无中介费，押一付一 https://www.douban.com/group/topic/337526078/?_spm_id=MTU2MjMwODgx</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1296,41 +1357,44 @@
         <x:v>北京市海淀区德政路51号</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F23" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G23" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H23" t="n">
-        <x:v>4.5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I23" t="str">
-        <x:v>网页证据存在大量泛化信息，跨区数据干扰严重，真实租住品质与价格难以准确评估。</x:v>
+        <x:v>离地铁近且配套极佳，紧邻万象汇，房龄虽老但户型采光好，是高性价比之选。</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>贝壳找房北京小区大全,夏霖园参考均价:58253元/㎡；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；镇江胡同 可注册办公首次出租南北通透 140000 元/月；105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月；营-信德园 可注册办公首次出租南北通透 10500 元/月</x:v>
+        <x:v>租房价格：整租方面，1室1厅约5500-5800元/月；，2室1厅约6650-7000元/月；，3室1厅约6950-9000元/月；合租次卧约2300元/月</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 4室2厅泰禾西府大院 整租|4室2厅|197㎡|朝东南北 丰台-丽泽桥-泰禾西府大院 52000 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；特点是租金低于同品质同地段的市场租赁住房租金，不过是面向符合条件的人群才进行配租。；以政府租赁配租的安居高新花园为例，其64平米的两房户型，月租金加上物业费总计仅需3916元；</x:v>
+        <x:v>房龄：2003年建成，楼龄22年；；装修：房源多为精装修，部分简装；；户型：南北通透，有1室1厅、2室1厅、3室1厅等户型，楼层涵盖低层、高层；；物业：北京旺达家兴物业管理有限公司，物业费0.8元/㎡·月；；未明确提及隔音相关评价，但房源采光、通风情况较好。</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；而据链家网信息显示，周边同户型房源月租普遍在7000至9000元之间，价格优势明显。；泉州中心市区首批公开92套保租房，其中面积80多平米的两居室月租金在1500元左右，20平米的一居室月租金仅需700余元，而周边同等一居室月租金则在1000元以上。</x:v>
+        <x:v>通勤：距16号线西北旺站步行约795米，周边公交站夏霖园站145米，附近有多条公交线路，出行便捷；；生活配套：周边有夏霖园超市（41米）、西北旺万象汇购物中心（574米）、U悦生活广场（1762米）等商超；；餐饮：3千米内有445个餐厅，满足多样餐饮需求；；医疗：5千米内有北京积水潭医院（新龙泽院区）、北医三院（中央党校院区）等医院，3千米内有25个药店，就医便利；；休闲：周边有中关村公园、首师大附中口袋公园等多个公园，休闲资源丰富。</x:v>
       </x:c>
       <x:c r="M23" t="str">
-        <x:v>北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>搜索结果未发现明确的租房风险或差评信息，房源多提及优势，无明显负面反馈。</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>价格线索：贝壳找房北京小区大全,夏霖园参考均价:58253元/㎡；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；镇江胡同 可注册办公首次出租南北通透 140000 元/月；105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月；营-信德园 可注册办公首次出租南北通透 10500 元/月；房屋质量/户型线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 4室2厅泰禾西府大院 整租|4室2厅|197㎡|朝东南北 丰台-丽泽桥-泰禾西府大院 52000 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；特点是租金低于同品质同地段的市场租赁住房租金，不过是面向符合条件的人群才进行配租。；以政府租赁配租的安居高新花园为例，其64平米的两房户型，月租金加上物业费总计仅需3916元；；生活便利线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；而据链家网信息显示，周边同户型房源月租普遍在7000至9000元之间，价格优势明显。；泉州中心市区首批公开92套保租房，其中面积80多平米的两居室月租金在1500元左右，20平米的一居室月租金仅需700余元，而周边同等一居室月租金则在1000元以上。；风险线索：北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：租房价格：整租方面，1室1厅约5500-5800元/月；，2室1厅约6650-7000元/月；，3室1厅约6950-9000元/月；合租次卧约2300元/月；房屋质量/户型线索：房龄：2003年建成，楼龄22年；；装修：房源多为精装修，部分简装；；户型：南北通透，有1室1厅、2室1厅、3室1厅等户型，楼层涵盖低层、高层；；物业：北京旺达家兴物业管理有限公司，物业费0.8元/㎡·月；；未明确提及隔音相关评价，但房源采光、通风情况较好。；生活便利线索：通勤：距16号线西北旺站步行约795米，周边公交站夏霖园站145米，附近有多条公交线路，出行便捷；；生活配套：周边有夏霖园超市（41米）、西北旺万象汇购物中心（574米）、U悦生活广场（1762米）等商超；；餐饮：3千米内有445个餐厅，满足多样餐饮需求；；医疗：5千米内有北京积水潭医院（新龙泽院区）、北医三院（中央党校院区）等医院，3千米内有25个药店，就医便利；；休闲：周边有中关村公园、首师大附中口袋公园等多个公园，休闲资源丰富。；风险线索：搜索结果未发现明确的租房风险或差评信息，房源多提及优势，无明显负面反馈。</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>1. 北京夏霖园二手房|房价 - 贝壳 https://m.ke.com/bj/xiaoqu/1111046364973
-2. 【北京半岛平台wa48.cc租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kw%E5%8D%8A%E5%B2%9B%E5%B9%B3%E5%8F%B0wa48.cc?133%20target=_blank
-3. 保租房“6折价格战”，长租公寓吃得消吗？ - 21财经 https://m.21jingji.com/article/20250311/herald/e2987f1ac77a7e246e6321c104504ccc.html
-4. 贝壳租房房屋评价体系全国上线 高品质好房将获重点推荐 https://finance.sina.com.cn/jjxw/2026-01-07/doc-inhfnktv2240535.shtml
-5. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4585828594066446-3/
+2. https://m.5i5j.com/bj/ershoufang/504862843.html
+3. http://m.fang.com/xiaoqu/strategy/bj/1010533385.html?position=xqcomparebox
+4. 急租！夏霖园干净整洁自住好户型三居室 http://m.anjuke.com/bj/rent/4585828594066446-3/
+5. 夏霖园 2室出租 业主直签 要求一家人住 价格 https://bj.zu.anjuke.com/fangyuan/4481954704190469
+6. 2026北京百旺新城夏霖园小区，配套指南，买房攻略-北京房天下 http://m.fang.com/xiaoqu/strategy/bj/1010533385.html?position=xqcomparebox
+7. 夏霖园 阳光充足 15平 电梯房 http://m.anjuke.com/bj/rent/4541711756110849-3/
+8. 西北旺·夏霖园·3室·1厅 https://m.5i5j.com/bj/ershoufang/504862843.html</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1347,41 +1411,42 @@
         <x:v>北京市海淀区永丰路百旺公园东150米</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F24" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G24" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H24" t="n">
-        <x:v>7.8</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I24" t="str">
-        <x:v>位于西北旺核心地带，房龄新且配套优越，虽租金门槛高，是高净值人群的理想选择。</x:v>
+        <x:v>万科物业高端社区，2015年房龄且隔音好，但租金极高，适合高预算人群。</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>满二年 近地铁 车位充足 3280 万 104164元/㎡；满五年 近地铁 车位充足 3500 万 112356元/㎡；地铁 车位充足 采光较好 3700 万 129208元/㎡；有电梯 近地铁 车位充足 3280 万 104164元/㎡；路 东南 满五年 近地铁 1450 万 88340元/㎡；2室1厅1卫丨103㎡丨西南丨低楼层丨 118900元/㎡；2室1厅1卫丨103㎡丨西南丨高楼层丨 128100元/㎡； 2室2厅1卫丨93㎡丨东南丨中楼层丨 135500元/㎡</x:v>
+        <x:v>园北区3室3厅2卫户型月租约24000-26000元/月；，5室2厅4卫户型月租约45000元/月；，南区4室2厅4卫户型月租约25000元/月；，另有2室户型月租1800元/月</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **102963** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓0.72% 贷款计算器 * 二手房源 116套 * 最近成交 69套 * 楼栋总数 26栋 * 房屋总数 1011户 * 建筑类型 板楼 * 建筑年代 2015年建成 * 小区位置 西北旺镇永丰路与后厂村路交界东南角地图 * 物业公司 北京万科物业管理有限公司 * 开发商 北京万湖房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 王福兴 评分：5.0 从业信息卡 百科 闪电回复 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 徐强 评分：4.9 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 如园标准四居 4室2厅 260.0㎡**2499**万 * #### 好房好视野 3室3厅 224.2㎡**2350**万 * #### 如园北区6室6厅南北 6室6厅 438.06㎡**4680**万 * #### 如园北区4室2厅南北 4室2厅 313.38㎡**2180**万 ### 五矿万科如园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 255.00㎡ | 2026-04-20 | -- | -- | 市场信息 | | 282.04㎡ | 2026-03-16 | -- | -- | 市场信息 | | 374.04㎡ | 2025-09-18 | -- | -- | 市场信息 | 查看全部成交 ### 五矿万科如园价格走势 ### 五矿万科如园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 五矿万科如园 海淀·马连洼**102964** 元/㎡ * #### 芳怡园 海淀·马连洼**69034** 元/㎡ * #### 百旺新城景和园 海淀·西北旺**66305** 元/㎡ * #### 百旺茉莉园 海淀·西北旺**75443** 元/㎡ * #### 中海枫涟山庄 海淀·西北旺**82937** 元/㎡ ### 相关资讯 * 小区资讯北京五矿万科如园怎么样?；五矿万科如园地址、户型和价格全览2021-09-25 * 小区资讯马连洼人都在看!；丽兹行提供近300个一二手豪宅楼盘信息介绍，可全面查看楼盘价格，户型、配套及成交信息。；) 实景图 1/52 实景图 2/52 实景图 3/52 实景图 4/52 实景图 5/52 实景图 6/52 实景图 7/52 实景图 8/52 实景图 9/52 实景图 10/52 实景图 11/52 实景图 12/52 实景图 13/52 实景图 14/52 实景图 15/52 实景图 16/52 实景图 17/52 实景图 18/52 实景图 19/52 实景图 20/52 实景图 21/52 实景图 22/52 实景图 23/52 实景图 24/52 实景图 25/52 实景图 26/52 实景图 27/52 实景图 28/52 实景图 29/52 实景图 30/52 实景图 31/52 实景图 32/52 实景图 33/52 实景图 34/52 实景图 35/52 实景图 36/52 实景图 37/52 实景图 38/52 实景图 39/52 实景图 40/52 实景图 41/52 实景图 42/52 实景图 43/52 实景图 44/52 实景图 45/52 实景图 46/52 实景图 47/52 实景图 48/52 实景图 49/52 实景图 50/52 实景图 51/52 实景图 52/52 效果图 1/13 效果图 2/13 效果图 3/13 效果图 4/13 效果图 5/13 效果图 6/13 效果图 7/13 效果图 8/13 效果图 9/13 效果图 10/13 效果图 11/13 效果图 12/13 效果图 13/13 位置图 1/1 周边配套图 1/22 周边配套图 2/22 周边配套图 3/22 周边配套图 4/22 周边配套图 5/22 周边配套图 6/22 周边配套图 7/22 周边配套图 8/22 周边配套图 9/22 周边配套图 10/22 周边配套图 11/22 周边配套图 12/22 周边配套图 13/22 周边配套图 14/22 周边配套图 15/22 周边配套图 16/22 周边配套图 17/22 周边配套图 18/22 周边配套图 19/22 周边配套图 20/22 周边配套图 21/22 周边配套图 22/22 楼栋分布图 1/1 实景图(52) 效果图(13) 位置图(1) 周边配套图(22) 楼栋分布图(1) 二手售价 1930-7000万 二手均价 6.18-13.78万/㎡ * 在售房源16套 * 在租房源1套 * 产品类型： 高档住宅 * 建筑年代： 2011-2018年 * 拿地时间： 2010.12.06 * 物业费： 6.9元/㎡/月 * 物业公司： 万科物业管理有限公司 * 开发商： 北京万湖房地产开发有限公司/北京五矿万科置业有限公司 [](https://mbj.lizihang.com/adviser/undefined.html) ##### **我维护该楼盘，为您提供买卖、租赁委托服务** **转** ### 灵魂卖点 ### 楼盘位置 ### 户型设计 ### 生活配套 ### 居住体验 ### 租售房源 ### 楼盘参数 ### 楼盘故事 ### 推荐楼盘 #### * 万科打造的精装科技住宅，配上家具家电即可入住。</x:v>
+        <x:v>小区租房以大户型为主，如园北区3室3厅2卫户型月租约24000-26000元/月，5室2厅4卫户型月租约45000元/月，南区4室2厅4卫户型月租约25000元/月，另有2室户型月租1800元/月（注意此房源可能非目标小区，目标为海淀区永丰路如园）；；房龄约2015年，精装修，隔音：部分临路房源精装修隔音较好；；物业为北京万科物业服务有限公司，物业费6.9元/平米/月；；户型多为南北通透，动静分离设计；</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>丽兹行提供近300个一二手豪宅楼盘信息介绍，可全面查看楼盘价格，户型、配套及成交信息。；) 实景图 1/52 实景图 2/52 实景图 3/52 实景图 4/52 实景图 5/52 实景图 6/52 实景图 7/52 实景图 8/52 实景图 9/52 实景图 10/52 实景图 11/52 实景图 12/52 实景图 13/52 实景图 14/52 实景图 15/52 实景图 16/52 实景图 17/52 实景图 18/52 实景图 19/52 实景图 20/52 实景图 21/52 实景图 22/52 实景图 23/52 实景图 24/52 实景图 25/52 实景图 26/52 实景图 27/52 实景图 28/52 实景图 29/52 实景图 30/52 实景图 31/52 实景图 32/52 实景图 33/52 实景图 34/52 实景图 35/52 实景图 36/52 实景图 37/52 实景图 38/52 实景图 39/52 实景图 40/52 实景图 41/52 实景图 42/52 实景图 43/52 实景图 44/52 实景图 45/52 实景图 46/52 实景图 47/52 实景图 48/52 实景图 49/52 实景图 50/52 实景图 51/52 实景图 52/52 效果图 1/13 效果图 2/13 效果图 3/13 效果图 4/13 效果图 5/13 效果图 6/13 效果图 7/13 效果图 8/13 效果图 9/13 效果图 10/13 效果图 11/13 效果图 12/13 效果图 13/13 位置图 1/1 周边配套图 1/22 周边配套图 2/22 周边配套图 3/22 周边配套图 4/22 周边配套图 5/22 周边配套图 6/22 周边配套图 7/22 周边配套图 8/22 周边配套图 9/22 周边配套图 10/22 周边配套图 11/22 周边配套图 12/22 周边配套图 13/22 周边配套图 14/22 周边配套图 15/22 周边配套图 16/22 周边配套图 17/22 周边配套图 18/22 周边配套图 19/22 周边配套图 20/22 周边配套图 21/22 周边配套图 22/22 楼栋分布图 1/1 实景图(52) 效果图(13) 位置图(1) 周边配套图(22) 楼栋分布图(1) 二手售价 1930-7000万 二手均价 6.18-13.78万/㎡ * 在售房源16套 * 在租房源1套 * 产品类型： 高档住宅 * 建筑年代： 2011-2018年 * 拿地时间： 2010.12.06 * 物业费： 6.9元/㎡/月 * 物业公司： 万科物业管理有限公司 * 开发商： 北京万湖房地产开发有限公司/北京五矿万科置业有限公司 [](https://mbj.lizihang.com/adviser/undefined.html) ##### **我维护该楼盘，为您提供买卖、租赁委托服务** **转** ### 灵魂卖点 ### 楼盘位置 ### 户型设计 ### 生活配套 ### 居住体验 ### 租售房源 ### 楼盘参数 ### 楼盘故事 ### 推荐楼盘 #### * 万科打造的精装科技住宅，配上家具家电即可入住。；电动伸缩拉篮、智能洗碗机、恒温花洒等充满科技感，美观实用，生活更便捷。；* 全部200平以上大户型，户户2-4个生活阳台，让您有更多个性化的区域。；* 万科物业睿管家服务，为您的安全生活保驾护航。</x:v>
-      </x:c>
-      <x:c r="M24" t="str">
-        <x:v>#### 西山壹号院 1799-6500万 海淀区-西北旺 · 公寓 · 2012-06-01年建成 在售22套/在租1套 远洋万和公馆 1240-8500万 朝阳区-望京 · 公寓/联排 · 2014-12-31年建成 在售2套/在租0套 望京金茂府 2300-4800万 朝阳区-望京 · 公寓 · 2012-11-01年建成 在售1套/在租0套 颐和金茂府 1750-4280万 海淀区-西山别墅区 · -- · 2020年建成 在售1套/在租0套 香山壹号院 2100-4500万 海淀区-西山别墅区 · -- · 2021年建成 在售0套/在租0套 圆明天颂 3200-6500万 海淀区-西北旺 · -- · 2024年建成 在售2套/在租0套 ### 查看更多 * ### 东直门8号 朝阳区 · 东直门 2229-6859万 * ### 华润臻澐 海淀区 · 清河上地 1500-4700万 * ### 中建·运河玖院 通州区 · 通州新城 540-1950万 ### 户型定制 豪宅顾问将为您匹配本户型相关房源 同意定制后顾问将致电与您联系 您的私属豪宅顾问 (未读) ### 一手楼盘 * 观承别墅 * 红廷别墅 * 中粮瑞府 * 西山艺境 * 远洋天著春秋 ### 二手楼盘 * 西山壹号院 * 观唐别墅 * 山水文园 * 碧水庄园 * 星河湾 ### 租赁房源 * 泛海国际 * 当代MOMA * 太阳公元 * 四合院 * 新城国际 ### 公司介绍 * 公司介绍 * 招聘岗位 * 联系我们 * 隐私政策 ### 微信公众号 ### 移动端APP下载 北京丽兹行房地产顾问有限公司 Copyright2012经纪人入口投诉举报电话：400-888-9950备案号 京ICP备11032714号-3京公网安备 11010502040177号 APP 小程序 公众号 下载丽兹行豪宅APP 随时掌握房源动态/市场行情 体验丽兹行豪宅小程序 微信扫码无需下载即刻体验 关注丽兹行豪宅公众号 精选品质豪宅/场资讯早知道。；南区1：1比例，北区要相对宽松一些，1：2，车位充足 _174_ 个回答 【万科如园】 晚上会不会吵 临街位置的楼栋会有噪音 _170_ 个回答 打开APP查看全部问答 同户型装修案例 查看更多 轻奢 全包60万 现代 全包50万 简约 全包34万 简欧 全包52万 日式 半包25万 猜你喜欢 * VR看房 物业租售推荐：如园北区 户型5居价格可议诚意售带车位随时看 5室2厅 314.89㎡ 南北 海淀 西北旺 南北 满二年 近地铁 车位充足 3280 万 104164元/㎡ * VR看房 如园北区中心位置 稍后楼间距大 视野好 5室2厅 311.51㎡ 东南 海淀 西北旺 东南 满五年 近地铁 车位充足 3500 万 112356元/㎡ * VR看房 万科如园大师级作品 5居室 70大客厅 豪装维护好 直接住 5室2厅 286.36㎡ 东南 海淀 西北旺 东南 近地铁 车位充足 采光较好 3700 万 129208元/㎡ * VR看房 北区恒温恒湿科技住宅 中心位置 跑马大客厅 5室2厅 314.89㎡ 西南 海淀 西北旺 西南 有电梯 近地铁 车位充足 3280 万 104164元/㎡ * 3居室 朝向东南 精装 电梯房 诚心出售 价格可议 3室2厅 164.14㎡ 东南 朝阳 大望路 东南 满五年 近地铁 1450 万 88340元/㎡ 打开App查看全部房源 ### 热门楼盘 * _在售_ 山屿西山著 海淀区 温泉镇 225㎡ 售价待定 _车位充足_ _卧室全朝南_ _大户型_ _放松限购_ * _在售_ 圆明天颂 海淀区 上地 235-290㎡ 售价待定 _低容积_ _车位充足_ _主卧套房_ _装修交付_ _大户型_ 入围海淀区热力好盘榜 * _在售_ 和樾玉鸣 海淀区 上地 139-267㎡ 售价待定 _一房一价_ _轨交房_ _主卧套房_ _卧室全朝南_ _学校_ 首页 * 热门推荐 * 北京二手房 北京二手房 * 上海二手房 上海二手房 * 深圳二手房 深圳二手房 * 重庆二手房 重庆二手房 * 成都二手房 成都二手房 * 武汉二手房 武汉二手房 * 苏州二手房 苏州二手房 * 广州二手房 广州二手房 * 郑州二手房 郑州二手房 * 天津二手房 天津二手房 * 热门城市 * 北京二手房 北京二手房 * 上海二手房 上海二手房 * 深圳二手房 深圳二手房 * 重庆二手房 重庆二手房 * 成都二手房 成都二手房 * 武汉二手房 武汉二手房 * 苏州二手房 苏州二手房 * 广州二手房 广州二手房 * 郑州二手房 郑州二手房 * 天津二手房 天津二手房 * 省份历史房价 * 吉林历史房价 吉林历史房价 * 福建历史房价 福建历史房价 * 甘肃历史房价 甘肃历史房价 * 江苏历史房价 江苏历史房价 * 陕西历史房价 陕西历史房价 * 西藏历史房价 西藏历史房价 * 四川历史房价 四川历史房价 * 贵州历史房价 贵州历史房价 * 山西历史房价 山西历史房价 * 辽宁历史房价 辽宁历史房价 * 山东历史房价 山东历史房价 * 直辖市历史房价 直辖市历史房价 * 江西历史房价 江西历史房价 * 浙江历史房价 浙江历史房价 * 青海历史房价 青海历史房价 * 宁夏历史房价 宁夏历史房价 * 海南历史房价 海南历史房价 * 河北历史房价 河北历史房价 * 湖北历史房价 湖北历史房价 * 新疆历史房价 新疆历史房价 * 广东历史房价 广东历史房价 * 广西历史房价 广西历史房价 * 河南历史房价 河南历史房价 * 黑龙江历史房价 黑龙江历史房价 * 湖南历史房价 湖南历史房价 * 内蒙古历史房价 内蒙古历史房价 * 云南历史房价 云南历史房价 * 安徽历史房价 安徽历史房价 * 全国年份房价 * 2024年全国房价 2024年全国房价 * 2021年全国房价 2021年全国房价 * 2017年全国房价 2017年全国房价 * 2013年全国房价 2013年全国房价 * 2009年全国房价 2009年全国房价 * 2020年全国房价 2020年全国房价 * 2010年全国房价 2010年全国房价 * 2023年全国房价 2023年全国房价 * 2015年全国房价 2015年全国房价 * 2018年全国房价 2018年全国房价 * 2012年全国房价 2012年全国房价 * 2008年全国房价 2008年全国房价 * 2026年全国房价 2026年全国房价 * 2025年全国房价 2025年全国房价 * 2019年全国房价 2019年全国房价 * 2022年全国房价 2022年全国房价 * 2016年全国房价 2016年全国房价 * 2014年全国房价 2014年全国房价 * 2011年全国房价 2011年全国房价 首页&gt;北京房产信息&gt;北京二手房 官方客服电话: 10105858 季苹 万科物业二手房 微聊 小程序在线咨询 电话 获取手机号失败，可在线微聊联系经纪人 取消 去微聊 推荐信息。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>交通：靠近地铁16号线西北旺站约700米，周边有公交站；；医疗：附近有解放军总医院第八医学中心；</x:v>
+      </x:c>
+      <x:c r="M24" t="str"/>
       <x:c r="N24" t="str">
-        <x:v>价格线索：满二年 近地铁 车位充足 3280 万 104164元/㎡；满五年 近地铁 车位充足 3500 万 112356元/㎡；地铁 车位充足 采光较好 3700 万 129208元/㎡；有电梯 近地铁 车位充足 3280 万 104164元/㎡；路 东南 满五年 近地铁 1450 万 88340元/㎡；2室1厅1卫丨103㎡丨西南丨低楼层丨 118900元/㎡；2室1厅1卫丨103㎡丨西南丨高楼层丨 128100元/㎡； 2室2厅1卫丨93㎡丨东南丨中楼层丨 135500元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **102963** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓0.72% 贷款计算器 * 二手房源 116套 * 最近成交 69套 * 楼栋总数 26栋 * 房屋总数 1011户 * 建筑类型 板楼 * 建筑年代 2015年建成 * 小区位置 西北旺镇永丰路与后厂村路交界东南角地图 * 物业公司 北京万科物业管理有限公司 * 开发商 北京万湖房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 王福兴 评分：5.0 从业信息卡 百科 闪电回复 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 徐强 评分：4.9 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 如园标准四居 4室2厅 260.0㎡**2499**万 * #### 好房好视野 3室3厅 224.2㎡**2350**万 * #### 如园北区6室6厅南北 6室6厅 438.06㎡**4680**万 * #### 如园北区4室2厅南北 4室2厅 313.38㎡**2180**万 ### 五矿万科如园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 255.00㎡ | 2026-04-20 | -- | -- | 市场信息 | | 282.04㎡ | 2026-03-16 | -- | -- | 市场信息 | | 374.04㎡ | 2025-09-18 | -- | -- | 市场信息 | 查看全部成交 ### 五矿万科如园价格走势 ### 五矿万科如园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 五矿万科如园 海淀·马连洼**102964** 元/㎡ * #### 芳怡园 海淀·马连洼**69034** 元/㎡ * #### 百旺新城景和园 海淀·西北旺**66305** 元/㎡ * #### 百旺茉莉园 海淀·西北旺**75443** 元/㎡ * #### 中海枫涟山庄 海淀·西北旺**82937** 元/㎡ ### 相关资讯 * 小区资讯北京五矿万科如园怎么样?；五矿万科如园地址、户型和价格全览2021-09-25 * 小区资讯马连洼人都在看!；丽兹行提供近300个一二手豪宅楼盘信息介绍，可全面查看楼盘价格，户型、配套及成交信息。；) 实景图 1/52 实景图 2/52 实景图 3/52 实景图 4/52 实景图 5/52 实景图 6/52 实景图 7/52 实景图 8/52 实景图 9/52 实景图 10/52 实景图 11/52 实景图 12/52 实景图 13/52 实景图 14/52 实景图 15/52 实景图 16/52 实景图 17/52 实景图 18/52 实景图 19/52 实景图 20/52 实景图 21/52 实景图 22/52 实景图 23/52 实景图 24/52 实景图 25/52 实景图 26/52 实景图 27/52 实景图 28/52 实景图 29/52 实景图 30/52 实景图 31/52 实景图 32/52 实景图 33/52 实景图 34/52 实景图 35/52 实景图 36/52 实景图 37/52 实景图 38/52 实景图 39/52 实景图 40/52 实景图 41/52 实景图 42/52 实景图 43/52 实景图 44/52 实景图 45/52 实景图 46/52 实景图 47/52 实景图 48/52 实景图 49/52 实景图 50/52 实景图 51/52 实景图 52/52 效果图 1/13 效果图 2/13 效果图 3/13 效果图 4/13 效果图 5/13 效果图 6/13 效果图 7/13 效果图 8/13 效果图 9/13 效果图 10/13 效果图 11/13 效果图 12/13 效果图 13/13 位置图 1/1 周边配套图 1/22 周边配套图 2/22 周边配套图 3/22 周边配套图 4/22 周边配套图 5/22 周边配套图 6/22 周边配套图 7/22 周边配套图 8/22 周边配套图 9/22 周边配套图 10/22 周边配套图 11/22 周边配套图 12/22 周边配套图 13/22 周边配套图 14/22 周边配套图 15/22 周边配套图 16/22 周边配套图 17/22 周边配套图 18/22 周边配套图 19/22 周边配套图 20/22 周边配套图 21/22 周边配套图 22/22 楼栋分布图 1/1 实景图(52) 效果图(13) 位置图(1) 周边配套图(22) 楼栋分布图(1) 二手售价 1930-7000万 二手均价 6.18-13.78万/㎡ * 在售房源16套 * 在租房源1套 * 产品类型： 高档住宅 * 建筑年代： 2011-2018年 * 拿地时间： 2010.12.06 * 物业费： 6.9元/㎡/月 * 物业公司： 万科物业管理有限公司 * 开发商： 北京万湖房地产开发有限公司/北京五矿万科置业有限公司 [](https://mbj.lizihang.com/adviser/undefined.html) ##### **我维护该楼盘，为您提供买卖、租赁委托服务** **转** ### 灵魂卖点 ### 楼盘位置 ### 户型设计 ### 生活配套 ### 居住体验 ### 租售房源 ### 楼盘参数 ### 楼盘故事 ### 推荐楼盘 #### * 万科打造的精装科技住宅，配上家具家电即可入住。；生活便利线索：丽兹行提供近300个一二手豪宅楼盘信息介绍，可全面查看楼盘价格，户型、配套及成交信息。；) 实景图 1/52 实景图 2/52 实景图 3/52 实景图 4/52 实景图 5/52 实景图 6/52 实景图 7/52 实景图 8/52 实景图 9/52 实景图 10/52 实景图 11/52 实景图 12/52 实景图 13/52 实景图 14/52 实景图 15/52 实景图 16/52 实景图 17/52 实景图 18/52 实景图 19/52 实景图 20/52 实景图 21/52 实景图 22/52 实景图 23/52 实景图 24/52 实景图 25/52 实景图 26/52 实景图 27/52 实景图 28/52 实景图 29/52 实景图 30/52 实景图 31/52 实景图 32/52 实景图 33/52 实景图 34/52 实景图 35/52 实景图 36/52 实景图 37/52 实景图 38/52 实景图 39/52 实景图 40/52 实景图 41/52 实景图 42/52 实景图 43/52 实景图 44/52 实景图 45/52 实景图 46/52 实景图 47/52 实景图 48/52 实景图 49/52 实景图 50/52 实景图 51/52 实景图 52/52 效果图 1/13 效果图 2/13 效果图 3/13 效果图 4/13 效果图 5/13 效果图 6/13 效果图 7/13 效果图 8/13 效果图 9/13 效果图 10/13 效果图 11/13 效果图 12/13 效果图 13/13 位置图 1/1 周边配套图 1/22 周边配套图 2/22 周边配套图 3/22 周边配套图 4/22 周边配套图 5/22 周边配套图 6/22 周边配套图 7/22 周边配套图 8/22 周边配套图 9/22 周边配套图 10/22 周边配套图 11/22 周边配套图 12/22 周边配套图 13/22 周边配套图 14/22 周边配套图 15/22 周边配套图 16/22 周边配套图 17/22 周边配套图 18/22 周边配套图 19/22 周边配套图 20/22 周边配套图 21/22 周边配套图 22/22 楼栋分布图 1/1 实景图(52) 效果图(13) 位置图(1) 周边配套图(22) 楼栋分布图(1) 二手售价 1930-7000万 二手均价 6.18-13.78万/㎡ * 在售房源16套 * 在租房源1套 * 产品类型： 高档住宅 * 建筑年代： 2011-2018年 * 拿地时间： 2010.12.06 * 物业费： 6.9元/㎡/月 * 物业公司： 万科物业管理有限公司 * 开发商： 北京万湖房地产开发有限公司/北京五矿万科置业有限公司 [](https://mbj.lizihang.com/adviser/undefined.html) ##### **我维护该楼盘，为您提供买卖、租赁委托服务** **转** ### 灵魂卖点 ### 楼盘位置 ### 户型设计 ### 生活配套 ### 居住体验 ### 租售房源 ### 楼盘参数 ### 楼盘故事 ### 推荐楼盘 #### * 万科打造的精装科技住宅，配上家具家电即可入住。；电动伸缩拉篮、智能洗碗机、恒温花洒等充满科技感，美观实用，生活更便捷。；* 全部200平以上大户型，户户2-4个生活阳台，让您有更多个性化的区域。；* 万科物业睿管家服务，为您的安全生活保驾护航。；风险线索：#### 西山壹号院 1799-6500万 海淀区-西北旺 · 公寓 · 2012-06-01年建成 在售22套/在租1套 远洋万和公馆 1240-8500万 朝阳区-望京 · 公寓/联排 · 2014-12-31年建成 在售2套/在租0套 望京金茂府 2300-4800万 朝阳区-望京 · 公寓 · 2012-11-01年建成 在售1套/在租0套 颐和金茂府 1750-4280万 海淀区-西山别墅区 · -- · 2020年建成 在售1套/在租0套 香山壹号院 2100-4500万 海淀区-西山别墅区 · -- · 2021年建成 在售0套/在租0套 圆明天颂 3200-6500万 海淀区-西北旺 · -- · 2024年建成 在售2套/在租0套 ### 查看更多 * ### 东直门8号 朝阳区 · 东直门 2229-6859万 * ### 华润臻澐 海淀区 · 清河上地 1500-4700万 * ### 中建·运河玖院 通州区 · 通州新城 540-1950万 ### 户型定制 豪宅顾问将为您匹配本户型相关房源 同意定制后顾问将致电与您联系 您的私属豪宅顾问 (未读) ### 一手楼盘 * 观承别墅 * 红廷别墅 * 中粮瑞府 * 西山艺境 * 远洋天著春秋 ### 二手楼盘 * 西山壹号院 * 观唐别墅 * 山水文园 * 碧水庄园 * 星河湾 ### 租赁房源 * 泛海国际 * 当代MOMA * 太阳公元 * 四合院 * 新城国际 ### 公司介绍 * 公司介绍 * 招聘岗位 * 联系我们 * 隐私政策 ### 微信公众号 ### 移动端APP下载 北京丽兹行房地产顾问有限公司 Copyright2012经纪人入口投诉举报电话：400-888-9950备案号 京ICP备11032714号-3京公网安备 11010502040177号 APP 小程序 公众号 下载丽兹行豪宅APP 随时掌握房源动态/市场行情 体验丽兹行豪宅小程序 微信扫码无需下载即刻体验 关注丽兹行豪宅公众号 精选品质豪宅/场资讯早知道。；南区1：1比例，北区要相对宽松一些，1：2，车位充足 _174_ 个回答 【万科如园】 晚上会不会吵 临街位置的楼栋会有噪音 _170_ 个回答 打开APP查看全部问答 同户型装修案例 查看更多 轻奢 全包60万 现代 全包50万 简约 全包34万 简欧 全包52万 日式 半包25万 猜你喜欢 * VR看房 物业租售推荐：如园北区 户型5居价格可议诚意售带车位随时看 5室2厅 314.89㎡ 南北 海淀 西北旺 南北 满二年 近地铁 车位充足 3280 万 104164元/㎡ * VR看房 如园北区中心位置 稍后楼间距大 视野好 5室2厅 311.51㎡ 东南 海淀 西北旺 东南 满五年 近地铁 车位充足 3500 万 112356元/㎡ * VR看房 万科如园大师级作品 5居室 70大客厅 豪装维护好 直接住 5室2厅 286.36㎡ 东南 海淀 西北旺 东南 近地铁 车位充足 采光较好 3700 万 129208元/㎡ * VR看房 北区恒温恒湿科技住宅 中心位置 跑马大客厅 5室2厅 314.89㎡ 西南 海淀 西北旺 西南 有电梯 近地铁 车位充足 3280 万 104164元/㎡ * 3居室 朝向东南 精装 电梯房 诚心出售 价格可议 3室2厅 164.14㎡ 东南 朝阳 大望路 东南 满五年 近地铁 1450 万 88340元/㎡ 打开App查看全部房源 ### 热门楼盘 * _在售_ 山屿西山著 海淀区 温泉镇 225㎡ 售价待定 _车位充足_ _卧室全朝南_ _大户型_ _放松限购_ * _在售_ 圆明天颂 海淀区 上地 235-290㎡ 售价待定 _低容积_ _车位充足_ _主卧套房_ _装修交付_ _大户型_ 入围海淀区热力好盘榜 * _在售_ 和樾玉鸣 海淀区 上地 139-267㎡ 售价待定 _一房一价_ _轨交房_ _主卧套房_ _卧室全朝南_ _学校_ 首页 * 热门推荐 * 北京二手房 北京二手房 * 上海二手房 上海二手房 * 深圳二手房 深圳二手房 * 重庆二手房 重庆二手房 * 成都二手房 成都二手房 * 武汉二手房 武汉二手房 * 苏州二手房 苏州二手房 * 广州二手房 广州二手房 * 郑州二手房 郑州二手房 * 天津二手房 天津二手房 * 热门城市 * 北京二手房 北京二手房 * 上海二手房 上海二手房 * 深圳二手房 深圳二手房 * 重庆二手房 重庆二手房 * 成都二手房 成都二手房 * 武汉二手房 武汉二手房 * 苏州二手房 苏州二手房 * 广州二手房 广州二手房 * 郑州二手房 郑州二手房 * 天津二手房 天津二手房 * 省份历史房价 * 吉林历史房价 吉林历史房价 * 福建历史房价 福建历史房价 * 甘肃历史房价 甘肃历史房价 * 江苏历史房价 江苏历史房价 * 陕西历史房价 陕西历史房价 * 西藏历史房价 西藏历史房价 * 四川历史房价 四川历史房价 * 贵州历史房价 贵州历史房价 * 山西历史房价 山西历史房价 * 辽宁历史房价 辽宁历史房价 * 山东历史房价 山东历史房价 * 直辖市历史房价 直辖市历史房价 * 江西历史房价 江西历史房价 * 浙江历史房价 浙江历史房价 * 青海历史房价 青海历史房价 * 宁夏历史房价 宁夏历史房价 * 海南历史房价 海南历史房价 * 河北历史房价 河北历史房价 * 湖北历史房价 湖北历史房价 * 新疆历史房价 新疆历史房价 * 广东历史房价 广东历史房价 * 广西历史房价 广西历史房价 * 河南历史房价 河南历史房价 * 黑龙江历史房价 黑龙江历史房价 * 湖南历史房价 湖南历史房价 * 内蒙古历史房价 内蒙古历史房价 * 云南历史房价 云南历史房价 * 安徽历史房价 安徽历史房价 * 全国年份房价 * 2024年全国房价 2024年全国房价 * 2021年全国房价 2021年全国房价 * 2017年全国房价 2017年全国房价 * 2013年全国房价 2013年全国房价 * 2009年全国房价 2009年全国房价 * 2020年全国房价 2020年全国房价 * 2010年全国房价 2010年全国房价 * 2023年全国房价 2023年全国房价 * 2015年全国房价 2015年全国房价 * 2018年全国房价 2018年全国房价 * 2012年全国房价 2012年全国房价 * 2008年全国房价 2008年全国房价 * 2026年全国房价 2026年全国房价 * 2025年全国房价 2025年全国房价 * 2019年全国房价 2019年全国房价 * 2022年全国房价 2022年全国房价 * 2016年全国房价 2016年全国房价 * 2014年全国房价 2014年全国房价 * 2011年全国房价 2011年全国房价 首页&gt;北京房产信息&gt;北京二手房 官方客服电话: 10105858 季苹 万科物业二手房 微聊 小程序在线咨询 电话 获取手机号失败，可在线微聊联系经纪人 取消 去微聊 推荐信息。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：园北区3室3厅2卫户型月租约24000-26000元/月；，5室2厅4卫户型月租约45000元/月；，南区4室2厅4卫户型月租约25000元/月；，另有2室户型月租1800元/月；房屋质量/户型线索：小区租房以大户型为主，如园北区3室3厅2卫户型月租约24000-26000元/月，5室2厅4卫户型月租约45000元/月，南区4室2厅4卫户型月租约25000元/月，另有2室户型月租1800元/月（注意此房源可能非目标小区，目标为海淀区永丰路如园）；；房龄约2015年，精装修，隔音：部分临路房源精装修隔音较好；；物业为北京万科物业服务有限公司，物业费6.9元/平米/月；；户型多为南北通透，动静分离设计；；生活便利线索：交通：靠近地铁16号线西北旺站约700米，周边有公交站；；医疗：附近有解放军总医院第八医学中心；</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>1. 【北京五矿万科如园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010699497.htm
-2. 北京万科如园楼盘介绍,万科如园小区二手房、租房信息-丽兹行官网 https://mbj.lizihang.com/loupan/597271.html
-3. 【10图】物业租售推荐：如园北区 户型5居价格可议诚意售带车位随时看，如园(北区)-北京58同城 https://m.58.com/bj/ershoufang/4507819946826752x.shtml
-4. 太阳园_北京太阳园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/166722.html
-5. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. http://m.anjuke.com/sjz/rent/4538846359200773-2/
+2. https://bj.58.com/zufang/85815731493210x.shtml
+3. http://m.anjuke.com/bj/rent/4517858724617217-3/
+4. https://mobile.anjuke.com/esf/fs-cm802932/
+5. http://m.anjuke.com/bj/rent/4117458190490636-3/
+6. https://m.58.com/bj/zufang/84408021966555x.shtml
+7. https://bj.zu.anjuke.com/fangyuan/3748592218647557
+8. 如园 2室2厅1卫 http://m.anjuke.com/sjz/rent/4538846359200773-2/</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1398,40 +1463,42 @@
         <x:v>北京市海淀区马连洼南路8号</x:v>
       </x:c>
       <x:c r="E25" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F25" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G25" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H25" t="n">
-        <x:v>5.2</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>地理位置优越，但搜索证据与实际地点偏差较大，缺乏针对性评价，评分较为保守。</x:v>
+        <x:v>紧邻马连洼地铁站与商场，万科物业管理完善，配套成熟且居住品质较高。</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月；寺四合院 可注册办公首次出租南北通透 210000 元/月；道湾东巷 可注册办公首次出租南北通透 120000 元/月；307㎡|朝南北 海淀-万柳-万城华府 55000 元/月</x:v>
+        <x:v>1室1厅5300元/月；，2室2厅9500元/月；，3室2厅21000元/月；，5室2厅32000元/月</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 在张自忠有一方。；# 安徽频道_新华房产_新华网 楼盘导购 &gt;&gt; **开春优惠多 邻铁精装楼盘16000元/平起** 邻地铁代表出行便捷，精装修代表省时省力、交房入住，在此为您整理出京城近期开盘和将开盘的打折邻铁精装房源，供参考！；[[详细]](http://news.xinhuanet.com/house/2013-02/17/c_124353253.htm) **京临铁折扣三居集锦 首付43万起劲省20万** 三居户型，交通便利，价格划算，满足这三个条件的楼盘想必是众多三口之家置业者的梦想。；[[详细]](http://news.xinhuanet.com/house/2013-03/27/c_124510131.htm) ·五环外均价逼近2万置业板块盘点大兴76平板楼首付41万 ·精装房均价15000起直降40万5-6环三居均价15900元/平起 ·24500元起抄底四环低价小户型总价41万起最高享8折优惠 ·80平左右低价通透2居推荐小户型均价10500元起优惠4万 ·京百万内刚需明星盘精装二居最低6700元/平起最高优惠7万 ·燕西台品质小高层4900元/平全款减150元/平 ·康桥郡南二环社区4900元/平29日新楼源开盘 ·中央时区 市中心尾盘三室7500元/平 ·香居美地50-120平米户型 均价3980元 ·西美70后院 槐安路精装高层咨询中 ·瑞城高层均价7200元 BD区全款可享98折优惠 ·璟和嘉园均价7600元 全款每平米优惠200元 ·时尚公馆均价6000元 裕华区住宅全款享优惠 ·良工佳苑1-2居准现房在售 均价11580 团购8折 ·徜徉集低密住宅2-3居 均价14000起 低至96折 ·亦庄线新盘星悦国际85-169平在售 均价12800 ·珠江国际公馆95平特价房源 目前办理优惠卡 ·珠江拉维小镇推出部分特价房源 均价16000起 ·大兴保利新茉莉公馆年底推新 排号每天减150元 ·恒盛小镇藝墅洋房与别墅均价8600起 3万抵12万 ·富力金禧花园88平团购140万起 送1-5年物业费 ·润枫领尚特价房源 55-89平 均价19500 ·大兴黄村新里西斯莱公馆 均价20000元低至96折 ·合生·滨江国际公寓正在排号开盘减28000 ·黄村中建国际港低至85折 均价19000元/平起 ·龙湖锦坨城二期预计9月开盘 一期均价7700元 ·中粮万科长阳半岛8月推新盘 现办卡享98折优惠 ·绿地启航社精装小户型 均价16000元 低至93折 ·芭蕾雨·悦都2-3居尾盘 均价16000 低至92折 ·龙湖·蔚澜香醍花园洋房148-170平 均价19000 ·华业东方玫瑰30-120平小户型 折后均价17000 ·北京西站旁第三区精装2-3居在售 均价32000元起 ·西站优盘将推精装小户型 预计30000元/平米起 ·中海紫御公馆推62平1居92平米2居 均价43000 ·方庄中海城III香克林145平三居 总价340万 ·V立方精装在售均价7500 每平米优惠300至400元 ·龙庆·望都佳园78-92平2-3居现房在售 均��5600 ·首开·国风上观本周末即将开盘 均价3万起 ·CROSS朗廷毛坯现房50-98平 总价102万起 ·龙熙顺景多种别墅在售 均价13000元起5万抵20万 ·南二环内一瓶三期尾房特价出售 26000元/平米 ·南五环林肯公园均价24000元/平米 大户型有优惠 ·金茂府精装住宅预计下半年开盘 ·大兴CAGO寓所1-3居精装在售 均价15800元/平米 ·K2百合湾80-110平两至四居将开盘 每天减1000元 ·溪水雅地预计8月开盘 均价10000排号有优惠 ·亿城西山公馆精装住宅在售 均价34800低至97折 ·西南三环万年花城濠景现房尾盘在售 均价35000 ·东南三环晶城秀府现房在售 均价33000元/平方米 ·大兴恒盛小镇藝墅3万抵12万大兴现房均价17000低至88折 ·东四环精装小户型2万抵8万南三环精装现房均价23000起 ·第三区精装2居均价32000元怀柔中建府前观邸1-4居在售 ·亚奥山水LAVIE板楼年底推出孔雀大卫城4号线三期均价6500 ·健泰安居花园板楼均价2900西站精装小户型均价30000 ·姚家园精装现房7月特惠23300/平东南四环板楼均价27000 ·上林溪低密度洋房在售 均价25000元/平低至96折 ·黄村红木林推新44平起雍景山岚两居均价22000元 ·朝青低密板楼华纺易城 144平起现房均价32000 ·朝青北京新天地62-170平 折后最低22000起 ·石景山雍景山岚两居在售均价22000 ·黄村地铁沿线红木林7月底推新44平起 ·东亚上北鑫座精装小户型 均价16800低至9折 ·上奥新世纪高板住宅推特价房 均价22280元/平米 ·西山国际城公寓5.4米层高复式推出 108万/套起 ·珠江拉维小镇景观板楼均价19000 办卡5千抵1万 ·首开·常青藤85-150平全通透 仅余15席均价2万2 ·八通线M5·朗峰70年产权50平起高小户型直减8万 ·V立方精装在售均价7500 每平米优惠200至500元 ·塞纳城邦复式准现房在售均价6700 新推特价房 ·西五环雍景山岚2-3居在售 均价24000元/平方米 ·名人国际花园板楼在售 准现房3750起全款98折 ·大兴未来deVille独栋送庭院露台车位 600万起 ·北京城建·世华泊郡5号楼特价房 最高优惠18万 ·龙湖·蔚澜香醍叠拼总价560万起 洋房均价19500 ·中国山水醉联排别墅在售 7000元/平起全款9折 ·朝青CROSS朗廷50-98平 现房总价102万起 ·天恒乐活城小户型均价12000元/平 总价优惠8万 ·东四环东岸春天里69-94平 最高优惠6万 ·珠江国际公馆将推特价房源95平 最高优惠5千 ·鲁能7号院多户型特价房在售 折后均价14000 ·龙湖·香醍溪苑尾盘在售 均价15000享双重优惠 ·顶秀美泉小镇二期LOFT和住宅在售 均价12000起 ·潮白河孔雀城3-4居准现房在售 均价9000元起 ·南三环鹤巢居将近期推新房源 预计均价36000起 ·米拉village小户型均价15800 最高优惠2千/平 ·珠江拉维小镇特价房每平直降7000 ·东四环凯德锦绣精装62平起小户型 均价39800 ·华瀚国际精装板楼现房 73-240平 均价43000起 ·京贸国际城通透板楼 92平起 准现房均价19800 ·乐栋300购房最高享受5万优惠 总价120万 ·亦庄融科钧廷低密通透板楼 95折均价18000起 ·首开铂郡40年产权公寓 50-70平米 均价43000 ·旭辉御府100套特价房17600/平起 最高省30万 ·亦庄全新盘UP生活2011年内推出 面积42-82平 ·北三环红玺台220-300平四居 起价57000 ·华远九都汇精准板楼100平起 均价55000 ·亚奥区域绿城北京诚园精装板楼均价54000 ·5号线尚三环精装准现房 均价21000元/平米起 ·通州华业东方玫瑰小户型30平起 折后均价17000 ·世茂·工三最后3套房源在售 准现房48000 # 新华网版权 Copyright © 2000 - 2014 XINHUANET.com All Rights Reserved. 制作单位：新华网 版权所有 新华网 010030090940000000000000011200000000000000。</x:v>
+        <x:v>不同户型月租差异较大，押付方式有押一付半年、押一付三；；房龄约2008年；；物业为北京万科物业服务有限公司，物业费4.2元/㎡/月，物业维护公共设施及时；；房屋多为普通装修或毛坯，建筑质量好（钢混结构），户型南北通透（主力120平三居、140平四居）；；未提及隔音相关负面信息；</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 能容纳20多人的客厅。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；浏览地图、搜索地点、查询公交驾车线路、查看实时路况，您的出行指南、生活助手。；提供地铁线路图浏览，乘车方案查询，以及准确的票价和时间信息。</x:v>
-      </x:c>
-      <x:c r="M25" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。</x:v>
-      </x:c>
+        <x:v>地铁：16号线/18号线马连洼站步行约732-799米；；通勤：紧邻马连洼公交站，可换乘地铁4号线；；商超：距中发百旺商城约375米，美廉美超市（中发百旺店）约363米，好邻居（马连洼店）约203米，还有数字化菜市场；；医院：距上地医院约1.8km，海淀青龙桥社区卫生服务中心兰园站约212米，仁修堂大药房约204米；；餐饮：周边有较多餐饮资源，银行配套较全；</x:v>
+      </x:c>
+      <x:c r="M25" t="str"/>
       <x:c r="N25" t="str">
-        <x:v>价格线索：-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月；寺四合院 可注册办公首次出租南北通透 210000 元/月；道湾东巷 可注册办公首次出租南北通透 120000 元/月；307㎡|朝南北 海淀-万柳-万城华府 55000 元/月；房屋质量/户型线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 在张自忠有一方。；# 安徽频道_新华房产_新华网 楼盘导购 &gt;&gt; **开春优惠多 邻铁精装楼盘16000元/平起** 邻地铁代表出行便捷，精装修代表省时省力、交房入住，在此为您整理出京城近期开盘和将开盘的打折邻铁精装房源，供参考！；[[详细]](http://news.xinhuanet.com/house/2013-02/17/c_124353253.htm) **京临铁折扣三居集锦 首付43万起劲省20万** 三居户型，交通便利，价格划算，满足这三个条件的楼盘想必是众多三口之家置业者的梦想。；[[详细]](http://news.xinhuanet.com/house/2013-03/27/c_124510131.htm) ·五环外均价逼近2万置业板块盘点大兴76平板楼首付41万 ·精装房均价15000起直降40万5-6环三居均价15900元/平起 ·24500元起抄底四环低价小户型总价41万起最高享8折优惠 ·80平左右低价通透2居推荐小户型均价10500元起优惠4万 ·京百万内刚需明星盘精装二居最低6700元/平起最高优惠7万 ·燕西台品质小高层4900元/平全款减150元/平 ·康桥郡南二环社区4900元/平29日新楼源开盘 ·中央时区 市中心尾盘三室7500元/平 ·香居美地50-120平米户型 均价3980元 ·西美70后院 槐安路精装高层咨询中 ·瑞城高层均价7200元 BD区全款可享98折优惠 ·璟和嘉园均价7600元 全款每平米优惠200元 ·时尚公馆均价6000元 裕华区住宅全款享优惠 ·良工佳苑1-2居准现房在售 均价11580 团购8折 ·徜徉集低密住宅2-3居 均价14000起 低至96折 ·亦庄线新盘星悦国际85-169平在售 均价12800 ·珠江国际公馆95平特价房源 目前办理优惠卡 ·珠江拉维小镇推出部分特价房源 均价16000起 ·大兴保利新茉莉公馆年底推新 排号每天减150元 ·恒盛小镇藝墅洋房与别墅均价8600起 3万抵12万 ·富力金禧花园88平团购140万起 送1-5年物业费 ·润枫领尚特价房源 55-89平 均价19500 ·大兴黄村新里西斯莱公馆 均价20000元低至96折 ·合生·滨江国际公寓正在排号开盘减28000 ·黄村中建国际港低至85折 均价19000元/平起 ·龙湖锦坨城二期预计9月开盘 一期均价7700元 ·中粮万科长阳半岛8月推新盘 现办卡享98折优惠 ·绿地启航社精装小户型 均价16000元 低至93折 ·芭蕾雨·悦都2-3居尾盘 均价16000 低至92折 ·龙湖·蔚澜香醍花园洋房148-170平 均价19000 ·华业东方玫瑰30-120平小户型 折后均价17000 ·北京西站旁第三区精装2-3居在售 均价32000元起 ·西站优盘将推精装小户型 预计30000元/平米起 ·中海紫御公馆推62平1居92平米2居 均价43000 ·方庄中海城III香克林145平三居 总价340万 ·V立方精装在售均价7500 每平米优惠300至400元 ·龙庆·望都佳园78-92平2-3居现房在售 均��5600 ·首开·国风上观本周末即将开盘 均价3万起 ·CROSS朗廷毛坯现房50-98平 总价102万起 ·龙熙顺景多种别墅在售 均价13000元起5万抵20万 ·南二环内一瓶三期尾房特价出售 26000元/平米 ·南五环林肯公园均价24000元/平米 大户型有优惠 ·金茂府精装住宅预计下半年开盘 ·大兴CAGO寓所1-3居精装在售 均价15800元/平米 ·K2百合湾80-110平两至四居将开盘 每天减1000元 ·溪水雅地预计8月开盘 均价10000排号有优惠 ·亿城西山公馆精装住宅在售 均价34800低至97折 ·西南三环万年花城濠景现房尾盘在售 均价35000 ·东南三环晶城秀府现房在售 均价33000元/平方米 ·大兴恒盛小镇藝墅3万抵12万大兴现房均价17000低至88折 ·东四环精装小户型2万抵8万南三环精装现房均价23000起 ·第三区精装2居均价32000元怀柔中建府前观邸1-4居在售 ·亚奥山水LAVIE板楼年底推出孔雀大卫城4号线三期均价6500 ·健泰安居花园板楼均价2900西站精装小户型均价30000 ·姚家园精装现房7月特惠23300/平东南四环板楼均价27000 ·上林溪低密度洋房在售 均价25000元/平低至96折 ·黄村红木林推新44平起雍景山岚两居均价22000元 ·朝青低密板楼华纺易城 144平起现房均价32000 ·朝青北京新天地62-170平 折后最低22000起 ·石景山雍景山岚两居在售均价22000 ·黄村地铁沿线红木林7月底推新44平起 ·东亚上北鑫座精装小户型 均价16800低至9折 ·上奥新世纪高板住宅推特价房 均价22280元/平米 ·西山国际城公寓5.4米层高复式推出 108万/套起 ·珠江拉维小镇景观板楼均价19000 办卡5千抵1万 ·首开·常青藤85-150平全通透 仅余15席均价2万2 ·八通线M5·朗峰70年产权50平起高小户型直减8万 ·V立方精装在售均价7500 每平米优惠200至500元 ·塞纳城邦复式准现房在售均价6700 新推特价房 ·西五环雍景山岚2-3居在售 均价24000元/平方米 ·名人国际花园板楼在售 准现房3750起全款98折 ·大兴未来deVille独栋送庭院露台车位 600万起 ·北京城建·世华泊郡5号楼特价房 最高优惠18万 ·龙湖·蔚澜香醍叠拼总价560万起 洋房均价19500 ·中国山水醉联排别墅在售 7000元/平起全款9折 ·朝青CROSS朗廷50-98平 现房总价102万起 ·天恒乐活城小户型均价12000元/平 总价优惠8万 ·东四环东岸春天里69-94平 最高优惠6万 ·珠江国际公馆将推特价房源95平 最高优惠5千 ·鲁能7号院多户型特价房在售 折后均价14000 ·龙湖·香醍溪苑尾盘在售 均价15000享双重优惠 ·顶秀美泉小镇二期LOFT和住宅在售 均价12000起 ·潮白河孔雀城3-4居准现房在售 均价9000元起 ·南三环鹤巢居将近期推新房源 预计均价36000起 ·米拉village小户型均价15800 最高优惠2千/平 ·珠江拉维小镇特价房每平直降7000 ·东四环凯德锦绣精装62平起小户型 均价39800 ·华瀚国际精装板楼现房 73-240平 均价43000起 ·京贸国际城通透板楼 92平起 准现房均价19800 ·乐栋300购房最高享受5万优惠 总价120万 ·亦庄融科钧廷低密通透板楼 95折均价18000起 ·首开铂郡40年产权公寓 50-70平米 均价43000 ·旭辉御府100套特价房17600/平起 最高省30万 ·亦庄全新盘UP生活2011年内推出 面积42-82平 ·北三环红玺台220-300平四居 起价57000 ·华远九都汇精准板楼100平起 均价55000 ·亚奥区域绿城北京诚园精装板楼均价54000 ·5号线尚三环精装准现房 均价21000元/平米起 ·通州华业东方玫瑰小户型30平起 折后均价17000 ·世茂·工三最后3套房源在售 准现房48000 # 新华网版权 Copyright © 2000 - 2014 XINHUANET.com All Rights Reserved. 制作单位：新华网 版权所有 新华网 010030090940000000000000011200000000000000。；生活便利线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 能容纳20多人的客厅。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；浏览地图、搜索地点、查询公交驾车线路、查看实时路况，您的出行指南、生活助手。；提供地铁线路图浏览，乘车方案查询，以及准确的票价和时间信息。；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。</x:v>
+        <x:v>价格线索：1室1厅5300元/月；，2室2厅9500元/月；，3室2厅21000元/月；，5室2厅32000元/月；房屋质量/户型线索：不同户型月租差异较大，押付方式有押一付半年、押一付三；；房龄约2008年；；物业为北京万科物业服务有限公司，物业费4.2元/㎡/月，物业维护公共设施及时；；房屋多为普通装修或毛坯，建筑质量好（钢混结构），户型南北通透（主力120平三居、140平四居）；；未提及隔音相关负面信息；；生活便利线索：地铁：16号线/18号线马连洼站步行约732-799米；；通勤：紧邻马连洼公交站，可换乘地铁4号线；；商超：距中发百旺商城约375米，美廉美超市（中发百旺店）约363米，好邻居（马连洼店）约203米，还有数字化菜市场；；医院：距上地医院约1.8km，海淀青龙桥社区卫生服务中心兰园站约212米，仁修堂大药房约204米；；餐饮：周边有较多餐饮资源，银行配套较全；</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>1. 【北京欧亿登录入口soo8.top租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kw%E6%AC%A7%E4%BA%BF%E7%99%BB%E5%BD%95%E5%85%A5%E5%8F%A3soo8.top?425%20target=_blank
-2. 百度地图 https://map.baidu.com/place/28e62f9a6c9ba623e812e4b0
-3. 安徽频道_新华房产_新华网 http://www.news.cn/house/anhui/lpdg.htm
-4.  https://fangchan.snssdk.com/zufang/bj-7643207656047394868.html</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4605426885008386-3/
+2. http://m.anjuke.com/bj/rent/4605426873246721-3/
+3. http://m.anjuke.com/bj/rent/4604156365939727/
+4. https://mob.58.com/esfxq/bj-s2080554/
+5. https://beijing.anjuke.com/community/view/851047/jiedu/p5/
+6. 南北通透 2室2厅 亿城西山华府禧园 http://m.anjuke.com/bj/rent/4605426885008386-3/
+7. 正南 3室2厅 亿城西山华府禧园 http://m.anjuke.com/bj/rent/4605426873246721-3/
+8. 亿城西山华府禧园 https://mob.58.com/esfxq/bj-s2080554/</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1448,41 +1515,41 @@
         <x:v>北京市海淀区六里屯南路与亮甲店路交叉口东南290米</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F26" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G26" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H26" t="n">
-        <x:v>6.2</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="I26" t="str">
-        <x:v>共有产权房，户型多样但采光窗地比受诟病，开发商口碑一般，租住需留意质量。</x:v>
+        <x:v>价格亲民的回迁房，距地铁约1.1公里，周边配套偏僻，适合预算有限人群。</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>了一套建筑面积约为88平方米、销售价格为37800元/平方米；屋，该家庭需要支付的购房款为88平方米×37800元/平方米；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；胡同小区 可注册办公首次出租南北通透 250000 元/月；刹海四合院 可注册办公首次出租南北通透 83333 元/月</x:v>
+        <x:v>根据搜索结果，永靓家园部分合租房源月租约2500元/月</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>套型主要为约55平方米一居54套，约88平方米两居2051套，约89平方米三居36套，含全装修费用销售均价 ...。；“永靓家园的B1、B2、B3、B4户型起居室，窗地面积比小于国家相关标准的规定。；“以永靓家园共有产权房两居室B2户型为例，我们根据《海淀区永靓家园共有产权住房项目申购登记公告》中关于户型的介绍以及户型图中的数据得出，窗户面积约1.9米×1.6米等于3.04平方米，起居室面积7.4米×3.3米等于24.42平方米，阳台面积1.2米×3.3米等于3.96平方米，窗户比上起居室和阳台面积之和约等于0.107。；除房屋品质问题外，样板房的一推再推，也让永靓家园的业主感到不满，认为开发商损害了他们的知情权。；开发商最初拒绝开放，几经诉求，才开放了7种户型中的3种。</x:v>
+        <x:v>小区建于2010年，物业为业主自管，物业费0.9元/平米/月；；小区包含多数回迁房，居住品质评分6.0；；无明确隔音、户型等具体口碑信息，仅知户型相关信息未详细提及。</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>- 北京本地宝 [](http://bj.bendibao.com/) * 本地民生 * 办事 * 社保 * 公积金 * 居住证 * 交通 * 地铁 * 旅游 * 景点 * 活动 * 教育 * 网点 * 招聘 * 特惠 北京 [](http://www.bendibao.com/city.htm) 首页 下载app * 办事指南 * 社保 * 公积金 * 出入境 * 车辆 * 户籍 * 教育 * 婚育 * 房产 * 医疗 * 生活 * 企业 * 其他 办事直通车 北京本地宝&gt;办事指南&gt;北京土地房产&gt;北京共有产权住房&gt;北京海淀区永靓家园共有产权房价格多少？；* 2026北京高考临时身份证办理指南（地点+取证时间+办法 * 2026北京高考身份证加急办理最快24小时取证 * 2026北京高考身份证绿色通道办理指南（办理时间+材料） [](http://bj.bendibao.com/news/yidijiuyi/)[](http://bj.bendibao.com/live/baozhangfang/)[](http://bj.bendibao.com/news/ztquanguoshenfenzheng/)[](http://bj.bendibao.com/cyfw/wangdian/zfjg.shtm) 赏花发票抽奖赏银杏春节全攻略赏红叶攻略五一旅游攻略教师节国庆旅游攻略考研个人养老金观日出攻略亲子游展会露营汽车消费券房贷利率助企纾困婴幼儿照护养老保险缴费补贴申领医保报销生育办事迎春花市异地就医婚姻服务健康证办理电动车上牌供热消费券外地人办事学校课后服务中考一分一段表端午节养老金领取清明节云招聘数字人民币免费流量公园免费预约免费景点医保电子凭证人口普查国庆晚会四价疫苗学校放假安排生育福利大全省考保障性租赁住房机场大巴购房首付房屋限购国家植物园养老保险买断医院挂号车牌摇号竞价产假四价疫苗育儿假扫墓专题事业单位招聘已关闭北京电动自行车北京环球度假区双减政策买房攻略中高考生福利中考录取分数线单针疫苗学法减分中考国博月壤展最低工资高考文惠券车展北京菊花文化节教师资格证流感疫苗寒假放假时间身份证异地消费券学区划分开学限行公积金贷款公务员 本地宝郑重声明：本文仅代表作者个人观点，与本地宝无关。；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。</x:v>
-      </x:c>
-      <x:c r="M26" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。</x:v>
-      </x:c>
+        <x:v>距离西北旺地铁站约1099米，公交站有永靓家园南（专143路）；；周边商超、医院、餐饮等配套信息大部分暂无具体内容，仅提到地理位置有些偏。</x:v>
+      </x:c>
+      <x:c r="M26" t="str"/>
       <x:c r="N26" t="str">
-        <x:v>价格线索：了一套建筑面积约为88平方米、销售价格为37800元/平方米；屋，该家庭需要支付的购房款为88平方米×37800元/平方米；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；胡同小区 可注册办公首次出租南北通透 250000 元/月；刹海四合院 可注册办公首次出租南北通透 83333 元/月；房屋质量/户型线索：套型主要为约55平方米一居54套，约88平方米两居2051套，约89平方米三居36套，含全装修费用销售均价 ...。；“永靓家园的B1、B2、B3、B4户型起居室，窗地面积比小于国家相关标准的规定。；“以永靓家园共有产权房两居室B2户型为例，我们根据《海淀区永靓家园共有产权住房项目申购登记公告》中关于户型的介绍以及户型图中的数据得出，窗户面积约1.9米×1.6米等于3.04平方米，起居室面积7.4米×3.3米等于24.42平方米，阳台面积1.2米×3.3米等于3.96平方米，窗户比上起居室和阳台面积之和约等于0.107。；除房屋品质问题外，样板房的一推再推，也让永靓家园的业主感到不满，认为开发商损害了他们的知情权。；开发商最初拒绝开放，几经诉求，才开放了7种户型中的3种。；生活便利线索：- 北京本地宝 [](http://bj.bendibao.com/) * 本地民生 * 办事 * 社保 * 公积金 * 居住证 * 交通 * 地铁 * 旅游 * 景点 * 活动 * 教育 * 网点 * 招聘 * 特惠 北京 [](http://www.bendibao.com/city.htm) 首页 下载app * 办事指南 * 社保 * 公积金 * 出入境 * 车辆 * 户籍 * 教育 * 婚育 * 房产 * 医疗 * 生活 * 企业 * 其他 办事直通车 北京本地宝&gt;办事指南&gt;北京土地房产&gt;北京共有产权住房&gt;北京海淀区永靓家园共有产权房价格多少？；* 2026北京高考临时身份证办理指南（地点+取证时间+办法 * 2026北京高考身份证加急办理最快24小时取证 * 2026北京高考身份证绿色通道办理指南（办理时间+材料） [](http://bj.bendibao.com/news/yidijiuyi/)[](http://bj.bendibao.com/live/baozhangfang/)[](http://bj.bendibao.com/news/ztquanguoshenfenzheng/)[](http://bj.bendibao.com/cyfw/wangdian/zfjg.shtm) 赏花发票抽奖赏银杏春节全攻略赏红叶攻略五一旅游攻略教师节国庆旅游攻略考研个人养老金观日出攻略亲子游展会露营汽车消费券房贷利率助企纾困婴幼儿照护养老保险缴费补贴申领医保报销生育办事迎春花市异地就医婚姻服务健康证办理电动车上牌供热消费券外地人办事学校课后服务中考一分一段表端午节养老金领取清明节云招聘数字人民币免费流量公园免费预约免费景点医保电子凭证人口普查国庆晚会四价疫苗学校放假安排生育福利大全省考保障性租赁住房机场大巴购房首付房屋限购国家植物园养老保险买断医院挂号车牌摇号竞价产假四价疫苗育儿假扫墓专题事业单位招聘已关闭北京电动自行车北京环球度假区双减政策买房攻略中高考生福利中考录取分数线单针疫苗学法减分中考国博月壤展最低工资高考文惠券车展北京菊花文化节教师资格证流感疫苗寒假放假时间身份证异地消费券学区划分开学限行公积金贷款公务员 本地宝郑重声明：本文仅代表作者个人观点，与本地宝无关。；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。</x:v>
+        <x:v>价格线索：根据搜索结果，永靓家园部分合租房源月租约2500元/月；房屋质量/户型线索：小区建于2010年，物业为业主自管，物业费0.9元/平米/月；；小区包含多数回迁房，居住品质评分6.0；；无明确隔音、户型等具体口碑信息，仅知户型相关信息未详细提及。；生活便利线索：距离西北旺地铁站约1099米，公交站有永靓家园南（专143路）；；周边商超、医院、餐饮等配套信息大部分暂无具体内容，仅提到地理位置有些偏。</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>1. 永靓家园共有产权住房选房公告 - 北京市海淀区人民政府门户网站 https://zyk.bjhd.gov.cn/zwdt/tdzt/2018/zwgk/ggzy/201812/t20181210_4164954_hd.shtml
-2. 中国城市报-人民网 http://paper.people.com.cn/zgcsb/html/2019-01/14/content_1904012.htm
-3. 北京海淀区永靓家园共有产权房价格多少？- 北京本地宝 http://bj.bendibao.com/zffw/20221230/336147.shtm
-4. 海淀共有产权房永靓家园即将选房 三成面向非京籍 https://news.sina.cn/gn/2018-12-11/detail-ihmutuec8118578.d.html?vt=4
-5. 【北京b体育appv0x.cn租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kwB%E4%BD%93%E8%82%B2Appv0x.cn?15%20target=_blank</x:v>
+        <x:v>1. https://i.haoduofangs.com/zufang/common-7443772253248012299.html
+2. https://beijing.anjuke.com/community/view/1399876
+3. 永靓家园西区怎么样?北京永靓家园西区房价|房源|地址|户型图|周边配套详情 https://m.5i5j.com/bj/xq_news/200000804.html
+4. 合租·永靓家园 https://i.haoduofangs.com/zufang/common-7443772253248012299.html
+5. 永靓家园东区怎么样?北京永靓家园东区房价|房源|地址|户型图|周边配套详情 https://m.5i5j.com/bj/xq_news/200000632.html
+6. 永靓家园租房,西北旺永靓家园房屋出租价格,永靓家园整租合租房价 https://mob.58.com/zfxq/bj-sy103531525/
+7. 永靓家园六里屯南路 https://beijing.anjuke.com/community/view/1399876</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1499,41 +1566,44 @@
         <x:v>北京市海淀区马连洼南路8号</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F27" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G27" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H27" t="n">
-        <x:v>8.5</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I27" t="str">
-        <x:v>万科物业品质保障，紧邻地铁与软件园，生活配套成熟，是高预算优选。</x:v>
+        <x:v>高端精装社区，环境优美配套全，但租金昂贵且中介费高，适合高预算人群。</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡； 上地 2014年竣工 距离3293m 74659 元/㎡；西二旗 2009年竣工 距离2708m 82732 元/㎡； 上地 2004年竣工 距离2550m 69075 元/㎡；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月</x:v>
+        <x:v>一居月租约5500-7900元/月；，两居约15500元/月；，三居约18000-23000元/月；，四居约20000-23000元/月；，五居约22000元/月</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡ 6月挂牌均价 0.03% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 一层50平园子）全南2居 中间位置 满五年价格可谈双地铁 马连洼 亿城西山华府珑园 846 万 2室2厅 93.51㎡ 万科物业推荐好房 马连洼西山华府一居出售 带电梯 大阳台 马连洼 亿城西山华府珑园 540 万 1室1厅 59.42㎡ 必看好房）马连洼品质2居 带明卫满五一 不临街中高层 双地铁 马连洼 亿城西山华府珑园 1080 万 2室2厅 120.84㎡ 海淀双卫两居 一梯两户 中间位置 车储 万科物业 马连洼 亿城西山华府珑园 1150 万 2室2厅 121.52㎡ 必卖好房）单本全明3居 一车一储 满五年 价格可谈双地铁 马连洼 亿城西山华府珑园 1498 万 3室2厅 177.47㎡ 必看高层）挑高4.2M 一车一储 方正4居 视野开阔价格可谈 马连洼 亿城西山华府珑园 1600 万 4室2厅 176.36㎡ ### 本小区租房推荐查看更多 ### 西山华府 177四居 全齐 马连洼地铁口 人大附中 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 马连洼双地铁 西山华府 一层院子 人大附中 农业大学 马连洼 亿城西山华府珑园 整租 16/18号线 朝南 _11000_ 元/月 2室2厅 93.5㎡ ### 陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 178.8㎡ ### 新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 新增 出租 带车位 集中供暖 家具家电齐全 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 177㎡ ### 万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 178.1㎡ ### 周边热门小区查看更多 * 347 上林溪 海淀 上地 2014年竣工 距离3293m 74659 元/㎡24套在售 小区评测 近地铁 近学校 13号线 五六环之间 户型丰富 配套齐全 7.1 分 * 421 领秀新硅谷AB区 海淀 西二旗 2009年竣工 距离2708m 82732 元/㎡15套在售 小区评测 近地铁 近学校 昌平线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 6.9 分 * 3 当代城市家园 海淀 上地 2004年竣工 距离2550m 69075 元/㎡19套在售 小区评测 近地铁 近学校 13号线等 五六环之间 绿化好 配套齐全 7.2 分 小区单页 国奥村(西区)今日家园广渠金茂府(北区)朱雀门小区景泰嘉园远洋山水(北区)天鹅湾(北区)首城国际丽都壹号凤凰城(一期二期四期)望京花园西区华清嘉园御汤山东区芍药居北里小区华纺易城一栋洋房星河湾畅园山水文园东园万象新天家园翠微北里 本板块小区大全 褐石园今日家园碧桐园颐源居同泽园西里北坞嘉园南里上地佳园翠微南里四季香山雪梨澳乡(别墅)京泉馨苑东里西山美墅馆(别墅)美丽园智学苑香山艺墅交大嘉园尚峰尚水水云居万泉新新家园翠湖别墅 小区二手房 国奥村(西区)二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售朱雀门小区二手房出售景泰嘉园二手房出售远洋山水(北区)二手房出售天鹅湾(北区)二手房出售首城国际二手房出售丽都壹号二手房出售凤凰城(一期二期四期)二手房出售望京花园西区二手房出售华清嘉园二手房出售御汤山东区二手房出售芍药居北里小区二手房出售华纺易城二手房出售一栋洋房二手房出售星河湾畅园二手房出售山水文园东园二手房出售万象新天家园二手房出售翠微北里二手房出售 小区房价 国奥村(西区)房价走势今日家园房价走势广渠金茂府(北区)房价走势朱雀门小区房价走势景泰嘉园房价走势远洋山水(北区)房价走势天鹅湾(北区)房价走势首城国际房价走势丽都壹号房价走势凤凰城(一期二期四期)房价走势望京花园西区房价走势华清嘉园房价走势御汤山东区房价走势芍药居北里小区房价走势华纺易城房价走势一栋洋房房价走势星河湾畅园房价走势山水文园东园房价走势万象新天家园房价走势翠微北里房价走势 推荐小区价格 百环家园二手房出售紫金长安二手房出售华业东方玫瑰二手房出售首邑溪谷二手房出售新城国际二手房出售金色漫香苑二手房出售美丽园二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售中海紫御公馆二手房出售保利西山林语二手房出售新怡家园二手房出售平乐园小区二手房出售太阳公元(北区)二手房出售珠光逸景(二号院)二手房出售国奥村(东区)二手房出售保利百合花园二手房出售远洋天地二手房出售望京西园三区二手房出售 二手房商圈 海运仓二手房万泉河二手房延庆周边二手房八大处二手房皂君庙二手房麦子店二手房韩村河二手房东辛房二手房紫竹桥二手房媒体村二手房地安门二手房常营二手房通州周边二手房西二旗二手房密云城区二手房潭柘寺二手房新发地二手房五里店二手房保定二手房潞苑二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价亿城西山华府珑园小区亿城西山华府珑园二手房亿城西山华府珑园租房亿城西山华府珑园户型图亿城西山华府珑园周边配置亿城西山华府珑园亿城西山华府珑园实景图亿城西山华府珑园经纪人亿城西山华府珑园房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;亿城西山华府珑园 安居客小区频道，为您提供北京亿城西山华府珑园2009年房价趋势、走势图，亿城西山华府珑园二手房均价价格信息， 及时查询亿城西山华府珑园房价走势、了解亿城西山华府珑园房价上涨还是下跌，预测亿城西山华府珑园房价暴跌暴涨，亿城西山华府珑园房价多少钱一平米？；# 马连洼亿城西山华府珑园附近租合租房子,马连洼附近租房价格,三室两厅合租-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;马连洼小区 &gt;亿城西山华府珑园&gt;亿城西山华府珑园附近小区租房 亿城西山华府珑园 * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 厅室： * 不限 * 一室 * 二室 * 三室 * 四室 * 四室以上 方式： * 不限 * 整套出租 * 合租出租 小区附近房 * 19000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 19000 元西山华府珑园四居两厅3卫，随时可以看房入住，配套齐全跟业主签 4室2厅 / 177.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 19000 元陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 19000 元新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元西山华府 177四居 全齐 马连洼地铁口 人大附中 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元西山华府珑园，一层有院，随时看房实拍图跟业主签可长租 2室1厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 * 19000 元南北通透 4室2厅 亿城西山华府珑园 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 * 11000 元马连洼双地铁 西山华府 一层院子 人大附中 农业大学 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元马连洼 西山华府 四居两卫 可以长租 随时看房 空置 随时住 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 精装修 * 20000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 20000 元新增 出租 带车位 集中供暖 家具家电齐全 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元业主人好事少 可长租 陪读妈妈必踩好房 马连洼 农大南路 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元西山华府 一层的两居室 家具齐全 方便看 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 安顺租房 * 武威租房 * 敦煌租房 * 澄迈租房 * 洛阳租房 * 安达租房 * 郴州租房 * 如皋租房 * 东海租房 * 新沂租房 * 宜春租房 * 四平租房 * 长岭租房 * 东营租房 * 青州租房 * 宜宾租房 * 喀什租房 * 石河子租房 * 克孜勒苏租房 * 金华租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 亿城西山华府禧园租房 * 竹园小区租房 * 百草园社区租房 * 菊花盛苑租房 * 菊园租房 * 兰园小区租房 * 绿苑小区租房 * 梅园(海淀)租房 * 广泰小区租房 * 梅园甲租房 * 万德嘉园(一区)租房 * 紫城嘉园租房 * 苗圃家属楼租房 * 水利社区二号院租房 * 万树园租房 * 圆明园西路3号院租房 * 天秀花园澄秀园租房 * 润千秋佳苑租房 * 水利社区1号院租房 * 东馨园租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅租房 * 两房租房 * 标准两居租房 * 3居租房 * 简装修出租 * 欧式豪华出租 * 隔音好租房 * 宜居住租房 * 带监控出租 * 免费转租出租 * 顶楼复式合租房 * 个人出租出租 * 业主直租合租房 * 特惠合租房 * 特价房租房 * loft复式合租房 * 双卫生间租房 * 大学附近合租房 * 景点附近出租 * 热门商圈附近出租 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 4室2厅泰禾西府大院 整租|4室2厅|197㎡|朝东南北 丰台-丽泽桥-泰禾西府大院 52000 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 ) 南北通透国锐金嵿5室2厅精装修 整租|5室2厅|277㎡|朝南北 大兴-亦庄-国锐金嵿 30000 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。</x:v>
+        <x:v>一居月租约5500-7900元/月，两居约15500元/月，三居约18000-23000元/月，四居约20000-23000元/月，五居约22000元/月，户型不同价格差异较大，押一付三为主，部分房源押一付一，中介佣金多为1个月租金。；房龄未明确提及，小区绿化率高（约40%），容积率低（1.5），房屋均为精装修；；小区物业方面有万科物业及麦田房产等提供相关服务，但未提及隔音、物业细节（如服务质量），户型多南北通透，楼龄看起来较新（无老旧描述）。；搜索结果中未找到明确的房屋隔音差、物业差评等负面信息，但部分房源描述的中介佣金及付款方式需提前确认；</x:v>
       </x:c>
       <x:c r="L27" t="str">
-        <x:v>from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡ 6月挂牌均价 0.03% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 一层50平园子）全南2居 中间位置 满五年价格可谈双地铁 马连洼 亿城西山华府珑园 846 万 2室2厅 93.51㎡ 万科物业推荐好房 马连洼西山华府一居出售 带电梯 大阳台 马连洼 亿城西山华府珑园 540 万 1室1厅 59.42㎡ 必看好房）马连洼品质2居 带明卫满五一 不临街中高层 双地铁 马连洼 亿城西山华府珑园 1080 万 2室2厅 120.84㎡ 海淀双卫两居 一梯两户 中间位置 车储 万科物业 马连洼 亿城西山华府珑园 1150 万 2室2厅 121.52㎡ 必卖好房）单本全明3居 一车一储 满五年 价格可谈双地铁 马连洼 亿城西山华府珑园 1498 万 3室2厅 177.47㎡ 必看高层）挑高4.2M 一车一储 方正4居 视野开阔价格可谈 马连洼 亿城西山华府珑园 1600 万 4室2厅 176.36㎡ ### 本小区租房推荐查看更多 ### 西山华府 177四居 全齐 马连洼地铁口 人大附中 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 马连洼双地铁 西山华府 一层院子 人大附中 农业大学 马连洼 亿城西山华府珑园 整租 16/18号线 朝南 _11000_ 元/月 2室2厅 93.5㎡ ### 陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 178.8㎡ ### 新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 新增 出租 带车位 集中供暖 家具家电齐全 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 177㎡ ### 万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 178.1㎡ ### 周边热门小区查看更多 * 347 上林溪 海淀 上地 2014年竣工 距离3293m 74659 元/㎡24套在售 小区评测 近地铁 近学校 13号线 五六环之间 户型丰富 配套齐全 7.1 分 * 421 领秀新硅谷AB区 海淀 西二旗 2009年竣工 距离2708m 82732 元/㎡15套在售 小区评测 近地铁 近学校 昌平线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 6.9 分 * 3 当代城市家园 海淀 上地 2004年竣工 距离2550m 69075 元/㎡19套在售 小区评测 近地铁 近学校 13号线等 五六环之间 绿化好 配套齐全 7.2 分 小区单页 国奥村(西区)今日家园广渠金茂府(北区)朱雀门小区景泰嘉园远洋山水(北区)天鹅湾(北区)首城国际丽都壹号凤凰城(一期二期四期)望京花园西区华清嘉园御汤山东区芍药居北里小区华纺易城一栋洋房星河湾畅园山水文园东园万象新天家园翠微北里 本板块小区大全 褐石园今日家园碧桐园颐源居同泽园西里北坞嘉园南里上地佳园翠微南里四季香山雪梨澳乡(别墅)京泉馨苑东里西山美墅馆(别墅)美丽园智学苑香山艺墅交大嘉园尚峰尚水水云居万泉新新家园翠湖别墅 小区二手房 国奥村(西区)二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售朱雀门小区二手房出售景泰嘉园二手房出售远洋山水(北区)二手房出售天鹅湾(北区)二手房出售首城国际二手房出售丽都壹号二手房出售凤凰城(一期二期四期)二手房出售望京花园西区二手房出售华清嘉园二手房出售御汤山东区二手房出售芍药居北里小区二手房出售华纺易城二手房出售一栋洋房二手房出售星河湾畅园二手房出售山水文园东园二手房出售万象新天家园二手房出售翠微北里二手房出售 小区房价 国奥村(西区)房价走势今日家园房价走势广渠金茂府(北区)房价走势朱雀门小区房价走势景泰嘉园房价走势远洋山水(北区)房价走势天鹅湾(北区)房价走势首城国际房价走势丽都壹号房价走势凤凰城(一期二期四期)房价走势望京花园西区房价走势华清嘉园房价走势御汤山东区房价走势芍药居北里小区房价走势华纺易城房价走势一栋洋房房价走势星河湾畅园房价走势山水文园东园房价走势万象新天家园房价走势翠微北里房价走势 推荐小区价格 百环家园二手房出售紫金长安二手房出售华业东方玫瑰二手房出售首邑溪谷二手房出售新城国际二手房出售金色漫香苑二手房出售美丽园二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售中海紫御公馆二手房出售保利西山林语二手房出售新怡家园二手房出售平乐园小区二手房出售太阳公元(北区)二手房出售珠光逸景(二号院)二手房出售国奥村(东区)二手房出售保利百合花园二手房出售远洋天地二手房出售望京西园三区二手房出售 二手房商圈 海运仓二手房万泉河二手房延庆周边二手房八大处二手房皂君庙二手房麦子店二手房韩村河二手房东辛房二手房紫竹桥二手房媒体村二手房地安门二手房常营二手房通州周边二手房西二旗二手房密云城区二手房潭柘寺二手房新发地二手房五里店二手房保定二手房潞苑二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价亿城西山华府珑园小区亿城西山华府珑园二手房亿城西山华府珑园租房亿城西山华府珑园户型图亿城西山华府珑园周边配置亿城西山华府珑园亿城西山华府珑园实景图亿城西山华府珑园经纪人亿城西山华府珑园房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;亿城西山华府珑园 安居客小区频道，为您提供北京亿城西山华府珑园2009年房价趋势、走势图，亿城西山华府珑园二手房均价价格信息， 及时查询亿城西山华府珑园房价走势、了解亿城西山华府珑园房价上涨还是下跌，预测亿城西山华府珑园房价暴跌暴涨，亿城西山华府珑园房价多少钱一平米？；# 马连洼亿城西山华府珑园附近租合租房子,马连洼附近租房价格,三室两厅合租-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;马连洼小区 &gt;亿城西山华府珑园&gt;亿城西山华府珑园附近小区租房 亿城西山华府珑园 * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 厅室： * 不限 * 一室 * 二室 * 三室 * 四室 * 四室以上 方式： * 不限 * 整套出租 * 合租出租 小区附近房 * 19000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 19000 元西山华府珑园四居两厅3卫，随时可以看房入住，配套齐全跟业主签 4室2厅 / 177.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 19000 元陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 19000 元新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元西山华府 177四居 全齐 马连洼地铁口 人大附中 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元西山华府珑园，一层有院，随时看房实拍图跟业主签可长租 2室1厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 * 19000 元南北通透 4室2厅 亿城西山华府珑园 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 * 11000 元马连洼双地铁 西山华府 一层院子 人大附中 农业大学 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元马连洼 西山华府 四居两卫 可以长租 随时看房 空置 随时住 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 精装修 * 20000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 20000 元新增 出租 带车位 集中供暖 家具家电齐全 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元业主人好事少 可长租 陪读妈妈必踩好房 马连洼 农大南路 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元西山华府 一层的两居室 家具齐全 方便看 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 安顺租房 * 武威租房 * 敦煌租房 * 澄迈租房 * 洛阳租房 * 安达租房 * 郴州租房 * 如皋租房 * 东海租房 * 新沂租房 * 宜春租房 * 四平租房 * 长岭租房 * 东营租房 * 青州租房 * 宜宾租房 * 喀什租房 * 石河子租房 * 克孜勒苏租房 * 金华租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 亿城西山华府禧园租房 * 竹园小区租房 * 百草园社区租房 * 菊花盛苑租房 * 菊园租房 * 兰园小区租房 * 绿苑小区租房 * 梅园(海淀)租房 * 广泰小区租房 * 梅园甲租房 * 万德嘉园(一区)租房 * 紫城嘉园租房 * 苗圃家属楼租房 * 水利社区二号院租房 * 万树园租房 * 圆明园西路3号院租房 * 天秀花园澄秀园租房 * 润千秋佳苑租房 * 水利社区1号院租房 * 东馨园租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅租房 * 两房租房 * 标准两居租房 * 3居租房 * 简装修出租 * 欧式豪华出租 * 隔音好租房 * 宜居住租房 * 带监控出租 * 免费转租出租 * 顶楼复式合租房 * 个人出租出租 * 业主直租合租房 * 特惠合租房 * 特价房租房 * loft复式合租房 * 双卫生间租房 * 大学附近合租房 * 景点附近出租 * 热门商圈附近出租 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。</x:v>
+        <x:v>生活配套：周边有中发百旺商城、农大超市等商超，厢黄旗公园、马莲园等休闲场所；；医疗有北京八珍堂中医医院、北京颐北中医门诊部、青龙桥社区卫生服务中心等；；餐饮资源未详细提及，但周边有商超及公园，日常餐饮需求可满足。</x:v>
       </x:c>
       <x:c r="M27" t="str">
-        <x:v># 马连洼亿城西山华府珑园附近租合租房子,马连洼附近租房价格,三室两厅合租-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;马连洼小区 &gt;亿城西山华府珑园&gt;亿城西山华府珑园附近小区租房 亿城西山华府珑园 * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 厅室： * 不限 * 一室 * 二室 * 三室 * 四室 * 四室以上 方式： * 不限 * 整套出租 * 合租出租 小区附近房 * 19000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 19000 元西山华府珑园四居两厅3卫，随时可以看房入住，配套齐全跟业主签 4室2厅 / 177.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 19000 元陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 19000 元新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元西山华府 177四居 全齐 马连洼地铁口 人大附中 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元西山华府珑园，一层有院，随时看房实拍图跟业主签可长租 2室1厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 * 19000 元南北通透 4室2厅 亿城西山华府珑园 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 * 11000 元马连洼双地铁 西山华府 一层院子 人大附中 农业大学 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元马连洼 西山华府 四居两卫 可以长租 随时看房 空置 随时住 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 精装修 * 20000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 20000 元新增 出租 带车位 集中供暖 家具家电齐全 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元业主人好事少 可长租 陪读妈妈必踩好房 马连洼 农大南路 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元西山华府 一层的两居室 家具齐全 方便看 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 安顺租房 * 武威租房 * 敦煌租房 * 澄迈租房 * 洛阳租房 * 安达租房 * 郴州租房 * 如皋租房 * 东海租房 * 新沂租房 * 宜春租房 * 四平租房 * 长岭租房 * 东营租房 * 青州租房 * 宜宾租房 * 喀什租房 * 石河子租房 * 克孜勒苏租房 * 金华租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 亿城西山华府禧园租房 * 竹园小区租房 * 百草园社区租房 * 菊花盛苑租房 * 菊园租房 * 兰园小区租房 * 绿苑小区租房 * 梅园(海淀)租房 * 广泰小区租房 * 梅园甲租房 * 万德嘉园(一区)租房 * 紫城嘉园租房 * 苗圃家属楼租房 * 水利社区二号院租房 * 万树园租房 * 圆明园西路3号院租房 * 天秀花园澄秀园租房 * 润千秋佳苑租房 * 水利社区1号院租房 * 东馨园租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅租房 * 两房租房 * 标准两居租房 * 3居租房 * 简装修出租 * 欧式豪华出租 * 隔音好租房 * 宜居住租房 * 带监控出租 * 免费转租出租 * 顶楼复式合租房 * 个人出租出租 * 业主直租合租房 * 特惠合租房 * 特价房租房 * loft复式合租房 * 双卫生间租房 * 大学附近合租房 * 景点附近出租 * 热门商圈附近出租 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。</x:v>
+        <x:v>小区物业方面有万科物业及麦田房产等提供相关服务，但未提及隔音、物业细节（如服务质量），户型多南北通透，楼龄看起来较新（无老旧描述）。；搜索结果中未找到明确的房屋隔音差、物业差评等负面信息，但部分房源描述的中介佣金及付款方式需提前确认；</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>价格线索：录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡； 上地 2014年竣工 距离3293m 74659 元/㎡；西二旗 2009年竣工 距离2708m 82732 元/㎡； 上地 2004年竣工 距离2550m 69075 元/㎡；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；房屋质量/户型线索：from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡ 6月挂牌均价 0.03% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 一层50平园子）全南2居 中间位置 满五年价格可谈双地铁 马连洼 亿城西山华府珑园 846 万 2室2厅 93.51㎡ 万科物业推荐好房 马连洼西山华府一居出售 带电梯 大阳台 马连洼 亿城西山华府珑园 540 万 1室1厅 59.42㎡ 必看好房）马连洼品质2居 带明卫满五一 不临街中高层 双地铁 马连洼 亿城西山华府珑园 1080 万 2室2厅 120.84㎡ 海淀双卫两居 一梯两户 中间位置 车储 万科物业 马连洼 亿城西山华府珑园 1150 万 2室2厅 121.52㎡ 必卖好房）单本全明3居 一车一储 满五年 价格可谈双地铁 马连洼 亿城西山华府珑园 1498 万 3室2厅 177.47㎡ 必看高层）挑高4.2M 一车一储 方正4居 视野开阔价格可谈 马连洼 亿城西山华府珑园 1600 万 4室2厅 176.36㎡ ### 本小区租房推荐查看更多 ### 西山华府 177四居 全齐 马连洼地铁口 人大附中 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 马连洼双地铁 西山华府 一层院子 人大附中 农业大学 马连洼 亿城西山华府珑园 整租 16/18号线 朝南 _11000_ 元/月 2室2厅 93.5㎡ ### 陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 178.8㎡ ### 新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 新增 出租 带车位 集中供暖 家具家电齐全 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 177㎡ ### 万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 178.1㎡ ### 周边热门小区查看更多 * 347 上林溪 海淀 上地 2014年竣工 距离3293m 74659 元/㎡24套在售 小区评测 近地铁 近学校 13号线 五六环之间 户型丰富 配套齐全 7.1 分 * 421 领秀新硅谷AB区 海淀 西二旗 2009年竣工 距离2708m 82732 元/㎡15套在售 小区评测 近地铁 近学校 昌平线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 6.9 分 * 3 当代城市家园 海淀 上地 2004年竣工 距离2550m 69075 元/㎡19套在售 小区评测 近地铁 近学校 13号线等 五六环之间 绿化好 配套齐全 7.2 分 小区单页 国奥村(西区)今日家园广渠金茂府(北区)朱雀门小区景泰嘉园远洋山水(北区)天鹅湾(北区)首城国际丽都壹号凤凰城(一期二期四期)望京花园西区华清嘉园御汤山东区芍药居北里小区华纺易城一栋洋房星河湾畅园山水文园东园万象新天家园翠微北里 本板块小区大全 褐石园今日家园碧桐园颐源居同泽园西里北坞嘉园南里上地佳园翠微南里四季香山雪梨澳乡(别墅)京泉馨苑东里西山美墅馆(别墅)美丽园智学苑香山艺墅交大嘉园尚峰尚水水云居万泉新新家园翠湖别墅 小区二手房 国奥村(西区)二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售朱雀门小区二手房出售景泰嘉园二手房出售远洋山水(北区)二手房出售天鹅湾(北区)二手房出售首城国际二手房出售丽都壹号二手房出售凤凰城(一期二期四期)二手房出售望京花园西区二手房出售华清嘉园二手房出售御汤山东区二手房出售芍药居北里小区二手房出售华纺易城二手房出售一栋洋房二手房出售星河湾畅园二手房出售山水文园东园二手房出售万象新天家园二手房出售翠微北里二手房出售 小区房价 国奥村(西区)房价走势今日家园房价走势广渠金茂府(北区)房价走势朱雀门小区房价走势景泰嘉园房价走势远洋山水(北区)房价走势天鹅湾(北区)房价走势首城国际房价走势丽都壹号房价走势凤凰城(一期二期四期)房价走势望京花园西区房价走势华清嘉园房价走势御汤山东区房价走势芍药居北里小区房价走势华纺易城房价走势一栋洋房房价走势星河湾畅园房价走势山水文园东园房价走势万象新天家园房价走势翠微北里房价走势 推荐小区价格 百环家园二手房出售紫金长安二手房出售华业东方玫瑰二手房出售首邑溪谷二手房出售新城国际二手房出售金色漫香苑二手房出售美丽园二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售中海紫御公馆二手房出售保利西山林语二手房出售新怡家园二手房出售平乐园小区二手房出售太阳公元(北区)二手房出售珠光逸景(二号院)二手房出售国奥村(东区)二手房出售保利百合花园二手房出售远洋天地二手房出售望京西园三区二手房出售 二手房商圈 海运仓二手房万泉河二手房延庆周边二手房八大处二手房皂君庙二手房麦子店二手房韩村河二手房东辛房二手房紫竹桥二手房媒体村二手房地安门二手房常营二手房通州周边二手房西二旗二手房密云城区二手房潭柘寺二手房新发地二手房五里店二手房保定二手房潞苑二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价亿城西山华府珑园小区亿城西山华府珑园二手房亿城西山华府珑园租房亿城西山华府珑园户型图亿城西山华府珑园周边配置亿城西山华府珑园亿城西山华府珑园实景图亿城西山华府珑园经纪人亿城西山华府珑园房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;亿城西山华府珑园 安居客小区频道，为您提供北京亿城西山华府珑园2009年房价趋势、走势图，亿城西山华府珑园二手房均价价格信息， 及时查询亿城西山华府珑园房价走势、了解亿城西山华府珑园房价上涨还是下跌，预测亿城西山华府珑园房价暴跌暴涨，亿城西山华府珑园房价多少钱一平米？；# 马连洼亿城西山华府珑园附近租合租房子,马连洼附近租房价格,三室两厅合租-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;马连洼小区 &gt;亿城西山华府珑园&gt;亿城西山华府珑园附近小区租房 亿城西山华府珑园 * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 厅室： * 不限 * 一室 * 二室 * 三室 * 四室 * 四室以上 方式： * 不限 * 整套出租 * 合租出租 小区附近房 * 19000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 19000 元西山华府珑园四居两厅3卫，随时可以看房入住，配套齐全跟业主签 4室2厅 / 177.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 19000 元陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 19000 元新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元西山华府 177四居 全齐 马连洼地铁口 人大附中 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元西山华府珑园，一层有院，随时看房实拍图跟业主签可长租 2室1厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 * 19000 元南北通透 4室2厅 亿城西山华府珑园 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 * 11000 元马连洼双地铁 西山华府 一层院子 人大附中 农业大学 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元马连洼 西山华府 四居两卫 可以长租 随时看房 空置 随时住 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 精装修 * 20000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 20000 元新增 出租 带车位 集中供暖 家具家电齐全 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元业主人好事少 可长租 陪读妈妈必踩好房 马连洼 农大南路 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元西山华府 一层的两居室 家具齐全 方便看 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 安顺租房 * 武威租房 * 敦煌租房 * 澄迈租房 * 洛阳租房 * 安达租房 * 郴州租房 * 如皋租房 * 东海租房 * 新沂租房 * 宜春租房 * 四平租房 * 长岭租房 * 东营租房 * 青州租房 * 宜宾租房 * 喀什租房 * 石河子租房 * 克孜勒苏租房 * 金华租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 亿城西山华府禧园租房 * 竹园小区租房 * 百草园社区租房 * 菊花盛苑租房 * 菊园租房 * 兰园小区租房 * 绿苑小区租房 * 梅园(海淀)租房 * 广泰小区租房 * 梅园甲租房 * 万德嘉园(一区)租房 * 紫城嘉园租房 * 苗圃家属楼租房 * 水利社区二号院租房 * 万树园租房 * 圆明园西路3号院租房 * 天秀花园澄秀园租房 * 润千秋佳苑租房 * 水利社区1号院租房 * 东馨园租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅租房 * 两房租房 * 标准两居租房 * 3居租房 * 简装修出租 * 欧式豪华出租 * 隔音好租房 * 宜居住租房 * 带监控出租 * 免费转租出租 * 顶楼复式合租房 * 个人出租出租 * 业主直租合租房 * 特惠合租房 * 特价房租房 * loft复式合租房 * 双卫生间租房 * 大学附近合租房 * 景点附近出租 * 热门商圈附近出租 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 4室2厅泰禾西府大院 整租|4室2厅|197㎡|朝东南北 丰台-丽泽桥-泰禾西府大院 52000 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 ) 南北通透国锐金嵿5室2厅精装修 整租|5室2厅|277㎡|朝南北 大兴-亦庄-国锐金嵿 30000 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；生活便利线索：from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 亿城西山华府珑园6月均价走势 90656 元/㎡ 6月挂牌均价 0.03% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 一层50平园子）全南2居 中间位置 满五年价格可谈双地铁 马连洼 亿城西山华府珑园 846 万 2室2厅 93.51㎡ 万科物业推荐好房 马连洼西山华府一居出售 带电梯 大阳台 马连洼 亿城西山华府珑园 540 万 1室1厅 59.42㎡ 必看好房）马连洼品质2居 带明卫满五一 不临街中高层 双地铁 马连洼 亿城西山华府珑园 1080 万 2室2厅 120.84㎡ 海淀双卫两居 一梯两户 中间位置 车储 万科物业 马连洼 亿城西山华府珑园 1150 万 2室2厅 121.52㎡ 必卖好房）单本全明3居 一车一储 满五年 价格可谈双地铁 马连洼 亿城西山华府珑园 1498 万 3室2厅 177.47㎡ 必看高层）挑高4.2M 一车一储 方正4居 视野开阔价格可谈 马连洼 亿城西山华府珑园 1600 万 4室2厅 176.36㎡ ### 本小区租房推荐查看更多 ### 西山华府 177四居 全齐 马连洼地铁口 人大附中 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 马连洼双地铁 西山华府 一层院子 人大附中 农业大学 马连洼 亿城西山华府珑园 整租 16/18号线 朝南 _11000_ 元/月 2室2厅 93.5㎡ ### 陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 178.8㎡ ### 新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _19000_ 元/月 4室2厅 177㎡ ### 新增 出租 带车位 集中供暖 家具家电齐全 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 177㎡ ### 万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 马连洼 亿城西山华府珑园 整租 16/18号线 南北 _20000_ 元/月 4室2厅 178.1㎡ ### 周边热门小区查看更多 * 347 上林溪 海淀 上地 2014年竣工 距离3293m 74659 元/㎡24套在售 小区评测 近地铁 近学校 13号线 五六环之间 户型丰富 配套齐全 7.1 分 * 421 领秀新硅谷AB区 海淀 西二旗 2009年竣工 距离2708m 82732 元/㎡15套在售 小区评测 近地铁 近学校 昌平线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 6.9 分 * 3 当代城市家园 海淀 上地 2004年竣工 距离2550m 69075 元/㎡19套在售 小区评测 近地铁 近学校 13号线等 五六环之间 绿化好 配套齐全 7.2 分 小区单页 国奥村(西区)今日家园广渠金茂府(北区)朱雀门小区景泰嘉园远洋山水(北区)天鹅湾(北区)首城国际丽都壹号凤凰城(一期二期四期)望京花园西区华清嘉园御汤山东区芍药居北里小区华纺易城一栋洋房星河湾畅园山水文园东园万象新天家园翠微北里 本板块小区大全 褐石园今日家园碧桐园颐源居同泽园西里北坞嘉园南里上地佳园翠微南里四季香山雪梨澳乡(别墅)京泉馨苑东里西山美墅馆(别墅)美丽园智学苑香山艺墅交大嘉园尚峰尚水水云居万泉新新家园翠湖别墅 小区二手房 国奥村(西区)二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售朱雀门小区二手房出售景泰嘉园二手房出售远洋山水(北区)二手房出售天鹅湾(北区)二手房出售首城国际二手房出售丽都壹号二手房出售凤凰城(一期二期四期)二手房出售望京花园西区二手房出售华清嘉园二手房出售御汤山东区二手房出售芍药居北里小区二手房出售华纺易城二手房出售一栋洋房二手房出售星河湾畅园二手房出售山水文园东园二手房出售万象新天家园二手房出售翠微北里二手房出售 小区房价 国奥村(西区)房价走势今日家园房价走势广渠金茂府(北区)房价走势朱雀门小区房价走势景泰嘉园房价走势远洋山水(北区)房价走势天鹅湾(北区)房价走势首城国际房价走势丽都壹号房价走势凤凰城(一期二期四期)房价走势望京花园西区房价走势华清嘉园房价走势御汤山东区房价走势芍药居北里小区房价走势华纺易城房价走势一栋洋房房价走势星河湾畅园房价走势山水文园东园房价走势万象新天家园房价走势翠微北里房价走势 推荐小区价格 百环家园二手房出售紫金长安二手房出售华业东方玫瑰二手房出售首邑溪谷二手房出售新城国际二手房出售金色漫香苑二手房出售美丽园二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售中海紫御公馆二手房出售保利西山林语二手房出售新怡家园二手房出售平乐园小区二手房出售太阳公元(北区)二手房出售珠光逸景(二号院)二手房出售国奥村(东区)二手房出售保利百合花园二手房出售远洋天地二手房出售望京西园三区二手房出售 二手房商圈 海运仓二手房万泉河二手房延庆周边二手房八大处二手房皂君庙二手房麦子店二手房韩村河二手房东辛房二手房紫竹桥二手房媒体村二手房地安门二手房常营二手房通州周边二手房西二旗二手房密云城区二手房潭柘寺二手房新发地二手房五里店二手房保定二手房潞苑二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价亿城西山华府珑园小区亿城西山华府珑园二手房亿城西山华府珑园租房亿城西山华府珑园户型图亿城西山华府珑园周边配置亿城西山华府珑园亿城西山华府珑园实景图亿城西山华府珑园经纪人亿城西山华府珑园房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;亿城西山华府珑园 安居客小区频道，为您提供北京亿城西山华府珑园2009年房价趋势、走势图，亿城西山华府珑园二手房均价价格信息， 及时查询亿城西山华府珑园房价走势、了解亿城西山华府珑园房价上涨还是下跌，预测亿城西山华府珑园房价暴跌暴涨，亿城西山华府珑园房价多少钱一平米？；# 马连洼亿城西山华府珑园附近租合租房子,马连洼附近租房价格,三室两厅合租-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;马连洼小区 &gt;亿城西山华府珑园&gt;亿城西山华府珑园附近小区租房 亿城西山华府珑园 * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 厅室： * 不限 * 一室 * 二室 * 三室 * 四室 * 四室以上 方式： * 不限 * 整套出租 * 合租出租 小区附近房 * 19000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 19000 元西山华府珑园四居两厅3卫，随时可以看房入住，配套齐全跟业主签 4室2厅 / 177.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 19000 元陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 19000 元新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元西山华府 177四居 全齐 马连洼地铁口 人大附中 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元西山华府珑园，一层有院，随时看房实拍图跟业主签可长租 2室1厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 * 19000 元南北通透 4室2厅 亿城西山华府珑园 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 * 11000 元马连洼双地铁 西山华府 一层院子 人大附中 农业大学 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元马连洼 西山华府 四居两卫 可以长租 随时看房 空置 随时住 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 精装修 * 20000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 20000 元新增 出租 带车位 集中供暖 家具家电齐全 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元业主人好事少 可长租 陪读妈妈必踩好房 马连洼 农大南路 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元西山华府 一层的两居室 家具齐全 方便看 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 安顺租房 * 武威租房 * 敦煌租房 * 澄迈租房 * 洛阳租房 * 安达租房 * 郴州租房 * 如皋租房 * 东海租房 * 新沂租房 * 宜春租房 * 四平租房 * 长岭租房 * 东营租房 * 青州租房 * 宜宾租房 * 喀什租房 * 石河子租房 * 克孜勒苏租房 * 金华租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 亿城西山华府禧园租房 * 竹园小区租房 * 百草园社区租房 * 菊花盛苑租房 * 菊园租房 * 兰园小区租房 * 绿苑小区租房 * 梅园(海淀)租房 * 广泰小区租房 * 梅园甲租房 * 万德嘉园(一区)租房 * 紫城嘉园租房 * 苗圃家属楼租房 * 水利社区二号院租房 * 万树园租房 * 圆明园西路3号院租房 * 天秀花园澄秀园租房 * 润千秋佳苑租房 * 水利社区1号院租房 * 东馨园租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅租房 * 两房租房 * 标准两居租房 * 3居租房 * 简装修出租 * 欧式豪华出租 * 隔音好租房 * 宜居住租房 * 带监控出租 * 免费转租出租 * 顶楼复式合租房 * 个人出租出租 * 业主直租合租房 * 特惠合租房 * 特价房租房 * loft复式合租房 * 双卫生间租房 * 大学附近合租房 * 景点附近出租 * 热门商圈附近出租 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 在张自忠有一方。；风险线索：# 马连洼亿城西山华府珑园附近租合租房子,马连洼附近租房价格,三室两厅合租-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;马连洼小区 &gt;亿城西山华府珑园&gt;亿城西山华府珑园附近小区租房 亿城西山华府珑园 * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 厅室： * 不限 * 一室 * 二室 * 三室 * 四室 * 四室以上 方式： * 不限 * 整套出租 * 合租出租 小区附近房 * 19000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 19000 元西山华府珑园四居两厅3卫，随时可以看房入住，配套齐全跟业主签 4室2厅 / 177.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 19000 元陪读妈妈必踩好房 业主人好事少 可长租 小区环境美滋滋 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 19000 元新上 老业主的房子 四居三卫 初次出租 随时入住 可长租 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元西山华府 177四居 全齐 马连洼地铁口 人大附中 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元西山华府珑园，一层有院，随时看房实拍图跟业主签可长租 2室1厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 * 19000 元南北通透 4室2厅 亿城西山华府珑园 4室2厅 / 178.82㎡ 推荐理由： 邻地铁 * 11000 元马连洼双地铁 西山华府 一层院子 人大附中 农业大学 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 19000 元马连洼 西山华府 四居两卫 可以长租 随时看房 空置 随时住 4室2厅 / 177.00㎡ 推荐理由： 邻地铁 精装修 * 20000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 20000 元新增 出租 带车位 集中供暖 家具家电齐全 4室2厅 / 177㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 11000 元业主人好事少 可长租 陪读妈妈必踩好房 马连洼 农大南路 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元西山华府 一层的两居室 家具齐全 方便看 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 安顺租房 * 武威租房 * 敦煌租房 * 澄迈租房 * 洛阳租房 * 安达租房 * 郴州租房 * 如皋租房 * 东海租房 * 新沂租房 * 宜春租房 * 四平租房 * 长岭租房 * 东营租房 * 青州租房 * 宜宾租房 * 喀什租房 * 石河子租房 * 克孜勒苏租房 * 金华租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 亿城西山华府禧园租房 * 竹园小区租房 * 百草园社区租房 * 菊花盛苑租房 * 菊园租房 * 兰园小区租房 * 绿苑小区租房 * 梅园(海淀)租房 * 广泰小区租房 * 梅园甲租房 * 万德嘉园(一区)租房 * 紫城嘉园租房 * 苗圃家属楼租房 * 水利社区二号院租房 * 万树园租房 * 圆明园西路3号院租房 * 天秀花园澄秀园租房 * 润千秋佳苑租房 * 水利社区1号院租房 * 东馨园租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅租房 * 两房租房 * 标准两居租房 * 3居租房 * 简装修出租 * 欧式豪华出租 * 隔音好租房 * 宜居住租房 * 带监控出租 * 免费转租出租 * 顶楼复式合租房 * 个人出租出租 * 业主直租合租房 * 特惠合租房 * 特价房租房 * loft复式合租房 * 双卫生间租房 * 大学附近合租房 * 景点附近出租 * 热门商圈附近出租 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。</x:v>
+        <x:v>价格线索：一居月租约5500-7900元/月；，两居约15500元/月；，三居约18000-23000元/月；，四居约20000-23000元/月；，五居约22000元/月；房屋质量/户型线索：一居月租约5500-7900元/月，两居约15500元/月，三居约18000-23000元/月，四居约20000-23000元/月，五居约22000元/月，户型不同价格差异较大，押一付三为主，部分房源押一付一，中介佣金多为1个月租金。；房龄未明确提及，小区绿化率高（约40%），容积率低（1.5），房屋均为精装修；；小区物业方面有万科物业及麦田房产等提供相关服务，但未提及隔音、物业细节（如服务质量），户型多南北通透，楼龄看起来较新（无老旧描述）。；搜索结果中未找到明确的房屋隔音差、物业差评等负面信息，但部分房源描述的中介佣金及付款方式需提前确认；；生活便利线索：生活配套：周边有中发百旺商城、农大超市等商超，厢黄旗公园、马莲园等休闲场所；；医疗有北京八珍堂中医医院、北京颐北中医门诊部、青龙桥社区卫生服务中心等；；餐饮资源未详细提及，但周边有商超及公园，日常餐饮需求可满足。；风险线索：小区物业方面有万科物业及麦田房产等提供相关服务，但未提及隔音、物业细节（如服务质量），户型多南北通透，楼龄看起来较新（无老旧描述）。；搜索结果中未找到明确的房屋隔音差、物业差评等负面信息，但部分房源描述的中介佣金及付款方式需提前确认；</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>1. 亿城西山华府珑园房价, 亿城西山华府珑园亿城西山华府珑园房价走势图, 亿城西山华府珑园价格均价多少钱-安居客 https://m.anjuke.com/bj/trendency/community/851045/
-2. 马连洼亿城西山华府珑园附近租合租房子,马连洼附近租房价格,三室两厅合租-北京58同城 https://mob.58.com/zfxq/bj-sy100403413/fujinchuzu/
-3. 【北京华体育app官方入口wa38.cc租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kw%E5%8D%8E%E4%BD%93%E8%82%B2app%E5%AE%98%E6%96%B9%E5%85%A5%E5%8F%A3wa38.cc?835%20target=_blank
-4. 亿城西山华府(珑园)二手房,2室1厅 亿城西山华府(珑园),房源位于马连洼南路8号-幸福里 https://fangchan.snssdk.com/ershoufang/bj-7443718847539970098.html
-5. 亿城西山华府,热门小区,北京法拍二手房源-金铂顺昌房拍网,北京产交所 https://www.fangpaiwang.com/xiaoqu-344.html</x:v>
+        <x:v>1. https://bj.zu.anjuke.com/fangyuan/4186594230217731
+2. http://m.anjuke.com/bj/rent/4555993753037836-3/
+3. http://m.anjuke.com/bj/rent/3922979718733824-3/
+4. https://bj.zu.anjuke.com/fangyuan/4408360916804620
+5. http://m.anjuke.com/bj/rent/4365753755901959-3/
+6. http://m.anjuke.com/bj/community/851045/rent/fx1/
+7. https://m.anjuke.com/bj/rent/4178919224798208-3/?fromm=&amp;shangquan_id=5968&amp;from=tw_zfdy_cnxh_click&amp;isauction=1
+8. 新出 西山华府珑园 分区大四居 品质上乘 位置安静 可长租 https://bj.zu.anjuke.com/fangyuan/4186594230217731</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1550,39 +1620,44 @@
         <x:v>东北旺南路33号</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F28" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G28" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H28" t="n">
-        <x:v>4.5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I28" t="str">
-        <x:v>搜索证据较为泛化，缺乏小区核心优劣势描述，评分保守，建议实地调研。</x:v>
+        <x:v>紧邻软件园，交通极便且居住清静，租金适中，是网易员工的高性价比之选。</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>55000 元/月；12000 元/月；65000 元/月；58000 元/月；180000 元/月；138000 元/月；75000 元/月；80000 元/月</x:v>
+        <x:v>的2室1厅1卫精装修房源月租约6300-6800元/月；（如6300元/月；、6500元/月；、6800元/月；另有整租2室2厅7200元/月；、合租次卧2200元/月</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v># 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；58000 元/月 [](https://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；30000 元/月 [](https://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；22000 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。</x:v>
+        <x:v>东旭园整租房源月租：2026年6月更新的2室1厅1卫精装修房源月租约6300-6800元/月（如6300元/月、6500元/月、6800元/月）；；户型以2室1厅（1卫）南北朝向为主，有简单装修和精装修两种；；房屋为板楼，楼层多在中层/低层（共5-6层）；；用户提及小区整体居住清静，但未明确提及隔音、物业细节，房龄未找到公开信息，装修状况以精装修为主，家具家电齐全。</x:v>
       </x:c>
       <x:c r="L28" t="str">
-        <x:v>) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；交通便利南北通透 18000 元/月 [](https://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；采光好周边配套齐 21800 元/月 [](https://www.fang.com/chuzu/3_486903096_1.htm) 清华大学双清苑 附小陪读 全新精装南北三居室 首次出 整租|3室2厅|122㎡|朝南北 海淀-学院路-双清苑 距昌平线学知园站约1157米。；交通便利周边配套齐采光好 20000 元/月 [](https://www.fang.com/chuzu/3_486864130_1.htm) 20套起看 万柳书院万城华府 2居南北通透 有车位有 整租|2室2厅|116㎡|朝南北 海淀-万柳-万城华府龙园 距10号线火器营站约436米。；交通便利周边配套齐首次出租 3000 元/月 [](https://www.fang.com/chuzu/3_481166418_1.htm) 西直门凯德茂。</x:v>
+        <x:v>交通：临近18号线上地软件园站（步行约594米）、东北旺站（步行约1639米），周边有东馨园南门站等公交站；；商超：步行可达千禧百旺生活超市；；医院：附近有东北旺乡医院；；餐饮、生活配套设施齐全，小区周边生活氛围较浓郁。</x:v>
       </x:c>
       <x:c r="M28" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未发现明确的租房风险或差评信息；</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>价格线索：55000 元/月；12000 元/月；65000 元/月；58000 元/月；180000 元/月；138000 元/月；75000 元/月；80000 元/月；房屋质量/户型线索：# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；58000 元/月 [](https://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；30000 元/月 [](https://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；22000 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。；生活便利线索：) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；交通便利南北通透 18000 元/月 [](https://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；采光好周边配套齐 21800 元/月 [](https://www.fang.com/chuzu/3_486903096_1.htm) 清华大学双清苑 附小陪读 全新精装南北三居室 首次出 整租|3室2厅|122㎡|朝南北 海淀-学院路-双清苑 距昌平线学知园站约1157米。；交通便利周边配套齐采光好 20000 元/月 [](https://www.fang.com/chuzu/3_486864130_1.htm) 20套起看 万柳书院万城华府 2居南北通透 有车位有 整租|2室2厅|116㎡|朝南北 海淀-万柳-万城华府龙园 距10号线火器营站约436米。；交通便利周边配套齐首次出租 3000 元/月 [](https://www.fang.com/chuzu/3_481166418_1.htm) 西直门凯德茂。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：的2室1厅1卫精装修房源月租约6300-6800元/月；（如6300元/月；、6500元/月；、6800元/月；另有整租2室2厅7200元/月；、合租次卧2200元/月；房屋质量/户型线索：东旭园整租房源月租：2026年6月更新的2室1厅1卫精装修房源月租约6300-6800元/月（如6300元/月、6500元/月、6800元/月）；；户型以2室1厅（1卫）南北朝向为主，有简单装修和精装修两种；；房屋为板楼，楼层多在中层/低层（共5-6层）；；用户提及小区整体居住清静，但未明确提及隔音、物业细节，房龄未找到公开信息，装修状况以精装修为主，家具家电齐全。；生活便利线索：交通：临近18号线上地软件园站（步行约594米）、东北旺站（步行约1639米），周边有东馨园南门站等公交站；；商超：步行可达千禧百旺生活超市；；医院：附近有东北旺乡医院；；餐饮、生活配套设施齐全，小区周边生活氛围较浓郁。；风险线索：未发现明确的租房风险或差评信息；</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>1. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_253028bj/
-2. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-3. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml</x:v>
+        <x:v>1. https://m.map.360.cn/site/detail/8347bab249cfec93
+2. http://m.anjuke.com/bj/rent/4605350484304911-3/
+3. http://m.anjuke.com/bj/rent/4556955683185665/
+4. http://m.anjuke.com/bj/community/81321/rent/l1/
+5. 【东旭园】东旭园二手房_东旭园租房_360地图 https://m.map.360.cn/site/detail/8347bab249cfec93
+6. 整租西北旺东旭园2室1厅 http://m.anjuke.com/bj/rent/4605350484304911-3/
+7. 东北旺 东旭园 温馨两居 配置齐全 自住精装 可长租 http://m.anjuke.com/bj/rent/4556955683185665/
+8. 东旭园租房 http://m.anjuke.com/bj/community/81321/rent/l1/</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1599,40 +1674,44 @@
         <x:v>北京市海淀区德政路87号</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F29" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G29" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H29" t="n">
-        <x:v>3.5</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I29" t="str">
-        <x:v>地处西城学区，距离网易大厦通勤距离远，且多为高价老旧小区，不建议租住。</x:v>
+        <x:v>离地铁近且生活配套成熟，餐饮发达，但房龄较老且物业口碑一般。</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>6万 2室1厅1卫丨68㎡丨南丨顶层丨 129200元/㎡； 1室1厅1卫丨47㎡丨西南丨高楼层丨 143600元/㎡； 2室1厅1卫丨69㎡丨西南丨低楼层丨 119400元/㎡；90000_ 元/m² 北露园，小区价格103260元/㎡</x:v>
+        <x:v>整租2室1厅约6800-7000元/月；、整租2室1厅约63000元/月；合租主卧约2400-3000元/月；、合租独卫约3000-3700元/月</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>北京吉屋网提供北京北露园二手房出售信息、北露园二手房价格，包括及时更新北京北露园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 北露园_北京北露园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_西城小区_&gt;_北露园 更新于 2026-06-01 10:56:02 [](https://bj.jiwu.com/tu/4234202.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234203.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234204.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234205.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234206.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234207.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234208.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234209.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234210.html "北露园实景图图片")[](https://bj.jiwu.com/tu/3741310.html "北露园实景图图片") # 北露园 别名：北露园 加入本地买房群 关注 _北京 - 西城 - 扣钟北路_ 发地址到手机 参考均价 _103260 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1993_ 小区户数 _1194_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-83群（304） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源全部房源 * [](https://bj.jiwu.com/esf/37411478.html "北露园 楼龄新，环境好，双南向 采光好 精装修，满5唯一公房")北露园 楼龄新，环境好，双南向 采光好 精装修，满5唯一公房 876万 2室1厅1卫丨68㎡丨南丨顶层丨 129200元/㎡ 北露园 | 西城 - | 1993年建 * [](https://bj.jiwu.com/esf/37226867.html "阜成门 北露园 1室1厅 93年楼龄 采光好")阜成门 北露园 1室1厅 93年楼龄 采光好 675万 1室1厅1卫丨47㎡丨西南丨高楼层丨 143600元/㎡ 北露园 | 西城 - | 1993年建 * [](https://bj.jiwu.com/esf/37226868.html "北露园 低楼层 西南朝向 采光好 楼龄新 不临街 大客厅")北露园 低楼层 西南朝向 采光好 楼龄新 不临街 大客厅 820万 2室1厅1卫丨69㎡丨西南丨低楼层丨 119400元/㎡ 北露园 | 西城 - | 1993年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(1) 全部户型 [](https://bj.jiwu.com/huxing/688898.html "北露园2室1厅1卫92㎡户型图")2室1厅1卫 92㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；## 北露园 _扣钟北路_ 发地址到手机 参考均价 _103260 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1993_ 小区户数 _1194_ 车位数量 _-_ 询成交价 新房源通知 加入买房群 北京买房交流群-83群（304） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？</x:v>
+        <x:v>整租2室1厅约6800-7000元/月、整租2室1厅约63000元/月（价格偏高，疑似大面积或特殊户型）；；房龄约2003-2004年，1/2号楼为9层电梯房，其余为6层板楼无电梯；；部分房源隔音好，户型以56平一居、70+平两居、96+平三居为主；；部分房源精装修，有公共设施配套；；物业整体评价偏负面，存在物业差的反馈；</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>北京吉屋网提供北京北露园二手房出售信息、北露园二手房价格，包括及时更新北京北露园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 北露园_北京北露园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_西城小区_&gt;_北露园 更新于 2026-06-01 10:56:02 [](https://bj.jiwu.com/tu/4234202.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234203.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234204.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234205.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234206.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234207.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234208.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234209.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234210.html "北露园实景图图片")[](https://bj.jiwu.com/tu/3741310.html "北露园实景图图片") # 北露园 别名：北露园 加入本地买房群 关注 _北京 - 西城 - 扣钟北路_ 发地址到手机 参考均价 _103260 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1993_ 小区户数 _1194_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-83群（304） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源全部房源 * [](https://bj.jiwu.com/esf/37411478.html "北露园 楼龄新，环境好，双南向 采光好 精装修，满5唯一公房")北露园 楼龄新，环境好，双南向 采光好 精装修，满5唯一公房 876万 2室1厅1卫丨68㎡丨南丨顶层丨 129200元/㎡ 北露园 | 西城 - | 1993年建 * [](https://bj.jiwu.com/esf/37226867.html "阜成门 北露园 1室1厅 93年楼龄 采光好")阜成门 北露园 1室1厅 93年楼龄 采光好 675万 1室1厅1卫丨47㎡丨西南丨高楼层丨 143600元/㎡ 北露园 | 西城 - | 1993年建 * [](https://bj.jiwu.com/esf/37226868.html "北露园 低楼层 西南朝向 采光好 楼龄新 不临街 大客厅")北露园 低楼层 西南朝向 采光好 楼龄新 不临街 大客厅 820万 2室1厅1卫丨69㎡丨西南丨低楼层丨 119400元/㎡ 北露园 | 西城 - | 1993年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(1) 全部户型 [](https://bj.jiwu.com/huxing/688898.html "北露园2室1厅1卫92㎡户型图")2室1厅1卫 92㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?</x:v>
+        <x:v>部分房源精装修，有公共设施配套；；地铁16号线西北旺站步行约300-800米，周边有公交站；；内部有超市发，南门有洗衣店、小吃店，步行1公里有百望山森林公园；；周边有中关村软件园、百度等企业，餐饮配套发达；</x:v>
       </x:c>
       <x:c r="M29" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。；#### 格拉斯小镇 1150万-2.4亿 通州区-通州别墅区 · 叠拼/联排/独栋 · 2007-04-20年建成 在售8套/在租0套 富成花园 3600万-1.6亿 朝阳区-亚运村小营 · 公寓/独栋 · 1998-01-01年建成 在售1套/在租0套 融创北京壹号庄园（东方普罗旺斯） 3200万-1.35亿 昌平区-奥北别墅区 · 公寓/独栋 · 2005-05-01年建成 在售5套/在租0套 ### 查看更多 * ### 建发海晏 海淀区 · 清河上地 2500-4100万 * ### 鼓楼四合院 西城区 · 鼓楼 暂无报价 * ### 懋源云纪 顺义区 · 后沙峪中央别墅区 1500-4000万 ### 户型定制 豪宅顾问将为您匹配本户型相关房源 同意定制后顾问将致电与您联系 您的私属豪宅顾问 (未读) ### 一手楼盘 * 观承别墅 * 红廷别墅 * 中粮瑞府 * 西山艺境 * 远洋天著春秋 ### 二手楼盘 * 西山壹号院 * 观唐别墅 * 山水文园 * 碧水庄园 * 星河湾 ### 租赁房源 * 泛海国际 * 当代MOMA * 太阳公元 * 四合院 * 新城国际 ### 公司介绍 * 公司介绍 * 招聘岗位 * 联系我们 * 隐私政策 ### 微信公众号 ### 移动端APP下载 北京丽兹行房地产顾问有限公司 Copyright2012经纪人入口投诉举报电话：400-888-9950备案号 京ICP备11032714号-3京公网安备 11010502040177号 APP 小程序 公众号 下载丽兹行豪宅APP 随时掌握房源动态/市场行情 体验丽兹行豪宅小程序 微信扫码无需下载即刻体验 关注丽兹行豪宅公众号 精选品质豪宅/场资讯早知道</x:v>
+        <x:v>物业整体评价偏负面，存在物业差的反馈；</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>价格线索：6万 2室1厅1卫丨68㎡丨南丨顶层丨 129200元/㎡； 1室1厅1卫丨47㎡丨西南丨高楼层丨 143600元/㎡； 2室1厅1卫丨69㎡丨西南丨低楼层丨 119400元/㎡；90000_ 元/m² 北露园，小区价格103260元/㎡；房屋质量/户型线索：北京吉屋网提供北京北露园二手房出售信息、北露园二手房价格，包括及时更新北京北露园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 北露园_北京北露园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_西城小区_&gt;_北露园 更新于 2026-06-01 10:56:02 [](https://bj.jiwu.com/tu/4234202.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234203.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234204.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234205.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234206.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234207.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234208.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234209.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234210.html "北露园实景图图片")[](https://bj.jiwu.com/tu/3741310.html "北露园实景图图片") # 北露园 别名：北露园 加入本地买房群 关注 _北京 - 西城 - 扣钟北路_ 发地址到手机 参考均价 _103260 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1993_ 小区户数 _1194_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-83群（304） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源全部房源 * [](https://bj.jiwu.com/esf/37411478.html "北露园 楼龄新，环境好，双南向 采光好 精装修，满5唯一公房")北露园 楼龄新，环境好，双南向 采光好 精装修，满5唯一公房 876万 2室1厅1卫丨68㎡丨南丨顶层丨 129200元/㎡ 北露园 | 西城 - | 1993年建 * [](https://bj.jiwu.com/esf/37226867.html "阜成门 北露园 1室1厅 93年楼龄 采光好")阜成门 北露园 1室1厅 93年楼龄 采光好 675万 1室1厅1卫丨47㎡丨西南丨高楼层丨 143600元/㎡ 北露园 | 西城 - | 1993年建 * [](https://bj.jiwu.com/esf/37226868.html "北露园 低楼层 西南朝向 采光好 楼龄新 不临街 大客厅")北露园 低楼层 西南朝向 采光好 楼龄新 不临街 大客厅 820万 2室1厅1卫丨69㎡丨西南丨低楼层丨 119400元/㎡ 北露园 | 西城 - | 1993年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(1) 全部户型 [](https://bj.jiwu.com/huxing/688898.html "北露园2室1厅1卫92㎡户型图")2室1厅1卫 92㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；## 北露园 _扣钟北路_ 发地址到手机 参考均价 _103260 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1993_ 小区户数 _1194_ 车位数量 _-_ 询成交价 新房源通知 加入买房群 北京买房交流群-83群（304） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；生活便利线索：北京吉屋网提供北京北露园二手房出售信息、北露园二手房价格，包括及时更新北京北露园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 北露园_北京北露园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_西城小区_&gt;_北露园 更新于 2026-06-01 10:56:02 [](https://bj.jiwu.com/tu/4234202.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234203.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234204.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234205.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234206.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234207.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234208.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234209.html "北露园实景图图片")[](https://bj.jiwu.com/tu/4234210.html "北露园实景图图片")[](https://bj.jiwu.com/tu/3741310.html "北露园实景图图片") # 北露园 别名：北露园 加入本地买房群 关注 _北京 - 西城 - 扣钟北路_ 发地址到手机 参考均价 _103260 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1993_ 小区户数 _1194_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-83群（304） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源全部房源 * [](https://bj.jiwu.com/esf/37411478.html "北露园 楼龄新，环境好，双南向 采光好 精装修，满5唯一公房")北露园 楼龄新，环境好，双南向 采光好 精装修，满5唯一公房 876万 2室1厅1卫丨68㎡丨南丨顶层丨 129200元/㎡ 北露园 | 西城 - | 1993年建 * [](https://bj.jiwu.com/esf/37226867.html "阜成门 北露园 1室1厅 93年楼龄 采光好")阜成门 北露园 1室1厅 93年楼龄 采光好 675万 1室1厅1卫丨47㎡丨西南丨高楼层丨 143600元/㎡ 北露园 | 西城 - | 1993年建 * [](https://bj.jiwu.com/esf/37226868.html "北露园 低楼层 西南朝向 采光好 楼龄新 不临街 大客厅")北露园 低楼层 西南朝向 采光好 楼龄新 不临街 大客厅 820万 2室1厅1卫丨69㎡丨西南丨低楼层丨 119400元/㎡ 北露园 | 西城 - | 1993年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(1) 全部户型 [](https://bj.jiwu.com/huxing/688898.html "北露园2室1厅1卫92㎡户型图")2室1厅1卫 92㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。；#### 格拉斯小镇 1150万-2.4亿 通州区-通州别墅区 · 叠拼/联排/独栋 · 2007-04-20年建成 在售8套/在租0套 富成花园 3600万-1.6亿 朝阳区-亚运村小营 · 公寓/独栋 · 1998-01-01年建成 在售1套/在租0套 融创北京壹号庄园（东方普罗旺斯） 3200万-1.35亿 昌平区-奥北别墅区 · 公寓/独栋 · 2005-05-01年建成 在售5套/在租0套 ### 查看更多 * ### 建发海晏 海淀区 · 清河上地 2500-4100万 * ### 鼓楼四合院 西城区 · 鼓楼 暂无报价 * ### 懋源云纪 顺义区 · 后沙峪中央别墅区 1500-4000万 ### 户型定制 豪宅顾问将为您匹配本户型相关房源 同意定制后顾问将致电与您联系 您的私属豪宅顾问 (未读) ### 一手楼盘 * 观承别墅 * 红廷别墅 * 中粮瑞府 * 西山艺境 * 远洋天著春秋 ### 二手楼盘 * 西山壹号院 * 观唐别墅 * 山水文园 * 碧水庄园 * 星河湾 ### 租赁房源 * 泛海国际 * 当代MOMA * 太阳公元 * 四合院 * 新城国际 ### 公司介绍 * 公司介绍 * 招聘岗位 * 联系我们 * 隐私政策 ### 微信公众号 ### 移动端APP下载 北京丽兹行房地产顾问有限公司 Copyright2012经纪人入口投诉举报电话：400-888-9950备案号 京ICP备11032714号-3京公网安备 11010502040177号 APP 小程序 公众号 下载丽兹行豪宅APP 随时掌握房源动态/市场行情 体验丽兹行豪宅小程序 微信扫码无需下载即刻体验 关注丽兹行豪宅公众号 精选品质豪宅/场资讯早知道</x:v>
+        <x:v>价格线索：整租2室1厅约6800-7000元/月；、整租2室1厅约63000元/月；合租主卧约2400-3000元/月；、合租独卫约3000-3700元/月；房屋质量/户型线索：整租2室1厅约6800-7000元/月、整租2室1厅约63000元/月（价格偏高，疑似大面积或特殊户型）；；房龄约2003-2004年，1/2号楼为9层电梯房，其余为6层板楼无电梯；；部分房源隔音好，户型以56平一居、70+平两居、96+平三居为主；；部分房源精装修，有公共设施配套；；物业整体评价偏负面，存在物业差的反馈；；生活便利线索：部分房源精装修，有公共设施配套；；地铁16号线西北旺站步行约300-800米，周边有公交站；；内部有超市发，南门有洗衣店、小吃店，步行1公里有百望山森林公园；；周边有中关村软件园、百度等企业，餐饮配套发达；；风险线索：物业整体评价偏负面，存在物业差的反馈；</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>1. 北露园_北京北露园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/171398.html
-2. 秋露园（必看好房）2室1厅 南北通透 满五 价可大聊,北京海淀西北旺百旺新城冬晴园二手房2室-房天下 https://m.fang.com/esf/bj/3_485754175.html
-3. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-4. 北京晴翠园楼盘介绍,晴翠园小区二手房、租房信息-丽兹行官网 https://www.lizihang.com/loupan/597600.html</x:v>
+        <x:v>1. http://m.anjuke.com/bj/community/851953/rent/fx2-x1/
+2. http://m.anjuke.com/bj/rent/3188681032571906-3/
+3. http://m.anjuke.com/bj/community/851953/rent/zj105-zx4/
+4. http://m.anjuke.com/bj/community/851953/jiedu/
+5. http://m.anjuke.com/bj/community/851953/rent/fx4-lx1/
+6. 秋露园租房 http://m.anjuke.com/bj/community/851953/rent/fx2-x1/
+7. 秋露园 3室1厅1卫 南北通透 精装修 电梯房 http://m.anjuke.com/bj/rent/3188681032571906-3/
+8. 秋露园租房 http://m.anjuke.com/bj/community/851953/rent/zj105-zx4/</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1649,36 +1728,42 @@
         <x:v>北京市海淀区圆明园西路（马连洼地铁站A西北口步行220米）</x:v>
       </x:c>
       <x:c r="E30" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F30" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G30" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H30" t="n">
-        <x:v>6.8</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I30" t="str">
-        <x:v>位于海淀马连洼，生活配套成熟，但网页证据多为二手房买卖信息，租金参考性一般。</x:v>
-      </x:c>
-      <x:c r="J30" t="str">
-        <x:v>125000_ 元/m² 梅园，小区价格50275元/㎡；000 ·东南三环晶城秀府现房在售 均价33000元/平方米；价房 ·西五环雍景山岚2-3居在售 均价24000元/平方米</x:v>
-      </x:c>
+        <x:v>距离地铁站极近，配套成熟且环境安静，虽房龄较老但户型方正，通勤非常便利。</x:v>
+      </x:c>
+      <x:c r="J30" t="str"/>
       <x:c r="K30" t="str">
-        <x:v>北京吉屋网提供北京梅园二手房出售信息、梅园二手房价格，包括及时更新北京梅园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 梅园_北京梅园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_梅园 更新于 2026-06-01 10:50:38 [](https://bj.jiwu.com/tu/4233277.html "梅园实景图图片")[](https://bj.jiwu.com/tu/4233278.html "梅园实景图图片")[](https://bj.jiwu.com/tu/4233279.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479947.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479948.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479949.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479950.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479951.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479952.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479953.html "梅园实景图图片") # 梅园 别名：梅园小区 加入本地买房群 关注 _北京 - 海淀 - 暂无资料_ 发地址到手机 参考均价 _50275 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _320户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小��主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-91群（377） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(2)3室(3) 全部户型 [](https://bj.jiwu.com/huxing/661710.html "梅园1室1厅1卫60㎡户型图")1室1厅1卫 60㎡咨询户型房源 [](https://bj.jiwu.com/huxing/661711.html "梅园2室1厅1卫110㎡户型图")2室1厅1卫 110㎡咨询户型房源 [](https://bj.jiwu.com/huxing/661712.html "梅园2室2厅1卫80㎡户型图")2室2厅1卫 80㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；## 梅园 _暂无资料_ 发地址到手机 参考均价 _50275 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _320户_ 车位数量 _-_ 询成交价 新房源通知 加入买房群 北京买房交流群-91群（377） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？</x:v>
+        <x:v>房龄：1998年建成，楼栋共7栋；；装修：房源多为精装修；；户型：朝向多南北通透，有两室、三室户型，户型方正；；物业：北京东居物业，物业费0.8-0.9元/㎡/月；；隔音、质量方面未明确提及差评，房源整体家电齐全、环境安静；</x:v>
       </x:c>
       <x:c r="L30" t="str">
-        <x:v>北京吉屋网提供北京梅园二手房出售信息、梅园二手房价格，包括及时更新北京梅园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 梅园_北京梅园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_梅园 更新于 2026-06-01 10:50:38 [](https://bj.jiwu.com/tu/4233277.html "梅园实景图图片")[](https://bj.jiwu.com/tu/4233278.html "梅园实景图图片")[](https://bj.jiwu.com/tu/4233279.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479947.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479948.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479949.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479950.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479951.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479952.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479953.html "梅园实景图图片") # 梅园 别名：梅园小区 加入本地买房群 关注 _北京 - 海淀 - 暂无资料_ 发地址到手机 参考均价 _50275 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _320户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小��主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-91群（377） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 感谢群主的推荐，很匹配我的诉求哇 * 看了群主发的区域解读，受益良多啊 * 都在说是上车好时候，大家怎么看啊 * 最近都说是上车好时候，大家怎么看 加入北京交流群，掌握一手楼市信息 加入群聊 小区问答 * 问 梅园“五证”有哪些？；梅园周边配套齐全，并且交通便捷。</x:v>
-      </x:c>
-      <x:c r="M30" t="str"/>
+        <x:v>通勤：距16号线马连洼站步行约256米，周边有公交；；商超：步行可达中发百旺商城、北京华联BHG Mall，还有一诺果蔬生鲜超市等；；医院：附近有解放军总医院第八医学中心；；餐饮：周边配套成熟，餐饮资源丰富；</x:v>
+      </x:c>
+      <x:c r="M30" t="str">
+        <x:v>隔音、质量方面未明确提及差评，房源整体家电齐全、环境安静；；无明确差评信息，未发现同名误命中风险。；无明确差评信息，未发现同名误命中风险</x:v>
+      </x:c>
       <x:c r="N30" t="str">
-        <x:v>价格线索：125000_ 元/m² 梅园，小区价格50275元/㎡；000 ·东南三环晶城秀府现房在售 均价33000元/平方米；价房 ·西五环雍景山岚2-3居在售 均价24000元/平方米；房屋质量/户型线索：北京吉屋网提供北京梅园二手房出售信息、梅园二手房价格，包括及时更新北京梅园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 梅园_北京梅园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_梅园 更新于 2026-06-01 10:50:38 [](https://bj.jiwu.com/tu/4233277.html "梅园实景图图片")[](https://bj.jiwu.com/tu/4233278.html "梅园实景图图片")[](https://bj.jiwu.com/tu/4233279.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479947.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479948.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479949.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479950.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479951.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479952.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479953.html "梅园实景图图片") # 梅园 别名：梅园小区 加入本地买房群 关注 _北京 - 海淀 - 暂无资料_ 发地址到手机 参考均价 _50275 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _320户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小��主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-91群（377） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(2)3室(3) 全部户型 [](https://bj.jiwu.com/huxing/661710.html "梅园1室1厅1卫60㎡户型图")1室1厅1卫 60㎡咨询户型房源 [](https://bj.jiwu.com/huxing/661711.html "梅园2室1厅1卫110㎡户型图")2室1厅1卫 110㎡咨询户型房源 [](https://bj.jiwu.com/huxing/661712.html "梅园2室2厅1卫80㎡户型图")2室2厅1卫 80㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；## 梅园 _暂无资料_ 发地址到手机 参考均价 _50275 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _320户_ 车位数量 _-_ 询成交价 新房源通知 加入买房群 北京买房交流群-91群（377） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；生活便利线索：北京吉屋网提供北京梅园二手房出售信息、梅园二手房价格，包括及时更新北京梅园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 梅园_北京梅园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_梅园 更新于 2026-06-01 10:50:38 [](https://bj.jiwu.com/tu/4233277.html "梅园实景图图片")[](https://bj.jiwu.com/tu/4233278.html "梅园实景图图片")[](https://bj.jiwu.com/tu/4233279.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479947.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479948.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479949.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479950.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479951.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479952.html "梅园实景图图片")[](https://bj.jiwu.com/tu/3479953.html "梅园实景图图片") # 梅园 别名：梅园小区 加入本地买房群 关注 _北京 - 海淀 - 暂无资料_ 发地址到手机 参考均价 _50275 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _320户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小��主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-91群（377） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 感谢群主的推荐，很匹配我的诉求哇 * 看了群主发的区域解读，受益良多啊 * 都在说是上车好时候，大家怎么看啊 * 最近都说是上车好时候，大家怎么看 加入北京交流群，掌握一手楼市信息 加入群聊 小区问答 * 问 梅园“五证”有哪些？；梅园周边配套齐全，并且交通便捷。</x:v>
+        <x:v>房屋质量/户型线索：房龄：1998年建成，楼栋共7栋；；装修：房源多为精装修；；户型：朝向多南北通透，有两室、三室户型，户型方正；；物业：北京东居物业，物业费0.8-0.9元/㎡/月；；隔音、质量方面未明确提及差评，房源整体家电齐全、环境安静；；生活便利线索：通勤：距16号线马连洼站步行约256米，周边有公交；；商超：步行可达中发百旺商城、北京华联BHG Mall，还有一诺果蔬生鲜超市等；；医院：附近有解放军总医院第八医学中心；；餐饮：周边配套成熟，餐饮资源丰富；；风险线索：隔音、质量方面未明确提及差评，房源整体家电齐全、环境安静；；无明确差评信息，未发现同名误命中风险。；无明确差评信息，未发现同名误命中风险</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>1. 梅园_北京梅园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/150247.html
-2. 安徽频道_新华房产_新华网 https://www.news.cn/house/anhui/lpdg.htm</x:v>
+        <x:v>1. http://m.anjuke.com/ch/rent/4562734535138310-3/
+2. http://m.anjuke.com/bj/rent/4537379190025220-3/
+3. http://m.anjuke.com/bj/rent/4524639158248448-3/
+4. https://bj.zu.anjuke.com/fangyuan/4240509559201792?psid=1936bebae318643dabfa80e34d56054b&amp;shangquan_id=5968
+5. https://m.lianjia.com/news/bj/xiaoqu/1111027378427.html
+6. https://bj.zu.anjuke.com/fangyuan/4159582402292741
+7. 马连洼地铁站精装三居 三卧室一样大 干净整洁 和业主签约长租 http://m.anjuke.com/ch/rent/4562734535138310-3/
+8. 马连洼 梅园甲小区 精装大三居 实图拍摄 业主人好价格可谈 http://m.anjuke.com/bj/rent/4537379190025220-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1695,40 +1780,44 @@
         <x:v>北京市海淀区马连洼竹园3号</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F31" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G31" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H31" t="n">
-        <x:v>6.2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I31" t="str">
-        <x:v>户型跨度大，但搜索结果夹杂大量无关豪宅及办公数据，对普通租房的参考价值受限。</x:v>
+        <x:v>租金价格适中，精装修且家电齐全，生活配套完善，适合追求性价比的租客。</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>竹园小区，小区价格72283元/㎡；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；寺四合院 可注册办公首次出租南北通透 210000 元/月；105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月；道湾东巷 可注册办公首次出租南北通透 120000 元/月</x:v>
+        <x:v>整租2室1厅月租5500-6000元/月；（面积57.8-64㎡），整租3室1厅7600元/月；（97.79㎡），合租主卧3200元/月</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>户型2-4室、建面73-104㎡。；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等竹园 ...。；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。</x:v>
+        <x:v>装修均为精装修，房龄未明确提及，户型多为南北通透或朝向好，配备家具家电齐全；；未提及隔音、物业的相关评价；</x:v>
       </x:c>
       <x:c r="L31" t="str">
-        <x:v>了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等竹园 ...。；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;</x:v>
+        <x:v>周边有聪聪生鲜超市、中发百旺商城，距离北京八珍堂中医医院约1082米，配套餐饮等生活设施齐全；；临近马连洼公交车站，通勤较便利；</x:v>
       </x:c>
       <x:c r="M31" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未搜索到明确的租房差评或风险信息，暂未发现同名误命中的情况。；未搜索到明确的租房差评或风险信息，暂未发现同名误命中的情况</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>价格线索：竹园小区，小区价格72283元/㎡；-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；寺四合院 可注册办公首次出租南北通透 210000 元/月；105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月；道湾东巷 可注册办公首次出租南北通透 120000 元/月；房屋质量/户型线索：户型2-4室、建面73-104㎡。；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等竹园 ...。；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；生活便利线索：了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等竹园 ...。；) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：整租2室1厅月租5500-6000元/月；（面积57.8-64㎡），整租3室1厅7600元/月；（97.79㎡），合租主卧3200元/月；房屋质量/户型线索：装修均为精装修，房龄未明确提及，户型多为南北通透或朝向好，配备家具家电齐全；；未提及隔音、物业的相关评价；；生活便利线索：周边有聪聪生鲜超市、中发百旺商城，距离北京八珍堂中医医院约1082米，配套餐饮等生活设施齐全；；临近马连洼公交车站，通勤较便利；；风险线索：未搜索到明确的租房差评或风险信息，暂未发现同名误命中的情况。；未搜索到明确的租房差评或风险信息，暂未发现同名误命中的情况</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>1. 竹园小区 - 北京买房- 吉屋网 https://bj.jiwu.com/loupan/170418.html
-2. 【北京pg娱乐电子游戏ty64.cc租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kwpg%E5%A8%B1%E4%B9%90%E7%94%B5%E5%AD%90%E6%B8%B8%E6%88%8Fty64.cc?71%20target=_blank
-3. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-4. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. https://bj.zu.anjuke.com/fangyuan/3843693340697613
+2. http://m.anjuke.com/bj/rent/4304033543465995-3/
+3. http://m.anjuke.com/dongyang/rent/4505947044490248-3/
+4. http://m.anjuke.com/bj/rent/4368739042567180-3/
+5. http://m.anjuke.com/bj/rent/4326489487695883-3/
+6. http://m.anjuke.com/bj/rent/4579525180533773-3/
+7. https://bj.zu.anjuke.com/fangyuan/4198781799312384
+8. 【多图】竹园小区，马连洼租房，低楼层采光好 竹园小区 干净两居 业主直签 配套全齐 可优惠，海淀租房 https://bj.zu.anjuke.com/fangyuan/3843693340697613</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1745,40 +1834,44 @@
         <x:v>北京市海淀区竹园东街</x:v>
       </x:c>
       <x:c r="E32" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G32" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H32" t="n">
-        <x:v>5.8</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I32" t="str">
-        <x:v>证据受高价四合院及办公房源严重干扰，缺乏有效居住质量描述，建议谨慎参考。</x:v>
+        <x:v>租金最亲民，周边生活极其便利，但属于老旧步梯楼且距离地铁站较远。</x:v>
       </x:c>
       <x:c r="J32" t="str">
-        <x:v>-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；胡同小区 可注册办公首次出租南北通透 250000 元/月；后小井胡同 可注册办公首次出租南北通透 60000 元/月；东四三条 可注册办公首次出租南北通透 300000 元/月；800㎡|朝南 海淀-万柳-万城华府 180000 元/月</x:v>
+        <x:v>单间合租2100-2650元/月；，整租2室5200-6500元/月；，整租3室9000元/月</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 4室2厅泰禾西府大院 整租|4室2厅|197㎡|朝东南北 丰台-丽泽桥-泰禾西府大院 52000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？</x:v>
+        <x:v>房龄较老（多层6层步梯），多为精装修，部分简单装修；；未提及隔音相关评价；；物业方面有提到小区治安严，但未具体评价物业服务质量；</x:v>
       </x:c>
       <x:c r="L32" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？</x:v>
+        <x:v>交通：临近16号线马连洼站（步行约1578米）、18号线上地站（步行约1454米），附近有菊园公交站；；商超：步行25米到千禧百旺连锁超市，还有中发百旺商城；；医院：附近有北京八珍堂中医医院、和平医院、西苑医院；；餐饮及生活配套齐全，环境有绿化、停车场，休闲有厢黄旗公园等；；暂未搜索到明确的租房风险或差评信息，部分房源为中介房源，需注意服务费及佣金情况，部分房源距离地铁有一定步行距离（约1.5公里）。</x:v>
       </x:c>
       <x:c r="M32" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 国子监。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>暂未搜索到明确的租房风险或差评信息，部分房源为中介房源，需注意服务费及佣金情况，部分房源距离地铁有一定步行距离（约1.5公里）。；暂未搜索到明确的租房风险或差评信息，部分房源为中介房源，需注意服务费及佣金情况，部分房源距离地铁有一定步行距离（约1.5公里）</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>价格线索：-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；胡同小区 可注册办公首次出租南北通透 250000 元/月；后小井胡同 可注册办公首次出租南北通透 60000 元/月；东四三条 可注册办公首次出租南北通透 300000 元/月；800㎡|朝南 海淀-万柳-万城华府 180000 元/月；房屋质量/户型线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 4室2厅泰禾西府大院 整租|4室2厅|197㎡|朝东南北 丰台-丽泽桥-泰禾西府大院 52000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 ) 5室2厅枫丹壹号2期 整租|5室2厅|218㎡|朝南北 大兴-亦庄-枫丹壹号二期 32000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；生活便利线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 国子监。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：单间合租2100-2650元/月；，整租2室5200-6500元/月；，整租3室9000元/月；房屋质量/户型线索：房龄较老（多层6层步梯），多为精装修，部分简单装修；；未提及隔音相关评价；；物业方面有提到小区治安严，但未具体评价物业服务质量；；生活便利线索：交通：临近16号线马连洼站（步行约1578米）、18号线上地站（步行约1454米），附近有菊园公交站；；商超：步行25米到千禧百旺连锁超市，还有中发百旺商城；；医院：附近有北京八珍堂中医医院、和平医院、西苑医院；；餐饮及生活配套齐全，环境有绿化、停车场，休闲有厢黄旗公园等；；暂未搜索到明确的租房风险或差评信息，部分房源为中介房源，需注意服务费及佣金情况，部分房源距离地铁有一定步行距离（约1.5公里）。；风险线索：暂未搜索到明确的租房风险或差评信息，部分房源为中介房源，需注意服务费及佣金情况，部分房源距离地铁有一定步行距离（约1.5公里）。；暂未搜索到明确的租房风险或差评信息，部分房源为中介房源，需注意服务费及佣金情况，部分房源距离地铁有一定步行距离（约1.5公里）</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>1. 【北京pa视讯wa48.cc租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kwPA%E8%A7%86%E8%AE%AFwa48.cc?595%20target=_blank
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-4. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml</x:v>
+        <x:v>1. https://m.map.360.cn/site/detail/80d6348b7249a7fe
+2. http://m.anjuke.com/bj/rent/4599406764338182-3/
+3. https://bj.zu.anjuke.com/fangyuan/4139766461603848
+4. http://m.anjuke.com/bj/rent/4363199711419401-3/
+5. http://m.anjuke.com/bj/rent/3840944178162690-3/
+6. http://m.anjuke.com/bj/rent/2983862836309007-3/
+7. http://m.anjuke.com/bj/rent/4366110773830667-3/
+8. http://m.anjuke.com/bj/rent/4592577105601541-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1795,39 +1888,44 @@
         <x:v>北京市海淀区圆明园西路和马连洼北路交叉口南260米</x:v>
       </x:c>
       <x:c r="E33" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F33" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G33" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H33" t="n">
-        <x:v>8</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="I33" t="str">
-        <x:v>马连洼核心居住区，通勤网易极近，人气评分较高，是该区域非常稳妥的租住选择。</x:v>
+        <x:v>位置优越，靠近地铁和大型商超，户型采光好，是网易员工通勤的优质选择。</x:v>
       </x:c>
       <x:c r="J33" t="str">
-        <x:v>房价涨幅排行 * 1 #### 百草园 67788元/㎡；% * 2 #### 圆明园西路3号院 75057元/㎡；8% * 3 #### 农大附中家属院 59059元/㎡；4.48% * 4 #### 和樾玉鸣 108704元/㎡；跌幅排行 * 1 #### 润千秋佳苑 73885元/㎡；5.68% * 2 #### 菊花盛苑 66268元/㎡；5.07% * 3 #### 紫城嘉园 80765元/㎡；.39% * 4 #### 部队家属院 35786元/㎡</x:v>
+        <x:v>整租价格约6000-8000元/月；（如2室1厅60-65平约6000-6700元/月；，1室1厅约6200元/月；，3室1厅约7600-8000元/月；），合租主卧约3000元/月</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v># 马连洼梅园房价_马连洼梅园价格_马连洼梅园二手房价格-北京房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明厦门福州长沙南宁长春沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；* 问【沿湖南区】 要看短租房 * 沉默： 您好，小区有短租的房子，您可以联系我带您看房 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；* 初娟娟： 您好密云这边租房子物业费和暖气费都需要自己交，物业费2.36元每平米 * 问 租房能落户吗？</x:v>
+        <x:v>房龄未明确提及，现有房源多为精装修，户型以南北通透、明厨明卫为主；；隔音信息未明确；</x:v>
       </x:c>
       <x:c r="L33" t="str">
-        <x:v>) * 我的房天下 * 特价房 * 我的房产圈 退出) 我要卖房 输入中文/拼音/拼音首字母或用上下键选择 房天下_&gt;_北京二手房_&gt;_海淀二手房_&gt;_马连洼二手房 分享 收藏 马连洼人气小区榜第19名 ### 马连洼梅园 8.4/10分查看评分别名：新梅园 * 小区首页 * 小区行情 * 小区攻略 * 小区详情 * 小区相册 * 二手房 * 法拍房 * 租房 * 小区成交 ### 马连洼梅园小区价格走势 ### 马连洼板块房价涨幅排行 * 1 #### 百草园 67788元/㎡↑6.83% * 2 #### 圆明园西路3号院 75057元/㎡↑5.28% * 3 #### 农大附中家属院 59059元/㎡↑4.48% * 4 #### 和樾玉鸣 108704元/㎡↑3.62% ### 马连洼房价跌幅排行 * 1 #### 润千秋佳苑 73885元/㎡↓-5.68% * 2 #### 菊花盛苑 66268元/㎡↓-5.07% * 3 #### 紫城嘉园 80765元/㎡↓-3.39% * 4 #### 部队家属院 35786元/㎡↓-3.00% ### 本楼盘二手房房源更多 * 2室1厅/75.36㎡410万 * 3室1厅/73.5㎡365万 * 2室1厅/57.9㎡379万 * 3室1厅/73.5㎡399万 ### 周边楼盘二手房房源 * 百草园 * 圆明园西路3号院 1套 * 农大附中家属院 * 和樾玉鸣 5套 免责声明：本网站不保证所有小区信息完全真实可靠，最终以政府部门登记备案为准，请谨慎核查。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。</x:v>
+        <x:v>交通：距地铁16号线马连洼站约592米，16号线农大南路站约1003米，紧邻圆明园西路北口公交站；；商业：周边有超市发便民菜店、中发百旺商城、北京华联BHG Mall等；；医疗：邻近解放军总医院第八医学中心；；休闲：靠近中国银行城市森林公园等公园；；疫情期间小区曾关闭部分门可能影响出行；</x:v>
       </x:c>
       <x:c r="M33" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未发现明确针对租房的负面风险差评。；未发现明确针对租房的负面风险差评</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>价格线索：房价涨幅排行 * 1 #### 百草园 67788元/㎡；% * 2 #### 圆明园西路3号院 75057元/㎡；8% * 3 #### 农大附中家属院 59059元/㎡；4.48% * 4 #### 和樾玉鸣 108704元/㎡；跌幅排行 * 1 #### 润千秋佳苑 73885元/㎡；5.68% * 2 #### 菊花盛苑 66268元/㎡；5.07% * 3 #### 紫城嘉园 80765元/㎡；.39% * 4 #### 部队家属院 35786元/㎡；房屋质量/户型线索：# 马连洼梅园房价_马连洼梅园价格_马连洼梅园二手房价格-北京房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明厦门福州长沙南宁长春沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；* 问【沿湖南区】 要看短租房 * 沉默： 您好，小区有短租的房子，您可以联系我带您看房 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；* 初娟娟： 您好密云这边租房子物业费和暖气费都需要自己交，物业费2.36元每平米 * 问 租房能落户吗？；生活便利线索：) * 我的房天下 * 特价房 * 我的房产圈 退出) 我要卖房 输入中文/拼音/拼音首字母或用上下键选择 房天下_&gt;_北京二手房_&gt;_海淀二手房_&gt;_马连洼二手房 分享 收藏 马连洼人气小区榜第19名 ### 马连洼梅园 8.4/10分查看评分别名：新梅园 * 小区首页 * 小区行情 * 小区攻略 * 小区详情 * 小区相册 * 二手房 * 法拍房 * 租房 * 小区成交 ### 马连洼梅园小区价格走势 ### 马连洼板块房价涨幅排行 * 1 #### 百草园 67788元/㎡↑6.83% * 2 #### 圆明园西路3号院 75057元/㎡↑5.28% * 3 #### 农大附中家属院 59059元/㎡↑4.48% * 4 #### 和樾玉鸣 108704元/㎡↑3.62% ### 马连洼房价跌幅排行 * 1 #### 润千秋佳苑 73885元/㎡↓-5.68% * 2 #### 菊花盛苑 66268元/㎡↓-5.07% * 3 #### 紫城嘉园 80765元/㎡↓-3.39% * 4 #### 部队家属院 35786元/㎡↓-3.00% ### 本楼盘二手房房源更多 * 2室1厅/75.36㎡410万 * 3室1厅/73.5㎡365万 * 2室1厅/57.9㎡379万 * 3室1厅/73.5㎡399万 ### 周边楼盘二手房房源 * 百草园 * 圆明园西路3号院 1套 * 农大附中家属院 * 和樾玉鸣 5套 免责声明：本网站不保证所有小区信息完全真实可靠，最终以政府部门登记备案为准，请谨慎核查。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：整租价格约6000-8000元/月；（如2室1厅60-65平约6000-6700元/月；，1室1厅约6200元/月；，3室1厅约7600-8000元/月；），合租主卧约3000元/月；房屋质量/户型线索：房龄未明确提及，现有房源多为精装修，户型以南北通透、明厨明卫为主；；隔音信息未明确；；生活便利线索：交通：距地铁16号线马连洼站约592米，16号线农大南路站约1003米，紧邻圆明园西路北口公交站；；商业：周边有超市发便民菜店、中发百旺商城、北京华联BHG Mall等；；医疗：邻近解放军总医院第八医学中心；；休闲：靠近中国银行城市森林公园等公园；；疫情期间小区曾关闭部分门可能影响出行；；风险线索：未发现明确针对租房的负面风险差评。；未发现明确针对租房的负面风险差评</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>1. 马连洼梅园房价_马连洼梅园价格_马连洼梅园二手房价格-北京房天下 https://esf.fang.com/loupan/1010499783/fangjia.htm
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4606654947353605-3/
+2. http://m.anjuke.com/bj/rent/4597168027589635-3/
+3. https://m.xflapp.com/owner-comment/6580943571384271118/7055841614773616670
+4. http://m.anjuke.com/bj/rent/4594091470756865-3/
+5. http://m.anjuke.com/bj/rent/4596118812814338-3/
+6. http://m.anjuke.com/bj/community/248748/rent/fx3-zj109/
+7. http://m.anjuke.com/bj/rent/4598177865786372-3/
+8. 马连洼地铁站 梅园双卧朝南 干净整洁 配置齐全 业主直签长租 http://m.anjuke.com/bj/rent/4606654947353605-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1844,41 +1942,44 @@
         <x:v>北京市海淀区后厂村路与永丰路交汇处</x:v>
       </x:c>
       <x:c r="E34" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F34" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G34" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H34" t="n">
-        <x:v>7.8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I34" t="str">
-        <x:v>万科高品质次新房，近地铁且车位充足，虽无直接租金数据，但属于高端改善型选择。</x:v>
+        <x:v>高端精装社区，物业优良且通勤便利，但租金极高，部分临街楼栋有噪音干扰。</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>% 车位配比 1:2 车位租金 583-630元/月； 车位管理费 150元/月；满二年 近地铁 车位充足 3280 万 104164元/㎡；满五年 近地铁 车位充足 3500 万 112356元/㎡；地铁 车位充足 采光较好 3700 万 129208元/㎡；有电梯 近地铁 车位充足 3280 万 104164元/㎡；路 东南 满五年 近地铁 1450 万 88340元/㎡</x:v>
+        <x:v>3居室月租约2.5万-2.8万/月；，4居室月租约3万-4.2万/月；，5居室及以上月租约3.6万-4万/月</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **102963** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓0.72% 贷款计算器 * 二手房源 116套 * 最近成交 69套 * 楼栋总数 26栋 * 房屋总数 1011户 * 建筑类型 板楼 * 建筑年代 2015年建成 * 小区位置 西北旺镇永丰路与后厂村路交界东南角地图 * 物业公司 北京万科物业管理有限公司 * 开发商 北京万湖房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 王福兴 评分：5.0 从业信息卡 百科 闪电回复 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 徐强 评分：4.9 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 如园标准四居 4室2厅 260.0㎡**2499**万 * #### 好房好视野 3室3厅 224.2㎡**2350**万 * #### 如园北区6室6厅南北 6室6厅 438.06㎡**4680**万 * #### 如园北区4室2厅南北 4室2厅 313.38㎡**2180**万 ### 五矿万科如园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 255.00㎡ | 2026-04-20 | -- | -- | 市场信息 | | 282.04㎡ | 2026-03-16 | -- | -- | 市场信息 | | 374.04㎡ | 2025-09-18 | -- | -- | 市场信息 | 查看全部成交 ### 五矿万科如园价格走势 ### 五矿万科如园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 五矿万科如园 海淀·马连洼**102964** 元/㎡ * #### 芳怡园 海淀·马连洼**69034** 元/㎡ * #### 百旺新城景和园 海淀·西北旺**66305** 元/㎡ * #### 百旺茉莉园 海淀·西北旺**75443** 元/㎡ * #### 中海枫涟山庄 海淀·西北旺**82937** 元/㎡ ### 相关资讯 * 小区资讯北京五矿万科如园怎么样?；五矿万科如园地址、户型和价格全览2021-09-25 * 小区资讯马连洼人都在看!；丽兹行提供近300个一二手豪宅楼盘信息介绍，可全面查看楼盘价格，户型、配套及成交信息。；) 实景图 1/52 实景图 2/52 实景图 3/52 实景图 4/52 实景图 5/52 实景图 6/52 实景图 7/52 实景图 8/52 实景图 9/52 实景图 10/52 实景图 11/52 实景图 12/52 实景图 13/52 实景图 14/52 实景图 15/52 实景图 16/52 实景图 17/52 实景图 18/52 实景图 19/52 实景图 20/52 实景图 21/52 实景图 22/52 实景图 23/52 实景图 24/52 实景图 25/52 实景图 26/52 实景图 27/52 实景图 28/52 实景图 29/52 实景图 30/52 实景图 31/52 实景图 32/52 实景图 33/52 实景图 34/52 实景图 35/52 实景图 36/52 实景图 37/52 实景图 38/52 实景图 39/52 实景图 40/52 实景图 41/52 实景图 42/52 实景图 43/52 实景图 44/52 实景图 45/52 实景图 46/52 实景图 47/52 实景图 48/52 实景图 49/52 实景图 50/52 实景图 51/52 实景图 52/52 效果图 1/13 效果图 2/13 效果图 3/13 效果图 4/13 效果图 5/13 效果图 6/13 效果图 7/13 效果图 8/13 效果图 9/13 效果图 10/13 效果图 11/13 效果图 12/13 效果图 13/13 位置图 1/1 周边配套图 1/22 周边配套图 2/22 周边配套图 3/22 周边配套图 4/22 周边配套图 5/22 周边配套图 6/22 周边配套图 7/22 周边配套图 8/22 周边配套图 9/22 周边配套图 10/22 周边配套图 11/22 周边配套图 12/22 周边配套图 13/22 周边配套图 14/22 周边配套图 15/22 周边配套图 16/22 周边配套图 17/22 周边配套图 18/22 周边配套图 19/22 周边配套图 20/22 周边配套图 21/22 周边配套图 22/22 楼栋分布图 1/1 实景图(52) 效果图(13) 位置图(1) 周边配套图(22) 楼栋分布图(1) 二手售价 1930-7000万 二手均价 6.18-13.78万/㎡ * 在售房源16套 * 在租房源1套 * 产品类型： 高档住宅 * 建筑年代： 2011-2018年 * 拿地时间： 2010.12.06 * 物业费： 6.9元/㎡/月 * 物业公司： 万科物业管理有限公司 * 开发商： 北京万湖房地产开发有限公司/北京五矿万科置业有限公司 [](https://bj.lizihang.com/adviser/153128.html) ##### 高瑞昂 **我维护该楼盘，为您提供买卖、租赁委托服务** **4008192629转8616** ### 灵魂卖点 ### 楼盘位置 ### 户型设计 ### 生活配套 ### 居住体验 ### 租售房源 ### 楼盘参数 ### 楼盘故事 ### 推荐楼盘 #### * 万科打造的精装科技住宅，配上家具家电即可入住。</x:v>
+        <x:v>3居室月租约2.5万-2.8万/月，4居室月租约3万-4.2万/月，5居室及以上月租约3.6万-4万/月，均为精装修且含物业费等（部分房租包含物业费）；；房龄约2015年（部分信息显示2011年建成需注意差异，需确认；；实际搜索结果中摘要6显示建筑年代2015），装修为高标准精装修（北区装修标准1.2万-1.5万/㎡），户型南北通透且楼间距大（约50米），物业为万科物业，24小时安保，隔音方面提及临街楼栋可能有噪音，非临街区域安静；；搜索结果中不同摘要显示房龄存在2011年和2015年的差异，需注意同名小区或信息误写的可能；；临街楼栋存在噪音问题。</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>丽兹行提供近300个一二手豪宅楼盘信息介绍，可全面查看楼盘价格，户型、配套及成交信息。；) 实景图 1/52 实景图 2/52 实景图 3/52 实景图 4/52 实景图 5/52 实景图 6/52 实景图 7/52 实景图 8/52 实景图 9/52 实景图 10/52 实景图 11/52 实景图 12/52 实景图 13/52 实景图 14/52 实景图 15/52 实景图 16/52 实景图 17/52 实景图 18/52 实景图 19/52 实景图 20/52 实景图 21/52 实景图 22/52 实景图 23/52 实景图 24/52 实景图 25/52 实景图 26/52 实景图 27/52 实景图 28/52 实景图 29/52 实景图 30/52 实景图 31/52 实景图 32/52 实景图 33/52 实景图 34/52 实景图 35/52 实景图 36/52 实景图 37/52 实景图 38/52 实景图 39/52 实景图 40/52 实景图 41/52 实景图 42/52 实景图 43/52 实景图 44/52 实景图 45/52 实景图 46/52 实景图 47/52 实景图 48/52 实景图 49/52 实景图 50/52 实景图 51/52 实景图 52/52 效果图 1/13 效果图 2/13 效果图 3/13 效果图 4/13 效果图 5/13 效果图 6/13 效果图 7/13 效果图 8/13 效果图 9/13 效果图 10/13 效果图 11/13 效果图 12/13 效果图 13/13 位置图 1/1 周边配套图 1/22 周边配套图 2/22 周边配套图 3/22 周边配套图 4/22 周边配套图 5/22 周边配套图 6/22 周边配套图 7/22 周边配套图 8/22 周边配套图 9/22 周边配套图 10/22 周边配套图 11/22 周边配套图 12/22 周边配套图 13/22 周边配套图 14/22 周边配套图 15/22 周边配套图 16/22 周边配套图 17/22 周边配套图 18/22 周边配套图 19/22 周边配套图 20/22 周边配套图 21/22 周边配套图 22/22 楼栋分布图 1/1 实景图(52) 效果图(13) 位置图(1) 周边配套图(22) 楼栋分布图(1) 二手售价 1930-7000万 二手均价 6.18-13.78万/㎡ * 在售房源16套 * 在租房源1套 * 产品类型： 高档住宅 * 建筑年代： 2011-2018年 * 拿地时间： 2010.12.06 * 物业费： 6.9元/㎡/月 * 物业公司： 万科物业管理有限公司 * 开发商： 北京万湖房地产开发有限公司/北京五矿万科置业有限公司 [](https://bj.lizihang.com/adviser/153128.html) ##### 高瑞昂 **我维护该楼盘，为您提供买卖、租赁委托服务** **4008192629转8616** ### 灵魂卖点 ### 楼盘位置 ### 户型设计 ### 生活配套 ### 居住体验 ### 租售房源 ### 楼盘参数 ### 楼盘故事 ### 推荐楼盘 #### * 万科打造的精装科技住宅，配上家具家电即可入住。；电动伸缩拉篮、智能洗碗机、恒温花洒等充满科技感，美观实用，生活更便捷。；* 全部200平以上大户型，户户2-4个生活阳台，让您有更多个性化的区域。；* 万科物业睿管家服务，为您的安全生活保驾护航。</x:v>
+        <x:v>距离地铁16号线西北旺站约700米，通勤便利；；小区周边有百旺公园等，毗邻中关村软件园；；生活配套方面有商超、医院等（摘要中提及周边配套完善但未详细列举，不过从位置判断属于海淀西北旺成熟区域）；</x:v>
       </x:c>
       <x:c r="M34" t="str">
-        <x:v>2011-04 开盘前夕，案名定为《万科如园》 2011-12 12月9日如园正式开盘，首期开盘均价4.2万/平 2016-12 如园西侧地铁16号线正式开通 2018-06 如园所有楼栋全部交付，正式进入二手房时代 #### 西山壹号院 1799-6500万 海淀区-西北旺 · 公寓 · 2012-06-01年建成 在售22套/在租1套 远洋万和公馆 1240-8500万 朝阳区-望京 · 公寓/联排 · 2014-12-31年建成 在售2套/在租0套 望京金茂府 2300-4800万 朝阳区-望京 · 公寓 · 2012-11-01年建成 在售1套/在租0套 颐和金茂府 1750-4280万 海淀区-西山别墅区 · -- · 2020年建成 在售1套/在租0套 香山壹号院 2100-4500万 海淀区-西山别墅区 · -- · 2021年建成 在售0套/在租0套 圆明天颂 3200-6500万 海淀区-西北旺 · -- · 2024年建成 在售2套/在租0套 ### 查看更多 * ### 东直门8号 朝阳区 · 东直门 2229-6859万 * ### 华润臻澐 海淀区 · 清河上地 1500-4700万 * ### 中建·运河玖院 通州区 · 通州新城 540-1950万 ### 户型定制 豪宅顾问将为您匹配本户型相关房源 同意定制后顾问将致电与您联系 您的私属豪宅顾问 (未读) ### 一手楼盘 * 观承别墅 * 红廷别墅 * 中粮瑞府 * 西山艺境 * 远洋天著春秋 ### 二手楼盘 * 西山壹号院 * 观唐别墅 * 山水文园 * 碧水庄园 * 星河湾 ### 租赁房源 * 泛海国际 * 当代MOMA * 太阳公元 * 四合院 * 新城国际 ### 公司介绍 * 公司介绍 * 招聘岗位 * 联系我们 * 隐私政策 ### 微信公众号 ### 移动端APP下载 北京丽兹行房地产顾问有限公司 Copyright2012经纪人入口投诉举报电话：400-888-9950备案号 京ICP备11032714号-3京公网安备 11010502040177号 APP 小程序 公众号 下载丽兹行豪宅APP 随时掌握房源动态/市场行情 体验丽兹行豪宅小程序 微信扫码无需下载即刻体验 关注丽兹行豪宅公众号 精选品质豪宅/场资讯早知道。；南区1：1比例，北区要相对宽松一些，1：2，车位充足 _174_ 个回答 【万科如园】 晚上会不会吵 临街位置的楼栋会有噪音 _170_ 个回答 打开APP查看全部问答 同户型装修案例 查看更多 轻奢 全包60万 现代 全包50万 简约 全包34万 简欧 全包52万 日式 半包25万 猜你喜欢 * VR看房 物业租售推荐：如园北区 户型5居价格可议诚意售带车位随时看 5室2厅 314.89㎡ 南北 海淀 西北旺 南北 满二年 近地铁 车位充足 3280 万 104164元/㎡ * VR看房 如园北区中心位置 稍后楼间距大 视野好 5室2厅 311.51㎡ 东南 海淀 西北旺 东南 满五年 近地铁 车位充足 3500 万 112356元/㎡ * VR看房 万科如园大师级作品 5居室 70大客厅 豪装维护好 直接住 5室2厅 286.36㎡ 东南 海淀 西北旺 东南 近地铁 车位充足 采光较好 3700 万 129208元/㎡ * VR看房 北区恒温恒湿科技住宅 中心位置 跑马大客厅 5室2厅 314.89㎡ 西南 海淀 西北旺 西南 有电梯 近地铁 车位充足 3280 万 104164元/㎡ * 3居室 朝向东南 精装 电梯房 诚心出售 价格可议 3室2厅 164.14㎡ 东南 朝阳 大望路 东南 满五年 近地铁 1450 万 88340元/㎡ 打开App查看全部房源 ### 热门楼盘 * _在售_ 山屿西山著 海淀区 温泉镇 225㎡ 售价待定 _车位充足_ _卧室全朝南_ _大户型_ _放松限购_ * _在售_ 圆明天颂 海淀区 上地 235-290㎡ 售价待定 _低容积_ _车位充足_ _主卧套房_ _装修交付_ _大户型_ 入围海淀区热力好盘榜 * _在售_ 和樾玉鸣 海淀区 上地 139-267㎡ 售价待定 _一房一价_ _轨交房_ _主卧套房_ _卧室全朝南_ _学校_ 首页 * 热门推荐 * 北京二手房 北京二手房 * 上海二手房 上海二手房 * 深圳二手房 深圳二手房 * 重庆二手房 重庆二手房 * 成都二手房 成都二手房 * 武汉二手房 武汉二手房 * 苏州二手房 苏州二手房 * 广州二手房 广州二手房 * 郑州二手房 郑州二手房 * 天津二手房 天津二手房 * 热门城市 * 北京二手房 北京二手房 * 上海二手房 上海二手房 * 深圳二手房 深圳二手房 * 重庆二手房 重庆二手房 * 成都二手房 成都二手房 * 武汉二手房 武汉二手房 * 苏州二手房 苏州二手房 * 广州二手房 广州二手房 * 郑州二手房 郑州二手房 * 天津二手房 天津二手房 * 省份历史房价 * 吉林历史房价 吉林历史房价 * 福建历史房价 福建历史房价 * 甘肃历史房价 甘肃历史房价 * 江苏历史房价 江苏历史房价 * 陕西历史房价 陕西历史房价 * 西藏历史房价 西藏历史房价 * 四川历史房价 四川历史房价 * 贵州历史房价 贵州历史房价 * 山西历史房价 山西历史房价 * 辽宁历史房价 辽宁历史房价 * 山东历史房价 山东历史房价 * 直辖市历史房价 直辖市历史房价 * 江西历史房价 江西历史房价 * 浙江历史房价 浙江历史房价 * 青海历史房价 青海历史房价 * 宁夏历史房价 宁夏历史房价 * 海南历史房价 海南历史房价 * 河北历史房价 河北历史房价 * 湖北历史房价 湖北历史房价 * 新疆历史房价 新疆历史房价 * 广东历史房价 广东历史房价 * 广西历史房价 广西历史房价 * 河南历史房价 河南历史房价 * 黑龙江历史房价 黑龙江历史房价 * 湖南历史房价 湖南历史房价 * 内蒙古历史房价 内蒙古历史房价 * 云南历史房价 云南历史房价 * 安徽历史房价 安徽历史房价 * 全国年份房价 * 2024年全国房价 2024年全国房价 * 2021年全国房价 2021年全国房价 * 2017年全国房价 2017年全国房价 * 2013年全国房价 2013年全国房价 * 2009年全国房价 2009年全国房价 * 2020年全国房价 2020年全国房价 * 2010年全国房价 2010年全国房价 * 2023年全国房价 2023年全国房价 * 2015年全国房价 2015年全国房价 * 2018年全国房价 2018年全国房价 * 2012年全国房价 2012年全国房价 * 2008年全国房价 2008年全国房价 * 2026年全国房价 2026年全国房价 * 2025年全国房价 2025年全国房价 * 2019年全国房价 2019年全国房价 * 2022年全国房价 2022年全国房价 * 2016年全国房价 2016年全国房价 * 2014年全国房价 2014年全国房价 * 2011年全国房价 2011年全国房价 首页&gt;北京房产信息&gt;北京二手房 官方客服电话: 10105858 季苹 万科物业二手房 微聊 小程序在线咨询 电话 获取手机号失败，可在线微聊联系经纪人 取消 去微聊 推荐信息。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>实际搜索结果中摘要6显示建筑年代2015），装修为高标准精装修（北区装修标准1.2万-1.5万/㎡），户型南北通透且楼间距大（约50米），物业为万科物业，24小时安保，隔音方面提及临街楼栋可能有噪音，非临街区域安静；；临街楼栋存在噪音问题。；临街楼栋存在噪音问题</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>价格线索：% 车位配比 1:2 车位租金 583-630元/月； 车位管理费 150元/月；满二年 近地铁 车位充足 3280 万 104164元/㎡；满五年 近地铁 车位充足 3500 万 112356元/㎡；地铁 车位充足 采光较好 3700 万 129208元/㎡；有电梯 近地铁 车位充足 3280 万 104164元/㎡；路 东南 满五年 近地铁 1450 万 88340元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) [](https://esf.fang.com/loupan/1010699497/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **102963** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓0.72% 贷款计算器 * 二手房源 116套 * 最近成交 69套 * 楼栋总数 26栋 * 房屋总数 1011户 * 建筑类型 板楼 * 建筑年代 2015年建成 * 小区位置 西北旺镇永丰路与后厂村路交界东南角地图 * 物业公司 北京万科物业管理有限公司 * 开发商 北京万湖房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 王福兴 评分：5.0 从业信息卡 百科 闪电回复 ##### 李金山 评分：4.9 从业信息卡 闪电回复 ##### 徐强 评分：4.9 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 如园标准四居 4室2厅 260.0㎡**2499**万 * #### 好房好视野 3室3厅 224.2㎡**2350**万 * #### 如园北区6室6厅南北 6室6厅 438.06㎡**4680**万 * #### 如园北区4室2厅南北 4室2厅 313.38㎡**2180**万 ### 五矿万科如园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 255.00㎡ | 2026-04-20 | -- | -- | 市场信息 | | 282.04㎡ | 2026-03-16 | -- | -- | 市场信息 | | 374.04㎡ | 2025-09-18 | -- | -- | 市场信息 | 查看全部成交 ### 五矿万科如园价格走势 ### 五矿万科如园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 五矿万科如园 海淀·马连洼**102964** 元/㎡ * #### 芳怡园 海淀·马连洼**69034** 元/㎡ * #### 百旺新城景和园 海淀·西北旺**66305** 元/㎡ * #### 百旺茉莉园 海淀·西北旺**75443** 元/㎡ * #### 中海枫涟山庄 海淀·西北旺**82937** 元/㎡ ### 相关资讯 * 小区资讯北京五矿万科如园怎么样?；五矿万科如园地址、户型和价格全览2021-09-25 * 小区资讯马连洼人都在看!；丽兹行提供近300个一二手豪宅楼盘信息介绍，可全面查看楼盘价格，户型、配套及成交信息。；) 实景图 1/52 实景图 2/52 实景图 3/52 实景图 4/52 实景图 5/52 实景图 6/52 实景图 7/52 实景图 8/52 实景图 9/52 实景图 10/52 实景图 11/52 实景图 12/52 实景图 13/52 实景图 14/52 实景图 15/52 实景图 16/52 实景图 17/52 实景图 18/52 实景图 19/52 实景图 20/52 实景图 21/52 实景图 22/52 实景图 23/52 实景图 24/52 实景图 25/52 实景图 26/52 实景图 27/52 实景图 28/52 实景图 29/52 实景图 30/52 实景图 31/52 实景图 32/52 实景图 33/52 实景图 34/52 实景图 35/52 实景图 36/52 实景图 37/52 实景图 38/52 实景图 39/52 实景图 40/52 实景图 41/52 实景图 42/52 实景图 43/52 实景图 44/52 实景图 45/52 实景图 46/52 实景图 47/52 实景图 48/52 实景图 49/52 实景图 50/52 实景图 51/52 实景图 52/52 效果图 1/13 效果图 2/13 效果图 3/13 效果图 4/13 效果图 5/13 效果图 6/13 效果图 7/13 效果图 8/13 效果图 9/13 效果图 10/13 效果图 11/13 效果图 12/13 效果图 13/13 位置图 1/1 周边配套图 1/22 周边配套图 2/22 周边配套图 3/22 周边配套图 4/22 周边配套图 5/22 周边配套图 6/22 周边配套图 7/22 周边配套图 8/22 周边配套图 9/22 周边配套图 10/22 周边配套图 11/22 周边配套图 12/22 周边配套图 13/22 周边配套图 14/22 周边配套图 15/22 周边配套图 16/22 周边配套图 17/22 周边配套图 18/22 周边配套图 19/22 周边配套图 20/22 周边配套图 21/22 周边配套图 22/22 楼栋分布图 1/1 实景图(52) 效果图(13) 位置图(1) 周边配套图(22) 楼栋分布图(1) 二手售价 1930-7000万 二手均价 6.18-13.78万/㎡ * 在售房源16套 * 在租房源1套 * 产品类型： 高档住宅 * 建筑年代： 2011-2018年 * 拿地时间： 2010.12.06 * 物业费： 6.9元/㎡/月 * 物业公司： 万科物业管理有限公司 * 开发商： 北京万湖房地产开发有限公司/北京五矿万科置业有限公司 [](https://bj.lizihang.com/adviser/153128.html) ##### 高瑞昂 **我维护该楼盘，为您提供买卖、租赁委托服务** **4008192629转8616** ### 灵魂卖点 ### 楼盘位置 ### 户型设计 ### 生活配套 ### 居住体验 ### 租售房源 ### 楼盘参数 ### 楼盘故事 ### 推荐楼盘 #### * 万科打造的精装科技住宅，配上家具家电即可入住。；生活便利线索：丽兹行提供近300个一二手豪宅楼盘信息介绍，可全面查看楼盘价格，户型、配套及成交信息。；) 实景图 1/52 实景图 2/52 实景图 3/52 实景图 4/52 实景图 5/52 实景图 6/52 实景图 7/52 实景图 8/52 实景图 9/52 实景图 10/52 实景图 11/52 实景图 12/52 实景图 13/52 实景图 14/52 实景图 15/52 实景图 16/52 实景图 17/52 实景图 18/52 实景图 19/52 实景图 20/52 实景图 21/52 实景图 22/52 实景图 23/52 实景图 24/52 实景图 25/52 实景图 26/52 实景图 27/52 实景图 28/52 实景图 29/52 实景图 30/52 实景图 31/52 实景图 32/52 实景图 33/52 实景图 34/52 实景图 35/52 实景图 36/52 实景图 37/52 实景图 38/52 实景图 39/52 实景图 40/52 实景图 41/52 实景图 42/52 实景图 43/52 实景图 44/52 实景图 45/52 实景图 46/52 实景图 47/52 实景图 48/52 实景图 49/52 实景图 50/52 实景图 51/52 实景图 52/52 效果图 1/13 效果图 2/13 效果图 3/13 效果图 4/13 效果图 5/13 效果图 6/13 效果图 7/13 效果图 8/13 效果图 9/13 效果图 10/13 效果图 11/13 效果图 12/13 效果图 13/13 位置图 1/1 周边配套图 1/22 周边配套图 2/22 周边配套图 3/22 周边配套图 4/22 周边配套图 5/22 周边配套图 6/22 周边配套图 7/22 周边配套图 8/22 周边配套图 9/22 周边配套图 10/22 周边配套图 11/22 周边配套图 12/22 周边配套图 13/22 周边配套图 14/22 周边配套图 15/22 周边配套图 16/22 周边配套图 17/22 周边配套图 18/22 周边配套图 19/22 周边配套图 20/22 周边配套图 21/22 周边配套图 22/22 楼栋分布图 1/1 实景图(52) 效果图(13) 位置图(1) 周边配套图(22) 楼栋分布图(1) 二手售价 1930-7000万 二手均价 6.18-13.78万/㎡ * 在售房源16套 * 在租房源1套 * 产品类型： 高档住宅 * 建筑年代： 2011-2018年 * 拿地时间： 2010.12.06 * 物业费： 6.9元/㎡/月 * 物业公司： 万科物业管理有限公司 * 开发商： 北京万湖房地产开发有限公司/北京五矿万科置业有限公司 [](https://bj.lizihang.com/adviser/153128.html) ##### 高瑞昂 **我维护该楼盘，为您提供买卖、租赁委托服务** **4008192629转8616** ### 灵魂卖点 ### 楼盘位置 ### 户型设计 ### 生活配套 ### 居住体验 ### 租售房源 ### 楼盘参数 ### 楼盘故事 ### 推荐楼盘 #### * 万科打造的精装科技住宅，配上家具家电即可入住。；电动伸缩拉篮、智能洗碗机、恒温花洒等充满科技感，美观实用，生活更便捷。；* 全部200平以上大户型，户户2-4个生活阳台，让您有更多个性化的区域。；* 万科物业睿管家服务，为您的安全生活保驾护航。；风险线索：2011-04 开盘前夕，案名定为《万科如园》 2011-12 12月9日如园正式开盘，首期开盘均价4.2万/平 2016-12 如园西侧地铁16号线正式开通 2018-06 如园所有楼栋全部交付，正式进入二手房时代 #### 西山壹号院 1799-6500万 海淀区-西北旺 · 公寓 · 2012-06-01年建成 在售22套/在租1套 远洋万和公馆 1240-8500万 朝阳区-望京 · 公寓/联排 · 2014-12-31年建成 在售2套/在租0套 望京金茂府 2300-4800万 朝阳区-望京 · 公寓 · 2012-11-01年建成 在售1套/在租0套 颐和金茂府 1750-4280万 海淀区-西山别墅区 · -- · 2020年建成 在售1套/在租0套 香山壹号院 2100-4500万 海淀区-西山别墅区 · -- · 2021年建成 在售0套/在租0套 圆明天颂 3200-6500万 海淀区-西北旺 · -- · 2024年建成 在售2套/在租0套 ### 查看更多 * ### 东直门8号 朝阳区 · 东直门 2229-6859万 * ### 华润臻澐 海淀区 · 清河上地 1500-4700万 * ### 中建·运河玖院 通州区 · 通州新城 540-1950万 ### 户型定制 豪宅顾问将为您匹配本户型相关房源 同意定制后顾问将致电与您联系 您的私属豪宅顾问 (未读) ### 一手楼盘 * 观承别墅 * 红廷别墅 * 中粮瑞府 * 西山艺境 * 远洋天著春秋 ### 二手楼盘 * 西山壹号院 * 观唐别墅 * 山水文园 * 碧水庄园 * 星河湾 ### 租赁房源 * 泛海国际 * 当代MOMA * 太阳公元 * 四合院 * 新城国际 ### 公司介绍 * 公司介绍 * 招聘岗位 * 联系我们 * 隐私政策 ### 微信公众号 ### 移动端APP下载 北京丽兹行房地产顾问有限公司 Copyright2012经纪人入口投诉举报电话：400-888-9950备案号 京ICP备11032714号-3京公网安备 11010502040177号 APP 小程序 公众号 下载丽兹行豪宅APP 随时掌握房源动态/市场行情 体验丽兹行豪宅小程序 微信扫码无需下载即刻体验 关注丽兹行豪宅公众号 精选品质豪宅/场资讯早知道。；南区1：1比例，北区要相对宽松一些，1：2，车位充足 _174_ 个回答 【万科如园】 晚上会不会吵 临街位置的楼栋会有噪音 _170_ 个回答 打开APP查看全部问答 同户型装修案例 查看更多 轻奢 全包60万 现代 全包50万 简约 全包34万 简欧 全包52万 日式 半包25万 猜你喜欢 * VR看房 物业租售推荐：如园北区 户型5居价格可议诚意售带车位随时看 5室2厅 314.89㎡ 南北 海淀 西北旺 南北 满二年 近地铁 车位充足 3280 万 104164元/㎡ * VR看房 如园北区中心位置 稍后楼间距大 视野好 5室2厅 311.51㎡ 东南 海淀 西北旺 东南 满五年 近地铁 车位充足 3500 万 112356元/㎡ * VR看房 万科如园大师级作品 5居室 70大客厅 豪装维护好 直接住 5室2厅 286.36㎡ 东南 海淀 西北旺 东南 近地铁 车位充足 采光较好 3700 万 129208元/㎡ * VR看房 北区恒温恒湿科技住宅 中心位置 跑马大客厅 5室2厅 314.89㎡ 西南 海淀 西北旺 西南 有电梯 近地铁 车位充足 3280 万 104164元/㎡ * 3居室 朝向东南 精装 电梯房 诚心出售 价格可议 3室2厅 164.14㎡ 东南 朝阳 大望路 东南 满五年 近地铁 1450 万 88340元/㎡ 打开App查看全部房源 ### 热门楼盘 * _在售_ 山屿西山著 海淀区 温泉镇 225㎡ 售价待定 _车位充足_ _卧室全朝南_ _大户型_ _放松限购_ * _在售_ 圆明天颂 海淀区 上地 235-290㎡ 售价待定 _低容积_ _车位充足_ _主卧套房_ _装修交付_ _大户型_ 入围海淀区热力好盘榜 * _在售_ 和樾玉鸣 海淀区 上地 139-267㎡ 售价待定 _一房一价_ _轨交房_ _主卧套房_ _卧室全朝南_ _学校_ 首页 * 热门推荐 * 北京二手房 北京二手房 * 上海二手房 上海二手房 * 深圳二手房 深圳二手房 * 重庆二手房 重庆二手房 * 成都二手房 成都二手房 * 武汉二手房 武汉二手房 * 苏州二手房 苏州二手房 * 广州二手房 广州二手房 * 郑州二手房 郑州二手房 * 天津二手房 天津二手房 * 热门城市 * 北京二手房 北京二手房 * 上海二手房 上海二手房 * 深圳二手房 深圳二手房 * 重庆二手房 重庆二手房 * 成都二手房 成都二手房 * 武汉二手房 武汉二手房 * 苏州二手房 苏州二手房 * 广州二手房 广州二手房 * 郑州二手房 郑州二手房 * 天津二手房 天津二手房 * 省份历史房价 * 吉林历史房价 吉林历史房价 * 福建历史房价 福建历史房价 * 甘肃历史房价 甘肃历史房价 * 江苏历史房价 江苏历史房价 * 陕西历史房价 陕西历史房价 * 西藏历史房价 西藏历史房价 * 四川历史房价 四川历史房价 * 贵州历史房价 贵州历史房价 * 山西历史房价 山西历史房价 * 辽宁历史房价 辽宁历史房价 * 山东历史房价 山东历史房价 * 直辖市历史房价 直辖市历史房价 * 江西历史房价 江西历史房价 * 浙江历史房价 浙江历史房价 * 青海历史房价 青海历史房价 * 宁夏历史房价 宁夏历史房价 * 海南历史房价 海南历史房价 * 河北历史房价 河北历史房价 * 湖北历史房价 湖北历史房价 * 新疆历史房价 新疆历史房价 * 广东历史房价 广东历史房价 * 广西历史房价 广西历史房价 * 河南历史房价 河南历史房价 * 黑龙江历史房价 黑龙江历史房价 * 湖南历史房价 湖南历史房价 * 内蒙古历史房价 内蒙古历史房价 * 云南历史房价 云南历史房价 * 安徽历史房价 安徽历史房价 * 全国年份房价 * 2024年全国房价 2024年全国房价 * 2021年全国房价 2021年全国房价 * 2017年全国房价 2017年全国房价 * 2013年全国房价 2013年全国房价 * 2009年全国房价 2009年全国房价 * 2020年全国房价 2020年全国房价 * 2010年全国房价 2010年全国房价 * 2023年全国房价 2023年全国房价 * 2015年全国房价 2015年全国房价 * 2018年全国房价 2018年全国房价 * 2012年全国房价 2012年全国房价 * 2008年全国房价 2008年全国房价 * 2026年全国房价 2026年全国房价 * 2025年全国房价 2025年全国房价 * 2019年全国房价 2019年全国房价 * 2022年全国房价 2022年全国房价 * 2016年全国房价 2016年全国房价 * 2014年全国房价 2014年全国房价 * 2011年全国房价 2011年全国房价 首页&gt;北京房产信息&gt;北京二手房 官方客服电话: 10105858 季苹 万科物业二手房 微聊 小程序在线咨询 电话 获取手机号失败，可在线微聊联系经纪人 取消 去微聊 推荐信息。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：3居室月租约2.5万-2.8万/月；，4居室月租约3万-4.2万/月；，5居室及以上月租约3.6万-4万/月；房屋质量/户型线索：3居室月租约2.5万-2.8万/月，4居室月租约3万-4.2万/月，5居室及以上月租约3.6万-4万/月，均为精装修且含物业费等（部分房租包含物业费）；；房龄约2015年（部分信息显示2011年建成需注意差异，需确认；；实际搜索结果中摘要6显示建筑年代2015），装修为高标准精装修（北区装修标准1.2万-1.5万/㎡），户型南北通透且楼间距大（约50米），物业为万科物业，24小时安保，隔音方面提及临街楼栋可能有噪音，非临街区域安静；；搜索结果中不同摘要显示房龄存在2011年和2015年的差异，需注意同名小区或信息误写的可能；；临街楼栋存在噪音问题。；生活便利线索：距离地铁16号线西北旺站约700米，通勤便利；；小区周边有百旺公园等，毗邻中关村软件园；；生活配套方面有商超、医院等（摘要中提及周边配套完善但未详细列举，不过从位置判断属于海淀西北旺成熟区域）；；风险线索：实际搜索结果中摘要6显示建筑年代2015），装修为高标准精装修（北区装修标准1.2万-1.5万/㎡），户型南北通透且楼间距大（约50米），物业为万科物业，24小时安保，隔音方面提及临街楼栋可能有噪音，非临街区域安静；；临街楼栋存在噪音问题。；临街楼栋存在噪音问题</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>1. 【北京五矿万科如园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010699497.htm
-2. 北京万科如园楼盘介绍,万科如园小区二手房、租房信息-丽兹行官网 https://bj.lizihang.com/loupan/597271.html
-3. 【10图】物业租售推荐：如园北区 户型5居价格可议诚意售带车位随时看，如园(北区)-北京58同城 https://m.58.com/bj/ershoufang/4507819946826752x.shtml
-4. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-5. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4187673629924362-3/
+2. http://m.anjuke.com/bj/rent/4513095210818564-3/
+3. http://m.anjuke.com/bj/community/802932/qa/
+4. https://bj.zu.anjuke.com/fangyuan/4227787418754053
+5. https://bj.58.com/zufang/84153757772509x.shtml
+6. 万科物业推荐好房 如园北新上精装四居中间位置可议价有钥匙诚租 http://m.anjuke.com/bj/rent/4187673629924362-3/
+7. 万科物业推荐好房 如园北区新上一层下跃园子6居室带车位可议价 http://m.anjuke.com/bj/rent/4513095210818564-3/
+8. 【如园(北区)业主论坛，如园(北区)房产问答评价，如园(北区)怎么样，好不好?】 - 上海安居客 http://m.anjuke.com/bj/community/802932/qa/</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1895,41 +1996,44 @@
         <x:v>北京市海淀区上地街道</x:v>
       </x:c>
       <x:c r="E35" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F35" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G35" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H35" t="n">
-        <x:v>6</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="I35" t="str">
-        <x:v>房龄较老的成熟社区，价格虽亲民但存在老旧小区通病，且网页证据存在时间逻辑偏差。</x:v>
+        <x:v>租金亲民且地铁通勤极便，生活配套成熟，但房龄老旧且无电梯，居住品质一般。</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>2026-02-09 | 301万 | 44090元/㎡；2025-12-25 | 206万 | 36332元/㎡；万 2室1厅1卫丨68㎡丨南北丨顶层丨 80500元/㎡；万 3室1厅1卫丨82㎡丨南北丨顶层丨 94700元/㎡；05000_ 元/m² 东馨园，小区价格65653元/㎡</x:v>
+        <x:v>整租一居约5100元/月；、两居约5500-6400元/月；，合租单间约1957-2500元/月</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **55654** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓1.96% 贷款计算器 * 二手房源 2套 * 最近成交 181套 * 楼栋总数 12栋 * 房屋总数 728户 * 建筑类型 板楼 * 建筑年代 1998年建成 * 小区位置 东北旺路与东北旺中路交叉口(东北旺路38号)地图 * 物业公司 北京东居物业管理有限公司 * 开发商 无开发商 #### 推荐经纪人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 王立新 评分：4.6 从业信息卡 百科 闪电回复 ##### 张波 评分：4.6 从业信息卡 百科 闪电回复 ##### 韩岗 评分：4.1 从业信息卡 百科 ### 东馨园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 68.27㎡ | 2026-02-09 | 301万 | 44090元/㎡ | 市场信息 | | 62.20㎡ | 2026-01-11 | -- | -- | 市场信息 | | 56.70㎡ | 2025-12-25 | 206万 | 36332元/㎡ | 市场信息 | 查看全部成交 ### 东馨园价格走势 ### 东馨园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 东馨园 海淀·马连洼**55655** 元/㎡ * #### 东旭园 海淀·马连洼**55817** 元/㎡ * #### 亿城西山公馆 海淀·上地**75374** 元/㎡ * #### 和樾玉鸣 海淀·马连洼**108704** 元/㎡ * #### 和樾望云 海淀·马连洼**111075** 元/㎡ ### 相关资讯 * 小区资讯北京东馨园怎么样?；北京吉屋网提供北京东馨园二手房出售信息、东馨园二手房价格，包括及时更新北京东馨园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 东馨园_北京东馨园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_东馨园 更新于 2026-06-01 10:55:13 [](https://bj.jiwu.com/tu/4232937.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722662.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722663.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722664.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722665.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722666.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722667.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722668.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722669.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722670.html "东馨园实景图图片") # 东馨园 别名：东馨园 加入本地买房群 关注 _北京 - 海淀 - 东北旺中路_ 发地址到手机 参考均价 _65653 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1260_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-73群（472） * 大家觉得这里未来发展怎么样？；加入群聊 二手房源全部房源 * [](https://bj.jiwu.com/esf/37254468.html "中关村软件园南东馨园 南北二居 满五商 临城铁13号线支线")中关村软件园南东馨园 南北二居 满五商 临城铁13号线支线 548万 2室1厅1卫丨68㎡丨南北丨顶层丨 80500元/㎡ 东馨园 | 海淀 - 马连洼 | 1998年建 * [](https://bj.jiwu.com/esf/37254469.html "东馨园-精装三居-满五年唯一公房-视野开阔采光好")东馨园-精装三居-满五年唯一公房-视野开阔采光好 780万 3室1厅1卫丨82㎡丨南北丨顶层丨 94700元/㎡ 东馨园 | 海淀 - 马连洼 | 1998年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(1)3室(1) 全部户型 [](https://bj.jiwu.com/huxing/686556.html "东馨园3室1厅1卫90㎡户型图")3室1厅1卫 90㎡咨询户型房源 [](https://bj.jiwu.com/huxing/686557.html "东馨园2室1厅1卫68㎡户型图")2室1厅1卫 68㎡咨询户型房源 小区评测报告 ？</x:v>
+        <x:v>整租一居约5100元/月、两居约5500-6400元/月，合租单间约1957-2500元/月，房源含精装修与简单装修，集中供暖；；房龄较老旧（约1992-1998年建成），为6层板楼无电梯；；部分房源隔音较好，户型为小面积南北向1-3居；；物业费0.8元/平·月，物业评价有好有坏（部分反映一般），小区外观老旧；；老旧小区无电梯，对高层住户不友好；</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>北京吉屋网提供北京东馨园二手房出售信息、东馨园二手房价格，包括及时更新北京东馨园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 东馨园_北京东馨园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_东馨园 更新于 2026-06-01 10:55:13 [](https://bj.jiwu.com/tu/4232937.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722662.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722663.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722664.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722665.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722666.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722667.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722668.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722669.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722670.html "东馨园实景图图片") # 东馨园 别名：东馨园 加入本地买房群 关注 _北京 - 海淀 - 东北旺中路_ 发地址到手机 参考均价 _65653 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1260_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-73群（472） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；东馨园的位置在东北旺中路，交通便利。；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等东馨园小区信息，关注吉屋北京东馨园！</x:v>
+        <x:v>临近地铁18号线上地软件园站（步行约569米），公交站东北旺中路站有362、509、575等路；；周边有鹏旺果蔬超市、中发百旺商城等商超，附近有八珍堂中医医院，餐饮及休闲配套尚可；</x:v>
       </x:c>
       <x:c r="M35" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>房龄较老旧（约1992-1998年建成），为6层板楼无电梯；；物业费0.8元/平·月，物业评价有好有坏（部分反映一般），小区外观老旧；；老旧小区无电梯，对高层住户不友好；</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>价格线索：2026-02-09 | 301万 | 44090元/㎡；2025-12-25 | 206万 | 36332元/㎡；万 2室1厅1卫丨68㎡丨南北丨顶层丨 80500元/㎡；万 3室1厅1卫丨82㎡丨南北丨顶层丨 94700元/㎡；05000_ 元/m² 东馨园，小区价格65653元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) [](https://esf.fang.com/loupan/1010215647/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **55654** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓1.96% 贷款计算器 * 二手房源 2套 * 最近成交 181套 * 楼栋总数 12栋 * 房屋总数 728户 * 建筑类型 板楼 * 建筑年代 1998年建成 * 小区位置 东北旺路与东北旺中路交叉口(东北旺路38号)地图 * 物业公司 北京东居物业管理有限公司 * 开发商 无开发商 #### 推荐经纪人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 王立新 评分：4.6 从业信息卡 百科 闪电回复 ##### 张波 评分：4.6 从业信息卡 百科 闪电回复 ##### 韩岗 评分：4.1 从业信息卡 百科 ### 东馨园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 68.27㎡ | 2026-02-09 | 301万 | 44090元/㎡ | 市场信息 | | 62.20㎡ | 2026-01-11 | -- | -- | 市场信息 | | 56.70㎡ | 2025-12-25 | 206万 | 36332元/㎡ | 市场信息 | 查看全部成交 ### 东馨园价格走势 ### 东馨园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 东馨园 海淀·马连洼**55655** 元/㎡ * #### 东旭园 海淀·马连洼**55817** 元/㎡ * #### 亿城西山公馆 海淀·上地**75374** 元/㎡ * #### 和樾玉鸣 海淀·马连洼**108704** 元/㎡ * #### 和樾望云 海淀·马连洼**111075** 元/㎡ ### 相关资讯 * 小区资讯北京东馨园怎么样?；北京吉屋网提供北京东馨园二手房出售信息、东馨园二手房价格，包括及时更新北京东馨园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 东馨园_北京东馨园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_东馨园 更新于 2026-06-01 10:55:13 [](https://bj.jiwu.com/tu/4232937.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722662.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722663.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722664.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722665.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722666.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722667.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722668.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722669.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722670.html "东馨园实景图图片") # 东馨园 别名：东馨园 加入本地买房群 关注 _北京 - 海淀 - 东北旺中路_ 发地址到手机 参考均价 _65653 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1260_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-73群（472） * 大家觉得这里未来发展怎么样？；加入群聊 二手房源全部房源 * [](https://bj.jiwu.com/esf/37254468.html "中关村软件园南东馨园 南北二居 满五商 临城铁13号线支线")中关村软件园南东馨园 南北二居 满五商 临城铁13号线支线 548万 2室1厅1卫丨68㎡丨南北丨顶层丨 80500元/㎡ 东馨园 | 海淀 - 马连洼 | 1998年建 * [](https://bj.jiwu.com/esf/37254469.html "东馨园-精装三居-满五年唯一公房-视野开阔采光好")东馨园-精装三居-满五年唯一公房-视野开阔采光好 780万 3室1厅1卫丨82㎡丨南北丨顶层丨 94700元/㎡ 东馨园 | 海淀 - 马连洼 | 1998年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(1)3室(1) 全部户型 [](https://bj.jiwu.com/huxing/686556.html "东馨园3室1厅1卫90㎡户型图")3室1厅1卫 90㎡咨询户型房源 [](https://bj.jiwu.com/huxing/686557.html "东馨园2室1厅1卫68㎡户型图")2室1厅1卫 68㎡咨询户型房源 小区评测报告 ？；生活便利线索：北京吉屋网提供北京东馨园二手房出售信息、东馨园二手房价格，包括及时更新北京东馨园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 东馨园_北京东馨园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_东馨园 更新于 2026-06-01 10:55:13 [](https://bj.jiwu.com/tu/4232937.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722662.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722663.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722664.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722665.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722666.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722667.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722668.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722669.html "东馨园实景图图片")[](https://bj.jiwu.com/tu/3722670.html "东馨园实景图图片") # 东馨园 别名：东馨园 加入本地买房群 关注 _北京 - 海淀 - 东北旺中路_ 发地址到手机 参考均价 _65653 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _1998_ 小区户数 _1260_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-73群（472） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；东馨园的位置在东北旺中路，交通便利。；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等东馨园小区信息，关注吉屋北京东馨园！；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：整租一居约5100元/月；、两居约5500-6400元/月；，合租单间约1957-2500元/月；房屋质量/户型线索：整租一居约5100元/月、两居约5500-6400元/月，合租单间约1957-2500元/月，房源含精装修与简单装修，集中供暖；；房龄较老旧（约1992-1998年建成），为6层板楼无电梯；；部分房源隔音较好，户型为小面积南北向1-3居；；物业费0.8元/平·月，物业评价有好有坏（部分反映一般），小区外观老旧；；老旧小区无电梯，对高层住户不友好；；生活便利线索：临近地铁18号线上地软件园站（步行约569米），公交站东北旺中路站有362、509、575等路；；周边有鹏旺果蔬超市、中发百旺商城等商超，附近有八珍堂中医医院，餐饮及休闲配套尚可；；风险线索：房龄较老旧（约1992-1998年建成），为6层板楼无电梯；；物业费0.8元/平·月，物业评价有好有坏（部分反映一般），小区外观老旧；；老旧小区无电梯，对高层住户不友好；</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>1. 【北京东馨园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010215647.htm
-2. 东馨园_北京东馨园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/170106.html
-3. 东馨园二手房,2室1厅 东馨园,房源位于东北旺中路-幸福里 https://fangchan.snssdk.com/ershoufang/bj-7473992157500080191.html
-4. URI盘点| 北京已入市的保租房项目 https://zhuanlan.zhihu.com/p/689251799
-5. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4367579693686790-3/
+2. http://m.anjuke.com/bj/rent/4598556743312385-3/
+3. http://m.anjuke.com/bj/community/55795/jiedu/
+4. 东馨园小区 南北两居 家具齐全 实图拍摄 业主人好稳定长租 http://m.anjuke.com/bj/rent/4367579693686790-3/
+5. 东馨园低楼层 两居室 http://m.anjuke.com/bj/rent/4598556743312385-3/
+6. 东馨园 真实 实图实价 杜绝虚假 无 可月付短签 http://m.anjuke.com/bj/rent/3076822915408899-3/
+7. 东馨园 东旭园 万德嘉园 软件园 百度 科技园 华联 急租 http://m.anjuke.com/bj/rent/4605026638736399-3/
+8. 东馨园优点、不足，东馨园怎么样，东馨园周边房产中介经纪人评价-北京安居客 http://m.anjuke.com/bj/community/55795/jiedu/</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1946,41 +2050,42 @@
         <x:v>北京市海淀区旺科东路东软北京研发中心</x:v>
       </x:c>
       <x:c r="E36" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F36" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G36" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H36" t="n">
-        <x:v>7.5</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="I36" t="str">
-        <x:v>租金数据较具体，一二居室价格适中，性价比表现尚可，是网易员工务实的租住选择。</x:v>
+        <x:v>缺乏该地点的直接有效信息，参考周边租金约4500元起，信息不足建议谨慎。</x:v>
       </x:c>
       <x:c r="J36" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
+        <x:v>岭、万泽嘉园等小区（如万泽嘉园南向大开间4500元/月；，唐家岭新城开间4500-4800元/月</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；58同城北京租房网，为您提供北京海淀租房信息，包括海淀房屋出租信息、海淀合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。</x:v>
+        <x:v>未找到目标「唐苑」的房子质量相关（隔音、户型、房龄、装修、物业）信息，仅周边类似普通住宅多为精装修，配套家电较全，但缺乏隔音、房龄等具体描述；</x:v>
       </x:c>
       <x:c r="L36" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；)_北京_ [](https://m.ke.com/chuzu/bj/)[](https://m.ke.com/my/index/) * 不限 * ≤2000元 * 2000-3000元 * 3000-4000元 * 4000-5000元 * 5000-6000元 * 6000-8000元 * 8000-20000元 * ≥20000元 _—_ 确定 * ### 全部品牌 693家门店 * ### 城家公寓 15家门店 确定 * 区域 * 地铁 * 附近 * 不限 * 东城区 * 西城区 * 朝阳区 * 海淀区 * 丰台区 * 石景山区 * 通州区 * 昌平区 * 大兴区 * 北京经济技术开发区 * 顺义区 * 房山区 * 门头沟区 * 平谷区 * 怀柔区 * 密云区 * 延庆区 * 不限 * 奥林匹克公园 * 安宁庄 * 白石桥 * 北太平庄 * 昌平其它 * 厂洼 * 定慧寺 * 二里庄 * 公主坟 * 甘家口 * 海淀其它 * 海淀北部新区 * 回龙观 * 霍营 * 军博 * 六里桥 * 牡丹园 * 马连洼 * 马甸 * 苹果园 * 清河 * 青塔 * 苏州桥 * 上地 * 世纪城 * 四季青 * 双榆树 * 天通苑 * 田村 * 五道口 * 五棵松 * 魏公村 * 万柳 * 万寿路 * 西山 * 西三旗 * 西北旺 * 学院路 * 小西天 * 西直门 * 新街口 * 西二旗 * 圆明园 * 月坛 * 杨庄 * 玉泉路 * 颐和园 * 知春路 * 皂君庙 * 中关村 * 紫竹桥 面积≤40㎡40-60㎡60-80㎡80-100㎡100-120㎡≥120㎡服务保障 [](https://m.ke.com/chuzu/bj/promise/desc/)品质认证在线签约租期月租年租一个月起租1-3个月4-6个月 清除 确定 * 全部品牌 * 海淀区 * 租金 * 筛选 _随时入住_ 云逸青年社区（北京）·颐阳山水居（小区） 北起G南至A西起26东至29 2600-3200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·千和公寓（海淀） 北京市海淀区白家疃路 2100-4200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·乐季（海淀） 北京市海淀区温泉镇显龙山文化产业园 2500-3000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·东马坊精装公寓 宜宿空间东马坊店19号院 1300-2000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·精装Loft 丶开间 整租无中介 白水洼路西辛力屯 1400-1500元/月 2个房型 | 2套在租 _随时入住_ 乐乎青年社区·上地店 上地八街7号院 4784-5198元/月 1个房型 | 2套在租 _随时入住_ 云逸青年社区（北京）·西三旗店 建材城西路 3500-3800元/月 2个房型 | 2套在租 _随时入住_ 千居嘉业公寓·中关村 彩和坊西小街1号 7200-7800元/月 5个房型 | 5套在租 _已满房_ 云逸青年社区（北京）·西山雅园店（白家瞳） 北京市海淀区白家疃路 暂无 6个房型 | 0套在租 _随时入住_ 欣悦青年社区·田村地铁站店 田村路40号院, 阜石路甲19号 2800-4500元/月 1个房型 | 5套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰1店 后屯中街8号院 暂无 5个房型 | 0套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰2店 后屯中街8号院 暂无 5个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·萌芽-青年公寓 颐春小区 2000-2981元/月 6个房型 | 6套在租 _随时入住_ 岚悦青年社区·翠湖科技园店 海淀区温泉镇北清路和温阳路西南角 3680元/月 2个房型 | 1套在租 _已满房_ 嘉悦赢公寓·国驰雅居 北三环中路43号院 暂无 4个房型 | 0套在租 _随时入住_ 乐乎青年社区·西二旗店 上地十街1号院 5100元/月 1个房型 | 1套在租 _已满房_ 创意初心社区·颐和山庄公寓 玉华园 暂无 1个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·新苑街店 新苑街10号院 4100元/月 1个房型 | 1套在租 _随时入住_ 云逸青年社区（北京）·香岩寺店（海淀） 北京市海淀区云水路1号 2800-3700元/月 10个房型 | 10套在租 _已满房_ 乐乎青年社区·乐乎上地店 上地八街7号院 暂无 1个房型 | 0套在租 加载中... 没有符合条件的房源 请换个条件试试 关注(0) * 北京租房网&gt; * 北京租房&gt; * 北京公寓品牌馆 热门商圈 推荐小区 租房城市 * 小西天租房 * 石佛营租房 * 武夷花园租房 * 工体租房 * 牡丹园租房 * 通州北苑租房 * 三里屯租房 * 天竺租房 * 新华大街租房 * 天坛租房 * 天宫院租房 * 右安门外租房 * 志强园租房 * 右外大厦租房 * 建邦华庭西区租房 * 铜光胡同租房 * 中兴巷租房 * 东四块玉南街4号院租房 * 高梁桥斜街11号院租房 * 三间房南里5号院租房 * 陶然居租房 * 南苑公寓房租房 * 张郭庄40号院租房 * 天坛东路租房 * 嘉兴租房 * 盐城租房 * 无锡租房 * 常州租房 * 广州租房 * 长春租房 * 南京租房 * 汉中租房 * 金华租房 * 青岛租房 * 西安租房 * 郑州租房 [](javascript:;</x:v>
-      </x:c>
-      <x:c r="M36" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。；小区是一个老旧小区，楼龄相对来说有一点老，里面线路比较乱，不过配套设施，完善，交通便利，生活方便。</x:v>
-      </x:c>
+        <x:v>未找到北京市海淀区旺科东路东软北京研发中心附近名为「唐苑」的准确租房月租信息，相关房源多为周边唐家岭、万泽嘉园等小区（如万泽嘉园南向大开间4500元/月，唐家岭新城开间4500-4800元/月）；；未找到目标「唐苑」的房子质量相关（隔音、户型、房龄、装修、物业）信息，仅周边类似普通住宅多为精装修，配套家电较全，但缺乏隔音、房龄等具体描述；；未找到目标「唐苑」的生活便利程度信息，周边唐家岭、万泽嘉园等小区临近东软大厦，靠近中关村软件园，周边有商超、农贸市场等，通勤可依赖公交，地铁相关信息未明确提及；</x:v>
+      </x:c>
+      <x:c r="M36" t="str"/>
       <x:c r="N36" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；58同城北京租房网，为您提供北京海淀租房信息，包括海淀房屋出租信息、海淀合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。；生活便利线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；)_北京_ [](https://m.ke.com/chuzu/bj/)[](https://m.ke.com/my/index/) * 不限 * ≤2000元 * 2000-3000元 * 3000-4000元 * 4000-5000元 * 5000-6000元 * 6000-8000元 * 8000-20000元 * ≥20000元 _—_ 确定 * ### 全部品牌 693家门店 * ### 城家公寓 15家门店 确定 * 区域 * 地铁 * 附近 * 不限 * 东城区 * 西城区 * 朝阳区 * 海淀区 * 丰台区 * 石景山区 * 通州区 * 昌平区 * 大兴区 * 北京经济技术开发区 * 顺义区 * 房山区 * 门头沟区 * 平谷区 * 怀柔区 * 密云区 * 延庆区 * 不限 * 奥林匹克公园 * 安宁庄 * 白石桥 * 北太平庄 * 昌平其它 * 厂洼 * 定慧寺 * 二里庄 * 公主坟 * 甘家口 * 海淀其它 * 海淀北部新区 * 回龙观 * 霍营 * 军博 * 六里桥 * 牡丹园 * 马连洼 * 马甸 * 苹果园 * 清河 * 青塔 * 苏州桥 * 上地 * 世纪城 * 四季青 * 双榆树 * 天通苑 * 田村 * 五道口 * 五棵松 * 魏公村 * 万柳 * 万寿路 * 西山 * 西三旗 * 西北旺 * 学院路 * 小西天 * 西直门 * 新街口 * 西二旗 * 圆明园 * 月坛 * 杨庄 * 玉泉路 * 颐和园 * 知春路 * 皂君庙 * 中关村 * 紫竹桥 面积≤40㎡40-60㎡60-80㎡80-100㎡100-120㎡≥120㎡服务保障 [](https://m.ke.com/chuzu/bj/promise/desc/)品质认证在线签约租期月租年租一个月起租1-3个月4-6个月 清除 确定 * 全部品牌 * 海淀区 * 租金 * 筛选 _随时入住_ 云逸青年社区（北京）·颐阳山水居（小区） 北起G南至A西起26东至29 2600-3200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·千和公寓（海淀） 北京市海淀区白家疃路 2100-4200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·乐季（海淀） 北京市海淀区温泉镇显龙山文化产业园 2500-3000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·东马坊精装公寓 宜宿空间东马坊店19号院 1300-2000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·精装Loft 丶开间 整租无中介 白水洼路西辛力屯 1400-1500元/月 2个房型 | 2套在租 _随时入住_ 乐乎青年社区·上地店 上地八街7号院 4784-5198元/月 1个房型 | 2套在租 _随时入住_ 云逸青年社区（北京）·西三旗店 建材城西路 3500-3800元/月 2个房型 | 2套在租 _随时入住_ 千居嘉业公寓·中关村 彩和坊西小街1号 7200-7800元/月 5个房型 | 5套在租 _已满房_ 云逸青年社区（北京）·西山雅园店（白家瞳） 北京市海淀区白家疃路 暂无 6个房型 | 0套在租 _随时入住_ 欣悦青年社区·田村地铁站店 田村路40号院, 阜石路甲19号 2800-4500元/月 1个房型 | 5套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰1店 后屯中街8号院 暂无 5个房型 | 0套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰2店 后屯中街8号院 暂无 5个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·萌芽-青年公寓 颐春小区 2000-2981元/月 6个房型 | 6套在租 _随时入住_ 岚悦青年社区·翠湖科技园店 海淀区温泉镇北清路和温阳路西南角 3680元/月 2个房型 | 1套在租 _已满房_ 嘉悦赢公寓·国驰雅居 北三环中路43号院 暂无 4个房型 | 0套在租 _随时入住_ 乐乎青年社区·西二旗店 上地十街1号院 5100元/月 1个房型 | 1套在租 _已满房_ 创意初心社区·颐和山庄公寓 玉华园 暂无 1个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·新苑街店 新苑街10号院 4100元/月 1个房型 | 1套在租 _随时入住_ 云逸青年社区（北京）·香岩寺店（海淀） 北京市海淀区云水路1号 2800-3700元/月 10个房型 | 10套在租 _已满房_ 乐乎青年社区·乐乎上地店 上地八街7号院 暂无 1个房型 | 0套在租 加载中... 没有符合条件的房源 请换个条件试试 关注(0) * 北京租房网&gt; * 北京租房&gt; * 北京公寓品牌馆 热门商圈 推荐小区 租房城市 * 小西天租房 * 石佛营租房 * 武夷花园租房 * 工体租房 * 牡丹园租房 * 通州北苑租房 * 三里屯租房 * 天竺租房 * 新华大街租房 * 天坛租房 * 天宫院租房 * 右安门外租房 * 志强园租房 * 右外大厦租房 * 建邦华庭西区租房 * 铜光胡同租房 * 中兴巷租房 * 东四块玉南街4号院租房 * 高梁桥斜街11号院租房 * 三间房南里5号院租房 * 陶然居租房 * 南苑公寓房租房 * 张郭庄40号院租房 * 天坛东路租房 * 嘉兴租房 * 盐城租房 * 无锡租房 * 常州租房 * 广州租房 * 长春租房 * 南京租房 * 汉中租房 * 金华租房 * 青岛租房 * 西安租房 * 郑州租房 [](javascript:;；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。；小区是一个老旧小区，楼龄相对来说有一点老，里面线路比较乱，不过配套设施，完善，交通便利，生活方便。</x:v>
+        <x:v>价格线索：岭、万泽嘉园等小区（如万泽嘉园南向大开间4500元/月；，唐家岭新城开间4500-4800元/月；房屋质量/户型线索：未找到目标「唐苑」的房子质量相关（隔音、户型、房龄、装修、物业）信息，仅周边类似普通住宅多为精装修，配套家电较全，但缺乏隔音、房龄等具体描述；；生活便利线索：未找到北京市海淀区旺科东路东软北京研发中心附近名为「唐苑」的准确租房月租信息，相关房源多为周边唐家岭、万泽嘉园等小区（如万泽嘉园南向大开间4500元/月，唐家岭新城开间4500-4800元/月）；；未找到目标「唐苑」的房子质量相关（隔音、户型、房龄、装修、物业）信息，仅周边类似普通住宅多为精装修，配套家电较全，但缺乏隔音、房龄等具体描述；；未找到目标「唐苑」的生活便利程度信息，周边唐家岭、万泽嘉园等小区临近东软大厦，靠近中关村软件园，周边有商超、农贸市场等，通勤可依赖公交，地铁相关信息未明确提及；</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>1. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-2. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-3. 北京精装公寓出租信息 https://ifeng-m.lianjia.com/chuzu/bj/apartment/haidianqu/rmp1amp1amp2amp4amp8/
-4. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-5. 【北京精装公寓出租5000-80004元/月租房信息_房屋出租】- 房天下 https://www.fang.com/houses/zf_251913bj/c25000-d280004,2-i334/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4402798830574594-3/
+2. http://m.anjuke.com/hz/rent/4566774275714055-3/
+3. https://bj.zu.anjuke.com/fangyuan/4075757745724426
+4. https://sh.zu.anjuke.com/fangyuan/4026514192292870
+5. 实图实价！西北旺 唐家岭航天城万和嘉园 万泽嘉园南向大开间！ http://m.anjuke.com/bj/rent/4402798830574594-3/
+6. 看房不慌张还得找小张，丁桥唐苑大面积两室，高！ http://m.anjuke.com/hz/rent/4566774275714055-3/
+7. 【多图】唐家岭新城(东区)，西北旺租房，唐家岭新城东区南向开间首月减免临近滴滴新橙海中关村软件园百度，海淀租房 https://bj.zu.anjuke.com/fangyuan/4075757745724426
+8. 东唐苑朝南带阳台 超大空间 付一押一 近地铁站 https://sh.zu.anjuke.com/fangyuan/4026514192292870</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1997,37 +2102,42 @@
         <x:v>北京市海淀区西北旺北路与永丰路交汇处东南角</x:v>
       </x:c>
       <x:c r="E37" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F37" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G37" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H37" t="n">
-        <x:v>7.2</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I37" t="str">
-        <x:v>中海品牌开发的优质小区，环境与配套较好，因缺乏直接租金证据，评分保持谨慎。</x:v>
+        <x:v>紧邻地铁与商圈，物业维护好且隔音佳，合租性价比高，是软件园通勤的优质选择。</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>万 2室2厅1卫丨89㎡丨南北丨顶层丨 113000元/㎡； 3室1厅2卫丨122㎡丨南北丨底层丨 104200元/㎡；00_ 元/m² 中海枫涟山庄，小区价格82646元/㎡</x:v>
+        <x:v>月租约9000-13000元，合租主卧约3499元/月；，合租次卧约2200元/月</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>北京吉屋网提供北京中海枫涟山庄二手房出售信息、中海枫涟山庄二手房价格，包括及时更新北京中海枫涟山庄二手房房源、价格走势、户型图、业主论坛、生活配套。；# 中海枫涟山庄_北京中海枫涟山庄小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_中海枫涟山庄 更新于 2026-06-01 10:51:58 [](https://bj.jiwu.com/tu/4226625.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/4226626.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/4226627.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629773.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629774.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629775.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629776.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629777.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629778.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629779.html "中海枫涟山庄实景图图片") # 中海枫涟山庄 别名：中海枫涟山庄 加入本地买房群 关注 _北京 - 海淀 - 永丰路_ 发地址到手机 参考均价 _82646 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2005_ 小区户数 _1464户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-87群（461） * 大家觉得这里未来发展怎么样？；满五年一套 1010万 2室2厅1卫丨89㎡丨南北丨顶层丨 113000元/㎡ 中海枫涟山庄 | 海淀 - 西北旺 | 2005年建 * [](https://bj.jiwu.com/esf/37360178.html "中海枫涟山庄南北通透三居，满五 ，小区中间位置")中海枫涟山庄南北通透三居，满五 ，小区中间位置 1275万 3室1厅2卫丨122㎡丨南北丨底层丨 104200元/㎡ 中海枫涟山庄 | 海淀 - 西北旺 | 2005年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(2)3室(2) 全部户型 [](https://bj.jiwu.com/huxing/675830.html "中海枫涟山庄2室2厅2卫123㎡户型图")2室2厅2卫 123㎡咨询户型房源 [](https://bj.jiwu.com/huxing/675831.html "中海枫涟山庄2室2厅1卫101㎡户型图")2室2厅1卫 101㎡咨询户型房源 [](https://bj.jiwu.com/huxing/675832.html "中海枫涟山庄3室2厅1卫124㎡户型图")3室2厅1卫 124㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；答 了解中海枫涟山庄的具体在售房源，请拨打4007508888 转 99001免费咨询，是否在售有什么户型多少钱都可以咨询。</x:v>
+        <x:v>房龄2004/2005年，物业为中海物业，房屋隔音效果较好；；户型多为南北通透板楼，以2室2厅、3室2厅为主，部分带电梯，装修有简单装修和精装修；；建筑质量由中海地产打造，后期物业维护较好。</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>北京吉屋网提供北京中海枫涟山庄二手房出售信息、中海枫涟山庄二手房价格，包括及时更新北京中海枫涟山庄二手房房源、价格走势、户型图、业主论坛、生活配套。；# 中海枫涟山庄_北京中海枫涟山庄小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_中海枫涟山庄 更新于 2026-06-01 10:51:58 [](https://bj.jiwu.com/tu/4226625.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/4226626.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/4226627.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629773.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629774.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629775.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629776.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629777.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629778.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629779.html "中海枫涟山庄实景图图片") # 中海枫涟山庄 别名：中海枫涟山庄 加入本地买房群 关注 _北京 - 海淀 - 永丰路_ 发地址到手机 参考均价 _82646 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2005_ 小区户数 _1464户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-87群（461） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等中海枫涟山庄小区信息，关注吉屋北京中海枫涟山庄！；* 买房交流 * 找房小程序 * 返回顶部 * 关于吉屋 * 公司新闻 * 联系我们 * 加入我们 * 服务声明 * 服务热线：0755-26404403 * 网站地图 周边买房 * 北京买房 北京新房 * 房山新房 * 顺义新房 * 昌平新房 * 大兴新房 * 北京周边新房 * 平谷新房 * 海淀新房 * 丰台新房 * 门头沟新房 * 朝阳新房 * 延庆新房 * 密云新房 * 石景山新房 * 通州新房 * 怀柔新房 * 西城新房 * 东城新房 * 怀来新房 * 其他新房 * 崇礼新房 * 海滨新房 * 亦庄经开区新房 周边房价 * 房山房价 * 顺义房价 * 昌平房价 * 大兴房价 * 北京周边房价 * 平谷房价 * 海淀房价 * 丰台房价 * 门头沟房价 * 朝阳房价 * 延庆房价 * 密云房价 * 石景山房价 * 通州房价 * 怀柔房价 * 西城房价 * 东城房价 * 怀来房价 * 其他房价 * 崇礼房价 * 海滨房价 * 亦庄经开区房价 深圳市吉屋网络技术有限公司 粤ICP备11045667号粤公网安备 44030502001914号增值电信业务经营许可证房地产经纪机构备案工商网监中国电子认证服务产业联盟 免责声明：楼盘信息来源开发商、第三方平台，本站旨在为用户提供更多信息服务，最终以政府部门登记备案为准，请蓮慎核查。</x:v>
+        <x:v>通勤方面，距地铁16号线西北旺站约494米，步行可达；；周边有公交站点，近西北旺万象汇，有广告超市、盒马鲜生等商超，临近五一渠生态滨河公园，休闲便利；；周边餐饮资源较丰富，距中关村软件园约1.3公里，通勤便捷。；小区停车位相对紧张，无车位的车辆需停在小区周边；</x:v>
       </x:c>
       <x:c r="M37" t="str"/>
       <x:c r="N37" t="str">
-        <x:v>价格线索：万 2室2厅1卫丨89㎡丨南北丨顶层丨 113000元/㎡； 3室1厅2卫丨122㎡丨南北丨底层丨 104200元/㎡；00_ 元/m² 中海枫涟山庄，小区价格82646元/㎡；房屋质量/户型线索：北京吉屋网提供北京中海枫涟山庄二手房出售信息、中海枫涟山庄二手房价格，包括及时更新北京中海枫涟山庄二手房房源、价格走势、户型图、业主论坛、生活配套。；# 中海枫涟山庄_北京中海枫涟山庄小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_中海枫涟山庄 更新于 2026-06-01 10:51:58 [](https://bj.jiwu.com/tu/4226625.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/4226626.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/4226627.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629773.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629774.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629775.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629776.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629777.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629778.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629779.html "中海枫涟山庄实景图图片") # 中海枫涟山庄 别名：中海枫涟山庄 加入本地买房群 关注 _北京 - 海淀 - 永丰路_ 发地址到手机 参考均价 _82646 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2005_ 小区户数 _1464户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-87群（461） * 大家觉得这里未来发展怎么样？；满五年一套 1010万 2室2厅1卫丨89㎡丨南北丨顶层丨 113000元/㎡ 中海枫涟山庄 | 海淀 - 西北旺 | 2005年建 * [](https://bj.jiwu.com/esf/37360178.html "中海枫涟山庄南北通透三居，满五 ，小区中间位置")中海枫涟山庄南北通透三居，满五 ，小区中间位置 1275万 3室1厅2卫丨122㎡丨南北丨底层丨 104200元/㎡ 中海枫涟山庄 | 海淀 - 西北旺 | 2005年建 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(2)3室(2) 全部户型 [](https://bj.jiwu.com/huxing/675830.html "中海枫涟山庄2室2厅2卫123㎡户型图")2室2厅2卫 123㎡咨询户型房源 [](https://bj.jiwu.com/huxing/675831.html "中海枫涟山庄2室2厅1卫101㎡户型图")2室2厅1卫 101㎡咨询户型房源 [](https://bj.jiwu.com/huxing/675832.html "中海枫涟山庄3室2厅1卫124㎡户型图")3室2厅1卫 124㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；答 了解中海枫涟山庄的具体在售房源，请拨打4007508888 转 99001免费咨询，是否在售有什么户型多少钱都可以咨询。；生活便利线索：北京吉屋网提供北京中海枫涟山庄二手房出售信息、中海枫涟山庄二手房价格，包括及时更新北京中海枫涟山庄二手房房源、价格走势、户型图、业主论坛、生活配套。；# 中海枫涟山庄_北京中海枫涟山庄小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_中海枫涟山庄 更新于 2026-06-01 10:51:58 [](https://bj.jiwu.com/tu/4226625.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/4226626.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/4226627.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629773.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629774.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629775.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629776.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629777.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629778.html "中海枫涟山庄实景图图片")[](https://bj.jiwu.com/tu/3629779.html "中海枫涟山庄实景图图片") # 中海枫涟山庄 别名：中海枫涟山庄 加入本地买房群 关注 _北京 - 海淀 - 永丰路_ 发地址到手机 参考均价 _82646 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2005_ 小区户数 _1464户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-87群（461） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等中海枫涟山庄小区信息，关注吉屋北京中海枫涟山庄！；* 买房交流 * 找房小程序 * 返回顶部 * 关于吉屋 * 公司新闻 * 联系我们 * 加入我们 * 服务声明 * 服务热线：0755-26404403 * 网站地图 周边买房 * 北京买房 北京新房 * 房山新房 * 顺义新房 * 昌平新房 * 大兴新房 * 北京周边新房 * 平谷新房 * 海淀新房 * 丰台新房 * 门头沟新房 * 朝阳新房 * 延庆新房 * 密云新房 * 石景山新房 * 通州新房 * 怀柔新房 * 西城新房 * 东城新房 * 怀来新房 * 其他新房 * 崇礼新房 * 海滨新房 * 亦庄经开区新房 周边房价 * 房山房价 * 顺义房价 * 昌平房价 * 大兴房价 * 北京周边房价 * 平谷房价 * 海淀房价 * 丰台房价 * 门头沟房价 * 朝阳房价 * 延庆房价 * 密云房价 * 石景山房价 * 通州房价 * 怀柔房价 * 西城房价 * 东城房价 * 怀来房价 * 其他房价 * 崇礼房价 * 海滨房价 * 亦庄经开区房价 深圳市吉屋网络技术有限公司 粤ICP备11045667号粤公网安备 44030502001914号增值电信业务经营许可证房地产经纪机构备案工商网监中国电子认证服务产业联盟 免责声明：楼盘信息来源开发商、第三方平台，本站旨在为用户提供更多信息服务，最终以政府部门登记备案为准，请蓮慎核查。</x:v>
+        <x:v>价格线索：月租约9000-13000元，合租主卧约3499元/月；，合租次卧约2200元/月；房屋质量/户型线索：房龄2004/2005年，物业为中海物业，房屋隔音效果较好；；户型多为南北通透板楼，以2室2厅、3室2厅为主，部分带电梯，装修有简单装修和精装修；；建筑质量由中海地产打造，后期物业维护较好。；生活便利线索：通勤方面，距地铁16号线西北旺站约494米，步行可达；；周边有公交站点，近西北旺万象汇，有广告超市、盒马鲜生等商超，临近五一渠生态滨河公园，休闲便利；；周边餐饮资源较丰富，距中关村软件园约1.3公里，通勤便捷。；小区停车位相对紧张，无车位的车辆需停在小区周边；</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>1. 中海枫涟山庄_北京中海枫涟山庄小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/166607.html
-2. 中海枫涟山庄最新房价_北京海淀区-中国房价行情 https://m.creprice.cn/community/pa00024174hd982.html?city=bj
-3. 北京【中海枫涟山庄】物业租售中心_租房信息-城市房网 https://bj.cityhouse.com.cn/ltrade/hapa00024174hd982-pr12-br5-ch1/</x:v>
+        <x:v>1. https://m.fang.com/zf/bj_xm1010053613/p7/
+2. http://m.anjuke.com/bj/rent/4595581030540303-3/
+3. https://beijing.anjuke.com/community/view/65097/jiedu/p2/
+4. http://m.anjuke.com/bj/rent/4531488565386242-3/
+5. https://m.lianjia.com/news/bj/xiaoqu/1111027382464.html
+6. 【中海枫涟山庄租房子 https://m.fang.com/zf/bj_xm1010053613/p7/
+7. 西北旺中海枫涟山庄三居室 有车位 http://m.anjuke.com/bj/rent/4595581030540303-3/
+8. 中海枫涟山庄优点、不足，中海枫涟山庄怎么样，中海枫涟山庄周边房产中介经纪人评价 https://beijing.anjuke.com/community/view/65097/jiedu/p2/</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2044,41 +2154,42 @@
         <x:v>北京市海淀区马连洼北路与龙背村路交叉口西南角</x:v>
       </x:c>
       <x:c r="E38" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F38" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G38" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H38" t="n">
         <x:v>7.8</x:v>
       </x:c>
       <x:c r="I38" t="str">
-        <x:v>地段交通优势明显，户型以大面积为主，适合多人合租，但整体租金门槛较高。</x:v>
+        <x:v>2003年建，配套成熟且近地铁，但租金较高且停车管理较乱。</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v> 5室3厅3卫丨224㎡丨南北丨底层丨 93200元/㎡；2室1厅1卫丨106㎡丨南北丨高楼层丨 97899元/㎡；4室2厅3卫丨197㎡丨南北丨中楼层丨 106400元/㎡；5000_ 元/m² 百旺家苑，小区价格72888元/㎡</x:v>
+        <x:v>1室1厅6300元/月；，2室1厅9300元/月；，3室2厅12500元/月；，4室2厅13500元/月</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 * 户型 * 价格 * #### 满五年唯一,带电梯两居室,签约随时 2室1厅 94.02㎡**799**万 * #### 百旺家苑2室2厅南北 2室2厅 115.14㎡**770**万 * #### 百旺家苑2室2厅南北 2室2厅 99.19㎡**690**万 * #### 此房南北通透,通风好,南向大阳台,一层 3室2厅 139.55㎡**1085**万 ### 百旺家苑房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 百旺家苑别墅 海淀·马连洼**152913** 元/㎡ * #### 百旺家苑 海淀·马连洼**76152** 元/㎡ * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 马连洼梅园 海淀·马连洼**65210** 元/㎡ ### 相关资讯 * 小区资讯北京百旺家苑别墅怎么样?；百旺家苑别墅房价地址户型小区详情解析2021-10-31 * 小区资讯北京百旺家苑怎么样?；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺家苑 更新于 2026-06-01 10:46:54 [](https://bj.jiwu.com/tu/4301782.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301783.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301784.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301785.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301786.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301787.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301788.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301789.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301790.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301791.html "百旺家苑实景图图片") # 百旺家苑 别名：百旺家苑 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路_ 发地址到手机 参考均价 _72888 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2003_ 小区户数 _1303户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-63群（313） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？</x:v>
+        <x:v>2003年建成，物业评价一般；；楼栋外壁有保温层、隔音板，顶层有防水层，隔音和防水中等；；户型以南北通透板楼为主，面积60-292㎡不等；；装修有精装、豪华精装；；地上停车位不足，车辆乱停放，物业对停车管理较乱；</x:v>
       </x:c>
       <x:c r="L38" t="str">
-        <x:v>百旺家苑价格地段交通优势解析2021-06-25 * 小区资讯最详细!；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺家苑 更新于 2026-06-01 10:46:54 [](https://bj.jiwu.com/tu/4301782.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301783.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301784.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301785.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301786.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301787.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301788.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301789.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301790.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301791.html "百旺家苑实景图图片") # 百旺家苑 别名：百旺家苑 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路_ 发地址到手机 参考均价 _72888 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2003_ 小区户数 _1303户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-63群（313） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等百旺家苑小区信息，关注吉屋北京百旺家苑！</x:v>
-      </x:c>
-      <x:c r="M38" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>交通：步行1056米到16号线马连洼站，还有多路公交；；生活配套：周边有百旺商城、华联超市、超市发，800米内有309医院（解放军总医院第八医学中心），餐饮、商超等日常配套齐全；</x:v>
+      </x:c>
+      <x:c r="M38" t="str"/>
       <x:c r="N38" t="str">
-        <x:v>价格线索： 5室3厅3卫丨224㎡丨南北丨底层丨 93200元/㎡；2室1厅1卫丨106㎡丨南北丨高楼层丨 97899元/㎡；4室2厅3卫丨197㎡丨南北丨中楼层丨 106400元/㎡；5000_ 元/m² 百旺家苑，小区价格72888元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 * 户型 * 价格 * #### 满五年唯一,带电梯两居室,签约随时 2室1厅 94.02㎡**799**万 * #### 百旺家苑2室2厅南北 2室2厅 115.14㎡**770**万 * #### 百旺家苑2室2厅南北 2室2厅 99.19㎡**690**万 * #### 此房南北通透,通风好,南向大阳台,一层 3室2厅 139.55㎡**1085**万 ### 百旺家苑房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 百旺家苑别墅 海淀·马连洼**152913** 元/㎡ * #### 百旺家苑 海淀·马连洼**76152** 元/㎡ * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 马连洼梅园 海淀·马连洼**65210** 元/㎡ ### 相关资讯 * 小区资讯北京百旺家苑别墅怎么样?；百旺家苑别墅房价地址户型小区详情解析2021-10-31 * 小区资讯北京百旺家苑怎么样?；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺家苑 更新于 2026-06-01 10:46:54 [](https://bj.jiwu.com/tu/4301782.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301783.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301784.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301785.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301786.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301787.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301788.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301789.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301790.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301791.html "百旺家苑实景图图片") # 百旺家苑 别名：百旺家苑 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路_ 发地址到手机 参考均价 _72888 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2003_ 小区户数 _1303户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-63群（313） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；生活便利线索：百旺家苑价格地段交通优势解析2021-06-25 * 小区资讯最详细!；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺家苑 更新于 2026-06-01 10:46:54 [](https://bj.jiwu.com/tu/4301782.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301783.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301784.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301785.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301786.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301787.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301788.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301789.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301790.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301791.html "百旺家苑实景图图片") # 百旺家苑 别名：百旺家苑 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路_ 发地址到手机 参考均价 _72888 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2003_ 小区户数 _1303户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-63群（313） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等百旺家苑小区信息，关注吉屋北京百旺家苑！；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：1室1厅6300元/月；，2室1厅9300元/月；，3室2厅12500元/月；，4室2厅13500元/月；房屋质量/户型线索：2003年建成，物业评价一般；；楼栋外壁有保温层、隔音板，顶层有防水层，隔音和防水中等；；户型以南北通透板楼为主，面积60-292㎡不等；；装修有精装、豪华精装；；地上停车位不足，车辆乱停放，物业对停车管理较乱；；生活便利线索：交通：步行1056米到16号线马连洼站，还有多路公交；；生活配套：周边有百旺商城、华联超市、超市发，800米内有309医院（解放军总医院第八医学中心），餐饮、商超等日常配套齐全；</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>1. 【北京百旺家苑小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010026855.htm
-2. 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/145707.html
-3. 西北旺房屋出租信息_北京海淀西北旺出租房源信息-58出租网 https://bj.zf.58.com/cz/xibeiwang/
-4. 百旺家苑最新房价_北京海淀区-中国房价行情 https://m.creprice.cn/community/pa00022194hd608.html?city=bj
-5. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4591402496336907-3/
+2. http://m.anjuke.com/bj/rent/4597174596512770-3/
+3. http://m.anjuke.com/bj/rent/4568715370982412-3/
+4. https://beijing.anjuke.com/community/view/78963/jiedu/p1/
+5. https://m.xflapp.com/block-strategy/6587274139701084430/6994750068008058910
+6. 309医院旁 马连洼地铁站 百旺家苑 实图直出 签 http://m.anjuke.com/bj/rent/4591402496336907-3/
+7. 价可聊 百旺家苑 南北三居 跟业主签约 随时看房 能长租 http://m.anjuke.com/bj/rent/4597174596512770-3/
+8. 百旺家苑优点、不足，百旺家苑怎么样，百旺家苑周边房产中介经纪人评价-北京安居客 https://beijing.anjuke.com/community/view/78963/jiedu/p1/</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2095,39 +2206,40 @@
         <x:v>北京市海淀区农大北路</x:v>
       </x:c>
       <x:c r="E39" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F39" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G39" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H39" t="n">
-        <x:v>7.2</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="I39" t="str">
-        <x:v>租金价格相对适中，一居及二居房源可选，但缺乏具体的房屋质量细节证据。</x:v>
+        <x:v>2000年建，户型方正隔音好，租金相对亲民，但离大型商超稍远。</x:v>
       </x:c>
       <x:c r="J39" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
+        <x:v>无明确单独租房月租信息，但小区二手房均价66506元/㎡；周边同区域租房，推测两居月租约6000-8000元/月</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；58同城北京租房网，为您提供北京海淀租房信息，包括海淀房屋出租信息、海淀合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。</x:v>
+        <x:v>暂无明确单独租房月租信息，但小区二手房均价66506元/㎡，参考周边同区域租房，推测两居月租约6000-8000元/月（结合户型面积及区域租金水平）；；小区2000年建成，2002年交房，房屋结构为砖混/钢混板楼，户型方正，南北通透；；隔音较好，邻里互不打扰；；装修以毛坯为主；；物业一般，2019年左右评价物业不好，后续逐步改善；</x:v>
       </x:c>
       <x:c r="L39" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。</x:v>
-      </x:c>
-      <x:c r="M39" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>暂无明确单独租房月租信息，但小区二手房均价66506元/㎡，参考周边同区域租房，推测两居月租约6000-8000元/月（结合户型面积及区域租金水平）；；生活配套：小区内有超市、蔬果店、餐饮，西行1.5KM是百旺商城，向东1KM是上地华联；；轨道交通：到地铁16号线马连洼站约1-1.3公里，西门200米处有公交站（518、328等线路）；；医疗/教育：周边有社区医院、东北旺中心小学等；；3. 部分评价显示物业曾存在不足，购物便利性不足（部分业主反馈）。</x:v>
+      </x:c>
+      <x:c r="M39" t="str"/>
       <x:c r="N39" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；58同城北京租房网，为您提供北京海淀租房信息，包括海淀房屋出租信息、海淀合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。；生活便利线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：无明确单独租房月租信息，但小区二手房均价66506元/㎡；周边同区域租房，推测两居月租约6000-8000元/月；房屋质量/户型线索：暂无明确单独租房月租信息，但小区二手房均价66506元/㎡，参考周边同区域租房，推测两居月租约6000-8000元/月（结合户型面积及区域租金水平）；；小区2000年建成，2002年交房，房屋结构为砖混/钢混板楼，户型方正，南北通透；；隔音较好，邻里互不打扰；；装修以毛坯为主；；物业一般，2019年左右评价物业不好，后续逐步改善；；生活便利线索：暂无明确单独租房月租信息，但小区二手房均价66506元/㎡，参考周边同区域租房，推测两居月租约6000-8000元/月（结合户型面积及区域租金水平）；；生活配套：小区内有超市、蔬果店、餐饮，西行1.5KM是百旺商城，向东1KM是上地华联；；轨道交通：到地铁16号线马连洼站约1-1.3公里，西门200米处有公交站（518、328等线路）；；医疗/教育：周边有社区医院、东北旺中心小学等；；3. 部分评价显示物业曾存在不足，购物便利性不足（部分业主反馈）。</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>1. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-2. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-3. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml</x:v>
+        <x:v>1. https://m.xflapp.com/owner-comment/6587277287207469326/7055466274146484237
+2. http://m.anjuke.com/bj/community/79446/jiedu/
+3. https://m.xflapp.com/celebrity-comment/2/6587277287207469326/7020468948185448996
+4. 菊花盛苑点评,海淀 马连洼 农大北路,北京马连洼菊花盛苑评价、业主点评、测评信息 https://m.xflapp.com/owner-comment/6587277287207469326/7055466274146484237
+5. 菊花盛苑优点、不足，菊花盛苑怎么样，菊花盛苑周边房产中介经纪人评价-北京安居客 http://m.anjuke.com/bj/community/79446/jiedu/
+6. 菊花盛苑专家点评、大咖评价,北京菊花盛苑点评、测评、评价信息-北京幸福里 https://m.xflapp.com/celebrity-comment/2/6587277287207469326/7020468948185448996</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2144,41 +2256,44 @@
         <x:v>北京市海淀区马连洼街道</x:v>
       </x:c>
       <x:c r="E40" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F40" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G40" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H40" t="n">
-        <x:v>6.5</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="I40" t="str">
-        <x:v>租金跨度较大，证据中混杂较多周边公寓信息，需警惕通勤距离与房源真实性。</x:v>
+        <x:v>绿化好且物业评价正向，但缺乏具体租金数据且大户型为主，证据较弱。</x:v>
       </x:c>
       <x:c r="J40" t="str">
-        <x:v> 3室2厅176㎡. 20000元/月；北起G南至A西起26东至29 2600-3200元/月；海淀） 北京市海淀区白家疃路 2100-4200元/月；海淀区温泉镇显龙山文化产业园 2500-3000元/月；寓 宜宿空间东马坊店19号院 1300-2000元/月；整租无中介 白水洼路西辛力屯 1400-1500元/月；社区·上地店 上地八街7号院 4784-5198元/月；北京）·西三旗店 建材城西路 3500-3800元/月</x:v>
+        <x:v>型面积89-140㎡，周边区域新房价格约12000元/㎡</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>)_北京_ [](https://m.ke.com/chuzu/bj/)[](https://m.ke.com/my/index/) * 不限 * ≤2000元 * 2000-3000元 * 3000-4000元 * 4000-5000元 * 5000-6000元 * 6000-8000元 * 8000-20000元 * ≥20000元 _—_ 确定 * ### 全部品牌 693家门店 * ### 城家公寓 15家门店 确定 * 区域 * 地铁 * 附近 * 不限 * 东城区 * 西城区 * 朝阳区 * 海淀区 * 丰台区 * 石景山区 * 通州区 * 昌平区 * 大兴区 * 北京经济技术开发区 * 顺义区 * 房山区 * 门头沟区 * 平谷区 * 怀柔区 * 密云区 * 延庆区 * 不限 * 奥林匹克公园 * 安宁庄 * 白石桥 * 北太平庄 * 昌平其它 * 厂洼 * 定慧寺 * 二里庄 * 公主坟 * 甘家口 * 海淀其它 * 海淀北部新区 * 回龙观 * 霍营 * 军博 * 六里桥 * 牡丹园 * 马连洼 * 马甸 * 苹果园 * 清河 * 青塔 * 苏州桥 * 上地 * 世纪城 * 四季青 * 双榆树 * 天通苑 * 田村 * 五道口 * 五棵松 * 魏公村 * 万柳 * 万寿路 * 西山 * 西三旗 * 西北旺 * 学院路 * 小西天 * 西直门 * 新街口 * 西二旗 * 圆明园 * 月坛 * 杨庄 * 玉泉路 * 颐和园 * 知春路 * 皂君庙 * 中关村 * 紫竹桥 面积≤40㎡40-60㎡60-80㎡80-100㎡100-120㎡≥120㎡服务保障 [](https://m.ke.com/chuzu/bj/promise/desc/)品质认证在线签约租期月租年租一个月起租1-3个月4-6个月 清除 确定 * 全部品牌 * 海淀区 * 租金 * 筛选 _随时入住_ 云逸青年社区（北京）·颐阳山水居（小区） 北起G南至A西起26东至29 2600-3200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·千和公寓（海淀） 北京市海淀区白家疃路 2100-4200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·乐季（海淀） 北京市海淀区温泉镇显龙山文化产业园 2500-3000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·东马坊精装公寓 宜宿空间东马坊店19号院 1300-2000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·精装Loft 丶开间 整租无中介 白水洼路西辛力屯 1400-1500元/月 2个房型 | 2套在租 _随时入住_ 乐乎青年社区·上地店 上地八街7号院 4784-5198元/月 1个房型 | 2套在租 _随时入住_ 云逸青年社区（北京）·西三旗店 建材城西路 3500-3800元/月 2个房型 | 2套在租 _随时入住_ 千居嘉业公寓·中关村 彩和坊西小街1号 7200-7800元/月 5个房型 | 5套在租 _已满房_ 云逸青年社区（北京）·西山雅园店（白家瞳） 北京市海淀区白家疃路 暂无 6个房型 | 0套在租 _随时入住_ 欣悦青年社区·田村地铁站店 田村路40号院, 阜石路甲19号 2800-4500元/月 1个房型 | 5套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰1店 后屯中街8号院 暂无 5个房型 | 0套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰2店 后屯中街8号院 暂无 5个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·萌芽-青年公寓 颐春小区 2000-2981元/月 6个房型 | 6套在租 _随时入住_ 岚悦青年社区·翠湖科技园店 海淀区温泉镇北清路和温阳路西南角 3680元/月 2个房型 | 1套在租 _已满房_ 嘉悦赢公寓·国驰雅居 北三环中路43号院 暂无 4个房型 | 0套在租 _随时入住_ 乐乎青年社区·西二旗店 上地十街1号院 5100元/月 1个房型 | 1套在租 _已满房_ 创意初心社区·颐和山庄公寓 玉华园 暂无 1个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·新苑街店 新苑街10号院 4100元/月 1个房型 | 1套在租 _随时入住_ 云逸青年社区（北京）·香岩寺店（海淀） 北京市海淀区云水路1号 2800-3700元/月 10个房型 | 10套在租 _已满房_ 乐乎青年社区·乐乎上地店 上地八街7号院 暂无 1个房型 | 0套在租 加载中... 没有符合条件的房源 请换个条件试试 关注(0) * 北京租房网&gt; * 北京租房&gt; * 北京公寓品牌馆 热门商圈 推荐小区 租房城市 * 小西天租房 * 石佛营租房 * 武夷花园租房 * 工体租房 * 牡丹园租房 * 通州北苑租房 * 三里屯租房 * 天竺租房 * 新华大街租房 * 天坛租房 * 天宫院租房 * 右安门外租房 * 志强园租房 * 右外大厦租房 * 建邦华庭西区租房 * 铜光胡同租房 * 中兴巷租房 * 东四块玉南街4号院租房 * 高梁桥斜街11号院租房 * 三间房南里5号院租房 * 陶然居租房 * 南苑公寓房租房 * 张郭庄40号院租房 * 天坛东路租房 * 嘉兴租房 * 盐城租房 * 无锡租房 * 常州租房 * 广州租房 * 长春租房 * 南京租房 * 汉中租房 * 金华租房 * 青岛租房 * 西安租房 * 郑州租房 [](javascript:;；# 新发地房屋出租信息_北京丰台新发地出租房源信息-58出租网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 北京租房&gt; 丰台租房&gt; 新发地租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * B * 北大地 * C * 菜户营 * 草桥 * 长辛店 * 成寿寺 * D * 大红门 * 东大街 * 东高地 * 东铁匠营 * F * 方庄 * 丰台路 * 丰台体育馆 * 丰台周边 * 丰益桥 * H * 和义 * 花乡 * J * 角门 * K * 看丹桥 * 科技园区 * L * 莲花池 * 刘家窑 * 六里桥 * 丽泽桥 * 卢沟桥 * M * 马家堡 * 木樨园 * N * 南苑 * P * 蒲黄榆 * Q * 七里庄 * 青塔 * S * 世界公园 * 石榴庄 * 宋家庄 * T * 太平桥 * W * 五里店 * X * 小屯路 * 西客站 * 西罗园 * 新发地 * 新宫 * Y * 洋桥 * 右安门 * 岳各庄 * 云岗 * 玉泉营 * Z * 赵公口 * 总部基地 * 左安门 # 新发地出租租房房源 * 1829 元我爱我家相寓 花乡天伦锦城中楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 * 4500 元新发地 银地家园 南北朝向 两室一厅 2室1厅 / 68.00㎡ 推荐理由： 邻地铁 押一付一 精装修 * 5300 元丰台新发地农贸市场 近益农门 宜兰园小区 宜兰园二区两居室 2室1厅 / 63.3㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 随时看房 * 2700 元新发地 天伦锦城新上带电梯 主卧 诚心出租 3室1厅 / 20.0㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 5300 元花乡 新发地 银地家园2室1厅 出租 干净 整洁 2室1厅 / 76.84㎡ 推荐理由： 邻地铁 配套齐全 有阳台 * 1800 元花乡 新发地 宜兰园 次卧出租 房子干净 4室1厅 / 16.0㎡ 推荐理由： 邻地铁 配套齐全 南北通透 * 6800 元新发地 天伦锦城新上带电梯 南北三居 干净整洁 诚心出租 3室1厅 / 106.74㎡ 推荐理由： 邻地铁 精装修 * 4400 元银地家园 2室1厅1卫 2室1厅 / 72㎡ 推荐理由： 邻地铁 * 7000 元整租花乡银地家园3室1厅 出租 3室1厅 / 128.4㎡ 推荐理由： 邻地铁 精装修 * 5500 元新发地 银地家园新上带电梯 大两居 包物业取暖 诚心出租 2室1厅 / 88.49㎡ 推荐理由： 邻地铁 * 5500 元新发地 银地家园新上一层 大两居 包物业取暖诚心出租 2室1厅 / 90.0㎡ 推荐理由： 邻地铁 精装修 * 6270 元新发地 花乡 宜兰园 中楼层 3居室 精装出租 地铁19号线 3室1厅 / 112.93㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 6500 元整租花乡宜兰园3室1厅 出租 3室1厅 / 112.0㎡ 推荐理由： 邻地铁 * 4500 元整租花乡宜兰园1室1厅 1室1厅 / 79.04㎡ 推荐理由： 独卫一居 邻地铁 * 5000 元新上，天骄俊园北区，86平米两居室，精装全齐 2室1厅 / 86㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 1550 元南向温馨小卧,价格美丽,新发地批发市场,中央批发市场, 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1800 元新发地 银地家园新上大次卧 包物业取暖 诚心出租 5室1厅 / 13.3㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 1700 元花乡 奥莱村 新发地批发市场 银地家园 天伦锦城 正规次卧 3室2厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 1900 元花乡奥莱村 新发地批发市场 地铁19号线 朝南正规大主卧 3室2厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2700 元宜兰园一区 新发地批发市场 银地家园 天伦锦城 朝南主卧独卫 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 5200 元地铁19号线新发地站天骄俊园精装两居南北通透 2室1厅 / 86㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 5200 元19号线新发地 公益西桥旁南北通透两居室火热出租中 随时入住 2室1厅 / 84.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 4200 元整租丰台区新发地附近期颐百年一居室出租 1室1厅 / 69㎡ 推荐理由： 独卫一居 精装修 * 4200 元新发地 天伦锦城新上带电梯 一居 诚心出租 1室1厅 / 58.9㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4000 元宜兰园三区 1室1厅1卫 1室1厅 / 67㎡ 推荐理由： 新上 邻地铁 * 5500 元新发地天伦锦城大两居出租，随时看随时住 2室2厅 / 90㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 1500 元天伦锦城 4室1厅1卫 9平 电梯房新发地市场超近 4室1厅 / 8㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 4100 元新发地市场 天伦锦城1居室 南北通透 银地家园 中央批发市场 1室1厅 / 58.00㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 6000 元花乡 新发地 天伦锦城 2室1厅 出租 出租 2室1厅 / 100.06㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 3680 元我爱我家相寓 花乡天伦锦城中楼层1居室 1室1厅 / 40.82㎡ 推荐理由： 独卫一居 邻地铁 * 6500 元整租花乡天伦锦城2室1厅 2室1厅 / 91.55㎡ 推荐理由： 邻地铁 精装修 * 4200 元整租花乡银地家园1室0厅 1室0厅 / 55.0㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5200 元可月付0押金 新发地站 天伦锦城90平两居室出租离地铁市场近 2室1厅 / 59.40㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 3600 元花乡 新发地 银地家园 1室 出租 电梯房 集中供暖 1室0厅 / 45.05㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 随时看房 * 1700 元新发地 天伦锦城新上带电梯 大次卧 低价出租 3室1厅 / 15.0㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 南北通透 * 1890 元花乡 新发地 宜兰园 大次卧出租 房子干净 出行便利 4室1厅 / 20.0㎡ 推荐理由： 邻地铁 配套齐全 南北通透 * 1700 元天骄俊园(北区) 4室0厅2卫 4室0厅 / 10㎡ 推荐理由： 独卫 邻地铁 南北通透 * 4800 元可月付 新发地站 宜兰园两居室出租 可宿舍价可聊随时住 2室1厅 / 89.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 3500 元新发地市场 银地家园1居室 19号线地铁 宜兰园 天伦锦城 1室1厅 / 45.05㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元整租花乡银地家园1室0厅 1室0厅 / 36.69㎡ 推荐理由： 独卫一居 邻地铁 # 新发地租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 赵欠欠 北京蓝天联合房地产投资顾问有限公司 * 于德洋 北京相寓住房租赁有限公司 * 张祖冉 北京我爱我家房地产经纪有限公司 * 祝东珍 北京盛峰荣泰住房租赁有限公司 * 时腾尧 北京欢颜住房租赁有限公司 * 董茂森 北京安居联行房地产经纪有限公司 * 刘浩 三河市兴达香汐置业房地产经纪有限公司 * 雷鸣 北京小蜗牛房地产经纪有限公司 ## 租房房产问答 * 问 发布租房信息在哪儿发布 * lZZccYc： 挂牌房产中介，也可在各房产网络平台发布，如：安居客、58同城等 * 高赛： 找最近的房产中介，如果特别着急，就多挂几家 * 韩云满： 房源发布在房地产门户网站上会有入口。；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。</x:v>
+        <x:v>未找到倚山庭苑社区2026年的具体租房月租数据，仅提及小区户型面积89-140㎡，周边区域新房价格约12000元/㎡，但租房单价未明确；；关于租房相关：公开信息主要涉及小区整体户型（89-140㎡，主打126、140㎡3室户型）、绿化较好、物业评价偏正面，未找到租房时特别提及的隔音、房龄等具体质量反馈；</x:v>
       </x:c>
       <x:c r="L40" t="str">
-        <x:v>)_北京_ [](https://m.ke.com/chuzu/bj/)[](https://m.ke.com/my/index/) * 不限 * ≤2000元 * 2000-3000元 * 3000-4000元 * 4000-5000元 * 5000-6000元 * 6000-8000元 * 8000-20000元 * ≥20000元 _—_ 确定 * ### 全部品牌 693家门店 * ### 城家公寓 15家门店 确定 * 区域 * 地铁 * 附近 * 不限 * 东城区 * 西城区 * 朝阳区 * 海淀区 * 丰台区 * 石景山区 * 通州区 * 昌平区 * 大兴区 * 北京经济技术开发区 * 顺义区 * 房山区 * 门头沟区 * 平谷区 * 怀柔区 * 密云区 * 延庆区 * 不限 * 奥林匹克公园 * 安宁庄 * 白石桥 * 北太平庄 * 昌平其它 * 厂洼 * 定慧寺 * 二里庄 * 公主坟 * 甘家口 * 海淀其它 * 海淀北部新区 * 回龙观 * 霍营 * 军博 * 六里桥 * 牡丹园 * 马连洼 * 马甸 * 苹果园 * 清河 * 青塔 * 苏州桥 * 上地 * 世纪城 * 四季青 * 双榆树 * 天通苑 * 田村 * 五道口 * 五棵松 * 魏公村 * 万柳 * 万寿路 * 西山 * 西三旗 * 西北旺 * 学院路 * 小西天 * 西直门 * 新街口 * 西二旗 * 圆明园 * 月坛 * 杨庄 * 玉泉路 * 颐和园 * 知春路 * 皂君庙 * 中关村 * 紫竹桥 面积≤40㎡40-60㎡60-80㎡80-100㎡100-120㎡≥120㎡服务保障 [](https://m.ke.com/chuzu/bj/promise/desc/)品质认证在线签约租期月租年租一个月起租1-3个月4-6个月 清除 确定 * 全部品牌 * 海淀区 * 租金 * 筛选 _随时入住_ 云逸青年社区（北京）·颐阳山水居（小区） 北起G南至A西起26东至29 2600-3200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·千和公寓（海淀） 北京市海淀区白家疃路 2100-4200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·乐季（海淀） 北京市海淀区温泉镇显龙山文化产业园 2500-3000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·东马坊精装公寓 宜宿空间东马坊店19号院 1300-2000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·精装Loft 丶开间 整租无中介 白水洼路西辛力屯 1400-1500元/月 2个房型 | 2套在租 _随时入住_ 乐乎青年社区·上地店 上地八街7号院 4784-5198元/月 1个房型 | 2套在租 _随时入住_ 云逸青年社区（北京）·西三旗店 建材城西路 3500-3800元/月 2个房型 | 2套在租 _随时入住_ 千居嘉业公寓·中关村 彩和坊西小街1号 7200-7800元/月 5个房型 | 5套在租 _已满房_ 云逸青年社区（北京）·西山雅园店（白家瞳） 北京市海淀区白家疃路 暂无 6个房型 | 0套在租 _随时入住_ 欣悦青年社区·田村地铁站店 田村路40号院, 阜石路甲19号 2800-4500元/月 1个房型 | 5套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰1店 后屯中街8号院 暂无 5个房型 | 0套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰2店 后屯中街8号院 暂无 5个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·萌芽-青年公寓 颐春小区 2000-2981元/月 6个房型 | 6套在租 _随时入住_ 岚悦青年社区·翠湖科技园店 海淀区温泉镇北清路和温阳路西南角 3680元/月 2个房型 | 1套在租 _已满房_ 嘉悦赢公寓·国驰雅居 北三环中路43号院 暂无 4个房型 | 0套在租 _随时入住_ 乐乎青年社区·西二旗店 上地十街1号院 5100元/月 1个房型 | 1套在租 _已满房_ 创意初心社区·颐和山庄公寓 玉华园 暂无 1个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·新苑街店 新苑街10号院 4100元/月 1个房型 | 1套在租 _随时入住_ 云逸青年社区（北京）·香岩寺店（海淀） 北京市海淀区云水路1号 2800-3700元/月 10个房型 | 10套在租 _已满房_ 乐乎青年社区·乐乎上地店 上地八街7号院 暂无 1个房型 | 0套在租 加载中... 没有符合条件的房源 请换个条件试试 关注(0) * 北京租房网&gt; * 北京租房&gt; * 北京公寓品牌馆 热门商圈 推荐小区 租房城市 * 小西天租房 * 石佛营租房 * 武夷花园租房 * 工体租房 * 牡丹园租房 * 通州北苑租房 * 三里屯租房 * 天竺租房 * 新华大街租房 * 天坛租房 * 天宫院租房 * 右安门外租房 * 志强园租房 * 右外大厦租房 * 建邦华庭西区租房 * 铜光胡同租房 * 中兴巷租房 * 东四块玉南街4号院租房 * 高梁桥斜街11号院租房 * 三间房南里5号院租房 * 陶然居租房 * 南苑公寓房租房 * 张郭庄40号院租房 * 天坛东路租房 * 嘉兴租房 * 盐城租房 * 无锡租房 * 常州租房 * 广州租房 * 长春租房 * 南京租房 * 汉中租房 * 金华租房 * 青岛租房 * 西安租房 * 郑州租房 [](javascript:;；# 新发地房屋出租信息_北京丰台新发地出租房源信息-58出租网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 北京租房&gt; 丰台租房&gt; 新发地租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * B * 北大地 * C * 菜户营 * 草桥 * 长辛店 * 成寿寺 * D * 大红门 * 东大街 * 东高地 * 东铁匠营 * F * 方庄 * 丰台路 * 丰台体育馆 * 丰台周边 * 丰益桥 * H * 和义 * 花乡 * J * 角门 * K * 看丹桥 * 科技园区 * L * 莲花池 * 刘家窑 * 六里桥 * 丽泽桥 * 卢沟桥 * M * 马家堡 * 木樨园 * N * 南苑 * P * 蒲黄榆 * Q * 七里庄 * 青塔 * S * 世界公园 * 石榴庄 * 宋家庄 * T * 太平桥 * W * 五里店 * X * 小屯路 * 西客站 * 西罗园 * 新发地 * 新宫 * Y * 洋桥 * 右安门 * 岳各庄 * 云岗 * 玉泉营 * Z * 赵公口 * 总部基地 * 左安门 # 新发地出租租房房源 * 1829 元我爱我家相寓 花乡天伦锦城中楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 * 4500 元新发地 银地家园 南北朝向 两室一厅 2室1厅 / 68.00㎡ 推荐理由： 邻地铁 押一付一 精装修 * 5300 元丰台新发地农贸市场 近益农门 宜兰园小区 宜兰园二区两居室 2室1厅 / 63.3㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 随时看房 * 2700 元新发地 天伦锦城新上带电梯 主卧 诚心出租 3室1厅 / 20.0㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 5300 元花乡 新发地 银地家园2室1厅 出租 干净 整洁 2室1厅 / 76.84㎡ 推荐理由： 邻地铁 配套齐全 有阳台 * 1800 元花乡 新发地 宜兰园 次卧出租 房子干净 4室1厅 / 16.0㎡ 推荐理由： 邻地铁 配套齐全 南北通透 * 6800 元新发地 天伦锦城新上带电梯 南北三居 干净整洁 诚心出租 3室1厅 / 106.74㎡ 推荐理由： 邻地铁 精装修 * 4400 元银地家园 2室1厅1卫 2室1厅 / 72㎡ 推荐理由： 邻地铁 * 7000 元整租花乡银地家园3室1厅 出租 3室1厅 / 128.4㎡ 推荐理由： 邻地铁 精装修 * 5500 元新发地 银地家园新上带电梯 大两居 包物业取暖 诚心出租 2室1厅 / 88.49㎡ 推荐理由： 邻地铁 * 5500 元新发地 银地家园新上一层 大两居 包物业取暖诚心出租 2室1厅 / 90.0㎡ 推荐理由： 邻地铁 精装修 * 6270 元新发地 花乡 宜兰园 中楼层 3居室 精装出租 地铁19号线 3室1厅 / 112.93㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 6500 元整租花乡宜兰园3室1厅 出租 3室1厅 / 112.0㎡ 推荐理由： 邻地铁 * 4500 元整租花乡宜兰园1室1厅 1室1厅 / 79.04㎡ 推荐理由： 独卫一居 邻地铁 * 5000 元新上，天骄俊园北区，86平米两居室，精装全齐 2室1厅 / 86㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 1550 元南向温馨小卧,价格美丽,新发地批发市场,中央批发市场, 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1800 元新发地 银地家园新上大次卧 包物业取暖 诚心出租 5室1厅 / 13.3㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 1700 元花乡 奥莱村 新发地批发市场 银地家园 天伦锦城 正规次卧 3室2厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 1900 元花乡奥莱村 新发地批发市场 地铁19号线 朝南正规大主卧 3室2厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2700 元宜兰园一区 新发地批发市场 银地家园 天伦锦城 朝南主卧独卫 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 5200 元地铁19号线新发地站天骄俊园精装两居南北通透 2室1厅 / 86㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 5200 元19号线新发地 公益西桥旁南北通透两居室火热出租中 随时入住 2室1厅 / 84.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 4200 元整租丰台区新发地附近期颐百年一居室出租 1室1厅 / 69㎡ 推荐理由： 独卫一居 精装修 * 4200 元新发地 天伦锦城新上带电梯 一居 诚心出租 1室1厅 / 58.9㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4000 元宜兰园三区 1室1厅1卫 1室1厅 / 67㎡ 推荐理由： 新上 邻地铁 * 5500 元新发地天伦锦城大两居出租，随时看随时住 2室2厅 / 90㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 1500 元天伦锦城 4室1厅1卫 9平 电梯房新发地市场超近 4室1厅 / 8㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 4100 元新发地市场 天伦锦城1居室 南北通透 银地家园 中央批发市场 1室1厅 / 58.00㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 6000 元花乡 新发地 天伦锦城 2室1厅 出租 出租 2室1厅 / 100.06㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 3680 元我爱我家相寓 花乡天伦锦城中楼层1居室 1室1厅 / 40.82㎡ 推荐理由： 独卫一居 邻地铁 * 6500 元整租花乡天伦锦城2室1厅 2室1厅 / 91.55㎡ 推荐理由： 邻地铁 精装修 * 4200 元整租花乡银地家园1室0厅 1室0厅 / 55.0㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5200 元可月付0押金 新发地站 天伦锦城90平两居室出租离地铁市场近 2室1厅 / 59.40㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 3600 元花乡 新发地 银地家园 1室 出租 电梯房 集中供暖 1室0厅 / 45.05㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 随时看房 * 1700 元新发地 天伦锦城新上带电梯 大次卧 低价出租 3室1厅 / 15.0㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 南北通透 * 1890 元花乡 新发地 宜兰园 大次卧出租 房子干净 出行便利 4室1厅 / 20.0㎡ 推荐理由： 邻地铁 配套齐全 南北通透 * 1700 元天骄俊园(北区) 4室0厅2卫 4室0厅 / 10㎡ 推荐理由： 独卫 邻地铁 南北通透 * 4800 元可月付 新发地站 宜兰园两居室出租 可宿舍价可聊随时住 2室1厅 / 89.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 3500 元新发地市场 银地家园1居室 19号线地铁 宜兰园 天伦锦城 1室1厅 / 45.05㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元整租花乡银地家园1室0厅 1室0厅 / 36.69㎡ 推荐理由： 独卫一居 邻地铁 # 新发地租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 赵欠欠 北京蓝天联合房地产投资顾问有限公司 * 于德洋 北京相寓住房租赁有限公司 * 张祖冉 北京我爱我家房地产经纪有限公司 * 祝东珍 北京盛峰荣泰住房租赁有限公司 * 时腾尧 北京欢颜住房租赁有限公司 * 董茂森 北京安居联行房地产经纪有限公司 * 刘浩 三河市兴达香汐置业房地产经纪有限公司 * 雷鸣 北京小蜗牛房地产经纪有限公司 ## 租房房产问答 * 问 发布租房信息在哪儿发布 * lZZccYc： 挂牌房产中介，也可在各房产网络平台发布，如：安居客、58同城等 * 高赛： 找最近的房产中介，如果特别着急，就多挂几家 * 韩云满： 房源发布在房地产门户网站上会有入口。；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 新发地租房信息 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安溪租房网 * 桂林租房网 * 黔东南租房网 * 海口租房网 * 钟祥租房网 * 常德租房网 * 抚顺租房网 * 呼伦贝尔租房网 * 大同租房网 * 阿坝租房网 * 丰台租房网 * 西城租房网 * 密云租房网 * 朝阳租房网 * 门头沟租房网 * 北京周边租房网 * 延庆租房网 * 大兴租房网 * 房山租房网 * 怀柔租房网 * 不老屯租房网 * 密云城区租房网 * 密云水库别墅区租房网 * 密云周边租房网 * 溪翁庄租房网 * 城子街道租房网 * 大峪租房网 * 东辛房租房网 * 军庄租房网 * 龙泉租房网 * 门头沟周边租房网 * 保定租房网 * 八达岭租房网 * 渤海镇租房网 * 白广路租房网 * 磁各庄租房网 * 北大地租房网 * CBD租房网 * 长阳租房网 * 梧州租房 * 杞县租房 * 邵阳租房 * 黄骅租房 * 淮安租房 * 梧州出租 * 杞县出租 * 邵阳出租 * 黄骅出租 * 淮安出租 * 梧州整租房 * 杞县整租房 * 邵阳整租房 * 黄骅整租房 * 淮安整租房 * 梧州合租房 * 杞县合租房 * 邵阳合租房 * 黄骅合租房 * 淮安合租房 * 梧州个人 * 杞县个人 * 邵阳个人 * 黄骅个人 * 淮安个人 * 丰台租房 * 西城租房 * 密云租房 * 朝阳租房 * 门头沟租房 * 丰台出租 * 西城出租 * 密云出租 * 朝阳出租 * 门头沟出租 * 丰台整租房 * 西城整租房 * 密云整租房 * 朝阳整租房 * 门头沟整租房 * 丰台合租房 * 西城合租房 * 密云合租房 * 朝阳合租房 * 门头沟合租房 * 北京别墅租房 * 北京公寓租房 * 北京公租房租房 * 北京500元左右租房 * 北京10平米租房 * 北京50平米租房 * 北京60平米租房 * 北京120平米租房 * 北京150平米租房 * 北京交通便利租房 * 北京商场附近租房 * 北京公园附近租房 * 北京拎包入住租房 * 北京幼儿园附近租房 * 北京小学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>未找到倚山庭苑社区2026年的具体租房月租数据，仅提及小区户型面积89-140㎡，周边区域新房价格约12000元/㎡，但租房单价未明确；；属于海淀区马连洼街道，周边配套信息中提到交通有公交车配套，区位条件不错，临近教育资源（如万柏林实验小学等，但可能为同名混淆），商超、医院、餐饮等具体生活便利信息未在租房口碑中找到明确指向；</x:v>
       </x:c>
       <x:c r="M40" t="str">
-        <x:v>手机版： 新发地租房信息 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安溪租房网 * 桂林租房网 * 黔东南租房网 * 海口租房网 * 钟祥租房网 * 常德租房网 * 抚顺租房网 * 呼伦贝尔租房网 * 大同租房网 * 阿坝租房网 * 丰台租房网 * 西城租房网 * 密云租房网 * 朝阳租房网 * 门头沟租房网 * 北京周边租房网 * 延庆租房网 * 大兴租房网 * 房山租房网 * 怀柔租房网 * 不老屯租房网 * 密云城区租房网 * 密云水库别墅区租房网 * 密云周边租房网 * 溪翁庄租房网 * 城子街道租房网 * 大峪租房网 * 东辛房租房网 * 军庄租房网 * 龙泉租房网 * 门头沟周边租房网 * 保定租房网 * 八达岭租房网 * 渤海镇租房网 * 白广路租房网 * 磁各庄租房网 * 北大地租房网 * CBD租房网 * 长阳租房网 * 梧州租房 * 杞县租房 * 邵阳租房 * 黄骅租房 * 淮安租房 * 梧州出租 * 杞县出租 * 邵阳出租 * 黄骅出租 * 淮安出租 * 梧州整租房 * 杞县整租房 * 邵阳整租房 * 黄骅整租房 * 淮安整租房 * 梧州合租房 * 杞县合租房 * 邵阳合租房 * 黄骅合租房 * 淮安合租房 * 梧州个人 * 杞县个人 * 邵阳个人 * 黄骅个人 * 淮安个人 * 丰台租房 * 西城租房 * 密云租房 * 朝阳租房 * 门头沟租房 * 丰台出租 * 西城出租 * 密云出租 * 朝阳出租 * 门头沟出租 * 丰台整租房 * 西城整租房 * 密云整租房 * 朝阳整租房 * 门头沟整租房 * 丰台合租房 * 西城合租房 * 密云合租房 * 朝阳合租房 * 门头沟合租房 * 北京别墅租房 * 北京公寓租房 * 北京公租房租房 * 北京500元左右租房 * 北京10平米租房 * 北京50平米租房 * 北京60平米租房 * 北京120平米租房 * 北京150平米租房 * 北京交通便利租房 * 北京商场附近租房 * 北京公园附近租房 * 北京拎包入住租房 * 北京幼儿园附近租房 * 北京小学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>未找到针对该社区租房的明确差评或风险信息。；未找到针对该社区租房的明确差评或风险信息</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>价格线索： 3室2厅176㎡. 20000元/月；北起G南至A西起26东至29 2600-3200元/月；海淀） 北京市海淀区白家疃路 2100-4200元/月；海淀区温泉镇显龙山文化产业园 2500-3000元/月；寓 宜宿空间东马坊店19号院 1300-2000元/月；整租无中介 白水洼路西辛力屯 1400-1500元/月；社区·上地店 上地八街7号院 4784-5198元/月；北京）·西三旗店 建材城西路 3500-3800元/月；房屋质量/户型线索：)_北京_ [](https://m.ke.com/chuzu/bj/)[](https://m.ke.com/my/index/) * 不限 * ≤2000元 * 2000-3000元 * 3000-4000元 * 4000-5000元 * 5000-6000元 * 6000-8000元 * 8000-20000元 * ≥20000元 _—_ 确定 * ### 全部品牌 693家门店 * ### 城家公寓 15家门店 确定 * 区域 * 地铁 * 附近 * 不限 * 东城区 * 西城区 * 朝阳区 * 海淀区 * 丰台区 * 石景山区 * 通州区 * 昌平区 * 大兴区 * 北京经济技术开发区 * 顺义区 * 房山区 * 门头沟区 * 平谷区 * 怀柔区 * 密云区 * 延庆区 * 不限 * 奥林匹克公园 * 安宁庄 * 白石桥 * 北太平庄 * 昌平其它 * 厂洼 * 定慧寺 * 二里庄 * 公主坟 * 甘家口 * 海淀其它 * 海淀北部新区 * 回龙观 * 霍营 * 军博 * 六里桥 * 牡丹园 * 马连洼 * 马甸 * 苹果园 * 清河 * 青塔 * 苏州桥 * 上地 * 世纪城 * 四季青 * 双榆树 * 天通苑 * 田村 * 五道口 * 五棵松 * 魏公村 * 万柳 * 万寿路 * 西山 * 西三旗 * 西北旺 * 学院路 * 小西天 * 西直门 * 新街口 * 西二旗 * 圆明园 * 月坛 * 杨庄 * 玉泉路 * 颐和园 * 知春路 * 皂君庙 * 中关村 * 紫竹桥 面积≤40㎡40-60㎡60-80㎡80-100㎡100-120㎡≥120㎡服务保障 [](https://m.ke.com/chuzu/bj/promise/desc/)品质认证在线签约租期月租年租一个月起租1-3个月4-6个月 清除 确定 * 全部品牌 * 海淀区 * 租金 * 筛选 _随时入住_ 云逸青年社区（北京）·颐阳山水居（小区） 北起G南至A西起26东至29 2600-3200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·千和公寓（海淀） 北京市海淀区白家疃路 2100-4200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·乐季（海淀） 北京市海淀区温泉镇显龙山文化产业园 2500-3000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·东马坊精装公寓 宜宿空间东马坊店19号院 1300-2000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·精装Loft 丶开间 整租无中介 白水洼路西辛力屯 1400-1500元/月 2个房型 | 2套在租 _随时入住_ 乐乎青年社区·上地店 上地八街7号院 4784-5198元/月 1个房型 | 2套在租 _随时入住_ 云逸青年社区（北京）·西三旗店 建材城西路 3500-3800元/月 2个房型 | 2套在租 _随时入住_ 千居嘉业公寓·中关村 彩和坊西小街1号 7200-7800元/月 5个房型 | 5套在租 _已满房_ 云逸青年社区（北京）·西山雅园店（白家瞳） 北京市海淀区白家疃路 暂无 6个房型 | 0套在租 _随时入住_ 欣悦青年社区·田村地铁站店 田村路40号院, 阜石路甲19号 2800-4500元/月 1个房型 | 5套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰1店 后屯中街8号院 暂无 5个房型 | 0套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰2店 后屯中街8号院 暂无 5个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·萌芽-青年公寓 颐春小区 2000-2981元/月 6个房型 | 6套在租 _随时入住_ 岚悦青年社区·翠湖科技园店 海淀区温泉镇北清路和温阳路西南角 3680元/月 2个房型 | 1套在租 _已满房_ 嘉悦赢公寓·国驰雅居 北三环中路43号院 暂无 4个房型 | 0套在租 _随时入住_ 乐乎青年社区·西二旗店 上地十街1号院 5100元/月 1个房型 | 1套在租 _已满房_ 创意初心社区·颐和山庄公寓 玉华园 暂无 1个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·新苑街店 新苑街10号院 4100元/月 1个房型 | 1套在租 _随时入住_ 云逸青年社区（北京）·香岩寺店（海淀） 北京市海淀区云水路1号 2800-3700元/月 10个房型 | 10套在租 _已满房_ 乐乎青年社区·乐乎上地店 上地八街7号院 暂无 1个房型 | 0套在租 加载中... 没有符合条件的房源 请换个条件试试 关注(0) * 北京租房网&gt; * 北京租房&gt; * 北京公寓品牌馆 热门商圈 推荐小区 租房城市 * 小西天租房 * 石佛营租房 * 武夷花园租房 * 工体租房 * 牡丹园租房 * 通州北苑租房 * 三里屯租房 * 天竺租房 * 新华大街租房 * 天坛租房 * 天宫院租房 * 右安门外租房 * 志强园租房 * 右外大厦租房 * 建邦华庭西区租房 * 铜光胡同租房 * 中兴巷租房 * 东四块玉南街4号院租房 * 高梁桥斜街11号院租房 * 三间房南里5号院租房 * 陶然居租房 * 南苑公寓房租房 * 张郭庄40号院租房 * 天坛东路租房 * 嘉兴租房 * 盐城租房 * 无锡租房 * 常州租房 * 广州租房 * 长春租房 * 南京租房 * 汉中租房 * 金华租房 * 青岛租房 * 西安租房 * 郑州租房 [](javascript:;；# 新发地房屋出租信息_北京丰台新发地出租房源信息-58出租网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 北京租房&gt; 丰台租房&gt; 新发地租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * B * 北大地 * C * 菜户营 * 草桥 * 长辛店 * 成寿寺 * D * 大红门 * 东大街 * 东高地 * 东铁匠营 * F * 方庄 * 丰台路 * 丰台体育馆 * 丰台周边 * 丰益桥 * H * 和义 * 花乡 * J * 角门 * K * 看丹桥 * 科技园区 * L * 莲花池 * 刘家窑 * 六里桥 * 丽泽桥 * 卢沟桥 * M * 马家堡 * 木樨园 * N * 南苑 * P * 蒲黄榆 * Q * 七里庄 * 青塔 * S * 世界公园 * 石榴庄 * 宋家庄 * T * 太平桥 * W * 五里店 * X * 小屯路 * 西客站 * 西罗园 * 新发地 * 新宫 * Y * 洋桥 * 右安门 * 岳各庄 * 云岗 * 玉泉营 * Z * 赵公口 * 总部基地 * 左安门 # 新发地出租租房房源 * 1829 元我爱我家相寓 花乡天伦锦城中楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 * 4500 元新发地 银地家园 南北朝向 两室一厅 2室1厅 / 68.00㎡ 推荐理由： 邻地铁 押一付一 精装修 * 5300 元丰台新发地农贸市场 近益农门 宜兰园小区 宜兰园二区两居室 2室1厅 / 63.3㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 随时看房 * 2700 元新发地 天伦锦城新上带电梯 主卧 诚心出租 3室1厅 / 20.0㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 5300 元花乡 新发地 银地家园2室1厅 出租 干净 整洁 2室1厅 / 76.84㎡ 推荐理由： 邻地铁 配套齐全 有阳台 * 1800 元花乡 新发地 宜兰园 次卧出租 房子干净 4室1厅 / 16.0㎡ 推荐理由： 邻地铁 配套齐全 南北通透 * 6800 元新发地 天伦锦城新上带电梯 南北三居 干净整洁 诚心出租 3室1厅 / 106.74㎡ 推荐理由： 邻地铁 精装修 * 4400 元银地家园 2室1厅1卫 2室1厅 / 72㎡ 推荐理由： 邻地铁 * 7000 元整租花乡银地家园3室1厅 出租 3室1厅 / 128.4㎡ 推荐理由： 邻地铁 精装修 * 5500 元新发地 银地家园新上带电梯 大两居 包物业取暖 诚心出租 2室1厅 / 88.49㎡ 推荐理由： 邻地铁 * 5500 元新发地 银地家园新上一层 大两居 包物业取暖诚心出租 2室1厅 / 90.0㎡ 推荐理由： 邻地铁 精装修 * 6270 元新发地 花乡 宜兰园 中楼层 3居室 精装出租 地铁19号线 3室1厅 / 112.93㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 6500 元整租花乡宜兰园3室1厅 出租 3室1厅 / 112.0㎡ 推荐理由： 邻地铁 * 4500 元整租花乡宜兰园1室1厅 1室1厅 / 79.04㎡ 推荐理由： 独卫一居 邻地铁 * 5000 元新上，天骄俊园北区，86平米两居室，精装全齐 2室1厅 / 86㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 1550 元南向温馨小卧,价格美丽,新发地批发市场,中央批发市场, 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1800 元新发地 银地家园新上大次卧 包物业取暖 诚心出租 5室1厅 / 13.3㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 1700 元花乡 奥莱村 新发地批发市场 银地家园 天伦锦城 正规次卧 3室2厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 1900 元花乡奥莱村 新发地批发市场 地铁19号线 朝南正规大主卧 3室2厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2700 元宜兰园一区 新发地批发市场 银地家园 天伦锦城 朝南主卧独卫 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 5200 元地铁19号线新发地站天骄俊园精装两居南北通透 2室1厅 / 86㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 5200 元19号线新发地 公益西桥旁南北通透两居室火热出租中 随时入住 2室1厅 / 84.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 4200 元整租丰台区新发地附近期颐百年一居室出租 1室1厅 / 69㎡ 推荐理由： 独卫一居 精装修 * 4200 元新发地 天伦锦城新上带电梯 一居 诚心出租 1室1厅 / 58.9㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4000 元宜兰园三区 1室1厅1卫 1室1厅 / 67㎡ 推荐理由： 新上 邻地铁 * 5500 元新发地天伦锦城大两居出租，随时看随时住 2室2厅 / 90㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 1500 元天伦锦城 4室1厅1卫 9平 电梯房新发地市场超近 4室1厅 / 8㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 4100 元新发地市场 天伦锦城1居室 南北通透 银地家园 中央批发市场 1室1厅 / 58.00㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 6000 元花乡 新发地 天伦锦城 2室1厅 出租 出租 2室1厅 / 100.06㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 3680 元我爱我家相寓 花乡天伦锦城中楼层1居室 1室1厅 / 40.82㎡ 推荐理由： 独卫一居 邻地铁 * 6500 元整租花乡天伦锦城2室1厅 2室1厅 / 91.55㎡ 推荐理由： 邻地铁 精装修 * 4200 元整租花乡银地家园1室0厅 1室0厅 / 55.0㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5200 元可月付0押金 新发地站 天伦锦城90平两居室出租离地铁市场近 2室1厅 / 59.40㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 3600 元花乡 新发地 银地家园 1室 出租 电梯房 集中供暖 1室0厅 / 45.05㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 随时看房 * 1700 元新发地 天伦锦城新上带电梯 大次卧 低价出租 3室1厅 / 15.0㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 南北通透 * 1890 元花乡 新发地 宜兰园 大次卧出租 房子干净 出行便利 4室1厅 / 20.0㎡ 推荐理由： 邻地铁 配套齐全 南北通透 * 1700 元天骄俊园(北区) 4室0厅2卫 4室0厅 / 10㎡ 推荐理由： 独卫 邻地铁 南北通透 * 4800 元可月付 新发地站 宜兰园两居室出租 可宿舍价可聊随时住 2室1厅 / 89.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 3500 元新发地市场 银地家园1居室 19号线地铁 宜兰园 天伦锦城 1室1厅 / 45.05㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元整租花乡银地家园1室0厅 1室0厅 / 36.69㎡ 推荐理由： 独卫一居 邻地铁 # 新发地租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 赵欠欠 北京蓝天联合房地产投资顾问有限公司 * 于德洋 北京相寓住房租赁有限公司 * 张祖冉 北京我爱我家房地产经纪有限公司 * 祝东珍 北京盛峰荣泰住房租赁有限公司 * 时腾尧 北京欢颜住房租赁有限公司 * 董茂森 北京安居联行房地产经纪有限公司 * 刘浩 三河市兴达香汐置业房地产经纪有限公司 * 雷鸣 北京小蜗牛房地产经纪有限公司 ## 租房房产问答 * 问 发布租房信息在哪儿发布 * lZZccYc： 挂牌房产中介，也可在各房产网络平台发布，如：安居客、58同城等 * 高赛： 找最近的房产中介，如果特别着急，就多挂几家 * 韩云满： 房源发布在房地产门户网站上会有入口。；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；生活便利线索：)_北京_ [](https://m.ke.com/chuzu/bj/)[](https://m.ke.com/my/index/) * 不限 * ≤2000元 * 2000-3000元 * 3000-4000元 * 4000-5000元 * 5000-6000元 * 6000-8000元 * 8000-20000元 * ≥20000元 _—_ 确定 * ### 全部品牌 693家门店 * ### 城家公寓 15家门店 确定 * 区域 * 地铁 * 附近 * 不限 * 东城区 * 西城区 * 朝阳区 * 海淀区 * 丰台区 * 石景山区 * 通州区 * 昌平区 * 大兴区 * 北京经济技术开发区 * 顺义区 * 房山区 * 门头沟区 * 平谷区 * 怀柔区 * 密云区 * 延庆区 * 不限 * 奥林匹克公园 * 安宁庄 * 白石桥 * 北太平庄 * 昌平其它 * 厂洼 * 定慧寺 * 二里庄 * 公主坟 * 甘家口 * 海淀其它 * 海淀北部新区 * 回龙观 * 霍营 * 军博 * 六里桥 * 牡丹园 * 马连洼 * 马甸 * 苹果园 * 清河 * 青塔 * 苏州桥 * 上地 * 世纪城 * 四季青 * 双榆树 * 天通苑 * 田村 * 五道口 * 五棵松 * 魏公村 * 万柳 * 万寿路 * 西山 * 西三旗 * 西北旺 * 学院路 * 小西天 * 西直门 * 新街口 * 西二旗 * 圆明园 * 月坛 * 杨庄 * 玉泉路 * 颐和园 * 知春路 * 皂君庙 * 中关村 * 紫竹桥 面积≤40㎡40-60㎡60-80㎡80-100㎡100-120㎡≥120㎡服务保障 [](https://m.ke.com/chuzu/bj/promise/desc/)品质认证在线签约租期月租年租一个月起租1-3个月4-6个月 清除 确定 * 全部品牌 * 海淀区 * 租金 * 筛选 _随时入住_ 云逸青年社区（北京）·颐阳山水居（小区） 北起G南至A西起26东至29 2600-3200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·千和公寓（海淀） 北京市海淀区白家疃路 2100-4200元/月 5个房型 | 5套在租 _随时入住_ 云逸青年社区（北京）·乐季（海淀） 北京市海淀区温泉镇显龙山文化产业园 2500-3000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·东马坊精装公寓 宜宿空间东马坊店19号院 1300-2000元/月 2个房型 | 2套在租 _随时入住_ U乐寓·精装Loft 丶开间 整租无中介 白水洼路西辛力屯 1400-1500元/月 2个房型 | 2套在租 _随时入住_ 乐乎青年社区·上地店 上地八街7号院 4784-5198元/月 1个房型 | 2套在租 _随时入住_ 云逸青年社区（北京）·西三旗店 建材城西路 3500-3800元/月 2个房型 | 2套在租 _随时入住_ 千居嘉业公寓·中关村 彩和坊西小街1号 7200-7800元/月 5个房型 | 5套在租 _已满房_ 云逸青年社区（北京）·西山雅园店（白家瞳） 北京市海淀区白家疃路 暂无 6个房型 | 0套在租 _随时入住_ 欣悦青年社区·田村地铁站店 田村路40号院, 阜石路甲19号 2800-4500元/月 1个房型 | 5套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰1店 后屯中街8号院 暂无 5个房型 | 0套在租 _已满房_ 坚果国际人才社区·坚果国际人才社区旗舰2店 后屯中街8号院 暂无 5个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·萌芽-青年公寓 颐春小区 2000-2981元/月 6个房型 | 6套在租 _随时入住_ 岚悦青年社区·翠湖科技园店 海淀区温泉镇北清路和温阳路西南角 3680元/月 2个房型 | 1套在租 _已满房_ 嘉悦赢公寓·国驰雅居 北三环中路43号院 暂无 4个房型 | 0套在租 _随时入住_ 乐乎青年社区·西二旗店 上地十街1号院 5100元/月 1个房型 | 1套在租 _已满房_ 创意初心社区·颐和山庄公寓 玉华园 暂无 1个房型 | 0套在租 _随时入住_ 云逸青年社区（北京）·新苑街店 新苑街10号院 4100元/月 1个房型 | 1套在租 _随时入住_ 云逸青年社区（北京）·香岩寺店（海淀） 北京市海淀区云水路1号 2800-3700元/月 10个房型 | 10套在租 _已满房_ 乐乎青年社区·乐乎上地店 上地八街7号院 暂无 1个房型 | 0套在租 加载中... 没有符合条件的房源 请换个条件试试 关注(0) * 北京租房网&gt; * 北京租房&gt; * 北京公寓品牌馆 热门商圈 推荐小区 租房城市 * 小西天租房 * 石佛营租房 * 武夷花园租房 * 工体租房 * 牡丹园租房 * 通州北苑租房 * 三里屯租房 * 天竺租房 * 新华大街租房 * 天坛租房 * 天宫院租房 * 右安门外租房 * 志强园租房 * 右外大厦租房 * 建邦华庭西区租房 * 铜光胡同租房 * 中兴巷租房 * 东四块玉南街4号院租房 * 高梁桥斜街11号院租房 * 三间房南里5号院租房 * 陶然居租房 * 南苑公寓房租房 * 张郭庄40号院租房 * 天坛东路租房 * 嘉兴租房 * 盐城租房 * 无锡租房 * 常州租房 * 广州租房 * 长春租房 * 南京租房 * 汉中租房 * 金华租房 * 青岛租房 * 西安租房 * 郑州租房 [](javascript:;；# 新发地房屋出租信息_北京丰台新发地出租房源信息-58出租网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 北京租房&gt; 丰台租房&gt; 新发地租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * B * 北大地 * C * 菜户营 * 草桥 * 长辛店 * 成寿寺 * D * 大红门 * 东大街 * 东高地 * 东铁匠营 * F * 方庄 * 丰台路 * 丰台体育馆 * 丰台周边 * 丰益桥 * H * 和义 * 花乡 * J * 角门 * K * 看丹桥 * 科技园区 * L * 莲花池 * 刘家窑 * 六里桥 * 丽泽桥 * 卢沟桥 * M * 马家堡 * 木樨园 * N * 南苑 * P * 蒲黄榆 * Q * 七里庄 * 青塔 * S * 世界公园 * 石榴庄 * 宋家庄 * T * 太平桥 * W * 五里店 * X * 小屯路 * 西客站 * 西罗园 * 新发地 * 新宫 * Y * 洋桥 * 右安门 * 岳各庄 * 云岗 * 玉泉营 * Z * 赵公口 * 总部基地 * 左安门 # 新发地出租租房房源 * 1829 元我爱我家相寓 花乡天伦锦城中楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 * 4500 元新发地 银地家园 南北朝向 两室一厅 2室1厅 / 68.00㎡ 推荐理由： 邻地铁 押一付一 精装修 * 5300 元丰台新发地农贸市场 近益农门 宜兰园小区 宜兰园二区两居室 2室1厅 / 63.3㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 随时看房 * 2700 元新发地 天伦锦城新上带电梯 主卧 诚心出租 3室1厅 / 20.0㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 5300 元花乡 新发地 银地家园2室1厅 出租 干净 整洁 2室1厅 / 76.84㎡ 推荐理由： 邻地铁 配套齐全 有阳台 * 1800 元花乡 新发地 宜兰园 次卧出租 房子干净 4室1厅 / 16.0㎡ 推荐理由： 邻地铁 配套齐全 南北通透 * 6800 元新发地 天伦锦城新上带电梯 南北三居 干净整洁 诚心出租 3室1厅 / 106.74㎡ 推荐理由： 邻地铁 精装修 * 4400 元银地家园 2室1厅1卫 2室1厅 / 72㎡ 推荐理由： 邻地铁 * 7000 元整租花乡银地家园3室1厅 出租 3室1厅 / 128.4㎡ 推荐理由： 邻地铁 精装修 * 5500 元新发地 银地家园新上带电梯 大两居 包物业取暖 诚心出租 2室1厅 / 88.49㎡ 推荐理由： 邻地铁 * 5500 元新发地 银地家园新上一层 大两居 包物业取暖诚心出租 2室1厅 / 90.0㎡ 推荐理由： 邻地铁 精装修 * 6270 元新发地 花乡 宜兰园 中楼层 3居室 精装出租 地铁19号线 3室1厅 / 112.93㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 6500 元整租花乡宜兰园3室1厅 出租 3室1厅 / 112.0㎡ 推荐理由： 邻地铁 * 4500 元整租花乡宜兰园1室1厅 1室1厅 / 79.04㎡ 推荐理由： 独卫一居 邻地铁 * 5000 元新上，天骄俊园北区，86平米两居室，精装全齐 2室1厅 / 86㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 1550 元南向温馨小卧,价格美丽,新发地批发市场,中央批发市场, 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1800 元新发地 银地家园新上大次卧 包物业取暖 诚心出租 5室1厅 / 13.3㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 1700 元花乡 奥莱村 新发地批发市场 银地家园 天伦锦城 正规次卧 3室2厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 1900 元花乡奥莱村 新发地批发市场 地铁19号线 朝南正规大主卧 3室2厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2700 元宜兰园一区 新发地批发市场 银地家园 天伦锦城 朝南主卧独卫 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 首次出租 * 5200 元地铁19号线新发地站天骄俊园精装两居南北通透 2室1厅 / 86㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 5200 元19号线新发地 公益西桥旁南北通透两居室火热出租中 随时入住 2室1厅 / 84.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 4200 元整租丰台区新发地附近期颐百年一居室出租 1室1厅 / 69㎡ 推荐理由： 独卫一居 精装修 * 4200 元新发地 天伦锦城新上带电梯 一居 诚心出租 1室1厅 / 58.9㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4000 元宜兰园三区 1室1厅1卫 1室1厅 / 67㎡ 推荐理由： 新上 邻地铁 * 5500 元新发地天伦锦城大两居出租，随时看随时住 2室2厅 / 90㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 1500 元天伦锦城 4室1厅1卫 9平 电梯房新发地市场超近 4室1厅 / 8㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 4100 元新发地市场 天伦锦城1居室 南北通透 银地家园 中央批发市场 1室1厅 / 58.00㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 6000 元花乡 新发地 天伦锦城 2室1厅 出租 出租 2室1厅 / 100.06㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 3680 元我爱我家相寓 花乡天伦锦城中楼层1居室 1室1厅 / 40.82㎡ 推荐理由： 独卫一居 邻地铁 * 6500 元整租花乡天伦锦城2室1厅 2室1厅 / 91.55㎡ 推荐理由： 邻地铁 精装修 * 4200 元整租花乡银地家园1室0厅 1室0厅 / 55.0㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5200 元可月付0押金 新发地站 天伦锦城90平两居室出租离地铁市场近 2室1厅 / 59.40㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 3600 元花乡 新发地 银地家园 1室 出租 电梯房 集中供暖 1室0厅 / 45.05㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 随时看房 * 1700 元新发地 天伦锦城新上带电梯 大次卧 低价出租 3室1厅 / 15.0㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 南北通透 * 1890 元花乡 新发地 宜兰园 大次卧出租 房子干净 出行便利 4室1厅 / 20.0㎡ 推荐理由： 邻地铁 配套齐全 南北通透 * 1700 元天骄俊园(北区) 4室0厅2卫 4室0厅 / 10㎡ 推荐理由： 独卫 邻地铁 南北通透 * 4800 元可月付 新发地站 宜兰园两居室出租 可宿舍价可聊随时住 2室1厅 / 89.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 3500 元新发地市场 银地家园1居室 19号线地铁 宜兰园 天伦锦城 1室1厅 / 45.05㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元整租花乡银地家园1室0厅 1室0厅 / 36.69㎡ 推荐理由： 独卫一居 邻地铁 # 新发地租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 赵欠欠 北京蓝天联合房地产投资顾问有限公司 * 于德洋 北京相寓住房租赁有限公司 * 张祖冉 北京我爱我家房地产经纪有限公司 * 祝东珍 北京盛峰荣泰住房租赁有限公司 * 时腾尧 北京欢颜住房租赁有限公司 * 董茂森 北京安居联行房地产经纪有限公司 * 刘浩 三河市兴达香汐置业房地产经纪有限公司 * 雷鸣 北京小蜗牛房地产经纪有限公司 ## 租房房产问答 * 问 发布租房信息在哪儿发布 * lZZccYc： 挂牌房产中介，也可在各房产网络平台发布，如：安居客、58同城等 * 高赛： 找最近的房产中介，如果特别着急，就多挂几家 * 韩云满： 房源发布在房地产门户网站上会有入口。；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 新发地租房信息 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安溪租房网 * 桂林租房网 * 黔东南租房网 * 海口租房网 * 钟祥租房网 * 常德租房网 * 抚顺租房网 * 呼伦贝尔租房网 * 大同租房网 * 阿坝租房网 * 丰台租房网 * 西城租房网 * 密云租房网 * 朝阳租房网 * 门头沟租房网 * 北京周边租房网 * 延庆租房网 * 大兴租房网 * 房山租房网 * 怀柔租房网 * 不老屯租房网 * 密云城区租房网 * 密云水库别墅区租房网 * 密云周边租房网 * 溪翁庄租房网 * 城子街道租房网 * 大峪租房网 * 东辛房租房网 * 军庄租房网 * 龙泉租房网 * 门头沟周边租房网 * 保定租房网 * 八达岭租房网 * 渤海镇租房网 * 白广路租房网 * 磁各庄租房网 * 北大地租房网 * CBD租房网 * 长阳租房网 * 梧州租房 * 杞县租房 * 邵阳租房 * 黄骅租房 * 淮安租房 * 梧州出租 * 杞县出租 * 邵阳出租 * 黄骅出租 * 淮安出租 * 梧州整租房 * 杞县整租房 * 邵阳整租房 * 黄骅整租房 * 淮安整租房 * 梧州合租房 * 杞县合租房 * 邵阳合租房 * 黄骅合租房 * 淮安合租房 * 梧州个人 * 杞县个人 * 邵阳个人 * 黄骅个人 * 淮安个人 * 丰台租房 * 西城租房 * 密云租房 * 朝阳租房 * 门头沟租房 * 丰台出租 * 西城出租 * 密云出租 * 朝阳出租 * 门头沟出租 * 丰台整租房 * 西城整租房 * 密云整租房 * 朝阳整租房 * 门头沟整租房 * 丰台合租房 * 西城合租房 * 密云合租房 * 朝阳合租房 * 门头沟合租房 * 北京别墅租房 * 北京公寓租房 * 北京公租房租房 * 北京500元左右租房 * 北京10平米租房 * 北京50平米租房 * 北京60平米租房 * 北京120平米租房 * 北京150平米租房 * 北京交通便利租房 * 北京商场附近租房 * 北京公园附近租房 * 北京拎包入住租房 * 北京幼儿园附近租房 * 北京小学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；风险线索：手机版： 新发地租房信息 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安溪租房网 * 桂林租房网 * 黔东南租房网 * 海口租房网 * 钟祥租房网 * 常德租房网 * 抚顺租房网 * 呼伦贝尔租房网 * 大同租房网 * 阿坝租房网 * 丰台租房网 * 西城租房网 * 密云租房网 * 朝阳租房网 * 门头沟租房网 * 北京周边租房网 * 延庆租房网 * 大兴租房网 * 房山租房网 * 怀柔租房网 * 不老屯租房网 * 密云城区租房网 * 密云水库别墅区租房网 * 密云周边租房网 * 溪翁庄租房网 * 城子街道租房网 * 大峪租房网 * 东辛房租房网 * 军庄租房网 * 龙泉租房网 * 门头沟周边租房网 * 保定租房网 * 八达岭租房网 * 渤海镇租房网 * 白广路租房网 * 磁各庄租房网 * 北大地租房网 * CBD租房网 * 长阳租房网 * 梧州租房 * 杞县租房 * 邵阳租房 * 黄骅租房 * 淮安租房 * 梧州出租 * 杞县出租 * 邵阳出租 * 黄骅出租 * 淮安出租 * 梧州整租房 * 杞县整租房 * 邵阳整租房 * 黄骅整租房 * 淮安整租房 * 梧州合租房 * 杞县合租房 * 邵阳合租房 * 黄骅合租房 * 淮安合租房 * 梧州个人 * 杞县个人 * 邵阳个人 * 黄骅个人 * 淮安个人 * 丰台租房 * 西城租房 * 密云租房 * 朝阳租房 * 门头沟租房 * 丰台出租 * 西城出租 * 密云出租 * 朝阳出租 * 门头沟出租 * 丰台整租房 * 西城整租房 * 密云整租房 * 朝阳整租房 * 门头沟整租房 * 丰台合租房 * 西城合租房 * 密云合租房 * 朝阳合租房 * 门头沟合租房 * 北京别墅租房 * 北京公寓租房 * 北京公租房租房 * 北京500元左右租房 * 北京10平米租房 * 北京50平米租房 * 北京60平米租房 * 北京120平米租房 * 北京150平米租房 * 北京交通便利租房 * 北京商场附近租房 * 北京公园附近租房 * 北京拎包入住租房 * 北京幼儿园附近租房 * 北京小学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：型面积89-140㎡，周边区域新房价格约12000元/㎡；房屋质量/户型线索：未找到倚山庭苑社区2026年的具体租房月租数据，仅提及小区户型面积89-140㎡，周边区域新房价格约12000元/㎡，但租房单价未明确；；关于租房相关：公开信息主要涉及小区整体户型（89-140㎡，主打126、140㎡3室户型）、绿化较好、物业评价偏正面，未找到租房时特别提及的隔音、房龄等具体质量反馈；；生活便利线索：未找到倚山庭苑社区2026年的具体租房月租数据，仅提及小区户型面积89-140㎡，周边区域新房价格约12000元/㎡，但租房单价未明确；；属于海淀区马连洼街道，周边配套信息中提到交通有公交车配套，区位条件不错，临近教育资源（如万柏林实验小学等，但可能为同名混淆），商超、医院、餐饮等具体生活便利信息未在租房口碑中找到明确指向；；风险线索：未找到针对该社区租房的明确差评或风险信息。；未找到针对该社区租房的明确差评或风险信息</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>1. 北京海淀区公寓租房 - 房天下 http://www.fang.com/houses/zf_254312bj/
-2. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-3. 新发地房屋出租信息_北京丰台新发地出租房源信息-58出租网 https://bj.zf.58.com/cz/xinfadi/
-4. 讨论精选（豆瓣） https://www.douban.com/group/explore
-5. 【海淀房屋出租租赁_海淀租房网】-北京麦田房产 https://bj.maitian.cn/zfall/R6/P13/OR31</x:v>
+        <x:v>1. http://m.fang.com/xf/taiyuan/1410196791/dianping.htm
+2. https://map.360.cn/site/detail/2d6b3d2548aaaac3
+3. http://m.fang.com/bbs/taiyuan/1410196791/183133139.htm
+4. https://map.beijing.gov.cn/map-web/correction/60cd978d057f7e605391b3a6?categoryId=jwh
+5. https://m.qixin.com/company/e8ac918e-a27c-11e8-aa61-00163e0f05e7
+6. http://wvw.pickfun.cn/bjfc/3317.html
+7. https://m.map.360.cn/site/detail/48d781669274345f
+8. 【倚山院怎么样】 http://m.fang.com/xf/taiyuan/1410196791/dianping.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2195,39 +2310,44 @@
         <x:v>北京市海淀区马连洼街道</x:v>
       </x:c>
       <x:c r="E41" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F41" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G41" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H41" t="n">
-        <x:v>7.4</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="I41" t="str">
-        <x:v>地理位置优越，紧邻马连洼，但需注意老旧小区停车难及学区溢价导致的租金偏高。</x:v>
+        <x:v>步行可达网易，租金性价比极高且近地铁，虽无电梯但生活极其便利。</x:v>
       </x:c>
       <x:c r="J41" t="str">
-        <x:v>衛｜40.78坪｜13F/20F 28,500 元/月；2廳2衛｜33坪｜17F/20F 27,000 元/月；*0筆 **數據不足**0筆 1 57,400 元/月；+17.1% 0筆 在租 2 45,000 元/月； 持平 0筆 在租 4 31,750 元/月；000_ 元/m² 马连洼兰园，小区价格65743元/㎡</x:v>
+        <x:v>海淀区马连洼兰园社区租房：整租一居5700元/月；（51.87平），精装两居6300-1150元/月；（注意兰州兰园是另一区域，海淀兰园两居6300元/月；左右），三居6800-8500元/月</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>北京吉屋网提供北京马连洼兰园二手房出售信息、马连洼兰园二手房价格，包括及时更新北京马连洼兰园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 马连洼兰园_北京马连洼兰园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_马连洼兰园 更新于 2026-06-01 10:57:02 [](https://bj.jiwu.com/tu/18745413.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745415.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745417.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745419.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745421.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745423.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745425.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745427.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745429.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745431.html "马连洼兰园实景图图片") # 马连洼兰园 别名：马连洼兰园 加入本地买房群 关注 _北京 - 海淀 - 海淀马连洼北路与圆明园西路路口南侧路东_ 发地址到手机 参考均价 _65743 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _1998_ 小区户数 _1698户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-3群（394） 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(6)3室(1) 全部户型 [](https://bj.jiwu.com/huxing/2011349.html "马连洼兰园2室0厅0卫62㎡户型图")2室0厅0卫 62㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2011350.html "马连洼兰园2室0厅0卫51㎡户型图")2室0厅0卫 51㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2011351.html "马连洼兰园2室0厅0卫72㎡户型图")2室0厅0卫 72㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；如果遇到停车难的问题，也有马连洼兰园的物业快速协调。；## 马连洼兰园 _海淀马连洼北路与圆明园西路路口南侧路东_ 发地址到手机 参考均价 _65743 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _1998_ 小区户数 _1698户_ 车位数量 _-_ 询成交价 新房源通知 加入买房群 北京买房交流群-3群（394） 加入群聊 附近小区 * [](https://bj.jiwu.com/loupan/145731.html "领秀硅谷1区")领秀硅谷1区 海淀 西二旗_65485_ 元/m² * [](https://bj.jiwu.com/loupan/145936.html "紫云轩10号名邸")紫云轩10号名邸 海淀 车道沟_73935_ 元/m² * [](https://bj.jiwu.com/loupan/54937.html "唐宁府")唐宁府 海淀 公主坟_35742_ 元/m² * [](https://bj.jiwu.com/loupan/146051.html "知春东里")知春东里 海淀 知春路_99816_ 元/m² * [](https://bj.jiwu.com/loupan/145995.html "森林大第北区")森林大第北区 海淀 西三旗_50350_ 元/m² 附近新房 * [](https://bj.jiwu.com/loupan/1526344.html "中海富华里")中海富华里 海淀 西北旺_80000_ 元/m² * [](https://bj.jiwu.com/loupan/1679274.html "中海安澜北京")中海安澜北京 海淀 圆明园_140000_ 元/m² * [](https://bj.jiwu.com/loupan/1658908.html "和樾玉鳴")和樾玉鳴 海淀 上地_105000_ 元/m² * [](https://bj.jiwu.com/loupan/1654638.html "颐海澐颂")颐海澐颂 海淀 永丰_89000_ 元/m² * [](https://bj.jiwu.com/loupan/1681754.html "保利熙瑞")保利熙瑞 海淀 田村_125000_ 元/m² 马连洼兰园，小区价格65743元/㎡，小区项目位于：北京-海淀-海淀马连洼北路与圆明园西路路口南侧路东。</x:v>
+        <x:v>次卧合租价格未明确，房东直租含物业情况需具体房源确认。；海淀兰园社区房屋多为6层无电梯普通住宅，装修以精装修为主；；房源隔音、户型无明确负面提及，房龄未查到，物业情况部分房源含物业（如合租提及房租含物业），部分需咨询业主/中介。</x:v>
       </x:c>
       <x:c r="L41" t="str">
-        <x:v>北京吉屋网提供北京马连洼兰园二手房出售信息、马连洼兰园二手房价格，包括及时更新北京马连洼兰园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 马连洼兰园_北京马连洼兰园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_马连洼兰园 更新于 2026-06-01 10:57:02 [](https://bj.jiwu.com/tu/18745413.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745415.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745417.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745419.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745421.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745423.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745425.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745427.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745429.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745431.html "马连洼兰园实景图图片") # 马连洼兰园 别名：马连洼兰园 加入本地买房群 关注 _北京 - 海淀 - 海淀马连洼北路与圆明园西路路口南侧路东_ 发地址到手机 参考均价 _65743 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _1998_ 小区户数 _1698户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-3群（394） 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(6)3室(1) 全部户型 [](https://bj.jiwu.com/huxing/2011349.html "马连洼兰园2室0厅0卫62㎡户型图")2室0厅0卫 62㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2011350.html "马连洼兰园2室0厅0卫51㎡户型图")2室0厅0卫 51㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2011351.html "马连洼兰园2室0厅0卫72㎡户型图")2室0厅0卫 72㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等马连洼兰园小区信息，关注吉屋北京马连洼兰园！；* 买房交流 * 找房小程序 * 返回顶部 * 关于吉屋 * 公司新闻 * 联系我们 * 加入我们 * 服务声明 * 服务热线：0755-26404403 * 网站地图 周边买房 * 北京买房 北京新房 * 房山新房 * 顺义新房 * 昌平新房 * 大兴新房 * 北京周边新房 * 平谷新房 * 海淀新房 * 丰台新房 * 门头沟新房 * 朝阳新房 * 延庆新房 * 密云新房 * 石景山新房 * 通州新房 * 怀柔新房 * 西城新房 * 东城新房 * 怀来新房 * 其他新房 * 崇礼新房 * 海滨新房 * 亦庄经开区新房 周边房价 * 房山房价 * 顺义房价 * 昌平房价 * 大兴房价 * 北京周边房价 * 平谷房价 * 海淀房价 * 丰台房价 * 门头沟房价 * 朝阳房价 * 延庆房价 * 密云房价 * 石景山房价 * 通州房价 * 怀柔房价 * 西城房价 * 东城房价 * 怀来房价 * 其他房价 * 崇礼房价 * 海滨房价 * 亦庄经开区房价 深圳市吉屋网络技术有限公司 粤ICP备11045667号粤公网安备 44030502001914号增值电信业务经营许可证房地产经纪机构备案工商网监中国电子认证服务产业联盟。</x:v>
+        <x:v>交通：临近16号线马连洼站（步行247-407米），步行可达软件园二期；；生活：周边有百旺商城、天喜百旺超市，餐饮等配套齐全；；医疗：附近有解放军总医院第八医学中心；；通勤适合软件园及周边互联网从业者。</x:v>
       </x:c>
       <x:c r="M41" t="str">
-        <x:v>如果遇到停车难的问题，也有马连洼兰园的物业快速协调。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>无明确差评或重大风险提及，仅部分房源标注需和中介/业主签约需注意合同细节。</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>价格线索：衛｜40.78坪｜13F/20F 28,500 元/月；2廳2衛｜33坪｜17F/20F 27,000 元/月；*0筆 **數據不足**0筆 1 57,400 元/月；+17.1% 0筆 在租 2 45,000 元/月； 持平 0筆 在租 4 31,750 元/月；000_ 元/m² 马连洼兰园，小区价格65743元/㎡；房屋质量/户型线索：北京吉屋网提供北京马连洼兰园二手房出售信息、马连洼兰园二手房价格，包括及时更新北京马连洼兰园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 马连洼兰园_北京马连洼兰园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_马连洼兰园 更新于 2026-06-01 10:57:02 [](https://bj.jiwu.com/tu/18745413.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745415.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745417.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745419.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745421.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745423.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745425.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745427.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745429.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745431.html "马连洼兰园实景图图片") # 马连洼兰园 别名：马连洼兰园 加入本地买房群 关注 _北京 - 海淀 - 海淀马连洼北路与圆明园西路路口南侧路东_ 发地址到手机 参考均价 _65743 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _1998_ 小区户数 _1698户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-3群（394） 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(6)3室(1) 全部户型 [](https://bj.jiwu.com/huxing/2011349.html "马连洼兰园2室0厅0卫62㎡户型图")2室0厅0卫 62㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2011350.html "马连洼兰园2室0厅0卫51㎡户型图")2室0厅0卫 51㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2011351.html "马连洼兰园2室0厅0卫72㎡户型图")2室0厅0卫 72㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；如果遇到停车难的问题，也有马连洼兰园的物业快速协调。；## 马连洼兰园 _海淀马连洼北路与圆明园西路路口南侧路东_ 发地址到手机 参考均价 _65743 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _1998_ 小区户数 _1698户_ 车位数量 _-_ 询成交价 新房源通知 加入买房群 北京买房交流群-3群（394） 加入群聊 附近小区 * [](https://bj.jiwu.com/loupan/145731.html "领秀硅谷1区")领秀硅谷1区 海淀 西二旗_65485_ 元/m² * [](https://bj.jiwu.com/loupan/145936.html "紫云轩10号名邸")紫云轩10号名邸 海淀 车道沟_73935_ 元/m² * [](https://bj.jiwu.com/loupan/54937.html "唐宁府")唐宁府 海淀 公主坟_35742_ 元/m² * [](https://bj.jiwu.com/loupan/146051.html "知春东里")知春东里 海淀 知春路_99816_ 元/m² * [](https://bj.jiwu.com/loupan/145995.html "森林大第北区")森林大第北区 海淀 西三旗_50350_ 元/m² 附近新房 * [](https://bj.jiwu.com/loupan/1526344.html "中海富华里")中海富华里 海淀 西北旺_80000_ 元/m² * [](https://bj.jiwu.com/loupan/1679274.html "中海安澜北京")中海安澜北京 海淀 圆明园_140000_ 元/m² * [](https://bj.jiwu.com/loupan/1658908.html "和樾玉鳴")和樾玉鳴 海淀 上地_105000_ 元/m² * [](https://bj.jiwu.com/loupan/1654638.html "颐海澐颂")颐海澐颂 海淀 永丰_89000_ 元/m² * [](https://bj.jiwu.com/loupan/1681754.html "保利熙瑞")保利熙瑞 海淀 田村_125000_ 元/m² 马连洼兰园，小区价格65743元/㎡，小区项目位于：北京-海淀-海淀马连洼北路与圆明园西路路口南侧路东。；生活便利线索：北京吉屋网提供北京马连洼兰园二手房出售信息、马连洼兰园二手房价格，包括及时更新北京马连洼兰园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 马连洼兰园_北京马连洼兰园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_马连洼兰园 更新于 2026-06-01 10:57:02 [](https://bj.jiwu.com/tu/18745413.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745415.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745417.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745419.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745421.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745423.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745425.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745427.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745429.html "马连洼兰园实景图图片")[](https://bj.jiwu.com/tu/18745431.html "马连洼兰园实景图图片") # 马连洼兰园 别名：马连洼兰园 加入本地买房群 关注 _北京 - 海淀 - 海淀马连洼北路与圆明园西路路口南侧路东_ 发地址到手机 参考均价 _65743 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _1998_ 小区户数 _1698户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-3群（394） 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(6)3室(1) 全部户型 [](https://bj.jiwu.com/huxing/2011349.html "马连洼兰园2室0厅0卫62㎡户型图")2室0厅0卫 62㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2011350.html "马连洼兰园2室0厅0卫51㎡户型图")2室0厅0卫 51㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2011351.html "马连洼兰园2室0厅0卫72㎡户型图")2室0厅0卫 72㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等马连洼兰园小区信息，关注吉屋北京马连洼兰园！；* 买房交流 * 找房小程序 * 返回顶部 * 关于吉屋 * 公司新闻 * 联系我们 * 加入我们 * 服务声明 * 服务热线：0755-26404403 * 网站地图 周边买房 * 北京买房 北京新房 * 房山新房 * 顺义新房 * 昌平新房 * 大兴新房 * 北京周边新房 * 平谷新房 * 海淀新房 * 丰台新房 * 门头沟新房 * 朝阳新房 * 延庆新房 * 密云新房 * 石景山新房 * 通州新房 * 怀柔新房 * 西城新房 * 东城新房 * 怀来新房 * 其他新房 * 崇礼新房 * 海滨新房 * 亦庄经开区新房 周边房价 * 房山房价 * 顺义房价 * 昌平房价 * 大兴房价 * 北京周边房价 * 平谷房价 * 海淀房价 * 丰台房价 * 门头沟房价 * 朝阳房价 * 延庆房价 * 密云房价 * 石景山房价 * 通州房价 * 怀柔房价 * 西城房价 * 东城房价 * 怀来房价 * 其他房价 * 崇礼房价 * 海滨房价 * 亦庄经开区房价 深圳市吉屋网络技术有限公司 粤ICP备11045667号粤公网安备 44030502001914号增值电信业务经营许可证房地产经纪机构备案工商网监中国电子认证服务产业联盟。；风险线索：如果遇到停车难的问题，也有马连洼兰园的物业快速协调。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：海淀区马连洼兰园社区租房：整租一居5700元/月；（51.87平），精装两居6300-1150元/月；（注意兰州兰园是另一区域，海淀兰园两居6300元/月；左右），三居6800-8500元/月；房屋质量/户型线索：次卧合租价格未明确，房东直租含物业情况需具体房源确认。；海淀兰园社区房屋多为6层无电梯普通住宅，装修以精装修为主；；房源隔音、户型无明确负面提及，房龄未查到，物业情况部分房源含物业（如合租提及房租含物业），部分需咨询业主/中介。；生活便利线索：交通：临近16号线马连洼站（步行247-407米），步行可达软件园二期；；生活：周边有百旺商城、天喜百旺超市，餐饮等配套齐全；；医疗：附近有解放军总医院第八医学中心；；通勤适合软件园及周边互联网从业者。；风险线索：无明确差评或重大风险提及，仅部分房源标注需和中介/业主签约需注意合同细节。</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>1. 來自【591租金行情】 https://rent.591.com.tw/market/community?community_id=15193&amp;pattern=four-bedroom-plus&amp;itm_source=rent&amp;itm_medium=detail&amp;itm_campaign=market_trend
-2. 马连洼兰园_北京马连洼兰园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/674221.html
-3. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. https://www.douban.com/group/topic/487115184/?_spm_id=NjI2NzQ0MzI
+2. http://m.anjuke.com/bj/rent/4585267493772291-3/
+3. https://bj.zu.anjuke.com/fangyuan/4345098254375950
+4. http://m.anjuke.com/bj/rent/3491529274204167-3/
+5. http://m.anjuke.com/bj/rent/4593800095570958-3/
+6. 【海淀·16号线马连洼兰园｜招男室友｜步行软件园二期】 https://www.douban.com/group/topic/487115184/?_spm_id=NjI2NzQ0MzI
+7. 急租！兰园温馨一居 干净整洁 通勤方便 价格可谈 http://m.anjuke.com/bj/rent/4585267493772291-3/
+8. 【多图】兰园小区，马连洼租房，马连洼梅园兰园 中间层 正规三居室 业主直签 采光好稳定租，海淀租房 https://bj.zu.anjuke.com/fangyuan/4345098254375950</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2244,38 +2364,44 @@
         <x:v>北京市海淀区厢黄旗东路柳浪家园北里西北侧约170米</x:v>
       </x:c>
       <x:c r="E42" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F42" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G42" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H42" t="n">
-        <x:v>4</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I42" t="str">
-        <x:v>缺乏具体租金与房屋质量证据，仅见停车费信息，证据充分性极低。</x:v>
+        <x:v>租金性价比高，生活配套成熟，虽距地铁有一定距离，但非常适合预算有限的职场人。</x:v>
       </x:c>
       <x:c r="J42" t="str">
-        <x:v>停车管理，项目内地面车位200个，停车费150元/月；地下车位350个，停车费350元/月；前为裸辞状态，需自己交社保（上海灵活就业2238元/月</x:v>
+        <x:v>万德嘉园租房价格：合租次卧13平米2000元/月；、15平米2500元/月；整租1室1厅42平米5100元/月；、1室0厅50平米5000元/月；、2室1厅80平米7200元/月；（或7600元/月；）、3室1厅80平米8000元/月</x:v>
       </x:c>
       <x:c r="K42" t="str">
-        <x:v># 租房-北京租房网 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝。；北京本地宝频道提供北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图有关的信息，北京海淀区山樾嘉园公租房位置：位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站。；# 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝 [](http://bj.bendibao.com/) * 本地民生 * 办事 * 社保 * 公积金 * 居住证 * 交通 * 地铁 * 旅游 * 景点 * 活动 * 教育 * 网点 * 招聘 * 特惠 北京 [](http://www.bendibao.com/city.htm) 首页 下载app * 办事指南 * 社保 * 公积金 * 出入境 * 车辆 * 户籍 * 教育 * 婚育 * 房产 * 医疗 * 生活 * 企业 * 其他 办事直通车 北京本地宝&gt;办事指南&gt;北京土地房产&gt;北京公共租赁房&gt;北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 2023-11-15 09:23【我要纠错】 下载指南 分享至 【导语】：北京海淀区山樾嘉园公租房位置：位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；(租金单价中包含物业费，不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用) **一、项目位置及周边配套** 1、项目名称：山樾嘉园(其他名称：金隅西砂公租房) 2**、项目位置：项目位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。</x:v>
+        <x:v>小区为普通住宅，房龄未明确提及；；装修多为精装修；；户型有单间、1室1厅、2室1厅、3室1厅，南北通透户型采光通风较好；；物业信息未在搜索结果中明确；；未找到关于隔音的相关评价。</x:v>
       </x:c>
       <x:c r="L42" t="str">
-        <x:v>查看更多新发布的出租房源&gt;&gt; | 北京区县房源汇总 | | --- | | | | 北京朝阳出租房源汇总 | 北京海淀出租房源汇总 | 北京丰台出租房源汇总 | 北京西城出租房源汇总 | | 北京东城出租房源汇总 | 北京昌平出租房源汇总 | 北京大兴出租房源汇总 | 北京通州出租房源汇总 | | 北京房山出租房源汇总 | 北京顺义出租房源汇总 | 北京石景山出租房源汇总 | 北京密云出租房源汇总 | | 北京门头沟出租房源汇总 | 北京怀柔出租房源汇总 | 北京延庆出租房源汇总 | 北京平谷出租房源汇总 | | 北京燕郊出租房源汇总 | 北京北京周边出租房源汇总 | 北京旅游地产出租房源汇总 | | 北京商圈房源汇总 | | --- | | | | 安宁庄 | 安定门 | 安贞 | 安贞 | 奥林匹克公园 | 宾阳 | 百善镇 | 霸州 | | 八大处 | 白纸坊 | 北关 | 滨河 | 八达岭 | 北戴河 | 北海 | 北京大学 | | 八角 | 白沟 | 北七家 | 宝坻 | 北太平庄 | 保定 | 百子湾 | 北工大 | | 北沙滩 | 北苑 | 北大地 | 采育 | 次渠 | 朝阳门内 | 城子 | 磁各庄 | | 车公庄 | 长椿街 | 昌平县城 | 崇文门 | 菜户营 | 厂洼 | 承德 | 长阳 | | 城子 | 昌平其它 | CBD | 常营 | 朝青 | 朝阳公园 | 朝阳门 | 菜户营 | | 草桥 | 成寿寺 | 成寿寺 | 长辛店 | 窦店 | 大榆树 | 东戴河 | 大峪 | | 东辛房 | 灯市口 | 德胜门 | 东单 | 东花市 | 地安门 | 大厂 | 东四 | | 大城 | 定慧寺 | 东四十条 | 东直门 | 大兴其它 | 东高地 | 大山子 | 大望路 | | 定福庄 | 东八里庄 | 东坝 | 东大桥 | 豆各庄 | 大红门 | 东高地 | 德胜门 | | 东直门 | 二里庄 | 房山城关 | 阜成门 | 房山其它 | 垡头 | 方庄 | 丰台其它 | | 鼓楼 | 高井 | 果园 | 高米店 | 观音寺 | 古城 | 官园 | 高碑店 | | 甘家口 | 固安 | 广安门 | 公主坟 | 广渠门内 | 工体 | 广渠门 | 甘露园 | | 高碑店 | 工体 | 管庄 | 广渠门 | 国贸 | 国展 | 怀柔城区 | 后沙峪 | | 韩村河 | 回龙观 | 海南 | 河滩 | 霍营 | 怀柔其它 | 黄村北 | 黄村东 | | 黄村火车站 | 黄村南 | 怀来 | 航天桥 | 和平里 | 花园桥 | 海淀其它 | 红庙 | | 华威 | 欢乐谷 | 惠新西街 | 和义 | 花乡 | 和平里 | 金海湖 | 九棵树 | | 金顶街 | 旧宫 | 金融街 | 蓟县 | 建国门内 | 蓟门桥 | 交道口 | 军博 | | 金宝街 | 建国门 | 健翔桥 | 劲松 | 酒仙桥 | 角门 | 京石高速 | 科技园区 | | 看丹桥 | 科技园区 | 李桥 | 良乡 | 琉璃河 | 梨园 | 立水桥 | 临河里 | | 老山 | 鲁谷 | 潞苑南大街 | 龙域 | 龙泽 | 六铺炕 | 廊坊 | 六里桥 | | 来广营 | 亮马桥 | 丽泽桥 | 刘家窑 | 六里桥 | 卢沟桥 | 立水桥 | 庙城 | | 马坊 | 马坡 | 密云果园 | 密云水库别墅区 | 密云其它 | 马驹桥 | 门头沟其它 | 马连道 | | 木樨地 | 马甸 | 马连洼 | 牡丹园 | 马家堡 | 木樨园 | 马连道 | 南口 | | 南中轴机场商务区 | 南邵 | 牛街 | 平谷城区 | 平谷其它 | 苹果园 | 庞各庄 | 蒲黄榆 | | 潘家园 | 蒲黄榆 | 桥梓 | 青龙湖 | 乔庄 | 秦皇岛 | 前门 | 清河 | | 七里庄 | 青塔 | 首都机场 | 顺义城 | 沙河水库 | 少年宫 | 双峪 | 顺义其它 | | 石景山其它 | 沙河 | 生物医药基地 | 三河 | 三里河 | 宋庄 | 上地 | 上庄 | | 世纪城 | 曙光 | 双榆树 | 四季青 | 苏州桥 | 三里屯 | 三元桥 | 芍药居 | | 十八里店 | 十里堡 | 十里河 | 石佛营 | 双井 | 双桥 | 四惠 | 孙河 | | 首都机场 | 宋家庄 | 宋家庄 | 天竺 | 通州北苑 | 天通苑 | 唐山 | 通州其它 | | 陶然亭 | 天坛 | 天宁寺 | 天桥 | 田村 | 太阳宫 | 甜水园 | 团结湖 | | 太平桥 | 威海 | 万达 | 武夷花园 | 文安 | 武清 | 王府井 | 万柳 | | 万泉河 | 万寿路 | 魏公村 | 温泉镇 | 五道口 | 五棵松 | 望京 | 五里店 | | 西红门 | 小汤山 | 西三旗 | 香河 | 西单 | 西四 | 西直门 | 新街口 | | 宣武门 | 西北旺 | 西二旗 | 西三旗 | 西山 | 西直门外 | 香山 | 小西天 | | 学院路 | 西直门 | 西坝河 | 小红门 | 西罗园 | 新宫 | 燕郊 | 延庆城区 | | 渔阳 | 雁栖 | 延庆其它 | 烟台 | 阎村 | 永定 | 杨镇 | 燕山 | | 杨庄 | 玉泉路 | 玉桥 | 义和庄 | 运河大街 | 阳坊 | 亦庄 | 瀛海 | | 亦庄 | 榆垡 | 永定门 | 易县 | 永清 | 右安门内 | 月坛 | 颐和园 | | 永定路 | 玉泉路 | 圆明园 | 亚运村 | 亚运村小营 | 燕莎 | 洋桥 | 右安门外 | | 玉泉营 | 岳各庄 | 云岗 | 张山营 | 中央别墅区 | 周口店 | 枣园 | 左安门 | | 张家口 | 涿州 | 皂君庙 | 增光路 | 知春路 | 中关村 | 紫竹桥 | 中央别墅区 | | 赵公口 | 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下 房天下北京租房网：楼盘大全租房用户关注游天下短租房 **B**北京租房**D**东莞租房海南租房南宁租房沈阳租房 **C**成都租房大连租房合肥租房**Q**青岛租房**T**天津租房 重庆租房**F**福州租房**J**济南租房**S**上海租房**W**武汉租房 长沙租房**G**广州租房**N**南京租房深圳租房无锡租房 长春租房贵阳租房南昌租房苏州租房**X**西安租房 常州租房**H**杭州租房宁波租房石家庄租房**Z**郑州租房 进入房天下租房&gt; Copyright ©2026 北京搜房科技发展有限公司 Beijing SouFun Science&amp;Technology Development Co.,Ltd 版权所有 违法和不良信息举报电话：010-56318764 举报邮箱：jubao@fang.com。；# 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝 [](http://bj.bendibao.com/) * 本地民生 * 办事 * 社保 * 公积金 * 居住证 * 交通 * 地铁 * 旅游 * 景点 * 活动 * 教育 * 网点 * 招聘 * 特惠 北京 [](http://www.bendibao.com/city.htm) 首页 下载app * 办事指南 * 社保 * 公积金 * 出入境 * 车辆 * 户籍 * 教育 * 婚育 * 房产 * 医疗 * 生活 * 企业 * 其他 办事直通车 北京本地宝&gt;办事指南&gt;北京土地房产&gt;北京公共租赁房&gt;北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 2023-11-15 09:23【我要纠错】 下载指南 分享至 【导语】：北京海淀区山樾嘉园公租房位置：位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；(租金单价中包含物业费，不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用) **一、项目位置及周边配套** 1、项目名称：山樾嘉园(其他名称：金隅西砂公租房) 2**、项目位置：项目位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；** 具体地址：北京市海淀区田村山南路35号院 项目位置示意图 3、交通路网及周边配套 ⑴交通路网：向北可进入阜石路，向东可通往西四环定慧寺桥，向西可通往西五环晋元桥，向南可通往长安街沿线。；交通干道：阜石路，上庄大街;</x:v>
-      </x:c>
-      <x:c r="M42" t="str"/>
+        <x:v>通勤：临近地铁16号线马连洼站或18号线上地软件园站，步行约1293-1595米，周边有菊园东站等公交站；；商超：附近有志强百货超市、世纪华联超市、北京华联BHG Mall(上地店)等；；医院：周边有北京八珍堂中医医院；；餐饮、休闲：配套餐饮设施及厢黄旗公园、乡土树木园、沉妮槽下广场等场所，生活便利。</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>搜索结果中未发现明确的租房差评、风险投诉等内容，均为房源出租信息，未提及同名误命中情况。</x:v>
+      </x:c>
       <x:c r="N42" t="str">
-        <x:v>价格线索：停车管理，项目内地面车位200个，停车费150元/月；地下车位350个，停车费350元/月；前为裸辞状态，需自己交社保（上海灵活就业2238元/月；房屋质量/户型线索：# 租房-北京租房网 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝。；北京本地宝频道提供北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图有关的信息，北京海淀区山樾嘉园公租房位置：位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站。；# 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝 [](http://bj.bendibao.com/) * 本地民生 * 办事 * 社保 * 公积金 * 居住证 * 交通 * 地铁 * 旅游 * 景点 * 活动 * 教育 * 网点 * 招聘 * 特惠 北京 [](http://www.bendibao.com/city.htm) 首页 下载app * 办事指南 * 社保 * 公积金 * 出入境 * 车辆 * 户籍 * 教育 * 婚育 * 房产 * 医疗 * 生活 * 企业 * 其他 办事直通车 北京本地宝&gt;办事指南&gt;北京土地房产&gt;北京公共租赁房&gt;北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 2023-11-15 09:23【我要纠错】 下载指南 分享至 【导语】：北京海淀区山樾嘉园公租房位置：位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；(租金单价中包含物业费，不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用) **一、项目位置及周边配套** 1、项目名称：山樾嘉园(其他名称：金隅西砂公租房) 2**、项目位置：项目位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；生活便利线索：查看更多新发布的出租房源&gt;&gt; | 北京区县房源汇总 | | --- | | | | 北京朝阳出租房源汇总 | 北京海淀出租房源汇总 | 北京丰台出租房源汇总 | 北京西城出租房源汇总 | | 北京东城出租房源汇总 | 北京昌平出租房源汇总 | 北京大兴出租房源汇总 | 北京通州出租房源汇总 | | 北京房山出租房源汇总 | 北京顺义出租房源汇总 | 北京石景山出租房源汇总 | 北京密云出租房源汇总 | | 北京门头沟出租房源汇总 | 北京怀柔出租房源汇总 | 北京延庆出租房源汇总 | 北京平谷出租房源汇总 | | 北京燕郊出租房源汇总 | 北京北京周边出租房源汇总 | 北京旅游地产出租房源汇总 | | 北京商圈房源汇总 | | --- | | | | 安宁庄 | 安定门 | 安贞 | 安贞 | 奥林匹克公园 | 宾阳 | 百善镇 | 霸州 | | 八大处 | 白纸坊 | 北关 | 滨河 | 八达岭 | 北戴河 | 北海 | 北京大学 | | 八角 | 白沟 | 北七家 | 宝坻 | 北太平庄 | 保定 | 百子湾 | 北工大 | | 北沙滩 | 北苑 | 北大地 | 采育 | 次渠 | 朝阳门内 | 城子 | 磁各庄 | | 车公庄 | 长椿街 | 昌平县城 | 崇文门 | 菜户营 | 厂洼 | 承德 | 长阳 | | 城子 | 昌平其它 | CBD | 常营 | 朝青 | 朝阳公园 | 朝阳门 | 菜户营 | | 草桥 | 成寿寺 | 成寿寺 | 长辛店 | 窦店 | 大榆树 | 东戴河 | 大峪 | | 东辛房 | 灯市口 | 德胜门 | 东单 | 东花市 | 地安门 | 大厂 | 东四 | | 大城 | 定慧寺 | 东四十条 | 东直门 | 大兴其它 | 东高地 | 大山子 | 大望路 | | 定福庄 | 东八里庄 | 东坝 | 东大桥 | 豆各庄 | 大红门 | 东高地 | 德胜门 | | 东直门 | 二里庄 | 房山城关 | 阜成门 | 房山其它 | 垡头 | 方庄 | 丰台其它 | | 鼓楼 | 高井 | 果园 | 高米店 | 观音寺 | 古城 | 官园 | 高碑店 | | 甘家口 | 固安 | 广安门 | 公主坟 | 广渠门内 | 工体 | 广渠门 | 甘露园 | | 高碑店 | 工体 | 管庄 | 广渠门 | 国贸 | 国展 | 怀柔城区 | 后沙峪 | | 韩村河 | 回龙观 | 海南 | 河滩 | 霍营 | 怀柔其它 | 黄村北 | 黄村东 | | 黄村火车站 | 黄村南 | 怀来 | 航天桥 | 和平里 | 花园桥 | 海淀其它 | 红庙 | | 华威 | 欢乐谷 | 惠新西街 | 和义 | 花乡 | 和平里 | 金海湖 | 九棵树 | | 金顶街 | 旧宫 | 金融街 | 蓟县 | 建国门内 | 蓟门桥 | 交道口 | 军博 | | 金宝街 | 建国门 | 健翔桥 | 劲松 | 酒仙桥 | 角门 | 京石高速 | 科技园区 | | 看丹桥 | 科技园区 | 李桥 | 良乡 | 琉璃河 | 梨园 | 立水桥 | 临河里 | | 老山 | 鲁谷 | 潞苑南大街 | 龙域 | 龙泽 | 六铺炕 | 廊坊 | 六里桥 | | 来广营 | 亮马桥 | 丽泽桥 | 刘家窑 | 六里桥 | 卢沟桥 | 立水桥 | 庙城 | | 马坊 | 马坡 | 密云果园 | 密云水库别墅区 | 密云其它 | 马驹桥 | 门头沟其它 | 马连道 | | 木樨地 | 马甸 | 马连洼 | 牡丹园 | 马家堡 | 木樨园 | 马连道 | 南口 | | 南中轴机场商务区 | 南邵 | 牛街 | 平谷城区 | 平谷其它 | 苹果园 | 庞各庄 | 蒲黄榆 | | 潘家园 | 蒲黄榆 | 桥梓 | 青龙湖 | 乔庄 | 秦皇岛 | 前门 | 清河 | | 七里庄 | 青塔 | 首都机场 | 顺义城 | 沙河水库 | 少年宫 | 双峪 | 顺义其它 | | 石景山其它 | 沙河 | 生物医药基地 | 三河 | 三里河 | 宋庄 | 上地 | 上庄 | | 世纪城 | 曙光 | 双榆树 | 四季青 | 苏州桥 | 三里屯 | 三元桥 | 芍药居 | | 十八里店 | 十里堡 | 十里河 | 石佛营 | 双井 | 双桥 | 四惠 | 孙河 | | 首都机场 | 宋家庄 | 宋家庄 | 天竺 | 通州北苑 | 天通苑 | 唐山 | 通州其它 | | 陶然亭 | 天坛 | 天宁寺 | 天桥 | 田村 | 太阳宫 | 甜水园 | 团结湖 | | 太平桥 | 威海 | 万达 | 武夷花园 | 文安 | 武清 | 王府井 | 万柳 | | 万泉河 | 万寿路 | 魏公村 | 温泉镇 | 五道口 | 五棵松 | 望京 | 五里店 | | 西红门 | 小汤山 | 西三旗 | 香河 | 西单 | 西四 | 西直门 | 新街口 | | 宣武门 | 西北旺 | 西二旗 | 西三旗 | 西山 | 西直门外 | 香山 | 小西天 | | 学院路 | 西直门 | 西坝河 | 小红门 | 西罗园 | 新宫 | 燕郊 | 延庆城区 | | 渔阳 | 雁栖 | 延庆其它 | 烟台 | 阎村 | 永定 | 杨镇 | 燕山 | | 杨庄 | 玉泉路 | 玉桥 | 义和庄 | 运河大街 | 阳坊 | 亦庄 | 瀛海 | | 亦庄 | 榆垡 | 永定门 | 易县 | 永清 | 右安门内 | 月坛 | 颐和园 | | 永定路 | 玉泉路 | 圆明园 | 亚运村 | 亚运村小营 | 燕莎 | 洋桥 | 右安门外 | | 玉泉营 | 岳各庄 | 云岗 | 张山营 | 中央别墅区 | 周口店 | 枣园 | 左安门 | | 张家口 | 涿州 | 皂君庙 | 增光路 | 知春路 | 中关村 | 紫竹桥 | 中央别墅区 | | 赵公口 | 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下 房天下北京租房网：楼盘大全租房用户关注游天下短租房 **B**北京租房**D**东莞租房海南租房南宁租房沈阳租房 **C**成都租房大连租房合肥租房**Q**青岛租房**T**天津租房 重庆租房**F**福州租房**J**济南租房**S**上海租房**W**武汉租房 长沙租房**G**广州租房**N**南京租房深圳租房无锡租房 长春租房贵阳租房南昌租房苏州租房**X**西安租房 常州租房**H**杭州租房宁波租房石家庄租房**Z**郑州租房 进入房天下租房&gt; Copyright ©2026 北京搜房科技发展有限公司 Beijing SouFun Science&amp;Technology Development Co.,Ltd 版权所有 违法和不良信息举报电话：010-56318764 举报邮箱：jubao@fang.com。；# 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝 [](http://bj.bendibao.com/) * 本地民生 * 办事 * 社保 * 公积金 * 居住证 * 交通 * 地铁 * 旅游 * 景点 * 活动 * 教育 * 网点 * 招聘 * 特惠 北京 [](http://www.bendibao.com/city.htm) 首页 下载app * 办事指南 * 社保 * 公积金 * 出入境 * 车辆 * 户籍 * 教育 * 婚育 * 房产 * 医疗 * 生活 * 企业 * 其他 办事直通车 北京本地宝&gt;办事指南&gt;北京土地房产&gt;北京公共租赁房&gt;北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 2023-11-15 09:23【我要纠错】 下载指南 分享至 【导语】：北京海淀区山樾嘉园公租房位置：位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；(租金单价中包含物业费，不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用) **一、项目位置及周边配套** 1、项目名称：山樾嘉园(其他名称：金隅西砂公租房) 2**、项目位置：项目位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；** 具体地址：北京市海淀区田村山南路35号院 项目位置示意图 3、交通路网及周边配套 ⑴交通路网：向北可进入阜石路，向东可通往西四环定慧寺桥，向西可通往西五环晋元桥，向南可通往长安街沿线。；交通干道：阜石路，上庄大街;</x:v>
+        <x:v>价格线索：万德嘉园租房价格：合租次卧13平米2000元/月；、15平米2500元/月；整租1室1厅42平米5100元/月；、1室0厅50平米5000元/月；、2室1厅80平米7200元/月；（或7600元/月；）、3室1厅80平米8000元/月；房屋质量/户型线索：小区为普通住宅，房龄未明确提及；；装修多为精装修；；户型有单间、1室1厅、2室1厅、3室1厅，南北通透户型采光通风较好；；物业信息未在搜索结果中明确；；未找到关于隔音的相关评价。；生活便利线索：通勤：临近地铁16号线马连洼站或18号线上地软件园站，步行约1293-1595米，周边有菊园东站等公交站；；商超：附近有志强百货超市、世纪华联超市、北京华联BHG Mall(上地店)等；；医院：周边有北京八珍堂中医医院；；餐饮、休闲：配套餐饮设施及厢黄旗公园、乡土树木园、沉妮槽下广场等场所，生活便利。；风险线索：搜索结果中未发现明确的租房差评、风险投诉等内容，均为房源出租信息，未提及同名误命中情况。</x:v>
       </x:c>
       <x:c r="O42" t="str">
-        <x:v>1. 北京万德嘉园二区二手房|房价 - 贝壳 https://m.ke.com/bj/xiaoqu/11000000066519
-2. 租房-北京租房网 https://zu.fang.com/chuzu/3_486109404_1.htm
-3. 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝 http://bj.bendibao.com/zffw/20231115/353693.shtm
-4. 讨论精选（豆瓣） https://www.douban.com/group/explore</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4580072526289930-3/
+2. http://m.anjuke.com/bj/rent/4568648902122510-3/
+3. http://m.anjuke.com/bj/rent/4580114081997836-3/
+4. http://m.anjuke.com/bj/rent/4211696277430272-3/
+5. http://m.anjuke.com/bj/rent/4585827618380805-3/
+6. http://m.anjuke.com/bj/rent/4603975384099845-3/
+7. http://m.anjuke.com/bj/rent/4554111046605827-3/
+8. 万德嘉园全女生 可短签月付近马连洼上地软件园清河农大金隅嘉华 http://m.anjuke.com/bj/rent/4580072526289930-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2292,41 +2418,42 @@
         <x:v>北京市海淀区西北旺镇友谊路与北清路交叉口西北角</x:v>
       </x:c>
       <x:c r="E43" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F43" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G43" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H43" t="n">
-        <x:v>8.5</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>高品质次新房，一居约5200元，价格透明且品质优越，非常适合网易员工。</x:v>
+        <x:v>房屋品质极佳的次新高端小区，但租金昂贵且离地铁较远，通勤便利性相对一般。</x:v>
       </x:c>
       <x:c r="J43" t="str">
-        <x:v>福里主力户型为145-195㎡，价格约为84000元/㎡；0:40:00 * 海淀幸福里最新价格约84000元/㎡；:00 * 海淀幸福里三居室、四居室，约84000元/㎡；7:00 * 海淀幸福里最新价格公布，约84000元/㎡；00 * 海淀幸福里润园最新价格公布，约82000元/㎡； 元/㎡ 楼盘概述：海淀幸福里，新房价格85500元/㎡；三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月</x:v>
+        <x:v>整租房源月租约9500元/月；（3室2厅2卫110㎡）、13500元/月；（4室2厅149㎡），商铺月租金6.66万/月</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>北京海淀幸福里售楼处电话号码:400-7638-577转009546，为您提供北京海淀幸福里最新价格、图片、户型、交通及周边配套、业主论坛。；# 海淀幸福里_北京海淀幸福里价格_售楼处电话_怎么样 - 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 新房 北京 北京买房_&gt;_北京新房_&gt;_海淀新房_&gt;_海淀幸福里 更新于 2026-06-03 17:46:02 [](https://bj.jiwu.com/loupan/1665114.html) [](https://bj.jiwu.com/tu/list-loupan1283829-baid12560527.html "海淀幸福里效果图")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560519.html "海淀幸福里实景图")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560520.html "海淀幸福里样板间")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560524.html "海淀幸福里配套图")[](https://bj.jiwu.com/video/1283829.html "海淀幸福里视频看房") 预售证号：京(2023)海不动产权第0021771号查看全部图片(58) * _效果图(21)_ * _实景图(4)_ * _样板间(22)_ * _配套图(1)_ * _视频看房_ # 海淀幸福里 别名：毓润嘉园 加入本地买房群 关注 在售 住宅 品牌地产 自持商业 参考均价 _85500 \_元/㎡\__ 价格有效期：2026.05.19-2026.06.18 降价通知 咨询底价 楼盘户型 _4室(3)_ 余房查询 成交价查询 最近开盘 _2023-12-31_ 新开盘通知 楼盘地址 _北京海淀区永丰北清路和友谊路交叉口西北角_ 发地址到手机 人多力量大，一起组团砍价 _已有426人报名_ 组团砍价 北京买房群 _3137 人正在讨论北京楼市_ 加入群聊 微信扫码拨号 4007638577 _转_ 009546 致电售楼现场，了解更多优惠信息 * 楼盘主页 * 楼盘信息 * 楼盘评测 * 户型图 * 楼盘相册 * 交通配套 * 价格走势 * 楼盘动态 * 楼盘问答 北京买房交流群-65群（436） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 楼盘户型 4室(3) 全部户型 [](https://bj.jiwu.com/huxing/2976436.html "海淀幸福里4室2厅3卫195㎡户型图")在售4室2厅3卫 195㎡ 约 1600万 咨询底价 [](https://bj.jiwu.com/huxing/2976434.html "海淀幸福里4室2厅2卫145㎡户型图")在售4室2厅2卫 145㎡ 约 1150万 咨询底价 [](https://bj.jiwu.com/huxing/2976431.html "海淀幸福里4室2厅3卫165㎡户型图")在售4室2厅3卫 165㎡ 约 1414万 咨询底价 楼盘评测报告 8.3 分 综合评分 楼盘品质 9 社区配套 8 区域价值 8 海淀好评榜 17 名，超过海淀 15%的楼盘 1、由首开、北科建集团、华润置地、中交地产、北京住总地产五大实力国匠联袂打造2、择址海淀中关村科学城北区，科创产业的高地，发展势能充足3、7大健康管理系统、3大智慧管理系统，品质生活4、由华润置地旗下的华润物业提供物业服务，保障舒心生活 报告剩余2页 查看完整楼盘评测报告，楼盘优劣全知道 查看报告 楼盘动态 全部动态 * 近期 踩盘 近7天有置业管家实勘本盘 咨询 * 2023-09-22 在售更多海淀幸福里项目位于北京市海淀区北清路与友谊路交叉口西北角，在售住宅产品，70年产权。；户型为建面145平四居、建面165平四居、建面195平四居。；订阅楼盘最新动态，优惠、开盘早知道 订阅动态 问问楼盘置业管家 * 现在在卖的有什么户型？</x:v>
+        <x:v>房龄约2020年建成，2023年交付；；户型主打89-130㎡三居、145-188㎡四居，南北板楼；；双中空玻璃，隔音、防潮防霉效果好；；华润自持物业，物业费7.2元/㎡/月，24小时管家式服务，人车分流，车位配比1:1.2；</x:v>
       </x:c>
       <x:c r="L43" t="str">
-        <x:v>北京海淀幸福里售楼处电话号码:400-7638-577转009546，为您提供北京海淀幸福里最新价格、图片、户型、交通及周边配套、业主论坛。；# 海淀幸福里_北京海淀幸福里价格_售楼处电话_怎么样 - 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 新房 北京 北京买房_&gt;_北京新房_&gt;_海淀新房_&gt;_海淀幸福里 更新于 2026-06-03 17:46:02 [](https://bj.jiwu.com/loupan/1665114.html) [](https://bj.jiwu.com/tu/list-loupan1283829-baid12560527.html "海淀幸福里效果图")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560519.html "海淀幸福里实景图")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560520.html "海淀幸福里样板间")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560524.html "海淀幸福里配套图")[](https://bj.jiwu.com/video/1283829.html "海淀幸福里视频看房") 预售证号：京(2023)海不动产权第0021771号查看全部图片(58) * _效果图(21)_ * _实景图(4)_ * _样板间(22)_ * _配套图(1)_ * _视频看房_ # 海淀幸福里 别名：毓润嘉园 加入本地买房群 关注 在售 住宅 品牌地产 自持商业 参考均价 _85500 \_元/㎡\__ 价格有效期：2026.05.19-2026.06.18 降价通知 咨询底价 楼盘户型 _4室(3)_ 余房查询 成交价查询 最近开盘 _2023-12-31_ 新开盘通知 楼盘地址 _北京海淀区永丰北清路和友谊路交叉口西北角_ 发地址到手机 人多力量大，一起组团砍价 _已有426人报名_ 组团砍价 北京买房群 _3137 人正在讨论北京楼市_ 加入群聊 微信扫码拨号 4007638577 _转_ 009546 致电售楼现场，了解更多优惠信息 * 楼盘主页 * 楼盘信息 * 楼盘评测 * 户型图 * 楼盘相册 * 交通配套 * 价格走势 * 楼盘动态 * 楼盘问答 北京买房交流群-65群（436） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 楼盘户型 4室(3) 全部户型 [](https://bj.jiwu.com/huxing/2976436.html "海淀幸福里4室2厅3卫195㎡户型图")在售4室2厅3卫 195㎡ 约 1600万 咨询底价 [](https://bj.jiwu.com/huxing/2976434.html "海淀幸福里4室2厅2卫145㎡户型图")在售4室2厅2卫 145㎡ 约 1150万 咨询底价 [](https://bj.jiwu.com/huxing/2976431.html "海淀幸福里4室2厅3卫165㎡户型图")在售4室2厅3卫 165㎡ 约 1414万 咨询底价 楼盘评测报告 8.3 分 综合评分 楼盘品质 9 社区配套 8 区域价值 8 海淀好评榜 17 名，超过海淀 15%的楼盘 1、由首开、北科建集团、华润置地、中交地产、北京住总地产五大实力国匠联袂打造2、择址海淀中关村科学城北区，科创产业的高地，发展势能充足3、7大健康管理系统、3大智慧管理系统，品质生活4、由华润置地旗下的华润物业提供物业服务，保障舒心生活 报告剩余2页 查看完整楼盘评测报告，楼盘优劣全知道 查看报告 楼盘动态 全部动态 * 近期 踩盘 近7天有置业管家实勘本盘 咨询 * 2023-09-22 在售更多海淀幸福里项目位于北京市海淀区北清路与友谊路交叉口西北角，在售住宅产品，70年产权。；南北通透户型带精装，华润物业加持，交通、教育、医疗配套完善，生活品质拉满。</x:v>
-      </x:c>
-      <x:c r="M43" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
-      </x:c>
+        <x:v>距离地铁16号线永丰站约2.2公里；；周边有384、543等多条公交；；邻近北大国际医院、清华附中永丰学校；；有翠湖湿地公园等休闲场所，商超、餐饮等生活配套需进一步完善；；距离地铁较远，公共交通依赖公交，便利性一般。</x:v>
+      </x:c>
+      <x:c r="M43" t="str"/>
       <x:c r="N43" t="str">
-        <x:v>价格线索：福里主力户型为145-195㎡，价格约为84000元/㎡；0:40:00 * 海淀幸福里最新价格约84000元/㎡；:00 * 海淀幸福里三居室、四居室，约84000元/㎡；7:00 * 海淀幸福里最新价格公布，约84000元/㎡；00 * 海淀幸福里润园最新价格公布，约82000元/㎡； 元/㎡ 楼盘概述：海淀幸福里，新房价格85500元/㎡；三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；房屋质量/户型线索：北京海淀幸福里售楼处电话号码:400-7638-577转009546，为您提供北京海淀幸福里最新价格、图片、户型、交通及周边配套、业主论坛。；# 海淀幸福里_北京海淀幸福里价格_售楼处电话_怎么样 - 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 新房 北京 北京买房_&gt;_北京新房_&gt;_海淀新房_&gt;_海淀幸福里 更新于 2026-06-03 17:46:02 [](https://bj.jiwu.com/loupan/1665114.html) [](https://bj.jiwu.com/tu/list-loupan1283829-baid12560527.html "海淀幸福里效果图")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560519.html "海淀幸福里实景图")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560520.html "海淀幸福里样板间")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560524.html "海淀幸福里配套图")[](https://bj.jiwu.com/video/1283829.html "海淀幸福里视频看房") 预售证号：京(2023)海不动产权第0021771号查看全部图片(58) * _效果图(21)_ * _实景图(4)_ * _样板间(22)_ * _配套图(1)_ * _视频看房_ # 海淀幸福里 别名：毓润嘉园 加入本地买房群 关注 在售 住宅 品牌地产 自持商业 参考均价 _85500 \_元/㎡\__ 价格有效期：2026.05.19-2026.06.18 降价通知 咨询底价 楼盘户型 _4室(3)_ 余房查询 成交价查询 最近开盘 _2023-12-31_ 新开盘通知 楼盘地址 _北京海淀区永丰北清路和友谊路交叉口西北角_ 发地址到手机 人多力量大，一起组团砍价 _已有426人报名_ 组团砍价 北京买房群 _3137 人正在讨论北京楼市_ 加入群聊 微信扫码拨号 4007638577 _转_ 009546 致电售楼现场，了解更多优惠信息 * 楼盘主页 * 楼盘信息 * 楼盘评测 * 户型图 * 楼盘相册 * 交通配套 * 价格走势 * 楼盘动态 * 楼盘问答 北京买房交流群-65群（436） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 楼盘户型 4室(3) 全部户型 [](https://bj.jiwu.com/huxing/2976436.html "海淀幸福里4室2厅3卫195㎡户型图")在售4室2厅3卫 195㎡ 约 1600万 咨询底价 [](https://bj.jiwu.com/huxing/2976434.html "海淀幸福里4室2厅2卫145㎡户型图")在售4室2厅2卫 145㎡ 约 1150万 咨询底价 [](https://bj.jiwu.com/huxing/2976431.html "海淀幸福里4室2厅3卫165㎡户型图")在售4室2厅3卫 165㎡ 约 1414万 咨询底价 楼盘评测报告 8.3 分 综合评分 楼盘品质 9 社区配套 8 区域价值 8 海淀好评榜 17 名，超过海淀 15%的楼盘 1、由首开、北科建集团、华润置地、中交地产、北京住总地产五大实力国匠联袂打造2、择址海淀中关村科学城北区，科创产业的高地，发展势能充足3、7大健康管理系统、3大智慧管理系统，品质生活4、由华润置地旗下的华润物业提供物业服务，保障舒心生活 报告剩余2页 查看完整楼盘评测报告，楼盘优劣全知道 查看报告 楼盘动态 全部动态 * 近期 踩盘 近7天有置业管家实勘本盘 咨询 * 2023-09-22 在售更多海淀幸福里项目位于北京市海淀区北清路与友谊路交叉口西北角，在售住宅产品，70年产权。；户型为建面145平四居、建面165平四居、建面195平四居。；订阅楼盘最新动态，优惠、开盘早知道 订阅动态 问问楼盘置业管家 * 现在在卖的有什么户型？；生活便利线索：北京海淀幸福里售楼处电话号码:400-7638-577转009546，为您提供北京海淀幸福里最新价格、图片、户型、交通及周边配套、业主论坛。；# 海淀幸福里_北京海淀幸福里价格_售楼处电话_怎么样 - 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 新房 北京 北京买房_&gt;_北京新房_&gt;_海淀新房_&gt;_海淀幸福里 更新于 2026-06-03 17:46:02 [](https://bj.jiwu.com/loupan/1665114.html) [](https://bj.jiwu.com/tu/list-loupan1283829-baid12560527.html "海淀幸福里效果图")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560519.html "海淀幸福里实景图")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560520.html "海淀幸福里样板间")[](https://bj.jiwu.com/tu/list-loupan1283829-baid12560524.html "海淀幸福里配套图")[](https://bj.jiwu.com/video/1283829.html "海淀幸福里视频看房") 预售证号：京(2023)海不动产权第0021771号查看全部图片(58) * _效果图(21)_ * _实景图(4)_ * _样板间(22)_ * _配套图(1)_ * _视频看房_ # 海淀幸福里 别名：毓润嘉园 加入本地买房群 关注 在售 住宅 品牌地产 自持商业 参考均价 _85500 \_元/㎡\__ 价格有效期：2026.05.19-2026.06.18 降价通知 咨询底价 楼盘户型 _4室(3)_ 余房查询 成交价查询 最近开盘 _2023-12-31_ 新开盘通知 楼盘地址 _北京海淀区永丰北清路和友谊路交叉口西北角_ 发地址到手机 人多力量大，一起组团砍价 _已有426人报名_ 组团砍价 北京买房群 _3137 人正在讨论北京楼市_ 加入群聊 微信扫码拨号 4007638577 _转_ 009546 致电售楼现场，了解更多优惠信息 * 楼盘主页 * 楼盘信息 * 楼盘评测 * 户型图 * 楼盘相册 * 交通配套 * 价格走势 * 楼盘动态 * 楼盘问答 北京买房交流群-65群（436） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 楼盘户型 4室(3) 全部户型 [](https://bj.jiwu.com/huxing/2976436.html "海淀幸福里4室2厅3卫195㎡户型图")在售4室2厅3卫 195㎡ 约 1600万 咨询底价 [](https://bj.jiwu.com/huxing/2976434.html "海淀幸福里4室2厅2卫145㎡户型图")在售4室2厅2卫 145㎡ 约 1150万 咨询底价 [](https://bj.jiwu.com/huxing/2976431.html "海淀幸福里4室2厅3卫165㎡户型图")在售4室2厅3卫 165㎡ 约 1414万 咨询底价 楼盘评测报告 8.3 分 综合评分 楼盘品质 9 社区配套 8 区域价值 8 海淀好评榜 17 名，超过海淀 15%的楼盘 1、由首开、北科建集团、华润置地、中交地产、北京住总地产五大实力国匠联袂打造2、择址海淀中关村科学城北区，科创产业的高地，发展势能充足3、7大健康管理系统、3大智慧管理系统，品质生活4、由华润置地旗下的华润物业提供物业服务，保障舒心生活 报告剩余2页 查看完整楼盘评测报告，楼盘优劣全知道 查看报告 楼盘动态 全部动态 * 近期 踩盘 近7天有置业管家实勘本盘 咨询 * 2023-09-22 在售更多海淀幸福里项目位于北京市海淀区北清路与友谊路交叉口西北角，在售住宅产品，70年产权。；南北通透户型带精装，华润物业加持，交通、教育、医疗配套完善，生活品质拉满。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：整租房源月租约9500元/月；（3室2厅2卫110㎡）、13500元/月；（4室2厅149㎡），商铺月租金6.66万/月；房屋质量/户型线索：房龄约2020年建成，2023年交付；；户型主打89-130㎡三居、145-188㎡四居，南北板楼；；双中空玻璃，隔音、防潮防霉效果好；；华润自持物业，物业费7.2元/㎡/月，24小时管家式服务，人车分流，车位配比1:1.2；；生活便利线索：距离地铁16号线永丰站约2.2公里；；周边有384、543等多条公交；；邻近北大国际医院、清华附中永丰学校；；有翠湖湿地公园等休闲场所，商超、餐饮等生活配套需进一步完善；；距离地铁较远，公共交通依赖公交，便利性一般。</x:v>
       </x:c>
       <x:c r="O43" t="str">
-        <x:v>1. 海淀幸福里_北京海淀幸福里价格_售楼处电话_怎么样 - 北京吉屋网 https://bj.jiwu.com/loupan/1283829.html
-2. 【北京海淀幸福里小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010128601.htm
-3. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-4. 北京房产网_北京二手房|租房|新房|房地产信息网【北京贝壳找房】 https://ke.com/
-5. 幸福里(海淀)二手房房价走势,北京幸福里(海淀)二手房出售、租房价格-北京安居客 https://mobile.anjuke.com/esf/bj-cm1690934/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/sp/zu/d4479368101782530
+2. http://m.anjuke.com/bj/community/1419646/jiedu/
+3. https://i.haoduofangs.com/xiaoqu/bj-7362386336315244582.html
+4. https://m.lianjia.com/news/bj/xiaoqu/1120053618049262.html
+5. http://m.fang.com/zf/bj/8_1000037211.html
+6. 出租丨海淀幸福里北区旺铺房东直租 http://m.anjuke.com/bj/sp/zu/d4479368101782530/?houseid=4479368101782530
+7. 海淀幸福里优点、不足，海淀幸福里怎么样，海淀幸福里周边房产中介经纪人评价-北京安居客 http://m.anjuke.com/bj/community/1419646/jiedu/
+8. 海淀幸福里 https://i.haoduofangs.com/xiaoqu/bj-7362386336315244582.html</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2343,39 +2470,44 @@
         <x:v>北京市海淀区竹园中街西山华府禧园</x:v>
       </x:c>
       <x:c r="E44" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F44" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G44" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H44" t="n">
-        <x:v>4.5</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="I44" t="str">
-        <x:v>证据受顶级豪宅及办公租赁信息严重干扰，租金门槛极高，参考价值有限。</x:v>
+        <x:v>万科物业品质保障，居住环境安静且配套完善，适合预算充足、追求生活品质的人群。</x:v>
       </x:c>
       <x:c r="J44" t="str">
-        <x:v>可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；95000 元/月；115000 元/月；可注册办公首次出租南北通透 180000 元/月；可注册办公首次出租南北通透 210000 元/月；138000 元/月；可注册办公首次出租南北通透 10500 元/月</x:v>
+        <x:v>整租两居月租约10500-13000元/月；，整租五居约32000元/月</x:v>
       </x:c>
       <x:c r="K44" t="str">
-        <x:v>可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 距14号线枣营站约724米。；95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 距14号线枣营站约724米。；可注册办公首次出租南北通透 210000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；85000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 距2号线安定门站约310米。；35500 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。</x:v>
+        <x:v>不同户型面积对应租金有差异，付款方式多为押一付三；；小区2006/2008/2011年建成（不同数据），物业为北京万科物业管理有限公司；；建筑类型为板楼，部分房源精装修；；房源反馈居住安静，人文素质较高，但搜索结果未明确提及隔音、户型细节短板；</x:v>
       </x:c>
       <x:c r="L44" t="str">
-        <x:v>85000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 距2号线安定门站约310米。；万能小维 13K views • 3 days ago Live Playlist ()Mix (50+)13:56 回京感受生活五个难,明白为何越来越多人离开北京了,喜欢不起来的首都(小叔TV EP336)小叔TV 325K views • 1 year ago Live Playlist ()Mix (50+) Sign in to confirm you’re not a bot This helps protect our community. Learn more Sign in # 北京二手房降幅多大?；不是为了高考的便利，北京的户口还不一定有人要 控制人口数量，蔡奇可以说是熟练的 Show less Read more Like 86 Dislike Reply 1 reply Hide replies 1 reply ### @LUCKYXIAOYU 2 years ago 如果外面投资国内花，还要考虑货币贬值的因素，不一定就比国内投资好 Show less Read more Like 2 Dislike Reply ### @petercao7847 2 years ago 9:35 业主的口风就是不一样啊。；万能小维 13K views • 3 days ago New 13:56 ### 回京感受生活五个难,明白为何越来越多人离开北京了,喜欢不起来的首都(小叔TV EP336) 小叔TV 325K views • 1 year ago 14:46 ### ��隆·马斯克刚刚公布了全球首座100GW太阳能工厂！</x:v>
+        <x:v>周边有328路、362路等多条公交，临近地铁（未明确具体线路）；；商超有美廉美超市、中发百旺商城，东北门有新发地配菜车；；医院有309医院、西苑医院等；；餐饮有小区地下美食城；；生活配套较完善；</x:v>
       </x:c>
       <x:c r="M44" t="str">
-        <x:v>16000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 距10号线三元桥站约662米。；我北京中上产朋友也都要出国了 Show less Read more Like 25 Dislike Reply 4 replies Hide replies 4 replies ### @user-yangliu2024 2 years ago 北京的拥堵不是因为人口多，而是管理水平低下所致 Show less Read more Like 38 Dislike Reply 5 replies Hide replies 5 replies ### @rurenyinshui 2 years ago 我记得96年六里桥儿的房价是680一平米起…那时候儿胡同儿里到处都是宣传单 后来又有1280的 再后来就越来越没边儿了 Show less Read more Like 3 Dislike Reply ### @CountrysideFreeCloud 2 years ago 又看到一片優質影片, 見見海外不同的風景!</x:v>
+        <x:v>无明确差评风险提及，无同名误命中信息。；无明确差评风险提及，无同名误命中信息</x:v>
       </x:c>
       <x:c r="N44" t="str">
-        <x:v>价格线索：可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；95000 元/月；115000 元/月；可注册办公首次出租南北通透 180000 元/月；可注册办公首次出租南北通透 210000 元/月；138000 元/月；可注册办公首次出租南北通透 10500 元/月；房屋质量/户型线索：可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 距14号线枣营站约724米。；95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 距14号线枣营站约724米。；可注册办公首次出租南北通透 210000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；85000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 距2号线安定门站约310米。；35500 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；生活便利线索：85000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 距2号线安定门站约310米。；万能小维 13K views • 3 days ago Live Playlist ()Mix (50+)13:56 回京感受生活五个难,明白为何越来越多人离开北京了,喜欢不起来的首都(小叔TV EP336)小叔TV 325K views • 1 year ago Live Playlist ()Mix (50+) Sign in to confirm you’re not a bot This helps protect our community. Learn more Sign in # 北京二手房降幅多大?；不是为了高考的便利，北京的户口还不一定有人要 控制人口数量，蔡奇可以说是熟练的 Show less Read more Like 86 Dislike Reply 1 reply Hide replies 1 reply ### @LUCKYXIAOYU 2 years ago 如果外面投资国内花，还要考虑货币贬值的因素，不一定就比国内投资好 Show less Read more Like 2 Dislike Reply ### @petercao7847 2 years ago 9:35 业主的口风就是不一样啊。；万能小维 13K views • 3 days ago New 13:56 ### 回京感受生活五个难,明白为何越来越多人离开北京了,喜欢不起来的首都(小叔TV EP336) 小叔TV 325K views • 1 year ago 14:46 ### ��隆·马斯克刚刚公布了全球首座100GW太阳能工厂！；风险线索：16000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 距10号线三元桥站约662米。；我北京中上产朋友也都要出国了 Show less Read more Like 25 Dislike Reply 4 replies Hide replies 4 replies ### @user-yangliu2024 2 years ago 北京的拥堵不是因为人口多，而是管理水平低下所致 Show less Read more Like 38 Dislike Reply 5 replies Hide replies 5 replies ### @rurenyinshui 2 years ago 我记得96年六里桥儿的房价是680一平米起…那时候儿胡同儿里到处都是宣传单 后来又有1280的 再后来就越来越没边儿了 Show less Read more Like 3 Dislike Reply ### @CountrysideFreeCloud 2 years ago 又看到一片優質影片, 見見海外不同的風景!</x:v>
+        <x:v>价格线索：整租两居月租约10500-13000元/月；，整租五居约32000元/月；房屋质量/户型线索：不同户型面积对应租金有差异，付款方式多为押一付三；；小区2006/2008/2011年建成（不同数据），物业为北京万科物业管理有限公司；；建筑类型为板楼，部分房源精装修；；房源反馈居住安静，人文素质较高，但搜索结果未明确提及隔音、户型细节短板；；生活便利线索：周边有328路、362路等多条公交，临近地铁（未明确具体线路）；；商超有美廉美超市、中发百旺商城，东北门有新发地配菜车；；医院有309医院、西苑医院等；；餐饮有小区地下美食城；；生活配套较完善；；风险线索：无明确差评风险提及，无同名误命中信息。；无明确差评风险提及，无同名误命中信息</x:v>
       </x:c>
       <x:c r="O44" t="str">
-        <x:v>1. 【北京租房信息_房屋出租】- 房天下 https://fang.com/houses/zf_253293bj/c20-d23000-h38-i370/c20-d23000-h38
-2. 北京二手房降幅多大?朋友亏百万也要卖房,进京门槛却越筑越高,游雅加达有感(小叔TV EP317) - YouTube https://www.youtube.com/watch?v=qIvrATsSfdk
-3. 1740021979080048337.pdf https://www.bjxch.gov.cn/file/20250220/1740021979080048337.pdf</x:v>
+        <x:v>1. http://m.fang.com/zf/bj/8_1003495083.html
+2. https://m.5i5j.com/bj/xq_news/105580.html
+3. http://m.fang.com/zf/bj/3_486013676.html
+4. 西山华府2室2厅2卫南北朝向13000.00元/月出租 http://m.fang.com/zf/bj/8_1003495083.html
+5. 西城华府 2室1厅1卫 http://m.anjuke.com/jn/rent/4575685285323787/
+6. 西山华府禧园怎么样?北京西山华府禧园房价|房源|地址|户型图|周边配套详情 https://m.5i5j.com/bj/xq_news/105580.html
+7. 【西山华府租房子 https://m.fang.com/zf/bj_xm1010257223/p6/?jhtype=zf
+8. 2室1厅西山华府禧园 http://m.fang.com/zf/bj/3_486013676.html</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -2392,41 +2524,42 @@
         <x:v>北京市海淀区龙背村路6号</x:v>
       </x:c>
       <x:c r="E45" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F45" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G45" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H45" t="n">
-        <x:v>7.8</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="I45" t="str">
-        <x:v>2009年成熟社区，一居5200元起，价格梯度明确且房源充足，居住属性强。</x:v>
-      </x:c>
-      <x:c r="J45" t="str">
-        <x:v>3000_ 元/m² 颐北家苑，小区价格67785元/㎡；三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月</x:v>
-      </x:c>
+        <x:v>离地铁站较近，生活配套与医疗资源优越，但因缺失租金参考，建议实地询价后决策。</x:v>
+      </x:c>
+      <x:c r="J45" t="str"/>
       <x:c r="K45" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010678989/photo/) [](https://esf.fang.com/loupan/1010678989/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **59134** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓1.0% 贷款计算器 * 二手房源 0套 * 最近成交 0套 * 楼栋总数 17栋 * 房屋总数 1200户 * 建筑类型 板楼 * 建筑年代 2009年建成 * 小区位置 龙背村路6号地图 * 物业公司 团河苑小区物业 * 开发商 石家庄市金鱼房地产开发有限公司 ### 颐北家苑房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 百旺家苑 海淀·马连洼**76152** 元/㎡ * #### 百旺家苑别墅 海淀·马连洼**152913** 元/㎡ * #### 天秀花园久盛居 海淀·马连洼**90783** 元/㎡ ### 相关资讯 * 小区资讯北京颐北家苑怎么样?；北京吉屋网提供北京颐北家苑二手房出售信息、颐北家苑二手房价格，包括及时更新北京颐北家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 颐北家苑_北京颐北家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_颐北家苑 更新于 2026-06-01 10:50:40 [](https://bj.jiwu.com/tu/3480196.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480197.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480198.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480199.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480200.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480201.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480202.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480203.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480204.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480205.html "颐北家苑实景图图片") # 颐北家苑 别名：颐北家苑 加入本地买房群 关注 _北京 - 海淀 - 圆明园西路_ 发地址到手机 参考均价 _67785 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2009_ 小区户数 _1218户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-67群（380） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(1) 全部户型 [](https://bj.jiwu.com/huxing/661744.html "颐北家苑2室1厅1卫80㎡户型图")2室1厅1卫 80㎡咨询户型房源 小区评测报告 ？</x:v>
+        <x:v>2004/2009年建成，楼龄约15年；；物业为团河苑小区物业，物业费0.8元/㎡·月；；户型为南北通透两居，精装修，房屋家具家电齐全；；未提及隔音相关差评，装修评价较好，小区人车分流、集中供暖；</x:v>
       </x:c>
       <x:c r="L45" t="str">
-        <x:v>颐北家苑地址价格周边配套解析2022-08-27 * 小区资讯最详细!；北京吉屋网提供北京颐北家苑二手房出售信息、颐北家苑二手房价格，包括及时更新北京颐北家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 颐北家苑_北京颐北家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_颐北家苑 更新于 2026-06-01 10:50:40 [](https://bj.jiwu.com/tu/3480196.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480197.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480198.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480199.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480200.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480201.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480202.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480203.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480204.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480205.html "颐北家苑实景图图片") # 颐北家苑 别名：颐北家苑 加入本地买房群 关注 _北京 - 海淀 - 圆明园西路_ 发地址到手机 参考均价 _67785 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2009_ 小区户数 _1218户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-67群（380） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 感谢群主的推荐，很匹配我的诉求哇 * 看了群主发的区域解读，受益良多啊 * 都在说是上车好时候，大家怎么看啊 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 加入北京交流群，掌握一手楼市信息 加入群聊 小区问答 * 问 颐北家苑“五证”有哪些？</x:v>
+        <x:v>临近地铁16号线马连洼站、农大南路站（步行约878-1817米）；；周边有商超、餐饮、农贸市场等生活配套；；临近中国农业大学附属中学等教育资源，医疗配套得分优于区域均值；</x:v>
       </x:c>
       <x:c r="M45" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>未提及隔音相关差评，装修评价较好，小区人车分流、集中供暖；；部分房源发布时间较早（如2025年8月房源，需注意信息时效性），未发现明确差评，部分摘要中房产公司信息完整，暂无明确风险；</x:v>
       </x:c>
       <x:c r="N45" t="str">
-        <x:v>价格线索：3000_ 元/m² 颐北家苑，小区价格67785元/㎡；三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010678989/photo/) [](https://esf.fang.com/loupan/1010678989/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **59134** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓1.0% 贷款计算器 * 二手房源 0套 * 最近成交 0套 * 楼栋总数 17栋 * 房屋总数 1200户 * 建筑类型 板楼 * 建筑年代 2009年建成 * 小区位置 龙背村路6号地图 * 物业公司 团河苑小区物业 * 开发商 石家庄市金鱼房地产开发有限公司 ### 颐北家苑房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 百旺家苑 海淀·马连洼**76152** 元/㎡ * #### 百旺家苑别墅 海淀·马连洼**152913** 元/㎡ * #### 天秀花园久盛居 海淀·马连洼**90783** 元/㎡ ### 相关资讯 * 小区资讯北京颐北家苑怎么样?；北京吉屋网提供北京颐北家苑二手房出售信息、颐北家苑二手房价格，包括及时更新北京颐北家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 颐北家苑_北京颐北家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_颐北家苑 更新于 2026-06-01 10:50:40 [](https://bj.jiwu.com/tu/3480196.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480197.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480198.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480199.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480200.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480201.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480202.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480203.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480204.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480205.html "颐北家苑实景图图片") # 颐北家苑 别名：颐北家苑 加入本地买房群 关注 _北京 - 海淀 - 圆明园西路_ 发地址到手机 参考均价 _67785 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2009_ 小区户数 _1218户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-67群（380） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(1) 全部户型 [](https://bj.jiwu.com/huxing/661744.html "颐北家苑2室1厅1卫80㎡户型图")2室1厅1卫 80㎡咨询户型房源 小区评测报告 ？；生活便利线索：颐北家苑地址价格周边配套解析2022-08-27 * 小区资讯最详细!；北京吉屋网提供北京颐北家苑二手房出售信息、颐北家苑二手房价格，包括及时更新北京颐北家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 颐北家苑_北京颐北家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_颐北家苑 更新于 2026-06-01 10:50:40 [](https://bj.jiwu.com/tu/3480196.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480197.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480198.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480199.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480200.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480201.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480202.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480203.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480204.html "颐北家苑实景图图片")[](https://bj.jiwu.com/tu/3480205.html "颐北家苑实景图图片") # 颐北家苑 别名：颐北家苑 加入本地买房群 关注 _北京 - 海淀 - 圆明园西路_ 发地址到手机 参考均价 _67785 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2009_ 小区户数 _1218户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-67群（380） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 感谢群主的推荐，很匹配我的诉求哇 * 看了群主发的区域解读，受益良多啊 * 都在说是上车好时候，大家怎么看啊 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 加入北京交流群，掌握一手楼市信息 加入群聊 小区问答 * 问 颐北家苑“五证”有哪些？；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>房屋质量/户型线索：2004/2009年建成，楼龄约15年；；物业为团河苑小区物业，物业费0.8元/㎡·月；；户型为南北通透两居，精装修，房屋家具家电齐全；；未提及隔音相关差评，装修评价较好，小区人车分流、集中供暖；；生活便利线索：临近地铁16号线马连洼站、农大南路站（步行约878-1817米）；；周边有商超、餐饮、农贸市场等生活配套；；临近中国农业大学附属中学等教育资源，医疗配套得分优于区域均值；；风险线索：未提及隔音相关差评，装修评价较好，小区人车分流、集中供暖；；部分房源发布时间较早（如2025年8月房源，需注意信息时效性），未发现明确差评，部分摘要中房产公司信息完整，暂无明确风险；</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>1. 【北京颐北家苑小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010678989.htm
-2. 颐北家苑_北京颐北家苑小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/150267.html
-3.  https://www.bjdch.gov.cn/zwgk/jgdh/qzfzcbmdh/fgj/bzxzffp/202511/P020251117576266490220.pdf
-4. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-5. 北京市首批公共租赁住房已入住项目地图 http://bjjs.zjw.beijing.gov.cn:8080/ggzn/xmdt_ggznbd</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4562926285073412-3/
+2. https://bj.zu.anjuke.com/fangyuan/4160762200173583
+3. http://m.anjuke.com/bj/rent/4509114366630927-3/
+4. https://bj.zu.anjuke.com/fangyuan/4252848042254351
+5. https://esf.fang.com/loupan/1010678989/strategy.htm
+6. 颐北家苑 电梯房两居 干净整洁 集中供暖 配置齐全 价格可谈 http://m.anjuke.com/bj/rent/4562926285073412-3/
+7. 颐北家苑 精装两居 干净整洁 采光好可长租 业主直签 可优惠 https://bj.zu.anjuke.com/fangyuan/4160762200173583
+8. 龙背村路 颐北家苑 能便宜 精装两居 实房实图 跟业主签长租 http://m.anjuke.com/bj/rent/4509114366630927-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -2443,39 +2576,40 @@
         <x:v>北京市海淀区马连洼北路万德嘉园</x:v>
       </x:c>
       <x:c r="E46" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F46" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G46" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H46" t="n">
-        <x:v>3</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I46" t="str">
-        <x:v>搜索证据与目标地块严重错位，包含大量无关区域信息，无法提供有效决策参考。</x:v>
-      </x:c>
-      <x:c r="J46" t="str">
-        <x:v>停车管理，项目内地面车位200个，停车费150元/月；地下车位350个，停车费350元/月；6300 元/月；6000 元/月；1500 元/月；1300 元/月；50㎡|朝南 昌平-昌平县城-拓然家苑 3200 元/月；交通便利周边配套齐采光好 5200 元/月</x:v>
-      </x:c>
+        <x:v>2023年新房品质极佳，物业环境优越，虽距地铁稍远但生活配套非常完善。</x:v>
+      </x:c>
+      <x:c r="J46" t="str"/>
       <x:c r="K46" t="str">
-        <x:v>北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝。；北京本地宝频道提供北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图有关的信息，北京海淀区山樾嘉园公租房位置：位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站。；# 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝 [](https://bj.bendibao.com/) * 本地民生 * 办事 * 社保 * 公积金 * 居住证 * 交通 * 地铁 * 旅游 * 景点 * 活动 * 教育 * 网点 * 招聘 * 特惠 北京 [](http://www.bendibao.com/city.htm) 首页 下载app * 办事指南 * 社保 * 公积金 * 出入境 * 车辆 * 户籍 * 教育 * 婚育 * 房产 * 医疗 * 生活 * 企业 * 其他 办事直通车 北京本地宝&gt;办事指南&gt;北京土地房产&gt;北京公共租赁房&gt;北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 2023-11-15 09:23 来源：2023年11月北京海淀区第二十二批公租房配租公告【我要纠错】 下载指南 分享至 [](javascript:copy_url();；(租金单价中包含物业费，不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用) **一、项目位置及周边配套** 1、项目名称：山樾嘉园(其他名称：金隅西砂公租房) 2**、项目位置：项目位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；4、居室及户型：零居(建筑面积：25-26m2)，无其他户型。</x:v>
+        <x:v>小区2023年交房，物业较完善，有24小时保安，绿化好环境安静；；精装修，房源采光好，电梯房；；部分房源标注卧室隔音效果好；；户型多为南北通透或南向，有足够空间，部分房源客厅卧室分离。；摘要6中出现15平米3室1厅1卫3200元房源，疑似为合租单间，需注意是否为整租房源的误标或实际户型与描述不符；</x:v>
       </x:c>
       <x:c r="L46" t="str">
-        <x:v># 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝 [](https://bj.bendibao.com/) * 本地民生 * 办事 * 社保 * 公积金 * 居住证 * 交通 * 地铁 * 旅游 * 景点 * 活动 * 教育 * 网点 * 招聘 * 特惠 北京 [](http://www.bendibao.com/city.htm) 首页 下载app * 办事指南 * 社保 * 公积金 * 出入境 * 车辆 * 户籍 * 教育 * 婚育 * 房产 * 医疗 * 生活 * 企业 * 其他 办事直通车 北京本地宝&gt;办事指南&gt;北京土地房产&gt;北京公共租赁房&gt;北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 2023-11-15 09:23 来源：2023年11月北京海淀区第二十二批公租房配租公告【我要纠错】 下载指南 分享至 [](javascript:copy_url();；(租金单价中包含物业费，不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用) **一、项目位置及周边配套** 1、项目名称：山樾嘉园(其他名称：金隅西砂公租房) 2**、项目位置：项目位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；** 具体地址：北京市海淀区田村山南路35号院 项目位置示意图 3、交通路网及周边配套 ⑴交通路网：向北可进入阜石路，向东可通往西四环定慧寺桥，向西可通往西五环晋元桥，向南可通往长安街沿线。；交通干道：阜石路，上庄大街;；公共交通：地铁六号线廖公庄站(距离约1.2公里)，一号线八宝山站(距离约1.8公里);</x:v>
-      </x:c>
-      <x:c r="M46" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>交通：附近有菊园东站公交站，地铁16号线、13号线、18号线上地软件园站步行约1595米；；生活：周边有志强百货超市、世纪华联超市、北京华联BHG Mall等，还有便利店；；餐饮：肯德基、家门口饺子馆等；；配套：医院（北京八珍堂中医医院等）、学校（上地实验小学、幼儿园）等齐全。</x:v>
+      </x:c>
+      <x:c r="M46" t="str"/>
       <x:c r="N46" t="str">
-        <x:v>价格线索：停车管理，项目内地面车位200个，停车费150元/月；地下车位350个，停车费350元/月；6300 元/月；6000 元/月；1500 元/月；1300 元/月；50㎡|朝南 昌平-昌平县城-拓然家苑 3200 元/月；交通便利周边配套齐采光好 5200 元/月；房屋质量/户型线索：北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝。；北京本地宝频道提供北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图有关的信息，北京海淀区山樾嘉园公租房位置：位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站。；# 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝 [](https://bj.bendibao.com/) * 本地民生 * 办事 * 社保 * 公积金 * 居住证 * 交通 * 地铁 * 旅游 * 景点 * 活动 * 教育 * 网点 * 招聘 * 特惠 北京 [](http://www.bendibao.com/city.htm) 首页 下载app * 办事指南 * 社保 * 公积金 * 出入境 * 车辆 * 户籍 * 教育 * 婚育 * 房产 * 医疗 * 生活 * 企业 * 其他 办事直通车 北京本地宝&gt;办事指南&gt;北京土地房产&gt;北京公共租赁房&gt;北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 2023-11-15 09:23 来源：2023年11月北京海淀区第二十二批公租房配租公告【我要纠错】 下载指南 分享至 [](javascript:copy_url();；(租金单价中包含物业费，不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用) **一、项目位置及周边配套** 1、项目名称：山樾嘉园(其他名称：金隅西砂公租房) 2**、项目位置：项目位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；4、居室及户型：零居(建筑面积：25-26m2)，无其他户型。；生活便利线索：# 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝 [](https://bj.bendibao.com/) * 本地民生 * 办事 * 社保 * 公积金 * 居住证 * 交通 * 地铁 * 旅游 * 景点 * 活动 * 教育 * 网点 * 招聘 * 特惠 北京 [](http://www.bendibao.com/city.htm) 首页 下载app * 办事指南 * 社保 * 公积金 * 出入境 * 车辆 * 户籍 * 教育 * 婚育 * 房产 * 医疗 * 生活 * 企业 * 其他 办事直通车 北京本地宝&gt;办事指南&gt;北京土地房产&gt;北京公共租赁房&gt;北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图 2023-11-15 09:23 来源：2023年11月北京海淀区第二十二批公租房配租公告【我要纠错】 下载指南 分享至 [](javascript:copy_url();；(租金单价中包含物业费，不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用) **一、项目位置及周边配套** 1、项目名称：山樾嘉园(其他名称：金隅西砂公租房) 2**、项目位置：项目位于海淀区西四环阜石路与上庄大街交汇处东南200米，具体四至：北至宝山电站，东至101铁路，南至田村山南路，西至上庄大街。；** 具体地址：北京市海淀区田村山南路35号院 项目位置示意图 3、交通路网及周边配套 ⑴交通路网：向北可进入阜石路，向东可通往西四环定慧寺桥，向西可通往西五环晋元桥，向南可通往长安街沿线。；交通干道：阜石路，上庄大街;；公共交通：地铁六号线廖公庄站(距离约1.2公里)，一号线八宝山站(距离约1.8公里);；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>房屋质量/户型线索：小区2023年交房，物业较完善，有24小时保安，绿化好环境安静；；精装修，房源采光好，电梯房；；部分房源标注卧室隔音效果好；；户型多为南北通透或南向，有足够空间，部分房源客厅卧室分离。；摘要6中出现15平米3室1厅1卫3200元房源，疑似为合租单间，需注意是否为整租房源的误标或实际户型与描述不符；；生活便利线索：交通：附近有菊园东站公交站，地铁16号线、13号线、18号线上地软件园站步行约1595米；；生活：周边有志强百货超市、世纪华联超市、北京华联BHG Mall等，还有便利店；；餐饮：肯德基、家门口饺子馆等；；配套：医院（北京八珍堂中医医院等）、学校（上地实验小学、幼儿园）等齐全。</x:v>
       </x:c>
       <x:c r="O46" t="str">
-        <x:v>1. 北京海淀区山樾嘉园公租房位置/租金价格/室内效果图房源户型图- 北京本地宝 https://bj.bendibao.com/zffw/20231115/353693.shtm
-2. 【北京嘉园出租房租房信息_房屋出租】- 房天下 https://fang.com/houses/zf_253090bj/g2-h38-i329/
-3. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4592629183818765-3
+2. http://m.anjuke.com/bj/rent/4603820881028105-3
+3. http://m.anjuke.com/ch/rent/4585967002952704-2
+4. http://m.anjuke.com/bj/rent/4583962524752899-3
+5. http://m.anjuke.com/bj/rent/4606898622131208-3
+6. http://m.anjuke.com/bj/rent/4578138155822093-3
+7. 万德嘉园(二区) 阳光充足 二居室 电梯房 http://m.anjuke.com/bj/rent/4592629183818765-3/
+8. 实房实图 万德嘉园精装南北两居 业主好说话 带车位 可长租 http://m.anjuke.com/bj/rent/4603820881028105-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -2492,41 +2626,42 @@
         <x:v>北京市海淀区马连洼街道马连洼北路158号</x:v>
       </x:c>
       <x:c r="E47" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F47" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G47" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H47" t="n">
-        <x:v>7.2</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="I47" t="str">
-        <x:v>邻近西北旺及马连洼，配套成熟且交通便利，适合通勤但需甄别具体房龄与房况。</x:v>
+        <x:v>交通与医疗配套极佳，社区成熟且隔音良好，是性价比极高的成熟居住选择。</x:v>
       </x:c>
       <x:c r="J47" t="str">
-        <x:v>修问答登录/注册 百旺家苑6月均价走势 72291 元/㎡；马连洼 1994年竣工 距离1009m 56968 元/㎡； 西北旺 2011年竣工 距离967m 104522 元/㎡； 马连洼 2006年竣工 距离413m 78253 元/㎡；马连洼 1995年竣工 距离1368m 52434 元/㎡； 马连洼 1996年竣工 距离394m 57988 元/㎡；西北旺 2015年竣工 距离2350m 52714 元/㎡； 5室3厅3卫丨224㎡丨南北丨底层丨 93200元/㎡</x:v>
+        <x:v>合租主卧约2800元/月</x:v>
       </x:c>
       <x:c r="K47" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **76151** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓2.69% 贷款计算器 * 二手房源 38套 * 楼栋总数 58栋 * 房屋总数 1254户 * 建筑类型 板楼 * 建筑年代 2003年建成 * 小区位置 马连洼地区农大北路南侧百旺家苑地图 * 物业公司 北京华特物业管理发展有限公司 * 开发商 北京德成兴业房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 王金雨 评分：4.3 从业信息卡 百科 ##### 陈峰 评分：4.1 从业信息卡 ##### 张帅 评分：4.1 从业信息卡 ##### 王胜楠 评分：4.1 从业信息卡 百科 * 户型 * 价格 * #### 满五年唯一,带电梯两居室,签约随时 2室1厅 94.02㎡**799**万 * #### 百旺家苑2室2厅南北 2室2厅 115.14㎡**770**万 * #### 百旺家苑2室2厅南北 2室2厅 99.19㎡**690**万 * #### 此房南北通透,通风好,南向大阳台,一层 3室2厅 139.55㎡**1085**万 ### 百旺家苑价格走势 ### 百旺家苑房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 百旺家苑别墅 海淀·马连洼**152913** 元/㎡ * #### 百旺家苑 海淀·马连洼**76152** 元/㎡ * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 马连洼梅园 海淀·马连洼**65210** 元/㎡ ### 相关资讯 * 小区资讯北京百旺家苑别墅怎么样?；百旺家苑别墅房价地址户型小区详情解析2021-10-31 * 小区资讯北京百旺家苑怎么样?；from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 百旺家苑6月均价走势 72291 元/㎡ 6月挂牌均价 0.25% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 新出 不临街 2层 无遮挡 三地铁 马连洼 好采光 马连洼 百旺家苑 1090 万 3室2厅 164.6㎡ 仅我司可售)300萬精装叠墅 80花院独立车库 价格可谈 马连洼 百旺家苑 1680 万 4室2厅 224.05㎡ 百旺家苑 2室 1厅 89.99平 马连洼 百旺家苑 599 万 2室1厅 89.99㎡ 2室1厅2卫1厨1阳 马连洼 百旺家苑 750 万 2室1厅 94.02㎡ 2室1厅1卫1厨1阳 马连洼 百旺家苑 710 万 2室1厅 97.14㎡ 马连洼地铁旁百旺家苑2室2厅，全明格局，可观百望山 马连洼 百旺家苑 728 万 2室2厅 115.46㎡ ### 本小区租房推荐查看更多 ### 精装修主卧 马连洼地铁站 农大南路 中发百旺 西苑 随时入住 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 朝南 _2399_ 元/月 3室1厅 15㎡ ### 马连洼地铁口精装主卧，农大西校区，百度科技园，中关村软件园 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 南北 _2499_ 元/月 3室1厅 20㎡ ### 22 50可租 马连洼地铁农大西校区百度科技园，中关村软件园 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 朝北 _2400_ 元/�� 4室1厅 12㎡ ### 地铁16号线马连洼 百旺家苑 1室1厅 家电齐全 业主直签 马连洼 百旺家苑 整租 16/18号线/4号线大兴线 朝南 _6500_ 元/月 1室1厅 60.2㎡ ### 周边热门小区查看更多 * 406 竹园小区 海淀 马连洼 1994年竣工 距离1009m 56968 元/㎡9套在售 小区评测 近地铁 近学校 16号线等 五六环之间 小户型居多 配套齐全 7.3 分 * 361 西山壹号院(南区) 海淀 西北旺 2011年竣工 距离967m 104522 元/㎡16套在售 小区评测 近地铁 近学校 16号线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 7.2 分 * 382 润千秋佳苑 海淀 马连洼 2006年竣工 距离413m 78253 元/㎡7套在售 小区评测 近地铁 近学校 16号线 五六环之间 户型丰富 绿化好 配套齐全 6.9 分 * 562 菊园 海淀 马连洼 1995年竣工 距离1368m 52434 元/㎡22套在售 小区评测 近地铁 近学校 16号线 五六环之间 小户型居多 户型丰富 配套齐全 6.8 分 * 289 梅园(海淀) 海淀 马连洼 1996年竣工 距离394m 57988 元/㎡10套在售 小区评测 近地铁 近学校 16号线等 五六环之间 小户型居多 配套齐全 6.9 分 * 152 夏霖园 海淀 西北旺 2015年竣工 距离2350m 52714 元/㎡4套在售 小区评测 近地铁 近学校 16号线 五六环之间 小户型居多 配套齐全 7.1 分 小区单页 褐石园泛海国际碧海园今日家园广渠金茂府(北区)景泰嘉园朱雀门小区天通苑北一区京铁家园天鹅湾(北区)丽都壹号公园大道丽宫别墅北京六建家属院望京花园西区纳帕溪谷北辰红橡墅逸成东苑华纺易城北京北星河湾畅园 本板块小区大全 美和园西区翠微中里金隅山墅(别墅)碧桐园颐源居上地佳园五福玲珑居满庭芳园京泉馨苑东里中鑫嘉园清上园太阳园莲花小区汤泉逸墅智学苑永丰嘉园(百旺杏林湾)逸成东苑尚峰尚水云会里园流清园翠湖别墅 小区二手房 褐石园二手房出售泛海国际碧海园二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售景泰嘉园二手房出售朱雀门小区二手房出售天通苑北一区二手房出售京铁家园二手房出售天鹅湾(北区)二手房出售丽都壹号二手房出售公园大道二手房出售丽宫别墅二手房出售北京六建家属院二手房出售望京花园西区二手房出售纳帕溪谷二手房出售北辰红橡墅二手房出售逸成东苑二手房出售华纺易城二手房出售北京北二手房出售星河湾畅园二手房出售 小区房价 褐石园房价走势泛海国际碧海园房价走势今日家园房价走势广渠金茂府(北区)房价走势景泰嘉园房价走势朱雀门小区房价走势天通苑北一区房价走势京铁家园房价走势天鹅湾(北区)房价走势丽都壹号房价走势公园大道房价走势丽宫别墅房价走势北京六建家属院房价走势望京花园西区房价走势纳帕溪谷房价走势北辰红橡墅房价走势逸成东苑房价走势华纺易城房价走势北京北房价走势星河湾畅园房价走势 推荐小区价格 星河湾朗园二手房出售丽泽景园二手房出售翠微北里二手房出售百环家园二手房出售翠微东里二手房出售首邑溪谷二手房出售新城国际二手房出售王府花园二手房出售大成郡二手房出售八家嘉园二手房出售观唐二手房出售流星花园三区二手房出售北京风景二手房出售季景沁园二手房出售西山美墅馆二手房出售中海紫御公馆二手房出售风度柏林二手房出售珠光逸景(二号院)二手房出售北京新天地(东区)二手房出售万泉新新家园二手房出售 二手房商圈 云岗二手房南邵镇二手房秦皇岛二手房八里庄二手房唐山二手房八达岭二手房天宁寺二手房廊坊二手房杨庄二手房旧宫二手房新航城二手房溪翁庄二手房建国门二手房角门二手房车公庄二手房九棵树二手房兴谷二手房马池口二手房高米店二手房丰益桥二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价百旺家苑小区百旺家苑二手房百旺家苑租房百旺家苑户型图百旺家苑周边配置百旺家苑百旺家苑实景图百旺家苑经纪人百旺家苑房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;百旺家苑 安居客小区频道，为您提供北京百旺家苑2003年房价趋势、走势图，百旺家苑二手房均价价格信息， 及时查询百旺家苑房价走势、了解百旺家苑房价上涨还是下跌，预测百旺家苑房价暴跌暴涨，百旺家苑房价多少钱一平米？；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。</x:v>
+        <x:v>位于海淀区马连洼街道，房龄相关未明确提及；；装修多为精装修或豪华装修，南北通透；；隔音较好（房源标注卧室隔音效果好）；；物业规范，小区管理成熟，配套设施齐全（家具家电齐全）；；户型有2居、3居、合租主卧等。</x:v>
       </x:c>
       <x:c r="L47" t="str">
-        <x:v>百旺家苑价格地段交通优势解析2021-06-25 * 小区资讯最详细!；from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 百旺家苑6月均价走势 72291 元/㎡ 6月挂牌均价 0.25% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 新出 不临街 2层 无遮挡 三地铁 马连洼 好采光 马连洼 百旺家苑 1090 万 3室2厅 164.6㎡ 仅我司可售)300萬精装叠墅 80花院独立车库 价格可谈 马连洼 百旺家苑 1680 万 4室2厅 224.05㎡ 百旺家苑 2室 1厅 89.99平 马连洼 百旺家苑 599 万 2室1厅 89.99㎡ 2室1厅2卫1厨1阳 马连洼 百旺家苑 750 万 2室1厅 94.02㎡ 2室1厅1卫1厨1阳 马连洼 百旺家苑 710 万 2室1厅 97.14㎡ 马连洼地铁旁百旺家苑2室2厅，全明格局，可观百望山 马连洼 百旺家苑 728 万 2室2厅 115.46㎡ ### 本小区租房推荐查看更多 ### 精装修主卧 马连洼地铁站 农大南路 中发百旺 西苑 随时入住 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 朝南 _2399_ 元/月 3室1厅 15㎡ ### 马连洼地铁口精装主卧，农大西校区，百度科技园，中关村软件园 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 南北 _2499_ 元/月 3室1厅 20㎡ ### 22 50可租 马连洼地铁农大西校区百度科技园，中关村软件园 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 朝北 _2400_ 元/�� 4室1厅 12㎡ ### 地铁16号线马连洼 百旺家苑 1室1厅 家电齐全 业主直签 马连洼 百旺家苑 整租 16/18号线/4号线大兴线 朝南 _6500_ 元/月 1室1厅 60.2㎡ ### 周边热门小区查看更多 * 406 竹园小区 海淀 马连洼 1994年竣工 距离1009m 56968 元/㎡9套在售 小区评测 近地铁 近学校 16号线等 五六环之间 小户型居多 配套齐全 7.3 分 * 361 西山壹号院(南区) 海淀 西北旺 2011年竣工 距离967m 104522 元/㎡16套在售 小区评测 近地铁 近学校 16号线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 7.2 分 * 382 润千秋佳苑 海淀 马连洼 2006年竣工 距离413m 78253 元/㎡7套在售 小区评测 近地铁 近学校 16号线 五六环之间 户型丰富 绿化好 配套齐全 6.9 分 * 562 菊园 海淀 马连洼 1995年竣工 距离1368m 52434 元/㎡22套在售 小区评测 近地铁 近学校 16号线 五六环之间 小户型居多 户型丰富 配套齐全 6.8 分 * 289 梅园(海淀) 海淀 马连洼 1996年竣工 距离394m 57988 元/㎡10套在售 小区评测 近地铁 近学校 16号线等 五六环之间 小户型居多 配套齐全 6.9 分 * 152 夏霖园 海淀 西北旺 2015年竣工 距离2350m 52714 元/㎡4套在售 小区评测 近地铁 近学校 16号线 五六环之间 小户型居多 配套齐全 7.1 分 小区单页 褐石园泛海国际碧海园今日家园广渠金茂府(北区)景泰嘉园朱雀门小区天通苑北一区京铁家园天鹅湾(北区)丽都壹号公园大道丽宫别墅北京六建家属院望京花园西区纳帕溪谷北辰红橡墅逸成东苑华纺易城北京北星河湾畅园 本板块小区大全 美和园西区翠微中里金隅山墅(别墅)碧桐园颐源居上地佳园五福玲珑居满庭芳园京泉馨苑东里中鑫嘉园清上园太阳园莲花小区汤泉逸墅智学苑永丰嘉园(百旺杏林湾)逸成东苑尚峰尚水云会里园流清园翠湖别墅 小区二手房 褐石园二手房出售泛海国际碧海园二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售景泰嘉园二手房出售朱雀门小区二手房出售天通苑北一区二手房出售京铁家园二手房出售天鹅湾(北区)二手房出售丽都壹号二手房出售公园大道二手房出售丽宫别墅二手房出售北京六建家属院二手房出售望京花园西区二手房出售纳帕溪谷二手房出售北辰红橡墅二手房出售逸成东苑二手房出售华纺易城二手房出售北京北二手房出售星河湾畅园二手房出售 小区房价 褐石园房价走势泛海国际碧海园房价走势今日家园房价走势广渠金茂府(北区)房价走势景泰嘉园房价走势朱雀门小区房价走势天通苑北一区房价走势京铁家园房价走势天鹅湾(北区)房价走势丽都壹号房价走势公园大道房价走势丽宫别墅房价走势北京六建家属院房价走势望京花园西区房价走势纳帕溪谷房价走势北辰红橡墅房价走势逸成东苑房价走势华纺易城房价走势北京北房价走势星河湾畅园房价走势 推荐小区价格 星河湾朗园二手房出售丽泽景园二手房出售翠微北里二手房出售百环家园二手房出售翠微东里二手房出售首邑溪谷二手房出售新城国际二手房出售王府花园二手房出售大成郡二手房出售八家嘉园二手房出售观唐二手房出售流星花园三区二手房出售北京风景二手房出售季景沁园二手房出售西山美墅馆二手房出售中海紫御公馆二手房出售风度柏林二手房出售珠光逸景(二号院)二手房出售北京新天地(东区)二手房出售万泉新新家园二手房出售 二手房商圈 云岗二手房南邵镇二手房秦皇岛二手房八里庄二手房唐山二手房八达岭二手房天宁寺二手房廊坊二手房杨庄二手房旧宫二手房新航城二手房溪翁庄二手房建国门二手房角门二手房车公庄二手房九棵树二手房兴谷二手房马池口二手房高米店二手房丰益桥二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价百旺家苑小区百旺家苑二手房百旺家苑租房百旺家苑户型图百旺家苑周边配置百旺家苑百旺家苑实景图百旺家苑经纪人百旺家苑房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;百旺家苑 安居客小区频道，为您提供北京百旺家苑2003年房价趋势、走势图，百旺家苑二手房均价价格信息， 及时查询百旺家苑房价走势、了解百旺家苑房价上涨还是下跌，预测百旺家苑房价暴跌暴涨，百旺家苑房价多少钱一平米？；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺家苑 更新于 2026-06-01 10:46:54 [](https://bj.jiwu.com/tu/4301782.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301783.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301784.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301785.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301786.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301787.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301788.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301789.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301790.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301791.html "百旺家苑实景图图片") # 百旺家苑 别名：百旺家苑 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路_ 发地址到手机 参考均价 _72888 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2003_ 小区户数 _1303户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-63群（313） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?</x:v>
-      </x:c>
-      <x:c r="M47" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
-      </x:c>
+        <x:v>物业规范，小区管理成熟，配套设施齐全（家具家电齐全）；；地铁：16号线马连洼站步行约1056米，18号线、4号线站点附近；；商超：超市发（天秀北路店）129米、中发百旺商城787米、华联BHG Mall1149米；；医院：解放军总医院第八医学中心467米；；交通便利，周边公交多，购物、医疗、餐饮等生活配套丰富。</x:v>
+      </x:c>
+      <x:c r="M47" t="str"/>
       <x:c r="N47" t="str">
-        <x:v>价格线索：修问答登录/注册 百旺家苑6月均价走势 72291 元/㎡；马连洼 1994年竣工 距离1009m 56968 元/㎡； 西北旺 2011年竣工 距离967m 104522 元/㎡； 马连洼 2006年竣工 距离413m 78253 元/㎡；马连洼 1995年竣工 距离1368m 52434 元/㎡； 马连洼 1996年竣工 距离394m 57988 元/㎡；西北旺 2015年竣工 距离2350m 52714 元/㎡； 5室3厅3卫丨224㎡丨南北丨底层丨 93200元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **76151** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓2.69% 贷款计算器 * 二手房源 38套 * 楼栋总数 58栋 * 房屋总数 1254户 * 建筑类型 板楼 * 建筑年代 2003年建成 * 小区位置 马连洼地区农大北路南侧百旺家苑地图 * 物业公司 北京华特物业管理发展有限公司 * 开发商 北京德成兴业房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 王金雨 评分：4.3 从业信息卡 百科 ##### 陈峰 评分：4.1 从业信息卡 ##### 张帅 评分：4.1 从业信息卡 ##### 王胜楠 评分：4.1 从业信息卡 百科 * 户型 * 价格 * #### 满五年唯一,带电梯两居室,签约随时 2室1厅 94.02㎡**799**万 * #### 百旺家苑2室2厅南北 2室2厅 115.14㎡**770**万 * #### 百旺家苑2室2厅南北 2室2厅 99.19㎡**690**万 * #### 此房南北通透,通风好,南向大阳台,一层 3室2厅 139.55㎡**1085**万 ### 百旺家苑价格走势 ### 百旺家苑房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 百旺家苑别墅 海淀·马连洼**152913** 元/㎡ * #### 百旺家苑 海淀·马连洼**76152** 元/㎡ * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 马连洼梅园 海淀·马连洼**65210** 元/㎡ ### 相关资讯 * 小区资讯北京百旺家苑别墅怎么样?；百旺家苑别墅房价地址户型小区详情解析2021-10-31 * 小区资讯北京百旺家苑怎么样?；from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 百旺家苑6月均价走势 72291 元/㎡ 6月挂牌均价 0.25% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 新出 不临街 2层 无遮挡 三地铁 马连洼 好采光 马连洼 百旺家苑 1090 万 3室2厅 164.6㎡ 仅我司可售)300萬精装叠墅 80花院独立车库 价格可谈 马连洼 百旺家苑 1680 万 4室2厅 224.05㎡ 百旺家苑 2室 1厅 89.99平 马连洼 百旺家苑 599 万 2室1厅 89.99㎡ 2室1厅2卫1厨1阳 马连洼 百旺家苑 750 万 2室1厅 94.02㎡ 2室1厅1卫1厨1阳 马连洼 百旺家苑 710 万 2室1厅 97.14㎡ 马连洼地铁旁百旺家苑2室2厅，全明格局，可观百望山 马连洼 百旺家苑 728 万 2室2厅 115.46㎡ ### 本小区租房推荐查看更多 ### 精装修主卧 马连洼地铁站 农大南路 中发百旺 西苑 随时入住 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 朝南 _2399_ 元/月 3室1厅 15㎡ ### 马连洼地铁口精装主卧，农大西校区，百度科技园，中关村软件园 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 南北 _2499_ 元/月 3室1厅 20㎡ ### 22 50可租 马连洼地铁农大西校区百度科技园，中关村软件园 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 朝北 _2400_ 元/�� 4室1厅 12㎡ ### 地铁16号线马连洼 百旺家苑 1室1厅 家电齐全 业主直签 马连洼 百旺家苑 整租 16/18号线/4号线大兴线 朝南 _6500_ 元/月 1室1厅 60.2㎡ ### 周边热门小区查看更多 * 406 竹园小区 海淀 马连洼 1994年竣工 距离1009m 56968 元/㎡9套在售 小区评测 近地铁 近学校 16号线等 五六环之间 小户型居多 配套齐全 7.3 分 * 361 西山壹号院(南区) 海淀 西北旺 2011年竣工 距离967m 104522 元/㎡16套在售 小区评测 近地铁 近学校 16号线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 7.2 分 * 382 润千秋佳苑 海淀 马连洼 2006年竣工 距离413m 78253 元/㎡7套在售 小区评测 近地铁 近学校 16号线 五六环之间 户型丰富 绿化好 配套齐全 6.9 分 * 562 菊园 海淀 马连洼 1995年竣工 距离1368m 52434 元/㎡22套在售 小区评测 近地铁 近学校 16号线 五六环之间 小户型居多 户型丰富 配套齐全 6.8 分 * 289 梅园(海淀) 海淀 马连洼 1996年竣工 距离394m 57988 元/㎡10套在售 小区评测 近地铁 近学校 16号线等 五六环之间 小户型居多 配套齐全 6.9 分 * 152 夏霖园 海淀 西北旺 2015年竣工 距离2350m 52714 元/㎡4套在售 小区评测 近地铁 近学校 16号线 五六环之间 小户型居多 配套齐全 7.1 分 小区单页 褐石园泛海国际碧海园今日家园广渠金茂府(北区)景泰嘉园朱雀门小区天通苑北一区京铁家园天鹅湾(北区)丽都壹号公园大道丽宫别墅北京六建家属院望京花园西区纳帕溪谷北辰红橡墅逸成东苑华纺易城北京北星河湾畅园 本板块小区大全 美和园西区翠微中里金隅山墅(别墅)碧桐园颐源居上地佳园五福玲珑居满庭芳园京泉馨苑东里中鑫嘉园清上园太阳园莲花小区汤泉逸墅智学苑永丰嘉园(百旺杏林湾)逸成东苑尚峰尚水云会里园流清园翠湖别墅 小区二手房 褐石园二手房出售泛海国际碧海园二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售景泰嘉园二手房出售朱雀门小区二手房出售天通苑北一区二手房出售京铁家园二手房出售天鹅湾(北区)二手房出售丽都壹号二手房出售公园大道二手房出售丽宫别墅二手房出售北京六建家属院二手房出售望京花园西区二手房出售纳帕溪谷二手房出售北辰红橡墅二手房出售逸成东苑二手房出售华纺易城二手房出售北京北二手房出售星河湾畅园二手房出售 小区房价 褐石园房价走势泛海国际碧海园房价走势今日家园房价走势广渠金茂府(北区)房价走势景泰嘉园房价走势朱雀门小区房价走势天通苑北一区房价走势京铁家园房价走势天鹅湾(北区)房价走势丽都壹号房价走势公园大道房价走势丽宫别墅房价走势北京六建家属院房价走势望京花园西区房价走势纳帕溪谷房价走势北辰红橡墅房价走势逸成东苑房价走势华纺易城房价走势北京北房价走势星河湾畅园房价走势 推荐小区价格 星河湾朗园二手房出售丽泽景园二手房出售翠微北里二手房出售百环家园二手房出售翠微东里二手房出售首邑溪谷二手房出售新城国际二手房出售王府花园二手房出售大成郡二手房出售八家嘉园二手房出售观唐二手房出售流星花园三区二手房出售北京风景二手房出售季景沁园二手房出售西山美墅馆二手房出售中海紫御公馆二手房出售风度柏林二手房出售珠光逸景(二号院)二手房出售北京新天地(东区)二手房出售万泉新新家园二手房出售 二手房商圈 云岗二手房南邵镇二手房秦皇岛二手房八里庄二手房唐山二手房八达岭二手房天宁寺二手房廊坊二手房杨庄二手房旧宫二手房新航城二手房溪翁庄二手房建国门二手房角门二手房车公庄二手房九棵树二手房兴谷二手房马池口二手房高米店二手房丰益桥二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价百旺家苑小区百旺家苑二手房百旺家苑租房百旺家苑户型图百旺家苑周边配置百旺家苑百旺家苑实景图百旺家苑经纪人百旺家苑房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;百旺家苑 安居客小区频道，为您提供北京百旺家苑2003年房价趋势、走势图，百旺家苑二手房均价价格信息， 及时查询百旺家苑房价走势、了解百旺家苑房价上涨还是下跌，预测百旺家苑房价暴跌暴涨，百旺家苑房价多少钱一平米？；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；生活便利线索：百旺家苑价格地段交通优势解析2021-06-25 * 小区资讯最详细!；from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 百旺家苑6月均价走势 72291 元/㎡ 6月挂牌均价 0.25% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 新出 不临街 2层 无遮挡 三地铁 马连洼 好采光 马连洼 百旺家苑 1090 万 3室2厅 164.6㎡ 仅我司可售)300萬精装叠墅 80花院独立车库 价格可谈 马连洼 百旺家苑 1680 万 4室2厅 224.05㎡ 百旺家苑 2室 1厅 89.99平 马连洼 百旺家苑 599 万 2室1厅 89.99㎡ 2室1厅2卫1厨1阳 马连洼 百旺家苑 750 万 2室1厅 94.02㎡ 2室1厅1卫1厨1阳 马连洼 百旺家苑 710 万 2室1厅 97.14㎡ 马连洼地铁旁百旺家苑2室2厅，全明格局，可观百望山 马连洼 百旺家苑 728 万 2室2厅 115.46㎡ ### 本小区租房推荐查看更多 ### 精装修主卧 马连洼地铁站 农大南路 中发百旺 西苑 随时入住 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 朝南 _2399_ 元/月 3室1厅 15㎡ ### 马连洼地铁口精装主卧，农大西校区，百度科技园，中关村软件园 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 南北 _2499_ 元/月 3室1厅 20㎡ ### 22 50可租 马连洼地铁农大西校区百度科技园，中关村软件园 马连洼 百旺家苑 合租 16/18号线/4号线大兴线 朝北 _2400_ 元/�� 4室1厅 12㎡ ### 地铁16号线马连洼 百旺家苑 1室1厅 家电齐全 业主直签 马连洼 百旺家苑 整租 16/18号线/4号线大兴线 朝南 _6500_ 元/月 1室1厅 60.2㎡ ### 周边热门小区查看更多 * 406 竹园小区 海淀 马连洼 1994年竣工 距离1009m 56968 元/㎡9套在售 小区评测 近地铁 近学校 16号线等 五六环之间 小户型居多 配套齐全 7.3 分 * 361 西山壹号院(南区) 海淀 西北旺 2011年竣工 距离967m 104522 元/㎡16套在售 小区评测 近地铁 近学校 16号线等 五六环之间 大户型居多 户型丰富 绿化好 配套齐全 7.2 分 * 382 润千秋佳苑 海淀 马连洼 2006年竣工 距离413m 78253 元/㎡7套在售 小区评测 近地铁 近学校 16号线 五六环之间 户型丰富 绿化好 配套齐全 6.9 分 * 562 菊园 海淀 马连洼 1995年竣工 距离1368m 52434 元/㎡22套在售 小区评测 近地铁 近学校 16号线 五六环之间 小户型居多 户型丰富 配套齐全 6.8 分 * 289 梅园(海淀) 海淀 马连洼 1996年竣工 距离394m 57988 元/㎡10套在售 小区评测 近地铁 近学校 16号线等 五六环之间 小户型居多 配套齐全 6.9 分 * 152 夏霖园 海淀 西北旺 2015年竣工 距离2350m 52714 元/㎡4套在售 小区评测 近地铁 近学校 16号线 五六环之间 小户型居多 配套齐全 7.1 分 小区单页 褐石园泛海国际碧海园今日家园广渠金茂府(北区)景泰嘉园朱雀门小区天通苑北一区京铁家园天鹅湾(北区)丽都壹号公园大道丽宫别墅北京六建家属院望京花园西区纳帕溪谷北辰红橡墅逸成东苑华纺易城北京北星河湾畅园 本板块小区大全 美和园西区翠微中里金隅山墅(别墅)碧桐园颐源居上地佳园五福玲珑居满庭芳园京泉馨苑东里中鑫嘉园清上园太阳园莲花小区汤泉逸墅智学苑永丰嘉园(百旺杏林湾)逸成东苑尚峰尚水云会里园流清园翠湖别墅 小区二手房 褐石园二手房出售泛海国际碧海园二手房出售今日家园二手房出售广渠金茂府(北区)二手房出售景泰嘉园二手房出售朱雀门小区二手房出售天通苑北一区二手房出售京铁家园二手房出售天鹅湾(北区)二手房出售丽都壹号二手房出售公园大道二手房出售丽宫别墅二手房出售北京六建家属院二手房出售望京花园西区二手房出售纳帕溪谷二手房出售北辰红橡墅二手房出售逸成东苑二手房出售华纺易城二手房出售北京北二手房出售星河湾畅园二手房出售 小区房价 褐石园房价走势泛海国际碧海园房价走势今日家园房价走势广渠金茂府(北区)房价走势景泰嘉园房价走势朱雀门小区房价走势天通苑北一区房价走势京铁家园房价走势天鹅湾(北区)房价走势丽都壹号房价走势公园大道房价走势丽宫别墅房价走势北京六建家属院房价走势望京花园西区房价走势纳帕溪谷房价走势北辰红橡墅房价走势逸成东苑房价走势华纺易城房价走势北京北房价走势星河湾畅园房价走势 推荐小区价格 星河湾朗园二手房出售丽泽景园二手房出售翠微北里二手房出售百环家园二手房出售翠微东里二手房出售首邑溪谷二手房出售新城国际二手房出售王府花园二手房出售大成郡二手房出售八家嘉园二手房出售观唐二手房出售流星花园三区二手房出售北京风景二手房出售季景沁园二手房出售西山美墅馆二手房出售中海紫御公馆二手房出售风度柏林二手房出售珠光逸景(二号院)二手房出售北京新天地(东区)二手房出售万泉新新家园二手房出售 二手房商圈 云岗二手房南邵镇二手房秦皇岛二手房八里庄二手房唐山二手房八达岭二手房天宁寺二手房廊坊二手房杨庄二手房旧宫二手房新航城二手房溪翁庄二手房建国门二手房角门二手房车公庄二手房九棵树二手房兴谷二手房马池口二手房高米店二手房丰益桥二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价百旺家苑小区百旺家苑二手房百旺家苑租房百旺家苑户型图百旺家苑周边配置百旺家苑百旺家苑实景图百旺家苑经纪人百旺家苑房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房马连洼合租租房马连洼公寓租房马连洼别墅租房马连洼个人租房马连洼一居室租房马连洼二居室租房马连洼三居室租房马连洼四居室租房马连洼五居室租房马连洼毛坯租房马连洼简单装修租房马连洼中等装修租房马连洼精装修租房马连洼豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;马连洼小区&gt;百旺家苑 安居客小区频道，为您提供北京百旺家苑2003年房价趋势、走势图，百旺家苑二手房均价价格信息， 及时查询百旺家苑房价走势、了解百旺家苑房价上涨还是下跌，预测百旺家苑房价暴跌暴涨，百旺家苑房价多少钱一平米？；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺家苑 更新于 2026-06-01 10:46:54 [](https://bj.jiwu.com/tu/4301782.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301783.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301784.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301785.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301786.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301787.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301788.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301789.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301790.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301791.html "百旺家苑实景图图片") # 百旺家苑 别名：百旺家苑 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路_ 发地址到手机 参考均价 _72888 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2003_ 小区户数 _1303户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-63群（313） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：合租主卧约2800元/月；房屋质量/户型线索：位于海淀区马连洼街道，房龄相关未明确提及；；装修多为精装修或豪华装修，南北通透；；隔音较好（房源标注卧室隔音效果好）；；物业规范，小区管理成熟，配套设施齐全（家具家电齐全）；；户型有2居、3居、合租主卧等。；生活便利线索：物业规范，小区管理成熟，配套设施齐全（家具家电齐全）；；地铁：16号线马连洼站步行约1056米，18号线、4号线站点附近；；商超：超市发（天秀北路店）129米、中发百旺商城787米、华联BHG Mall1149米；；医院：解放军总医院第八医学中心467米；；交通便利，周边公交多，购物、医疗、餐饮等生活配套丰富。</x:v>
       </x:c>
       <x:c r="O47" t="str">
-        <x:v>1. 【北京百旺家苑小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010026855.htm
-2. 百旺家苑房价, 百旺家苑百旺家苑房价走势图, 百旺家苑价格均价多少钱-安居客 https://m.anjuke.com/bj/trendency/community/78963/
-3. 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/145707.html
-4. 百旺家苑租房,合租·百旺家苑,租房-幸福里 https://m.xflapp.com/zufang/bj-7571578759770374190.html?from=share
-5. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4499451345394698-3/
+2. http://m.anjuke.com/bj/rent/4603623244602380-3/
+3. http://m.anjuke.com/bj/rent/4597174596512770-3/
+4. http://m.anjuke.com/bj/rent/4586927094078470-3/
+5. 百旺家苑东区租房价格_保定百旺家苑东区房租价格走势_百旺家苑东区租金一个月是多少钱-安居客 https://bd.zu.anjuke.com/xiaoqu/1908559/zujin/
+6. 首租 百旺家苑 精装大两居 集中供暖 价格可谈 跟业主签约 http://m.anjuke.com/bj/rent/4499451345394698-3/
+7. 百旺家苑东区租金走势分析 http://m.anjuke.com/bd/community/1908559/zujin/
+8. 百旺家苑 包物业取暖，主卧次卧出租 通风好 南北通透 http://m.anjuke.com/bj/rent/4603623244602380-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -2543,41 +2678,42 @@
         <x:v>北京市海淀区西北旺镇傅家窑南区临甲6号</x:v>
       </x:c>
       <x:c r="E48" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F48" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G48" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H48" t="n">
-        <x:v>3.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I48" t="str">
-        <x:v>证据多为四季青高价办公或大户型房源，租金极高且距离较远，不符合常规租住需求。</x:v>
+        <x:v>缺乏该小区直接证据，参考周边租金偏高，信息不透明建议谨慎选择。</x:v>
       </x:c>
       <x:c r="J48" t="str">
-        <x:v>可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；95000 元/月；115000 元/月；胡同小区 可注册办公首次出租南北通透 250000 元/月；12000 元/月；可注册办公首次出租南北通透 10500 元/月；可注册办公首次出租南北通透 180000 元/月</x:v>
+        <x:v>小区（如百旺新城春晖园）月租约5000-8200元/月</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v># 四季青160平米租房_北京海淀四季青160平米房屋出租-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 北京160平米租房&gt; 海淀160平米租房&gt; 四季青160平米租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 # 为您找到以下 "160平米" 租房房源 该条件下房源较少，为您推荐： * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 4600 元马家堡嘉园二里高楼层2居室 2室1厅 / 56.92㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 1000 元大兴 1室1厅1卫 1室1厅 / 25㎡ 推荐理由： * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 6600 元我爱我家相寓 西直门交大东路19号院高楼层2居室 2室1厅 / 53.2㎡ 推荐理由： 邻地铁 精装修 * 2500 元温都水城 朝南大复式押一付一 TBD云集中心 平西府地铁站 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元我爱我家相寓 安贞安贞里二区高楼层3居室次卧1 3室1厅 / 12.0㎡ 推荐理由： 邻地铁 精装修 * 2500 元惠新西街中直5号院高楼层3居室次卧2 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 1868 元宋家庄榴景秀苑低楼层3居室次卧1 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 * 5700 元我爱我家相寓 石佛营东风苑小区低楼层1居室 1室1厅 / 55.12㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 8500 元(可以搬家保洁)（周边方便）（业主人好）（高层） 1室1厅 / 76.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1300 元出租南邵地铁站500米合租北次，随时入住看房 3室0厅 / 15㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4100 元我爱我家相寓 角门角门东里低楼层1居室 1室1厅 / 40.8㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4800 元整租龙泽新龙城二期1室1厅 1室1厅 / 54.43㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元幸福时光(通州) 2室1厅1卫 2室1厅 / 89.96㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 5800 元整租木樨地白云观南里2室1厅 2室1厅 / 53.3㎡ 推荐理由： 邻地铁 精装修 * 2400 元实拍 次渠京东班车 民水民电 物业直签0中介费 一二三居都有 1室1厅 / 50㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5900 元新出，丽新嘉园东区 南向一居随时入住 1室1厅 / 65㎡ 推荐理由： 独卫一居 邻地铁 精装修 随时看房 * 8800 元正南 1室1厅 金石美苑 1室1厅 / 72.0㎡ 推荐理由： 独卫一居 邻地铁 * 5600 元整租马家堡福海棠2室1厅 2室1厅 / 74.29㎡ 推荐理由： 精装修 * 5500 元整租北工大松榆东里1室1厅 1室1厅 / 63.88㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 6175 元我爱我家相寓 东大桥芳草地西街中楼层2居室 2室1厅 / 47.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 1000 元西山口村住房 1室0厅1卫 1室0厅 / 25㎡ 推荐理由： 邻地铁 押一付一 * 3000 元我爱我家相寓 惠新西街安苑里中楼层3居室主卧 3室1厅 / 18.0㎡ 推荐理由： 邻地铁 * 2300 元中关村壹号 用友 中关村软件园永旺家园主卧出租价格2300 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 南北通透 * 6800 元整租回龙观国仕汇3室1厅 3室1厅 / 120.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 2100 元北京城建北京密码(东区) 2室1厅1卫 2室1厅 / 57㎡ 推荐理由： 配套齐全 * 800 元辛力庄村住房 1室0厅1卫 1室0厅 / 20㎡ 推荐理由： 押一付一 配套齐全 精装修 首次出租 * 4600 元急租成寿寺地铁口恒悦城南向大开间家电齐全随时看房 1室0厅 / 48㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 5500 元整租劲松劲松八区2室1厅 2室1厅 / 69.28㎡ 推荐理由： 邻地铁 配套齐全 精装修 # 四季青租房房产中介 * 康涛 怡家（北京）住房租赁有限公司 * 于成 北京首嘉房住房租赁有限公司 * 田田 北京天通伟业房地产经纪有限公司 * 初金波 北京麦田房产经纪有限公司 * 周建宇 北京云帆温居住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 王英辉 北京金城阜业房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 常利 北京中世禾房地产经纪有限公司 * 姚景昱 北京欢颜住房租赁有限公司 ## 租房房产问答 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；* 初娟娟： 您好密云这边租房子物业费和暖气费都需要自己交，物业费2.36元每平米 * 问 租房能办居住证吗 * 9mD9xD9： 你好，租房可以办理居住证。；长阳半岛2号院 这个小区主打两居室 三居室 一居室一般都在一层 是属于变异户型 套数比较少 目前在租的一居室没有 租金一般在4500左右 * 陈耀忠： 您好，长阳半岛2号院的租金基本在3800-55000元之间。；* oRZJFym： 您好很高兴为您解答问题:我是麦田柳国华，霞公府位于故宫东侧500米处，租房看房子面积和装修，一个月大约10-15万之间 * 胡海阳： 您好，霞公府小区出租的房源，大概是10万元一个月 * 法瑞玲： 你好，租金大概9万， * 赵长峥： 您好，霞公府小户型的租金在10万左右 * 罗庆瑜： 早安？</x:v>
+        <x:v>未搜索到「百旺青居」对应的房子质量相关信息，同区域相近小区（如百旺家苑）为精装修，房龄较新，物业评价良好，部分房源隔音效果较好；</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v># 四季青160平米租房_北京海淀四季青160平米房屋出租-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 北京160平米租房&gt; 海淀160平米租房&gt; 四季青160平米租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 # 为您找到以下 "160平米" 租房房源 该条件下房源较少，为您推荐： * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 4600 元马家堡嘉园二里高楼层2居室 2室1厅 / 56.92㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 1000 元大兴 1室1厅1卫 1室1厅 / 25㎡ 推荐理由： * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 6600 元我爱我家相寓 西直门交大东路19号院高楼层2居室 2室1厅 / 53.2㎡ 推荐理由： 邻地铁 精装修 * 2500 元温都水城 朝南大复式押一付一 TBD云集中心 平西府地铁站 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元我爱我家相寓 安贞安贞里二区高楼层3居室次卧1 3室1厅 / 12.0㎡ 推荐理由： 邻地铁 精装修 * 2500 元惠新西街中直5号院高楼层3居室次卧2 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 1868 元宋家庄榴景秀苑低楼层3居室次卧1 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 * 5700 元我爱我家相寓 石佛营东风苑小区低楼层1居室 1室1厅 / 55.12㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 8500 元(可以搬家保洁)（周边方便）（业主人好）（高层） 1室1厅 / 76.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1300 元出租南邵地铁站500米合租北次，随时入住看房 3室0厅 / 15㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4100 元我爱我家相寓 角门角门东里低楼层1居室 1室1厅 / 40.8㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4800 元整租龙泽新龙城二期1室1厅 1室1厅 / 54.43㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元幸福时光(通州) 2室1厅1卫 2室1厅 / 89.96㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 5800 元整租木樨地白云观南里2室1厅 2室1厅 / 53.3㎡ 推荐理由： 邻地铁 精装修 * 2400 元实拍 次渠京东班车 民水民电 物业直签0中介费 一二三居都有 1室1厅 / 50㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5900 元新出，丽新嘉园东区 南向一居随时入住 1室1厅 / 65㎡ 推荐理由： 独卫一居 邻地铁 精装修 随时看房 * 8800 元正南 1室1厅 金石美苑 1室1厅 / 72.0㎡ 推荐理由： 独卫一居 邻地铁 * 5600 元整租马家堡福海棠2室1厅 2室1厅 / 74.29㎡ 推荐理由： 精装修 * 5500 元整租北工大松榆东里1室1厅 1室1厅 / 63.88㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 6175 元我爱我家相寓 东大桥芳草地西街中楼层2居室 2室1厅 / 47.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 1000 元西山口村住房 1室0厅1卫 1室0厅 / 25㎡ 推荐理由： 邻地铁 押一付一 * 3000 元我爱我家相寓 惠新西街安苑里中楼层3居室主卧 3室1厅 / 18.0㎡ 推荐理由： 邻地铁 * 2300 元中关村壹号 用友 中关村软件园永旺家园主卧出租价格2300 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 南北通透 * 6800 元整租回龙观国仕汇3室1厅 3室1厅 / 120.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 2100 元北京城建北京密码(东区) 2室1厅1卫 2室1厅 / 57㎡ 推荐理由： 配套齐全 * 800 元辛力庄村住房 1室0厅1卫 1室0厅 / 20㎡ 推荐理由： 押一付一 配套齐全 精装修 首次出租 * 4600 元急租成寿寺地铁口恒悦城南向大开间家电齐全随时看房 1室0厅 / 48㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 5500 元整租劲松劲松八区2室1厅 2室1厅 / 69.28㎡ 推荐理由： 邻地铁 配套齐全 精装修 # 四季青租房房产中介 * 康涛 怡家（北京）住房租赁有限公司 * 于成 北京首嘉房住房租赁有限公司 * 田田 北京天通伟业房地产经纪有限公司 * 初金波 北京麦田房产经纪有限公司 * 周建宇 北京云帆温居住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 王英辉 北京金城阜业房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 常利 北京中世禾房地产经纪有限公司 * 姚景昱 北京欢颜住房租赁有限公司 ## 租房房产问答 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；手机版： 四季青160平米租房 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安阳租房网 * 肇东租房网 * 张家界租房网 * 长岭租房网 * 微山租房网 * 东平租房网 * 太原租房网 * 定边租房网 * 昆明租房网 * 怒江租房网 * 西城租房网 * 怀柔租房网 * 朝阳租房网 * 门头沟租房网 * 平谷租房网 * 海淀租房网 * 大兴租房网 * 房山租房网 * 通州租房网 * 昌平租房网 * CBD租房网 * 安慧桥租房网 * 安贞租房网 * 奥林匹克公园租房网 * 百子湾租房网 * 八里庄租房网 * 北沙滩租房网 * 北苑租房网 * 常营租房网 * 朝青板块租房网 * 朝外大街租房网 * 磁各庄租房网 * 八里桥租房网 * 渤海镇租房网 * 安宁庄租房网 * 滨河路租房网 * 城子街道租房网 * 长阳租房网 * 百善租房网 * 白广路租房网 * 巢湖租房 * 嘉峪关租房 * 平顶山租房 * 沧州租房 * 阿克苏租房 * 巢湖出租 * 嘉峪关出租 * 平顶山出租 * 沧州出租 * 阿克苏出租 * 巢湖整租房 * 嘉峪关整租房 * 平顶山整租房 * 沧州整租房 * 阿克苏整租房 * 巢湖合租房 * 嘉峪关合租房 * 平顶山合租房 * 沧州合租房 * 阿克苏合租房 * 巢湖个人 * 嘉峪关个人 * 平顶山个人 * 沧州个人 * 阿克苏个人 * 西城租房 * 怀柔租房 * 朝阳租房 * 门头沟租房 * 平谷租房 * 西城出租 * 怀柔出租 * 朝阳出租 * 门头沟出租 * 平谷出租 * 西城整租房 * 怀柔整租房 * 朝阳整租房 * 门头沟整租房 * 平谷整租房 * 西城合租房 * 怀柔合租房 * 朝阳合租房 * 门头沟合租房 * 平谷合租房 * 北京一室一厅租房 * 北京两室一厅租房 * 北京两室一卫租房 * 北京四室两厅租房 * 北京五室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京190平米租房 * 北京商场附近租房 * 北京学校附近租房 * 北京新小区租房 * 北京幼儿园附近租房 * 北京小学附近租房 * 北京大学附近租房 * 北京整租租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；可注册办公首次出租南北通透 75000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 距5号线张自忠路站约621米。；交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。</x:v>
-      </x:c>
-      <x:c r="M48" t="str">
-        <x:v>手机版： 四季青160平米租房 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安阳租房网 * 肇东租房网 * 张家界租房网 * 长岭租房网 * 微山租房网 * 东平租房网 * 太原租房网 * 定边租房网 * 昆明租房网 * 怒江租房网 * 西城租房网 * 怀柔租房网 * 朝阳租房网 * 门头沟租房网 * 平谷租房网 * 海淀租房网 * 大兴租房网 * 房山租房网 * 通州租房网 * 昌平租房网 * CBD租房网 * 安慧桥租房网 * 安贞租房网 * 奥林匹克公园租房网 * 百子湾租房网 * 八里庄租房网 * 北沙滩租房网 * 北苑租房网 * 常营租房网 * 朝青板块租房网 * 朝外大街租房网 * 磁各庄租房网 * 八里桥租房网 * 渤海镇租房网 * 安宁庄租房网 * 滨河路租房网 * 城子街道租房网 * 长阳租房网 * 百善租房网 * 白广路租房网 * 巢湖租房 * 嘉峪关租房 * 平顶山租房 * 沧州租房 * 阿克苏租房 * 巢湖出租 * 嘉峪关出租 * 平顶山出租 * 沧州出租 * 阿克苏出租 * 巢湖整租房 * 嘉峪关整租房 * 平顶山整租房 * 沧州整租房 * 阿克苏整租房 * 巢湖合租房 * 嘉峪关合租房 * 平顶山合租房 * 沧州合租房 * 阿克苏合租房 * 巢湖个人 * 嘉峪关个人 * 平顶山个人 * 沧州个人 * 阿克苏个人 * 西城租房 * 怀柔租房 * 朝阳租房 * 门头沟租房 * 平谷租房 * 西城出租 * 怀柔出租 * 朝阳出租 * 门头沟出租 * 平谷出租 * 西城整租房 * 怀柔整租房 * 朝阳整租房 * 门头沟整租房 * 平谷整租房 * 西城合租房 * 怀柔合租房 * 朝阳合租房 * 门头沟合租房 * 平谷合租房 * 北京一室一厅租房 * 北京两室一厅租房 * 北京两室一卫租房 * 北京四室两厅租房 * 北京五室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京190平米租房 * 北京商场附近租房 * 北京学校附近租房 * 北京新小区租房 * 北京幼儿园附近租房 * 北京小学附近租房 * 北京大学附近租房 * 北京整租租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开��,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 距10号线三元桥站约662米。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>未搜索到「百旺青居」对应的生活便利度信息，同区域相近小区靠近地铁（16号线、18号线等），周边有商超、医院等配套，通勤较为便利；</x:v>
+      </x:c>
+      <x:c r="M48" t="str"/>
       <x:c r="N48" t="str">
-        <x:v>价格线索：可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；95000 元/月；115000 元/月；胡同小区 可注册办公首次出租南北通透 250000 元/月；12000 元/月；可注册办公首次出租南北通透 10500 元/月；可注册办公首次出租南北通透 180000 元/月；房屋质量/户型线索：# 四季青160平米租房_北京海淀四季青160平米房屋出租-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 北京160平米租房&gt; 海淀160平米租房&gt; 四季青160平米租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 # 为您找到以下 "160平米" 租房房源 该条件下房源较少，为您推荐： * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 4600 元马家堡嘉园二里高楼层2居室 2室1厅 / 56.92㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 1000 元大兴 1室1厅1卫 1室1厅 / 25㎡ 推荐理由： * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 6600 元我爱我家相寓 西直门交大东路19号院高楼层2居室 2室1厅 / 53.2㎡ 推荐理由： 邻地铁 精装修 * 2500 元温都水城 朝南大复式押一付一 TBD云集中心 平西府地铁站 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元我爱我家相寓 安贞安贞里二区高楼层3居室次卧1 3室1厅 / 12.0㎡ 推荐理由： 邻地铁 精装修 * 2500 元惠新西街中直5号院高楼层3居室次卧2 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 1868 元宋家庄榴景秀苑低楼层3居室次卧1 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 * 5700 元我爱我家相寓 石佛营东风苑小区低楼层1居室 1室1厅 / 55.12㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 8500 元(可以搬家保洁)（周边方便）（业主人好）（高层） 1室1厅 / 76.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1300 元出租南邵地铁站500米合租北次，随时入住看房 3室0厅 / 15㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4100 元我爱我家相寓 角门角门东里低楼层1居室 1室1厅 / 40.8㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4800 元整租龙泽新龙城二期1室1厅 1室1厅 / 54.43㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元幸福时光(通州) 2室1厅1卫 2室1厅 / 89.96㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 5800 元整租木樨地白云观南里2室1厅 2室1厅 / 53.3㎡ 推荐理由： 邻地铁 精装修 * 2400 元实拍 次渠京东班车 民水民电 物业直签0中介费 一二三居都有 1室1厅 / 50㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5900 元新出，丽新嘉园东区 南向一居随时入住 1室1厅 / 65㎡ 推荐理由： 独卫一居 邻地铁 精装修 随时看房 * 8800 元正南 1室1厅 金石美苑 1室1厅 / 72.0㎡ 推荐理由： 独卫一居 邻地铁 * 5600 元整租马家堡福海棠2室1厅 2室1厅 / 74.29㎡ 推荐理由： 精装修 * 5500 元整租北工大松榆东里1室1厅 1室1厅 / 63.88㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 6175 元我爱我家相寓 东大桥芳草地西街中楼层2居室 2室1厅 / 47.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 1000 元西山口村住房 1室0厅1卫 1室0厅 / 25㎡ 推荐理由： 邻地铁 押一付一 * 3000 元我爱我家相寓 惠新西街安苑里中楼层3居室主卧 3室1厅 / 18.0㎡ 推荐理由： 邻地铁 * 2300 元中关村壹号 用友 中关村软件园永旺家园主卧出租价格2300 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 南北通透 * 6800 元整租回龙观国仕汇3室1厅 3室1厅 / 120.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 2100 元北京城建北京密码(东区) 2室1厅1卫 2室1厅 / 57㎡ 推荐理由： 配套齐全 * 800 元辛力庄村住房 1室0厅1卫 1室0厅 / 20㎡ 推荐理由： 押一付一 配套齐全 精装修 首次出租 * 4600 元急租成寿寺地铁口恒悦城南向大开间家电齐全随时看房 1室0厅 / 48㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 5500 元整租劲松劲松八区2室1厅 2室1厅 / 69.28㎡ 推荐理由： 邻地铁 配套齐全 精装修 # 四季青租房房产中介 * 康涛 怡家（北京）住房租赁有限公司 * 于成 北京首嘉房住房租赁有限公司 * 田田 北京天通伟业房地产经纪有限公司 * 初金波 北京麦田房产经纪有限公司 * 周建宇 北京云帆温居住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 王英辉 北京金城阜业房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 常利 北京中世禾房地产经纪有限公司 * 姚景昱 北京欢颜住房租赁有限公司 ## 租房房产问答 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；* 初娟娟： 您好密云这边租房子物业费和暖气费都需要自己交，物业费2.36元每平米 * 问 租房能办居住证吗 * 9mD9xD9： 你好，租房可以办理居住证。；长阳半岛2号院 这个小区主打两居室 三居室 一居室一般都在一层 是属于变异户型 套数比较少 目前在租的一居室没有 租金一般在4500左右 * 陈耀忠： 您好，长阳半岛2号院的租金基本在3800-55000元之间。；* oRZJFym： 您好很高兴为您解答问题:我是麦田柳国华，霞公府位于故宫东侧500米处，租房看房子面积和装修，一个月大约10-15万之间 * 胡海阳： 您好，霞公府小区出租的房源，大概是10万元一个月 * 法瑞玲： 你好，租金大概9万， * 赵长峥： 您好，霞公府小户型的租金在10万左右 * 罗庆瑜： 早安？；生活便利线索：# 四季青160平米租房_北京海淀四季青160平米房屋出租-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 北京160平米租房&gt; 海淀160平米租房&gt; 四季青160平米租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 # 为您找到以下 "160平米" 租房房源 该条件下房源较少，为您推荐： * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 4600 元马家堡嘉园二里高楼层2居室 2室1厅 / 56.92㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 1000 元大兴 1室1厅1卫 1室1厅 / 25㎡ 推荐理由： * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 6600 元我爱我家相寓 西直门交大东路19号院高楼层2居室 2室1厅 / 53.2㎡ 推荐理由： 邻地铁 精装修 * 2500 元温都水城 朝南大复式押一付一 TBD云集中心 平西府地铁站 1室1厅 / 40.0㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元我爱我家相寓 安贞安贞里二区高楼层3居室次卧1 3室1厅 / 12.0㎡ 推荐理由： 邻地铁 精装修 * 2500 元惠新西街中直5号院高楼层3居室次卧2 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 1868 元宋家庄榴景秀苑低楼层3居室次卧1 3室1厅 / 10.0㎡ 推荐理由： 邻地铁 * 5700 元我爱我家相寓 石佛营东风苑小区低楼层1居室 1室1厅 / 55.12㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 8500 元(可以搬家保洁)（周边方便）（业主人好）（高层） 1室1厅 / 76.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1300 元出租南邵地铁站500米合租北次，随时入住看房 3室0厅 / 15㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4100 元我爱我家相寓 角门角门东里低楼层1居室 1室1厅 / 40.8㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 4800 元整租龙泽新龙城二期1室1厅 1室1厅 / 54.43㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 3600 元幸福时光(通州) 2室1厅1卫 2室1厅 / 89.96㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 * 5800 元整租木樨地白云观南里2室1厅 2室1厅 / 53.3㎡ 推荐理由： 邻地铁 精装修 * 2400 元实拍 次渠京东班车 民水民电 物业直签0中介费 一二三居都有 1室1厅 / 50㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5900 元新出，丽新嘉园东区 南向一居随时入住 1室1厅 / 65㎡ 推荐理由： 独卫一居 邻地铁 精装修 随时看房 * 8800 元正南 1室1厅 金石美苑 1室1厅 / 72.0㎡ 推荐理由： 独卫一居 邻地铁 * 5600 元整租马家堡福海棠2室1厅 2室1厅 / 74.29㎡ 推荐理由： 精装修 * 5500 元整租北工大松榆东里1室1厅 1室1厅 / 63.88㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 * 6175 元我爱我家相寓 东大桥芳草地西街中楼层2居室 2室1厅 / 47.82㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 6600 元我爱我家相寓 紫竹桥七贤村中楼层2居室 2室1厅 / 77.3㎡ 推荐理由： 邻地铁 * 1000 元西山口村住房 1室0厅1卫 1室0厅 / 25㎡ 推荐理由： 邻地铁 押一付一 * 3000 元我爱我家相寓 惠新西街安苑里中楼层3居室主卧 3室1厅 / 18.0㎡ 推荐理由： 邻地铁 * 2300 元中关村壹号 用友 中关村软件园永旺家园主卧出租价格2300 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 南北通透 * 6800 元整租回龙观国仕汇3室1厅 3室1厅 / 120.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 2100 元北京城建北京密码(东区) 2室1厅1卫 2室1厅 / 57㎡ 推荐理由： 配套齐全 * 800 元辛力庄村住房 1室0厅1卫 1室0厅 / 20㎡ 推荐理由： 押一付一 配套齐全 精装修 首次出租 * 4600 元急租成寿寺地铁口恒悦城南向大开间家电齐全随时看房 1室0厅 / 48㎡ 推荐理由： 独卫一居 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 5500 元整租劲松劲松八区2室1厅 2室1厅 / 69.28㎡ 推荐理由： 邻地铁 配套齐全 精装修 # 四季青租房房产中介 * 康涛 怡家（北京）住房租赁有限公司 * 于成 北京首嘉房住房租赁有限公司 * 田田 北京天通伟业房地产经纪有限公司 * 初金波 北京麦田房产经纪有限公司 * 周建宇 北京云帆温居住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 王英辉 北京金城阜业房地产经纪有限公司 * 张影 北京唯家兴荣房地产经纪有限公司 * 常利 北京中世禾房地产经纪有限公司 * 姚景昱 北京欢颜住房租赁有限公司 ## 租房房产问答 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；手机版： 四季青160平米租房 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安阳租房网 * 肇东租房网 * 张家界租房网 * 长岭租房网 * 微山租房网 * 东平租房网 * 太原租房网 * 定边租房网 * 昆明租房网 * 怒江租房网 * 西城租房网 * 怀柔租房网 * 朝阳租房网 * 门头沟租房网 * 平谷租房网 * 海淀租房网 * 大兴租房网 * 房山租房网 * 通州租房网 * 昌平租房网 * CBD租房网 * 安慧桥租房网 * 安贞租房网 * 奥林匹克公园租房网 * 百子湾租房网 * 八里庄租房网 * 北沙滩租房网 * 北苑租房网 * 常营租房网 * 朝青板块租房网 * 朝外大街租房网 * 磁各庄租房网 * 八里桥租房网 * 渤海镇租房网 * 安宁庄租房网 * 滨河路租房网 * 城子街道租房网 * 长阳租房网 * 百善租房网 * 白广路租房网 * 巢湖租房 * 嘉峪关租房 * 平顶山租房 * 沧州租房 * 阿克苏租房 * 巢湖出租 * 嘉峪关出租 * 平顶山出租 * 沧州出租 * 阿克苏出租 * 巢湖整租房 * 嘉峪关整租房 * 平顶山整租房 * 沧州整租房 * 阿克苏整租房 * 巢湖合租房 * 嘉峪关合租房 * 平顶山合租房 * 沧州合租房 * 阿克苏合租房 * 巢湖个人 * 嘉峪关个人 * 平顶山个人 * 沧州个人 * 阿克苏个人 * 西城租房 * 怀柔租房 * 朝阳租房 * 门头沟租房 * 平谷租房 * 西城出租 * 怀柔出租 * 朝阳出租 * 门头沟出租 * 平谷出租 * 西城整租房 * 怀柔整租房 * 朝阳整租房 * 门头沟整租房 * 平谷整租房 * 西城合租房 * 怀柔合租房 * 朝阳合租房 * 门头沟合租房 * 平谷合租房 * 北京一室一厅租房 * 北京两室一厅租房 * 北京两室一卫租房 * 北京四室两厅租房 * 北京五室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京190平米租房 * 北京商场附近租房 * 北京学校附近租房 * 北京新小区租房 * 北京幼儿园附近租房 * 北京小学附近租房 * 北京大学附近租房 * 北京整租租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；可注册办公首次出租南北通透 75000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 距5号线张自忠路站约621米。；交通便利南北通透 18000 元/月 ) 能容纳20多人的客厅。；风险线索：手机版： 四季青160平米租房 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 安阳租房网 * 肇东租房网 * 张家界租房网 * 长岭租房网 * 微山租房网 * 东平租房网 * 太原租房网 * 定边租房网 * 昆明租房网 * 怒江租房网 * 西城租房网 * 怀柔租房网 * 朝阳租房网 * 门头沟租房网 * 平谷租房网 * 海淀租房网 * 大兴租房网 * 房山租房网 * 通州租房网 * 昌平租房网 * CBD租房网 * 安慧桥租房网 * 安贞租房网 * 奥林匹克公园租房网 * 百子湾租房网 * 八里庄租房网 * 北沙滩租房网 * 北苑租房网 * 常营租房网 * 朝青板块租房网 * 朝外大街租房网 * 磁各庄租房网 * 八里桥租房网 * 渤海镇租房网 * 安宁庄租房网 * 滨河路租房网 * 城子街道租房网 * 长阳租房网 * 百善租房网 * 白广路租房网 * 巢湖租房 * 嘉峪关租房 * 平顶山租房 * 沧州租房 * 阿克苏租房 * 巢湖出租 * 嘉峪关出租 * 平顶山出租 * 沧州出租 * 阿克苏出租 * 巢湖整租房 * 嘉峪关整租房 * 平顶山整租房 * 沧州整租房 * 阿克苏整租房 * 巢湖合租房 * 嘉峪关合租房 * 平顶山合租房 * 沧州合租房 * 阿克苏合租房 * 巢湖个人 * 嘉峪关个人 * 平顶山个人 * 沧州个人 * 阿克苏个人 * 西城租房 * 怀柔租房 * 朝阳租房 * 门头沟租房 * 平谷租房 * 西城出租 * 怀柔出租 * 朝阳出租 * 门头沟出租 * 平谷出租 * 西城整租房 * 怀柔整租房 * 朝阳整租房 * 门头沟整租房 * 平谷整租房 * 西城合租房 * 怀柔合租房 * 朝阳合租房 * 门头沟合租房 * 平谷合租房 * 北京一室一厅租房 * 北京两室一厅租房 * 北京两室一卫租房 * 北京四室两厅租房 * 北京五室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京190平米租房 * 北京商场附近租房 * 北京学校附近租房 * 北京新小区租房 * 北京幼儿园附近租房 * 北京小学附近租房 * 北京大学附近租房 * 北京整租租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开��,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 距10号线三元桥站约662米。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：小区（如百旺新城春晖园）月租约5000-8200元/月；房屋质量/户型线索：未搜索到「百旺青居」对应的房子质量相关信息，同区域相近小区（如百旺家苑）为精装修，房龄较新，物业评价良好，部分房源隔音效果较好；；生活便利线索：未搜索到「百旺青居」对应的生活便利度信息，同区域相近小区靠近地铁（16号线、18号线等），周边有商超、医院等配套，通勤较为便利；</x:v>
       </x:c>
       <x:c r="O48" t="str">
-        <x:v>1. 四季青160平米租房_北京海淀四季青160平米房屋出租-北京58同城 https://bj.zf.58.com/ssc-48/sijiqinghd/
-2. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://zu.fang.com/default.htm
-3. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-4. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-5. 讨论精选（豆瓣） https://www.douban.com/group/explore</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4595185072415751-3/
+2. http://m.fang.com/xiaoqu/strategy/ts/1316572383.html?position=pingfenbox
+3. http://m.fang.com/zf/bj_xm1010516711/
+4. http://m.anjuke.com/bj/rent/4499451345394698-3/
+5. http://m.anjuke.com/bj/rent/4551706775100428-3/
+6. 马连洼地铁 百旺家苑精装3居 业主初次出租 价格可谈 http://m.anjuke.com/bj/rent/4595185072415751-3/
+7. 小区信息全方位解读 http://m.fang.com/xiaoqu/strategy/ts/1316572383.html?position=pingfenbox
+8. 【百旺新城春晖园租房子_北京海淀百旺新城春晖园租房信息】北京手机房天下 http://m.fang.com/zf/bj_xm1010516711/</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -2594,39 +2730,42 @@
         <x:v>北京市海淀区羊场1号正南方向150米</x:v>
       </x:c>
       <x:c r="E49" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F49" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G49" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H49" t="n">
-        <x:v>8.8</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I49" t="str">
-        <x:v>位于马连洼核心地段，房龄较新且租金数据详实，通勤极便，是综合推荐度最高的小区。</x:v>
-      </x:c>
-      <x:c r="J49" t="str">
-        <x:v> * 四室 * 四室以上 小区本月租金 5683元/月；㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月；㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月；独立阳台 邻地铁 精装修 南北通透 * 2300 元/月；独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月；2厅二手房 188.79㎡ 1500万 79454元/㎡；4室2厅2卫丨189㎡丨南北丨中楼层丨 85800元/㎡； 3室2厅2卫丨177㎡丨南北丨底层丨 87400元/㎡</x:v>
-      </x:c>
+        <x:v>环境安静绿化好，生活医疗便利，但房龄较老且无电梯，高层居住体验受限。</x:v>
+      </x:c>
+      <x:c r="J49" t="str"/>
       <x:c r="K49" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 * 户型 * 价格 * #### 马连洼·天秀花园澄秀园·2室·2厅 2室2厅 90.65㎡**660**万 * #### 2007年商品房,满五唯一商品房,产权清晰 2室1厅 62.54㎡**399**万 * #### 天秀花园澄秀园2室1厅西 1室1厅 65.19㎡**329**万 * #### 马连洼·天秀花园澄秀园·3室·1厅 3室1厅 89.12㎡**738**万 ### 天秀花园澄秀园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 75.75㎡ | 2026-03-08 | -- | -- | 市场信息 | | 86.84㎡ | 2025-08-31 | -- | -- | 市场信息 | | 108.27㎡ | 2025-05-22 | -- | -- | 市场信息 | 查看全部成交 ### 天秀花园澄秀园价格走势 ### 天秀花园澄秀园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 水利局小区 海淀·马连洼**57363** 元/㎡ * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园久盛居 海淀·马连洼**90783** 元/㎡ * #### 马连洼梅园 海淀·马连洼**65210** 元/㎡ ### 相关资讯 * 小区资讯北京天秀花园澄秀园怎么样?；* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 天秀花园澄秀园 &gt;* 天秀花园澄秀园租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 天秀花园澄秀园 海淀 / 马连洼 / 天秀路 小区信息 建筑类别: 多层 总 户 数: 542 建筑年代: 2007年 绿 化 率: 33% 停 车 位:暂无数据 ### 天秀花园澄秀园租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 5683元/月 0.02% 天秀花园澄秀园 ### 天秀花园澄秀园出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 天秀花园澄秀园 精装小两居 南北通透 价格合适 随时看 * 2室1厅|65.19㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月 * * 马连洼天秀花园澄秀 电梯房 精装修 可月付 近地铁 * 3室1厅|11.4㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月 * * 天秀花园澄秀园 3室1厅2卫 * 3室1厅|15㎡ * 马连洼 * 独卫 独立阳台 邻地铁 精装修 南北通透 * 2300 元/月 * * 整租马连洼天秀花园澄秀园1室1厅 * 1室1厅|61.66㎡ * 马连洼 * 独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 天秀花园澄秀园 * 水利社区1号院 * 天秀花园久盛居 * 颐北家苑 * 水利社区二号院 * 圆明园西路甲1号院 * 梅园(海淀) * 百旺家苑 * 天秀花园古月园 * 梅园甲 * 裕隆新村 * 圆明园西路3号院 * 兰园小区 * 农大附中家属院 * 黑山扈路甲17号院 * 润千秋佳苑 * 天秀花园安和园 * 亿城西山华府禧园 * 荷塘月舍 * 农科社区(北区) * 西山庭院 * 亿城西山华府珑园 * 北京大学肖家河教职工家属院二区 * 百草园社区 * 北京大学肖家河教职工家属院三区 * 正黄旗西区 * 正黄旗东区 * 大有北里 * 竹园小区 * 丰泽盈和 首页北京租房天秀花园澄秀园。；本项目是海开在天秀版块的又一力作，规划建筑用地面积4.2万平米，住宅建筑面积5.3万平米，由3栋6.5层的点式楼和9栋6.5层条式板楼组成，主力户型面积为65-130平米，使用率90%左右,是最适合居住的精致型户型。；收藏 2 有用+1 北京市海淀区2007年建成的普通住宅小区 北京海开房地产股份有限公司多年来一直致力于在海淀区内打造精品项目，曾先后开发建设了玉阜嘉园、玉海园、海泰大厦、知春大厦、四通大厦等为代表的一批项目，其丰富的房地产开发经验在房地产业内有口皆碑。</x:v>
+        <x:v>房龄约2007年，为6层普通住宅无电梯（高层不适合老人），户型多南北通透/东西向，部分带露台/复试，装修多为精装修；；隔音相关无明确差评反馈，物业信息未明确提及，小区密度低、绿化较好，建筑质量评价较好；；该小区为老旧小区，无电梯高楼层不适合老人；</x:v>
       </x:c>
       <x:c r="L49" t="str">
-        <x:v>58同城北京小区租房频道为您提供天秀花园澄秀园租房信息，包括天秀花园澄秀园最新出租房源，一室，二室，三室，四室，四室以上租房房源，租金走势和天秀花园澄秀园小区周边租房信息等。；* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 天秀花园澄秀园 &gt;* 天秀花园澄秀园租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 天秀花园澄秀园 海淀 / 马连洼 / 天秀路 小区信息 建筑类别: 多层 总 户 数: 542 建筑年代: 2007年 绿 化 率: 33% 停 车 位:暂无数据 ### 天秀花园澄秀园租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 5683元/月 0.02% 天秀花园澄秀园 ### 天秀花园澄秀园出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 天秀花园澄秀园 精装小两居 南北通透 价格合适 随时看 * 2室1厅|65.19㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月 * * 马连洼天秀花园澄秀 电梯房 精装修 可月付 近地铁 * 3室1厅|11.4㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月 * * 天秀花园澄秀园 3室1厅2卫 * 3室1厅|15㎡ * 马连洼 * 独卫 独立阳台 邻地铁 精装修 南北通透 * 2300 元/月 * * 整租马连洼天秀花园澄秀园1室1厅 * 1室1厅|61.66㎡ * 马连洼 * 独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 天秀花园澄秀园 * 水利社区1号院 * 天秀花园久盛居 * 颐北家苑 * 水利社区二号院 * 圆明园西路甲1号院 * 梅园(海淀) * 百旺家苑 * 天秀花园古月园 * 梅园甲 * 裕隆新村 * 圆明园西路3号院 * 兰园小区 * 农大附中家属院 * 黑山扈路甲17号院 * 润千秋佳苑 * 天秀花园安和园 * 亿城西山华府禧园 * 荷塘月舍 * 农科社区(北区) * 西山庭院 * 亿城西山华府珑园 * 北京大学肖家河教职工家属院二区 * 百草园社区 * 北京大学肖家河教职工家属院三区 * 正黄旗西区 * 正黄旗东区 * 大有北里 * 竹园小区 * 丰泽盈和 首页北京租房天秀花园澄秀园。；秉承“为海淀区知识新贵打造理想生活居所”的理念，海开在天秀板块已经建造了“海开天秀花园”和“天秀.泊心湾”这种建筑与与自然充分交融的独特产品,在建筑设计细节上充分体现了独特意蕴与人文关怀。；## 配套信息 播报 编辑 地铁：4号线 安河桥北 [](https://baike.baidu.com/pic/%E5%A4%A9%E7%A7%80%E8%8A%B1%E5%9B%AD%E6%BE%84%E7%A7%80%E5%9B%AD/12790482/0/e1fe9925bc315c60c127fa928fb1cb1349547719?；fr=lemma&amp;fromModule=lemma_content-image) 公交：333路 中国农业大学西校区 学校：红缨幼儿园、清华大学幼儿园、体大幼儿园、北京市海淀区红山小学、101中学、中关村实验中学、中央民族干部学院 医院：309医院、上地医院、西苑医院、二炮医院、海淀区青龙桥医院 银行：农业银行黑山户路储蓄所、北京农村商业银行天秀分理处 超市：万树园社区超市、美廉美超市、宝客隆超市、天秀花园超市、百旺苑超市 餐饮：北京田园庄饭店、康岛酒楼、未名山庄、三正大酒楼 ## 售卖信息 播报 编辑 价格走势：本月均价：43258元/平米，环比上月上涨4.01%，小区共有出售房源0套，出租房源0套，服务该小区的经纪人有0位。</x:v>
-      </x:c>
-      <x:c r="M49" t="str"/>
+        <x:v>1.通勤：临近16号线农大南路地铁站（步行约1.1公里），靠近18号线、4号线相关站点，周边有391路等公交；；2.商超：步行可达中发百旺商城、北京华联BHG Mall、天秀生活超市等；；3.医疗：距解放军总医院第八医学中心约765米；；4.餐饮/生活配套：周边餐饮、生活设施齐全，小区内有超市、健身场地等；</x:v>
+      </x:c>
+      <x:c r="M49" t="str">
+        <x:v>隔音相关无明确差评反馈，物业信息未明确提及，小区密度低、绿化较好，建筑质量评价较好；；该小区为老旧小区，无电梯高楼层不适合老人；</x:v>
+      </x:c>
       <x:c r="N49" t="str">
-        <x:v>价格线索： * 四室 * 四室以上 小区本月租金 5683元/月；㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月；㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月；独立阳台 邻地铁 精装修 南北通透 * 2300 元/月；独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月；2厅二手房 188.79㎡ 1500万 79454元/㎡；4室2厅2卫丨189㎡丨南北丨中楼层丨 85800元/㎡； 3室2厅2卫丨177㎡丨南北丨底层丨 87400元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 * 户型 * 价格 * #### 马连洼·天秀花园澄秀园·2室·2厅 2室2厅 90.65㎡**660**万 * #### 2007年商品房,满五唯一商品房,产权清晰 2室1厅 62.54㎡**399**万 * #### 天秀花园澄秀园2室1厅西 1室1厅 65.19㎡**329**万 * #### 马连洼·天秀花园澄秀园·3室·1厅 3室1厅 89.12㎡**738**万 ### 天秀花园澄秀园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 75.75㎡ | 2026-03-08 | -- | -- | 市场信息 | | 86.84㎡ | 2025-08-31 | -- | -- | 市场信息 | | 108.27㎡ | 2025-05-22 | -- | -- | 市场信息 | 查看全部成交 ### 天秀花园澄秀园价格走势 ### 天秀花园澄秀园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 水利局小区 海淀·马连洼**57363** 元/㎡ * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园久盛居 海淀·马连洼**90783** 元/㎡ * #### 马连洼梅园 海淀·马连洼**65210** 元/㎡ ### 相关资讯 * 小区资讯北京天秀花园澄秀园怎么样?；* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 天秀花园澄秀园 &gt;* 天秀花园澄秀园租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 天秀花园澄秀园 海淀 / 马连洼 / 天秀路 小区信息 建筑类别: 多层 总 户 数: 542 建筑年代: 2007年 绿 化 率: 33% 停 车 位:暂无数据 ### 天秀花园澄秀园租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 5683元/月 0.02% 天秀花园澄秀园 ### 天秀花园澄秀园出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 天秀花园澄秀园 精装小两居 南北通透 价格合适 随时看 * 2室1厅|65.19㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月 * * 马连洼天秀花园澄秀 电梯房 精装修 可月付 近地铁 * 3室1厅|11.4㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月 * * 天秀花园澄秀园 3室1厅2卫 * 3室1厅|15㎡ * 马连洼 * 独卫 独立阳台 邻地铁 精装修 南北通透 * 2300 元/月 * * 整租马连洼天秀花园澄秀园1室1厅 * 1室1厅|61.66㎡ * 马连洼 * 独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 天秀花园澄秀园 * 水利社区1号院 * 天秀花园久盛居 * 颐北家苑 * 水利社区二号院 * 圆明园西路甲1号院 * 梅园(海淀) * 百旺家苑 * 天秀花园古月园 * 梅园甲 * 裕隆新村 * 圆明园西路3号院 * 兰园小区 * 农大附中家属院 * 黑山扈路甲17号院 * 润千秋佳苑 * 天秀花园安和园 * 亿城西山华府禧园 * 荷塘月舍 * 农科社区(北区) * 西山庭院 * 亿城西山华府珑园 * 北京大学肖家河教职工家属院二区 * 百草园社区 * 北京大学肖家河教职工家属院三区 * 正黄旗西区 * 正黄旗东区 * 大有北里 * 竹园小区 * 丰泽盈和 首页北京租房天秀花园澄秀园。；本项目是海开在天秀版块的又一力作，规划建筑用地面积4.2万平米，住宅建筑面积5.3万平米，由3栋6.5层的点式楼和9栋6.5层条式板楼组成，主力户型面积为65-130平米，使用率90%左右,是最适合居住的精致型户型。；收藏 2 有用+1 北京市海淀区2007年建成的普通住宅小区 北京海开房地产股份有限公司多年来一直致力于在海淀区内打造精品项目，曾先后开发建设了玉阜嘉园、玉海园、海泰大厦、知春大厦、四通大厦等为代表的一批项目，其丰富的房地产开发经验在房地产业内有口皆碑。；生活便利线索：58同城北京小区租房频道为您提供天秀花园澄秀园租房信息，包括天秀花园澄秀园最新出租房源，一室，二室，三室，四室，四室以上租房房源，租金走势和天秀花园澄秀园小区周边租房信息等。；* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 天秀花园澄秀园 &gt;* 天秀花园澄秀园租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 天秀花园澄秀园 海淀 / 马连洼 / 天秀路 小区信息 建筑类别: 多层 总 户 数: 542 建筑年代: 2007年 绿 化 率: 33% 停 车 位:暂无数据 ### 天秀花园澄秀园租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 5683元/月 0.02% 天秀花园澄秀园 ### 天秀花园澄秀园出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 天秀花园澄秀园 精装小两居 南北通透 价格合适 随时看 * 2室1厅|65.19㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月 * * 马连洼天秀花园澄秀 电梯房 精装修 可月付 近地铁 * 3室1厅|11.4㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月 * * 天秀花园澄秀园 3室1厅2卫 * 3室1厅|15㎡ * 马连洼 * 独卫 独立阳台 邻地铁 精装修 南北通透 * 2300 元/月 * * 整租马连洼天秀花园澄秀园1室1厅 * 1室1厅|61.66㎡ * 马连洼 * 独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 天秀花园澄秀园 * 水利社区1号院 * 天秀花园久盛居 * 颐北家苑 * 水利社区二号院 * 圆明园西路甲1号院 * 梅园(海淀) * 百旺家苑 * 天秀花园古月园 * 梅园甲 * 裕隆新村 * 圆明园西路3号院 * 兰园小区 * 农大附中家属院 * 黑山扈路甲17号院 * 润千秋佳苑 * 天秀花园安和园 * 亿城西山华府禧园 * 荷塘月舍 * 农科社区(北区) * 西山庭院 * 亿城西山华府珑园 * 北京大学肖家河教职工家属院二区 * 百草园社区 * 北京大学肖家河教职工家属院三区 * 正黄旗西区 * 正黄旗东区 * 大有北里 * 竹园小区 * 丰泽盈和 首页北京租房天秀花园澄秀园。；秉承“为海淀区知识新贵打造理想生活居所”的理念，海开在天秀板块已经建造了“海开天秀花园”和“天秀.泊心湾”这种建筑与与自然充分交融的独特产品,在建筑设计细节上充分体现了独特意蕴与人文关怀。；## 配套信息 播报 编辑 地铁：4号线 安河桥北 [](https://baike.baidu.com/pic/%E5%A4%A9%E7%A7%80%E8%8A%B1%E5%9B%AD%E6%BE%84%E7%A7%80%E5%9B%AD/12790482/0/e1fe9925bc315c60c127fa928fb1cb1349547719?；fr=lemma&amp;fromModule=lemma_content-image) 公交：333路 中国农业大学西校区 学校：红缨幼儿园、清华大学幼儿园、体大幼儿园、北京市海淀区红山小学、101中学、中关村实验中学、中央民族干部学院 医院：309医院、上地医院、西苑医院、二炮医院、海淀区青龙桥医院 银行：农业银行黑山户路储蓄所、北京农村商业银行天秀分理处 超市：万树园社区超市、美廉美超市、宝客隆超市、天秀花园超市、百旺苑超市 餐饮：北京田园庄饭店、康岛酒楼、未名山庄、三正大酒楼 ## 售卖信息 播报 编辑 价格走势：本月均价：43258元/平米，环比上月上涨4.01%，小区共有出售房源0套，出租房源0套，服务该小区的经纪人有0位。</x:v>
+        <x:v>房屋质量/户型线索：房龄约2007年，为6层普通住宅无电梯（高层不适合老人），户型多南北通透/东西向，部分带露台/复试，装修多为精装修；；隔音相关无明确差评反馈，物业信息未明确提及，小区密度低、绿化较好，建筑质量评价较好；；该小区为老旧小区，无电梯高楼层不适合老人；；生活便利线索：1.通勤：临近16号线农大南路地铁站（步行约1.1公里），靠近18号线、4号线相关站点，周边有391路等公交；；2.商超：步行可达中发百旺商城、北京华联BHG Mall、天秀生活超市等；；3.医疗：距解放军总医院第八医学中心约765米；；4.餐饮/生活配套：周边餐饮、生活设施齐全，小区内有超市、健身场地等；；风险线索：隔音相关无明确差评反馈，物业信息未明确提及，小区密度低、绿化较好，建筑质量评价较好；；该小区为老旧小区，无电梯高楼层不适合老人；</x:v>
       </x:c>
       <x:c r="O49" t="str">
-        <x:v>1. 【北京天秀花园澄秀园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010090280.htm
-2. 【天秀花园澄秀园，北京天秀花园澄秀园租房，最新出租房源，租金走势信息】- 北京58同城 https://m.58.com/bj/xq/600375/
-3. 天秀花园澄秀园 https://baike.baidu.com/item/%E5%A4%A9%E7%A7%80%E8%8A%B1%E5%9B%AD%E6%BE%84%E7%A7%80%E5%9B%AD/12790482
-4. 天秀花园古月园房价怎么样？ 北京天秀花园古月园房源|户型图|小区车位|交通地址详情分析 https://m.ke.com/news/bj/xiaoqu/1111027380063.html
-5. 天秀花园古月园_北京天秀花园古月园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/166716.html</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4576982772161536-3/
+2. http://m.anjuke.com/ch/rent/4565666585551872-3/
+3. http://m.anjuke.com/dongyang/rent/4524980267195393-3/
+4. http://m.anjuke.com/bj/community/187304/jiedu/
+5. http://m.anjuke.com/bj/rent/4566840211840004-3/
+6. http://m.anjuke.com/bj/rent/4597928491541513-3/
+7. 租金可谈 天秀花园澄秀园 80平 大两居 实房实图 业主直签 http://m.anjuke.com/bj/rent/4576982772161536-3/
+8. 天秀花园澄秀园 精装大三居 配置齐全 干净整洁 价格可优惠 http://m.anjuke.com/ch/rent/4565666585551872-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -2643,39 +2782,44 @@
         <x:v>北京市海淀区西北旺四街与茉莉园北路交叉口东南方向264米</x:v>
       </x:c>
       <x:c r="E50" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F50" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G50" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H50" t="n">
         <x:v>8.5</x:v>
       </x:c>
       <x:c r="I50" t="str">
-        <x:v>离网易近，租金较高但配套成熟，证据充分，是互联网大厂员工的首选小区。</x:v>
+        <x:v>紧邻地铁和万象汇，通勤极便，房龄适中且户型方正，需留意局部装修噪音。</x:v>
       </x:c>
       <x:c r="J50" t="str">
-        <x:v>2026-02-25 | 665万 | 57787元/㎡；2026-01-26 | 708万 | 56654元/㎡；百旺茉莉园(一期)租金 ; 一室8000元/月；0.00% ; 二室9703元/月；+3.73% ; 三室12375元/月；+3.13% ; 四室15000元/月；0.00% ; 四室以上16500元/月；000_ 元/m² 百旺茉莉园，小区价格78958元/㎡</x:v>
+        <x:v>整租两居约9800元/月；、3居12800元/月；、5居16500元/月；，合租主卧约3800元/月</x:v>
       </x:c>
       <x:c r="K50" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **75443** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.8% 贷款计算器 * 二手房源 87套 * 最近成交 357套 * 楼栋总数 58栋 * 房屋总数 2145户 * 建筑类型 板塔结合 * 建筑年代 2005年建成 * 小区位置 (海淀)德政路南茉莉园地图 * 物业公司 北京德成永信物业管理有限公司 * 开发商 北京德成兴业房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 李强 评分：4.6 从业信息卡 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 ### 百旺茉莉园主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010077340/photo/?；北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺茉莉园_北京百旺茉莉园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺茉莉园 更新于 2026-06-01 10:51:55 [](https://bj.jiwu.com/tu/4226505.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/4226506.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/4226507.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628429.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628430.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628431.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628432.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628433.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628434.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628435.html "百旺茉莉园实景图图片") # 百旺茉莉园 别名：百旺茉莉园 加入本地买房群 关注 _北京 - 海淀 - 海淀区西北旺四街_ 发地址到手机 参考均价 _78958 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _1490_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-78群（447） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(3)3室(2)4室(1) 全部户型 [](https://bj.jiwu.com/huxing/675689.html "百旺茉莉园3室2厅2卫178㎡户型图")3室2厅2卫 178㎡咨询户型房源 [](https://bj.jiwu.com/huxing/675690.html "百旺茉莉园1室1厅1卫户型图")1室1厅1卫咨询户型房源 [](https://bj.jiwu.com/huxing/675691.html "百旺茉莉园4室2厅2卫297㎡户型图")4室2厅2卫 297㎡咨询户型房源 小区评测报告 ？</x:v>
+        <x:v>房龄约2005年，有板塔结合楼栋；；户型主打方正、明厨明卫；；物业为北京德成永信物业，物业费4.8元/㎡·月，小区绿化率40%，部分高层带电梯；；存在楼上装修噪音影响的情况；；未发现明确针对租房的差评或误命中风险，仅部分用户反映楼上装修噪音问题。</x:v>
       </x:c>
       <x:c r="L50" t="str">
-        <x:v>北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺茉莉园_北京百旺茉莉园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺茉莉园 更新于 2026-06-01 10:51:55 [](https://bj.jiwu.com/tu/4226505.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/4226506.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/4226507.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628429.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628430.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628431.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628432.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628433.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628434.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628435.html "百旺茉莉园实景图图片") # 百旺茉莉园 别名：百旺茉莉园 加入本地买房群 关注 _北京 - 海淀 - 海淀区西北旺四街_ 发地址到手机 参考均价 _78958 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _1490_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-78群（447） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(3)3室(2)4室(1) 全部户型 [](https://bj.jiwu.com/huxing/675689.html "百旺茉莉园3室2厅2卫178㎡户型图")3室2厅2卫 178㎡咨询户型房源 [](https://bj.jiwu.com/huxing/675690.html "百旺茉莉园1室1厅1卫户型图")1室1厅1卫咨询户型房源 [](https://bj.jiwu.com/huxing/675691.html "百旺茉莉园4室2厅2卫297㎡户型图")4室2厅2卫 297㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?</x:v>
-      </x:c>
-      <x:c r="M50" t="str"/>
+        <x:v>临近16号线西北旺站（步行约445米），周边有华联超市、盒马鲜生、西北旺万象汇等商超，百旺公园近，餐饮、休闲配套全，通勤及生活便利；</x:v>
+      </x:c>
+      <x:c r="M50" t="str">
+        <x:v>存在楼上装修噪音影响的情况；；未发现明确针对租房的差评或误命中风险，仅部分用户反映楼上装修噪音问题。；未发现明确针对租房的差评或误命中风险，仅部分用户反映楼上装修噪音问题</x:v>
+      </x:c>
       <x:c r="N50" t="str">
-        <x:v>价格线索：2026-02-25 | 665万 | 57787元/㎡；2026-01-26 | 708万 | 56654元/㎡；百旺茉莉园(一期)租金 ; 一室8000元/月；0.00% ; 二室9703元/月；+3.73% ; 三室12375元/月；+3.13% ; 四室15000元/月；0.00% ; 四室以上16500元/月；000_ 元/m² 百旺茉莉园，小区价格78958元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **75443** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.8% 贷款计算器 * 二手房源 87套 * 最近成交 357套 * 楼栋总数 58栋 * 房屋总数 2145户 * 建筑类型 板塔结合 * 建筑年代 2005年建成 * 小区位置 (海淀)德政路南茉莉园地图 * 物业公司 北京德成永信物业管理有限公司 * 开发商 北京德成兴业房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 李强 评分：4.6 从业信息卡 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 ### 百旺茉莉园主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010077340/photo/?；北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺茉莉园_北京百旺茉莉园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺茉莉园 更新于 2026-06-01 10:51:55 [](https://bj.jiwu.com/tu/4226505.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/4226506.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/4226507.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628429.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628430.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628431.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628432.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628433.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628434.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628435.html "百旺茉莉园实景图图片") # 百旺茉莉园 别名：百旺茉莉园 加入本地买房群 关注 _北京 - 海淀 - 海淀区西北旺四街_ 发地址到手机 参考均价 _78958 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _1490_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-78群（447） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(3)3室(2)4室(1) 全部户型 [](https://bj.jiwu.com/huxing/675689.html "百旺茉莉园3室2厅2卫178㎡户型图")3室2厅2卫 178㎡咨询户型房源 [](https://bj.jiwu.com/huxing/675690.html "百旺茉莉园1室1厅1卫户型图")1室1厅1卫咨询户型房源 [](https://bj.jiwu.com/huxing/675691.html "百旺茉莉园4室2厅2卫297㎡户型图")4室2厅2卫 297㎡咨询户型房源 小区评测报告 ？；生活便利线索：北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺茉莉园_北京百旺茉莉园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺茉莉园 更新于 2026-06-01 10:51:55 [](https://bj.jiwu.com/tu/4226505.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/4226506.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/4226507.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628429.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628430.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628431.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628432.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628433.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628434.html "百旺茉莉园实景图图片")[](https://bj.jiwu.com/tu/3628435.html "百旺茉莉园实景图图片") # 百旺茉莉园 别名：百旺茉莉园 加入本地买房群 关注 _北京 - 海淀 - 海淀区西北旺四街_ 发地址到手机 参考均价 _78958 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _-_ 小区户数 _1490_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-78群（447） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(1)2室(3)3室(2)4室(1) 全部户型 [](https://bj.jiwu.com/huxing/675689.html "百旺茉莉园3室2厅2卫178㎡户型图")3室2厅2卫 178㎡咨询户型房源 [](https://bj.jiwu.com/huxing/675690.html "百旺茉莉园1室1厅1卫户型图")1室1厅1卫咨询户型房源 [](https://bj.jiwu.com/huxing/675691.html "百旺茉莉园4室2厅2卫297㎡户型图")4室2厅2卫 297㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?</x:v>
+        <x:v>价格线索：整租两居约9800元/月；、3居12800元/月；、5居16500元/月；，合租主卧约3800元/月；房屋质量/户型线索：房龄约2005年，有板塔结合楼栋；；户型主打方正、明厨明卫；；物业为北京德成永信物业，物业费4.8元/㎡·月，小区绿化率40%，部分高层带电梯；；存在楼上装修噪音影响的情况；；未发现明确针对租房的差评或误命中风险，仅部分用户反映楼上装修噪音问题。；生活便利线索：临近16号线西北旺站（步行约445米），周边有华联超市、盒马鲜生、西北旺万象汇等商超，百旺公园近，餐饮、休闲配套全，通勤及生活便利；；风险线索：存在楼上装修噪音影响的情况；；未发现明确针对租房的差评或误命中风险，仅部分用户反映楼上装修噪音问题。；未发现明确针对租房的差评或误命中风险，仅部分用户反映楼上装修噪音问题</x:v>
       </x:c>
       <x:c r="O50" t="str">
-        <x:v>1. 【北京百旺茉莉园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010077340.htm
-2. 百旺茉莉园(一期)详情介绍 - 58同城 http://mob.58.com/zfxq/bj-sy100394652/
-3. 百旺茉莉园_北京百旺茉莉园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/166584.html
-4. 百旺茉莉园(一期),百旺茉莉园(一期)房源,西北旺永丰路西,百旺茉莉园(一期)房价、二手房、租房信息-幸福里 https://fangchan.toutiao.com/xiaoqu/bj-6581412573957062919.html
-5. 百旺茉莉园二手房 - 司法拍卖房产【瀚海法拍网】 https://www.fapai.cn/xiaoqu/125.html?houseId=7642</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4534839460715528-3/
+2. http://m.anjuke.com/bj/rent/3951641476358157-3/
+3. http://m.anjuke.com/bj/rent/4602078407273476-3/
+4. http://m.anjuke.com/bj/rent/4516262462612486-3/
+5. https://m.xflapp.com/owner-comment/6581412573957062919/7017272827875197477
+6. https://esf.fang.com/loupan/1010077340.htm
+7. 这么好的茉莉园真的没人看看吗 http://m.anjuke.com/bj/rent/4534839460715528-3/
+8. 社区环境好 随时起租 南北通透 3室2厅 百旺茉莉园(一期) http://m.anjuke.com/bj/rent/3951641476358157-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -2692,40 +2836,42 @@
         <x:v>北京市海淀区绿苑201号</x:v>
       </x:c>
       <x:c r="E51" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F51" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G51" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H51" t="n">
-        <x:v>3</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="I51" t="str">
-        <x:v>搜索证据严重偏离，混入大量豪宅信息，缺乏该小区真实数据，评分较为保守。</x:v>
+        <x:v>租金较低且生活配套成熟，但房龄极老（70年代）且离地铁较远，品质受限。</x:v>
       </x:c>
       <x:c r="J51" t="str">
-        <x:v>-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；寺四合院 可注册办公首次出租南北通透 210000 元/月；105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月；道湾东巷 可注册办公首次出租南北通透 120000 元/月；镇江胡同 可注册办公首次出租南北通透 140000 元/月</x:v>
+        <x:v>合租主卧：2199-3000元/月；（如朝南主卧2766元/月；、朝南主卧2199元/月；整租：6800-9400元/月；（如2室整租6800元/月；、3室整租7500-9400元/月</x:v>
       </x:c>
       <x:c r="K51" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 丽苑公寓 [](https://www.yudinggongyu.com/) 010-6882-8588 * 首页 * 北京服务式公寓 * 服务式公寓地图 * 优惠活动 * 公寓新闻 * 推广服务 * 联系我们 首页&gt;北京服务式公寓&gt;王府井 # 丽苑公寓 ¥**25000** 起/月 评分：4.7 预约参观 优质房源 专业服务，品质保障 * 小区名称 丽苑公寓地图 * 出租房型 1-3 居室 * 房型面积 105-225 m² * 公寓类型 服务式公寓 * 所在区域 北京市东城区王府井金鱼胡同18号 * 地铁路线 * 租售属性 出租 * 看房时间 提前预约 * 室内 丽苑公寓 房源简介 * ### 2014 开业 * ### 2014 装修 * ### 不允许养宠物 宠物政策 北京丽苑公寓毗邻王府井大街和金宝街，交通便捷，地铁五号线及1号张近在咫尺，周边名胜古迹及旅游景点比比皆是。；60平方米的户型设计，简约而温馨，最适合单身时尚的您在京小住。</x:v>
+        <x:v>建于1970年，无物业公司；；板楼为主，户型多为2室1厅、3室1厅；；部分房源精装修，家电家具齐全；；提及环境优雅、干净整洁，但未明确提到隔音情况；；摘要6中提到的十堰市绿苑小区（非目标海淀区绿苑201号）信息，房龄较老、停车位不足，需明确区分该误命中信息（非本次查询的海淀区绿苑201号）。</x:v>
       </x:c>
       <x:c r="L51" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；丽苑公寓毗邻王府井大街和金宝街，交通便捷，地铁五号线及1号张近在咫尺，周边名胜古迹及旅游景点比比皆是。；# 丽苑公寓 [](https://www.yudinggongyu.com/) 010-6882-8588 * 首页 * 北京服务式公寓 * 服务式公寓地图 * 优惠活动 * 公寓新闻 * 推广服务 * 联系我们 首页&gt;北京服务式公寓&gt;王府井 # 丽苑公寓 ¥**25000** 起/月 评分：4.7 预约参观 优质房源 专业服务，品质保障 * 小区名称 丽苑公寓地图 * 出租房型 1-3 居室 * 房型面积 105-225 m² * 公寓类型 服务式公寓 * 所在区域 北京市东城区王府井金鱼胡同18号 * 地铁路线 * 租售属性 出租 * 看房时间 提前预约 * 室内 丽苑公寓 房源简介 * ### 2014 开业 * ### 2014 装修 * ### 不允许养宠物 宠物政策 北京丽苑公寓毗邻王府井大街和金宝街，交通便捷，地铁五号线及1号张近在咫尺，周边名胜古迹及旅游景点比比皆是。</x:v>
-      </x:c>
-      <x:c r="M51" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>交通：地铁16号线农大南路站步行约1584米，16号线马连洼站步行约1944米，近上地、软件园、中关村，通勤便利；；生活配套：步行可达超市、菜场、百旺商城，餐饮、购物、休闲一站式满足；；紧邻中国农业大学西区，周边有小学、中学，教育资源近。</x:v>
+      </x:c>
+      <x:c r="M51" t="str"/>
       <x:c r="N51" t="str">
-        <x:v>价格线索：-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；寺四合院 可注册办公首次出租南北通透 210000 元/月；105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月；道湾东巷 可注册办公首次出租南北通透 120000 元/月；镇江胡同 可注册办公首次出租南北通透 140000 元/月；房屋质量/户型线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 丽苑公寓 [](https://www.yudinggongyu.com/) 010-6882-8588 * 首页 * 北京服务式公寓 * 服务式公寓地图 * 优惠活动 * 公寓新闻 * 推广服务 * 联系我们 首页&gt;北京服务式公寓&gt;王府井 # 丽苑公寓 ¥**25000** 起/月 评分：4.7 预约参观 优质房源 专业服务，品质保障 * 小区名称 丽苑公寓地图 * 出租房型 1-3 居室 * 房型面积 105-225 m² * 公寓类型 服务式公寓 * 所在区域 北京市东城区王府井金鱼胡同18号 * 地铁路线 * 租售属性 出租 * 看房时间 提前预约 * 室内 丽苑公寓 房源简介 * ### 2014 开业 * ### 2014 装修 * ### 不允许养宠物 宠物政策 北京丽苑公寓毗邻王府井大街和金宝街，交通便捷，地铁五号线及1号张近在咫尺，周边名胜古迹及旅游景点比比皆是。；60平方米的户型设计，简约而温馨，最适合单身时尚的您在京小住。；生活便利线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；丽苑公寓毗邻王府井大街和金宝街，交通便捷，地铁五号线及1号张近在咫尺，周边名胜古迹及旅游景点比比皆是。；# 丽苑公寓 [](https://www.yudinggongyu.com/) 010-6882-8588 * 首页 * 北京服务式公寓 * 服务式公寓地图 * 优惠活动 * 公寓新闻 * 推广服务 * 联系我们 首页&gt;北京服务式公寓&gt;王府井 # 丽苑公寓 ¥**25000** 起/月 评分：4.7 预约参观 优质房源 专业服务，品质保障 * 小区名称 丽苑公寓地图 * 出租房型 1-3 居室 * 房型面积 105-225 m² * 公寓类型 服务式公寓 * 所在区域 北京市东城区王府井金鱼胡同18号 * 地铁路线 * 租售属性 出租 * 看房时间 提前预约 * 室内 丽苑公寓 房源简介 * ### 2014 开业 * ### 2014 装修 * ### 不允许养宠物 宠物政策 北京丽苑公寓毗邻王府井大街和金宝街，交通便捷，地铁五号线及1号张近在咫尺，周边名胜古迹及旅游景点比比皆是。；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：合租主卧：2199-3000元/月；（如朝南主卧2766元/月；、朝南主卧2199元/月；整租：6800-9400元/月；（如2室整租6800元/月；、3室整租7500-9400元/月；房屋质量/户型线索：建于1970年，无物业公司；；板楼为主，户型多为2室1厅、3室1厅；；部分房源精装修，家电家具齐全；；提及环境优雅、干净整洁，但未明确提到隔音情况；；摘要6中提到的十堰市绿苑小区（非目标海淀区绿苑201号）信息，房龄较老、停车位不足，需明确区分该误命中信息（非本次查询的海淀区绿苑201号）。；生活便利线索：交通：地铁16号线农大南路站步行约1584米，16号线马连洼站步行约1944米，近上地、软件园、中关村，通勤便利；；生活配套：步行可达超市、菜场、百旺商城，餐饮、购物、休闲一站式满足；；紧邻中国农业大学西区，周边有小学、中学，教育资源近。</x:v>
       </x:c>
       <x:c r="O51" t="str">
-        <x:v>1. 【北京pg娱乐电子游戏ty64.cc租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kwpg%E5%A8%B1%E4%B9%90%E7%94%B5%E5%AD%90%E6%B8%B8%E6%88%8Fty64.cc?71%20target=_blank
-2. 丽苑公寓 https://www.yudinggongyu.com/beijing/46.cshtml
-3. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-4. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. https://bj.zu.anjuke.com/fangyuan/4319294663306247
+2. http://m.anjuke.com/bj/rent/4479535429889036-3/
+3. http://m.anjuke.com/shi/community/684899/zujin/
+4. https://m.5i5j.com/bj/xq_news/61180.html
+5. https://beijing.anjuke.com/community/props/rent/850634
+6. 【多图】绿苑小区，马连洼租房，价格能谈，绿苑小区，朝南精装主卧，集中供暖，全女生合租，海淀租房 https://bj.zu.anjuke.com/fangyuan/4319294663306247
+7. 北京绿苑小区房源 近农大近地铁 生活舒适出行方便 http://m.anjuke.com/bj/rent/4479535429889036-3/
+8. 绿苑小区租房价格 http://m.anjuke.com/shi/community/684899/zujin/</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -2742,40 +2888,42 @@
         <x:v>海淀区永丰路与茉莉园南路交汇处西北侧</x:v>
       </x:c>
       <x:c r="E52" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F52" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G52" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H52" t="n">
-        <x:v>8.2</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="I52" t="str">
-        <x:v>地理位置优越，租金水平透明，虽有部分泛化SEO信息，但整体居住推荐度高。</x:v>
+        <x:v>位于大厂核心区，配套完善且交通极便，是网易员工平衡品质与通勤的首选。</x:v>
       </x:c>
       <x:c r="J52" t="str">
-        <x:v>2026-02-25 | 665万 | 57787元/㎡；2026-01-26 | 708万 | 56654元/㎡；三室 * 四室 * 四室以上 * 一室 8000元/月； 0.00% * 二室 9200元/月；-5.11% * 三室 12133元/月；-1.59% * 四室 15000元/月； 0.00% * 四室以上 16500元/月；称 月租金 涨跌幅 * 1.臻园(南区)12600元/月</x:v>
+        <x:v>合租：16号线西北旺站附近，次卧1800-2300元/月；，主卧3999-4199元/月；整租：3室1厅11500元/月；（129.41㎡）、3室2厅10200-13000元/月；、4室2厅15000-21500元/月；、5室2厅16500元/月</x:v>
       </x:c>
       <x:c r="K52" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **75443** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.8% 贷款计算器 * 二手房源 87套 * 最近成交 357套 * 楼栋总数 58栋 * 房屋总数 2145户 * 建筑类型 板塔结合 * 建筑年代 2005年建成 * 小区位置 (海淀)德政路南茉莉园地图 * 物业公司 北京德成永信物业管理有限公司 * 开发商 北京德成兴业房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 李强 评分：4.6 从业信息卡 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 ### 百旺茉莉园主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010077340/photo/?；# 百旺茉莉园(一期)租房,西北旺百旺茉莉园(一期)房屋出租价格,百旺茉莉园(一期)整租合租房价-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;西北旺小区 &gt;百旺茉莉园(一期)&gt;百旺茉莉园(一期)租房 百旺茉莉园(一期) * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 # 百旺茉莉园(一期) * 物业类型：公寓住宅 * 竣工时间：2005 * 总户数：1498 * 容积数：1.34 * 建筑类型：多层、小高层 * 统一供暖：否 * 停车位：1723（1:1.15） * 车位管理费：暂无数据 * 小区地址：西北旺四街 * 幼儿园：暂无数据 * 小学：海淀区中关村第二小学百旺校区 * 初中：暂无数据 * 权属类别：商品房住宅 * 产权年限：暂无数据 * 总建面积：暂无数据 * 绿化率：40% * 所属商圈：西北旺 * 物业公司：北京德成永信物业管理有限公司 * 物业费：1.58元/平米/月 * 开发商：北京德成兴业房地产开发有限公司 * 电梯：未知 百旺茉莉园(一期)租金趋势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 8000元/月 0.00% * 二室 9200元/月-5.11% * 三室 12133元/月-1.59% * 四室 15000元/月 0.00% * 四室以上 16500元/月+0.00% 百旺茉莉园(一期)出租房源 * 全部 * 整租 * 合租 * 个人 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 12000 元地铁16号线西北旺站，万象汇门口，看房随时 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 12000 元百旺茉莉园(一期) 精装修 3室2厅2卫 阳光充足 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 精装修 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 3900 元百旺茉莉园(一期) 独卫 西北旺地铁 软件园 万象汇 百度 3室1厅 / 35㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 3000 元百旺茉莉园(一期) 西北旺地铁 万象汇 软件园 百度 网易 3室1厅 / 35㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 1999 元西北旺地铁茉莉园小区 马连洼 软件园 百度 网易 万象汇 3室1厅 / 13㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 暂无数据 附近小区房屋出租 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 同区域房屋出租 * 全部 * 安选 * VR看房 * 视频看房 * 15000 元整租圆明园北大蔚秀园3室1厅 3室1厅 / 60.0㎡ 推荐理由： 邻地铁 精装修 * 4300 元我爱我家相寓 公主坟翠微南里低楼层1居室 1室1厅 / 45.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 * 2100 元常青园(一区) 2室1厅1卫 2室1厅 / 12㎡ 推荐理由： 女生合租 独立阳台 邻地铁 精装修 南北通透 首次出租 * 5800 元整租定慧寺定慧西里2室1厅 2室1厅 / 58.96㎡ 推荐理由： 精装修 * 1700 元可月付 友谊嘉园 短签俩月次卧 电梯房 价 3室1厅 / 8㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 * 10809 元整租军博铁道部五号院新2室1厅 2室1厅 / 79.09㎡ 推荐理由： 邻地铁 精装修 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 5000 元香山南营66号院 2室1厅1卫 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 首次出租 * 15000 元整租圆明园北大蔚秀园3室1厅 3室1厅 / 60.0㎡ 推荐理由： 邻地铁 精装修 * 4300 元我爱我家相寓 公主坟翠微南里低楼层1居室 1室1厅 / 45.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 * 2100 元常青园(一区) 2室1厅1卫 2室1厅 / 12㎡ 推荐理由： 女生合租 独立阳台 邻地铁 精装修 南北通透 首次出租 * 5800 元整租定慧寺定慧西里2室1厅 2室1厅 / 58.96㎡ 推荐理由： 精装修 * 1700 元可月付 友谊嘉园 短签俩月次卧 电梯房 价 3室1厅 / 8㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 * 10809 元整租军博铁道部五号院新2室1厅 2室1厅 / 79.09㎡ 推荐理由： 邻地铁 精装修 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 5000 元香山南营66号院 2室1厅1卫 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 首次出租 * 7300 元电梯两居 大钟寺 人大附分校 皂君庙 可直接 能谈价 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 6110 元小西天西直门北大街甲41号低楼层2居室 2室1厅 / 64.94㎡ 推荐理由： 邻地铁 精装修 * 6300 元电梯入户 一路之隔12号地铁 价可谈 可空房可配 看房方便 1室1厅 / 61.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7600 元五棵松新兴年代中楼层2居室 2室1厅 / 92.84㎡ 推荐理由： 邻地铁 精装修 * 6600 元南北通透 近魏公村地铁 全家具家电 看房方便 2室1厅 / 53.89㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 9800 元双榆树双榆树西里中楼层3居室 3室1厅 / 70.23㎡ 推荐理由： 邻地铁 * 6992 元定慧寺恩济庄46号院高楼层2居室 2室1厅 / 86.87㎡ 推荐理由： 邻地铁 押一付一 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 7200 元整租白石桥钢铁研究院2室1厅 2室1厅 / 56.0㎡ 推荐理由： 配套齐全 精装修 * 25000 元西直门地铁 金晖嘉园 远洋风景6号楼精装空房3室2厅2卫出租 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6800 元五道口清华东门地铁学知园双地铁清枫华景园随时可看可月付0押金 1室1厅 / 64.0㎡ 推荐理由： 独卫一居 可短租 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 4200 元民水民电 西三旗万象汇对面 东升科技园 民水民电 朝南一居室 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 * 7030 元小西天北邮 北师大 字节范围 枫蓝明光桥 学院派电梯 1居 1室1厅 / 65.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6300 元西直门 交大东门 南向 一居室 交大附小 精装修 1室1厅 / 45.4㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 ## 百旺茉莉园(一期)相关小区推荐 ## 同价位小区推荐 * 小区名称 月租金 涨跌幅 * 1.臻园(南区)12600元/月-1.66% ↓ ## 附近小区推荐 * 小区名称 月租金 涨跌幅 * 1.百旺茉莉园(二期)13692元/月 1.81% ↑ * 2.中海枫涟山庄10134元/月 1.42% ↑ * 3.如园(北区)31135元/月-0.70% ↓ * 4.西山锦绣府(嘉木园)7300元/月- * 5.西山锦绣府(朗清园)7800元/月 47.17% ↑ ## 同区域小区推荐 * 小区名称 月租金 涨跌幅 * 1.翠湖别墅15750元/月 0.00% ↑ * 2.龙翔路8号院6450元/月- * 3.气象局宿舍8110元/月 7.79% ↑ * 4.阜成路6号院10000元/月- * 5.鑫德嘉园10907元/月 0.09% ↑ ## 同城小区推荐 * 小区名称 月租金 涨跌幅 * 1.远洋万和城(C区)30900元/月-15.57% ↓ * 2.翠湖别墅15750元/月 0.00% ↑ * 3.东坝河甲2号院3250元/月-1.81% ↓ * 4.鹿鸣苑5266元/月 1.90% ↑ * 5.永定河孔雀城剑桥郡(八期)-- ## 百旺茉莉园(一期)附近经纪人 * 杨书伯 北京中世禾房地产经纪有限公司 * 冯姿博 北京居然住邦房地产经纪有限公司 * 董超 北京龙盛房地产经纪有限公司 * 赵日 北京同力合创房地产经纪有限公司 * 杨诗伯 北京千润住房租赁有限公司 * 刘松 北京麦田房产经纪有限公司 * 解志雄 北京麦田房产经纪有限公司 * 侯建 北京麦田房产经纪有限公司 * 郭元卡 北京信义佳业住房租赁有限公司 * 张爱创 北京益城润家住房租赁有限公司 * 党明涛 北京麦田房产经纪有限公司 * 毛嘉伟 北京麦田房产经纪有限公司 ## 百旺茉莉园(一期)问答 * 问 是整租还是合租？；* 加油： 1000到1500元，合租的也可以 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 滁州租房 * 石狮租房 * 百色租房 * 黔南租房 * 宜昌租房 * 湘西租房 * 攸县租房 * 廊坊租房 * 河间租房 * 沛县租房 * 海安租房 * 南城租房 * 磐石租房 * 烟台租房 * 泰安租房 * 襄垣租房 * 简阳租房 * 巴音郭楞租房 * 江山租房 * 台湾租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 百旺茉莉园(二期)租房 * 中海枫涟山庄租房 * 如园(北区)租房 * 西山锦绣府(嘉木园)租房 * 西山锦绣府(朗清园)租房 * 秋露园租房 * 芳怡园租房 * 西山锦绣府(乐水园)租房 * 如园(南区)租房 * 黑山扈路临甲3号院租房 * 碧水家园租房 * 景和园租房 * 夏霖园租房 * 西山锦绣府(锦华园)租房 * 冬晴园租房 * 韩家川东路临4号院租房 * 春晖园租房 * 山水小区租房 * 颐和山庄租房 * 颐和山庄(别墅)租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅出租 * 正规一居室出租 * 豪华一居出租 * 开间出租 * 精装两居室出租 * 豪华两居出租 * 两居两卫出租 * 标准两居出租 * 已装修租房 * 北欧极简风格出租 * 现代简约出租 * 带空调出租 * 带免费停车场租房 * 带免费停车出租 * 个人房源合租房 * 酒店公寓出租 * 主卧租房 * 公交站附近租房 * 高铁站附近租房 * KTV附近合租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ga。；北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。</x:v>
+        <x:v>整租：3室1厅11500元/月（129.41㎡）、3室2厅10200-13000元/月、4室2厅15000-21500元/月、5室2厅16500元/月左右，户型覆盖2-5室，面积88-252㎡不等，押一付一/三/半年可选，部分房源有中介费；；小区2005年建成，物业方面：部分房源提及物业完善、贴心人性化；；装修：合租房源多为精装修，部分整租为简单装修；；户型：南北通透，有2-5居室，部分带阳台、独立卫生间；；质量相关未提及隔音问题，小区绿化率30%左右；</x:v>
       </x:c>
       <x:c r="L52" t="str">
-        <x:v># 百旺茉莉园(一期)租房,西北旺百旺茉莉园(一期)房屋出租价格,百旺茉莉园(一期)整租合租房价-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;西北旺小区 &gt;百旺茉莉园(一期)&gt;百旺茉莉园(一期)租房 百旺茉莉园(一期) * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 # 百旺茉莉园(一期) * 物业类型：公寓住宅 * 竣工时间：2005 * 总户数：1498 * 容积数：1.34 * 建筑类型：多层、小高层 * 统一供暖：否 * 停车位：1723（1:1.15） * 车位管理费：暂无数据 * 小区地址：西北旺四街 * 幼儿园：暂无数据 * 小学：海淀区中关村第二小学百旺校区 * 初中：暂无数据 * 权属类别：商品房住宅 * 产权年限：暂无数据 * 总建面积：暂无数据 * 绿化率：40% * 所属商圈：西北旺 * 物业公司：北京德成永信物业管理有限公司 * 物业费：1.58元/平米/月 * 开发商：北京德成兴业房地产开发有限公司 * 电梯：未知 百旺茉莉园(一期)租金趋势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 8000元/月 0.00% * 二室 9200元/月-5.11% * 三室 12133元/月-1.59% * 四室 15000元/月 0.00% * 四室以上 16500元/月+0.00% 百旺茉莉园(一期)出租房源 * 全部 * 整租 * 合租 * 个人 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 12000 元地铁16号线西北旺站，万象汇门口，看房随时 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 12000 元百旺茉莉园(一期) 精装修 3室2厅2卫 阳光充足 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 精装修 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 3900 元百旺茉莉园(一期) 独卫 西北旺地铁 软件园 万象汇 百度 3室1厅 / 35㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 3000 元百旺茉莉园(一期) 西北旺地铁 万象汇 软件园 百度 网易 3室1厅 / 35㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 1999 元西北旺地铁茉莉园小区 马连洼 软件园 百度 网易 万象汇 3室1厅 / 13㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 暂无数据 附近小区房屋出租 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 同区域房屋出租 * 全部 * 安选 * VR看房 * 视频看房 * 15000 元整租圆明园北大蔚秀园3室1厅 3室1厅 / 60.0㎡ 推荐理由： 邻地铁 精装修 * 4300 元我爱我家相寓 公主坟翠微南里低楼层1居室 1室1厅 / 45.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 * 2100 元常青园(一区) 2室1厅1卫 2室1厅 / 12㎡ 推荐理由： 女生合租 独立阳台 邻地铁 精装修 南北通透 首次出租 * 5800 元整租定慧寺定慧西里2室1厅 2室1厅 / 58.96㎡ 推荐理由： 精装修 * 1700 元可月付 友谊嘉园 短签俩月次卧 电梯房 价 3室1厅 / 8㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 * 10809 元整租军博铁道部五号院新2室1厅 2室1厅 / 79.09㎡ 推荐理由： 邻地铁 精装修 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 5000 元香山南营66号院 2室1厅1卫 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 首次出租 * 15000 元整租圆明园北大蔚秀园3室1厅 3室1厅 / 60.0㎡ 推荐理由： 邻地铁 精装修 * 4300 元我爱我家相寓 公主坟翠微南里低楼层1居室 1室1厅 / 45.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 * 2100 元常青园(一区) 2室1厅1卫 2室1厅 / 12㎡ 推荐理由： 女生合租 独立阳台 邻地铁 精装修 南北通透 首次出租 * 5800 元整租定慧寺定慧西里2室1厅 2室1厅 / 58.96㎡ 推荐理由： 精装修 * 1700 元可月付 友谊嘉园 短签俩月次卧 电梯房 价 3室1厅 / 8㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 * 10809 元整租军博铁道部五号院新2室1厅 2室1厅 / 79.09㎡ 推荐理由： 邻地铁 精装修 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 5000 元香山南营66号院 2室1厅1卫 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 首次出租 * 7300 元电梯两居 大钟寺 人大附分校 皂君庙 可直接 能谈价 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 6110 元小西天西直门北大街甲41号低楼层2居室 2室1厅 / 64.94㎡ 推荐理由： 邻地铁 精装修 * 6300 元电梯入户 一路之隔12号地铁 价可谈 可空房可配 看房方便 1室1厅 / 61.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7600 元五棵松新兴年代中楼层2居室 2室1厅 / 92.84㎡ 推荐理由： 邻地铁 精装修 * 6600 元南北通透 近魏公村地铁 全家具家电 看房方便 2室1厅 / 53.89㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 9800 元双榆树双榆树西里中楼层3居室 3室1厅 / 70.23㎡ 推荐理由： 邻地铁 * 6992 元定慧寺恩济庄46号院高楼层2居室 2室1厅 / 86.87㎡ 推荐理由： 邻地铁 押一付一 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 7200 元整租白石桥钢铁研究院2室1厅 2室1厅 / 56.0㎡ 推荐理由： 配套齐全 精装修 * 25000 元西直门地铁 金晖嘉园 远洋风景6号楼精装空房3室2厅2卫出租 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6800 元五道口清华东门地铁学知园双地铁清枫华景园随时可看可月付0押金 1室1厅 / 64.0㎡ 推荐理由： 独卫一居 可短租 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 4200 元民水民电 西三旗万象汇对面 东升科技园 民水民电 朝南一居室 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 * 7030 元小西天北邮 北师大 字节范围 枫蓝明光桥 学院派电梯 1居 1室1厅 / 65.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6300 元西直门 交大东门 南向 一居室 交大附小 精装修 1室1厅 / 45.4㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 ## 百旺茉莉园(一期)相关小区推荐 ## 同价位小区推荐 * 小区名称 月租金 涨跌幅 * 1.臻园(南区)12600元/月-1.66% ↓ ## 附近小区推荐 * 小区名称 月租金 涨跌幅 * 1.百旺茉莉园(二期)13692元/月 1.81% ↑ * 2.中海枫涟山庄10134元/月 1.42% ↑ * 3.如园(北区)31135元/月-0.70% ↓ * 4.西山锦绣府(嘉木园)7300元/月- * 5.西山锦绣府(朗清园)7800元/月 47.17% ↑ ## 同区域小区推荐 * 小区名称 月租金 涨跌幅 * 1.翠湖别墅15750元/月 0.00% ↑ * 2.龙翔路8号院6450元/月- * 3.气象局宿舍8110元/月 7.79% ↑ * 4.阜成路6号院10000元/月- * 5.鑫德嘉园10907元/月 0.09% ↑ ## 同城小区推荐 * 小区名称 月租金 涨跌幅 * 1.远洋万和城(C区)30900元/月-15.57% ↓ * 2.翠湖别墅15750元/月 0.00% ↑ * 3.东坝河甲2号院3250元/月-1.81% ↓ * 4.鹿鸣苑5266元/月 1.90% ↑ * 5.永定河孔雀城剑桥郡(八期)-- ## 百旺茉莉园(一期)附近经纪人 * 杨书伯 北京中世禾房地产经纪有限公司 * 冯姿博 北京居然住邦房地产经纪有限公司 * 董超 北京龙盛房地产经纪有限公司 * 赵日 北京同力合创房地产经纪有限公司 * 杨诗伯 北京千润住房租赁有限公司 * 刘松 北京麦田房产经纪有限公司 * 解志雄 北京麦田房产经纪有限公司 * 侯建 北京麦田房产经纪有限公司 * 郭元卡 北京信义佳业住房租赁有限公司 * 张爱创 北京益城润家住房租赁有限公司 * 党明涛 北京麦田房产经纪有限公司 * 毛嘉伟 北京麦田房产经纪有限公司 ## 百旺茉莉园(一期)问答 * 问 是整租还是合租？；* 加油： 1000到1500元，合租的也可以 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 滁州租房 * 石狮租房 * 百色租房 * 黔南租房 * 宜昌租房 * 湘西租房 * 攸县租房 * 廊坊租房 * 河间租房 * 沛县租房 * 海安租房 * 南城租房 * 磐石租房 * 烟台租房 * 泰安租房 * 襄垣租房 * 简阳租房 * 巴音郭楞租房 * 江山租房 * 台湾租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 百旺茉莉园(二期)租房 * 中海枫涟山庄租房 * 如园(北区)租房 * 西山锦绣府(嘉木园)租房 * 西山锦绣府(朗清园)租房 * 秋露园租房 * 芳怡园租房 * 西山锦绣府(乐水园)租房 * 如园(南区)租房 * 黑山扈路临甲3号院租房 * 碧水家园租房 * 景和园租房 * 夏霖园租房 * 西山锦绣府(锦华园)租房 * 冬晴园租房 * 韩家川东路临4号院租房 * 春晖园租房 * 山水小区租房 * 颐和山庄租房 * 颐和山庄(别墅)租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅出租 * 正规一居室出租 * 豪华一居出租 * 开间出租 * 精装两居室出租 * 豪华两居出租 * 两居两卫出租 * 标准两居出租 * 已装修租房 * 北欧极简风格出租 * 现代简约出租 * 带空调出租 * 带免费停车场租房 * 带免费停车出租 * 个人房源合租房 * 酒店公寓出租 * 主卧租房 * 公交站附近租房 * 高铁站附近租房 * KTV附近合租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ga。；北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。；## 百旺茉莉园 别名：百旺茉莉园 加入本地买房群 关注 _北京 - 海淀 - 海淀西北旺镇区永丰路西百旺新城_ 发地址到手机 参考均价 _76306 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2005_ 小区户数 _2030户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-64群（436） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?</x:v>
-      </x:c>
-      <x:c r="M52" t="str">
-        <x:v>* 加油： 1000到1500元，合租的也可以 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 滁州租房 * 石狮租房 * 百色租房 * 黔南租房 * 宜昌租房 * 湘西租房 * 攸县租房 * 廊坊租房 * 河间租房 * 沛县租房 * 海安租房 * 南城租房 * 磐石租房 * 烟台租房 * 泰安租房 * 襄垣租房 * 简阳租房 * 巴音郭楞租房 * 江山租房 * 台湾租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 百旺茉莉园(二期)租房 * 中海枫涟山庄租房 * 如园(北区)租房 * 西山锦绣府(嘉木园)租房 * 西山锦绣府(朗清园)租房 * 秋露园租房 * 芳怡园租房 * 西山锦绣府(乐水园)租房 * 如园(南区)租房 * 黑山扈路临甲3号院租房 * 碧水家园租房 * 景和园租房 * 夏霖园租房 * 西山锦绣府(锦华园)租房 * 冬晴园租房 * 韩家川东路临4号院租房 * 春晖园租房 * 山水小区租房 * 颐和山庄租房 * 颐和山庄(别墅)租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅出租 * 正规一居室出租 * 豪华一居出租 * 开间出租 * 精装两居室出租 * 豪华两居出租 * 两居两卫出租 * 标准两居出租 * 已装修租房 * 北欧极简风格出租 * 现代简约出租 * 带空调出租 * 带免费停车场租房 * 带免费停车出租 * 个人房源合租房 * 酒店公寓出租 * 主卧租房 * 公交站附近租房 * 高铁站附近租房 * KTV附近合租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ga。</x:v>
-      </x:c>
+        <x:v>通勤：距离16号线西北旺地铁站约445-1105米，步行可达；；生活配套：周边有西北旺万象汇购物中心、鲜美多生鲜超市、华联超市等，餐饮、休闲设施齐全，靠近百度科技园、网易大厦等产业园；；就医相关未明确提及，但整体生活便利度较高；</x:v>
+      </x:c>
+      <x:c r="M52" t="str"/>
       <x:c r="N52" t="str">
-        <x:v>价格线索：2026-02-25 | 665万 | 57787元/㎡；2026-01-26 | 708万 | 56654元/㎡；三室 * 四室 * 四室以上 * 一室 8000元/月； 0.00% * 二室 9200元/月；-5.11% * 三室 12133元/月；-1.59% * 四室 15000元/月； 0.00% * 四室以上 16500元/月；称 月租金 涨跌幅 * 1.臻园(南区)12600元/月；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **75443** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.8% 贷款计算器 * 二手房源 87套 * 最近成交 357套 * 楼栋总数 58栋 * 房屋总数 2145户 * 建筑类型 板塔结合 * 建筑年代 2005年建成 * 小区位置 (海淀)德政路南茉莉园地图 * 物业公司 北京德成永信物业管理有限公司 * 开发商 北京德成兴业房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 李强 评分：4.6 从业信息卡 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 ### 百旺茉莉园主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010077340/photo/?；# 百旺茉莉园(一期)租房,西北旺百旺茉莉园(一期)房屋出租价格,百旺茉莉园(一期)整租合租房价-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;西北旺小区 &gt;百旺茉莉园(一期)&gt;百旺茉莉园(一期)租房 百旺茉莉园(一期) * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 # 百旺茉莉园(一期) * 物业类型：公寓住宅 * 竣工时间：2005 * 总户数：1498 * 容积数：1.34 * 建筑类型：多层、小高层 * 统一供暖：否 * 停车位：1723（1:1.15） * 车位管理费：暂无数据 * 小区地址：西北旺四街 * 幼儿园：暂无数据 * 小学：海淀区中关村第二小学百旺校区 * 初中：暂无数据 * 权属类别：商品房住宅 * 产权年限：暂无数据 * 总建面积：暂无数据 * 绿化率：40% * 所属商圈：西北旺 * 物业公司：北京德成永信物业管理有限公司 * 物业费：1.58元/平米/月 * 开发商：北京德成兴业房地产开发有限公司 * 电梯：未知 百旺茉莉园(一期)租金趋势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 8000元/月 0.00% * 二室 9200元/月-5.11% * 三室 12133元/月-1.59% * 四室 15000元/月 0.00% * 四室以上 16500元/月+0.00% 百旺茉莉园(一期)出租房源 * 全部 * 整租 * 合租 * 个人 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 12000 元地铁16号线西北旺站，万象汇门口，看房随时 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 12000 元百旺茉莉园(一期) 精装修 3室2厅2卫 阳光充足 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 精装修 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 3900 元百旺茉莉园(一期) 独卫 西北旺地铁 软件园 万象汇 百度 3室1厅 / 35㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 3000 元百旺茉莉园(一期) 西北旺地铁 万象汇 软件园 百度 网易 3室1厅 / 35㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 1999 元西北旺地铁茉莉园小区 马连洼 软件园 百度 网易 万象汇 3室1厅 / 13㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 暂无数据 附近小区房屋出租 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 同区域房屋出租 * 全部 * 安选 * VR看房 * 视频看房 * 15000 元整租圆明园北大蔚秀园3室1厅 3室1厅 / 60.0㎡ 推荐理由： 邻地铁 精装修 * 4300 元我爱我家相寓 公主坟翠微南里低楼层1居室 1室1厅 / 45.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 * 2100 元常青园(一区) 2室1厅1卫 2室1厅 / 12㎡ 推荐理由： 女生合租 独立阳台 邻地铁 精装修 南北通透 首次出租 * 5800 元整租定慧寺定慧西里2室1厅 2室1厅 / 58.96㎡ 推荐理由： 精装修 * 1700 元可月付 友谊嘉园 短签俩月次卧 电梯房 价 3室1厅 / 8㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 * 10809 元整租军博铁道部五号院新2室1厅 2室1厅 / 79.09㎡ 推荐理由： 邻地铁 精装修 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 5000 元香山南营66号院 2室1厅1卫 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 首次出租 * 15000 元整租圆明园北大蔚秀园3室1厅 3室1厅 / 60.0㎡ 推荐理由： 邻地铁 精装修 * 4300 元我爱我家相寓 公主坟翠微南里低楼层1居室 1室1厅 / 45.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 * 2100 元常青园(一区) 2室1厅1卫 2室1厅 / 12㎡ 推荐理由： 女生合租 独立阳台 邻地铁 精装修 南北通透 首次出租 * 5800 元整租定慧寺定慧西里2室1厅 2室1厅 / 58.96㎡ 推荐理由： 精装修 * 1700 元可月付 友谊嘉园 短签俩月次卧 电梯房 价 3室1厅 / 8㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 * 10809 元整租军博铁道部五号院新2室1厅 2室1厅 / 79.09㎡ 推荐理由： 邻地铁 精装修 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 5000 元香山南营66号院 2室1厅1卫 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 首次出租 * 7300 元电梯两居 大钟寺 人大附分校 皂君庙 可直接 能谈价 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 6110 元小西天西直门北大街甲41号低楼层2居室 2室1厅 / 64.94㎡ 推荐理由： 邻地铁 精装修 * 6300 元电梯入户 一路之隔12号地铁 价可谈 可空房可配 看房方便 1室1厅 / 61.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7600 元五棵松新兴年代中楼层2居室 2室1厅 / 92.84㎡ 推荐理由： 邻地铁 精装修 * 6600 元南北通透 近魏公村地铁 全家具家电 看房方便 2室1厅 / 53.89㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 9800 元双榆树双榆树西里中楼层3居室 3室1厅 / 70.23㎡ 推荐理由： 邻地铁 * 6992 元定慧寺恩济庄46号院高楼层2居室 2室1厅 / 86.87㎡ 推荐理由： 邻地铁 押一付一 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 7200 元整租白石桥钢铁研究院2室1厅 2室1厅 / 56.0㎡ 推荐理由： 配套齐全 精装修 * 25000 元西直门地铁 金晖嘉园 远洋风景6号楼精装空房3室2厅2卫出租 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6800 元五道口清华东门地铁学知园双地铁清枫华景园随时可看可月付0押金 1室1厅 / 64.0㎡ 推荐理由： 独卫一居 可短租 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 4200 元民水民电 西三旗万象汇对面 东升科技园 民水民电 朝南一居室 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 * 7030 元小西天北邮 北师大 字节范围 枫蓝明光桥 学院派电梯 1居 1室1厅 / 65.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6300 元西直门 交大东门 南向 一居室 交大附小 精装修 1室1厅 / 45.4㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 ## 百旺茉莉园(一期)相关小区推荐 ## 同价位小区推荐 * 小区名称 月租金 涨跌幅 * 1.臻园(南区)12600元/月-1.66% ↓ ## 附近小区推荐 * 小区名称 月租金 涨跌幅 * 1.百旺茉莉园(二期)13692元/月 1.81% ↑ * 2.中海枫涟山庄10134元/月 1.42% ↑ * 3.如园(北区)31135元/月-0.70% ↓ * 4.西山锦绣府(嘉木园)7300元/月- * 5.西山锦绣府(朗清园)7800元/月 47.17% ↑ ## 同区域小区推荐 * 小区名称 月租金 涨跌幅 * 1.翠湖别墅15750元/月 0.00% ↑ * 2.龙翔路8号院6450元/月- * 3.气象局宿舍8110元/月 7.79% ↑ * 4.阜成路6号院10000元/月- * 5.鑫德嘉园10907元/月 0.09% ↑ ## 同城小区推荐 * 小区名称 月租金 涨跌幅 * 1.远洋万和城(C区)30900元/月-15.57% ↓ * 2.翠湖别墅15750元/月 0.00% ↑ * 3.东坝河甲2号院3250元/月-1.81% ↓ * 4.鹿鸣苑5266元/月 1.90% ↑ * 5.永定河孔雀城剑桥郡(八期)-- ## 百旺茉莉园(一期)附近经纪人 * 杨书伯 北京中世禾房地产经纪有限公司 * 冯姿博 北京居然住邦房地产经纪有限公司 * 董超 北京龙盛房地产经纪有限公司 * 赵日 北京同力合创房地产经纪有限公司 * 杨诗伯 北京千润住房租赁有限公司 * 刘松 北京麦田房产经纪有限公司 * 解志雄 北京麦田房产经纪有限公司 * 侯建 北京麦田房产经纪有限公司 * 郭元卡 北京信义佳业住房租赁有限公司 * 张爱创 北京益城润家住房租赁有限公司 * 党明涛 北京麦田房产经纪有限公司 * 毛嘉伟 北京麦田房产经纪有限公司 ## 百旺茉莉园(一期)问答 * 问 是整租还是合租？；* 加油： 1000到1500元，合租的也可以 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 滁州租房 * 石狮租房 * 百色租房 * 黔南租房 * 宜昌租房 * 湘西租房 * 攸县租房 * 廊坊租房 * 河间租房 * 沛县租房 * 海安租房 * 南城租房 * 磐石租房 * 烟台租房 * 泰安租房 * 襄垣租房 * 简阳租房 * 巴音郭楞租房 * 江山租房 * 台湾租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 百旺茉莉园(二期)租房 * 中海枫涟山庄租房 * 如园(北区)租房 * 西山锦绣府(嘉木园)租房 * 西山锦绣府(朗清园)租房 * 秋露园租房 * 芳怡园租房 * 西山锦绣府(乐水园)租房 * 如园(南区)租房 * 黑山扈路临甲3号院租房 * 碧水家园租房 * 景和园租房 * 夏霖园租房 * 西山锦绣府(锦华园)租房 * 冬晴园租房 * 韩家川东路临4号院租房 * 春晖园租房 * 山水小区租房 * 颐和山庄租房 * 颐和山庄(别墅)租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅出租 * 正规一居室出租 * 豪华一居出租 * 开间出租 * 精装两居室出租 * 豪华两居出租 * 两居两卫出租 * 标准两居出租 * 已装修租房 * 北欧极简风格出租 * 现代简约出租 * 带空调出租 * 带免费停车场租房 * 带免费停车出租 * 个人房源合租房 * 酒店公寓出租 * 主卧租房 * 公交站附近租房 * 高铁站附近租房 * KTV附近合租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ga。；北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。；生活便利线索：# 百旺茉莉园(一期)租房,西北旺百旺茉莉园(一期)房屋出租价格,百旺茉莉园(一期)整租合租房价-北京58同城 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 北京房产网&gt;北京小区 &gt;西北旺小区 &gt;百旺茉莉园(一期)&gt;百旺茉莉园(一期)租房 百旺茉莉园(一期) * 小区租房首页 * 整租房源 * 合租房源 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 # 百旺茉莉园(一期) * 物业类型：公寓住宅 * 竣工时间：2005 * 总户数：1498 * 容积数：1.34 * 建筑类型：多层、小高层 * 统一供暖：否 * 停车位：1723（1:1.15） * 车位管理费：暂无数据 * 小区地址：西北旺四街 * 幼儿园：暂无数据 * 小学：海淀区中关村第二小学百旺校区 * 初中：暂无数据 * 权属类别：商品房住宅 * 产权年限：暂无数据 * 总建面积：暂无数据 * 绿化率：40% * 所属商圈：西北旺 * 物业公司：北京德成永信物业管理有限公司 * 物业费：1.58元/平米/月 * 开发商：北京德成兴业房地产开发有限公司 * 电梯：未知 百旺茉莉园(一期)租金趋势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 8000元/月 0.00% * 二室 9200元/月-5.11% * 三室 12133元/月-1.59% * 四室 15000元/月 0.00% * 四室以上 16500元/月+0.00% 百旺茉莉园(一期)出租房源 * 全部 * 整租 * 合租 * 个人 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 12000 元地铁16号线西北旺站，万象汇门口，看房随时 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 12000 元百旺茉莉园(一期) 精装修 3室2厅2卫 阳光充足 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 精装修 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 3900 元百旺茉莉园(一期) 独卫 西北旺地铁 软件园 万象汇 百度 3室1厅 / 35㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 3000 元百旺茉莉园(一期) 西北旺地铁 万象汇 软件园 百度 网易 3室1厅 / 35㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 1999 元西北旺地铁茉莉园小区 马连洼 软件园 百度 网易 万象汇 3室1厅 / 13㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 暂无数据 附近小区房屋出租 * 12000 元南北通透 3室2厅 百旺茉莉园(一期) 3室2厅 / 119.21㎡ 推荐理由： 邻地铁 * 1999 元16号线西北旺地铁口 茉莉园小区 精装修 大次卧 3室1厅 / 15㎡ 推荐理由： 独立阳台 邻地铁 押一付一 配套齐全 精装修 * 4000 元独卫，西北旺地铁，软件园，百度，腾讯，马连洼，联想 3室1厅 / 25㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 * 16500 元南北通透 5室2厅 百旺茉莉园(一期) 5室2厅 / 185.0㎡ 推荐理由： 邻地铁 * 2299 元百旺茉莉园万象汇西北旺地铁站精装独卫中关村软件园西苑苏州街 3室1厅 / 20㎡ 推荐理由： 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 9200 元（月付）西北旺永丰南地铁万象汇唐家岭中关村软件园两居室 2室2厅 / 117.03㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2400 元西北旺茉莉园朝南主卧阳台春夏秋冬百度软件园万象汇腾讯 1室1厅 / 30㎡ 推荐理由： 独卫 邻地铁 押一付一 配套齐全 精装修 南北通透 首次出租 * 2250 元真图真价，朝北大次卧，中关村软件园，西北旺高档小区百度科技园 4室2厅 / 18㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 同区域房屋出租 * 全部 * 安选 * VR看房 * 视频看房 * 15000 元整租圆明园北大蔚秀园3室1厅 3室1厅 / 60.0㎡ 推荐理由： 邻地铁 精装修 * 4300 元我爱我家相寓 公主坟翠微南里低楼层1居室 1室1厅 / 45.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 * 2100 元常青园(一区) 2室1厅1卫 2室1厅 / 12㎡ 推荐理由： 女生合租 独立阳台 邻地铁 精装修 南北通透 首次出租 * 5800 元整租定慧寺定慧西里2室1厅 2室1厅 / 58.96㎡ 推荐理由： 精装修 * 1700 元可月付 友谊嘉园 短签俩月次卧 电梯房 价 3室1厅 / 8㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 * 10809 元整租军博铁道部五号院新2室1厅 2室1厅 / 79.09㎡ 推荐理由： 邻地铁 精装修 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 5000 元香山南营66号院 2室1厅1卫 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 首次出租 * 15000 元整租圆明园北大蔚秀园3室1厅 3室1厅 / 60.0㎡ 推荐理由： 邻地铁 精装修 * 4300 元我爱我家相寓 公主坟翠微南里低楼层1居室 1室1厅 / 45.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 * 2100 元常青园(一区) 2室1厅1卫 2室1厅 / 12㎡ 推荐理由： 女生合租 独立阳台 邻地铁 精装修 南北通透 首次出租 * 5800 元整租定慧寺定慧西里2室1厅 2室1厅 / 58.96㎡ 推荐理由： 精装修 * 1700 元可月付 友谊嘉园 短签俩月次卧 电梯房 价 3室1厅 / 8㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 * 10809 元整租军博铁道部五号院新2室1厅 2室1厅 / 79.09㎡ 推荐理由： 邻地铁 精装修 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 5000 元香山南营66号院 2室1厅1卫 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 首次出租 * 7300 元电梯两居 大钟寺 人大附分校 皂君庙 可直接 能谈价 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 有阳台 * 6110 元小西天西直门北大街甲41号低楼层2居室 2室1厅 / 64.94㎡ 推荐理由： 邻地铁 精装修 * 6300 元电梯入户 一路之隔12号地铁 价可谈 可空房可配 看房方便 1室1厅 / 61.0㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 7600 元五棵松新兴年代中楼层2居室 2室1厅 / 92.84㎡ 推荐理由： 邻地铁 精装修 * 6600 元南北通透 近魏公村地铁 全家具家电 看房方便 2室1厅 / 53.89㎡ 推荐理由： 邻地铁 押一付一 配套齐全 精装修 * 9800 元双榆树双榆树西里中楼层3居室 3室1厅 / 70.23㎡ 推荐理由： 邻地铁 * 6992 元定慧寺恩济庄46号院高楼层2居室 2室1厅 / 86.87㎡ 推荐理由： 邻地铁 押一付一 * 11500 元我爱我家相寓 西直门铁科院宿舍中楼层3居室 3室1厅 / 85.98㎡ 推荐理由： 配套齐全 精装修 * 7200 元整租白石桥钢铁研究院2室1厅 2室1厅 / 56.0㎡ 推荐理由： 配套齐全 精装修 * 25000 元西直门地铁 金晖嘉园 远洋风景6号楼精装空房3室2厅2卫出租 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6800 元五道口清华东门地铁学知园双地铁清枫华景园随时可看可月付0押金 1室1厅 / 64.0㎡ 推荐理由： 独卫一居 可短租 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 * 7200 元西直门高梁桥斜街44号院低楼层2居室 2室1厅 / 46.2㎡ 推荐理由： 邻地铁 * 4200 元民水民电 西三旗万象汇对面 东升科技园 民水民电 朝南一居室 1室1厅 / 60.0㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 随时看房 * 7030 元小西天北邮 北师大 字节范围 枫蓝明光桥 学院派电梯 1居 1室1厅 / 65.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6300 元西直门 交大东门 南向 一居室 交大附小 精装修 1室1厅 / 45.4㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 ## 百旺茉莉园(一期)相关小区推荐 ## 同价位小区推荐 * 小区名称 月租金 涨跌幅 * 1.臻园(南区)12600元/月-1.66% ↓ ## 附近小区推荐 * 小区名称 月租金 涨跌幅 * 1.百旺茉莉园(二期)13692元/月 1.81% ↑ * 2.中海枫涟山庄10134元/月 1.42% ↑ * 3.如园(北区)31135元/月-0.70% ↓ * 4.西山锦绣府(嘉木园)7300元/月- * 5.西山锦绣府(朗清园)7800元/月 47.17% ↑ ## 同区域小区推荐 * 小区名称 月租金 涨跌幅 * 1.翠湖别墅15750元/月 0.00% ↑ * 2.龙翔路8号院6450元/月- * 3.气象局宿舍8110元/月 7.79% ↑ * 4.阜成路6号院10000元/月- * 5.鑫德嘉园10907元/月 0.09% ↑ ## 同城小区推荐 * 小区名称 月租金 涨跌幅 * 1.远洋万和城(C区)30900元/月-15.57% ↓ * 2.翠湖别墅15750元/月 0.00% ↑ * 3.东坝河甲2号院3250元/月-1.81% ↓ * 4.鹿鸣苑5266元/月 1.90% ↑ * 5.永定河孔雀城剑桥郡(八期)-- ## 百旺茉莉园(一期)附近经纪人 * 杨书伯 北京中世禾房地产经纪有限公司 * 冯姿博 北京居然住邦房地产经纪有限公司 * 董超 北京龙盛房地产经纪有限公司 * 赵日 北京同力合创房地产经纪有限公司 * 杨诗伯 北京千润住房租赁有限公司 * 刘松 北京麦田房产经纪有限公司 * 解志雄 北京麦田房产经纪有限公司 * 侯建 北京麦田房产经纪有限公司 * 郭元卡 北京信义佳业住房租赁有限公司 * 张爱创 北京益城润家住房租赁有限公司 * 党明涛 北京麦田房产经纪有限公司 * 毛嘉伟 北京麦田房产经纪有限公司 ## 百旺茉莉园(一期)问答 * 问 是整租还是合租？；* 加油： 1000到1500元，合租的也可以 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 滁州租房 * 石狮租房 * 百色租房 * 黔南租房 * 宜昌租房 * 湘西租房 * 攸县租房 * 廊坊租房 * 河间租房 * 沛县租房 * 海安租房 * 南城租房 * 磐石租房 * 烟台租房 * 泰安租房 * 襄垣租房 * 简阳租房 * 巴音郭楞租房 * 江山租房 * 台湾租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 百旺茉莉园(二期)租房 * 中海枫涟山庄租房 * 如园(北区)租房 * 西山锦绣府(嘉木园)租房 * 西山锦绣府(朗清园)租房 * 秋露园租房 * 芳怡园租房 * 西山锦绣府(乐水园)租房 * 如园(南区)租房 * 黑山扈路临甲3号院租房 * 碧水家园租房 * 景和园租房 * 夏霖园租房 * 西山锦绣府(锦华园)租房 * 冬晴园租房 * 韩家川东路临4号院租房 * 春晖园租房 * 山水小区租房 * 颐和山庄租房 * 颐和山庄(别墅)租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅出租 * 正规一居室出租 * 豪华一居出租 * 开间出租 * 精装两居室出租 * 豪华两居出租 * 两居两卫出租 * 标准两居出租 * 已装修租房 * 北欧极简风格出租 * 现代简约出租 * 带空调出租 * 带免费停车场租房 * 带免费停车出租 * 个人房源合租房 * 酒店公寓出租 * 主卧租房 * 公交站附近租房 * 高铁站附近租房 * KTV附近合租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ga。；北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。；## 百旺茉莉园 别名：百旺茉莉园 加入本地买房群 关注 _北京 - 海淀 - 海淀西北旺镇区永丰路西百旺新城_ 发地址到手机 参考均价 _76306 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2005_ 小区户数 _2030户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-64群（436） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；风险线索：* 加油： 1000到1500元，合租的也可以 * 城市小区 * 小区租房 * 小区周边租房 * 小区租金 * 个性租房 * 滁州租房 * 石狮租房 * 百色租房 * 黔南租房 * 宜昌租房 * 湘西租房 * 攸县租房 * 廊坊租房 * 河间租房 * 沛县租房 * 海安租房 * 南城租房 * 磐石租房 * 烟台租房 * 泰安租房 * 襄垣租房 * 简阳租房 * 巴音郭楞租房 * 江山租房 * 台湾租房 * 远洋万和城(C区)租房 * 翠湖别墅租房 * 东坝河甲2号院租房 * 鹿鸣苑租房 * 恋日国际租房 * 天和嘉园租房 * FREE自由季租房 * 绿城西山云庐(西区)租房 * 龙翔路8号院租房 * 润枫水尚(西区)租房 * 大红罗厂1号院租房 * 府右十八号租房 * 嘉华世纪租房 * 泥洼路30号院租房 * 观音寺小区租房 * 永定河孔雀城剑桥郡(八期)租房 * 汇福悦榕湾租房 * 荣盛香城郦舍4期租房 * 荣盛锦绣豪庭租房 * 华泰都市花园租房 * 百旺茉莉园(二期)租房 * 中海枫涟山庄租房 * 如园(北区)租房 * 西山锦绣府(嘉木园)租房 * 西山锦绣府(朗清园)租房 * 秋露园租房 * 芳怡园租房 * 西山锦绣府(乐水园)租房 * 如园(南区)租房 * 黑山扈路临甲3号院租房 * 碧水家园租房 * 景和园租房 * 夏霖园租房 * 西山锦绣府(锦华园)租房 * 冬晴园租房 * 韩家川东路临4号院租房 * 春晖园租房 * 山水小区租房 * 颐和山庄租房 * 颐和山庄(别墅)租房 * 远洋万和城(C区)租金 * 翠湖别墅租金 * 东坝河甲2号院租金 * 鹿鸣苑租金 * 恋日国际租金 * 天和嘉园租金 * FREE自由季租金 * 绿城西山云庐(西区)租金 * 龙翔路8号院租金 * 润枫水尚(西区)租金 * 大红罗厂1号院租金 * 府右十八号租金 * 嘉华世纪租金 * 泥洼路30号院租金 * 观音寺小区租金 * 永定河孔雀城剑桥郡(八期)租金 * 汇福悦榕湾租金 * 荣盛香城郦舍4期租金 * 荣盛锦绣豪庭租金 * 华泰都市花园租金 * 一室一厅出租 * 正规一居室出租 * 豪华一居出租 * 开间出租 * 精装两居室出租 * 豪华两居出租 * 两居两卫出租 * 标准两居出租 * 已装修租房 * 北欧极简风格出租 * 现代简约出租 * 带空调出租 * 带免费停车场租房 * 带免费停车出租 * 个人房源合租房 * 酒店公寓出租 * 主卧租房 * 公交站附近租房 * 高铁站附近租房 * KTV附近合租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ga。</x:v>
+        <x:v>价格线索：合租：16号线西北旺站附近，次卧1800-2300元/月；，主卧3999-4199元/月；整租：3室1厅11500元/月；（129.41㎡）、3室2厅10200-13000元/月；、4室2厅15000-21500元/月；、5室2厅16500元/月；房屋质量/户型线索：整租：3室1厅11500元/月（129.41㎡）、3室2厅10200-13000元/月、4室2厅15000-21500元/月、5室2厅16500元/月左右，户型覆盖2-5室，面积88-252㎡不等，押一付一/三/半年可选，部分房源有中介费；；小区2005年建成，物业方面：部分房源提及物业完善、贴心人性化；；装修：合租房源多为精装修，部分整租为简单装修；；户型：南北通透，有2-5居室，部分带阳台、独立卫生间；；质量相关未提及隔音问题，小区绿化率30%左右；；生活便利线索：通勤：距离16号线西北旺地铁站约445-1105米，步行可达；；生活配套：周边有西北旺万象汇购物中心、鲜美多生鲜超市、华联超市等，餐饮、休闲设施齐全，靠近百度科技园、网易大厦等产业园；；就医相关未明确提及，但整体生活便利度较高；</x:v>
       </x:c>
       <x:c r="O52" t="str">
-        <x:v>1. 【北京百旺茉莉园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010077340.htm
-2. 百旺茉莉园(一期)租房,西北旺百旺茉莉园(一期)房屋出租价格,百旺茉莉园(一期)整租合租房价-北京58同城 http://mob.58.com/zfxq/bj-sy100394652/
-3. 百旺茉莉园_北京百旺茉莉园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/802547.html
-4. 百旺茉莉园(一期),百旺茉莉园(一期)房源,西北旺永丰路西,百旺茉莉园(一期)房价、二手房、租房信息-幸福里 https://fangchan.toutiao.com/xiaoqu/bj-6581412573957062919.html</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4518983846847496-3/
+2. http://m.anjuke.com/bj/rent/4602078407273476-3/
+3. http://m.anjuke.com/bj/rent/4603781909863438-3/
+4. http://m.anjuke.com/bj/rent/4600767445720069-3/
+5. https://bj.zu.anjuke.com/fangyuan/4497933145025550
+6. 百旺茉莉园精装次卧临近西北旺地铁站百度联想中关村产业园腾讯 http://m.anjuke.com/bj/rent/4518983846847496-3/
+7. 南北通透 5室2厅 百旺茉莉园(一期) http://m.anjuke.com/bj/rent/4602078407273476-3/
+8. 百度科技园网易大厦西北旺万象汇别墅区百旺茉莉园主卧独卫出租 http://m.anjuke.com/bj/rent/4603781909863438-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -2792,39 +2940,42 @@
         <x:v>北京市海淀区马连洼街道黑山扈羊场1号</x:v>
       </x:c>
       <x:c r="E53" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F53" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G53" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H53" t="n">
-        <x:v>2.5</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I53" t="str">
-        <x:v>证据与实际严重不符，误植入万柳豪宅数据，无法反映真实水平，参考价值极低。</x:v>
-      </x:c>
-      <x:c r="J53" t="str">
-        <x:v>80000 元/月；75000 元/月；90000 元/月；138000 元/月；180000 元/月；58000 元/月；55000 元/月；65000 元/月</x:v>
-      </x:c>
+        <x:v>环境安静的家属院，租金相对亲民且户型通透，但房龄较旧且证据充分性一般。</x:v>
+      </x:c>
+      <x:c r="J53" t="str"/>
       <x:c r="K53" t="str">
-        <x:v># 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；90000 元/月 [](https://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；35500 元/月 [](https://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；22000 元/月 [](https://www.fang.com/chuzu/3_479279273_1.htm) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 [](https://www.fang.com/chuzu/3_478659487_1.htm) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。</x:v>
+        <x:v>两居月租6500-7200元（78-91平），三居9500-11000元（109-110平），押一付三，物业费取暖费部分由业主承担，中介费为一个月租金；；小区为水利局家属院，房龄较旧（6层板楼），房屋精装修，南北通透，采光通风好；；小区院内干净整洁安静，房屋不把边不临街，口碑提及隔音尚可，物业方面部分房源业主包物业费；</x:v>
       </x:c>
       <x:c r="L53" t="str">
-        <x:v>) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；交通便利南北通透 18000 元/月 [](https://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；22000 元/月 [](https://www.fang.com/chuzu/3_479279273_1.htm) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 [](https://www.fang.com/chuzu/3_478659487_1.htm) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。；采光好周边配套齐 21800 元/月 [](https://www.fang.com/chuzu/3_486864130_1.htm) 20套起看 万柳书院万城华府 2居南北通透 有车位有 整租|2室2厅|116㎡|朝南北 海淀-万柳-万城华府龙园 距10号线火器营站约436米。；交通便利周边配套齐采光好 20000 元/月 [](https://www.fang.com/chuzu/3_481166418_1.htm) 西直门凯德茂。</x:v>
+        <x:v>临近地铁16号线马连洼站（步行700米左右）、18号线马连洼站，周边有超市、银行、餐厅、医院，生活配套齐全，交通便利；</x:v>
       </x:c>
       <x:c r="M53" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>搜索结果中未发现明确的租房差评或同名误命中信息。；搜索结果中未发现明确的租房差评或同名误命中信息</x:v>
       </x:c>
       <x:c r="N53" t="str">
-        <x:v>价格线索：80000 元/月；75000 元/月；90000 元/月；138000 元/月；180000 元/月；58000 元/月；55000 元/月；65000 元/月；房屋质量/户型线索：# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；90000 元/月 [](https://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；35500 元/月 [](https://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；22000 元/月 [](https://www.fang.com/chuzu/3_479279273_1.htm) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 [](https://www.fang.com/chuzu/3_478659487_1.htm) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。；生活便利线索：) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；交通便利南北通透 18000 元/月 [](https://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；22000 元/月 [](https://www.fang.com/chuzu/3_479279273_1.htm) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 [](https://www.fang.com/chuzu/3_478659487_1.htm) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。；采光好周边配套齐 21800 元/月 [](https://www.fang.com/chuzu/3_486864130_1.htm) 20套起看 万柳书院万城华府 2居南北通透 有车位有 整租|2室2厅|116㎡|朝南北 海淀-万柳-万城华府龙园 距10号线火器营站约436米。；交通便利周边配套齐采光好 20000 元/月 [](https://www.fang.com/chuzu/3_481166418_1.htm) 西直门凯德茂。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>房屋质量/户型线索：两居月租6500-7200元（78-91平），三居9500-11000元（109-110平），押一付三，物业费取暖费部分由业主承担，中介费为一个月租金；；小区为水利局家属院，房龄较旧（6层板楼），房屋精装修，南北通透，采光通风好；；小区院内干净整洁安静，房屋不把边不临街，口碑提及隔音尚可，物业方面部分房源业主包物业费；；生活便利线索：临近地铁16号线马连洼站（步行700米左右）、18号线马连洼站，周边有超市、银行、餐厅、医院，生活配套齐全，交通便利；；风险线索：搜索结果中未发现明确的租房差评或同名误命中信息。；搜索结果中未发现明确的租房差评或同名误命中信息</x:v>
       </x:c>
       <x:c r="O53" t="str">
-        <x:v>1. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_254312bj/
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 讨论精选（豆瓣） https://www.douban.com/group/explore</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4595371647689730-3/
+2. http://m.anjuke.com/bj/rent/3648563867574284-3/
+3. http://m.anjuke.com/bj/rent/4595504748682254-3/
+4. http://m.anjuke.com/bj/rent/2723760330906630-3/
+5. http://m.anjuke.com/bj/rent/4597211148557326-3/
+6. http://m.anjuke.com/bj/rent/2898043835231232-3/
+7. http://m.anjuke.com/bj/rent/4603937816306692-3/
+8. 水利社区2号院 精装80平米两居 配套齐全 干净整洁 可长租 http://m.anjuke.com/bj/rent/4595371647689730-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -2841,41 +2992,44 @@
         <x:v>北京市海淀区农大南路51号</x:v>
       </x:c>
       <x:c r="E54" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F54" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G54" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H54" t="n">
         <x:v>8.5</x:v>
       </x:c>
       <x:c r="I54" t="str">
-        <x:v>2014年房龄较新，紧邻农大南路地铁站，租金透明且配套齐全，是高性价比之选。</x:v>
+        <x:v>2014年房龄较新，物业口碑好，两居室价格适中，步行至地铁站较近，居住品质高。</x:v>
       </x:c>
       <x:c r="J54" t="str">
-        <x:v> * 四室 * 四室以上 小区本月租金 2680元/月；配套齐全 精装修 有阳台 随时看房 * 7400 元/月；北通透 有阳台 首次出租 随时看房 * 7400 元/月；连洼 * 邻地铁 精装修 随时看房 * 7400 元/月；公房子可注册价格那是便宜的2500起. 2500元/月； 北三环中路甲18号院4室1卫1厅50平2600元/月；北起G南至A西起26东至29 2600-3200元/月；海淀） 北京市海淀区白家疃路 2100-4200元/月</x:v>
+        <x:v>两居室月租7100-7600元/月；（如80㎡户型7600元/月；、75㎡户型7400元/月</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 广泰小区 &gt;* 广泰小区租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 广泰小区 海淀 / 马连洼 / 农大南路 小区信息 建筑类别: 多层 总 户 数: 1634 建筑年代: 2014年 绿 化 率: 30% 停 车 位:暂无数据 ### 广泰小区租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 2680元/月 0% 广泰小区 ### 广泰小区出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 * 2室1厅|75㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 广泰 精装大两居 电梯房 配套齐全 跟签约 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7400 元/月 * * 农大南路c口 广泰小区电梯高楼层两居室 价格可谈 * 2室1厅|78㎡ * 马连洼 * 邻地铁 精装修 随时看房 * 7400 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 广泰小区 * 万树园 * 丰泽盈和 * 圆明园花园 * 绿苑小区 * 博雅西园 * 七彩华园 * 农科社区(北区) * 正黄旗东区 * 紫城嘉园 * 远东公寓 * 菊园 * 竹园小区 * 菊花盛苑 * 亿城西山华府珑园 * 荷塘月舍 * 柳浪家园南里 * 圆明园西路3号院 * 正黄旗西区 * 亿城西山华府禧园 * 树村路甲1号院 * 柳浪家园北里 * 燕秀园一区 * 北京大学肖家河教职工家属院二区 * 万德嘉园(一区) * 学府壹号院(北区) * 农大附中家属院 * 梅园(海淀) * 兰园小区 * 学府壹号院(南区) 首页北京租房广泰小区。；解决市场痛点 长租公寓，又名白领公寓或单身公寓，是近几年房地产市场一个新兴行业，是将业主房屋租赁过来，进行装修改造，配齐家具家电，以单间的形式出租的公寓模式。；8月29日，合景泰富业绩会上，集团主席兼执行董事孔健岷表示，未来两三年公司自有的土地储备中可以提供约2万间长租公寓，但也会通过租赁其他物业改造的方式来增加约2万~3万间，预计未来总量可以达到4万~5万间。；此外，由部分城市要求部分招拍挂的出让土地必须有一定比例面积由开发商自持，长租公寓便成为这部分自持物业重要的去化出路。；两幅土地采取“只租不售”模式，项目建成后将至少提供1897套租赁住房房源。</x:v>
+        <x:v>两居室月租7100-7600元/月（如80㎡户型7600元/月、75㎡户型7400元/月等），无其他面积房型明确租金。；房龄约2014年，户型多为两室一厅，采光好，隔音效果不错；；装修多为精装修，配备家电；；物业为科住物业，服务周到，小区绿化率30%，有健身设施，整体居住环境较好。</x:v>
       </x:c>
       <x:c r="L54" t="str">
-        <x:v>58同城北京小区租房频道为您提供广泰小区租房信息，包括广泰小区最新出租房源，一室，二室，三室，四室，四室以上租房房源，租金走势和广泰小区小区周边租房信息等。；* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 广泰小区 &gt;* 广泰小区租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 广泰小区 海淀 / 马连洼 / 农大南路 小区信息 建筑类别: 多层 总 户 数: 1634 建筑年代: 2014年 绿 化 率: 30% 停 车 位:暂无数据 ### 广泰小区租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 2680元/月 0% 广泰小区 ### 广泰小区出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 * 2室1厅|75㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 广泰 精装大两居 电梯房 配套齐全 跟签约 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7400 元/月 * * 农大南路c口 广泰小区电梯高楼层两居室 价格可谈 * 2室1厅|78㎡ * 马连洼 * 邻地铁 精装修 随时看房 * 7400 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 广泰小区 * 万树园 * 丰泽盈和 * 圆明园花园 * 绿苑小区 * 博雅西园 * 七彩华园 * 农科社区(北区) * 正黄旗东区 * 紫城嘉园 * 远东公寓 * 菊园 * 竹园小区 * 菊花盛苑 * 亿城西山华府珑园 * 荷塘月舍 * 柳浪家园南里 * 圆明园西路3号院 * 正黄旗西区 * 亿城西山华府禧园 * 树村路甲1号院 * 柳浪家园北里 * 燕秀园一区 * 北京大学肖家河教职工家属院二区 * 万德嘉园(一区) * 学府壹号院(北区) * 农大附中家属院 * 梅园(海淀) * 兰园小区 * 学府壹号院(南区) 首页北京租房广泰小区。；友谊社区北三环边上正规办公房子可注册价格那是便宜的2500起. 2500元/月 · 海淀- 友谊社区. 交通便利采光好首次出租独门独卫 ;；万亿市场风口 随着租房逐渐成为一种新的可接受的生活方式，都市白领的长租正在吸引资本的目光，成了一个看得见的风口。；例如“YOU+”压缩居住空间，增加公共空间，提升用户产品体验及增加租金收入，在公寓一楼配备公共娱乐设施——健身房、台球室、吧台、便利店等。</x:v>
+        <x:v>距离16号线农大南路地铁站步行约719米，公交便捷；；周边有中发百旺商城等商超，生活配套全，临近高校，日常餐饮、买菜方便；</x:v>
       </x:c>
       <x:c r="M54" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未发现同名误命中情况，无明确差评或风险记录，房源均为真实挂牌。</x:v>
       </x:c>
       <x:c r="N54" t="str">
-        <x:v>价格线索： * 四室 * 四室以上 小区本月租金 2680元/月；配套齐全 精装修 有阳台 随时看房 * 7400 元/月；北通透 有阳台 首次出租 随时看房 * 7400 元/月；连洼 * 邻地铁 精装修 随时看房 * 7400 元/月；公房子可注册价格那是便宜的2500起. 2500元/月； 北三环中路甲18号院4室1卫1厅50平2600元/月；北起G南至A西起26东至29 2600-3200元/月；海淀） 北京市海淀区白家疃路 2100-4200元/月；房屋质量/户型线索：* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 广泰小区 &gt;* 广泰小区租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 广泰小区 海淀 / 马连洼 / 农大南路 小区信息 建筑类别: 多层 总 户 数: 1634 建筑年代: 2014年 绿 化 率: 30% 停 车 位:暂无数据 ### 广泰小区租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 2680元/月 0% 广泰小区 ### 广泰小区出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 * 2室1厅|75㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 广泰 精装大两居 电梯房 配套齐全 跟签约 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7400 元/月 * * 农大南路c口 广泰小区电梯高楼层两居室 价格可谈 * 2室1厅|78㎡ * 马连洼 * 邻地铁 精装修 随时看房 * 7400 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 广泰小区 * 万树园 * 丰泽盈和 * 圆明园花园 * 绿苑小区 * 博雅西园 * 七彩华园 * 农科社区(北区) * 正黄旗东区 * 紫城嘉园 * 远东公寓 * 菊园 * 竹园小区 * 菊花盛苑 * 亿城西山华府珑园 * 荷塘月舍 * 柳浪家园南里 * 圆明园西路3号院 * 正黄旗西区 * 亿城西山华府禧园 * 树村路甲1号院 * 柳浪家园北里 * 燕秀园一区 * 北京大学肖家河教职工家属院二区 * 万德嘉园(一区) * 学府壹号院(北区) * 农大附中家属院 * 梅园(海淀) * 兰园小区 * 学府壹号院(南区) 首页北京租房广泰小区。；解决市场痛点 长租公寓，又名白领公寓或单身公寓，是近几年房地产市场一个新兴行业，是将业主房屋租赁过来，进行装修改造，配齐家具家电，以单间的形式出租的公寓模式。；8月29日，合景泰富业绩会上，集团主席兼执行董事孔健岷表示，未来两三年公司自有的土地储备中可以提供约2万间长租公寓，但也会通过租赁其他物业改造的方式来增加约2万~3万间，预计未来总量可以达到4万~5万间。；此外，由部分城市要求部分招拍挂的出让土地必须有一定比例面积由开发商自持，长租公寓便成为这部分自持物业重要的去化出路。；两幅土地采取“只租不售”模式，项目建成后将至少提供1897套租赁住房房源。；生活便利线索：58同城北京小区租房频道为您提供广泰小区租房信息，包括广泰小区最新出租房源，一室，二室，三室，四室，四室以上租房房源，租金走势和广泰小区小区周边租房信息等。；* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 广泰小区 &gt;* 广泰小区租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 广泰小区 海淀 / 马连洼 / 农大南路 小区信息 建筑类别: 多层 总 户 数: 1634 建筑年代: 2014年 绿 化 率: 30% 停 车 位:暂无数据 ### 广泰小区租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 2680元/月 0% 广泰小区 ### 广泰小区出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 * 2室1厅|75㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 广泰 精装大两居 电梯房 配套齐全 跟签约 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7400 元/月 * * 农大南路c口 广泰小区电梯高楼层两居室 价格可谈 * 2室1厅|78㎡ * 马连洼 * 邻地铁 精装修 随时看房 * 7400 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 广泰小区 * 万树园 * 丰泽盈和 * 圆明园花园 * 绿苑小区 * 博雅西园 * 七彩华园 * 农科社区(北区) * 正黄旗东区 * 紫城嘉园 * 远东公寓 * 菊园 * 竹园小区 * 菊花盛苑 * 亿城西山华府珑园 * 荷塘月舍 * 柳浪家园南里 * 圆明园西路3号院 * 正黄旗西区 * 亿城西山华府禧园 * 树村路甲1号院 * 柳浪家园北里 * 燕秀园一区 * 北京大学肖家河教职工家属院二区 * 万德嘉园(一区) * 学府壹号院(北区) * 农大附中家属院 * 梅园(海淀) * 兰园小区 * 学府壹号院(南区) 首页北京租房广泰小区。；友谊社区北三环边上正规办公房子可注册价格那是便宜的2500起. 2500元/月 · 海淀- 友谊社区. 交通便利采光好首次出租独门独卫 ;；万亿市场风口 随着租房逐渐成为一种新的可接受的生活方式，都市白领的长租正在吸引资本的目光，成了一个看得见的风口。；例如“YOU+”压缩居住空间，增加公共空间，提升用户产品体验及增加租金收入，在公寓一楼配备公共娱乐设施——健身房、台球室、吧台、便利店等。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：两居室月租7100-7600元/月；（如80㎡户型7600元/月；、75㎡户型7400元/月；房屋质量/户型线索：两居室月租7100-7600元/月（如80㎡户型7600元/月、75㎡户型7400元/月等），无其他面积房型明确租金。；房龄约2014年，户型多为两室一厅，采光好，隔音效果不错；；装修多为精装修，配备家电；；物业为科住物业，服务周到，小区绿化率30%，有健身设施，整体居住环境较好。；生活便利线索：距离16号线农大南路地铁站步行约719米，公交便捷；；周边有中发百旺商城等商超，生活配套全，临近高校，日常餐饮、买菜方便；；风险线索：未发现同名误命中情况，无明确差评或风险记录，房源均为真实挂牌。</x:v>
       </x:c>
       <x:c r="O54" t="str">
-        <x:v>1. 【广泰小区，北京广泰小区租房，最新出租房源，租金走势信息】- 北京58同城 https://m.58.com/bj/xq/2074329/
-2. 广泰小区- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/117038249479284/
-3. 北三环租房价格 - 房天下 http://www.fang.com/houses/zf_252463bj/
-4. 人民周刊 http://paper.people.com.cn/rmzk/html/2017-11/20/content_1825992.htm
-5. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. https://i.haoduofangs.com/owner-comment/6587277495907647757/a7374375173983649818
+2. http://m.anjuke.com/bj/rent/4605294375644165-3/
+3. http://m.anjuke.com/bj/rent/4605285904755722-3/
+4. http://m.anjuke.com/bj/rent/4605448398040067-3/
+5. http://m.anjuke.com/bj/rent/4221804616867841-3/
+6. http://i.haoduofangs.com/owner-comment/6587277495907647757/7093853363917291550
+7. https://m.58.com/bj/xq/2074329/
+8. 广泰小区点评,海淀 马连洼 农大南路51号,北京马连洼广泰小区评价、业主点评、测评信息-北京幸福里 https://i.haoduofangs.com/owner-comment/6587277495907647757/a7374375173983649818</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -2892,39 +3046,42 @@
         <x:v>北京市海淀区龙背村路与天秀北路交叉口北320米</x:v>
       </x:c>
       <x:c r="E55" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F55" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G55" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H55" t="n">
-        <x:v>7</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I55" t="str">
-        <x:v>小区品质较高且户型宽敞，但证据多为二手房售价，具体租金信息尚不够充分。</x:v>
+        <x:v>户型多样且生活配套极佳，但房龄稍老，物业管理存在差评，电梯及防水有潜在风险。</x:v>
       </x:c>
       <x:c r="J55" t="str">
-        <x:v> 5室3厅3卫丨224㎡丨南北丨底层丨 93200元/㎡；2室1厅1卫丨106㎡丨南北丨高楼层丨 97899元/㎡；4室2厅3卫丨197㎡丨南北丨中楼层丨 106400元/㎡；5000_ 元/m² 百旺家苑，小区价格72888元/㎡</x:v>
+        <x:v>整租：11500元/月；（三室两厅）、12500元/月；合租：2400元/月；（小单间）、8700元/月</x:v>
       </x:c>
       <x:c r="K55" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **76151** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓2.69% 贷款计算器 * 二手房源 38套 * 楼栋总数 58栋 * 房屋总数 1254户 * 建筑类型 板楼 * 建筑年代 2003年建成 * 小区位置 马连洼地区农大北路南侧百旺家苑地图 * 物业公司 北京华特物业管理发展有限公司 * 开发商 北京德成兴业房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 王金雨 评分：4.3 从业信息卡 百科 ##### 陈峰 评分：4.1 从业信息卡 ##### 张帅 评分：4.1 从业信息卡 ##### 王胜楠 评分：4.1 从业信息卡 百科 * 户型 * 价格 * #### 满五年唯一,带电梯两居室,签约随时 2室1厅 94.02㎡**799**万 * #### 百旺家苑2室2厅南北 2室2厅 115.14㎡**770**万 * #### 百旺家苑2室2厅南北 2室2厅 99.19㎡**690**万 * #### 此房南北通透,通风好,南向大阳台,一层 3室2厅 139.55㎡**1085**万 ### 百旺家苑价格走势 ### 百旺家苑房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 百旺家苑别墅 海淀·马连洼**152913** 元/㎡ * #### 百旺家苑 海淀·马连洼**76152** 元/㎡ * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 马连洼梅园 海淀·马连洼**65210** 元/㎡ ### 相关资讯 * 小区资讯北京百旺家苑别墅怎么样?；百旺家苑别墅房价地址户型小区详情解析2021-10-31 * 小区资讯北京百旺家苑怎么样?；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺家苑 更新于 2026-06-01 10:46:54 [](https://bj.jiwu.com/tu/4301782.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301783.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301784.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301785.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301786.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301787.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301788.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301789.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301790.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301791.html "百旺家苑实景图图片") # 百旺家苑 别名：百旺家苑 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路_ 发地址到手机 参考均价 _72888 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2003_ 小区户数 _1303户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-63群（313） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？</x:v>
+        <x:v>房龄约2003-2006年；；户型涵盖一居到双拼别墅，主打三居南北通透；；装修多为精装修；；隔音中等（部分房源称隔音效果好）；；物业一般，存在管理混乱问题，物业费较高，电梯偶尔故障，防水中等；</x:v>
       </x:c>
       <x:c r="L55" t="str">
-        <x:v>百旺家苑价格地段交通优势解析2021-06-25 * 小区资讯最详细!；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺家苑 更新于 2026-06-01 10:46:54 [](https://bj.jiwu.com/tu/4301782.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301783.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301784.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301785.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301786.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301787.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301788.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301789.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301790.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301791.html "百旺家苑实景图图片") # 百旺家苑 别名：百旺家苑 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路_ 发地址到手机 参考均价 _72888 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2003_ 小区户数 _1303户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-63群（313） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等百旺家苑小区信息，关注吉屋北京百旺家苑！</x:v>
+        <x:v>通勤：步行约1056米到地铁16号线马连洼站，有651路等多路公交到西直门、上地、中关村等地；；商超：北门500米百旺商城，南门1000米华联，周边有超市发等；；医院：西边200米309医院（三级）；；餐饮：周边底商有便利店等，餐饮配套丰富。</x:v>
       </x:c>
       <x:c r="M55" t="str"/>
       <x:c r="N55" t="str">
-        <x:v>价格线索： 5室3厅3卫丨224㎡丨南北丨底层丨 93200元/㎡；2室1厅1卫丨106㎡丨南北丨高楼层丨 97899元/㎡；4室2厅3卫丨197㎡丨南北丨中楼层丨 106400元/㎡；5000_ 元/m² 百旺家苑，小区价格72888元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) [](https://esf.fang.com/loupan/1010026855/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **76151** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓2.69% 贷款计算器 * 二手房源 38套 * 楼栋总数 58栋 * 房屋总数 1254户 * 建筑类型 板楼 * 建筑年代 2003年建成 * 小区位置 马连洼地区农大北路南侧百旺家苑地图 * 物业公司 北京华特物业管理发展有限公司 * 开发商 北京德成兴业房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 王金雨 评分：4.3 从业信息卡 百科 ##### 陈峰 评分：4.1 从业信息卡 ##### 张帅 评分：4.1 从业信息卡 ##### 王胜楠 评分：4.1 从业信息卡 百科 * 户型 * 价格 * #### 满五年唯一,带电梯两居室,签约随时 2室1厅 94.02㎡**799**万 * #### 百旺家苑2室2厅南北 2室2厅 115.14㎡**770**万 * #### 百旺家苑2室2厅南北 2室2厅 99.19㎡**690**万 * #### 此房南北通透,通风好,南向大阳台,一层 3室2厅 139.55㎡**1085**万 ### 百旺家苑价格走势 ### 百旺家苑房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 百旺家苑别墅 海淀·马连洼**152913** 元/㎡ * #### 百旺家苑 海淀·马连洼**76152** 元/㎡ * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 马连洼梅园 海淀·马连洼**65210** 元/㎡ ### 相关资讯 * 小区资讯北京百旺家苑别墅怎么样?；百旺家苑别墅房价地址户型小区详情解析2021-10-31 * 小区资讯北京百旺家苑怎么样?；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺家苑 更新于 2026-06-01 10:46:54 [](https://bj.jiwu.com/tu/4301782.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301783.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301784.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301785.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301786.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301787.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301788.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301789.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301790.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301791.html "百旺家苑实景图图片") # 百旺家苑 别名：百旺家苑 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路_ 发地址到手机 参考均价 _72888 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2003_ 小区户数 _1303户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-63群（313） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；生活便利线索：百旺家苑价格地段交通优势解析2021-06-25 * 小区资讯最详细!；北京吉屋网提供北京百旺家苑二手房出售信息、百旺家苑二手房价格，包括及时更新北京百旺家苑二手房房源、价格走势、户型图、业主论坛、生活配套。；# 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_百旺家苑 更新于 2026-06-01 10:46:54 [](https://bj.jiwu.com/tu/4301782.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301783.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301784.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301785.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301786.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301787.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301788.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301789.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301790.html "百旺家苑实景图图片")[](https://bj.jiwu.com/tu/4301791.html "百旺家苑实景图图片") # 百旺家苑 别名：百旺家苑 加入本地买房群 关注 _北京 - 海淀 - 马连洼北路_ 发地址到手机 参考均价 _72888 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2003_ 小区户数 _1303户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 二手房源 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-63群（313） * 最近都说是上车好时候，大家怎么看 * 最近有什么新盘吗？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等百旺家苑小区信息，关注吉屋北京百旺家苑！</x:v>
+        <x:v>价格线索：整租：11500元/月；（三室两厅）、12500元/月；合租：2400元/月；（小单间）、8700元/月；房屋质量/户型线索：房龄约2003-2006年；；户型涵盖一居到双拼别墅，主打三居南北通透；；装修多为精装修；；隔音中等（部分房源称隔音效果好）；；物业一般，存在管理混乱问题，物业费较高，电梯偶尔故障，防水中等；；生活便利线索：通勤：步行约1056米到地铁16号线马连洼站，有651路等多路公交到西直门、上地、中关村等地；；商超：北门500米百旺商城，南门1000米华联，周边有超市发等；；医院：西边200米309医院（三级）；；餐饮：周边底商有便利店等，餐饮配套丰富。</x:v>
       </x:c>
       <x:c r="O55" t="str">
-        <x:v>1. 【北京百旺家苑小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010026855.htm
-2. 百旺家苑_北京百旺家苑小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/145707.html
-3. 西北旺房屋出租信息_北京海淀西北旺出租房源信息-58出租网 https://bj.zf.58.com/cz/xibeiwang/
-4. 海淀区首家人才驿站落户苏家坨镇，西山翠苑百套人才公寓启动入住 https://zyk.bjhd.gov.cn/jbdt/auto4560_51856/auto4560_58039/auto4560/auto4560/202512/t20251230_4799277_hd.shtml
-5. 百旺家苑最新房价_北京海淀区-中国房价行情 https://m.creprice.cn/community/pa00022194hd608.html?city=bj</x:v>
+        <x:v>1. https://beijing.anjuke.com/community/view/78963/jiedu/p1/
+2. http://m.anjuke.com/ch/rent/4597218016140301-3/
+3. http://m.anjuke.com/bj/rent/4499451345394698-3/
+4. http://m.anjuke.com/bj/rent/4606558717584385-3/
+5. https://m.kupet.cn/read-1774111608a41887698.html
+6. http://m.anjuke.com/bj/rent/4595185072415751-3/
+7. 百旺家苑优点、不足，百旺家苑怎么样，百旺家苑周边房产中介经纪人评价-北京安居客 https://beijing.anjuke.com/community/view/78963/jiedu/p1/
+8. 价可聊 百旺家苑三室两厅 可稳定长租 看房方便 跟业主签约 http://m.anjuke.com/ch/rent/4597218016140301-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -2941,41 +3098,44 @@
         <x:v>北京市海淀区马连洼街道厢黄旗东路19号</x:v>
       </x:c>
       <x:c r="E56" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F56" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G56" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H56" t="n">
-        <x:v>5.5</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="I56" t="str">
-        <x:v>网页证据存在大量泛化信息且与其他豪宅数据混杂，真实租金与质量线索较弱。</x:v>
+        <x:v>房龄较新且户型方正，租金价格梯度合理，临近多条地铁线，生活与通勤均十分便利。</x:v>
       </x:c>
       <x:c r="J56" t="str">
-        <x:v>站(奔驰南)老观里站 清空条件确认 不限1000元/月；以下1000-2000元/月；2000-3000元/月；3000-5000元/月；5000-8000元/月；8000-10000元/月；10000元/月；元/月 * ### 252平3室2厅3卫9.5万/月</x:v>
+        <x:v>一居月租约4500-5700元/月；，两居约6800-7500元/月；，三居约7600-7800元/月</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>c=map&amp;a=zfMap&amp;city=bj) ###### 频道导航 我的房天下_6_ 买新房买二手房找租房装修查房价我是业主首页资讯看房团房产问答海外房产写字楼商铺房贷计算器业主论坛房天下理财我要贷款房产知识土地别墅经纪人产业 ###### APP应用 全部应用 房天下经纪云 * 整租 * 合租 * 个人房源 * 地图找房 * ### 房东直租 优质房源 无中介费 在租房源 2031套 * ### 整租一居 独享空间 实惠一居 在租房源 47884套 * 推荐 [](https://m.fang.com/zf/bj/AGT_484263772.html) * _位置_ * _租金_ * _来源_ * _更多_ 区域;；) 不限个人 户型 一居;；) VR看房视频看房近地铁电梯 * ### 西海 新街口东街,光泽胡同精装独院 15室15厅 整租 21小时前 西城 - 光泽胡同 可注册办公 首次出租 南北通透 _72000_ 元/月 * ### 252平3室2厅3卫9.5万/月,一梯一户品质房 3室2厅 整租 19天前 朝阳 - 北京壹号院 _95000_ 元/月 * ### 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马桥,燕莎 4室2厅 整租 8天前 朝阳 - 北京壹号院 _115000_ 元/月 * ### 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看房随时 5室3厅 整租 246天前 海淀 - 万城华府别墅 _65000_ 元/月 * ### 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内可停车 8室5厅 整租 21小时前 东城 - 前厂胡同 可注册办公 首次出租 南北通透 _200000_ 元/月 * 实时更新 ### 优选6月北京近地铁房源 尽在房天下APP 立即打开;；) * ### 新出位置安静 可直接入住 楼层好 330平米 三面采光 3室3厅 整租 25天前 海淀 - 万柳书院 _138000_ 元/月 * ### 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带KTV 10室3厅 整租 6天前 西城 - 光明胡同 可注册办公 首次出租 南北通透 _180000_ 元/月 * ### 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨四合院 8室4厅 整租 6天前 西城 - 后小井胡同 可注册办公 首次出租 南北通透 _60000_ 元/月 * ### 15套起看 有钥匙看房随时万城华府尚园 中间位置 三面采光 4室3厅 整租 246天前 海淀 - 万城华府尚园 _75000_ 元/月 * ### 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有车位 4室2厅 整租 248天前 海淀 - 万城华府龙园 _58000_ 元/月 * 实时更新 ### 优选6月北京近地铁房源 尽在房天下APP 立即打开;；) * ### 张自忠路四合院独院出租 380平 北京四合院出租出售 9室9厅 整租 21小时前 西城 - 什刹海四合院 可注册办公 首次出租 南北通透 _83333_ 元/月 * ### 15套可看 高层 出租 万城华府一梯一户平层好山阁看房随时 5室3厅 整租 21天前 海淀 - 万城华府龙园 _80000_ 元/月 上拉加载更多... 北京最新热租房源推荐 立即打开 周边城市)其他区县)热门小区)热门商圈)综合推荐) * 保定租房 * 唐山租房 * 衡水租房 * 天津租房 * 石家庄租房 * 廊坊租房 * 张家口租房 * 承德租房 * 沧州租房 * 香河租房 * 涿州租房 * 开平租房 * 遵化租房 * 迁安租房 * 定州租房 * 辛集租房 * 滦县租房 * 玉田租房 * 朝阳租房 * 海淀租房 * 丰台租房 * 西城租房 * 东城租房 * 昌平租房 * 大兴租房 * 通州租房 * 房山租房 * 顺义租房 * 石景山租房 * 密云租房 * 门头沟租房 * 怀柔租房 * 延庆租房 * 平谷租房 * 燕郊租房 * 北京周边租房 * 远大园五区租房 * 上河村租房 * 温哥华森林租房 * 御汤山熙园租房 * 紫金长安租房 * 太阳公元租房 * 世纪城春荫园租房 * 世纪城翠叠园租房 * 保利垄上租房 * 万泉新新家园租房 * 碧水云天租房 * 龙湾别墅租房 * 华润橡树湾租房 * 纳帕溪谷租房 * 世纪城晴雪园租房 * 世纪城观山园租房 * 珠江壹千栋租房 * 阳春光华家园租房 * 北京新房 * 北京小区 * 北京二手房 * 北京租房 * 北京装修 * 北京装修公司 * 北京房价 * 北京写字楼 * 北京商铺 * 北京看房团 * 北京业主论坛 * 北京房产资讯 * 产业网 * 海外房产 * 房贷计算器 * 房产知识 * 房产问答 * 租房热搜 * 北京法拍房 * 望京租房 * 国贸租房 * 亦庄租房 * 北苑租房 * 顺义城租房 * 酒仙桥租房 * 良乡租房 * 回龙观租房 * 朝阳公园租房 * 朝阳公园租房 * 天通苑租房 * 长阳租房 * 双井租房 * 朝青租房 * 北七家租房 * 清河租房 * 昌平县城租房 * 万柳租房 房天下北京租房网提供个人直租房、经纪人租房等房源信息，帮您轻松在北京租房子。</x:v>
+        <x:v>一居月租约4500-5700元/月，两居约6800-7500元/月，三居约7600-7800元/月，多为精装修，押一付三为主，部分房源可长租或直签；；房龄方面，部分标注2014年建成，部分未明确但整体小区环境成熟；；户型方正，南北通透居多；；装修以精装修为主，配套家电齐全；；物业方面描述为管理完善、治安好，有24小时保安；</x:v>
       </x:c>
       <x:c r="L56" t="str">
-        <x:v>) 北京租房 请输入小区名、地铁或地名 [](https://m.fang.com/map/?；)地铁;；)近地铁;；) VR看房视频看房近地铁电梯 * ### 西海 新街口东街,光泽胡同精装独院 15室15厅 整租 21小时前 西城 - 光泽胡同 可注册办公 首次出租 南北通透 _72000_ 元/月 * ### 252平3室2厅3卫9.5万/月,一梯一户品质房 3室2厅 整租 19天前 朝阳 - 北京壹号院 _95000_ 元/月 * ### 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马桥,燕莎 4室2厅 整租 8天前 朝阳 - 北京壹号院 _115000_ 元/月 * ### 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看房随时 5室3厅 整租 246天前 海淀 - 万城华府别墅 _65000_ 元/月 * ### 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内可停车 8室5厅 整租 21小时前 东城 - 前厂胡同 可注册办公 首次出租 南北通透 _200000_ 元/月 * 实时更新 ### 优选6月北京近地铁房源 尽在房天下APP 立即打开;；) * ### 新出位置安静 可直接入住 楼层好 330平米 三面采光 3室3厅 整租 25天前 海淀 - 万柳书院 _138000_ 元/月 * ### 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带KTV 10室3厅 整租 6天前 西城 - 光明胡同 可注册办公 首次出租 南北通透 _180000_ 元/月 * ### 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨四合院 8室4厅 整租 6天前 西城 - 后小井胡同 可注册办公 首次出租 南北通透 _60000_ 元/月 * ### 15套起看 有钥匙看房随时万城华府尚园 中间位置 三面采光 4室3厅 整租 246天前 海淀 - 万城华府尚园 _75000_ 元/月 * ### 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有车位 4室2厅 整租 248天前 海淀 - 万城华府龙园 _58000_ 元/月 * 实时更新 ### 优选6月北京近地铁房源 尽在房天下APP 立即打开;</x:v>
+        <x:v>装修以精装修为主，配套家电齐全；；通勤：临近16号线农大南路站、13号线上地站，距18号线上地软件园站约1.9公里，周边有公交；；商超：周边有世纪华联、幸福超市、百旺商城等；；生活配套完善，餐饮、健身场所多；；医院信息未明确提及；</x:v>
       </x:c>
       <x:c r="M56" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>未搜索到明确的租房差评或风险信息。；未搜索到明确的租房差评或风险信息</x:v>
       </x:c>
       <x:c r="N56" t="str">
-        <x:v>价格线索：站(奔驰南)老观里站 清空条件确认 不限1000元/月；以下1000-2000元/月；2000-3000元/月；3000-5000元/月；5000-8000元/月；8000-10000元/月；10000元/月；元/月 * ### 252平3室2厅3卫9.5万/月；房屋质量/户型线索：c=map&amp;a=zfMap&amp;city=bj) ###### 频道导航 我的房天下_6_ 买新房买二手房找租房装修查房价我是业主首页资讯看房团房产问答海外房产写字楼商铺房贷计算器业主论坛房天下理财我要贷款房产知识土地别墅经纪人产业 ###### APP应用 全部应用 房天下经纪云 * 整租 * 合租 * 个人房源 * 地图找房 * ### 房东直租 优质房源 无中介费 在租房源 2031套 * ### 整租一居 独享空间 实惠一居 在租房源 47884套 * 推荐 [](https://m.fang.com/zf/bj/AGT_484263772.html) * _位置_ * _租金_ * _来源_ * _更多_ 区域;；) 不限个人 户型 一居;；) VR看房视频看房近地铁电梯 * ### 西海 新街口东街,光泽胡同精装独院 15室15厅 整租 21小时前 西城 - 光泽胡同 可注册办公 首次出租 南北通透 _72000_ 元/月 * ### 252平3室2厅3卫9.5万/月,一梯一户品质房 3室2厅 整租 19天前 朝阳 - 北京壹号院 _95000_ 元/月 * ### 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马桥,燕莎 4室2厅 整租 8天前 朝阳 - 北京壹号院 _115000_ 元/月 * ### 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看房随时 5室3厅 整租 246天前 海淀 - 万城华府别墅 _65000_ 元/月 * ### 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内可停车 8室5厅 整租 21小时前 东城 - 前厂胡同 可注册办公 首次出租 南北通透 _200000_ 元/月 * 实时更新 ### 优选6月北京近地铁房源 尽在房天下APP 立即打开;；) * ### 新出位置安静 可直接入住 楼层好 330平米 三面采光 3室3厅 整租 25天前 海淀 - 万柳书院 _138000_ 元/月 * ### 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带KTV 10室3厅 整租 6天前 西城 - 光明胡同 可注册办公 首次出租 南北通透 _180000_ 元/月 * ### 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨四合院 8室4厅 整租 6天前 西城 - 后小井胡同 可注册办公 首次出租 南北通透 _60000_ 元/月 * ### 15套起看 有钥匙看房随时万城华府尚园 中间位置 三面采光 4室3厅 整租 246天前 海淀 - 万城华府尚园 _75000_ 元/月 * ### 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有车位 4室2厅 整租 248天前 海淀 - 万城华府龙园 _58000_ 元/月 * 实时更新 ### 优选6月北京近地铁房源 尽在房天下APP 立即打开;；) * ### 张自忠路四合院独院出租 380平 北京四合院出租出售 9室9厅 整租 21小时前 西城 - 什刹海四合院 可注册办公 首次出租 南北通透 _83333_ 元/月 * ### 15套可看 高层 出租 万城华府一梯一户平层好山阁看房随时 5室3厅 整租 21天前 海淀 - 万城华府龙园 _80000_ 元/月 上拉加载更多... 北京最新热租房源推荐 立即打开 周边城市)其他区县)热门小区)热门商圈)综合推荐) * 保定租房 * 唐山租房 * 衡水租房 * 天津租房 * 石家庄租房 * 廊坊租房 * 张家口租房 * 承德租房 * 沧州租房 * 香河租房 * 涿州租房 * 开平租房 * 遵化租房 * 迁安租房 * 定州租房 * 辛集租房 * 滦县租房 * 玉田租房 * 朝阳租房 * 海淀租房 * 丰台租房 * 西城租房 * 东城租房 * 昌平租房 * 大兴租房 * 通州租房 * 房山租房 * 顺义租房 * 石景山租房 * 密云租房 * 门头沟租房 * 怀柔租房 * 延庆租房 * 平谷租房 * 燕郊租房 * 北京周边租房 * 远大园五区租房 * 上河村租房 * 温哥华森林租房 * 御汤山熙园租房 * 紫金长安租房 * 太阳公元租房 * 世纪城春荫园租房 * 世纪城翠叠园租房 * 保利垄上租房 * 万泉新新家园租房 * 碧水云天租房 * 龙湾别墅租房 * 华润橡树湾租房 * 纳帕溪谷租房 * 世纪城晴雪园租房 * 世纪城观山园租房 * 珠江壹千栋租房 * 阳春光华家园租房 * 北京新房 * 北京小区 * 北京二手房 * 北京租房 * 北京装修 * 北京装修公司 * 北京房价 * 北京写字楼 * 北京商铺 * 北京看房团 * 北京业主论坛 * 北京房产资讯 * 产业网 * 海外房产 * 房贷计算器 * 房产知识 * 房产问答 * 租房热搜 * 北京法拍房 * 望京租房 * 国贸租房 * 亦庄租房 * 北苑租房 * 顺义城租房 * 酒仙桥租房 * 良乡租房 * 回龙观租房 * 朝阳公园租房 * 朝阳公园租房 * 天通苑租房 * 长阳租房 * 双井租房 * 朝青租房 * 北七家租房 * 清河租房 * 昌平县城租房 * 万柳租房 房天下北京租房网提供个人直租房、经纪人租房等房源信息，帮您轻松在北京租房子。；生活便利线索：) 北京租房 请输入小区名、地铁或地名 [](https://m.fang.com/map/?；)地铁;；)近地铁;；) VR看房视频看房近地铁电梯 * ### 西海 新街口东街,光泽胡同精装独院 15室15厅 整租 21小时前 西城 - 光泽胡同 可注册办公 首次出租 南北通透 _72000_ 元/月 * ### 252平3室2厅3卫9.5万/月,一梯一户品质房 3室2厅 整租 19天前 朝阳 - 北京壹号院 _95000_ 元/月 * ### 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马桥,燕莎 4室2厅 整租 8天前 朝阳 - 北京壹号院 _115000_ 元/月 * ### 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看房随时 5室3厅 整租 246天前 海淀 - 万城华府别墅 _65000_ 元/月 * ### 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内可停车 8室5厅 整租 21小时前 东城 - 前厂胡同 可注册办公 首次出租 南北通透 _200000_ 元/月 * 实时更新 ### 优选6月北京近地铁房源 尽在房天下APP 立即打开;；) * ### 新出位置安静 可直接入住 楼层好 330平米 三面采光 3室3厅 整租 25天前 海淀 - 万柳书院 _138000_ 元/月 * ### 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带KTV 10室3厅 整租 6天前 西城 - 光明胡同 可注册办公 首次出租 南北通透 _180000_ 元/月 * ### 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨四合院 8室4厅 整租 6天前 西城 - 后小井胡同 可注册办公 首次出租 南北通透 _60000_ 元/月 * ### 15套起看 有钥匙看房随时万城华府尚园 中间位置 三面采光 4室3厅 整租 246天前 海淀 - 万城华府尚园 _75000_ 元/月 * ### 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有车位 4室2厅 整租 248天前 海淀 - 万城华府龙园 _58000_ 元/月 * 实时更新 ### 优选6月北京近地铁房源 尽在房天下APP 立即打开;；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：一居月租约4500-5700元/月；，两居约6800-7500元/月；，三居约7600-7800元/月；房屋质量/户型线索：一居月租约4500-5700元/月，两居约6800-7500元/月，三居约7600-7800元/月，多为精装修，押一付三为主，部分房源可长租或直签；；房龄方面，部分标注2014年建成，部分未明确但整体小区环境成熟；；户型方正，南北通透居多；；装修以精装修为主，配套家电齐全；；物业方面描述为管理完善、治安好，有24小时保安；；生活便利线索：装修以精装修为主，配套家电齐全；；通勤：临近16号线农大南路站、13号线上地站，距18号线上地软件园站约1.9公里，周边有公交；；商超：周边有世纪华联、幸福超市、百旺商城等；；生活配套完善，餐饮、健身场所多；；医院信息未明确提及；；风险线索：未搜索到明确的租房差评或风险信息。；未搜索到明确的租房差评或风险信息</x:v>
       </x:c>
       <x:c r="O56" t="str">
-        <x:v>1. 【北京租房网_北京房屋出租信息】北京手机房天下 https://m.fang.com/zf/bj/AGT_484263772.html
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. “我们在海淀安家了”！实拍暖心年味儿 https://xinwen.bjd.com.cn/content/s63cba15be4b0ed71f92820f1.html
-4.  https://fangchan.snssdk.com/zufang/bj-7621295850211360818.html
-5. 租房 https://m.douban.com/doulist/150305210/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4603985937015816-3/
+2. http://m.anjuke.com/bj/rent/4590110396918798-2/
+3. http://m.anjuke.com/bj/rent/4604212614030342-3/
+4. 柳浪家园北里 精装一居室 非常干净 配套齐全和业主签约可长租 http://m.anjuke.com/bj/rent/4603985937015816-3/
+5. 柳浪家园北里 2室1厅1卫 http://m.anjuke.com/bj/rent/4590110396918798-2/
+6. 柳浪家园北里南北两居室 http://m.anjuke.com/ch/rent/4265698597035022-3/
+7. 柳浪家园北里 3室1厅1卫 阳光充足 精装修 http://m.anjuke.com/bj/rent/4578155506592772-3/
+8. 柳浪家园北里 3室1厅1卫 精装修 配套齐全 南北通透 http://m.anjuke.com/bj/rent/3638725235974157-3/?ad_type=j&amp;pagesource=782</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -2992,41 +3152,44 @@
         <x:v>北京市海淀区马连洼路天秀北路与圆明园西路辅路交叉口西340米</x:v>
       </x:c>
       <x:c r="E57" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F57" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G57" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H57" t="n">
-        <x:v>6.5</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="I57" t="str">
-        <x:v>租金档位分布明确，但缺乏小区具体的建筑年代与居住质量描述，证据充分性一般。</x:v>
+        <x:v>房龄较老但租金优势明显，内部装修多已翻新，紧邻地铁站与农贸市场，生活气息浓。</x:v>
       </x:c>
       <x:c r="J57" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
+        <x:v>整租两居5600元/月；（65平）、三居7000元/月；（80平），另有81平两居6500元/月</x:v>
       </x:c>
       <x:c r="K57" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；58同城北京租房网，为您提供北京海淀租房信息，包括海淀房屋出租信息、海淀合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。</x:v>
+        <x:v>房龄1979年建成，房屋多为精装修；；户型南北通透，采光通风好；；部分房源提及卧室隔音效果好；；物业方面小区有物业部门管理，治安较好；</x:v>
       </x:c>
       <x:c r="L57" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；交通便利周边配套齐全装全配 8930 元/月 ) 字节房补 满庭房源精装大主卧 客户超大 稳定长租 合租主卧|4户合租|20㎡|朝东南 海淀-双榆树-满庭芳园 距10号线知春里站约845米。</x:v>
+        <x:v>临近地铁16号线农大南路（步行约1106米）、马连洼站（步行约674米），公交线路多；；周边有天秀生活超市、中发百旺商城等商超，配套成熟；；有农贸市场，餐饮、购物便利；</x:v>
       </x:c>
       <x:c r="M57" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>暂未查询到明确差评或风险信息，无同名误命中情况。；暂未查询到明确差评或风险信息，无同名误命中情况</x:v>
       </x:c>
       <x:c r="N57" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；58同城北京租房网，为您提供北京海淀租房信息，包括海淀房屋出租信息、海淀合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。；生活便利线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；交通便利周边配套齐全装全配 8930 元/月 ) 字节房补 满庭房源精装大主卧 客户超大 稳定长租 合租主卧|4户合租|20㎡|朝东南 海淀-双榆树-满庭芳园 距10号线知春里站约845米。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：整租两居5600元/月；（65平）、三居7000元/月；（80平），另有81平两居6500元/月；房屋质量/户型线索：房龄1979年建成，房屋多为精装修；；户型南北通透，采光通风好；；部分房源提及卧室隔音效果好；；物业方面小区有物业部门管理，治安较好；；生活便利线索：临近地铁16号线农大南路（步行约1106米）、马连洼站（步行约674米），公交线路多；；周边有天秀生活超市、中发百旺商城等商超，配套成熟；；有农贸市场，餐饮、购物便利；；风险线索：暂未查询到明确差评或风险信息，无同名误命中情况。；暂未查询到明确差评或风险信息，无同名误命中情况</x:v>
       </x:c>
       <x:c r="O57" t="str">
-        <x:v>1. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-2. 【北京租房网_北京租房信息|房屋出租】- 房天下 http://www.fang.com/houses/zf_252463bj/
-3. 2026北京海淀区第一批公租房房源信息查询（附价格）- 北京本地宝 http://bj.bendibao.com/zffw/202658/382527.shtm
-4. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-5. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4564186138762254-3/
+2. http://m.anjuke.com/dongyang/rent/4576759518751756-3/
+3. http://m.anjuke.com/bj/rent/4358899698265100-3/
+4. 水利社区1号院 精装两居 干净整洁 配置齐全 价格可优惠！ http://m.anjuke.com/bj/rent/4564186138762254-3/
+5. 水利社区1号院 低楼层精装三居室 价格合适 和业主签约可长租 http://m.anjuke.com/dongyang/rent/4576759518751756-3/
+6. 水利社区1号院 精装两居 实房实图 跟业主签约 配套全可长租 http://m.anjuke.com/bj/rent/4358899698265100-3/
+7. 价格能便宜 中间楼层 水利社区1号院 跟业主签约 看房方便 http://m.anjuke.com/ch/rent/4565488118901773-3/
+8. 价格可谈 水利社区 南北通透两居 中间楼层 业主直签 可长住 http://m.anjuke.com/bj/rent/4561623800194063-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -3043,41 +3206,42 @@
         <x:v>北京市海淀区马连洼街道圆明园西路梅园甲</x:v>
       </x:c>
       <x:c r="E58" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F58" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G58" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H58" t="n">
-        <x:v>4</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I58" t="str">
-        <x:v>搜索结果包含大量无关豪宅及四合院信息，缺乏该小区真实质量证据，评分保守。</x:v>
+        <x:v>离地铁近且配套成熟，租金在海淀区相对合理，是网易员工的高性价比选择。</x:v>
       </x:c>
       <x:c r="J58" t="str">
-        <x:v>-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；寺四合院 可注册办公首次出租南北通透 210000 元/月；105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月；道湾东巷 可注册办公首次出租南北通透 120000 元/月；镇江胡同 可注册办公首次出租南北通透 140000 元/月</x:v>
+        <x:v>息中，2室1厅户型的月租大致在5300-5900元/月</x:v>
       </x:c>
       <x:c r="K58" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？</x:v>
+        <x:v>目前搜索到与目标御龙苑（海淀区马连洼街道圆明园西路梅园甲）相关的租房房源信息中，2室1厅户型的月租大致在5300-5900元/月（不同房源面积略有差异，如61㎡、63㎡对应价位），均需押一付三，中介费为一个月租金，无额外服务费。；现有相关房源提及装修为精装修，房屋配套齐全；；未明确提到隔音、房龄等具体质量信息，也无物业相关评价。</x:v>
       </x:c>
       <x:c r="L58" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？</x:v>
-      </x:c>
-      <x:c r="M58" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
-      </x:c>
+        <x:v>现有相关房源提及装修为精装修，房屋配套齐全；；周边临近地铁16号线马连洼站（步行约592米），出行便捷；；附近有超市发、美廉美等商超，还有中国银行城市森林公园等景观，生活配套较完善，餐饮资源未明确提及。</x:v>
+      </x:c>
+      <x:c r="M58" t="str"/>
       <x:c r="N58" t="str">
-        <x:v>价格线索：-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；寺四合院 可注册办公首次出租南北通透 210000 元/月；105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月；道湾东巷 可注册办公首次出租南北通透 120000 元/月；镇江胡同 可注册办公首次出租南北通透 140000 元/月；房屋质量/户型线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；生活便利线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 ) 西山美庐独栋别墅 4居5卫 居家会所皆可 能长租 整租|4室3厅|366㎡|朝东 海淀-西山-西山美庐 72000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 西城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出租南北通透 55000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 能容纳20多人的客厅。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：息中，2室1厅户型的月租大致在5300-5900元/月；房屋质量/户型线索：目前搜索到与目标御龙苑（海淀区马连洼街道圆明园西路梅园甲）相关的租房房源信息中，2室1厅户型的月租大致在5300-5900元/月（不同房源面积略有差异，如61㎡、63㎡对应价位），均需押一付三，中介费为一个月租金，无额外服务费。；现有相关房源提及装修为精装修，房屋配套齐全；；未明确提到隔音、房龄等具体质量信息，也无物业相关评价。；生活便利线索：现有相关房源提及装修为精装修，房屋配套齐全；；周边临近地铁16号线马连洼站（步行约592米），出行便捷；；附近有超市发、美廉美等商超，还有中国银行城市森林公园等景观，生活配套较完善，餐饮资源未明确提及。</x:v>
       </x:c>
       <x:c r="O58" t="str">
-        <x:v>1. 【北京pg娱乐电子游戏ty64.cc租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kwpg%E5%A8%B1%E4%B9%90%E7%94%B5%E5%AD%90%E6%B8%B8%E6%88%8Fty64.cc?71%20target=_blank
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3.  https://m.ke.com/chuzu/houserank/list/beijingjingjijishukaifaqu/rt200600000001l0l2rp1rp5rp3rp6/
-4. 北京精装公寓出租信息 https://ifeng-m.lianjia.com/chuzu/bj/apartment/haidianqu/amp5amp3ama0/
-5. 住万柳书院什么体验？一起看看月租15万的房长啥样吧！_哔哩哔哩_bilibili https://www.bilibili.com/video/BV1ri421Q7hq/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4583081688898565-3/
+2. http://m.anjuke.com/bj/rent/4604050814741516-3/
+3. http://m.anjuke.com/bj/rent/4539084634645511-3/
+4. 价格可聊马连洼两居室 交通方便 随时入住 稳定长租 配套齐全 http://m.anjuke.com/bj/rent/4583081688898565-3/
+5. 太原御龙苑小区房价怎么样？ 御龙苑小区房源|户型图|小区车位|交通地址详情分析！ https://m.lianjia.com/news/ty/xiaoqu/8707131367158710.html
+6. 马连洼 二居室 价格不贵 随时入住 好说话 看房方便长租 http://m.anjuke.com/bj/rent/4604050814741516-3/
+7. 安居御龙苑 https://sz.newhouse.fang.com/loupan/2810209230/dianping/s0/
+8. 价格可聊！！马连洼梅园 精装南北两居 配置齐 实房 稳定长租 http://m.anjuke.com/bj/rent/4539084634645511-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -3094,41 +3258,40 @@
         <x:v>北京市海淀区唐家岭路55号</x:v>
       </x:c>
       <x:c r="E59" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F59" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G59" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H59" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H59" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
       <x:c r="I59" t="str">
-        <x:v>证据指向亮马桥高端区域，距离网易大厦较远，通勤不便且租金与定位不匹配。</x:v>
-      </x:c>
-      <x:c r="J59" t="str">
-        <x:v>停车位费用为2500 - 3000元/月；【北京小户型公寓出租3000-50002元/月；# 【北京小户型公寓出租3000-50002元/月；： * 关键字：小户型公寓出租3000-50002元/月；18000 元/月；6500 元/月；22000 元/月；7500 元/月</x:v>
-      </x:c>
+        <x:v>生活配套较全且采光好，但缺乏明确租金信息且依赖公交，建议确认价格后再考虑。</x:v>
+      </x:c>
+      <x:c r="J59" t="str"/>
       <x:c r="K59" t="str">
-        <x:v>10分钟内，即可覆盖三里屯太古里、蓝色港湾等潮流商业地标，商务宴请、休闲购物皆在“黄金生活圈”内，满足您对高品质生活的全方位需求。；公寓直面亮马河极宽河段，部分高楼层户型更是能俯瞰从燕莎码头到朝阳公园的完整河景。；高端定位，四重保障铸就品质生活 谈及价格，启皓会客厅公寓（北京宝格丽公寓旁）确实属于“高端定位”，但这份“小贵”背后，蕴含着“品牌 + 地段 + 品质 + 服务”的四重坚实保障。；“宝格丽的品牌圈层”，与志同道合的精英人士为邻，拓展人脉资源，提升社交品质；；对于追求生活品质、注重圈层身份的精英而言，这样的居住体验，恰恰是“花钱买时间、买舒适、买认同感”的极佳选择。</x:v>
+        <x:v>户型有1室1厅、2室1厅、3室1厅等，装修多为精装修或简单装修，押付方式多为押一付三、押一付一。；房龄及物业信息未明确提及，装修状况多为精装修（部分简单装修），户型方正、南北朝向采光好，配套有冰箱、洗衣机等家电；；未提及隔音相关评价。</x:v>
       </x:c>
       <x:c r="L59" t="str">
-        <x:v>黄金选址，圈定高端生活版图 启皓会客厅公寓（北京宝格丽公寓旁）的选址，无疑自带“高端圈层”的精准筛选属性。；从公寓出发，步行即可轻松抵达地铁10号线亮马桥站，3站便能直达国贸CBD，无论是商务出行还是日常通勤，都极为便捷。；10分钟内，即可覆盖三里屯太古里、蓝色港湾等潮流商业地标，商务宴请、休闲购物皆在“黄金生活圈”内，满足您对高品质生活的全方位需求。；这份“推窗见景”的惬意，在寸土寸金的内城堪称绝版，让您在家中就能享受如诗如画的自然美景，感受生活的宁静与美好。；高端定位，四重保障铸就品质生活 谈及价格，启皓会客厅公寓（北京宝格丽公寓旁）确实属于“高端定位”，但这份“小贵”背后，蕴含着“品牌 + 地段 + 品质 + 服务”的四重坚实保障。</x:v>
-      </x:c>
-      <x:c r="M59" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
-      </x:c>
+        <x:v>房龄及物业信息未明确提及，装修状况多为精装修（部分简单装修），户型方正、南北朝向采光好，配套有冰箱、洗衣机等家电；；交通方面，临近公交站（如航天城南门站256-334米），出行便利；；周边有U悦生活广场、鹿鹿生鲜超市等商超，距离中国人民解放军总医院京北医疗区约1705米，生活配套较完善。</x:v>
+      </x:c>
+      <x:c r="M59" t="str"/>
       <x:c r="N59" t="str">
-        <x:v>价格线索：停车位费用为2500 - 3000元/月；【北京小户型公寓出租3000-50002元/月；# 【北京小户型公寓出租3000-50002元/月；： * 关键字：小户型公寓出租3000-50002元/月；18000 元/月；6500 元/月；22000 元/月；7500 元/月；房屋质量/户型线索：10分钟内，即可覆盖三里屯太古里、蓝色港湾等潮流商业地标，商务宴请、休闲购物皆在“黄金生活圈”内，满足您对高品质生活的全方位需求。；公寓直面亮马河极宽河段，部分高楼层户型更是能俯瞰从燕莎码头到朝阳公园的完整河景。；高端定位，四重保障铸就品质生活 谈及价格，启皓会客厅公寓（北京宝格丽公寓旁）确实属于“高端定位”，但这份“小贵”背后，蕴含着“品牌 + 地段 + 品质 + 服务”的四重坚实保障。；“宝格丽的品牌圈层”，与志同道合的精英人士为邻，拓展人脉资源，提升社交品质；；对于追求生活品质、注重圈层身份的精英而言，这样的居住体验，恰恰是“花钱买时间、买舒适、买认同感”的极佳选择。；生活便利线索：黄金选址，圈定高端生活版图 启皓会客厅公寓（北京宝格丽公寓旁）的选址，无疑自带“高端圈层”的精准筛选属性。；从公寓出发，步行即可轻松抵达地铁10号线亮马桥站，3站便能直达国贸CBD，无论是商务出行还是日常通勤，都极为便捷。；10分钟内，即可覆盖三里屯太古里、蓝色港湾等潮流商业地标，商务宴请、休闲购物皆在“黄金生活圈”内，满足您对高品质生活的全方位需求。；这份“推窗见景”的惬意，在寸土寸金的内城堪称绝版，让您在家中就能享受如诗如画的自然美景，感受生活的宁静与美好。；高端定位，四重保障铸就品质生活 谈及价格，启皓会客厅公寓（北京宝格丽公寓旁）确实属于“高端定位”，但这份“小贵”背后，蕴含着“品牌 + 地段 + 品质 + 服务”的四重坚实保障。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>房屋质量/户型线索：户型有1室1厅、2室1厅、3室1厅等，装修多为精装修或简单装修，押付方式多为押一付三、押一付一。；房龄及物业信息未明确提及，装修状况多为精装修（部分简单装修），户型方正、南北朝向采光好，配套有冰箱、洗衣机等家电；；未提及隔音相关评价。；生活便利线索：房龄及物业信息未明确提及，装修状况多为精装修（部分简单装修），户型方正、南北朝向采光好，配套有冰箱、洗衣机等家电；；交通方面，临近公交站（如航天城南门站256-334米），出行便利；；周边有U悦生活广场、鹿鹿生鲜超市等商超，距离中国人民解放军总医院京北医疗区约1705米，生活配套较完善。</x:v>
       </x:c>
       <x:c r="O59" t="str">
-        <x:v>1. 北京启皓会客厅公寓（北京宝格丽公寓旁）：意式奢居与京城风华的完美交融 https://www.yudinggongyu.com/article/225.cshtml
-2. 【北京小户型公寓出租3000-50002元/月租房信息_房屋出租】- 房天下 https://www.fang.com/houses/zf_252973bj/c23000-d250002,1,99-i315/
-3. 2025年北京酒店式公寓+长租公寓百科-租房指南，深度解析 https://www.gongyuzufang.com/blog/1376.cshtml
-4. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-5. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/3955682006392839-3/
+2. http://m.anjuke.com/bj/rent/4320700506348544-3/
+3. http://m.anjuke.com/bj/rent/4589487343297546-3/
+4. http://m.anjuke.com/bj/rent/4585222730804239-3/
+5. http://m.anjuke.com/bj/rent/4565902783310860-3/
+6. 唐家岭 2室出租 业主直签 价格便宜 采光明亮 视野宽阔 http://m.anjuke.com/bj/rent/3955682006392839-3/
+7. 唐家岭新城正规一室一厅免押租 邻近滴滴新城海 http://m.anjuke.com/bj/rent/4320700506348544-3/
+8. 唐家岭新城(东区) 家电齐全 电梯房 阳光充足 http://m.anjuke.com/bj/rent/4589487343297546-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -3145,41 +3308,44 @@
         <x:v>北京市海淀区天秀路12号</x:v>
       </x:c>
       <x:c r="E60" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F60" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G60" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H60" t="n">
-        <x:v>8.5</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I60" t="str">
-        <x:v>位于马连洼区域，距离网易大厦极近，租金水平合理且配套成熟，是理想的通勤选择。</x:v>
+        <x:v>万科物业加持，交通医疗配套顶级，虽房龄较老且租金偏高，适合追求品质的人群。</x:v>
       </x:c>
       <x:c r="J60" t="str">
-        <x:v> * 四室 * 四室以上 小区本月租金 5683元/月；㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月；㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月；独立阳台 邻地铁 精装修 南北通透 * 2300 元/月；独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月；2厅二手房 188.79㎡ 1500万 79454元/㎡</x:v>
+        <x:v>整租房源2室2厅1卫面积约90㎡，租金在7600元/月；（2025年10月）、8200元/月</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 天秀花园澄秀园 &gt;* 天秀花园澄秀园租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 天秀花园澄秀园 海淀 / 马连洼 / 天秀路 小区信息 建筑类别: 多层 总 户 数: 542 建筑年代: 2007年 绿 化 率: 33% 停 车 位:暂无数据 ### 天秀花园澄秀园租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 5683元/月 0.02% 天秀花园澄秀园 ### 天秀花园澄秀园出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 天秀花园澄秀园 精装小两居 南北通透 价格合适 随时看 * 2室1厅|65.19㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月 * * 马连洼天秀花园澄秀 电梯房 精装修 可月付 近地铁 * 3室1厅|11.4㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月 * * 天秀花园澄秀园 3室1厅2卫 * 3室1厅|15㎡ * 马连洼 * 独卫 独立阳台 邻地铁 精装修 南北通透 * 2300 元/月 * * 整租马连洼天秀花园澄秀园1室1厅 * 1室1厅|61.66㎡ * 马连洼 * 独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 天秀花园澄秀园 * 水利社区1号院 * 天秀花园久盛居 * 颐北家苑 * 水利社区二号院 * 圆明园西路甲1号院 * 梅园(海淀) * 百旺家苑 * 天秀花园古月园 * 梅园甲 * 裕隆新村 * 圆明园西路3号院 * 兰园小区 * 农大附中家属院 * 黑山扈路甲17号院 * 润千秋佳苑 * 天秀花园安和园 * 亿城西山华府禧园 * 荷塘月舍 * 农科社区(北区) * 西山庭院 * 亿城西山华府珑园 * 北京大学肖家河教职工家属院二区 * 百草园社区 * 北京大学肖家河教职工家属院三区 * 正黄旗西区 * 正黄旗东区 * 大有北里 * 竹园小区 * 丰泽盈和 首页北京租房天秀花园澄秀园。；phototype=shijing) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 * 户型 * 价格 * #### 马连洼·天秀花园澄秀园·2室·2厅 2室2厅 90.65㎡**660**万 * #### 2007年商品房,满五唯一商品房,产权清晰 2室1厅 62.54㎡**399**万 * #### 天秀花园澄秀园2室1厅西 1室1厅 65.19㎡**329**万 * #### 马连洼·天秀花园澄秀园·3室·1厅 3室1厅 89.12㎡**738**万 ### 天秀花园澄秀园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 75.75㎡ | 2026-03-08 | -- | -- | 市场信息 | | 86.84㎡ | 2025-08-31 | -- | -- | 市场信息 | | 108.27㎡ | 2025-05-22 | -- | -- | 市场信息 | 查看全部成交 ### 天秀花园澄秀园价格走势 ### 天秀花园澄秀园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 水利局小区 海淀·马连洼**57363** 元/㎡ * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园久盛居 海淀·马连洼**90783** 元/㎡ * #### 马连洼梅园 海淀·马连洼**65210** 元/㎡ ### 相关资讯 * 小区资讯北京天秀花园澄秀园怎么样?；北京天秀花园古月园房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下天秀花园古月园房价、房源、户型、环境、交通等周边配套的相关问题！</x:v>
+        <x:v>小区2000年建成，2栋共120户，板楼结构，物业公司为北京万科物业，物业费0.8元/㎡·月；；在售户型主打96㎡左右三居；；装修多为精装修，房屋配置齐全；；未搜索到明确的隔音、户型、房龄、物业相关差评信息，仅提及楼龄19年（2026年时），房屋维护情况未明确反馈。</x:v>
       </x:c>
       <x:c r="L60" t="str">
-        <x:v>58同城北京小区租房频道为您提供天秀花园澄秀园租房信息，包括天秀花园澄秀园最新出租房源，一室，二室，三室，四室，四室以上租房房源，租金走势和天秀花园澄秀园小区周边租房信息等。；* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 天秀花园澄秀园 &gt;* 天秀花园澄秀园租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 天秀花园澄秀园 海淀 / 马连洼 / 天秀路 小区信息 建筑类别: 多层 总 户 数: 542 建筑年代: 2007年 绿 化 率: 33% 停 车 位:暂无数据 ### 天秀花园澄秀园租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 5683元/月 0.02% 天秀花园澄秀园 ### 天秀花园澄秀园出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 天秀花园澄秀园 精装小两居 南北通透 价格合适 随时看 * 2室1厅|65.19㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月 * * 马连洼天秀花园澄秀 电梯房 精装修 可月付 近地铁 * 3室1厅|11.4㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月 * * 天秀花园澄秀园 3室1厅2卫 * 3室1厅|15㎡ * 马连洼 * 独卫 独立阳台 邻地铁 精装修 南北通透 * 2300 元/月 * * 整租马连洼天秀花园澄秀园1室1厅 * 1室1厅|61.66㎡ * 马连洼 * 独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 天秀花园澄秀园 * 水利社区1号院 * 天秀花园久盛居 * 颐北家苑 * 水利社区二号院 * 圆明园西路甲1号院 * 梅园(海淀) * 百旺家苑 * 天秀花园古月园 * 梅园甲 * 裕隆新村 * 圆明园西路3号院 * 兰园小区 * 农大附中家属院 * 黑山扈路甲17号院 * 润千秋佳苑 * 天秀花园安和园 * 亿城西山华府禧园 * 荷塘月舍 * 农科社区(北区) * 西山庭院 * 亿城西山华府珑园 * 北京大学肖家河教职工家属院二区 * 百草园社区 * 北京大学肖家河教职工家属院三区 * 正黄旗西区 * 正黄旗东区 * 大有北里 * 竹园小区 * 丰泽盈和 首页北京租房天秀花园澄秀园。；北京天秀花园古月园房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下天秀花园古月园房价、房源、户型、环境、交通等周边配套的相关问题！；### 天秀花园古月园交通状况如何？</x:v>
+        <x:v>交通：周边2km内有马连洼、农大南路等3个地铁站，25个公交站（如天秀花园西站等）；；配套：周边有中国农业大学附属中小学等教育资源，309医院等医疗资源，商超、餐饮等生活配套较完善，通勤及生活便利度较好。</x:v>
       </x:c>
       <x:c r="M60" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未搜索到明确的隔音、户型、房龄、物业相关差评信息，仅提及楼龄19年（2026年时），房屋维护情况未明确反馈。</x:v>
       </x:c>
       <x:c r="N60" t="str">
-        <x:v>价格线索： * 四室 * 四室以上 小区本月租金 5683元/月；㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月；㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月；独立阳台 邻地铁 精装修 南北通透 * 2300 元/月；独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月；2厅二手房 188.79㎡ 1500万 79454元/㎡；房屋质量/户型线索：* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 天秀花园澄秀园 &gt;* 天秀花园澄秀园租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 天秀花园澄秀园 海淀 / 马连洼 / 天秀路 小区信息 建筑类别: 多层 总 户 数: 542 建筑年代: 2007年 绿 化 率: 33% 停 车 位:暂无数据 ### 天秀花园澄秀园租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 5683元/月 0.02% 天秀花园澄秀园 ### 天秀花园澄秀园出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 天秀花园澄秀园 精装小两居 南北通透 价格合适 随时看 * 2室1厅|65.19㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月 * * 马连洼天秀花园澄秀 电梯房 精装修 可月付 近地铁 * 3室1厅|11.4㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月 * * 天秀花园澄秀园 3室1厅2卫 * 3室1厅|15㎡ * 马连洼 * 独卫 独立阳台 邻地铁 精装修 南北通透 * 2300 元/月 * * 整租马连洼天秀花园澄秀园1室1厅 * 1室1厅|61.66㎡ * 马连洼 * 独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 天秀花园澄秀园 * 水利社区1号院 * 天秀花园久盛居 * 颐北家苑 * 水利社区二号院 * 圆明园西路甲1号院 * 梅园(海淀) * 百旺家苑 * 天秀花园古月园 * 梅园甲 * 裕隆新村 * 圆明园西路3号院 * 兰园小区 * 农大附中家属院 * 黑山扈路甲17号院 * 润千秋佳苑 * 天秀花园安和园 * 亿城西山华府禧园 * 荷塘月舍 * 农科社区(北区) * 西山庭院 * 亿城西山华府珑园 * 北京大学肖家河教职工家属院二区 * 百草园社区 * 北京大学肖家河教职工家属院三区 * 正黄旗西区 * 正黄旗东区 * 大有北里 * 竹园小区 * 丰泽盈和 首页北京租房天秀花园澄秀园。；phototype=shijing) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) [](https://esf.fang.com/loupan/1010090280/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 * 户型 * 价格 * #### 马连洼·天秀花园澄秀园·2室·2厅 2室2厅 90.65㎡**660**万 * #### 2007年商品房,满五唯一商品房,产权清晰 2室1厅 62.54㎡**399**万 * #### 天秀花园澄秀园2室1厅西 1室1厅 65.19㎡**329**万 * #### 马连洼·天秀花园澄秀园·3室·1厅 3室1厅 89.12㎡**738**万 ### 天秀花园澄秀园成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 75.75㎡ | 2026-03-08 | -- | -- | 市场信息 | | 86.84㎡ | 2025-08-31 | -- | -- | 市场信息 | | 108.27㎡ | 2025-05-22 | -- | -- | 市场信息 | 查看全部成交 ### 天秀花园澄秀园价格走势 ### 天秀花园澄秀园房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 天秀花园澄秀园 海淀·马连洼**61481** 元/㎡ * #### 水利局小区 海淀·马连洼**57363** 元/㎡ * #### 颐北家苑 海淀·马连洼**59134** 元/㎡ * #### 天秀花园久盛居 海淀·马连洼**90783** 元/㎡ * #### 马连洼梅园 海淀·马连洼**65210** 元/㎡ ### 相关资讯 * 小区资讯北京天秀花园澄秀园怎么样?；北京天秀花园古月园房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下天秀花园古月园房价、房源、户型、环境、交通等周边配套的相关问题！；生活便利线索：58同城北京小区租房频道为您提供天秀花园澄秀园租房信息，包括天秀花园澄秀园最新出租房源，一室，二室，三室，四室，四室以上租房房源，租金走势和天秀花园澄秀园小区周边租房信息等。；* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 天秀花园澄秀园 &gt;* 天秀花园澄秀园租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 天秀花园澄秀园 海淀 / 马连洼 / 天秀路 小区信息 建筑类别: 多层 总 户 数: 542 建筑年代: 2007年 绿 化 率: 33% 停 车 位:暂无数据 ### 天秀花园澄秀园租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 5683元/月 0.02% 天秀花园澄秀园 ### 天秀花园澄秀园出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 天秀花园澄秀园 精装小两居 南北通透 价格合适 随时看 * 2室1厅|65.19㎡ * 马连洼 * 邻地铁 精装修 * 6400 元/月 * * 马连洼天秀花园澄秀 电梯房 精装修 可月付 近地铁 * 3室1厅|11.4㎡ * 马连洼 * 邻地铁 精装修 * 2147 元/月 * * 天秀花园澄秀园 3室1厅2卫 * 3室1厅|15㎡ * 马连洼 * 独卫 独立阳台 邻地铁 精装修 南北通透 * 2300 元/月 * * 整租马连洼天秀花园澄秀园1室1厅 * 1室1厅|61.66㎡ * 马连洼 * 独卫一居 邻地铁 配套齐全 精装修 * 6200 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 天秀花园澄秀园 * 水利社区1号院 * 天秀花园久盛居 * 颐北家苑 * 水利社区二号院 * 圆明园西路甲1号院 * 梅园(海淀) * 百旺家苑 * 天秀花园古月园 * 梅园甲 * 裕隆新村 * 圆明园西路3号院 * 兰园小区 * 农大附中家属院 * 黑山扈路甲17号院 * 润千秋佳苑 * 天秀花园安和园 * 亿城西山华府禧园 * 荷塘月舍 * 农科社区(北区) * 西山庭院 * 亿城西山华府珑园 * 北京大学肖家河教职工家属院二区 * 百草园社区 * 北京大学肖家河教职工家属院三区 * 正黄旗西区 * 正黄旗东区 * 大有北里 * 竹园小区 * 丰泽盈和 首页北京租房天秀花园澄秀园。；北京天秀花园古月园房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下天秀花园古月园房价、房源、户型、环境、交通等周边配套的相关问题！；### 天秀花园古月园交通状况如何？；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：整租房源2室2厅1卫面积约90㎡，租金在7600元/月；（2025年10月）、8200元/月；房屋质量/户型线索：小区2000年建成，2栋共120户，板楼结构，物业公司为北京万科物业，物业费0.8元/㎡·月；；在售户型主打96㎡左右三居；；装修多为精装修，房屋配置齐全；；未搜索到明确的隔音、户型、房龄、物业相关差评信息，仅提及楼龄19年（2026年时），房屋维护情况未明确反馈。；生活便利线索：交通：周边2km内有马连洼、农大南路等3个地铁站，25个公交站（如天秀花园西站等）；；配套：周边有中国农业大学附属中小学等教育资源，309医院等医疗资源，商超、餐饮等生活配套较完善，通勤及生活便利度较好。；风险线索：未搜索到明确的隔音、户型、房龄、物业相关差评信息，仅提及楼龄19年（2026年时），房屋维护情况未明确反馈。</x:v>
       </x:c>
       <x:c r="O60" t="str">
-        <x:v>1. 【天秀花园澄秀园，北京天秀花园澄秀园租房，最新出租房源，租金走势信息】- 北京58同城 https://m.58.com/bj/xq/600375/
-2. 【北京天秀花园澄秀园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010090280.htm
-3. 天秀花园古月园房价怎么样？ 北京天秀花园古月园房源|户型图|小区车位|交通地址详情分析 https://m.ke.com/news/bj/xiaoqu/1111027380063.html
-4. 天秀花园久盛居_百度百科 https://baike.baidu.com/item/%E5%A4%A9%E7%A7%80%E8%8A%B1%E5%9B%AD%E4%B9%85%E7%9B%9B%E5%B1%85/23075919
-5. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml</x:v>
+        <x:v>1. https://m.58.com/bj/zufang/84054859396826x.shtml
+2. http://m.anjuke.com/bj/rent/4139302612413446-3/
+3. https://esf.fang.com/loupan/1010677291/strategy.htm
+4. https://m.ke.com/news/bj/xiaoqu/1111027380065.html
+5. 【7图】久盛居天秀花园，农业大学，309医院，马连洼安河桥北地铁，天秀路 https://m.58.com/bj/zufang/84054859396826x.shtml
+6. 久盛居 天秀花园 农业大学 309医院家属楼 国防大学 http://m.anjuke.com/bj/rent/4139302612413446-3/?ad_type=j&amp;pagesource=12
+7. 2026北京天秀花园久盛居小区，配套指南，买房攻略 https://esf.fang.com/loupan/1010677291/strategy.htm
+8. 北京天秀花园久盛居房价怎么样？ 天秀花园久盛居房源|户型图|小区车位|交通地址详情分析！ https://m.ke.com/news/bj/xiaoqu/1111027380065.html</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -3196,41 +3362,44 @@
         <x:v>北京市海淀区黑龙潭路58号</x:v>
       </x:c>
       <x:c r="E61" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F61" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G61" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H61" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H61" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="I61" t="str">
-        <x:v>证据多为丰台、宋家庄等地的泛化房源信息，缺乏针对该公寓的有效描述，参考性极弱。</x:v>
+        <x:v>价格极具吸引力，但缺乏具体房源细节且存在信息混淆风险，证据充分性较弱。</x:v>
       </x:c>
       <x:c r="J61" t="str">
-        <x:v>交通便利周边配套齐采光好 5000 元/月；居青年公寓 交通便利周边配套齐全装全配 2050 元/月；5700 元/月；5㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月；可注册办公首次出租南北通透 5400 元/月；6500 元/月；|45㎡|朝南 丰台-科技园区-小满寓 2900 元/月；交通便利采光好首次出租 4800 元/月</x:v>
+        <x:v>相似区域黑龙潭路附近公寓月租约2200-3500元/月</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v># 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：青年公寓租房信息条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486536909_1.htm) 双安边上青年公寓正规精装修一居目前便宜长租位置好交通 整租|1室1厅|45㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；5700 元/月 [](http://www.fang.com/chuzu/3_486916186_1.htm) 宋家庄精装修公寓交通方便拎包入住 整租|1室1厅|25㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月 [](http://www.fang.com/chuzu/3_486912209_1.htm) 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校 整租|1室1厅|43㎡|朝北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；首选青年 整租|1室1厅|45㎡|朝南 丰台-科技园区-小满寓 2900 元/月 [](http://www.fang.com/chuzu/3_486905609_1.htm) 双安青年公寓正规精装修一居全齐南向有电梯看房子可以随 整租|1室1厅|45㎡|朝南北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；首选青年 整租|1室0厅|28㎡|朝南 丰台-科技园区-小满寓 2300 元/月 [](http://www.fang.com/chuzu/3_486949558_1.htm) 精美公寓环保材料精装修无服务费,房租包含网络、物业费 整租|2室1厅|68㎡|朝南北 海淀-西三旗-自隅青年公寓 交通便利采光好全装全配 6700 元/月 [](http://www.fang.com/chuzu/3_486895310_1.htm) 相寓 皂君庙·青年公寓·中楼层·1居室 整租|1室1厅|42㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。</x:v>
+        <x:v>未明确该公寓的隔音、户型、房龄、物业等具体质量信息，搜索结果中同类区域精装公寓隔音和配套较好；</x:v>
       </x:c>
       <x:c r="L61" t="str">
-        <x:v>首页&gt;北京服务式公寓&gt;三元桥 商业区 * 全部 * CBD * 王府井 * 建国门 * 朝阳门 * 东直门 * 三里屯 * 朝阳公园 * 燕莎 * 三元桥 * 望京丽都 * 亚运村 * 中关村 * 金融街 * 大兴丰台 行政区 * 全部 * 东城区 * 朝阳区 * 西城区 * 海淀区 * 丰台区 * 大兴区 * 昌平区 * 顺义区 * 默认排序 * 热门公寓 * 价格 * 服务式公寓地图 * 共找到 4 个项目房源 * 橡树公馆 ¥**14000** 起/月 朝阳区东三环霞光里66号远洋新干线D座 64-171 m² 开间-3 居室 * 远洋公馆服务公寓 ¥**18000** 起/月 霞光里66号远洋公馆(近三元桥) 80-170 m² 1-2 居室 * 霄云里8号服务公寓 ¥**12000** 起/月 北京市朝阳区霄云里8号 68-101 m² 开间-两居 居室 * 华远九都汇服务式公寓 ¥**18500** 起/月 小亮马桥西路6号院北京华远九都汇 68-210 m² 开间-3 居室 上一页)1下一页) ### 公寓推荐 北京嘉里公寓 * 公寓租房 * 城区租房 * 商圈租房 * 高端租房 * 合作项目 * 友情链接 北京公寓租房 北京城区租房 建国门租房朝阳门月租公寓东直门月租公寓三里屯工体短租公寓朝阳公园租房三元桥租房亮马桥租房北京协和医院东院区望京丽都酒仙桥租房海淀中关村租房金融街服务公寓大兴服务公寓 御金台国际公寓Serviced Apartment in Beijing誉订服务式公寓华商壹棠服务公寓财富中心千禧公寓 望悦国际社区东方豪庭公寓国贸公寓佳兆业铂域行政公寓北京嘉里公寓国贸世纪公寓财富中心千禧公寓中国大饭店公馆雅诗阁盛世博瑞服务公寓京广中心公寓紫檀万豪行政公寓汇贤豪庭公寓银都华悦公邸世桥国贸公寓国贸公寓东方豪庭公寓东方豪庭公寓东四78号精品公寓北京福庭酒店公寓北京瑞吉公寓北京三全公寓山水广场公寓金隅环贸国际公寓北京光耀公寓新金山酒店公寓来福士服务公寓东环广场公寓东湖别墅达美奥克伍德华庭公寓佰舍工体东迎坊公寓达美奥克伍德雅居服务公寓华熙国际公寓三全公寓北京凯宾斯基公寓首农东苑公寓光明公寓亮马河公寓缦合行政公寓北京橡树公馆远洋公馆服务公寓金悦豪庭公寓北京嘉里公寓丽都公寓汇贤豪庭公寓北京丽都公寓北京瑞吉公寓金隅环贸国际公寓北京东迎坊服务式公寓国贸世纪公寓北京嘉里公寓金融街行政公寓东方豪庭公寓京广中心公寓国贸公寓东方广场公寓 快速链接 北京服务式公寓酒店包月高端公寓 服务式公寓地图酒店包月地图高端公寓地图 首页常见问题公寓新闻关于我们联系我们 联系方式 邮箱：nestfinder@126.com 关注我们 * 官方微信公众号 * 销售微信号 © Copyright © 2026誉订北京服务式公寓网 版权所有 京ICP备2020043848号-1 * [](https://www.yudinggongyu.com/faq/) * [](https://www.yudinggongyu.com/map1/) * 010-6882.8588 * *。；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：青年公寓租房信息条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486536909_1.htm) 双安边上青年公寓正规精装修一居目前便宜长租位置好交通 整租|1室1厅|45㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；交通便利周边配套齐采光好 5000 元/月 [](http://www.fang.com/chuzu/3_486917250_1.htm) 张郭庄14号线精美公寓出租民水价格便宜 整租|1室1厅|31㎡|朝南 丰台-长辛店-中铁建悦居青年公寓 交通便利周边配套齐全装全配 2050 元/月 [](http://www.fang.com/chuzu/3_486895311_1.htm) 整租·皂君庙·青年公寓·1室·1厅 整租|1室1厅|41㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；5700 元/月 [](http://www.fang.com/chuzu/3_486916186_1.htm) 宋家庄精装修公寓交通方便拎包入住 整租|1室1厅|25㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月 [](http://www.fang.com/chuzu/3_486912209_1.htm) 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校 整租|1室1厅|43㎡|朝北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；6500 元/月 [](http://www.fang.com/chuzu/3_486946183_1.htm) 丰台区房山线大葆台地铁丰台科技园通勤?</x:v>
+        <x:v>未明确该公寓的隔音、户型、房龄、物业等具体质量信息，搜索结果中同类区域精装公寓隔音和配套较好；；未明确该公寓具体通勤/地铁/商超/医院情况，黑龙潭路西北旺片区周边配套较全，交通便利；</x:v>
       </x:c>
       <x:c r="M61" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；北京商报记者丨李晗 随着毕业季租房热的到来，关于租房乱象的投诉不断增多。；她通过小红书、抖音等平台搜索发现，针对安居客虚假房源、低价引流的投诉不在少数，相关帖文超过30条。；平台以“租客举证不足”为由简单驳回投诉，实质上是将自身对房源信息负有的主动核验法定义务转嫁给处于弱势的消费者。</x:v>
+        <x:v>搜索结果中未发现针对兆安公寓（目标地址）的差评信息，但存在同音字混淆（如兆丰家园等误匹配），需注意地址准确性。；搜索结果中未发现针对兆安公寓（目标地址）的差评信息，但存在同音字混淆（如兆丰家园等误匹配），需注意地址准确性</x:v>
       </x:c>
       <x:c r="N61" t="str">
-        <x:v>价格线索：交通便利周边配套齐采光好 5000 元/月；居青年公寓 交通便利周边配套齐全装全配 2050 元/月；5700 元/月；5㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月；可注册办公首次出租南北通透 5400 元/月；6500 元/月；|45㎡|朝南 丰台-科技园区-小满寓 2900 元/月；交通便利采光好首次出租 4800 元/月；房屋质量/户型线索：# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：青年公寓租房信息条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486536909_1.htm) 双安边上青年公寓正规精装修一居目前便宜长租位置好交通 整租|1室1厅|45㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；5700 元/月 [](http://www.fang.com/chuzu/3_486916186_1.htm) 宋家庄精装修公寓交通方便拎包入住 整租|1室1厅|25㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月 [](http://www.fang.com/chuzu/3_486912209_1.htm) 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校 整租|1室1厅|43㎡|朝北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；首选青年 整租|1室1厅|45㎡|朝南 丰台-科技园区-小满寓 2900 元/月 [](http://www.fang.com/chuzu/3_486905609_1.htm) 双安青年公寓正规精装修一居全齐南向有电梯看房子可以随 整租|1室1厅|45㎡|朝南北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；首选青年 整租|1室0厅|28㎡|朝南 丰台-科技园区-小满寓 2300 元/月 [](http://www.fang.com/chuzu/3_486949558_1.htm) 精美公寓环保材料精装修无服务费,房租包含网络、物业费 整租|2室1厅|68㎡|朝南北 海淀-西三旗-自隅青年公寓 交通便利采光好全装全配 6700 元/月 [](http://www.fang.com/chuzu/3_486895310_1.htm) 相寓 皂君庙·青年公寓·中楼层·1居室 整租|1室1厅|42㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；生活便利线索：首页&gt;北京服务式公寓&gt;三元桥 商业区 * 全部 * CBD * 王府井 * 建国门 * 朝阳门 * 东直门 * 三里屯 * 朝阳公园 * 燕莎 * 三元桥 * 望京丽都 * 亚运村 * 中关村 * 金融街 * 大兴丰台 行政区 * 全部 * 东城区 * 朝阳区 * 西城区 * 海淀区 * 丰台区 * 大兴区 * 昌平区 * 顺义区 * 默认排序 * 热门公寓 * 价格 * 服务式公寓地图 * 共找到 4 个项目房源 * 橡树公馆 ¥**14000** 起/月 朝阳区东三环霞光里66号远洋新干线D座 64-171 m² 开间-3 居室 * 远洋公馆服务公寓 ¥**18000** 起/月 霞光里66号远洋公馆(近三元桥) 80-170 m² 1-2 居室 * 霄云里8号服务公寓 ¥**12000** 起/月 北京市朝阳区霄云里8号 68-101 m² 开间-两居 居室 * 华远九都汇服务式公寓 ¥**18500** 起/月 小亮马桥西路6号院北京华远九都汇 68-210 m² 开间-3 居室 上一页)1下一页) ### 公寓推荐 北京嘉里公寓 * 公寓租房 * 城区租房 * 商圈租房 * 高端租房 * 合作项目 * 友情链接 北京公寓租房 北京城区租房 建国门租房朝阳门月租公寓东直门月租公寓三里屯工体短租公寓朝阳公园租房三元桥租房亮马桥租房北京协和医院东院区望京丽都酒仙桥租房海淀中关村租房金融街服务公寓大兴服务公寓 御金台国际公寓Serviced Apartment in Beijing誉订服务式公寓华商壹棠服务公寓财富中心千禧公寓 望悦国际社区东方豪庭公寓国贸公寓佳兆业铂域行政公寓北京嘉里公寓国贸世纪公寓财富中心千禧公寓中国大饭店公馆雅诗阁盛世博瑞服务公寓京广中心公寓紫檀万豪行政公寓汇贤豪庭公寓银都华悦公邸世桥国贸公寓国贸公寓东方豪庭公寓东方豪庭公寓东四78号精品公寓北京福庭酒店公寓北京瑞吉公寓北京三全公寓山水广场公寓金隅环贸国际公寓北京光耀公寓新金山酒店公寓来福士服务公寓东环广场公寓东湖别墅达美奥克伍德华庭公寓佰舍工体东迎坊公寓达美奥克伍德雅居服务公寓华熙国际公寓三全公寓北京凯宾斯基公寓首农东苑公寓光明公寓亮马河公寓缦合行政公寓北京橡树公馆远洋公馆服务公寓金悦豪庭公寓北京嘉里公寓丽都公寓汇贤豪庭公寓北京丽都公寓北京瑞吉公寓金隅环贸国际公寓北京东迎坊服务式公寓国贸世纪公寓北京嘉里公寓金融街行政公寓东方豪庭公寓京广中心公寓国贸公寓东方广场公寓 快速链接 北京服务式公寓酒店包月高端公寓 服务式公寓地图酒店包月地图高端公寓地图 首页常见问题公寓新闻关于我们联系我们 联系方式 邮箱：nestfinder@126.com 关注我们 * 官方微信公众号 * 销售微信号 © Copyright © 2026誉订北京服务式公寓网 版权所有 京ICP备2020043848号-1 * [](https://www.yudinggongyu.com/faq/) * [](https://www.yudinggongyu.com/map1/) * 010-6882.8588 * *。；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：青年公寓租房信息条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486536909_1.htm) 双安边上青年公寓正规精装修一居目前便宜长租位置好交通 整租|1室1厅|45㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；交通便利周边配套齐采光好 5000 元/月 [](http://www.fang.com/chuzu/3_486917250_1.htm) 张郭庄14号线精美公寓出租民水价格便宜 整租|1室1厅|31㎡|朝南 丰台-长辛店-中铁建悦居青年公寓 交通便利周边配套齐全装全配 2050 元/月 [](http://www.fang.com/chuzu/3_486895311_1.htm) 整租·皂君庙·青年公寓·1室·1厅 整租|1室1厅|41㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；5700 元/月 [](http://www.fang.com/chuzu/3_486916186_1.htm) 宋家庄精装修公寓交通方便拎包入住 整租|1室1厅|25㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月 [](http://www.fang.com/chuzu/3_486912209_1.htm) 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校 整租|1室1厅|43㎡|朝北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；6500 元/月 [](http://www.fang.com/chuzu/3_486946183_1.htm) 丰台区房山线大葆台地铁丰台科技园通勤?；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；北京商报记者丨李晗 随着毕业季租房热的到来，关于租房乱象的投诉不断增多。；她通过小红书、抖音等平台搜索发现，针对安居客虚假房源、低价引流的投诉不在少数，相关帖文超过30条。；平台以“租客举证不足”为由简单驳回投诉，实质上是将自身对房源信息负有的主动核验法定义务转嫁给处于弱势的消费者。</x:v>
+        <x:v>价格线索：相似区域黑龙潭路附近公寓月租约2200-3500元/月；房屋质量/户型线索：未明确该公寓的隔音、户型、房龄、物业等具体质量信息，搜索结果中同类区域精装公寓隔音和配套较好；；生活便利线索：未明确该公寓的隔音、户型、房龄、物业等具体质量信息，搜索结果中同类区域精装公寓隔音和配套较好；；未明确该公寓具体通勤/地铁/商超/医院情况，黑龙潭路西北旺片区周边配套较全，交通便利；；风险线索：搜索结果中未发现针对兆安公寓（目标地址）的差评信息，但存在同音字混淆（如兆丰家园等误匹配），需注意地址准确性。；搜索结果中未发现针对兆安公寓（目标地址）的差评信息，但存在同音字混淆（如兆丰家园等误匹配），需注意地址准确性</x:v>
       </x:c>
       <x:c r="O61" t="str">
-        <x:v>1. 三元桥服务公寓租房价格_北京三元桥酒店公寓出租-北京誉订服务公寓网 https://www.yudinggongyu.com/syq/
-2. 【北京租房网_北京租房信息|房屋出租】- 房天下 http://www.fang.com/houses/zf_261936bj/
-3. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-4. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-5. 挂牌1800元，实看2500元！知名租房平台被指虚假房源、低价引流… - 21经济网 https://www.21jingji.com/article/20260416/herald/7b75ed9a45d5071f762ce7fb1d122493.html</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4595496292623360-3/
+2. http://m.anjuke.com/bj/rent/4603988924849159-3/
+3. http://m.fang.com/zf/bj/3_484952386.html
+4. 物业整租 精装公寓 0中介 押一付一 近地铁 隔音好 采光好 http://m.anjuke.com/bj/rent/4595496292623360-3/
+5. 温泉 带客厅 带卫生间 环保园 西北旺 航材院 黑山扈 http://m.anjuke.com/bj/rent/4603988924849159-3/
+6. 整租小西天天兆家园2室2厅 http://m.anjuke.com/bj/rent/4590250557793287-3/
+7. 整租!!近北安河地铁 免费停车 家电齐全 可养猫 http://m.anjuke.com/bj/rent/4272893326449667-3/
+8. 交通便（近地铁公交），配套全（商超学校），环境好（高绿化率） http://m.fang.com/zf/bj/3_484952386.html</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -3247,41 +3416,44 @@
         <x:v>北京市海淀区黑龙潭路58号</x:v>
       </x:c>
       <x:c r="E62" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F62" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G62" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H62" t="n">
-        <x:v>3.2</x:v>
+        <x:v>5.8</x:v>
       </x:c>
       <x:c r="I62" t="str">
-        <x:v>租金极高且多为豪宅大户型，距离网易大厦较远，不符合常规租房通勤需求。</x:v>
+        <x:v>租金参考价偏高且具体质量信息缺失，虽临近地铁但需警惕同名房源误导。</x:v>
       </x:c>
       <x:c r="J62" t="str">
-        <x:v>55000 元/月；12000 元/月；65000 元/月；58000 元/月；180000 元/月；138000 元/月；75000 元/月；80000 元/月</x:v>
+        <x:v>泉湾公寓的月租信息，同区域类似项目租金约14300元/月</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v># 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；58000 元/月 [](https://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；30000 元/月 [](https://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；22000 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。</x:v>
+        <x:v>无对应公寓的质量相关（隔音、户型、房龄、装修、物业）明确口碑信息，搜索结果中类似住宅有隔音处理、次新小区等描述但非目标项目；</x:v>
       </x:c>
       <x:c r="L62" t="str">
-        <x:v>) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；交通便利南北通透 18000 元/月 [](https://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；采光好周边配套齐 21800 元/月 [](https://www.fang.com/chuzu/3_486903096_1.htm) 清华大学双清苑 附小陪读 全新精装南北三居室 首次出 整租|3室2厅|122㎡|朝南北 海淀-学院路-双清苑 距昌平线学知园站约1157米。；交通便利周边配套齐采光好 20000 元/月 [](https://www.fang.com/chuzu/3_486864130_1.htm) 20套起看 万柳书院万城华府 2居南北通透 有车位有 整租|2室2厅|116㎡|朝南北 海淀-万柳-万城华府龙园 距10号线火器营站约436米。；交通便利周边配套齐首次出租 3000 元/月 [](https://www.fang.com/chuzu/3_481166418_1.htm) 西直门凯德茂。</x:v>
+        <x:v>周边有公交站（328路、584路等），临近地铁16号线西北旺站，周边有商圈配套，通勤和基础交通便利，但商超、医院等细节未提及；</x:v>
       </x:c>
       <x:c r="M62" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>搜索结果中存在同名误命中情况（如珠海恒大海泉湾、普陀区香泉苑、石景山玉泉西里公寓），需注意区分，无明确目标公寓的差评风险信息。；搜索结果中存在同名误命中情况（如珠海恒大海泉湾、普陀区香泉苑、石景山玉泉西里公寓），需注意区分，无明确目标公寓的差评风险信息</x:v>
       </x:c>
       <x:c r="N62" t="str">
-        <x:v>价格线索：55000 元/月；12000 元/月；65000 元/月；58000 元/月；180000 元/月；138000 元/月；75000 元/月；80000 元/月；房屋质量/户型线索：# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；58000 元/月 [](https://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；30000 元/月 [](https://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；22000 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。；生活便利线索：) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区租房子条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_485564954_1.htm) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 距10号线火器营站约421米。；交通便利南北通透 18000 元/月 [](https://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；采光好周边配套齐 21800 元/月 [](https://www.fang.com/chuzu/3_486903096_1.htm) 清华大学双清苑 附小陪读 全新精装南北三居室 首次出 整租|3室2厅|122㎡|朝南北 海淀-学院路-双清苑 距昌平线学知园站约1157米。；交通便利周边配套齐采光好 20000 元/月 [](https://www.fang.com/chuzu/3_486864130_1.htm) 20套起看 万柳书院万城华府 2居南北通透 有车位有 整租|2室2厅|116㎡|朝南北 海淀-万柳-万城华府龙园 距10号线火器营站约436米。；交通便利周边配套齐首次出租 3000 元/月 [](https://www.fang.com/chuzu/3_481166418_1.htm) 西直门凯德茂。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：泉湾公寓的月租信息，同区域类似项目租金约14300元/月；房屋质量/户型线索：无对应公寓的质量相关（隔音、户型、房龄、装修、物业）明确口碑信息，搜索结果中类似住宅有隔音处理、次新小区等描述但非目标项目；；生活便利线索：周边有公交站（328路、584路等），临近地铁16号线西北旺站，周边有商圈配套，通勤和基础交通便利，但商超、医院等细节未提及；；风险线索：搜索结果中存在同名误命中情况（如珠海恒大海泉湾、普陀区香泉苑、石景山玉泉西里公寓），需注意区分，无明确目标公寓的差评风险信息。；搜索结果中存在同名误命中情况（如珠海恒大海泉湾、普陀区香泉苑、石景山玉泉西里公寓），需注意区分，无明确目标公寓的差评风险信息</x:v>
       </x:c>
       <x:c r="O62" t="str">
-        <x:v>1. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_253028bj/
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-4. 北京公寓出租_北京精装公寓出租信息-北京链家找房 https://m.lianjia.com/chuzu/bj/apartment/haidianbeibuxinqu1/rmp5amp5amp0/
-5.  https://raw.githubusercontent.com/Airead/excise/c70b572c7e72f8529d50da660f4da80841f90520/airscrapy/demo/tutorial/rscript/raw_58_house.csv</x:v>
+        <x:v>1. https://ctrip.city8.com/bj/hotel/885kwi82123ib5798e
+2. https://m.fang.com/note/bj_2572476.html
+3. http://m.anjuke.com/bj/rent/3879177989467151-3/
+4. http://m.anjuke.com/zh/community/807457/jiedu/
+5. http://m.anjuke.com/bj/rent/4564011125218308-3/
+6. 香泉湾公寓旅行指南 https://ctrip.city8.com/bj/hotel/885kwi82123ib5798e
+7. 九重降噪系统+139㎡通透三居，海淀新盘藏着多少生活哲学？ https://m.fang.com/note/bj_2572476.html
+8. 【香泉苑租房信息 https://m.fang.com/houses/zf_406497_sh/p2/</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -3298,41 +3470,42 @@
         <x:v>圆明园西路水利局小区黑山沪羊场1号</x:v>
       </x:c>
       <x:c r="E63" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F63" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G63" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H63" t="n">
-        <x:v>6.8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="I63" t="str">
-        <x:v>位于学院路及清河周边，租金水平适中且配套成熟，是通勤网易的务实选择。</x:v>
+        <x:v>生活配套齐全且租金相对合理，属于通勤距离与居住品质较均衡的家属院。</x:v>
       </x:c>
       <x:c r="J63" t="str">
-        <x:v>【北京海淀区房屋出租5000-8000223元/月；# 【北京海淀区房屋出租5000-8000223元/月；* 关键字：海淀区房屋出租5000-8000223元/月；8500 元/月；-双泉嘉苑 周边配套齐独门独卫交通便利 8800 元/月；8900 元/月；交通便利周边配套齐全装全配 8930 元/月；9000 元/月</x:v>
+        <x:v>、3号院等）租房价格整租2居约6500-7800元/月；（精装修），单间或小面积房型约500元/月</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；# 【北京海淀区房屋出租5000-8000223元/月租房信息_房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀区房屋出租5000-8000223元/月条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://fang.com/chuzu/3_486508934_1.htm) 2室2厅世纪城三期烟树园 整租|2室2厅|84㎡|朝西南 海淀-世纪城-世纪城三期烟树园 距12号线蓝靛厂站约643米。</x:v>
+        <x:v>未搜索到海淀区圆明园西路水利局家属院（黑山沪羊场1号）的直接租房价格信息，周边同类区域（圆明园西路51号院、3号院等）租房价格整租2居约6500-7800元/月（精装修），单间或小面积房型约500元/月（非目标小区）；；未获取该小区直接隔音、房龄、物业等口碑细节，周边同类型家属院（圆明园西路51号院）描述为小区环境不错、有停车位、精装修，房屋南北通透采光好，物业信息未明确；</x:v>
       </x:c>
       <x:c r="L63" t="str">
-        <x:v>) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀区房屋出租5000-8000223元/月条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://fang.com/chuzu/3_486508934_1.htm) 2室2厅世纪城三期烟树园 整租|2室2厅|84㎡|朝西南 海淀-世纪城-世纪城三期烟树园 距12号线蓝靛厂站约643米。；8500 元/月 [](https://fang.com/chuzu/3_486480546_1.htm) 学院路 新辰里附近 双泉嘉苑 两居室出租 配套齐全 整租|2室1厅|85㎡|朝南 海淀-学院路-双泉嘉苑 周边配套齐独门独卫交通便利 8800 元/月 [](https://fang.com/chuzu/3_486696643_1.htm) 整租·甘家口·建设部大院·2室·1厅 整租|2室1厅|72㎡|朝南北 海淀-增光路-建设部大院 距16号线二里沟站约453米。；交通便利周边配套齐全装全配 8930 元/月 [](https://fang.com/chuzu/3_486941180_1.htm) 3室1厅人济山庄一期 整租|3室1厅|195㎡|朝东 海淀-紫竹桥-人济山庄 距16号线万寿寺站约780米。；9000 元/月 [](https://fang.com/chuzu/3_485198288_1.htm) 五道口 华联购物中心旁 暂安处 80多平三居出租 可 整租|3室1厅|81㎡|朝南北 海淀-五道口-暂安处 距13号线五道口站约455米。；周边配套齐独门独卫交通便利 9000 元/月 [](https://fang.com/chuzu/3_475596136_1.htm) 六道口,农大南门,清崋东路9号院,精装两居出租,随时 整租|2室1厅|105㎡|朝南北 海淀-学院路-清华东路27号院 距15号线六道口站约356米。</x:v>
-      </x:c>
-      <x:c r="M63" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
-      </x:c>
+        <x:v>未搜索到海淀区圆明园西路水利局家属院（黑山沪羊场1号）的直接租房价格信息，周边同类区域（圆明园西路51号院、3号院等）租房价格整租2居约6500-7800元/月（精装修），单间或小面积房型约500元/月（非目标小区）；；未获取该小区直接隔音、房龄、物业等口碑细节，周边同类型家属院（圆明园西路51号院）描述为小区环境不错、有停车位、精装修，房屋南北通透采光好，物业信息未明确；；未获取该小区直接通勤地铁信息，周边圆明园西路51号院步行到16号线农大南路约1181米、4号线西苑约1655米，周边有北京华联BHG Mall、龙湖星悦荟等商超，附近有北医三院（中央党校院区）等医疗资源，生活配套较全；</x:v>
+      </x:c>
+      <x:c r="M63" t="str"/>
       <x:c r="N63" t="str">
-        <x:v>价格线索：【北京海淀区房屋出租5000-8000223元/月；# 【北京海淀区房屋出租5000-8000223元/月；* 关键字：海淀区房屋出租5000-8000223元/月；8500 元/月；-双泉嘉苑 周边配套齐独门独卫交通便利 8800 元/月；8900 元/月；交通便利周边配套齐全装全配 8930 元/月；9000 元/月；房屋质量/户型线索：承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；# 【北京海淀区房屋出租5000-8000223元/月租房信息_房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀区房屋出租5000-8000223元/月条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://fang.com/chuzu/3_486508934_1.htm) 2室2厅世纪城三期烟树园 整租|2室2厅|84㎡|朝西南 海淀-世纪城-世纪城三期烟树园 距12号线蓝靛厂站约643米。；生活便利线索：) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀区房屋出租5000-8000223元/月条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://fang.com/chuzu/3_486508934_1.htm) 2室2厅世纪城三期烟树园 整租|2室2厅|84㎡|朝西南 海淀-世纪城-世纪城三期烟树园 距12号线蓝靛厂站约643米。；8500 元/月 [](https://fang.com/chuzu/3_486480546_1.htm) 学院路 新辰里附近 双泉嘉苑 两居室出租 配套齐全 整租|2室1厅|85㎡|朝南 海淀-学院路-双泉嘉苑 周边配套齐独门独卫交通便利 8800 元/月 [](https://fang.com/chuzu/3_486696643_1.htm) 整租·甘家口·建设部大院·2室·1厅 整租|2室1厅|72㎡|朝南北 海淀-增光路-建设部大院 距16号线二里沟站约453米。；交通便利周边配套齐全装全配 8930 元/月 [](https://fang.com/chuzu/3_486941180_1.htm) 3室1厅人济山庄一期 整租|3室1厅|195㎡|朝东 海淀-紫竹桥-人济山庄 距16号线万寿寺站约780米。；9000 元/月 [](https://fang.com/chuzu/3_485198288_1.htm) 五道口 华联购物中心旁 暂安处 80多平三居出租 可 整租|3室1厅|81㎡|朝南北 海淀-五道口-暂安处 距13号线五道口站约455米。；周边配套齐独门独卫交通便利 9000 元/月 [](https://fang.com/chuzu/3_475596136_1.htm) 六道口,农大南门,清崋东路9号院,精装两居出租,随时 整租|2室1厅|105㎡|朝南北 海淀-学院路-清华东路27号院 距15号线六道口站约356米。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：、3号院等）租房价格整租2居约6500-7800元/月；（精装修），单间或小面积房型约500元/月；房屋质量/户型线索：未搜索到海淀区圆明园西路水利局家属院（黑山沪羊场1号）的直接租房价格信息，周边同类区域（圆明园西路51号院、3号院等）租房价格整租2居约6500-7800元/月（精装修），单间或小面积房型约500元/月（非目标小区）；；未获取该小区直接隔音、房龄、物业等口碑细节，周边同类型家属院（圆明园西路51号院）描述为小区环境不错、有停车位、精装修，房屋南北通透采光好，物业信息未明确；；生活便利线索：未搜索到海淀区圆明园西路水利局家属院（黑山沪羊场1号）的直接租房价格信息，周边同类区域（圆明园西路51号院、3号院等）租房价格整租2居约6500-7800元/月（精装修），单间或小面积房型约500元/月（非目标小区）；；未获取该小区直接隔音、房龄、物业等口碑细节，周边同类型家属院（圆明园西路51号院）描述为小区环境不错、有停车位、精装修，房屋南北通透采光好，物业信息未明确；；未获取该小区直接通勤地铁信息，周边圆明园西路51号院步行到16号线农大南路约1181米、4号线西苑约1655米，周边有北京华联BHG Mall、龙湖星悦荟等商超，附近有北医三院（中央党校院区）等医疗资源，生活配套较全；</x:v>
       </x:c>
       <x:c r="O63" t="str">
-        <x:v>1.  https://www.bjdch.gov.cn/zwgk/jgdh/qzfzcbmdh/fgj/bzxzffp/202511/P020251117576266490220.pdf
-2. 2023年8月北京海淀区公租房价格一览表- 北京本地宝 http://bj.bendibao.com/zffw/2023821/351359.shtm
-3. 【北京海淀区房屋出租5000-8000223元/月租房信息_房屋出租】- 房天下 https://fang.com/houses/zf_252999bj/c25000-d28000223,4,-h34-i33/
-4. 海淀区2026年第一批公共租赁住房直接发放选房通知单配租及2026年 ... https://zyk.bjhd.gov.cn/jbdt/auto4522_51806/zdly/bzzf/fpfy/202605/t20260506_4814032.shtml
-5. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/</x:v>
+        <x:v>1. https://bj.zu.anjuke.com/fangyuan/4217360686361612
+2. http://m.anjuke.com/zixing/rent/4582611990883333-2/
+3. http://m.anjuke.com/bj/rent/4585437863877634-3/
+4. http://m.anjuke.com/hc/rent/4219388118555652-3/
+5. http://m.anjuke.com/bj/rent/4598359255753740-3/
+6. http://m.anjuke.com/jmjs/rent/4577129937972236-3/
+7. http://m.anjuke.com/bj/rent/4139451677433867-3/
+8. 西苑101圆明园 邮局家属院 精装2居 实房实图 和业主直签 https://bj.zu.anjuke.com/fangyuan/4217360686361612</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -3349,39 +3522,44 @@
         <x:v>北京市海淀区西北旺镇回民公墓</x:v>
       </x:c>
       <x:c r="E64" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F64" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G64" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H64" t="n">
-        <x:v>4</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="I64" t="str">
-        <x:v>房源信息杂乱且多指向丰台等远郊区域，证据指向性差，通勤不确定性极大。</x:v>
+        <x:v>价格极具优势但房屋质量与环境存疑，适合预算有限且对环境要求不高者。</x:v>
       </x:c>
       <x:c r="J64" t="str">
-        <x:v>交通便利周边配套齐采光好 5000 元/月；居青年公寓 交通便利周边配套齐全装全配 2050 元/月；5700 元/月；5㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月；可注册办公首次出租南北通透 5400 元/月；6500 元/月；|45㎡|朝南 丰台-科技园区-小满寓 2900 元/月；交通便利采光好首次出租 4800 元/月</x:v>
+        <x:v>区域西北旺镇周边公寓单间月租约1800-2650元/月；，整租约4800元/月</x:v>
       </x:c>
       <x:c r="K64" t="str">
-        <x:v># 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：青年公寓租房信息条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486536909_1.htm) 双安边上青年公寓正规精装修一居目前便宜长租位置好交通 整租|1室1厅|45㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；5700 元/月 [](https://www.fang.com/chuzu/3_486916186_1.htm) 宋家庄精装修公寓交通方便拎包入住 整租|1室1厅|25㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月 [](https://www.fang.com/chuzu/3_486912209_1.htm) 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校 整租|1室1厅|43㎡|朝北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；首选青年 整租|1室1厅|45㎡|朝南 丰台-科技园区-小满寓 2900 元/月 [](https://www.fang.com/chuzu/3_486905609_1.htm) 双安青年公寓正规精装修一居全齐南向有电梯看房子可以随 整租|1室1厅|45㎡|朝南北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；首选青年 整租|1室0厅|28㎡|朝南 丰台-科技园区-小满寓 2300 元/月 [](https://www.fang.com/chuzu/3_486949558_1.htm) 精美公寓环保材料精装修无服务费,房租包含网络、物业费 整租|2室1厅|68㎡|朝南北 海淀-西三旗-自隅青年公寓 交通便利采光好全装全配 6700 元/月 [](https://www.fang.com/chuzu/3_486895310_1.htm) 相寓 皂君庙·青年公寓·中楼层·1居室 整租|1室1厅|42㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。</x:v>
+        <x:v>未明确「向安公寓」具体质量参数，参考西北旺镇周边部分安置房/公寓存在隔音差、户型设计普通、物业维护一般等问题；；若为安置类型建筑，房龄可能较长，配套装修参差不齐；；若该公寓属安置类房产，可能存在产权交易、物业纠纷等潜在风险，需核实具体产权性质。；若该公寓属安置类房产，可能存在产权交易、物业纠纷等潜在风险，需核实具体产权性质</x:v>
       </x:c>
       <x:c r="L64" t="str">
-        <x:v>) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：青年公寓租房信息条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486536909_1.htm) 双安边上青年公寓正规精装修一居目前便宜长租位置好交通 整租|1室1厅|45㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；交通便利周边配套齐采光好 5000 元/月 [](https://www.fang.com/chuzu/3_486917250_1.htm) 张郭庄14号线精美公寓出租民水价格便宜 整租|1室1厅|31㎡|朝南 丰台-长辛店-中铁建悦居青年公寓 交通便利周边配套齐全装全配 2050 元/月 [](https://www.fang.com/chuzu/3_486895311_1.htm) 整租·皂君庙·青年公寓·1室·1厅 整租|1室1厅|41㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；5700 元/月 [](https://www.fang.com/chuzu/3_486916186_1.htm) 宋家庄精装修公寓交通方便拎包入住 整租|1室1厅|25㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月 [](https://www.fang.com/chuzu/3_486912209_1.htm) 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校 整租|1室1厅|43㎡|朝北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；6500 元/月 [](https://www.fang.com/chuzu/3_486946183_1.htm) 丰台区房山线大葆台地铁丰台科技园通勤?；交通便利采光好首次出租 4800 元/月 [](https://www.fang.com/chuzu/3_486931476_1.htm) 精美公寓一居室使用面积达到40平无服务费房租包含网络 整租|1室1厅|46㎡|朝南 海淀-西三旗-自隅青年公寓 交通便利独门独卫采光好 5700 元/月 [](https://www.fang.com/chuzu/3_486895267_1.htm) 相寓 皂君庙·青年公寓·低楼层·1居室 整租|1室1厅|42㎡|朝北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。</x:v>
-      </x:c>
-      <x:c r="M64" t="str"/>
+        <x:v>未找到「向安公寓」明确月租信息，同区域西北旺镇周边公寓单间月租约1800-2650元/月，整租约4800元/月左右；；未明确「向安公寓」具体质量参数，参考西北旺镇周边部分安置房/公寓存在隔音差、户型设计普通、物业维护一般等问题；；若为安置类型建筑，房龄可能较长，配套装修参差不齐；；未明确「向安公寓」周边通勤、商超等具体配套，西北旺镇整体配套较完善，临近地铁16号线及多个公交站点，周边万象汇等商超较多，但回民公墓区域可能周边商业密度偏低；</x:v>
+      </x:c>
+      <x:c r="M64" t="str">
+        <x:v>未明确「向安公寓」具体质量参数，参考西北旺镇周边部分安置房/公寓存在隔音差、户型设计普通、物业维护一般等问题；</x:v>
+      </x:c>
       <x:c r="N64" t="str">
-        <x:v>价格线索：交通便利周边配套齐采光好 5000 元/月；居青年公寓 交通便利周边配套齐全装全配 2050 元/月；5700 元/月；5㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月；可注册办公首次出租南北通透 5400 元/月；6500 元/月；|45㎡|朝南 丰台-科技园区-小满寓 2900 元/月；交通便利采光好首次出租 4800 元/月；房屋质量/户型线索：# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：青年公寓租房信息条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486536909_1.htm) 双安边上青年公寓正规精装修一居目前便宜长租位置好交通 整租|1室1厅|45㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；5700 元/月 [](https://www.fang.com/chuzu/3_486916186_1.htm) 宋家庄精装修公寓交通方便拎包入住 整租|1室1厅|25㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月 [](https://www.fang.com/chuzu/3_486912209_1.htm) 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校 整租|1室1厅|43㎡|朝北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；首选青年 整租|1室1厅|45㎡|朝南 丰台-科技园区-小满寓 2900 元/月 [](https://www.fang.com/chuzu/3_486905609_1.htm) 双安青年公寓正规精装修一居全齐南向有电梯看房子可以随 整租|1室1厅|45㎡|朝南北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；首选青年 整租|1室0厅|28㎡|朝南 丰台-科技园区-小满寓 2300 元/月 [](https://www.fang.com/chuzu/3_486949558_1.htm) 精美公寓环保材料精装修无服务费,房租包含网络、物业费 整租|2室1厅|68㎡|朝南北 海淀-西三旗-自隅青年公寓 交通便利采光好全装全配 6700 元/月 [](https://www.fang.com/chuzu/3_486895310_1.htm) 相寓 皂君庙·青年公寓·中楼层·1居室 整租|1室1厅|42㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；生活便利线索：) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：青年公寓租房信息条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486536909_1.htm) 双安边上青年公寓正规精装修一居目前便宜长租位置好交通 整租|1室1厅|45㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；交通便利周边配套齐采光好 5000 元/月 [](https://www.fang.com/chuzu/3_486917250_1.htm) 张郭庄14号线精美公寓出租民水价格便宜 整租|1室1厅|31㎡|朝南 丰台-长辛店-中铁建悦居青年公寓 交通便利周边配套齐全装全配 2050 元/月 [](https://www.fang.com/chuzu/3_486895311_1.htm) 整租·皂君庙·青年公寓·1室·1厅 整租|1室1厅|41㎡|朝南 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；5700 元/月 [](https://www.fang.com/chuzu/3_486916186_1.htm) 宋家庄精装修公寓交通方便拎包入住 整租|1室1厅|25㎡|朝西 丰台-宋家庄-右寓青年公寓 3380 元/月 [](https://www.fang.com/chuzu/3_486912209_1.htm) 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校 整租|1室1厅|43㎡|朝北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。；6500 元/月 [](https://www.fang.com/chuzu/3_486946183_1.htm) 丰台区房山线大葆台地铁丰台科技园通勤?；交通便利采光好首次出租 4800 元/月 [](https://www.fang.com/chuzu/3_486931476_1.htm) 精美公寓一居室使用面积达到40平无服务费房租包含网络 整租|1室1厅|46㎡|朝南 海淀-西三旗-自隅青年公寓 交通便利独门独卫采光好 5700 元/月 [](https://www.fang.com/chuzu/3_486895267_1.htm) 相寓 皂君庙·青年公寓·低楼层·1居室 整租|1室1厅|42㎡|朝北 海淀-皂君庙-双安青年公寓 距4号线大兴线人民大学站约485米。</x:v>
+        <x:v>价格线索：区域西北旺镇周边公寓单间月租约1800-2650元/月；，整租约4800元/月；房屋质量/户型线索：未明确「向安公寓」具体质量参数，参考西北旺镇周边部分安置房/公寓存在隔音差、户型设计普通、物业维护一般等问题；；若为安置类型建筑，房龄可能较长，配套装修参差不齐；；若该公寓属安置类房产，可能存在产权交易、物业纠纷等潜在风险，需核实具体产权性质。；若该公寓属安置类房产，可能存在产权交易、物业纠纷等潜在风险，需核实具体产权性质；生活便利线索：未找到「向安公寓」明确月租信息，同区域西北旺镇周边公寓单间月租约1800-2650元/月，整租约4800元/月左右；；未明确「向安公寓」具体质量参数，参考西北旺镇周边部分安置房/公寓存在隔音差、户型设计普通、物业维护一般等问题；；若为安置类型建筑，房龄可能较长，配套装修参差不齐；；未明确「向安公寓」周边通勤、商超等具体配套，西北旺镇整体配套较完善，临近地铁16号线及多个公交站点，周边万象汇等商超较多，但回民公墓区域可能周边商业密度偏低；；风险线索：未明确「向安公寓」具体质量参数，参考西北旺镇周边部分安置房/公寓存在隔音差、户型设计普通、物业维护一般等问题；</x:v>
       </x:c>
       <x:c r="O64" t="str">
-        <x:v>1. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_261936bj/
-2. 海淀组团内配租922套青年公寓 https://open.beijing.gov.cn/html//haidian/gzdt/2025/6/1750038168814.html
-3. 北京海淀区青年公寓地址在哪里?项目介绍- 北京本地宝 http://bj.bendibao.com/zffw/202566/373174.shtm
-4. 选定922套高品质房源 北京海淀区启动青年公寓试点工作 https://www.stdaily.com/web/gdxw/2025-06/06/content_351160.html
-5. 海淀推近千套“青年公寓” 头两年租金打六折！-36氪 https://m.36kr.com/p/3322984450484737</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4543142442605569-3/
+2. https://www.163.com/dy/article/K9TKC2FR05239VSD.html
+3. http://m.anjuke.com/bj/rent/4254100078341124-3/
+4. https://www.douban.com/group/topic/486861053/?_spm_id=MTM0MzU1MzMx
+5. https://m.anjuke.com/bj/rent/4198181384216577/
+6. 西北旺商圈旁整租公寓，月租1800元，采光好配套齐全拎包住 http://m.anjuke.com/bj/rent/4543142442605569-3/
+7. 安置房这么便宜，为啥很多人不愿意买？住进去才知道，有多坑！ https://www.163.com/dy/article/K9TKC2FR05239VSD.html
+8. 西北旺 全朝南2居 近万象汇 16号线 马连洼 上地 西六 http://m.anjuke.com/bj/rent/4254100078341124-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -3398,41 +3576,42 @@
         <x:v>北京市海淀区黑龙潭路兆安公寓东侧约60米</x:v>
       </x:c>
       <x:c r="E65" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F65" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G65" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H65" t="n">
-        <x:v>5.2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I65" t="str">
-        <x:v>租金线索较清晰且位置尚可，但证据多为泛化列表，缺乏具体房源质量描述。</x:v>
+        <x:v>租金适中且周边生活设施尚可，但目前轨道交通不便，房屋质量信息缺失。</x:v>
       </x:c>
       <x:c r="J65" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
+        <x:v>，周边黑龙潭路附近普通住宅一居室月租大概4500元/月；左右，部分分散式公寓低至1350元/月</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；58同城北京租房网，为您提供北京海淀租房信息，包括海淀房屋出租信息、海淀合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。</x:v>
+        <x:v>暂未搜索到该小区明确的房龄、隔音、物业等房屋质量相关口碑信息，仅知道部分周边黑龙潭路附近房源为精装修；</x:v>
       </x:c>
       <x:c r="L65" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。</x:v>
-      </x:c>
-      <x:c r="M65" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
-      </x:c>
+        <x:v>暂无黑龙潭58号院（海淀区）官方明确的平均月租数据，周边黑龙潭路附近普通住宅一居室月租大概4500元/月左右，部分分散式公寓低至1350元/月（非对应小区，可能混淆）；；暂未搜索到该小区明确的房龄、隔音、物业等房屋质量相关口碑信息，仅知道部分周边黑龙潭路附近房源为精装修；；交通方面，黑龙潭路有651、633、330等公交线路，地铁M16号线在建；；生活配套上，周边有多个超市（惠购生鲜超市、华联超市），公园（画眉山滨水公园等），园区商业待建中；</x:v>
+      </x:c>
+      <x:c r="M65" t="str"/>
       <x:c r="N65" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；* 用户60709： 附近小区出租的房子都是业主负担物业费，供暖费，其它使用产生的费用是租户自己负担。；58同城北京租房网，为您提供北京海淀租房信息，包括海淀房屋出租信息、海淀合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。；生活便利线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：，周边黑龙潭路附近普通住宅一居室月租大概4500元/月；左右，部分分散式公寓低至1350元/月；房屋质量/户型线索：暂未搜索到该小区明确的房龄、隔音、物业等房屋质量相关口碑信息，仅知道部分周边黑龙潭路附近房源为精装修；；生活便利线索：暂无黑龙潭58号院（海淀区）官方明确的平均月租数据，周边黑龙潭路附近普通住宅一居室月租大概4500元/月左右，部分分散式公寓低至1350元/月（非对应小区，可能混淆）；；暂未搜索到该小区明确的房龄、隔音、物业等房屋质量相关口碑信息，仅知道部分周边黑龙潭路附近房源为精装修；；交通方面，黑龙潭路有651、633、330等公交线路，地铁M16号线在建；；生活配套上，周边有多个超市（惠购生鲜超市、华联超市），公园（画眉山滨水公园等），园区商业待建中；</x:v>
       </x:c>
       <x:c r="O65" t="str">
-        <x:v>1. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-2. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_254312bj/
-3. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/amp6amp4ama0/
-4. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml
-5. 【海淀房屋出租租赁_海淀租房网】-北京麦田房产 https://bj.maitian.cn/zfall/R6/P5/PG5</x:v>
+        <x:v>1. https://map.360.cn/site/detail/b9aed6bd385a4ead
+2. http://m.anjuke.com/lj/rent/4503310545480705-3/
+3. https://m.58.com/bj/zufang/82738400327515x.shtml
+4. http://m.anjuke.com/bj/rent/4518811691901961-3/
+5. https://m.58.com/bj/zufang/83893858504925x.shtml
+6. https://m.58.com/lj/zufang/4126624730737667x.shtml
+7. 黑龙潭路58号院 https://map.360.cn/site/detail/b9aed6bd385a4ead
+8. 黑龙潭 电梯公寓 一室一厅 http://m.anjuke.com/lj/rent/4503310545480705-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -3449,41 +3628,42 @@
         <x:v>北京市海淀区西北旺地区邓庄南路13号</x:v>
       </x:c>
       <x:c r="E66" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F66" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G66" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H66" t="n">
-        <x:v>8.2</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I66" t="str">
-        <x:v>距离软件园极近，一居室约5300元，2011年建成且配套成熟，是网易员工首选。</x:v>
+        <x:v>租金性价比高，房龄较新且隔音良好，虽距地铁有距离但生活配套基本能满足。</x:v>
       </x:c>
       <x:c r="J66" t="str">
-        <x:v>唐家岭新城(东区). 1室1厅 整租. 5300元/月；2室1厅二手房 78.49㎡ 308万 39241元/㎡；2室2厅二手房 83.82㎡ 357万 42592元/㎡；1室0厅二手房 46.07㎡ 240万 52095元/㎡；可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；95000 元/月；115000 元/月</x:v>
+        <x:v>开间约2300元/月；（合租，20㎡）、小两居约5300元/月；（整租，55㎡）、三居室约6300元/月；（整租，78㎡），合租单间约2800元/月</x:v>
       </x:c>
       <x:c r="K66" t="str">
-        <x:v>免押金月付）西北旺永丰南地铁万象汇唐家岭中关村软件园一居室. 海淀- 西北旺 唐家岭新城(东区). 1室1厅 整租. 5300元/月. 非常棒的户型，适合一家人居住，.。；北京唐家岭新城房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下唐家岭新城房价、房源、户型、环境、交通等周边配套的相关问题！；### 唐家岭新城小区简介 唐家岭新城由未知于2011年建成建成；；小区物业公司为北京东居物业管理有限公司，物业费用2.3至2.38元/平米/月。</x:v>
+        <x:v>房龄约2012-2013年，属于回迁房未下发房本；；户型涵盖46㎡开间、55-83㎡一/两居、105-126㎡三居，电梯高层板楼；；装修以精装修为主；；隔音效果较好；；物业为唐家岭本村物业，物业费1.8-2.38元/月/㎡，服务基本随叫随到；</x:v>
       </x:c>
       <x:c r="L66" t="str">
-        <x:v>免押金月付）西北旺永丰南地铁万象汇唐家岭中关村软件园一居室. 海淀- 西北旺 唐家岭新城(东区). 1室1厅 整租. 5300元/月. 非常棒的户型，适合一家人居住，.。；北京唐家岭新城房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下唐家岭新城房价、房源、户型、环境、交通等周边配套的相关问题！；### 唐家岭新城交通状况如何？；快速直达专线203路 唐家岭新城附近地铁：371路;</x:v>
-      </x:c>
-      <x:c r="M66" t="str">
-        <x:v>35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 距10号线三元桥站约662米。</x:v>
-      </x:c>
+        <x:v>通勤：距西二旗地铁（13号线）约3000米，16号线永丰南站约1500米，周边有公交站（航天城南门、邓庄南路等）；；生活配套：往西500米有超市发，步行可达U悦生活广场、鹿鹿生鲜等商超，周边餐饮、休闲设施较多；；医疗：就近有306医院、解放军总医院京北医疗区等；；商超配套有部分待招商情况；；小区部分大型商超尚未完全开业，配套成熟度不足。</x:v>
+      </x:c>
+      <x:c r="M66" t="str"/>
       <x:c r="N66" t="str">
-        <x:v>价格线索：唐家岭新城(东区). 1室1厅 整租. 5300元/月；2室1厅二手房 78.49㎡ 308万 39241元/㎡；2室2厅二手房 83.82㎡ 357万 42592元/㎡；1室0厅二手房 46.07㎡ 240万 52095元/㎡；可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；95000 元/月；115000 元/月；房屋质量/户型线索：免押金月付）西北旺永丰南地铁万象汇唐家岭中关村软件园一居室. 海淀- 西北旺 唐家岭新城(东区). 1室1厅 整租. 5300元/月. 非常棒的户型，适合一家人居住，.。；北京唐家岭新城房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下唐家岭新城房价、房源、户型、环境、交通等周边配套的相关问题！；### 唐家岭新城小区简介 唐家岭新城由未知于2011年建成建成；；小区物业公司为北京东居物业管理有限公司，物业费用2.3至2.38元/平米/月。；生活便利线索：免押金月付）西北旺永丰南地铁万象汇唐家岭中关村软件园一居室. 海淀- 西北旺 唐家岭新城(东区). 1室1厅 整租. 5300元/月. 非常棒的户型，适合一家人居住，.。；北京唐家岭新城房源|户型图|小区车位|交通地址详情分析。；今天小编就和大家一起来详细了解一下唐家岭新城房价、房源、户型、环境、交通等周边配套的相关问题！；### 唐家岭新城交通状况如何？；快速直达专线203路 唐家岭新城附近地铁：371路;；风险线索：35500 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 距10号线三元桥站约662米。</x:v>
+        <x:v>价格线索：开间约2300元/月；（合租，20㎡）、小两居约5300元/月；（整租，55㎡）、三居室约6300元/月；（整租，78㎡），合租单间约2800元/月；房屋质量/户型线索：房龄约2012-2013年，属于回迁房未下发房本；；户型涵盖46㎡开间、55-83㎡一/两居、105-126㎡三居，电梯高层板楼；；装修以精装修为主；；隔音效果较好；；物业为唐家岭本村物业，物业费1.8-2.38元/月/㎡，服务基本随叫随到；；生活便利线索：通勤：距西二旗地铁（13号线）约3000米，16号线永丰南站约1500米，周边有公交站（航天城南门、邓庄南路等）；；生活配套：往西500米有超市发，步行可达U悦生活广场、鹿鹿生鲜等商超，周边餐饮、休闲设施较多；；医疗：就近有306医院、解放军总医院京北医疗区等；；商超配套有部分待招商情况；；小区部分大型商超尚未完全开业，配套成熟度不足。</x:v>
       </x:c>
       <x:c r="O66" t="str">
-        <x:v>1. 北京唐家岭新城(东区)租房子 http://m.anjuke.com/bj/community/952642/rent/
-2. 唐家岭新城房价怎么样？ 北京唐家岭新城房源|户型图|小区车位|交通地址详情分析 https://m.ke.com/news/bj/xiaoqu/1111027379885.html
-3. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://zu.fang.com/default.htm
-4. 上地租房_北京海淀上地租房信息|上地租房价格信息-58租房网 https://bj.zf.58.com/shangdi/
-5. 唐家岭新城(东区)房子适合一家三口住吗？_北京房价_聚汇数据 https://fangjia.gotohui.com/list/6899.html</x:v>
+        <x:v>1. http://m.anjuke.com/bj/community/952642/jiedu/
+2. http://m.anjuke.com/bj/rent/4582736847070214-3/
+3. http://m.anjuke.com/ch/rent/4602504389977094-3/
+4. http://m.anjuke.com/ch/rent/4596555089308682-3/
+5. http://m.anjuke.com/bj/rent/4499557210479621-3/
+6. 唐家岭新城(东区)优点、不足，唐家岭新城(东区)怎么样，唐家岭新城(东区)周边房产中介经纪人评价-北京安居客 http://m.anjuke.com/bj/community/952642/jiedu/
+7. 唐家岭新城(东区) 3室1厅1卫 阳光充足 http://m.anjuke.com/bj/rent/4582736847070214-3/
+8. 西北旺唐家岭新城东区小两居可做一居随时看房入住滴滴新橙海 http://m.anjuke.com/ch/rent/4602504389977094-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -3500,40 +3680,42 @@
         <x:v>北京市海淀区圆明园西路甲1号</x:v>
       </x:c>
       <x:c r="E67" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F67" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G67" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H67" t="n">
-        <x:v>6.5</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="I67" t="str">
-        <x:v>租金水平适中，但公开证据多为泛化的平台SEO信息，缺乏小区内部质量的深度描述。</x:v>
-      </x:c>
-      <x:c r="J67" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
-      </x:c>
+        <x:v>临近地铁16号线，合租价格极具优势，但房龄偏老且具体房源信息不够详尽。</x:v>
+      </x:c>
+      <x:c r="J67" t="str"/>
       <x:c r="K67" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010647555/photo/) [](https://esf.fang.com/loupan/1010647555/photo/) [](https://esf.fang.com/loupan/1010647555/photo/) [](https://esf.fang.com/loupan/1010647555/photo/) [](https://esf.fang.com/loupan/1010647555/photo/) [](https://esf.fang.com/loupan/1010647555/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **55710** 元/㎡ 小区均价仅供参考，不可作为交易等依据 贷款计算器 * 二手房源 0套 * 最近成交 0套 * 楼栋总数 1栋 * 房屋总数 30户 * 建筑类型 板楼 * 建筑年代 2000年建成 * 小区位置 北京市海淀区圆明园西路地图 * 物业公司 天津融创物业管理有限公司北京分公司 * 开发商 北京城建房地产开发有限公司、中国农业大学 ### 圆明园西路甲1号院房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 圆明园西路甲1号院 海淀·马连洼**55710** 元/㎡ * #### 圆明园西路1号院 海淀·马连洼**待定** * #### 水利局小区 海淀·马连洼**57363** 元/㎡ * #### 天秀花园久盛居 海淀·马连洼**90783** 元/㎡ * #### 天秀花园古月园 海淀·马连洼**73659** 元/㎡ ### 相关资讯 * 小区资讯北京圆明园西路甲1号院怎么样?；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？</x:v>
+        <x:v>整租3室1厅月租约7600-8100元，合租单间月租约1225-2400元，198-2000年建成，部分房源精装修，押一付一/押一付三可选；；1998-2000年建成，物业为天津融创物业北京分公司，物业费0.8元/㎡·月；；户型齐全（主打二居、三居）；；部分房源为精装修、集中供暖，家电配置较全；；未提及隔音相关差评；</x:v>
       </x:c>
       <x:c r="L67" t="str">
-        <x:v>圆明园西路甲1号院地址配套价格详情了解2022-07-11 * 小区资讯圆明园租房,圆明园西路甲1号院最新房源报告!；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>交通：16号线农大南路站步行约849-1116米，马连洼站（在建）约916米，周边26个公交站；；购物：小区配套有超市；；医疗：周边有卫生服务设施；；餐饮：周边生活配套完善；</x:v>
       </x:c>
       <x:c r="M67" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；**3. 北大科技园上地园区** **建成时间：** 2012年 **位置商圈：** 上地信息路，临近西二旗 **面积区间：** 独栋/半独栋 1500-5000平米 **物业类型：** 大学科技园，低密度研发楼群 **租金水平：** 5.0-5.8元/平米/天 **交通配套：** 地铁13号线上地站，上下班高峰期略拥堵，建议错峰。；**4. 骚子营1号文创园** **建成时间：** 2020年（改造完成） **位置商圈：** 海淀骚子营路 **面积区间：** 200-800平米（部分为独栋小楼） **物业类型：** 老旧厂房改造文创园 **租金水平：** 4.5-5.5元/平米/天 **交通配套：** 公交便利，自驾更方便，园区内停车免费。</x:v>
+        <x:v>未提及隔音相关差评；；未发现明确差评或风险，部分房源需咨询经纪人确认租期等细节。；未发现明确差评或风险，部分房源需咨询经纪人确认租期等细节</x:v>
       </x:c>
       <x:c r="N67" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010647555/photo/) [](https://esf.fang.com/loupan/1010647555/photo/) [](https://esf.fang.com/loupan/1010647555/photo/) [](https://esf.fang.com/loupan/1010647555/photo/) [](https://esf.fang.com/loupan/1010647555/photo/) [](https://esf.fang.com/loupan/1010647555/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 上一个下一个 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **55710** 元/㎡ 小区均价仅供参考，不可作为交易等依据 贷款计算器 * 二手房源 0套 * 最近成交 0套 * 楼栋总数 1栋 * 房屋总数 30户 * 建筑类型 板楼 * 建筑年代 2000年建成 * 小区位置 北京市海淀区圆明园西路地图 * 物业公司 天津融创物业管理有限公司北京分公司 * 开发商 北京城建房地产开发有限公司、中国农业大学 ### 圆明园西路甲1号院房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 圆明园西路甲1号院 海淀·马连洼**55710** 元/㎡ * #### 圆明园西路1号院 海淀·马连洼**待定** * #### 水利局小区 海淀·马连洼**57363** 元/㎡ * #### 天秀花园久盛居 海淀·马连洼**90783** 元/㎡ * #### 天秀花园古月园 海淀·马连洼**73659** 元/㎡ ### 相关资讯 * 小区资讯北京圆明园西路甲1号院怎么样?；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 问 租房的话用交物业费吗？；生活便利线索：圆明园西路甲1号院地址配套价格详情了解2022-07-11 * 小区资讯圆明园租房,圆明园西路甲1号院最新房源报告!；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；**3. 北大科技园上地园区** **建成时间：** 2012年 **位置商圈：** 上地信息路，临近西二旗 **面积区间：** 独栋/半独栋 1500-5000平米 **物业类型：** 大学科技园，低密度研发楼群 **租金水平：** 5.0-5.8元/平米/天 **交通配套：** 地铁13号线上地站，上下班高峰期略拥堵，建议错峰。；**4. 骚子营1号文创园** **建成时间：** 2020年（改造完成） **位置商圈：** 海淀骚子营路 **面积区间：** 200-800平米（部分为独栋小楼） **物业类型：** 老旧厂房改造文创园 **租金水平：** 4.5-5.5元/平米/天 **交通配套：** 公交便利，自驾更方便，园区内停车免费。</x:v>
+        <x:v>房屋质量/户型线索：整租3室1厅月租约7600-8100元，合租单间月租约1225-2400元，198-2000年建成，部分房源精装修，押一付一/押一付三可选；；1998-2000年建成，物业为天津融创物业北京分公司，物业费0.8元/㎡·月；；户型齐全（主打二居、三居）；；部分房源为精装修、集中供暖，家电配置较全；；未提及隔音相关差评；；生活便利线索：交通：16号线农大南路站步行约849-1116米，马连洼站（在建）约916米，周边26个公交站；；购物：小区配套有超市；；医疗：周边有卫生服务设施；；餐饮：周边生活配套完善；；风险线索：未提及隔音相关差评；；未发现明确差评或风险，部分房源需咨询经纪人确认租期等细节。；未发现明确差评或风险，部分房源需咨询经纪人确认租期等细节</x:v>
       </x:c>
       <x:c r="O67" t="str">
-        <x:v>1. 【北京圆明园西路甲1号院小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010647555.htm
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 「海淀圆明园西独栋办公楼怎么租？企房房西苑房源实拍租金揭秘/办公楼出租」- 写字楼租房网 https://bj-sydc.com/article.php?id=46255
-4. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml</x:v>
+        <x:v>1. https://i-hl.haoduofangs.com/zufang/bj-7595217293415268398.html
+2. https://m.fang.com/xiaoqu/strategy/bj/1010647555.html?position=xqcomparebox
+3. https://m.anjuke.com/bj/rent/1247728021-3/
+4. 合租·圆明园西路甲1号院 https://i-hl.haoduofangs.com/zufang/bj-7595217293415268398.html
+5. 2026北京圆明园西路甲1号院小区，配套指南，买房攻略-北京房天下 https://m.fang.com/xiaoqu/strategy/bj/1010647555.html?position=xqcomparebox
+6. 圆明园西路甲1号院 可整租!房屋出租，包网费取暖费，押一付一 https://m.anjuke.com/bj/rent/1247728021-3/
+7. 圆明园西路甲1号院 https://esf.fang.com/loupan/1010647555/housedetail.htm
+8. 2026北京圆明园西路甲1号院小区，配套指南，买房攻略 https://esf.fang.com/loupan/1010647555/strategy.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -3550,7 +3732,7 @@
         <x:v>北京市海淀区厢黄旗东路上地实验小学(树村分校)北侧约60米</x:v>
       </x:c>
       <x:c r="E68" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F68" t="n">
         <x:v>8</x:v>
@@ -3559,32 +3741,35 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H68" t="n">
-        <x:v>4</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="I68" t="str">
-        <x:v>证据混杂大量万柳豪宅及办公信息，租金极高且定位不准，不符合普通租房决策需求。</x:v>
+        <x:v>缺乏直接租金和质量数据，且距离地铁站较远，证据存在泛化风险，建议保守考虑。</x:v>
       </x:c>
       <x:c r="J68" t="str">
-        <x:v>80000 元/月；75000 元/月；90000 元/月；138000 元/月；180000 元/月；58000 元/月；55000 元/月；65000 元/月</x:v>
+        <x:v>号线农大南路附近同价位区域整租1室0厅约4500元/月</x:v>
       </x:c>
       <x:c r="K68" t="str">
-        <x:v># 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；90000 元/月 [](https://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；35500 元/月 [](https://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；22000 元/月 [](https://www.fang.com/chuzu/3_479279273_1.htm) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 [](https://www.fang.com/chuzu/3_478659487_1.htm) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。</x:v>
+        <x:v>暂无厢黄旗东路1号院直接租房价格信息，搜索到的周边16号线农大南路附近同价位区域整租1室0厅约4500元/月，精装修；；未找到厢黄旗东路1号院明确的房子质量（隔音、户型、房龄、装修、物业）口碑信息，仅周边同区域房源多为精装修普通住宅，房龄及物业情况未提及；</x:v>
       </x:c>
       <x:c r="L68" t="str">
-        <x:v>) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；交通便利南北通透 18000 元/月 [](https://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；22000 元/月 [](https://www.fang.com/chuzu/3_479279273_1.htm) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 [](https://www.fang.com/chuzu/3_478659487_1.htm) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。；采光好周边配套齐 21800 元/月 [](https://www.fang.com/chuzu/3_486864130_1.htm) 20套起看 万柳书院万城华府 2居南北通透 有车位有 整租|2室2厅|116㎡|朝南北 海淀-万柳-万城华府龙园 距10号线火器营站约436米。；交通便利周边配套齐采光好 20000 元/月 [](https://www.fang.com/chuzu/3_481166418_1.htm) 西直门凯德茂。</x:v>
+        <x:v>暂无厢黄旗东路1号院直接租房价格信息，搜索到的周边16号线农大南路附近同价位区域整租1室0厅约4500元/月，精装修；；未找到厢黄旗东路1号院明确的房子质量（隔音、户型、房龄、装修、物业）口碑信息，仅周边同区域房源多为精装修普通住宅，房龄及物业情况未提及；；厢黄旗东路1号院周边生活配套较便利，距离厢黄旗东路站公交站约154米，有623路、专28路等公交；；附近有南里超市、超市发（柳浪家园店）、世纪华联超市等商超，距北京市上地医院约680米，靠近厢黄旗公园、乡土树木园等休闲场所，但地铁16号线农大南路站约1910米，距离较远；</x:v>
       </x:c>
       <x:c r="M68" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>未搜索到厢黄旗东路1号院相关的租房风险、差评信息，部分搜索结果命中同名不同区域小区（如银川东路1号、郑州城东路1号院等），需注意区分地址为北京市海淀区厢黄旗东路的房源。；未搜索到厢黄旗东路1号院相关的租房风险、差评信息，部分搜索结果命中同名不同区域小区（如银川东路1号、郑州城东路1号院等），需注意区分地址为北京市海淀区厢黄旗东路的房源</x:v>
       </x:c>
       <x:c r="N68" t="str">
-        <x:v>价格线索：80000 元/月；75000 元/月；90000 元/月；138000 元/月；180000 元/月；58000 元/月；55000 元/月；65000 元/月；房屋质量/户型线索：# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；90000 元/月 [](https://www.fang.com/chuzu/3_486848522_1.htm) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 距10号线巴沟站约328米。；35500 元/月 [](https://www.fang.com/chuzu/3_486912512_1.htm) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 距10号线长春桥站约1007米。；22000 元/月 [](https://www.fang.com/chuzu/3_479279273_1.htm) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 [](https://www.fang.com/chuzu/3_478659487_1.htm) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。；生活便利线索：) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；交通便利南北通透 18000 元/月 [](https://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；22000 元/月 [](https://www.fang.com/chuzu/3_479279273_1.htm) 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长 整租|7室3厅|898㎡|朝东 海淀-西山-西山美庐 115000 元/月 [](https://www.fang.com/chuzu/3_478659487_1.htm) 四季青 西山美庐 独栋别墅 随时看房 配套齐全 整租|6室3厅|875㎡|朝南 海淀-西山-西山美庐 99900 元/月 [](https://www.fang.com/chuzu/3_484597082_1.htm) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 距10号线长春桥站约490米。；采光好周边配套齐 21800 元/月 [](https://www.fang.com/chuzu/3_486864130_1.htm) 20套起看 万柳书院万城华府 2居南北通透 有车位有 整租|2室2厅|116㎡|朝南北 海淀-万柳-万城华府龙园 距10号线火器营站约436米。；交通便利周边配套齐采光好 20000 元/月 [](https://www.fang.com/chuzu/3_481166418_1.htm) 西直门凯德茂。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：号线农大南路附近同价位区域整租1室0厅约4500元/月；房屋质量/户型线索：暂无厢黄旗东路1号院直接租房价格信息，搜索到的周边16号线农大南路附近同价位区域整租1室0厅约4500元/月，精装修；；未找到厢黄旗东路1号院明确的房子质量（隔音、户型、房龄、装修、物业）口碑信息，仅周边同区域房源多为精装修普通住宅，房龄及物业情况未提及；；生活便利线索：暂无厢黄旗东路1号院直接租房价格信息，搜索到的周边16号线农大南路附近同价位区域整租1室0厅约4500元/月，精装修；；未找到厢黄旗东路1号院明确的房子质量（隔音、户型、房龄、装修、物业）口碑信息，仅周边同区域房源多为精装修普通住宅，房龄及物业情况未提及；；厢黄旗东路1号院周边生活配套较便利，距离厢黄旗东路站公交站约154米，有623路、专28路等公交；；附近有南里超市、超市发（柳浪家园店）、世纪华联超市等商超，距北京市上地医院约680米，靠近厢黄旗公园、乡土树木园等休闲场所，但地铁16号线农大南路站约1910米，距离较远；；风险线索：未搜索到厢黄旗东路1号院相关的租房风险、差评信息，部分搜索结果命中同名不同区域小区（如银川东路1号、郑州城东路1号院等），需注意区分地址为北京市海淀区厢黄旗东路的房源。；未搜索到厢黄旗东路1号院相关的租房风险、差评信息，部分搜索结果命中同名不同区域小区（如银川东路1号、郑州城东路1号院等），需注意区分地址为北京市海淀区厢黄旗东路的房源</x:v>
       </x:c>
       <x:c r="O68" t="str">
-        <x:v>1. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_254312bj/
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 2026北京海淀区第一批公租房房源信息查询（附价格）- 北京本地宝 https://bj.bendibao.com/zffw/202658/382527.shtm
-4. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian/
-5. 北京海淀合租1居室房源出租, 3500 RMB/月, 近地鐵16号线, 溫馨小窩、乾淨治愈 - Wellcee唯心所寓 https://www.wellcee.com/tw/rent-apartment/1779423513593559</x:v>
+        <x:v>1. https://map.360.cn/site/detail/1deb1c5001ba8e49（360地图-厢黄旗东路1号院）
+2. http://m.anjuke.com/dongyang/rent/4571416233733130-3/（安居客-周边租房信息）
+3. 厢黄旗东路1号院 https://map.360.cn/site/detail/1deb1c5001ba8e49
+4. 整租|出行便捷 采光好 周边设施齐全 家电齐全 http://m.anjuke.com/dongyang/rent/4571416233733130-3/
+5. 银川东路1号真实测评｜青岛人绝对想不到的5分钟生活圈 http://m.fang.com/note/qd_2258203.html
+6. 城东路1号院租房价格_郑州城东路1号院房租价格走势_城东路1号院租金一个月是多少钱-安居客 https://zz.zu.anjuke.com/xiaoqu/831474/zujin/
+7. 我爱我家WAP https://m.5i5j.com/bj/ershoufang/housetags/503885649.html
+8. 厢黄旗 林科院 纯南向两居 采光好 实房实图 跟业主签约 http://m.anjuke.com/bj/rent/4337811603483663-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -3601,37 +3786,42 @@
         <x:v>北京市海淀区上地街道</x:v>
       </x:c>
       <x:c r="E69" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F69" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G69" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H69" t="n">
-        <x:v>2.5</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="I69" t="str">
-        <x:v>证据显示该地主要为写字楼办公空间而非住宅社区，无法作为居住用途进行推荐。</x:v>
+        <x:v>租金极低且无中介费，生活配套完善，适合预算有限的单身人群，但空间较小。</x:v>
       </x:c>
       <x:c r="J69" t="str">
-        <x:v>) # 上地国际科技创业园大厦 * 29374元/㎡；色 198.0㎡ 1.9元/㎡·天 **11000元/月；利 198.0㎡ 1.9元/㎡·天 **11000元/月；通便利 198.0㎡ 2元/㎡·天 **12000元/月；区 154.0㎡ 1.9元/㎡·天 **9000元/月；0-2000㎡2000㎡以上 价格 不限10000元/㎡；以下10000-20000元/㎡；20000-30000元/㎡</x:v>
+        <x:v>等房源）租房价格：整租1室1厅1500-2500元/月；，1室0厅1000-1500元/月</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v># 【上地国际科技创业园大厦,写字楼•办公楼出租•出售•租赁价格信息】-北京海淀上地•写字楼•-北京写字楼网-房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津重庆成都苏州武汉西安东莞昆明杭州济南无锡郑州南昌青岛石家庄南京大连长沙香港 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) # 上地国际科技创业园大厦 * 29374元/㎡ 在售均价 * 14套在售房源 * 4元/㎡·天 在租均价 * 14套在租房源 * 物业类别 -- * 建筑面积 160000.0㎡ * 总楼层数 -- * 竣工时间 2000-07-01 * 物业费用 6元/㎡·月 * 物业公司 创业物业管理公司 * 电梯数量 -- * 楼盘地址 海淀-上地 上地信息路2号 地图 推荐经纪人&gt; * ## 兰会华 打电话 * ## 石子玉 打电话 * ## 杨威 打电话 * ## 褚福潺 打电话 ### 本楼盘热门出租房源 面积 不限100㎡以下100-200㎡200-300㎡300-500㎡500-800㎡800-1000㎡1000-2000㎡2000㎡以上 价格 不限3元/㎡·天以下3-4元/㎡·天4-5元/㎡·天5-7元/㎡·天7-9元/㎡·天9-12元/㎡·天12-15元/㎡·天15-20元/㎡·天20-25元/㎡·天25元/㎡·天以上 房源 面积 单价 月租金 特色 198.0㎡ 1.9元/㎡·天 **11000元/月** 可注册 交通便利 中心商务区 154.36㎡ 2元/㎡·天 **2元/月** 免中介费 可注册 交通便利 198.0㎡ 1.9元/㎡·天 **11000元/月** 免中介费 可注册 交通便利 198.0㎡ 2元/㎡·天 **12000元/月** 可注册 交通便利 中心商务区 154.0㎡ 1.9元/㎡·天 **9000元/月** 可注册 交通便利 中心商务区 查看出租房源 &gt; ### 本楼盘热门出售房源 面积 不限100㎡以下100-200㎡200-300㎡300-500㎡500-800㎡800-1000㎡1000-2000㎡2000㎡以上 价格 不限10000元/㎡以下10000-20000元/㎡20000-30000元/㎡30000-50000元/㎡50000元/㎡以上 房源 面积 单价 总价 特色 195.0㎡ 16000元/㎡ **--** 可注册 交通便利 中心商务区 192.0㎡ 18000元/㎡ **--** 可注册 交通便利 中心商务区 350.0㎡ 18000元/㎡ **--** 可注册 交通便利 繁华商圈 155.0㎡ 17000元/㎡ **--** 可注册 交通便利 中心商务区 525.0㎡ 15000元/㎡ **--** 可注册 交通便利 中心商务区 查看出售房源 &gt; ### 房贷计算器 开始计算) ## 房贷计算器 选择基本情况，帮您快速计算房贷 估算总价：_万_ 首付成数： 1.5成) * 1.5成 * 2成 * 2.5成 * 3成 * 3.5成 * 4成 * 4.5成 * 5成 * 5.5成 * 6成 * 6.5成 * 7成 * 7.5成 * 8成 贷款类别： 商业贷款) * 商业贷款 * 公积金贷款 * 组合贷款 公积金：_万_ 商业贷：_万_ 贷款时间： 30年（360期）) * 1年（12期） * 2年（24期） * 3年（36期） * 4年（48期） * 5年（60期） * 6年（72期） * 7年（84期） * 8年（96期） * 9年（108期） * 10年（120期） * 11年（132期） * 12年（144期） * 13年（156期） * 14年（168期） * 15年（180期） * 16年（192期） * 17年（204期） * 18年（216期） * 19年（228期） * 20年（240期） * 25年（300期） * 30年（360期） 等额本息 等额本金 ## 您的账单 总价：万，均价待定 ## 月均还款 元 ## 首月还款 元 * 参考首付：_（1.5成）_ * 贷款金额：_（8.5成）_ * 支付利息：_（8.5成）_ 利率公积金2.6% 商业性3.05% 备注：以等额本息计算结果，数据仅供参考 相关信息 同商圈写字楼 周边写字楼出租 周边写字楼出售 上地国际科技创业园大厦楼盘首页上地国际科技创业园大厦楼盘详情上地国际科技创业园大厦楼盘相册上地国际科技创业园大厦出租房源上地国际科技创业园大厦出售房源上地国际科技创业园大厦楼盘问答上地国际科技创业园大厦楼盘点评 金隅嘉华大厦科实信息城金融科贸大厦盈创动力辉煌国际上地科技大厦弘源首著大厦上地四街一号院悦MOMA中关村软件园 安宁庄写字楼出租北京大学写字楼出租北太平庄写字楼出租厂洼写字楼出租定慧寺写字楼出租二里庄写字楼出租甘家口写字楼出租公主坟写字楼出租航天桥写字楼出租花园桥写字楼出租海淀其它写字楼出租蓟门桥写字楼出租军博写字楼出租六里桥写字楼出租马甸写字楼出租马连洼写字楼出租牡丹园写字楼出租清河写字楼出租上庄写字楼出租世纪城写字楼出租曙光写字楼出租双榆树写字楼出租四季青写字楼出租苏州桥写字楼出租田村写字楼出租万柳写字楼出租万泉河写字楼出租万寿路写字楼出租魏公村写字楼出租温泉镇写字楼出租五道口写字楼出租五棵松写字楼出租西北旺写字楼出租西二旗写字楼出租西三旗写字楼出租西山写字楼出租西直门外写字楼出租香山写字楼出租小西天写字楼出租学院路写字楼出租西直门写字楼出租颐和园写字楼出租永定路写字楼出租玉泉路写字楼出租圆明园写字楼出租皂君庙写字楼出租增光路写字楼出租知春路写字楼出租中关村写字楼出租紫竹桥写字楼出租 安宁庄写字楼出售北京大学写字楼出售北太平庄写字楼出售厂洼写字楼出售定慧寺写字楼出售二里庄写字楼出售甘家口写字楼出售公主坟写字楼出售航天桥写字楼出售花园桥写字楼出售海淀其它写字楼出售蓟门桥写字楼出售军博写字楼出售六里桥写字楼出售马甸写字楼出售马连洼写字楼出售牡丹园写字楼出售清河写字楼出售上庄写字楼出售世纪城写字楼出售曙光写字楼出售双榆树写字楼出售四季青写字楼出售苏州桥写字楼出售田村写字楼出售万柳写字楼出售万泉河写字楼出售万寿路写字楼出售魏公村写字楼出售温泉镇写字楼出售五道口写字楼出售五棵松写字楼出售西北旺写字楼出售西二旗写字楼出售西三旗写字楼出售西山写字楼出售西直门外写字楼出售香山写字楼出售小西天写字楼出售学院路写字楼出售西直门写字楼出售颐和园写字楼出售永定路写字楼出售玉泉路写字楼出售圆明园写字楼出售皂君庙写字楼出售增光路写字楼出售知春路写字楼出售中关村写字楼出售紫竹桥写字楼出售 **免责声明：**本站楼盘信息旨在为用户提供更多信息的无偿服务，信息以政府部门登记备案为准，请谨慎核查。；这里我也分享几个当时重点看的园区，都是企房房平台上的真实房源，覆盖了不同需求： **1. 企房房严选推荐（上地信息产业基地及周边）** .**位置商圈**：上地信息产业基地核心区 .**面积区间**：150-5000平米灵活分割 .**物业类型**：5A甲级写字楼 .**租金水平**：**6.8 - 8.5元/平米/天**（含物业） .**交通配套**：近地铁13号线/昌平线西二旗站，公交线路密集，园区班车多。；.**入驻亮点**：**企房房的重点合作楼盘**，楼宇品质高，大堂气派，物业服务口碑好。；**2. 中关村环保园-示范园R0** .**位置商圈**：北清路中关村环保园 .**面积区间**：整层2000平米起，可分租 .**物业类型**：独栋/半独栋研发楼 .**租金水平**：**4.5 - 6.0元/平米/天** .**交通配套**：依赖自驾或园区班车���未来有地铁规划。</x:v>
+        <x:v>上地科技园社区（关联朱房小区等房源）租房价格：整租1室1厅1500-2500元/月，1室0厅1000-1500元/月，精装修房源更高，押一付一/押一付三灵活支付，无中介房源多，服务费/中介费0元；；关联房源多为精装修，部分简单装修；；户型多为1室0厅或1室1厅，面积20-30平米；；房龄未明确提及，物业方面部分房源为物业自持，提供24h安保维修、入住保洁服务；；隔音、户型细节未明确，装修整体偏简洁适合单身/青年人群。</x:v>
       </x:c>
       <x:c r="L69" t="str">
-        <x:v>) # 上地国际科技创业园大厦 * 29374元/㎡ 在售均价 * 14套在售房源 * 4元/㎡·天 在租均价 * 14套在租房源 * 物业类别 -- * 建筑面积 160000.0㎡ * 总楼层数 -- * 竣工时间 2000-07-01 * 物业费用 6元/㎡·月 * 物业公司 创业物业管理公司 * 电梯数量 -- * 楼盘地址 海淀-上地 上地信息路2号 地图 推荐经纪人&gt; * ## 兰会华 打电话 * ## 石子玉 打电话 * ## 杨威 打电话 * ## 褚福潺 打电话 ### 本楼盘热门出租房源 面积 不限100㎡以下100-200㎡200-300㎡300-500㎡500-800㎡800-1000㎡1000-2000㎡2000㎡以上 价格 不限3元/㎡·天以下3-4元/㎡·天4-5元/㎡·天5-7元/㎡·天7-9元/㎡·天9-12元/㎡·天12-15元/㎡·天15-20元/㎡·天20-25元/㎡·天25元/㎡·天以上 房源 面积 单价 月租金 特色 198.0㎡ 1.9元/㎡·天 **11000元/月** 可注册 交通便利 中心商务区 154.36㎡ 2元/㎡·天 **2元/月** 免中介费 可注册 交通便利 198.0㎡ 1.9元/㎡·天 **11000元/月** 免中介费 可注册 交通便利 198.0㎡ 2元/㎡·天 **12000元/月** 可注册 交通便利 中心商务区 154.0㎡ 1.9元/㎡·天 **9000元/月** 可注册 交通便利 中心商务区 查看出租房源 &gt; ### 本楼盘热门出售房源 面积 不限100㎡以下100-200㎡200-300㎡300-500㎡500-800㎡800-1000㎡1000-2000㎡2000㎡以上 价格 不限10000元/㎡以下10000-20000元/㎡20000-30000元/㎡30000-50000元/㎡50000元/㎡以上 房源 面积 单价 总价 特色 195.0㎡ 16000元/㎡ **--** 可注册 交通便利 中心商务区 192.0㎡ 18000元/㎡ **--** 可注册 交通便利 中心商务区 350.0㎡ 18000元/㎡ **--** 可注册 交通便利 繁华商圈 155.0㎡ 17000元/㎡ **--** 可注册 交通便利 中心商务区 525.0㎡ 15000元/㎡ **--** 可注册 交通便利 中心商务区 查看出售房源 &gt; ### 房贷计算器 开始计算) ## 房贷计算器 选择基本情况，帮您快速计算房贷 估算总价：_万_ 首付成数： 1.5成) * 1.5成 * 2成 * 2.5成 * 3成 * 3.5成 * 4成 * 4.5成 * 5成 * 5.5成 * 6成 * 6.5成 * 7成 * 7.5成 * 8成 贷款类别： 商业贷款) * 商业贷款 * 公积金贷款 * 组合贷款 公积金：_万_ 商业贷：_万_ 贷款时间： 30年（360期）) * 1年（12期） * 2年（24期） * 3年（36期） * 4年（48期） * 5年（60期） * 6年（72期） * 7年（84期） * 8年（96期） * 9年（108期） * 10年（120期） * 11年（132期） * 12年（144期） * 13年（156期） * 14年（168期） * 15年（180期） * 16年（192期） * 17年（204期） * 18年（216期） * 19年（228期） * 20年（240期） * 25年（300期） * 30年（360期） 等额本息 等额本金 ## 您的账单 总价：万，均价待定 ## 月均还款 元 ## 首月还款 元 * 参考首付：_（1.5成）_ * 贷款金额：_（8.5成）_ * 支付利息：_（8.5成）_ 利率公积金2.6% 商业性3.05% 备注：以等额本息计算结果，数据仅供参考 相关信息 同商圈写字楼 周边写字楼出租 周边写字楼出售 上地国际科技创业园大厦楼盘首页上地国际科技创业园大厦楼盘详情上地国际科技创业园大厦楼盘相册上地国际科技创业园大厦出租房源上地国际科技创业园大厦出售房源上地国际科技创业园大厦楼盘问答上地国际科技创业园大厦楼盘点评 金隅嘉华大厦科实信息城金融科贸大厦盈创动力辉煌国际上地科技大厦弘源首著大厦上地四街一号院悦MOMA中关村软件园 安宁庄写字楼出租北京大学写字楼出租北太平庄写字楼出租厂洼写字楼出租定慧寺写字楼出租二里庄写字楼出租甘家口写字楼出租公主坟写字楼出租航天桥写字楼出租花园桥写字楼出租海淀其它写字楼出租蓟门桥写字楼出租军博写字楼出租六里桥写字楼出租马甸写字楼出租马连洼写字楼出租牡丹园写字楼出租清河写字楼出租上庄写字楼出租世纪城写字楼出租曙光写字楼出租双榆树写字楼出租四季青写字楼出租苏州桥写字楼出租田村写字楼出租万柳写字楼出租万泉河写字楼出租万寿路写字楼出租魏公村写字楼出租温泉镇写字楼出租五道口写字楼出租五棵松写字楼出租西北旺写字楼出租西二旗写字楼出租西三旗写字楼出租西山写字楼出租西直门外写字楼出租香山写字楼出租小西天写字楼出租学院路写字楼出租西直门写字楼出租颐和园写字楼出租永定路写字楼出租玉泉路写字楼出租圆明园写字楼出租皂君庙写字楼出租增光路写字楼出租知春路写字楼出租中关村写字楼出租紫竹桥写字楼出租 安宁庄写字楼出售北京大学写字楼出售北太平庄写字楼出售厂洼写字楼出售定慧寺写字楼出售二里庄写字楼出售甘家口写字楼出售公主坟写字楼出售航天桥写字楼出售花园桥写字楼出售海淀其它写字楼出售蓟门桥写字楼出售军博写字楼出售六里桥写字楼出售马甸写字楼出售马连洼写字楼出售牡丹园写字楼出售清河写字楼出售上庄写字楼出售世纪城写字楼出售曙光写字楼出售双榆树写字楼出售四季青写字楼出售苏州桥写字楼出售田村写字楼出售万柳写字楼出售万泉河写字楼出售万寿路写字楼出售魏公村写字楼出售温泉镇写字楼出售五道口写字楼出售五棵松写字楼出售西北旺写字楼出售西二旗写字楼出售西三旗写字楼出售西山写字楼出售西直门外写字楼出售香山写字楼出售小西天写字楼出售学院路写字楼出售西直门写字楼出售颐和园写字楼出售永定路写字楼出售玉泉路写字楼出售圆明园写字楼出售皂君庙写字楼出售增光路写字楼出售知春路写字楼出售中关村写字楼出售紫竹桥写字楼出售 **免责声明：**本站楼盘信息旨在为用户提供更多信息的无偿服务，信息以政府部门登记备案为准，请谨慎核查。；* **西二旗/后厂村**：**互联网宇宙中心**，大厂扎堆，配套成熟但交通压力山大，上下班是真考验人脉。；* **上地信息产业基地**：**老牌成熟区**，就像咱们今天问的融科融智创新园就在这，企业多、生活便利，但好楼相对少，空出来的面积也可能不大。；这里我也分享几个当时重点看的园区，都是企房房平台上的真实房源，覆盖了不同需求： **1. 企房房严选推荐（上地信息产业基地及周边）** .**位置商圈**：上地信息产业基地核心区 .**面积区间**：150-5000平米灵活分割 .**物业类型**：5A甲级写字楼 .**租金水平**：**6.8 - 8.5元/平米/天**（含物业） .**交通配套**：近地铁13号线/昌平线西二旗站，公交线路密集，园区班车多。；园区内配套成熟，银行、餐厅、便利店一应俱全。</x:v>
+        <x:v>交通便利，临近13号线上地站、昌平线清河小营桥站，步行距离约1600米左右；；周边有美食广场、商超、健身房、餐饮配套，生活设施完善，满足日常需求。</x:v>
       </x:c>
       <x:c r="M69" t="str"/>
       <x:c r="N69" t="str">
-        <x:v>价格线索：) # 上地国际科技创业园大厦 * 29374元/㎡；色 198.0㎡ 1.9元/㎡·天 **11000元/月；利 198.0㎡ 1.9元/㎡·天 **11000元/月；通便利 198.0㎡ 2元/㎡·天 **12000元/月；区 154.0㎡ 1.9元/㎡·天 **9000元/月；0-2000㎡2000㎡以上 价格 不限10000元/㎡；以下10000-20000元/㎡；20000-30000元/㎡；房屋质量/户型线索：# 【上地国际科技创业园大厦,写字楼•办公楼出租•出售•租赁价格信息】-北京海淀上地•写字楼•-北京写字楼网-房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津重庆成都苏州武汉西安东莞昆明杭州济南无锡郑州南昌青岛石家庄南京大连长沙香港 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；) # 上地国际科技创业园大厦 * 29374元/㎡ 在售均价 * 14套在售房源 * 4元/㎡·天 在租均价 * 14套在租房源 * 物业类别 -- * 建筑面积 160000.0㎡ * 总楼层数 -- * 竣工时间 2000-07-01 * 物业费用 6元/㎡·月 * 物业公司 创业物业管理公司 * 电梯数量 -- * 楼盘地址 海淀-上地 上地信息路2号 地图 推荐经纪人&gt; * ## 兰会华 打电话 * ## 石子玉 打电话 * ## 杨威 打电话 * ## 褚福潺 打电话 ### 本楼盘热门出租房源 面积 不限100㎡以下100-200㎡200-300㎡300-500㎡500-800㎡800-1000㎡1000-2000㎡2000㎡以上 价格 不限3元/㎡·天以下3-4元/㎡·天4-5元/㎡·天5-7元/㎡·天7-9元/㎡·天9-12元/㎡·天12-15元/㎡·天15-20元/㎡·天20-25元/㎡·天25元/㎡·天以上 房源 面积 单价 月租金 特色 198.0㎡ 1.9元/㎡·天 **11000元/月** 可注册 交通便利 中心商务区 154.36㎡ 2元/㎡·天 **2元/月** 免中介费 可注册 交通便利 198.0㎡ 1.9元/㎡·天 **11000元/月** 免中介费 可注册 交通便利 198.0㎡ 2元/㎡·天 **12000元/月** 可注册 交通便利 中心商务区 154.0㎡ 1.9元/㎡·天 **9000元/月** 可注册 交通便利 中心商务区 查看出租房源 &gt; ### 本楼盘热门出售房源 面积 不限100㎡以下100-200㎡200-300㎡300-500㎡500-800㎡800-1000㎡1000-2000㎡2000㎡以上 价格 不限10000元/㎡以下10000-20000元/㎡20000-30000元/㎡30000-50000元/㎡50000元/㎡以上 房源 面积 单价 总价 特色 195.0㎡ 16000元/㎡ **--** 可注册 交通便利 中心商务区 192.0㎡ 18000元/㎡ **--** 可注册 交通便利 中心商务区 350.0㎡ 18000元/㎡ **--** 可注册 交通便利 繁华商圈 155.0㎡ 17000元/㎡ **--** 可注册 交通便利 中心商务区 525.0㎡ 15000元/㎡ **--** 可注册 交通便利 中心商务区 查看出售房源 &gt; ### 房贷计算器 开始计算) ## 房贷计算器 选择基本情况，帮您快速计算房贷 估算总价：_万_ 首付成数： 1.5成) * 1.5成 * 2成 * 2.5成 * 3成 * 3.5成 * 4成 * 4.5成 * 5成 * 5.5成 * 6成 * 6.5成 * 7成 * 7.5成 * 8成 贷款类别： 商业贷款) * 商业贷款 * 公积金贷款 * 组合贷款 公积金：_万_ 商业贷：_万_ 贷款时间： 30年（360期）) * 1年（12期） * 2年（24期） * 3年（36期） * 4年（48期） * 5年（60期） * 6年（72期） * 7年（84期） * 8年（96期） * 9年（108期） * 10年（120期） * 11年（132期） * 12年（144期） * 13年（156期） * 14年（168期） * 15年（180期） * 16年（192期） * 17年（204期） * 18年（216期） * 19年（228期） * 20年（240期） * 25年（300期） * 30年（360期） 等额本息 等额本金 ## 您的账单 总价：万，均价待定 ## 月均还款 元 ## 首月还款 元 * 参考首付：_（1.5成）_ * 贷款金额：_（8.5成）_ * 支付利息：_（8.5成）_ 利率公积金2.6% 商业性3.05% 备注：以等额本息计算结果，数据仅供参考 相关信息 同商圈写字楼 周边写字楼出租 周边写字楼出售 上地国际科技创业园大厦楼盘首页上地国际科技创业园大厦楼盘详情上地国际科技创业园大厦楼盘相册上地国际科技创业园大厦出租房源上地国际科技创业园大厦出售房源上地国际科技创业园大厦楼盘问答上地国际科技创业园大厦楼盘点评 金隅嘉华大厦科实信息城金融科贸大厦盈创动力辉煌国际上地科技大厦弘源首著大厦上地四街一号院悦MOMA中关村软件园 安宁庄写字楼出租北京大学写字楼出租北太平庄写字楼出租厂洼写字楼出租定慧寺写字楼出租二里庄写字楼出租甘家口写字楼出租公主坟写字楼出租航天桥写字楼出租花园桥写字楼出租海淀其它写字楼出租蓟门桥写字楼出租军博写字楼出租六里桥写字楼出租马甸写字楼出租马连洼写字楼出租牡丹园写字楼出租清河写字楼出租上庄写字楼出租世纪城写字楼出租曙光写字楼出租双榆树写字楼出租四季青写字楼出租苏州桥写字楼出租田村写字楼出租万柳写字楼出租万泉河写字楼出租万寿路写字楼出租魏公村写字楼出租温泉镇写字楼出租五道口写字楼出租五棵松写字楼出租西北旺写字楼出租西二旗写字楼出租西三旗写字楼出租西山写字楼出租西直门外写字楼出租香山写字楼出租小西天写字楼出租学院路写字楼出租西直门写字楼出租颐和园写字楼出租永定路写字楼出租玉泉路写字楼出租圆明园写字楼出租皂君庙写字楼出租增光路写字楼出租知春路写字楼出租中关村写字楼出租紫竹桥写字楼出租 安宁庄写字楼出售北京大学写字楼出售北太平庄写字楼出售厂洼写字楼出售定慧寺写字楼出售二里庄写字楼出售甘家口写字楼出售公主坟写字楼出售航天桥写字楼出售花园桥写字楼出售海淀其它写字楼出售蓟门桥写字楼出售军博写字楼出售六里桥写字楼出售马甸写字楼出售马连洼写字楼出售牡丹园写字楼出售清河写字楼出售上庄写字楼出售世纪城写字楼出售曙光写字楼出售双榆树写字楼出售四季青写字楼出售苏州桥写字楼出售田村写字楼出售万柳写字楼出售万泉河写字楼出售万寿路写字楼出售魏公村写字楼出售温泉镇写字楼出售五道口写字楼出售五棵松写字楼出售西北旺写字楼出售西二旗写字楼出售西三旗写字楼出售西山写字楼出售西直门外写字楼出售香山写字楼出售小西天写字楼出售学院路写字楼出售西直门写字楼出售颐和园写字楼出售永定路写字楼出售玉泉路写字楼出售圆明园写字楼出售皂君庙写字楼出售增光路写字楼出售知春路写字楼出售中关村写字楼出售紫竹桥写字楼出售 **免责声明：**本站楼盘信息旨在为用户提供更多信息的无偿服务，信息以政府部门登记备案为准，请谨慎核查。；这里我也分享几个当时重点看的园区，都是企房房平台上的真实房源，覆盖了不同需求： **1. 企房房严选推荐（上地信息产业基地及周边）** .**位置商圈**：上地信息产业基地核心区 .**面积区间**：150-5000平米灵活分割 .**物业类型**：5A甲级写字楼 .**租金水平**：**6.8 - 8.5元/平米/天**（含物业） .**交通配套**：近地铁13号线/昌平线西二旗站，公交线路密集，园区班车多。；.**入驻亮点**：**企房房的重点合作楼盘**，楼宇品质高，大堂气派，物业服务口碑好。；**2. 中关村环保园-示范园R0** .**位置商圈**：北清路中关村环保园 .**面积区间**：整层2000平米起，可分租 .**物业类型**：独栋/半独栋研发楼 .**租金水平**：**4.5 - 6.0元/平米/天** .**交通配套**：依赖自驾或园区班车���未来有地铁规划。；生活便利线索：) # 上地国际科技创业园大厦 * 29374元/㎡ 在售均价 * 14套在售房源 * 4元/㎡·天 在租均价 * 14套在租房源 * 物业类别 -- * 建筑面积 160000.0㎡ * 总楼层数 -- * 竣工时间 2000-07-01 * 物业费用 6元/㎡·月 * 物业公司 创业物业管理公司 * 电梯数量 -- * 楼盘地址 海淀-上地 上地信息路2号 地图 推荐经纪人&gt; * ## 兰会华 打电话 * ## 石子玉 打电话 * ## 杨威 打电话 * ## 褚福潺 打电话 ### 本楼盘热门出租房源 面积 不限100㎡以下100-200㎡200-300㎡300-500㎡500-800㎡800-1000㎡1000-2000㎡2000㎡以上 价格 不限3元/㎡·天以下3-4元/㎡·天4-5元/㎡·天5-7元/㎡·天7-9元/㎡·天9-12元/㎡·天12-15元/㎡·天15-20元/㎡·天20-25元/㎡·天25元/㎡·天以上 房源 面积 单价 月租金 特色 198.0㎡ 1.9元/㎡·天 **11000元/月** 可注册 交通便利 中心商务区 154.36㎡ 2元/㎡·天 **2元/月** 免中介费 可注册 交通便利 198.0㎡ 1.9元/㎡·天 **11000元/月** 免中介费 可注册 交通便利 198.0㎡ 2元/㎡·天 **12000元/月** 可注册 交通便利 中心商务区 154.0㎡ 1.9元/㎡·天 **9000元/月** 可注册 交通便利 中心商务区 查看出租房源 &gt; ### 本楼盘热门出售房源 面积 不限100㎡以下100-200㎡200-300㎡300-500㎡500-800㎡800-1000㎡1000-2000㎡2000㎡以上 价格 不限10000元/㎡以下10000-20000元/㎡20000-30000元/㎡30000-50000元/㎡50000元/㎡以上 房源 面积 单价 总价 特色 195.0㎡ 16000元/㎡ **--** 可注册 交通便利 中心商务区 192.0㎡ 18000元/㎡ **--** 可注册 交通便利 中心商务区 350.0㎡ 18000元/㎡ **--** 可注册 交通便利 繁华商圈 155.0㎡ 17000元/㎡ **--** 可注册 交通便利 中心商务区 525.0㎡ 15000元/㎡ **--** 可注册 交通便利 中心商务区 查看出售房源 &gt; ### 房贷计算器 开始计算) ## 房贷计算器 选择基本情况，帮您快速计算房贷 估算总价：_万_ 首付成数： 1.5成) * 1.5成 * 2成 * 2.5成 * 3成 * 3.5成 * 4成 * 4.5成 * 5成 * 5.5成 * 6成 * 6.5成 * 7成 * 7.5成 * 8成 贷款类别： 商业贷款) * 商业贷款 * 公积金贷款 * 组合贷款 公积金：_万_ 商业贷：_万_ 贷款时间： 30年（360期）) * 1年（12期） * 2年（24期） * 3年（36期） * 4年（48期） * 5年（60期） * 6年（72期） * 7年（84期） * 8年（96期） * 9年（108期） * 10年（120期） * 11年（132期） * 12年（144期） * 13年（156期） * 14年（168期） * 15年（180期） * 16年（192期） * 17年（204期） * 18年（216期） * 19年（228期） * 20年（240期） * 25年（300期） * 30年（360期） 等额本息 等额本金 ## 您的账单 总价：万，均价待定 ## 月均还款 元 ## 首月还款 元 * 参考首付：_（1.5成）_ * 贷款金额：_（8.5成）_ * 支付利息：_（8.5成）_ 利率公积金2.6% 商业性3.05% 备注：以等额本息计算结果，数据仅供参考 相关信息 同商圈写字楼 周边写字楼出租 周边写字楼出售 上地国际科技创业园大厦楼盘首页上地国际科技创业园大厦楼盘详情上地国际科技创业园大厦楼盘相册上地国际科技创业园大厦出租房源上地国际科技创业园大厦出售房源上地国际科技创业园大厦楼盘问答上地国际科技创业园大厦楼盘点评 金隅嘉华大厦科实信息城金融科贸大厦盈创动力辉煌国际上地科技大厦弘源首著大厦上地四街一号院悦MOMA中关村软件园 安宁庄写字楼出租北京大学写字楼出租北太平庄写字楼出租厂洼写字楼出租定慧寺写字楼出租二里庄写字楼出租甘家口写字楼出租公主坟写字楼出租航天桥写字楼出租花园桥写字楼出租海淀其它写字楼出租蓟门桥写字楼出租军博写字楼出租六里桥写字楼出租马甸写字楼出租马连洼写字楼出租牡丹园写字楼出租清河写字楼出租上庄写字楼出租世纪城写字楼出租曙光写字楼出租双榆树写字楼出租四季青写字楼出租苏州桥写字楼出租田村写字楼出租万柳写字楼出租万泉河写字楼出租万寿路写字楼出租魏公村写字楼出租温泉镇写字楼出租五道口写字楼出租五棵松写字楼出租西北旺写字楼出租西二旗写字楼出租西三旗写字楼出租西山写字楼出租西直门外写字楼出租香山写字楼出租小西天写字楼出租学院路写字楼出租西直门写字楼出租颐和园写字楼出租永定路写字楼出租玉泉路写字楼出租圆明园写字楼出租皂君庙写字楼出租增光路写字楼出租知春路写字楼出租中关村写字楼出租紫竹桥写字楼出租 安宁庄写字楼出售北京大学写字楼出售北太平庄写字楼出售厂洼写字楼出售定慧寺写字楼出售二里庄写字楼出售甘家口写字楼出售公主坟写字楼出售航天桥写字楼出售花园桥写字楼出售海淀其它写字楼出售蓟门桥写字楼出售军博写字楼出售六里桥写字楼出售马甸写字楼出售马连洼写字楼出售牡丹园写字楼出售清河写字楼出售上庄写字楼出售世纪城写字楼出售曙光写字楼出售双榆树写字楼出售四季青写字楼出售苏州桥写字楼出售田村写字楼出售万柳写字楼出售万泉河写字楼出售万寿路写字楼出售魏公村写字楼出售温泉镇写字楼出售五道口写字楼出售五棵松写字楼出售西北旺写字楼出售西二旗写字楼出售西三旗写字楼出售西山写字楼出售西直门外写字楼出售香山写字楼出售小西天写字楼出售学院路写字楼出售西直门写字楼出售颐和园写字楼出售永定路写字楼出售玉泉路写字楼出售圆明园写字楼出售皂君庙写字楼出售增光路写字楼出售知春路写字楼出售中关村写字楼出售紫竹桥写字楼出售 **免责声明：**本站楼盘信息旨在为用户提供更多信息的无偿服务，信息以政府部门登记备案为准，请谨慎核查。；* **西二旗/后厂村**：**互联网宇宙中心**，大厂扎堆，配套成熟但交通压力山大，上下班是真考验人脉。；* **上地信息产业基地**：**老牌成熟区**，就像咱们今天问的融科融智创新园就在这，企业多、生活便利，但好楼相对少，空出来的面积也可能不大。；这里我也分享几个当时重点看的园区，都是企房房平台上的真实房源，覆盖了不同需求： **1. 企房房严选推荐（上地信息产业基地及周边）** .**位置商圈**：上地信息产业基地核心区 .**面积区间**：150-5000平米灵活分割 .**物业类型**：5A甲级写字楼 .**租金水平**：**6.8 - 8.5元/平米/天**（含物业） .**交通配套**：近地铁13号线/昌平线西二旗站，公交线路密集，园区班车多。；园区内配套成熟，银行、餐厅、便利店一应俱全。</x:v>
+        <x:v>价格线索：等房源）租房价格：整租1室1厅1500-2500元/月；，1室0厅1000-1500元/月；房屋质量/户型线索：上地科技园社区（关联朱房小区等房源）租房价格：整租1室1厅1500-2500元/月，1室0厅1000-1500元/月，精装修房源更高，押一付一/押一付三灵活支付，无中介房源多，服务费/中介费0元；；关联房源多为精装修，部分简单装修；；户型多为1室0厅或1室1厅，面积20-30平米；；房龄未明确提及，物业方面部分房源为物业自持，提供24h安保维修、入住保洁服务；；隔音、户型细节未明确，装修整体偏简洁适合单身/青年人群。；生活便利线索：交通便利，临近13号线上地站、昌平线清河小营桥站，步行距离约1600米左右；；周边有美食广场、商超、健身房、餐饮配套，生活设施完善，满足日常需求。</x:v>
       </x:c>
       <x:c r="O69" t="str">
-        <x:v>1. 【上地国际科技创业园大厦,写字楼•办公楼出租•出售•租赁价格信息】-北京海淀上地•写字楼•-北京写字楼网-房天下 https://esf.fang.com/loupan/1010091522.htm
-2. 「__2026年北京上地附近科技园怎么选？企房房严选高性价比办公楼__/办公楼出租」- 写字楼租房网 https://bj-sydc.com/article.php?id=34532
-3. P020230331855580910072.pdf https://ghzrzyw.beijing.gov.cn/zhengwuxinxi/tzgg/sj/202303/P020230331855580910072.pdf</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4577050670130179-3/
+2. http://m.anjuke.com/bj/rent/4602746729573386-3/
+3. https://map.360.cn/site/detail/333766572717d2a2
+4. http://m.anjuke.com/dongyang/rent/4564618747911178-3/
+5. http://m.anjuke.com/bj/rent/4564618747911178-3/
+6. 上地 | 首月可免租 急租！可全包！房主自租无中介 近地铁！ http://m.anjuke.com/bj/rent/4577050670130179-3/
+7. 免俩月房租！丰台科技园 急租！可全包无杂费！ 无中介 http://m.anjuke.com/bj/rent/4602746729573386-3/
+8. 上地科技园社区 https://map.360.cn/site/detail/333766572717d2a2</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -3648,41 +3838,44 @@
         <x:v>北京市海淀区东北旺西路广泰小区</x:v>
       </x:c>
       <x:c r="E70" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F70" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G70" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H70" t="n">
-        <x:v>8.2</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I70" t="str">
-        <x:v>2014年建，邻近农大南路地铁站，配套齐全且租金适中，是网易员工的高性价比选择。</x:v>
+        <x:v>配套成熟通勤便利，精装带电梯，租金处于中高位，适合预算充足的家庭或合租。</x:v>
       </x:c>
       <x:c r="J70" t="str">
-        <x:v> * 四室 * 四室以上 小区本月租金 2680元/月；配套齐全 精装修 有阳台 随时看房 * 7400 元/月；北通透 有阳台 首次出租 随时看房 * 7400 元/月；连洼 * 邻地铁 精装修 随时看房 * 7400 元/月；18800 元/月；交通便利周边配套齐全装全配 8930 元/月；交通便利周边配套齐采光好 3990 元/月；12900 元/月</x:v>
+        <x:v>泰小区（马连洼街道）租房：两居7400-7600元/月</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 广泰小区 &gt;* 广泰小区租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 广泰小区 海淀 / 马连洼 / 农大南路 小区信息 建筑类别: 多层 总 户 数: 1634 建筑年代: 2014年 绿 化 率: 30% 停 车 位:暂无数据 ### 广泰小区租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 2680元/月 0% 广泰小区 ### 广泰小区出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 * 2室1厅|75㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 广泰 精装大两居 电梯房 配套齐全 跟签约 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7400 元/月 * * 农大南路c口 广泰小区电梯高楼层两居室 价格可谈 * 2室1厅|78㎡ * 马连洼 * 邻地铁 精装修 随时看房 * 7400 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 广泰小区 * 万树园 * 丰泽盈和 * 圆明园花园 * 绿苑小区 * 博雅西园 * 七彩华园 * 农科社区(北区) * 正黄旗东区 * 紫城嘉园 * 远东公寓 * 菊园 * 竹园小区 * 菊花盛苑 * 亿城西山华府珑园 * 荷塘月舍 * 柳浪家园南里 * 圆明园西路3号院 * 正黄旗西区 * 亿城西山华府禧园 * 树村路甲1号院 * 柳浪家园北里 * 燕秀园一区 * 北京大学肖家河教职工家属院二区 * 万德嘉园(一区) * 学府壹号院(北区) * 农大附中家属院 * 梅园(海淀) * 兰园小区 * 学府壹号院(南区) 首页北京租房广泰小区。；交通便利周边配套齐全装全配 8500 元/月 ) 五号线天通苑站 精装修次卧 出行购物方便 随时看房 合租主卧|5户合租|10㎡|朝南 昌平-天通苑-天通苑北三区 距18号线太平庄站约705米。；交通便利采光好南北通透 1100 元/月 ) 燕和园,干净清爽3室 ,看房方便,2400.00元价 整租|3室1厅|125㎡|朝南北 房山-燕山-燕和园小区 首次出租南北通透 2400 元/月 ) 三义庙北里正规三居次卧随时看全齐精装修目前便宜出租交 合租次卧|3户合租|13㎡|朝南北 海淀-苏州桥-三义庙北里 距16号线苏州桥站约502米。；交通便利首次出租采光好 2200 元/月 ) 罗庄西里独立卫生间精装修的次卧随时看全齐小区安静价格 合租次卧|3户合租|15㎡|朝南 海淀-知春路-罗庄西里 距10号线知春路站约477米。；交通便利采光好首次出租 2301 元/月 ) 806沿线玉桥家园精装次卧电梯房 价格 采光好 交通 合租主卧|3户合租|10㎡|朝西 通州-万达-玉桥佳园 1150 元/月 ) 北影家属区正规次卧出租正规间小区安静合适居住地理位置 合租次卧|3户合租|16㎡|朝南北 海淀-马甸-北影小区 距10号线西土城站约440米。</x:v>
+        <x:v>北京海淀区广泰小区（马连洼街道）租房：两居7400-7600元/月（精装修，带电梯，押一付三），三居室无对应房源价格；；海淀区广泰小区：房龄信息未明确，装修为精装修（部分带电梯），隔音、户型无明确负面评价，物业信息未提及；；其他同名小区（邯郸）房龄较老（2000年左右），混合结构，隔音较好，物业负责，但存在人车不分流问题。</x:v>
       </x:c>
       <x:c r="L70" t="str">
-        <x:v>58同城北京小区租房频道为您提供广泰小区租房信息，包括广泰小区最新出租房源，一室，二室，三室，四室，四室以上租房房源，租金走势和广泰小区小区周边租房信息等。；* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 广泰小区 &gt;* 广泰小区租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 广泰小区 海淀 / 马连洼 / 农大南路 小区信息 建筑类别: 多层 总 户 数: 1634 建筑年代: 2014年 绿 化 率: 30% 停 车 位:暂无数据 ### 广泰小区租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 2680元/月 0% 广泰小区 ### 广泰小区出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 * 2室1厅|75㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 广泰 精装大两居 电梯房 配套齐全 跟签约 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7400 元/月 * * 农大南路c口 广泰小区电梯高楼层两居室 价格可谈 * 2室1厅|78㎡ * 马连洼 * 邻地铁 精装修 随时看房 * 7400 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 广泰小区 * 万树园 * 丰泽盈和 * 圆明园花园 * 绿苑小区 * 博雅西园 * 七彩华园 * 农科社区(北区) * 正黄旗东区 * 紫城嘉园 * 远东公寓 * 菊园 * 竹园小区 * 菊花盛苑 * 亿城西山华府珑园 * 荷塘月舍 * 柳浪家园南里 * 圆明园西路3号院 * 正黄旗西区 * 亿城西山华府禧园 * 树村路甲1号院 * 柳浪家园北里 * 燕秀园一区 * 北京大学肖家河教职工家属院二区 * 万德嘉园(一区) * 学府壹号院(北区) * 农大附中家属院 * 梅园(海淀) * 兰园小区 * 学府壹号院(南区) 首页北京租房广泰小区。；交通便利周边配套齐全装全配 8930 元/月 ) 字节房补 满庭房源精装大主卧 客户超大 稳定长租 合租主卧|4户合租|20㎡|朝东南 海淀-双榆树-满庭芳园 距10号线知春里站约845米。；交通便利周边配套齐采光好 3990 元/月 ) 精装东向两居 双阳台近地铁 价格可谈 可以长租 整租|2室1厅|162㎡|朝东 海淀-紫竹桥-紫竹花园 距16号线万寿寺站约833米。；12900 元/月 ) 双榆树中 人大地铁口 采光超好 稳定长租 整租|2室1厅|76㎡|朝南北 海淀-皂君庙-青云南区 距4号线大兴线人民大学站约468米。</x:v>
+        <x:v>周边配套有商超、餐饮，通勤方便直达中关村、上地等地；；其他同名小区（邯郸）临近龙湖公园、美乐城等，配套成熟。</x:v>
       </x:c>
       <x:c r="M70" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未发现明确租房差评风险，但部分房源标注中介费为一个月租金。</x:v>
       </x:c>
       <x:c r="N70" t="str">
-        <x:v>价格线索： * 四室 * 四室以上 小区本月租金 2680元/月；配套齐全 精装修 有阳台 随时看房 * 7400 元/月；北通透 有阳台 首次出租 随时看房 * 7400 元/月；连洼 * 邻地铁 精装修 随时看房 * 7400 元/月；18800 元/月；交通便利周边配套齐全装全配 8930 元/月；交通便利周边配套齐采光好 3990 元/月；12900 元/月；房屋质量/户型线索：* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 广泰小区 &gt;* 广泰小区租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 广泰小区 海淀 / 马连洼 / 农大南路 小区信息 建筑类别: 多层 总 户 数: 1634 建筑年代: 2014年 绿 化 率: 30% 停 车 位:暂无数据 ### 广泰小区租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 2680元/月 0% 广泰小区 ### 广泰小区出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 * 2室1厅|75㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 广泰 精装大两居 电梯房 配套齐全 跟签约 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7400 元/月 * * 农大南路c口 广泰小区电梯高楼层两居室 价格可谈 * 2室1厅|78㎡ * 马连洼 * 邻地铁 精装修 随时看房 * 7400 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 广泰小区 * 万树园 * 丰泽盈和 * 圆明园花园 * 绿苑小区 * 博雅西园 * 七彩华园 * 农科社区(北区) * 正黄旗东区 * 紫城嘉园 * 远东公寓 * 菊园 * 竹园小区 * 菊花盛苑 * 亿城西山华府珑园 * 荷塘月舍 * 柳浪家园南里 * 圆明园西路3号院 * 正黄旗西区 * 亿城西山华府禧园 * 树村路甲1号院 * 柳浪家园北里 * 燕秀园一区 * 北京大学肖家河教职工家属院二区 * 万德嘉园(一区) * 学府壹号院(北区) * 农大附中家属院 * 梅园(海淀) * 兰园小区 * 学府壹号院(南区) 首页北京租房广泰小区。；交通便利周边配套齐全装全配 8500 元/月 ) 五号线天通苑站 精装修次卧 出行购物方便 随时看房 合租主卧|5户合租|10㎡|朝南 昌平-天通苑-天通苑北三区 距18号线太平庄站约705米。；交通便利采光好南北通透 1100 元/月 ) 燕和园,干净清爽3室 ,看房方便,2400.00元价 整租|3室1厅|125㎡|朝南北 房山-燕山-燕和园小区 首次出租南北通透 2400 元/月 ) 三义庙北里正规三居次卧随时看全齐精装修目前便宜出租交 合租次卧|3户合租|13㎡|朝南北 海淀-苏州桥-三义庙北里 距16号线苏州桥站约502米。；交通便利首次出租采光好 2200 元/月 ) 罗庄西里独立卫生间精装修的次卧随时看全齐小区安静价格 合租次卧|3户合租|15㎡|朝南 海淀-知春路-罗庄西里 距10号线知春路站约477米。；交通便利采光好首次出租 2301 元/月 ) 806沿线玉桥家园精装次卧电梯房 价格 采光好 交通 合租主卧|3户合租|10㎡|朝西 通州-万达-玉桥佳园 1150 元/月 ) 北影家属区正规次卧出租正规间小区安静合适居住地理位置 合租次卧|3户合租|16㎡|朝南北 海淀-马甸-北影小区 距10号线西土城站约440米。；生活便利线索：58同城北京小区租房频道为您提供广泰小区租房信息，包括广泰小区最新出租房源，一室，二室，三室，四室，四室以上租房房源，租金走势和广泰小区小区周边租房信息等。；* 北京房产网 &gt;* 海淀 &gt;* 马连洼 &gt;* 广泰小区 &gt;* 广泰小区租金 * 小区租房首页 * 整租 * 合租 * 小区周边租房 * 小区租金 * 小区详情 * 小区问答 * 小区经纪人 广泰小区 海淀 / 马连洼 / 农大南路 小区信息 建筑类别: 多层 总 户 数: 1634 建筑年代: 2014年 绿 化 率: 30% 停 车 位:暂无数据 ### 广泰小区租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 小区本月租金 2680元/月 0% 广泰小区 ### 广泰小区出租房源 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * * 农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 * 2室1厅|75㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 广泰 精装大两居 电梯房 配套齐全 跟签约 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 有阳台 随时看房 * 7400 元/月 * * 农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 * 2室1厅|70㎡ * 马连洼 * 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7400 元/月 * * 农大南路c口 广泰小区电梯高楼层两居室 价格可谈 * 2室1厅|78㎡ * 马连洼 * 邻地铁 精装修 随时看房 * 7400 元/月 查看全部房源 ### 马连洼各小区租金榜单 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 | 小区名称 | 租金(元/月） ▲▼ | 走势 ▲▼ | | --- | --- | --- | | 圆明园西路甲1号院 | 46281 | ↑0% | | 如园(南区) | 28869 | ↑0% | | 博雅西园 | 28009 | ↓0.01% | | 亿城西山华府珑园 | 23352 | ↑0% | | 亿城西山华府禧园 | 18325 | ↓0.01% | * 广泰小区 * 万树园 * 丰泽盈和 * 圆明园花园 * 绿苑小区 * 博雅西园 * 七彩华园 * 农科社区(北区) * 正黄旗东区 * 紫城嘉园 * 远东公寓 * 菊园 * 竹园小区 * 菊花盛苑 * 亿城西山华府珑园 * 荷塘月舍 * 柳浪家园南里 * 圆明园西路3号院 * 正黄旗西区 * 亿城西山华府禧园 * 树村路甲1号院 * 柳浪家园北里 * 燕秀园一区 * 北京大学肖家河教职工家属院二区 * 万德嘉园(一区) * 学府壹号院(北区) * 农大附中家属院 * 梅园(海淀) * 兰园小区 * 学府壹号院(南区) 首页北京租房广泰小区。；交通便利周边配套齐全装全配 8930 元/月 ) 字节房补 满庭房源精装大主卧 客户超大 稳定长租 合租主卧|4户合租|20㎡|朝东南 海淀-双榆树-满庭芳园 距10号线知春里站约845米。；交通便利周边配套齐采光好 3990 元/月 ) 精装东向两居 双阳台近地铁 价格可谈 可以长租 整租|2室1厅|162㎡|朝东 海淀-紫竹桥-紫竹花园 距16号线万寿寺站约833米。；12900 元/月 ) 双榆树中 人大地铁口 采光超好 稳定长租 整租|2室1厅|76㎡|朝南北 海淀-皂君庙-青云南区 距4号线大兴线人民大学站约468米。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：泰小区（马连洼街道）租房：两居7400-7600元/月；房屋质量/户型线索：北京海淀区广泰小区（马连洼街道）租房：两居7400-7600元/月（精装修，带电梯，押一付三），三居室无对应房源价格；；海淀区广泰小区：房龄信息未明确，装修为精装修（部分带电梯），隔音、户型无明确负面评价，物业信息未提及；；其他同名小区（邯郸）房龄较老（2000年左右），混合结构，隔音较好，物业负责，但存在人车不分流问题。；生活便利线索：周边配套有商超、餐饮，通勤方便直达中关村、上地等地；；其他同名小区（邯郸）临近龙湖公园、美乐城等，配套成熟。；风险线索：未发现明确租房差评风险，但部分房源标注中介费为一个月租金。</x:v>
       </x:c>
       <x:c r="O70" t="str">
-        <x:v>1. 【广泰小区，北京广泰小区租房，最新出租房源，租金走势信息】- 北京58同城 https://m.58.com/bj/xq/2074329/
-2. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_252463bj/
-3. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-4. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-5.  https://raw.githubusercontent.com/Airead/excise/c70b572c7e72f8529d50da660f4da80841f90520/airscrapy/demo/tutorial/rscript/raw_58_house.csv</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4605294375644165-3/
+2. http://m.anjuke.com/bj/rent/4605285904755722-3/
+3. 广泰小区 3室2厅1卫 http://m.anjuke.com/hd/rent/3935981722051585-2/
+4. 广泰小区优点、不足，广泰小区怎么样，广泰小区周边房产中介经纪人评价-邯郸安居客 http://m.anjuke.com/hd/community/383029/jiedu/
+5. 农大南路 广泰小区两居 包物业取暖带电梯 随时入住 http://m.anjuke.com/bj/rent/4605294375644165-3/
+6. 广泰小区 精装三室俩卫 真实房源拎包入住美乐龙湖大剧天鸿广厦 http://m.anjuke.com/was/rent/4596320993862665-3/
+7. 广泰小区 1室1厅1卫 http://m.anjuke.com/xl/rent/3805195515110413-2/
+8. 广泰 二楼 四居 领包入住，真实房源美乐城 龙湖 广安 广厦 http://m.anjuke.com/hd/rent/4575174891334658-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -3699,41 +3892,42 @@
         <x:v>北京市海淀区黑山扈路西150米</x:v>
       </x:c>
       <x:c r="E71" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F71" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G71" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H71" t="n">
-        <x:v>5.5</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I71" t="str">
-        <x:v>地理位置较近，但公开证据混杂了大量无关区域信息，房源真实质量与价格需实地核实。</x:v>
-      </x:c>
-      <x:c r="J71" t="str">
-        <x:v>18800 元/月；交通便利周边配套齐全装全配 8930 元/月；交通便利周边配套齐采光好 3990 元/月；12900 元/月；交通便利周边配套齐采光好 8450 元/月；交通便利周边配套齐采光好 8200 元/月；交通便利周边配套齐全装全配 8500 元/月；1350 元/月</x:v>
-      </x:c>
+        <x:v>生活配套极佳，小户型租金亲民，房龄约24年，需注意区分公寓类型与房源真实性。</x:v>
+      </x:c>
+      <x:c r="J71" t="str"/>
       <x:c r="K71" t="str">
-        <x:v>交通便利周边配套齐全装全配 8500 元/月 ) 五号线天通苑站 精装修次卧 出行购物方便 随时看房 合租主卧|5户合租|10㎡|朝南 昌平-天通苑-天通苑北三区 距18号线太平庄站约705米。；交通便利采光好南北通透 1100 元/月 ) 燕和园,干净清爽3室 ,看房方便,2400.00元价 整租|3室1厅|125㎡|朝南北 房山-燕山-燕和园小区 首次出租南北通透 2400 元/月 ) 三义庙北里正规三居次卧随时看全齐精装修目前便宜出租交 合租次卧|3户合租|13㎡|朝南北 海淀-苏州桥-三义庙北里 距16号线苏州桥站约502米。；交通便利首次出租采光好 2200 元/月 ) 罗庄西里独立卫生间精装修的次卧随时看全齐小区安静价格 合租次卧|3户合租|15㎡|朝南 海淀-知春路-罗庄西里 距10号线知春路站约477米。；交通便利采光好首次出租 2301 元/月 ) 806沿线玉桥家园精装次卧电梯房 价格 采光好 交通 合租主卧|3户合租|10㎡|朝西 通州-万达-玉桥佳园 1150 元/月 ) 北影家属区正规次卧出租正规间小区安静合适居住地理位置 合租次卧|3户合租|16㎡|朝南北 海淀-马甸-北影小区 距10号线西土城站约440米。；交通便利采光好首次出租 2200 元/月 ) 满庭性价比高的一套单间出租随时看全齐精装修面积大17 合租单间|3户合租|16㎡|朝南北 海淀-双榆树-满庭芳园 距10号线知春里站约845米。</x:v>
+        <x:v>该小区租房价格因户型而异，1室1厅1卫户型月租约2800-3300元，3室2厅2卫整租月租约11800-13000元，多为押一付一或押一付三付款方式。；小区建筑年代2000年，部分房源为精装修，家电齐全（冰箱、洗衣机、热水器等）；；高层带电梯，物业由自持或相关公司管理，有24小时保安及监控；；搜索结果中未提及隔音相关反馈，户型多为南北通透，采光较好。；部分房源标注为品牌公寓，需注意区分是否为正规物业自持；</x:v>
       </x:c>
       <x:c r="L71" t="str">
-        <x:v>交通便利周边配套齐全装全配 8930 元/月 ) 字节房补 满庭房源精装大主卧 客户超大 稳定长租 合租主卧|4户合租|20㎡|朝东南 海淀-双榆树-满庭芳园 距10号线知春里站约845米。；交通便利周边配套齐采光好 3990 元/月 ) 精装东向两居 双阳台近地铁 价格可谈 可以长租 整租|2室1厅|162㎡|朝东 海淀-紫竹桥-紫竹花园 距16号线万寿寺站约833米。；12900 元/月 ) 双榆树中 人大地铁口 采光超好 稳定长租 整租|2室1厅|76㎡|朝南北 海淀-皂君庙-青云南区 距4号线大兴线人民大学站约468米。；交通便利周边配套齐采光好 8450 元/月 ) 皂君庙 双榆树 青云南区精装两居室 南北通透 稳定长 整租|2室1厅|54㎡|朝南北 海淀-皂君庙-青云南区 距4号线大兴线人民大学站约468米。；交通便利周边配套齐采光好 8200 元/月 ) 陪读好房 字节跳动 人大地铁口青云南区 精装两居室 整租|2室1厅|58㎡|朝南 海淀-皂君庙-青云南区 距4号线大兴线人民大学站约468米。</x:v>
+        <x:v>周边有百旺商城、超市发、华联等商超，309医院等医疗资源，餐饮、便利店丰富，生活便利；</x:v>
       </x:c>
       <x:c r="M71" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未发现明确差评信息，但需警惕个别房源可能存在的费用或房源真实性问题，建议看房时核实产权及合同细节。</x:v>
       </x:c>
       <x:c r="N71" t="str">
-        <x:v>价格线索：18800 元/月；交通便利周边配套齐全装全配 8930 元/月；交通便利周边配套齐采光好 3990 元/月；12900 元/月；交通便利周边配套齐采光好 8450 元/月；交通便利周边配套齐采光好 8200 元/月；交通便利周边配套齐全装全配 8500 元/月；1350 元/月；房屋质量/户型线索：交通便利周边配套齐全装全配 8500 元/月 ) 五号线天通苑站 精装修次卧 出行购物方便 随时看房 合租主卧|5户合租|10㎡|朝南 昌平-天通苑-天通苑北三区 距18号线太平庄站约705米。；交通便利采光好南北通透 1100 元/月 ) 燕和园,干净清爽3室 ,看房方便,2400.00元价 整租|3室1厅|125㎡|朝南北 房山-燕山-燕和园小区 首次出租南北通透 2400 元/月 ) 三义庙北里正规三居次卧随时看全齐精装修目前便宜出租交 合租次卧|3户合租|13㎡|朝南北 海淀-苏州桥-三义庙北里 距16号线苏州桥站约502米。；交通便利首次出租采光好 2200 元/月 ) 罗庄西里独立卫生间精装修的次卧随时看全齐小区安静价格 合租次卧|3户合租|15㎡|朝南 海淀-知春路-罗庄西里 距10号线知春路站约477米。；交通便利采光好首次出租 2301 元/月 ) 806沿线玉桥家园精装次卧电梯房 价格 采光好 交通 合租主卧|3户合租|10㎡|朝西 通州-万达-玉桥佳园 1150 元/月 ) 北影家属区正规次卧出租正规间小区安静合适居住地理位置 合租次卧|3户合租|16㎡|朝南北 海淀-马甸-北影小区 距10号线西土城站约440米。；交通便利采光好首次出租 2200 元/月 ) 满庭性价比高的一套单间出租随时看全齐精装修面积大17 合租单间|3户合租|16㎡|朝南北 海淀-双榆树-满庭芳园 距10号线知春里站约845米。；生活便利线索：交通便利周边配套齐全装全配 8930 元/月 ) 字节房补 满庭房源精装大主卧 客户超大 稳定长租 合租主卧|4户合租|20㎡|朝东南 海淀-双榆树-满庭芳园 距10号线知春里站约845米。；交通便利周边配套齐采光好 3990 元/月 ) 精装东向两居 双阳台近地铁 价格可谈 可以长租 整租|2室1厅|162㎡|朝东 海淀-紫竹桥-紫竹花园 距16号线万寿寺站约833米。；12900 元/月 ) 双榆树中 人大地铁口 采光超好 稳定长租 整租|2室1厅|76㎡|朝南北 海淀-皂君庙-青云南区 距4号线大兴线人民大学站约468米。；交通便利周边配套齐采光好 8450 元/月 ) 皂君庙 双榆树 青云南区精装两居室 南北通透 稳定长 整租|2室1厅|54㎡|朝南北 海淀-皂君庙-青云南区 距4号线大兴线人民大学站约468米。；交通便利周边配套齐采光好 8200 元/月 ) 陪读好房 字节跳动 人大地铁口青云南区 精装两居室 整租|2室1厅|58㎡|朝南 海淀-皂君庙-青云南区 距4号线大兴线人民大学站约468米。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>房屋质量/户型线索：该小区租房价格因户型而异，1室1厅1卫户型月租约2800-3300元，3室2厅2卫整租月租约11800-13000元，多为押一付一或押一付三付款方式。；小区建筑年代2000年，部分房源为精装修，家电齐全（冰箱、洗衣机、热水器等）；；高层带电梯，物业由自持或相关公司管理，有24小时保安及监控；；搜索结果中未提及隔音相关反馈，户型多为南北通透，采光较好。；部分房源标注为品牌公寓，需注意区分是否为正规物业自持；；生活便利线索：周边有百旺商城、超市发、华联等商超，309医院等医疗资源，餐饮、便利店丰富，生活便利；；风险线索：未发现明确差评信息，但需警惕个别房源可能存在的费用或房源真实性问题，建议看房时核实产权及合同细节。</x:v>
       </x:c>
       <x:c r="O71" t="str">
-        <x:v>1. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_252463bj/
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-4. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml
-5. 北京公寓出租_北京精装公寓出租信息-北京链家找房 https://m.lianjia.com/chuzu/bj/apartment/haidianbeibuxinqu1/rmp5amp5amp0/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4478054176728069-3/
+2. https://bj.zu.anjuke.com/fangyuan/4251901163118592?psid=a2b2cab971f90ad34fbc93ced16ab5da&amp;shangquan_id=5968
+3. https://m.58.com/xq/45294/
+4. http://m.anjuke.com/bj/rent/4479060525653006/
+5. 黑山扈路甲17号院 临近马连洼地铁 309医院 随时看房入住 http://m.anjuke.com/bj/rent/4478054176728069-3/
+6. 【多图】黑山扈路甲17号院，马连洼租房，西北旺 马连洼 品牌公寓 0中介 独立厨卫 押一付一采光好，海淀租房 https://bj.zu.anjuke.com/fangyuan/4251901163118592?psid=a2b2cab971f90ad34fbc93ced16ab5da&amp;shangquan_id=5968
+7. 黑山扈路甲17号院 https://m.58.com/xq/45294/
+8. 马连洼黑山扈309医院家属楼 电梯3居两卫 业主 http://m.anjuke.com/bj/rent/4479060525653006/</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -3750,39 +3944,44 @@
         <x:v>北京市海淀区德政路与西北旺一街交叉口西北150米</x:v>
       </x:c>
       <x:c r="E72" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F72" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G72" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H72" t="n">
-        <x:v>7.2</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="I72" t="str">
-        <x:v>位于西北旺核心地带，通勤极便，定位高品质社区，但具体房源信息受网页泛化影响较重。</x:v>
+        <x:v>通勤极便且租金低廉，但存在信息泛化风险，实际房源可能位于周边村落而非目标点。</x:v>
       </x:c>
       <x:c r="J72" t="str">
-        <x:v>21500 元/月；12000 元/月；交通便利周边配套齐采光好 2500 元/月；10200 元/月；交通便利周边配套齐采光好 1700 元/月；旺-颐和山庄 交通便利周边配套齐采光好 1200 元/月；2400 元/月；2600 元/月</x:v>
+        <x:v>合租房单间约1300-2200元/月；20平），整租分散式公寓1室约1800-2200元/月；（25-30平），整租两居室约4000元/月</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>西北旺高品质小区租房_北京海淀西北旺高品质小区房屋出租-北京58同城。；58租房网，为您提供北京海淀西北旺高品质小区租房,西北旺高品质小区房屋出租,西北旺高品质小区整租，西北旺高品质小区合租信息。；58租房网，为您提供北京西北旺高品质小区租房,西北旺高品质小区房屋出租,西北旺高品质小区整租，西北旺高品质小区合租信息！；手机版： 西北旺高品质小区租房 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索。；# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;</x:v>
+        <x:v>装修多为全新精装修，配备品牌全新家电；；户型以一居室开间或合租单间为主，部分户型方正采光好；；有信息提到房间隔音效果较好，部分房源为低层/总层数2-6层建筑；；提供免费维修服务，楼内外有监控覆盖，部分物业可提供入住保洁、居住证办理等服务；；公开信息中未提及明确房龄；</x:v>
       </x:c>
       <x:c r="L72" t="str">
-        <x:v>* 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * [](https://bj.zf.58.com/) * [](https://bj.zf.58.com/zz/xibeiwang/) * [](https://bj.zf.58.com/hz/xibeiwang/) * [](https://bj.zf.58.com/gr/xibeiwang/) * [](https://bj.58.com/pinpaigongyu/) * [](https://bj.58.com/xq/) * [](https://bj.zf.58.com/zujin/) * 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 ## 西北旺租房房产中介 * 陈永胜 北京德佑嘉业住房租赁有限公司 * 于成 北京首嘉房住房租赁有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 田田 北京天通伟业房地产经纪有限公司 * 王成云 北京中恒建业住房租赁有限公司 * 郑莹莹 北京顺安家住房租赁有限公司 * 于意然 北京爱玛家房地产经纪有限公司 * 于占奎 万邦阿尔法（北京）住房租赁有限公司 * 严晓琴 北京嘉弘伟业房地产经纪有限公司 ## 租房房产问答 * 问 合租房都是多少钱？；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：西北旺公寓出租条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486950500_1.htm) 4室2厅百旺茉莉园2期 整租|4室2厅|251㎡|朝南北 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。；12000 元/月 [](https://www.fang.com/chuzu/3_486625663_1.htm) 立水桥地铁 茉莉园精装主卧独卫 19平朝西 四家两卫 合租主卧|3户合租|19㎡|朝南 海淀-西北旺-茉莉园 距16号线西北旺站约349米。；交通便利周边配套齐采光好 2500 元/月 [](https://www.fang.com/chuzu/3_486950501_1.htm) 2室2厅百旺茉莉园2期 整租|2室2厅|114㎡|朝南北 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。；交通便利周边配套齐采光好 1700 元/月 [](https://www.fang.com/chuzu/3_486707295_1.htm) 西北旺 永丰南 中关村集成电路设计园 用友产业园 颐 合租主卧|3户合租|15㎡|朝南 海淀-西北旺-颐和山庄 交通便利周边配套齐采光好 1200 元/月 [](https://www.fang.com/chuzu/3_486789909_1.htm) 西北旺茉莉园西里次卧出租 合租次卧|3户合租|15㎡|朝南 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。</x:v>
-      </x:c>
-      <x:c r="M72" t="str"/>
+        <x:v>通勤：临近地铁16号线西北旺站，周边公交便利，短距离可达中关村软件园、百度、网易、腾讯等互联网企业园区，通勤中关村、西二旗方便；；商超：周边有西北旺万象汇、超市、菜市场，购物买菜方便；；配套：周边覆盖餐饮、咖啡厅、健身房，医院、公园配套齐全，可满足日常需求；；搜索结果中多数房源标注为冷泉村住房、碧水家园等周边小区，未检索到目标地址「北京市海淀区德政路与西北旺一街交叉口西北150米」西北旺社区青年汇的直接匹配租房口碑信息，存在同名误命中、信息泛化的风险；</x:v>
+      </x:c>
+      <x:c r="M72" t="str">
+        <x:v>公开差评信息较少，未检索到集中负面评价。；公开差评信息较少，未检索到集中负面评价</x:v>
+      </x:c>
       <x:c r="N72" t="str">
-        <x:v>价格线索：21500 元/月；12000 元/月；交通便利周边配套齐采光好 2500 元/月；10200 元/月；交通便利周边配套齐采光好 1700 元/月；旺-颐和山庄 交通便利周边配套齐采光好 1200 元/月；2400 元/月；2600 元/月；房屋质量/户型线索：西北旺高品质小区租房_北京海淀西北旺高品质小区房屋出租-北京58同城。；58租房网，为您提供北京海淀西北旺高品质小区租房,西北旺高品质小区房屋出租,西北旺高品质小区整租，西北旺高品质小区合租信息。；58租房网，为您提供北京西北旺高品质小区租房,西北旺高品质小区房屋出租,西北旺高品质小区整租，西北旺高品质小区合租信息！；手机版： 西北旺高品质小区租房 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索。；# 【北京租房网_北京租房信息|房屋出租】- 房天下 [](https://www.fang.com/) 北京 北京上海广州深圳天津成都重庆武汉苏州杭州南京济南石家庄西安郑州无锡青岛南昌东莞大连昆明长春长沙福州南宁沈阳珠海香港更多城市&gt;&gt; 首页 新房 * 本月开盘 * 热门楼盘 * 本月交房 * 楼盘新动态 * 特价房 * 楼盘导购 * 新房排行榜 * 购房知识 * 看房团 * 特价房 二手房 * 在售房源 * 业主真房源 * 找小区 * 找别墅 * 查成交 * 二手房排行榜 * 购房知识 * 法拍房 * 我要卖房 * 直播看房 租房 * 在租房源 * 个人房源 * 整租房源 * 合租房源 * 别墅房源 * 租房知识 * 免费发布出租 查房价 探房笔记 装修家居 * 家装案例 * 装修攻略 * 家居圈 * 家居资讯 * 免费设计 * 免费验房 * 装修报价 商铺写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 写字楼楼盘 * 商铺出租 * 商铺出售 * 商铺新盘 * 商铺楼盘 海外房产 * 澳大利亚房产 * 新加坡房产 * 马来西亚房产 * 泰国房产 * 日本房产 * 阿联酋房产 资讯 * 房产快讯 * 房产问答 * 房产知识 * 房产圈 * 百科 直播看房 地产数据 * 房产交易 * 土地市场 * 研究报告 * 物业数据 * 数据商城 更多 * 土地 * 产业 * 中指云 * 地产数据 * 土地市场 * 研究报告 * 百城价格指数 * 地产文库 * 数据商城 * 业主论坛 * 精华帖 * 装修论坛 * 购房圈 * VR全景看房 * 加盟房天下 * 房天下视频 更多服务;；生活便利线索：* 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * [](https://bj.zf.58.com/) * [](https://bj.zf.58.com/zz/xibeiwang/) * [](https://bj.zf.58.com/hz/xibeiwang/) * [](https://bj.zf.58.com/gr/xibeiwang/) * [](https://bj.58.com/pinpaigongyu/) * [](https://bj.58.com/xq/) * [](https://bj.zf.58.com/zujin/) * 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 ## 西北旺租房房产中介 * 陈永胜 北京德佑嘉业住房租赁有限公司 * 于成 北京首嘉房住房租赁有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 田田 北京天通伟业房地产经纪有限公司 * 王成云 北京中恒建业住房租赁有限公司 * 郑莹莹 北京顺安家住房租赁有限公司 * 于意然 北京爱玛家房地产经纪有限公司 * 于占奎 万邦阿尔法（北京）住房租赁有限公司 * 严晓琴 北京嘉弘伟业房地产经纪有限公司 ## 租房房产问答 * 问 合租房都是多少钱？；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：西北旺公寓出租条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486950500_1.htm) 4室2厅百旺茉莉园2期 整租|4室2厅|251㎡|朝南北 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。；12000 元/月 [](https://www.fang.com/chuzu/3_486625663_1.htm) 立水桥地铁 茉莉园精装主卧独卫 19平朝西 四家两卫 合租主卧|3户合租|19㎡|朝南 海淀-西北旺-茉莉园 距16号线西北旺站约349米。；交通便利周边配套齐采光好 2500 元/月 [](https://www.fang.com/chuzu/3_486950501_1.htm) 2室2厅百旺茉莉园2期 整租|2室2厅|114㎡|朝南北 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。；交通便利周边配套齐采光好 1700 元/月 [](https://www.fang.com/chuzu/3_486707295_1.htm) 西北旺 永丰南 中关村集成电路设计园 用友产业园 颐 合租主卧|3户合租|15㎡|朝南 海淀-西北旺-颐和山庄 交通便利周边配套齐采光好 1200 元/月 [](https://www.fang.com/chuzu/3_486789909_1.htm) 西北旺茉莉园西里次卧出租 合租次卧|3户合租|15㎡|朝南 海淀-西北旺-百旺茉莉园 距16号线西北旺站约349米。</x:v>
+        <x:v>价格线索：合租房单间约1300-2200元/月；20平），整租分散式公寓1室约1800-2200元/月；（25-30平），整租两居室约4000元/月；房屋质量/户型线索：装修多为全新精装修，配备品牌全新家电；；户型以一居室开间或合租单间为主，部分户型方正采光好；；有信息提到房间隔音效果较好，部分房源为低层/总层数2-6层建筑；；提供免费维修服务，楼内外有监控覆盖，部分物业可提供入住保洁、居住证办理等服务；；公开信息中未提及明确房龄；；生活便利线索：通勤：临近地铁16号线西北旺站，周边公交便利，短距离可达中关村软件园、百度、网易、腾讯等互联网企业园区，通勤中关村、西二旗方便；；商超：周边有西北旺万象汇、超市、菜市场，购物买菜方便；；配套：周边覆盖餐饮、咖啡厅、健身房，医院、公园配套齐全，可满足日常需求；；搜索结果中多数房源标注为冷泉村住房、碧水家园等周边小区，未检索到目标地址「北京市海淀区德政路与西北旺一街交叉口西北150米」西北旺社区青年汇的直接匹配租房口碑信息，存在同名误命中、信息泛化的风险；；风险线索：公开差评信息较少，未检索到集中负面评价。；公开差评信息较少，未检索到集中负面评价</x:v>
       </x:c>
       <x:c r="O72" t="str">
-        <x:v>1. 西北旺高品质小区租房_北京海淀西北旺高品质小区房屋出租-北京58同城 http://mob.58.com/zf/cq/ssc-63/xibeiwang/
-2. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_252240bj/
-3. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-4. 北京公寓出租_北京精装公寓出租信息-北京链家找房 https://ifeng-m.lianjia.com/chuzu/bj/apartment/haidianqu/amp3ama0/
-5. 海淀组团内配租922套青年公寓 - 开放北京 https://open.beijing.gov.cn/html//haidian/gzdt/2025/6/1750038168814.html</x:v>
+        <x:v>1. ["西北旺（青年社区） 万象汇 中关村软件园 网易 百度 新浪","http://m.anjuke.com/bj/rent/4470610888629251-3/"]
+2. ["地铁16号线西北旺精装公寓 可直达中关村通勤西二旗，押一付一","http://m.anjuke.com/bj/rent/4581070293050371-3/"]
+3. ["北京西北旺租房子怎么样","https://m.kupet.cn/read-1774213832a47580088.html"]
+4. 西北旺（青年社区） 万象汇 中关村软件园 网易 百度 新浪 http://m.anjuke.com/bj/rent/4470610888629251-3/
+5. 西北旺超值整租！1800元每月，温馨独居公寓配套完善 http://m.anjuke.com/bj/rent/4543318725782531-3/
+6. 地铁16号线西北旺精装公寓 可直达中关村通勤西二旗，押一付一 http://m.anjuke.com/bj/rent/4581070293050371-3/
+7. 北京西北旺租房子怎么样 https://m.kupet.cn/read-1774213832a47580088.html
+8. 无中介 直签 创业单间 西北旺 万象汇 用友产业园 马连洼 http://m.anjuke.com/bj/rent/4588055098354689-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -3799,41 +3998,42 @@
         <x:v>黑山扈羊场1号</x:v>
       </x:c>
       <x:c r="E73" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F73" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G73" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H73" t="n">
-        <x:v>7.5</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="I73" t="str">
-        <x:v>邻近中关村软件园，租金区间跨度大，一居室5200元起，适合追求通勤效率的员工。</x:v>
+        <x:v>缺乏该地址直接证据，仅能参考周边配套，具体居住品质与租金存在较大不确定性。</x:v>
       </x:c>
       <x:c r="J73" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
+        <x:v>近）的租房价格：天秀花园安和园精装大两居9000元/月；黑山扈路临甲3号院的房源价格在1500-2700元/月</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>1居室·12个户型. 63㎡~73㎡. 在售325万起 ;；2居室·16个户型. 63㎡~93㎡. 在售498万起 ;；3居室·19个户型. 81㎡~131㎡. 在售430万起 ;；4居室·5个户型. 107㎡~123㎡. 在售960万起 ...。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;</x:v>
+        <x:v>搜索结果中未直接匹配「天秀北路10号」的租房信息，同区域（黑山扈路附近）的租房价格：天秀花园安和园精装大两居9000元/月，黑山扈路临甲3号院的房源价格在1500-2700元/月不等，多为整租公寓或小户型；；未找到「天秀北路10号」的房屋质量相关信息，同区域提及的房源特点：天秀花园安和园为精装修、普通住宅，房屋采光通风好；；黑山扈路临甲3号院多为精装修公寓，提供24小时维修服务，部分房源为实体墙（隔音较好），房龄等具体信息未明确；</x:v>
       </x:c>
       <x:c r="L73" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；地铁 10 号线与通往首都国际机场的机场快线无缝衔接，宛如一条条灵动的脉络，将 CBD 商... * 北京雅诗阁来福士中心服务公寓秋冬旅行在燕京,尊享之旅解锁老城秋日秘境 2025-11-15 * 北京财富中心千禧公寓将换牌，服务品质持续升级 2025年11月14日，北京财富中心千禧公寓发布重要公告，宣布因管理协议到期，公寓将进行品牌升级，自2026年1月起启用全新品牌名称“御金台国际公寓 @ 北京财富中心”，同时管理方也将发生变更。；管理协议到期，品牌管理方变更 据公告内容，北京财富中心千禧 2025-11-14 * 国贸公寓住进国贸CBD核心区带露台顶级公寓的非凡体验 2025-10-30 * 北京启皓会客厅公寓：意式奢居与京城风华的完美交融 2025-10-30 * 金隅酒管荣膺"2025中国住房租赁高端服务典范企业"：以品质与创新定义行业新标杆 2025-04-16 雅诗阁有限公司2025年成绩抢先看：全球拓展与中国市场多点突破 2025年，雅诗阁有限公司（以下简称“雅诗阁”）在全球旅宿业的舞台上大放异彩，凭借强大的增长韧性与高效的战略执行力，在项... * 福庭六周年感恩献礼：北京福庭酒店公寓的温情之旅,六载春秋，感恩同行 2025-12-13 * 拥有北京时尚的方式，是住在这里——三里屯一号公寓 在城市的宏大叙事中，家宛如一枚独特的徽章，承载着身份与生活的深刻注脚。</x:v>
-      </x:c>
-      <x:c r="M73" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；首先环境特别安静，隔音超棒，完全没有嘈杂噪音，晚上睡得特别安稳，睡眠浅也完全不用担心。</x:v>
-      </x:c>
+        <x:v>未找到「天秀北路10号」的生活便利信息，同区域配套：临近16号线地铁（步行约1400米），周边有超市、商场（如西北旺万象汇）、餐饮等，交通和基础生活设施便利，适合上班族，通勤至上地、清河等区域较方便；</x:v>
+      </x:c>
+      <x:c r="M73" t="str"/>
       <x:c r="N73" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：1居室·12个户型. 63㎡~73㎡. 在售325万起 ;；2居室·16个户型. 63㎡~93㎡. 在售498万起 ;；3居室·19个户型. 81㎡~131㎡. 在售430万起 ;；4居室·5个户型. 107㎡~123㎡. 在售960万起 ...。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；生活便利线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；地铁 10 号线与通往首都国际机场的机场快线无缝衔接，宛如一条条灵动的脉络，将 CBD 商... * 北京雅诗阁来福士中心服务公寓秋冬旅行在燕京,尊享之旅解锁老城秋日秘境 2025-11-15 * 北京财富中心千禧公寓将换牌，服务品质持续升级 2025年11月14日，北京财富中心千禧公寓发布重要公告，宣布因管理协议到期，公寓将进行品牌升级，自2026年1月起启用全新品牌名称“御金台国际公寓 @ 北京财富中心”，同时管理方也将发生变更。；管理协议到期，品牌管理方变更 据公告内容，北京财富中心千禧 2025-11-14 * 国贸公寓住进国贸CBD核心区带露台顶级公寓的非凡体验 2025-10-30 * 北京启皓会客厅公寓：意式奢居与京城风华的完美交融 2025-10-30 * 金隅酒管荣膺"2025中国住房租赁高端服务典范企业"：以品质与创新定义行业新标杆 2025-04-16 雅诗阁有限公司2025年成绩抢先看：全球拓展与中国市场多点突破 2025年，雅诗阁有限公司（以下简称“雅诗阁”）在全球旅宿业的舞台上大放异彩，凭借强大的增长韧性与高效的战略执行力，在项... * 福庭六周年感恩献礼：北京福庭酒店公寓的温情之旅,六载春秋，感恩同行 2025-12-13 * 拥有北京时尚的方式，是住在这里——三里屯一号公寓 在城市的宏大叙事中，家宛如一枚独特的徽章，承载着身份与生活的深刻注脚。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；首先环境特别安静，隔音超棒，完全没有嘈杂噪音，晚上睡得特别安稳，睡眠浅也完全不用担心。</x:v>
+        <x:v>价格线索：近）的租房价格：天秀花园安和园精装大两居9000元/月；黑山扈路临甲3号院的房源价格在1500-2700元/月；房屋质量/户型线索：搜索结果中未直接匹配「天秀北路10号」的租房信息，同区域（黑山扈路附近）的租房价格：天秀花园安和园精装大两居9000元/月，黑山扈路临甲3号院的房源价格在1500-2700元/月不等，多为整租公寓或小户型；；未找到「天秀北路10号」的房屋质量相关信息，同区域提及的房源特点：天秀花园安和园为精装修、普通住宅，房屋采光通风好；；黑山扈路临甲3号院多为精装修公寓，提供24小时维修服务，部分房源为实体墙（隔音较好），房龄等具体信息未明确；；生活便利线索：未找到「天秀北路10号」的生活便利信息，同区域配套：临近16号线地铁（步行约1400米），周边有超市、商场（如西北旺万象汇）、餐饮等，交通和基础生活设施便利，适合上班族，通勤至上地、清河等区域较方便；</x:v>
       </x:c>
       <x:c r="O73" t="str">
-        <x:v>1. 北京天秀花园澄秀园二手房|房价 - 贝壳 https://m.ke.com/bj/xiaoqu/1111027380062
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 天秀花园安和园租房,房屋出租信息,整租,合租-天秀花园安和园小区网-北京房天下 https://esf.fang.com/loupan/1010555745/chuzu/list/h316/
-4. 北京酒店式公寓-出租（长租、短租、月租）-北京服务式公寓预订网 https://www.yudinggongyu.com/
-5. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4121285797011471-3/
+2. http://m.anjuke.com/bj/rent/4114702952541185-3/
+3. https://m.58.com/bj/zufang/3975149875108879x.shtml
+4. http://m.anjuke.com/bj/rent/4537143839204359-3/
+5. http://m.anjuke.com/bj/rent/4353858797661190-3/?ad_type=z&amp;pagesource=12
+6. https://m.anjuke.com/bj/rent/3676397397122059-3/?ad_type=j&amp;pagesource=782
+7. http://m.anjuke.com/bj/rent/4507668402351111-3/
+8. 【多图】天秀花园安和园，马连洼租房，黑山扈路 天秀花园安和园 南北向精装大两居 和业主签约可长租，海淀租房 http://m.anjuke.com/bj/rent/4121285797011471-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -3850,41 +4050,42 @@
         <x:v>北京市海淀区马连洼北路8号院（马连洼地铁站A西北口步行350米）</x:v>
       </x:c>
       <x:c r="E74" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F74" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G74" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H74" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I74" t="str">
-        <x:v>证据多为海淀区泛化信息，缺乏该小区具体细节，评分较为保守。</x:v>
-      </x:c>
-      <x:c r="J74" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
-      </x:c>
+        <x:v>距离地铁极近，配套成熟且环境安静，租金符合区域水平，是高性价比的优选。</x:v>
+      </x:c>
+      <x:c r="J74" t="str"/>
       <x:c r="K74" t="str">
-        <x:v>承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？</x:v>
+        <x:v>月租方面，海淀马连洼梅园甲（即问题中“新梅甲”，属于同名近似小区）的整租房源，3室1厅1卫86㎡户型月租7800元，2室1厅1卫78㎡户型月租5200元，2室1厅1卫60㎡户型月租6200元，整体符合该区域租房价格水平。；房子质量：物业方面，小区有专业物业部门管理，规范有序；；装修以精装修为主；；户型多为南北朝向或东西朝向，采光较好；；未提及隔音差等明确问题，小区环境安静；</x:v>
       </x:c>
       <x:c r="L74" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。</x:v>
+        <x:v>未提及房龄具体数据，小区配套家电齐全。；生活便利程度：通勤便利，距离16号线马连洼站步行约256米，靠近公交站点；；商超配套有中发百旺商城、北京华联BHG Mall等，周边有菜市场，购物方便；；医疗资源有解放军总医院第八医学中心；；餐饮等生活配套齐全，休闲有城市森林公园。</x:v>
       </x:c>
       <x:c r="M74" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未提及隔音差等明确问题，小区环境安静；</x:v>
       </x:c>
       <x:c r="N74" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；生活便利线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区公寓租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](https://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>房屋质量/户型线索：月租方面，海淀马连洼梅园甲（即问题中“新梅甲”，属于同名近似小区）的整租房源，3室1厅1卫86㎡户型月租7800元，2室1厅1卫78㎡户型月租5200元，2室1厅1卫60㎡户型月租6200元，整体符合该区域租房价格水平。；房子质量：物业方面，小区有专业物业部门管理，规范有序；；装修以精装修为主；；户型多为南北朝向或东西朝向，采光较好；；未提及隔音差等明确问题，小区环境安静；；生活便利线索：未提及房龄具体数据，小区配套家电齐全。；生活便利程度：通勤便利，距离16号线马连洼站步行约256米，靠近公交站点；；商超配套有中发百旺商城、北京华联BHG Mall等，周边有菜市场，购物方便；；医疗资源有解放军总医院第八医学中心；；餐饮等生活配套齐全，休闲有城市森林公园。；风险线索：未提及隔音差等明确问题，小区环境安静；</x:v>
       </x:c>
       <x:c r="O74" t="str">
-        <x:v>1. 2023年8月北京海淀区公租房价格一览表- 北京本地宝 https://bj.bendibao.com/zffw/2023821/351359.shtm
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://www.fang.com/houses/zf_254312bj/
-4. 北京房产网_北京二手房|租房|新房|房地产信息网【北京贝壳找房】 https://ke.com/
-5. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/45755000024524836491-3/
+2. https://bj.zu.anjuke.com/fangyuan/4240509559201792
+3. 马连洼 梅园甲三居室 随时入住 可合租 出行方便 业主直签 http://m.anjuke.com/bj/rent/4575500002452483-3/
+4. Quality 奢华法式复古风|全屋高端定制|马戏城久光商圈 http://m.anjuke.com/sh/rent/4597559794836491-3/
+5. 马连洼梅园甲 精装两居 包物业取暖实房配置齐 跟业主签可长租 http://m.anjuke.com/bj/rent/4363473630782465-3/
+6. 三房——宽居享静谧，出行自悠然，新梅公寓 http://m.anjuke.com/sh/rent/4525764917849099-3/
+7. 【多图】梅园甲，马连洼租房，马连洼梅园甲 干净两居 低楼层 价格可谈 跟业主签约 可长租，海淀租房 https://bj.zu.anjuke.com/fangyuan/4240509559201792
+8. 【多图】新梅公寓(一期)，古美罗阳租房，1号线外环路站旁 近中庚漫游城 莲花国际 南方商城 红象汇，闵行租房 https://sh.zu.anjuke.com/fangyuan/4160806281931778</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -3901,38 +4102,42 @@
         <x:v>北京市海淀区永丰中路99号</x:v>
       </x:c>
       <x:c r="E75" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F75" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G75" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H75" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I75" t="str">
-        <x:v>位于海淀区，配套信息较全，但具体租金及居住体验证据有限。</x:v>
+        <x:v>租金门槛较低，生活配套齐全，但房龄较老且多为步梯房，距离地铁站稍远。</x:v>
       </x:c>
       <x:c r="J75" t="str">
-        <x:v>8000_ 元/m² 颐和山庄，小区价格31198元/㎡</x:v>
+        <x:v>整租方面，1室1厅30㎡月租约3000元/月；，2室1厅85㎡复式月租5000元/月；，2室2厅80㎡月租4700元/月；合租方面，主卧20㎡月租1800元/月；，别墅1室1厅35㎡月租2900元/月；，价格区间约1800-5000元/月</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **71017** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.35% 贷款计算器 * 最近成交 0套 * 楼栋总数 47栋 * 房屋总数 10000户 * 建筑类型 板楼 * 建筑年代 2001年建成 * 小区位置 永丰中路99号地图 * 物业公司 北京同力物业管理有限责任公司 * 开发商 北京同力盛业责任有限公司 #### 推荐经纪人 ##### 王立新 评分：4.6 从业信息卡 百科 闪电回复 ### 颐和山庄房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 颐和山庄 海淀·西北旺**71018** 元/㎡ * #### 碧水家园 海淀·西北旺**71018** 元/㎡ * #### 西六砖瓦厂 海淀·西北旺**43740** 元/㎡ * #### 宏丰西路1号院 海淀·西北旺**待定** * #### 西六建材工贸宿舍 海淀·西北旺**53763** 元/㎡ ### 相关资讯 * 小区资讯北京颐和山庄怎么样?；北京吉屋网提供北京颐和山庄二手房出售信息、颐和山庄二手房价格，包括及时更新北京颐和山庄二手房房源、价格走势、户型图、业主论坛、生活配套。；# 颐和山庄_北京颐和山庄小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_颐和山庄 更新于 2026-06-01 10:55:14 [](https://bj.jiwu.com/tu/4232947.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/4232948.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722958.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722959.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722960.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722961.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722962.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722963.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722964.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722965.html "颐和山庄实景图图片") # 颐和山庄 别名：颐和山庄 加入本地买房群 关注 _北京 - 海淀 - 永丰中路99号_ 发地址到手机 参考均价 _31198 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2001_ 小区户数 _1884_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-57群（329） * 大家觉得这里未来发展怎么样？；加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(1)3室(1) 全部户型 [](https://bj.jiwu.com/huxing/686607.html "颐和山庄3室1厅1卫117㎡户型图")3室1厅1卫 117㎡咨询户型房源 [](https://bj.jiwu.com/huxing/686608.html "颐和山庄2室1厅1卫90㎡户型图")2室1厅1卫 90㎡咨询户型房源 小区评测报告 ？</x:v>
+        <x:v>合租方面，主卧20㎡月租1800元/月，别墅1室1厅35㎡月租2900元/月，价格区间约1800-5000元/月，不同户型、面积、装修的房源月租差异较大。；房龄：该小区颐和山庄（海淀区）1998年建成，部分房源描述为步梯房；；装修：精装修房源较多，部分房源配备全新家具家电；；隔音：部分房源提到卧室不紧挨，隔音效果好；；物业：小区有24小时安保巡视，物业负责；</x:v>
       </x:c>
       <x:c r="L75" t="str">
-        <x:v>北京吉屋网提供北京颐和山庄二手房出售信息、颐和山庄二手房价格，包括及时更新北京颐和山庄二手房房源、价格走势、户型图、业主论坛、生活配套。；# 颐和山庄_北京颐和山庄小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_颐和山庄 更新于 2026-06-01 10:55:14 [](https://bj.jiwu.com/tu/4232947.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/4232948.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722958.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722959.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722960.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722961.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722962.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722963.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722964.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722965.html "颐和山庄实景图图片") # 颐和山庄 别名：颐和山庄 加入本地买房群 关注 _北京 - 海淀 - 永丰中路99号_ 发地址到手机 参考均价 _31198 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2001_ 小区户数 _1884_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-57群（329） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 感谢群主的推荐，很匹配我的诉求哇 * 看了群主发的区域解读，受益良多啊 * 都在说是上车好时候，大家怎么看啊 * 最近都说是上车好时候，大家怎么看 加入北京交流群，掌握一手楼市信息 加入群聊 小区问答 * 问 颐和山庄优势有哪些？；答 颐和山庄的优势有1、颐和山庄地段位于永丰中路99号，交通设施便利，生活便捷。</x:v>
+        <x:v>通勤：临近地铁16号线西北旺站，步行约1800-1900米，周边有449路、697路等公交线路；；商超：步行可达颐和乐超市、鲜美多生鲜超市，附近有西北旺万象汇（约1.6公里）；；医院：周边有颐和山庄门诊部，距离309医院两站地；；餐饮：小区周边有川渝小厨、山西面馆等各类餐饮店铺；；生活配套：附近有五一渠生态滨河公园等多个公园，银行、邮局等设施齐全。</x:v>
       </x:c>
       <x:c r="M75" t="str"/>
       <x:c r="N75" t="str">
-        <x:v>价格线索：8000_ 元/m² 颐和山庄，小区价格31198元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) [](https://esf.fang.com/loupan/1010170365/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **71017** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.35% 贷款计算器 * 最近成交 0套 * 楼栋总数 47栋 * 房屋总数 10000户 * 建筑类型 板楼 * 建筑年代 2001年建成 * 小区位置 永丰中路99号地图 * 物业公司 北京同力物业管理有限责任公司 * 开发商 北京同力盛业责任有限公司 #### 推荐经纪人 ##### 王立新 评分：4.6 从业信息卡 百科 闪电回复 ### 颐和山庄房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 颐和山庄 海淀·西北旺**71018** 元/㎡ * #### 碧水家园 海淀·西北旺**71018** 元/㎡ * #### 西六砖瓦厂 海淀·西北旺**43740** 元/㎡ * #### 宏丰西路1号院 海淀·西北旺**待定** * #### 西六建材工贸宿舍 海淀·西北旺**53763** 元/㎡ ### 相关资讯 * 小区资讯北京颐和山庄怎么样?；北京吉屋网提供北京颐和山庄二手房出售信息、颐和山庄二手房价格，包括及时更新北京颐和山庄二手房房源、价格走势、户型图、业主论坛、生活配套。；# 颐和山庄_北京颐和山庄小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_颐和山庄 更新于 2026-06-01 10:55:14 [](https://bj.jiwu.com/tu/4232947.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/4232948.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722958.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722959.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722960.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722961.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722962.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722963.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722964.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722965.html "颐和山庄实景图图片") # 颐和山庄 别名：颐和山庄 加入本地买房群 关注 _北京 - 海淀 - 永丰中路99号_ 发地址到手机 参考均价 _31198 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2001_ 小区户数 _1884_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-57群（329） * 大家觉得这里未来发展怎么样？；加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 2室(1)3室(1) 全部户型 [](https://bj.jiwu.com/huxing/686607.html "颐和山庄3室1厅1卫117㎡户型图")3室1厅1卫 117㎡咨询户型房源 [](https://bj.jiwu.com/huxing/686608.html "颐和山庄2室1厅1卫90㎡户型图")2室1厅1卫 90㎡咨询户型房源 小区评测报告 ？；生活便利线索：北京吉屋网提供北京颐和山庄二手房出售信息、颐和山庄二手房价格，包括及时更新北京颐和山庄二手房房源、价格走势、户型图、业主论坛、生活配套。；# 颐和山庄_北京颐和山庄小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_海淀小区_&gt;_颐和山庄 更新于 2026-06-01 10:55:14 [](https://bj.jiwu.com/tu/4232947.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/4232948.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722958.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722959.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722960.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722961.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722962.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722963.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722964.html "颐和山庄实景图图片")[](https://bj.jiwu.com/tu/3722965.html "颐和山庄实景图图片") # 颐和山庄 别名：颐和山庄 加入本地买房群 关注 _北京 - 海淀 - 永丰中路99号_ 发地址到手机 参考均价 _31198 \_元/㎡\__ 咨询成交价 物业类型 _公寓_ 建成时间 _2001_ 小区户数 _1884_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-57群（329） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 感谢群主的推荐，很匹配我的诉求哇 * 看了群主发的区域解读，受益良多啊 * 都在说是上车好时候，大家怎么看啊 * 最近都说是上车好时候，大家怎么看 加入北京交流群，掌握一手楼市信息 加入群聊 小区问答 * 问 颐和山庄优势有哪些？；答 颐和山庄的优势有1、颐和山庄地段位于永丰中路99号，交通设施便利，生活便捷。</x:v>
+        <x:v>价格线索：整租方面，1室1厅30㎡月租约3000元/月；，2室1厅85㎡复式月租5000元/月；，2室2厅80㎡月租4700元/月；合租方面，主卧20㎡月租1800元/月；，别墅1室1厅35㎡月租2900元/月；，价格区间约1800-5000元/月；房屋质量/户型线索：合租方面，主卧20㎡月租1800元/月，别墅1室1厅35㎡月租2900元/月，价格区间约1800-5000元/月，不同户型、面积、装修的房源月租差异较大。；房龄：该小区颐和山庄（海淀区）1998年建成，部分房源描述为步梯房；；装修：精装修房源较多，部分房源配备全新家具家电；；隔音：部分房源提到卧室不紧挨，隔音效果好；；物业：小区有24小时安保巡视，物业负责；；生活便利线索：通勤：临近地铁16号线西北旺站，步行约1800-1900米，周边有449路、697路等公交线路；；商超：步行可达颐和乐超市、鲜美多生鲜超市，附近有西北旺万象汇（约1.6公里）；；医院：周边有颐和山庄门诊部，距离309医院两站地；；餐饮：小区周边有川渝小厨、山西面馆等各类餐饮店铺；；生活配套：附近有五一渠生态滨河公园等多个公园，银行、邮局等设施齐全。</x:v>
       </x:c>
       <x:c r="O75" t="str">
-        <x:v>1. 【北京颐和山庄小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010170365.htm
-2. 颐和山庄_北京颐和山庄小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/170133.html
-3. 龙湖颐和原著 - 丽兹豪宅网 https://msh.lizihang.com/loupan/597585.html
-4. 房产-北京本地宝 https://m.bj.bendibao.com/zffw/list_15_294_69.htm</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4604997944927234-3/
+2. http://m.anjuke.com/bj/rent/4551574290508815-3/
+3. http://m.fang.com/zf/bj/1_61406834.html
+4. http://m.anjuke.com/bj/rent/4599989286296590-3/
+5. http://m.anjuke.com/zixing/rent/4514542826707972-3/
+6. 海淀西北旺 颐和山庄主卧 近用友 中关村壹号 软件园 万象汇 http://m.anjuke.com/bj/rent/4604997944927234-3/
+7. 颐和山庄 紫霄园 两居室 复式 配套齐全 业主之前婚房 http://m.anjuke.com/bj/rent/4551574290508815-3/
+8. 海淀西北旺颐和山庄 1室1厅 30㎡ 3000元/月 http://m.fang.com/zf/bj/1_61406834.html</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -3949,39 +4154,42 @@
         <x:v>北京市海淀区马连洼街道</x:v>
       </x:c>
       <x:c r="E76" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F76" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G76" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H76" t="n">
-        <x:v>4.5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I76" t="str">
-        <x:v>搜索结果包含大量异地及泛化信息，缺乏针对该社区的有效证据。</x:v>
+        <x:v>地理位置优越，租金性价比高，户型采光好，适合在网易及周边大厂工作的员工。</x:v>
       </x:c>
       <x:c r="J76" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
+        <x:v>马连洼菊园社区租房：整租两居室5800-6000元/月；㎡，精装修，2026年5月更新）、一居室5500元/月；合租次卧2100元/月</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>“公寓有36平方米到124平方米的多样化户型，家电齐全，配备了智能管理系统，以低于周边市场价30%的租金定价，新市民、青年人等可‘拎包入住’。；” 徐萍介绍，这个保障性租赁住房项目很受欢迎，单身公寓户型长期供不应求，已成为吴中区新市民和青年人安居的优选居住小区。；北京昌平区—— “好房子”，让居住品质再升级 本报记者 李建广 傍晚，阳光漫过转角阳台，将斑驳的光影洒向卧室、洒进客厅。；在北京城区的老房子住了20多年，“70多平方米小三居，没客厅，隔音差，朝向也不好。；”刘先生畅想着入住后的新生活：打开智能面板，一键可控制全屋空调、新风和地暖系统，接入小区智慧系统，可以实现一键呼梯、智联物业等。</x:v>
+        <x:v>海淀区马连洼菊园社区租房：整租两居室5800-6000元/月（面积59.7-64.3㎡，精装修，2026年5月更新）、一居室5500元/月（2024年9月更新，房源真实）；；海淀区马连洼菊园社区：房源为普通住宅，房龄未提及；；户型多为南北通透采光好，精装修，家具家电齐全；；未提及隔音效果；；物业情况未公开；</x:v>
       </x:c>
       <x:c r="L76" t="str">
-        <x:v>——编 者 江苏苏州市—— 青年公寓，为新市民打造梦的港湾 本报记者 姚雪青 租住50平方米的精装单身公寓，24小时管家服务，楼下有超市，门口是公交……对00后苏州新市民孙倩来说，这就是“梦的港湾”。；1号楼的青年会客厅配套了共享洗衣房、瑜伽室、自习室，每周举办非遗展示、手工绘图、夜校读书会等活动；；2022年，为满足周边产业园区及科创企业青年的住房需求，区属国资企业出资回购，盘活存量房资源，将其转型为保障性租赁住房项目。；“公寓有36平方米到124平方米的多样化户型，家电齐全，配备了智能管理系统，以低于周边市场价30%的租金定价，新市民、青年人等可‘拎包入住’。；”刘先生畅想着入住后的新生活：打开智能面板，一键可控制全屋空调、新风和地暖系统，接入小区智慧系统，可以实现一键呼梯、智联物业等。</x:v>
-      </x:c>
-      <x:c r="M76" t="str">
-        <x:v>在北京城区的老房子住了20多年，“70多平方米小三居，没客厅，隔音差，朝向也不好。；不仅如此，小区内违建成风，公共区域被私人‘圈占’，导致居民停车难、出行难，活动空间受限。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
-      </x:c>
+        <x:v>附近有购物中心、超市、医院（待确认具体医院）；</x:v>
+      </x:c>
+      <x:c r="M76" t="str"/>
       <x:c r="N76" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：“公寓有36平方米到124平方米的多样化户型，家电齐全，配备了智能管理系统，以低于周边市场价30%的租金定价，新市民、青年人等可‘拎包入住’。；” 徐萍介绍，这个保障性租赁住房项目很受欢迎，单身公寓户型长期供不应求，已成为吴中区新市民和青年人安居的优选居住小区。；北京昌平区—— “好房子”，让居住品质再升级 本报记者 李建广 傍晚，阳光漫过转角阳台，将斑驳的光影洒向卧室、洒进客厅。；在北京城区的老房子住了20多年，“70多平方米小三居，没客厅，隔音差，朝向也不好。；”刘先生畅想着入住后的新生活：打开智能面板，一键可控制全屋空调、新风和地暖系统，接入小区智慧系统，可以实现一键呼梯、智联物业等。；生活便利线索：——编 者 江苏苏州市—— 青年公寓，为新市民打造梦的港湾 本报记者 姚雪青 租住50平方米的精装单身公寓，24小时管家服务，楼下有超市，门口是公交……对00后苏州新市民孙倩来说，这就是“梦的港湾”。；1号楼的青年会客厅配套了共享洗衣房、瑜伽室、自习室，每周举办非遗展示、手工绘图、夜校读书会等活动；；2022年，为满足周边产业园区及科创企业青年的住房需求，区属国资企业出资回购，盘活存量房资源，将其转型为保障性租赁住房项目。；“公寓有36平方米到124平方米的多样化户型，家电齐全，配备了智能管理系统，以低于周边市场价30%的租金定价，新市民、青年人等可‘拎包入住’。；”刘先生畅想着入住后的新生活：打开智能面板，一键可控制全屋空调、新风和地暖系统，接入小区智慧系统，可以实现一键呼梯、智联物业等。；风险线索：在北京城区的老房子住了20多年，“70多平方米小三居，没客厅，隔音差，朝向也不好。；不仅如此，小区内违建成风，公共区域被私人‘圈占’，导致居民停车难、出行难，活动空间受限。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：马连洼菊园社区租房：整租两居室5800-6000元/月；㎡，精装修，2026年5月更新）、一居室5500元/月；合租次卧2100元/月；房屋质量/户型线索：海淀区马连洼菊园社区租房：整租两居室5800-6000元/月（面积59.7-64.3㎡，精装修，2026年5月更新）、一居室5500元/月（2024年9月更新，房源真实）；；海淀区马连洼菊园社区：房源为普通住宅，房龄未提及；；户型多为南北通透采光好，精装修，家具家电齐全；；未提及隔音效果；；物业情况未公开；；生活便利线索：附近有购物中心、超市、医院（待确认具体医院）；</x:v>
       </x:c>
       <x:c r="O76" t="str">
-        <x:v>1. 我们的美丽城市 我们的宜居家园（产经观察） https://paper.people.com.cn/rmrb/pc/content/202507/23/content_30089825.html
-2. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-3. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4580107748895756-3/
+2. http://m.anjuke.com/bj/rent/4592589039709186-3/
+3. http://m.anjuke.com/bj/rent/3699108603502600-3/
+4. http://m.anjuke.com/bj/rent/3730782738980872-3/
+5. 上新了 马连洼地铁站 菊园南北通透两居室 随时可以看房啦 http://m.anjuke.com/bj/rent/4580107748895756-3/
+6. 菊园社区 3室2厅1卫 http://m.anjuke.com/zmd/rent/4063217511558151-2/
+7. 【多图】菊园，马连洼租房，马连洼菊园 南北一居室 实房实图 配套齐全 和业主签约可长租，海淀租房 https://m.anjuke.com/bj/rent/3699108603502600-3/
+8. 保租房 月付 菊园社区大社区！嘉定西300米民用水电 http://m.anjuke.com/sh/rent/4507838825980934-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -3998,40 +4206,44 @@
         <x:v>北京市海淀区土井村社区路</x:v>
       </x:c>
       <x:c r="E77" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F77" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G77" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H77" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H77" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="I77" t="str">
-        <x:v>缺乏小区特异性证据，仅有海淀区大范围参考价格，建议实地考察。</x:v>
+        <x:v>缺乏该小区的直接有效信息，存在名称混淆风险，建议实地核实后再做决策。</x:v>
       </x:c>
       <x:c r="J77" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
+        <x:v>域土井村路周边万和嘉园等小区一居室月租约4700元/月</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？</x:v>
+        <x:v>未找到「晨间花园」该地址下的房子质量相关（隔音、户型、房龄、装修、物业）信息，同区域周边小区如万和嘉园为精装修、安保严格（进出需门禁）、双周保洁，但该信息非「晨间花园」本身；</x:v>
       </x:c>
       <x:c r="L77" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区附近租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。</x:v>
+        <x:v>未找到目标小区「晨间花园」在北京市海淀区土井村社区路的明确月租信息，同区域土井村路周边万和嘉园等小区一居室月租约4700元/月，存在一定价格参考；；未找到「晨间花园」该地址下的房子质量相关（隔音、户型、房龄、装修、物业）信息，同区域周边小区如万和嘉园为精装修、安保严格（进出需门禁）、双周保洁，但该信息非「晨间花园」本身；；未找到「晨间花园」该地址的通勤、地铁、商超等便利信息，同区域土井村路周边有唐家岭新城公交站（换乘495、447等线路），商超、餐饮等生活配套较齐全，邻近商圈及医院等资源；</x:v>
       </x:c>
       <x:c r="M77" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>未找到「晨间花园」该地址相关的租房差评或风险信息，但搜索结果中出现「晨月园」「星晨花园」「晨曦花园」等同名/相似名称的其他小区房源，需注意区分非目标小区信息。；未找到「晨间花园」该地址相关的租房差评或风险信息，但搜索结果中出现「晨月园」「星晨花园」「晨曦花园」等同名/相似名称的其他小区房源，需注意区分非目标小区信息</x:v>
       </x:c>
       <x:c r="N77" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；生活便利线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 # 海淀整租房 查看更多 * 5500 元整租西直门交大东路4号院1室1厅 1室1厅 / 55.34㎡ 推荐理由： 独卫一居 精装修 * 25000 元整租西直门远洋风景3室2厅 3室2厅 / 160.67㎡ 推荐理由： 邻地铁 精装修 * 10600 元双榆树满庭芳园中楼层2居室 2室1厅 / 87.4㎡ 推荐理由： 邻地铁 * 5800 元我爱我家相寓 田村西木小区低楼层2居室 2室1厅 / 45.3㎡ 推荐理由： 邻地铁 精装修 * 8200 元双榆树知春路52号院低楼层2居室 2室1厅 / 61.8㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 11400 元我爱我家相寓 中关村东南小区低楼层3居室 3室1厅 / 71.7㎡ 推荐理由： 邻地铁 押一付一 配套齐全 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 2300 元16号线整租公寓通勤华为北研所，荣耀，用友，百度腾讯 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 3200 元西二旗领秀新硅谷2号院中楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 3300 元我爱我家相寓 西直门交大东路56号院低楼层3居室主卧 3室1厅 / 15.0㎡ 推荐理由： 邻地铁 押一付一 精装修 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：小高层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：小高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：小高层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 张腾冲 北京麦田房产经纪有限公司 * 赵超 北京相寓住房租赁有限公司 * 刘海兵 北京锦秀前程住房租赁有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 刘馨泽 北京美丽新居房地产经纪有限公司 * 郭世超 北京我爱我家房地产经纪有限公司 * 杜亚兵 北京相寓住房租赁有限公司 * 田敬云 北京烁巢房地产经纪有限公司 * 吕江淼 北京中润置家住房租赁有限公司 * 叶春旭 北京相寓住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 星梦： 您好，转租需要先征得业主的同意，然后可以自己在网上发布信息也可以委托到周边中介公司。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：北京海淀区附近租房条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486863817_1.htm) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 距10号线火器营站约436米。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 梅州租房网 * 酒泉租房网 * 三沙租房网 * 开封租房网 * 宜都租房网 * 广水租房网 * 正定租房网 * 分宜租房网 * 枣庄租房网 * 乐清租房网 * 北京周边租房网 * 顺义租房网 * 东城租房网 * 房山租房网 * 通州租房网 * 海淀租房网 * 怀柔租房网 * 密云租房网 * 丰台租房网 * 门头沟租房网 * 渤海镇租房网 * 怀柔城区租房网 * 怀柔周边租房网 * 庙城租房网 * 桥梓租房网 * 雁栖租房网 * 安定门租房网 * 北京站租房网 * 北新桥租房网 * 朝阳门租房网 * 崇文门租房网 * 八里桥租房网 * 长阳租房网 * 不老屯租房网 * 城子街道租房网 * 东方太阳城租房网 * 安宁庄租房网 * 北大地租房网 * 保定租房网 * 汝州租房 * 沈丘租房 * 天门租房 * 磁县租房 * 宝鸡租房 * 汝州出租 * 沈丘出租 * 天门出租 * 磁县出租 * 宝鸡出租 * 汝州整租房 * 沈丘整租房 * 天门整租房 * 磁县整租房 * 宝鸡整租房 * 汝州合租房 * 沈丘合租房 * 天门合租房 * 磁县合租房 * 宝鸡合租房 * 汝州个人 * 沈丘个人 * 天门个人 * 磁县个人 * 宝鸡个人 * 北京周边租房 * 顺义租房 * 东城租房 * 房山租房 * 通州租房 * 北京周边出租 * 顺义出租 * 东城出租 * 房山出租 * 通州出租 * 北京周边整租房 * 顺义整租房 * 东城整租房 * 房山整租房 * 通州整租房 * 北京周边合租房 * 顺义合租房 * 东城合租房 * 房山合租房 * 通州合租房 * 北京两室两厅租房 * 北京平房租房 * 北京25平米租房 * 北京40平米租房 * 北京110平米租房 * 北京130平米租房 * 北京170平米租房 * 北京200平米租房 * 北京复式租房 * 北京公园附近租房 * 北京公交站点附近租房 * 北京loft租房 * 北京家电齐全租房 * 北京幼儿园附近租房 * 北京中学附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：域土井村路周边万和嘉园等小区一居室月租约4700元/月；房屋质量/户型线索：未找到「晨间花园」该地址下的房子质量相关（隔音、户型、房龄、装修、物业）信息，同区域周边小区如万和嘉园为精装修、安保严格（进出需门禁）、双周保洁，但该信息非「晨间花园」本身；；生活便利线索：未找到目标小区「晨间花园」在北京市海淀区土井村社区路的明确月租信息，同区域土井村路周边万和嘉园等小区一居室月租约4700元/月，存在一定价格参考；；未找到「晨间花园」该地址下的房子质量相关（隔音、户型、房龄、装修、物业）信息，同区域周边小区如万和嘉园为精装修、安保严格（进出需门禁）、双周保洁，但该信息非「晨间花园」本身；；未找到「晨间花园」该地址的通勤、地铁、商超等便利信息，同区域土井村路周边有唐家岭新城公交站（换乘495、447等线路），商超、餐饮等生活配套较齐全，邻近商圈及医院等资源；；风险线索：未找到「晨间花园」该地址相关的租房差评或风险信息，但搜索结果中出现「晨月园」「星晨花园」「晨曦花园」等同名/相似名称的其他小区房源，需注意区分非目标小区信息。；未找到「晨间花园」该地址相关的租房差评或风险信息，但搜索结果中出现「晨月园」「星晨花园」「晨曦花园」等同名/相似名称的其他小区房源，需注意区分非目标小区信息</x:v>
       </x:c>
       <x:c r="O77" t="str">
-        <x:v>1. 2023年8月北京海淀区公租房价格一览表- 北京本地宝 https://bj.bendibao.com/zffw/2023821/351359.shtm
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 【北京租房网_北京租房信息|房屋出租】- 房天下 http://www.fang.com/houses/zf_254201bj/
-4. P020260519600520806930.pdf https://www.cscec.com/tzzgxnew/ESGbg/esghw/202605/P020260519600520806930.pdf</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4600783621155852-3/
+2. http://m.fang.com/zf/bj/3_480141586.html
+3. http://m.anjuke.com/cang/rent/4603626875331597-3/
+4. https://bj.city8.com/885z2x821j8hb00586_address
+5. 晨月园 2室1厅1卫 家电齐全 阳光充足 http://m.anjuke.com/bj/rent/4600783621155852-3/
+6. 星晨花园(一期) 2室2厅1卫 http://m.anjuke.com/cd/rent/4375583135996941/
+7. 唐家岭 万和嘉园 图景嘉园 一居室 开间 随时入住 http://m.fang.com/zf/bj/3_480141586.html
+8. 月付 没有中介 只交电费 晨曦花园 国富中心 东体意明 http://m.anjuke.com/cang/rent/4603626875331597-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -4048,41 +4260,44 @@
         <x:v>北京市海淀区竹园西街兰园小区东北侧</x:v>
       </x:c>
       <x:c r="E78" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F78" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G78" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H78" t="n">
-        <x:v>7.2</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I78" t="str">
-        <x:v>离网易极近且租金极低，但多为老旧小区，存在停车难和噪音风险，适合预算有限者。</x:v>
+        <x:v>租金极具优势且配套成熟，但房龄超50年，需警惕设施老旧及居住品质。</x:v>
       </x:c>
       <x:c r="J78" t="str">
-        <x:v>洼-万德嘉园 交通便利周边配套齐采光好 3000 元/月；交通便利 2500 元/月；交通便利周边配套齐采光好 1200 元/月；连洼-芳怡园 交通便利周边配套齐采光好 1800 元/月；交通便利周边配套齐采光好 2000 元/月；交通便利周边配套齐采光好 2200 元/月；洼-万德嘉园 交通便利周边配套齐采光好 1000 元/月；社区(北区) 交通便利周边配套齐采光好 1500 元/月</x:v>
+        <x:v>（兰园/马连洼片区）租房月租：整租1室约1500元/月；（物业自持，无中介），2室约5900-6800元/月</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>) 北京房产网&gt;北京租房网&gt; 北京租房&gt; 海淀租房&gt; 马连洼租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * 方正 * 延寿 * 木兰 * 垫江 * 綦江 * 南川 * 梁平 * 万盛 * 奉节 * 云阳 * 丰都 * 彭水 * 忠县 * 秀山 * 黔江 * 武隆 * 巫山 * 石柱 * 酉阳 * 城口 * 巫溪 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 # 马连洼出租租房房源 * 2200 元裕和嘉园次卧 上地清河 软件园二期 滴滴湾流 小米元中心百度 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 南北通透 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 2800 元我爱我家相寓 马连洼丰泽盈和中楼层3居室主卧 3室1厅 / 19.5㎡ 推荐理由： 邻地铁 * 6500 元业主直签 裕隆新村精装两居室 实图拍摄 家具齐全 随时入住 2室1厅 / 80.22㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 9300 元南北通透 3室2厅 博雅西园 3室2厅 / 110.0㎡ 推荐理由： 邻地铁 * 8500 元树村丽景苑 2室2厅1卫 南北通透 集中供暖 2室2厅 / 94㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 随时看房 * 6600 元整租马连洼菊园2室1厅 2室1厅 / 53.9㎡ 推荐理由： 邻地铁 精装修 * 5400 元大有北里精致一居室干净整洁近安河桥北地铁中关村颐和园 1室1厅 / 49㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 有阳台 首次出租 * 7200 元万树园 精装南北通透2居室 长租稳定 家电齐全 随时看房 2室1厅 / 89.58㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1500 元山水小区大次卧 近地铁包物业取暖 中关村软件园 16号线直达 7室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6000 元马连洼梅园 精装两居 实房实图 跟业主签约 配套全齐 可长租 2室1厅 / 65.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 8600 元4号线安河桥北 天秀花园安和园精装三居室 价格可谈 随时看房 3室1厅 / 102.75㎡ 推荐理由： 邻地铁 精装修 随时看房 * 1500 元整租| 海淀小单间 实图实价房主直签 近地铁13号线上地清河 1室0厅 / 13㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 随时看房 * 1500 元首月立减！；隔音好！；1室0厅 / 15㎡ 推荐理由： 独卫一居 押一付一 配套齐全 南北通透 随时看房 * 5300 元毕业季 0押月付 整租 马连洼 裕和嘉园1室1厅 1室1厅 / 47.48㎡ 推荐理由： 独卫一居 精装修 * 2000 元手慢无 绿苑小区 正规次卧 可短签 农大南路 马连洼 可月付 3室1厅 / 10㎡ 推荐理由： 可短租 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 7400 元农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 2室1厅 / 75㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 5900 元明厨明卫 马连洼梅园 精装两局 中间楼层 价格可谈 跟签 2室1厅 / 63.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 1950 元首月减免 近万霖大厦 百度科技园 农大西校区 字节跳动软件园 3室1厅 / 13㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 2100 元西北旺 中关村软件园 百度 网易 东馨园 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 19000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 6800 元农大南路 农大西小区圆明园西路3号院精装三居室 和业主签约 3室1厅 / 60.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5100 元农大对面 3号院一居 干净整洁 采光超好 价格可谈 交通便利 1室1厅 / 42㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6000 元东北旺 东馨园 精装两居 实房实图 跟业主签约 配套全可长租 2室1厅 / 59.90㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 9500 元南北通透 3室1厅 百旺家苑 3室1厅 / 104.55㎡ 推荐理由： 邻地铁 * 2300 元东北旺 临近滴滴大厦 软通动力 软件园一二期 出租主卧 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 5200 元马连洼 柳浪北里 精装一居室 配套齐全 上地三街 万霖大厦 1室1厅 / 46.25㎡ 推荐理由： 独卫一居 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 8500 元业主直签 树村丽景苑小区 集中供暖 精装两居室 随时入住 2室1厅 / 84.00㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 随时看房 * 2600 元马连洼植保所农大西校区万霖大厦字节跳动软件园药用植物研究所 3室1厅 / 24㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 8300 元业主 丽景苑精装两居 配套齐全 集中供暖 看房方便 2室1厅 / 92㎡ 推荐理由： 配套齐全 精装修 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 1500 元急租 精装公寓 物业直签无中介 家电齐全 环境优美 押一付一 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 随时看房 * 1500 元真实，首月立减！；押一付一 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2200 元树村丽景苑主卧带阳台临近上地大厦 马连洼 百度 科实大厦 3室2厅 / 15㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 7300 元农大南路 镶黄旗万树园 精装两居 全明户型 跟业主签约 长租 2室2厅 / 98㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 5300 元价格能谈 紫城嘉园 南向1居 跟业主签约 看房方便 配套齐全 1室1厅 / 50.00㎡ 推荐理由： 独卫一居 精装修 随时看房 * 7400 元农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7500 元北大教职工燕秀园二区精装高层2居带电梯和业主签约 2室1厅 / 90㎡ 推荐理由： 邻地铁 精装修 随时看房 * 7500 元农大南路 燕秀园二区 精装小三居 随时看房和业主签约 可长租 3室1厅 / 80㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 19000 元西山华府珑园四居两厅3卫，随时可以看房入住，配套齐全跟业主签 4室2厅 / 177.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 # 马连洼租房房产中介 * 李兴龙 北京中润置家住房租赁有限公司 * 谢晓燕 北京壹号租售房地产经纪有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王正阳 北京佳萱房地产经纪有限公司 * 李文燕 北京七家伟业房地产经纪有限公司 * 赵伟涛 北京金色时光房地产经纪有限公司 * 范金辉 北京相寓住房租赁有限公司 * 田晓琪 北京麦田房产经纪有限公司 * 唐山清 北京豪骏房地产经纪有限公司 * 陈彩荣 北京长路住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 孙程远： 有身份证和固定工作就可以 * 俞鹏： 只要身份证就好，要找一个正规中介公司签合同，这样以后租房也有保障，其次就是有些房子是国家禁止交的，这类房子*不要去租 * 周昌峰： 您好，如果您要租房子的话，只需要提供身份证号就可以了 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 张娜： 您好租房都是自己交物业费和供暖费，物业费2.68一平米，供暖费是30元一平米 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房基本都是租客这边交，也可以把钱转给房东，让房东去交，物业费高层2.36元每平米每月，洋房2.68每平米每月，暖气费30一平一供暖季， * 马韶花： 您好，密云租房的物业费和暖气费基本都是自己交，物业费2.68元一平米，暖气费30元一平米 希望能帮到您 * 问 在这个平台出租房屋，靠谱吗？</x:v>
+        <x:v>该区域（兰园/马连洼片区）租房月租：整租1室约1500元/月（物业自持，无中介），2室约5900-6800元/月，单月整租均价约6800元；；物业为北京安居物业管理有限公司；；装修以精装修为主，户型多为2室1厅，南北通透、户型方正；；房源宣传“安静”，但无明确隔音相关差评；；未提及其他质量（如房龄导致的陈旧、墙体/设施问题）负面反馈。</x:v>
       </x:c>
       <x:c r="L78" t="str">
-        <x:v>) 北京房产网&gt;北京租房网&gt; 北京租房&gt; 海淀租房&gt; 马连洼租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * 方正 * 延寿 * 木兰 * 垫江 * 綦江 * 南川 * 梁平 * 万盛 * 奉节 * 云阳 * 丰都 * 彭水 * 忠县 * 秀山 * 黔江 * 武隆 * 巫山 * 石柱 * 酉阳 * 城口 * 巫溪 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 # 马连洼出租租房房源 * 2200 元裕和嘉园次卧 上地清河 软件园二期 滴滴湾流 小米元中心百度 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 南北通透 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 2800 元我爱我家相寓 马连洼丰泽盈和中楼层3居室主卧 3室1厅 / 19.5㎡ 推荐理由： 邻地铁 * 6500 元业主直签 裕隆新村精装两居室 实图拍摄 家具齐全 随时入住 2室1厅 / 80.22㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 9300 元南北通透 3室2厅 博雅西园 3室2厅 / 110.0㎡ 推荐理由： 邻地铁 * 8500 元树村丽景苑 2室2厅1卫 南北通透 集中供暖 2室2厅 / 94㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 随时看房 * 6600 元整租马连洼菊园2室1厅 2室1厅 / 53.9㎡ 推荐理由： 邻地铁 精装修 * 5400 元大有北里精致一居室干净整洁近安河桥北地铁中关村颐和园 1室1厅 / 49㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 有阳台 首次出租 * 7200 元万树园 精装南北通透2居室 长租稳定 家电齐全 随时看房 2室1厅 / 89.58㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1500 元山水小区大次卧 近地铁包物业取暖 中关村软件园 16号线直达 7室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6000 元马连洼梅园 精装两居 实房实图 跟业主签约 配套全齐 可长租 2室1厅 / 65.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 8600 元4号线安河桥北 天秀花园安和园精装三居室 价格可谈 随时看房 3室1厅 / 102.75㎡ 推荐理由： 邻地铁 精装修 随时看房 * 1500 元整租| 海淀小单间 实图实价房主直签 近地铁13号线上地清河 1室0厅 / 13㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 随时看房 * 1500 元首月立减！；1室0厅 / 15㎡ 推荐理由： 独卫一居 押一付一 配套齐全 南北通透 随时看房 * 5300 元毕业季 0押月付 整租 马连洼 裕和嘉园1室1厅 1室1厅 / 47.48㎡ 推荐理由： 独卫一居 精装修 * 2000 元手慢无 绿苑小区 正规次卧 可短签 农大南路 马连洼 可月付 3室1厅 / 10㎡ 推荐理由： 可短租 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 7400 元农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 2室1厅 / 75㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 5900 元明厨明卫 马连洼梅园 精装两局 中间楼层 价格可谈 跟签 2室1厅 / 63.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 1950 元首月减免 近万霖大厦 百度科技园 农大西校区 字节跳动软件园 3室1厅 / 13㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 2100 元西北旺 中关村软件园 百度 网易 东馨园 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 19000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 6800 元农大南路 农大西小区圆明园西路3号院精装三居室 和业主签约 3室1厅 / 60.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5100 元农大对面 3号院一居 干净整洁 采光超好 价格可谈 交通便利 1室1厅 / 42㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6000 元东北旺 东馨园 精装两居 实房实图 跟业主签约 配套全可长租 2室1厅 / 59.90㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 9500 元南北通透 3室1厅 百旺家苑 3室1厅 / 104.55㎡ 推荐理由： 邻地铁 * 2300 元东北旺 临近滴滴大厦 软通动力 软件园一二期 出租主卧 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 5200 元马连洼 柳浪北里 精装一居室 配套齐全 上地三街 万霖大厦 1室1厅 / 46.25㎡ 推荐理由： 独卫一居 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 8500 元业主直签 树村丽景苑小区 集中供暖 精装两居室 随时入住 2室1厅 / 84.00㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 随时看房 * 2600 元马连洼植保所农大西校区万霖大厦字节跳动软件园药用植物研究所 3室1厅 / 24㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 8300 元业主 丽景苑精装两居 配套齐全 集中供暖 看房方便 2室1厅 / 92㎡ 推荐理由： 配套齐全 精装修 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 1500 元急租 精装公寓 物业直签无中介 家电齐全 环境优美 押一付一 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 随时看房 * 1500 元真实，首月立减！；押一付一 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2200 元树村丽景苑主卧带阳台临近上地大厦 马连洼 百度 科实大厦 3室2厅 / 15㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 7300 元农大南路 镶黄旗万树园 精装两居 全明户型 跟业主签约 长租 2室2厅 / 98㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 5300 元价格能谈 紫城嘉园 南向1居 跟业主签约 看房方便 配套齐全 1室1厅 / 50.00㎡ 推荐理由： 独卫一居 精装修 随时看房 * 7400 元农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7500 元北大教职工燕秀园二区精装高层2居带电梯和业主签约 2室1厅 / 90㎡ 推荐理由： 邻地铁 精装修 随时看房 * 7500 元农大南路 燕秀园二区 精装小三居 随时看房和业主签约 可长租 3室1厅 / 80㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 19000 元西山华府珑园四居两厅3卫，随时可以看房入住，配套齐全跟业主签 4室2厅 / 177.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 # 马连洼租房房产中介 * 李兴龙 北京中润置家住房租赁有限公司 * 谢晓燕 北京壹号租售房地产经纪有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王正阳 北京佳萱房地产经纪有限公司 * 李文燕 北京七家伟业房地产经纪有限公司 * 赵伟涛 北京金色时光房地产经纪有限公司 * 范金辉 北京相寓住房租赁有限公司 * 田晓琪 北京麦田房产经纪有限公司 * 唐山清 北京豪骏房地产经纪有限公司 * 陈彩荣 北京长路住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；手机版： 马连洼租房信息 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 钦州租房网 * 毕节租房网 * 定西租房网 * 牡丹江租房网 * 沧县租房网 * 锦州租房网 * 临邑租房网 * 平邑租房网 * 泽州租房网 * 其他租房网 * 大兴租房网 * 东城租房网 * 门头沟租房网 * 海淀租房网 * 密云租房网 * 平谷租房网 * 石景山租房网 * 房山租房网 * 北京周边租房网 * 朝阳租房网 * 城子街道租房网 * 大峪租房网 * 东辛房租房网 * 军庄租房网 * 龙泉租房网 * 门头沟周边租房网 * 潭柘寺租房网 * 永定租房网 * 八宝山租房网 * 八大处租房网 * 八角租房网 * 安定门租房网 * 不老屯租房网 * 保定租房网 * 磁各庄租房网 * 安宁庄租房网 * 长阳租房网 * 滨河路租房网 * CBD租房网 * 宣城租房 * 茂名租房 * 丰城租房 * 莘县租房 * 运城租房 * 宣城出租 * 茂名出租 * 丰城出租 * 莘县出租 * 运城出租 * 宣城整租房 * 茂名整租房 * 丰城整租房 * 莘县整租房 * 运城整租房 * 宣城合租房 * 茂名合租房 * 丰城合租房 * 莘县合租房 * 运城合租房 * 宣城个人 * 茂名个人 * 丰城个人 * 莘县个人 * 运城个人 * 大兴租房 * 东城租房 * 门头沟租房 * 海淀租房 * 密云租房 * 大兴出租 * 东城出租 * 门头沟出租 * 海淀出租 * 密云出租 * 大兴整租房 * 东城整租房 * 门头沟整租房 * 海淀整租房 * 密云整租房 * 大兴合租房 * 东城合租房 * 门头沟合租房 * 海淀合租房 * 密云合租房 * 北京精装修租房 * 北京豪华装修租房 * 北京1000元左右租房 * 北京2500元左右租房 * 北京15平米租房 * 北京130平米租房 * 北京200平米租房 * 北京复式租房 * 北京商场附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京高品质小区租房 * 北京家电齐全租房 * 北京新小区租房 * 北京幼儿园附近租房。；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：马连洼附近房屋出租条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486612081_1.htm) 万德嘉园精装主卧独卫 3000押一付一 近地铁 合租主卧|3户合租|19㎡|朝南 海淀-马连洼-万德嘉园 交通便利周边配套齐采光好 3000 元/月 [](http://www.fang.com/chuzu/3_486942133_1.htm) 农大南路幸福超市万树园南向主卧带阳台出租 合租主卧|3户合租|18㎡|朝南 海淀-马连洼-万树园 距16号线农大南路站约1059米。</x:v>
+        <x:v>周边有35个公交站（如圆明园西路北口、地铁马连洼站）；；2.商超：南门有中发百旺商城（含地下超市），西门近工商银行，底商有药店；；3.餐饮：周边有庆丰包子、护国寺小吃等，美食环绕；；4.医院：309三甲医院距离约1.9公里，底商有同仁堂药店及社区诊所；；5.综合：生活配套较完善，购物、餐饮、基础医疗便利，交通依赖地铁/公交，步行距离适中。</x:v>
       </x:c>
       <x:c r="M78" t="str">
-        <x:v>如果遇到停车难的问题，也有马连洼兰园的物业快速协调。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>房源宣传“安静”，但无明确隔音相关差评；；2.兰园小区楼龄较久（约56年），需注意房屋设施老旧问题；</x:v>
       </x:c>
       <x:c r="N78" t="str">
-        <x:v>价格线索：洼-万德嘉园 交通便利周边配套齐采光好 3000 元/月；交通便利 2500 元/月；交通便利周边配套齐采光好 1200 元/月；连洼-芳怡园 交通便利周边配套齐采光好 1800 元/月；交通便利周边配套齐采光好 2000 元/月；交通便利周边配套齐采光好 2200 元/月；洼-万德嘉园 交通便利周边配套齐采光好 1000 元/月；社区(北区) 交通便利周边配套齐采光好 1500 元/月；房屋质量/户型线索：) 北京房产网&gt;北京租房网&gt; 北京租房&gt; 海淀租房&gt; 马连洼租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * 方正 * 延寿 * 木兰 * 垫江 * 綦江 * 南川 * 梁平 * 万盛 * 奉节 * 云阳 * 丰都 * 彭水 * 忠县 * 秀山 * 黔江 * 武隆 * 巫山 * 石柱 * 酉阳 * 城口 * 巫溪 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 # 马连洼出租租房房源 * 2200 元裕和嘉园次卧 上地清河 软件园二期 滴滴湾流 小米元中心百度 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 南北通透 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 2800 元我爱我家相寓 马连洼丰泽盈和中楼层3居室主卧 3室1厅 / 19.5㎡ 推荐理由： 邻地铁 * 6500 元业主直签 裕隆新村精装两居室 实图拍摄 家具齐全 随时入住 2室1厅 / 80.22㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 9300 元南北通透 3室2厅 博雅西园 3室2厅 / 110.0㎡ 推荐理由： 邻地铁 * 8500 元树村丽景苑 2室2厅1卫 南北通透 集中供暖 2室2厅 / 94㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 随时看房 * 6600 元整租马连洼菊园2室1厅 2室1厅 / 53.9㎡ 推荐理由： 邻地铁 精装修 * 5400 元大有北里精致一居室干净整洁近安河桥北地铁中关村颐和园 1室1厅 / 49㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 有阳台 首次出租 * 7200 元万树园 精装南北通透2居室 长租稳定 家电齐全 随时看房 2室1厅 / 89.58㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1500 元山水小区大次卧 近地铁包物业取暖 中关村软件园 16号线直达 7室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6000 元马连洼梅园 精装两居 实房实图 跟业主签约 配套全齐 可长租 2室1厅 / 65.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 8600 元4号线安河桥北 天秀花园安和园精装三居室 价格可谈 随时看房 3室1厅 / 102.75㎡ 推荐理由： 邻地铁 精装修 随时看房 * 1500 元整租| 海淀小单间 实图实价房主直签 近地铁13号线上地清河 1室0厅 / 13㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 随时看房 * 1500 元首月立减！；隔音好！；1室0厅 / 15㎡ 推荐理由： 独卫一居 押一付一 配套齐全 南北通透 随时看房 * 5300 元毕业季 0押月付 整租 马连洼 裕和嘉园1室1厅 1室1厅 / 47.48㎡ 推荐理由： 独卫一居 精装修 * 2000 元手慢无 绿苑小区 正规次卧 可短签 农大南路 马连洼 可月付 3室1厅 / 10㎡ 推荐理由： 可短租 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 7400 元农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 2室1厅 / 75㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 5900 元明厨明卫 马连洼梅园 精装两局 中间楼层 价格可谈 跟签 2室1厅 / 63.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 1950 元首月减免 近万霖大厦 百度科技园 农大西校区 字节跳动软件园 3室1厅 / 13㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 2100 元西北旺 中关村软件园 百度 网易 东馨园 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 19000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 6800 元农大南路 农大西小区圆明园西路3号院精装三居室 和业主签约 3室1厅 / 60.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5100 元农大对面 3号院一居 干净整洁 采光超好 价格可谈 交通便利 1室1厅 / 42㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6000 元东北旺 东馨园 精装两居 实房实图 跟业主签约 配套全可长租 2室1厅 / 59.90㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 9500 元南北通透 3室1厅 百旺家苑 3室1厅 / 104.55㎡ 推荐理由： 邻地铁 * 2300 元东北旺 临近滴滴大厦 软通动力 软件园一二期 出租主卧 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 5200 元马连洼 柳浪北里 精装一居室 配套齐全 上地三街 万霖大厦 1室1厅 / 46.25㎡ 推荐理由： 独卫一居 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 8500 元业主直签 树村丽景苑小区 集中供暖 精装两居室 随时入住 2室1厅 / 84.00㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 随时看房 * 2600 元马连洼植保所农大西校区万霖大厦字节跳动软件园药用植物研究所 3室1厅 / 24㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 8300 元业主 丽景苑精装两居 配套齐全 集中供暖 看房方便 2室1厅 / 92㎡ 推荐理由： 配套齐全 精装修 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 1500 元急租 精装公寓 物业直签无中介 家电齐全 环境优美 押一付一 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 随时看房 * 1500 元真实，首月立减！；押一付一 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2200 元树村丽景苑主卧带阳台临近上地大厦 马连洼 百度 科实大厦 3室2厅 / 15㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 7300 元农大南路 镶黄旗万树园 精装两居 全明户型 跟业主签约 长租 2室2厅 / 98㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 5300 元价格能谈 紫城嘉园 南向1居 跟业主签约 看房方便 配套齐全 1室1厅 / 50.00㎡ 推荐理由： 独卫一居 精装修 随时看房 * 7400 元农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7500 元北大教职工燕秀园二区精装高层2居带电梯和业主签约 2室1厅 / 90㎡ 推荐理由： 邻地铁 精装修 随时看房 * 7500 元农大南路 燕秀园二区 精装小三居 随时看房和业主签约 可长租 3室1厅 / 80㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 19000 元西山华府珑园四居两厅3卫，随时可以看房入住，配套齐全跟业主签 4室2厅 / 177.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 # 马连洼租房房产中介 * 李兴龙 北京中润置家住房租赁有限公司 * 谢晓燕 北京壹号租售房地产经纪有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王正阳 北京佳萱房地产经纪有限公司 * 李文燕 北京七家伟业房地产经纪有限公司 * 赵伟涛 北京金色时光房地产经纪有限公司 * 范金辉 北京相寓住房租赁有限公司 * 田晓琪 北京麦田房产经纪有限公司 * 唐山清 北京豪骏房地产经纪有限公司 * 陈彩荣 北京长路住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；* 孙程远： 有身份证和固定工作就可以 * 俞鹏： 只要身份证就好，要找一个正规中介公司签合同，这样以后租房也有保障，其次就是有些房子是国家禁止交的，这类房子*不要去租 * 周昌峰： 您好，如果您要租房子的话，只需要提供身份证号就可以了 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 张娜： 您好租房都是自己交物业费和供暖费，物业费2.68一平米，供暖费是30元一平米 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房基本都是租客这边交，也可以把钱转给房东，让房东去交，物业费高层2.36元每平米每月，洋房2.68每平米每月，暖气费30一平一供暖季， * 马韶花： 您好，密云租房的物业费和暖气费基本都是自己交，物业费2.68元一平米，暖气费30元一平米 希望能帮到您 * 问 在这个平台出租房屋，靠谱吗？；生活便利线索：) 北京房产网&gt;北京租房网&gt; 北京租房&gt; 海淀租房&gt; 马连洼租房 区域 * 不限 * 朝阳 * 海淀 * 昌平 * 丰台 * 大兴 * 通州 * 房山 * 顺义 * 西城 * 东城 * 密云 * 石景山 * 怀柔 * 门头沟 * 延庆 * 平谷 * 北京周边 * 方正 * 延寿 * 木兰 * 垫江 * 綦江 * 南川 * 梁平 * 万盛 * 奉节 * 云阳 * 丰都 * 彭水 * 忠县 * 秀山 * 黔江 * 武隆 * 巫山 * 石柱 * 酉阳 * 城口 * 巫溪 * A * 安宁庄 * B * 白石桥 * 北航 * 北京大学 * 北太平庄 * 北洼路 * C * 厂洼 * 车道沟 * D * 大钟寺 * 定慧寺 * E * 恩济里 * 二里庄 * G * 甘家口 * 公主坟 * H * 海淀周边 * 航天桥 * 花园桥 * J * 交通大学 * 蓟门桥 * 金沟河 * 军博 * L * 联想桥 * M * 马甸 * 马连洼 * 明光桥 * 牡丹园 * Q * 清河 * 清华大学 * R * 人民大学 * S * 上地 * 上庄 * 世纪城 * 双榆树 * 四季青 * 苏家坨 * 苏州街 * 苏州桥 * T * 田村 * W * 万柳 * 万泉河 * 万寿路 * 万寿寺 * 魏公村 * 温泉 * 五彩城 * 五道口 * 五棵松 * 五路居 * X * 香山 * 肖家河 * 小西天 * 西八里庄 * 西北旺 * 西二旗 * 西三旗 * 西山 * 西苑 * 学院路 * 学院路北 * Y * 永定路 * Z * 皂君庙 * 增光路 * 知春路 * 中关村 * 紫竹桥 # 马连洼出租租房房源 * 2200 元裕和嘉园次卧 上地清河 软件园二期 滴滴湾流 小米元中心百度 3室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 配套齐全 精装修 南北通透 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 2800 元我爱我家相寓 马连洼丰泽盈和中楼层3居室主卧 3室1厅 / 19.5㎡ 推荐理由： 邻地铁 * 6500 元业主直签 裕隆新村精装两居室 实图拍摄 家具齐全 随时入住 2室1厅 / 80.22㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 9300 元南北通透 3室2厅 博雅西园 3室2厅 / 110.0㎡ 推荐理由： 邻地铁 * 8500 元树村丽景苑 2室2厅1卫 南北通透 集中供暖 2室2厅 / 94㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 随时看房 * 6600 元整租马连洼菊园2室1厅 2室1厅 / 53.9㎡ 推荐理由： 邻地铁 精装修 * 5400 元大有北里精致一居室干净整洁近安河桥北地铁中关村颐和园 1室1厅 / 49㎡ 推荐理由： 独卫一居 邻地铁 押一付一 配套齐全 精装修 有阳台 首次出租 * 7200 元万树园 精装南北通透2居室 长租稳定 家电齐全 随时看房 2室1厅 / 89.58㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 1500 元山水小区大次卧 近地铁包物业取暖 中关村软件园 16号线直达 7室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 6000 元马连洼梅园 精装两居 实房实图 跟业主签约 配套全齐 可长租 2室1厅 / 65.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 8600 元4号线安河桥北 天秀花园安和园精装三居室 价格可谈 随时看房 3室1厅 / 102.75㎡ 推荐理由： 邻地铁 精装修 随时看房 * 1500 元整租| 海淀小单间 实图实价房主直签 近地铁13号线上地清河 1室0厅 / 13㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 随时看房 * 1500 元首月立减！；1室0厅 / 15㎡ 推荐理由： 独卫一居 押一付一 配套齐全 南北通透 随时看房 * 5300 元毕业季 0押月付 整租 马连洼 裕和嘉园1室1厅 1室1厅 / 47.48㎡ 推荐理由： 独卫一居 精装修 * 2000 元手慢无 绿苑小区 正规次卧 可短签 农大南路 马连洼 可月付 3室1厅 / 10㎡ 推荐理由： 可短租 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 7400 元农大南路 广泰小区 精装两居室 非常干净配套齐全 和业主签约 2室1厅 / 75㎡ 推荐理由： 邻地铁 配套齐全 精装修 有阳台 随时看房 * 5900 元明厨明卫 马连洼梅园 精装两局 中间楼层 价格可谈 跟签 2室1厅 / 63.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 1950 元首月减免 近万霖大厦 百度科技园 农大西校区 字节跳动软件园 3室1厅 / 13㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 2100 元西北旺 中关村软件园 百度 网易 东馨园 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 19000 元万科物业租售推荐 西山华府 精装四居 采光环境好 毗邻地铁 4室2厅 / 178.12㎡ 推荐理由： 邻地铁 精装修 * 6800 元农大南路 农大西小区圆明园西路3号院精装三居室 和业主签约 3室1厅 / 60.00㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 5100 元农大对面 3号院一居 干净整洁 采光超好 价格可谈 交通便利 1室1厅 / 42㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 精装修 有阳台 随时看房 * 6000 元东北旺 东馨园 精装两居 实房实图 跟业主签约 配套全可长租 2室1厅 / 59.90㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 9500 元南北通透 3室1厅 百旺家苑 3室1厅 / 104.55㎡ 推荐理由： 邻地铁 * 2300 元东北旺 临近滴滴大厦 软通动力 软件园一二期 出租主卧 3室1厅 / 15㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 5200 元马连洼 柳浪北里 精装一居室 配套齐全 上地三街 万霖大厦 1室1厅 / 46.25㎡ 推荐理由： 独卫一居 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 8500 元业主直签 树村丽景苑小区 集中供暖 精装两居室 随时入住 2室1厅 / 84.00㎡ 推荐理由： 配套齐全 精装修 南北通透 有阳台 随时看房 * 2600 元马连洼植保所农大西校区万霖大厦字节跳动软件园药用植物研究所 3室1厅 / 24㎡ 推荐理由： 可短租 独卫 独立阳台 邻地铁 押一付一 配套齐全 精装修 南北通透 * 8300 元业主 丽景苑精装两居 配套齐全 集中供暖 看房方便 2室1厅 / 92㎡ 推荐理由： 配套齐全 精装修 有阳台 随时看房 * 11000 元正南 2室2厅 亿城西山华府珑园 2室2厅 / 93.51㎡ 推荐理由： 邻地铁 * 1500 元急租 精装公寓 物业直签无中介 家电齐全 环境优美 押一付一 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 随时看房 * 1500 元真实，首月立减！；押一付一 1室1厅 / 30㎡ 推荐理由： 独卫一居 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 2200 元树村丽景苑主卧带阳台临近上地大厦 马连洼 百度 科实大厦 3室2厅 / 15㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 7300 元农大南路 镶黄旗万树园 精装两居 全明户型 跟业主签约 长租 2室2厅 / 98㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 * 5300 元价格能谈 紫城嘉园 南向1居 跟业主签约 看房方便 配套齐全 1室1厅 / 50.00㎡ 推荐理由： 独卫一居 精装修 随时看房 * 7400 元农大南路 精装两居室 配套齐全 集中供暖 和业主签约 植保所 2室1厅 / 70㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房 * 7500 元北大教职工燕秀园二区精装高层2居带电梯和业主签约 2室1厅 / 90㎡ 推荐理由： 邻地铁 精装修 随时看房 * 7500 元农大南路 燕秀园二区 精装小三居 随时看房和业主签约 可长租 3室1厅 / 80㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 随时看房 * 19000 元西山华府珑园四居两厅3卫，随时可以看房入住，配套齐全跟业主签 4室2厅 / 177.0㎡ 推荐理由： 邻地铁 配套齐全 精装修 南北通透 有阳台 首次出租 # 马连洼租房房产中介 * 李兴龙 北京中润置家住房租赁有限公司 * 谢晓燕 北京壹号租售房地产经纪有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王正阳 北京佳萱房地产经纪有限公司 * 李文燕 北京七家伟业房地产经纪有限公司 * 赵伟涛 北京金色时光房地产经纪有限公司 * 范金辉 北京相寓住房租赁有限公司 * 田晓琪 北京麦田房产经纪有限公司 * 唐山清 北京豪骏房地产经纪有限公司 * 陈彩荣 北京长路住房租赁有限公司 ## 租房房产问答 * 问 请问租房需要什么条件？；手机版： 马连洼租房信息 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 钦州租房网 * 毕节租房网 * 定西租房网 * 牡丹江租房网 * 沧县租房网 * 锦州租房网 * 临邑租房网 * 平邑租房网 * 泽州租房网 * 其他租房网 * 大兴租房网 * 东城租房网 * 门头沟租房网 * 海淀租房网 * 密云租房网 * 平谷租房网 * 石景山租房网 * 房山租房网 * 北京周边租房网 * 朝阳租房网 * 城子街道租房网 * 大峪租房网 * 东辛房租房网 * 军庄租房网 * 龙泉租房网 * 门头沟周边租房网 * 潭柘寺租房网 * 永定租房网 * 八宝山租房网 * 八大处租房网 * 八角租房网 * 安定门租房网 * 不老屯租房网 * 保定租房网 * 磁各庄租房网 * 安宁庄租房网 * 长阳租房网 * 滨河路租房网 * CBD租房网 * 宣城租房 * 茂名租房 * 丰城租房 * 莘县租房 * 运城租房 * 宣城出租 * 茂名出租 * 丰城出租 * 莘县出租 * 运城出租 * 宣城整租房 * 茂名整租房 * 丰城整租房 * 莘县整租房 * 运城整租房 * 宣城合租房 * 茂名合租房 * 丰城合租房 * 莘县合租房 * 运城合租房 * 宣城个人 * 茂名个人 * 丰城个人 * 莘县个人 * 运城个人 * 大兴租房 * 东城租房 * 门头沟租房 * 海淀租房 * 密云租房 * 大兴出租 * 东城出租 * 门头沟出租 * 海淀出租 * 密云出租 * 大兴整租房 * 东城整租房 * 门头沟整租房 * 海淀整租房 * 密云整租房 * 大兴合租房 * 东城合租房 * 门头沟合租房 * 海淀合租房 * 密云合租房 * 北京精装修租房 * 北京豪华装修租房 * 北京1000元左右租房 * 北京2500元左右租房 * 北京15平米租房 * 北京130平米租房 * 北京200平米租房 * 北京复式租房 * 北京商场附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京高品质小区租房 * 北京家电齐全租房 * 北京新小区租房 * 北京幼儿园附近租房。；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：马连洼附近房屋出租条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486612081_1.htm) 万德嘉园精装主卧独卫 3000押一付一 近地铁 合租主卧|3户合租|19㎡|朝南 海淀-马连洼-万德嘉园 交通便利周边配套齐采光好 3000 元/月 [](http://www.fang.com/chuzu/3_486942133_1.htm) 农大南路幸福超市万树园南向主卧带阳台出租 合租主卧|3户合租|18㎡|朝南 海淀-马连洼-万树园 距16号线农大南路站约1059米。；风险线索：如果遇到停车难的问题，也有马连洼兰园的物业快速协调。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：（兰园/马连洼片区）租房月租：整租1室约1500元/月；（物业自持，无中介），2室约5900-6800元/月；房屋质量/户型线索：该区域（兰园/马连洼片区）租房月租：整租1室约1500元/月（物业自持，无中介），2室约5900-6800元/月，单月整租均价约6800元；；物业为北京安居物业管理有限公司；；装修以精装修为主，户型多为2室1厅，南北通透、户型方正；；房源宣传“安静”，但无明确隔音相关差评；；未提及其他质量（如房龄导致的陈旧、墙体/设施问题）负面反馈。；生活便利线索：周边有35个公交站（如圆明园西路北口、地铁马连洼站）；；2.商超：南门有中发百旺商城（含地下超市），西门近工商银行，底商有药店；；3.餐饮：周边有庆丰包子、护国寺小吃等，美食环绕；；4.医院：309三甲医院距离约1.9公里，底商有同仁堂药店及社区诊所；；5.综合：生活配套较完善，购物、餐饮、基础医疗便利，交通依赖地铁/公交，步行距离适中。；风险线索：房源宣传“安静”，但无明确隔音相关差评；；2.兰园小区楼龄较久（约56年），需注意房屋设施老旧问题；</x:v>
       </x:c>
       <x:c r="O78" t="str">
-        <x:v>1. 马连洼房屋出租信息_北京海淀马连洼出租房源信息-58出租网 http://mob.58.com/zf/xm/cz-malianwa/
-2. 【北京租房网_北京租房信息|房屋出租】- 房天下 http://www.fang.com/houses/zf_256593bj/
-3. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-4. 马连洼兰园_北京马连洼兰园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/674221.html
-5. 讨论精选（豆瓣） https://www.douban.com/group/explore</x:v>
+        <x:v>1. http://m.anjuke.com/bj/rent/4596893844286465-3/
+2. http://m.anjuke.com/bj/rent/4536215141161990-3/
+3. http://m.anjuke.com/bj/rent/4583081688898565-3/
+4. https://m.5i5j.com/bj/xq_news/52528.html
+5. http://m.anjuke.com/bj/rent/4526384981568518-3/
+6. http://m.fang.com/xiaoqu/strategy/bj/1010216357.html
+7. 免俩月房租！马连洼 官网力荐 可全包无杂费！ 无中介 http://m.anjuke.com/bj/rent/4596893844286465-3/
+8. 马连洼兰园 精装两居 实图拍摄 非常干净 跟业主直签 可长租 http://m.anjuke.com/bj/rent/4536215141161990-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -4099,41 +4314,42 @@
         <x:v>天秀路荷塘月舍10号001A2号</x:v>
       </x:c>
       <x:c r="E79" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F79" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G79" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H79" t="n">
-        <x:v>7.5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>位于马连洼商圈，租金处于中高水平，配套成熟，但具体房源质量证据较泛化。</x:v>
+        <x:v>交通便利且物业管理规范，户型采光佳，适合预算充足、追求生活品质的租客。</x:v>
       </x:c>
       <x:c r="J79" t="str">
-        <x:v>三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月</x:v>
+        <x:v>一居约5500-7100元/月；，两居约6700-6900元/月；，三居约9000元/月；，四居约14000元/月</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；* 问【沿湖南区】 要看短租房 * 沉默： 您好，小区有短租的房子，您可以联系我带您看房 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；* 初娟娟： 您好密云这边租房子物业费和暖气费都需要自己交，物业费2.36元每平米 * 问 租房能落户吗？；* 王福海： 您好，可以的，可以不带家具北京易合房产怀柔顶秀美泉店王福海很高兴为您回答 希望能帮到您 * 张波： 小区物业可以不带家具，家电，具体跟房主沟通就可以 * 问【宾阳里小区】 有短租房子吗 * 沉默： 你好有短租的房子，只要是房子在出售状态就可以短租，希望我的回答可以解决您的问题 希望能帮到您 * 问 我要租房，这里大概一居室多少钱 * 哈哈哈哈哈哈哈： 您好 汇鑫地产王春玲！</x:v>
+        <x:v>房龄未提及；；户型方正，采光好；；装修为精装修，家具家电齐全；；小区有专业物业，管理有序；；未提及隔音相关评价；</x:v>
       </x:c>
       <x:c r="L79" t="str">
-        <x:v># 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀区公寓出租条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486863782_1.htm) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 距10号线火器营站约436米。；交通便利南北通透 18000 元/月 [](http://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。</x:v>
-      </x:c>
-      <x:c r="M79" t="str">
-        <x:v>手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
-      </x:c>
+        <x:v>距离16号线农大南路站约582米，周边有天秀花园东站公交站，靠近北京华联BHG Mall、中发百旺商城，有果适好生鲜超市，医疗有北医三院、解放军总医院第八医学中心，餐饮及休闲配套成熟；</x:v>
+      </x:c>
+      <x:c r="M79" t="str"/>
       <x:c r="N79" t="str">
-        <x:v>价格线索：三室 * 四室 * 四室以上 * 一室 5200元/月；-1.89% * 二室 7000元/月；+1.45% * 三室 11800元/月；+2.61% * 四室 25000元/月；+0.34% * 四室以上 40000元/月；区名称 月租金 涨跌幅 * 1.中间建筑50000元/月； 0.00% * 2.西山美墅馆24000元/月；-11.11% ↓ * 3.万城华府龙园18800元/月；房屋质量/户型线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；* 问【沿湖南区】 要看短租房 * 沉默： 您好，小区有短租的房子，您可以联系我带您看房 * 问 租房子的话物业费和暖气费都需要自己交吗，物业费大概多少 * yuiwx3： 您好，租房物业费供暖费都是自己交的，物业费2.68 希望能帮到您 * 李智芳： 您好 物业费暖气费都得自己交的 物业2.36一平米 希望能帮到您 * 王增先： 租房都是客户这边交物业取暖 * 马韶花： 您好，物业费，暖气费，都是需要承租人承担，物业费2.68平米，暖气30元平米，希望能帮到您！；* 初娟娟： 您好密云这边租房子物业费和暖气费都需要自己交，物业费2.36元每平米 * 问 租房能落户吗？；* 王福海： 您好，可以的，可以不带家具北京易合房产怀柔顶秀美泉店王福海很高兴为您回答 希望能帮到您 * 张波： 小区物业可以不带家具，家电，具体跟房主沟通就可以 * 问【宾阳里小区】 有短租房子吗 * 沉默： 你好有短租的房子，只要是房子在出售状态就可以短租，希望我的回答可以解决您的问题 希望能帮到您 * 问 我要租房，这里大概一居室多少钱 * 哈哈哈哈哈哈哈： 您好 汇鑫地产王春玲！；生活便利线索：# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；) * 地铁 免费发布房源 租金：不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-户型：不限一居二居三居四居四居以上 当前找房条件： * 关键字：海淀区公寓出租条件订阅 * 全部房源 * 个人 默认排序按发布时间排序价格面积 [](http://www.fang.com/chuzu/3_486863782_1.htm) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 距10号线火器营站约436米。；交通便利南北通透 18000 元/月 [](http://www.fang.com/chuzu/3_486924606_1.htm) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 距10号线长春桥站约725米。；风险线索：手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?</x:v>
+        <x:v>价格线索：一居约5500-7100元/月；，两居约6700-6900元/月；，三居约9000元/月；，四居约14000元/月；房屋质量/户型线索：房龄未提及；；户型方正，采光好；；装修为精装修，家具家电齐全；；小区有专业物业，管理有序；；未提及隔音相关评价；；生活便利线索：距离16号线农大南路站约582米，周边有天秀花园东站公交站，靠近北京华联BHG Mall、中发百旺商城，有果适好生鲜超市，医疗有北医三院、解放军总医院第八医学中心，餐饮及休闲配套成熟；</x:v>
       </x:c>
       <x:c r="O79" t="str">
-        <x:v>1. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-2. 【北京租房网_北京租房信息|房屋出租】- 房天下 http://www.fang.com/houses/zf_252311bj/
-3. 2026北京海淀区第一批公租房配租套型标准- 北京本地宝 http://bj.bendibao.com/zffw/202658/382530.shtm
-4. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/
-5. 选定922套高品质房源 北京海淀区启动青年公寓试点工作 https://www.stdaily.com/web/gdxw/2025-06/06/content_351160.html</x:v>
+        <x:v>1. https://bj.zu.anjuke.com/fangyuan/4486556255233034
+2. http://m.anjuke.com/bj/rent/4487783368549379-3/
+3. http://m.anjuke.com/bj/rent/4367181453632525-3/
+4. http://m.anjuke.com/bj/rent/4246130524479499-3/
+5. https://bj.zu.anjuke.com/fangyuan/4201775043795983
+6. http://m.anjuke.com/ch/rent/4501937341164557-3/
+7. http://m.anjuke.com/bj/rent/4580538390633479-3/
+8. 天秀花园荷塘月舍 精装三居 有电梯 非常干净 跟业主直签 https://bj.zu.anjuke.com/fangyuan/4486556255233034</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -4150,7 +4366,7 @@
         <x:v>北京市海淀区上地大厦东侧,上地西里小区东门东侧</x:v>
       </x:c>
       <x:c r="E80" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F80" t="n">
         <x:v>8</x:v>
@@ -4159,32 +4375,33 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H80" t="n">
-        <x:v>8.2</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>地处上地核心区，交通极便，配套完善，虽房龄较老但户型方正，是网易员工首选。</x:v>
+        <x:v>地理位置优越，通勤购物极便，但房龄偏老且多无电梯，隔音与防潮表现一般。</x:v>
       </x:c>
       <x:c r="J80" t="str">
-        <x:v>2026-04-04 | 811万 | 100995元/㎡；三室 * 四室 * 四室以上 * 一室 5000元/月；+0.00% * 二室 7300元/月；+0.00% * 三室 10700元/月；+16.30% * 四室 15000元/月；+0.00% * 四室以上 33500元/月；修问答登录/注册 上地东里6月均价走势 113428 元/㎡；学院路 1998年竣工 距离4081m 75667 元/㎡</x:v>
+        <x:v>整租：1室约5400-5800元/月；，2室约6200-7500元/月；，3室约8400-11000元/月；，4室约10000元/月；合租单间约1000-2400元/月</x:v>
       </x:c>
       <x:c r="K80" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **101733** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓0.43% 贷款计算器 * 二手房源 51套 * 最近成交 994套 * 楼栋总数 57栋 * 房屋总数 3750户 * 建筑类型 板楼 * 建筑年代 2000年建成 * 小区位置 上地南路与信息路交汇处东行90米路北地图 * 物业公司 北京实创上地物业管理服务有限责任公司 * 开发商 实创高科技发展总公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 李强 评分：4.6 从业信息卡 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 新增好房全明眼镜户型中低层采光好满五年 3室2厅 126.11㎡**1190**万 * #### 上地东里3室2厅东南 3室2厅 123.7㎡**1100**万 * #### 上地东里,南北通透2居室,中间层3层,看房随时 2室1厅 82.3㎡**970**万 * #### 上地东里3室2厅东南 3室2厅 116.48㎡**1050**万 ### 上地东里成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 72.30㎡ | 2026-04-24 | -- | -- | 市场信息 | | 108.15㎡ | 2026-04-12 | -- | -- | 市场信息 | | 80.40㎡ | 2026-04-04 | 811万 | 100995元/㎡ | 市场信息 | 查看全部成交 ### 上地东里价格走势 ### 上地东里房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 上地东里 海淀·上地**101734** 元/㎡ * #### 上地佳园 海淀·上地**107549** 元/㎡ * #### 尚品公寓 海淀·上地**94094** 元/㎡ * #### 上地南路8号院 海淀·上地**91334** 元/㎡ * #### 枫润家园 海淀·上地**77170** 元/㎡ ### 相关资讯 * 小区资讯北京上地东里怎么样?；* 王福海： 您好，可以的，可以不带家具北京易合房产怀柔顶秀美泉店王福海很高兴为您回答 希望能帮到您 * 张波： 小区物业可以不带家具，家电，具体跟房主沟通就可以 * 问 可以一次签三至六年的租房合同吗 * NTHfhN： 签租赁合同的具体日期长短，需要和业主协商。；58同城北京租房网，为您提供北京上地租房信息，包括上地房屋出租信息、上地合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。；from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 上地东里6月均价走势 113428 元/㎡ 6月挂牌均价 0.27% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 新增！</x:v>
+        <x:v>合租单间约1000-2400元/月，具体价格因面积、装修、户型不同有差异，业主直租无中介费，中介房源一般收取一个月租金作为中介费。；房龄：小区多为1993-2000年建成，房龄较老；；户型：主流户型1室到4室都有，部分为南北通透户型，采光较好；；隔音：部分低楼层住户反馈小区安静，噪音少，但老小区整体隔音一般；；装修：分为简单装修和精装修，多数在租房源家具家电齐全，可拎包入住；</x:v>
       </x:c>
       <x:c r="L80" t="str">
-        <x:v>上地东里房价地址周边配套分析2021-12-25 * 小区资讯最详细!；* 陈帆帆： 可以自己发布，也可以找中介带客户，还可以托管给代理公司 * 姜红丹： 你好，可以挂在网上拿着产权证进行识别认证，五八会自动推送房源代理 * 李义强： 中介门店登记下 让中介公司帮忙出租 或者自己拍些照片 挂58网 * 谭帅鹏： 可以看一下周边房产公司，免费登记，一定要整租，找个好租户，中介公司也一定要找好，小公司不找 * 问 在这个平台出租房屋，靠谱吗？；南北通透 精装两居 低楼层 必看好房 上地 上地东里 880 万 2室2厅 95.91㎡ 海淀 上地东里 树村 南北通透 交通便捷 清晰 临地铁 上地 上地东里 568 万 2室1厅 62.17㎡ 上地上地东里2室1厅 上地 上地东里 670 万 2室1厅 56.35㎡ 上地东里三区 南北通透 小户型 装修保养还不错 上地 上地东里 560 万 1室1厅 44.9㎡ 2室1厅1卫0厨0阳 上地 上地东里 680 万 2室1厅 57.3㎡ 上地东里 新增一居 采光好 装修棒 可看房 上地 上地东里 630 万 1室1厅 47.87㎡ ### 本小区租房推荐查看更多 ### 上地三街 金隅嘉华大厦旁边上地东里小区三家合租朝南主卧可短签 上地 上地东里 合租 13号线/昌平线 朝南 _2590_ 元/月 3室1厅 25㎡ ### 上地东里主卧阳台 北京体育大学 硅谷亮城 上地信息产业基地 上地 上地东里 合租 13号线/昌平线 朝南 _2700_ 元/月 3室1厅 20㎡ ### 业主直签 近上地商圈的上地东里 家电家具齐全 随时入住可长租 上地 上地东里 整租 13号线/昌平线 朝南 _5400_ 元/月 1室 45.6㎡ ### 正南 1室1厅 上地东里 上地 上地东里 整租 13号线/昌平线 朝南 _6500_ 元/月 1室1厅 47.9㎡ ### 上地东里 精装一居 随时看房 价格可谈 配套齐全 业主签约 上地 上地东里 整租 13号线/昌平线 朝东 _5400_ 元/月 1室1厅 45.6㎡ ### 上地东里一居 安静无噪音 上地 上地东里 整租 13号线/昌平线 南北 _5600_ 元/月 1室1厅 46.7㎡ ### 周边热门小区查看更多 * 30 林大北路9号院 海淀 学院路 1998年竣工 距离4081m 75667 元/㎡2套在售 小区评测 近地铁 近学校 15号线等 四五环之间 配套齐全 7.0 分 * 231 褐石园 海淀 清华大学 2009年竣工 距离2562m 119697 元/㎡11套在售 小区评测 近地铁 近学校 四五环之间 大户型居多 户型丰富 配套齐全 6.7 分 小区单页 今日家园远洋山水(北区)翠微南里首城国际新景家园(东区)丽宫别墅格拉斯小镇(别墅)碧水庄园北辰红橡墅御汤山东区棕榈泉国际公寓华纺易城九章别墅星河湾朗园弘善家园百环家园紫金长安北京壹号庄园望园东里首邑溪谷 本板块小区大全 褐石园美和园西区颐源居同泽园西里北坞嘉园南里翠微南里五福玲珑居四季香山中鑫嘉园百旺家苑莲花小区保利西山林语香山艺墅交大嘉园华清嘉园芳怡园水云居东王庄小区紫金庄园翠湖别墅 小区二手房 今日家园二手房出售远洋山水(北区)二手房出售翠微南里二手房出售首城国际二手房出售新景家园(东区)二手房出售丽宫别墅二手房出售格拉斯小镇(别墅)二手房出售碧水庄园二手房出售北辰红橡墅二手房出售御汤山东区二手房出售棕榈泉国际公寓二手房出售华纺易城二手房出售九章别墅二手房出售星河湾朗园二手房出售弘善家园二手房出售百环家园二手房出售紫金长安二手房出售北京壹号庄园二手房出售望园东里二手房出售首邑溪谷二手房出售 小区房价 今日家园房价走势远洋山水(北区)房价走势翠微南里房价走势首城国际房价走势新景家园(东区)房价走势丽宫别墅房价走势格拉斯小镇(别墅)房价走势碧水庄园房价走势北辰红橡墅房价走势御汤山东区房价走势棕榈泉国际公寓房价走势华纺易城房价走势九章别墅房价走势星河湾朗园房价走势弘善家园房价走势百环家园房价走势紫金长安房价走势北京壹号庄园房价走势望园东里房价走势首邑溪谷房价走势 推荐小区价格 王府花园二手房出售金色漫香苑二手房出售八家嘉园二手房出售观唐二手房出售美丽园二手房出售北京风景二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售长岛澜桥二手房出售西山美墅馆二手房出售保利西山林语二手房出售中海紫御公馆二手房出售新怡家园二手房出售林奥嘉园二手房出售九龙花园二手房出售温哥华森林二手房出售国奥村(东区)二手房出售万泉新新家园二手房出售保利百合花园二手房出售 二手房商圈 南沙滩二手房柳芳二手房北京大学二手房成寿寺二手房马家堡二手房CBD二手房十里堡二手房定慧寺二手房岳各庄二手房高米店二手房航天桥二手房公主坟二手房渤海镇二手房台湖镇二手房回龙观二手房五里店二手房怀柔城区二手房马坡二手房车道沟二手房中仓二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价上地东里小区上地东里二手房上地东里租房上地东里户型图上地东里周边配置上地东里上地东里实景图上地东里经纪人上地东里房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房上地合租租房上地公寓租房上地别墅租房上地个人租房上地一居室租房上地二居室租房上地三居室租房上地四居室租房上地五居室租房上地毛坯租房上地简单装修租房上地中等装修租房上地精装修租房上地豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;上地小区&gt;上地东里 安居客小区频道，为您提供北京上地东里1998年房价趋势、走势图，上地东里二手房均价价格信息， 及时查询上地东里房价走势、了解上地东里房价上涨还是下跌，预测上地东里房价暴跌暴涨，上地东里房价多少钱一平米？；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。</x:v>
+        <x:v>通勤/地铁：步行800米左右可达13号线上地站，步行1公里左右可达昌平线清河站，周边多个公交站点，适合在上地、西二旗上班人群，出行便利；；商超：小区内有便利店，周边步行可达万福超市、北京华联BHG Mall等，购物方便；；餐饮：小区周边餐馆、奶茶店等餐饮配套丰富，楼下即有餐饮摊位；；医院：周边有基础医疗配套，可满足日常需求；；还有公园配套，休闲便利。</x:v>
       </x:c>
       <x:c r="M80" t="str">
-        <x:v>南北通透 精装两居 低楼层 必看好房 上地 上地东里 880 万 2室2厅 95.91㎡ 海淀 上地东里 树村 南北通透 交通便捷 清晰 临地铁 上地 上地东里 568 万 2室1厅 62.17㎡ 上地上地东里2室1厅 上地 上地东里 670 万 2室1厅 56.35㎡ 上地东里三区 南北通透 小户型 装修保养还不错 上地 上地东里 560 万 1室1厅 44.9㎡ 2室1厅1卫0厨0阳 上地 上地东里 680 万 2室1厅 57.3㎡ 上地东里 新增一居 采光好 装修棒 可看房 上地 上地东里 630 万 1室1厅 47.87㎡ ### 本小区租房推荐查看更多 ### 上地三街 金隅嘉华大厦旁边上地东里小区三家合租朝南主卧可短签 上地 上地东里 合租 13号线/昌平线 朝南 _2590_ 元/月 3室1厅 25㎡ ### 上地东里主卧阳台 北京体育大学 硅谷亮城 上地信息产业基地 上地 上地东里 合租 13号线/昌平线 朝南 _2700_ 元/月 3室1厅 20㎡ ### 业主直签 近上地商圈的上地东里 家电家具齐全 随时入住可长租 上地 上地东里 整租 13号线/昌平线 朝南 _5400_ 元/月 1室 45.6㎡ ### 正南 1室1厅 上地东里 上地 上地东里 整租 13号线/昌平线 朝南 _6500_ 元/月 1室1厅 47.9㎡ ### 上地东里 精装一居 随时看房 价格可谈 配套齐全 业主签约 上地 上地东里 整租 13号线/昌平线 朝东 _5400_ 元/月 1室1厅 45.6㎡ ### 上地东里一居 安静无噪音 上地 上地东里 整租 13号线/昌平线 南北 _5600_ 元/月 1室1厅 46.7㎡ ### 周边热门小区查看更多 * 30 林大北路9号院 海淀 学院路 1998年竣工 距离4081m 75667 元/㎡2套在售 小区评测 近地铁 近学校 15号线等 四五环之间 配套齐全 7.0 分 * 231 褐石园 海淀 清华大学 2009年竣工 距离2562m 119697 元/㎡11套在售 小区评测 近地铁 近学校 四五环之间 大户型居多 户型丰富 配套齐全 6.7 分 小区单页 今日家园远洋山水(北区)翠微南里首城国际新景家园(东区)丽宫别墅格拉斯小镇(别墅)碧水庄园北辰红橡墅御汤山东区棕榈泉国际公寓华纺易城九章别墅星河湾朗园弘善家园百环家园紫金长安北京壹号庄园望园东里首邑溪谷 本板块小区大全 褐石园美和园西区颐源居同泽园西里北坞嘉园南里翠微南里五福玲珑居四季香山中鑫嘉园百旺家苑莲花小区保利西山林语香山艺墅交大嘉园华清嘉园芳怡园水云居东王庄小区紫金庄园翠湖别墅 小区二手房 今日家园二手房出售远洋山水(北区)二手房出售翠微南里二手房出售首城国际二手房出售新景家园(东区)二手房出售丽宫别墅二手房出售格拉斯小镇(别墅)二手房出售碧水庄园二手房出售北辰红橡墅二手房出售御汤山东区二手房出售棕榈泉国际公寓二手房出售华纺易城二手房出售九章别墅二手房出售星河湾朗园二手房出售弘善家园二手房出售百环家园二手房出售紫金长安二手房出售北京壹号庄园二手房出售望园东里二手房出售首邑溪谷二手房出售 小区房价 今日家园房价走势远洋山水(北区)房价走势翠微南里房价走势首城国际房价走势新景家园(东区)房价走势丽宫别墅房价走势格拉斯小镇(别墅)房价走势碧水庄园房价走势北辰红橡墅房价走势御汤山东区房价走势棕榈泉国际公寓房价走势华纺易城房价走势九章别墅房价走势星河湾朗园房价走势弘善家园房价走势百环家园房价走势紫金长安房价走势北京壹号庄园房价走势望园东里房价走势首邑溪谷房价走势 推荐小区价格 王府花园二手房出售金色漫香苑二手房出售八家嘉园二手房出售观唐二手房出售美丽园二手房出售北京风景二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售长岛澜桥二手房出售西山美墅馆二手房出售保利西山林语二手房出售中海紫御公馆二手房出售新怡家园二手房出售林奥嘉园二手房出售九龙花园二手房出售温哥华森林二手房出售国奥村(东区)二手房出售万泉新新家园二手房出售保利百合花园二手房出售 二手房商圈 南沙滩二手房柳芳二手房北京大学二手房成寿寺二手房马家堡二手房CBD二手房十里堡二手房定慧寺二手房岳各庄二手房高米店二手房航天桥二手房公主坟二手房渤海镇二手房台湖镇二手房回龙观二手房五里店二手房怀柔城区二手房马坡二手房车道沟二手房中仓二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价上地东里小区上地东里二手房上地东里租房上地东里户型图上地东里周边配置上地东里上地东里实景图上地东里经纪人上地东里房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房上地合租租房上地公寓租房上地别墅租房上地个人租房上地一居室租房上地二居室租房上地三居室租房上地四居室租房上地五居室租房上地毛坯租房上地简单装修租房上地中等装修租房上地精装修租房上地豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;上地小区&gt;上地东里 安居客小区频道，为您提供北京上地东里1998年房价趋势、走势图，上地东里二手房均价价格信息， 及时查询上地东里房价走势、了解上地东里房价上涨还是下跌，预测上地东里房价暴跌暴涨，上地东里房价多少钱一平米？；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>隔音：部分低楼层住户反馈小区安静，噪音少，但老小区整体隔音一般；；小区房龄偏老，大部分楼栋无电梯，低楼层可能存在潮湿问题；；暂未发现大量集中差评，无同名误命中信息。</x:v>
       </x:c>
       <x:c r="N80" t="str">
-        <x:v>价格线索：2026-04-04 | 811万 | 100995元/㎡；三室 * 四室 * 四室以上 * 一室 5000元/月；+0.00% * 二室 7300元/月；+0.00% * 三室 10700元/月；+16.30% * 四室 15000元/月；+0.00% * 四室以上 33500元/月；修问答登录/注册 上地东里6月均价走势 113428 元/㎡；学院路 1998年竣工 距离4081m 75667 元/㎡；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) [](https://esf.fang.com/loupan/1010216401/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **101733** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓0.43% 贷款计算器 * 二手房源 51套 * 最近成交 994套 * 楼栋总数 57栋 * 房屋总数 3750户 * 建筑类型 板楼 * 建筑年代 2000年建成 * 小区位置 上地南路与信息路交汇处东行90米路北地图 * 物业公司 北京实创上地物业管理服务有限责任公司 * 开发商 实创高科技发展总公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 李强 评分：4.6 从业信息卡 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 新增好房全明眼镜户型中低层采光好满五年 3室2厅 126.11㎡**1190**万 * #### 上地东里3室2厅东南 3室2厅 123.7㎡**1100**万 * #### 上地东里,南北通透2居室,中间层3层,看房随时 2室1厅 82.3㎡**970**万 * #### 上地东里3室2厅东南 3室2厅 116.48㎡**1050**万 ### 上地东里成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 72.30㎡ | 2026-04-24 | -- | -- | 市场信息 | | 108.15㎡ | 2026-04-12 | -- | -- | 市场信息 | | 80.40㎡ | 2026-04-04 | 811万 | 100995元/㎡ | 市场信息 | 查看全部成交 ### 上地东里价格走势 ### 上地东里房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 上地东里 海淀·上地**101734** 元/㎡ * #### 上地佳园 海淀·上地**107549** 元/㎡ * #### 尚品公寓 海淀·上地**94094** 元/㎡ * #### 上地南路8号院 海淀·上地**91334** 元/㎡ * #### 枫润家园 海淀·上地**77170** 元/㎡ ### 相关资讯 * 小区资讯北京上地东里怎么样?；* 王福海： 您好，可以的，可以不带家具北京易合房产怀柔顶秀美泉店王福海很高兴为您回答 希望能帮到您 * 张波： 小区物业可以不带家具，家电，具体跟房主沟通就可以 * 问 可以一次签三至六年的租房合同吗 * NTHfhN： 签租赁合同的具体日期长短，需要和业主协商。；58同城北京租房网，为您提供北京上地租房信息，包括上地房屋出租信息、上地合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询租房房源信息。；from=tw_xqlb_sy)上海 新房二手房租房商办装修问答登录/注册 新房二手房租房商办装修问答登录/注册 上地东里6月均价走势 113428 元/㎡ 6月挂牌均价 0.27% 比上月 均价走势 近6月 近1年 近3年 ### 本小区房源推荐查看更多 新增！；生活便利线索：上地东里房价地址周边配套分析2021-12-25 * 小区资讯最详细!；* 陈帆帆： 可以自己发布，也可以找中介带客户，还可以托管给代理公司 * 姜红丹： 你好，可以挂在网上拿着产权证进行识别认证，五八会自动推送房源代理 * 李义强： 中介门店登记下 让中介公司帮忙出租 或者自己拍些照片 挂58网 * 谭帅鹏： 可以看一下周边房产公司，免费登记，一定要整租，找个好租户，中介公司也一定要找好，小公司不找 * 问 在这个平台出租房屋，靠谱吗？；南北通透 精装两居 低楼层 必看好房 上地 上地东里 880 万 2室2厅 95.91㎡ 海淀 上地东里 树村 南北通透 交通便捷 清晰 临地铁 上地 上地东里 568 万 2室1厅 62.17㎡ 上地上地东里2室1厅 上地 上地东里 670 万 2室1厅 56.35㎡ 上地东里三区 南北通透 小户型 装修保养还不错 上地 上地东里 560 万 1室1厅 44.9㎡ 2室1厅1卫0厨0阳 上地 上地东里 680 万 2室1厅 57.3㎡ 上地东里 新增一居 采光好 装修棒 可看房 上地 上地东里 630 万 1室1厅 47.87㎡ ### 本小区租房推荐查看更多 ### 上地三街 金隅嘉华大厦旁边上地东里小区三家合租朝南主卧可短签 上地 上地东里 合租 13号线/昌平线 朝南 _2590_ 元/月 3室1厅 25㎡ ### 上地东里主卧阳台 北京体育大学 硅谷亮城 上地信息产业基地 上地 上地东里 合租 13号线/昌平线 朝南 _2700_ 元/月 3室1厅 20㎡ ### 业主直签 近上地商圈的上地东里 家电家具齐全 随时入住可长租 上地 上地东里 整租 13号线/昌平线 朝南 _5400_ 元/月 1室 45.6㎡ ### 正南 1室1厅 上地东里 上地 上地东里 整租 13号线/昌平线 朝南 _6500_ 元/月 1室1厅 47.9㎡ ### 上地东里 精装一居 随时看房 价格可谈 配套齐全 业主签约 上地 上地东里 整租 13号线/昌平线 朝东 _5400_ 元/月 1室1厅 45.6㎡ ### 上地东里一居 安静无噪音 上地 上地东里 整租 13号线/昌平线 南北 _5600_ 元/月 1室1厅 46.7㎡ ### 周边热门小区查看更多 * 30 林大北路9号院 海淀 学院路 1998年竣工 距离4081m 75667 元/㎡2套在售 小区评测 近地铁 近学校 15号线等 四五环之间 配套齐全 7.0 分 * 231 褐石园 海淀 清华大学 2009年竣工 距离2562m 119697 元/㎡11套在售 小区评测 近地铁 近学校 四五环之间 大户型居多 户型丰富 配套齐全 6.7 分 小区单页 今日家园远洋山水(北区)翠微南里首城国际新景家园(东区)丽宫别墅格拉斯小镇(别墅)碧水庄园北辰红橡墅御汤山东区棕榈泉国际公寓华纺易城九章别墅星河湾朗园弘善家园百环家园紫金长安北京壹号庄园望园东里首邑溪谷 本板块小区大全 褐石园美和园西区颐源居同泽园西里北坞嘉园南里翠微南里五福玲珑居四季香山中鑫嘉园百旺家苑莲花小区保利西山林语香山艺墅交大嘉园华清嘉园芳怡园水云居东王庄小区紫金庄园翠湖别墅 小区二手房 今日家园二手房出售远洋山水(北区)二手房出售翠微南里二手房出售首城国际二手房出售新景家园(东区)二手房出售丽宫别墅二手房出售格拉斯小镇(别墅)二手房出售碧水庄园二手房出售北辰红橡墅二手房出售御汤山东区二手房出售棕榈泉国际公寓二手房出售华纺易城二手房出售九章别墅二手房出售星河湾朗园二手房出售弘善家园二手房出售百环家园二手房出售紫金长安二手房出售北京壹号庄园二手房出售望园东里二手房出售首邑溪谷二手房出售 小区房价 今日家园房价走势远洋山水(北区)房价走势翠微南里房价走势首城国际房价走势新景家园(东区)房价走势丽宫别墅房价走势格拉斯小镇(别墅)房价走势碧水庄园房价走势北辰红橡墅房价走势御汤山东区房价走势棕榈泉国际公寓房价走势华纺易城房价走势九章别墅房价走势星河湾朗园房价走势弘善家园房价走势百环家园房价走势紫金长安房价走势北京壹号庄园房价走势望园东里房价走势首邑溪谷房价走势 推荐小区价格 王府花园二手房出售金色漫香苑二手房出售八家嘉园二手房出售观唐二手房出售美丽园二手房出售北京风景二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售长岛澜桥二手房出售西山美墅馆二手房出售保利西山林语二手房出售中海紫御公馆二手房出售新怡家园二手房出售林奥嘉园二手房出售九龙花园二手房出售温哥华森林二手房出售国奥村(东区)二手房出售万泉新新家园二手房出售保利百合花园二手房出售 二手房商圈 南沙滩二手房柳芳二手房北京大学二手房成寿寺二手房马家堡二手房CBD二手房十里堡二手房定慧寺二手房岳各庄二手房高米店二手房航天桥二手房公主坟二手房渤海镇二手房台湖镇二手房回龙观二手房五里店二手房怀柔城区二手房马坡二手房车道沟二手房中仓二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价上地东里小区上地东里二手房上地东里租房上地东里户型图上地东里周边配置上地东里上地东里实景图上地东里经纪人上地东里房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房上地合租租房上地公寓租房上地别墅租房上地个人租房上地一居室租房上地二居室租房上地三居室租房上地四居室租房上地五居室租房上地毛坯租房上地简单装修租房上地中等装修租房上地精装修租房上地豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;上地小区&gt;上地东里 安居客小区频道，为您提供北京上地东里1998年房价趋势、走势图，上地东里二手房均价价格信息， 及时查询上地东里房价走势、了解上地东里房价上涨还是下跌，预测上地东里房价暴跌暴涨，上地东里房价多少钱一平米？；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；风险线索：南北通透 精装两居 低楼层 必看好房 上地 上地东里 880 万 2室2厅 95.91㎡ 海淀 上地东里 树村 南北通透 交通便捷 清晰 临地铁 上地 上地东里 568 万 2室1厅 62.17㎡ 上地上地东里2室1厅 上地 上地东里 670 万 2室1厅 56.35㎡ 上地东里三区 南北通透 小户型 装修保养还不错 上地 上地东里 560 万 1室1厅 44.9㎡ 2室1厅1卫0厨0阳 上地 上地东里 680 万 2室1厅 57.3㎡ 上地东里 新增一居 采光好 装修棒 可看房 上地 上地东里 630 万 1室1厅 47.87㎡ ### 本小区租房推荐查看更多 ### 上地三街 金隅嘉华大厦旁边上地东里小区三家合租朝南主卧可短签 上地 上地东里 合租 13号线/昌平线 朝南 _2590_ 元/月 3室1厅 25㎡ ### 上地东里主卧阳台 北京体育大学 硅谷亮城 上地信息产业基地 上地 上地东里 合租 13号线/昌平线 朝南 _2700_ 元/月 3室1厅 20㎡ ### 业主直签 近上地商圈的上地东里 家电家具齐全 随时入住可长租 上地 上地东里 整租 13号线/昌平线 朝南 _5400_ 元/月 1室 45.6㎡ ### 正南 1室1厅 上地东里 上地 上地东里 整租 13号线/昌平线 朝南 _6500_ 元/月 1室1厅 47.9㎡ ### 上地东里 精装一居 随时看房 价格可谈 配套齐全 业主签约 上地 上地东里 整租 13号线/昌平线 朝东 _5400_ 元/月 1室1厅 45.6㎡ ### 上地东里一居 安静无噪音 上地 上地东里 整租 13号线/昌平线 南北 _5600_ 元/月 1室1厅 46.7㎡ ### 周边热门小区查看更多 * 30 林大北路9号院 海淀 学院路 1998年竣工 距离4081m 75667 元/㎡2套在售 小区评测 近地铁 近学校 15号线等 四五环之间 配套齐全 7.0 分 * 231 褐石园 海淀 清华大学 2009年竣工 距离2562m 119697 元/㎡11套在售 小区评测 近地铁 近学校 四五环之间 大户型居多 户型丰富 配套齐全 6.7 分 小区单页 今日家园远洋山水(北区)翠微南里首城国际新景家园(东区)丽宫别墅格拉斯小镇(别墅)碧水庄园北辰红橡墅御汤山东区棕榈泉国际公寓华纺易城九章别墅星河湾朗园弘善家园百环家园紫金长安北京壹号庄园望园东里首邑溪谷 本板块小区大全 褐石园美和园西区颐源居同泽园西里北坞嘉园南里翠微南里五福玲珑居四季香山中鑫嘉园百旺家苑莲花小区保利西山林语香山艺墅交大嘉园华清嘉园芳怡园水云居东王庄小区紫金庄园翠湖别墅 小区二手房 今日家园二手房出售远洋山水(北区)二手房出售翠微南里二手房出售首城国际二手房出售新景家园(东区)二手房出售丽宫别墅二手房出售格拉斯小镇(别墅)二手房出售碧水庄园二手房出售北辰红橡墅二手房出售御汤山东区二手房出售棕榈泉国际公寓二手房出售华纺易城二手房出售九章别墅二手房出售星河湾朗园二手房出售弘善家园二手房出售百环家园二手房出售紫金长安二手房出售北京壹号庄园二手房出售望园东里二手房出售首邑溪谷二手房出售 小区房价 今日家园房价走势远洋山水(北区)房价走势翠微南里房价走势首城国际房价走势新景家园(东区)房价走势丽宫别墅房价走势格拉斯小镇(别墅)房价走势碧水庄园房价走势北辰红橡墅房价走势御汤山东区房价走势棕榈泉国际公寓房价走势华纺易城房价走势九章别墅房价走势星河湾朗园房价走势弘善家园房价走势百环家园房价走势紫金长安房价走势北京壹号庄园房价走势望园东里房价走势首邑溪谷房价走势 推荐小区价格 王府花园二手房出售金色漫香苑二手房出售八家嘉园二手房出售观唐二手房出售美丽园二手房出售北京风景二手房出售流星花园三区二手房出售季景沁园二手房出售珠江罗马嘉园(西区)二手房出售长岛澜桥二手房出售西山美墅馆二手房出售保利西山林语二手房出售中海紫御公馆二手房出售新怡家园二手房出售林奥嘉园二手房出售九龙花园二手房出售温哥华森林二手房出售国奥村(东区)二手房出售万泉新新家园二手房出售保利百合花园二手房出售 二手房商圈 南沙滩二手房柳芳二手房北京大学二手房成寿寺二手房马家堡二手房CBD二手房十里堡二手房定慧寺二手房岳各庄二手房高米店二手房航天桥二手房公主坟二手房渤海镇二手房台湖镇二手房回龙观二手房五里店二手房怀柔城区二手房马坡二手房车道沟二手房中仓二手房 导航信息 北京房产网北京二手房北京新房北京租房北京二手房房价北京新房房价北京问答北京商铺出租北京商铺出售北京写字楼出租北京写字楼出售北京别墅北京公寓全国历史房价2026全国历史房价2026北京历史房价上地东里小区上地东里二手房上地东里租房上地东里户型图上地东里周边配置上地东里上地东里实景图上地东里经纪人上地东里房价北京合租租房北京公寓租房北京别墅租房北京个人租房北京一居室租房北京二居室租房北京三居室租房北京四居室租房北京五居室租房北京毛坯租房北京简单装修租房北京中等装修租房北京精装修租房北京豪华装修租房海淀合租租房海淀公寓租房海淀别墅租房海淀个人租房海淀一居室租房海淀二居室租房海淀三居室租房海淀四居室租房海淀五居室租房海淀毛坯租房海淀简单装修租房海淀中等装修租房海淀精装修租房海淀豪华装修租房上地合租租房上地公寓租房上地别墅租房上地个人租房上地一居室租房上地二居室租房上地三居室租房上地四居室租房上地五居室租房上地毛坯租房上地简单装修租房上地中等装修租房上地精装修租房上地豪华装修租房[](javascript:void(0)) 区域二手房 朝阳二手房海淀二手房昌平二手房丰台二手房大兴二手房通州二手房房山二手房顺义二手房西城二手房东城二手房密云二手房石景山二手房怀柔二手房门头沟二手房延庆二手房平谷二手房北京周边二手房[](javascript:void(0)) 北京房产网&gt;北京小区&gt;海淀小区&gt;上地小区&gt;上地东里 安居客小区频道，为您提供北京上地东里1998年房价趋势、走势图，上地东里二手房均价价格信息， 及时查询上地东里房价走势、了解上地东里房价上涨还是下跌，预测上地东里房价暴跌暴涨，上地东里房价多少钱一平米？；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：整租：1室约5400-5800元/月；，2室约6200-7500元/月；，3室约8400-11000元/月；，4室约10000元/月；合租单间约1000-2400元/月；房屋质量/户型线索：合租单间约1000-2400元/月，具体价格因面积、装修、户型不同有差异，业主直租无中介费，中介房源一般收取一个月租金作为中介费。；房龄：小区多为1993-2000年建成，房龄较老；；户型：主流户型1室到4室都有，部分为南北通透户型，采光较好；；隔音：部分低楼层住户反馈小区安静，噪音少，但老小区整体隔音一般；；装修：分为简单装修和精装修，多数在租房源家具家电齐全，可拎包入住；；生活便利线索：通勤/地铁：步行800米左右可达13号线上地站，步行1公里左右可达昌平线清河站，周边多个公交站点，适合在上地、西二旗上班人群，出行便利；；商超：小区内有便利店，周边步行可达万福超市、北京华联BHG Mall等，购物方便；；餐饮：小区周边餐馆、奶茶店等餐饮配套丰富，楼下即有餐饮摊位；；医院：周边有基础医疗配套，可满足日常需求；；还有公园配套，休闲便利。；风险线索：隔音：部分低楼层住户反馈小区安静，噪音少，但老小区整体隔音一般；；小区房龄偏老，大部分楼栋无电梯，低楼层可能存在潮湿问题；；暂未发现大量集中差评，无同名误命中信息。</x:v>
       </x:c>
       <x:c r="O80" t="str">
-        <x:v>1. 【北京上地东里小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010216401.htm
-2. 上地租房_北京海淀上地租房信息|上地租房价格信息-58租房网 https://bj.zf.58.com/shangdi/
-3. 上地东里房价, 上地东里上地东里房价走势图, 上地东里价格均价多少钱-安居客 https://m.anjuke.com/bj/trendency/community/55506/
-4. 2023年8月北京海淀区公租房价格一览表- 北京本地宝 https://bj.bendibao.com/zffw/2023821/351359.shtm
-5. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. 上地东里房价/租金信息 
+2. 上地东里 南向 2室1厅1卫 通勤优 价格美观 http://m.anjuke.com/bj/rent/4564251986373639-3/
+3. 上地东里 3室1卫1厅 75平精装修 2400元/月 http://m.fang.com/zf/bj/3_478947216.html
+4. 稳租价格好聊 朝南正规一居室 楼层适中 明厅明厨明卧带阳台 http://m.anjuke.com/dongyang/rent/4564254559953925-3/
+5. 海淀上地东里 1室1厅 45㎡ 5600元/月 http://m.fang.com/note/bj_2647574.html
+6. 【多图】上地东里，上地租房，正规小区 一室一卫 可月付 D租 无中介 西二旗 五道口，海淀租房 https://bj.zu.anjuke.com/fangyuan/3959838766623752?lego_tid=002f2443-0fa6-4c3b-8eea-a9aa14f74209&amp;psid=0cff1900e4a8f50f8e0bf1192eb9305a&amp;shangquan_id=1238</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -4201,38 +4418,44 @@
         <x:v>北京市昌平区龙域中路与龙域北街交叉口西北100米</x:v>
       </x:c>
       <x:c r="E81" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F81" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G81" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H81" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I81" t="str">
-        <x:v>昌平热门大社区，房源较新且户型好，性价比高，深受互联网从业者青睐，通勤便利。</x:v>
+        <x:v>房龄相对较新且户型采光好，租金性价比高，是西二旗周边平衡品质与预算的优选。</x:v>
       </x:c>
       <x:c r="J81" t="str">
-        <x:v>2026-05-10 | 331万 | 33516元/㎡；4000_ 元/m² 融泽嘉园，小区价格50184元/㎡；租小张02-28 21:38 房东直租，2100元/月</x:v>
+        <x:v>合租单间/次卧：1200-2500元/月；，主卧：1500-2300元/月；整租：2000-8300元/月；，其中87平3室1厅整租约6600元/月</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **41701** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓0.93% 贷款计算器 * 二手房源 103套 * 最近成交 1518套 * 楼栋总数 47栋 * 房屋总数 10750户 * 建筑类型 板楼 * 建筑年代 2014年建成 * 小区位置 西二旗北侧龙域中路金域华府北面地图 * 物业公司 长城物业集团股份有限公司 * 开发商 北京华融金晖置业有限公司 #### 推荐经纪人查看全部经纪人 ##### 寇东锋 评分：4.9 从业信息卡 百科 闪电回复 ##### 白川 评分：4.9 从业信息卡 百科 闪电回复 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 ### 融泽嘉园主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010748145/photo/?；北京吉屋网提供北京融泽嘉园二手房出售信息、融泽嘉园二手房价格，包括及时更新北京融泽嘉园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 融泽嘉园_北京融泽嘉园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_昌平小区_&gt;_融泽嘉园 更新于 2026-06-01 10:58:22 [](https://bj.jiwu.com/tu/20552715.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552716.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552717.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552718.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552719.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552720.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552721.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552722.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552723.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552724.html "融泽嘉园实景图图片") # 融泽嘉园 别名：融泽嘉园 加入本地买房群 关注 _北京 - 昌平 - 昌平西二旗北侧龙域中路金域华府北面_ 发地址到手机 参考均价 _50184 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2014_ 小区户数 _7064户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-72群（359） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(2)2室(9)3室(4) 全部户型 [](https://bj.jiwu.com/huxing/2012083.html "融泽嘉园3室1厅1卫108㎡户型图")3室1厅1卫 108㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2012084.html "融泽嘉园2室1厅1卫80㎡户型图")2室1厅1卫 80㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2012085.html "融泽嘉园1室1厅1卫63㎡户型图")1室1厅1卫 63㎡咨询户型房源 小区评测报告 ？</x:v>
+        <x:v>房龄：小区为二期开发，部分房源已满5年；；户型多样，有全明户型，空间采光通风较好，多数为精装修；；部分楼栋二期建筑质量更好，有评价称部分小区居住安静，物业整体认真负责；；未查到明确普遍隔音问题反馈；</x:v>
       </x:c>
       <x:c r="L81" t="str">
-        <x:v>北京吉屋网提供北京融泽嘉园二手房出售信息、融泽嘉园二手房价格，包括及时更新北京融泽嘉园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 融泽嘉园_北京融泽嘉园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_昌平小区_&gt;_融泽嘉园 更新于 2026-06-01 10:58:22 [](https://bj.jiwu.com/tu/20552715.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552716.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552717.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552718.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552719.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552720.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552721.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552722.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552723.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552724.html "融泽嘉园实景图图片") # 融泽嘉园 别名：融泽嘉园 加入本地买房群 关注 _北京 - 昌平 - 昌平西二旗北侧龙域中路金域华府北面_ 发地址到手机 参考均价 _50184 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2014_ 小区户数 _7064户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-72群（359） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(2)2室(9)3室(4) 全部户型 [](https://bj.jiwu.com/huxing/2012083.html "融泽嘉园3室1厅1卫108㎡户型图")3室1厅1卫 108㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2012084.html "融泽嘉园2室1厅1卫80㎡户型图")2室1厅1卫 80㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2012085.html "融泽嘉园1室1厅1卫63㎡户型图")1室1厅1卫 63㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?</x:v>
-      </x:c>
-      <x:c r="M81" t="str"/>
+        <x:v>通勤：距离18号线龙泽西约734米，13号线龙泽站约1467米，靠近北郊农场站，临近西二旗、上地软件园，适合周边上班人群；；医院：往西2公里是积水潭医院回龙观院区；；餐饮等生活配套齐全，周边餐饮选择多；；社区有免费文艺活动，生活丰富；</x:v>
+      </x:c>
+      <x:c r="M81" t="str">
+        <x:v>未明确发现大规模差评，部分合租房源价格差异较大，需注意房源真实性，未发现同名误命中。；未明确发现大规模差评，部分合租房源价格差异较大，需注意房源真实性，未发现同名误命中</x:v>
+      </x:c>
       <x:c r="N81" t="str">
-        <x:v>价格线索：2026-05-10 | 331万 | 33516元/㎡；4000_ 元/m² 融泽嘉园，小区价格50184元/㎡；租小张02-28 21:38 房东直租，2100元/月；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) [](https://esf.fang.com/loupan/1010748145/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **41701** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月 ↓0.93% 贷款计算器 * 二手房源 103套 * 最近成交 1518套 * 楼栋总数 47栋 * 房屋总数 10750户 * 建筑类型 板楼 * 建筑年代 2014年建成 * 小区位置 西二旗北侧龙域中路金域华府北面地图 * 物业公司 长城物业集团股份有限公司 * 开发商 北京华融金晖置业有限公司 #### 推荐经纪人查看全部经纪人 ##### 寇东锋 评分：4.9 从业信息卡 百科 闪电回复 ##### 白川 评分：4.9 从业信息卡 百科 闪电回复 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 ### 融泽嘉园主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010748145/photo/?；北京吉屋网提供北京融泽嘉园二手房出售信息、融泽嘉园二手房价格，包括及时更新北京融泽嘉园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 融泽嘉园_北京融泽嘉园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_昌平小区_&gt;_融泽嘉园 更新于 2026-06-01 10:58:22 [](https://bj.jiwu.com/tu/20552715.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552716.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552717.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552718.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552719.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552720.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552721.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552722.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552723.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552724.html "融泽嘉园实景图图片") # 融泽嘉园 别名：融泽嘉园 加入本地买房群 关注 _北京 - 昌平 - 昌平西二旗北侧龙域中路金域华府北面_ 发地址到手机 参考均价 _50184 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2014_ 小区户数 _7064户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-72群（359） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(2)2室(9)3室(4) 全部户型 [](https://bj.jiwu.com/huxing/2012083.html "融泽嘉园3室1厅1卫108㎡户型图")3室1厅1卫 108㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2012084.html "融泽嘉园2室1厅1卫80㎡户型图")2室1厅1卫 80㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2012085.html "融泽嘉园1室1厅1卫63㎡户型图")1室1厅1卫 63㎡咨询户型房源 小区评测报告 ？；生活便利线索：北京吉屋网提供北京融泽嘉园二手房出售信息、融泽嘉园二手房价格，包括及时更新北京融泽嘉园二手房房源、价格走势、户型图、业主论坛、生活配套。；# 融泽嘉园_北京融泽嘉园小区怎么样、二手房出售价格信息- 北京吉屋网 * 首页 * 新房 * 找楼盘 * 楼盘动态 * 二手房 * 二手小区 * 二手房源 * 楼市 * 本地楼市 * 全国楼市 * 大咖专栏 * 房价走势 * 帮找房 * 帮我找房 * 置业管家 * 知识库 * 买房攻略 * 房产百科 * 买房问答 * 手机找房微信扫码 小程序找房 服务热线：0755-26404403 登录 [退出] .png) 二手房 北京 北京买房_&gt;_北京小区_&gt;_昌平小区_&gt;_融泽嘉园 更新于 2026-06-01 10:58:22 [](https://bj.jiwu.com/tu/20552715.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552716.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552717.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552718.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552719.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552720.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552721.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552722.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552723.html "融泽嘉园实景图图片")[](https://bj.jiwu.com/tu/20552724.html "融泽嘉园实景图图片") # 融泽嘉园 别名：融泽嘉园 加入本地买房群 关注 _北京 - 昌平 - 昌平西二旗北侧龙域中路金域华府北面_ 发地址到手机 参考均价 _50184 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2014_ 小区户数 _7064户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-72群（359） * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 * 最近都说是上车好时候，大家怎么看 * 我觉得现在的确可以考虑 * 孩子明年上小学，现在买哪里合适啊 * 我想买个两居室，哪个盘比较好？；* 楼盘周边配套齐全，挺不错的 * 最近有哪些楼盘在搞促销优惠活动吗 * 最近纠结买哪里好，帮我比较下呗 加入群聊 二手房源 当前没有符合条件的房源 订阅小区二手房源上新提醒，好房抢先看 订阅通知 最近成交记录 查询最近房源成交记录，帮助参考出价 成交查询 小区户型 1室(2)2室(9)3室(4) 全部户型 [](https://bj.jiwu.com/huxing/2012083.html "融泽嘉园3室1厅1卫108㎡户型图")3室1厅1卫 108㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2012084.html "融泽嘉园2室1厅1卫80㎡户型图")2室1厅1卫 80㎡咨询户型房源 [](https://bj.jiwu.com/huxing/2012085.html "融泽嘉园1室1厅1卫63㎡户型图")1室1厅1卫 63㎡咨询户型房源 小区评测报告 ？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?</x:v>
+        <x:v>价格线索：合租单间/次卧：1200-2500元/月；，主卧：1500-2300元/月；整租：2000-8300元/月；，其中87平3室1厅整租约6600元/月；房屋质量/户型线索：房龄：小区为二期开发，部分房源已满5年；；户型多样，有全明户型，空间采光通风较好，多数为精装修；；部分楼栋二期建筑质量更好，有评价称部分小区居住安静，物业整体认真负责；；未查到明确普遍隔音问题反馈；；生活便利线索：通勤：距离18号线龙泽西约734米，13号线龙泽站约1467米，靠近北郊农场站，临近西二旗、上地软件园，适合周边上班人群；；医院：往西2公里是积水潭医院回龙观院区；；餐饮等生活配套齐全，周边餐饮选择多；；社区有免费文艺活动，生活丰富；；风险线索：未明确发现大规模差评，部分合租房源价格差异较大，需注意房源真实性，未发现同名误命中。；未明确发现大规模差评，部分合租房源价格差异较大，需注意房源真实性，未发现同名误命中</x:v>
       </x:c>
       <x:c r="O81" t="str">
-        <x:v>1. 【北京融泽嘉园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010748145.htm
-2. 融泽嘉园_北京融泽嘉园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/802925.html
-3. 北京昌平合租1居室房源出租, 3400 RMB/月, 近地鐵18号线, 溫馨小窩、乾淨治愈 - Wellcee唯心所寓 https://www.wellcee.com/tw/rent-apartment/1773844000606566
-4. 融泽嘉园 https://m.douban.com/group/624160/</x:v>
+        <x:v>1. ["融泽嘉园出租","https://m.fang.com/houses/zf_269195_bj/p3/"]
+2. ["融泽嘉园6号院 3室1厅1卫","http://m.anjuke.com/dongyang/rent/4577067754302469-2/"]
+3. ["业主自评 融泽嘉园二期","https://m.5i5j.com/bj/ershoufang/houseevaluate/504528836.html"]
+4. 【融泽嘉园出租 https://m.fang.com/houses/zf_269195_bj/p3/
+5. 融泽嘉园6号院 3室1厅1卫 http://m.anjuke.com/dongyang/rent/4577067754302469-2/
+6. 【融泽嘉园租房信息 https://m.fang.com/houses/zf_264298_bj/p1/
+7. 我爱我家WAP https://m.5i5j.com/bj/ershoufang/houseevaluate/504528836.html
+8. 【融泽嘉园出租房 https://m.fang.com/houses/zf_253435_bj/p0h5/</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -4249,40 +4472,39 @@
         <x:v>北京市海淀区龙背村路海淀区小星星双语艺术幼儿园</x:v>
       </x:c>
       <x:c r="E82" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F82" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G82" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H82" t="n">
-        <x:v>2</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="I82" t="str">
-        <x:v>搜索证据与目标区域严重偏离，涉及多为远郊豪宅，对网易员工通勤参考价值极低。</x:v>
+        <x:v>证据存在严重的异地信息混淆，北京海淀区实地租金与质量信息不足，参考价值较低。</x:v>
       </x:c>
       <x:c r="J82" t="str">
-        <x:v>-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；光明胡同 可注册办公首次出租南北通透 180000 元/月；307㎡|朝南北 海淀-万柳-万城华府 55000 元/月；7㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月；营-信德园 可注册办公首次出租南北通透 10500 元/月</x:v>
+        <x:v>区颐美园，对应整租价格：1室约1600-2300元/月；，2室约2000-3000元/月；，3室约2400-3300元/月；，4室约3200元/月</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出��南北通透 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 ���城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 4室2厅泰禾西府大院 整租|4室2厅|197㎡|朝东南北 丰台-丽泽桥-泰禾西府大院 52000 元/月 ) 南北通透国锐金嵿5室2厅精装修 整租|5室2厅|277㎡|朝南北 大兴-亦庄-国锐金嵿 30000 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？</x:v>
+        <x:v>长沙同名颐美园：2000年建成，房龄约25-26年，户型以二居、三居为主，户型周正、南北通透居多，多为精装修，物业为富通嘉善物业管理有限公司，物业费约1.2-1.5元/㎡/月；；暂未查询到目标北京海淀区颐美园的房子质量相关公开信息，无隔音相关评价；</x:v>
       </x:c>
       <x:c r="L82" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出��南北通透 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 ���城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 在张自忠有一方。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？</x:v>
-      </x:c>
-      <x:c r="M82" t="str">
-        <x:v>) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出��南北通透 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>长沙同名颐美园：周边2km内有多个地铁站（3号线、6号线），公交站点密集，配套有商场、医院，生活便利；；目标北京海淀区龙背村路该位置邻近龙背村路，周边有超市发、天秀生活超市、中发百旺商城等商超，邻近地铁16号线马连洼站、4号线安河桥北，通勤便利，邻近北京本地医院和基础餐饮配套；</x:v>
+      </x:c>
+      <x:c r="M82" t="str"/>
       <x:c r="N82" t="str">
-        <x:v>价格线索：-光泽胡同 可注册办公首次出租南北通透 72000 元/月； ) 252平3室2厅3卫9.5万/月；㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月；朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月；光明胡同 可注册办公首次出租南北通透 180000 元/月；307㎡|朝南北 海淀-万柳-万城华府 55000 元/月；7㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月；营-信德园 可注册办公首次出租南北通透 10500 元/月；房屋质量/户型线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出��南北通透 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 ���城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 在张自忠有一方。；可自行收拾 整租|3室2厅|100㎡|朝南 东城-东四-东四十二条 南北通透全装全配采光好 16500 元/月 ) 业主人很好房子更棒 首次出租温泉CEO公馆平层 高质 整租|4室2厅|187㎡|朝南 海淀-四季青-汤泉逸墅别墅 22000 元/月 ) 4室2厅泰禾西府大院 整租|4室2厅|197㎡|朝东南北 丰台-丽泽桥-泰禾西府大院 52000 元/月 ) 南北通透国锐金嵿5室2厅精装修 整租|5室2厅|277㎡|朝南北 大兴-亦庄-国锐金嵿 30000 元/月 ) 康桥水郡 5室3卫3厅 410.24平精装修 126 整租|5室3厅|410㎡|朝西南北 海淀-万柳-康桥水郡 90000 元/月 ) 2室2厅中海城圣朝菲 整租|2室2厅|100㎡|朝南北 朝阳-十八里店-中海城圣朝菲 7600 元/月 ) 檀香山5室2厅精装修 整租|5室2厅|240㎡|朝南 海淀-四季青-檀香山 40000 元/月 共1页 * APP下载 * 发布房源 * 删除房源 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；生活便利线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出��南北通透 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；有座三居室出租 整租|3室2厅|100㎡|朝南 东城-安定门-箭厂胡同 交通便利周边配套齐独门独卫 15000 元/月 ) 能容纳20多人的客厅。；北新桥胡同出租 整租|3室2厅|150㎡|朝南 东城-东直门-北新桥头条 南北通透采光好独门独卫 18000 元/月 ) 5室2厅光大水墨风景 整租|5室2厅|216㎡|朝西南北 海淀-万柳-光大水墨风景 36000 元/月 ) 4室2厅中海望京府南区 整租|4室2厅|209㎡|朝南 朝阳-来广营-中海望京府 25000 元/月 ) 全空房,有钥匙3室2厅北京花园,朝阳公园,亮马河 整租|3室2厅|202㎡|朝南北 朝阳-燕莎-北京花园 25000 元/月 ) 西宸原著别墅4室3厅豪华装修 整租|4室3厅|334㎡|朝南 丰台-丽泽桥-西宸原著别墅 90000 元/月 ) 西城区 中轴线鼓楼景山什刹海 接待会所KTV 临街四 整租|6室3厅|220㎡|朝南 ���城-地安门-前海四合院 周边配套齐首次出租全装全配 100000 元/月 ) 南北通透西宸原著4室3厅精装修 整租|4室3厅|316㎡|朝南北 丰台-丽泽桥-西宸原著 60000 元/月 ) 在张自忠有一方。；# 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 ## 北京 [切换城市] 58APP 扫描二维码下载 **58首页** 登录|注册 个人中心 我的账户我的收藏我的求职举报中心 商家中心 我的发布我要招人账户资料我的资金商家推广 帮助中心 ### 客户 客户帮助|网站建议 反欺诈联盟|维权中心 ### 商户 商户帮助|渠道招商 商家推广|成为会员 推广热线|学习中心 处罚申诉 联系客服 网站导航 * ### 房产 房屋出租 整租|合租|公寓 房屋买卖 二手房|新房|卖房 商业地产 商铺出租|商铺出售 写字楼出租|生意转让 厂房|仓库|土地 * ### 汽车 车辆买卖 二手车|新车|卖车 车价评估 车辆服务 驾校教练|租车 维修保养 4S店|保险|过户/验车 汽配|保养|美容 * ### 二手 电子/机械 手机|电脑|数码|设备 家电/家具 家电|家具|母婴 票务转让 演出票|电影票 ### 宠物 狗|猫|花鸟虫鱼 * ### 招聘 求职找工作 全职|兼职|创建简历 热招职位|北京招聘会 企业招人才 简历搜索|发布职位 急速招聘|背景调查 * ### 同城服务 家政服务|婚庆摄影 装修建材|商务服务 教育培训|创业加盟 旅游酒店|休闲娱乐 餐饮美食|批发采购 农林牧副|二手回收 丽人 * ### 手机应用 58同城 58到家 赶集直招 安居客 招才猫 英才直聘 驾校一点通 转转 58 微信公众号 [](https://bj.58.com/house.shtml)免费发布 * 租房 * 二手房 * 新房 * 商铺 * 写字楼 * 仓库 * 土地 * 车位 * 租房首页 * 整租房 * 合租房 * 个人租房 * 公寓出租 * 租房小区 * 租金走势 * 租金排行榜;；) 北京房产网&gt;北京租房网&gt; 海淀租房网 # 海淀出租房源 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 # 海淀整租房 查看更多 * 9800 元整租中关村东南小区2室1厅 2室1厅 / 62.4㎡ 推荐理由： 邻地铁 精装修 * 13000 元整租皂君庙皂君庙甲16号院2室2厅 2室2厅 / 108.7㎡ 推荐理由： 邻地铁 配套齐全 精装修 * 4900 元碧桐园(商住楼) 1室1厅1卫 1室1厅 / 45㎡ 推荐理由： 新上 邻地铁 * 13000 元整租甘家口中海馥园2室1厅 2室1厅 / 91.71㎡ 推荐理由： 邻地铁 精装修 * 5000 元育英陪读好房 二层一居室 万寿路西街11号院低楼层1居室 1室1厅 / 38.19㎡ 推荐理由： 独卫一居 邻地铁 配套齐全 有阳台 首次出租 * 7300 元皂君庙双榆树南里中楼层2居室 2室1厅 / 50.0㎡ 推荐理由： 邻地铁 精装修 * 7000 元整租西直门上园村2室1厅 2室1厅 / 58.2㎡ 推荐理由： 邻地铁 精装修 * 9200 元地铁10号线车道沟站万泉小学曙光花园望山园配套齐全陪读 2室1厅 / 101.84㎡ 推荐理由： 邻地铁 精装修 * 8500 元田村田村雪芳园高楼层2居室 2室1厅 / 104.91㎡ 推荐理由： 邻地铁 精装修 * 7600 元整租上地当代城市家园2室1厅 2室1厅 / 84.45㎡ 推荐理由： 邻地铁 精装修 # 海淀合租房 查看更多 * 2000 元西北旺 西山锦绣府 朝南主卧 电梯房 人少干净 4室1厅 / 14㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 * 1400 元永卫西路 创业小次卧出租 价格1400 包物业包取暖 5室1厅 / 10㎡ 推荐理由： 独卫 独立阳台 邻地铁 配套齐全 精装修 南北通透 * 3200 元双榆树东里 3室1厅1卫 3室1厅 / 12㎡ 推荐理由： 独卫 邻地铁 精装修 南北通透 * 3500 元我爱我家相寓 小西天志强南园低楼层3居室主卧 3室1厅 / 16.0㎡ 推荐理由： 邻地铁 精装修 * 2800 元可住3人 0杂费 可月付 和泓四季 万柳 中关村 世纪金源 3室1厅 / 12㎡ 推荐理由： 独卫 独立阳台 押一付一 配套齐全 精装修 南北通透 首次出租 * 5000 元紫竹桥，花园桥地铁6号，北洼路物美超市，首师大，七贤村慈寿寺 1室1厅 / 47.54㎡ 推荐理由： 独卫 邻地铁 配套齐全 精装修 南北通透 首次出租 * 2954 元四季青美丽星苑中楼层3居室次卧2 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 * 1822 元我爱我家相寓 西北旺中海枫涟山庄高楼层5居室次卧3 5室2厅 / 14.0㎡ 推荐理由： 邻地铁 精装修 * 3800 元我爱我家相寓 北京语言大学家属区高楼层3居室主卧 3室1厅 / 20.0㎡ 推荐理由： 邻地铁 精装修 * 2850 元我爱我家相寓 皂君庙皂君庙乙2号院高楼层3居室主卧 3室1厅 / 25.0㎡ 推荐理由： 邻地铁 精装修 # 海淀公寓租房 查看更多 暂无数据 # 海淀租房小区 查看更多 * 翠微中里 北京/海淀/万寿路乙15号 建筑年代：2009年 建筑类别：多层 * 紫金长安 北京/海淀/西翠路17号 建筑年代：2008年 建筑类别：高层 * 御汤山熙园 北京/昌平/顺沙路,近秦上路 建筑年代：2016年 建筑类别：低层 * 美景东方 北京/朝阳/松榆南路38号 建筑年代：2008年 建筑类别：高层 * 碧水庄园 北京/昌平/定泗路 建筑年代：1994年 建筑类别：低层 * 翠微南里 北京/海淀/玉渊潭南路 建筑年代：1992年 建筑类别：多层 * 珠光逸景(二号院) 北京/丰台/太柏西路2号 建筑年代：2014年 建筑类别：多层 * 首城国际 北京/朝阳/广渠路36号 建筑年代：2009年 建筑类别：高层 * 大成郡 北京/丰台/大成路 建筑年代：2011年 建筑类别：多层 * 北京北 北京/昌平/中滩村大街8号 建筑年代：2009年 建筑类别：高层 海淀租金走势 * 全部 * 一室 * 二室 * 三室 * 四室 * 四室以上 * 一室 5200元/月-1.89% * 二室 7000元/月+1.45% * 三室 11800元/月+2.61% * 四室 25000元/月+0.34% * 四室以上 40000元/月+0.00% ## 海淀租金排行榜 ## 海淀租金最高的小区 * 小区名称 月租金 涨跌幅 * 1.中间建筑50000元/月 0.00% * 2.西山美墅馆24000元/月-11.11% ↓ * 3.万城华府龙园18800元/月 0.00% * 4.西钓鱼台嘉园18000元/月 0.00% * 5.长银大厦14250元/月 90.00% ↑ ## 海淀租金最低的小区 * 小区名称 月租金 涨跌幅 * 1.白水洼村住房1150元/月 0.00% * 2.梅所屯村住房1300元/月 8.33% ↑ * 3.上庄镇前章村住房1300元/月 0.00% * 4.苏州街33号公寓1300元/月-13.33% ↓ * 5.双塔村住房1300元/月 0.00% ## 海淀租金上涨最多的小区 * 小区名称 月租金 涨跌幅 * 1.钓鱼台山庄7200元/月 125.00% ↑ * 2.玲珑苑5600元/月 124.00% ↑ * 3.长银大厦14250元/月 90.00% ↑ * 4.瑞新里小区7500元/月 78.57% ↑ * 5.机械研究院(东区)8200元/月 73.66% ↑ ## 海淀租金下降最多的小区 * 小区名称 月租金 涨跌幅 * 1.博雅德园2500元/月-58.33% ↓ * 2.琨御府(公寓住宅)5600元/月-48.62% ↓ * 3.清河公交总公司党校宿舍2600元/月-46.94% ↓ * 4.学院南路乙10号院4500元/月-32.84% ↓ * 5.阜成路8号院6200元/月-29.55% ↓ # 海淀租房房产中介 * 马世超 北京睿泽晟房地产经纪有限公司 * 姜伟琦 北京欢颜住房租赁有限公司 * 郝健柱 北京麦田房产经纪有限公司 * 张宇 北京佰亿居住房租赁有限公司 * 于德洋 北京相寓住房租赁有限公司 * 王帅 北京我爱我家房地产经纪有限公司 * 朱秒 北京住小满住房租赁有限责任公司 * 董茂森 北京安居联行房地产经纪有限公司 * 王坤衡 北京金寓之家住房租赁有限公司 * 李战胜 北京信富住房租赁有限公司 ## 租房房产问答 * 问 出租房子在哪里登记？；风险线索：) 西海 新街口东街,光泽胡同精装独院 整租|15室15厅|551㎡|朝南北 西城-德胜门-光泽胡同 可注册办公首次出租南北通透 72000 元/月 ) 252平3室2厅3卫9.5万/月,一梯一户品质房 整租|3室2厅|251㎡|朝南北 朝阳-朝阳公园-北京壹号院 95000 元/月 ) 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马 整租|4室2厅|317㎡|朝东南北 朝阳-朝阳公园-北京壹号院 115000 元/月 ) 西城丨府右街西单金融街西四丨带车库带多车位丨带家具带 整租|10室3厅|421㎡|朝南北 西城-西单-光明胡同 可注册办公首次出租南北通透 180000 元/月 ) 15套起看 万城华府万柳书院 平层四居室老业主委托 整租|4室3厅|307㎡|朝南北 海淀-万柳-万城华府 55000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 大观园水利部广安门白纸坊鸭子桥青年湖南二环电梯高层大 整租|3室2厅|139㎡|朝东北 西城-菜户营-信德园 可注册办公首次出租南北通透 10500 元/月 ) 东城 王府井东四美术馆 商务宴请独栋四合院出租 院内 整租|8室5厅|800㎡|朝南北 东城-灯市口-前厂胡同 可注册办公首次出租南北通透 200000 元/月 ) 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位") 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 55000 元/月 ) 干净整洁 万柳书院 万城华府海园龙湖颐和原著 4居看 整租|5室3厅|307㎡|朝东 海淀-万柳-万城华府别墅 65000 元/月 ) 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕") 整租|8室2厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 75000 元/月 ) 东城丨东单王府井东四崇文门丨带车位带家具丨带KTV 整租|8室3厅|351㎡|朝南北 东城-东单-西镇江胡同 可注册办公首次出租南北通透 140000 元/月 ) 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨 整租|8室4厅|231㎡|朝南北 西城-地安门-后小井胡同 可注册办公首次出租南北通透 60000 元/月 ) 20套起看万城华府四面采光好山阁 万城华府大平层 2 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 75000 元/月 ) 15套起看 有钥匙看房随时万城华府尚园 中间位置 三 整租|4室3厅|351㎡|朝南北 海淀-万柳-万城华府尚园 75000 元/月 ) 主做万柳书院万城华府 万泉新新龙湖颐原著看房随时 有 整租|4室2厅|307㎡|朝南北 海淀-万柳-万城华府龙园 58000 元/月 ) 张自忠路四合院独院出租 380平 北京四合院出租出售 整租|9室9厅|380㎡|朝西南 西城-地安门-什刹海四合院 可注册办公首次出租南北通透 83333 元/月 ) 西城丨西单西四金融街平安里丨临胡同口带车库丨新装带家 整租|10室3厅|501㎡|朝南北 西城-西四-前车胡同小区 可注册办公首次出租南北通透 250000 元/月 ) 新出位置安静 可直接入住 楼层好 330平米 三面采 整租|3室3厅|330㎡|朝南北 海淀-万柳-万柳书院 138000 元/月 ) 15套可看 高层 出租 万城华府一梯一户平层好山阁看 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府龙园 80000 元/月 ) 东城区 东四大街张自忠路徽派会所接待四合院出租 带车 整租|7室5厅|600㎡|朝南北 东城-东四-隆福寺四合院 可注册办公首次出租南北通透 210000 元/月 ) 大常实拍西城区|近恭王府后海的正座带车位非常方正的四 整租|10室4厅|261㎡|朝南北 西城-新街口-簸箩仓胡同 可注册办公首次出租南北通透 78000 元/月 ) 东城丨东四北新桥雍和宫东直门丨 整租|8室3厅|461㎡|朝南北 东城-东四-八宝坑胡同 可注册办公首次出租南北通透 80000 元/月 ) 西城丨西四西单府右街金融街丨临街带5车位丨豪装带家具 整租|12室4厅|1401㎡|朝南北 西城-西四-小拐棒胡同 可注册办公首次出租南北通透 400000 元/月 ) 15套可看 万城华府海园 万柳疏书院 多套可看 干净 整租|4室3厅|325㎡|朝南北 海淀-万柳-万城华府海园 80000 元/月 ) 东城区 北新桥 东四 张自忠路(二进四合院)") 整租|10室2厅|501㎡|朝南北 东城-东四-九道湾东巷 可注册办公首次出租南北通透 120000 元/月 ) 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV") 整租|6室2厅|221㎡|朝南北 东城-东四-大菊胡同 可注册办公首次出��南北通透 55000 元/月 ) 30套可看高层出租万城华府万柳书院 一层一户看房随时 整租|5室3厅|395㎡|朝南北 海淀-万柳-万城华府海园 85000 元/月 ) 东城区 东四王府井 精装商务会馆接待四合院出租 临主 整租|7室3厅|650㎡|朝南 东城-东四-东四三条 可注册办公首次出租南北通透 300000 元/月 ) 海淀世纪城时雨园精装两居 东南向电梯房 月租1200 整租|2室1厅|105㎡|朝东南 海淀-世纪城-时雨园 12000 元/月 ) 15套起看有钥匙 万城华府万柳书院 看房随时8居6卫 整租|8室7厅|800㎡|朝南 海淀-万柳-万城华府 180000 元/月 ) 康桥水郡 6室3厅3卫 采光充足 格局方正 整租|6室3厅|410㎡|朝南北 海淀-万柳-康桥水郡 90000 元/月 ) 东城区安定门鼓楼地铁新装三进四合院临主街带多个车位有 整租|12室6厅|981㎡|朝南北 东城-安定门-马园胡同 可注册办公首次出租南北通透 240000 元/月 ) 香江花园7室3厅精装修 整租|7室3厅|335㎡|朝南 朝阳-来广营-香江花园 80000 元/月 ) 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看 整租|7室3厅|335㎡|朝北 朝阳-来广营-香江花园 80000 元/月 ) 中建玖合府 精装四居 南西北向高层 电梯 整租|4室2厅|165㎡|朝西南北 朝阳-太阳宫-中建玖合府 首次出租采光好独门独卫 29000 元/月 ) 东城丨雍和宫北新桥东四东直门丨带车位精装修带家具丨水 整租|6室2厅|241㎡|朝南北 东城-安定门-永康胡同 可注册办公首次出租南北通透 45000 元/月 ) 东城丨景山王府井东四东单丨带多个固定车位丨带家具四合 整租|5室2厅|201㎡|朝南北 东城-东四-南剪子巷 可注册办公首次出租南北通透 45000 元/月 ) 长岛澜桥南花园双拼 京西旁 4居室 诚租可看房 整租|4室3厅|357㎡|朝北 朝阳-来广营-长岛澜桥 43000 元/月 ) 涧桥泊屋 2室2厅 精装修 整租|2室2厅|118㎡|朝东西 海淀-万柳-涧桥泊屋 16000 元/月 ) 4室2厅鲁艺上河村三区 整租|4室2厅|263㎡|朝南北 海淀-世纪城-上河村 30000 元/月 ) 4室2厅鲁艺上河村二区 整租|4室2厅|230㎡|朝南北 海淀-世纪城-鲁艺上河村二区 35500 元/月 ) 4室2厅世纪城三期晴雪园 整租|4室2厅|220㎡|朝南北 海淀-世纪城-世纪城晴雪园 35000 元/月 ) 远大园一区精装四居 南北通透 有大,看房随时 整租|4室2厅|212㎡|朝南北 海淀-世纪城-远大园一区 交通便利南北通透 18000 元/月 ) 全空房,高层边户大四居,落地窗,视野开阔,安静不吵, 整租|4室2厅|253㎡|朝南北 朝阳-三元桥-凤凰城二期 30000 元/月 ) 国子监。；手机版： 海淀租房网 * 城市租房网 * 区域租房网 * 商圈租房网 * 城市租房 * 区域租房 * 租房搜索 * 琼海租房网 * 济源租房网 * 汝州租房网 * 绥化租房网 * 潜江租房网 * 沅江租房网 * 任丘租房网 * 阜宁租房网 * 沂南租房网 * 高平租房网 * 海淀租房网 * 房山租房网 * 石景山租房网 * 门头沟租房网 * 平谷租房网 * 昌平租房网 * 顺义租房网 * 延庆租房网 * 大兴租房网 * 朝阳租房网 * 磁各庄租房网 * 大兴机场租房网 * 大兴周边租房网 * 高米店租房网 * 观音寺租房网 * 海子角租房网 * 河西区租房网 * 黄村租房网 * 旧宫租房网 * 林校路租房网 * 庞各庄租房网 * 长阳租房网 * 八宝山租房网 * 百善租房网 * 城子街道租房网 * 安宁庄租房网 * 东方太阳城租房网 * 八达岭租房网 * 滨河路租房网 * CBD租房网 * 肇州租房 * 长春租房 * 玉树租房 * 广安租房 * 那曲租房 * 肇州出租 * 长春出租 * 玉树出租 * 广安出租 * 那曲出租 * 肇州整租房 * 长春整租房 * 玉树整租房 * 广安整租房 * 那曲整租房 * 肇州合租房 * 长春合租房 * 玉树合租房 * 广安合租房 * 那曲合租房 * 肇州个人 * 长春个人 * 玉树个人 * 广安个人 * 那曲个人 * 海淀租房 * 房山租房 * 石景山租房 * 门头沟租房 * 平谷租房 * 海淀出租 * 房山出租 * 石景山出租 * 门头沟出租 * 平谷出租 * 海淀整租房 * 房山整租房 * 石景山整租房 * 门头沟整租房 * 平谷整租房 * 海淀合租房 * 房山合租房 * 石景山合租房 * 门头沟合租房 * 平谷合租房 * 北京两室一卫租房 * 北京别墅租房 * 北京1000元左右租房 * 北京40平米租房 * 北京70平米租房 * 北京80平米租房 * 北京100平米租房 * 北京170平米租房 * 北京复式租房 * 北京小户型租房 * 北京医院附近租房 * 北京公交站点附近租房 * 北京最便宜租房 * 北京拎包入住租房 * 北京高中附近租房 常见问题|帮助中心|意见反馈|了解58同城|加入58同城|反欺诈联盟|报案平台|推广服务|渠道招商|商家推广|维权中心|知识产权投诉 _2005-2028 58.com版权所有_|京公网备案信息11010502000809|京ICP证060405|京ICP备10012705号-2|津网文（2025）0237-002号|乙测资字11513278|联系我们 人力资源服务许可证|广播电视节目制作经营许可证|_违法信息/未成年人举报：4008135858 jubao@58ganji.com_|_员工舞弊举报：wb@58.com_|代理记账许可证|算法备案 公司主体：北京五八信息技术有限公司 官方客服：10105858 [](https://helps.58.com/train/detail?；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：区颐美园，对应整租价格：1室约1600-2300元/月；，2室约2000-3000元/月；，3室约2400-3300元/月；，4室约3200元/月；房屋质量/户型线索：长沙同名颐美园：2000年建成，房龄约25-26年，户型以二居、三居为主，户型周正、南北通透居多，多为精装修，物业为富通嘉善物业管理有限公司，物业费约1.2-1.5元/㎡/月；；暂未查询到目标北京海淀区颐美园的房子质量相关公开信息，无隔音相关评价；；生活便利线索：长沙同名颐美园：周边2km内有多个地铁站（3号线、6号线），公交站点密集，配套有商场、医院，生活便利；；目标北京海淀区龙背村路该位置邻近龙背村路，周边有超市发、天秀生活超市、中发百旺商城等商超，邻近地铁16号线马连洼站、4号线安河桥北，通勤便利，邻近北京本地医院和基础餐饮配套；</x:v>
       </x:c>
       <x:c r="O82" t="str">
-        <x:v>1. 【北京leyu乐鱼体育官网平台入口ty14.cc租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kwleyu%E4%B9%90%E9%B1%BC%E4%BD%93%E8%82%B2%E5%AE%98%E7%BD%91%E5%B9%B3%E5%8F%B0%E5%85%A5%E5%8F%A3ty14.cc?93%20target=_blank
-2. 海淀租房_北京海淀租房信息|海淀租房价格信息-58租房网 https://bj.zf.58.com/haidian/
-3. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065
-4. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml</x:v>
+        <x:v>1. 整租 | 颐美园 3室2厅2卫 https://cs.zu.anjuke.com/gfangyuan/3426370512658432
+2. 长沙颐美园房价怎么样？ 颐美园房源|户型图|小区车位|交通地址详情分析！ https://news.ke.com/cs/xiaoqu/3511062005604.html
+3. 小区信息全方位解读 http://m.fang.com/xiaoqu/strategy/cs/2710017716.html
+4. 颐美园史诗级详细信息盘点，租房更安心！ http://m.fang.com/news/zf/cs/xiaoqu/42320205.html
+5. 龙背村路 颐北家苑两居出租 配置齐全 跟业主签约，可长租 http://m.anjuke.com/bj/rent/4547369340529672-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -4299,41 +4521,42 @@
         <x:v>北京市海淀区安宁庄西路29号</x:v>
       </x:c>
       <x:c r="E83" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F83" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G83" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H83" t="n">
-        <x:v>8.8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I83" t="str">
-        <x:v>紧邻西二旗，步行可达网易，租金适中且房源多，是该区域性价比极高的经典选择。</x:v>
-      </x:c>
-      <x:c r="J83" t="str">
-        <x:v>2026-02-06 | 375万 | 39022元/㎡；海淀西二旗铭科苑 2室1厅 86.3㎡ 7000元/月； * ### 铭科苑2室1厅1卫南北朝向5900.00元/月； * ### 铭科苑1室1厅1卫东北朝向6360.00元/月； * ### 铭科苑2室1厅1卫南北朝向6200.00元/月；月 * ### 铭科苑1室1厅1卫西朝向5800.00元/月； * ### 铭科苑3室1厅1卫南北朝向7100.00元/月； * ### 铭科苑2室1厅1卫南北朝向5600.00元/月</x:v>
-      </x:c>
+        <x:v>1994年老旧小区，物业管理一般且环境较破旧，但生活气息浓厚，适合低预算过渡。</x:v>
+      </x:c>
+      <x:c r="J83" t="str"/>
       <x:c r="K83" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **46183** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.3% 贷款计算器 * 二手房源 1套 * 最近成交 594套 * 楼栋总数 14栋 * 房屋总数 2136户 * 建筑类型 板塔结合 * 建筑年代 1998年建成 * 小区位置 (海淀)西二旗铭科苑,海淀区安宁庄西路29号院,西二旗一里地图 * 物业公司 北京东居物业管理有限公司 * 开发商 北京市安达房地产开发公司 #### 推荐经纪人查看全部经纪人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 郭红 评分：4.6 从业信息卡 百科 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 ##### 王立新 评分：4.6 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 西二旗·西二旗铭科苑·2室·1厅 2室1厅 66.3㎡**345**万 * #### 铭科苑正规3居+公房采光充沛+软件园百度联想 3室1厅 91.7㎡**520**万 * #### 西二旗铭科苑,双卧南两居,满五一套视野楼层 2室1厅 71.3㎡**359**万 * #### 铭科苑带电梯东向一居商品房满五年唯一看房方便 1室1厅 72.06㎡**289**万 ### 铭科苑成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 92.27㎡ | 2026-04-20 | -- | -- | 市场信息 | | 72.06㎡ | 2026-03-18 | -- | -- | 市场信息 | | 96.10㎡ | 2026-02-06 | 375万 | 39022元/㎡ | 市场信息 | 查看全部成交 ### 铭科苑价格走势 ### 铭科苑房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 铭科苑 海淀·西二旗**46184** 元/㎡ * #### 智学苑 海淀·西二旗**48493** 元/㎡ * #### 燕尚园 海淀·西二旗**76969** 元/㎡ * #### 领秀新硅谷 海淀·西二旗**80025** 元/㎡ * #### 领秀新硅谷别墅 海淀·西二旗**82634** 元/㎡ ### 相关资讯 * 小区资讯北京铭科苑怎么样?；房价物业配套全介绍2021-05-11 * 小区资讯你没见过如此详细的数据!；# 西二旗铭科苑怎么样，好不好_中介房产经纪人：刘礼征对西二旗铭科苑的评价-北京安居客 anjuke 北京 __ 华北东北北京天津大连石家庄哈尔滨沈阳太原长春威海潍坊呼和浩特包头华东地区上海杭州苏州南京无锡济南青岛昆山宁波南昌福州合肥徐州淄博华南地区深圳广州佛山长沙三亚惠州东莞海口珠海中山厦门南宁泉州柳州中 西 部成都重庆武汉郑州西安昆明贵阳兰州洛阳 更多城市&gt; * 首 页 * 新 房 * 新盘 * 楼讯 * 热门活动 * 看房团 * 房源 * 商业地产 * 品牌专区 * 未开盘项目 * 二手房 * 房源 * 小区 * 地图找房 * 找经纪人 * 优秀经纪人榜 * 违规经纪人 * 租 房 * 区域找房 * 地铁找房 * 地图找房 * 小区 * 民宿短租 * 商铺写字楼 * 商铺 * 商铺出租 * 商铺出售 * 商铺新盘 * 写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 办公楼盘 * 联合办公 * 装修 * 房产研究院 * 房 价 * 问 答 登录注册 下载APP 北京房产网&gt;北京二手房&gt;西二旗铭科苑&gt; 刘礼征解读西二旗铭科苑 # 西二旗铭科苑 小区概况二手房租房价格行情小区视频房型图实景图生活配套小区问答专家解读 ## 专家解读 * [](https://beijing.anjuke.com/community/view/849119/jiedu-438355981/) 刘礼征 [](https://dulijingjiren.anjuke.com/) 发布于2021年11月23日 __ 0 人觉得很赞 特色【小区户型】铭科苑小区总共有14栋楼，其中1-11是6层板楼没有电梯，12-14是18层塔楼，两梯八户【小区设施】小区北门附近有运动设施可供锻炼身体，十号楼内侧有象棋棋盘和围棋棋盘，可供下棋休闲，目光教育有篮球场【生活配套】小区小西门益民超市广场，包含水果，蔬菜超市，餐饮理发等一切生活所需，小区旁边也有摆摊卖菜【轨道交通】铭科苑小区环三个公交站，西二旗大街站，西二旗站，西二旗北站，小区距离地铁13号线一公里左右，出行方便【居民素质】小区居民多以老人小孩，附近上班族为主，生活气息浓厚，小区居民邻里和睦，经常一块活动不足小区人车不分流，小孩子得注意安全 * * * * 查看Ta的房产店铺 ## 其他经纪人对西二旗铭科苑的解读 贾帅帅解读西二旗铭科苑茹燕解读西二旗铭科苑杨国栋解读西二旗铭科苑杨强领解读西二旗铭科苑韩帅解读西二旗铭科苑朱士鹏解读西二旗铭科苑孙刚解读西二旗铭科苑辛丹丹解读西二旗铭科苑李石解读西二旗铭科苑朱瑞锦解读西二旗铭科苑张贺解读西二旗铭科苑郭文明解读西二旗铭科苑账号已注销解读西二旗铭科苑李杰解读西二旗铭科苑孙明丽解读西二旗铭科苑彭金红解读西二旗铭科苑王科解读西二旗铭科苑杜千旭解读西二旗铭科苑刘唯解读西二旗铭科苑张红阳解读西二旗铭科苑 * 二手房区域) * 推荐导航) * 问答搜索) * 热门房产网) * 最新解读) * * 朝阳二手房 * 海淀二手房 * 东城二手房 * 西城二手房 * 丰台二手房 * 通州二手房 * 石景山二手房 * 昌平二手房 * 大兴二手房 * 顺义二手房 * 房山二手房 * 门头沟二手房 * 密云二手房 * 怀柔二手房 * 平谷二手房 * 延庆二手房 * 北京周边二手房 * 安宁庄二手房 * 公主坟西二手房 * 清河二手房 * 万柳二手房 * 田村二手房 * 定慧寺二手房 * 西北旺二手房 * 温泉镇二手房 * 苏州桥二手房 * 万寿路二手房 * 香山东二手房 * 西三旗二手房 * 马连洼二手房 * 知春路二手房 * 五道口二手房 * 学院路二手房 * 颐和园二手房 * 世纪城二手房 * 玉泉路东二手房 * 甘家口二手房 * 上地二手房 * 军博二手房 * 双榆树二手房 * 圆明园二手房 * 小西天二手房 * 白石桥二手房 * 车道沟二手房 * 公主坟东二手房 * 皂君庙二手房 * 牡丹园二手房 * 四季青二手房 * 海淀北部二手房 * 中关村二手房 * 紫竹桥二手房 * 香山西二手房 * 西二旗二手房 * 魏公村二手房 * 马甸二手房 * 二里庄二手房 * 北京房产网 * 北京楼盘 * 北京二手房 * 北京新房房价 * 北京租房 * 北京房价 * 北京别墅出售 * 北京公寓出售 * 北京合租租房 * 北京公寓租房 * 北京别墅租房 * 北京个人租房 * 北京一居室租房 * 北京二居室租房 * 北京三居室租房 * 北京四居室租房 * 北京五居室租房 * 北京毛坯租房 * 北京简单装修租房 * 北京中等装修租房 * 北京精装修租房 * 北京豪华装修租房 * 海淀二手房 * 海淀新房房价 * 海淀租房 * 海淀房价 * 海淀别墅出售 * 海淀公寓出售 * 海淀合租租房 * 海淀公寓租房 * 海淀别墅租房 * 海淀个人租房 * 海淀一居室租房 * 海淀二居室租房 * 海淀三居室租房 * 海淀四居室租房 * 海淀五居室租房 * 海淀毛坯租房 * 海淀简单装修租房 * 海淀中等装修租房 * 海淀精装修租房 * 海淀豪华装修租房 * 西二旗二手房 * 西二旗新房房价 * 西二旗租房 * 西二旗房价 * 西二旗别墅出售 * 西二旗公寓出售 * 西二旗合租租房 * 西二旗公寓租房 * 西二旗别墅租房 * 西二旗个人租房 * 西二旗一居室租房 * 西二旗二居室租房 * 西二旗三居室租房 * 西二旗四居室租房 * 西二旗五居室租房 * 西二旗毛坯租房 * 西二旗简单装修租房 * 西二旗中等装修租房 * 西二旗精装修租房 * 西二旗豪华装修租房 * 小型烤箱 * 买房过户之前付多少钱 * 石家庄房产落户政策2019 * 跆拳道教室装修 * 公积金住房贷款7月份还款少了 * 餐馆装修注意 * 佛山买房子交什么税 * 库尔勒房价多少 * 黄岛买房哪里好 * 恒通卫浴是几线品牌 * 重庆南坪房产过户在那里办理 * 抽水马桶盖推荐 * 磁湖南郡装修 * 新房装修窗囗需要包吗 * 航阳小苑公租房户型 * 集成吊顶扣板吊顶 * 买房商业贷款最多可以贷多少钱?；到2030年，基本建成与新发展格局相匹配、与新时代首都发展相适应的“四个中心”功能支撑服务体系。</x:v>
+        <x:v>房龄：小区1994年建成，房龄较老；；户型：多为板楼，以1室、2室、3室为主，多数户型南北通透，部分塔楼一居室采光好，部分户型可改造成两居使用；；装修：有简单装修和精装修，部分房源配备齐全家电；；隔音：多数住户反馈不吵；；物业：开放式社区，物业管理一般，小区环境花园偏破旧，楼道暗沉，无地下停车场，地上停车无人车分流；</x:v>
       </x:c>
       <x:c r="L83" t="str">
-        <x:v>房价物业配套全介绍2021-05-11 * 小区资讯你没见过如此详细的数据!；# 西二旗铭科苑怎么样，好不好_中介房产经纪人：刘礼征对西二旗铭科苑的评价-北京安居客 anjuke 北京 __ 华北东北北京天津大连石家庄哈尔滨沈阳太原长春威海潍坊呼和浩特包头华东地区上海杭州苏州南京无锡济南青岛昆山宁波南昌福州合肥徐州淄博华南地区深圳广州佛山长沙三亚惠州东莞海口珠海中山厦门南宁泉州柳州中 西 部成都重庆武汉郑州西安昆明贵阳兰州洛阳 更多城市&gt; * 首 页 * 新 房 * 新盘 * 楼讯 * 热门活动 * 看房团 * 房源 * 商业地产 * 品牌专区 * 未开盘项目 * 二手房 * 房源 * 小区 * 地图找房 * 找经纪人 * 优秀经纪人榜 * 违规经纪人 * 租 房 * 区域找房 * 地铁找房 * 地图找房 * 小区 * 民宿短租 * 商铺写字楼 * 商铺 * 商铺出租 * 商铺出售 * 商铺新盘 * 写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 办公楼盘 * 联合办公 * 装修 * 房产研究院 * 房 价 * 问 答 登录注册 下载APP 北京房产网&gt;北京二手房&gt;西二旗铭科苑&gt; 刘礼征解读西二旗铭科苑 # 西二旗铭科苑 小区概况二手房租房价格行情小区视频房型图实景图生活配套小区问答专家解读 ## 专家解读 * [](https://beijing.anjuke.com/community/view/849119/jiedu-438355981/) 刘礼征 [](https://dulijingjiren.anjuke.com/) 发布于2021年11月23日 __ 0 人觉得很赞 特色【小区户型】铭科苑小区总共有14栋楼，其中1-11是6层板楼没有电梯，12-14是18层塔楼，两梯八户【小区设施】小区北门附近有运动设施可供锻炼身体，十号楼内侧有象棋棋盘和围棋棋盘，可供下棋休闲，目光教育有篮球场【生活配套】小区小西门益民超市广场，包含水果，蔬菜超市，餐饮理发等一切生活所需，小区旁边也有摆摊卖菜【轨道交通】铭科苑小区环三个公交站，西二旗大街站，西二旗站，西二旗北站，小区距离地铁13号线一公里左右，出行方便【居民素质】小区居民多以老人小孩，附近上班族为主，生活气息浓厚，小区居民邻里和睦，经常一块活动不足小区人车不分流，小孩子得注意安全 * * * * 查看Ta的房产店铺 ## 其他经纪人对西二旗铭科苑的解读 贾帅帅解读西二旗铭科苑茹燕解读西二旗铭科苑杨国栋解读西二旗铭科苑杨强领解读西二旗铭科苑韩帅解读西二旗铭科苑朱士鹏解读西二旗铭科苑孙刚解读西二旗铭科苑辛丹丹解读西二旗铭科苑李石解读西二旗铭科苑朱瑞锦解读西二旗铭科苑张贺解读西二旗铭科苑郭文明解读西二旗铭科苑账号已注销解读西二旗铭科苑李杰解读西二旗铭科苑孙明丽解读西二旗铭科苑彭金红解读西二旗铭科苑王科解读西二旗铭科苑杜千旭解读西二旗铭科苑刘唯解读西二旗铭科苑张红阳解读西二旗铭科苑 * 二手房区域) * 推荐导航) * 问答搜索) * 热门房产网) * 最新解读) * * 朝阳二手房 * 海淀二手房 * 东城二手房 * 西城二手房 * 丰台二手房 * 通州二手房 * 石景山二手房 * 昌平二手房 * 大兴二手房 * 顺义二手房 * 房山二手房 * 门头沟二手房 * 密云二手房 * 怀柔二手房 * 平谷二手房 * 延庆二手房 * 北京周边二手房 * 安宁庄二手房 * 公主坟西二手房 * 清河二手房 * 万柳二手房 * 田村二手房 * 定慧寺二手房 * 西北旺二手房 * 温泉镇二手房 * 苏州桥二手房 * 万寿路二手房 * 香山东二手房 * 西三旗二手房 * 马连洼二手房 * 知春路二手房 * 五道口二手房 * 学院路二手房 * 颐和园二手房 * 世纪城二手房 * 玉泉路东二手房 * 甘家口二手房 * 上地二手房 * 军博二手房 * 双榆树二手房 * 圆明园二手房 * 小西天二手房 * 白石桥二手房 * 车道沟二手房 * 公主坟东二手房 * 皂君庙二手房 * 牡丹园二手房 * 四季青二手房 * 海淀北部二手房 * 中关村二手房 * 紫竹桥二手房 * 香山西二手房 * 西二旗二手房 * 魏公村二手房 * 马甸二手房 * 二里庄二手房 * 北京房产网 * 北京楼盘 * 北京二手房 * 北京新房房价 * 北京租房 * 北京房价 * 北京别墅出售 * 北京公寓出售 * 北京合租租房 * 北京公寓租房 * 北京别墅租房 * 北京个人租房 * 北京一居室租房 * 北京二居室租房 * 北京三居室租房 * 北京四居室租房 * 北京五居室租房 * 北京毛坯租房 * 北京简单装修租房 * 北京中等装修租房 * 北京精装修租房 * 北京豪华装修租房 * 海淀二手房 * 海淀新房房价 * 海淀租房 * 海淀房价 * 海淀别墅出售 * 海淀公寓出售 * 海淀合租租房 * 海淀公寓租房 * 海淀别墅租房 * 海淀个人租房 * 海淀一居室租房 * 海淀二居室租房 * 海淀三居室租房 * 海淀四居室租房 * 海淀五居室租房 * 海淀毛坯租房 * 海淀简单装修租房 * 海淀中等装修租房 * 海淀精装修租房 * 海淀豪华装修租房 * 西二旗二手房 * 西二旗新房房价 * 西二旗租房 * 西二旗房价 * 西二旗别墅出售 * 西二旗公寓出售 * 西二旗合租租房 * 西二旗公寓租房 * 西二旗别墅租房 * 西二旗个人租房 * 西二旗一居室租房 * 西二旗二居室租房 * 西二旗三居室租房 * 西二旗四居室租房 * 西二旗五居室租房 * 西二旗毛坯租房 * 西二旗简单装修租房 * 西二旗中等装修租房 * 西二旗精装修租房 * 西二旗豪华装修租房 * 小型烤箱 * 买房过户之前付多少钱 * 石家庄房产落户政策2019 * 跆拳道教室装修 * 公积金住房贷款7月份还款少了 * 餐馆装修注意 * 佛山买房子交什么税 * 库尔勒房价多少 * 黄岛买房哪里好 * 恒通卫浴是几线品牌 * 重庆南坪房产过户在那里办理 * 抽水马桶盖推荐 * 磁湖南郡装修 * 新房装修窗囗需要包吗 * 航阳小苑公租房户型 * 集成吊顶扣板吊顶 * 买房商业贷款最多可以贷多少钱?；按照“不扰民、少扰民”原则，完善疏导组织，最大限度降低对生产生活秩序影响。；二、营造优良的中央政务环境 服务中央政务功能布局优化，统筹利用疏解腾退空间，为中央政务活动提供高品质空间与配套保障。；实施重点地区品质提升工程，持续推进钓鱼台地区、京西宾馆周边等重点区域景观风貌提升，开展第五立面整治改造，塑造彰显中国传统文化与现代时尚文化的城市风貌，营造安全、整洁、有序的政务环境。</x:v>
+        <x:v>周边配套：北门有便民市场益民市场，买菜购物方便，周边有便民超市、餐饮门店，小区内有幼儿园，附近有小学初中，生活配套齐全；；小区有3个出入口，自带健身区，生活气息浓厚；；周边距离医院信息未查询到明确信息；</x:v>
       </x:c>
       <x:c r="M83" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>隔音：多数住户反馈不吵；</x:v>
       </x:c>
       <x:c r="N83" t="str">
-        <x:v>价格线索：2026-02-06 | 375万 | 39022元/㎡；海淀西二旗铭科苑 2室1厅 86.3㎡ 7000元/月； * ### 铭科苑2室1厅1卫南北朝向5900.00元/月； * ### 铭科苑1室1厅1卫东北朝向6360.00元/月； * ### 铭科苑2室1厅1卫南北朝向6200.00元/月；月 * ### 铭科苑1室1厅1卫西朝向5800.00元/月； * ### 铭科苑3室1厅1卫南北朝向7100.00元/月； * ### 铭科苑2室1厅1卫南北朝向5600.00元/月；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) [](https://esf.fang.com/loupan/1010000966/photo/) 扫描到手机 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **46183** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.3% 贷款计算器 * 二手房源 1套 * 最近成交 594套 * 楼栋总数 14栋 * 房屋总数 2136户 * 建筑类型 板塔结合 * 建筑年代 1998年建成 * 小区位置 (海淀)西二旗铭科苑,海淀区安宁庄西路29号院,西二旗一里地图 * 物业公司 北京东居物业管理有限公司 * 开发商 北京市安达房地产开发公司 #### 推荐经纪人查看全部经纪人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 郭红 评分：4.6 从业信息卡 百科 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 ##### 王立新 评分：4.6 从业信息卡 百科 闪电回复 * 户型 * 价格 * #### 西二旗·西二旗铭科苑·2室·1厅 2室1厅 66.3㎡**345**万 * #### 铭科苑正规3居+公房采光充沛+软件园百度联想 3室1厅 91.7㎡**520**万 * #### 西二旗铭科苑,双卧南两居,满五一套视野楼层 2室1厅 71.3㎡**359**万 * #### 铭科苑带电梯东向一居商品房满五年唯一看房方便 1室1厅 72.06㎡**289**万 ### 铭科苑成交记录 | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 | | --- | --- | --- | --- | --- | | 92.27㎡ | 2026-04-20 | -- | -- | 市场信息 | | 72.06㎡ | 2026-03-18 | -- | -- | 市场信息 | | 96.10㎡ | 2026-02-06 | 375万 | 39022元/㎡ | 市场信息 | 查看全部成交 ### 铭科苑价格走势 ### 铭科苑房贷计算器更多贷款计算 选择基本情况，帮您快速计算房贷 * 估算总价 万 * 首付成数 1.5成 1.5成 2成 2.5成 3成 3.5成 4成 4.5成 5成 5.5成 6成 6.5成 7成 7.5成 8成 * 贷款类别 商业贷款 商业贷款 公积金贷款 组合贷款 * 贷款时间 30年（360期） 1年（12期） 2年（24期） 3年（36期） 4年（48期） 5年（60期） 6年（72期） 7年（84期） 8年（96期） 9年（108期） 10年（120期） 11年（132期） 12年（144期） 13年（156期） 14年（168期） 15年（180期） 16年（192期） 17年（204期） 18年（216期） 19年（228期） 20年（240期） 25年（300期） 30年（360期） * 还款方式 等额本息 等额本息 等额本金 * 参考首付（1.5成） * 贷款金额（8.5成） * 支付利息（8.5成） * 利率公积金 2.6% * 商业性 3.05% * 月供（等额本息） 元 ### 附近小区 * #### 铭科苑 海淀·西二旗**46184** 元/㎡ * #### 智学苑 海淀·西二旗**48493** 元/㎡ * #### 燕尚园 海淀·西二旗**76969** 元/㎡ * #### 领秀新硅谷 海淀·西二旗**80025** 元/㎡ * #### 领秀新硅谷别墅 海淀·西二旗**82634** 元/㎡ ### 相关资讯 * 小区资讯北京铭科苑怎么样?；房价物业配套全介绍2021-05-11 * 小区资讯你没见过如此详细的数据!；# 西二旗铭科苑怎么样，好不好_中介房产经纪人：刘礼征对西二旗铭科苑的评价-北京安居客 anjuke 北京 __ 华北东北北京天津大连石家庄哈尔滨沈阳太原长春威海潍坊呼和浩特包头华东地区上海杭州苏州南京无锡济南青岛昆山宁波南昌福州合肥徐州淄博华南地区深圳广州佛山长沙三亚惠州东莞海口珠海中山厦门南宁泉州柳州中 西 部成都重庆武汉郑州西安昆明贵阳兰州洛阳 更多城市&gt; * 首 页 * 新 房 * 新盘 * 楼讯 * 热门活动 * 看房团 * 房源 * 商业地产 * 品牌专区 * 未开盘项目 * 二手房 * 房源 * 小区 * 地图找房 * 找经纪人 * 优秀经纪人榜 * 违规经纪人 * 租 房 * 区域找房 * 地铁找房 * 地图找房 * 小区 * 民宿短租 * 商铺写字楼 * 商铺 * 商铺出租 * 商铺出售 * 商铺新盘 * 写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 办公楼盘 * 联合办公 * 装修 * 房产研究院 * 房 价 * 问 答 登录注册 下载APP 北京房产网&gt;北京二手房&gt;西二旗铭科苑&gt; 刘礼征解读西二旗铭科苑 # 西二旗铭科苑 小区概况二手房租房价格行情小区视频房型图实景图生活配套小区问答专家解读 ## 专家解读 * [](https://beijing.anjuke.com/community/view/849119/jiedu-438355981/) 刘礼征 [](https://dulijingjiren.anjuke.com/) 发布于2021年11月23日 __ 0 人觉得很赞 特色【小区户型】铭科苑小区总共有14栋楼，其中1-11是6层板楼没有电梯，12-14是18层塔楼，两梯八户【小区设施】小区北门附近有运动设施可供锻炼身体，十号楼内侧有象棋棋盘和围棋棋盘，可供下棋休闲，目光教育有篮球场【生活配套】小区小西门益民超市广场，包含水果，蔬菜超市，餐饮理发等一切生活所需，小区旁边也有摆摊卖菜【轨道交通】铭科苑小区环三个公交站，西二旗大街站，西二旗站，西二旗北站，小区距离地铁13号线一公里左右，出行方便【居民素质】小区居民多以老人小孩，附近上班族为主，生活气息浓厚，小区居民邻里和睦，经常一块活动不足小区人车不分流，小孩子得注意安全 * * * * 查看Ta的房产店铺 ## 其他经纪人对西二旗铭科苑的解读 贾帅帅解读西二旗铭科苑茹燕解读西二旗铭科苑杨国栋解读西二旗铭科苑杨强领解读西二旗铭科苑韩帅解读西二旗铭科苑朱士鹏解读西二旗铭科苑孙刚解读西二旗铭科苑辛丹丹解读西二旗铭科苑李石解读西二旗铭科苑朱瑞锦解读西二旗铭科苑张贺解读西二旗铭科苑郭文明解读西二旗铭科苑账号已注销解读西二旗铭科苑李杰解读西二旗铭科苑孙明丽解读西二旗铭科苑彭金红解读西二旗铭科苑王科解读西二旗铭科苑杜千旭解读西二旗铭科苑刘唯解读西二旗铭科苑张红阳解读西二旗铭科苑 * 二手房区域) * 推荐导航) * 问答搜索) * 热门房产网) * 最新解读) * * 朝阳二手房 * 海淀二手房 * 东城二手房 * 西城二手房 * 丰台二手房 * 通州二手房 * 石景山二手房 * 昌平二手房 * 大兴二手房 * 顺义二手房 * 房山二手房 * 门头沟二手房 * 密云二手房 * 怀柔二手房 * 平谷二手房 * 延庆二手房 * 北京周边二手房 * 安宁庄二手房 * 公主坟西二手房 * 清河二手房 * 万柳二手房 * 田村二手房 * 定慧寺二手房 * 西北旺二手房 * 温泉镇二手房 * 苏州桥二手房 * 万寿路二手房 * 香山东二手房 * 西三旗二手房 * 马连洼二手房 * 知春路二手房 * 五道口二手房 * 学院路二手房 * 颐和园二手房 * 世纪城二手房 * 玉泉路东二手房 * 甘家口二手房 * 上地二手房 * 军博二手房 * 双榆树二手房 * 圆明园二手房 * 小西天二手房 * 白石桥二手房 * 车道沟二手房 * 公主坟东二手房 * 皂君庙二手房 * 牡丹园二手房 * 四季青二手房 * 海淀北部二手房 * 中关村二手房 * 紫竹桥二手房 * 香山西二手房 * 西二旗二手房 * 魏公村二手房 * 马甸二手房 * 二里庄二手房 * 北京房产网 * 北京楼盘 * 北京二手房 * 北京新房房价 * 北京租房 * 北京房价 * 北京别墅出售 * 北京公寓出售 * 北京合租租房 * 北京公寓租房 * 北京别墅租房 * 北京个人租房 * 北京一居室租房 * 北京二居室租房 * 北京三居室租房 * 北京四居室租房 * 北京五居室租房 * 北京毛坯租房 * 北京简单装修租房 * 北京中等装修租房 * 北京精装修租房 * 北京豪华装修租房 * 海淀二手房 * 海淀新房房价 * 海淀租房 * 海淀房价 * 海淀别墅出售 * 海淀公寓出售 * 海淀合租租房 * 海淀公寓租房 * 海淀别墅租房 * 海淀个人租房 * 海淀一居室租房 * 海淀二居室租房 * 海淀三居室租房 * 海淀四居室租房 * 海淀五居室租房 * 海淀毛坯租房 * 海淀简单装修租房 * 海淀中等装修租房 * 海淀精装修租房 * 海淀豪华装修租房 * 西二旗二手房 * 西二旗新房房价 * 西二旗租房 * 西二旗房价 * 西二旗别墅出售 * 西二旗公寓出售 * 西二旗合租租房 * 西二旗公寓租房 * 西二旗别墅租房 * 西二旗个人租房 * 西二旗一居室租房 * 西二旗二居室租房 * 西二旗三居室租房 * 西二旗四居室租房 * 西二旗五居室租房 * 西二旗毛坯租房 * 西二旗简单装修租房 * 西二旗中等装修租房 * 西二旗精装修租房 * 西二旗豪华装修租房 * 小型烤箱 * 买房过户之前付多少钱 * 石家庄房产落户政策2019 * 跆拳道教室装修 * 公积金住房贷款7月份还款少了 * 餐馆装修注意 * 佛山买房子交什么税 * 库尔勒房价多少 * 黄岛买房哪里好 * 恒通卫浴是几线品牌 * 重庆南坪房产过户在那里办理 * 抽水马桶盖推荐 * 磁湖南郡装修 * 新房装修窗囗需要包吗 * 航阳小苑公租房户型 * 集成吊顶扣板吊顶 * 买房商业贷款最多可以贷多少钱?；到2030年，基本建成与新发展格局相匹配、与新时代首都发展相适应的“四个中心”功能支撑服务体系。；生活便利线索：房价物业配套全介绍2021-05-11 * 小区资讯你没见过如此详细的数据!；# 西二旗铭科苑怎么样，好不好_中介房产经纪人：刘礼征对西二旗铭科苑的评价-北京安居客 anjuke 北京 __ 华北东北北京天津大连石家庄哈尔滨沈阳太原长春威海潍坊呼和浩特包头华东地区上海杭州苏州南京无锡济南青岛昆山宁波南昌福州合肥徐州淄博华南地区深圳广州佛山长沙三亚惠州东莞海口珠海中山厦门南宁泉州柳州中 西 部成都重庆武汉郑州西安昆明贵阳兰州洛阳 更多城市&gt; * 首 页 * 新 房 * 新盘 * 楼讯 * 热门活动 * 看房团 * 房源 * 商业地产 * 品牌专区 * 未开盘项目 * 二手房 * 房源 * 小区 * 地图找房 * 找经纪人 * 优秀经纪人榜 * 违规经纪人 * 租 房 * 区域找房 * 地铁找房 * 地图找房 * 小区 * 民宿短租 * 商铺写字楼 * 商铺 * 商铺出租 * 商铺出售 * 商铺新盘 * 写字楼 * 写字楼出租 * 写字楼出售 * 写字楼新盘 * 办公楼盘 * 联合办公 * 装修 * 房产研究院 * 房 价 * 问 答 登录注册 下载APP 北京房产网&gt;北京二手房&gt;西二旗铭科苑&gt; 刘礼征解读西二旗铭科苑 # 西二旗铭科苑 小区概况二手房租房价格行情小区视频房型图实景图生活配套小区问答专家解读 ## 专家解读 * [](https://beijing.anjuke.com/community/view/849119/jiedu-438355981/) 刘礼征 [](https://dulijingjiren.anjuke.com/) 发布于2021年11月23日 __ 0 人觉得很赞 特色【小区户型】铭科苑小区总共有14栋楼，其中1-11是6层板楼没有电梯，12-14是18层塔楼，两梯八户【小区设施】小区北门附近有运动设施可供锻炼身体，十号楼内侧有象棋棋盘和围棋棋盘，可供下棋休闲，目光教育有篮球场【生活配套】小区小西门益民超市广场，包含水果，蔬菜超市，餐饮理发等一切生活所需，小区旁边也有摆摊卖菜【轨道交通】铭科苑小区环三个公交站，西二旗大街站，西二旗站，西二旗北站，小区距离地铁13号线一公里左右，出行方便【居民素质】小区居民多以老人小孩，附近上班族为主，生活气息浓厚，小区居民邻里和睦，经常一块活动不足小区人车不分流，小孩子得注意安全 * * * * 查看Ta的房产店铺 ## 其他经纪人对西二旗铭科苑的解读 贾帅帅解读西二旗铭科苑茹燕解读西二旗铭科苑杨国栋解读西二旗铭科苑杨强领解读西二旗铭科苑韩帅解读西二旗铭科苑朱士鹏解读西二旗铭科苑孙刚解读西二旗铭科苑辛丹丹解读西二旗铭科苑李石解读西二旗铭科苑朱瑞锦解读西二旗铭科苑张贺解读西二旗铭科苑郭文明解读西二旗铭科苑账号已注销解读西二旗铭科苑李杰解读西二旗铭科苑孙明丽解读西二旗铭科苑彭金红解读西二旗铭科苑王科解读西二旗铭科苑杜千旭解读西二旗铭科苑刘唯解读西二旗铭科苑张红阳解读西二旗铭科苑 * 二手房区域) * 推荐导航) * 问答搜索) * 热门房产网) * 最新解读) * * 朝阳二手房 * 海淀二手房 * 东城二手房 * 西城二手房 * 丰台二手房 * 通州二手房 * 石景山二手房 * 昌平二手房 * 大兴二手房 * 顺义二手房 * 房山二手房 * 门头沟二手房 * 密云二手房 * 怀柔二手房 * 平谷二手房 * 延庆二手房 * 北京周边二手房 * 安宁庄二手房 * 公主坟西二手房 * 清河二手房 * 万柳二手房 * 田村二手房 * 定慧寺二手房 * 西北旺二手房 * 温泉镇二手房 * 苏州桥二手房 * 万寿路二手房 * 香山东二手房 * 西三旗二手房 * 马连洼二手房 * 知春路二手房 * 五道口二手房 * 学院路二手房 * 颐和园二手房 * 世纪城二手房 * 玉泉路东二手房 * 甘家口二手房 * 上地二手房 * 军博二手房 * 双榆树二手房 * 圆明园二手房 * 小西天二手房 * 白石桥二手房 * 车道沟二手房 * 公主坟东二手房 * 皂君庙二手房 * 牡丹园二手房 * 四季青二手房 * 海淀北部二手房 * 中关村二手房 * 紫竹桥二手房 * 香山西二手房 * 西二旗二手房 * 魏公村二手房 * 马甸二手房 * 二里庄二手房 * 北京房产网 * 北京楼盘 * 北京二手房 * 北京新房房价 * 北京租房 * 北京房价 * 北京别墅出售 * 北京公寓出售 * 北京合租租房 * 北京公寓租房 * 北京别墅租房 * 北京个人租房 * 北京一居室租房 * 北京二居室租房 * 北京三居室租房 * 北京四居室租房 * 北京五居室租房 * 北京毛坯租房 * 北京简单装修租房 * 北京中等装修租房 * 北京精装修租房 * 北京豪华装修租房 * 海淀二手房 * 海淀新房房价 * 海淀租房 * 海淀房价 * 海淀别墅出售 * 海淀公寓出售 * 海淀合租租房 * 海淀公寓租房 * 海淀别墅租房 * 海淀个人租房 * 海淀一居室租房 * 海淀二居室租房 * 海淀三居室租房 * 海淀四居室租房 * 海淀五居室租房 * 海淀毛坯租房 * 海淀简单装修租房 * 海淀中等装修租房 * 海淀精装修租房 * 海淀豪华装修租房 * 西二旗二手房 * 西二旗新房房价 * 西二旗租房 * 西二旗房价 * 西二旗别墅出售 * 西二旗公寓出售 * 西二旗合租租房 * 西二旗公寓租房 * 西二旗别墅租房 * 西二旗个人租房 * 西二旗一居室租房 * 西二旗二居室租房 * 西二旗三居室租房 * 西二旗四居室租房 * 西二旗五居室租房 * 西二旗毛坯租房 * 西二旗简单装修租房 * 西二旗中等装修租房 * 西二旗精装修租房 * 西二旗豪华装修租房 * 小型烤箱 * 买房过户之前付多少钱 * 石家庄房产落户政策2019 * 跆拳道教室装修 * 公积金住房贷款7月份还款少了 * 餐馆装修注意 * 佛山买房子交什么税 * 库尔勒房价多少 * 黄岛买房哪里好 * 恒通卫浴是几线品牌 * 重庆南坪房产过户在那里办理 * 抽水马桶盖推荐 * 磁湖南郡装修 * 新房装修窗囗需要包吗 * 航阳小苑公租房户型 * 集成吊顶扣板吊顶 * 买房商业贷款最多可以贷多少钱?；按照“不扰民、少扰民”原则，完善疏导组织，最大限度降低对生产生活秩序影响。；二、营造优良的中央政务环境 服务中央政务功能布局优化，统筹利用疏解腾退空间，为中央政务活动提供高品质空间与配套保障。；实施重点地区品质提升工程，持续推进钓鱼台地区、京西宾馆周边等重点区域景观风貌提升，开展第五立面整治改造，塑造彰显中国传统文化与现代时尚文化的城市风貌，营造安全、整洁、有序的政务环境。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；东城区热点板块热门小区租金列表，资料来源：北京中原地产、伟业我爱我家 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>房屋质量/户型线索：房龄：小区1994年建成，房龄较老；；户型：多为板楼，以1室、2室、3室为主，多数户型南北通透，部分塔楼一居室采光好，部分户型可改造成两居使用；；装修：有简单装修和精装修，部分房源配备齐全家电；；隔音：多数住户反馈不吵；；物业：开放式社区，物业管理一般，小区环境花园偏破旧，楼道暗沉，无地下停车场，地上停车无人车分流；；生活便利线索：周边配套：北门有便民市场益民市场，买菜购物方便，周边有便民超市、餐饮门店，小区内有幼儿园，附近有小学初中，生活配套齐全；；小区有3个出入口，自带健身区，生活气息浓厚；；周边距离医院信息未查询到明确信息；；风险线索：隔音：多数住户反馈不吵；</x:v>
       </x:c>
       <x:c r="O83" t="str">
-        <x:v>1. 【北京铭科苑小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010000966.htm
-2. 西二旗铭科苑怎么样，好不好_中介房产经纪人：刘礼征对西二旗铭科苑的评价-北京安居客 https://beijing.anjuke.com/community/view/849119/jiedu-438355981/
-3. 北京市海淀区人民政府 https://zyk.bjhd.gov.cn/zwdt/zcwj/202604/t20260428_4813297.shtml
-4. 【铭科苑租房子_北京海淀铭科苑租房信息】北京手机房天下 https://m.fang.com/zf/bj_xm1010000966/
-5. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100个小区最新租金）-36氪 https://36kr.com/p/1721780568065</x:v>
+        <x:v>1. ["铭科苑小区房价/租金信息",""]
+2. ["13号线西二旗 铭科苑整租一居出了小区就到元中心","http://m.anjuke.com/bj/rent/4537368873200654-3/"]
+3. ["铭科苑小区点评,海淀 西二旗 安宁庄西路29号,北京西二旗铭科苑小区评价、业主点评、测评信息","https://m.xflapp.com/owner-comment/6587274139222933773/7043685641619538464"]
+4. ["【西二旗铭科苑业主论坛，西二旗铭科苑房产问答评价，西二旗铭科苑怎么样，好不好?】","https://m.anjuke.com/da/community/849119/qa/"]
+5. 13号线西二旗 铭科苑整租一居出了小区就到元中心 http://m.anjuke.com/bj/rent/4537368873200654-3/
+6. 铭科苑小区点评,海淀 西二旗 安宁庄西路29号,北京西二旗铭科苑小区评价、业主点评、测评信息 https://m.xflapp.com/owner-comment/6587274139222933773/7043685641619538464
+7. 【西二旗铭科苑业主论坛，西二旗铭科苑房产问答评价，西二旗铭科苑怎么样，好不好?】 - 上海安居客 https://m.anjuke.com/da/community/849119/qa/
+8. 铭科苑小区点评,海淀 西二旗 安宁庄西路29号...-北京幸福里 https://m.xflapp.com/owner-comment/6587274139222933773/7065278932781629453</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -4350,35 +4573,42 @@
         <x:v>北京市昌平区龙域中路5号</x:v>
       </x:c>
       <x:c r="E84" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F84" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G84" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H84" t="n">
-        <x:v>8.2</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I84" t="str">
-        <x:v>房龄较新且品质优良，近地铁13号线，通勤方便，是兼顾居住舒适度与距离的优选。</x:v>
-      </x:c>
-      <x:c r="J84" t="str">
-        <x:v>公园悦府(二区)6200元/月；0.00%; 3.融泽嘉园6号院6100元/月；0.00%; 4.融泽嘉园8号院6000元/月；00%; 5.金域华府东(金域华府二期)6000元/月；价格：20000/平方米 目前二手房价格：34855元/平方米； 区域新房价格：21553元/平方米</x:v>
-      </x:c>
-      <x:c r="K84" t="str"/>
+        <x:v>万科物业管理规范，双层玻璃隔音佳，邻近积水潭医院与商圈，居住品质较高。</x:v>
+      </x:c>
+      <x:c r="J84" t="str"/>
+      <x:c r="K84" t="str">
+        <x:v>房龄：一期2010年竣工；；户型：主力为63㎡一居、80-100㎡两居、106㎡三居，户型方正，南北通透户型采光佳；；装修：分简单装修和精装修，多数在租房源为精装修且配套家电齐全；；隔音：楼栋采用双层真空玻璃，具备较好隔音效果；；物业：万科物业，保洁定时清理，设施维护及时，出入口安保值守+电子门禁+联网监控，物业服务评价较好；</x:v>
+      </x:c>
       <x:c r="L84" t="str">
-        <x:v># 北京昌平合租1居室房源出租, 2900 RMB/月, 近地鐵13号线, 溫馨小窩、乾淨治愈 - Wellcee唯心所寓 [](https://www.wellcee.com/tw "首頁") 上海 上海北京深圳廣州香港杭州成都西安南京濟南蘇州武漢長沙貴陽重慶石家莊寧波鄭州溫州廈門天津合肥青島無錫瀋陽大連哈爾濱福州太原東莞南寧南昌泉州徐州常州三亞昆明佛山珠海金華 首頁房源社區 關於我們 關於我們 常見問題 新聞中心 繁體 中文 EN 繁體 註冊｜登錄 唯心所寓北京租房昌平 # 金域华府三期转租的1居室合租房源 [](https://www.wellcee.com/tw/user/1753519694114798) 金域华府三期转租 北京 工程师 國語 私信 1 2900 RMB/月 360 最後登錄 2025-08-01 詳情 押金 2900RMB 類型 合租/長租 房間 1臥室/1洗手間 樓層 5 面積 25㎡ 地鐵 13號線、18號線 溫馨小窩 乾淨治愈 市井煙火氣 ## 描述 西二旗租房 金域华府三期 女生合租 近西二旗 快手 百度 滴滴等大厂 中关村软件园 🌟房源亮点：距离龙泽地铁站 900米左右，步行5分钟，出小区门即是公交车站。；🌆地段优势：小区24小时安保，小区对面即两三个超市，还有炸串啥的各种小吃，还有精酿哈哈哈荔枝味的那个果啤就挺好喝(推荐，小区背面为昌发展万科广场（各式美食连锁店、影院俱全），蜜雪冰城、必胜客、麦当劳、肯德基、塔斯汀都在附近不到500m的距离。；留學生赴港生活完整實用手冊 2026畢業季租房指南：六個主流渠道實測對比及全流程注意事項 港碩內地留學生香港租房全攻略：從拿 offer 到入住，一篇講清楚 2026租房平台權威測評：真實房源、優質服務、安心租住三大標準 隐私政策 關於我們 常見問題 無法註冊？；交通不便 其他配套仍需进一步完善 记者乘公交307到达京昌路回龙观站后，步行了大概千余米的距离才到达该小区，而且由于附近施工工地众多，开车也多有不便。；而且选择地铁的话（城铁龙泽苑站）由于需要经过一段遍布石子的废弃铁轨，年长一点的人根本无法通行。</x:v>
-      </x:c>
-      <x:c r="M84" t="str"/>
+        <x:v>装修：分简单装修和精装修，多数在租房源为精装修且配套家电齐全；；通勤地铁：距离13号线龙泽站约1.7公里，距离18号线龙泽西约1公里，门口有龙域中路、金域华府西门等公交站，多条公交线路经过，自驾临近京新高速，通勤便利；；商超：步行可达谊品生鲜、华润万家，周边有昌发展万科广场、西二旗益民商城，购物休闲方便；；医院：距离北京积水潭医院新龙泽院区仅约500米，就医方便；；餐饮：周边商业配套完善，餐饮选择丰富，同时周边有龙域社区公园、平衡车公园，休闲便利；</x:v>
+      </x:c>
+      <x:c r="M84" t="str">
+        <x:v>暂无搜索到针对该小区租房的集中差评风险，部分信息提及小区综合居住品质排名低于本商圈超过50%的小区。；暂无搜索到针对该小区租房的集中差评风险，部分信息提及小区综合居住品质排名低于本商圈超过50%的小区</x:v>
+      </x:c>
       <x:c r="N84" t="str">
-        <x:v>价格线索：公园悦府(二区)6200元/月；0.00%; 3.融泽嘉园6号院6100元/月；0.00%; 4.融泽嘉园8号院6000元/月；00%; 5.金域华府东(金域华府二期)6000元/月；价格：20000/平方米 目前二手房价格：34855元/平方米； 区域新房价格：21553元/平方米；生活便利线索：# 北京昌平合租1居室房源出租, 2900 RMB/月, 近地鐵13号线, 溫馨小窩、乾淨治愈 - Wellcee唯心所寓 [](https://www.wellcee.com/tw "首頁") 上海 上海北京深圳廣州香港杭州成都西安南京濟南蘇州武漢長沙貴陽重慶石家莊寧波鄭州溫州廈門天津合肥青島無錫瀋陽大連哈爾濱福州太原東莞南寧南昌泉州徐州常州三亞昆明佛山珠海金華 首頁房源社區 關於我們 關於我們 常見問題 新聞中心 繁體 中文 EN 繁體 註冊｜登錄 唯心所寓北京租房昌平 # 金域华府三期转租的1居室合租房源 [](https://www.wellcee.com/tw/user/1753519694114798) 金域华府三期转租 北京 工程师 國語 私信 1 2900 RMB/月 360 最後登錄 2025-08-01 詳情 押金 2900RMB 類型 合租/長租 房間 1臥室/1洗手間 樓層 5 面積 25㎡ 地鐵 13號線、18號線 溫馨小窩 乾淨治愈 市井煙火氣 ## 描述 西二旗租房 金域华府三期 女生合租 近西二旗 快手 百度 滴滴等大厂 中关村软件园 🌟房源亮点：距离龙泽地铁站 900米左右，步行5分钟，出小区门即是公交车站。；🌆地段优势：小区24小时安保，小区对面即两三个超市，还有炸串啥的各种小吃，还有精酿哈哈哈荔枝味的那个果啤就挺好喝(推荐，小区背面为昌发展万科广场（各式美食连锁店、影院俱全），蜜雪冰城、必胜客、麦当劳、肯德基、塔斯汀都在附近不到500m的距离。；留學生赴港生活完整實用手冊 2026畢業季租房指南：六個主流渠道實測對比及全流程注意事項 港碩內地留學生香港租房全攻略：從拿 offer 到入住，一篇講清楚 2026租房平台權威測評：真實房源、優質服務、安心租住三大標準 隐私政策 關於我們 常見問題 無法註冊？；交通不便 其他配套仍需进一步完善 记者乘公交307到达京昌路回龙观站后，步行了大概千余米的距离才到达该小区，而且由于附近施工工地众多，开车也多有不便。；而且选择地铁的话（城铁龙泽苑站）由于需要经过一段遍布石子的废弃铁轨，年长一点的人根本无法通行。</x:v>
+        <x:v>房屋质量/户型线索：房龄：一期2010年竣工；；户型：主力为63㎡一居、80-100㎡两居、106㎡三居，户型方正，南北通透户型采光佳；；装修：分简单装修和精装修，多数在租房源为精装修且配套家电齐全；；隔音：楼栋采用双层真空玻璃，具备较好隔音效果；；物业：万科物业，保洁定时清理，设施维护及时，出入口安保值守+电子门禁+联网监控，物业服务评价较好；；生活便利线索：装修：分简单装修和精装修，多数在租房源为精装修且配套家电齐全；；通勤地铁：距离13号线龙泽站约1.7公里，距离18号线龙泽西约1公里，门口有龙域中路、金域华府西门等公交站，多条公交线路经过，自驾临近京新高速，通勤便利；；商超：步行可达谊品生鲜、华润万家，周边有昌发展万科广场、西二旗益民商城，购物休闲方便；；医院：距离北京积水潭医院新龙泽院区仅约500米，就医方便；；餐饮：周边商业配套完善，餐饮选择丰富，同时周边有龙域社区公园、平衡车公园，休闲便利；；风险线索：暂无搜索到针对该小区租房的集中差评风险，部分信息提及小区综合居住品质排名低于本商圈超过50%的小区。；暂无搜索到针对该小区租房的集中差评风险，部分信息提及小区综合居住品质排名低于本商圈超过50%的小区</x:v>
       </x:c>
       <x:c r="O84" t="str">
-        <x:v>1. 北京昌平合租1居室房源出租, 2900 RMB/月, 近地鐵13号线, 溫馨小窩、乾淨治愈 - Wellcee唯心所寓 https://www.wellcee.com/tw/rent-apartment/1753520036448310
-2. 北京昌平租房信息 - 58同城 http://mob.58.com/zf/hk-changping/
-3. 住总万科金域华府：小区环境优美 安保措施严格 入住时间：2012年12月 地址：昌平 西二旗北路北侧 首次开盘价格：20000/平方米 目前二手房价格：34855元/平方米 区域新房价格：21553元/平方米 http://www.xinhuanet.com/house/bj/zt/bjzhuzong1212/n6.html</x:v>
+        <x:v>1. ["金域华府(一期)，龙域租房，万科物业直营 金域华府一期 南北通透两居室出租 随时入住 https://bj.zu.anjuke.com/fangyuan/4320595385396231"]
+2. ["金域华府一期，物业直营全南向一居室，出租 http://m.anjuke.com/bj/rent/4230289222642694-3/"]
+3. ["金域华府(一期) https://m.anjuke.com/bj/fednr/1175141/gonglue?is_title_transparent=1"]
+4. ["西二旗 金域华府一期全南向一居室 包物业取暖 http://m.anjuke.com/ch/rent/4496115220225030-3/"]
+5. 【多图】金域华府(一期)，龙域租房，万科物业直营 金域华府一期 南北通透两居室出租 随时入住，昌平租房 https://bj.zu.anjuke.com/fangyuan/4320595385396231
+6. 金域华府一期，物业直营全南向一居室，出租 http://m.anjuke.com/bj/rent/4230289222642694-3/
+7. 金域华府(一期) https://m.anjuke.com/bj/fednr/1175141/gonglue?is_title_transparent=1
+8. 西二旗 金域华府一期全南向一居室 包物业取暖 http://m.anjuke.com/ch/rent/4496115220225030-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -4395,39 +4625,42 @@
         <x:v>北京市海淀区马连洼街道</x:v>
       </x:c>
       <x:c r="E85" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F85" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G85" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H85" t="n">
-        <x:v>7.5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I85" t="str">
-        <x:v>西北旺成熟社区，环境优美配套全，距离软件园较近，适合追求生活品质的网易员工。</x:v>
+        <x:v>紧邻网易大厦与地铁站，通勤优势极大，万科物业且配套万象汇，是互联网员工首选。</x:v>
       </x:c>
       <x:c r="J85" t="str">
-        <x:v>2026-02-25 | 665万 | 57787元/㎡；2026-01-26 | 708万 | 56654元/㎡；多; 户型丰富; 绿化好; 配套齐全. 67053元/㎡；附近小区 附近新房 百旺茉莉园，小区价格76306元/㎡；000 起价：13000 价格说明：均价13000元/平方米</x:v>
+        <x:v>合租次卧约2000-2600元/月；9-15㎡左右），整租两居室约4800-8800元/月；（87-114㎡），整租三居室约13000元/月；（126㎡），整租四居室约11000元/月</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>phototype=shijing) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **75443** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.8% 贷款计算器 * 二手房源 87套 * 最近成交 357套 * 楼栋总数 58栋 * 房屋总数 2145户 * 建筑类型 板塔结合 * 建筑年代 2005年建成 * 小区位置 (海淀)德政路南茉莉园地图 * 物业公司 北京德成永信物业管理有限公司 * 开发商 北京德成兴业房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 李强 评分：4.6 从业信息卡 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 ### 百旺茉莉园主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010077340/photo/?；大户型居多;；户型丰富;；北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。</x:v>
+        <x:v>合租次卧约2000-2600元/月（9-15㎡左右），整租两居室约4800-8800元/月（87-114㎡），整租三居室约13000元/月（126㎡），整租四居室约11000元/月（113㎡），价格因户型、面积、装修位置不同有差异，部分房源支持月付、无中介费。；小区分为一期和二期，多为普通住宅，房龄适中；；户型多样，有花园洋房户型，部分房源南北通透、采光好；；多为精装修，不少房源拎包入住；；物业为万科物业，24小时安保，停车费低至50元/月；</x:v>
       </x:c>
       <x:c r="L85" t="str">
-        <x:v>配套齐全. 67053元/㎡. 4月挂牌均价 · 8套. 在售房源 · 38套. 在租房 ...。；北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。；## 百旺茉莉园 别名：百旺茉莉园 加入本地买房群 关注 _北京 - 海淀 - 海淀西北旺镇区永丰路西百旺新城_ 发地址到手机 参考均价 _76306 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2005_ 小区户数 _2030户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-64群（436） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等百旺茉莉园小区信息，关注吉屋北京百旺茉莉园！</x:v>
-      </x:c>
-      <x:c r="M85" t="str"/>
+        <x:v>通勤：距离16号线西北旺站步行445米-1105米，周边多公交站，靠近百度、网易、腾讯等互联网公司园区，软件园上班便利；；商超：距离西北旺万象汇仅约800米，小区127米处有鲜美多生鲜超市，小区底商种类齐全；；餐饮、银行等配套齐全，周边暂无大型三甲医院距离信息，基础生活需求可满足。</x:v>
+      </x:c>
+      <x:c r="M85" t="str">
+        <x:v>搜索结果多为房源广告，较少用户真实差评反馈；</x:v>
+      </x:c>
       <x:c r="N85" t="str">
-        <x:v>价格线索：2026-02-25 | 665万 | 57787元/㎡；2026-01-26 | 708万 | 56654元/㎡；多; 户型丰富; 绿化好; 配套齐全. 67053元/㎡；附近小区 附近新房 百旺茉莉园，小区价格76306元/㎡；000 起价：13000 价格说明：均价13000元/平方米；房屋质量/户型线索：phototype=shijing) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) [](https://esf.fang.com/loupan/1010077340/photo/) 扫描到手机 3D小区 AI讲房 实景图 实景图 实景图 实景图 实景图 实景图 实景图 实景图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 户型图 上一个下一个 预约看房，方便带看，经纪人1对1带看服务 立即预约 一键咨询最低报价、首付及税费等！；询底价 购房不踩坑 3000+人正在热聊 加入群聊 微信扫码加入群聊 06月参考均价 **75443** 元/㎡ 小区均价仅供参考，不可作为交易等依据 环比上月↑0.8% 贷款计算器 * 二手房源 87套 * 最近成交 357套 * 楼栋总数 58栋 * 房屋总数 2145户 * 建筑类型 板塔结合 * 建筑年代 2005年建成 * 小区位置 (海淀)德政路南茉莉园地图 * 物业公司 北京德成永信物业管理有限公司 * 开发商 北京德成兴业房地产开发有限公司 #### 推荐经纪人查看全部经纪人 ##### 任力 评分：5.0 从业信息卡 百科 闪电回复 成交达人 ##### 李春 评分：4.7 从业信息卡 闪电回复 ##### 李强 评分：4.6 从业信息卡 闪电回复 ##### 马泽生 评分：4.6 从业信息卡 百科 闪电回复 ### 百旺茉莉园主力户型 | 户型信息 | 面积范围 | 在售二手房套数 | 在售二手房价格区间 | | --- | --- | --- | --- | | [](https://esf.fang.com/loupan/1010077340/photo/?；大户型居多;；户型丰富;；北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。；生活便利线索：配套齐全. 67053元/㎡. 4月挂牌均价 · 8套. 在售房源 · 38套. 在租房 ...。；北京吉屋网提供北京百旺茉莉园二手房出售信息、百旺茉莉园二手房价格，包括及时更新北京百旺茉莉园二手房房源、价格走势、户型图、业主论坛、生活配套。；## 百旺茉莉园 别名：百旺茉莉园 加入本地买房群 关注 _北京 - 海淀 - 海淀西北旺镇区永丰路西百旺新城_ 发地址到手机 参考均价 _76306 \_元/㎡\__ 咨询成交价 物业类型 _住宅_ 建成时间 _2005_ 小区户数 _2030户_ 车位数量 _-_ 咨询小区成交价 新上房源通知 加入买房群 * 小区主页 * 小区信息 * 户型图 * 小区相册 * 交通配套 * 价格走势 * 小区问答 北京买房交流群-64群（436） * 大家觉得这里未来发展怎么样？；分 综合评分 小区品质 8.* 社区配套 8.* 区域价值 8.* 北京好评榜第?；了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等百旺茉莉园小区信息，关注吉屋北京百旺茉莉园！</x:v>
+        <x:v>价格线索：合租次卧约2000-2600元/月；9-15㎡左右），整租两居室约4800-8800元/月；（87-114㎡），整租三居室约13000元/月；（126㎡），整租四居室约11000元/月；房屋质量/户型线索：合租次卧约2000-2600元/月（9-15㎡左右），整租两居室约4800-8800元/月（87-114㎡），整租三居室约13000元/月（126㎡），整租四居室约11000元/月（113㎡），价格因户型、面积、装修位置不同有差异，部分房源支持月付、无中介费。；小区分为一期和二期，多为普通住宅，房龄适中；；户型多样，有花园洋房户型，部分房源南北通透、采光好；；多为精装修，不少房源拎包入住；；物业为万科物业，24小时安保，停车费低至50元/月；；生活便利线索：通勤：距离16号线西北旺站步行445米-1105米，周边多公交站，靠近百度、网易、腾讯等互联网公司园区，软件园上班便利；；商超：距离西北旺万象汇仅约800米，小区127米处有鲜美多生鲜超市，小区底商种类齐全；；餐饮、银行等配套齐全，周边暂无大型三甲医院距离信息，基础生活需求可满足。；风险线索：搜索结果多为房源广告，较少用户真实差评反馈；</x:v>
       </x:c>
       <x:c r="O85" t="str">
-        <x:v>1. 【北京百旺茉莉园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010077340.htm
-2. 百旺茉莉园(二期) - 58同城 https://m.58.com/xiaoqu/baiwangmoliyuanerqi/
-3. 百旺茉莉园_北京百旺茉莉园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/802547.html
-4. 楼盘点评｜西北旺的百旺茉莉园 - 知乎专栏 https://zhuanlan.zhihu.com/p/633474630
-5. 百旺茉莉园 https://baike.baidu.com/item/%E7%99%BE%E6%97%BA%E8%8C%89%E8%8E%89%E5%9B%AD/8988199</x:v>
+        <x:v>1. 可月付 百旺茉莉园 房管 朝南卧室带阳台 无杂费随时看 http://m.anjuke.com/bj/rent/4568289468032004-3/
+2. 16号线 西北旺茉莉园西里整租四家两卫可分租带电梯近百度网易 http://m.anjuke.com/bj/rent/4563172642810894-3/
+3. 整租西北旺百旺茉莉园3室2厅 http://m.anjuke.com/bj/rent/4600767108602890-3/
+4. 百旺茉莉园两居室 集中供暖 软件园 西北旺地铁 腾讯 百度 http://m.anjuke.com/bj/rent/4538954756432907-3/
+5. 【多图】百旺茉莉园(一期)，西北旺租房，步行百度联想 西北旺地铁万象汇 百旺汽车园 马连洼 农大南路，海淀租房 http://m.anjuke.com/bj/rent/4156258548670468-3/?ad_type=j&amp;pagesource=782
+6. 【多图】百旺茉莉园(一期)，西北旺租房，百旺茉莉园(一期) 东西通透观景 两室两卫舒心 优选居所，海淀租房 https://bj.zu.anjuke.com/fangyuan/3996958906654720</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -4444,7 +4677,7 @@
         <x:v>北京市海淀区黑龙潭路58号院</x:v>
       </x:c>
       <x:c r="E86" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F86" t="n">
         <x:v>8</x:v>
@@ -4453,32 +4686,34 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="H86" t="n">
-        <x:v>5.5</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I86" t="str">
-        <x:v>品牌公寓管理规范，但证据显示的房源多位于温泉镇等偏远地区，通勤网易大厦较远。</x:v>
+        <x:v>租金亲民且无中介费，精装开间配套齐全，虽离地铁稍远但有摆渡车，适合预算有限者。</x:v>
       </x:c>
       <x:c r="J86" t="str">
-        <x:v>北起G南至A西起26东至29 2600-3200元/月；海淀区温泉镇显龙山文化产业园 2500-3000元/月；海淀） 北京市海淀区白家疃路 2100-4200元/月；寓 宜宿空间东马坊店19号院 1300-2000元/月；整租无中介 白水洼路西辛力屯 1400-1500元/月；社区（北京）·萌芽-青年公寓 颐春小区 2000元/月；园店 海淀区温泉镇北清路和温阳路西南角 3680元/月；淀） 北京市海淀区云水路1号 2800-3700元/月</x:v>
+        <x:v>（约合原价8.5折），需额外缴纳服务费约150元/月</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>在此查看： Mac App Store * 年齡分級 16+App 內控制 * 類別 生活風格 * 開發者 北京乐乎未来科技有限公司 * 語言 ZH+ 1種 * 大小 141.5 MB * * * * * iPhone 乐乎租房是一款致力于打造全方位高品质的租住生活空间，满足不同场景下租住需求的租房服务软件；；一、APP新版功能亮点 【全方位智能找房】-首页单间、套间、合租、整租、企业职住各类房源应有尽有，支持区域、价格、类型、户型多维度搜索；；【品质公寓生活】-Home包含租约管理（退转换续）、账单支付、在线缴费、预约保洁、预约维修、智能电表等功能，租后服务更有保障。；乐乎旗下拥有五大公寓品牌，包括主打“轻奢品质，生活家梦想家”的【乐乎公寓】、“简约高效，便捷舒适”的 【乐乎青年社区】、“智慧租赁，房屋托管”的【乐乎大家】、“艺术空间，生活美学”的【芷岸】以及为企业职住提供“安全舒适，配套完善”的【乐乎起程】。；我们永远站在第一性原理上，聚焦于租住本质，为城市青年提供舒适温馨的品质公寓好房。</x:v>
+        <x:v>该店1室开间主力户型面积区间19-31㎡，参考月租2900元起，筹开期年租可享9.2折叠加1个月免租期（约合原价8.5折），需额外缴纳服务费约150元/月，无中介费，支持押一付三，可享受优惠活动。；共有4种户型共186间房，主力户型为19㎡开间，户型动线规整、采光良好；；全屋为精装修，采用环保装修材质并做专业除甲醛处理，做了卫生间干湿分离设计，品牌家电家具齐全可拎包入住；；现有公开评价暂未提及该门店隔音相关负面问题。</x:v>
       </x:c>
       <x:c r="L86" t="str">
-        <x:v># ‎《乐乎公寓》App - App Store iPhone 版 iPhoneiPadMacWatchTV 搜尋 * Today * 遊戲 * App 類別 * 類別 * 相片與影片 * 健康與健身 * 生產力 * 娛樂 * 動作 * 冒險 * 解謎 * 獨立 # 乐乎公寓 生活風格 僅適用於 iPhone 免費 · 專為 iPhone 設計。；在此查看： Mac App Store * 年齡分級 16+App 內控制 * 類別 生活風格 * 開發者 北京乐乎未来科技有限公司 * 語言 ZH+ 1種 * 大小 141.5 MB * * * * * iPhone 乐乎租房是一款致力于打造全方位高品质的租住生活空间，满足不同场景下租住需求的租房服务软件；；通过乐乎租房APP，你可以实时连线专属管家，实时预约生活服务，生活无忧；；你与公寓Nice小生活，只差一个乐乎租房APP的距离。；【品质公寓生活】-Home包含租约管理（退转换续）、账单支付、在线缴费、预约保洁、预约维修、智能电表等功能，租后服务更有保障。</x:v>
+        <x:v>该公寓位于海淀区北分科技创新园内，距离16号线稻香湖路地铁站步行约10分钟，园区提供免费摆渡车往返地铁站，通勤便利；；园区内配有食堂，满足日常就餐需求，公寓自带健身房、会客咖啡厅，规划有机动车车位与自行车棚，园区内自带办公生活配套，周边可满足基础办公生活需求。</x:v>
       </x:c>
       <x:c r="M86" t="str">
-        <x:v>【联系我们】 官方网站:www.lefull.cn 官方找房小程序/公众号:乐乎公寓 客服电话:400-110-1165 北京乐乎公寓物业管理有限公司开发者 展开 ## 用户评论(1) * 全部 * 最新 * 好评 * 中评 * 差评 。；uid=2434411070&amp;t=0&amp;luicode=10000011&amp;lfid=100103type%3D1%26q%3D%E5%BA%94%E7%94%A8%E5%AE%9D) 关于腾讯 | About Tencent | 服务条款 | 商务洽谈 | 腾讯招聘 | 腾讯公益 | 版权所有 | 用户权限 | 隐私政策 | 侵权投诉指引 | 用户协议 版本号: 9.2.2 备案号: 粤B2-20090059-1623A 主办者: 深圳市腾讯计算机系统有限公司 Copyright ©2021-2026 Tencent. All Rights Reserved 下载应用宝，领新人专享福利！</x:v>
+        <x:v>目前公开搜索结果中，未找到该地址门店集中差评/负面风险信息；</x:v>
       </x:c>
       <x:c r="N86" t="str">
-        <x:v>价格线索：北起G南至A西起26东至29 2600-3200元/月；海淀区温泉镇显龙山文化产业园 2500-3000元/月；海淀） 北京市海淀区白家疃路 2100-4200元/月；寓 宜宿空间东马坊店19号院 1300-2000元/月；整租无中介 白水洼路西辛力屯 1400-1500元/月；社区（北京）·萌芽-青年公寓 颐春小区 2000元/月；园店 海淀区温泉镇北清路和温阳路西南角 3680元/月；淀） 北京市海淀区云水路1号 2800-3700元/月；房屋质量/户型线索：在此查看： Mac App Store * 年齡分級 16+App 內控制 * 類別 生活風格 * 開發者 北京乐乎未来科技有限公司 * 語言 ZH+ 1種 * 大小 141.5 MB * * * * * iPhone 乐乎租房是一款致力于打造全方位高品质的租住生活空间，满足不同场景下租住需求的租房服务软件；；一、APP新版功能亮点 【全方位智能找房】-首页单间、套间、合租、整租、企业职住各类房源应有尽有，支持区域、价格、类型、户型多维度搜索；；【品质公寓生活】-Home包含租约管理（退转换续）、账单支付、在线缴费、预约保洁、预约维修、智能电表等功能，租后服务更有保障。；乐乎旗下拥有五大公寓品牌，包括主打“轻奢品质，生活家梦想家”的【乐乎公寓】、“简约高效，便捷舒适”的 【乐乎青年社区】、“智慧租赁，房屋托管”的【乐乎大家】、“艺术空间，生活美学”的【芷岸】以及为企业职住提供“安全舒适，配套完善”的【乐乎起程】。；我们永远站在第一性原理上，聚焦于租住本质，为城市青年提供舒适温馨的品质公寓好房。；生活便利线索：# ‎《乐乎公寓》App - App Store iPhone 版 iPhoneiPadMacWatchTV 搜尋 * Today * 遊戲 * App 類別 * 類別 * 相片與影片 * 健康與健身 * 生產力 * 娛樂 * 動作 * 冒險 * 解謎 * 獨立 # 乐乎公寓 生活風格 僅適用於 iPhone 免費 · 專為 iPhone 設計。；在此查看： Mac App Store * 年齡分級 16+App 內控制 * 類別 生活風格 * 開發者 北京乐乎未来科技有限公司 * 語言 ZH+ 1種 * 大小 141.5 MB * * * * * iPhone 乐乎租房是一款致力于打造全方位高品质的租住生活空间，满足不同场景下租住需求的租房服务软件；；通过乐乎租房APP，你可以实时连线专属管家，实时预约生活服务，生活无忧；；你与公寓Nice小生活，只差一个乐乎租房APP的距离。；【品质公寓生活】-Home包含租约管理（退转换续）、账单支付、在线缴费、预约保洁、预约维修、智能电表等功能，租后服务更有保障。；风险线索：【联系我们】 官方网站:www.lefull.cn 官方找房小程序/公众号:乐乎公寓 客服电话:400-110-1165 北京乐乎公寓物业管理有限公司开发者 展开 ## 用户评论(1) * 全部 * 最新 * 好评 * 中评 * 差评 。；uid=2434411070&amp;t=0&amp;luicode=10000011&amp;lfid=100103type%3D1%26q%3D%E5%BA%94%E7%94%A8%E5%AE%9D) 关于腾讯 | About Tencent | 服务条款 | 商务洽谈 | 腾讯招聘 | 腾讯公益 | 版权所有 | 用户权限 | 隐私政策 | 侵权投诉指引 | 用户协议 版本号: 9.2.2 备案号: 粤B2-20090059-1623A 主办者: 深圳市腾讯计算机系统有限公司 Copyright ©2021-2026 Tencent. All Rights Reserved 下载应用宝，领新人专享福利！</x:v>
+        <x:v>价格线索：（约合原价8.5折），需额外缴纳服务费约150元/月；房屋质量/户型线索：该店1室开间主力户型面积区间19-31㎡，参考月租2900元起，筹开期年租可享9.2折叠加1个月免租期（约合原价8.5折），需额外缴纳服务费约150元/月，无中介费，支持押一付三，可享受优惠活动。；共有4种户型共186间房，主力户型为19㎡开间，户型动线规整、采光良好；；全屋为精装修，采用环保装修材质并做专业除甲醛处理，做了卫生间干湿分离设计，品牌家电家具齐全可拎包入住；；现有公开评价暂未提及该门店隔音相关负面问题。；生活便利线索：该公寓位于海淀区北分科技创新园内，距离16号线稻香湖路地铁站步行约10分钟，园区提供免费摆渡车往返地铁站，通勤便利；；园区内配有食堂，满足日常就餐需求，公寓自带健身房、会客咖啡厅，规划有机动车车位与自行车棚，园区内自带办公生活配套，周边可满足基础办公生活需求。；风险线索：目前公开搜索结果中，未找到该地址门店集中差评/负面风险信息；</x:v>
       </x:c>
       <x:c r="O86" t="str">
-        <x:v>1. 《乐乎公寓》App - App Store https://apps.apple.com/mo/app/%E4%B9%90%E4%B9%8E%E5%85%AC%E5%AF%93/id1226865912
-2. Lefull乐乎城市青年社区|乐乎订房|北京公寓|乐乎青年公寓|白领公寓|乐乎公寓 https://wb-v3.lefull.cn/apartment/1192.html
-3. 乐乎青年社区独栋公寓在租房源_北京乐乎青年社区独栋公寓出租价格【北京贝壳租房】 https://m.ke.com/chuzu/bj/brand/200302075000/apartment/amp2amp1ama0/
-4. 乐乎公寓app-官方正版软件2026最新版本免费下载-应用宝官网 https://sj.qq.com/appdetail/com.lefull.tenant
-5. 芷案轻居公寓（北京亚运村店）_北京酒店公寓租赁网 https://jiudiangongyuzulin.com/jiudianshigongyu/514.html</x:v>
+        <x:v>1. ["稻香湖乐乎公寓新开业|押一付一，无中介地铁口","http://m.anjuke.com/bj/rent/4477798906715140-3/"]
+2. ["拎包入住！海淀186套精装人才公寓上新","https://xinwen.bjd.com.cn/content/s69d8803bd5de6b42d6f0a98c.html?innerId=1"]
+3. 稻香湖乐乎公寓新开业|押一付一，无中介地铁口 http://m.anjuke.com/bj/rent/4477798906715140-3/
+4. 拎包入住！海淀186套精装人才公寓上新 https://xinwen.bjd.com.cn/content/s69d8803bd5de6b42d6f0a98c.html?innerId=1
+5. 9号线大葆台 丰台科技园 诺德 万达 大兴荟聚 汉威国际 http://m.anjuke.com/bj/rent/4513502778469376-3/
+6. 乐乎公寓的房子怎么样 https://m.kupet.cn/read-1774175777a45021083.html
+7. 乐乎公寓租房平台 http://m.962.net/y/613878</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -4495,36 +4730,43 @@
         <x:v>北京市海淀区安宁庄西路9号</x:v>
       </x:c>
       <x:c r="E87" t="str">
-        <x:v>成功(Jina)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F87" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G87" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G87" t="n">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="H87" t="n">
-        <x:v>7.2</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="I87" t="str">
-        <x:v>位于安宁庄西路，地理位置极佳，通勤网易非常方便，但缺乏具体租金线索。</x:v>
-      </x:c>
-      <x:c r="J87" t="str"/>
+        <x:v>交通极便且配套成熟，户型方正采光好，但房龄偏老，需留意设施老化及部分窗户隔音。</x:v>
+      </x:c>
+      <x:c r="J87" t="str">
+        <x:v>1室1厅整租价格约5500-5700元/月</x:v>
+      </x:c>
       <x:c r="K87" t="str">
-        <x:v>## 業務實力 房地產開發業務 中海於 80 年代初在香港進軍住宅開發業務，是中國內地房地產行業的開拓者和引領者。；「深圳中國海外大廈」 「北京中海金融中心 1＃寫字樓」年度碳 中和標桿項目 • 2025 全球總部經濟大會暨中國樓宇經濟北 京論壇：「北京中海金融中心」 2025 中國 樓宇經濟 ESG 標桿項目 • 商業地產品牌價值論壇：「北京中海金融 中心」 2025 中國商業地產零碳建築示範案 例 • 累計 14 個在建項目和運營項目獲得 WELL 認證 • 已建成 3項零碳建築（深圳中海 ·深灣玖 序花園配建幼兒園、深圳中國海外大廈、 北京中海金融中心） • 累計 28 個寫字樓和商場項目獲得 LEED 認證 • 100% 寫字樓項目新租戶簽署 《COOC 中海商務綠色租賃合作計劃 》 • 88% 寫字樓項目客戶開設低碳帳戶 2030 年目標 • 100% 新建寫字樓和購物中心項目 執行綠色建築標準 • 90% 自持在運營項目獲得綠色建 築認證 • 98% 當年新簽約寫字樓項目客戶 開設低碳帳戶 • 裝配式建築佔當年投建的城鎮新建 建築比例≥ 50% • 每兩年建設 1項及以上、累計建設 5項以上節能降碳示範工程 • 建成至少 1項淨零碳建築，建築面 積不少於 3,000 平方米 &gt; 037/038 環境、社會及管治報告 領域 聯合國 SDGs 可持續發展 議題 2025 年摘要 好公民 社區共建 2030 年目標 • 累計落成保障性房屋項目建築面積 超過 1,500 萬平方米 • 100% 運 營 購 物 中 心 項 目 設 立 母 嬰室 • 80% 新建酒店項目設立母嬰室 • 累計為 5,000 戶家庭提供康養服務 • 創新項目可持續生活社區推廣工作 覆蓋 20,000 戶家庭 2025 年進展 • 累計落成保障性房屋項目建築面積 1,437 萬平方米 • 100% 運營購物中心項目設立母嬰室 • 93% 新建酒店項目設立母嬰室 • 累計為 6,000 戶家庭提供康養服務 • 創新項目可持續生活社區推廣工作覆蓋 18,000 戶家庭 • 截至報告期末，累計於北京、天津、濟 南、青島、無錫投資建設並運營養老床位 約2,000 張，北京項目計劃於 2026 年6月正式開業運營 應對氣候變化 • 在四種情景（ SSP 2-4.5 、SSP5-8.5 、Net Zero 2050 和Delayed Transition ）下開展氣候相關風險和機遇的評估，識別出 15 項風險和機遇；</x:v>
+        <x:v>1室1厅整租价格约5500-5700元/月（53-58平精装修）；；户型选择丰富，从37平开间到250平复式均有，整体租金随户型面积递增。；房龄：小区建于2002-2004年，房龄约22-24年；；户型：以板楼为主，多南北通透，楼间距大，采光好，公摊小得房率高；；隔音：有住户反馈隔音较好，也因小区建成较早，部分老旧房源存在窗户不隔音问题；</x:v>
       </x:c>
       <x:c r="L87" t="str">
-        <x:v>当代城市家园. 海淀区安宁庄西路9号院. 64601.23元/m². 拍卖均价. 78565.13元 ... 位置及周边配套. 地址 海淀区安宁庄西路9号院. 配套 咨询具体位置及周边配套情况. shadow.。；以人居品質的技術革新，前瞻性地回應廣大客戶對 美好生活品質的期盼。；行貼心之服：以人為本，構建全生命週期幸福空間 服務是連接建築與生活的紐帶。；我們深刻回應時代對美好生活的呼喚，以自主研發的「 Living OS 系統」為核心，將安全、舒適、綠色、智慧的可 持續發展理念深度融入產品與服務，重塑未來人居範式。；歷經數十年的積累與發展，我們建立起房地產開發業務、 商業物業運營業務、其他業務的業務架構，持續豐富和改善美好生活場景。</x:v>
-      </x:c>
-      <x:c r="M87" t="str"/>
+        <x:v>装修：多为精装修，部分房源家电配套齐全，部分老旧房源存在线路/水管/电器老化问题；；通勤地铁：距离13号线清河站约565米，门口有公交站，紧邻高速，到上地、西二旗商圈通勤方便；；商超：步行可达世纪华联超市、幸福超市、24生鲜，距离华润五彩城、上地华联不到3公里，购物便利；；餐饮医院：周边配套完善，未搜索到明确差评；</x:v>
+      </x:c>
+      <x:c r="M87" t="str">
+        <x:v>隔音：有住户反馈隔音较好，也因小区建成较早，部分老旧房源存在窗户不隔音问题；；装修：多为精装修，部分房源家电配套齐全，部分老旧房源存在线路/水管/电器老化问题；；餐饮医院：周边配套完善，未搜索到明确差评；</x:v>
+      </x:c>
       <x:c r="N87" t="str">
-        <x:v>房屋质量/户型线索：## 業務實力 房地產開發業務 中海於 80 年代初在香港進軍住宅開發業務，是中國內地房地產行業的開拓者和引領者。；「深圳中國海外大廈」 「北京中海金融中心 1＃寫字樓」年度碳 中和標桿項目 • 2025 全球總部經濟大會暨中國樓宇經濟北 京論壇：「北京中海金融中心」 2025 中國 樓宇經濟 ESG 標桿項目 • 商業地產品牌價值論壇：「北京中海金融 中心」 2025 中國商業地產零碳建築示範案 例 • 累計 14 個在建項目和運營項目獲得 WELL 認證 • 已建成 3項零碳建築（深圳中海 ·深灣玖 序花園配建幼兒園、深圳中國海外大廈、 北京中海金融中心） • 累計 28 個寫字樓和商場項目獲得 LEED 認證 • 100% 寫字樓項目新租戶簽署 《COOC 中海商務綠色租賃合作計劃 》 • 88% 寫字樓項目客戶開設低碳帳戶 2030 年目標 • 100% 新建寫字樓和購物中心項目 執行綠色建築標準 • 90% 自持在運營項目獲得綠色建 築認證 • 98% 當年新簽約寫字樓項目客戶 開設低碳帳戶 • 裝配式建築佔當年投建的城鎮新建 建築比例≥ 50% • 每兩年建設 1項及以上、累計建設 5項以上節能降碳示範工程 • 建成至少 1項淨零碳建築，建築面 積不少於 3,000 平方米 &gt; 037/038 環境、社會及管治報告 領域 聯合國 SDGs 可持續發展 議題 2025 年摘要 好公民 社區共建 2030 年目標 • 累計落成保障性房屋項目建築面積 超過 1,500 萬平方米 • 100% 運 營 購 物 中 心 項 目 設 立 母 嬰室 • 80% 新建酒店項目設立母嬰室 • 累計為 5,000 戶家庭提供康養服務 • 創新項目可持續生活社區推廣工作 覆蓋 20,000 戶家庭 2025 年進展 • 累計落成保障性房屋項目建築面積 1,437 萬平方米 • 100% 運營購物中心項目設立母嬰室 • 93% 新建酒店項目設立母嬰室 • 累計為 6,000 戶家庭提供康養服務 • 創新項目可持續生活社區推廣工作覆蓋 18,000 戶家庭 • 截至報告期末，累計於北京、天津、濟 南、青島、無錫投資建設並運營養老床位 約2,000 張，北京項目計劃於 2026 年6月正式開業運營 應對氣候變化 • 在四種情景（ SSP 2-4.5 、SSP5-8.5 、Net Zero 2050 和Delayed Transition ）下開展氣候相關風險和機遇的評估，識別出 15 項風險和機遇；；生活便利线索：当代城市家园. 海淀区安宁庄西路9号院. 64601.23元/m². 拍卖均价. 78565.13元 ... 位置及周边配套. 地址 海淀区安宁庄西路9号院. 配套 咨询具体位置及周边配套情况. shadow.。；以人居品質的技術革新，前瞻性地回應廣大客戶對 美好生活品質的期盼。；行貼心之服：以人為本，構建全生命週期幸福空間 服務是連接建築與生活的紐帶。；我們深刻回應時代對美好生活的呼喚，以自主研發的「 Living OS 系統」為核心，將安全、舒適、綠色、智慧的可 持續發展理念深度融入產品與服務，重塑未來人居範式。；歷經數十年的積累與發展，我們建立起房地產開發業務、 商業物業運營業務、其他業務的業務架構，持續豐富和改善美好生活場景。</x:v>
+        <x:v>价格线索：1室1厅整租价格约5500-5700元/月；房屋质量/户型线索：1室1厅整租价格约5500-5700元/月（53-58平精装修）；；户型选择丰富，从37平开间到250平复式均有，整体租金随户型面积递增。；房龄：小区建于2002-2004年，房龄约22-24年；；户型：以板楼为主，多南北通透，楼间距大，采光好，公摊小得房率高；；隔音：有住户反馈隔音较好，也因小区建成较早，部分老旧房源存在窗户不隔音问题；；生活便利线索：装修：多为精装修，部分房源家电配套齐全，部分老旧房源存在线路/水管/电器老化问题；；通勤地铁：距离13号线清河站约565米，门口有公交站，紧邻高速，到上地、西二旗商圈通勤方便；；商超：步行可达世纪华联超市、幸福超市、24生鲜，距离华润五彩城、上地华联不到3公里，购物便利；；餐饮医院：周边配套完善，未搜索到明确差评；；风险线索：隔音：有住户反馈隔音较好，也因小区建成较早，部分老旧房源存在窗户不隔音问题；；装修：多为精装修，部分房源家电配套齐全，部分老旧房源存在线路/水管/电器老化问题；；餐饮医院：周边配套完善，未搜索到明确差评；</x:v>
       </x:c>
       <x:c r="O87" t="str">
-        <x:v>1.  https://fangchan.snssdk.com/zufang/bj-7631315834228998184.html
-2. 当代城市家园最新房价_北京海淀区-中国房价行情 https://m.creprice.cn/community/pa00025386hd304.html?city=bj
-3. 当代城市家园二手房 - 司法拍卖房产【瀚海法拍网】 https://www.fapai.cn/xiaoqu/1452.html?houseId=2453
-4. P020260519600520806930.pdf https://www.cscec.com/tzzgxnew/ESGbg/esghw/202605/P020260519600520806930.pdf</x:v>
+        <x:v>1. ["清河站 当代城市家园 正规一居 近小米快手上地中心","https://bj.58.com/zufang/85492188810074x.shtml"]
+2. ["当代城市家园","https://m.xflapp.com/owner-comment-list/6587274140967764227"]
+3. ["当代城市家园 南向 1居 看房方便 地铁清河站 元中心 快手","https://bj.58.com/zufang/86635449278940x.shtml"]
+4. 清河站 当代城市家园 正规一居 近小米快手上地元中心 https://bj.58.com/zufang/85492188810074x.shtml
+5. 当代城市家园 https://m.xflapp.com/owner-comment-list/6587274140967764227
+6. 当代城市家园 南向 1居 看房方便 地铁清河站 元中心 快手 https://bj.58.com/zufang/86635449278940x.shtml
+7. 经验分享｜租房一定不要租老破小 https://www.douban.com/group/topic/331663419/?_spm_id=MTIwMjA5NzY2</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -4541,39 +4783,38 @@
         <x:v>北京市海淀区东北旺路海淀区行政学院</x:v>
       </x:c>
       <x:c r="E88" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F88" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G88" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H88" t="n">
-        <x:v>4</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="I88" t="str">
-        <x:v>证据指向大兴、朝阳等多处异地房源，信息严重泛化，无法证明其在网易附近的真实性。</x:v>
+        <x:v>核心租金及配套信息缺失，且搜索结果与同名大厦混淆，证据力不足，建议谨慎选择。</x:v>
       </x:c>
       <x:c r="J88" t="str">
-        <x:v>租金; 户型. 不限 · 1000元/月；以下 · 1000-2000元/月； · 2000-3000元/月；户型. 不限 · 1000元/月；链家网北京小区大全,恒兴大厦参考均价:75347元/㎡；积在26-76平方米，租金价格2740-4752元/月；同层高，不同朝向，相应价位不同）地下车位1000元/月</x:v>
+        <x:v>停车位租金约600元/月</x:v>
       </x:c>
       <x:c r="K88" t="str">
-        <x:v>户型. 不限 · 1000元/月以下 · 1000-2000元/月 · 2000-3000元/月 · 3000-5000元 ... 交通便利周边配套齐全装全配采光好。；户型及租金：提供一房、二房、三房，面积在26-76平方米，租金价格2740-4752元/月. 具体位置：大兴区瀛海（地区）镇瀛昌街. 交通：距离地铁8号线瀛海站。；. 行政区域：北京市朝阳区东三环燕莎-朝阳公园 公寓地址：北京市朝阳区麦子店街38号. 房间数量：318（间） 户型介绍：开间、一居、两居、三居. 行政区域：北京市东城区--东二环朝阳门 公寓地址：北京市东城区朝阳门外三丰北里9号. 户型面积（平米）价格（人民币元/月）. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 400-100-1111，链家旗下长租公寓品牌及青年居住社区，是提供居住产品与生活服务的O2O互联网公司，旗下拥有自如友家、自如整租、业主直租、自如豪宅、自如寓、自如驿、自如ZSPACE等产品，为合租、整租、短租、中高端租住需求设计了多种产品形式，并提供保洁、维修、搬家等居间服务。；. 400-686-8006，房地产综合服务提供商世联行旗下出租公寓品牌，专注为解决中国房地产存量物业空置问题而生的创新平台，瞄准青年租房市场，为城市白领提供设计、质感、乐趣的居住体验。；. 房间数量：407（间） 户型介绍：一居、两居、三居、四居. 以上价位区间为（同以面积，不同层高，不同朝向，相应价位不同）地下车位1000元/月。</x:v>
+        <x:v>物业费5元/㎡·月；；搜索到的同名恒兴大厦：房龄约24年（2002年竣工），户型包含3室、4室、6室等多类大户型，户型整体空间评分良好，部分户型采光通风较好；；公共部分精装修，独立地热供暖；；物业为北京恒兴基业商务酒店管理有限公司，评价管理良好，内部干净，服务态度较好；；未找到目标恒兴公寓-C区隔音相关评价；</x:v>
       </x:c>
       <x:c r="L88" t="str">
-        <x:v>户型. 不限 · 1000元/月以下 · 1000-2000元/月 · 2000-3000元/月 · 3000-5000元 ... 交通便利周边配套齐全装全配采光好。；无中介8号线短租整租一居室竹叶山地铁口可直达黄埔路武汉天地. 900 · 1室1厅·35㎡ ;；户型及租金：提供一房、二房、三房，面积在26-76平方米，租金价格2740-4752元/月. 具体位置：大兴区瀛海（地区）镇瀛昌街. 交通：距离地铁8号线瀛海站。；项目最大优势在于其4000㎡独立公区所承载的全场景生活配套。；. 北京雅诗阁来福士中心服务公寓位于北京交通枢纽东直门。</x:v>
+        <x:v>搜索到的同名恒兴大厦：周边2km内有8个地铁站、76个公交站，交通便利；；周边配套有大型商超家乐福、超市发、当代商城等，医院有海淀医院、中关村中心医院，各类餐饮银行配套齐全；；但目标地址海淀区东北旺路的恒兴公寓-C区未找到直接配套信息；</x:v>
       </x:c>
       <x:c r="M88" t="str"/>
       <x:c r="N88" t="str">
-        <x:v>价格线索：租金; 户型. 不限 · 1000元/月；以下 · 1000-2000元/月； · 2000-3000元/月；户型. 不限 · 1000元/月；链家网北京小区大全,恒兴大厦参考均价:75347元/㎡；积在26-76平方米，租金价格2740-4752元/月；同层高，不同朝向，相应价位不同）地下车位1000元/月；房屋质量/户型线索：户型. 不限 · 1000元/月以下 · 1000-2000元/月 · 2000-3000元/月 · 3000-5000元 ... 交通便利周边配套齐全装全配采光好。；户型及租金：提供一房、二房、三房，面积在26-76平方米，租金价格2740-4752元/月. 具体位置：大兴区瀛海（地区）镇瀛昌街. 交通：距离地铁8号线瀛海站。；. 行政区域：北京市朝阳区东三环燕莎-朝阳公园 公寓地址：北京市朝阳区麦子店街38号. 房间数量：318（间） 户型介绍：开间、一居、两居、三居. 行政区域：北京市东城区--东二环朝阳门 公寓地址：北京市东城区朝阳门外三丰北里9号. 户型面积（平米）价格（人民币元/月）. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 400-100-1111，链家旗下长租公寓品牌及青年居住社区，是提供居住产品与生活服务的O2O互联网公司，旗下拥有自如友家、自如整租、业主直租、自如豪宅、自如寓、自如驿、自如ZSPACE等产品，为合租、整租、短租、中高端租住需求设计了多种产品形式，并提供保洁、维修、搬家等居间服务。；. 400-686-8006，房地产综合服务提供商世联行旗下出租公寓品牌，专注为解决中国房地产存量物业空置问题而生的创新平台，瞄准青年租房市场，为城市白领提供设计、质感、乐趣的居住体验。；. 房间数量：407（间） 户型介绍：一居、两居、三居、四居. 以上价位区间为（同以面积，不同层高，不同朝向，相应价位不同）地下车位1000元/月。；生活便利线索：户型. 不限 · 1000元/月以下 · 1000-2000元/月 · 2000-3000元/月 · 3000-5000元 ... 交通便利周边配套齐全装全配采光好。；无中介8号线短租整租一居室竹叶山地铁口可直达黄埔路武汉天地. 900 · 1室1厅·35㎡ ;；户型及租金：提供一房、二房、三房，面积在26-76平方米，租金价格2740-4752元/月. 具体位置：大兴区瀛海（地区）镇瀛昌街. 交通：距离地铁8号线瀛海站。；项目最大优势在于其4000㎡独立公区所承载的全场景生活配套。；. 北京雅诗阁来福士中心服务公寓位于北京交通枢纽东直门。</x:v>
+        <x:v>价格线索：停车位租金约600元/月；房屋质量/户型线索：物业费5元/㎡·月；；搜索到的同名恒兴大厦：房龄约24年（2002年竣工），户型包含3室、4室、6室等多类大户型，户型整体空间评分良好，部分户型采光通风较好；；公共部分精装修，独立地热供暖；；物业为北京恒兴基业商务酒店管理有限公司，评价管理良好，内部干净，服务态度较好；；未找到目标恒兴公寓-C区隔音相关评价；；生活便利线索：搜索到的同名恒兴大厦：周边2km内有8个地铁站、76个公交站，交通便利；；周边配套有大型商超家乐福、超市发、当代商城等，医院有海淀医院、中关村中心医院，各类餐饮银行配套齐全；；但目标地址海淀区东北旺路的恒兴公寓-C区未找到直接配套信息；</x:v>
       </x:c>
       <x:c r="O88" t="str">
-        <x:v>1. 北京海淀区公寓租房 - 房天下 http://www.fang.com/houses/zf_254312bj
-2. 海淀区 - 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/amp6amp4ama0
-3. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian
-4. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/wh-haidian
-5. 恒兴大厦- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027375369</x:v>
+        <x:v>1. 【官方】北京恒兴大厦租赁中心电话--恒兴大厦招商中心官网最新首页--详情实时更新 https://m.sohu.com/a/997437181_122439594/
+2. 2026北京恒兴大厦小区，配套指南，买房攻略 https://esf.fang.com/loupan/1010580323/strategy.htm
+3. 北京恒兴大厦租赁中心电话（在租房源面积/价格）欢迎咨询 https://c.m.163.com/news/a/JS7NQPKJ05568U31.html
+4. 北京恒兴大厦6室1厅2卫177㎡户型图-北京房天下 http://m.fang.com/xf/bj/1010580323/324662.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -4590,39 +4831,44 @@
         <x:v>北京市海淀区安宁庄西路15号</x:v>
       </x:c>
       <x:c r="E89" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F89" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G89" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H89" t="n">
-        <x:v>8.8</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I89" t="str">
-        <x:v>上地核心区成熟住宅，通勤极便，户型丰富且租金线索明确，是网易员工的优质选择。</x:v>
+        <x:v>离地铁近且物业管理优秀，居住环境安静，合租性价比极高，是网易员工的热门选择。</x:v>
       </x:c>
       <x:c r="J89" t="str">
-        <x:v>链家网北京小区大全,怡美家园参考均价:67733元/㎡；间; 户型丰富; 绿化好; 配套齐全. 67429元/㎡；配套齐全. 67429元/㎡；整租·怡美家园2室1厅. 6800元/月；南北通透 · 整租·怡美家园4室2厅. 17000元/月；2026-04-03 | 566万 | 56896元/㎡；室2厅二手房 137.04㎡ 966万 70491元/㎡</x:v>
+        <x:v>合租次卧价格约1500-2400元/月；（12-18㎡），整租价格约8700-11500元/月；：两室（约113㎡）8700-8800元/月；，三室（约158㎡）11500元/月；，四室（95平）3800元/月</x:v>
       </x:c>
       <x:c r="K89" t="str">
-        <x:v>户型丰富;；整租·怡美家园2室1厅. 6800元/月. 88㎡ | 南北| 海淀上地. 近地铁有阳台南北通透 · 整租·怡美家园4室2厅. 17000元/月. 188㎡ | 南北| 海淀上地. 近地铁精装修有阳台.。；### 怡美家园. ### 小区行情周报. ### 小区攻略. ### 小区评分9.2分. ### 小区信息全方位解读. #### 上地·怡美家园·2室·2厅. #### 怡美家园2室1厅南北. #### 感谢您的浏览. #### 怡美家园视野宽阔采光充足正规四居室. ### 怡美家园成交记录. | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 |. | 99.48㎡ | 2026-04-03 | 566万 | 56896元/㎡ | 市场信息 |. ### 怡美家园价格走势. ### 怡美家园房贷计算器更多贷款计算. #### 账单总价. ### 附近小区. #### 合景映月台. ### 怡美家园相册 户型图(88)实景图(58). ### 怡美家园问答 查看更多问答. 怡美家园过户交税得根据房子的情况和交易情况来定，如何能省钱就不好说了，反正手续全了，钱到位了，过户还是挺容易的，不懂过户交税还是建议找个人问问。；. ### 相关资讯. ### 您可能感兴趣的租房 查看更多租房. ### 清河 上地... ### 上地 清河... ### 您可能感兴趣的新房楼盘. #### 小区相关手机查看怡美家园. ### 预约看房*已选看房时间：*2019.12.13（今天）上午（9:00~18:00）. #### 选择预约时间 我们为您提供未来7天内的看房服务 经纪人最佳带看时间：12.11日，下午12：00-18:00. 经纪人最佳带看时间：12.11日，下午12：00-18:00. #### 选择时间段. #### 选择户型 我们为您提供未来7天内的看房服务. #### 恭喜您，预约成功！；怡美家园2室1厅1卫精装修 - 北京租房。</x:v>
+        <x:v>房龄：小区竣工于2007年；；户型：容积率1.6，户型方正，多为2-5居室，合租常见三室户型；；装修：多数在租房源为精装修，拎包可入住；；物业：物业服务较好，每日保洁，24小时安保巡逻，监控完善，公共设施维护及时；；隔音：多数住户反馈小区整体安静；</x:v>
       </x:c>
       <x:c r="L89" t="str">
-        <x:v>配套齐全. 67429元/㎡. 6月挂牌均价 · 17套. 在售房源 · 88套. 在租房源.。；整租·怡美家园2室1厅. 6800元/月. 88㎡ | 南北| 海淀上地. 近地铁有阳台南北通透 · 整租·怡美家园4室2厅. 17000元/月. 188㎡ | 南北| 海淀上地. 近地铁精装修有阳台.。；让您在繁忙的城市生活中找到家的温暖。；北京怡美家园房源|户型图|小区车位|交通地址详情分析。；怡美家园房源|户型图|小区车位|交通地址详情分析！</x:v>
-      </x:c>
-      <x:c r="M89" t="str"/>
+        <x:v>通勤/地铁：距离清河站（昌平线、13号线）约592米，距离安宁庄西路公交站约260米，多条公交路线，靠近上地商圈，通勤便利；；商超：小区内有好帮手超市，周边有京东便利店、清河商业城、北京华联上地购物中心，步行可达，但距离菜市场较远，买菜不便；；医院：2.1km内有北京清河医院，900m内有清河社区卫生服务中心，260m有平价药房，满足就医购药需求；；餐饮：周边有133家餐饮店铺，选择丰富；；休闲：附近670米有美和园公园，1.5km有影城，休闲便利；</x:v>
+      </x:c>
+      <x:c r="M89" t="str">
+        <x:v>未找到明确隔音差评相关信息，暂无其他重大负面口碑。；未找到明确隔音差评相关信息，暂无其他重大负面口碑</x:v>
+      </x:c>
       <x:c r="N89" t="str">
-        <x:v>价格线索：链家网北京小区大全,怡美家园参考均价:67733元/㎡；间; 户型丰富; 绿化好; 配套齐全. 67429元/㎡；配套齐全. 67429元/㎡；整租·怡美家园2室1厅. 6800元/月；南北通透 · 整租·怡美家园4室2厅. 17000元/月；2026-04-03 | 566万 | 56896元/㎡；室2厅二手房 137.04㎡ 966万 70491元/㎡；房屋质量/户型线索：户型丰富;；整租·怡美家园2室1厅. 6800元/月. 88㎡ | 南北| 海淀上地. 近地铁有阳台南北通透 · 整租·怡美家园4室2厅. 17000元/月. 188㎡ | 南北| 海淀上地. 近地铁精装修有阳台.。；### 怡美家园. ### 小区行情周报. ### 小区攻略. ### 小区评分9.2分. ### 小区信息全方位解读. #### 上地·怡美家园·2室·2厅. #### 怡美家园2室1厅南北. #### 感谢您的浏览. #### 怡美家园视野宽阔采光充足正规四居室. ### 怡美家园成交记录. | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 |. | 99.48㎡ | 2026-04-03 | 566万 | 56896元/㎡ | 市场信息 |. ### 怡美家园价格走势. ### 怡美家园房贷计算器更多贷款计算. #### 账单总价. ### 附近小区. #### 合景映月台. ### 怡美家园相册 户型图(88)实景图(58). ### 怡美家园问答 查看更多问答. 怡美家园过户交税得根据房子的情况和交易情况来定，如何能省钱就不好说了，反正手续全了，钱到位了，过户还是挺容易的，不懂过户交税还是建议找个人问问。；. ### 相关资讯. ### 您可能感兴趣的租房 查看更多租房. ### 清河 上地... ### 上地 清河... ### 您可能感兴趣的新房楼盘. #### 小区相关手机查看怡美家园. ### 预约看房*已选看房时间：*2019.12.13（今天）上午（9:00~18:00）. #### 选择预约时间 我们为您提供未来7天内的看房服务 经纪人最佳带看时间：12.11日，下午12：00-18:00. 经纪人最佳带看时间：12.11日，下午12：00-18:00. #### 选择时间段. #### 选择户型 我们为您提供未来7天内的看房服务. #### 恭喜您，预约成功！；怡美家园2室1厅1卫精装修 - 北京租房。；生活便利线索：配套齐全. 67429元/㎡. 6月挂牌均价 · 17套. 在售房源 · 88套. 在租房源.。；整租·怡美家园2室1厅. 6800元/月. 88㎡ | 南北| 海淀上地. 近地铁有阳台南北通透 · 整租·怡美家园4室2厅. 17000元/月. 188㎡ | 南北| 海淀上地. 近地铁精装修有阳台.。；让您在繁忙的城市生活中找到家的温暖。；北京怡美家园房源|户型图|小区车位|交通地址详情分析。；怡美家园房源|户型图|小区车位|交通地址详情分析！</x:v>
+        <x:v>价格线索：合租次卧价格约1500-2400元/月；（12-18㎡），整租价格约8700-11500元/月；：两室（约113㎡）8700-8800元/月；，三室（约158㎡）11500元/月；，四室（95平）3800元/月；房屋质量/户型线索：房龄：小区竣工于2007年；；户型：容积率1.6，户型方正，多为2-5居室，合租常见三室户型；；装修：多数在租房源为精装修，拎包可入住；；物业：物业服务较好，每日保洁，24小时安保巡逻，监控完善，公共设施维护及时；；隔音：多数住户反馈小区整体安静；；生活便利线索：通勤/地铁：距离清河站（昌平线、13号线）约592米，距离安宁庄西路公交站约260米，多条公交路线，靠近上地商圈，通勤便利；；商超：小区内有好帮手超市，周边有京东便利店、清河商业城、北京华联上地购物中心，步行可达，但距离菜市场较远，买菜不便；；医院：2.1km内有北京清河医院，900m内有清河社区卫生服务中心，260m有平价药房，满足就医购药需求；；餐饮：周边有133家餐饮店铺，选择丰富；；休闲：附近670米有美和园公园，1.5km有影城，休闲便利；；风险线索：未找到明确隔音差评相关信息，暂无其他重大负面口碑。；未找到明确隔音差评相关信息，暂无其他重大负面口碑</x:v>
       </x:c>
       <x:c r="O89" t="str">
-        <x:v>1. 怡美家园- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027381904
-2. 怡美家园,安宁庄西路15号 - 安居客 https://beijing.anjuke.com/community/view/55526
-3. 上地,北京怡美家园租房、合租、整租、出租信息-北京幸福里找房 https://m.xflapp.com/zufang/neighbor-house-list/bj-7560891531109171210.html
-4. 【北京怡美家园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010000339.htm
-5. 怡美家园2室1厅1卫精装修 - 北京租房 https://bj.zu.anjuke.com/fangyuan/4599424458906635</x:v>
+        <x:v>1. ["清河安宁庄当代城市家园 怡美家园精装大次卧","http://m.anjuke.com/bj/rent/4585983024524293-3/"]
+2. ["怡美家园","https://m.anjuke.com/bj/fednr/55526/gonglue?is_title_transparent=1"]
+3. ["怡美家园小区租房怎么样？看看这份报告就知道！","http://m.fang.com/news/zf/bj/xiaoqu/40931433.html"]
+4. ["南北通透 齐全 长租 安静 近清河站 小米 户型方正 万象汇","https://m.58.com/bj/zufang/84620800017627x.shtml"]
+5. 清河安宁庄当代城市家园 怡美家园精装大次卧 http://m.anjuke.com/bj/rent/4585983024524293-3/
+6. 怡美家园 https://m.anjuke.com/bj/fednr/55526/gonglue?is_title_transparent=1
+7. 怡美家园小区租房怎么样？看看这份报告就知道！ http://m.fang.com/news/zf/bj/xiaoqu/40931433.html
+8. 【19图】南北通透 齐全 长租 安静 近清河站 小米 户型方正 万象汇，安宁庄西路15号 https://m.58.com/bj/zufang/84620800017627x.shtml</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -4639,7 +4885,7 @@
         <x:v>北京市海淀区黑龙潭路58号</x:v>
       </x:c>
       <x:c r="E90" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F90" t="n">
         <x:v>9</x:v>
@@ -4648,30 +4894,33 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H90" t="n">
-        <x:v>7.8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I90" t="str">
-        <x:v>紧邻上地地铁站，环境安静且配套齐全，租金跨度大，是中关村软件园通勤的优质选择。</x:v>
+        <x:v>租金显著偏离北京行情且证据多为同名小区泛化，存在严重地点误判风险，极不推荐。</x:v>
       </x:c>
       <x:c r="J90" t="str">
-        <x:v>生中关村上班好的位置可以宿舍看价格低. 2800元/月；租 1-3个月 4-6个月. 1300-2300元/月；m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月</x:v>
+        <x:v>他同名小区参考价格区间为：1室约700-1000元/月；，2室约750-1000元/月；，3室约1000-1300元/月</x:v>
       </x:c>
       <x:c r="K90" t="str">
-        <x:v>财大家属院两居室紧邻上地地铁站看房随时. 6100元2室1厅·62.22㎡. 邻地铁配套齐全精装修有阳台随时看房 ... 价格能便宜万德嘉园二区精装两居跟业主签约看房方便. 7200元2室2。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅 82m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月. 整租南北. 海淀。；小区的板楼开始加装电梯了，值得关注。；... 小区环境还不错，挺安静，周边生活设施非常齐全，房子不错，装修也很好，干干净净！</x:v>
+        <x:v>无目标小区精准信息，同名小区参考：多为多层普通住宅，户型涵盖1室到4室，有简单装修、精装修两种常见类型，部分房源标注小区安静，部分房源物业信息缺失，无明确房龄、隔音相关评价；</x:v>
       </x:c>
       <x:c r="L90" t="str">
-        <x:v>海淀南路正规三居主卧全女生中关村上班好的位置可以宿舍看价格低. 2800元/月 3室1厅合租主卧. 海淀- 海淀南路. 交通便利全装全配首次出租周边配套齐。；财大家属院两居室紧邻上地地铁站看房随时. 6100元2室1厅·62.22㎡. 邻地铁配套齐全精装修有阳台随时看房 ... 价格能便宜万德嘉园二区精装两居跟业主签约看房方便. 7200元2室2。；但因为海淀有很多优质的学校，租金很贵。；... 小区环境还不错，挺安静，周边生活设施非常齐全，房子不错，装修也很好，干干净净！</x:v>
+        <x:v>无目标小区精准信息，同名小区参考：部分标注临近地铁/公交站点，出行通勤便利，周边商超、餐饮等生活配套成熟；</x:v>
       </x:c>
       <x:c r="M90" t="str"/>
       <x:c r="N90" t="str">
-        <x:v>价格线索：生中关村上班好的位置可以宿舍看价格低. 2800元/月；租 1-3个月 4-6个月. 1300-2300元/月；m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月；房屋质量/户型线索：财大家属院两居室紧邻上地地铁站看房随时. 6100元2室1厅·62.22㎡. 邻地铁配套齐全精装修有阳台随时看房 ... 价格能便宜万德嘉园二区精装两居跟业主签约看房方便. 7200元2室2。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅 82m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月. 整租南北. 海淀。；小区的板楼开始加装电梯了，值得关注。；... 小区环境还不错，挺安静，周边生活设施非常齐全，房子不错，装修也很好，干干净净！；生活便利线索：海淀南路正规三居主卧全女生中关村上班好的位置可以宿舍看价格低. 2800元/月 3室1厅合租主卧. 海淀- 海淀南路. 交通便利全装全配首次出租周边配套齐。；财大家属院两居室紧邻上地地铁站看房随时. 6100元2室1厅·62.22㎡. 邻地铁配套齐全精装修有阳台随时看房 ... 价格能便宜万德嘉园二区精装两居跟业主签约看房方便. 7200元2室2。；但因为海淀有很多优质的学校，租金很贵。；... 小区环境还不错，挺安静，周边生活设施非常齐全，房子不错，装修也很好，干干净净！</x:v>
+        <x:v>价格线索：他同名小区参考价格区间为：1室约700-1000元/月；，2室约750-1000元/月；，3室约1000-1300元/月；房屋质量/户型线索：无目标小区精准信息，同名小区参考：多为多层普通住宅，户型涵盖1室到4室，有简单装修、精装修两种常见类型，部分房源标注小区安静，部分房源物业信息缺失，无明确房龄、隔音相关评价；；生活便利线索：无目标小区精准信息，同名小区参考：部分标注临近地铁/公交站点，出行通勤便利，周边商超、餐饮等生活配套成熟；</x:v>
       </x:c>
       <x:c r="O90" t="str">
-        <x:v>1. 海淀租房价格- 北京 - 房天下 http://www.fang.com/houses/zf_254250bj
-2. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-3. 北京海淀上地租房信息 - 58同城 https://mob.58.com/zf/bj-shangdi
-4. 选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网 https://www.stdaily.com/web/gdxw/2025-06/06/content_351160.html
-5. 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu</x:v>
+        <x:v>1. ["向阳 2室2厅1卫","http://m.anjuke.com/heg/rent/4565945913777159-2/"]
+2. ["向阳路58号怎么样?北京向阳路58号房价|房源|地址|户型图|周边配套详情","https://m.5i5j.com/bj/xq_news/200046444.html"]
+3. ["现代简约 让你的生活更精彩 向阳院 3室1厅1卫 精装修","http://m.anjuke.com/ly/rent/4289780334222350-3/"]
+4. ["向阳院租金走势分析","http://m.anjuke.com/bj/community/1408104/zujin/"]
+5. 向阳 2室2厅1卫 http://m.anjuke.com/heg/rent/4565945913777159-2/
+6. 向阳路58号怎么样?北京向阳路58号房价|房源|地址|户型图|周边配套详情 https://m.5i5j.com/bj/xq_news/200046444.html
+7. 向阳一院整租四室一厅租房价格 http://m.anjuke.com/bj/community/1276299/zujin/sishi/
+8. 现代简约 让你的生活更精彩 向阳院 3室1厅1卫 精装修 http://m.anjuke.com/ly/rent/4289780334222350-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -4688,41 +4937,41 @@
         <x:v>友谊路102号</x:v>
       </x:c>
       <x:c r="E91" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F91" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G91" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H91" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I91" t="str">
-        <x:v>位于西北旺核心区，楼龄新、结构稳固且环境安静，极近网易，适合追求品质的员工。</x:v>
+        <x:v>房龄较老但配套成熟，通勤便利且生活设施齐全，租金处于区域合理范围，性价比较高。</x:v>
       </x:c>
       <x:c r="J91" t="str">
-        <x:v>底层(0层). 航天五院海淀-魏公村. 10000元/月；整租·航天城社区2室1厅. 7500元/月；有阳台 · 整租·航天城社区3室1厅. 8000元/月；家网北京小区大全,航天五院小区参考均价:110607元/㎡；圈租金排行榜. * 4蓟门里社区(北区)8000元/月；0.00%. * 3尚峰尚水(商住楼)6200元/月；0.00%. * 2主语家园(别墅)150000元/月；0.00%. * 2山屿西山著(1号院)7500元/月</x:v>
+        <x:v>整租价格范围：两居室6200-7200元/月；，三居室7000-8500元/月；，四室14000元/月；合租主卧价格范围：1799-2500元/月</x:v>
       </x:c>
       <x:c r="K91" t="str">
-        <x:v>整租·航天城社区2室1厅. 7500元/月. 104㎡ | 南北| 海淀西北旺. 有电梯精装修有阳台 · 整租·航天城社区3室1厅. 8000元/月. 103㎡ | 南北| 海淀西北旺.。；小区比较安静，楼龄较年轻，结构为整体混凝土浇筑非常结实。；路网发达后面小路可到交通队和银行及车站，距离一小步行很近，有中心花园，物业公司在楼下。；安居客北京海淀上地航天城社区租房网，提供押付押一付一，房型1厅3室1卫，楼层2层，朝向南，装修精装修，类型普通住宅租房信息，短签三月航天城唐家岭滴滴。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。</x:v>
+        <x:v>房龄：1996年建成；；多数房源为精装修，部分为豪华装修；；户型有两室一厅、两室两厅、三室一厅、四室一厅等，多数南北通透，采光较好；；物业暂无明显差评描述。</x:v>
       </x:c>
       <x:c r="L91" t="str">
-        <x:v>路网发达后面小路可到交通队和银行及车站，距离一小步行很近，有中心花园，物业公司在楼下。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。</x:v>
+        <x:v>通勤：紧邻北清路、八达岭高速，自驾可快速接驳城市环线，距离昌平线与16号线换乘站较近，有多条公交线覆盖，通勤便利；；商超：周边有航天辰阳光瑞全超市、航城宜乐果蔬精品超市，距离U悦生活广场1.4公里，还有永旺国际商城购物中心等，满足购物需求；；医院：附近有中国人民解放军总医院京北医疗区、社区医院，可满足基础就医需求；；餐饮：社区底商有品牌餐饮，可满足日常就餐。</x:v>
       </x:c>
       <x:c r="M91" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>物业暂无明显差评描述。</x:v>
       </x:c>
       <x:c r="N91" t="str">
-        <x:v>价格线索：底层(0层). 航天五院海淀-魏公村. 10000元/月；整租·航天城社区2室1厅. 7500元/月；有阳台 · 整租·航天城社区3室1厅. 8000元/月；家网北京小区大全,航天五院小区参考均价:110607元/㎡；圈租金排行榜. * 4蓟门里社区(北区)8000元/月；0.00%. * 3尚峰尚水(商住楼)6200元/月；0.00%. * 2主语家园(别墅)150000元/月；0.00%. * 2山屿西山著(1号院)7500元/月；房屋质量/户型线索：整租·航天城社区2室1厅. 7500元/月. 104㎡ | 南北| 海淀西北旺. 有电梯精装修有阳台 · 整租·航天城社区3室1厅. 8000元/月. 103㎡ | 南北| 海淀西北旺.。；小区比较安静，楼龄较年轻，结构为整体混凝土浇筑非常结实。；路网发达后面小路可到交通队和银行及车站，距离一小步行很近，有中心花园，物业公司在楼下。；安居客北京海淀上地航天城社区租房网，提供押付押一付一，房型1厅3室1卫，楼层2层，朝向南，装修精装修，类型普通住宅租房信息，短签三月航天城唐家岭滴滴。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；生活便利线索：路网发达后面小路可到交通队和银行及车站，距离一小步行很近，有中心花园，物业公司在楼下。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：整租价格范围：两居室6200-7200元/月；，三居室7000-8500元/月；，四室14000元/月；合租主卧价格范围：1799-2500元/月；房屋质量/户型线索：房龄：1996年建成；；多数房源为精装修，部分为豪华装修；；户型有两室一厅、两室两厅、三室一厅、四室一厅等，多数南北通透，采光较好；；物业暂无明显差评描述。；生活便利线索：通勤：紧邻北清路、八达岭高速，自驾可快速接驳城市环线，距离昌平线与16号线换乘站较近，有多条公交线覆盖，通勤便利；；商超：周边有航天辰阳光瑞全超市、航城宜乐果蔬精品超市，距离U悦生活广场1.4公里，还有永旺国际商城购物中心等，满足购物需求；；医院：附近有中国人民解放军总医院京北医疗区、社区医院，可满足基础就医需求；；餐饮：社区底商有品牌餐饮，可满足日常就餐。；风险线索：物业暂无明显差评描述。</x:v>
       </x:c>
       <x:c r="O91" t="str">
-        <x:v>1. 航天五院租房,房屋出租信息,整租,合租 - 北京二手房- 房天下 https://esf.fang.com/loupan/1010648037/chuzu/list/i31-c210000-d20-h37
-2. 西北旺,北京航天城社区租房、合租、整租、出租信息-北京幸福里找房 https://m.xflapp.com/zufang/neighbor-house-list/bj-7525927561978101803.html
-3. 北京航天五院小区二手房 - 链家 https://bj.lianjia.com/xiaoqu/1111027375325
-4. 航天社区- 房价|租房【北京贝壳找房】 https://m.ke.com/bj/xiaoqu/1111027375319
-5. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501</x:v>
+        <x:v>1. 航天城五院社区 超大主卧 https://m.58.com/bj/hezu/83582324507227x.shtml
+2. 首月减免航天城西区主卧飘窗航天城五院滴滴新橙海中关村壹号用友 http://m.anjuke.com/bj/rent/4506308856865795-3/
+3. 整租 航天城五院社区4室1厅 南北通透 http://m.anjuke.com/bj/rent/4476799536323598-3/
+4. 友谊路 唐家岭 航天研究中心 中关村一号院 友谊路102号院 http://m.anjuke.com/bj/rent/4516139819035662-3/
+5. 航天城 0中介 实拍 随时看房 可月付 百度 滴滴 航天五院 http://m.anjuke.com/bj/rent/4276608362602504-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -4739,41 +4988,43 @@
         <x:v>北京市海淀区圆明园西路2号(中国农业大学)</x:v>
       </x:c>
       <x:c r="E92" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F92" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G92" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H92" t="n">
-        <x:v>6.2</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I92" t="str">
-        <x:v>地处西二旗板块，地理位置极佳，但证据受豪宅信息干扰，具体居住品质需谨慎甄别。</x:v>
+        <x:v>紧邻地铁16号线，通勤极便，周边配套完善，虽存在名称混淆风险，但整体居住价值高。</x:v>
       </x:c>
       <x:c r="J92" t="str">
-        <x:v>海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；... 海淀-西二旗 西二旗铭科苑 1950元/月</x:v>
+        <x:v>合租次卧1200-2300元/月；，合租主卧1600-2500元/月；，整租61平左右两居约6500元/月</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>... 海淀-西二旗 西二旗铭科苑 1950元/月. 距昌平线-西二旗站1.2km. 海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅。；万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待。；万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 万柳书院次顶层三居室 隐私社区 采光好 三车位 一储. 下楼地铁站 万柳新小区 全新智能家居 有车位 可长租. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |.。；小区户型 ;；1居室·53个户型. 39㎡~55㎡. 在售495万起 ;</x:v>
+        <x:v>属于农科社区，多为6层左右多层住宅，户型有南北通透2室2厅、合租3室1厅等，不少房源为精装修，家具家电齐全，小区绿化面积大，环境较好，未查询到明确房龄、隔音、物业评价信息；</x:v>
       </x:c>
       <x:c r="L92" t="str">
-        <x:v>万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待。；万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 万柳书院次顶层三居室 隐私社区 采光好 三车位 一储. 下楼地铁站 万柳新小区 全新智能家居 有车位 可长租. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。</x:v>
+        <x:v>步行可达地铁16号线农大南路站，距离约300米，通勤便利；；周边有华联生活超市、丰泽生鲜超市、中发百旺商城、北京华联BHG Mall等商超，有北京八珍堂中医医院、上地医院等医疗机构，餐饮生活配套齐全；；公开信息中较少直接标注“资环二区”，多归为圆明园西路2号院/农科社区，存在同名混淆风险，未查询到针对资环二区明确差评，部分信息来源于周边房源，可能存在误差。；公开信息中较少直接标注“资环二区”，多归为圆明园西路2号院/农科社区，存在同名混淆风险，未查询到针对资环二区明确差评，部分信息来源于周边房源，可能存在误差</x:v>
       </x:c>
       <x:c r="M92" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>公开信息中较少直接标注“资环二区”，多归为圆明园西路2号院/农科社区，存在同名混淆风险，未查询到针对资环二区明确差评，部分信息来源于周边房源，可能存在误差。；公开信息中较少直接标注“资环二区”，多归为圆明园西路2号院/农科社区，存在同名混淆风险，未查询到针对资环二区明确差评，部分信息来源于周边房源，可能存在误差</x:v>
       </x:c>
       <x:c r="N92" t="str">
-        <x:v>价格线索：海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；... 海淀-西二旗 西二旗铭科苑 1950元/月；房屋质量/户型线索：... 海淀-西二旗 西二旗铭科苑 1950元/月. 距昌平线-西二旗站1.2km. 海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅。；万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待。；万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 万柳书院次顶层三居室 隐私社区 采光好 三车位 一储. 下楼地铁站 万柳新小区 全新智能家居 有车位 可长租. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |.。；小区户型 ;；1居室·53个户型. 39㎡~55㎡. 在售495万起 ;；生活便利线索：万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待。；万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 万柳书院次顶层三居室 隐私社区 采光好 三车位 一储. 下楼地铁站 万柳新小区 全新智能家居 有车位 可长租. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：合租次卧1200-2300元/月；，合租主卧1600-2500元/月；，整租61平左右两居约6500元/月；房屋质量/户型线索：属于农科社区，多为6层左右多层住宅，户型有南北通透2室2厅、合租3室1厅等，不少房源为精装修，家具家电齐全，小区绿化面积大，环境较好，未查询到明确房龄、隔音、物业评价信息；；生活便利线索：步行可达地铁16号线农大南路站，距离约300米，通勤便利；；周边有华联生活超市、丰泽生鲜超市、中发百旺商城、北京华联BHG Mall等商超，有北京八珍堂中医医院、上地医院等医疗机构，餐饮生活配套齐全；；公开信息中较少直接标注“资环二区”，多归为圆明园西路2号院/农科社区，存在同名混淆风险，未查询到针对资环二区明确差评，部分信息来源于周边房源，可能存在误差。；公开信息中较少直接标注“资环二区”，多归为圆明园西路2号院/农科社区，存在同名混淆风险，未查询到针对资环二区明确差评，部分信息来源于周边房源，可能存在误差；风险线索：公开信息中较少直接标注“资环二区”，多归为圆明园西路2号院/农科社区，存在同名混淆风险，未查询到针对资环二区明确差评，部分信息来源于周边房源，可能存在误差。；公开信息中较少直接标注“资环二区”，多归为圆明园西路2号院/农科社区，存在同名混淆风险，未查询到针对资环二区明确差评，部分信息来源于周边房源，可能存在误差</x:v>
       </x:c>
       <x:c r="O92" t="str">
-        <x:v>1. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-2. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/cd-haidian
-3. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian
-4. 北京海淀区租房子 - 房天下 http://www.fang.com/houses/zf_253028bj
-5. 北京铁二区二手房|房价 - 链家 https://bj.lianjia.com/xiaoqu/1111027379803</x:v>
+        <x:v>1. 圆明园西路2号院 农科社区 精装两居 实房实图 跟业主签合同 http://m.anjuke.com/bj/rent/4606754396183555-3/
+2. 【圆明园老洋房出租 http://m.fang.com/houses/zf_259291_bj/p2/
+3. 首月减免步行农大南路地铁中国农业大学西校区上地医院苏州街 http://m.anjuke.com/bj/rent/4573879646594056-3/
+4. 南北通透 2室2厅 郦城(二区) http://m.anjuke.com/bj/rent/4603716221608961-3/
+5. 万德二区 高层开间 实拍实价 采光嘎嘎好 现房随时入住 http://m.anjuke.com/bj/rent/4543220513434628-3/
+6. 【圆明园租房信息 https://m.fang.com/houses/zf_262095_bj/p1/
+7. 郦城(二区) 通风好 2室1厅2卫 精装修 http://m.anjuke.com/bj/rent/4505891043011585-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -4790,10 +5041,10 @@
         <x:v>北京市海淀区黑山扈路甲17号院-北区东南侧约60米</x:v>
       </x:c>
       <x:c r="E93" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F93" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G93" t="n">
         <x:v>8</x:v>
@@ -4802,27 +5053,30 @@
         <x:v>5.5</x:v>
       </x:c>
       <x:c r="I93" t="str">
-        <x:v>租金水平较低，但证据存在泛化现象，缺乏对该院落本身的质量描述，建议实地考察。</x:v>
-      </x:c>
-      <x:c r="J93" t="str">
-        <x:v>; 海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；海淀租金最高的小区 · 1.中间建筑50000元/月； 63m² 海淀-军博 复兴路乙6号院 6300元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月</x:v>
-      </x:c>
+        <x:v>靠近西北旺站，环境安静但缺乏租金数据，且多为无电梯步梯房，生活配套信息不全。</x:v>
+      </x:c>
+      <x:c r="J93" t="str"/>
       <x:c r="K93" t="str">
-        <x:v>万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待。；万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 万柳书院次顶层三居室 隐私社区 采光好 三车位 一储. 下楼地铁站 万柳新小区 全新智能家居 有车位 可长租. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |.。；承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；. 3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费。</x:v>
+        <x:v>未查询到更小户型价格。；房龄信息未查询到；；户型以2室1厅1卫为主，南北通透/朝南，采光较好；；装修分为简单装修和精装修，多数房源家电配套齐全；；小区环境安静舒适；</x:v>
       </x:c>
       <x:c r="L93" t="str">
-        <x:v>万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待。；万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 万柳书院次顶层三居室 隐私社区 采光好 三车位 一储. 下楼地铁站 万柳新小区 全新智能家居 有车位 可长租. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |.。；海淀-军博 复兴路乙6号院出租房源图片 海淀军博复兴路电梯两居家电齐全近地铁1号线出行方便随时入住 2室1厅 63m² 海淀-军博 复兴路乙6号院 6300元/月.。</x:v>
-      </x:c>
-      <x:c r="M93" t="str"/>
+        <x:v>装修分为简单装修和精装修，多数房源家电配套齐全；；通勤：靠近紫雀路公交站，多条公交线路可直达市区，距离16号线西北旺站约1.4公里左右；；商超：步行可达昌融超市、蔬菜水果店，周边1-2公里内有兴泉商业广场、华联超市环保园店、D15生活美学馆，购物便利；；餐饮：相关信息未查询到；；医院：相关信息未查询到；</x:v>
+      </x:c>
+      <x:c r="M93" t="str">
+        <x:v>无直接差评信息，房源为步梯无电梯，介意爬楼的租客需要注意；</x:v>
+      </x:c>
       <x:c r="N93" t="str">
-        <x:v>价格线索：; 海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；海淀租金最高的小区 · 1.中间建筑50000元/月； 63m² 海淀-军博 复兴路乙6号院 6300元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；房屋质量/户型线索：万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待。；万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 万柳书院次顶层三居室 隐私社区 采光好 三车位 一储. 下楼地铁站 万柳新小区 全新智能家居 有车位 可长租. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |.。；承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；. 3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费。；生活便利线索：万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待。；万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. 10套起看 万城华府 万柳书院 大面宽 采光好 干净. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. 新出位置安静 可直接入住 楼层好 330平米 三面采. 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 万城华府 平层五居室 拎包入住 家具家电齐全 同看. 万城华府业主次出租 别墅 一层带 花圃 带车位配套齐. 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 联排别墅 精装修联排 六居 独立花园私家车库 可居家. 10套起看 万城华府 复式官邸 看房随时 有车位 干. 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 万柳书院次顶层三居室 隐私社区 采光好 三车位 一储. 下楼地铁站 万柳新小区 全新智能家居 有车位 可长租. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |.。；海淀-军博 复兴路乙6号院出租房源图片 海淀军博复兴路电梯两居家电齐全近地铁1号线出行方便随时入住 2室1厅 63m² 海淀-军博 复兴路乙6号院 6300元/月.。</x:v>
+        <x:v>房屋质量/户型线索：未查询到更小户型价格。；房龄信息未查询到；；户型以2室1厅1卫为主，南北通透/朝南，采光较好；；装修分为简单装修和精装修，多数房源家电配套齐全；；小区环境安静舒适；；生活便利线索：装修分为简单装修和精装修，多数房源家电配套齐全；；通勤：靠近紫雀路公交站，多条公交线路可直达市区，距离16号线西北旺站约1.4公里左右；；商超：步行可达昌融超市、蔬菜水果店，周边1-2公里内有兴泉商业广场、华联超市环保园店、D15生活美学馆，购物便利；；餐饮：相关信息未查询到；；医院：相关信息未查询到；；风险线索：无直接差评信息，房源为步梯无电梯，介意爬楼的租客需要注意；</x:v>
       </x:c>
       <x:c r="O93" t="str">
-        <x:v>1. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-2. 北京海淀区租房子 - 房天下 http://www.fang.com/houses/zf_253028bj
-3. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/cd-haidian
-4. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian
-5. 2023年8月北京海淀区公租房价格一览表- 北京本地宝 http://bj.bendibao.com/zffw/2023821/351359.shtm</x:v>
+        <x:v>1. ["环保嘉苑(13号院) 家电齐全 2室1厅1卫 阳光充足","http://m.anjuke.com/bj/rent/4606817685988359-3/"]
+2. ["环保嘉苑(13号院) 2室1厅1卫 家电齐全 采光好","http://m.anjuke.com/bj/rent/4575321417868298-3/"]
+3. ["环保嘉苑(13号院) 2室1厅1卫 南北通透 精装修","http://m.anjuke.com/bj/rent/4596602113747972-3/"]
+4. 环保嘉苑(13号院) 家电齐全 2室1厅1卫 阳光充足 http://m.anjuke.com/bj/rent/4606817685988359-3/
+5. 三室 南北通透 近地铁 全天采光 随时入住 看房方便 https://m.58.com/sy/zufang/83360438008666x.shtml
+6. 环保嘉苑(13号院) 2室1厅1卫 家电齐全 采光好 http://m.anjuke.com/bj/rent/4575321417868298-3/
+7. 物业直签 精装整租 押一付一 交通便利 独厨独卫 http://m.anjuke.com/dongyang/rent/4537143839204359-3/
+8. 环保嘉苑(13号院) 2室1厅1卫 南北通透 精装修 http://m.anjuke.com/bj/rent/4596602113747972-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -4839,39 +5093,41 @@
         <x:v>北京市海淀区安宁庄路(上林溪西北侧)</x:v>
       </x:c>
       <x:c r="E94" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F94" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G94" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H94" t="n">
         <x:v>8.8</x:v>
       </x:c>
       <x:c r="I94" t="str">
-        <x:v>金隅物业品质保障，精装修交付且租金合理，紧邻科技园，生活配套成熟。</x:v>
+        <x:v>房龄新且装修好，步行可达大厂园区，通勤极便，配套成熟，是高品质首选。</x:v>
       </x:c>
       <x:c r="J94" t="str">
-        <x:v>. 交通便利周边配套齐采光好全装全配. 2800元/月；· 交通便利周边配套齐采光好全装全配. 2300元/月</x:v>
+        <x:v>整租：1室1厅约5000-5700元/月；，2室1厅约7500-8800元/月；，3室1厅约6800-8500元/月；合租：单间次卧约2000-2850元/月；，主卧（带阳台）约2600-3500元/月</x:v>
       </x:c>
       <x:c r="K94" t="str">
-        <x:v>1、金隅凤栖家园在西三旗，金隅的物业，品质方面不会差，精装修交付，西三旗是海淀东北门户，中关村东升科技园、中关村智能智造基地、西三旗（金隅）科技园的所在地。；金隅凤栖家园共有产权住房项目由北京金隅程远房地产开发有限公司开发建设，项目位于北京市海淀区清河安宁庄地区，销售均价44800元/建筑平方米(含全装修费用)。；北京金隅凤栖家园地址_户型图_房价 - 搜狐焦点。；北京金隅凤栖家园楼盘电话4006162877-412088，楼盘地址为北京市海淀区清河安宁庄地区（建设中），更多房价、地址、户型图、实景图、交通和周边配套等金隅凤栖家园楼盘详情信息，。；金隅凤栖家园交付，见证品质人居新标杆 - 凤凰网。</x:v>
+        <x:v>小区为较新住宅，多数房源为精装修，部分为首次出租；；户型以1-3居室为主，多南北通透、采光充足；；物业管理到位，集中供暖；；暂未查到大规模隔音问题差评，多数合租反映日常安静。；未发现明显大规模差评风险，暂未查询到集中性房屋质量或物业纠纷负面反馈，部分房源为个人转租，需注意核实房源产权和合同细节。</x:v>
       </x:c>
       <x:c r="L94" t="str">
-        <x:v>金隅凤栖家园. 8.1分. 地址. 海淀区安宁庄东路1号1820-618B、619B、624A地块R2二类 ... 交通便利周边配套齐采光好全装全配. 2800元/月 · 2室1厅。；小米快手元中心海淀安宁庄金隅凤栖家园精装次卧全女生合租 · 62天前 · 交通便利周边配套齐采光好全装全配. 2300元/月 ;；北京金隅凤栖家园楼盘电话4006162877-412088，楼盘地址为北京市海淀区清河安宁庄地区（建设中），更多房价、地址、户型图、实景图、交通和周边配套等金隅凤栖家园楼盘详情信息，。</x:v>
-      </x:c>
-      <x:c r="M94" t="str"/>
+        <x:v>位于海淀安宁庄，距离13号线清河站约1.1公里，近小米科技园、快手元中心，步行7-8分钟可达小米科技园，通勤对互联网从业者十分便利；；周边商超配套齐全，餐饮选择丰富，靠近清河商圈，距离医院等配套设施较近，生活便利度较高。</x:v>
+      </x:c>
+      <x:c r="M94" t="str">
+        <x:v>暂未查到大规模隔音问题差评，多数合租反映日常安静。；未发现明显大规模差评风险，暂未查询到集中性房屋质量或物业纠纷负面反馈，部分房源为个人转租，需注意核实房源产权和合同细节。</x:v>
+      </x:c>
       <x:c r="N94" t="str">
-        <x:v>价格线索：. 交通便利周边配套齐采光好全装全配. 2800元/月；· 交通便利周边配套齐采光好全装全配. 2300元/月；房屋质量/户型线索：1、金隅凤栖家园在西三旗，金隅的物业，品质方面不会差，精装修交付，西三旗是海淀东北门户，中关村东升科技园、中关村智能智造基地、西三旗（金隅）科技园的所在地。；金隅凤栖家园共有产权住房项目由北京金隅程远房地产开发有限公司开发建设，项目位于北京市海淀区清河安宁庄地区，销售均价44800元/建筑平方米(含全装修费用)。；北京金隅凤栖家园地址_户型图_房价 - 搜狐焦点。；北京金隅凤栖家园楼盘电话4006162877-412088，楼盘地址为北京市海淀区清河安宁庄地区（建设中），更多房价、地址、户型图、实景图、交通和周边配套等金隅凤栖家园楼盘详情信息，。；金隅凤栖家园交付，见证品质人居新标杆 - 凤凰网。；生活便利线索：金隅凤栖家园. 8.1分. 地址. 海淀区安宁庄东路1号1820-618B、619B、624A地块R2二类 ... 交通便利周边配套齐采光好全装全配. 2800元/月 · 2室1厅。；小米快手元中心海淀安宁庄金隅凤栖家园精装次卧全女生合租 · 62天前 · 交通便利周边配套齐采光好全装全配. 2300元/月 ;；北京金隅凤栖家园楼盘电话4006162877-412088，楼盘地址为北京市海淀区清河安宁庄地区（建设中），更多房价、地址、户型图、实景图、交通和周边配套等金隅凤栖家园楼盘详情信息，。</x:v>
+        <x:v>价格线索：整租：1室1厅约5000-5700元/月；，2室1厅约7500-8800元/月；，3室1厅约6800-8500元/月；合租：单间次卧约2000-2850元/月；，主卧（带阳台）约2600-3500元/月；房屋质量/户型线索：小区为较新住宅，多数房源为精装修，部分为首次出租；；户型以1-3居室为主，多南北通透、采光充足；；物业管理到位，集中供暖；；暂未查到大规模隔音问题差评，多数合租反映日常安静。；未发现明显大规模差评风险，暂未查询到集中性房屋质量或物业纠纷负面反馈，部分房源为个人转租，需注意核实房源产权和合同细节。；生活便利线索：位于海淀安宁庄，距离13号线清河站约1.1公里，近小米科技园、快手元中心，步行7-8分钟可达小米科技园，通勤对互联网从业者十分便利；；周边商超配套齐全，餐饮选择丰富，靠近清河商圈，距离医院等配套设施较近，生活便利度较高。；风险线索：暂未查到大规模隔音问题差评，多数合租反映日常安静。；未发现明显大规模差评风险，暂未查询到集中性房屋质量或物业纠纷负面反馈，部分房源为个人转租，需注意核实房源产权和合同细节。</x:v>
       </x:c>
       <x:c r="O94" t="str">
-        <x:v>1. 金隅凤栖家园详情- 租房 - 北京二手房- 房天下 https://esf.fang.com/loupan/1010194679.htm
-2. 北京海淀金隅凤栖家园租房信息】北京手机房天下 https://m.fang.com/zf/bj_xm1010194679
-3. 业主踩盘投稿：金隅凤栖家园618&amp;619地块，发现一些问题。 https://zhuanlan.zhihu.com/p/650545595
-4. 金隅凤栖家园 https://www.davfang.com/newHouse/6000000295
-5. 2023年5月北京海淀区金隅凤栖家园共有产权房递补选房公告 http://bj.bendibao.com/zffw/202356/347086.shtm</x:v>
+        <x:v>1. 整租·金隅凤栖家园 3室1厅-北京幸福里 https://m.xflapp.com/zufang/neighbor-house-list/bj-7365762179289169983.html
+2. 小米快手个人转租无中介费金隅凤栖主卧全女生3000 https://www.douban.com/group/topic/485416268/?_spm_id=MTM0MTQwODcw
+3. 【北京海淀区出租公寓10002元/月以下租房信息 https://fang.com/houses/zf_253712bj/c20-d210002,4,99-i388/
+4. 🌟首次出租!金隅凤栖家园南北通透三居室合租 https://m.fang.com/note/bj_150290.html
+5. 【海淀整租一居室 https://m.fang.com/houses/zf_259821_bj/p2h3/</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -4888,41 +5144,43 @@
         <x:v>北京市海淀区土井村东路87号大棚</x:v>
       </x:c>
       <x:c r="E95" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F95" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G95" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H95" t="n">
-        <x:v>6.2</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="I95" t="str">
-        <x:v>地铁上盖交通便利，但无独立小区且隔音差，人员构成复杂，居住环境较吵闹。</x:v>
+        <x:v>缺乏具体小区信息，证据多为区域泛化描述，房龄可能较老，建议谨慎实地考察。</x:v>
       </x:c>
       <x:c r="J95" t="str">
-        <x:v>高6层洋房4居) 便利周边配套齐独门独卫29500元/月；多; 户型丰富; 绿化好; 配套齐全. 73718元/㎡；配套齐全. 73718元/㎡；租金：仅提供一房、面积26平方米，租金价格2300元/月</x:v>
+        <x:v>区整租价格区间为：单间/次卧约2400-2500元/月；，一居室约4400-6500元/月；，两居室约6100-10500元/月；，三居室约7500-13500元/月</x:v>
       </x:c>
       <x:c r="K95" t="str">
-        <x:v>北京花园,精装修,安静,配套成熟,非底层。；总高6层洋房4居) 便利周边配套齐独门独卫29500元/月查看全部相关楼盘显示全部户型(10) 查看综合测评得分小区品质8.8 户型评分9.8。；地铁上盖地点不错，没有小区只有两栋楼，不隔音噪音很大，朋友家住这里两年经常吐槽，楼里有开公司的开补习班的特别吵，人员复杂安全不行。；大户型居多;；户型丰富;</x:v>
+        <x:v>未查询到目标小区对应房子质量相关公开信息，海淀同类老旧普通住宅小区多为简单装修/精装修，房龄普遍较长，户型多为1室1厅、2室1厅，隔音效果一般，未查询到目标小区物业相关评价；</x:v>
       </x:c>
       <x:c r="L95" t="str">
-        <x:v>北京花园,精装修,安静,配套成熟,非底层。；总高6层洋房4居) 便利周边配套齐独门独卫29500元/月查看全部相关楼盘显示全部户型(10) 查看综合测评得分小区品质8.8 户型评分9.8。；地铁上盖地点不错，没有小区只有两栋楼，不隔音噪音很大，朋友家住这里两年经常吐槽，楼里有开公司的开补习班的特别吵，人员复杂安全不行。；配套齐全. 73718元/㎡. 5月挂牌均价 · 7套. 在售房源 · 19套. 在租房源 · 估价 · 8.3. 小区评分.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。</x:v>
+        <x:v>未查询到目标小区对应生活配套信息，该区域海淀同类住宅区周边多临近地铁6号线、10号线等线路，步行到地铁站多在500-2000米范围内，周边分布有多家生活超市、餐饮门店，周边1公里内覆盖社区医疗机构，整体通勤及日常消费较为便利；</x:v>
       </x:c>
       <x:c r="M95" t="str">
-        <x:v>地铁上盖地点不错，没有小区只有两栋楼，不隔音噪音很大，朋友家住这里两年经常吐槽，楼里有开公司的开补习班的特别吵，人员复杂安全不行。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未查询到目标小区对应房子质量相关公开信息，海淀同类老旧普通住宅小区多为简单装修/精装修，房龄普遍较长，户型多为1室1厅、2室1厅，隔音效果一般，未查询到目标小区物业相关评价；</x:v>
       </x:c>
       <x:c r="N95" t="str">
-        <x:v>价格线索：高6层洋房4居) 便利周边配套齐独门独卫29500元/月；多; 户型丰富; 绿化好; 配套齐全. 73718元/㎡；配套齐全. 73718元/㎡；租金：仅提供一房、面积26平方米，租金价格2300元/月；房屋质量/户型线索：北京花园,精装修,安静,配套成熟,非底层。；总高6层洋房4居) 便利周边配套齐独门独卫29500元/月查看全部相关楼盘显示全部户型(10) 查看综合测评得分小区品质8.8 户型评分9.8。；地铁上盖地点不错，没有小区只有两栋楼，不隔音噪音很大，朋友家住这里两年经常吐槽，楼里有开公司的开补习班的特别吵，人员复杂安全不行。；大户型居多;；户型丰富;；生活便利线索：北京花园,精装修,安静,配套成熟,非底层。；总高6层洋房4居) 便利周边配套齐独门独卫29500元/月查看全部相关楼盘显示全部户型(10) 查看综合测评得分小区品质8.8 户型评分9.8。；地铁上盖地点不错，没有小区只有两栋楼，不隔音噪音很大，朋友家住这里两年经常吐槽，楼里有开公司的开补习班的特别吵，人员复杂安全不行。；配套齐全. 73718元/㎡. 5月挂牌均价 · 7套. 在售房源 · 19套. 在租房源 · 估价 · 8.3. 小区评分.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；风险线索：地铁上盖地点不错，没有小区只有两栋楼，不隔音噪音很大，朋友家住这里两年经常吐槽，楼里有开公司的开补习班的特别吵，人员复杂安全不行。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：区整租价格区间为：单间/次卧约2400-2500元/月；，一居室约4400-6500元/月；，两居室约6100-10500元/月；，三居室约7500-13500元/月；房屋质量/户型线索：未查询到目标小区对应房子质量相关公开信息，海淀同类老旧普通住宅小区多为简单装修/精装修，房龄普遍较长，户型多为1室1厅、2室1厅，隔音效果一般，未查询到目标小区物业相关评价；；生活便利线索：未查询到目标小区对应生活配套信息，该区域海淀同类住宅区周边多临近地铁6号线、10号线等线路，步行到地铁站多在500-2000米范围内，周边分布有多家生活超市、餐饮门店，周边1公里内覆盖社区医疗机构，整体通勤及日常消费较为便利；；风险线索：未查询到目标小区对应房子质量相关公开信息，海淀同类老旧普通住宅小区多为简单装修/精装修，房龄普遍较长，户型多为1室1厅、2室1厅，隔音效果一般，未查询到目标小区物业相关评价；</x:v>
       </x:c>
       <x:c r="O95" t="str">
-        <x:v>1. 北京花园- 二手房，租房 https://esf.fang.com/loupan/1010077660.htm
-2. 花园公寓- 房价|租房【北京贝壳找房】 https://m.ke.com/bj/xiaoqu/1111027375459
-3. 专家国际花园,后屯路 - 租房-北京安居客 https://beijing.anjuke.com/community/view/218348
-4. 北京北别墅竟才70 多万？带花园+ 大产权独立房本 - YouTube https://www.youtube.com/watch?v=c7Tx-1ZD3L4
-5. 北京安外花园二手房|房价 - 链家 https://bj.lianjia.com/xiaoqu/1111027375663</x:v>
+        <x:v>1. 花园村 低楼层 南北向两居室 随时入住 https://bj.zu.anjuke.com/fangyuan/4428190928512009
+2. 【7图】牡丹园地铁口，花园公寓精装一居室，设施齐全出行方便，看房随时 https://m.58.com/bj/zufang/4087417678683146h.shtml
+3. 【7图】牡丹园地铁口，花园公寓精装一居室，设施齐全出行方便，看房随时，花园东路32号 https://m.58.com/bj/zufang/4087417572486154h.shtml
+4. 花园桥，又一村，朝南1居，可长租，地铁610号线旁 http://m.anjuke.com/bj/rent/4520132545801222-3/
+5. 新上！花园桥 首师附 地铁6号线 精装出租 随时入住 http://m.anjuke.com/bj/rent/4576719614438404-3/
+6. 花园村社区 2室1厅1卫 精装修 南北通透 http://m.anjuke.com/bj/rent/4547009454402570-3/
+7. 【花园桥单间租房 https://m.fang.com/houses/zf_257921_bj/</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -4939,39 +5197,38 @@
         <x:v>北京市海淀区西北旺回民公墓秋枫阁员工公寓</x:v>
       </x:c>
       <x:c r="E96" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F96" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G96" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H96" t="n">
-        <x:v>6.5</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="I96" t="str">
-        <x:v>交通便利且配套齐全，但存在卫生清洁不到位及隔音问题，证据指向较为杂乱。</x:v>
-      </x:c>
-      <x:c r="J96" t="str">
-        <x:v> 3室2厅176㎡. 20000元/月；3室2厅176㎡. 20000元/月；租 1-3个月 4-6个月. 1300-2300元/月</x:v>
-      </x:c>
+        <x:v>疑似保租房或员工公寓，租金政策优惠但缺乏具体挂牌价，适合特定就业人群。</x:v>
+      </x:c>
+      <x:c r="J96" t="str"/>
       <x:c r="K96" t="str">
-        <x:v>邻地铁配套齐全精装修有阳台随时看房 · 整租马连洼柳浪家园南里1室1厅. 5600元1室1厅 ... 价格能便宜万德嘉园二区精装两居跟业主签约看房方便. 7200元2室2厅·81.00。；整个房间打扫非常不到位,很多地方都有灰尘,地毯清洁也不干净, 北京雅诗阁窗户隔音效果也有问题,还不含早餐。</x:v>
+        <x:v>未找到北京市海淀区秋枫阁员工公寓明确公开的租金价格，海淀区同类型面向青年的保租房项目梯度租金政策为：第1-2年按备案租金的60%缴纳，第3-4年70%，第5-6年80%，参考周边同品质项目，36平方米一居室前两年月租约2365元，租金单价范围约51-109.5元/平方米·月，租金一般包含家具家电使用费、物业费，不包含水电、供暖等费用。；无该项目明确的户型、隔音、房龄、装修、物业评价信息，海淀区同类型配套员工公寓多为LOFT设计，空间分区合理，配备智能家电、环保家具，拎包入住，提供24小时管家服务、智能化安全管理，物业服务完善。</x:v>
       </x:c>
       <x:c r="L96" t="str">
-        <x:v>邻地铁配套齐全精装修有阳台随时看房 · 整租马连洼柳浪家园南里1室1厅. 5600元1室1厅 ... 价格能便宜万德嘉园二区精装两居跟业主签约看房方便. 7200元2室2厅·81.00。</x:v>
+        <x:v>未找到北京市海淀区秋枫阁员工公寓明确公开的租金价格，海淀区同类型面向青年的保租房项目梯度租金政策为：第1-2年按备案租金的60%缴纳，第3-4年70%，第5-6年80%，参考周边同品质项目，36平方米一居室前两年月租约2365元，租金单价范围约51-109.5元/平方米·月，租金一般包含家具家电使用费、物业费，不包含水电、供暖等费用。；无该项目明确的户型、隔音、房龄、装修、物业评价信息，海淀区同类型配套员工公寓多为LOFT设计，空间分区合理，配备智能家电、环保家具，拎包入住，提供24小时管家服务、智能化安全管理，物业服务完善。；项目位于海淀区西北旺，无该项目明确的通勤、配套信息，同区域园区型员工公寓一般配建有便民食堂、公共休闲娱乐健身区域，周边未来多规划有商业配套，临近产业园区，通勤对在周边就业人员较为便利。</x:v>
       </x:c>
       <x:c r="M96" t="str"/>
       <x:c r="N96" t="str">
-        <x:v>价格线索： 3室2厅176㎡. 20000元/月；3室2厅176㎡. 20000元/月；租 1-3个月 4-6个月. 1300-2300元/月；房屋质量/户型线索：邻地铁配套齐全精装修有阳台随时看房 · 整租马连洼柳浪家园南里1室1厅. 5600元1室1厅 ... 价格能便宜万德嘉园二区精装两居跟业主签约看房方便. 7200元2室2厅·81.00。；整个房间打扫非常不到位,很多地方都有灰尘,地毯清洁也不干净, 北京雅诗阁窗户隔音效果也有问题,还不含早餐。；生活便利线索：邻地铁配套齐全精装修有阳台随时看房 · 整租马连洼柳浪家园南里1室1厅. 5600元1室1厅 ... 价格能便宜万德嘉园二区精装两居跟业主签约看房方便. 7200元2室2厅·81.00。</x:v>
+        <x:v>房屋质量/户型线索：未找到北京市海淀区秋枫阁员工公寓明确公开的租金价格，海淀区同类型面向青年的保租房项目梯度租金政策为：第1-2年按备案租金的60%缴纳，第3-4年70%，第5-6年80%，参考周边同品质项目，36平方米一居室前两年月租约2365元，租金单价范围约51-109.5元/平方米·月，租金一般包含家具家电使用费、物业费，不包含水电、供暖等费用。；无该项目明确的户型、隔音、房龄、装修、物业评价信息，海淀区同类型配套员工公寓多为LOFT设计，空间分区合理，配备智能家电、环保家具，拎包入住，提供24小时管家服务、智能化安全管理，物业服务完善。；生活便利线索：未找到北京市海淀区秋枫阁员工公寓明确公开的租金价格，海淀区同类型面向青年的保租房项目梯度租金政策为：第1-2年按备案租金的60%缴纳，第3-4年70%，第5-6年80%，参考周边同品质项目，36平方米一居室前两年月租约2365元，租金单价范围约51-109.5元/平方米·月，租金一般包含家具家电使用费、物业费，不包含水电、供暖等费用。；无该项目明确的户型、隔音、房龄、装修、物业评价信息，海淀区同类型配套员工公寓多为LOFT设计，空间分区合理，配备智能家电、环保家具，拎包入住，提供24小时管家服务、智能化安全管理，物业服务完善。；项目位于海淀区西北旺，无该项目明确的通勤、配套信息，同区域园区型员工公寓一般配建有便民食堂、公共休闲娱乐健身区域，周边未来多规划有商业配套，临近产业园区，通勤对在周边就业人员较为便利。</x:v>
       </x:c>
       <x:c r="O96" t="str">
-        <x:v>1. 海淀公寓出租_北京海淀酒店式公寓房屋出租价格，海淀商住两用租房 https://bj.zu.anjuke.com/gongyu-zufang/haidian
-2. 北京海淀上地租房信息 - 58同城 https://mob.58.com/zf/bj-shangdi
-3. 海淀酒店式公寓出租 - 房天下 http://www.fang.com/houses/zf_252307bj
-4. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu
-5. 海淀区酒店式公寓出租 https://www.gongyujia.com.cn/chuzu?aid=2</x:v>
+        <x:v>1. ["海淀922套青年公寓配租 青年人才可拎包入住","https://zyk.bjhd.gov.cn/ywdt/hdywx/202506/t20250611_4772428.shtml?type=computer"]
+2. ["最低51元㎡/月，北京海淀2161套保租房申请！附入口","http://news.qq.com/rain/a/20260408A07K0300"]
+3. ["秋枫阁民宿","https://www.wingontravel.com/hotel/detail-lijiang-130053330/qiufengge-homestay"]
+4. 海淀922套青年公寓配租 青年人才可拎包入住 https://zyk.bjhd.gov.cn/ywdt/hdywx/202506/t20250611_4772428.shtml?type=computer
+5. 秋枫阁民宿 https://www.wingontravel.com/hotel/detail-lijiang-130053330/qiufengge-homestay
+6. 最低51元㎡/月，北京海淀2161套保租房申请！附入口 http://news.qq.com/rain/a/20260408A07K0300</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -4988,7 +5245,7 @@
         <x:v>北京市海淀区西二旗安宁庄路11号院</x:v>
       </x:c>
       <x:c r="E97" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F97" t="n">
         <x:v>9</x:v>
@@ -4997,30 +5254,33 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H97" t="n">
-        <x:v>8.2</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="I97" t="str">
-        <x:v>位于核心科技区，物业管理规范且生活配套极其便利，适合周边上班族。</x:v>
+        <x:v>房龄较老且仅单栋楼，但胜在地理位置优越，通勤西二旗方便，租金相对亲民。</x:v>
       </x:c>
       <x:c r="J97" t="str">
-        <x:v>m² 海淀-安宁庄 安宁庄西路13号院 2700元/月；北京海淀区房屋出租3000-500013元/月；周边配套齐独门独卫交通便利. 4700元/月；租 1-3个月 4-6个月. 1300-2300元/月</x:v>
+        <x:v>域安宁庄周边小区：一居室租金约4000-4500元/月；，两居室约6000-7200元/月</x:v>
       </x:c>
       <x:c r="K97" t="str">
-        <x:v>物业自己管理得挺规整。；面积选择：户型从七八十平米的小开间，。；承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；. 3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费。</x:v>
+        <x:v>小区1987-1988年建成，房龄较老；；建筑类型为板楼/塔板结合，仅1栋楼共416户；；物业费3.18元/平米·月，物业公司为北京凯帝克物业管理有限责任公司，公开信息未提及明确隔音、户型、装修的用户评价；</x:v>
       </x:c>
       <x:c r="L97" t="str">
-        <x:v>周边配套齐独门独卫交通便利. 4700元/月. 相寓甘家口·车公庄西路14号院·高楼层·1居室. 整租|1室1厅|35㎡|朝南. 海淀-增光路-车公庄西路14号院. 距6号线白石桥南站约172米。；在北京海淀区，上地、西二旗板块是科技企业云集的核心区域，而安宁 ... 周边生活气息浓郁，配套极其便利。</x:v>
+        <x:v>公开渠道未查询到安宁庄路11号院公开的租房挂牌均价，同区域安宁庄周边小区：一居室租金约4000-4500元/月，两居室约6000-7200元/月，可作参考；；该小区位于海淀区西二旗安宁庄，临近清河站、西二旗地铁站（13号线、8号线、昌平线），周边公交覆盖，通勤到西二旗、上地科技园较方便；；同区域安宁庄周边有清河医院、物美超市、蓝岛金隅商圈、各类餐饮门店，可满足日常需求，但本小区公开周边配套信息较少；</x:v>
       </x:c>
       <x:c r="M97" t="str"/>
       <x:c r="N97" t="str">
-        <x:v>价格线索：m² 海淀-安宁庄 安宁庄西路13号院 2700元/月；北京海淀区房屋出租3000-500013元/月；周边配套齐独门独卫交通便利. 4700元/月；租 1-3个月 4-6个月. 1300-2300元/月；房屋质量/户型线索：物业自己管理得挺规整。；面积选择：户型从七八十平米的小开间，。；承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；. 3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费。；生活便利线索：周边配套齐独门独卫交通便利. 4700元/月. 相寓甘家口·车公庄西路14号院·高楼层·1居室. 整租|1室1厅|35㎡|朝南. 海淀-增光路-车公庄西路14号院. 距6号线白石桥南站约172米。；在北京海淀区，上地、西二旗板块是科技企业云集的核心区域，而安宁 ... 周边生活气息浓郁，配套极其便利。</x:v>
+        <x:v>价格线索：域安宁庄周边小区：一居室租金约4000-4500元/月；，两居室约6000-7200元/月；房屋质量/户型线索：小区1987-1988年建成，房龄较老；；建筑类型为板楼/塔板结合，仅1栋楼共416户；；物业费3.18元/平米·月，物业公司为北京凯帝克物业管理有限责任公司，公开信息未提及明确隔音、户型、装修的用户评价；；生活便利线索：公开渠道未查询到安宁庄路11号院公开的租房挂牌均价，同区域安宁庄周边小区：一居室租金约4000-4500元/月，两居室约6000-7200元/月，可作参考；；该小区位于海淀区西二旗安宁庄，临近清河站、西二旗地铁站（13号线、8号线、昌平线），周边公交覆盖，通勤到西二旗、上地科技园较方便；；同区域安宁庄周边有清河医院、物美超市、蓝岛金隅商圈、各类餐饮门店，可满足日常需求，但本小区公开周边配套信息较少；</x:v>
       </x:c>
       <x:c r="O97" t="str">
-        <x:v>1. 北京安宁庄路11号院二手房 - 链家 https://bj.lianjia.com/xiaoqu/1111042550527
-2. 海淀安宁庄租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian-q-annz
-3. 北京海淀区房屋出租3000-500013元/月租房信息 - 房天下 https://fang.com/houses/zf_252999bj/c23000-d2500013-h38-i327
-4. 「__2026年想在安宁庄东路租办公室，企房房揭秘甲16号真实租金与 ... https://bj-sydc.com/article.php?id=35325
-5. 北京安宁庄东路甲16号写字楼出租行情与靠谱租赁平台选择-企房房 https://www.qifangfang.com/index.php/home/news/d.html?id=59803</x:v>
+        <x:v>1. ["安宁庄路11号院 诸葛找房","https://m.zhuge.com/xiaoqu/bj/1030027/"]
+2. ["安宁庄路11号院 房天下","http://m.fang.com/xiaoqu/bj-1010129715.html"]
+3. 安宁庄路11号院 https://m.zhuge.com/xiaoqu/bj/1030027/
+4. 清河站旁 宣海家园一层两居室 不挑客户 可当宿舍 看房随时 https://bj.58.com/zufang/85868193079258x.shtml
+5. 15号线 5号线 关庄路11号院 电梯房 南北通透 精装修 http://m.anjuke.com/bj/rent/4487934002654221-3/
+6. 清河安宁庄 安宁佳园正规两居室 小米科技园 元中心快手西二旗 http://m.anjuke.com/bj/rent/4590004225238024-3/
+7. 安宁庄路11号院 http://m.fang.com/xiaoqu/bj-1010129715.html
+8. 0押月付，上地安宁庄，安宁佳园，小米元中心，泰山饭店，西二旗 http://m.anjuke.com/bj/rent/4496555902428172-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -5037,41 +5297,39 @@
         <x:v>北京市海淀区圆明园西路18号中发百旺商城F4</x:v>
       </x:c>
       <x:c r="E98" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F98" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G98" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H98" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I98" t="str">
-        <x:v>紧邻网易，百旺家苑户型方正且采光好，配套成熟，虽租金较高但通勤极便。</x:v>
+        <x:v>离地铁近且配套成熟，租金适中，虽为步梯房但通勤便利性极佳，证据充分。</x:v>
       </x:c>
       <x:c r="J98" t="str">
-        <x:v>房北京小区大全,冠城大通百旺府参考均价:63843元/㎡；链家网北京小区大全,百旺家苑参考均价:74419元/㎡</x:v>
+        <x:v>中该区域同位置两居室租金区间为5300-5900元/月；：58㎡简单装修两居约5300元/月；，60㎡简单装修两居约5500元/月；，59㎡精装修两居约5900元/月</x:v>
       </x:c>
       <x:c r="K98" t="str">
-        <x:v>户型齐全，主打户型方正,明厨,客厅朝南二居 ... 百旺家苑户型主要有60平-120平的户型方正,明厨,客厅朝南的二居、90平-164平的户型方正的三居、60平-85平的户型方正,明厨,主卧。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；但有些户型不好，比如一居客厅带斜角，有的两居户型是长条，居住品质会打折扣。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。</x:v>
+        <x:v>公开租房信息中该区域同位置两居室租金区间为5300-5900元/月：58㎡简单装修两居约5300元/月，60㎡简单装修两居约5500元/月，59㎡精装修两居约5900元/月；；该区域多为步梯普通住宅，楼层多为高/中层（总高6层），户型常见南北通透两室一厅，装修分为简单装修和精装修两类，多数房源家具家电齐全可直接入住；；公开信息未明确提及具体房龄、隔音情况以及物业评价；</x:v>
       </x:c>
       <x:c r="L98" t="str">
-        <x:v>安居客小区频道，提供百旺家苑二手房,平均房价72291元/平米,找百旺家苑二手房，百旺家苑租房，百旺家苑房价走势、实景图、房型图、周边交通配套信息就上安居客.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。</x:v>
-      </x:c>
-      <x:c r="M98" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>通勤：步行约592米可达16号线/18号线马连洼站，步行约1000米可达农大南路站，通勤便利；；商超：步行可达中发百旺商城，周边有美廉美超市、超市发便民菜店、北京华联BHG Mall，购物便捷；；医疗：距离解放军总医院第八医学中心约1公里，就医方便；；餐饮等其他生活配套可依托中发百旺商城及周边商圈满足需求；</x:v>
+      </x:c>
+      <x:c r="M98" t="str"/>
       <x:c r="N98" t="str">
-        <x:v>价格线索：房北京小区大全,冠城大通百旺府参考均价:63843元/㎡；链家网北京小区大全,百旺家苑参考均价:74419元/㎡；房屋质量/户型线索：户型齐全，主打户型方正,明厨,客厅朝南二居 ... 百旺家苑户型主要有60平-120平的户型方正,明厨,客厅朝南的二居、90平-164平的户型方正的三居、60平-85平的户型方正,明厨,主卧。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；但有些户型不好，比如一居客厅带斜角，有的两居户型是长条，居住品质会打折扣。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。；生活便利线索：安居客小区频道，提供百旺家苑二手房,平均房价72291元/平米,找百旺家苑二手房，百旺家苑租房，百旺家苑房价走势、实景图、房型图、周边交通配套信息就上安居客.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：中该区域同位置两居室租金区间为5300-5900元/月；：58㎡简单装修两居约5300元/月；，60㎡简单装修两居约5500元/月；，59㎡精装修两居约5900元/月；房屋质量/户型线索：公开租房信息中该区域同位置两居室租金区间为5300-5900元/月：58㎡简单装修两居约5300元/月，60㎡简单装修两居约5500元/月，59㎡精装修两居约5900元/月；；该区域多为步梯普通住宅，楼层多为高/中层（总高6层），户型常见南北通透两室一厅，装修分为简单装修和精装修两类，多数房源家具家电齐全可直接入住；；公开信息未明确提及具体房龄、隔音情况以及物业评价；；生活便利线索：通勤：步行约592米可达16号线/18号线马连洼站，步行约1000米可达农大南路站，通勤便利；；商超：步行可达中发百旺商城，周边有美廉美超市、超市发便民菜店、北京华联BHG Mall，购物便捷；；医疗：距离解放军总医院第八医学中心约1公里，就医方便；；餐饮等其他生活配套可依托中发百旺商城及周边商圈满足需求；</x:v>
       </x:c>
       <x:c r="O98" t="str">
-        <x:v>1. 百旺家苑,马连洼北路 https://beijing.anjuke.com/community/view/78963
-2. 百旺家苑- 二手房，租房-北京手机房天下 https://esf.fang.com/loupan/1010026855.htm
-3. 北京冠城大通百旺府二手房|房价 https://m.ke.com/bj/xiaoqu/1111027376165
-4. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100 ... https://m.36kr.com/p/1721780568065
-5. 达美奥克伍德华庭酒店公寓 - 短租 https://www.yudinggongyu.cn/beijing/36.cshtml</x:v>
+        <x:v>1. 地铁马连洼站百旺商城 农大 梅园南北通透 2室1厅 业主直签 http://m.anjuke.com/bj/rent/4360408603992077-3/
+2. 马连洼地铁口 309 中发百旺 梅园 2室1厅 业主直签 https://m.58.com/bj/zufang/84474582681947x.shtml
+3. 梅园 兰园 百旺家苑 软件园 百度 新浪 网易 腾讯 华联 http://m.anjuke.com/bj/rent/4578093315122176-3/
+4. 北京发租房避坑指南:17亿纳入监管，防止企业挪用租金押金 https://news.china.com/socialgd/10000169/20251225/49107895.html
+5. 怀柔市民请注意！这些住房租赁企业被警示 http://news.qq.com/rain/a/20251218A054E900</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -5088,39 +5346,44 @@
         <x:v>北京市海淀区马连洼街道</x:v>
       </x:c>
       <x:c r="E99" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F99" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G99" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H99" t="n">
-        <x:v>7.2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I99" t="str">
-        <x:v>海淀老牌社区，生活便利且有精装大户型，但房龄偏老，通勤距离略远于百旺。</x:v>
+        <x:v>房龄较老（70年代），虽绿化好且离地铁不远，但需关注老旧房屋的居住体验。</x:v>
       </x:c>
       <x:c r="J99" t="str">
-        <x:v>租 1-3个月 4-6个月. 1300-2300元/月；海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月； 3室2厅176㎡. 20000元/月；3室2厅176㎡. 20000元/月</x:v>
+        <x:v>55㎡2室1厅整租约5200元/月；，65㎡2室1厅整租约5600-5800元/月；，80㎡2室1厅整租约6500-6600元/月；，80㎡3室1厅整租约7000元/月；，106㎡3室2厅整租约9500元/月</x:v>
       </x:c>
       <x:c r="K99" t="str">
-        <x:v>小区户型 ;；1居室·4个户型. 42㎡~64㎡. 在售252万起 ;；2居室·43个户型. 50㎡~91㎡. 在售265万起 ;；3居室·8个户型. 67㎡~108㎡. 在售370万起。；水利社区2号院精装大三居中间层配套齐价格可谈业主签约 · 户型： 3室2厅2卫 · 装修： 精装修 · 面积： 109平米 · 朝向： 南北 · 楼层： 中层(共6层) · 类型： 普通住宅.。</x:v>
+        <x:v>小区建于1970年，房龄较老；；以板楼为主，主力户型为2室1厅，户型方正南北通透，采光通风较好；；多数在租房源为精装修，家具家电齐全可直接入住；；物业为单位自管物业，小区环境优雅绿化面积大，停车方便；；未查询到明确隔音相关评价；</x:v>
       </x:c>
       <x:c r="L99" t="str">
-        <x:v>水利社区2号院精装大三居中间层配套齐价格可谈业主签约 - 北京租房。；水利社区2号院精装大三居中间层配套齐价格可谈业主签约 · 户型： 3室2厅2卫 · 装修： 精装修 · 面积： 109平米 · 朝向： 南北 · 楼层： 中层(共6层) · 类型： 普通住宅.。；海淀区清华园街道政务服务中心:北京市海淀区清华大学校内照澜院;；2.申请家庭成员在本市均无住房且在本市生活；</x:v>
-      </x:c>
-      <x:c r="M99" t="str"/>
+        <x:v>通勤：距离16号线马连洼站步行约700-1300米，距离16号线农大南路站步行约1100-1900米，临近公交车站，出行便利；；配套：周边有超市、餐馆，生活配套设施齐全，未查询到明确医院相关信息；</x:v>
+      </x:c>
+      <x:c r="M99" t="str">
+        <x:v>搜索结果多为房源推广信息，较少真实租客口碑评价，小区分为1号院和2号院，存在名称泛化情况，未搜索到明确差评信息。；搜索结果多为房源推广信息，较少真实租客口碑评价，小区分为1号院和2号院，存在名称泛化情况，未搜索到明确差评信息</x:v>
+      </x:c>
       <x:c r="N99" t="str">
-        <x:v>价格线索：租 1-3个月 4-6个月. 1300-2300元/月；海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月； 3室2厅176㎡. 20000元/月；3室2厅176㎡. 20000元/月；房屋质量/户型线索：小区户型 ;；1居室·4个户型. 42㎡~64㎡. 在售252万起 ;；2居室·43个户型. 50㎡~91㎡. 在售265万起 ;；3居室·8个户型. 67㎡~108㎡. 在售370万起。；水利社区2号院精装大三居中间层配套齐价格可谈业主签约 · 户型： 3室2厅2卫 · 装修： 精装修 · 面积： 109平米 · 朝向： 南北 · 楼层： 中层(共6层) · 类型： 普通住宅.。；生活便利线索：水利社区2号院精装大三居中间层配套齐价格可谈业主签约 - 北京租房。；水利社区2号院精装大三居中间层配套齐价格可谈业主签约 · 户型： 3室2厅2卫 · 装修： 精装修 · 面积： 109平米 · 朝向： 南北 · 楼层： 中层(共6层) · 类型： 普通住宅.。；海淀区清华园街道政务服务中心:北京市海淀区清华大学校内照澜院;；2.申请家庭成员在本市均无住房且在本市生活；</x:v>
+        <x:v>价格线索：55㎡2室1厅整租约5200元/月；，65㎡2室1厅整租约5600-5800元/月；，80㎡2室1厅整租约6500-6600元/月；，80㎡3室1厅整租约7000元/月；，106㎡3室2厅整租约9500元/月；房屋质量/户型线索：小区建于1970年，房龄较老；；以板楼为主，主力户型为2室1厅，户型方正南北通透，采光通风较好；；多数在租房源为精装修，家具家电齐全可直接入住；；物业为单位自管物业，小区环境优雅绿化面积大，停车方便；；未查询到明确隔音相关评价；；生活便利线索：通勤：距离16号线马连洼站步行约700-1300米，距离16号线农大南路站步行约1100-1900米，临近公交车站，出行便利；；配套：周边有超市、餐馆，生活配套设施齐全，未查询到明确医院相关信息；；风险线索：搜索结果多为房源推广信息，较少真实租客口碑评价，小区分为1号院和2号院，存在名称泛化情况，未搜索到明确差评信息。；搜索结果多为房源推广信息，较少真实租客口碑评价，小区分为1号院和2号院，存在名称泛化情况，未搜索到明确差评信息</x:v>
       </x:c>
       <x:c r="O99" t="str">
-        <x:v>1. 水利局小区- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027379439
-2. 水利社区2号院精装大三居中间层配套齐价格可谈业主签约 - 北京租房 https://bj.zu.anjuke.com/fangyuan/4597211148557326?shangquan_id=5968&amp;is_auction=1
-3. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-4. 保障性住房申请资格审核 http://banshi.beijing.gov.cn/pubtask/task/1/110108000000/bb954ec6-803b-409b-9dd9-4baaeb17e628.html?locationCode=110108000000
-5. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu</x:v>
+        <x:v>1. 水利社区 精装干净两居 中间层采光好 配置齐全 价格可优惠! http://m.anjuke.com/bj/rent/4358927960054798-3/?ad_type=gz&amp;pagesource=12
+2. 水利社区怎么样?北京水利社区房价|房源|地址|户型图|周边配套详情 https://m.5i5j.com/bj/xq_news/10251.html
+3. 马连洼水利社区价格可谈 南北通透俩居室 配套全齐 与业主签约 https://m.anjuke.com/bj/rent/3648605847053324-3/?ad_type=gz
+4. 【多图】水利社区1号院，马连洼租房，水利社区 精装干净两居 中间层采光好 配置齐全 价格可优惠!，海淀租房 http://m.anjuke.com/bj/rent/4358927960054798-3/?ad_type=gz&amp;pagesource=12
+5. 马连洼水利社区价格可谈 南北通透俩居室 配套全齐 与业主签约 https://m.anjuke.com/bj/rent/3648605847053324-3/?ad_type=gz&amp;pagesource=12
+6. 水利社区1号院 低楼层 南北通透三居 干净整洁 跟业主直签 http://m.anjuke.com/ch/rent/4587133539769357-3/
+7. 马连洼地铁站水利社区精装两居室 http://m.anjuke.com/bj/rent/4514392581282831-3/
+8. 水利社区1号院 精装两居 中间层 配套齐全 跟业主直签可长住 http://m.anjuke.com/ch/rent/4564182553979908-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -5137,10 +5400,10 @@
         <x:v>北京市昌平区昌平路387号</x:v>
       </x:c>
       <x:c r="E100" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F100" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G100" t="n">
         <x:v>8</x:v>
@@ -5149,25 +5412,30 @@
         <x:v>6.5</x:v>
       </x:c>
       <x:c r="I100" t="str">
-        <x:v>位于昌平且临近地铁，合租价格极具竞争力，但房屋质量及环境证据较薄弱。</x:v>
-      </x:c>
-      <x:c r="J100" t="str">
-        <x:v>公园悦府(二区)6200元/月；0.00%; 3.融泽嘉园6号院6100元/月；0.00%; 4.融泽嘉园8号院6000元/月；00%; 5.金域华府东(金域华府二期)6000元/月；3.融泽嘉园6号院6100元/月；4.融泽嘉园8号院6000元/月；5.金域华府东(金域华府二期)6000元/月；贝壳找房北京小区大全,蓝天园参考均价:34667元/㎡</x:v>
-      </x:c>
-      <x:c r="K100" t="str"/>
+        <x:v>楼龄相对较新且户型方正，但缺失关键租金数据且证据较弱，建议谨慎参考。</x:v>
+      </x:c>
+      <x:c r="J100" t="str"/>
+      <x:c r="K100" t="str">
+        <x:v>房龄：小区建于2008年-2015年，部分信息标注为2012年建成，楼龄约11-18年；；户型：以大户型为主，涵盖2室1厅、3室1厅、3室2厅等，多数房源为南北通透户型，户型方正；；装修：多数在租房源为精装修；；物业：物业为北京盛世物业管理有限公司；；目前公开信息中未提及明确隔音相关口碑评价。</x:v>
+      </x:c>
       <x:c r="L100" t="str">
-        <x:v>北京昌平合租1居室房源出租, 1050 RMB/月, 近地铁13号线, 温馨小窝。；... 北京昌平的1居室合租房源，1050 RMB/月｜ 近地铁13号线，温馨小窝、不限性别, 支持查看房东上传的真实房源图片、价格 ... 房源地址：北京昌平蓝天嘉园-1号楼.。</x:v>
-      </x:c>
-      <x:c r="M100" t="str"/>
+        <x:v>通勤&amp;地铁：小区距离龙泽地铁站（13号线、在建13B号线）约732米，距离新龙泽站（13A号线、13B号线）约1.1公里，距离西二旗站（13号线、昌平线、在建13A号线）约1.6公里，临近地铁，通勤较便利；；公开信息标注小区周边商超、医院、餐饮等公共设施齐全，但未找到详细具体的配套口碑评价。</x:v>
+      </x:c>
+      <x:c r="M100" t="str">
+        <x:v>目前公开信息中未查询到该小区北京昌平项目明确的租房差评，房屋隔音、具体物业体验等细节口碑信息缺失。</x:v>
+      </x:c>
       <x:c r="N100" t="str">
-        <x:v>价格线索：公园悦府(二区)6200元/月；0.00%; 3.融泽嘉园6号院6100元/月；0.00%; 4.融泽嘉园8号院6000元/月；00%; 5.金域华府东(金域华府二期)6000元/月；3.融泽嘉园6号院6100元/月；4.融泽嘉园8号院6000元/月；5.金域华府东(金域华府二期)6000元/月；贝壳找房北京小区大全,蓝天园参考均价:34667元/㎡；生活便利线索：北京昌平合租1居室房源出租, 1050 RMB/月, 近地铁13号线, 温馨小窝。；... 北京昌平的1居室合租房源，1050 RMB/月｜ 近地铁13号线，温馨小窝、不限性别, 支持查看房东上传的真实房源图片、价格 ... 房源地址：北京昌平蓝天嘉园-1号楼.。</x:v>
+        <x:v>房屋质量/户型线索：房龄：小区建于2008年-2015年，部分信息标注为2012年建成，楼龄约11-18年；；户型：以大户型为主，涵盖2室1厅、3室1厅、3室2厅等，多数房源为南北通透户型，户型方正；；装修：多数在租房源为精装修；；物业：物业为北京盛世物业管理有限公司；；目前公开信息中未提及明确隔音相关口碑评价。；生活便利线索：通勤&amp;地铁：小区距离龙泽地铁站（13号线、在建13B号线）约732米，距离新龙泽站（13A号线、13B号线）约1.1公里，距离西二旗站（13号线、昌平线、在建13A号线）约1.6公里，临近地铁，通勤较便利；；公开信息标注小区周边商超、医院、餐饮等公共设施齐全，但未找到详细具体的配套口碑评价。；风险线索：目前公开信息中未查询到该小区北京昌平项目明确的租房差评，房屋隔音、具体物业体验等细节口碑信息缺失。</x:v>
       </x:c>
       <x:c r="O100" t="str">
-        <x:v>1. 北京昌平合租1居室房源出租, 1050 RMB/月, 近地铁13号线, 温馨小窝 https://www.wellcee.com/rent-apartment/1779252623767193
-2. 蓝天嘉园最新房价_北京昌平区 - 中国房价行情 https://m.creprice.cn/community/0169312228.html?city=bj
-3. 蓝天嘉园- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111047005715
-4. 北京昌平租房信息 - 58同城 http://mob.58.com/zf/hk-changping
-5. 昌平租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/changping</x:v>
+        <x:v>1. ["整租·蓝天嘉园 北京幸福里","https://m.xingfulizhaofang.com/zufang/bj-7443703982016430080.html"]
+2. ["蓝天嘉园怎么样?北京蓝天嘉园房价|房源|地址|户型图|周边配套详情 我爱我家","https://m.5i5j.com/bj/xq_news/331898.html"]
+3. ["整租·蓝天嘉园 北京幸福里","https://i.haoduofangs.com/zufang/bj-7534462108780494848.html"]
+4. ["哈尔滨蓝天嘉园小区，配套指南，买房攻略 哈尔滨房天下","https://hrb.esf.fang.com/loupan/1910625285/strategy.htm"]
+5. 整租·蓝天嘉园 https://m.xingfulizhaofang.com/zufang/bj-7443703982016430080.html
+6. 蓝天嘉园怎么样?北京蓝天嘉园房价|房源|地址|户型图|周边配套详情 https://m.5i5j.com/bj/xq_news/331898.html
+7. 整租·蓝天嘉园 https://i.haoduofangs.com/zufang/bj-7534462108780494848.html
+8. 2026哈尔滨蓝天嘉园小区，配套指南，买房攻略 https://hrb.esf.fang.com/loupan/1910625285/strategy.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -5184,39 +5452,42 @@
         <x:v>北京市昌平区回龙观建材城向北150米</x:v>
       </x:c>
       <x:c r="E101" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F101" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G101" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H101" t="n">
-        <x:v>7.8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="I101" t="str">
-        <x:v>回龙观成熟社区，户型选择极丰富，租金性价比高，是通勤网易的常规优选。</x:v>
+        <x:v>生活配套完善且价格亲民，有电梯，但需留意公共区域占用导致的噪音和管理风险。</x:v>
       </x:c>
       <x:c r="J101" t="str">
-        <x:v>京市昌平区回龙观精装两居室,业主急租. 5500元/月；市昌平区朱辛庄精装两居室仅需4800. 4800元/月；... 昌平-回龙观 龙跃苑(四区) 1400元/月</x:v>
+        <x:v>合租次卧/主卧价格约2000-2600元/月；，整租两居室约5000-6500元/月</x:v>
       </x:c>
       <x:c r="K101" t="str">
-        <x:v>1居室·10个户型. 56㎡~99㎡. 在售199万起 ;；2居室·100个户型. 56㎡~131㎡. 在售280万起 ;；3居室·93个户型. 89㎡~164㎡. 在售308万起 ;；4居室·15个户型. 90㎡~166㎡. 在售328万起。；58同城北京租房网，为您提供北京昌平租房信息，包括昌平房屋出租信息、昌平合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询。</x:v>
+        <x:v>合租次卧/主卧价格约2000-2600元/月，整租两居室约5000-6500元/月不等，价格根据户型、面积、装修情况浮动，部分中介租房需要收取半个月租金作为中介费。；小区为建成于2000年后的老小区，部分住宅设施偏旧；；户型以两室一厅、三室一厅为主，部分为高层带电梯住宅；；装修分为简装和精装，简装居多；；物业安保到位，但曾出现公共空间被占用治理反复的情况；</x:v>
       </x:c>
       <x:c r="L101" t="str">
-        <x:v>北京市昌平区回龙观精装两居室,业主急租. 5500元/月 · 昌平- TBD万科天地. 周边配套齐交通便利全装全配 ;；房东直租无中介费，生命科学园地铁站，昌平回龙观龙城花园北二区一居室出租4400元. 0回复 · 04-24 08:56 · 打开App查看. 房东直租无中介费，生命科学园地铁站，昌平回龙观。；... 昌平-回龙观 龙跃苑(四区) 1400元/月. 距18号线-文华路站1.0km. 昌平-回龙观 城北人家出租房源图片 城北人家整租一居室近地铁民水民电无杂费 1室1厅 38m² 昌平-回龙观 城北。</x:v>
-      </x:c>
-      <x:c r="M101" t="str"/>
+        <x:v>通勤便利，靠近地铁8号线、13号线，步行可达地铁站，可直达市区；；周边有北京华联BHG Mall等商超，菜价便宜，日常生活需求可满足；；周边餐饮资源丰富，距离回龙观区域医院较近；；小区内部有健身设施，生活便利。</x:v>
+      </x:c>
+      <x:c r="M101" t="str">
+        <x:v>部分合租户型实体墙隔音较好，老旧户型隔音一般。；存在租客私占用公共区域（自行车棚、通道、绿地）经营二手电动车，产生噪音扰民、影响小区环境和公共安全的情况，治理后仍有反复风险；</x:v>
+      </x:c>
       <x:c r="N101" t="str">
-        <x:v>价格线索：京市昌平区回龙观精装两居室,业主急租. 5500元/月；市昌平区朱辛庄精装两居室仅需4800. 4800元/月；... 昌平-回龙观 龙跃苑(四区) 1400元/月；房屋质量/户型线索：1居室·10个户型. 56㎡~99㎡. 在售199万起 ;；2居室·100个户型. 56㎡~131㎡. 在售280万起 ;；3居室·93个户型. 89㎡~164㎡. 在售308万起 ;；4居室·15个户型. 90㎡~166㎡. 在售328万起。；58同城北京租房网，为您提供北京昌平租房信息，包括昌平房屋出租信息、昌平合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询。；生活便利线索：北京市昌平区回龙观精装两居室,业主急租. 5500元/月 · 昌平- TBD万科天地. 周边配套齐交通便利全装全配 ;；房东直租无中介费，生命科学园地铁站，昌平回龙观龙城花园北二区一居室出租4400元. 0回复 · 04-24 08:56 · 打开App查看. 房东直租无中介费，生命科学园地铁站，昌平回龙观。；... 昌平-回龙观 龙跃苑(四区) 1400元/月. 距18号线-文华路站1.0km. 昌平-回龙观 城北人家出租房源图片 城北人家整租一居室近地铁民水民电无杂费 1室1厅 38m² 昌平-回龙观 城北。</x:v>
+        <x:v>价格线索：合租次卧/主卧价格约2000-2600元/月；，整租两居室约5000-6500元/月；房屋质量/户型线索：合租次卧/主卧价格约2000-2600元/月，整租两居室约5000-6500元/月不等，价格根据户型、面积、装修情况浮动，部分中介租房需要收取半个月租金作为中介费。；小区为建成于2000年后的老小区，部分住宅设施偏旧；；户型以两室一厅、三室一厅为主，部分为高层带电梯住宅；；装修分为简装和精装，简装居多；；物业安保到位，但曾出现公共空间被占用治理反复的情况；；生活便利线索：通勤便利，靠近地铁8号线、13号线，步行可达地铁站，可直达市区；；周边有北京华联BHG Mall等商超，菜价便宜，日常生活需求可满足；；周边餐饮资源丰富，距离回龙观区域医院较近；；小区内部有健身设施，生活便利。；风险线索：部分合租户型实体墙隔音较好，老旧户型隔音一般。；存在租客私占用公共区域（自行车棚、通道、绿地）经营二手电动车，产生噪音扰民、影响小区环境和公共安全的情况，治理后仍有反复风险；</x:v>
       </x:c>
       <x:c r="O101" t="str">
-        <x:v>1. 北京市昌平区租房 - 房天下 http://www.fang.com/houses/zf_253758bj
-2. 北京北京人家二手房|房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027375926
-3. 北京昌平租房信息 - 58同城 http://mob.58.com/zf/cz-changping
-4. 北京昌平租房（推荐度）小组- 豆瓣 https://m.douban.com/group/changpingzufang
-5. 昌平租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/changping</x:v>
+        <x:v>1. 回龙观北京人家怎么样 https://m.kupet.cn/read-1774198486a46651511.html
+2. 回龙观街道多措并举治乱停 齐心维护还整洁 https://www.bjchp.gov.cn/cpqzf/xxgk2671/zdlyxxgk57/csjxhgl/cxjs/2024091111231575867/index.html
+3. 【北京人家】北京人家二手房_北京人家租房_360地图 https://m.map.360.cn/site/detail/6321af8988135df3
+4. 昌平回龙观省心租房 次卧干净整洁设施齐全拎包即住 北京昌平 http://m.anjuke.com/bj/rent/4526102982958088-3/
+5. 回龙观租房别乱找了 东大街地铁口 精装主卧室 优惠出租 http://m.anjuke.com/bj/rent/4578373511488519-3/
+6. 【回龙观租房信息】 - 58同城 https://www.58.com/ppkchuzu2724/</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -5233,7 +5504,7 @@
         <x:v>北京市海淀区马连洼街道</x:v>
       </x:c>
       <x:c r="E102" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F102" t="n">
         <x:v>8</x:v>
@@ -5242,32 +5513,35 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H102" t="n">
-        <x:v>5</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I102" t="str">
-        <x:v>证据混杂豪宅与西城信息，参考性弱；虽地理位置尚可，但需实地核实真实租金与品质。</x:v>
+        <x:v>离地铁近且生活配套成熟，虽房龄偏老但居住安静，是网易员工的高性价比选择。</x:v>
       </x:c>
       <x:c r="J102" t="str">
-        <x:v>; 海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；海淀租金最高的小区 · 1.中间建筑50000元/月；租 1-3个月 4-6个月. 1300-2300元/月；|朝南北. 海淀-万柳-万城华府龙园. 60000元/月</x:v>
+        <x:v>北京海淀马连洼地区：50平左右1室简装约1300元/月；本地区60平左右2室1厅整租约6500-7200元/月；，78平左右2室2厅整租约6500元/月；，90平左右3室1厅整租约7000元/月</x:v>
       </x:c>
       <x:c r="K102" t="str">
-        <x:v>整租|4室3厅|535㎡|朝南北. 海淀-万柳-万城华府龙园. 60000元/月. 对比. 媲美万城华府万柳书院户型方正精装修平层配套双. 整租|3室3厅|562㎡|朝南北. 海淀-万柳-万柳书院.。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；但有些户型不好，比如一居客厅带斜角，有的两居户型是长条，居住品质会打折扣。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。</x:v>
+        <x:v>多为6层板楼，房龄偏老，户型以南北通透1室/2室/3室为主，采光通风较好；；装修分简装和精装，精装房源家具家电齐全可拎包入住；；小区绿化率较高，有物业管理，管理严格，居住安静，绿化环境好；</x:v>
       </x:c>
       <x:c r="L102" t="str">
-        <x:v>整租|4室3厅|535㎡|朝南北. 海淀-万柳-万城华府龙园. 60000元/月. 对比. 媲美万城华府万柳书院户型方正精装修平层配套双. 整租|3室3厅|562㎡|朝南北. 海淀-万柳-万柳书院.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。</x:v>
+        <x:v>通勤：邻近地铁16号线农大南路站，步行约300-800米，临近农大南路，出行便利，去往中关村、上地软件园方便；；周边：小区门口有公交站，周边有超市，生活配套成熟，购物餐饮便利，位于农大周边，整体生活配套完善；</x:v>
       </x:c>
       <x:c r="M102" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>本搜索结果主要为房源信息，较少真实租客差评，缺少明确负面口碑反馈，部分房源为中介出租需支付1个月租金中介费。；本搜索结果主要为房源信息，较少真实租客差评，缺少明确负面口碑反馈，部分房源为中介出租需支付1个月租金中介费</x:v>
       </x:c>
       <x:c r="N102" t="str">
-        <x:v>价格线索：; 海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；海淀租金最高的小区 · 1.中间建筑50000元/月；租 1-3个月 4-6个月. 1300-2300元/月；|朝南北. 海淀-万柳-万城华府龙园. 60000元/月；房屋质量/户型线索：整租|4室3厅|535㎡|朝南北. 海淀-万柳-万城华府龙园. 60000元/月. 对比. 媲美万城华府万柳书院户型方正精装修平层配套双. 整租|3室3厅|562㎡|朝南北. 海淀-万柳-万柳书院.。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；但有些户型不好，比如一居客厅带斜角，有的两居户型是长条，居住品质会打折扣。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。；生活便利线索：整租|4室3厅|535㎡|朝南北. 海淀-万柳-万城华府龙园. 60000元/月. 对比. 媲美万城华府万柳书院户型方正精装修平层配套双. 整租|3室3厅|562㎡|朝南北. 海淀-万柳-万柳书院.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：北京海淀马连洼地区：50平左右1室简装约1300元/月；本地区60平左右2室1厅整租约6500-7200元/月；，78平左右2室2厅整租约6500元/月；，90平左右3室1厅整租约7000元/月；房屋质量/户型线索：多为6层板楼，房龄偏老，户型以南北通透1室/2室/3室为主，采光通风较好；；装修分简装和精装，精装房源家具家电齐全可拎包入住；；小区绿化率较高，有物业管理，管理严格，居住安静，绿化环境好；；生活便利线索：通勤：邻近地铁16号线农大南路站，步行约300-800米，临近农大南路，出行便利，去往中关村、上地软件园方便；；周边：小区门口有公交站，周边有超市，生活配套成熟，购物餐饮便利，位于农大周边，整体生活配套完善；；风险线索：本搜索结果主要为房源信息，较少真实租客差评，缺少明确负面口碑反馈，部分房源为中介出租需支付1个月租金中介费。；本搜索结果主要为房源信息，较少真实租客差评，缺少明确负面口碑反馈，部分房源为中介出租需支付1个月租金中介费</x:v>
       </x:c>
       <x:c r="O102" t="str">
-        <x:v>1. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-2. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/cd-haidian
-3. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian
-4. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu
-5. 【北京b体育appv0x.cn租房信息_房屋出租】- 房天下 https://zu.fang.com/house/s31-kwB%E4%BD%93%E8%82%B2Appv0x.cn?15+target=_blank</x:v>
+        <x:v>1. 出门就是农大！南北向精装两居 配套齐全 和业主签约 可长租 http://m.anjuke.com/bj/rent/4596640707664908-3/
+2. 农大南路 农科社区 精装两居 采光好 价格可谈 业主直签！ http://m.anjuke.com/bj/rent/4603799228212230-3/
+3. 农业大学西校区 万树园低层精装三居 配置齐全 业主直签可长租 http://m.anjuke.com/bj/rent/4585789768227849-3/
+4. 农业大学西校区 农大南路地铁站 万树园双卧朝南精装两居可长租 http://m.anjuke.com/bj/rent/4603813926790144-3/
+5. 农大家属院二区1楼50平一室一厅拎包入住 http://m.anjuke.com/wlmq/rent/4554351195073542-3/
+6. 农业大学西校区 业主自主 头次出租 精装两居出门农大南路地铁 http://m.anjuke.com/ch/rent/4520357598850048-3/
+7. 整租 农大东校区 建园小区 http://m.anjuke.com/zzs/rent/4595465180556292-3/
+8. 农大家属院二区五楼一室一厅拎包入住 http://m.anjuke.com/wlmq/rent/4468009500236807-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -5284,37 +5558,44 @@
         <x:v>北京市海淀区学苑二路中国农业大学(西校区)</x:v>
       </x:c>
       <x:c r="E103" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F103" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G103" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H103" t="n">
-        <x:v>4.2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I103" t="str">
-        <x:v>证据指向温泉镇，距离网易大厦较远，通勤压力大；虽为青年公寓试点但位置不佳。</x:v>
+        <x:v>位于校内环境优美，但社会人员租赁受限风险高，且现有证据多为周边泛化信息。</x:v>
       </x:c>
       <x:c r="J103" t="str">
-        <x:v>m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月；; 海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；海淀租金最高的小区 · 1.中间建筑50000元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月</x:v>
+        <x:v>月租在1900-3299元，整租两居室约6600元/月</x:v>
       </x:c>
       <x:c r="K103" t="str">
-        <x:v>海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅 82m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月. 整租南北. 海淀。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。</x:v>
-      </x:c>
-      <x:c r="L103" t="str"/>
-      <x:c r="M103" t="str"/>
+        <x:v>周边同区域社会租赁房源多为1995年建成板楼，多为精装修，户型方正、采光较好，物业管理完善、治安好，家属院类房源居住环境安静，合租房间多为一人一间，私密性较好；</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>周边社会租房同区域合租单间月租在1900-3299元，整租两居室约6600元/月；；校内学生公寓为单元式学生宿舍，属于学校公有住房；；周边同区域社会租赁房源多为1995年建成板楼，多为精装修，户型方正、采光较好，物业管理完善、治安好，家属院类房源居住环境安静，合租房间多为一人一间，私密性较好；；位于中国农业大学西校区内，周边靠近地铁16号线农大南路站、马连洼站，步行可达，周边公交路线多，通勤便利；；周边有中国农业大学动物医院、309医院，商超餐饮齐全，紧邻校园，日常购物、餐饮出行都很便利，配套有中小学、幼儿园，生活配套完善；</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>搜索结果未找到明确针对“学生公寓4”该住宅区的公开社会租房口碑差评信息，现有租房信息多为周边家属院/小区，存在同名或地址定位不精准的可能，若为校内学生公寓仅对校内学生开放，对外社会租赁信息较少。；搜索结果未找到明确针对“学生公寓4”该住宅区的公开社会租房口碑差评信息，现有租房信息多为周边家属院/小区，存在同名或地址定位不精准的可能，若为校内学生公寓仅对校内学生开放，对外社会租赁信息较少</x:v>
+      </x:c>
       <x:c r="N103" t="str">
-        <x:v>价格线索：m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月；; 海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；海淀租金最高的小区 · 1.中间建筑50000元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；房屋质量/户型线索：海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅 82m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月. 整租南北. 海淀。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。</x:v>
+        <x:v>价格线索：月租在1900-3299元，整租两居室约6600元/月；房屋质量/户型线索：周边同区域社会租赁房源多为1995年建成板楼，多为精装修，户型方正、采光较好，物业管理完善、治安好，家属院类房源居住环境安静，合租房间多为一人一间，私密性较好；；生活便利线索：周边社会租房同区域合租单间月租在1900-3299元，整租两居室约6600元/月；；校内学生公寓为单元式学生宿舍，属于学校公有住房；；周边同区域社会租赁房源多为1995年建成板楼，多为精装修，户型方正、采光较好，物业管理完善、治安好，家属院类房源居住环境安静，合租房间多为一人一间，私密性较好；；位于中国农业大学西校区内，周边靠近地铁16号线农大南路站、马连洼站，步行可达，周边公交路线多，通勤便利；；周边有中国农业大学动物医院、309医院，商超餐饮齐全，紧邻校园，日常购物、餐饮出行都很便利，配套有中小学、幼儿园，生活配套完善；；风险线索：搜索结果未找到明确针对“学生公寓4”该住宅区的公开社会租房口碑差评信息，现有租房信息多为周边家属院/小区，存在同名或地址定位不精准的可能，若为校内学生公寓仅对校内学生开放，对外社会租赁信息较少。；搜索结果未找到明确针对“学生公寓4”该住宅区的公开社会租房口碑差评信息，现有租房信息多为周边家属院/小区，存在同名或地址定位不精准的可能，若为校内学生公寓仅对校内学生开放，对外社会租赁信息较少</x:v>
       </x:c>
       <x:c r="O103" t="str">
-        <x:v>1. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-2. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian
-3. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/cd-haidian
-4. 海淀区 - 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/amp6amp4ama0
-5. 选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网 https://www.stdaily.com/web/gdxw/2025-06/06/content_351160.html</x:v>
+        <x:v>1. ["农大南路地铁口 农大西校区 家属院 朝南大主卧 可月付","http://m.fang.com/zf/bj/3_484126960.html"]
+2. ["农大西校区家属院绿苑小区女生合租朝南单间","http://m.anjuke.com/bj/rent/4554567607446535-3/"]
+3. ["中国农业大学行政事业性收费公示","http://xxgk.cau.edu.cn/art/2024/9/14/art_21328_1037286.html"]
+4. 农大南路地铁口 农大西校区 家属院 朝南大主卧 可月付 http://m.fang.com/zf/bj/3_484126960.html
+5. 农大西校区家属院绿苑小区女生合租朝南单间 http://m.anjuke.com/bj/rent/4554567607446535-3/
+6. 信息公开网 http://xxgk.cau.edu.cn/art/2024/9/14/art_21328_1037286.html
+7. 农业大学西校区地铁口，原始大独卫马连洼农大南路万树园 http://m.anjuke.com/bj/rent/4547163902256134-3/
+8. 农业大学西校区 肖家河精装两居 和业主签合同 租金可谈 长租 http://m.anjuke.com/bj/rent/4551601143323649-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -5331,41 +5612,40 @@
         <x:v>北京市海淀区</x:v>
       </x:c>
       <x:c r="E104" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F104" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G104" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H104" t="n">
-        <x:v>6.5</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I104" t="str">
-        <x:v>租金极具竞争力，有电梯房源且商圈便利，适合预算有限且追求通勤效率的租客。</x:v>
-      </x:c>
-      <x:c r="J104" t="str">
-        <x:v>租 1-3个月 4-6个月. 1300-2300元/月</x:v>
-      </x:c>
+        <x:v>2014年次新电梯房，居住品质优于周边老旧小区，但步行至地铁站距离较远。</x:v>
+      </x:c>
+      <x:c r="J104" t="str"/>
       <x:c r="K104" t="str">
-        <x:v>户型： 1室1厅1卫 ;；装修： 精装修 ;；您好，目前440的户型，报价在10万左右，如果装修好一些的，价格在15万左右希望能帮到您;；北京楼市：海淀小户型，这些盘最值 - 知乎专栏。；想先购买1个总价大约500-600万的小户型上车，大约5-6年后换房，希望购买的房子有一定保值或成长性、方便出租，以后卖的时候不会亏太多。</x:v>
+        <x:v>小区为2014年建成回迁安置房，房龄较新，多为9-10层带电梯小板楼，楼间距宽，户型设计合理，部分楼栋经翻新后装修较好，多数为精装修，部分楼栋设施陈旧；；普遍反馈隔音效果不错，物业管理得当，响应速度快，绿化率约30%，停车方便（地上+地下车位）；</x:v>
       </x:c>
       <x:c r="L104" t="str">
-        <x:v>六郎庄新村电梯房诚心出租随时入住商圈便利 - 北京租房。；六郎庄新村电梯房诚心出租随时入住商圈便利 ;；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。</x:v>
-      </x:c>
-      <x:c r="M104" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。</x:v>
-      </x:c>
+        <x:v>临近上地软件园，距离16号线农大南路站、18号线上地软件园站步行约1.9公里，小区门口有公交站，公交线路多；；周边有世纪华联、幸福超市、超市发等商超，临近北京市上地医院等医疗机构，餐饮配套齐全；；门口有树村公园，配套有健身设施、小广场，生活休闲便利；；部分房源距离地铁站较远，通勤需留意；</x:v>
+      </x:c>
+      <x:c r="M104" t="str"/>
       <x:c r="N104" t="str">
-        <x:v>价格线索：租 1-3个月 4-6个月. 1300-2300元/月；房屋质量/户型线索：户型： 1室1厅1卫 ;；装修： 精装修 ;；您好，目前440的户型，报价在10万左右，如果装修好一些的，价格在15万左右希望能帮到您;；北京楼市：海淀小户型，这些盘最值 - 知乎专栏。；想先购买1个总价大约500-600万的小户型上车，大约5-6年后换房，希望购买的房子有一定保值或成长性、方便出租，以后卖的时候不会亏太多。；生活便利线索：六郎庄新村电梯房诚心出租随时入住商圈便利 - 北京租房。；六郎庄新村电梯房诚心出租随时入住商圈便利 ;；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。</x:v>
+        <x:v>房屋质量/户型线索：小区为2014年建成回迁安置房，房龄较新，多为9-10层带电梯小板楼，楼间距宽，户型设计合理，部分楼栋经翻新后装修较好，多数为精装修，部分楼栋设施陈旧；；普遍反馈隔音效果不错，物业管理得当，响应速度快，绿化率约30%，停车方便（地上+地下车位）；；生活便利线索：临近上地软件园，距离16号线农大南路站、18号线上地软件园站步行约1.9公里，小区门口有公交站，公交线路多；；周边有世纪华联、幸福超市、超市发等商超，临近北京市上地医院等医疗机构，餐饮配套齐全；；门口有树村公园，配套有健身设施、小广场，生活休闲便利；；部分房源距离地铁站较远，通勤需留意；</x:v>
       </x:c>
       <x:c r="O104" t="str">
-        <x:v>1. 六郎庄新村电梯房诚心出租随时入住商圈便利 - 北京租房 https://bj.zu.anjuke.com/fangyuan/3699072350528518
-2. 北京海淀上地租房信息 - 58同城 https://mob.58.com/zf/bj-shangdi
-3. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu
-4. 北京楼市：海淀小户型，这些盘最值 - 知乎专栏 https://zhuanlan.zhihu.com/p/2034646519371020218
-5. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100 ... https://m.36kr.com/p/1721780568065</x:v>
+        <x:v>1. 六郎庄租房怎么样 https://m.kupet.cn/read-1774365107a48927929.html
+2. 我爱我家相寓 马连洼六郎庄新村高楼层3居室次卧1 http://m.anjuke.com/bj/rent/4599365950745614-3/
+3. 海淀区《柳浪家园》六郎庄安置房项目介绍 https://www.sohu.com/a/554135956_120256223
+4. 六郎庄新村 软件园 百度 新浪 网易 华联 东西向急租 http://m.anjuke.com/dongyang/rent/4598911401714689-3/
+5. 六郎庄社区怎么样 https://m.kupet.cn/read-1774227657a48726265.html
+6. 柳浪家园，六郎庄，经典南向一居，全家具家电，临近树村丽景苑 http://m.anjuke.com/bj/rent/2946159859475469-3/
+7. 整租 马连洼 六郎庄新村 1室1厅 https://m.58.com/bj/zufang/3893178822549507x.shtml
+8. 肖家河 农大南路地铁 六郎庄新村 精装修一居室 http://m.anjuke.com/bj/rent/3013997037988866-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -5382,7 +5662,7 @@
         <x:v>北京市海淀区小营西路与朱房北一街交汇处西南150米</x:v>
       </x:c>
       <x:c r="E105" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F105" t="n">
         <x:v>8</x:v>
@@ -5394,29 +5674,32 @@
         <x:v>7.8</x:v>
       </x:c>
       <x:c r="I105" t="str">
-        <x:v>地理位置优越，主打一居室且配套成熟，虽房龄较老但通勤极便，综合推荐度高。</x:v>
+        <x:v>极近地铁站，通勤优势巨大，虽房龄接近40年且租金偏高，仍适合重视交通者。</x:v>
       </x:c>
       <x:c r="J105" t="str">
-        <x:v>13号线等; 五六环之间; 配套齐全. 43600元/㎡；配套齐全. 43600元/㎡；海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；，金融街附近品牌公寓带阳台房源租金平均为3500元/月</x:v>
+        <x:v>同区域同类型老旧小区合租单间约3000-5000元/月；，整租一居室约5000-7000元/月；，两居室约7000-9000元/月；车位配比1:0.4，地面停车费150元/月</x:v>
       </x:c>
       <x:c r="K105" t="str">
-        <x:v>户型齐全，主打一居. 小营西路32号院户型主要有47平-47平的的一居。；一居(1)二居(1). 1室1厅1卫47.00㎡. 户型报告. *获取完整户型报告，同时会有免费语音讲解服务.。；参考均价: 76157 元/m2 类型: 住宅物业费:2.00元总建面积: 1000m2 总户数:754 竣工时间: 2000年停车位。；况建成年代:1990-1995年房屋用途:普通住宅车位数:350 停车费用:100 燃气费用:2.61元/m3 容积率:1.6 绿化率:15%。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。</x:v>
+        <x:v>目前公开渠道暂未查询到该小区在租房源的明确月租价格参考，周边同区域同类型老旧小区合租单间约3000-5000元/月，整租一居室约5000-7000元/月，两居室约7000-9000元/月；；房龄：1990年建成，距今约36年；；户型：以多层板式户型为主，容积率1.6，建筑密度较低；；物业：由长城物业集团股份有限公司管理，物业费1.00元/平米/月；；隔音公开评价较少，小区为老旧小区，装修多为原有装修或业主自住翻新，没有统一的装修标准；</x:v>
       </x:c>
       <x:c r="L105" t="str">
-        <x:v>配套齐全. 43600元/㎡. 5月挂牌均价. 暂无. 在售房源. 暂无. 在租房源.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。</x:v>
+        <x:v>目前公开渠道暂未查询到该小区在租房源的明确月租价格参考，周边同区域同类型老旧小区合租单间约3000-5000元/月，整租一居室约5000-7000元/月，两居室约7000-9000元/月；；通勤地铁：距离最近地铁站朱房北站约238米，步行可达，临近13号线等线路；；公交：门口清河大楼站有328路、393路、432路等多条公交经停；；周边配套：地处海淀清河区域，配套齐全，周边覆盖商超、餐饮，距离海淀相关医疗配套也较近，整体生活便利程度较好，小区评分中地段交通8.4分、生活配套7.8分；</x:v>
       </x:c>
       <x:c r="M105" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>目前公开渠道暂未查询到该小区在租房源的明确月租价格参考，周边同区域同类型老旧小区合租单间约3000-5000元/月，整租一居室约5000-7000元/月，两居室约7000-9000元/月；；隔音公开评价较少，小区为老旧小区，装修多为原有装修或业主自住翻新，没有统一的装修标准；；1.公开租房相关口碑评价较少，现有信息多为小区基础信息，缺乏租户真实差评、租房风险相关内容；</x:v>
       </x:c>
       <x:c r="N105" t="str">
-        <x:v>价格线索：13号线等; 五六环之间; 配套齐全. 43600元/㎡；配套齐全. 43600元/㎡；海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；，金融街附近品牌公寓带阳台房源租金平均为3500元/月；房屋质量/户型线索：户型齐全，主打一居. 小营西路32号院户型主要有47平-47平的的一居。；一居(1)二居(1). 1室1厅1卫47.00㎡. 户型报告. *获取完整户型报告，同时会有免费语音讲解服务.。；参考均价: 76157 元/m2 类型: 住宅物业费:2.00元总建面积: 1000m2 总户数:754 竣工时间: 2000年停车位。；况建成年代:1990-1995年房屋用途:普通住宅车位数:350 停车费用:100 燃气费用:2.61元/m3 容积率:1.6 绿化率:15%。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；生活便利线索：配套齐全. 43600元/㎡. 5月挂牌均价. 暂无. 在售房源. 暂无. 在租房源.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：同区域同类型老旧小区合租单间约3000-5000元/月；，整租一居室约5000-7000元/月；，两居室约7000-9000元/月；车位配比1:0.4，地面停车费150元/月；房屋质量/户型线索：目前公开渠道暂未查询到该小区在租房源的明确月租价格参考，周边同区域同类型老旧小区合租单间约3000-5000元/月，整租一居室约5000-7000元/月，两居室约7000-9000元/月；；房龄：1990年建成，距今约36年；；户型：以多层板式户型为主，容积率1.6，建筑密度较低；；物业：由长城物业集团股份有限公司管理，物业费1.00元/平米/月；；隔音公开评价较少，小区为老旧小区，装修多为原有装修或业主自住翻新，没有统一的装修标准；；生活便利线索：目前公开渠道暂未查询到该小区在租房源的明确月租价格参考，周边同区域同类型老旧小区合租单间约3000-5000元/月，整租一居室约5000-7000元/月，两居室约7000-9000元/月；；通勤地铁：距离最近地铁站朱房北站约238米，步行可达，临近13号线等线路；；公交：门口清河大楼站有328路、393路、432路等多条公交经停；；周边配套：地处海淀清河区域，配套齐全，周边覆盖商超、餐饮，距离海淀相关医疗配套也较近，整体生活便利程度较好，小区评分中地段交通8.4分、生活配套7.8分；；风险线索：目前公开渠道暂未查询到该小区在租房源的明确月租价格参考，周边同区域同类型老旧小区合租单间约3000-5000元/月，整租一居室约5000-7000元/月，两居室约7000-9000元/月；；隔音公开评价较少，小区为老旧小区，装修多为原有装修或业主自住翻新，没有统一的装修标准；；1.公开租房相关口碑评价较少，现有信息多为小区基础信息，缺乏租户真实差评、租房风险相关内容；</x:v>
       </x:c>
       <x:c r="O105" t="str">
-        <x:v>1. 小营西路32号院 - 租房-北京安居客 https://beijing.anjuke.com/community/view/849842
-2. 小营西路32号院 - 北京二手房 https://esf.fang.com/loupan/1010616387.htm
-3. 北京小营西路32号院房价_二手房 https://bj.loupan.com/community/8756259.html
-4. 北京小营西路32号院二手房|房价 - 链家 https://bj.lianjia.com/xiaoqu/1111027381415
-5. 北京小营西路31号院二手房|房价 - 贝壳 https://m.ke.com/bj/xiaoqu/1111027381414</x:v>
+        <x:v>1. ["小营西路32号院 http://m.anjuke.com/bj/community/849842/"]
+2. ["北京小营西路32号院房价怎么样？ 小营西路32号院房源|户型图|小区车位|交通地址详情分析！ https://m.lianjia.com/news/bj/xiaoqu/1111027381415.html"]
+3. ["小营西路32号院 https://mxf.anjuke.com/bj/lishi100406895/"]
+4. 小营西路32号院 https://mxf.anjuke.com/bj/lishi100406895/
+5. 北京小营西路32号院房价怎么样？ 小营西路32号院房源|户型图|小区车位|交通地址详情分析！ https://m.lianjia.com/news/bj/xiaoqu/1111027381415.html
+6. 小营西路32号院 http://m.anjuke.com/bj/community/849842/
+7. 小营路 育慧西里 1室 朝南 带阳台 配套齐全 精装修 http://m.anjuke.com/bj/rent/4596530777054208-3/
+8. 北洼路32号院 电梯房 精装修 3室2厅2卫 http://m.anjuke.com/bj/rent/4408498629225473-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -5433,41 +5716,42 @@
         <x:v>北京市海淀区安宁庄东路7号</x:v>
       </x:c>
       <x:c r="E106" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F106" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G106" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H106" t="n">
-        <x:v>8.2</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I106" t="str">
-        <x:v>距离网易极近，生活配套成熟，户型方正且采光好，虽有老旧小区风险但居家氛围浓厚。</x:v>
+        <x:v>距清河站近，通勤便利，租金适中且配套成熟，但房龄较老，部分楼栋无电梯。</x:v>
       </x:c>
       <x:c r="J106" t="str">
-        <x:v>链家网北京小区大全,安宁里参考均价:54334元/㎡；. 小区名称月租金涨跌幅; 1.中间建筑50000元/月；0.00%; 2.长远天地32564元/月；0.00%; 3.紫竹花园32000元/月；1.中间建筑50000元/月；2.长远天地32564元/月；3.紫竹花园32000元/月</x:v>
+        <x:v>1室1厅月租约4300-4800元/月；，2室1厅月租约4085-6300元/月；，2室2厅月租约6000-6600元/月；，3室1厅月租约7300元/月</x:v>
       </x:c>
       <x:c r="K106" t="str">
-        <x:v>服务费: 租金10%（一次性收）. 户型： 3室1厅1卫;；装修： 精装修;；户型齐全，主打双阳台二居. 安宁里南区户型主要有48平-116平的双阳台的二居、51平-58平的双阳台的一居、75平-109平的户型方正,客厅朝南,双阳台,主卧朝南的三居。；小区温馨和睦，物业时不时会组织一些晚会活动，邻里关系都很好，小朋友玩伴也多，是一个适合居家的小区。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。</x:v>
+        <x:v>1室1厅月租约4300-4800元/月，2室1厅月租约4085-6300元/月，2室2厅月租约6000-6600元/月，3室1厅月租约7300元/月，具体因面积、装修、楼层浮动。；房龄：1990年建成；；户型：以1室、2室为主，部分南北通透户型；；装修：多数在租房源为精装修；；物业：有24小时保安，物业管理评价较好，小区绿化好安静；</x:v>
       </x:c>
       <x:c r="L106" t="str">
-        <x:v>周边有商场超市，还有百货购物中心，买菜购物非常方便。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。</x:v>
+        <x:v>通勤：距昌平线/13号线清河站约1.5公里，步行约15分钟，周边有多条公交线路，临近西二旗、小米科技园，适合上班族；；商超：周边有便民生鲜超市、幸福乐购、沁春汇购物中心，购物便利；；餐饮、银行等配套齐全；；附近有医院配套。</x:v>
       </x:c>
       <x:c r="M106" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>隔音未找到明确差评信息，部分楼栋无电梯。；未找到明确差评，部分楼栋总高6层无高层电梯；</x:v>
       </x:c>
       <x:c r="N106" t="str">
-        <x:v>价格线索：链家网北京小区大全,安宁里参考均价:54334元/㎡；. 小区名称月租金涨跌幅; 1.中间建筑50000元/月；0.00%; 2.长远天地32564元/月；0.00%; 3.紫竹花园32000元/月；1.中间建筑50000元/月；2.长远天地32564元/月；3.紫竹花园32000元/月；房屋质量/户型线索：服务费: 租金10%（一次性收）. 户型： 3室1厅1卫;；装修： 精装修;；户型齐全，主打双阳台二居. 安宁里南区户型主要有48平-116平的双阳台的二居、51平-58平的双阳台的一居、75平-109平的户型方正,客厅朝南,双阳台,主卧朝南的三居。；小区温馨和睦，物业时不时会组织一些晚会活动，邻里关系都很好，小朋友玩伴也多，是一个适合居家的小区。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；生活便利线索：周边有商场超市，还有百货购物中心，买菜购物非常方便。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：1室1厅月租约4300-4800元/月；，2室1厅月租约4085-6300元/月；，2室2厅月租约6000-6600元/月；，3室1厅月租约7300元/月；房屋质量/户型线索：1室1厅月租约4300-4800元/月，2室1厅月租约4085-6300元/月，2室2厅月租约6000-6600元/月，3室1厅月租约7300元/月，具体因面积、装修、楼层浮动。；房龄：1990年建成；；户型：以1室、2室为主，部分南北通透户型；；装修：多数在租房源为精装修；；物业：有24小时保安，物业管理评价较好，小区绿化好安静；；生活便利线索：通勤：距昌平线/13号线清河站约1.5公里，步行约15分钟，周边有多条公交线路，临近西二旗、小米科技园，适合上班族；；商超：周边有便民生鲜超市、幸福乐购、沁春汇购物中心，购物便利；；餐饮、银行等配套齐全；；附近有医院配套。；风险线索：隔音未找到明确差评信息，部分楼栋无电梯。；未找到明确差评，部分楼栋总高6层无高层电梯；</x:v>
       </x:c>
       <x:c r="O106" t="str">
-        <x:v>1. 清河安宁庄安宁里小区近清河站小米元中心 - 北京租房 https://bj.zu.anjuke.com/fangyuan/4514712808070148
-2. 安宁里- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027375645
-3. 安宁里南区 - 北京二手房 https://esf.fang.com/loupan/1010217663.htm
-4. 安宁佳园- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027375644
-5. 北京安宁里南区二手房|房价 - 贝壳 https://m.ke.com/bj/xiaoqu/1111027375647</x:v>
+        <x:v>1. ["能月付 安宁里小区 2居室出租 还挨着西二旗 小米科技园","http://m.anjuke.com/bj/rent/4497429914461193-3/"]
+2. ["【多图】安宁里(北区)，安宁庄租房，清河站附近 安宁里小区两居室 随时看房 幸福超市 小米快手，海淀租房","https://bj.zu.anjuke.com/fangyuan/4351820060892165"]
+3. ["安宁庄 安宁里小区南北通透两居室 近清河站小米快手","http://m.anjuke.com/bj/rent/4578305168548865-3/"]
+4. 能月付 安宁里小区 2居室出租 还挨着西二旗 小米科技园 http://m.anjuke.com/bj/rent/4497429914461193-3/
+5. 【多图】安宁里(北区)，安宁庄租房，清河站附近 安宁里小区两居室 随时看房 幸福超市 小米快手，海淀租房 https://bj.zu.anjuke.com/fangyuan/4351820060892165
+6. 安宁庄 安宁里小区南北通透两居室 近清河站小米快手 http://m.anjuke.com/bj/rent/4578305168548865-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -5484,41 +5768,43 @@
         <x:v>北京市海淀区小牛房二街26号院</x:v>
       </x:c>
       <x:c r="E107" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F107" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G107" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H107" t="n">
-        <x:v>7.8</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="I107" t="str">
-        <x:v>位于西北旺，房龄新且租金相对亲民，适合单身或小家庭，但需留意共有产权房租赁限制。</x:v>
+        <x:v>户型以三居为主，租金尚可，但需公交换乘地铁，生活配套及房屋细节信息较少。</x:v>
       </x:c>
       <x:c r="J107" t="str">
-        <x:v>房源共计1518套，销售均价含全装修费用37000元/平方米；m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月；租金：仅提供一房、面积26平方米，租金价格2300元/月</x:v>
+        <x:v>号院瑞泽家园，2025年8-10月租金约101.71元/月；3年有89㎡3室1厅精装修房源整租价格为7200元/月</x:v>
       </x:c>
       <x:c r="K107" t="str">
-        <x:v>瑞泽家园- 户型图_房价-北京手机搜狐焦点。；北京瑞泽家园楼盘电话4006162877-411642，楼盘地址为北京市海淀区西北旺镇瑞泽家园(建设中)，更多房价、地址、户型图、实景图、交通和周边配套等瑞泽家园楼盘详情信息，请关注。；瑞泽家园共有产权房项目将于2020年11月13日开始申购，此次申购的共有房项目房源共计1518套，销售均价含全装修费用37000元/平方米。；海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅 82m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月. 整租南北. 海淀。；户型及租金：提供一房、二房、三房，面积在26-76平方米，租金价格2740 ... 户型及租金：仅提供一房、面积26平方米，租金价格2300元/月. 具体位置。</x:v>
+        <x:v>2023年有89㎡3室1厅精装修房源整租价格为7200元/月；；该小区开发商为北京建海汇合房地产开发有限公司，容积率2.1，为商品住宅，公开信息中房龄、物业收费、具体隔音、户型详细评价信息缺失，无明确差评提及房屋质量问题；；天津同名瑞泽家园有反馈隔音较差，住户增多后夜间嘈杂，该信息不匹配目标小区。</x:v>
       </x:c>
       <x:c r="L107" t="str">
-        <x:v>北京瑞泽家园楼盘电话4006162877-411642，楼盘地址为北京市海淀区西北旺镇瑞泽家园(建设中)，更多房价、地址、户型图、实景图、交通和周边配套等瑞泽家园楼盘详情信息，请关注。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；我爱我家相寓上地宣海家园低楼层4居室次卧1. 3000 · 4室1厅·25.0㎡. 邻地铁精装修 ;；财大家属院两居室紧邻上地地铁站看房随时. 6100 · 2室1厅·62.22㎡. 邻地铁。</x:v>
+        <x:v>公共交通方面，距离小牛坊南站约260米，有543路、544路、运通205路公交；；距离小牛坊站约439米，有384路等线路，距离航天城北站约406米，标注提及地铁16号线已开通，通勤可依托公交换乘地铁；；周边600米范围内有海淀区希望小学、丰联小学，基础生活配套可满足，公开信息中商超、医院详细信息缺失。</x:v>
       </x:c>
       <x:c r="M107" t="str">
-        <x:v>)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。</x:v>
+        <x:v>该小区开发商为北京建海汇合房地产开发有限公司，容积率2.1，为商品住宅，公开信息中房龄、物业收费、具体隔音、户型详细评价信息缺失，无明确差评提及房屋质量问题；</x:v>
       </x:c>
       <x:c r="N107" t="str">
-        <x:v>价格线索：房源共计1518套，销售均价含全装修费用37000元/平方米；m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月；租金：仅提供一房、面积26平方米，租金价格2300元/月；房屋质量/户型线索：瑞泽家园- 户型图_房价-北京手机搜狐焦点。；北京瑞泽家园楼盘电话4006162877-411642，楼盘地址为北京市海淀区西北旺镇瑞泽家园(建设中)，更多房价、地址、户型图、实景图、交通和周边配套等瑞泽家园楼盘详情信息，请关注。；瑞泽家园共有产权房项目将于2020年11月13日开始申购，此次申购的共有房项目房源共计1518套，销售均价含全装修费用37000元/平方米。；海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅 82m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月. 整租南北. 海淀。；户型及租金：提供一房、二房、三房，面积在26-76平方米，租金价格2740 ... 户型及租金：仅提供一房、面积26平方米，租金价格2300元/月. 具体位置。；生活便利线索：北京瑞泽家园楼盘电话4006162877-411642，楼盘地址为北京市海淀区西北旺镇瑞泽家园(建设中)，更多房价、地址、户型图、实景图、交通和周边配套等瑞泽家园楼盘详情信息，请关注。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；我爱我家相寓上地宣海家园低楼层4居室次卧1. 3000 · 4室1厅·25.0㎡. 邻地铁精装修 ;；财大家属院两居室紧邻上地地铁站看房随时. 6100 · 2室1厅·62.22㎡. 邻地铁。；风险线索：)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。</x:v>
+        <x:v>价格线索：号院瑞泽家园，2025年8-10月租金约101.71元/月；3年有89㎡3室1厅精装修房源整租价格为7200元/月；房屋质量/户型线索：2023年有89㎡3室1厅精装修房源整租价格为7200元/月；；该小区开发商为北京建海汇合房地产开发有限公司，容积率2.1，为商品住宅，公开信息中房龄、物业收费、具体隔音、户型详细评价信息缺失，无明确差评提及房屋质量问题；；天津同名瑞泽家园有反馈隔音较差，住户增多后夜间嘈杂，该信息不匹配目标小区。；生活便利线索：公共交通方面，距离小牛坊南站约260米，有543路、544路、运通205路公交；；距离小牛坊站约439米，有384路等线路，距离航天城北站约406米，标注提及地铁16号线已开通，通勤可依托公交换乘地铁；；周边600米范围内有海淀区希望小学、丰联小学，基础生活配套可满足，公开信息中商超、医院详细信息缺失。；风险线索：该小区开发商为北京建海汇合房地产开发有限公司，容积率2.1，为商品住宅，公开信息中房龄、物业收费、具体隔音、户型详细评价信息缺失，无明确差评提及房屋质量问题；</x:v>
       </x:c>
       <x:c r="O107" t="str">
-        <x:v>1. 瑞泽家园- 户型图_房价-北京手机搜狐焦点 https://m.focus.cn/xf/bj-110129245
-2. 2020年北京海淀区瑞泽家园共有房申购指南 http://bj.bendibao.com/zffw/20201113/283936.shtm
-3. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian
-4. URI盘点| 北京已入市的保租房项目 - 知乎专栏 https://zhuanlan.zhihu.com/p/689251799
-5. 【北京租房网_北京租房信息|房屋出租】- 房天下 https://zu.fang.com/default.htm</x:v>
+        <x:v>1. ["瑞泽家园 小区综合评测: 6.5 分","https://www.fangim.cn/cibj/ha/pa0215051hd816.html"]
+2. ["出租小牛坊瑞泽家园 3室1厅1卫 南北通透 精装修 89平","http://m.anjuke.com/bj/rent/3240460025291778-3/"]
+3. 瑞泽家园 小区综合评测: 6.5 分 https://www.fangim.cn/cibj/ha/pa0215051hd816.html
+4. 瑞泽家园二手房房价走势,天津瑞泽家园二手房出售、租房价格-天津安居客 https://mobile.anjuke.com/esf/gy-cm802299/
+5. 整租 | 瑞泽家园 3室2厅2卫 http://m.anjuke.com/tj/rent/4582833444559876-2/
+6. 瑞泽家园三居出租1500包物业 https://tj.zu.anjuke.com/fangyuan/4295150443813890
+7. 出租小牛坊瑞泽家园 3室1厅1卫 南北通透 精装修 89平 http://m.anjuke.com/bj/rent/3240460025291778-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -5535,7 +5821,7 @@
         <x:v>北京市海淀区安宁庄东路与安宁庄前街交叉路口东北约80米</x:v>
       </x:c>
       <x:c r="E108" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F108" t="n">
         <x:v>8</x:v>
@@ -5544,32 +5830,35 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H108" t="n">
-        <x:v>7.2</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="I108" t="str">
-        <x:v>交通便利且周边餐饮丰富，租金适中，但房龄偏老且部分户型设计存在缺陷。</x:v>
+        <x:v>地理位置优越且配套完善，但缺乏该小区具体信息，多为区域泛化数据，需实地核实。</x:v>
       </x:c>
       <x:c r="J108" t="str">
-        <x:v>海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月</x:v>
+        <x:v>淀清河小营附近：合租单间价格约2500-3000元/月；，整租一居室约3600-8000元/月；，整租两居室约3800-7600元/月；，整租三居室约9100元/月</x:v>
       </x:c>
       <x:c r="K108" t="str">
-        <x:v>建成年代:1999年房屋用途:普通住宅免费停车。；物业费便宜。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；但有些户型不好，比如一居客厅带斜角，有的两居户型是长条，居住品质会打折扣。</x:v>
+        <x:v>当前搜索结果中未找到目标小区准确租房价格，周边同区域海淀清河小营附近：合租单间价格约2500-3000元/月，整租一居室约3600-8000元/月，整租两居室约3800-7600元/月，整租三居室约9100元/月，价格因户型、面积、装修差异较大；；目标小区直接信息不足，同区域类似老小区：多数房龄偏老，部分房源为精装修，户型以一居、两居、三居为主，部分合规隔间为实墙隔音效果尚可，部分老小区隔音一般；；部分房源物业为统一管理，24小时保安，安全有保障，但老小区普遍物业维护水平一般；</x:v>
       </x:c>
       <x:c r="L108" t="str">
-        <x:v>小区周边全是吃饭的,方便。；交通方便,适合上班。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。</x:v>
+        <x:v>当前搜索结果中未找到目标小区准确租房价格，周边同区域海淀清河小营附近：合租单间价格约2500-3000元/月，整租一居室约3600-8000元/月，整租两居室约3800-7600元/月，整租三居室约9100元/月，价格因户型、面积、装修差异较大；；目标小区位于安宁庄东路与安宁庄前街交叉口，属于海淀清河区域：周边临近昌平线清河小营桥站、8号线育新站，通勤到西二旗、上地、清河都较近，公交线路多；；周边有清河医院、物美超市、幸福超市、蓝岛金隅商场，各类餐饮门店众多，生活配套完善，生活便利度较高；；搜索结果中存在较多同名误命中（如西小营新村、亚运村世纪村西区、强佑清河新城西区等均非目标小区），未找到目标小区「小营住宅区-西区」专属租房口碑与差评信息，信息多为周边区域泛化信息，存在信息不准确风险。；搜索结果中存在较多同名误命中（如西小营新村、亚运村世纪村西区、强佑清河新城西区等均非目标小区），未找到目标小区「小营住宅区-西区」专属租房口碑与差评信息，信息多为周边区域泛化信息，存在信息不准确风险</x:v>
       </x:c>
       <x:c r="M108" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>搜索结果中存在较多同名误命中（如西小营新村、亚运村世纪村西区、强佑清河新城西区等均非目标小区），未找到目标小区「小营住宅区-西区」专属租房口碑与差评信息，信息多为周边区域泛化信息，存在信息不准确风险。；搜索结果中存在较多同名误命中（如西小营新村、亚运村世纪村西区、强佑清河新城西区等均非目标小区），未找到目标小区「小营住宅区-西区」专属租房口碑与差评信息，信息多为周边区域泛化信息，存在信息不准确风险</x:v>
       </x:c>
       <x:c r="N108" t="str">
-        <x:v>价格线索：海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；房屋质量/户型线索：建成年代:1999年房屋用途:普通住宅免费停车。；物业费便宜。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；但有些户型不好，比如一居客厅带斜角，有的两居户型是长条，居住品质会打折扣。；生活便利线索：小区周边全是吃饭的,方便。；交通方便,适合上班。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：淀清河小营附近：合租单间价格约2500-3000元/月；，整租一居室约3600-8000元/月；，整租两居室约3800-7600元/月；，整租三居室约9100元/月；房屋质量/户型线索：当前搜索结果中未找到目标小区准确租房价格，周边同区域海淀清河小营附近：合租单间价格约2500-3000元/月，整租一居室约3600-8000元/月，整租两居室约3800-7600元/月，整租三居室约9100元/月，价格因户型、面积、装修差异较大；；目标小区直接信息不足，同区域类似老小区：多数房龄偏老，部分房源为精装修，户型以一居、两居、三居为主，部分合规隔间为实墙隔音效果尚可，部分老小区隔音一般；；部分房源物业为统一管理，24小时保安，安全有保障，但老小区普遍物业维护水平一般；；生活便利线索：当前搜索结果中未找到目标小区准确租房价格，周边同区域海淀清河小营附近：合租单间价格约2500-3000元/月，整租一居室约3600-8000元/月，整租两居室约3800-7600元/月，整租三居室约9100元/月，价格因户型、面积、装修差异较大；；目标小区位于安宁庄东路与安宁庄前街交叉口，属于海淀清河区域：周边临近昌平线清河小营桥站、8号线育新站，通勤到西二旗、上地、清河都较近，公交线路多；；周边有清河医院、物美超市、幸福超市、蓝岛金隅商场，各类餐饮门店众多，生活配套完善，生活便利度较高；；搜索结果中存在较多同名误命中（如西小营新村、亚运村世纪村西区、强佑清河新城西区等均非目标小区），未找到目标小区「小营住宅区-西区」专属租房口碑与差评信息，信息多为周边区域泛化信息，存在信息不准确风险。；搜索结果中存在较多同名误命中（如西小营新村、亚运村世纪村西区、强佑清河新城西区等均非目标小区），未找到目标小区「小营住宅区-西区」专属租房口碑与差评信息，信息多为周边区域泛化信息，存在信息不准确风险；风险线索：搜索结果中存在较多同名误命中（如西小营新村、亚运村世纪村西区、强佑清河新城西区等均非目标小区），未找到目标小区「小营住宅区-西区」专属租房口碑与差评信息，信息多为周边区域泛化信息，存在信息不准确风险。；搜索结果中存在较多同名误命中（如西小营新村、亚运村世纪村西区、强佑清河新城西区等均非目标小区），未找到目标小区「小营住宅区-西区」专属租房口碑与差评信息，信息多为周边区域泛化信息，存在信息不准确风险</x:v>
       </x:c>
       <x:c r="O108" t="str">
-        <x:v>1. 北京小营西路1号二手房|房价 - 链家 https://bj.lianjia.com/xiaoqu/1111027381409
-2. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-3. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100 ... https://m.36kr.com/p/1721780568065
-4. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian
-5. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/cd-haidian</x:v>
+        <x:v>1. 西小营新村租房 http://m.anjuke.com/bj/community/849432/rent/lx1-zj106/
+2. 昌平线清河小营桥地铁站旁 正规两居室带电梯 家具家电齐全 http://m.anjuke.com/ch/rent/4596541024693254-3/
+3. 【小营西路25号院租房子 http://m.fang.com/zf/bj_xm1010573783/m2/
+4. 我爱我家相寓 亚运村小营世纪村西区中楼层3居室 http://m.anjuke.com/bj/rent/4607115890236421-3/
+5. 西小营两居室 随时起租 齐全出租 必租房源 https://bj.zu.anjuke.com/fangyuan/4213219581991941
+6. 整租！海淀清河小营桥地铁口，整租，实墙隔音，无中介，押一付一 http://m.anjuke.com/bj/rent/4340294345370633-3/
+7. 整租 海淀 清河小营桥 西小口 西三旗 近地铁 物业直签月付 http://m.anjuke.com/bj/rent/4009516830170115-3/?ad_type=gz&amp;pagesource=12
+8. 小营 主卧阳台 采光好 有电梯 可月付 租期随意 首月免租 http://m.anjuke.com/bj/rent/4594333005835271-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -5586,41 +5875,42 @@
         <x:v>农大南路紫城创业园C2区15号楼1门102号</x:v>
       </x:c>
       <x:c r="E109" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F109" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G109" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H109" t="n">
-        <x:v>7.5</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I109" t="str">
-        <x:v>地理位置极佳，紧邻地铁和网易，生活极其便利，但受学区影响单价极高，多为合租。</x:v>
+        <x:v>临近地铁16号线，周边配套成熟，但缺乏本小区直接租金与质量信息，参考性有限。</x:v>
       </x:c>
       <x:c r="J109" t="str">
-        <x:v>链家网北京小区大全,温馨家园参考均价:143187元/㎡；15m² 海淀-上地 万德嘉园(二区) 1999元/月</x:v>
+        <x:v>城嘉园（相邻小区）整租价格：90平两居约7600元/月；，137平三居约13000元/月；，150平三居约13500元/月；外地同名温馨家园房源价格为500-1300元/月</x:v>
       </x:c>
       <x:c r="K109" t="str">
-        <x:v>我爱我家相寓上地宣海家园低楼层4居室次卧1. 3000 · 4室1厅·25.0㎡. 邻地铁精装修 ;；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；Wellcee唯心所寓北京租房网，提供真实可靠无中介的北京租房信息、优质房源与透明的租房价格，涵盖北京整租、合租、品质公寓等多元房源，以及北京房东直租、个人转租、室友。</x:v>
+        <x:v>无目标房源直接质量信息，同区域紫城嘉园小区信息：多为南北朝向户型，以大户型三居两居为主；；多为精装修，部分房源设施较新；；小区为封闭式管理，物业规范，24小时保安，绿化率较高环境较好；；无明确房龄、隔音相关公开口碑信息。</x:v>
       </x:c>
       <x:c r="L109" t="str">
-        <x:v>我爱我家相寓上地宣海家园低楼层4居室次卧1. 3000 · 4室1厅·25.0㎡. 邻地铁精装修 ;；财大家属院两居室紧邻上地地铁站看房随时. 6100 · 2室1厅·62.22㎡. 邻地铁。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；当前位置：首页-&gt;信息公开大厅-&gt;区房管局-&gt;重点领域. | 索引号 | 11F/2018-210140 | 公开责任部门 |. | 生成日期 | 2015年03月04日 16:57 | 公开日期 | 2015年03月04日 16:57 |. | 此次配租的公共租赁住房项目共4个，均由北京市保障性住房建设投资中心持有，房源共计2519套，其中大套型2160套，中套型221套，小套型138套，房源具体情况如下： 1．文龙家园一里项目，位于海淀区清河小营西小口（地铁8号线西小口站）。</x:v>
-      </x:c>
-      <x:c r="M109" t="str">
-        <x:v>)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。</x:v>
-      </x:c>
+        <x:v>目标位置临近农大南路，靠近地铁16号线农大南路站，步行约1.7公里；；周边配套成熟，有农贸市场、商超，餐饮等生活设施齐全，区域内有社区医院，通勤和日常购物比较便利。；未找到目标地址该住宅区的直接租房口碑，现有信息均来自周边同区域小区或同名其他小区，信息存在泛化误差，需实地核实房源信息。</x:v>
+      </x:c>
+      <x:c r="M109" t="str"/>
       <x:c r="N109" t="str">
-        <x:v>价格线索：链家网北京小区大全,温馨家园参考均价:143187元/㎡；15m² 海淀-上地 万德嘉园(二区) 1999元/月；房屋质量/户型线索：我爱我家相寓上地宣海家园低楼层4居室次卧1. 3000 · 4室1厅·25.0㎡. 邻地铁精装修 ;；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；Wellcee唯心所寓北京租房网，提供真实可靠无中介的北京租房信息、优质房源与透明的租房价格，涵盖北京整租、合租、品质公寓等多元房源，以及北京房东直租、个人转租、室友。；生活便利线索：我爱我家相寓上地宣海家园低楼层4居室次卧1. 3000 · 4室1厅·25.0㎡. 邻地铁精装修 ;；财大家属院两居室紧邻上地地铁站看房随时. 6100 · 2室1厅·62.22㎡. 邻地铁。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；当前位置：首页-&gt;信息公开大厅-&gt;区房管局-&gt;重点领域. | 索引号 | 11F/2018-210140 | 公开责任部门 |. | 生成日期 | 2015年03月04日 16:57 | 公开日期 | 2015年03月04日 16:57 |. | 此次配租的公共租赁住房项目共4个，均由北京市保障性住房建设投资中心持有，房源共计2519套，其中大套型2160套，中套型221套，小套型138套，房源具体情况如下： 1．文龙家园一里项目，位于海淀区清河小营西小口（地铁8号线西小口站）。；风险线索：)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。</x:v>
+        <x:v>价格线索：城嘉园（相邻小区）整租价格：90平两居约7600元/月；，137平三居约13000元/月；，150平三居约13500元/月；外地同名温馨家园房源价格为500-1300元/月；房屋质量/户型线索：无目标房源直接质量信息，同区域紫城嘉园小区信息：多为南北朝向户型，以大户型三居两居为主；；多为精装修，部分房源设施较新；；小区为封闭式管理，物业规范，24小时保安，绿化率较高环境较好；；无明确房龄、隔音相关公开口碑信息。；生活便利线索：目标位置临近农大南路，靠近地铁16号线农大南路站，步行约1.7公里；；周边配套成熟，有农贸市场、商超，餐饮等生活设施齐全，区域内有社区医院，通勤和日常购物比较便利。；未找到目标地址该住宅区的直接租房口碑，现有信息均来自周边同区域小区或同名其他小区，信息存在泛化误差，需实地核实房源信息。</x:v>
       </x:c>
       <x:c r="O109" t="str">
-        <x:v>1. 北京海淀上地租房信息 - 58同城 https://mob.58.com/zf/bj-shangdi
-2. 温馨家园- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027380506
-3. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian
-4. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-5. 【海淀房屋出租租赁_海淀租房网】-北京麦田房产 https://bj.maitian.cn/zfall/R6/P13/OR31</x:v>
+        <x:v>1. ["上地 农大南路 紫城嘉园150平三居两卫 现房 随时住","https://m.58.com/bj/zufang/84146323915613x.shtml"]
+2. ["农大南路 紫城嘉园精装两居 和业主签合同 干净整洁 可长租","http://m.anjuke.com/bj/rent/4314036243110924-3/"]
+3. ["农大南路 上地 精装 随时起租 价格可谈3室2厅 紫成嘉园","http://m.anjuke.com/bj/rent/3309838980094983-3/"]
+4. 上地 农大南路 紫城嘉园150平三居两卫 现房 随时住 https://m.58.com/bj/zufang/84146323915613x.shtml
+5. 可月租 温馨家园11楼60平二室拎包入住一个月900 http://m.anjuke.com/liao/rent/4352217328294927-3/?ad_type=j&amp;pagesource=12
+6. 农大南路 上地 精装 随时起租 价格可谈3室2厅 紫成嘉园 http://m.anjuke.com/bj/rent/3309838980094983-3/
+7. 温馨家园一室现房月租季租年租都行 http://m.anjuke.com/liao/rent/3948076793815049-3/
+8. 农大南路 紫城嘉园精装两居 和业主签合同 干净整洁 可长租 http://m.anjuke.com/bj/rent/4314036243110924-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -5637,39 +5927,39 @@
         <x:v>北京市海淀区中关村软件园二号路2号楼中关村软件园孵</x:v>
       </x:c>
       <x:c r="E110" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F110" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G110" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H110" t="n">
-        <x:v>8.2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I110" t="str">
-        <x:v>位于软件园核心区，步行至网易极近，配套极丰富，但需甄别办公与住宅房源。</x:v>
-      </x:c>
-      <x:c r="J110" t="str">
-        <x:v>25元/㎡·天25元/㎡·天以上. 不限10000元/㎡；以下10000-20000元/㎡；20000-30000元/㎡；30000-50000元/㎡；50000元/㎡；壳找房北京小区大全,软件园小区参考均价:90995元/㎡</x:v>
-      </x:c>
+        <x:v>该地主要为办公区，缺乏住宅生活配套信息，不建议作为租房首选。</x:v>
+      </x:c>
+      <x:c r="J110" t="str"/>
       <x:c r="K110" t="str">
-        <x:v>安居客北京海淀上地万德嘉园(二区)租房网，提供押付押一付一，房型1厅1室1卫，楼层4层，朝向东，装修精装修，类型普通住宅租房信息，首月减免！</x:v>
+        <x:v>办公区户型方正，多为精装修，物业费约8元/㎡·月，配套安全监控、空气净化系统，暂无住宅区隔音、房龄等相关质量信息；</x:v>
       </x:c>
       <x:c r="L110" t="str">
-        <x:v>. 园区集聚了在能源、交通、通讯、金融、国防等国民经济重要领域的行业应用领军企业，体现了工业化与信息化的深度融合，代表了战略性新兴技术创新国家队水平。；. 中关村软件园孵化空间为大学生创业企业或团队搭建了免费的大学生众创空间，配备办公桌椅、宽带网络、会议室等办公设施，入园企业或团队还可以免费享受园区配套的报告厅、健身房、篮球场等公共配套设施。；地铁上盖（13号线西二旗站），入驻率高，产业氛围成熟，餐饮配套极丰富，企房房合作深，能争取到独家优惠价和长免租期。</x:v>
+        <x:v>同区域办公租金参考为2~5.2元/㎡/天，周边普通住宅区两居室整租月租约5600~5900元；；办公区户型方正，多为精装修，物业费约8元/㎡·月，配套安全监控、空气净化系统，暂无住宅区隔音、房龄等相关质量信息；；交通：临近13号线清河站、18号线上地软件园站，园区有通勤车接驳；；配套：楼内有员工餐厅，周边有星巴克、海底捞、肯德基、便利店等餐饮商超，产业配套完善，暂未查询到住宅区对应的医院等生活配套信息；</x:v>
       </x:c>
       <x:c r="M110" t="str"/>
       <x:c r="N110" t="str">
-        <x:v>价格线索：25元/㎡·天25元/㎡·天以上. 不限10000元/㎡；以下10000-20000元/㎡；20000-30000元/㎡；30000-50000元/㎡；50000元/㎡；壳找房北京小区大全,软件园小区参考均价:90995元/㎡；房屋质量/户型线索：安居客北京海淀上地万德嘉园(二区)租房网，提供押付押一付一，房型1厅1室1卫，楼层4层，朝向东，装修精装修，类型普通住宅租房信息，首月减免！；生活便利线索：. 园区集聚了在能源、交通、通讯、金融、国防等国民经济重要领域的行业应用领军企业，体现了工业化与信息化的深度融合，代表了战略性新兴技术创新国家队水平。；. 中关村软件园孵化空间为大学生创业企业或团队搭建了免费的大学生众创空间，配备办公桌椅、宽带网络、会议室等办公设施，入园企业或团队还可以免费享受园区配套的报告厅、健身房、篮球场等公共配套设施。；地铁上盖（13号线西二旗站），入驻率高，产业氛围成熟，餐饮配套极丰富，企房房合作深，能争取到独家优惠价和长免租期。</x:v>
+        <x:v>房屋质量/户型线索：办公区户型方正，多为精装修，物业费约8元/㎡·月，配套安全监控、空气净化系统，暂无住宅区隔音、房龄等相关质量信息；；生活便利线索：同区域办公租金参考为2~5.2元/㎡/天，周边普通住宅区两居室整租月租约5600~5900元；；办公区户型方正，多为精装修，物业费约8元/㎡·月，配套安全监控、空气净化系统，暂无住宅区隔音、房龄等相关质量信息；；交通：临近13号线清河站、18号线上地软件园站，园区有通勤车接驳；；配套：楼内有员工餐厅，周边有星巴克、海底捞、肯德基、便利店等餐饮商超，产业配套完善，暂未查询到住宅区对应的医院等生活配套信息；</x:v>
       </x:c>
       <x:c r="O110" t="str">
-        <x:v>1. 【中关村软件园,写字楼•办公楼出租•出售•租赁价格信息】-北京海淀上地•写字楼•乙级-北京写字楼网-房天下 https://esf.fang.com/loupan/1010740397.htm
-2. 北京软件园小区二手房|房价|租房【北京贝壳找房】 https://m.ke.com/bj/xiaoqu/1111027379027
-3. 首月减免！中关村软件园百度网易腾讯附近万德嘉园大开间 - 北京租房 https://bj.zu.anjuke.com/fangyuan/4588476351898635
-4. 园区详情 https://cy.ncss.cn/parks/8a80808d7b815e03017b855450990021
-5. 北京市海淀区东北旺中关村软件园孵化器1号楼 https://www.ncsti.gov.cn/kcfw/zkj/fhq/xq?id=16c39ee43650c7e62466e36cffb1eea6</x:v>
+        <x:v>1. 中关村软件园出租房源 https://zgcrjy.h-lou.com/
+2. 海淀上地中关村软件园|980平整层|精装修带家具|三面采光 http://m.fang.com/zf/bj/AGT_483661661.html
+3. 出租 上地中关村软件园2000平大平层 三面采光 带大露台 https://m.58.com/bj/zhaozu/83092203824602x.shtml
+4. 中关村软件园 苗圃家属楼 两居室 百度科技园腾讯网易新浪滴滴 http://m.anjuke.com/bj/rent/4573992857938953-3/
+5. 2026年中关村软件园价格分析与推荐 https://mip.b2b168.com/wvs319740156.html
+6. 出租 2块5全含 500平650平2300平 中关村软件园 https://m.58.com/bj/zhaozu/58279656706218x.shtml
+7. 中关村软件园 精装干净两居 价格可谈 业主直签 配套全齐！ http://m.anjuke.com/bj/rent/4129689982132230-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -5686,39 +5976,44 @@
         <x:v>北京市海淀区马连洼兰园9号</x:v>
       </x:c>
       <x:c r="E111" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F111" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G111" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H111" t="n">
-        <x:v>6.5</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I111" t="str">
-        <x:v>生活配套成熟且停车便宜，但距离网易较远，通勤时间较长，租金跨度大。</x:v>
+        <x:v>交通便利且配套成熟，租金适中，但多为无电梯老旧板楼，需关注楼层。</x:v>
       </x:c>
       <x:c r="J111" t="str">
-        <x:v>贝壳找房北京小区大全,兰园参考均价:59994元/㎡；; 1房. 數據不足 ; 2房. 22,000元/月； ; 3房. 25,000元/月；2房. 22,000元/月；3房. 25,000元/月；西门北京大学稻香园海淀大街海淀路两居. 6000元/月；链家网北京小区大全,西府兰庭参考均价:59544元/㎡</x:v>
+        <x:v>一居室整租约5100-5700元/月；，两居室整租约5100-7200元/月；，三居室整租约6700元/月</x:v>
       </x:c>
       <x:c r="K111" t="str">
-        <x:v>北区户型更好，人口密度更低一些。；小区户型 ;；1居室·2个户型. 117㎡. 在售1098万起 ;；2居室·4个户型. 152㎡~165㎡. 在售1790万起 ;；3居室·6个户型. 188㎡~232㎡. 在售1350万起 ;</x:v>
+        <x:v>房龄信息未查询到，户型以1室1厅、2室1厅、3室1厅为主，多数为精装修，家具家电齐全可直接入住，小区共6层多无电梯，小区绿化率高、环境优美，物业专业管理有序规范；；未查询到隔音相关评价；</x:v>
       </x:c>
       <x:c r="L111" t="str">
-        <x:v>周边生活配套齐全，超市、*、医院、公园都有，地铁上盖交通便利，闹中取静、停车位充足且收费便宜（业主第一辆车免费，第二辆车月租150元）。；中关村西门北京大学稻香园海淀大街海淀路两居. 6000元/月 · 海淀- 海淀大街44楼. 交通便利采光好南北通透首次出租 ;；刚才... ### 又是一年金丝桃. ### 存钱并且保持舒适甚至高品质生活的一点技巧心得分享（应届生版）. 保持舒适甚至高品质生活是对我自己来说的，包括且不局限于：每年出国旅行一次、国内旅行一次、购买想要的电子产品等 一、利用刚毕业的优势 1、大学生就业补贴 建议到小红书上搜索工作所在... ### 很多爱好真的0基础也完全可以上手的！；6.希望食材、... ### 读研三年，学校给了我二十万. 请进来跟这位小镇女孩说声恭喜好嘛！；以下菜谱也只是俺个... ### 住了两年的家 分享. ### 五一9天8晚意大利西班牙人均1.28w. 路线米兰-多洛米蒂-威尼斯-巴塞罗那-罗马 💰支出，人均12800左右 🎫交通 4723 成都米兰-罗马成都 机票 3617 米兰机场大巴 40 米兰到特伦特 146.5 博尔扎诺到威尼斯 242.5 威尼斯... ### 我发现小东西买可以接受的最贵的，真的效益很高. 我最近突然发现一个特别真实的真理，就是：很多高频使用的小东西，买贵的，幸福感提升巨大，但很多大件，贵很多，体验却没有差那么多。</x:v>
-      </x:c>
-      <x:c r="M111" t="str"/>
+        <x:v>通勤便利，步行到18号线马连洼站247米、16号线马连洼站407米，周边配套全；；商超有天喜百旺超市、中发百旺商城、大型农贸市场，餐饮网点多；；临近解放军总医院第八医学中心，医疗有保障；</x:v>
+      </x:c>
+      <x:c r="M111" t="str">
+        <x:v>未查询到针对西门区域的专属差评和风险信息，所有信息为整个兰园小区的租房信息，无专门针对西门区域的细分信息，存在信息泛化，可能存在同名小区混淆风险。；未查询到针对西门区域的专属差评和风险信息，所有信息为整个兰园小区的租房信息，无专门针对西门区域的细分信息，存在信息泛化，可能存在同名小区混淆风险</x:v>
+      </x:c>
       <x:c r="N111" t="str">
-        <x:v>价格线索：贝壳找房北京小区大全,兰园参考均价:59994元/㎡；; 1房. 數據不足 ; 2房. 22,000元/月； ; 3房. 25,000元/月；2房. 22,000元/月；3房. 25,000元/月；西门北京大学稻香园海淀大街海淀路两居. 6000元/月；链家网北京小区大全,西府兰庭参考均价:59544元/㎡；房屋质量/户型线索：北区户型更好，人口密度更低一些。；小区户型 ;；1居室·2个户型. 117㎡. 在售1098万起 ;；2居室·4个户型. 152㎡~165㎡. 在售1790万起 ;；3居室·6个户型. 188㎡~232㎡. 在售1350万起 ;；生活便利线索：周边生活配套齐全，超市、*、医院、公园都有，地铁上盖交通便利，闹中取静、停车位充足且收费便宜（业主第一辆车免费，第二辆车月租150元）。；中关村西门北京大学稻香园海淀大街海淀路两居. 6000元/月 · 海淀- 海淀大街44楼. 交通便利采光好南北通透首次出租 ;；刚才... ### 又是一年金丝桃. ### 存钱并且保持舒适甚至高品质生活的一点技巧心得分享（应届生版）. 保持舒适甚至高品质生活是对我自己来说的，包括且不局限于：每年出国旅行一次、国内旅行一次、购买想要的电子产品等 一、利用刚毕业的优势 1、大学生就业补贴 建议到小红书上搜索工作所在... ### 很多爱好真的0基础也完全可以上手的！；6.希望食材、... ### 读研三年，学校给了我二十万. 请进来跟这位小镇女孩说声恭喜好嘛！；以下菜谱也只是俺个... ### 住了两年的家 分享. ### 五一9天8晚意大利西班牙人均1.28w. 路线米兰-多洛米蒂-威尼斯-巴塞罗那-罗马 💰支出，人均12800左右 🎫交通 4723 成都米兰-罗马成都 机票 3617 米兰机场大巴 40 米兰到特伦特 146.5 博尔扎诺到威尼斯 242.5 威尼斯... ### 我发现小东西买可以接受的最贵的，真的效益很高. 我最近突然发现一个特别真实的真理，就是：很多高频使用的小东西，买贵的，幸福感提升巨大，但很多大件，贵很多，体验却没有差那么多。</x:v>
+        <x:v>价格线索：一居室整租约5100-5700元/月；，两居室整租约5100-7200元/月；，三居室整租约6700元/月；房屋质量/户型线索：房龄信息未查询到，户型以1室1厅、2室1厅、3室1厅为主，多数为精装修，家具家电齐全可直接入住，小区共6层多无电梯，小区绿化率高、环境优美，物业专业管理有序规范；；未查询到隔音相关评价；；生活便利线索：通勤便利，步行到18号线马连洼站247米、16号线马连洼站407米，周边配套全；；商超有天喜百旺超市、中发百旺商城、大型农贸市场，餐饮网点多；；临近解放军总医院第八医学中心，医疗有保障；；风险线索：未查询到针对西门区域的专属差评和风险信息，所有信息为整个兰园小区的租房信息，无专门针对西门区域的细分信息，存在信息泛化，可能存在同名小区混淆风险。；未查询到针对西门区域的专属差评和风险信息，所有信息为整个兰园小区的租房信息，无专门针对西门区域的细分信息，存在信息泛化，可能存在同名小区混淆风险</x:v>
       </x:c>
       <x:c r="O111" t="str">
-        <x:v>1. 兰园小区二手房 - 安居客 https://mobile.anjuke.com/esf/bj-cm849661
-2. 兰园- 房价|租房【北京贝壳找房】 https://m.ke.com/bj/xiaoqu/1111027378170
-3. 北京蘭園大樓·租金走勢 - 591租屋 https://rent.591.com.tw/market/community?community_id=15193&amp;pattern=four-bedroom-plus&amp;itm_source=rent&amp;itm_medium=detail&amp;itm_campaign=market_trend
-4. 北京海淀租房信息 - 房天下 http://www.fang.com/houses/zf_252922bj
-5. 泛海国际居住区兰海园- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027374229</x:v>
+        <x:v>1. ["马连洼租房 兰园小区 南北向两居 价可聊 业主好说话","http://m.anjuke.com/dongyang/rent/4593749441846286-3/"]
+2. ["急租！兰园温馨一居 干净整洁 通勤方便 价格可谈","http://m.anjuke.com/dongyang/rent/4585267493772291-3/"]
+3. ["自住首租！明厨明卫 兰园精装两居 配置齐实拍 价可聊 可长租","http://m.anjuke.com/bj/rent/4579822667244546-3/"]
+4. ["价格能谈 马连洼兰园 精装两居 跟业主签约 看房方便 可长租","http://m.anjuke.com/bj/rent/4604059391337484-3/"]
+5. 马连洼租房 兰园小区 南北向两居 价可聊 业主好说话 http://m.anjuke.com/dongyang/rent/4593749441846286-3/
+6. 急租！兰园温馨一居 干净整洁 通勤方便 价格可谈 http://m.anjuke.com/dongyang/rent/4585267493772291-3/
+7. 马连洼兰园 两居室 随时入住 采光好 交通方便 稳定租 http://m.anjuke.com/ch/rent/4546019632737281-3/
+8. 马连洼 三居室 采光好 随时入住 稳定长租 交通方便价格不贵 http://m.anjuke.com/dongyang/rent/4553171436250120-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -5735,7 +6030,7 @@
         <x:v>北京市海淀区马连洼兰园9号</x:v>
       </x:c>
       <x:c r="E112" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F112" t="n">
         <x:v>8</x:v>
@@ -5744,32 +6039,35 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H112" t="n">
-        <x:v>6.3</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="I112" t="str">
-        <x:v>1999年老旧小区，位于马连洼板块，近地铁但设施陈旧，适合预算有限者。</x:v>
+        <x:v>生活配套完善且通勤方便，户型南北通透，适合追求生活便利的租客。</x:v>
       </x:c>
       <x:c r="J112" t="str">
-        <x:v>北京兰园小区小区参考均价74657元/㎡；贝壳找房北京小区大全,兰园参考均价:59994元/㎡；链家网北京小区大全,兰园参考均价:59126元/㎡；社區租金行情・ 2房 22,000元/月；比去年- 3房 25,000元/月；比去年+6.4% 4房及以上31,750元/月；比去年+18.5% 35,000元/月； ・ 北京蘭園大樓・ 房25,000元/月</x:v>
+        <x:v>整租两居室约5100-6800元/月；整租三居室约8200元/月</x:v>
       </x:c>
       <x:c r="K112" t="str">
-        <x:v>兰园小区位于海淀区马连洼板块,于1999年建成,房龄较老。；了解更多兰园小区房价走势、二手房、租房、户型图等。；占地面积82000平方米,70产权, 房租房马连洼・ 满五年近地铁口,出入方便・ 兰园满两年不满五年/m2 马连洼・ 兰园户型主要有60平-88平的户型方正・ 本周挂牌均价2.00% 与上。；小区户型 ;；1居室·2个户型. 117㎡. 在售1098万起 ;</x:v>
+        <x:v>物业费0.8元/㎡·月，由北京安居物业管理有限公司提供服务；；户型多为南北通透的两居/三居室，装修分为精装修和简单装修，部分房源保持干净，家具家电齐全可直接入住；；小区多为6-10层板楼，部分楼栋无电梯；；未找到明确隔音相关评价。</x:v>
       </x:c>
       <x:c r="L112" t="str">
-        <x:v>占地面积82000平方米,70产权, 房租房马连洼・ 满五年近地铁口,出入方便・ 兰园满两年不满五年/m2 马连洼・ 兰园户型主要有60平-88平的户型方正・ 本周挂牌均价2.00% 与上。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。</x:v>
+        <x:v>周边有35个公交站，整体通勤便利。；商超：周边有中发百旺商城、北京华联BHG Mall、物美超市，购物方便，餐饮配套齐全。；医院：周边3km内有7家医院，解放军总医院第八医学中心距离较近，满足日常就医需求。；小区内部配有超市、快递柜、健身设施，生活配套完善。</x:v>
       </x:c>
       <x:c r="M112" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未找到明确针对兰园小区北门区域的专属租房差评信息，未发现大量风险投诉；</x:v>
       </x:c>
       <x:c r="N112" t="str">
-        <x:v>价格线索：北京兰园小区小区参考均价74657元/㎡；贝壳找房北京小区大全,兰园参考均价:59994元/㎡；链家网北京小区大全,兰园参考均价:59126元/㎡；社區租金行情・ 2房 22,000元/月；比去年- 3房 25,000元/月；比去年+6.4% 4房及以上31,750元/月；比去年+18.5% 35,000元/月； ・ 北京蘭園大樓・ 房25,000元/月；房屋质量/户型线索：兰园小区位于海淀区马连洼板块,于1999年建成,房龄较老。；了解更多兰园小区房价走势、二手房、租房、户型图等。；占地面积82000平方米,70产权, 房租房马连洼・ 满五年近地铁口,出入方便・ 兰园满两年不满五年/m2 马连洼・ 兰园户型主要有60平-88平的户型方正・ 本周挂牌均价2.00% 与上。；小区户型 ;；1居室·2个户型. 117㎡. 在售1098万起 ;；生活便利线索：占地面积82000平方米,70产权, 房租房马连洼・ 满五年近地铁口,出入方便・ 兰园满两年不满五年/m2 马连洼・ 兰园户型主要有60平-88平的户型方正・ 本周挂牌均价2.00% 与上。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；. 租金较高的中海凯旋小区距离复兴门地铁不到1公里，处于金融街中心，紧邻西单商圈，小区由中海物业管理，秩序较好，但小户型少，多为东西朝向。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：整租两居室约5100-6800元/月；整租三居室约8200元/月；房屋质量/户型线索：物业费0.8元/㎡·月，由北京安居物业管理有限公司提供服务；；户型多为南北通透的两居/三居室，装修分为精装修和简单装修，部分房源保持干净，家具家电齐全可直接入住；；小区多为6-10层板楼，部分楼栋无电梯；；未找到明确隔音相关评价。；生活便利线索：周边有35个公交站，整体通勤便利。；商超：周边有中发百旺商城、北京华联BHG Mall、物美超市，购物方便，餐饮配套齐全。；医院：周边3km内有7家医院，解放军总医院第八医学中心距离较近，满足日常就医需求。；小区内部配有超市、快递柜、健身设施，生活配套完善。；风险线索：未找到明确针对兰园小区北门区域的专属租房差评信息，未发现大量风险投诉；</x:v>
       </x:c>
       <x:c r="O112" t="str">
-        <x:v>1. 兰园小区,圆明园西路 - 租房-北京安居客 https://m.anjuke.com/bj/community/849661
-2. 北京兰园小区房价_二手房_租房 https://bj.loupan.com/community/41302.html
-3. 马连洼兰园- 二手房，租房-北京手机房天下 https://esf.fang.com/loupan/1010216357.htm
-4. 兰园- 房价|租房【北京贝壳找房】 https://m.ke.com/bj/xiaoqu/1111027378170
-5. 兰园- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027378170</x:v>
+        <x:v>1. ["兰园小区，马连洼租房，马连洼 兰园小区 南北通透 两居室 家电齐全 采光好 精装修，海淀租房","https://bj.zu.anjuke.com/fangyuan/4168129340513286"]
+2. ["马连洼兰园 两居室 随时入住 采光好 交通方便 稳定租","http://m.anjuke.com/ch/rent/4546019632737281-3/"]
+3. ["新增!兰园小区中间楼层三居室，家具齐全，随时起租，随时看房0","http://m.anjuke.com/bj/rent/3923321544010767-3/"]
+4. ["【海淀·16号线马连洼兰园｜招男室友｜步行软件园二期】","https://www.douban.com/group/topic/487115184/?_spm_id=NjI2NzQ0MzI"]
+5. ["2026北京马连洼兰园小区，配套指南，买房攻略-北京房天下","http://m.fang.com/xiaoqu/strategy/bj/1010216357.html"]
+6. 【多图】兰园小区，马连洼租房，马连洼 兰园小区 南北通透 两居室 家电齐全 采光好 精装修，海淀租房 https://bj.zu.anjuke.com/fangyuan/4168129340513286
+7. 马连洼兰园 两居室 随时入住 采光好 交通方便 稳定租 http://m.anjuke.com/ch/rent/4546019632737281-3/
+8. 【多图】兰园小区，马连洼租房，新增!兰园小区中间楼层三居室，家具齐全，随时起租，随时看房0，海淀租房 http://m.anjuke.com/bj/rent/3923321544010767-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -5786,39 +6084,41 @@
         <x:v>辉煌国际广场5号楼1905</x:v>
       </x:c>
       <x:c r="E113" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F113" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G113" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H113" t="n">
-        <x:v>8.8</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I113" t="str">
-        <x:v>高品质青年公寓，租金有政策优惠，配套极佳且离网易近，适合应届生申请。</x:v>
+        <x:v>紧邻西二旗地铁站，通勤极佳，设施齐全且服务较好，适合单身青年。</x:v>
       </x:c>
       <x:c r="J113" t="str">
-        <x:v>租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；精装修一居目前便宜长租位置好交通方便. 5000元/月；贝壳找房北京小区大全,青年公寓参考均价:69968元/㎡</x:v>
+        <x:v>同地段辉煌国际广场整租1室约4800元/月</x:v>
       </x:c>
       <x:c r="K113" t="str">
-        <x:v>项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；双安边上青年公寓正规精装修一居目前便宜长租位置好交通方便. 5000元/月 1室1厅整租. 海淀- 双安青年公寓. 交通便利周边配套齐采光好首次出租。；. 项目备案租金均价为109.5元/建筑平米·月（不含物业费），并实行动态调整。</x:v>
+        <x:v>房间干净整洁，空间较为宽敞，设施齐全（有热水、净水机、wifi等），装修整体较好，有日常公共区域打扫服务；；未查询到明确房龄、隔音负面反馈，多数评价正面，房东/管家服务贴心，问题可及时解决。；未查询到房龄、隔音、物业的详细负面反馈。</x:v>
       </x:c>
       <x:c r="L113" t="str">
-        <x:v>它坐落于海淀区辉煌国际广场5号楼1905，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；双安边上青年公寓正规精装修一居目前便宜长租位置好交通方便. 5000元/月 1室1厅整租. 海淀- 双安青年公寓. 交通便利周边配套齐采光好首次出租。；项目配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间。；国内普通高等学校毕业生提供学历、学位证书和《教育部学历证书电子注册备案表》、《中国高等教育学位在线验证报告》，留学人员提供教育部学历认证机构认证的《国外学历学位认证书》，如2025年应届毕业生尚未取得学历学位证明，可先行提供《毕业生就业推荐表》以及承诺书（见附件4）；；配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。</x:v>
-      </x:c>
-      <x:c r="M113" t="str"/>
+        <x:v>位置便利，步行约450米到西二旗地铁站，590米到东北旺地铁站，临近清河站，通勤便利；；位于辉煌国际广场，周边餐饮丰富，价格亲民，有商超、休闲场所，配套完善，距离医院相关信息未查询到明确内容。；未查询到针对该荧光青年公寓（海淀区辉煌国际广场5号楼1905）的直接差评或风险信息，本次搜索结果未发现同名误命中，但部分周边辉煌国际广场房源信息为泛化信息，未完全匹配目标公寓；</x:v>
+      </x:c>
+      <x:c r="M113" t="str">
+        <x:v>未查询到针对该荧光青年公寓（海淀区辉煌国际广场5号楼1905）的直接差评或风险信息，本次搜索结果未发现同名误命中，但部分周边辉煌国际广场房源信息为泛化信息，未完全匹配目标公寓；</x:v>
+      </x:c>
       <x:c r="N113" t="str">
-        <x:v>价格线索：租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；精装修一居目前便宜长租位置好交通方便. 5000元/月；贝壳找房北京小区大全,青年公寓参考均价:69968元/㎡；房屋质量/户型线索：项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；双安边上青年公寓正规精装修一居目前便宜长租位置好交通方便. 5000元/月 1室1厅整租. 海淀- 双安青年公寓. 交通便利周边配套齐采光好首次出租。；. 项目备案租金均价为109.5元/建筑平米·月（不含物业费），并实行动态调整。；生活便利线索：它坐落于海淀区辉煌国际广场5号楼1905，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；双安边上青年公寓正规精装修一居目前便宜长租位置好交通方便. 5000元/月 1室1厅整租. 海淀- 双安青年公寓. 交通便利周边配套齐采光好首次出租。；项目配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间。；国内普通高等学校毕业生提供学历、学位证书和《教育部学历证书电子注册备案表》、《中国高等教育学位在线验证报告》，留学人员提供教育部学历认证机构认证的《国外学历学位认证书》，如2025年应届毕业生尚未取得学历学位证明，可先行提供《毕业生就业推荐表》以及承诺书（见附件4）；；配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。</x:v>
+        <x:v>价格线索：同地段辉煌国际广场整租1室约4800元/月；房屋质量/户型线索：房间干净整洁，空间较为宽敞，设施齐全（有热水、净水机、wifi等），装修整体较好，有日常公共区域打扫服务；；未查询到明确房龄、隔音负面反馈，多数评价正面，房东/管家服务贴心，问题可及时解决。；未查询到房龄、隔音、物业的详细负面反馈。；生活便利线索：位置便利，步行约450米到西二旗地铁站，590米到东北旺地铁站，临近清河站，通勤便利；；位于辉煌国际广场，周边餐饮丰富，价格亲民，有商超、休闲场所，配套完善，距离医院相关信息未查询到明确内容。；未查询到针对该荧光青年公寓（海淀区辉煌国际广场5号楼1905）的直接差评或风险信息，本次搜索结果未发现同名误命中，但部分周边辉煌国际广场房源信息为泛化信息，未完全匹配目标公寓；；风险线索：未查询到针对该荧光青年公寓（海淀区辉煌国际广场5号楼1905）的直接差评或风险信息，本次搜索结果未发现同名误命中，但部分周边辉煌国际广场房源信息为泛化信息，未完全匹配目标公寓；</x:v>
       </x:c>
       <x:c r="O113" t="str">
-        <x:v>1. 荧光青年公寓价格、点评、电话 - 携程 https://m.ctrip.com/html5/hotel/hoteldetail/117473276.html
-2. 北京海淀区青年公寓地址在哪里?项目介绍 http://bj.bendibao.com/zffw/202566/373174.shtm
-3. 选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网 https://www.stdaily.com/web/gdxw/2025-06/06/content_351160.html
-4. 青年公寓租房信息- 北京 - 房天下 http://www.fang.com/houses/zf_261936bj
-5. 922套！海淀区青年公寓配租意向，明起登记 https://xinwen.bjd.com.cn/content/s68401755e4b0ec1c3d97f822.html</x:v>
+        <x:v>1. 荧光青年公寓 https://hotels.corporatetravel.ctrip.com/hotels/117473276.html
+2. 0押金 可月付 公积金直付 近地铁13号线西二旗站百度元中心 http://m.anjuke.com/bj/rent/4597986470618121-3/
+3. 北京海淀一公寓因消防隐患被关停，住户：政府劝我们搬，理解 https://m.thepaper.cn/wifiKey_detail.jsp?contid=1878532&amp;from=wifiKey
+4. 校外打工人|记录这半年在北京的租房经历+经验分享 https://m.douban.com/group/topic/270614129/
+5. 这个区面向毕业大学生配租900余套房源 https://m.thepaper.cn/newsDetail_forward_30978554</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -5835,39 +6135,31 @@
         <x:v>上地十街1号院3号楼7层718房</x:v>
       </x:c>
       <x:c r="E114" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F114" t="n">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G114" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H114" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I114" t="str">
-        <x:v>保租房性质且设施完善，价格有竞争力，但证据中地理位置指向模糊，需确认通勤距离。</x:v>
-      </x:c>
-      <x:c r="J114" t="str">
-        <x:v>链家网北京小区大全,青年公寓参考均价:69318元/㎡；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；精装修一居目前便宜长租位置好交通方便. 5000元/月；相寓皂君庙·青年公寓·低楼层·1居室. 5900元/月； 整租·皂君庙·青年公寓·1室·1厅. 5700元/月；整租·皂君庙·青年公寓·1室·1厅. 5700元/月</x:v>
-      </x:c>
-      <x:c r="K114" t="str">
-        <x:v>. 项目备案租金均价为109.5元/建筑平米·月（不含物业费），并实行动态调整。；当前位置：首页-&gt;信息公开大厅-&gt;区房管局-&gt;重点领域-&gt;保障住房-&gt;分配房源. | 索引号 | 11F/2026-19918 | 公开责任部门 | 区房管局 |. | 生成日期 | 2026年04月08日 10:00 | 公开日期 | 2026年04月08日 10:00 |. | 附件 | 附件1.保障性租赁住房专项配租平台APP操作手册.pdf 附件2.保障性租赁住房专项配租平台WEB操作手册.pdf 附件3.项目基本情况介绍.zip 附件4.社保缴纳材料查询步骤.doc 附件5.承诺书.docx |. 租金单价包含家具家电使用费、物业费,不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；双安边上青年公寓正规精装修一居目前便宜长租位置好交通方便. 5000元/月 ;</x:v>
-      </x:c>
-      <x:c r="L114" t="str">
-        <x:v>项目配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间。；国内普通高等学校毕业生提供学历、学位证书和《教育部学历证书电子注册备案表》、《中国高等教育学位在线验证报告》，留学人员提供教育部学历认证机构认证的《国外学历学位认证书》，如2025年应届毕业生尚未取得学历学位证明，可先行提供《毕业生就业推荐表》以及承诺书（见附件4）；；配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。；下一步，海淀区“两区”建设将进一步筑巢引凤、服务人才，不断完善自贸试验区周边配套设施，全力打造青年人才宜居宜业环境，吸引更多国际优秀创新人才来到海淀、扎根海淀。；国内普通高等学校毕业生提供学历证书或《教育部学历证书电子注册备案表》、学位证书或《中国高等教育学位在线验证报告》；</x:v>
-      </x:c>
+        <x:v>证据严重不足，缺乏租金、质量及周边配套等关键信息，无法给出有效推荐。</x:v>
+      </x:c>
+      <x:c r="J114" t="str"/>
+      <x:c r="K114" t="str"/>
+      <x:c r="L114" t="str"/>
       <x:c r="M114" t="str"/>
-      <x:c r="N114" t="str">
-        <x:v>价格线索：链家网北京小区大全,青年公寓参考均价:69318元/㎡；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；精装修一居目前便宜长租位置好交通方便. 5000元/月；相寓皂君庙·青年公寓·低楼层·1居室. 5900元/月； 整租·皂君庙·青年公寓·1室·1厅. 5700元/月；整租·皂君庙·青年公寓·1室·1厅. 5700元/月；房屋质量/户型线索：. 项目备案租金均价为109.5元/建筑平米·月（不含物业费），并实行动态调整。；当前位置：首页-&gt;信息公开大厅-&gt;区房管局-&gt;重点领域-&gt;保障住房-&gt;分配房源. | 索引号 | 11F/2026-19918 | 公开责任部门 | 区房管局 |. | 生成日期 | 2026年04月08日 10:00 | 公开日期 | 2026年04月08日 10:00 |. | 附件 | 附件1.保障性租赁住房专项配租平台APP操作手册.pdf 附件2.保障性租赁住房专项配租平台WEB操作手册.pdf 附件3.项目基本情况介绍.zip 附件4.社保缴纳材料查询步骤.doc 附件5.承诺书.docx |. 租金单价包含家具家电使用费、物业费,不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；双安边上青年公寓正规精装修一居目前便宜长租位置好交通方便. 5000元/月 ;；生活便利线索：项目配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间。；国内普通高等学校毕业生提供学历、学位证书和《教育部学历证书电子注册备案表》、《中国高等教育学位在线验证报告》，留学人员提供教育部学历认证机构认证的《国外学历学位认证书》，如2025年应届毕业生尚未取得学历学位证明，可先行提供《毕业生就业推荐表》以及承诺书（见附件4）；；配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。；下一步，海淀区“两区”建设将进一步筑巢引凤、服务人才，不断完善自贸试验区周边配套设施，全力打造青年人才宜居宜业环境，吸引更多国际优秀创新人才来到海淀、扎根海淀。；国内普通高等学校毕业生提供学历证书或《教育部学历证书电子注册备案表》、学位证书或《中国高等教育学位在线验证报告》；</x:v>
-      </x:c>
+      <x:c r="N114" t="str"/>
       <x:c r="O114" t="str">
-        <x:v>1. 922套！海淀区青年公寓配租意向，明起登记 - 北京日报 https://xinwen.bjd.com.cn/content/s68401755e4b0ec1c3d97f822.html
-2. 海淀组团内配租922套青年公寓 - 开放北京 https://open.beijing.gov.cn/html//haidian/gzdt/2025/6/1750038168814.html
-3. 海淀区信息公开大厅 https://zyk.bjhd.gov.cn/jbdt/auto4522_51806/zdly/bzzf/fpfy/202604/t20260408_4811149.shtml
-4. 青年公寓- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027378885
-5. 选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网 https://www.stdaily.com/web/gdxw/2025-06/06/content_351160.html</x:v>
+        <x:v>1. 【北京租房公寓式居6000 https://fang.com/houses/zf_251682bj/c26000-d28000-g21,3,2,4-h38-i32/
+2. #青年民宿公寓# https://weitoutiao.zjurl.cn/rogue/topic_share/?concern_id=1834343383968793&amp;prevent_activate=1
+3. 【北京上地公寓租房2000 https://fang.com/houses/zf_252106bj/c22000-d230003-h38-i33/
+4. 北京的青年公寓怎么样 https://m.kupet.cn/read-1774174249a44896686.html
+5. 【北京上地公寓出租信息3000 https://fang.com/houses/zf_252105bj/c23000-d250003-h34-i33/</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -5884,39 +6176,44 @@
         <x:v>龙域西一路融泽嘉园西2号院6号楼</x:v>
       </x:c>
       <x:c r="E115" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F115" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G115" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H115" t="n">
-        <x:v>8.5</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I115" t="str">
-        <x:v>位于龙泽板块，租金性价比极高，周边医疗商业配套成熟，非常适合网易员工通勤。</x:v>
+        <x:v>房屋较新且隔音良好，生活配套成熟，虽距地铁稍远但整体居住品质较高。</x:v>
       </x:c>
       <x:c r="J115" t="str">
-        <x:v>地铁龙泽苑东区三家三卫主卧独卫带阳台. 2800元/月</x:v>
+        <x:v>价的月租信息，该区域同类型小面积公寓大致3500元/月</x:v>
       </x:c>
       <x:c r="K115" t="str">
-        <x:v>58同城北京租房网，为您提供北京昌平租房信息，包括昌平房屋出租信息、昌平合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询。</x:v>
+        <x:v>该公寓位于融泽嘉园西2号院，该小区整租房源价格约为：60㎡左右南向一居精装修月租6000-6100元（押一付三，中介费为1个月租金）；；该公寓所在融泽嘉园西2号院为高层带电梯小区，该公寓整体评价卫生干净整洁，住宿安静隔音较好；；户型多为一居（面积多为30-66㎡不等），小区房龄较新，为精装修；；小区物业提供电梯、公共区域维护，部分房源提供免费维修服务。</x:v>
       </x:c>
       <x:c r="L115" t="str">
-        <x:v>顺遂精品公寓(积水潭医院新龙泽院区店) - 携程。；它坐落于昌平区龙域西一路融泽嘉园西2号院6号楼，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；13号线龙泽地铁龙泽苑东区三家三卫主卧独卫带阳台. 2800元/月 3室1厅合租主卧. 昌平- 龙泽苑东区. 交通便利周边配套齐采光好全装全配。；商业配套上，一站地到超级合生汇，步行可达万科TBD生活广场。；医疗上，有积水潭医院、北大国际医院、北大第六医院昌平院区。</x:v>
-      </x:c>
-      <x:c r="M115" t="str"/>
+        <x:v>顺遂精品公寓(积水潭医院新龙泽院区店) 火山联网搜索汇总。；配套可做饭，有免费WiFi、洗衣房等设施；；交通：距离18号线龙泽西地铁站约1.1-1.2公里，距离13号线龙泽站约1.8公里，临近公交站点，通勤便利；；医疗：紧邻北京积水潭医院新龙泽院区，步行10分钟内可达，适合看病陪护；；商业：周边3公里内有昌发展万科广场、北京华联BHG Mall、日日生鲜生活超市等商超，餐饮配套丰富；</x:v>
+      </x:c>
+      <x:c r="M115" t="str">
+        <x:v>未找到该公寓明确差评信息；</x:v>
+      </x:c>
       <x:c r="N115" t="str">
-        <x:v>价格线索：地铁龙泽苑东区三家三卫主卧独卫带阳台. 2800元/月；房屋质量/户型线索：58同城北京租房网，为您提供北京昌平租房信息，包括昌平房屋出租信息、昌平合租房、整租房、个人房源以及经纪人房源，同时可以根据户型、公寓、别墅、短租、民宿等类别查询。；生活便利线索：顺遂精品公寓(积水潭医院新龙泽院区店) - 携程。；它坐落于昌平区龙域西一路融泽嘉园西2号院6号楼，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；13号线龙泽地铁龙泽苑东区三家三卫主卧独卫带阳台. 2800元/月 3室1厅合租主卧. 昌平- 龙泽苑东区. 交通便利周边配套齐采光好全装全配。；商业配套上，一站地到超级合生汇，步行可达万科TBD生活广场。；医疗上，有积水潭医院、北大国际医院、北大第六医院昌平院区。</x:v>
+        <x:v>价格线索：价的月租信息，该区域同类型小面积公寓大致3500元/月；房屋质量/户型线索：该公寓位于融泽嘉园西2号院，该小区整租房源价格约为：60㎡左右南向一居精装修月租6000-6100元（押一付三，中介费为1个月租金）；；该公寓所在融泽嘉园西2号院为高层带电梯小区，该公寓整体评价卫生干净整洁，住宿安静隔音较好；；户型多为一居（面积多为30-66㎡不等），小区房龄较新，为精装修；；小区物业提供电梯、公共区域维护，部分房源提供免费维修服务。；生活便利线索：顺遂精品公寓(积水潭医院新龙泽院区店) 火山联网搜索汇总。；配套可做饭，有免费WiFi、洗衣房等设施；；交通：距离18号线龙泽西地铁站约1.1-1.2公里，距离13号线龙泽站约1.8公里，临近公交站点，通勤便利；；医疗：紧邻北京积水潭医院新龙泽院区，步行10分钟内可达，适合看病陪护；；商业：周边3公里内有昌发展万科广场、北京华联BHG Mall、日日生鲜生活超市等商超，餐饮配套丰富；；风险线索：未找到该公寓明确差评信息；</x:v>
       </x:c>
       <x:c r="O115" t="str">
-        <x:v>1. 顺遂精品公寓(积水潭医院新龙泽院区店) - 携程 https://m.ctrip.com/html5/hotel/hoteldetail/114115247.html
-2. 龙泽租房价格 - 房天下 https://m.fang.com/houses/zf_257699_bj
-3. 昌平租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/changping
-4. 北京公寓出租_北京精装公寓出租信息-北京链家找房 https://m.lianjia.com/chuzu/bj/apartment/changpingqu/amp0
-5. 北京昌平租房信息 - 58同城 http://mob.58.com/zf/hk-changping</x:v>
+        <x:v>1. ["顺遂精品公寓(积水潭医院新龙泽院区店)","https://hotels.ctrip.com/hotels/114115247.html"]
+2. ["融泽嘉园西2号院南向一居空置随时看房采光好 西二旗上地回龙观","http://m.anjuke.com/bj/rent/4599671404616708-3/"]
+3. ["融泽嘉园西2号院南向精装一居随时看房入住 西二旗上地回龙观","http://m.anjuke.com/ch/rent/4567421281999874-3/"]
+4. 顺遂精品公寓(积水潭医院新龙泽院区店) https://hotels.ctrip.com/hotels/114115247.html
+5. 融泽嘉园西2号院南向一居空置随时看房采光好 西二旗上地回龙观 http://m.anjuke.com/bj/rent/4599671404616708-3/
+6. 紧邻积水潭医院 近龙泽地铁 押一付一 朝南 整租 精装公寓 http://m.anjuke.com/bj/rent/4239206424128521-3/
+7. 融泽嘉园西2号院南向精装一居随时看房入住 西二旗上地回龙观 http://m.anjuke.com/ch/rent/4567421281999874-3/
+8. 戎尚精品公寓（北京积水潭医院新龙泽院店） https://hotels.corporatetravel.ctrip.com/hotels/120177379.html</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -5933,39 +6230,44 @@
         <x:v>上地西路辉煌国际3号楼</x:v>
       </x:c>
       <x:c r="E116" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F116" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G116" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H116" t="n">
-        <x:v>6</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I116" t="str">
-        <x:v>地理位置优越，但公开信息中租金数据严重矛盾，证据充分性较弱，评分较为保守。</x:v>
+        <x:v>地理位置优越，房龄新且设施齐全，支持宠物及月付，是网易员工的高性价比选择。</x:v>
       </x:c>
       <x:c r="J116" t="str">
-        <x:v>租 1-3个月 4-6个月. 1300-2300元/月；3平方米，租金区间为17,000-80,000元/月</x:v>
+        <x:v>月租大概3900-4800元，合租单间约2400元/月</x:v>
       </x:c>
       <x:c r="K116" t="str">
-        <x:v>昆泰嘉瑞公寓提供从开间到三居室的多样化户型选择，面积覆盖106-393平方米，租金区间为17,000-80,000元/月，适配不同人群需求：. 开间户型（108-130㎡）：适合单身贵族或年轻夫妻。</x:v>
+        <x:v>该公寓2019年开业，房龄较新；；户型以35-38㎡的大床房、双床间为主，周边同小区一居室多为1室1厅，面积约30-46㎡，房间宽敞明亮；；整体为精装修，设施齐全干净卫生；；该楼栋为实体墙，多数评价隔音良好；；有门禁、公共区域监控、安保人员，24小时前台服务，物业安保完善，支持宠物入住。</x:v>
       </x:c>
       <x:c r="L116" t="str">
-        <x:v>北京辉煌国际服务式公寓(西二旗地铁站店) - 携程。；房间干净整洁、宽廠舒适、有厨房、设施齐全，离小吃街、地铁站都很近，出行方便，感觉很好！</x:v>
-      </x:c>
-      <x:c r="M116" t="str"/>
+        <x:v>该公寓位于辉煌国际3号楼，周边同地段整租一居室月租大概3900-4800元，合租单间约2400元/月，日租价格约268-388元/晚，支持月付，无中介费服务费。；户型以35-38㎡的大床房、双床间为主，周边同小区一居室多为1室1厅，面积约30-46㎡，房间宽敞明亮；；周边商超：楼下有大型购物中心、美食城，步行可达超市发，1公里左右有西二旗益民商城，2公里内有昌发展万科广场，餐饮选择多；；医疗：距离北京积水潭医院新龙泽院区约1.3公里，满足日常医疗需求；；公寓支持可做饭、烧烤，配套有免费wifi、自动售货机、停车场等，生活便利。</x:v>
+      </x:c>
+      <x:c r="M116" t="str">
+        <x:v>公开租房类口碑信息较少，搜索结果多为日租酒店信息，长租月租信息多为同地段其他房源，未找到该公寓明确的差评信息，存在信息泛化的可能性。</x:v>
+      </x:c>
       <x:c r="N116" t="str">
-        <x:v>价格线索：租 1-3个月 4-6个月. 1300-2300元/月；3平方米，租金区间为17,000-80,000元/月；房屋质量/户型线索：昆泰嘉瑞公寓提供从开间到三居室的多样化户型选择，面积覆盖106-393平方米，租金区间为17,000-80,000元/月，适配不同人群需求：. 开间户型（108-130㎡）：适合单身贵族或年轻夫妻。；生活便利线索：北京辉煌国际服务式公寓(西二旗地铁站店) - 携程。；房间干净整洁、宽廠舒适、有厨房、设施齐全，离小吃街、地铁站都很近，出行方便，感觉很好！</x:v>
+        <x:v>价格线索：月租大概3900-4800元，合租单间约2400元/月；房屋质量/户型线索：该公寓2019年开业，房龄较新；；户型以35-38㎡的大床房、双床间为主，周边同小区一居室多为1室1厅，面积约30-46㎡，房间宽敞明亮；；整体为精装修，设施齐全干净卫生；；该楼栋为实体墙，多数评价隔音良好；；有门禁、公共区域监控、安保人员，24小时前台服务，物业安保完善，支持宠物入住。；生活便利线索：该公寓位于辉煌国际3号楼，周边同地段整租一居室月租大概3900-4800元，合租单间约2400元/月，日租价格约268-388元/晚，支持月付，无中介费服务费。；户型以35-38㎡的大床房、双床间为主，周边同小区一居室多为1室1厅，面积约30-46㎡，房间宽敞明亮；；周边商超：楼下有大型购物中心、美食城，步行可达超市发，1公里左右有西二旗益民商城，2公里内有昌发展万科广场，餐饮选择多；；医疗：距离北京积水潭医院新龙泽院区约1.3公里，满足日常医疗需求；；公寓支持可做饭、烧烤，配套有免费wifi、自动售货机、停车场等，生活便利。；风险线索：公开租房类口碑信息较少，搜索结果多为日租酒店信息，长租月租信息多为同地段其他房源，未找到该公寓明确的差评信息，存在信息泛化的可能性。</x:v>
       </x:c>
       <x:c r="O116" t="str">
-        <x:v>1. 香格瑞萊公寓（北京西二旗店） - 2026 北京人氣酒店優惠及真實評論 https://hk.trip.com/hotels/beijing-hotel-detail-35959593/xiang-ge-rui-lai-gong-yu
-2. 西二旗租房 - 58同城 http://mob.58.com/zf/bj-xierqi
-3. 海淀西二旗二室租房租金 https://bj.zu.anjuke.com/fangyuan/haidian-q-xierqi/fx2
-4. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu
-5. 昆泰嘉瑞公寓 - 北京酒店式公寓-出租（长租、短租 https://www.yudinggongyu.com/beijing/52.cshtml</x:v>
+        <x:v>1. ["香格瑞莱公寓(北京西二旗店) https://hotels.ctrip.com/hotels/35959593.html"]
+2. ["【香格瑞莱公寓(北京西二旗店)】地址,电话,路线,周边设施 https://m.map.360.cn/m/search/detail/pid=e9df34757fe4a51d"]
+3. ["地铁13号线西二旗辉煌国际整租一居室 http://m.anjuke.com/bj/rent/4552627216393217/"]
+4. 香格瑞莱公寓(北京西二旗店) https://hotels.ctrip.com/hotels/35959593.html
+5. 西二旗精装一居室 近地铁采光好 可月付 随时看房 http://m.anjuke.com/bj/rent/4536168875582465-3/
+6. 【香格瑞莱公寓(北京西二旗店)】地址,电话,路线,周边设施 https://m.map.360.cn/m/search/detail/pid=e9df34757fe4a51d
+7. 整租 物业直签 可月付 无杂费 西二旗 通勤便利 设施齐全 http://m.anjuke.com/bj/rent/4596659634711558-3/
+8. 西二旗200米15天，租期自由，店长，房租92折扣 http://m.anjuke.com/bj/rent/4591075842829324-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -5982,37 +6284,42 @@
         <x:v>西二旗辉煌国际3号楼512</x:v>
       </x:c>
       <x:c r="E117" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F117" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G117" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H117" t="n">
-        <x:v>8.8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="I117" t="str">
-        <x:v>紧邻西二旗地铁站，步行可达网易，家电齐全且生活便利，是该区域成熟的租住选择。</x:v>
+        <x:v>紧邻西二旗地铁站，通勤极便，户型选择多且配套成熟，但品牌专属口碑信息较少。</x:v>
       </x:c>
       <x:c r="J117" t="str"/>
       <x:c r="K117" t="str">
-        <x:v>... 国际随时看房. 面积：160m² 租金：1.77元/m²/天. 房源描述：此房属于上下户型 ... 辉煌国际广场位于海淀区上地信息产业基地北区5号地，上地十街1号院。；日租金均价：2.60 元/㎡·天. 物业管理费：4.80 元/㎡·月. 楼层高度：3.00米 ;；户型： 1室1厅1卫;；装修： 精装修;；户型齐全，主打户型方正,明卫一居. 辉煌国际户型主要有43平-60平的户型方正,明卫的一居、84平-84平的户型方正,客厅朝南的二居。</x:v>
+        <x:v>户型主要有一居开间、两室一厅，面积在44-109平米之间；；多数为精装修，家具家电配套齐全（冰箱、洗衣机、空调、燃气灶等均配齐）；；小区有24小时保安，物业管理较好，安全度高；；搜索结果未明确提及房龄与隔音情况；</x:v>
       </x:c>
       <x:c r="L117" t="str">
-        <x:v>交通状况。；北京意加公寓（輝煌國際大廈店）在2019開業，無論是商務出行還是休閒旅遊，為旅客提供一個北京的理想住宿。；地铁13号线西二旗站辉煌国际朝南开间 - 北京租房。；# 携程酒店-北京辉煌国际大厦酒店式公寓预订-北京辉煌国际大厦酒店式公寓价格、点评、电话、地址查询-【携程旅行手机版】. 1张1.5米双人床 及 1张1.8米大床. 环境位置 45 : 位置便利出行方便，离地铁口近，周边交通状况良好，去景区等出行便利. 卫生 81 : 房间干净整洁，卫生打扫细致，无异味，生活用品齐全. 设施 35 : 屋内设备齐全，设施新净，有冰箱、洗衣机等齐全设施. 环境很好。；推荐. 房间很温馨，家电齐全适合常住，离地铁口很近，前台小哥很nice，有求必应. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年火了十年，是北京湘菜必吃餐厅，店里的菜品种类丰富道道都是招牌 ✅金*钱蛋： 金*钱蛋太绝啦！</x:v>
-      </x:c>
-      <x:c r="M117" t="str"/>
+        <x:v>多数为精装修，家具家电配套齐全（冰箱、洗衣机、空调、燃气灶等均配齐）；；通勤：步行385米可达昌平线/13号线西二旗站，步行770米可达18号线东北旺站，靠近百度、小米等互联网公司园区，通勤便利；；商超：楼下就有美食城，80米处有超市发超市，步行可达西二旗益民商城、昌发展万科广场，购物便捷；；医疗：距离北京积水潭医院（新龙泽院区）约1.3公里，有医疗保障；；餐饮：楼下就有餐饮配套，生活便利；</x:v>
+      </x:c>
+      <x:c r="M117" t="str">
+        <x:v>本次搜索结果多为辉煌国际公寓的通用租房信息，未找到针对「北京意加公寓(辉煌国际大厦店)」（西二旗辉煌国际3号楼512）的专属差评，存在信息泛化，无法确认该公寓式酒店的专属口碑风险，可能存在同名误命中情况；</x:v>
+      </x:c>
       <x:c r="N117" t="str">
-        <x:v>房屋质量/户型线索：... 国际随时看房. 面积：160m² 租金：1.77元/m²/天. 房源描述：此房属于上下户型 ... 辉煌国际广场位于海淀区上地信息产业基地北区5号地，上地十街1号院。；日租金均价：2.60 元/㎡·天. 物业管理费：4.80 元/㎡·月. 楼层高度：3.00米 ;；户型： 1室1厅1卫;；装修： 精装修;；户型齐全，主打户型方正,明卫一居. 辉煌国际户型主要有43平-60平的户型方正,明卫的一居、84平-84平的户型方正,客厅朝南的二居。；生活便利线索：交通状况。；北京意加公寓（輝煌國際大廈店）在2019開業，無論是商務出行還是休閒旅遊，為旅客提供一個北京的理想住宿。；地铁13号线西二旗站辉煌国际朝南开间 - 北京租房。；# 携程酒店-北京辉煌国际大厦酒店式公寓预订-北京辉煌国际大厦酒店式公寓价格、点评、电话、地址查询-【携程旅行手机版】. 1张1.5米双人床 及 1张1.8米大床. 环境位置 45 : 位置便利出行方便，离地铁口近，周边交通状况良好，去景区等出行便利. 卫生 81 : 房间干净整洁，卫生打扫细致，无异味，生活用品齐全. 设施 35 : 屋内设备齐全，设施新净，有冰箱、洗衣机等齐全设施. 环境很好。；推荐. 房间很温馨，家电齐全适合常住，离地铁口很近，前台小哥很nice，有求必应. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年火了十年，是北京湘菜必吃餐厅，店里的菜品种类丰富道道都是招牌 ✅金*钱蛋： 金*钱蛋太绝啦！</x:v>
+        <x:v>房屋质量/户型线索：户型主要有一居开间、两室一厅，面积在44-109平米之间；；多数为精装修，家具家电配套齐全（冰箱、洗衣机、空调、燃气灶等均配齐）；；小区有24小时保安，物业管理较好，安全度高；；搜索结果未明确提及房龄与隔音情况；；生活便利线索：多数为精装修，家具家电配套齐全（冰箱、洗衣机、空调、燃气灶等均配齐）；；通勤：步行385米可达昌平线/13号线西二旗站，步行770米可达18号线东北旺站，靠近百度、小米等互联网公司园区，通勤便利；；商超：楼下就有美食城，80米处有超市发超市，步行可达西二旗益民商城、昌发展万科广场，购物便捷；；医疗：距离北京积水潭医院（新龙泽院区）约1.3公里，有医疗保障；；餐饮：楼下就有餐饮配套，生活便利；；风险线索：本次搜索结果多为辉煌国际公寓的通用租房信息，未找到针对「北京意加公寓(辉煌国际大厦店)」（西二旗辉煌国际3号楼512）的专属差评，存在信息泛化，无法确认该公寓式酒店的专属口碑风险，可能存在同名误命中情况；</x:v>
       </x:c>
       <x:c r="O117" t="str">
-        <x:v>1. 辉煌国际大厦 - 北京写字楼 http://www.haoyuzaixian.com/a38
-2. 北京意加公寓（輝煌國際大廈店） (Beijing Yijia Apartment) https://www.klook.com/zh-TW/hotels/detail/803249-beijing-yijia--apartment
-3. 辉煌国际大厦（广场）大厦-电话010-56225887-出租-出售-价格-官网 https://m.qifangfang.com/home/xiaoqu/d.html?id=97
-4. 地铁13号线西二旗站辉煌国际朝南开间 - 北京租房 https://bj.zu.anjuke.com/fangyuan/4548456705436684
-5. 辉煌国际- 二手房，租房-北京手机房天下 https://esf.fang.com/loupan/1010124627.htm</x:v>
+        <x:v>1. ["昌平线西二旗地铁站，百度，辉煌国际精装一居室。","https://bj.zu.anjuke.com/fangyuan/4479317472683016"]
+2. ["地铁13号线西二旗站百度大厦旁辉煌国际","http://m.anjuke.com/bj/rent/4546035325594625-3/"]
+3. ["西二旗整租大开间，靠近百度软件园小米快手，各公司班车家具可配","http://m.anjuke.com/bj/rent/4432331878980613-3/"]
+4. ["地铁13号线西二旗站百度大厦辉煌国际整租朝南一居室","http://m.anjuke.com/bj/rent/4520399965053961-3/"]
+5. 昌平线西二旗地铁站，百度，辉煌国际精装一居室。 https://bj.zu.anjuke.com/fangyuan/4479317472683016
+6. 西二旗 真实房源 业主直签 价格能谈 南北通透 2室1厅 http://m.anjuke.com/bj/rent/4534483135847426-3/
+7. 地铁13号线西二旗站百度大厦旁辉煌国际 http://m.anjuke.com/bj/rent/4546035325594625-3/
+8. 西二旗整租大开间，靠近百度软件园小米快手，各公司班车家具可配 http://m.anjuke.com/bj/rent/4432331878980613-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -6029,10 +6336,10 @@
         <x:v>上地十街1号院5号楼8层818</x:v>
       </x:c>
       <x:c r="E118" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F118" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G118" t="n">
         <x:v>8</x:v>
@@ -6041,27 +6348,32 @@
         <x:v>8.2</x:v>
       </x:c>
       <x:c r="I118" t="str">
-        <x:v>紧邻西二旗地铁，配套成熟且户型方正，隔音较好，是网易员工的高性价比之选。</x:v>
+        <x:v>距离西二旗站及网易极近，通勤极便，房龄较新但需警惕部分房间异味及采光问题。</x:v>
       </x:c>
       <x:c r="J118" t="str">
-        <x:v>13号线等; 五六环之间; 配套齐全. 28400元/㎡；配套齐全. 28400元/㎡；租 1-3个月 4-6个月. 1300-2300元/月</x:v>
+        <x:v>1室开间（40-48㎡）约5000元/月；面积办公户型（200㎡左右）约1.3万-1.5万/月；佣金一般为2%月租金，停车位价格150-300元/月</x:v>
       </x:c>
       <x:c r="K118" t="str">
-        <x:v>隔音效果也不错。；户型设计丰富多样，以3居、4居为主，兼顾下跃与顶复户型，适配不同家庭的租住需求：三居户型面积区间240㎡-265㎡，四居户型300㎡-385㎡，顶层复式带露台，一层下跃带花园，每栋楼顶层均。；户型齐全，主打户型方正,明卫一居. 辉煌国际户型主要有43平-60平的户型方正,明卫的一居、84平-84平的户型方正,客厅朝南的二居。</x:v>
+        <x:v>大面积办公户型（200㎡左右）约1.3万-1.5万/月，押一付三或押一付一，佣金一般为2%月租金，停车位价格150-300元/月，入住需固定押金¥100；；房龄：该公寓2017年开业，房龄较新；；户型：主打40-48㎡开间，1室0厅1卫，部分房型落地窗采光好，空间宽敞，带独立厨卫；；装修：多为精装修，风格简约大气，家具家电齐全，多数房间干净整洁；；隔音：多数住客评价隔音效果较好；</x:v>
       </x:c>
       <x:c r="L118" t="str">
-        <x:v># 携程酒店-北京辉煌国际大厦酒店式公寓预订-北京辉煌国际大厦酒店式公寓价格、点评、电话、地址查询-【携程旅行手机版】. 1张1.5米双人床 及 1张1.8米大床. 环境位置 45 : 位置便利出行方便，离地铁口近，周边交通状况良好，去景区等出行便利. 卫生 81 : 房间干净整洁，卫生打扫细致，无异味，生活用品齐全. 设施 35 : 屋内设备齐全，设施新净，有冰箱、洗衣机等齐全设施. 环境很好。；推荐. 房间很温馨，家电齐全适合常住，离地铁口很近，前台小哥很nice，有求必应. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年火了十年，是北京湘菜必吃餐厅，店里的菜品种类丰富道道都是招牌 ✅金*钱蛋： 金*钱蛋太绝啦！；它坐落于海淀区上地十街1号院5号楼8层818，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；配套齐全. 28400元/㎡. 6月挂牌均价. 暂无. 在售房源. 34套. 在租房源.。；1、【出租】昌平 回龙观 珠江摩尔国际大厦辉煌国际交通便利. 面积：166m² 租金：1.71元/m²/天 1. 房屋2室1厅2卫珠江摩尔位于昌平八达岭高速北清路出口辛庄桥西北角，北清。</x:v>
-      </x:c>
-      <x:c r="M118" t="str"/>
+        <x:v>通勤地铁：距离13号线西二旗站约300-380米，距离东北旺地铁站约690米，通勤非常便利；；周边配套：楼下有餐饮、员工食堂，周边咖啡、商超、健身房配套齐全，楼下停车位充足；；临近清河站（约2.1公里），周边银行网点多，满足日常金融需求，距离医院不算很近但区域医疗配套完善；</x:v>
+      </x:c>
+      <x:c r="M118" t="str">
+        <x:v>存在部分差评点：部分房型下水道异味重，部分标注有窗的房型实际窗外紧邻墙壁，无景观采光，部分房间设施存在小故障。；存在部分差评点：部分房型下水道异味重，部分标注有窗的房型实际窗外紧邻墙壁，无景观采光，部分房间设施存在小故障</x:v>
+      </x:c>
       <x:c r="N118" t="str">
-        <x:v>价格线索：13号线等; 五六环之间; 配套齐全. 28400元/㎡；配套齐全. 28400元/㎡；租 1-3个月 4-6个月. 1300-2300元/月；房屋质量/户型线索：隔音效果也不错。；户型设计丰富多样，以3居、4居为主，兼顾下跃与顶复户型，适配不同家庭的租住需求：三居户型面积区间240㎡-265㎡，四居户型300㎡-385㎡，顶层复式带露台，一层下跃带花园，每栋楼顶层均。；户型齐全，主打户型方正,明卫一居. 辉煌国际户型主要有43平-60平的户型方正,明卫的一居、84平-84平的户型方正,客厅朝南的二居。；生活便利线索：# 携程酒店-北京辉煌国际大厦酒店式公寓预订-北京辉煌国际大厦酒店式公寓价格、点评、电话、地址查询-【携程旅行手机版】. 1张1.5米双人床 及 1张1.8米大床. 环境位置 45 : 位置便利出行方便，离地铁口近，周边交通状况良好，去景区等出行便利. 卫生 81 : 房间干净整洁，卫生打扫细致，无异味，生活用品齐全. 设施 35 : 屋内设备齐全，设施新净，有冰箱、洗衣机等齐全设施. 环境很好。；推荐. 房间很温馨，家电齐全适合常住，离地铁口很近，前台小哥很nice，有求必应. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年火了十年，是北京湘菜必吃餐厅，店里的菜品种类丰富道道都是招牌 ✅金*钱蛋： 金*钱蛋太绝啦！；它坐落于海淀区上地十街1号院5号楼8层818，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；配套齐全. 28400元/㎡. 6月挂牌均价. 暂无. 在售房源. 34套. 在租房源.。；1、【出租】昌平 回龙观 珠江摩尔国际大厦辉煌国际交通便利. 面积：166m² 租金：1.71元/m²/天 1. 房屋2室1厅2卫珠江摩尔位于昌平八达岭高速北清路出口辛庄桥西北角，北清。</x:v>
+        <x:v>价格线索：1室开间（40-48㎡）约5000元/月；面积办公户型（200㎡左右）约1.3万-1.5万/月；佣金一般为2%月租金，停车位价格150-300元/月；房屋质量/户型线索：大面积办公户型（200㎡左右）约1.3万-1.5万/月，押一付三或押一付一，佣金一般为2%月租金，停车位价格150-300元/月，入住需固定押金¥100；；房龄：该公寓2017年开业，房龄较新；；户型：主打40-48㎡开间，1室0厅1卫，部分房型落地窗采光好，空间宽敞，带独立厨卫；；装修：多为精装修，风格简约大气，家具家电齐全，多数房间干净整洁；；隔音：多数住客评价隔音效果较好；；生活便利线索：通勤地铁：距离13号线西二旗站约300-380米，距离东北旺地铁站约690米，通勤非常便利；；周边配套：楼下有餐饮、员工食堂，周边咖啡、商超、健身房配套齐全，楼下停车位充足；；临近清河站（约2.1公里），周边银行网点多，满足日常金融需求，距离医院不算很近但区域医疗配套完善；；风险线索：存在部分差评点：部分房型下水道异味重，部分标注有窗的房型实际窗外紧邻墙壁，无景观采光，部分房间设施存在小故障。；存在部分差评点：部分房型下水道异味重，部分标注有窗的房型实际窗外紧邻墙壁，无景观采光，部分房间设施存在小故障</x:v>
       </x:c>
       <x:c r="O118" t="str">
-        <x:v>1. 北京辉煌国际大厦酒店式公寓 - 携程 https://m.ctrip.com/html5/hotel/hoteldetail/10928485.html
-2. 北京辉煌国际公寓二手房 https://beijing.anjuke.com/community/view/52686
-3. 北京壹号院 - 北京酒店式公寓租房网 https://www.gongyuzufang.com/beijing/29.cshtml
-4. 北京酒店式公寓-出租（长租、短租、月租）-北京服务式公寓预订网 https://www.yudinggongyu.com
-5. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu</x:v>
+        <x:v>1. ["西二旗地铁丨辉煌国际丨106平260平丨24h空调精装送免租","https://bj.sydc.anjuke.com/xzl-zu/7170199381/?houseid=4119958040423430&amp;legoHuiDu=0&amp;pt=1&amp;uniqid=9f9f01457b534b1893f553b6bff26c18&amp;zhidingLegoHuiDu=0"]
+2. ["北京辉煌国际大厦酒店式公寓","https://hotels.ctrip.com/hotels/10928485.html?sid=463781"]
+3. ["辉煌国际公寓，上地租房，13号线西二旗地铁口 上地十街辉煌国际开间 紧邻百度小米快手，海淀租房","http://m.anjuke.com/bj/rent/2466184272600076-3/"]
+4. ["【北京吉祥屋公寓(上地十街分店)】图片详情","https://m.map.360.cn/m/album/detail/pid=3095f14d0312f0ba"]
+5. 【多图】西二旗地铁丨辉煌国际丨106平260平丨24h空调精装送免租 https://bj.sydc.anjuke.com/xzl-zu/7170199381/?houseid=4119958040423430&amp;legoHuiDu=0&amp;pt=1&amp;uniqid=9f9f01457b534b1893f553b6bff26c18&amp;zhidingLegoHuiDu=0
+6. 【北京吉祥屋公寓(上地十街分店)】图片详情 https://m.map.360.cn/m/album/detail/pid=3095f14d0312f0ba
+7. 北京辉煌国际大厦酒店式公寓 https://hotels.ctrip.com/hotels/10928485.html?sid=463781
+8. 北京市海淀区上地街道上地十街1号院周边酒店,酒店价格,房间查询,在线预订 https://m.city8.com/bj/cater/886l658219ptb99857_address_hotel</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -6078,37 +6390,44 @@
         <x:v>融泽家园西2号院8号楼</x:v>
       </x:c>
       <x:c r="E119" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F119" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G119" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H119" t="n">
-        <x:v>7</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="I119" t="str">
-        <x:v>位于新龙泽附近，租金价格亲民，生活配套齐全，适合预算有限且通勤要求适中的租客。</x:v>
+        <x:v>价格相对亲民且生活配套全，但距离网易较远，且缺乏该公寓具体的独立租金证据。</x:v>
       </x:c>
       <x:c r="J119" t="str">
-        <x:v>沙路19号院,宜居之所交通便捷配套全. 3100元/月</x:v>
-      </x:c>
-      <x:c r="K119" t="str"/>
+        <x:v>家园西2号院合租单间月租大致为1300-1600元/月</x:v>
+      </x:c>
+      <x:c r="K119" t="str">
+        <x:v>公寓位于融泽家园西2号院，该小区2014年交付，房龄约12年；；小区户型以一居、两居、三居为主，由长城物业提供服务；；用户评价公寓房间干净整洁，精装修，设施齐全，通风好；；但小区本身存在楼上楼下隔音效果不理想的问题；</x:v>
+      </x:c>
       <x:c r="L119" t="str">
-        <x:v>北京市昌平区顺沙路19号院,宜居之所交通便捷配套全. 3100元/月 1室1厅整租. 昌平- 顺沙路19号院. 周边配套齐交通便利采光好全装全配。</x:v>
-      </x:c>
-      <x:c r="M119" t="str"/>
+        <x:v>戎尚精品公寓(北京积水潭医院新龙泽院店) 火山联网搜索汇总。；周边融泽家园西2号院合租单间月租大致为1300-1600元/月，目前公开渠道未找到该公寓单独的月租定价，信息参考周边同地段合租房源价格，多为押一付一，无中介费；；交通：距离18号线龙泽西地铁站约1.2公里，距离13号线龙泽站约2公里，周边有670、681等多路公交，临近京藏高速，通勤便利；；商超：步行东200米即到永辉超市，小区门口50米为美食街，配套餐饮齐全；；医院：步行到北京积水潭医院新龙泽院区不到10分钟，看病非常方便；</x:v>
+      </x:c>
+      <x:c r="M119" t="str">
+        <x:v>未找到明确的差评信息。；未找到明确的差评信息</x:v>
+      </x:c>
       <x:c r="N119" t="str">
-        <x:v>价格线索：沙路19号院,宜居之所交通便捷配套全. 3100元/月；生活便利线索：北京市昌平区顺沙路19号院,宜居之所交通便捷配套全. 3100元/月 1室1厅整租. 昌平- 顺沙路19号院. 周边配套齐交通便利采光好全装全配。</x:v>
+        <x:v>价格线索：家园西2号院合租单间月租大致为1300-1600元/月；房屋质量/户型线索：公寓位于融泽家园西2号院，该小区2014年交付，房龄约12年；；小区户型以一居、两居、三居为主，由长城物业提供服务；；用户评价公寓房间干净整洁，精装修，设施齐全，通风好；；但小区本身存在楼上楼下隔音效果不理想的问题；；生活便利线索：戎尚精品公寓(北京积水潭医院新龙泽院店) 火山联网搜索汇总。；周边融泽家园西2号院合租单间月租大致为1300-1600元/月，目前公开渠道未找到该公寓单独的月租定价，信息参考周边同地段合租房源价格，多为押一付一，无中介费；；交通：距离18号线龙泽西地铁站约1.2公里，距离13号线龙泽站约2公里，周边有670、681等多路公交，临近京藏高速，通勤便利；；商超：步行东200米即到永辉超市，小区门口50米为美食街，配套餐饮齐全；；医院：步行到北京积水潭医院新龙泽院区不到10分钟，看病非常方便；；风险线索：未找到明确的差评信息。；未找到明确的差评信息</x:v>
       </x:c>
       <x:c r="O119" t="str">
-        <x:v>1. 北京昌平租房信息 - 58同城 http://mob.58.com/zf/hk-changping
-2. 北京市昌平区租房 - 房天下 http://www.fang.com/houses/zf_253758bj
-3. 昌平租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/changping
-4. 北京精装公寓出租信息 - 链家 https://m.lianjia.com/chuzu/bj/apartment/amp4amp6
-5. 北京酒店式公寓-出租（长租、短租、月租）-北京服务式公寓预订网 https://www.yudinggongyu.com</x:v>
+        <x:v>1. ["戎尚精品公寓（北京积水潭医院新龙泽院店）","https://hotels.corporatetravel.ctrip.com/hotels/120177379.html"]
+2. ["融泽嘉园西2号院怎么样，好不好","http://m.anjuke.com/bj/community/910759/jiedu-476584814/"]
+3. ["积水潭个人租房","https://m.fang.com/houses/zf_259748_bj/p1h1/"]
+4. 可押一付一无中介费 步行18号线龙泽西直达软件园 http://m.anjuke.com/haining/rent/4571081835523075-3/
+5. 融泽嘉园西2号院怎么样，好不好 http://m.anjuke.com/bj/community/910759/jiedu-476584814/
+6. 戎尚精品公寓（北京积水潭医院新龙泽院店） https://hotels.corporatetravel.ctrip.com/hotels/120177379.html
+7. 融泽嘉园西2号院二手房怎么样|房源评论_北京我爱我家 https://m.5i5j.com/bj/ershoufang/brokerlists/504254338.html
+8. 【积水潭个人租房 https://m.fang.com/houses/zf_259748_bj/p1h1/</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -6125,37 +6444,44 @@
         <x:v>上地十街1号院辉煌国际3号楼</x:v>
       </x:c>
       <x:c r="E120" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F120" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G120" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H120" t="n">
-        <x:v>8</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I120" t="str">
-        <x:v>坐落于上地十街，复式户型且精装修，交通极便，适合追求品质与通勤效率的网易员工。</x:v>
-      </x:c>
-      <x:c r="J120" t="str"/>
+        <x:v>位于西二旗核心地段，通勤便利度极高，户型选择多样，但需确认是否支持长期租赁。</x:v>
+      </x:c>
+      <x:c r="J120" t="str">
+        <x:v>大厦内，住宅户型月租参考：约4300元-5000元/月；8元/㎡·天，大面积办公月租约1.4万-10万/月</x:v>
+      </x:c>
       <x:c r="K120" t="str">
-        <x:v>... 国际随时看房. 面积：160m² 租金：1.77元/m²/天. 房源描述：此房属于上下户型 ... 辉煌国际广场位于海淀区上地信息产业基地北区5号地，上地十街1号院。；隔音效果也不错。；户型齐全，主打户型方正,明卫一居. 辉煌国际户型主要有43平-60平的户型方正,明卫的一居、84平-84平的户型方正,客厅朝南的二居。；户型： 1室1厅1卫;；装修： 精装修;</x:v>
+        <x:v>该公寓位于辉煌国际大厦内，住宅户型月租参考：约4300元-5000元/月，40-50平米左右小户型为主；；辉煌国际大厦本身为成熟综合体，该公寓有精装修、简单装修可选，主力为40-50平米一居、80-110平米两居，LOFT户型层高可达6.6米可分隔；；物业为辉煌物业，配备高速电梯、中央空调、24小时安保，住客评价整体卫生干净，房间宽敞设施齐全，未发现明确隔音差评。；大厦建成于2000年后，房龄约20余年。</x:v>
       </x:c>
       <x:c r="L120" t="str">
-        <x:v>交通状况。；# 携程酒店-北京辉煌国际大厦酒店式公寓预订-北京辉煌国际大厦酒店式公寓价格、点评、电话、地址查询-【携程旅行手机版】. 1张1.5米双人床 及 1张1.8米大床. 环境位置 45 : 位置便利出行方便，离地铁口近，周边交通状况良好，去景区等出行便利. 卫生 81 : 房间干净整洁，卫生打扫细致，无异味，生活用品齐全. 设施 35 : 屋内设备齐全，设施新净，有冰箱、洗衣机等齐全设施. 环境很好。；推荐. 房间很温馨，家电齐全适合常住，离地铁口很近，前台小哥很nice，有求必应. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年火了十年，是北京湘菜必吃餐厅，店里的菜品种类丰富道道都是招牌 ✅金*钱蛋： 金*钱蛋太绝啦！；它坐落于海淀区上地十街1号院5号楼8层818，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；成熟商业环境，周边高科技企业林立。</x:v>
-      </x:c>
-      <x:c r="M120" t="str"/>
+        <x:v>通勤便利，步行约3分钟可达13号线/昌平线西二旗站（约400米），步行约700米可达东北旺站；；地下一层就是美食街，周边有超市发超市、西二旗益民商城、昌发展万科广场，距离北京积水潭医院新龙泽院区仅1.3公里，配套药店、餐饮商超齐全，生活便利度高。</x:v>
+      </x:c>
+      <x:c r="M120" t="str">
+        <x:v>物业为辉煌物业，配备高速电梯、中央空调、24小时安保，住客评价整体卫生干净，房间宽敞设施齐全，未发现明确隔音差评。；部分搜索结果为辉煌国际整体房源信息，针对王1976公寓的专门差评较少，未找到该公寓专属的大量租房负面反馈，存在信息泛化情况，不排除部分房源为日租/短租公寓而非长租的混淆可能。</x:v>
+      </x:c>
       <x:c r="N120" t="str">
-        <x:v>房屋质量/户型线索：... 国际随时看房. 面积：160m² 租金：1.77元/m²/天. 房源描述：此房属于上下户型 ... 辉煌国际广场位于海淀区上地信息产业基地北区5号地，上地十街1号院。；隔音效果也不错。；户型齐全，主打户型方正,明卫一居. 辉煌国际户型主要有43平-60平的户型方正,明卫的一居、84平-84平的户型方正,客厅朝南的二居。；户型： 1室1厅1卫;；装修： 精装修;；生活便利线索：交通状况。；# 携程酒店-北京辉煌国际大厦酒店式公寓预订-北京辉煌国际大厦酒店式公寓价格、点评、电话、地址查询-【携程旅行手机版】. 1张1.5米双人床 及 1张1.8米大床. 环境位置 45 : 位置便利出行方便，离地铁口近，周边交通状况良好，去景区等出行便利. 卫生 81 : 房间干净整洁，卫生打扫细致，无异味，生活用品齐全. 设施 35 : 屋内设备齐全，设施新净，有冰箱、洗衣机等齐全设施. 环境很好。；推荐. 房间很温馨，家电齐全适合常住，离地铁口很近，前台小哥很nice，有求必应. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年火了十年，是北京湘菜必吃餐厅，店里的菜品种类丰富道道都是招牌 ✅金*钱蛋： 金*钱蛋太绝啦！；它坐落于海淀区上地十街1号院5号楼8层818，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；成熟商业环境，周边高科技企业林立。</x:v>
+        <x:v>价格线索：大厦内，住宅户型月租参考：约4300元-5000元/月；8元/㎡·天，大面积办公月租约1.4万-10万/月；房屋质量/户型线索：该公寓位于辉煌国际大厦内，住宅户型月租参考：约4300元-5000元/月，40-50平米左右小户型为主；；辉煌国际大厦本身为成熟综合体，该公寓有精装修、简单装修可选，主力为40-50平米一居、80-110平米两居，LOFT户型层高可达6.6米可分隔；；物业为辉煌物业，配备高速电梯、中央空调、24小时安保，住客评价整体卫生干净，房间宽敞设施齐全，未发现明确隔音差评。；大厦建成于2000年后，房龄约20余年。；生活便利线索：通勤便利，步行约3分钟可达13号线/昌平线西二旗站（约400米），步行约700米可达东北旺站；；地下一层就是美食街，周边有超市发超市、西二旗益民商城、昌发展万科广场，距离北京积水潭医院新龙泽院区仅1.3公里，配套药店、餐饮商超齐全，生活便利度高。；风险线索：物业为辉煌物业，配备高速电梯、中央空调、24小时安保，住客评价整体卫生干净，房间宽敞设施齐全，未发现明确隔音差评。；部分搜索结果为辉煌国际整体房源信息，针对王1976公寓的专门差评较少，未找到该公寓专属的大量租房负面反馈，存在信息泛化情况，不排除部分房源为日租/短租公寓而非长租的混淆可能。</x:v>
       </x:c>
       <x:c r="O120" t="str">
-        <x:v>1. 辉煌国际大厦 - 北京写字楼 http://www.haoyuzaixian.com/a38
-2. 北京辉煌国际大厦酒店式公寓 - 携程 https://m.ctrip.com/html5/hotel/hoteldetail/10928485.html
-3. 辉煌国际- 二手房，租房-北京手机房天下 https://esf.fang.com/loupan/1010124627.htm
-4. 北京王1976公寓（輝煌國際大廈店）|2026年酒店推介北京人氣酒店 https://www.wingontravel.com/hotel/detail-beijing-18458447/beijing-wang1976-apartment-huihuang-international-mansion-shop
-5. 北京辉煌国际二手房|房价 - 链家 https://bj.lianjia.com/xiaoqu/1111027375017</x:v>
+        <x:v>1. ["北京王1976公寓(辉煌国际大厦店)预订价格,联系电话位置地址【携程酒店】","https://hotels.ctrip.com/hotels/dianping/18458447.html"]
+2. ["辉煌国际公寓 精装修 急租房源 电梯房","http://m.anjuke.com/bj/rent/4548456705436684-3/"]
+3. ["辉煌国际","https://www.bjhhgj.cn/index.html"]
+4. 北京王1976公寓(辉煌国际大厦店)预订价格,联系电话位置地址【携程酒店】 https://hotels.ctrip.com/hotels/dianping/18458447.html
+5. 辉煌国际 https://www.bjhhgj.cn/index.html
+6. 北京王1976公寓(辉煌国际大厦店) https://hotels.ctrip.com/hotels/18458447.html?isFull=F
+7. 辉煌国际公寓 精装修 急租房源 电梯房 http://m.anjuke.com/bj/rent/4548456705436684-3/
+8. 【多图】辉煌国际公寓，上地租房，辉煌国际公寓 可商用注册 空房基本 底子干净 价格能谈，海淀租房 https://bj.zu.anjuke.com/fangyuan/4370087130901516/</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -6172,41 +6498,43 @@
         <x:v>上地信息产业基地5号地辉煌国际3号楼5层</x:v>
       </x:c>
       <x:c r="E121" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F121" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G121" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H121" t="n">
-        <x:v>7.4</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="I121" t="str">
-        <x:v>地处西二旗核心区，环境安静且隔音佳，虽部分公开信息存在混杂，但地理位置优势明显。</x:v>
+        <x:v>地理位置优越，租金区间灵活，但部分房间设施陈旧且卫生评价一般，建议实地考察。</x:v>
       </x:c>
       <x:c r="J121" t="str">
-        <x:v>13号线等; 五六环之间; 配套齐全. 28400元/㎡；配套齐全. 28400元/㎡；同层高，不同朝向，相应价位不同）地下车位1000元/月</x:v>
+        <x:v>寓所在辉煌国际不同面积月租参考：40平约4500元/月；，52平约3500-4600元/月；，63平约5000元/月；，79平约5500元/月；，86平约7800元/月；，50平简单装修约5000元/月</x:v>
       </x:c>
       <x:c r="K121" t="str">
-        <x:v>公寓樓道乾淨整潔，同時小區內綠樹環抱、清新怡人，在這裡您不用擔心大都市的吵鬧，安靜的只有風吹。；隔音效果也不错。；户型齐全，主打户型方正,明卫一居 ... 辉煌国际户型主要有43平-60平的户型方正,明卫的一居、84平-84平的户型方正,客厅朝南的二居。；. 行政区域：北京市朝阳区东三环燕莎-朝阳公园 公寓地址：北京市朝阳区麦子店街38号. 房间数量：318（间） 户型介绍：开间、一居、两居、三居. 行政区域：北京市东城区--东二环朝阳门 公寓地址：北京市东城区朝阳门外三丰北里9号. 户型面积（平米）价格（人民币元/月）. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 400-100-1111，链家旗下长租公寓品牌及青年居住社区，是提供居住产品与生活服务的O2O互联网公司，旗下拥有自如友家、自如整租、业主直租、自如豪宅、自如寓、自如驿、自如ZSPACE等产品，为合租、整租、短租、中高端租住需求设计了多种产品形式，并提供保洁、维修、搬家等居间服务。；. 400-686-8006，房地产综合服务提供商世联行旗下出租公寓品牌，专注为解决中国房地产存量物业空置问题而生的创新平台，瞄准青年租房市场，为城市白领提供设计、质感、乐趣的居住体验。</x:v>
+        <x:v>该公寓所在辉煌国际不同面积月租参考：40平约4500元/月，52平约3500-4600元/月，63平约5000元/月，79平约5500元/月，86平约7800元/月，50平简单装修约5000元/月；；该公寓开业于2017年，多为精装修，部分房型设施老旧；；有评价提到隔音效果较好，楼道整洁，小区安静，物业管理安全有序，24小时保安巡视，出入需刷门禁卡；；房型多样，涵盖一室零厅/一室一厅等户型，部分房间大窗户采光好，部分存在设施问题如花洒固定器损坏、地漏排水不畅、浴室门关不严；；有住客评价提到部分房间设施老旧、卫生条件一般，个别设施存在损坏情况。</x:v>
       </x:c>
       <x:c r="L121" t="str">
-        <x:v>配套齐全. 28400元/㎡. 6月挂牌均价. 暂无. 在售房源. 34套. 在租房源.。；# 携程酒店-北京辉煌国际大厦酒店式公寓预订-北京辉煌国际大厦酒店式公寓价格、点评、电话、地址查询-【携程旅行手机版】. 1张1.5米双人床 及 1张1.8米大床. 环境位置 45 : 位置便利出行方便，离地铁口近，周边交通状况良好，去景区等出行便利. 卫生 81 : 房间干净整洁，卫生打扫细致，无异味，生活用品齐全. 设施 35 : 屋内设备齐全，设施新净，有冰箱、洗衣机等齐全设施. 环境很好。；推荐. 房间很温馨，家电齐全适合常住，离地铁口很近，前台小哥很nice，有求必应. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年火了十年，是北京湘菜必吃餐厅，店里的菜品种类丰富道道都是招牌 ✅金*钱蛋： 金*钱蛋太绝啦！；它坐落于海淀区上地十街1号院5号楼8层818，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；. 北京雅诗阁来福士中心服务公寓位于北京交通枢纽东直门。</x:v>
+        <x:v>位置位于海淀区上地信息产业基地，步行到13号线/昌平线西二旗地铁站约380-400米，到东北旺地铁站约670-770米，紧邻百度、快手总部，到中关村软件园步行约10分钟，通勤非常便利；；周边配套完善，小区内有超市、美食广场，楼下有餐饮、银行，周边有肯德基、麦当劳等餐饮，附近有益民商城、昌发展万科广场等商超，距离清河站仅2.1公里，生活出行十分便利。</x:v>
       </x:c>
       <x:c r="M121" t="str">
-        <x:v>公寓樓道乾淨整潔，同時小區內綠樹環抱、清新怡人，在這裡您不用擔心大都市的吵鬧，安靜的只有風吹。</x:v>
+        <x:v>该公寓开业于2017年，多为精装修，部分房型设施老旧；；有差评提到房子较旧，卫生条件一般。；有住客评价提到部分房间设施老旧、卫生条件一般，个别设施存在损坏情况。</x:v>
       </x:c>
       <x:c r="N121" t="str">
-        <x:v>价格线索：13号线等; 五六环之间; 配套齐全. 28400元/㎡；配套齐全. 28400元/㎡；同层高，不同朝向，相应价位不同）地下车位1000元/月；房屋质量/户型线索：公寓樓道乾淨整潔，同時小區內綠樹環抱、清新怡人，在這裡您不用擔心大都市的吵鬧，安靜的只有風吹。；隔音效果也不错。；户型齐全，主打户型方正,明卫一居 ... 辉煌国际户型主要有43平-60平的户型方正,明卫的一居、84平-84平的户型方正,客厅朝南的二居。；. 行政区域：北京市朝阳区东三环燕莎-朝阳公园 公寓地址：北京市朝阳区麦子店街38号. 房间数量：318（间） 户型介绍：开间、一居、两居、三居. 行政区域：北京市东城区--东二环朝阳门 公寓地址：北京市东城区朝阳门外三丰北里9号. 户型面积（平米）价格（人民币元/月）. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 400-100-1111，链家旗下长租公寓品牌及青年居住社区，是提供居住产品与生活服务的O2O互联网公司，旗下拥有自如友家、自如整租、业主直租、自如豪宅、自如寓、自如驿、自如ZSPACE等产品，为合租、整租、短租、中高端租住需求设计了多种产品形式，并提供保洁、维修、搬家等居间服务。；. 400-686-8006，房地产综合服务提供商世联行旗下出租公寓品牌，专注为解决中国房地产存量物业空置问题而生的创新平台，瞄准青年租房市场，为城市白领提供设计、质感、乐趣的居住体验。；生活便利线索：配套齐全. 28400元/㎡. 6月挂牌均价. 暂无. 在售房源. 34套. 在租房源.。；# 携程酒店-北京辉煌国际大厦酒店式公寓预订-北京辉煌国际大厦酒店式公寓价格、点评、电话、地址查询-【携程旅行手机版】. 1张1.5米双人床 及 1张1.8米大床. 环境位置 45 : 位置便利出行方便，离地铁口近，周边交通状况良好，去景区等出行便利. 卫生 81 : 房间干净整洁，卫生打扫细致，无异味，生活用品齐全. 设施 35 : 屋内设备齐全，设施新净，有冰箱、洗衣机等齐全设施. 环境很好。；推荐. 房间很温馨，家电齐全适合常住，离地铁口很近，前台小哥很nice，有求必应. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年. 喜欢吃香菜菜的朋友，赶紧看过来吧‼ 潇湘阁西二旗店开业了🎉他家可是2024必吃榜餐厅，在北京开了十年火了十年，是北京湘菜必吃餐厅，店里的菜品种类丰富道道都是招牌 ✅金*钱蛋： 金*钱蛋太绝啦！；它坐落于海淀区上地十街1号院5号楼8层818，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；. 北京雅诗阁来福士中心服务公寓位于北京交通枢纽东直门。；风险线索：公寓樓道乾淨整潔，同時小區內綠樹環抱、清新怡人，在這裡您不用擔心大都市的吵鬧，安靜的只有風吹。</x:v>
+        <x:v>价格线索：寓所在辉煌国际不同面积月租参考：40平约4500元/月；，52平约3500-4600元/月；，63平约5000元/月；，79平约5500元/月；，86平约7800元/月；，50平简单装修约5000元/月；房屋质量/户型线索：该公寓所在辉煌国际不同面积月租参考：40平约4500元/月，52平约3500-4600元/月，63平约5000元/月，79平约5500元/月，86平约7800元/月，50平简单装修约5000元/月；；该公寓开业于2017年，多为精装修，部分房型设施老旧；；有评价提到隔音效果较好，楼道整洁，小区安静，物业管理安全有序，24小时保安巡视，出入需刷门禁卡；；房型多样，涵盖一室零厅/一室一厅等户型，部分房间大窗户采光好，部分存在设施问题如花洒固定器损坏、地漏排水不畅、浴室门关不严；；有住客评价提到部分房间设施老旧、卫生条件一般，个别设施存在损坏情况。；生活便利线索：位置位于海淀区上地信息产业基地，步行到13号线/昌平线西二旗地铁站约380-400米，到东北旺地铁站约670-770米，紧邻百度、快手总部，到中关村软件园步行约10分钟，通勤非常便利；；周边配套完善，小区内有超市、美食广场，楼下有餐饮、银行，周边有肯德基、麦当劳等餐饮，附近有益民商城、昌发展万科广场等商超，距离清河站仅2.1公里，生活出行十分便利。；风险线索：该公寓开业于2017年，多为精装修，部分房型设施老旧；；有差评提到房子较旧，卫生条件一般。；有住客评价提到部分房间设施老旧、卫生条件一般，个别设施存在损坏情况。</x:v>
       </x:c>
       <x:c r="O121" t="str">
-        <x:v>1. 樂港酒店式公寓(北京輝煌國際店) - 全球訂房- 易遊網 https://hotel.eztravel.com.tw/detail-beijing-1-11216751/legang-apartment-hotel-beijing-brilliant-international-store
-2. 北京輝煌國際大廈酒店式公寓 - Trip.com https://hk.trip.com/hotels/beijing-hotel-detail-10928485/bei-jing-hui-huang-guo-ji-da-sha-jiu-dian-shi-gong-yu
-3. 北京辉煌国际公寓二手房 https://beijing.anjuke.com/community/view/52686
-4. 北京辉煌国际大厦酒店式公寓 - 携程 https://m.ctrip.com/html5/hotel/hoteldetail/10928485.html
-5. 辉煌国际- 二手房，租房-北京手机房天下 https://esf.fang.com/loupan/1010124627.htm</x:v>
+        <x:v>1. 乐港酒店式公寓(北京辉煌国际店)预订价格 https://hotels.ctrip.com/hotels/dianping/11216751.html
+2. 辉煌国际公寓 1室1厅1卫 急租房源 http://m.anjuke.com/bj/rent/4373108934077447-3/
+3. 乐港酒店式公寓(北京辉煌国际店) https://hotels.ctrip.com/hotels/11216751.html?isFull=T
+4. 推荐丨辉煌.国际46平63平85平112平197平 http://m.fang.com/zf/bj/3_485869405.html
+5. 乐港酒店式公寓(北京辉煌国际店)预订价格,联系电话位置地址【携程酒店】 https://hotels.ctrip.com/hotels/dianping/11216751.html?checkin=2018-04-04&amp;checkout=2018-04-05&amp;ishotsale=1
+6. 【多图】辉煌国际公寓，上地租房，辉煌国际公寓 可商用注册 空房基本 底子干净 价格能谈，海淀租房 https://bj.zu.anjuke.com/fangyuan/4370087130901516/
+7. 北京辉煌国际大厦酒店式公寓 https://hotels.ctrip.com/hotels/10928485.html?sid=463781</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -6223,39 +6551,44 @@
         <x:v>imoma服务中心</x:v>
       </x:c>
       <x:c r="E122" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F122" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G122" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H122" t="n">
-        <x:v>5.5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I122" t="str">
-        <x:v>名称虽标榜清河站，但详细地址指向西直门，证据存在严重冲突，需警惕虚假挂牌。</x:v>
+        <x:v>靠近清河站，房龄新且物业优，通勤便利，租金与品质平衡较好。</x:v>
       </x:c>
       <x:c r="J122" t="str">
-        <x:v>面积20-56平方米，租金价格4000-7500元/月；租 1-3个月 4-6个月. 1300-2300元/月</x:v>
+        <x:v>，41-50平米户型价格多在4700元-5000元/月；，60平米户型约5200元/月；，41平米西向户型报价6000元/月</x:v>
       </x:c>
       <x:c r="K122" t="str">
-        <x:v>为您提供IMOMA简介介绍、二手房房源、房屋出租信息、房价走势、IMOMA户型图、实景图、周边配套设施、。；iMOMA 恒湿恒温新风系统东南向物业管理好. 1室1厅/68.99m²/东/iMOMA · 240万 ;；iMOMA 东北向大户型业主诚意出售中. 1室1厅/95.46m²/东北/iMOMA · 260万 ;；户型及租金：仅提供一房，面积20-56平方米，租金价格4000-7500元/月. 具体位置：海淀区文慧园西路36号. 交通：距离地铁2号线、4号线、13号线西直门站直线约1200。</x:v>
+        <x:v>一居室开间月租约4700元-6000元不等，41-50平米户型价格多在4700元-5000元/月，60平米户型约5200元/月，41平米西向户型报价6000元/月；；户型以1室1厅/开间为主，户型方正、布局合理，多数房源采光好；；房龄较新，多为精装修，部分房源为全新装修，配备齐全家具家电，支持拎包入住；；部分不临街房源安静不吵，小区整体环境安静绿化高；；物业为酒店式管理，前台24小时值班，有24小时保安，需磁卡进出，安全性高，维修响应积极；</x:v>
       </x:c>
       <x:c r="L122" t="str">
-        <x:v>它坐落于海淀区imoma服务中心，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；为您提供IMOMA简介介绍、二手房房源、房屋出租信息、房价走势、IMOMA户型图、实景图、周边配套设施、。；户型及租金：仅提供一房，面积20-56平方米，租金价格4000-7500元/月. 具体位置：海淀区文慧园西路36号. 交通：距离地铁2号线、4号线、13号线西直门站直线约1200。</x:v>
-      </x:c>
-      <x:c r="M122" t="str"/>
+        <x:v>通勤：距离昌平线/13号线清河站步行约370米，到小米科技园步行仅约10分钟，距离快手元中心骑行仅需4分钟，周边有公交配套，通勤非常便利；；配套：周边数百米内有超市、健身房、餐馆、理发店，买菜、就餐购物都方便，周边配套有医院、银行等，满足日常需求；；快递可送上门，外卖可放楼下，生活便利度高。</x:v>
+      </x:c>
+      <x:c r="M122" t="str">
+        <x:v>部分不临街房源安静不吵，小区整体环境安静绿化高；；目前公开信息中未找到明确差评，信息多来自中介房源推广，实际租房价格、房屋情况可能与推广信息存在差异；</x:v>
+      </x:c>
       <x:c r="N122" t="str">
-        <x:v>价格线索：面积20-56平方米，租金价格4000-7500元/月；租 1-3个月 4-6个月. 1300-2300元/月；房屋质量/户型线索：为您提供IMOMA简介介绍、二手房房源、房屋出租信息、房价走势、IMOMA户型图、实景图、周边配套设施、。；iMOMA 恒湿恒温新风系统东南向物业管理好. 1室1厅/68.99m²/东/iMOMA · 240万 ;；iMOMA 东北向大户型业主诚意出售中. 1室1厅/95.46m²/东北/iMOMA · 260万 ;；户型及租金：仅提供一房，面积20-56平方米，租金价格4000-7500元/月. 具体位置：海淀区文慧园西路36号. 交通：距离地铁2号线、4号线、13号线西直门站直线约1200。；生活便利线索：它坐落于海淀区imoma服务中心，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；为您提供IMOMA简介介绍、二手房房源、房屋出租信息、房价走势、IMOMA户型图、实景图、周边配套设施、。；户型及租金：仅提供一房，面积20-56平方米，租金价格4000-7500元/月. 具体位置：海淀区文慧园西路36号. 交通：距离地铁2号线、4号线、13号线西直门站直线约1200。</x:v>
+        <x:v>价格线索：，41-50平米户型价格多在4700元-5000元/月；，60平米户型约5200元/月；，41平米西向户型报价6000元/月；房屋质量/户型线索：一居室开间月租约4700元-6000元不等，41-50平米户型价格多在4700元-5000元/月，60平米户型约5200元/月，41平米西向户型报价6000元/月；；户型以1室1厅/开间为主，户型方正、布局合理，多数房源采光好；；房龄较新，多为精装修，部分房源为全新装修，配备齐全家具家电，支持拎包入住；；部分不临街房源安静不吵，小区整体环境安静绿化高；；物业为酒店式管理，前台24小时值班，有24小时保安，需磁卡进出，安全性高，维修响应积极；；生活便利线索：通勤：距离昌平线/13号线清河站步行约370米，到小米科技园步行仅约10分钟，距离快手元中心骑行仅需4分钟，周边有公交配套，通勤非常便利；；配套：周边数百米内有超市、健身房、餐馆、理发店，买菜、就餐购物都方便，周边配套有医院、银行等，满足日常需求；；快递可送上门，外卖可放楼下，生活便利度高。；风险线索：部分不临街房源安静不吵，小区整体环境安静绿化高；；目前公开信息中未找到明确差评，信息多来自中介房源推广，实际租房价格、房屋情况可能与推广信息存在差异；</x:v>
       </x:c>
       <x:c r="O122" t="str">
-        <x:v>1. IMOMA住宿公寓（北京小米科技園清河站店） | 2026最新訂房優惠 https://tw.trip.com/hotels/beijing-hotel-detail-117739924/imoma-apartment
-2. IMOMA住宿公寓（北京小米科技園清河站店） - Trip.com https://hk.trip.com/hotels/beijing-hotel-detail-117739924/imoma-apartment
-3. IMOMA住宿公寓(北京小米科技园清河站店)价格 - 携程 https://m.ctrip.com/html5/hotel/hoteldetail/117739924.html
-4. IMOMA,安宁庄西路 - 租房-北京安居客 https://beijing.anjuke.com/community/view/1075101
-5. iMOMA - 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027378370</x:v>
+        <x:v>1. ["清河站 一居室 imoma下楼就是地铁口 小米科技园恒温恒湿","http://m.anjuke.com/bj/rent/3718204805000206-3/"]
+2. ["【多图】IMOMA，上地租房，1室1厅 IMOMA，海淀租房-北京58安居客","http://m.anjuke.com/bj/rent/4573933647553547-3/"]
+3. ["北京海淀|13号线清河地铁站imoma一居室公寓转租","https://www.douban.com/group/topic/341522452/?_spm_id=MTc5ODU1Nzcw"]
+4. ["应届毕业生免押金IMOMA东向开间 民水民电恒温恒湿科技住宅","http://m.anjuke.com/bj/rent/4537081817455619-3/"]
+5. 清河站 一居室 imoma下楼就是地铁口 小米科技园恒温恒湿 http://m.anjuke.com/bj/rent/3718204805000206-3/
+6. 【多图】IMOMA，上地租房，1室1厅 IMOMA，海淀租房-北京58安居客 http://m.anjuke.com/bj/rent/4573933647553547-3/
+7. 13号线清河站公寓式开间，imoma，小米科技园快手元中心 http://m.anjuke.com/bj/rent/3453175270679559-3/
+8. 清河站imoma 恒温恒湿 采光好 13号线地铁 知春路上地 http://m.anjuke.com/bj/rent/4564457627542531-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -6272,7 +6605,7 @@
         <x:v>西二旗上地十街辉煌国际3号楼</x:v>
       </x:c>
       <x:c r="E123" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F123" t="n">
         <x:v>8</x:v>
@@ -6281,32 +6614,35 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H123" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I123" t="str">
-        <x:v>证据多为全城豪宅泛化信息，缺乏针对网易大厦周边的实质性房源线索，参考价值极低。</x:v>
+        <x:v>位于西二旗核心区，租金门槛低，配套成熟，但需注意房源信息混杂风险。</x:v>
       </x:c>
       <x:c r="J123" t="str">
-        <x:v>海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月</x:v>
+        <x:v>50平米左右，大面积办公户型约1.3万-1.5万/月；，整体辉煌国际停车位充足，停车费150-300元/月</x:v>
       </x:c>
       <x:c r="K123" t="str">
-        <x:v>. 价格为长租价，租金包含物业费、取暖费、卫星电视费、会所、每周两次入室清洁、最短租期三个月。；承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；. 3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费。；. 3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。</x:v>
+        <x:v>该公寓位于海淀区辉煌国际，租房价格区间：小户型一居室月租大概3900元-4400元，面积在30-50平米左右，大面积办公户型约1.3万-1.5万/月；；户型以一居室小户型为主，也有大面积办公空间，房源多为精装修；；部分房源标注为实体墙隔音，保证独立私人空间；；房龄未查询到明确信息；；物业方面，部分同区域房源标注物业保安二十四小时巡逻随叫随到，整体辉煌国际停车位充足，停车费150-300元/月，配套基本家电家具齐全。</x:v>
       </x:c>
       <x:c r="L123" t="str">
-        <x:v># 丽都公寓. 北京丽都公寓承诺让您在北京的生活就象在家生活一样舒适满意。；这里您将自然轻松的过渡到北京的生活方式，一个完全的国际都市化生活方式－极其豪华与便利。；周边设施798艺术区、望京商业区、颐堤港购物中心、望京SOHO。；. 建国门租房 朝阳门月租公寓 东直门月租公寓 三里屯工体短租公寓 朝阳公园租房 三元桥租房 亮马桥租房 北京协和医院东院区 望京丽都酒仙桥租房 海淀中关村租房 金融街服务公寓 大兴服务公寓. 御金台国际公寓 Serviced Apartment in Beijing 誉订服务式公寓 华商壹棠服务公寓 财富中心千禧公寓. 望悦国际社区 东方豪庭公寓 国贸公寓 佳兆业铂域行政公寓 北京嘉里公寓 国贸世纪公寓 财富中心千禧公寓 中国大饭店公馆 雅诗阁盛世博瑞服务公寓 京广中心公寓 紫檀万豪行政公寓 汇贤豪庭公寓 银都华悦公邸 世桥国贸公寓 国贸公寓 东方豪庭公寓 东方豪庭公寓 东四78号精品公寓 北京福庭酒店公寓 北京瑞吉公寓 北京三全公寓 山水广场公寓 金隅环贸国际公寓 北京光耀公寓 新金山酒店公寓 来福士服务公寓 东环广场公寓 东湖别墅 达美奥克伍德华庭公寓 佰舍工体 东迎坊公寓 达美奥克伍德雅居服务公寓 华熙国际公寓 三全公寓 北京凯宾斯基公寓 首农东苑公寓 光明公寓 亮马河公寓 缦合行政公寓 北京橡树公馆 远洋公馆服务公寓 金悦豪庭公寓 北京嘉里公寓 丽都公寓 汇贤豪庭公寓 北京丽都公寓 北京瑞吉公寓 金隅环贸国际公寓 北京东迎坊服务式公寓 国贸世纪公寓 北京嘉里公寓 金融街行政公寓 东方豪庭公寓 京广中心公寓 国贸公寓 东方广场公寓. 首页 常见问题 公寓新闻 关于我们 联系我们.。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。</x:v>
+        <x:v>物业方面，部分同区域房源标注物业保安二十四小时巡逻随叫随到，整体辉煌国际停车位充足，停车费150-300元/月，配套基本家电家具齐全。；通勤：距离昌平线/13号线西二旗站步行约380米，距离18号线东北旺站步行约770米，靠近西二旗、软件园，通勤便利；；周边配套：楼下有员工食堂，周边银行配套齐全，商超、餐饮资源丰富，满足日常需求；；位置在上地十街，靠近产业园，周边办公人流密集，生活配套完善。</x:v>
       </x:c>
       <x:c r="M123" t="str">
-        <x:v>)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。</x:v>
+        <x:v>搜索结果中存在多处同名不同位置的房源误命中（如开封新龙御都国际、驻马店御都公园河畔等），未找到专门针对“北京御都服务公寓”的直接差评和风险反馈，部分房源为第三方租赁公司运营，具体服务质量需进一步核实，信息多为辉煌国际公寓的整体租房信息，需注意是否为本项目房源。</x:v>
       </x:c>
       <x:c r="N123" t="str">
-        <x:v>价格线索：海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；房屋质量/户型线索：. 价格为长租价，租金包含物业费、取暖费、卫星电视费、会所、每周两次入室清洁、最短租期三个月。；承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；选房前，如有腾退等原因产生的房源一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；. 3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费。；. 3.承租家庭缴纳的租金中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；生活便利线索：# 丽都公寓. 北京丽都公寓承诺让您在北京的生活就象在家生活一样舒适满意。；这里您将自然轻松的过渡到北京的生活方式，一个完全的国际都市化生活方式－极其豪华与便利。；周边设施798艺术区、望京商业区、颐堤港购物中心、望京SOHO。；. 建国门租房 朝阳门月租公寓 东直门月租公寓 三里屯工体短租公寓 朝阳公园租房 三元桥租房 亮马桥租房 北京协和医院东院区 望京丽都酒仙桥租房 海淀中关村租房 金融街服务公寓 大兴服务公寓. 御金台国际公寓 Serviced Apartment in Beijing 誉订服务式公寓 华商壹棠服务公寓 财富中心千禧公寓. 望悦国际社区 东方豪庭公寓 国贸公寓 佳兆业铂域行政公寓 北京嘉里公寓 国贸世纪公寓 财富中心千禧公寓 中国大饭店公馆 雅诗阁盛世博瑞服务公寓 京广中心公寓 紫檀万豪行政公寓 汇贤豪庭公寓 银都华悦公邸 世桥国贸公寓 国贸公寓 东方豪庭公寓 东方豪庭公寓 东四78号精品公寓 北京福庭酒店公寓 北京瑞吉公寓 北京三全公寓 山水广场公寓 金隅环贸国际公寓 北京光耀公寓 新金山酒店公寓 来福士服务公寓 东环广场公寓 东湖别墅 达美奥克伍德华庭公寓 佰舍工体 东迎坊公寓 达美奥克伍德雅居服务公寓 华熙国际公寓 三全公寓 北京凯宾斯基公寓 首农东苑公寓 光明公寓 亮马河公寓 缦合行政公寓 北京橡树公馆 远洋公馆服务公寓 金悦豪庭公寓 北京嘉里公寓 丽都公寓 汇贤豪庭公寓 北京丽都公寓 北京瑞吉公寓 金隅环贸国际公寓 北京东迎坊服务式公寓 国贸世纪公寓 北京嘉里公寓 金融街行政公寓 东方豪庭公寓 京广中心公寓 国贸公寓 东方广场公寓. 首页 常见问题 公寓新闻 关于我们 联系我们.。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；风险线索：)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四。；)1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 万城华府 万柳书院 万泉新新家园 龙湖颐和原著 5居. : 10套起看 万城华府 万柳书院 大面宽 采光好 干净. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 媲美万城华府 万柳书院 户型方正 精装修平层 配套双. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 西山美庐 独栋别墅 会所接待 私密性 停车方便 档次. : 西山美庐 业主配家具 全屋大落地窗,采光好 可会所接. : 15套起看 有钥匙 万城华府+万柳书院 客厅挑空 +. : 稳定长租 新上西山美庐 独栋别墅 会所居家 家电家具. : 四季青 西山美庐 独栋别墅 随时看房 配套齐全. : 联排别墅 精装修联排 六居 独立花园私家车库 可居家. : 西四环别墅 Wehouse 诸子阶 中式豪华装 茶室. : 西山 香山清琴 独栋别墅 随时看房 业主稳定 会所. 房天下北京租房网提供超过195124套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。</x:v>
+        <x:v>价格线索：50平米左右，大面积办公户型约1.3万-1.5万/月；，整体辉煌国际停车位充足，停车费150-300元/月；房屋质量/户型线索：该公寓位于海淀区辉煌国际，租房价格区间：小户型一居室月租大概3900元-4400元，面积在30-50平米左右，大面积办公户型约1.3万-1.5万/月；；户型以一居室小户型为主，也有大面积办公空间，房源多为精装修；；部分房源标注为实体墙隔音，保证独立私人空间；；房龄未查询到明确信息；；物业方面，部分同区域房源标注物业保安二十四小时巡逻随叫随到，整体辉煌国际停车位充足，停车费150-300元/月，配套基本家电家具齐全。；生活便利线索：物业方面，部分同区域房源标注物业保安二十四小时巡逻随叫随到，整体辉煌国际停车位充足，停车费150-300元/月，配套基本家电家具齐全。；通勤：距离昌平线/13号线西二旗站步行约380米，距离18号线东北旺站步行约770米，靠近西二旗、软件园，通勤便利；；周边配套：楼下有员工食堂，周边银行配套齐全，商超、餐饮资源丰富，满足日常需求；；位置在上地十街，靠近产业园，周边办公人流密集，生活配套完善。；风险线索：搜索结果中存在多处同名不同位置的房源误命中（如开封新龙御都国际、驻马店御都公园河畔等），未找到专门针对“北京御都服务公寓”的直接差评和风险反馈，部分房源为第三方租赁公司运营，具体服务质量需进一步核实，信息多为辉煌国际公寓的整体租房信息，需注意是否为本项目房源。</x:v>
       </x:c>
       <x:c r="O123" t="str">
-        <x:v>1. 丽都公寓 https://www.yudinggongyu.com/beijing/41.cshtml
-2. 丽都公寓 - 北京酒店式公寓租房网 https://www.gongyuzufang.com/beijing/93.cshtml
-3. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/cd-haidian
-4. 中國北京10 間最佳公寓 https://www.booking.com/apartments/city/cn/beijing.zh-tw.html
-5. 北京度假短租：在北京租赁公寓 - Expedia https://www.expedia.com/cn/Beijing-Vacation-Rentals.d178237.Travel-Guide-VacationRentals</x:v>
+        <x:v>1. ["【多图】辉煌国际公寓，上地租房，可月付免押金可公积金支付近西二旗地铁站可duan租租期灵活，海淀租房","https://bj.zu.anjuke.com/fangyuan/4397027768998913?shangquan_id=1238"]
+2. ["西二旗200米15天，租期自由，店长，房租92折扣","http://m.anjuke.com/bj/rent/4591075842829324-3/"]
+3. ["西二旗，软件园，辉煌国际精装修一居室4100","http://m.anjuke.com/bj/rent/4440949077044229-3/"]
+4. ["西二旗地铁丨辉煌国际丨106平260平丨24h空调精装送免租","https://bj.sydc.anjuke.com/xzl-zu/7170199381/?houseid=4119958040423430&amp;legoHuiDu=0&amp;pt=1&amp;uniqid=9f9f01457b534b1893f553b6bff26c18&amp;zhidingLegoHuiDu=0"]
+5. 【多图】辉煌国际公寓，上地租房，可月付免押金可公积金支付近西二旗地铁站可duan租租期灵活，海淀租房 https://bj.zu.anjuke.com/fangyuan/4397027768998913?shangquan_id=1238
+6. 御都国际 市民之家旁三室好房 另有多套好房出租 http://m.anjuke.com/kf/rent/4547643698322436-3/
+7. 西二旗200米15天，租期自由，店长，房租92折扣 http://m.anjuke.com/bj/rent/4591075842829324-3/
+8. 御都公园河畔 3室2厅2卫 http://m.anjuke.com/zmd/rent/4507943073131520-2/</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -6323,39 +6659,44 @@
         <x:v>北京市海淀区上地街道上地东路上地佳园23号楼</x:v>
       </x:c>
       <x:c r="E124" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F124" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G124" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H124" t="n">
-        <x:v>6.2</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="I124" t="str">
-        <x:v>属于温泉镇保障性住房，价格极具优势且配套全，但距离网易大厦较远且有申请门槛。</x:v>
+        <x:v>临近上地地铁站，生活便利，但缺乏具体房源及价格数据，证据较弱。</x:v>
       </x:c>
       <x:c r="J124" t="str">
-        <x:v>贝壳找房北京小区大全,青年公寓参考均价:69968元/㎡；租赁期第1-2、3-4、5-6年租金分别2365元/月；、2759元/月；和3153元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月</x:v>
+        <x:v>一月租价格，周边上地佳园小区整租一居室约5700元/月；、二居室约12000-13000元/月</x:v>
       </x:c>
       <x:c r="K124" t="str">
-        <x:v>租金方面，青年公寓的租金将在备案租金价格的基础上，头两年按照六折收取，最小的户型每月折后房租约1840元（下图）。；当前位置：首页-&gt;信息公开大厅-&gt;区房管局-&gt;重点领域-&gt;保障住房-&gt;分配房源. | 索引号 | 11F/2026-19918 | 公开责任部门 | 区房管局 |. | 生成日期 | 2026年04月08日 10:00 | 公开日期 | 2026年04月08日 10:00 |. | 附件 | 附件1.保障性租赁住房专项配租平台APP操作手册.pdf 附件2.保障性租赁住房专项配租平台WEB操作手册.pdf 附件3.项目基本情况介绍.zip 附件4.社保缴纳材料查询步骤.doc 附件5.承诺书.docx |. 租金单价包含家具家电使用费、物业费,不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；项目大致情况见下表：. 租金单价包含家具家电使用费、物业费,不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准. 为落实《北京市关于加快发展保障性租赁住房的实施方案》（京政办发〔2022〕9 号），保障性租赁住房主要用于缓解在本市无房的新市民、青年人等群体住房问题，重点保障新毕业大学生等群体。</x:v>
+        <x:v>未查询到该公寓具体的房龄、隔音、户型等直接评价信息，地址所在的上地佳园小区物业为北京亿方物业管理有限责任公司，周边同类青年公寓多为精装修，可拎包入住，暂无该公寓房屋质量的公开评价。</x:v>
       </x:c>
       <x:c r="L124" t="str">
-        <x:v>国内普通高等学校毕业生提供学历证书或《教育部学历证书电子注册备案表》、学位证书或《中国高等教育学位在线验证报告》；；如2026年1月1日（含）以后毕业的毕业生尚未取得学历、学位证书的，可先行提供《毕业生就业推荐表》（信息应清晰完整并加盖学校公章）或《教育部学籍在线验证报告》；；配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。；下一步，海淀区“两区”建设将进一步筑巢引凤、服务人才，不断完善自贸试验区周边配套设施，全力打造青年人才宜居宜业环境，吸引更多国际优秀创新人才来到海淀、扎根海淀。</x:v>
-      </x:c>
-      <x:c r="M124" t="str"/>
+        <x:v>搜索结果未直接匹配到该公寓明确的统一月租价格，周边上地佳园小区整租一居室约5700元/月、二居室约12000-13000元/月，暂无该公寓官方报价信息。；未查询到该公寓具体的房龄、隔音、户型等直接评价信息，地址所在的上地佳园小区物业为北京亿方物业管理有限责任公司，周边同类青年公寓多为精装修，可拎包入住，暂无该公寓房屋质量的公开评价。；地址位于海淀区上地街道，靠近13号线上地地铁站（步行约300米），周边有上地佳园等多个公交站点，公交线路丰富；；周边配套齐全，涵盖餐饮、商超、银行、医疗等生活设施，通勤出行十分便利。</x:v>
+      </x:c>
+      <x:c r="M124" t="str">
+        <x:v>未找到该公寓直接的口碑评价与差评信息，信息较为泛化。</x:v>
+      </x:c>
       <x:c r="N124" t="str">
-        <x:v>价格线索：贝壳找房北京小区大全,青年公寓参考均价:69968元/㎡；租赁期第1-2、3-4、5-6年租金分别2365元/月；、2759元/月；和3153元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；房屋质量/户型线索：租金方面，青年公寓的租金将在备案租金价格的基础上，头两年按照六折收取，最小的户型每月折后房租约1840元（下图）。；当前位置：首页-&gt;信息公开大厅-&gt;区房管局-&gt;重点领域-&gt;保障住房-&gt;分配房源. | 索引号 | 11F/2026-19918 | 公开责任部门 | 区房管局 |. | 生成日期 | 2026年04月08日 10:00 | 公开日期 | 2026年04月08日 10:00 |. | 附件 | 附件1.保障性租赁住房专项配租平台APP操作手册.pdf 附件2.保障性租赁住房专项配租平台WEB操作手册.pdf 附件3.项目基本情况介绍.zip 附件4.社保缴纳材料查询步骤.doc 附件5.承诺书.docx |. 租金单价包含家具家电使用费、物业费,不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；项目大致情况见下表：. 租金单价包含家具家电使用费、物业费,不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准. 为落实《北京市关于加快发展保障性租赁住房的实施方案》（京政办发〔2022〕9 号），保障性租赁住房主要用于缓解在本市无房的新市民、青年人等群体住房问题，重点保障新毕业大学生等群体。；生活便利线索：国内普通高等学校毕业生提供学历证书或《教育部学历证书电子注册备案表》、学位证书或《中国高等教育学位在线验证报告》；；如2026年1月1日（含）以后毕业的毕业生尚未取得学历、学位证书的，可先行提供《毕业生就业推荐表》（信息应清晰完整并加盖学校公章）或《教育部学籍在线验证报告》；；配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。；下一步，海淀区“两区”建设将进一步筑巢引凤、服务人才，不断完善自贸试验区周边配套设施，全力打造青年人才宜居宜业环境，吸引更多国际优秀创新人才来到海淀、扎根海淀。</x:v>
+        <x:v>价格线索：一月租价格，周边上地佳园小区整租一居室约5700元/月；、二居室约12000-13000元/月；房屋质量/户型线索：未查询到该公寓具体的房龄、隔音、户型等直接评价信息，地址所在的上地佳园小区物业为北京亿方物业管理有限责任公司，周边同类青年公寓多为精装修，可拎包入住，暂无该公寓房屋质量的公开评价。；生活便利线索：搜索结果未直接匹配到该公寓明确的统一月租价格，周边上地佳园小区整租一居室约5700元/月、二居室约12000-13000元/月，暂无该公寓官方报价信息。；未查询到该公寓具体的房龄、隔音、户型等直接评价信息，地址所在的上地佳园小区物业为北京亿方物业管理有限责任公司，周边同类青年公寓多为精装修，可拎包入住，暂无该公寓房屋质量的公开评价。；地址位于海淀区上地街道，靠近13号线上地地铁站（步行约300米），周边有上地佳园等多个公交站点，公交线路丰富；；周边配套齐全，涵盖餐饮、商超、银行、医疗等生活设施，通勤出行十分便利。；风险线索：未找到该公寓直接的口碑评价与差评信息，信息较为泛化。</x:v>
       </x:c>
       <x:c r="O124" t="str">
-        <x:v>1. 海淀推近千套“青年公寓” 头两年租金打六折！ - 36氪 https://m.36kr.com/p/3322984450484737
-2. 关于开展海淀区2026年青年公寓配租意向登记的公告 https://zyk.bjhd.gov.cn/jbdt/auto4522_51806/zdly/bzzf/fpfy/202604/t20260408_4811149.shtml
-3. 青年公寓- 房价|租房【北京贝壳找房】 https://m.ke.com/bj/xiaoqu/1111027378885
-4. 2026年北京海淀区青年公寓配租意向登记公告（房源+租金+申请条件）- 北京本地宝 http://bj.bendibao.com/zffw/202648/381846.shtm
-5. 2161套！海淀区青年公寓配租意向登记即将开始——_京报网 https://news.bjd.com.cn/2026/04/08/11676360.shtml</x:v>
+        <x:v>1. ["青年公寓怎么样?北京青年公寓房价|房源|地址|户型图|周边配套详情","https://m.5i5j.com/bj/xq_news/9306.html"]
+2. ["【bookhome+青花瓷青年公寓】地址,公交指南,位置示意图,地图位置","https://bj.city8.com/hotel/886v83820w2lba694f"]
+3. ["上地佳园 正规一居室 温馨居家 出门就是地铁站","http://m.anjuke.com/bj/rent/4605346263753741-3/"]
+4. 青年公寓怎么样?北京青年公寓房价|房源|地址|户型图|周边配套详情 https://m.5i5j.com/bj/xq_news/9306.html
+5. 【上地青年公寓出租 https://m.fang.com/houses/zf_253551_bj/p6h1/
+6. 【bookhome+青花瓷青年公寓】地址,公交指南,位置示意图,地图位置,周边酒店 https://bj.city8.com/hotel/886v83820w2lba694f
+7. 上地佳园 正规一居室 温馨居家 出门就是地铁站 http://m.anjuke.com/bj/rent/4605346263753741-3/
+8. 海淀922套青年公寓配租 青年人才可拎包入住 https://zyk.bjhd.gov.cn/ywdt/hdywx/202506/t20250611_4772428.shtml?type=computer</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -6372,39 +6713,40 @@
         <x:v>北京市上地十街辉煌国际大厦</x:v>
       </x:c>
       <x:c r="E125" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F125" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G125" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H125" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="I125" t="str">
-        <x:v>位于西二旗核心地段，步行可达网易，3000元左右的租金性价比极高，通勤首选。</x:v>
+        <x:v>极近西二旗站，精装一居室性价比高，物业管理完善，非常适合大厂通勤。</x:v>
       </x:c>
       <x:c r="J125" t="str">
-        <x:v>升科技园旁独立式公寓随时看房随时入住. 3000元/月</x:v>
+        <x:v>店）不同面积月租价格区间大致为：30㎡约3900元/月；、35㎡约5000元/月；、50㎡约4800-5000元/月；部分写字楼性质房源200㎡约1.3万-1.5万/月；000米内有幼儿园，停车位充足（150-300元/月</x:v>
       </x:c>
       <x:c r="K125" t="str">
-        <x:v>户型： 2室1厅1卫 ;；装修： 简单装修 ;</x:v>
+        <x:v>1.装修：基本为精装修，部分带品牌家具家电，可拎包入住；；2.户型：多为一居室开间，独门独户，部分为实体墙，大开间落地窗，采光较好；；3.隔音：标注实体墙房源隔音较好，大开间户型隐私性尚可；；4.房龄：未查询到明确房龄信息，楼盘为辉煌国际大厦商用物业；；5.物业：部分房源标注24小时保安巡逻、监控全覆盖，有管家服务，物业按季度收取中央空调基础运行费，夏季15元/㎡/季度、冬季18元/㎡/季度，不使用无需缴纳；</x:v>
       </x:c>
       <x:c r="L125" t="str">
-        <x:v>北京辉煌国际服务式公寓(西二旗地铁站店) - 携程。；它坐落于海淀区辉煌国际3号楼722，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；清河西三旗东升科技园旁独立式公寓随时看房随时入住. 3000元/月 1室1厅整租. 海淀- 极蜂空间公寓. 交通便利周边配套齐独门独卫采光好。；. ### 公寓推荐. 建国门租房 朝阳门月租公寓 东直门月租公寓 三里屯工体短租公寓 朝阳公园租房 三元桥租房 亮马桥租房 北京协和医院东院区 望京丽都酒仙桥租房 海淀中关村租房 金融街服务公寓 大兴服务公寓. 御金台国际公寓 Serviced Apartment in Beijing 誉订服务式公寓 华商壹棠服务公寓 财富中心千禧公寓. 望悦国际社区 东方豪庭公寓 国贸公寓 佳兆业铂域行政公寓 北京嘉里公寓 国贸世纪公寓 财富中心千禧公寓 中国大饭店公馆 雅诗阁盛世博瑞服务公寓 京广中心公寓 紫檀万豪行政公寓 汇贤豪庭公寓 银都华悦公邸 世桥国贸公寓 国贸公寓 东方豪庭公寓 东方豪庭公寓 东四78号精品公寓 北京福庭酒店公寓 北京瑞吉公寓 北京三全公寓 山水广场公寓 金隅环贸国际公寓 北京光耀公寓 新金山酒店公寓 来福士服。；. ### 公寓推荐. 建国门租房 朝阳门月租公寓 东直门月租公寓 三里屯工体短租公寓 朝阳公园租房 三元桥租房 亮马桥租房 北京协和医院东院区 望京丽都酒仙桥租房 海淀中关村租房 金融街服务公寓 大兴服务公寓. 御金台国际公寓 Serviced Apartment in Beijing 誉订服务式公寓 华商壹棠服务公寓 财富中心千禧公寓. 望悦国际社区 东方豪庭公寓 国贸公寓 佳兆业铂域行政公寓 北京嘉里公寓 国贸世纪公寓 财富中心千禧公寓 中国大饭店公馆 雅诗阁盛世博瑞服务公寓 京广中心公寓 紫檀万豪行政公寓 汇贤豪庭公寓 银都华悦公邸 世桥国贸公寓 国贸公寓 东方豪庭公寓 东方豪庭公寓 东四78号精品公寓 北京福庭酒店公寓 北京瑞吉公寓 北京三全公寓 山水广场公寓 金隅环贸国际公寓 北京光耀公寓 新金山酒店公寓 来福士服务公寓 东环广场公寓 东湖别墅 达美奥克伍德华庭公寓 佰舍工体 东迎坊公寓 达美奥克伍德雅居服务公寓 华熙国际公寓 三全公寓 北京凯宾斯基公寓 首农东苑公寓 光明公寓 亮马河公寓 缦合行政公寓 北京橡树公馆 远洋公馆服务公寓 金悦豪庭公寓 北京嘉里公寓 丽都公寓 汇贤豪庭公寓 北京丽都公寓 北京瑞吉公寓 金隅环贸国际公寓 北京东迎坊服务式公寓 国贸世纪公寓 北京嘉里公寓 金融街行政公寓 东方豪庭公寓 京广中心公寓 国贸公寓 东方广场公寓. 首页 常见问题 公寓新闻 关于我们 联系我们.。</x:v>
+        <x:v>海绵公寓(西二旗地铁站店) 火山联网搜索汇总。；辉煌国际大厦内海绵公寓（西二旗地铁站店）不同面积月租价格区间大致为：30㎡约3900元/月、35㎡约5000元/月、50㎡约4800-5000元/月，支持押一付一或押一付三，部分房源无中介费，部分可谈免租期；；1.通勤地铁：距离13号线/昌平线西二旗地铁站仅100-386米，步行可达，临近百度、快手总部，通勤互联网园区便利；；2.商超餐饮：楼下B1有超市和餐饮卖场，大厦楼下有员工食堂，周边配套餐饮充足；；3.其他配套：周边1000米内有幼儿园，停车位充足（150-300元/月），民水民电，可燃气做饭，满足日常生活需求，周边无大型医院信息，小型药店配套存在。</x:v>
       </x:c>
       <x:c r="M125" t="str"/>
       <x:c r="N125" t="str">
-        <x:v>价格线索：升科技园旁独立式公寓随时看房随时入住. 3000元/月；房屋质量/户型线索：户型： 2室1厅1卫 ;；装修： 简单装修 ;；生活便利线索：北京辉煌国际服务式公寓(西二旗地铁站店) - 携程。；它坐落于海淀区辉煌国际3号楼722，附近拥有众多景点，交通便利，是商务出差和休闲度假的理想选择。；清河西三旗东升科技园旁独立式公寓随时看房随时入住. 3000元/月 1室1厅整租. 海淀- 极蜂空间公寓. 交通便利周边配套齐独门独卫采光好。；. ### 公寓推荐. 建国门租房 朝阳门月租公寓 东直门月租公寓 三里屯工体短租公寓 朝阳公园租房 三元桥租房 亮马桥租房 北京协和医院东院区 望京丽都酒仙桥租房 海淀中关村租房 金融街服务公寓 大兴服务公寓. 御金台国际公寓 Serviced Apartment in Beijing 誉订服务式公寓 华商壹棠服务公寓 财富中心千禧公寓. 望悦国际社区 东方豪庭公寓 国贸公寓 佳兆业铂域行政公寓 北京嘉里公寓 国贸世纪公寓 财富中心千禧公寓 中国大饭店公馆 雅诗阁盛世博瑞服务公寓 京广中心公寓 紫檀万豪行政公寓 汇贤豪庭公寓 银都华悦公邸 世桥国贸公寓 国贸公寓 东方豪庭公寓 东方豪庭公寓 东四78号精品公寓 北京福庭酒店公寓 北京瑞吉公寓 北京三全公寓 山水广场公寓 金隅环贸国际公寓 北京光耀公寓 新金山酒店公寓 来福士服。；. ### 公寓推荐. 建国门租房 朝阳门月租公寓 东直门月租公寓 三里屯工体短租公寓 朝阳公园租房 三元桥租房 亮马桥租房 北京协和医院东院区 望京丽都酒仙桥租房 海淀中关村租房 金融街服务公寓 大兴服务公寓. 御金台国际公寓 Serviced Apartment in Beijing 誉订服务式公寓 华商壹棠服务公寓 财富中心千禧公寓. 望悦国际社区 东方豪庭公寓 国贸公寓 佳兆业铂域行政公寓 北京嘉里公寓 国贸世纪公寓 财富中心千禧公寓 中国大饭店公馆 雅诗阁盛世博瑞服务公寓 京广中心公寓 紫檀万豪行政公寓 汇贤豪庭公寓 银都华悦公邸 世桥国贸公寓 国贸公寓 东方豪庭公寓 东方豪庭公寓 东四78号精品公寓 北京福庭酒店公寓 北京瑞吉公寓 北京三全公寓 山水广场公寓 金隅环贸国际公寓 北京光耀公寓 新金山酒店公寓 来福士服务公寓 东环广场公寓 东湖别墅 达美奥克伍德华庭公寓 佰舍工体 东迎坊公寓 达美奥克伍德雅居服务公寓 华熙国际公寓 三全公寓 北京凯宾斯基公寓 首农东苑公寓 光明公寓 亮马河公寓 缦合行政公寓 北京橡树公馆 远洋公馆服务公寓 金悦豪庭公寓 北京嘉里公寓 丽都公寓 汇贤豪庭公寓 北京丽都公寓 北京瑞吉公寓 金隅环贸国际公寓 北京东迎坊服务式公寓 国贸世纪公寓 北京嘉里公寓 金融街行政公寓 东方豪庭公寓 京广中心公寓 国贸公寓 东方广场公寓. 首页 常见问题 公寓新闻 关于我们 联系我们.。</x:v>
+        <x:v>价格线索：店）不同面积月租价格区间大致为：30㎡约3900元/月；、35㎡约5000元/月；、50㎡约4800-5000元/月；部分写字楼性质房源200㎡约1.3万-1.5万/月；000米内有幼儿园，停车位充足（150-300元/月；房屋质量/户型线索：1.装修：基本为精装修，部分带品牌家具家电，可拎包入住；；2.户型：多为一居室开间，独门独户，部分为实体墙，大开间落地窗，采光较好；；3.隔音：标注实体墙房源隔音较好，大开间户型隐私性尚可；；4.房龄：未查询到明确房龄信息，楼盘为辉煌国际大厦商用物业；；5.物业：部分房源标注24小时保安巡逻、监控全覆盖，有管家服务，物业按季度收取中央空调基础运行费，夏季15元/㎡/季度、冬季18元/㎡/季度，不使用无需缴纳；；生活便利线索：海绵公寓(西二旗地铁站店) 火山联网搜索汇总。；辉煌国际大厦内海绵公寓（西二旗地铁站店）不同面积月租价格区间大致为：30㎡约3900元/月、35㎡约5000元/月、50㎡约4800-5000元/月，支持押一付一或押一付三，部分房源无中介费，部分可谈免租期；；1.通勤地铁：距离13号线/昌平线西二旗地铁站仅100-386米，步行可达，临近百度、快手总部，通勤互联网园区便利；；2.商超餐饮：楼下B1有超市和餐饮卖场，大厦楼下有员工食堂，周边配套餐饮充足；；3.其他配套：周边1000米内有幼儿园，停车位充足（150-300元/月），民水民电，可燃气做饭，满足日常生活需求，周边无大型医院信息，小型药店配套存在。</x:v>
       </x:c>
       <x:c r="O125" t="str">
-        <x:v>1. 北京辉煌国际服务式公寓(西二旗地铁站店) - 携程 https://m.ctrip.com/html5/hotel/hoteldetail/11211875.html
-2. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-3. 海淀区 - 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/amp6amp4ama0
-4. 西三旗公寓出租 - 房天下 http://www.fang.com/houses/zf_260066bj
-5. 北京海淀酒店公寓租房信息|海淀服务公寓出租|-北京誉订服务公寓网 https://www.yudinggongyu.com/beijing?aid=3</x:v>
+        <x:v>1. 【多图】西二旗地铁丨辉煌国际丨106平260平丨24h空调精装送免租 https://bj.sydc.anjuke.com/xzl-zu/7170199381/?houseid=4119958040423430&amp;legoHuiDu=0&amp;pt=1&amp;uniqid=9f9f01457b534b1893f553b6bff26c18&amp;zhidingLegoHuiDu=0
+2. 西二旗地铁旁一居室4800/月房东直租无中介费 https://www.douban.com/group/topic/334144182/?_spm_id=MTYxNTEzMDg5
+3. 西二旗200米15天，租期自由，店长，房租92折扣 http://m.anjuke.com/bj/rent/4591075842829324-3/
+4. 西二旗 上地通勤 品质公寓 无中介 民水民电 实体墙 可月付 http://m.anjuke.com/bj/rent/4588042784660489-3/
+5. 整租西二旗丨优选榜丨通勤百度丨免费停车丨免租期20天 http://m.anjuke.com/ch/rent/4545880065088524-3/
+6. 通勤西二旗 一居室 采光好家 电齐全 押一付一 近地铁 http://m.anjuke.com/bj/rent/4529449147704325-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -6421,7 +6763,7 @@
         <x:v>回龙观镇回龙观村东</x:v>
       </x:c>
       <x:c r="E126" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F126" t="n">
         <x:v>8</x:v>
@@ -6430,32 +6772,35 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H126" t="n">
-        <x:v>7.2</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="I126" t="str">
-        <x:v>临近龙泽站通勤便利，租金适中且配套齐全，但部分楼栋临近高速有噪音干扰。</x:v>
+        <x:v>临近龙泽站通勤便利，价格适中且配套齐全，但缺乏真实口碑且存在信息泛化风险。</x:v>
       </x:c>
       <x:c r="J126" t="str">
-        <x:v>地铁龙泽苑东区三家三卫主卧独卫带阳台. 2800元/月</x:v>
+        <x:v>站附近相似公寓整租价格：一居约2800-4600元/月；，两居约5000-5700元/月；，合租次卧约1500-1900元/月</x:v>
       </x:c>
       <x:c r="K126" t="str">
-        <x:v>缺点：一期有两限房，品质残次不齐，且居住密度较大；；二期、三期有的楼临高速，会有噪音问题，另外就是三期环境比较小。；北京新龙城现有149套房源在租，昌平-回龙观新龙城最新租房信息， ... 18㎡ | 南| 昌平回龙观. 近地铁精装修押一付一 · 合租·新龙城3室2厅南卧. 1750。；通勤西二旗近临地铁精装修物业内部有超市智能家居 - 北京租房。；通勤西二旗近临地铁精装修物业内部有超市智能家居 · 户型： 1室0厅1卫 · 装修： 精装修 · 面积： 30平米 · 朝向： 南 · 楼层： 低层(共6层) · 类型： 集中式公寓.。</x:v>
+        <x:v>无该公寓官方房龄公开信息，同区域该类公寓多为精装修，配备全新品牌家电；；户型多为一居独厨独卫或两居室，部分为实体墙；；公开信息中同位置类似房源标注隔音较好，楼道有24小时监控，提供管家安保、免费维修服务，装修以简约精装为主；</x:v>
       </x:c>
       <x:c r="L126" t="str">
-        <x:v>13号线龙泽地铁龙泽苑东区三家三卫主卧独卫带阳台. 2800元/月 3室1厅合租主卧. 昌平- 龙泽苑东区. 交通便利周边配套齐采光好全装全配。；地铁出行方便，附近有地铁13号线的龙泽站。；北京新龙城现有149套房源在租，昌平-回龙观新龙城最新租房信息， ... 18㎡ | 南| 昌平回龙观. 近地铁精装修押一付一 · 合租·新龙城3室2厅南卧. 1750。；通勤西二旗近临地铁精装修物业内部有超市智能家居 - 北京租房。；通勤西二旗近临地铁精装修物业内部有超市智能家居 · 户型： 1室0厅1卫 · 装修： 精装修 · 面积： 30平米 · 朝向： 南 · 楼层： 低层(共6层) · 类型： 集中式公寓.。</x:v>
+        <x:v>福龙精品公寓(回龙观龙泽地铁站店) 火山联网搜索汇总。；公开渠道未查询到该公寓明确统一月租价格，同区域龙泽地铁站附近相似公寓整租价格：一居约2800-4600元/月，两居约5000-5700元/月，合租次卧约1500-1900元/月，普遍支持押一付一，部分房源可月付无押金，部分收取10%左右每月服务费；；位置临近13号线龙泽、回龙观地铁站，通勤到西二旗等商圈方便；；周边有美廉美超市、华联商厦等商超，小区门口有多家餐饮店铺，周边配套菜市场、药店、快递站，满足日常需求；；暂无近距离大型医院信息，基础生活配套完善；</x:v>
       </x:c>
       <x:c r="M126" t="str">
-        <x:v>二期、三期有的楼临高速，会有噪音问题，另外就是三期环境比较小。</x:v>
+        <x:v>本次搜索未找到该公寓专属的直接口碑评价，搜索结果多为同区域其他小区房源，存在同名异地房源（厦门湖里区福龙公寓）误命中情况，公开信息中无该公寓明确的差评披露，信息匹配度较低，存在信息泛化风险。；本次搜索未找到该公寓专属的直接口碑评价，搜索结果多为同区域其他小区房源，存在同名异地房源（厦门湖里区福龙公寓）误命中情况，公开信息中无该公寓明确的差评披露，信息匹配度较低，存在信息泛化风险</x:v>
       </x:c>
       <x:c r="N126" t="str">
-        <x:v>价格线索：地铁龙泽苑东区三家三卫主卧独卫带阳台. 2800元/月；房屋质量/户型线索：缺点：一期有两限房，品质残次不齐，且居住密度较大；；二期、三期有的楼临高速，会有噪音问题，另外就是三期环境比较小。；北京新龙城现有149套房源在租，昌平-回龙观新龙城最新租房信息， ... 18㎡ | 南| 昌平回龙观. 近地铁精装修押一付一 · 合租·新龙城3室2厅南卧. 1750。；通勤西二旗近临地铁精装修物业内部有超市智能家居 - 北京租房。；通勤西二旗近临地铁精装修物业内部有超市智能家居 · 户型： 1室0厅1卫 · 装修： 精装修 · 面积： 30平米 · 朝向： 南 · 楼层： 低层(共6层) · 类型： 集中式公寓.。；生活便利线索：13号线龙泽地铁龙泽苑东区三家三卫主卧独卫带阳台. 2800元/月 3室1厅合租主卧. 昌平- 龙泽苑东区. 交通便利周边配套齐采光好全装全配。；地铁出行方便，附近有地铁13号线的龙泽站。；北京新龙城现有149套房源在租，昌平-回龙观新龙城最新租房信息， ... 18㎡ | 南| 昌平回龙观. 近地铁精装修押一付一 · 合租·新龙城3室2厅南卧. 1750。；通勤西二旗近临地铁精装修物业内部有超市智能家居 - 北京租房。；通勤西二旗近临地铁精装修物业内部有超市智能家居 · 户型： 1室0厅1卫 · 装修： 精装修 · 面积： 30平米 · 朝向： 南 · 楼层： 低层(共6层) · 类型： 集中式公寓.。；风险线索：二期、三期有的楼临高速，会有噪音问题，另外就是三期环境比较小。</x:v>
+        <x:v>价格线索：站附近相似公寓整租价格：一居约2800-4600元/月；，两居约5000-5700元/月；，合租次卧约1500-1900元/月；房屋质量/户型线索：无该公寓官方房龄公开信息，同区域该类公寓多为精装修，配备全新品牌家电；；户型多为一居独厨独卫或两居室，部分为实体墙；；公开信息中同位置类似房源标注隔音较好，楼道有24小时监控，提供管家安保、免费维修服务，装修以简约精装为主；；生活便利线索：福龙精品公寓(回龙观龙泽地铁站店) 火山联网搜索汇总。；公开渠道未查询到该公寓明确统一月租价格，同区域龙泽地铁站附近相似公寓整租价格：一居约2800-4600元/月，两居约5000-5700元/月，合租次卧约1500-1900元/月，普遍支持押一付一，部分房源可月付无押金，部分收取10%左右每月服务费；；位置临近13号线龙泽、回龙观地铁站，通勤到西二旗等商圈方便；；周边有美廉美超市、华联商厦等商超，小区门口有多家餐饮店铺，周边配套菜市场、药店、快递站，满足日常需求；；暂无近距离大型医院信息，基础生活配套完善；；风险线索：本次搜索未找到该公寓专属的直接口碑评价，搜索结果多为同区域其他小区房源，存在同名异地房源（厦门湖里区福龙公寓）误命中情况，公开信息中无该公寓明确的差评披露，信息匹配度较低，存在信息泛化风险。；本次搜索未找到该公寓专属的直接口碑评价，搜索结果多为同区域其他小区房源，存在同名异地房源（厦门湖里区福龙公寓）误命中情况，公开信息中无该公寓明确的差评披露，信息匹配度较低，存在信息泛化风险</x:v>
       </x:c>
       <x:c r="O126" t="str">
-        <x:v>1. 龙泽租房公寓- 北京 - 房天下 http://www.fang.com/houses/zf_252053bj
-2. 北京精装公寓出租信息 https://ifeng-m.lianjia.com/chuzu/bj/apartment/huilongguan2/rmp5amp0ama0ama4
-3. 北京昌平回龙观租房信息 - 58同城 http://mob.58.com/zf/cq-huilongguan
-4. 北京买房|昌平回龙观第一梯队小区看房测评 - 知乎专栏 https://zhuanlan.zhihu.com/p/30704615096
-5. 回龙观,北京新龙城租房、合租、整租、出租信息 - 幸福里 https://m.xflapp.com/zufang/neighbor-house-list/bj-7567356414159863827.html</x:v>
+        <x:v>1. ["回龙观龙泽精装全南两居室 http://m.anjuke.com/bj/rent/4288044667956228-3/"]
+2. ["0押金月付回龙观，龙泽地铁站，集中供暖，民水民电，精装一居 https://bj.zu.anjuke.com/fangyuan/4329315605339136?is_auction=1&amp;shangquan_id=6898"]
+3. ["带阳台完整独立房间 回龙观龙泽苑东区 地铁13号线龙泽站 下车即到 无任何中介费 房主直租 https://www.douban.com/group/topic/486713568/?_spm_id=MjU4NTY2OTAz"]
+4. ["福龙公寓(湖里)房屋品质怎么样，好不好 http://m.anjuke.com/xm/community/352508/jiedu-4779788-fwpz/"]
+5. 回龙观龙泽精装全南两居室 http://m.anjuke.com/bj/rent/4288044667956228-3/
+6. 物业0中介回龙观精装公寓独厨独卫押一付一实体墙隔音好 http://m.anjuke.com/bj/rent/3673739279278083-3/
+7. 带阳台完整独立房间 回龙观龙泽苑东区 地铁13号线龙泽站 下车即到 无任何中介费 房主直租 https://www.douban.com/group/topic/486713568/?_spm_id=MjU4NTY2OTAz
+8. 回龙观地铁站50米 可以养宠物 物业0中介 压一付一 http://m.anjuke.com/bj/rent/4513226048695306-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -6472,39 +6817,40 @@
         <x:v>北京市昌平区龙域中街回龙观村-西区西北侧</x:v>
       </x:c>
       <x:c r="E127" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F127" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G127" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H127" t="n">
-        <x:v>5.5</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I127" t="str">
-        <x:v>证据混杂了大量非本区域信息，回龙观周边房源虽价格低廉但真实品质存疑。</x:v>
-      </x:c>
-      <x:c r="J127" t="str">
-        <x:v>... 昌平-回龙观 流星花园三区 1500元/月；同层高，不同朝向，相应价位不同）地下车位1000元/月</x:v>
-      </x:c>
+        <x:v>距离网易大厦近，配套盒马及医院，精装整租性价比高，需确认商业产权性质。</x:v>
+      </x:c>
+      <x:c r="J127" t="str"/>
       <x:c r="K127" t="str">
-        <x:v>独卫一居带健身房繁华城景简约轻奢邻地铁押一付一配套齐全精装修. 花都廣場3室1厅1卫. 13800元3室1厅·50㎡. 邻地铁配套齐全精装修南北通透. 昌平合租房. 该条件下房源较。；. 行政区域：北京市朝阳区东三环燕莎-朝阳公园 公寓地址：北京市朝阳区麦子店街38号. 房间数量：318（间） 户型介绍：开间、一居、两居、三居. 行政区域：北京市东城区--东二环朝阳门 公寓地址：北京市东城区朝阳门外三丰北里9号. 户型面积（平米）价格（人民币元/月）. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 400-100-1111，链家旗下长租公寓品牌及青年居住社区，是提供居住产品与生活服务的O2O互联网公司，旗下拥有自如友家、自如整租、业主直租、自如豪宅、自如寓、自如驿、自如ZSPACE等产品，为合租、整租、短租、中高端租住需求设计了多种产品形式，并提供保洁、维修、搬家等居间服务。；. 400-686-8006，房地产综合服务提供商世联行旗下出租公寓品牌，专注为解决中国房地产存量物业空置问题而生的创新平台，瞄准青年租房市场，为城市白领提供设计、质感、乐趣的居住体验。；. 房间数量：407（间） 户型介绍：一居、两居、三居、四居. 以上价位区间为（同以面积，不同层高，不同朝向，相应价位不同）地下车位1000元/月。；. 租金价格包含：会所、物业管理费、供暖、宽带、wifi/卫星电视、水费、电费、每周2次保洁。</x:v>
+        <x:v>月租区间为2500元-4300元，主流1室1厅1卫（30平米朝南户型）月租3500元，押一付一，无中介费、服务费，整租为主。；户型：多为1室1厅1卫方正户型，采光通透，南北通透；；装修：精装修，家电齐全（冰箱、洗衣机、空调、智能门锁等配套齐全）；；未找到明确房龄、隔音、物业负面信息，标注为物业直签。</x:v>
       </x:c>
       <x:c r="L127" t="str">
-        <x:v>独卫一居带健身房繁华城景简约轻奢邻地铁押一付一配套齐全精装修. 花都廣場3室1厅1卫. 13800元3室1厅·50㎡. 邻地铁配套齐全精装修南北通透. 昌平合租房. 该条件下房源较。；... 昌平-回龙观 流星花园三区 1500元/月. 距8号线-平西府站917m. 昌平-回龙观 流星花园三区出租房源图片 8号线平西府流星花园三区南向主卧带卫生间配套全采光佳 3室1厅 20m²。；. 北京雅诗阁来福士中心服务公寓位于北京交通枢纽东直门。；作为北京来福士中心综合体的一部分，公寓坐享商场和写字楼的优势，为住客提供集餐饮、购物、休闲、文化、商务为一体的多元化生活方式。；地铁2号线、13号线和机场线在此交汇，为您的出行带来了极大的便利。</x:v>
-      </x:c>
-      <x:c r="M127" t="str"/>
+        <x:v>装修：精装修，家电齐全（冰箱、洗衣机、空调、智能门锁等配套齐全）；；通勤距离：距离18号线龙泽西地铁站约1公里，13号线/昌平线西二旗站约1.3公里，步行可达，楼下100米有多个公交线路；；距离龙域中心1公里，西二旗中关村软件园2公里，通勤上地、五道口、朱辛庄等产业区便利；；商超：600米到昌发展万科广场，500米到乐惠万家超市，700米到盒马鲜生；；医院：600米到积水潭医院龙泽院区；</x:v>
+      </x:c>
+      <x:c r="M127" t="str">
+        <x:v>餐饮：未明确差评，周边配套能满足日常餐饮需求；；未找到明确差评/风险信息，部分房源归属为回龙观新村西区商业楼，需进一步确认房源产权性质。</x:v>
+      </x:c>
       <x:c r="N127" t="str">
-        <x:v>价格线索：... 昌平-回龙观 流星花园三区 1500元/月；同层高，不同朝向，相应价位不同）地下车位1000元/月；房屋质量/户型线索：独卫一居带健身房繁华城景简约轻奢邻地铁押一付一配套齐全精装修. 花都廣場3室1厅1卫. 13800元3室1厅·50㎡. 邻地铁配套齐全精装修南北通透. 昌平合租房. 该条件下房源较。；. 行政区域：北京市朝阳区东三环燕莎-朝阳公园 公寓地址：北京市朝阳区麦子店街38号. 房间数量：318（间） 户型介绍：开间、一居、两居、三居. 行政区域：北京市东城区--东二环朝阳门 公寓地址：北京市东城区朝阳门外三丰北里9号. 户型面积（平米）价格（人民币元/月）. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 400-100-1111，链家旗下长租公寓品牌及青年居住社区，是提供居住产品与生活服务的O2O互联网公司，旗下拥有自如友家、自如整租、业主直租、自如豪宅、自如寓、自如驿、自如ZSPACE等产品，为合租、整租、短租、中高端租住需求设计了多种产品形式，并提供保洁、维修、搬家等居间服务。；. 400-686-8006，房地产综合服务提供商世联行旗下出租公寓品牌，专注为解决中国房地产存量物业空置问题而生的创新平台，瞄准青年租房市场，为城市白领提供设计、质感、乐趣的居住体验。；. 房间数量：407（间） 户型介绍：一居、两居、三居、四居. 以上价位区间为（同以面积，不同层高，不同朝向，相应价位不同）地下车位1000元/月。；. 租金价格包含：会所、物业管理费、供暖、宽带、wifi/卫星电视、水费、电费、每周2次保洁。；生活便利线索：独卫一居带健身房繁华城景简约轻奢邻地铁押一付一配套齐全精装修. 花都廣場3室1厅1卫. 13800元3室1厅·50㎡. 邻地铁配套齐全精装修南北通透. 昌平合租房. 该条件下房源较。；... 昌平-回龙观 流星花园三区 1500元/月. 距8号线-平西府站917m. 昌平-回龙观 流星花园三区出租房源图片 8号线平西府流星花园三区南向主卧带卫生间配套全采光佳 3室1厅 20m²。；. 北京雅诗阁来福士中心服务公寓位于北京交通枢纽东直门。；作为北京来福士中心综合体的一部分，公寓坐享商场和写字楼的优势，为住客提供集餐饮、购物、休闲、文化、商务为一体的多元化生活方式。；地铁2号线、13号线和机场线在此交汇，为您的出行带来了极大的便利。</x:v>
+        <x:v>房屋质量/户型线索：月租区间为2500元-4300元，主流1室1厅1卫（30平米朝南户型）月租3500元，押一付一，无中介费、服务费，整租为主。；户型：多为1室1厅1卫方正户型，采光通透，南北通透；；装修：精装修，家电齐全（冰箱、洗衣机、空调、智能门锁等配套齐全）；；未找到明确房龄、隔音、物业负面信息，标注为物业直签。；生活便利线索：装修：精装修，家电齐全（冰箱、洗衣机、空调、智能门锁等配套齐全）；；通勤距离：距离18号线龙泽西地铁站约1公里，13号线/昌平线西二旗站约1.3公里，步行可达，楼下100米有多个公交线路；；距离龙域中心1公里，西二旗中关村软件园2公里，通勤上地、五道口、朱辛庄等产业区便利；；商超：600米到昌发展万科广场，500米到乐惠万家超市，700米到盒马鲜生；；医院：600米到积水潭医院龙泽院区；；风险线索：餐饮：未明确差评，周边配套能满足日常餐饮需求；；未找到明确差评/风险信息，部分房源归属为回龙观新村西区商业楼，需进一步确认房源产权性质。</x:v>
       </x:c>
       <x:c r="O127" t="str">
-        <x:v>1. 北京昌平租房信息 - 58同城 http://mob.58.com/zf/hk-changping
-2. 昌平租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/changping
-3. 北京精装公寓出租信息 - 链家 https://m.lianjia.com/chuzu/bj/apartment/changpingqu/amp0
-4. 2025年北京酒店式公寓+长租公寓百科-租房指南，深度解析 https://www.gongyuzufang.com/blog/1376.cshtml
-5. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/huilongguan2</x:v>
+        <x:v>1. 实拍 实际2 5 0 0起一月 没中J费 真实房源18号线 http://m.anjuke.com/ch/rent/4594304111893514-3/
+2. 观庭精品公寓 物业直签 无中介 家电齐全 http://m.anjuke.com/bj/rent/4504847688510472-3/
+3. 建发观堂府 四居双卫 客厅面宽6米 高楼层 有车位 看房方便 https://m.58.com/bj/zufang/86986334770781x.shtml
+4. 2026上海观庭小区，配套指南，买房攻略 https://sh.esf.fang.com/loupan/1210160750/strategy.htm
+5. 实拍 昌平高端公寓 全屋智能 带投影 近地铁 可月付 http://m.anjuke.com/bj/rent/4397336304116742-3/
+6. 观庭 精装修 阳光充足 南北通透 http://m.anjuke.com/sh/rent/4490360794979339-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -6521,39 +6867,40 @@
         <x:v>北京市上地十街1号院5号楼</x:v>
       </x:c>
       <x:c r="E128" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F128" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G128" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H128" t="n">
-        <x:v>8.2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I128" t="str">
-        <x:v>位置优越紧邻西二旗，高品质青年公寓且有租金补贴，适合符合条件的应届生。</x:v>
-      </x:c>
-      <x:c r="J128" t="str">
-        <x:v>租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月</x:v>
-      </x:c>
+        <x:v>租金极具优势，适合低预算人群，但空间较小且装修简单，步行至地铁站稍远。</x:v>
+      </x:c>
+      <x:c r="J128" t="str"/>
       <x:c r="K128" t="str">
-        <x:v>租金方面，青年公寓的租金将在备案租金价格的基础上，头两年按照六折收取，最小的户型每月折后房租约1840元（下图）。；. 项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准. 为落实《北京市关于加快发展保障性租赁住房的实施方案》（京政办发〔2022〕9 号），保障性租赁住房主要用于缓解在本市无房的新市民、青年人等群体住房问题，重点保障新毕业大学生等群体。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。</x:v>
+        <x:v>暂未找到该门店明确的房龄、隔音、物业评价；；周边同类型公寓多为20㎡以内单间/1室0厅简单装修，户型偏小，配套基本家具家电，部分公寓存在隔音不佳的反馈；</x:v>
       </x:c>
       <x:c r="L128" t="str">
-        <x:v>... 西站店). 2025年开业|洗衣房|免费客房WiFi|可做饭. 详情·设施. 4.6很好. 197条. “交通很方便，离北京西站很近”. 距北京西站地铁站步行510米,约8分钟. 海淀区羊坊店路18号.。；项目配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间。；国内普通高等学校毕业生提供学历、学位证书和《教育部学历证书电子注册备案表》、《中国高等教育学位在线验证报告》，留学人员提供教育部学历认证机构认证的《国外学历学位认证书》，如2025年应届毕业生尚未取得学历学位证明，可先行提供《毕业生就业推荐表》以及承诺书(见附件4);；整租·皂君庙·青年公寓·1室·1厅. 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校. 海淀皂君庙双安青年公寓 1室1厅 41.7㎡ 650. 相寓 皂君庙·青年公寓·中楼层·1居室. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |. | | 常州租房 | **H** | 杭州租房 | | 宁波租房 | | 石家庄租房 | **Z** | 郑州租房 |.。；配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。</x:v>
+        <x:v>米果青年公寓(北京西二旗地铁站店) 火山联网搜索汇总。；西二旗周边同类型青年公寓单间月租多在1000-2200元区间，多数支持押一付一，无中介费，部分房源含水卫费60元/月、管理费2元/天；；周边同类型公寓多为20㎡以内单间/1室0厅简单装修，户型偏小，配套基本家具家电，部分公寓存在隔音不佳的反馈；；该门店位于海淀区上地十街，距离西二旗地铁站步行约1.7公里，周边靠近13号线、昌平线西二旗站，18号线上地软件园站，通勤到西二旗、上地软件园较为便利；；区域内有百度、快手等产业园，周边商超餐饮配套成熟，距离清河医院等医疗机构不远；</x:v>
       </x:c>
       <x:c r="M128" t="str"/>
       <x:c r="N128" t="str">
-        <x:v>价格线索：租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；房屋质量/户型线索：租金方面，青年公寓的租金将在备案租金价格的基础上，头两年按照六折收取，最小的户型每月折后房租约1840元（下图）。；. 项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准. 为落实《北京市关于加快发展保障性租赁住房的实施方案》（京政办发〔2022〕9 号），保障性租赁住房主要用于缓解在本市无房的新市民、青年人等群体住房问题，重点保障新毕业大学生等群体。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；生活便利线索：... 西站店). 2025年开业|洗衣房|免费客房WiFi|可做饭. 详情·设施. 4.6很好. 197条. “交通很方便，离北京西站很近”. 距北京西站地铁站步行510米,约8分钟. 海淀区羊坊店路18号.。；项目配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间。；国内普通高等学校毕业生提供学历、学位证书和《教育部学历证书电子注册备案表》、《中国高等教育学位在线验证报告》，留学人员提供教育部学历认证机构认证的《国外学历学位认证书》，如2025年应届毕业生尚未取得学历学位证明，可先行提供《毕业生就业推荐表》以及承诺书(见附件4);；整租·皂君庙·青年公寓·1室·1厅. 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校. 海淀皂君庙双安青年公寓 1室1厅 41.7㎡ 650. 相寓 皂君庙·青年公寓·中楼层·1居室. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |. | | 常州租房 | **H** | 杭州租房 | | 宁波租房 | | 石家庄租房 | **Z** | 郑州租房 |.。；配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。</x:v>
+        <x:v>房屋质量/户型线索：暂未找到该门店明确的房龄、隔音、物业评价；；周边同类型公寓多为20㎡以内单间/1室0厅简单装修，户型偏小，配套基本家具家电，部分公寓存在隔音不佳的反馈；；生活便利线索：米果青年公寓(北京西二旗地铁站店) 火山联网搜索汇总。；西二旗周边同类型青年公寓单间月租多在1000-2200元区间，多数支持押一付一，无中介费，部分房源含水卫费60元/月、管理费2元/天；；周边同类型公寓多为20㎡以内单间/1室0厅简单装修，户型偏小，配套基本家具家电，部分公寓存在隔音不佳的反馈；；该门店位于海淀区上地十街，距离西二旗地铁站步行约1.7公里，周边靠近13号线、昌平线西二旗站，18号线上地软件园站，通勤到西二旗、上地软件园较为便利；；区域内有百度、快手等产业园，周边商超餐饮配套成熟，距离清河医院等医疗机构不远；</x:v>
       </x:c>
       <x:c r="O128" t="str">
-        <x:v>1. 北京可寓青年公寓(北京西站店) - 携程 https://m.ctrip.com/html5/hotel/hoteldetail/131797552.html
-2. 2161套北京海淀青年公寓启动配租租金打六折-36氪 https://m.36kr.com/p/3760404621754887
-3. 海淀推近千套“青年公寓”头两年租金打六折 https://h5.ifeng.com/c/vivoArticle/v002oTDgMK7Vqsq9UbTt6B8KeNB88WGL6JPE3koM9VtPxOw__?isNews=1&amp;showComments=0
-4. 西三旗租房 - 58同城 https://mob.58.com/zf/bj-xisanqi
-5. 北京海淀区青年公寓地址在哪里?项目介绍- 北京本地宝 http://bj.bendibao.com/zffw/202566/373174.shtm</x:v>
+        <x:v>1. ["西二旗千元整租小窝告别合租地铁直达","http://m.anjuke.com/dongyang/rent/4511958162697220-3/"]
+2. ["雷军官宣小米青年公寓 应届生优先入住","https://3g.china.com/act/news/10000169/20250703/48552778.html"]
+3. ["西二旗千元租房近百度快手押一付一配套全随时住","http://m.anjuke.com/dongyang/rent/4511955000826885-3/"]
+4. 西二旗千元整租小窝告别合租地铁直达 http://m.anjuke.com/dongyang/rent/4511958162697220-3/
+5. 雷军官宣小米青年公寓 应届生优先入住 https://3g.china.com/act/news/10000169/20250703/48552778.html
+6. 西二旗千元租房近百度快手押一付一配套全随时住 http://m.anjuke.com/dongyang/rent/4511955000826885-3/
+7. 丰岭路26号米果公寓 南北通透 55平 家电齐全 随时看房 https://m.58.com/hz/zufang/82254407296605x.shtml
+8. 独立单间西二旗租房无中适合实习生，交通便利 配套齐全随时入住 http://m.anjuke.com/bj/rent/4519035653217284-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -6570,35 +6917,42 @@
         <x:v>永旺家园四区</x:v>
       </x:c>
       <x:c r="E129" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F129" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G129" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H129" t="n">
-        <x:v>0</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="I129" t="str">
-        <x:v>网页证据指向武汉地区房源，与北京网易大厦租房需求完全无关，不予推荐。</x:v>
+        <x:v>位于成熟住宅区，环境安保较好，通勤永丰及软件园便利，但需额外支付服务费。</x:v>
       </x:c>
       <x:c r="J129" t="str"/>
-      <x:c r="K129" t="str"/>
+      <x:c r="K129" t="str">
+        <x:v>整租1室户型（约45㎡）月租约4300-4350元，合租单间（约20㎡）月租约2100元，无中介费，部分房源需收取一次性服务费（租金6%或租金80%），支持押一付一、短签；；永旺家园四区为普通住宅小区，该公寓房源多为精装修，户型有整租1室0厅/1室1厅、合租单间，格局较为方正合理；；小区为低密度社区，绿化率约30%，物业管理完善，治安较好；；暂未查询到该公寓具体房龄及隔音负面反馈，小区本身为成熟社区，无明确老旧质量问题反馈；；暂未找到该公寓隔音、物业的明确针对性评价。</x:v>
+      </x:c>
       <x:c r="L129" t="str">
-        <x:v>无中介8号线短租整租一居室竹叶山地铁口可直达黄埔路武汉天地. 900 · 1室1厅·35㎡ ;</x:v>
-      </x:c>
-      <x:c r="M129" t="str"/>
+        <x:v>通勤：距离地铁16号线永丰南站步行约930米，紧邻用友软件园、中关村软件园，适合周边上班族，通勤便利；；周边配套：楼下商超、菜市场、餐饮、银行等生活设施齐全，日常购物买菜就餐便捷，未查询到近距离大型医院的明确信息；</x:v>
+      </x:c>
+      <x:c r="M129" t="str">
+        <x:v>暂未查询到该公寓具体房龄及隔音负面反馈，小区本身为成熟社区，无明确老旧质量问题反馈；；未查询到专属「北京薇薇妈公寓(4号店)」的直接口碑差评，搜索结果多为永旺家园四区的通用租房房源信息，存在同名误命中或信息泛化风险；</x:v>
+      </x:c>
       <x:c r="N129" t="str">
-        <x:v>生活便利线索：无中介8号线短租整租一居室竹叶山地铁口可直达黄埔路武汉天地. 900 · 1室1厅·35㎡ ;</x:v>
+        <x:v>房屋质量/户型线索：整租1室户型（约45㎡）月租约4300-4350元，合租单间（约20㎡）月租约2100元，无中介费，部分房源需收取一次性服务费（租金6%或租金80%），支持押一付一、短签；；永旺家园四区为普通住宅小区，该公寓房源多为精装修，户型有整租1室0厅/1室1厅、合租单间，格局较为方正合理；；小区为低密度社区，绿化率约30%，物业管理完善，治安较好；；暂未查询到该公寓具体房龄及隔音负面反馈，小区本身为成熟社区，无明确老旧质量问题反馈；；暂未找到该公寓隔音、物业的明确针对性评价。；生活便利线索：通勤：距离地铁16号线永丰南站步行约930米，紧邻用友软件园、中关村软件园，适合周边上班族，通勤便利；；周边配套：楼下商超、菜市场、餐饮、银行等生活设施齐全，日常购物买菜就餐便捷，未查询到近距离大型医院的明确信息；；风险线索：暂未查询到该公寓具体房龄及隔音负面反馈，小区本身为成熟社区，无明确老旧质量问题反馈；；未查询到专属「北京薇薇妈公寓(4号店)」的直接口碑差评，搜索结果多为永旺家园四区的通用租房房源信息，存在同名误命中或信息泛化风险；</x:v>
       </x:c>
       <x:c r="O129" t="str">
-        <x:v>1. 海淀区 - 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/amp6amp4ama0
-2. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-3. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian
-4. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/wh-haidian
-5. 北京租房攻略｜租房价格｜朝阳｜海淀｜东城｜昌平｜合租｜整租 ... https://www.wellcee.com/beijing/m/rent-apartment</x:v>
+        <x:v>1. ["永旺家园四区 西向开间 精装公寓式 实拍图啥都不缺 可住2人","http://m.anjuke.com/ch/rent/4467739625200646-3/"]
+2. ["永旺家园(四区) 1室1厅1卫 房屋维修 电梯房","http://m.anjuke.com/bj/rent/4602870136105999-3/"]
+3. ["实图实价 现房有钥匙 可办居住证 提供房本","https://bj.zu.anjuke.com/fangyuan/4421770009619456"]
+4. 永旺家园四区 西向开间 精装公寓式 实拍图啥都不缺 可住2人 http://m.anjuke.com/ch/rent/4467739625200646-3/
+5. 你是说 https://www.douban.com/group/topic/332138266/?_spm_id=MjgwNzUzODM0
+6. 永旺家园(四区) 1室1厅1卫 房屋维修 电梯房 http://m.anjuke.com/bj/rent/4602870136105999-3/
+7. 公寓被租客弄得满地垃圾难下脚，马桶满是排泄物！房东：头一回遇到这种事|齐鲁晚报·齐鲁壹点|北京市|女士|洗手台|生活垃圾_新浪新闻 https://k.sina.cn/article_5328858693_v13d9fee4502002cbdy.html
+8. 实图实价 现房有钥匙 可办居住证 提供房本 https://bj.zu.anjuke.com/fangyuan/4421770009619456</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -6615,7 +6969,7 @@
         <x:v>北京市海淀区安宁庄西二条IMOMA</x:v>
       </x:c>
       <x:c r="E130" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F130" t="n">
         <x:v>8</x:v>
@@ -6624,32 +6978,35 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H130" t="n">
-        <x:v>6.2</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I130" t="str">
-        <x:v>户型通透但临近高速有噪音，租金较高，配套信息多为泛化描述，建议实地确认。</x:v>
+        <x:v>离清河站近，通勤极便，2011年精装小区，配套成熟且采光好，是高性价比之选。</x:v>
       </x:c>
       <x:c r="J130" t="str">
-        <x:v> 3室2厅176㎡. 20000元/月；3室2厅176㎡. 20000元/月；租 1-3个月 4-6个月. 1300-2300元/月</x:v>
+        <x:v>小区，小区内出租房源：41平米朝南一居室5500元/月；，45平米朝东一居室开间5000元/月；，同区域两居室大致5500-6270元/月</x:v>
       </x:c>
       <x:c r="K130" t="str">
-        <x:v>缺点：西边两个楼临近京新高速，会有噪音影响，大家可以注意下。；小区户型多样，板楼多为两居室的小户型，南北通透，居住舒适；；塔楼多数为两居室和三居室。</x:v>
+        <x:v>小区楼龄：IMOMA小区建筑年代约为2011年，房源均为精装修，户型以一居开间、一居室为主，部分两居室，多带电梯，高楼层采光好无潮湿；；暂未找到明确隔音评价，小区车位充足，绿化率较高。</x:v>
       </x:c>
       <x:c r="L130" t="str">
-        <x:v>## 高端公寓. ### 公寓推荐. 建国门租房 朝阳门月租公寓 东直门月租公寓 三里屯工体短租公寓 朝阳公园租房 三元桥租房 亮马桥租房 北京协和医院东院区 望京丽都酒仙桥租房 海淀中关村租房 金融街服务公寓 大兴服务公寓. 御金台国际公寓 Serviced Apartment in Beijing 誉订服务式公寓 华商壹棠服务公寓 财富中心千禧公寓. 望悦国际社区 东方豪庭公寓 国贸公寓 佳兆业铂域行政公寓 北京嘉里公寓 国贸世纪公寓 财富中心千禧公寓 中国大饭店公馆 雅诗阁盛世博瑞服务公寓 京广中心公寓 紫檀万豪行政公寓 汇贤豪庭公寓 银都华悦公邸 世桥国贸公寓 国贸公寓 东方豪庭公寓 东方豪庭公寓 东四78号精品公寓 北京福庭酒店公寓 北京瑞吉公寓 北京三全公寓 山水广场公寓 金隅环贸国际公寓 北京光耀公寓 新金山酒店公寓 来福士服务公寓 东环广场公寓 东湖别墅 达美奥克伍德华庭公寓 佰舍工体 东迎坊公寓 达美奥克伍德雅居服务公寓 华熙国际公寓 三全公寓 北京凯宾斯基公寓 首农东苑公寓 光明公寓 亮马河公寓 缦合行政公寓 北京橡树公馆 远洋公馆服务公寓 金悦豪庭公寓 北京嘉里公。；## 高端公寓. ### 公寓推荐. 建国门租房 朝阳门月租公寓 东直门月租公寓 三里屯工体短租公寓 朝阳公园租房 三元桥租房 亮马桥租房 北京协和医院东院区 望京丽都酒仙桥租房 海淀中关村租房 金融街服务公寓 大兴服务公寓. 御金台国际公寓 Serviced Apartment in Beijing 誉订服务式公寓 华商壹棠服务公寓 财富中心千禧公寓. 望悦国际社区 东方豪庭公寓 国贸公寓 佳兆业铂域行政公寓 北京嘉里公寓 国贸世纪公寓 财富中心千禧公寓 中国大饭店公馆 雅诗阁盛世博瑞服务公寓 京广中心公寓 紫檀万豪行政公寓 汇贤豪庭公寓 银都华悦公邸 世桥国贸公寓 国贸公寓 东方豪庭公寓 东方豪庭公寓 东四78号精品公寓 北京福庭酒店公寓 北京瑞吉公寓 北京三全公寓 山水广场公寓 金隅环贸国际公寓 北京光耀公寓 新金山酒店公寓 来福士服务公寓 东环广场公寓 东湖别墅 达美奥克伍德华庭公寓 佰舍工体 东迎坊公寓 达美奥克伍德雅居服务公寓 华熙国际公寓 三全公寓 北京凯宾斯基公寓 首农东苑公寓 光明公寓 亮马河公寓 缦合行政公寓 北京橡树公馆 远洋公馆服务公寓 金悦豪庭公寓 北京嘉里公寓 丽都公寓 汇贤豪庭公寓 北京丽都公寓 北京瑞吉公寓 金隅环贸国际公寓 北京东迎坊服务式公寓 国贸世纪公寓 北京嘉里公寓 金融街行政公寓 东方豪庭公寓 京广中心公寓 国贸公寓 东方广场公寓. 首页 常见问题 公寓新闻 关于我们 联系我们.</x:v>
+        <x:v>通勤地铁：距离昌平线/13号线清河站约370米，步行可达，周边多个公交站，有多条公交线路，靠近G7，通勤便利；；商超：小区内有超市，门口就有生活超市，步行可达生鲜超市，距离北京沁春汇购物中心约1.3公里；；周边有安宁庄公园、上地公园等休闲场所，餐饮配套丰富，周边距离社区医院较近，整体生活便利程度高。</x:v>
       </x:c>
       <x:c r="M130" t="str">
-        <x:v>缺点：西边两个楼临近京新高速，会有噪音影响，大家可以注意下。</x:v>
+        <x:v>小区楼龄：IMOMA小区建筑年代约为2011年，房源均为精装修，户型以一居开间、一居室为主，部分两居室，多带电梯，高楼层采光好无潮湿；；搜索结果中找到的租房价格均为IMOMA小区房源，未找到颜社公寓本身专属租房的直接差评信息，部分房源信息为中介发布，价格可能存在浮动，存在中介费用/服务费差异；</x:v>
       </x:c>
       <x:c r="N130" t="str">
-        <x:v>价格线索： 3室2厅176㎡. 20000元/月；3室2厅176㎡. 20000元/月；租 1-3个月 4-6个月. 1300-2300元/月；房屋质量/户型线索：缺点：西边两个楼临近京新高速，会有噪音影响，大家可以注意下。；小区户型多样，板楼多为两居室的小户型，南北通透，居住舒适；；塔楼多数为两居室和三居室。；生活便利线索：## 高端公寓. ### 公寓推荐. 建国门租房 朝阳门月租公寓 东直门月租公寓 三里屯工体短租公寓 朝阳公园租房 三元桥租房 亮马桥租房 北京协和医院东院区 望京丽都酒仙桥租房 海淀中关村租房 金融街服务公寓 大兴服务公寓. 御金台国际公寓 Serviced Apartment in Beijing 誉订服务式公寓 华商壹棠服务公寓 财富中心千禧公寓. 望悦国际社区 东方豪庭公寓 国贸公寓 佳兆业铂域行政公寓 北京嘉里公寓 国贸世纪公寓 财富中心千禧公寓 中国大饭店公馆 雅诗阁盛世博瑞服务公寓 京广中心公寓 紫檀万豪行政公寓 汇贤豪庭公寓 银都华悦公邸 世桥国贸公寓 国贸公寓 东方豪庭公寓 东方豪庭公寓 东四78号精品公寓 北京福庭酒店公寓 北京瑞吉公寓 北京三全公寓 山水广场公寓 金隅环贸国际公寓 北京光耀公寓 新金山酒店公寓 来福士服务公寓 东环广场公寓 东湖别墅 达美奥克伍德华庭公寓 佰舍工体 东迎坊公寓 达美奥克伍德雅居服务公寓 华熙国际公寓 三全公寓 北京凯宾斯基公寓 首农东苑公寓 光明公寓 亮马河公寓 缦合行政公寓 北京橡树公馆 远洋公馆服务公寓 金悦豪庭公寓 北京嘉里公。；## 高端公寓. ### 公寓推荐. 建国门租房 朝阳门月租公寓 东直门月租公寓 三里屯工体短租公寓 朝阳公园租房 三元桥租房 亮马桥租房 北京协和医院东院区 望京丽都酒仙桥租房 海淀中关村租房 金融街服务公寓 大兴服务公寓. 御金台国际公寓 Serviced Apartment in Beijing 誉订服务式公寓 华商壹棠服务公寓 财富中心千禧公寓. 望悦国际社区 东方豪庭公寓 国贸公寓 佳兆业铂域行政公寓 北京嘉里公寓 国贸世纪公寓 财富中心千禧公寓 中国大饭店公馆 雅诗阁盛世博瑞服务公寓 京广中心公寓 紫檀万豪行政公寓 汇贤豪庭公寓 银都华悦公邸 世桥国贸公寓 国贸公寓 东方豪庭公寓 东方豪庭公寓 东四78号精品公寓 北京福庭酒店公寓 北京瑞吉公寓 北京三全公寓 山水广场公寓 金隅环贸国际公寓 北京光耀公寓 新金山酒店公寓 来福士服务公寓 东环广场公寓 东湖别墅 达美奥克伍德华庭公寓 佰舍工体 东迎坊公寓 达美奥克伍德雅居服务公寓 华熙国际公寓 三全公寓 北京凯宾斯基公寓 首农东苑公寓 光明公寓 亮马河公寓 缦合行政公寓 北京橡树公馆 远洋公馆服务公寓 金悦豪庭公寓 北京嘉里公寓 丽都公寓 汇贤豪庭公寓 北京丽都公寓 北京瑞吉公寓 金隅环贸国际公寓 北京东迎坊服务式公寓 国贸世纪公寓 北京嘉里公寓 金融街行政公寓 东方豪庭公寓 京广中心公寓 国贸公寓 东方广场公寓. 首页 常见问题 公寓新闻 关于我们 联系我们.；风险线索：缺点：西边两个楼临近京新高速，会有噪音影响，大家可以注意下。</x:v>
+        <x:v>价格线索：小区，小区内出租房源：41平米朝南一居室5500元/月；，45平米朝东一居室开间5000元/月；，同区域两居室大致5500-6270元/月；房屋质量/户型线索：小区楼龄：IMOMA小区建筑年代约为2011年，房源均为精装修，户型以一居开间、一居室为主，部分两居室，多带电梯，高楼层采光好无潮湿；；暂未找到明确隔音评价，小区车位充足，绿化率较高。；生活便利线索：通勤地铁：距离昌平线/13号线清河站约370米，步行可达，周边多个公交站，有多条公交线路，靠近G7，通勤便利；；商超：小区内有超市，门口就有生活超市，步行可达生鲜超市，距离北京沁春汇购物中心约1.3公里；；周边有安宁庄公园、上地公园等休闲场所，餐饮配套丰富，周边距离社区医院较近，整体生活便利程度高。；风险线索：小区楼龄：IMOMA小区建筑年代约为2011年，房源均为精装修，户型以一居开间、一居室为主，部分两居室，多带电梯，高楼层采光好无潮湿；；搜索结果中找到的租房价格均为IMOMA小区房源，未找到颜社公寓本身专属租房的直接差评信息，部分房源信息为中介发布，价格可能存在浮动，存在中介费用/服务费差异；</x:v>
       </x:c>
       <x:c r="O130" t="str">
-        <x:v>1. 海淀租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian
-2. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/wh-haidian
-3. 海淀区公寓出租- 北京 - 房天下 http://www.fang.com/houses/zf_252311bj
-4. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu
-5. 中国北京10大推荐公寓| Booking.com https://www.booking.com/apartments/city/cn/beijing.zh-cn.html</x:v>
+        <x:v>1. ["颜社公寓(安宁庄西二条分店)旅行指南","https://ctrip.city8.com/bj/hotel/886x20821119b492cc"]
+2. ["IMOMA精选一居室 独立开间 楼层装修很好 家的感觉","http://m.anjuke.com/bj/rent/3067763427304454-3/"]
+3. ["IMOMA 精装修 1室0厅1卫","http://m.anjuke.com/ch/rent/4555529709624332-3/"]
+4. 颜社公寓(安宁庄西二条分店)旅行指南 https://ctrip.city8.com/bj/hotel/886x20821119b492cc
+5. IMOMA精选一居室 独立开间 楼层装修很好 家的感觉 http://m.anjuke.com/bj/rent/3067763427304454-3/
+6. 0押金月付 清河上地西二旗安宁庄小米元中心精装低楼层两居室 http://m.anjuke.com/bj/rent/4524640052257796-3/
+7. IMOMA 精装修 1室0厅1卫 http://m.anjuke.com/ch/rent/4555529709624332-3/
+8. 安宁庄 带电梯 高楼层2居室 有钥匙 http://m.anjuke.com/ch/rent/4523351766934532-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -6666,39 +7023,42 @@
         <x:v>北京市昌平区龙域东一路融泽嘉园东6号院4号楼</x:v>
       </x:c>
       <x:c r="E131" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F131" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G131" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H131" t="n">
-        <x:v>5.2</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="I131" t="str">
-        <x:v>房源信息混杂且单价偏高，证据涉及多个不同区域，针对性较弱，评分保守。</x:v>
-      </x:c>
-      <x:c r="J131" t="str">
-        <x:v>在20-25平方米之间，租金约6000-7000元/月；... 昌平-回龙观 流星花园三区 1500元/月；同层高，不同朝向，相应价位不同）地下车位1000元/月</x:v>
-      </x:c>
+        <x:v>融泽嘉园新房合租，生活配套完善，但需警惕该小区个别房东恶意扣押金的风险。</x:v>
+      </x:c>
+      <x:c r="J131" t="str"/>
       <x:c r="K131" t="str">
-        <x:v>... 租金包水電上網提供剛需電器及生活用品. 10400元1室厅·140㎡. 干湿分离独卫邻地铁配套齐全精装修. 020D無隱形收費拎包入住租金包水電上網提供剛需電器及生活用品. 9900元1。；长租公寓在北京：面向青年租客、最小户型更抢手 - 界面新闻。；产品和租金水平：项目设有两种户型，面积在20-25平方米之间，租金约6000-7000元/月，房间配有独立卫生间、沙发、电视、冰箱、洗衣机等。；. 行政区域：北京市朝阳区东三环燕莎-朝阳公园 公寓地址：北京市朝阳区麦子店街38号. 房间数量：318（间） 户型介绍：开间、一居、两居、三居. 行政区域：北京市东城区--东二环朝阳门 公寓地址：北京市东城区朝阳门外三丰北里9号. 户型面积（平米）价格（人民币元/月）. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 400-100-1111，链家旗下长租公寓品牌及青年居住社区，是提供居住产品与生活服务的O2O互联网公司，旗下拥有自如友家、自如整租、业主直租、自如豪宅、自如寓、自如驿、自如ZSPACE等产品，为合租、整租、短租、中高端租住需求设计了多种产品形式，并提供保洁、维修、搬家等居间服务。；. 400-686-8006，房地产综合服务提供商世联行旗下出租公寓品牌，专注为解决中国房地产存量物业空置问题而生的创新平台，瞄准青年租房市场，为城市白领提供设计、质感、乐趣的居住体验。</x:v>
+        <x:v>房源属于融泽嘉园普通商品住宅小区，房龄较新，多为精装修，宜家/北欧风格设计，家电家具齐全拎包入住；；户型以多居室合租为主，单室面积15-20平，部分主卧带独立阳台；；小区容积率低绿化率高，部分不临街房源安静，未查到明确隔音差评，物业提供基本售后维修、公共区域保洁服务。</x:v>
       </x:c>
       <x:c r="L131" t="str">
-        <x:v>... 租金包水電上網提供剛需電器及生活用品. 10400元1室厅·140㎡. 干湿分离独卫邻地铁配套齐全精装修. 020D無隱形收費拎包入住租金包水電上網提供剛需電器及生活用品. 9900元1。；... 昌平-回龙观 流星花园三区 1500元/月. 距8号线-平西府站917m. 昌平-回龙观 流星花园三区出租房源图片 8号线平西府流星花园三区南向主卧带卫生间配套全采光佳 3室1厅 20m²。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；. 北京雅诗阁来福士中心服务公寓位于北京交通枢纽东直门。</x:v>
-      </x:c>
-      <x:c r="M131" t="str"/>
+        <x:v>商超：周边有昌发展万科广场、西二旗益民商城，盒马鲜生等超市近便；；配套：周边有多个社区公园，配套有医院、餐饮，可满足日常生活需求。</x:v>
+      </x:c>
+      <x:c r="M131" t="str">
+        <x:v>小区容积率低绿化率高，部分不临街房源安静，未查到明确隔音差评，物业提供基本售后维修、公共区域保洁服务。；未查询到针对该具体地址「泊客青年公寓」的专属差评，现有租房差评为融泽嘉园其他院落黑心房东恶意克扣押金事件，存在同名混淆风险；</x:v>
+      </x:c>
       <x:c r="N131" t="str">
-        <x:v>价格线索：在20-25平方米之间，租金约6000-7000元/月；... 昌平-回龙观 流星花园三区 1500元/月；同层高，不同朝向，相应价位不同）地下车位1000元/月；房屋质量/户型线索：... 租金包水電上網提供剛需電器及生活用品. 10400元1室厅·140㎡. 干湿分离独卫邻地铁配套齐全精装修. 020D無隱形收費拎包入住租金包水電上網提供剛需電器及生活用品. 9900元1。；长租公寓在北京：面向青年租客、最小户型更抢手 - 界面新闻。；产品和租金水平：项目设有两种户型，面积在20-25平方米之间，租金约6000-7000元/月，房间配有独立卫生间、沙发、电视、冰箱、洗衣机等。；. 行政区域：北京市朝阳区东三环燕莎-朝阳公园 公寓地址：北京市朝阳区麦子店街38号. 房间数量：318（间） 户型介绍：开间、一居、两居、三居. 行政区域：北京市东城区--东二环朝阳门 公寓地址：北京市东城区朝阳门外三丰北里9号. 户型面积（平米）价格（人民币元/月）. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 400-100-1111，链家旗下长租公寓品牌及青年居住社区，是提供居住产品与生活服务的O2O互联网公司，旗下拥有自如友家、自如整租、业主直租、自如豪宅、自如寓、自如驿、自如ZSPACE等产品，为合租、整租、短租、中高端租住需求设计了多种产品形式，并提供保洁、维修、搬家等居间服务。；. 400-686-8006，房地产综合服务提供商世联行旗下出租公寓品牌，专注为解决中国房地产存量物业空置问题而生的创新平台，瞄准青年租房市场，为城市白领提供设计、质感、乐趣的居住体验。；生活便利线索：... 租金包水電上網提供剛需電器及生活用品. 10400元1室厅·140㎡. 干湿分离独卫邻地铁配套齐全精装修. 020D無隱形收費拎包入住租金包水電上網提供剛需電器及生活用品. 9900元1。；... 昌平-回龙观 流星花园三区 1500元/月. 距8号线-平西府站917m. 昌平-回龙观 流星花园三区出租房源图片 8号线平西府流星花园三区南向主卧带卫生间配套全采光佳 3室1厅 20m²。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；. 北京雅诗阁来福士中心服务公寓位于北京交通枢纽东直门。</x:v>
+        <x:v>房屋质量/户型线索：房源属于融泽嘉园普通商品住宅小区，房龄较新，多为精装修，宜家/北欧风格设计，家电家具齐全拎包入住；；户型以多居室合租为主，单室面积15-20平，部分主卧带独立阳台；；小区容积率低绿化率高，部分不临街房源安静，未查到明确隔音差评，物业提供基本售后维修、公共区域保洁服务。；生活便利线索：商超：周边有昌发展万科广场、西二旗益民商城，盒马鲜生等超市近便；；配套：周边有多个社区公园，配套有医院、餐饮，可满足日常生活需求。；风险线索：小区容积率低绿化率高，部分不临街房源安静，未查到明确隔音差评，物业提供基本售后维修、公共区域保洁服务。；未查询到针对该具体地址「泊客青年公寓」的专属差评，现有租房差评为融泽嘉园其他院落黑心房东恶意克扣押金事件，存在同名混淆风险；</x:v>
       </x:c>
       <x:c r="O131" t="str">
-        <x:v>1. 北京昌平租房信息 - 58同城 http://mob.58.com/zf/hk-changping
-2. 长租公寓在北京：面向青年租客、最小户型更抢手 - 界面新闻 https://www.jiemian.com/article/1812155.html
-3. 昌平租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/changping
-4. 北京：保障性租赁房首次面向应届生配租 租金低于市场价格 http://bj.people.com.cn/n2/2022/0416/c82839-35226290.html
-5. 北京市昌平区租房 - 房天下 http://www.fang.com/houses/zf_253758bj</x:v>
+        <x:v>1. ["融泽嘉园东6号院，龙域租房，可月付 快手元中心 后厂村路 万家灯火 鹏寰大厦 百度大厦，昌平租房","http://m.anjuke.com/bj/rent/4329431109413888-3/?ad_type=z&amp;pagesource=10"]
+2. ["西二旗租房避雷贴 | 融泽嘉园黑心房东","https://www.douban.com/group/topic/312847114/?_spm_id=MTY5NTIzMDA3"]
+3. ["融泽嘉园东6号院合租主卧带阳台南向卧室 昌发展西二旗龙泽地铁","http://m.anjuke.com/bj/rent/4597997335587843-3/"]
+4. ["融泽嘉园东6号院 3室1厅1卫 家电齐全 南北通透","https://bj.zu.anjuke.com/fangyuan/3964138046151689"]
+5. 【多图】融泽嘉园东6号院，龙域租房，可月付 快手元中心 后厂村路 万家灯火 鹏寰大厦 百度大厦，昌平租房 http://m.anjuke.com/bj/rent/4329431109413888-3/?ad_type=z&amp;pagesource=10
+6. 西二旗租房避雷贴 | 融泽嘉园黑心房东 https://www.douban.com/group/topic/312847114/?_spm_id=MTY5NTIzMDA3
+7. 融泽嘉园东6号院合租主卧带阳台南向卧室 昌发展西二旗龙泽地铁 http://m.anjuke.com/bj/rent/4597997335587843-3/
+8. 融泽嘉园1号院 4室1厅1卫 15平 南北通透 配套齐全 http://m.anjuke.com/bj/rent/3325316364542989-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -6715,37 +7075,36 @@
         <x:v>北京市建材城西路新龙大厦B2新龙大厦b座15层</x:v>
       </x:c>
       <x:c r="E132" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F132" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="G132" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H132" t="n">
-        <x:v>4.5</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="I132" t="str">
-        <x:v>缺乏核心租金与质量数据，搜索结果多为天通苑等他区信息，有效证据严重不足。</x:v>
+        <x:v>位于新龙大厦，周边商超丰富，但房屋质量及租金信息缺失，且离地铁站稍远。</x:v>
       </x:c>
       <x:c r="J132" t="str"/>
       <x:c r="K132" t="str">
-        <x:v>品质租住生活新选择. ### 东方豪庭公寓. * [!</x:v>
+        <x:v>公开网络中无该门店房屋质量（隔音、户型、房龄、装修、物业）相关评价信息。</x:v>
       </x:c>
       <x:c r="L132" t="str">
-        <x:v>: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；品质租住生活新选择. ### 东方豪庭公寓. * [!；. * 北京望悦国际社区一键解锁国际菁英健康生活 悦运动 邀加入动型社区健康生活共同体，一键解锁国际菁英健康生活 清晨，跑步者的身影穿梭于社区林荫跑道；；在望悦国际社区，运动已不仅是一种习惯，更是一种生活方式——这里，是都市菁英的健康生活主场. 在望悦国际社区，运动不止于社区内部。</x:v>
+        <x:v>该公寓地址位于北京昌平建材城西路新龙大厦B座15层，周边靠近建材城西路，周边有地铁生命科学园站、朱辛庄站，距离1.5-2公里左右；；周边有新龙广场、龙旗购物中心等商超，餐饮配套丰富，距离昌平区中西医结合医院等医疗机构约3公里，通勤及生活配套相对便利。</x:v>
       </x:c>
       <x:c r="M132" t="str"/>
       <x:c r="N132" t="str">
-        <x:v>房屋质量/户型线索：品质租住生活新选择. ### 东方豪庭公寓. * [!；生活便利线索：: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；品质租住生活新选择. ### 东方豪庭公寓. * [!；. * 北京望悦国际社区一键解锁国际菁英健康生活 悦运动 邀加入动型社区健康生活共同体，一键解锁国际菁英健康生活 清晨，跑步者的身影穿梭于社区林荫跑道；；在望悦国际社区，运动已不仅是一种习惯，更是一种生活方式——这里，是都市菁英的健康生活主场. 在望悦国际社区，运动不止于社区内部。</x:v>
+        <x:v>房屋质量/户型线索：公开网络中无该门店房屋质量（隔音、户型、房龄、装修、物业）相关评价信息。；生活便利线索：该公寓地址位于北京昌平建材城西路新龙大厦B座15层，周边靠近建材城西路，周边有地铁生命科学园站、朱辛庄站，距离1.5-2公里左右；；周边有新龙广场、龙旗购物中心等商超，餐饮配套丰富，距离昌平区中西医结合医院等医疗机构约3公里，通勤及生活配套相对便利。</x:v>
       </x:c>
       <x:c r="O132" t="str">
-        <x:v>1. 北京市昌平区租房 - 房天下 http://www.fang.com/houses/zf_253758bj
-2. 昌平租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/changping
-3. 北京昌平租房信息 - 58同城 http://mob.58.com/zf/hk-changping
-4. 北京酒店式公寓租房网: 北京酒店式公寓出租-北京服务式租房价格 https://www.gongyuzufang.com
-5. 北京精装公寓出租信息 - 链家 https://m.lianjia.com/chuzu/bj/apartment/amp4amp6</x:v>
+        <x:v>1. 昌平区住房租赁企业和房地产经纪机构风险警示公告 https://credit.bjchp.gov.cn/dynamic/article?id=news_d544d545-9b20-4288-956c-a44e0d6b2cc2
+2. 愿景浣溪沙 电梯房 拎包入住 阳光充足 http://m.anjuke.com/jys/rent/4588123597153292-3/
+3. 愿景浣溪沙 2室2厅1卫 精装修 家电齐全 http://m.anjuke.com/cd/rent/4604217748317194-3/
+4. 黑猫投诉 - 新浪旗下消费者服务平台 https://tousu.sina.cn/complaint/union_index?keyword=%E9%9C%B8%E7%8E%8B%E6%9D%A1%E6%AC%BE&amp;sn=17381286607&amp;type=2</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -6762,39 +7121,42 @@
         <x:v>北京市回龙观村西区3号楼2单元1901</x:v>
       </x:c>
       <x:c r="E133" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F133" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G133" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H133" t="n">
-        <x:v>4.8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I133" t="str">
-        <x:v>价格区间明确且位置尚可，但网页提示装修材料不环保，存在健康风险，需警惕。</x:v>
+        <x:v>回龙观区域通勤便利且租金适中，但该公寓信息泛化，需防范小中介及定金风险。</x:v>
       </x:c>
       <x:c r="J133" t="str">
-        <x:v>... 北京市昌平区路松街. 3498-3798元/月；... 昌平-回龙观 流星花园三区 1500元/月</x:v>
+        <x:v>价，回龙观同区域合租次卧价格约1500-1800元/月；，整租1室价格约4000-5300元/月；，整租3室价格约6300元/月</x:v>
       </x:c>
       <x:c r="K133" t="str">
-        <x:v>价格说明：. 租金单价中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费。；装修材料不环保。；为您提供市场上具性价比的价格北京酒店式公寓出租信息. 超值. 全程0服务费，完整的服务式公寓房数据您可以全方位比较价格. 品质. 服务式公寓代表了同级住宅租赁市场更高的。；为您提供市场上具性价比的价格北京酒店式公寓出租信息. 超值. 全程0服务费，完整的服务式公寓房数据您可以全方位比较价格. 品质. 服务式公寓代表了同级住宅租赁市场更高的</x:v>
+        <x:v>未获取该公寓具体房龄、隔音、户型、装修、物业信息，同区域公寓普遍存在部分房源隔音较差，部分私人转租/小中介房源存在装修、家电老旧故障问题；</x:v>
       </x:c>
       <x:c r="L133" t="str">
-        <x:v>... 昌平-回龙观 流星花园三区 1500元/月. 距8号线-平西府站917m. 昌平-回龙观 流星花园三区出租房源图片 8号线平西府流星花园三区南向主卧带卫生间配套全采光佳 3室1厅 20m²。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。</x:v>
-      </x:c>
-      <x:c r="M133" t="str"/>
+        <x:v>该地址位于回龙观村，临近13号线回龙观站、18号线文华路站，通勤到西二旗等商圈便利，回龙观区域商超、餐饮、医疗配套成熟，生活便利性较好；；未找到该指定地址「洁癖公寓」的专属口碑信息，现有搜索结果均为周边泛化房源，存在同名误命中或信息不匹配风险，小中介/个人转租房源可能存在定金不退、私配钥匙、维修服务差、加价赚差价等潜在风险。；未找到该指定地址「洁癖公寓」的专属口碑信息，现有搜索结果均为周边泛化房源，存在同名误命中或信息不匹配风险，小中介/个人转租房源可能存在定金不退、私配钥匙、维修服务差、加价赚差价等潜在风险</x:v>
+      </x:c>
+      <x:c r="M133" t="str">
+        <x:v>未获取该公寓具体房龄、隔音、户型、装修、物业信息，同区域公寓普遍存在部分房源隔音较差，部分私人转租/小中介房源存在装修、家电老旧故障问题；</x:v>
+      </x:c>
       <x:c r="N133" t="str">
-        <x:v>价格线索：... 北京市昌平区路松街. 3498-3798元/月；... 昌平-回龙观 流星花园三区 1500元/月；房屋质量/户型线索：价格说明：. 租金单价中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费。；装修材料不环保。；为您提供市场上具性价比的价格北京酒店式公寓出租信息. 超值. 全程0服务费，完整的服务式公寓房数据您可以全方位比较价格. 品质. 服务式公寓代表了同级住宅租赁市场更高的。；为您提供市场上具性价比的价格北京酒店式公寓出租信息. 超值. 全程0服务费，完整的服务式公寓房数据您可以全方位比较价格. 品质. 服务式公寓代表了同级住宅租赁市场更高的；生活便利线索：... 昌平-回龙观 流星花园三区 1500元/月. 距8号线-平西府站917m. 昌平-回龙观 流星花园三区出租房源图片 8号线平西府流星花园三区南向主卧带卫生间配套全采光佳 3室1厅 20m²。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。</x:v>
+        <x:v>价格线索：价，回龙观同区域合租次卧价格约1500-1800元/月；，整租1室价格约4000-5300元/月；，整租3室价格约6300元/月；房屋质量/户型线索：未获取该公寓具体房龄、隔音、户型、装修、物业信息，同区域公寓普遍存在部分房源隔音较差，部分私人转租/小中介房源存在装修、家电老旧故障问题；；生活便利线索：该地址位于回龙观村，临近13号线回龙观站、18号线文华路站，通勤到西二旗等商圈便利，回龙观区域商超、餐饮、医疗配套成熟，生活便利性较好；；未找到该指定地址「洁癖公寓」的专属口碑信息，现有搜索结果均为周边泛化房源，存在同名误命中或信息不匹配风险，小中介/个人转租房源可能存在定金不退、私配钥匙、维修服务差、加价赚差价等潜在风险。；未找到该指定地址「洁癖公寓」的专属口碑信息，现有搜索结果均为周边泛化房源，存在同名误命中或信息不匹配风险，小中介/个人转租房源可能存在定金不退、私配钥匙、维修服务差、加价赚差价等潜在风险；风险线索：未获取该公寓具体房龄、隔音、户型、装修、物业信息，同区域公寓普遍存在部分房源隔音较差，部分私人转租/小中介房源存在装修、家电老旧故障问题；</x:v>
       </x:c>
       <x:c r="O133" t="str">
-        <x:v>1. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/shahe2/rmp3
-2. 北京昌平合租4居室房源出租, 2050 RMB/月, 近地鐵8号线, 溫馨小窩 https://www.wellcee.com/tw/rent-apartment/1765380609495628
-3. 北京租房攻略 - 知乎专栏 https://zhuanlan.zhihu.com/p/406125060
-4. 昌平租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/changping
-5. 北京市昌平区租房 - 房天下 http://www.fang.com/houses/zf_253758bj</x:v>
+        <x:v>1. 可月租 回龙观地铁了 有客厅室友女爱干净采光好 温馨舒适 http://m.anjuke.com/bj/rent/4604133577272329-3/
+2. 年轻人多次租房被坑，一年搬了五次家，你被房东或中介坑过吗？如何避坑？ https://view.inews.qq.com/k/20240312Q05OL600?no-redirect=1
+3. (全时间段)暑期租房攻略来啦!全是干货! https://www.nowcoder.com/feed/main/detail/d95173736bd54acb858fb176dbe38875?urlSource=extension-api
+4. 回龙观公寓整租，物业直签，看上的房间可预留 http://m.anjuke.com/bj/rent/4199548532596747-3/
+5. (全时间段)暑期租房攻略来啦!全是干货!_牛客网 https://www.nowcoder.com/feed/main/detail/d95173736bd54acb858fb176dbe38875?urlSource=extension-api
+6. 0押月付 回龙观整租南北通透3居2卫 明厨明卫低楼层很便宜 http://m.anjuke.com/bj/rent/4505997739633669-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -6811,39 +7173,42 @@
         <x:v>北京市海淀区黑龙潭路与西北旺圣经路交叉路口往西南约250米</x:v>
       </x:c>
       <x:c r="E134" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F134" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G134" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H134" t="n">
-        <x:v>8.5</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="I134" t="str">
-        <x:v>保租房租金优惠力度大，LOFT户型配套好，虽距地铁2公里但骑行通勤后厂村尚可。</x:v>
+        <x:v>临近大厂及地铁，租金极具性价比，但具体房源信息泛化，存在信息不匹配风险。</x:v>
       </x:c>
       <x:c r="J134" t="str">
-        <x:v>富华里汇园3室2厅98㎡ 7800元. 7800元/月；北京市海淀区永丰屯538号. 2500-3000元/月；0m² 海淀-西北旺 永旺家园(三区) 2470元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月</x:v>
+        <x:v>边同区位分散式公寓月租区间多为1800-3000元/月</x:v>
       </x:c>
       <x:c r="K134" t="str">
-        <x:v>. 租金方面，青年公寓的租金将在备案租金价格的基础上，**头两年按照六折收取**，**最小的户型每月折后房租约1840元（下图）**。；. 这个项目的一居室户型面积较小，但值得注意的是，922套房源的**全部房型采用的都是架空双层结构，类似“LOFT”格局**，即便是28平米的小一居，实际居住空间也还是比较充裕的。；. 价格方面，该项目的**备案租金均价为每月每建筑平米109.5元**（不含物业费），并实行动态调整。；. 项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准. 为落实《北京市关于加快发展保障性租赁住房的实施方案》（京政办发〔2022〕9 号），保障性租赁住房主要用于缓解在本市无房的新市民、青年人等群体住房问题，重点保障新毕业大学生等群体。</x:v>
+        <x:v>该公寓周边同区位分散式公寓月租区间多为1800-3000元/月，1室户型（约25-35平米）月租多在1800-2200元，多数房源支持押一付一，无中介费；；多为全新精装修，户型方正，多为1室0厅/1室1厅的小户型，采光通风较好；；楼内外有监控覆盖，隔音效果标注较好，家电配套齐全（含冰箱、洗衣机、空调、热水器等），物业提供免费维修、安保、垃圾清运服务；；未查询到明确房龄信息；</x:v>
       </x:c>
       <x:c r="L134" t="str">
-        <x:v>. 先看位置，这次配租的项目为**寓见西山保租房项目，地处温泉镇，北五环外，位于西北旺的西侧，地铁16号线屯佃站的往南**。；. 单从交通来看，这个项目距离地铁站点直线距离就有接近2公里，并不是太方便。；不过考虑到其周边的产业园区，还是一个就业人群可以接受的通勤距离。；再远一些，**距离大厂云集的后厂村直线距离5公里多**，骑行通行或是公交、打车出行也皆可。；. 项目**配备智能家电和木质环保家具**，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间。</x:v>
-      </x:c>
-      <x:c r="M134" t="str"/>
+        <x:v>该公寓周边同区位分散式公寓月租区间多为1800-3000元/月，1室户型（约25-35平米）月租多在1800-2200元，多数房源支持押一付一，无中介费；；楼内外有监控覆盖，隔音效果标注较好，家电配套齐全（含冰箱、洗衣机、空调、热水器等），物业提供免费维修、安保、垃圾清运服务；；距离地铁16号线西北旺站步行可达，通勤中关村软件园、西二旗、中关村便利，靠近百度、腾讯等互联网大厂；；周边有西北旺万象汇、海北枫林超市、恒利华购物中心，商超餐饮配套齐全，周边有医院及公园，生活便利，紧邻黑龙潭路，公交出行也较为方便；；现有搜索结果中未明确对应目标地址“北京市海淀区黑龙潭路与西北旺圣经路交叉路口往西南约250米”的“西北旺青年公寓”专属口碑差评，搜索结果多为周边同区域公寓房源，存在同名误命中、信息泛化风险，无法确认是否为目标公寓的真实口碑。</x:v>
+      </x:c>
+      <x:c r="M134" t="str">
+        <x:v>现有搜索结果中未明确对应目标地址“北京市海淀区黑龙潭路与西北旺圣经路交叉路口往西南约250米”的“西北旺青年公寓”专属口碑差评，搜索结果多为周边同区域公寓房源，存在同名误命中、信息泛化风险，无法确认是否为目标公寓的真实口碑。；现有搜索结果中未明确对应目标地址“北京市海淀区黑龙潭路与西北旺圣经路交叉路口往西南约250米”的“西北旺青年公寓”专属口碑差评，搜索结果多为周边同区域公寓房源，存在同名误命中、信息泛化风险，无法确认是否为目标公寓的真实口碑</x:v>
+      </x:c>
       <x:c r="N134" t="str">
-        <x:v>价格线索：富华里汇园3室2厅98㎡ 7800元. 7800元/月；北京市海淀区永丰屯538号. 2500-3000元/月；0m² 海淀-西北旺 永旺家园(三区) 2470元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；房屋质量/户型线索：. 租金方面，青年公寓的租金将在备案租金价格的基础上，**头两年按照六折收取**，**最小的户型每月折后房租约1840元（下图）**。；. 这个项目的一居室户型面积较小，但值得注意的是，922套房源的**全部房型采用的都是架空双层结构，类似“LOFT”格局**，即便是28平米的小一居，实际居住空间也还是比较充裕的。；. 价格方面，该项目的**备案租金均价为每月每建筑平米109.5元**（不含物业费），并实行动态调整。；. 项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准. 为落实《北京市关于加快发展保障性租赁住房的实施方案》（京政办发〔2022〕9 号），保障性租赁住房主要用于缓解在本市无房的新市民、青年人等群体住房问题，重点保障新毕业大学生等群体。；生活便利线索：. 先看位置，这次配租的项目为**寓见西山保租房项目，地处温泉镇，北五环外，位于西北旺的西侧，地铁16号线屯佃站的往南**。；. 单从交通来看，这个项目距离地铁站点直线距离就有接近2公里，并不是太方便。；不过考虑到其周边的产业园区，还是一个就业人群可以接受的通勤距离。；再远一些，**距离大厂云集的后厂村直线距离5公里多**，骑行通行或是公交、打车出行也皆可。；. 项目**配备智能家电和木质环保家具**，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间。</x:v>
+        <x:v>价格线索：边同区位分散式公寓月租区间多为1800-3000元/月；房屋质量/户型线索：该公寓周边同区位分散式公寓月租区间多为1800-3000元/月，1室户型（约25-35平米）月租多在1800-2200元，多数房源支持押一付一，无中介费；；多为全新精装修，户型方正，多为1室0厅/1室1厅的小户型，采光通风较好；；楼内外有监控覆盖，隔音效果标注较好，家电配套齐全（含冰箱、洗衣机、空调、热水器等），物业提供免费维修、安保、垃圾清运服务；；未查询到明确房龄信息；；生活便利线索：该公寓周边同区位分散式公寓月租区间多为1800-3000元/月，1室户型（约25-35平米）月租多在1800-2200元，多数房源支持押一付一，无中介费；；楼内外有监控覆盖，隔音效果标注较好，家电配套齐全（含冰箱、洗衣机、空调、热水器等），物业提供免费维修、安保、垃圾清运服务；；距离地铁16号线西北旺站步行可达，通勤中关村软件园、西二旗、中关村便利，靠近百度、腾讯等互联网大厂；；周边有西北旺万象汇、海北枫林超市、恒利华购物中心，商超餐饮配套齐全，周边有医院及公园，生活便利，紧邻黑龙潭路，公交出行也较为方便；；现有搜索结果中未明确对应目标地址“北京市海淀区黑龙潭路与西北旺圣经路交叉路口往西南约250米”的“西北旺青年公寓”专属口碑差评，搜索结果多为周边同区域公寓房源，存在同名误命中、信息泛化风险，无法确认是否为目标公寓的真实口碑。；风险线索：现有搜索结果中未明确对应目标地址“北京市海淀区黑龙潭路与西北旺圣经路交叉路口往西南约250米”的“西北旺青年公寓”专属口碑差评，搜索结果多为周边同区域公寓房源，存在同名误命中、信息泛化风险，无法确认是否为目标公寓的真实口碑。；现有搜索结果中未明确对应目标地址“北京市海淀区黑龙潭路与西北旺圣经路交叉路口往西南约250米”的“西北旺青年公寓”专属口碑差评，搜索结果多为周边同区域公寓房源，存在同名误命中、信息泛化风险，无法确认是否为目标公寓的真实口碑</x:v>
       </x:c>
       <x:c r="O134" t="str">
-        <x:v>1. 海淀推近千套“青年公寓”头两年租金打六折 https://h5.ifeng.com/c/vivoArticle/v002oTDgMK7Vqsq9UbTt6B8KeNB88WGL6JPE3koM9VtPxOw__?isNews=1&amp;showComments=0
-2. 西北旺公寓出租- 北京 - 房天下 http://www.fang.com/houses/zf_252240bj
-3. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu/rmp3amp0
-4. 北京公寓出租_北京精装公寓出租信息-北京链家找房 https://ifeng-m.lianjia.com/chuzu/bj/apartment/haidianqu/amp3ama0
-5. 海淀西北旺租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian-q-xibeiwang</x:v>
+        <x:v>1. 地铁16号线西北旺精装公寓 可直达中关村通勤西二旗，押一付一 http://m.anjuke.com/bj/rent/4581070293050371-3/
+2. 西北旺超值整租！1800元每月，温馨独居公寓配套完善 http://m.anjuke.com/bj/rent/4543318725782531-3/
+3. 西北旺地铁16号线 物业直招 无中介!! 通勤便利 领包入住，黑龙潭路 https://m.58.com/bj/zufang/84541466150234x.shtml
+4. 温泉 带客厅 带卫生间 环保园 西北旺 航材院 黑山扈 http://m.anjuke.com/bj/rent/4603988924849159-3/
+5. 西北旺 两居室正规主卧 室友一个女生 可步行通勤百度 网易 https://bj.zu.anjuke.com/fangyuan/4485500778212361
+6. 【8图】西北旺地铁16号线 物业直招 无中介!! 通勤便利 领包入住，黑龙潭路 https://m.58.com/bj/zufang/84541466150234x.shtml</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -6860,41 +7225,40 @@
         <x:v>北京市海淀区厢黄旗路绿苑小区南侧</x:v>
       </x:c>
       <x:c r="E135" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F135" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G135" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H135" t="n">
-        <x:v>6.5</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="I135" t="str">
-        <x:v>地理位置优越，但证据中混入异地低价信息，真实租金可能偏高，建议谨慎核实。</x:v>
-      </x:c>
-      <x:c r="J135" t="str">
-        <x:v>万树园，小区价格77675元/㎡；大单间楼下商场环境优美出行方便可做饭. 1100元/月</x:v>
-      </x:c>
+        <x:v>房龄较老但管理规范，步行可达地铁站，周边生活配套成熟，适合追求稳定的租客。</x:v>
+      </x:c>
+      <x:c r="J135" t="str"/>
       <x:c r="K135" t="str">
-        <x:v>户型1-3室、建面44-87㎡。；了解更多小区房源、房价、户型、绿化率、周边配套。；小区很安静，小区里面就有超市，平时拿不了的快递都可以放在那里，出门就有公交，里地铁站也不远。；• 户型介绍：南北通透的2室1厅1卫，精装修，带厨房，适合家庭居住。；配套齐全南北通透首次出租精装修押一付一有阳台. 大沥步行街旁精装大单间楼下商场环境优美出行方便可做饭. 1100元/月1室0厅·35㎡. 配套齐全南北通透首次出租精装修押一。</x:v>
+        <x:v>房龄：小区建成于1999-2001年；；装修：多数在租房源为精装修，部分为全新装修，家具家电齐全；；户型：有开间、一居、三居等，多数南北通透、布局合理，采光好；；隔音：部分合租房源标注卧室不紧挨，隔音效果较好；；物业：小区有专业管理，24小时安保巡视，管理有序规范，部分租房提供免费维修和保洁；</x:v>
       </x:c>
       <x:c r="L135" t="str">
-        <x:v>了解更多小区房源、房价、户型、绿化率、周边配套。；万树园3室1厅1卫房源出租，面积13㎡，朝向北，房源近地铁集中供暖绿化率高，周边配套完善，更多租房信息尽在幸福里APP. ... [海淀-马连洼]万树园. 交通. 教育. 医疗. 生活. 休闲.。；小区很安静，小区里面就有超市，平时拿不了的快递都可以放在那里，出门就有公交，里地铁站也不远。；最好的是，去上地上班根本就不堵，骑个车或是步行都很便利。；房源位置：位于厢黄旗路的万树园小区，交通便利，生活设施齐全。</x:v>
-      </x:c>
-      <x:c r="M135" t="str">
-        <x:v>最好的是，去上地上班根本就不堵，骑个车或是步行都很便利。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. * 关键字：c7c7.apo.ccm.ty14.cc清空全部条件订阅. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 东城区 北新桥 东四 张自忠路(二进四合院)"). : 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV"). : 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 康桥水郡 5室3卫3厅 410.24平精装修 126. 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>通勤地铁：步行约877米到地铁16号线农大南路站，门口有厢黄旗公交站，出行便利；；商超：周边有即全新生活便民超市、中发百旺商城，还有农贸市场，满足日常购物；；医院：步行约213米到北京八珍堂中医医院；；餐饮：周边餐饮配套齐全，生活便利；</x:v>
+      </x:c>
+      <x:c r="M135" t="str"/>
       <x:c r="N135" t="str">
-        <x:v>价格线索：万树园，小区价格77675元/㎡；大单间楼下商场环境优美出行方便可做饭. 1100元/月；房屋质量/户型线索：户型1-3室、建面44-87㎡。；了解更多小区房源、房价、户型、绿化率、周边配套。；小区很安静，小区里面就有超市，平时拿不了的快递都可以放在那里，出门就有公交，里地铁站也不远。；• 户型介绍：南北通透的2室1厅1卫，精装修，带厨房，适合家庭居住。；配套齐全南北通透首次出租精装修押一付一有阳台. 大沥步行街旁精装大单间楼下商场环境优美出行方便可做饭. 1100元/月1室0厅·35㎡. 配套齐全南北通透首次出租精装修押一。；生活便利线索：了解更多小区房源、房价、户型、绿化率、周边配套。；万树园3室1厅1卫房源出租，面积13㎡，朝向北，房源近地铁集中供暖绿化率高，周边配套完善，更多租房信息尽在幸福里APP. ... [海淀-马连洼]万树园. 交通. 教育. 医疗. 生活. 休闲.。；小区很安静，小区里面就有超市，平时拿不了的快递都可以放在那里，出门就有公交，里地铁站也不远。；最好的是，去上地上班根本就不堵，骑个车或是步行都很便利。；房源位置：位于厢黄旗路的万树园小区，交通便利，生活设施齐全。；风险线索：最好的是，去上地上班根本就不堵，骑个车或是步行都很便利。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. * 关键字：c7c7.apo.ccm.ty14.cc清空全部条件订阅. : 有钥0匙,北京壹号院 4室2厅 精装修 家具全,亮马. : 15套可看 万城华府海园 万柳疏书院 多套可看 干净. : 新出位置安静 可直接入住 楼层好 330平米 三面采. : 西城区 后海 什刹海 平安里(二进四合院)电动天幕电动天幕"). : 西城丨恭王府 什刹海 后海丨精装 带家具 近停车场丨. : 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). : 东城区 北新桥 东四 张自忠路(二进四合院)"). : 东城区 北新桥 张自忠路(3-4个车位)四合院 KT四合院 KTV"). : 香江花园 新出全新装独栋 简约7室 带地暖 诚租可看. : 全空房,高层边户大四居,落地窗,视野开阔,安静不吵,. : 康桥水郡 5室3卫3厅 410.24平精装修 126. 房天下北京租房网提供超过0套优质出租房源，海量房东直租房、经纪人租房信息，帮您轻松在北京租房子。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>房屋质量/户型线索：房龄：小区建成于1999-2001年；；装修：多数在租房源为精装修，部分为全新装修，家具家电齐全；；户型：有开间、一居、三居等，多数南北通透、布局合理，采光好；；隔音：部分合租房源标注卧室不紧挨，隔音效果较好；；物业：小区有专业管理，24小时安保巡视，管理有序规范，部分租房提供免费维修和保洁；；生活便利线索：通勤地铁：步行约877米到地铁16号线农大南路站，门口有厢黄旗公交站，出行便利；；商超：周边有即全新生活便民超市、中发百旺商城，还有农贸市场，满足日常购物；；医院：步行约213米到北京八珍堂中医医院；；餐饮：周边餐饮配套齐全，生活便利；</x:v>
       </x:c>
       <x:c r="O135" t="str">
-        <x:v>1. 万树园- 海淀小区 - 北京买房- 吉屋网 https://bj.jiwu.com/loupan/809093.html
-2. 合租·万树园 https://fangchan.snssdk.com/zufang/bj-7560063914759700523.html
-3. 万树园- 房价|租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027380474
-4. 新出农大南路万树园精装低楼层两居室业主签约 - 北京租房 https://bj.zu.anjuke.com/fangyuan/4596755333491715
-5. 万柳公寓租房房源 - 58同城 https://mob.58.com/zf/fs/gy-wanliubj</x:v>
+        <x:v>1. ["【7图】万树园 大面积三居 实房实图 跟业主签约 配套全齐 稳定长租，厢黄旗路","https://m.58.com/bj/zufang/4277296718683x.shtml"]
+2. ["实拍实价万树园朝南大卧室带阳台 农大南路西校区 农大地铁口","http://m.anjuke.com/bj/rent/4485173611209728-3/"]
+3. ["厢黄旗万树园 能便宜精装一居 实房实拍 配置齐全 跟业主签约","http://m.anjuke.com/bj/rent/4603942562999308-3/"]
+4. 【7图】万树园 大面积三居 实房实图 跟业主签约 配套全齐 稳定长租，厢黄旗路 https://m.58.com/bj/zufang/84277296718683x.shtml
+5. 【万树园整租三室一厅租房价格，北京万树园三室一厅房租价格走势信息】 http://m.58.com/bj/xq/336/r3/
+6. 实拍实价万树园朝南大卧室带阳台 农大南路西校区 农大地铁口 http://m.anjuke.com/bj/rent/4485173611209728-3/
+7. 厢黄旗万树园 能便宜精装一居 实房实拍 配置齐全 跟业主签约 http://m.anjuke.com/bj/rent/4603942562999308-3/
+8. 万树园 精装一居室 紧邻地铁站 签 配置齐全 http://m.anjuke.com/bj/rent/4586921728713731-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -6911,39 +7275,42 @@
         <x:v>北京市海淀区圆明园西路34号肖家河回迁住宅东区2号楼4单元404室,农科院植保所农大南路</x:v>
       </x:c>
       <x:c r="E136" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F136" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G136" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H136" t="n">
         <x:v>8.2</x:v>
       </x:c>
       <x:c r="I136" t="str">
-        <x:v>紧邻农大南路地铁站，精装电梯房且物业费低，通勤便利，是高品质租住的稳妥选择。</x:v>
+        <x:v>距离地铁站极近，通勤便利性极佳，租金透明且配套完善，是高性价比的合租首选。</x:v>
       </x:c>
       <x:c r="J136" t="str">
-        <x:v>区2室1厅1卫87平精装修整租房房源价格6500元/月；租 1-3个月 4-6个月. 1300-2300元/月</x:v>
+        <x:v>合租单间价格约2200元-2500元/月；（12-15平米南向单间），整租两居室约6200元/月</x:v>
       </x:c>
       <x:c r="K136" t="str">
-        <x:v>正黄旗东区3室1厅好房子精装修配置齐全 - 北京租房。；正黄旗东区3室1厅好房子精装修配置齐全 · 户型： 3室1厅1卫 · 装修： 精装修 · 面积： 12平米 · 朝向： 东西 · 楼层： 低层(共12层) · 类型： 普通住宅.。；北京海淀肖家河圆明园西路34号正黄旗东区2室1厅1卫87平精装修整租房房源价格6500元/月房子我实地看过，照片也是实地拍摄的，室内家具家电都是齐全的，均可正常使用，。；肖家河正黄旗东区三居室，随时看，电梯房，出门16号线农大南路 · 户型： 3室1厅1卫 · 装修： 精装修 · 面积： 85平米 · 朝向： 东西 · 楼层： 中层(共10层) · 类型： 普通。；小区环境闹中取静，楼下有一个固定车位收费合理，物业费用低。</x:v>
+        <x:v>小区为回迁住宅，房源多为精装修，户型以合租的3室1厅为主，出租单间多朝南，采光通风较好，房龄无公开信息；；物业无公开评价，隔音信息未查到，多为低层电梯房；</x:v>
       </x:c>
       <x:c r="L136" t="str">
-        <x:v>地铁农大南路站50米正黄旗东区，最后一间两家两卫，喜欢的抓紧！；☎️ 18210079075#精装全配拎包入住#实景拍摄带你看房 #好房推荐 #同城租房 #地铁口的房子.。</x:v>
-      </x:c>
-      <x:c r="M136" t="str"/>
+        <x:v>通勤：距离地铁16号线农大南路站步行约265米，步行到马连洼站约1.8公里，可换乘4号线，通勤中关村、上地方便；；商超：周边有果味蔬生鲜超市、华联生活超市、中发百旺商城、北京华联BHG Mall，小区内也有配套商业；；医院：距离北京八珍堂中医医院约906米；；餐饮：小区周边和院内有餐饮店铺；；生活配套齐全，比较便利；</x:v>
+      </x:c>
+      <x:c r="M136" t="str">
+        <x:v>未找到该公寓的差评和负面风险信息。；未找到该公寓的差评和负面风险信息</x:v>
+      </x:c>
       <x:c r="N136" t="str">
-        <x:v>价格线索：区2室1厅1卫87平精装修整租房房源价格6500元/月；租 1-3个月 4-6个月. 1300-2300元/月；房屋质量/户型线索：正黄旗东区3室1厅好房子精装修配置齐全 - 北京租房。；正黄旗东区3室1厅好房子精装修配置齐全 · 户型： 3室1厅1卫 · 装修： 精装修 · 面积： 12平米 · 朝向： 东西 · 楼层： 低层(共12层) · 类型： 普通住宅.。；北京海淀肖家河圆明园西路34号正黄旗东区2室1厅1卫87平精装修整租房房源价格6500元/月房子我实地看过，照片也是实地拍摄的，室内家具家电都是齐全的，均可正常使用，。；肖家河正黄旗东区三居室，随时看，电梯房，出门16号线农大南路 · 户型： 3室1厅1卫 · 装修： 精装修 · 面积： 85平米 · 朝向： 东西 · 楼层： 中层(共10层) · 类型： 普通。；小区环境闹中取静，楼下有一个固定车位收费合理，物业费用低。；生活便利线索：地铁农大南路站50米正黄旗东区，最后一间两家两卫，喜欢的抓紧！；☎️ 18210079075#精装全配拎包入住#实景拍摄带你看房 #好房推荐 #同城租房 #地铁口的房子.。</x:v>
+        <x:v>价格线索：合租单间价格约2200元-2500元/月；（12-15平米南向单间），整租两居室约6200元/月；房屋质量/户型线索：小区为回迁住宅，房源多为精装修，户型以合租的3室1厅为主，出租单间多朝南，采光通风较好，房龄无公开信息；；物业无公开评价，隔音信息未查到，多为低层电梯房；；生活便利线索：通勤：距离地铁16号线农大南路站步行约265米，步行到马连洼站约1.8公里，可换乘4号线，通勤中关村、上地方便；；商超：周边有果味蔬生鲜超市、华联生活超市、中发百旺商城、北京华联BHG Mall，小区内也有配套商业；；医院：距离北京八珍堂中医医院约906米；；餐饮：小区周边和院内有餐饮店铺；；生活配套齐全，比较便利；；风险线索：未找到该公寓的差评和负面风险信息。；未找到该公寓的差评和负面风险信息</x:v>
       </x:c>
       <x:c r="O136" t="str">
-        <x:v>1. 北京市海淀区正黄旗东区出租房 - 抖音 https://www.douyin.com/search/%E5%8C%97%E4%BA%AC%E5%B8%82%E6%B5%B7%E6%B7%80%E5%8C%BA%E6%AD%A3%E9%BB%84%E6%97%97%E4%B8%9C%E5%8C%BA%E5%87%BA%E7%A7%9F%E6%88%BF
-2. 正黄旗东区3室1厅好房子精装修配置齐全 - 北京租房 https://bj.zu.anjuke.com/fangyuan/4600120594424845
-3. 【7图】正黄旗东区80平大两居南北通透电梯高层采光佳 - 58同城 http://m.58.com/bj/zufang/86644940607322x.shtml
-4. 正黄旗东区租房子 - 北京二手房- 房天下 https://esf.fang.com/loupan/1010198053/chuzu
-5. 肖家河正黄旗东区三居室，随时看，电梯房，出门16号线农大南路 https://bj.zu.anjuke.com/fangyuan/4554147873547276</x:v>
+        <x:v>1. 正黄旗东区 3室1厅 好房子 精装修 配置齐全 http://m.anjuke.com/bj/rent/4603207602875392-3/
+2. 首月减免农大南路地铁站中央党校北大生物城亿城国际杜朗大厦 http://m.anjuke.com/bj/rent/4592271837912066-3/
+3. 正黄旗东区 3室1厅1卫 15平 家电齐全 http://m.anjuke.com/bj/rent/4572557543517198-3/
+4. 正黄旗东区 2室1厅1卫 http://m.anjuke.com/bj/rent/4559952232127499-2/
+5. 双卧朝南圆明园西路3号院精装两居 和业主签合同干净整洁可长租 https://m.58.com/bj/zufang/84310487591005x.shtml
+6. 我爱我家相寓 马连洼圆明园西路3号院中楼层4居室主卧 http://m.anjuke.com/bj/rent/4588652718711820-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -6960,39 +7327,42 @@
         <x:v>北京市海淀区圆明园西路34号肖家河回迁住宅4号楼3单元103室</x:v>
       </x:c>
       <x:c r="E137" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F137" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G137" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H137" t="n">
-        <x:v>4.5</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="I137" t="str">
-        <x:v>证据存在严重的地理位置描述冲突，房源真实性及具体信息存疑，评分较为保守。</x:v>
-      </x:c>
-      <x:c r="J137" t="str">
-        <x:v>租 1-3个月 4-6个月. 1300-2300元/月</x:v>
-      </x:c>
+        <x:v>交通便利且安保较好，但隔音评价较差且房源信息存在泛化风险，建议实地考察。</x:v>
+      </x:c>
+      <x:c r="J137" t="str"/>
       <x:c r="K137" t="str">
-        <x:v>圆明园西路3号院户型主要有45平-80平的户型方正,双阳台,主卧朝南的二居、61平-79平的户型方正,明卫,明厨的三居、42平-42平的明厨,客厅朝南的一居。；小区户型 ;；1居室·9个户型. 25㎡~43㎡. 在售190万起 ;；2居室·18个户型. 45㎡~85㎡. 在售288万起 ;；3居室·12个户型. 59㎡~98㎡. 在售510万起 ;</x:v>
+        <x:v>该公寓位于肖家河回迁住宅，房龄为回迁小区房龄，室内为精装修，配套家具家电齐全；；隔音普遍反映较差；；户型多为单间/小户型，该地址为1层单元房；；小区有物业，楼道每日保洁，有电梯、人脸识别、密码锁，管理较好；</x:v>
       </x:c>
       <x:c r="L137" t="str">
-        <x:v>户型及租金：提供一房、二房、三房，面积在26-76平方米，租金价格2740 ... 具体位置：海淀区文慧园西路36号. 交通：距离地铁2号线、4号线、13号线。</x:v>
-      </x:c>
-      <x:c r="M137" t="str"/>
+        <x:v>未查询到该门店明确公开的月租价格，周边同类型普通公寓单间月租约3000-4500元区间，支持押一付一，可短租月租；；该公寓位于肖家河回迁住宅，房龄为回迁小区房龄，室内为精装修，配套家具家电齐全；；通勤便利，距离地铁16号线农大南路站很近，周边多个公交站，线路覆盖广；；周边配套成熟，有社区便利店、商超，步行可达华联超市，餐饮设施丰富，周边满足日常就医、生活购物需求；</x:v>
+      </x:c>
+      <x:c r="M137" t="str">
+        <x:v>公开租房口碑信息较少，搜索结果存在同名/近似品牌误命中情况，未找到该门店直接差评信息，无法确认是否存在相关风险。；公开租房口碑信息较少，搜索结果存在同名/近似品牌误命中情况，未找到该门店直接差评信息，无法确认是否存在相关风险</x:v>
+      </x:c>
       <x:c r="N137" t="str">
-        <x:v>价格线索：租 1-3个月 4-6个月. 1300-2300元/月；房屋质量/户型线索：圆明园西路3号院户型主要有45平-80平的户型方正,双阳台,主卧朝南的二居、61平-79平的户型方正,明卫,明厨的三居、42平-42平的明厨,客厅朝南的一居。；小区户型 ;；1居室·9个户型. 25㎡~43㎡. 在售190万起 ;；2居室·18个户型. 45㎡~85㎡. 在售288万起 ;；3居室·12个户型. 59㎡~98㎡. 在售510万起 ;；生活便利线索：户型及租金：提供一房、二房、三房，面积在26-76平方米，租金价格2740 ... 具体位置：海淀区文慧园西路36号. 交通：距离地铁2号线、4号线、13号线。</x:v>
+        <x:v>房屋质量/户型线索：该公寓位于肖家河回迁住宅，房龄为回迁小区房龄，室内为精装修，配套家具家电齐全；；隔音普遍反映较差；；户型多为单间/小户型，该地址为1层单元房；；小区有物业，楼道每日保洁，有电梯、人脸识别、密码锁，管理较好；；生活便利线索：未查询到该门店明确公开的月租价格，周边同类型普通公寓单间月租约3000-4500元区间，支持押一付一，可短租月租；；该公寓位于肖家河回迁住宅，房龄为回迁小区房龄，室内为精装修，配套家具家电齐全；；通勤便利，距离地铁16号线农大南路站很近，周边多个公交站，线路覆盖广；；周边配套成熟，有社区便利店、商超，步行可达华联超市，餐饮设施丰富，周边满足日常就医、生活购物需求；；风险线索：公开租房口碑信息较少，搜索结果存在同名/近似品牌误命中情况，未找到该门店直接差评信息，无法确认是否存在相关风险。；公开租房口碑信息较少，搜索结果存在同名/近似品牌误命中情况，未找到该门店直接差评信息，无法确认是否存在相关风险</x:v>
       </x:c>
       <x:c r="O137" t="str">
-        <x:v>1. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/wh-haidian
-2. 圆明园西路3号院- 北京二手房 - 房天下 https://esf.fang.com/loupan/1010573863.htm
-3. 北京圆明园西路3号院二手房|房价 - 链家 https://bj.lianjia.com/xiaoqu/1111027381916
-4. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu
-5. 北京海淀整租2居室房源出租, 7400 RMB/月, 近地鐵13号线, 溫馨小窩 https://www.wellcee.com/tw/rent-apartment/1688623422093575</x:v>
+        <x:v>1. ["个人转租，国企公寓 https://www.douban.com/group/topic/337437117/?_spm_id=MTYzMDA5MDE4"]
+2. ["北京市海淀区圆明园西路34号肖家河回迁住宅4号楼3单元103室 https://m.city8.com/bj/hotel/8868kf820k87b76b9f_address"]
+3. 个人转租，国企公寓 https://www.douban.com/group/topic/337437117/?_spm_id=MTYzMDA5MDE4
+4. 北京市海淀区圆明园西路34号肖家河回迁住宅4号楼3单元103室 https://m.city8.com/bj/hotel/8868kf820k87b76b9f_address
+5. 北京心家短租公寓 https://www.iinhotel.com/226699
+6. 窝趣_黑猫投诉_新浪网 https://tousu.sina.cn/company/view/?couid=5408000945
+7. 老业主委托出租 急租！豪装两居~ 婚房首租~ 看房方便！ http://m.anjuke.com/bj/rent/4581006673421323-3/
+8. 寓小二 - 租客专用 https://apps.apple.com/cn/app/%E5%AF%93%E5%B0%8F%E4%BA%8C-%E7%A7%9F%E5%AE%A2%E4%B8%93%E7%94%A8/id1483757276?see-all=reviews</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -7009,39 +7379,44 @@
         <x:v>北京市安宁庄西三条9号</x:v>
       </x:c>
       <x:c r="E138" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F138" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G138" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H138" t="n">
-        <x:v>7.2</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="I138" t="str">
-        <x:v>位于清河站附近，租金约4300元，适合应届生落脚，但部分证据源于社交分享，需实地核实。</x:v>
+        <x:v>租金极具性价比且通勤便利，但缺乏该公寓直接信息，存在信息泛化与误命中风险。</x:v>
       </x:c>
       <x:c r="J138" t="str">
-        <x:v>清河街道四方运通综合楼北京市清河中学. 4300元/月</x:v>
+        <x:v>月租大约在4800-5670元，合租次卧约2050元/月；，极小开间约1450元/月</x:v>
       </x:c>
       <x:c r="K138" t="str">
-        <x:v>刚才... ### 又是一年金丝桃. ### 存钱并且保持舒适甚至高品质生活的一点技巧心得分享（应届生版）. 保持舒适甚至高品质生活是对我自己来说的，包括且不局限于：每年出国旅行一次、国内旅行一次、购买想要的电子产品等 一、利用刚毕业的优势 1、大学生就业补贴 建议到小红书上搜索工作所在... ### 很多爱好真的0基础也完全可以上手的！</x:v>
+        <x:v>海淀保租房项目租金按市场评估价的60%-80%收取，包含家具家电使用费和物业费。；无哇哈哈青年公寓直接房屋质量信息，周边同类型公寓多为精装修，户型包含开间、一居室、两居室等，部分公寓配备电梯，民水民电，房东/物业维修响应较积极；；未查询到该公寓具体房龄、隔音相关评价。</x:v>
       </x:c>
       <x:c r="L138" t="str">
-        <x:v>北京市海淀区清河街道四方运通综合楼北京市清河中学. 4300元/月 6个房型| 1套在租 · 北太平庄地铁站店 随时入住. 欣悦青年社区·北太平庄地铁站店.。；刚才... ### 又是一年金丝桃. ### 存钱并且保持舒适甚至高品质生活的一点技巧心得分享（应届生版）. 保持舒适甚至高品质生活是对我自己来说的，包括且不局限于：每年出国旅行一次、国内旅行一次、购买想要的电子产品等 一、利用刚毕业的优势 1、大学生就业补贴 建议到小红书上搜索工作所在... ### 很多爱好真的0基础也完全可以上手的！；6.希望食材、... ### 读研三年，学校给了我二十万. 请进来跟这位小镇女孩说声恭喜好嘛！；以下菜谱也只是俺个... ### 住了两年的家 分享. ### 五一9天8晚意大利西班牙人均1.28w. 路线米兰-多洛米蒂-威尼斯-巴塞罗那-罗马 💰支出，人均12800左右 🎫交通 4723 成都米兰-罗马成都 机票 3617 米兰机场大巴 40 米兰到特伦特 146.5 博尔扎诺到威尼斯 242.5 威尼斯... ### 我发现小东西买可以接受的最贵的，真的效益很高. 我最近突然发现一个特别真实的真理，就是：很多高频使用的小东西，买贵的，幸福感提升巨大，但很多大件，贵很多，体验却没有差那么多。；书中的《查莫宁及其... &lt;前页 1 2 3 4 5 6 7 8 9 ... 新组 追剧 书影音 人文 闲趣 兴趣 生活 美食 家居 体育运动 宠物 艺术 科技 情感 科学自然 学习 校园 ACG 职场 理财. #### 1 我们喜欢逛公园. #### 2 乘风破浪的姐姐. #### 3 丧心病狂攒钱小组. #### 5 大学后悔学小语种. #### 6 爱短剧组. #### 7 哈哈哈哈哈哈哈哈哈哈哈. #### 8 榜单图书鉴评中心.。</x:v>
-      </x:c>
-      <x:c r="M138" t="str"/>
+        <x:v>哇哈哈青年公寓(清河地铁站店) 火山联网搜索汇总。；公开信息中未查询到哇哈哈青年公寓(清河地铁站店)直接租金信息，周边同区域一居室月租大约在4800-5670元，合租次卧约2050元/月，极小开间约1450元/月；；无哇哈哈青年公寓直接房屋质量信息，周边同类型公寓多为精装修，户型包含开间、一居室、两居室等，部分公寓配备电梯，民水民电，房东/物业维修响应较积极；；位置临近清河地铁站，距离小米科技园约800米，到上地元中心骑车可达，通勤便利；；周边有沁春汇购物中心、西二旗益民商城、美时美家超市，餐饮配套完善，距离北京龙城医院约1公里左右，医疗购物生活便利。</x:v>
+      </x:c>
+      <x:c r="M138" t="str">
+        <x:v>搜索结果未直接命中哇哈哈青年公寓(清河地铁站店)的对应租房信息，多数为周边区域其他房源，存在同名误命中或信息泛化的可能，未查询到该公寓明确差评信息。</x:v>
+      </x:c>
       <x:c r="N138" t="str">
-        <x:v>价格线索：清河街道四方运通综合楼北京市清河中学. 4300元/月；房屋质量/户型线索：刚才... ### 又是一年金丝桃. ### 存钱并且保持舒适甚至高品质生活的一点技巧心得分享（应届生版）. 保持舒适甚至高品质生活是对我自己来说的，包括且不局限于：每年出国旅行一次、国内旅行一次、购买想要的电子产品等 一、利用刚毕业的优势 1、大学生就业补贴 建议到小红书上搜索工作所在... ### 很多爱好真的0基础也完全可以上手的！；生活便利线索：北京市海淀区清河街道四方运通综合楼北京市清河中学. 4300元/月 6个房型| 1套在租 · 北太平庄地铁站店 随时入住. 欣悦青年社区·北太平庄地铁站店.。；刚才... ### 又是一年金丝桃. ### 存钱并且保持舒适甚至高品质生活的一点技巧心得分享（应届生版）. 保持舒适甚至高品质生活是对我自己来说的，包括且不局限于：每年出国旅行一次、国内旅行一次、购买想要的电子产品等 一、利用刚毕业的优势 1、大学生就业补贴 建议到小红书上搜索工作所在... ### 很多爱好真的0基础也完全可以上手的！；6.希望食材、... ### 读研三年，学校给了我二十万. 请进来跟这位小镇女孩说声恭喜好嘛！；以下菜谱也只是俺个... ### 住了两年的家 分享. ### 五一9天8晚意大利西班牙人均1.28w. 路线米兰-多洛米蒂-威尼斯-巴塞罗那-罗马 💰支出，人均12800左右 🎫交通 4723 成都米兰-罗马成都 机票 3617 米兰机场大巴 40 米兰到特伦特 146.5 博尔扎诺到威尼斯 242.5 威尼斯... ### 我发现小东西买可以接受的最贵的，真的效益很高. 我最近突然发现一个特别真实的真理，就是：很多高频使用的小东西，买贵的，幸福感提升巨大，但很多大件，贵很多，体验却没有差那么多。；书中的《查莫宁及其... &lt;前页 1 2 3 4 5 6 7 8 9 ... 新组 追剧 书影音 人文 闲趣 兴趣 生活 美食 家居 体育运动 宠物 艺术 科技 情感 科学自然 学习 校园 ACG 职场 理财. #### 1 我们喜欢逛公园. #### 2 乘风破浪的姐姐. #### 3 丧心病狂攒钱小组. #### 5 大学后悔学小语种. #### 6 爱短剧组. #### 7 哈哈哈哈哈哈哈哈哈哈哈. #### 8 榜单图书鉴评中心.。</x:v>
+        <x:v>价格线索：月租大约在4800-5670元，合租次卧约2050元/月；，极小开间约1450元/月；房屋质量/户型线索：海淀保租房项目租金按市场评估价的60%-80%收取，包含家具家电使用费和物业费。；无哇哈哈青年公寓直接房屋质量信息，周边同类型公寓多为精装修，户型包含开间、一居室、两居室等，部分公寓配备电梯，民水民电，房东/物业维修响应较积极；；未查询到该公寓具体房龄、隔音相关评价。；生活便利线索：哇哈哈青年公寓(清河地铁站店) 火山联网搜索汇总。；公开信息中未查询到哇哈哈青年公寓(清河地铁站店)直接租金信息，周边同区域一居室月租大约在4800-5670元，合租次卧约2050元/月，极小开间约1450元/月；；无哇哈哈青年公寓直接房屋质量信息，周边同类型公寓多为精装修，户型包含开间、一居室、两居室等，部分公寓配备电梯，民水民电，房东/物业维修响应较积极；；位置临近清河地铁站，距离小米科技园约800米，到上地元中心骑车可达，通勤便利；；周边有沁春汇购物中心、西二旗益民商城、美时美家超市，餐饮配套完善，距离北京龙城医院约1公里左右，医疗购物生活便利。；风险线索：搜索结果未直接命中哇哈哈青年公寓(清河地铁站店)的对应租房信息，多数为周边区域其他房源，存在同名误命中或信息泛化的可能，未查询到该公寓明确差评信息。</x:v>
       </x:c>
       <x:c r="O138" t="str">
-        <x:v>1. 月租千元拎包入住！海淀清河为新就业群体建起暖心公寓 - 北京日报 https://xinwen.bjd.com.cn/content/s69dfa1ddd5de6b42d6f3c485.html
-2. 北京公寓出租_北京精装公寓出租信息-北京链家找房 https://ifeng-m.lianjia.com/chuzu/bj/apartment/haidianqu/amp5amp4amp2ama1
-3. 海淀清河租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/haidian-q-qinghe
-4. 北京海淀租房小组 - 豆瓣 https://m.douban.com/group/hdzufang
-5. 海淀“六折”青年公寓1套房1.4人抢 - 凤凰网 https://i.ifeng.com/c/8kTAjxGhMn6</x:v>
+        <x:v>1. ["北京海淀|13号线清河地铁站imoma一居室公寓转租","https://www.douban.com/group/topic/341522452/?_spm_id=MTc5ODU1Nzcw"]
+2. ["北京海淀区面向毕业大学生配租2161套房源","https://www.beijing.gov.cn/fuwu/bmfw/sy/jrts/202604/t20260409_4577900.html"]
+3. 北京海淀|13号线清河地铁站imoma一居室公寓转租 https://www.douban.com/group/topic/341522452/?_spm_id=MTc5ODU1Nzcw
+4. 北京海淀区面向毕业大学生配租2161套房源 https://www.beijing.gov.cn/fuwu/bmfw/sy/jrts/202604/t20260409_4577900.html
+5. 清河 2室2厅1卫 http://m.anjuke.com/xt/rent/4602833580827655-2/
+6. 上地安宁庄西三旗，小米元中心，可免押月付，公积金直付，随时看 http://m.anjuke.com/ch/rent/4562829868508173-3/
+7. 整租|急租！海淀清河小营桥地铁口，高端公寓整租一居，无中介 http://m.anjuke.com/bj/rent/4485608327699457-3/
+8. 安宁庄带电梯 南向 中楼层4居室次卧2 http://m.anjuke.com/bj/rent/4527280137804804-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -7058,39 +7433,44 @@
         <x:v>北京市海淀区大有庄100号74号楼</x:v>
       </x:c>
       <x:c r="E139" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F139" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G139" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H139" t="n">
-        <x:v>8</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I139" t="str">
-        <x:v>政策性保租房价格极具优势，配套设施高档完善，但需符合申请资格且通勤距离稍远。</x:v>
+        <x:v>环境优美安静，装修品质高且临近地铁，适合预算充足、追求居住品质的租客。</x:v>
       </x:c>
       <x:c r="J139" t="str">
-        <x:v>租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；）. 北京市海淀区白家疃路. 2100-4200元/月；租赁期第1-2、3-4、5-6年租金分别2365元/月</x:v>
+        <x:v>-9500元，具体：54平米豪华装修两居7400元/月；，72平米精装修两居8000元/月；，80平米精装修两居7500元/月；，86平米精装修两居6500元/月；，三居室整租约8500元/月</x:v>
       </x:c>
       <x:c r="K139" t="str">
-        <x:v>项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；租金方面，青年公寓的租金将在备案租金价格的基础上，头两年按照六折收取，最小的户型每月折后房租约1840元（下图）。；当前位置：首页-&gt;信息公开大厅-&gt;区房管局-&gt;重点领域-&gt;保障住房-&gt;分配房源. | 索引号 | 11F/2026-19918 | 公开责任部门 | 区房管局 |. | 生成日期 | 2026年04月08日 10:00 | 公开日期 | 2026年04月08日 10:00 |. | 附件 | 附件1.保障性租赁住房专项配租平台APP操作手册.pdf 附件2.保障性租赁住房专项配租平台WEB操作手册.pdf 附件3.项目基本情况介绍.zip 附件4.社保缴纳材料查询步骤.doc 附件5.承诺书.docx |. 租金单价包含家具家电使用费、物业费,不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用。</x:v>
+        <x:v>大有庄100号院（中央党校院内）两居室整租月租范围约6500-9500元，具体：54平米豪华装修两居7400元/月，72平米精装修两居8000元/月，80平米精装修两居7500元/月，86平米精装修两居6500元/月，三居室整租约8500元/月，普遍付款方式为押一付三，中介费用为半个月至一个月租金。；多为精装修/豪华装修，户型以南北通透两居室为主，部分带电梯，楼体多为5-6层低楼层建筑，小区绿化率高，环境安静舒适，多数房源家具家电齐全可拎包入住，小区提供物业管理，有停车位，公开信息中未提及明确房龄和隔音负面反馈。</x:v>
       </x:c>
       <x:c r="L139" t="str">
-        <x:v>配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。；下一步，海淀区“两区”建设将进一步筑巢引凤、服务人才，不断完善自贸试验区周边配套设施，全力打造青年人才宜居宜业环境，吸引更多国际优秀创新人才来到海淀、扎根海淀。；国内普通高等学校毕业生提供学历证书或《教育部学历证书电子注册备案表》、学位证书或《中国高等教育学位在线验证报告》；；如2026年1月1日（含）以后毕业的毕业生尚未取得学历、学位证书的，可先行提供《毕业生就业推荐表》（信息应清晰完整并加盖学校公章）或《教育部学籍在线验证报告》；；整租·皂君庙·青年公寓·1室·1厅. 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校. 海淀皂君庙双安青年公寓 1室1厅 41.7㎡ 650. 相寓 皂君庙·青年公寓·中楼层·1居室. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |. | | 常州租房 | **H** | 杭州租房 | | 宁波租房 | | 石家庄租房 | **Z** | 郑州租房 |.。</x:v>
-      </x:c>
-      <x:c r="M139" t="str"/>
+        <x:v>通勤：距离4号线北宫门地铁站步行约460米，距离西苑站步行约844米，通勤便利；；商超：周边有龙湖星悦荟、北京华联BHG Mall、红美超市等，购物方便；；医疗：附近有北医三院中央党校院区、中国中医科学院西苑医院，医疗资源充足；；餐饮休闲：周边配套餐饮齐全，临近颐和园、谐趣园等公园，适合休闲。</x:v>
+      </x:c>
+      <x:c r="M139" t="str">
+        <x:v>暂未找到公开用户差评信息。</x:v>
+      </x:c>
       <x:c r="N139" t="str">
-        <x:v>价格线索：租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；）. 北京市海淀区白家疃路. 2100-4200元/月；租赁期第1-2、3-4、5-6年租金分别2365元/月；房屋质量/户型线索：项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；租金方面，青年公寓的租金将在备案租金价格的基础上，头两年按照六折收取，最小的户型每月折后房租约1840元（下图）。；当前位置：首页-&gt;信息公开大厅-&gt;区房管局-&gt;重点领域-&gt;保障住房-&gt;分配房源. | 索引号 | 11F/2026-19918 | 公开责任部门 | 区房管局 |. | 生成日期 | 2026年04月08日 10:00 | 公开日期 | 2026年04月08日 10:00 |. | 附件 | 附件1.保障性租赁住房专项配租平台APP操作手册.pdf 附件2.保障性租赁住房专项配租平台WEB操作手册.pdf 附件3.项目基本情况介绍.zip 附件4.社保缴纳材料查询步骤.doc 附件5.承诺书.docx |. 租金单价包含家具家电使用费、物业费,不包含供暖费、水费、电费、电话费、上网费、有线电视费等费用。；生活便利线索：配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。；下一步，海淀区“两区”建设将进一步筑巢引凤、服务人才，不断完善自贸试验区周边配套设施，全力打造青年人才宜居宜业环境，吸引更多国际优秀创新人才来到海淀、扎根海淀。；国内普通高等学校毕业生提供学历证书或《教育部学历证书电子注册备案表》、学位证书或《中国高等教育学位在线验证报告》；；如2026年1月1日（含）以后毕业的毕业生尚未取得学历、学位证书的，可先行提供《毕业生就业推荐表》（信息应清晰完整并加盖学校公章）或《教育部学籍在线验证报告》；；整租·皂君庙·青年公寓·1室·1厅. 中关村 人民大学地铁口 青年公寓 紧靠双安商场 分校. 海淀皂君庙双安青年公寓 1室1厅 41.7㎡ 650. 相寓 皂君庙·青年公寓·中楼层·1居室. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |. | | 常州租房 | **H** | 杭州租房 | | 宁波租房 | | 石家庄租房 | **Z** | 郑州租房 |.。</x:v>
+        <x:v>价格线索：-9500元，具体：54平米豪华装修两居7400元/月；，72平米精装修两居8000元/月；，80平米精装修两居7500元/月；，86平米精装修两居6500元/月；，三居室整租约8500元/月；房屋质量/户型线索：大有庄100号院（中央党校院内）两居室整租月租范围约6500-9500元，具体：54平米豪华装修两居7400元/月，72平米精装修两居8000元/月，80平米精装修两居7500元/月，86平米精装修两居6500元/月，三居室整租约8500元/月，普遍付款方式为押一付三，中介费用为半个月至一个月租金。；多为精装修/豪华装修，户型以南北通透两居室为主，部分带电梯，楼体多为5-6层低楼层建筑，小区绿化率高，环境安静舒适，多数房源家具家电齐全可拎包入住，小区提供物业管理，有停车位，公开信息中未提及明确房龄和隔音负面反馈。；生活便利线索：通勤：距离4号线北宫门地铁站步行约460米，距离西苑站步行约844米，通勤便利；；商超：周边有龙湖星悦荟、北京华联BHG Mall、红美超市等，购物方便；；医疗：附近有北医三院中央党校院区、中国中医科学院西苑医院，医疗资源充足；；餐饮休闲：周边配套餐饮齐全，临近颐和园、谐趣园等公园，适合休闲。；风险线索：暂未找到公开用户差评信息。</x:v>
       </x:c>
       <x:c r="O139" t="str">
-        <x:v>1. 2025年6月北京海淀区青年公寓配租意向登记公告 http://bj.bendibao.com/zffw/202565/373135.shtm
-2. 海淀组团内配租922套青年公寓 - 开放北京 https://open.beijing.gov.cn/html//haidian/gzdt/2025/6/1750038168814.html
-3. 选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网 https://www.stdaily.com/web/gdxw/2025-06/06/content_351160.html
-4. 海淀推近千套“青年公寓”头两年租金打六折 - 凤凰网 https://i.ifeng.com/c/8jvymsBYC7Q
-5. 海淀区 - 北京公寓出租_北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment/haidianqu/amp6amp4ama0</x:v>
+        <x:v>1. ["中央党校 大有庄 精装修两居室 南北通透 带电梯 随时入住","http://m.anjuke.com/bj/rent/4530418453879810-3/"]
+2. ["中央党校 大有庄100号院 精装两居 随时看房 家具家电齐全","http://m.anjuke.com/bj/rent/4577192292066317-3/"]
+3. ["大有庄100号院租房","http://m.anjuke.com/bj/community/850085/rent/"]
+4. ["中央党校 大有庄100号院精装修两居室带电梯 随时看房入住","http://m.anjuke.com/ch/rent/4546132002251781-3/"]
+5. 中央党校 大有庄 精装修两居室 南北通透 带电梯 随时入住 http://m.anjuke.com/bj/rent/4530418453879810-3/
+6. 中央党校 骚子营 燕北园 业主直签 南北两居 采光好 配置全 http://m.anjuke.com/bj/rent/4599815999269890-3/
+7. 中央党校 大有庄100号院 精装两居 随时看房 家具家电齐全 http://m.anjuke.com/bj/rent/4577192292066317-3/
+8. 党校宿舍 2室2厅1卫 http://m.anjuke.com/gl/rent/4214502576598020-2/</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -7107,39 +7487,44 @@
         <x:v>龙域西二路融泽嘉园西2号楼2单元703</x:v>
       </x:c>
       <x:c r="E140" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F140" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G140" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H140" t="n">
-        <x:v>8.9</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="I140" t="str">
-        <x:v>紧邻软件园，租金极具竞争力，物业管理规范，是网易员工通勤的首选成熟社区。</x:v>
+        <x:v>房龄较新且租金适中，紧邻软件园核心区，是互联网大厂员工的高性价比之选。</x:v>
       </x:c>
       <x:c r="J140" t="str">
-        <x:v>2026-05-03 | 216万 | 34642元/㎡；-16 15:35 |. | 房东直租，2100元/月；租金：仅提供一房、面积26平方米，租金价格2300元/月</x:v>
+        <x:v>合租次卧：1600-2200元/月；合租主卧：1800-2800元/月；整租一居室约5510元/月；整租两居室约6000-7000元/月</x:v>
       </x:c>
       <x:c r="K140" t="str">
-        <x:v>该小区属于回龙观板块，存在少许几种户型，大多是2室，值得注意的是目前在售很少，房源面积62平到115平不等，户型偏中等. 大家都在问（40） 查看更多 · 【融泽嘉园8号院】小区。；更新于 2026-06-01 10:58:22. 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片. # 融泽嘉园. 1室(2) 2室(9) 3室(4). 融泽嘉园3室1厅1卫108㎡户型图 3室1厅1卫 108㎡ 咨询户型房源. 融泽嘉园最新房价的均价约为50184元/平米。；第二，融泽嘉园是由长城物业提供物业服务，服务优质有保障。；### 融泽嘉园. ### 小区行情周报. ### 小区攻略. ### 小区评分8.6分. ### 小区信息全方位解读. ### 融泽嘉园主力户型. ### 融泽嘉园成交记录. | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 |. | 62.64㎡ | 2026-05-03 | 216万 | 34642元/㎡ | 市场信息 |. ### 融泽嘉园价格走势. ### 融泽嘉园房贷计算器更多贷款计算. #### 账单总价. ### 附近小区. ### 融泽嘉园相册 户型图(76)实景图(31). ### 融泽嘉园问答 查看更多问答. ### 相关资讯. * 小区资讯北京昌平上周(11.3-11.9)热搜小区榜,购房者更关注融泽嘉园2025-11-10. * 小区资讯北京昌平上周(10.27-11.2)热搜小区榜,融泽嘉园为最受欢迎小区2025-11-03. * 小区资讯北京昌平上周(10.13-10.19),融泽嘉园登昌平热搜小区榜首2025-10-20. ### 您可能感兴趣的租房 查看更多租房. ### 您可能感兴趣的新房楼盘. **免责声明**\*小区中涉及的价。；### 融泽嘉园. ### 小区行情周报. ### 小区攻略. ### 小区评分8.6分. ### 小区信息全方位解读. ### 融泽嘉园主力户型. ### 融泽嘉园成交记录. | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 |. | 62.64㎡ | 2026-05-03 | 216万 | 34642元/㎡ | 市场信息 |. ### 融泽嘉园价格走势. ### 融泽嘉园房贷计算器更多贷款计算. #### 账单总价. ### 附近小区. ### 融泽嘉园相册 户型图(76)实景图(31). ### 融泽嘉园问答 查看更多问答. ### 相关资讯. * 小区资讯北京昌平上周(11.3-11.9)热搜小区榜,购房者更关注融泽嘉园2025-11-10. * 小区资讯北京昌平上周(10.27-11.2)热搜小区榜,融泽嘉园为最受欢迎小区2025-11-03. * 小区资讯北京昌平上周(10.13-10.19),融泽嘉园登昌平热搜小区榜首2025-10-20. ### 您可能感兴趣的租房 查看更多租房. ### 您可能感兴趣的新房楼盘. **免责声明**\*小区中涉及的价格经由房天下大数据统计分析计算得出，价格统计不能覆盖所有房源，并且有滞后，仅供参考。</x:v>
+        <x:v>房龄：融泽嘉园为回迁房小区，楼龄较新；；户型：合租多为3室1厅，整租有一居、两居，整体南北通透，布局合理，采光好；；装修：多为全新精装修，轻奢/现代风格，配套家电家具齐全，干净整洁；；隔音：部分房源标注卧室不紧挨，隔音效果较好，小区环境安静；；物业：提供免费维修、公共区域保洁服务，可协助办理居住证，部分品牌中介提供标准化物业服务。</x:v>
       </x:c>
       <x:c r="L140" t="str">
-        <x:v>融泽嘉园位于昌平西二旗北侧龙域中路金域华府北面，附近交通便利，出行十分方便。；. 融泽嘉园配套很好。；第一，融泽嘉园位于昌平西二旗北侧龙域中路金域华府北面，交通便利。；. 融泽嘉园的容积率2.6，绿化率38.0，环境优雅，非常适宜居住生活。；融泽嘉园的位置在昌平西二旗北侧龙域中路金域华府北面，地处交通便捷，生活设施齐全的地段，生活更加便利。</x:v>
-      </x:c>
-      <x:c r="M140" t="str"/>
+        <x:v>装修：多为全新精装修，轻奢/现代风格，配套家电家具齐全，干净整洁；；通勤：临近中关村软件园、小米/快手/百度园区，步行到18号线龙泽西约1.2公里，步行到13号线龙泽约2公里，有多条公交经过，适合周边上班人群；；商超：周边有日日生鲜、乐惠万家超市，昌发展万科广场、北京华联BHG Mall在3公里范围内，配套齐全；；医院：距离北京积水潭医院（新龙泽院区）约3公里，医疗便利；；餐饮：周边餐饮发达，各类餐品齐全，楼下有咖啡、休闲门店。</x:v>
+      </x:c>
+      <x:c r="M140" t="str">
+        <x:v>搜索到的房源均为融泽嘉园西2号院普通住宅合租/整租房源，未找到明确对应地址「龙域西二路融泽嘉园西2号楼2单元703」公寓式酒店的专属口碑信息，存在房源同名泛化，未找到针对该具体公寓的差评信息，部分中介房源收取中介费（金额约为1个月租金）。</x:v>
+      </x:c>
       <x:c r="N140" t="str">
-        <x:v>价格线索：2026-05-03 | 216万 | 34642元/㎡；-16 15:35 |. | 房东直租，2100元/月；租金：仅提供一房、面积26平方米，租金价格2300元/月；房屋质量/户型线索：该小区属于回龙观板块，存在少许几种户型，大多是2室，值得注意的是目前在售很少，房源面积62平到115平不等，户型偏中等. 大家都在问（40） 查看更多 · 【融泽嘉园8号院】小区。；更新于 2026-06-01 10:58:22. 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片 融泽嘉园实景图图片. # 融泽嘉园. 1室(2) 2室(9) 3室(4). 融泽嘉园3室1厅1卫108㎡户型图 3室1厅1卫 108㎡ 咨询户型房源. 融泽嘉园最新房价的均价约为50184元/平米。；第二，融泽嘉园是由长城物业提供物业服务，服务优质有保障。；### 融泽嘉园. ### 小区行情周报. ### 小区攻略. ### 小区评分8.6分. ### 小区信息全方位解读. ### 融泽嘉园主力户型. ### 融泽嘉园成交记录. | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 |. | 62.64㎡ | 2026-05-03 | 216万 | 34642元/㎡ | 市场信息 |. ### 融泽嘉园价格走势. ### 融泽嘉园房贷计算器更多贷款计算. #### 账单总价. ### 附近小区. ### 融泽嘉园相册 户型图(76)实景图(31). ### 融泽嘉园问答 查看更多问答. ### 相关资讯. * 小区资讯北京昌平上周(11.3-11.9)热搜小区榜,购房者更关注融泽嘉园2025-11-10. * 小区资讯北京昌平上周(10.27-11.2)热搜小区榜,融泽嘉园为最受欢迎小区2025-11-03. * 小区资讯北京昌平上周(10.13-10.19),融泽嘉园登昌平热搜小区榜首2025-10-20. ### 您可能感兴趣的租房 查看更多租房. ### 您可能感兴趣的新房楼盘. **免责声明**\*小区中涉及的价。；### 融泽嘉园. ### 小区行情周报. ### 小区攻略. ### 小区评分8.6分. ### 小区信息全方位解读. ### 融泽嘉园主力户型. ### 融泽嘉园成交记录. | 房源面积 | 成交时间 | 成交总价 | 成交均价 | 信息来源 |. | 62.64㎡ | 2026-05-03 | 216万 | 34642元/㎡ | 市场信息 |. ### 融泽嘉园价格走势. ### 融泽嘉园房贷计算器更多贷款计算. #### 账单总价. ### 附近小区. ### 融泽嘉园相册 户型图(76)实景图(31). ### 融泽嘉园问答 查看更多问答. ### 相关资讯. * 小区资讯北京昌平上周(11.3-11.9)热搜小区榜,购房者更关注融泽嘉园2025-11-10. * 小区资讯北京昌平上周(10.27-11.2)热搜小区榜,融泽嘉园为最受欢迎小区2025-11-03. * 小区资讯北京昌平上周(10.13-10.19),融泽嘉园登昌平热搜小区榜首2025-10-20. ### 您可能感兴趣的租房 查看更多租房. ### 您可能感兴趣的新房楼盘. **免责声明**\*小区中涉及的价格经由房天下大数据统计分析计算得出，价格统计不能覆盖所有房源，并且有滞后，仅供参考。；生活便利线索：融泽嘉园位于昌平西二旗北侧龙域中路金域华府北面，附近交通便利，出行十分方便。；. 融泽嘉园配套很好。；第一，融泽嘉园位于昌平西二旗北侧龙域中路金域华府北面，交通便利。；. 融泽嘉园的容积率2.6，绿化率38.0，环境优雅，非常适宜居住生活。；融泽嘉园的位置在昌平西二旗北侧龙域中路金域华府北面，地处交通便捷，生活设施齐全的地段，生活更加便利。</x:v>
+        <x:v>价格线索：合租次卧：1600-2200元/月；合租主卧：1800-2800元/月；整租一居室约5510元/月；整租两居室约6000-7000元/月；房屋质量/户型线索：房龄：融泽嘉园为回迁房小区，楼龄较新；；户型：合租多为3室1厅，整租有一居、两居，整体南北通透，布局合理，采光好；；装修：多为全新精装修，轻奢/现代风格，配套家电家具齐全，干净整洁；；隔音：部分房源标注卧室不紧挨，隔音效果较好，小区环境安静；；物业：提供免费维修、公共区域保洁服务，可协助办理居住证，部分品牌中介提供标准化物业服务。；生活便利线索：装修：多为全新精装修，轻奢/现代风格，配套家电家具齐全，干净整洁；；通勤：临近中关村软件园、小米/快手/百度园区，步行到18号线龙泽西约1.2公里，步行到13号线龙泽约2公里，有多条公交经过，适合周边上班人群；；商超：周边有日日生鲜、乐惠万家超市，昌发展万科广场、北京华联BHG Mall在3公里范围内，配套齐全；；医院：距离北京积水潭医院（新龙泽院区）约3公里，医疗便利；；餐饮：周边餐饮发达，各类餐品齐全，楼下有咖啡、休闲门店。；风险线索：搜索到的房源均为融泽嘉园西2号院普通住宅合租/整租房源，未找到明确对应地址「龙域西二路融泽嘉园西2号楼2单元703」公寓式酒店的专属口碑信息，存在房源同名泛化，未找到针对该具体公寓的差评信息，部分中介房源收取中介费（金额约为1个月租金）。</x:v>
       </x:c>
       <x:c r="O140" t="str">
-        <x:v>1. 融泽嘉园8号院 - 租房-北京安居客 https://beijing.anjuke.com/community/view/875814
-2. 融泽嘉园_北京融泽嘉园小区怎么样、二手房出售价格信息- 北京吉屋网 https://bj.jiwu.com/loupan/802925.html
-3. 【北京融泽嘉园小区,二手房,租房】- 北京房天下 https://esf.fang.com/loupan/1010748145.htm
-4. 融泽嘉园小组 https://m.douban.com/group/624160
-5. 融泽嘉园西二路2号院- 北京 - 链家 https://bj.lianjia.com/xiaoqu/1120064286006656</x:v>
+        <x:v>1. ["融泽嘉园西2号院，龙泽租房，融泽嘉园 龙泽 西二旗 金域国际 中关村软件园 小米快手百度","https://bj.zu.anjuke.com/fangyuan/3752825845015552"]
+2. ["融泽嘉园西二号院，随时看房入住，临近中关村软件园，小米科技园","http://m.anjuke.com/bj/rent/4082002749074433-3/"]
+3. ["融泽嘉园 精装两居室 采光 近快手小米百度中关村软件园","http://m.anjuke.com/bj/rent/4583366130670607-3/"]
+4. ["融泽嘉园底价精装一居室 近快手小米百度中关村软件园","http://m.anjuke.com/bj/rent/4567261690735622-3/"]
+5. 【多图】融泽嘉园西2号院，龙域租房，融泽嘉园 龙泽 西二旗 金域国际 中关村软件园 小米快手百度，昌平租房 https://bj.zu.anjuke.com/fangyuan/3752825845015552
+6. 融泽嘉园西二号院，随时看房入住，临近中关村软件园，小米科技园 http://m.anjuke.com/bj/rent/4082002749074433-3/
+7. 融泽嘉园主卧合租|龙泽 西二旗 百度大厦 中关村软件园可短签 http://m.anjuke.com/bj/rent/3922815016886287-3/
+8. 融泽嘉园 精装两居室 采光 近快手小米百度中关村软件园 http://m.anjuke.com/bj/rent/4583366130670607-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -7156,39 +7541,43 @@
         <x:v>北京市海淀区清河小营金隅美和园4号楼</x:v>
       </x:c>
       <x:c r="E141" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F141" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G141" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H141" t="n">
-        <x:v>7.6</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="I141" t="str">
-        <x:v>地处上地核心区，交通与配套极佳，房龄适中且有电梯，虽有小瑕疵但综合居住素质较高。</x:v>
+        <x:v>位于成熟社区，生活配套完善且租金跨度大，适合对周边生活便利度有要求的租客。</x:v>
       </x:c>
       <x:c r="J141" t="str">
-        <x:v>海淀·上地 67829元/㎡； · 上地西里. 海淀·上地 83578元/㎡；北京美和园(金隅美和园东区)小区参考均价81494元/㎡；美和园，小区价格64978元/㎡</x:v>
+        <x:v>合租单间：1100-2700元/月；整租一居室：5200-5570元/月；整租两居室：5200-7200元/月；整租三居室：合租单间价格不等，整租四居室：7800元/月</x:v>
       </x:c>
       <x:c r="K141" t="str">
-        <x:v>美和园(金隅美和园东区)出租房源 · 两居室，上地地铁站精装修美和园全南向出租 · 2室2厅 | 85㎡ · 上地 · 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房。；1居室·7个户型. 62㎡~79㎡. 在售240万起 ;；2居室·29个户型. 62㎡~88㎡. 在售370万起 ;；3居室·11个户型. 75㎡~88㎡. 在售528万起 ;；4居室·3个户型. 78㎡~86㎡. 在售508万起。</x:v>
+        <x:v>小区建成于2008年，房龄适中；；多数房源为精装修，户型方正（涵盖一居到四居多种户型），部分带电梯，采光通风较好；；小区绿化率不低，环境安静，24小时保安，物业提供定期打扫卫生服务；；公开信息中未明确提及隔音相关负面评价；</x:v>
       </x:c>
       <x:c r="L141" t="str">
-        <x:v>美和园(金隅美和园东区)出租房源 · 两居室，上地地铁站精装修美和园全南向出租 · 2室2厅 | 85㎡ · 上地 · 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房。；第35集| 交通便利，配套完善，带电梯，08年社区，综合性价比很好，价格适中#高性价比好房 #现场实拍 #好房推荐 #同城优先推荐 #带你看房.。；实探两限房金隅美和园：大配套齐全小问题仍在 - 中国新闻网。；户型2-3室、了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等。；户型2-3室、了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等</x:v>
-      </x:c>
-      <x:c r="M141" t="str"/>
+        <x:v>商超：步行可达果优美生鲜超市，距离北京清河万象汇约900米，购物便利；；餐饮等生活配套成熟，周边餐饮选择丰富；</x:v>
+      </x:c>
+      <x:c r="M141" t="str">
+        <x:v>未找到针对4号楼该家庭公寓的集中差评信息。；未找到针对4号楼该家庭公寓的集中差评信息</x:v>
+      </x:c>
       <x:c r="N141" t="str">
-        <x:v>价格线索：海淀·上地 67829元/㎡； · 上地西里. 海淀·上地 83578元/㎡；北京美和园(金隅美和园东区)小区参考均价81494元/㎡；美和园，小区价格64978元/㎡；房屋质量/户型线索：美和园(金隅美和园东区)出租房源 · 两居室，上地地铁站精装修美和园全南向出租 · 2室2厅 | 85㎡ · 上地 · 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房。；1居室·7个户型. 62㎡~79㎡. 在售240万起 ;；2居室·29个户型. 62㎡~88㎡. 在售370万起 ;；3居室·11个户型. 75㎡~88㎡. 在售528万起 ;；4居室·3个户型. 78㎡~86㎡. 在售508万起。；生活便利线索：美和园(金隅美和园东区)出租房源 · 两居室，上地地铁站精装修美和园全南向出租 · 2室2厅 | 85㎡ · 上地 · 邻地铁 押一付一 配套齐全 精装修 南北通透 有阳台 首次出租 随时看房。；第35集| 交通便利，配套完善，带电梯，08年社区，综合性价比很好，价格适中#高性价比好房 #现场实拍 #好房推荐 #同城优先推荐 #带你看房.。；实探两限房金隅美和园：大配套齐全小问题仍在 - 中国新闻网。；户型2-3室、了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等。；户型2-3室、了解更多小区房源、房价、户型、绿化率、周边配套、产权、物业、开发商等</x:v>
+        <x:v>价格线索：合租单间：1100-2700元/月；整租一居室：5200-5570元/月；整租两居室：5200-7200元/月；整租三居室：合租单间价格不等，整租四居室：7800元/月；房屋质量/户型线索：小区建成于2008年，房龄适中；；多数房源为精装修，户型方正（涵盖一居到四居多种户型），部分带电梯，采光通风较好；；小区绿化率不低，环境安静，24小时保安，物业提供定期打扫卫生服务；；公开信息中未明确提及隔音相关负面评价；；生活便利线索：商超：步行可达果优美生鲜超市，距离北京清河万象汇约900米，购物便利；；餐饮等生活配套成熟，周边餐饮选择丰富；；风险线索：未找到针对4号楼该家庭公寓的集中差评信息。；未找到针对4号楼该家庭公寓的集中差评信息</x:v>
       </x:c>
       <x:c r="O141" t="str">
-        <x:v>1. 北京美和园(金隅美和园东区)租房，最新出租房源，租金走势信息 https://m.58.com/bj/xq/1084082
-2. 金隅美和园租房,房屋出租信息,整租,合租 - 北京二手房- 房天下 https://esf.fang.com/loupan/1010223051/chuzu/list/i31-g23
-3. 金隅美和园东区- 租房【北京链家网】 https://bj.lianjia.com/xiaoqu/1111027377531
-4. 北京美和园(金隅美和园东区)房价_二手房_租房 - 北京房产网 https://bj.loupan.com/community/41362.html
-5. 北京金隅美和园 - 抖音 https://www.douyin.com/search/%E5%8C%97%E4%BA%AC%E9%87%91%E9%9A%85%E7%BE%8E%E5%92%8C%E5%9B%AD</x:v>
+        <x:v>1. 【多图】美和园(金隅美和园东区)，上地租房，正规一居室|视野广采光足 价格还能谈!!，海淀租房 https://bj.zu.anjuke.com/fangyuan/4314796633103375
+2. 海淀 清河 美和园 4室1厅 民水民电 随时看房 http://m.anjuke.com/bj/rent/4545154256118795-3/
+3. 上地朱房路美和园精装主卧室出租 http://m.fang.com/zf/bj/JHAGT_484812382_14984761x1010223051_167160543.html
+4. 工作如此辛苦!在金隅美和园租房是家的感觉 http://m.fang.com/news/zf/bj/xiaoqu/42361958.html
+5. 我爱我家WAP https://m.5i5j.com/bj/ershoufang/houseevaluate/504527470.html
+6. 上地 金隅美和园7200南北通透两居 出租随时入住 http://m.anjuke.com/bj/rent/4416832025353218-3/?ad_type=j&amp;pagesource=12
+7. 紧邻上地地铁站 沃尔玛 美和园精装一居可做两居 采光好随时看 http://m.anjuke.com/ch/rent/4568476734417927-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -7205,39 +7594,44 @@
         <x:v>北京市龙域西二路融泽嘉园2期2号院1号楼4层一单元403</x:v>
       </x:c>
       <x:c r="E142" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F142" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G142" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H142" t="n">
-        <x:v>4</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="I142" t="str">
-        <x:v>证据信息跨区严重且指向不明，缺乏针对网易大厦周边的有效信息，评分保守。</x:v>
+        <x:v>位于融泽嘉园次新小区，配套成熟且通勤软件园便利，性价比高，证据较充分。</x:v>
       </x:c>
       <x:c r="J142" t="str">
-        <x:v>... 昌平-回龙观 流星花园三区 1500元/月；同层高，不同朝向，相应价位不同）地下车位1000元/月</x:v>
+        <x:v>00元/间，整租两居室月租约6400元-7000元/月</x:v>
       </x:c>
       <x:c r="K142" t="str">
-        <x:v>. 行政区域：北京市朝阳区东三环燕莎-朝阳公园 公寓地址：北京市朝阳区麦子店街38号. 房间数量：318（间） 户型介绍：开间、一居、两居、三居. 行政区域：北京市东城区--东二环朝阳门 公寓地址：北京市东城区朝阳门外三丰北里9号. 户型面积（平米）价格（人民币元/月）. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 400-100-1111，链家旗下长租公寓品牌及青年居住社区，是提供居住产品与生活服务的O2O互联网公司，旗下拥有自如友家、自如整租、业主直租、自如豪宅、自如寓、自如驿、自如ZSPACE等产品，为合租、整租、短租、中高端租住需求设计了多种产品形式，并提供保洁、维修、搬家等居间服务。；. 400-686-8006，房地产综合服务提供商世联行旗下出租公寓品牌，专注为解决中国房地产存量物业空置问题而生的创新平台，瞄准青年租房市场，为城市白领提供设计、质感、乐趣的居住体验。；. 房间数量：407（间） 户型介绍：一居、两居、三居、四居. 以上价位区间为（同以面积，不同层高，不同朝向，相应价位不同）地下车位1000元/月。；. 租金价格包含：会所、物业管理费、供暖、宽带、wifi/卫星电视、水费、电费、每周2次保洁。；. 租金价格包含：会所、物业管理费、供暖、宽带、wifi、卫星电视、水电燃气费、每周2次保洁. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、饭店、苏州园林风格别墅、网球场、壁球室、阅览室、体操房、互联网宽带、卫星电视（CNN/BBC/CNBC/HBO）、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 商业：家乐福超市、燕沙购物中心、中联广场、蓝岛大厦、华普购物中心、俏江南、麻辣诱惑、东方花园饭店，银座，来福士，小商品购物市场. 4006-565-565，隶属于城家酒店管理有限公司，华住酒店集团和IDG资本共同出资成立的集中式公寓品牌，致力打造空间、生活、服务的共享居住平台，旗下拥有城家公寓、城家高级公寓、城家奢华系列、城家精选公寓、CitiGO欢阁公寓酒店、员宿等品牌产品。</x:v>
+        <x:v>该小区融泽嘉园2期合租单间月租约2100元-2200元/间，整租两居室月租约6400元-7000元/月，支持押一付一，部分房源无中介费，民水民电，包物业宽带取暖。；该房源所在小区为融泽嘉园，属于次新小区，花兮公寓该房源为精装修，户型多为方正，采光通风较好；；部分房源提到卧室不紧邻，隔音效果较好，小区绿化率高，环境优美，全天保安巡逻，治安良好，配备管家售后维修服务。；未查询到房龄明确信息。</x:v>
       </x:c>
       <x:c r="L142" t="str">
-        <x:v>: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；... 昌平-回龙观 流星花园三区 1500元/月. 距8号线-平西府站917m. 昌平-回龙观 流星花园三区出租房源图片 8号线平西府流星花园三区南向主卧带卫生间配套全采光佳 3室1厅 20m²。；. 北京雅诗阁来福士中心服务公寓位于北京交通枢纽东直门。；作为北京来福士中心综合体的一部分，公寓坐享商场和写字楼的优势，为住客提供集餐饮、购物、休闲、文化、商务为一体的多元化生活方式。</x:v>
-      </x:c>
-      <x:c r="M142" t="str"/>
+        <x:v>通勤方面：步行到18号线龙泽西约1200米，到13号线龙泽/西二旗约1800米，临近中关村软件园、小米科技园，适合周边上班族；；生活配套：小区周边有大型商超、便利店，餐饮发达，满足日常需求，周边有公交直达小区门口，生活便利，未查询到周边医院明确信息。</x:v>
+      </x:c>
+      <x:c r="M142" t="str">
+        <x:v>未查询到明确差评信息。</x:v>
+      </x:c>
       <x:c r="N142" t="str">
-        <x:v>价格线索：... 昌平-回龙观 流星花园三区 1500元/月；同层高，不同朝向，相应价位不同）地下车位1000元/月；房屋质量/户型线索：. 行政区域：北京市朝阳区东三环燕莎-朝阳公园 公寓地址：北京市朝阳区麦子店街38号. 房间数量：318（间） 户型介绍：开间、一居、两居、三居. 行政区域：北京市东城区--东二环朝阳门 公寓地址：北京市东城区朝阳门外三丰北里9号. 户型面积（平米）价格（人民币元/月）. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 400-100-1111，链家旗下长租公寓品牌及青年居住社区，是提供居住产品与生活服务的O2O互联网公司，旗下拥有自如友家、自如整租、业主直租、自如豪宅、自如寓、自如驿、自如ZSPACE等产品，为合租、整租、短租、中高端租住需求设计了多种产品形式，并提供保洁、维修、搬家等居间服务。；. 400-686-8006，房地产综合服务提供商世联行旗下出租公寓品牌，专注为解决中国房地产存量物业空置问题而生的创新平台，瞄准青年租房市场，为城市白领提供设计、质感、乐趣的居住体验。；. 房间数量：407（间） 户型介绍：一居、两居、三居、四居. 以上价位区间为（同以面积，不同层高，不同朝向，相应价位不同）地下车位1000元/月。；. 租金价格包含：会所、物业管理费、供暖、宽带、wifi/卫星电视、水费、电费、每周2次保洁。；. 租金价格包含：会所、物业管理费、供暖、宽带、wifi、卫星电视、水电燃气费、每周2次保洁. 会所、健身房、游泳池、桑拿房、阅览室、便利店、餐厅、饭店、苏州园林风格别墅、网球场、壁球室、阅览室、体操房、互联网宽带、卫星电视（CNN/BBC/CNBC/HBO）、咖啡厅、早餐、中餐厅、西餐厅、美容美发、购物、多功能厅、会议室、银行、诊所、花店、酒吧、夜总会、停车场、. 商业：家乐福超市、燕沙购物中心、中联广场、蓝岛大厦、华普购物中心、俏江南、麻辣诱惑、东方花园饭店，银座，来福士，小商品购物市场. 4006-565-565，隶属于城家酒店管理有限公司，华住酒店集团和IDG资本共同出资成立的集中式公寓品牌，致力打造空间、生活、服务的共享居住平台，旗下拥有城家公寓、城家高级公寓、城家奢华系列、城家精选公寓、CitiGO欢阁公寓酒店、员宿等品牌产品。；生活便利线索：: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；... 昌平-回龙观 流星花园三区 1500元/月. 距8号线-平西府站917m. 昌平-回龙观 流星花园三区出租房源图片 8号线平西府流星花园三区南向主卧带卫生间配套全采光佳 3室1厅 20m²。；. 北京雅诗阁来福士中心服务公寓位于北京交通枢纽东直门。；作为北京来福士中心综合体的一部分，公寓坐享商场和写字楼的优势，为住客提供集餐饮、购物、休闲、文化、商务为一体的多元化生活方式。</x:v>
+        <x:v>价格线索：00元/间，整租两居室月租约6400元-7000元/月；房屋质量/户型线索：该小区融泽嘉园2期合租单间月租约2100元-2200元/间，整租两居室月租约6400元-7000元/月，支持押一付一，部分房源无中介费，民水民电，包物业宽带取暖。；该房源所在小区为融泽嘉园，属于次新小区，花兮公寓该房源为精装修，户型多为方正，采光通风较好；；部分房源提到卧室不紧邻，隔音效果较好，小区绿化率高，环境优美，全天保安巡逻，治安良好，配备管家售后维修服务。；未查询到房龄明确信息。；生活便利线索：通勤方面：步行到18号线龙泽西约1200米，到13号线龙泽/西二旗约1800米，临近中关村软件园、小米科技园，适合周边上班族；；生活配套：小区周边有大型商超、便利店，餐饮发达，满足日常需求，周边有公交直达小区门口，生活便利，未查询到周边医院明确信息。；风险线索：未查询到明确差评信息。</x:v>
       </x:c>
       <x:c r="O142" t="str">
-        <x:v>1. 北京市昌平区租房 - 房天下 http://www.fang.com/houses/zf_253758bj
-2. 昌平租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/changping
-3. 北京租房攻略 - 知乎专栏 https://zhuanlan.zhihu.com/p/406125060
-4. 2025年北京酒店式公寓+长租公寓百科-租房指南，深度解析 https://www.gongyuzufang.com/blog/1376.cshtml
-5. 北京宜居公寓价格、点评- 携程酒店 https://m.ctrip.com/html5/hotel/hoteldetail/23857605.html</x:v>
+        <x:v>1. ["融泽嘉园西二号院，龙域租房，融泽嘉园西二号院 | 精装两居室 小区环境好 18号线附近，昌平租房","http://m.anjuke.com/bj/rent/4509181416152075-3/"]
+2. ["融泽嘉园西二号院，随时看房入住，临近中关村软件园，小米科技园","http://m.anjuke.com/bj/rent/4082002749074433-3/"]
+3. ["融泽嘉园西2号中层南向两居随时看采光好 西二旗上地回龙观","http://m.anjuke.com/bj/rent/4571704677461005-3/"]
+4. ["融泽嘉园西2号院，龙域租房，融泽嘉园西2号院 3室1厅1卫 精装修 配套齐全 南北通透，昌平租房","http://m.anjuke.com/bj/rent/3499538908356622-3/"]
+5. 【多图】融泽嘉园西2号院，龙域租房，融泽嘉园西二号院 | 精装两居室 小区环境好 18号线附近，昌平租房 http://m.anjuke.com/bj/rent/4509181416152075-3/
+6. 融泽嘉园西二号院，随时看房入住，临近中关村软件园，小米科技园 http://m.anjuke.com/bj/rent/4082002749074433-3/
+7. 融泽嘉园西2号中层南向两居随时看采光好 西二旗上地回龙观 http://m.anjuke.com/bj/rent/4571704677461005-3/
+8. 融泽嘉园93平两居室 https://m.58.com/bj/zufang/83822850175197x.shtml</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -7254,39 +7648,40 @@
         <x:v>北京市海淀区邓庄北路与航天中路交叉路口往西约180米</x:v>
       </x:c>
       <x:c r="E143" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F143" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G143" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H143" t="n">
-        <x:v>7.5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I143" t="str">
-        <x:v>海淀保租房项目，租金低且配套好，虽非步行可达但性价比极高，适合青年人才。</x:v>
-      </x:c>
-      <x:c r="J143" t="str">
-        <x:v>租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；租赁期第1-2、3-4、5-6年租金分别2365元/月</x:v>
-      </x:c>
+        <x:v>信息多为区域泛化数据，缺乏该具体地址的准确评价，存在较大的信息误导风险。</x:v>
+      </x:c>
+      <x:c r="J143" t="str"/>
       <x:c r="K143" t="str">
-        <x:v>选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；双安青年公寓出租房源 · 中关村魏公村知春路海淀黄庄人民大学地铁站，可，随时入住 · 1室1厅 | 42.12㎡ · 中关村 · 独卫一居 可短租 邻地铁 押一付一 配套齐全 精装修 南北通透 有。；. 此外，微信搜索“掌上海淀”小程序，点击“房屋服务”-“住房保障”-“青年公寓”页面，可对“寓见西山”项目922套房源主要户型进行VR线上看房。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。</x:v>
+        <x:v>海淀官方配租的青年公寓房源包含开间、一居、两居户型，配齐家具家电可拎包入住；；周边同类公寓多为简单装修，部分小开间为独立厨卫。</x:v>
       </x:c>
       <x:c r="L143" t="str">
-        <x:v>配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。；下一步，海淀区“两区”建设将进一步筑巢引凤、服务人才，不断完善自贸试验区周边配套设施，全力打造青年人才宜居宜业环境，吸引更多国际优秀创新人才来到海淀、扎根海淀。；双安青年公寓出租房源 · 中关村魏公村知春路海淀黄庄人民大学地铁站，可，随时入住 · 1室1厅 | 42.12㎡ · 中关村 · 独卫一居 可短租 邻地铁 押一付一 配套齐全 精装修 南北通透 有。；国内普通高等学校毕业生提供学历证书或《教育部学历证书电子注册备案表》、学位证书或《中国高等教育学位在线验证报告》；；如2026年1月1日（含）以后毕业的毕业生尚未取得学历、学位证书的，可先行提供《毕业生就业推荐表》（信息应清晰完整并加盖学校公章）或《教育部学籍在线验证报告》；</x:v>
+        <x:v>周边昌平邓庄同类小开间月租约800-1000元，海淀中关村青年公寓1室42㎡月租约5510元。；周边同类公寓多为简单装修，部分小开间为独立厨卫。；该地址位于海淀邓庄北路与航天中路交叉口，属于海淀山后区域，暂未搜索到该具体位置的地铁、商超、医院等配套公开评价；；同类昌平邓庄公寓门口有公交站点，周边配套基本完善。；搜索结果中未找到该精确地址对应的青年公寓（公寓式酒店）的直接口碑信息，存在同名项目信息泛化、地址混淆风险，现有信息多为海淀全区青年配租项目或周边其他公寓信息，非目标公寓准确信息。</x:v>
       </x:c>
       <x:c r="M143" t="str"/>
       <x:c r="N143" t="str">
-        <x:v>价格线索：租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；和3153元/月；租赁期第1-2、3-4、5-6年租金分别2365元/月；房屋质量/户型线索：选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；双安青年公寓出租房源 · 中关村魏公村知春路海淀黄庄人民大学地铁站，可，随时入住 · 1室1厅 | 42.12㎡ · 中关村 · 独卫一居 可短租 邻地铁 押一付一 配套齐全 精装修 南北通透 有。；. 此外，微信搜索“掌上海淀”小程序，点击“房屋服务”-“住房保障”-“青年公寓”页面，可对“寓见西山”项目922套房源主要户型进行VR线上看房。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准。；生活便利线索：配租项目为寓见西山保租房，位于海淀组团内，温泉镇古莲路66号，房源共计922套，配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间，同时，中关村温泉科技园围绕青年人才多元文化需求，系统规划贯穿全年的主题社群活动。；下一步，海淀区“两区”建设将进一步筑巢引凤、服务人才，不断完善自贸试验区周边配套设施，全力打造青年人才宜居宜业环境，吸引更多国际优秀创新人才来到海淀、扎根海淀。；双安青年公寓出租房源 · 中关村魏公村知春路海淀黄庄人民大学地铁站，可，随时入住 · 1室1厅 | 42.12㎡ · 中关村 · 独卫一居 可短租 邻地铁 押一付一 配套齐全 精装修 南北通透 有。；国内普通高等学校毕业生提供学历证书或《教育部学历证书电子注册备案表》、学位证书或《中国高等教育学位在线验证报告》；；如2026年1月1日（含）以后毕业的毕业生尚未取得学历、学位证书的，可先行提供《毕业生就业推荐表》（信息应清晰完整并加盖学校公章）或《教育部学籍在线验证报告》；</x:v>
+        <x:v>房屋质量/户型线索：海淀官方配租的青年公寓房源包含开间、一居、两居户型，配齐家具家电可拎包入住；；周边同类公寓多为简单装修，部分小开间为独立厨卫。；生活便利线索：周边昌平邓庄同类小开间月租约800-1000元，海淀中关村青年公寓1室42㎡月租约5510元。；周边同类公寓多为简单装修，部分小开间为独立厨卫。；该地址位于海淀邓庄北路与航天中路交叉口，属于海淀山后区域，暂未搜索到该具体位置的地铁、商超、医院等配套公开评价；；同类昌平邓庄公寓门口有公交站点，周边配套基本完善。；搜索结果中未找到该精确地址对应的青年公寓（公寓式酒店）的直接口碑信息，存在同名项目信息泛化、地址混淆风险，现有信息多为海淀全区青年配租项目或周边其他公寓信息，非目标公寓准确信息。</x:v>
       </x:c>
       <x:c r="O143" t="str">
-        <x:v>1. 选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网 https://www.stdaily.com/web/gdxw/2025-06/06/content_351160.html
-2. 海淀组团内配租922套青年公寓 - 开放北京 https://open.beijing.gov.cn/html//haidian/gzdt/2025/6/1750038168814.html
-3. 北京双安青年公寓租房，最新出租房源，租金走势信息 - 58同城 https://m.58.com/bj/xq/379566
-4. 海淀青年公寓启动试点，922套房源今起向新毕业大学生开放登记 https://m.bjnews.com.cn/detail/1749117682129578.html
-5. 2026年北京海淀区青年公寓配租意向登记公告（房源+租金+申请条件） http://bj.bendibao.com/zffw/202648/381846.shtm</x:v>
+        <x:v>1. ["2161套北京海淀青年公寓启动配租 租金打六折","https://36kr.com/p/3760404621754887"]
+2. ["北京海淀区面向毕业大学生配租2161套房源","https://www.beijing.gov.cn/fuwu/bmfw/sy/jrts/202604/t20260409_4577900.html"]
+3. ["昌平邓庄整租公寓押一付一无中介独立厨卫配置齐全","https://m.anjuke.com/bj/rent/3390771355197452-3/?fromm=&amp;shangquan_id=7425&amp;from=tw_zfdy_txqfy_click&amp;isauction=1"]
+4. ["青年公寓整租 急租 价格可谈 找我可看多套对比","https://m.58.com/bj/zufang/3939695804066829x.shtml"]
+5. 2161套北京海淀青年公寓启动配租 租金打六折 https://36kr.com/p/3760404621754887
+6. 昌平邓庄整租公寓押一付一无中介独立厨卫配置齐全 https://m.anjuke.com/bj/rent/3390771355197452-3/?fromm=&amp;shangquan_id=7425&amp;from=tw_zfdy_txqfy_click&amp;isauction=1
+7. 青年公寓整租 急租 价格可谈 找我可看多套对比 https://m.58.com/bj/zufang/3939695804066829x.shtml
+8. 北京海淀区面向毕业大学生配租2161套房源 https://www.beijing.gov.cn/fuwu/bmfw/sy/jrts/202604/t20260409_4577900.html</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -7303,41 +7698,36 @@
         <x:v>北京市海淀区黑龙潭路58号</x:v>
       </x:c>
       <x:c r="E144" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F144" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G144" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H144" t="n">
-        <x:v>4.5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I144" t="str">
-        <x:v>搜索结果充斥大量无关豪宅信息，缺乏对该公寓本身的实质性描述，参考价值有限。</x:v>
-      </x:c>
-      <x:c r="J144" t="str">
-        <x:v>.. 北京市海淀区白家疃路. 2100-4200元/月；; 海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；海淀租金最高的小区 · 1.中间建筑50000元/月；m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月</x:v>
-      </x:c>
+        <x:v>公开渠道未查询到该公寓的有效质量与配套信息，缺乏决策依据，不建议选择。</x:v>
+      </x:c>
+      <x:c r="J144" t="str"/>
       <x:c r="K144" t="str">
-        <x:v>新出位置安静 可直接入住 楼层好 330平米 三面采. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 清华大学北门 褐石园|190㎡精装大平层 清华陪读优. 15套可看 有钥匙 万城华府龙园 南向一居 价格好谈. 整租·紫竹桥·主语家园·3室·2厅. 拒绝虚假 褐石园 大两居 108平 带车位 实拍. 清华大学南门 蓝旗营 4居室两卫 148平 钥匙房. 实价 北大西门 畅春园 57号 4层三居 实拍 钥匙. 清华大学家属院 双清苑 三居两卫 带车位 随时看. 实价实拍 褐石园别墅 4居室两卫 超大厨房 带2车位. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房。；新出位置安静 可直接入住 楼层好 330平米 三面采. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 清华大学北门 褐石园|190㎡精装大平层 清华陪读优. 15套可看 有钥匙 万城华府龙园 南向一居 价格好谈. 整租·紫竹桥·主语家园·3室·2厅. 拒绝虚假 褐石园 大两居 108平 带车位 实拍. 清华大学南门 蓝旗营 4居室两卫 148平 钥匙房. 实价 北大西门 畅春园 57号 4层三居 实拍 钥匙. 清华大学家属院 双清苑 三居两卫 带车位 随时看. 实价实拍 褐石园别墅 4居室两卫 超大厨房 带2车位. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅 82m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月. 整租南北. 海淀。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。</x:v>
+        <x:v>未搜索到该地址鑫兴公寓关于隔音、户型、房龄、装修、物业的相关质量信息，搜索结果未匹配到目标公寓。</x:v>
       </x:c>
       <x:c r="L144" t="str">
-        <x:v>新出位置安静 可直接入住 楼层好 330平米 三面采. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 清华大学北门 褐石园|190㎡精装大平层 清华陪读优. 15套可看 有钥匙 万城华府龙园 南向一居 价格好谈. 整租·紫竹桥·主语家园·3室·2厅. 拒绝虚假 褐石园 大两居 108平 带车位 实拍. 清华大学南门 蓝旗营 4居室两卫 148平 钥匙房. 实价 北大西门 畅春园 57号 4层三居 实拍 钥匙. 清华大学家属院 双清苑 三居两卫 带车位 随时看. 实价实拍 褐石园别墅 4居室两卫 超大厨房 带2车位. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房。；新出位置安静 可直接入住 楼层好 330平米 三面采. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 清华大学北门 褐石园|190㎡精装大平层 清华陪读优. 15套可看 有钥匙 万城华府龙园 南向一居 价格好谈. 整租·紫竹桥·主语家园·3室·2厅. 拒绝虚假 褐石园 大两居 108平 带车位 实拍. 清华大学南门 蓝旗营 4居室两卫 148平 钥匙房. 实价 北大西门 畅春园 57号 4层三居 实拍 钥匙. 清华大学家属院 双清苑 三居两卫 带车位 随时看. 实价实拍 褐石园别墅 4居室两卫 超大厨房 带2车位. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。</x:v>
-      </x:c>
-      <x:c r="M144" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
-      </x:c>
+        <x:v>未搜索到该地址鑫兴公寓关于通勤、地铁、商超、医院、餐饮的相关便利度信息，搜索结果未匹配到目标公寓。</x:v>
+      </x:c>
+      <x:c r="M144" t="str"/>
       <x:c r="N144" t="str">
-        <x:v>价格线索：.. 北京市海淀区白家疃路. 2100-4200元/月；; 海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；海淀租金最高的小区 · 1.中间建筑50000元/月；m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月；租赁期第1—2、3—4、5—6年租金分别2365元/月；、2759元/月；房屋质量/户型线索：新出位置安静 可直接入住 楼层好 330平米 三面采. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 清华大学北门 褐石园|190㎡精装大平层 清华陪读优. 15套可看 有钥匙 万城华府龙园 南向一居 价格好谈. 整租·紫竹桥·主语家园·3室·2厅. 拒绝虚假 褐石园 大两居 108平 带车位 实拍. 清华大学南门 蓝旗营 4居室两卫 148平 钥匙房. 实价 北大西门 畅春园 57号 4层三居 实拍 钥匙. 清华大学家属院 双清苑 三居两卫 带车位 随时看. 实价实拍 褐石园别墅 4居室两卫 超大厨房 带2车位. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房。；新出位置安静 可直接入住 楼层好 330平米 三面采. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 清华大学北门 褐石园|190㎡精装大平层 清华陪读优. 15套可看 有钥匙 万城华府龙园 南向一居 价格好谈. 整租·紫竹桥·主语家园·3室·2厅. 拒绝虚假 褐石园 大两居 108平 带车位 实拍. 清华大学南门 蓝旗营 4居室两卫 148平 钥匙房. 实价 北大西门 畅春园 57号 4层三居 实拍 钥匙. 清华大学家属院 双清苑 三居两卫 带车位 随时看. 实价实拍 褐石园别墅 4居室两卫 超大厨房 带2车位. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅 82m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月. 整租南北. 海淀。；选定922套高品质房源 北京海淀区启动青年公寓试点工作 - 中国科技网。；# 选定922套高品质房源 北京海淀区启动青年公寓试点工作. 6月5日，记者从北京海淀区获悉，近日，海淀区发布《开展2025年青年公寓专项配租意向登记公告》，正式启动青年公寓试点工作。；生活便利线索：新出位置安静 可直接入住 楼层好 330平米 三面采. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 清华大学北门 褐石园|190㎡精装大平层 清华陪读优. 15套可看 有钥匙 万城华府龙园 南向一居 价格好谈. 整租·紫竹桥·主语家园·3室·2厅. 拒绝虚假 褐石园 大两居 108平 带车位 实拍. 清华大学南门 蓝旗营 4居室两卫 148平 钥匙房. 实价 北大西门 畅春园 57号 4层三居 实拍 钥匙. 清华大学家属院 双清苑 三居两卫 带车位 随时看. 实价实拍 褐石园别墅 4居室两卫 超大厨房 带2车位. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房。；新出位置安静 可直接入住 楼层好 330平米 三面采. 15套可看 万城华府海园 万柳疏书院 多套可看 干净. 25套起看 万柳书院 万城华府海园(五居大平层)1车1车位"). 顶豪 西山美庐 高端社区 半山流水独栋 会所接待 长. 四季青 西山美庐 独栋别墅 随时看房 配套齐全. 康桥水郡 5室3卫3厅 410.24平精装修 126. 世纪城垂虹园精装次卧 中层 家电齐全 房东直租 不收. 清华大学北门 褐石园|190㎡精装大平层 清华陪读优. 15套可看 有钥匙 万城华府龙园 南向一居 价格好谈. 整租·紫竹桥·主语家园·3室·2厅. 拒绝虚假 褐石园 大两居 108平 带车位 实拍. 清华大学南门 蓝旗营 4居室两卫 148平 钥匙房. 实价 北大西门 畅春园 57号 4层三居 实拍 钥匙. 清华大学家属院 双清苑 三居两卫 带车位 随时看. 实价实拍 褐石园别墅 4居室两卫 超大厨房 带2车位. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>房屋质量/户型线索：未搜索到该地址鑫兴公寓关于隔音、户型、房龄、装修、物业的相关质量信息，搜索结果未匹配到目标公寓。；生活便利线索：未搜索到该地址鑫兴公寓关于通勤、地铁、商超、医院、餐饮的相关便利度信息，搜索结果未匹配到目标公寓。</x:v>
       </x:c>
       <x:c r="O144" t="str">
-        <x:v>1. 北京精装公寓出租信息 - 链家 https://m.lianjia.com/chuzu/bj/apartment/amp4amp6
-2. 北京海淀区租房攻略（附租金费用） - 知乎专栏 https://zhuanlan.zhihu.com/p/625328501
-3. 北京海淀租房信息 - 58同城 http://mob.58.com/zf/cd-haidian
-4. 北京精装公寓出租信息-北京贝壳找房 https://m.ke.com/chuzu/bj/apartment
-5. 北京海淀区公寓租房 - 房天下 http://www.fang.com/houses/zf_254312bj</x:v>
+        <x:v>1. 【北京海淀个人房源出租100032元/月以下租房信息 https://fang.com/houses/zf_253749bj/c20-d2100032-h33-i395/
+2. 2026吉林鑫兴馨苑小区，配套指南，买房攻略 https://jl.esf.fang.com/loupan/1711213663/strategy.htm
+3. 【北京海淀区房子出租5000 https://fang.com/houses/zf_253578bj/c25000-d280004-h34-i353/
+4. 无中介 实墙隔音 押一付一 通透大窗 西二期 霍营回龙观 http://m.anjuke.com/bj/rent/3462150180693004-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -7354,39 +7744,40 @@
         <x:v>北京市海淀区冷泉东路北京市中关村外国语学校(海淀校区)东侧约220米</x:v>
       </x:c>
       <x:c r="E145" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F145" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G145" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H145" t="n">
         <x:v>5.5</x:v>
       </x:c>
       <x:c r="I145" t="str">
-        <x:v>位于海淀冷泉区域，离网易大厦较近，但证据混杂了大量无关内容，需实地考察。</x:v>
-      </x:c>
-      <x:c r="J145" t="str">
-        <x:v>前为裸辞状态，需自己交社保（上海灵活就业2238元/月；积在33-92平方米，租金价格3100-8500元/月</x:v>
-      </x:c>
+        <x:v>位于冷泉区域，租金较低且临近地铁，但具体房源信息模糊，需警惕噪音干扰。</x:v>
+      </x:c>
+      <x:c r="J145" t="str"/>
       <x:c r="K145" t="str">
-        <x:v>. 保持舒适甚至高品质生活是对我自己来说的，包括且不局限于：每年出国旅行一次、国内旅行一次、购买想要的电子产品等 一、利用刚毕业的优势 1、大学生就业补贴 建议到小红书上搜索工作所在... 我是个纯正工科生，本科研究生都是学的工科，虽然小时候对“艺术”类的东西很喜欢，但是没有经历过系统培训加上小时候互联网不像现在这么发达，导致一直没有发展出什么兴趣爱好特长之类的... 作为一个： 1.口味刁钻 2.不想吃外卖，因为外卖重油重盐。；户型及租金：提供一房、二房、三房，面积在33-92平方米，租金价格3100-8500元/月. 具体位置：朝阳区康化路安正街16号. 交通：486路、638路. 特色：项目。；户型及租金：提供一房、二房、三房，面积在33-92平方米，租金价格3100-8500元/月. 具体位置：朝阳区康化路安正街16号. 交通：486路、638路. 特色：项目</x:v>
+        <x:v>公开渠道无该公寓明确的房龄、户型、隔音、装修、物业的专属评价信息；；周边同区域类似公寓多为精装修，1室1厅30平米左右户型为主，安保24小时值班，有免费物业管理维修，该公寓地址标注显示靠近地铁线路，部分临近轨道/快速路的周边小区存在低频噪音震动干扰问题。</x:v>
       </x:c>
       <x:c r="L145" t="str">
-        <x:v>先说结论：5月1k挑战惜败... \_(:°з」∠)\_ 本月开销3289元，其中灵活就业22... ### 几个生活得更轻松的小妙招. 1、去健身房游泳馆这些地方洗澡洗头 这样就不用收拾浴室、捡排水口的头发了 健身房游泳馆的热水也很足 洗起来比在家里爽而且省了水费 2、买相同的纯色袜子 最好是纯白袜 这样洗完晒干也不用叠 随手一抓就是一双 永远不会... ### 在五月的最后一天，看落日. ### 记录一下和朋友去越南旅游的穿搭. 本人155cm45kg 梨形身材 朋友158cm 50kg 微梨 我们出去玩的穿搭会很重视【舒适度】！；还想写一些提升生活幸福感的小物，比如杯垫，睡眠眼罩，香氛等。；友邻们如果有推荐的家居好物也请评... ### 很爱做饭，每天都想冲回家做饭. ### 你为啥老不喂我. ### 江浙沪打零工，低成本生活：月开销两千，平淡的幸福。；. 我在南京，租房生活，物欲不高，知足常乐。；. 保持舒适甚至高品质生活是对我自己来说的，包括且不局限于：每年出国旅行一次、国内旅行一次、购买想要的电子产品等 一、利用刚毕业的优势 1、大学生就业补贴 建议到小红书上搜索工作所在... 我是个纯正工科生，本科研究生都是学的工科，虽然小时候对“艺术”类的东西很喜欢，但是没有经历过系统培训加上小时候互联网不像现在这么发达，导致一直没有发展出什么兴趣爱好特长之类的... 作为一个： 1.口味刁钻 2.不想吃外卖，因为外卖重油重盐。</x:v>
-      </x:c>
-      <x:c r="M145" t="str"/>
+        <x:v>公开渠道未查询到该公寓官方公布的明确月租价格，周边同类型海淀西北旺冷泉区域精装1室1厅公寓月租约2200元起，押一付一，无中介费，民水民电。；周边同区域类似公寓多为精装修，1室1厅30平米左右户型为主，安保24小时值班，有免费物业管理维修，该公寓地址标注显示靠近地铁线路，部分临近轨道/快速路的周边小区存在低频噪音震动干扰问题。；该公寓位于海淀区中关村外国语学校海淀校区东侧，周边冷泉区域有餐饮超市配套，距离最近地铁约463米，标注有停车场可免费停车，通勤到西北旺商圈较便利，具体公共交通接驳信息未明确公开。</x:v>
+      </x:c>
+      <x:c r="M145" t="str">
+        <x:v>周边同区域类似公寓多为精装修，1室1厅30平米左右户型为主，安保24小时值班，有免费物业管理维修，该公寓地址标注显示靠近地铁线路，部分临近轨道/快速路的周边小区存在低频噪音震动干扰问题。</x:v>
+      </x:c>
       <x:c r="N145" t="str">
-        <x:v>价格线索：前为裸辞状态，需自己交社保（上海灵活就业2238元/月；积在33-92平方米，租金价格3100-8500元/月；房屋质量/户型线索：. 保持舒适甚至高品质生活是对我自己来说的，包括且不局限于：每年出国旅行一次、国内旅行一次、购买想要的电子产品等 一、利用刚毕业的优势 1、大学生就业补贴 建议到小红书上搜索工作所在... 我是个纯正工科生，本科研究生都是学的工科，虽然小时候对“艺术”类的东西很喜欢，但是没有经历过系统培训加上小时候互联网不像现在这么发达，导致一直没有发展出什么兴趣爱好特长之类的... 作为一个： 1.口味刁钻 2.不想吃外卖，因为外卖重油重盐。；户型及租金：提供一房、二房、三房，面积在33-92平方米，租金价格3100-8500元/月. 具体位置：朝阳区康化路安正街16号. 交通：486路、638路. 特色：项目。；户型及租金：提供一房、二房、三房，面积在33-92平方米，租金价格3100-8500元/月. 具体位置：朝阳区康化路安正街16号. 交通：486路、638路. 特色：项目；生活便利线索：先说结论：5月1k挑战惜败... \_(:°з」∠)\_ 本月开销3289元，其中灵活就业22... ### 几个生活得更轻松的小妙招. 1、去健身房游泳馆这些地方洗澡洗头 这样就不用收拾浴室、捡排水口的头发了 健身房游泳馆的热水也很足 洗起来比在家里爽而且省了水费 2、买相同的纯色袜子 最好是纯白袜 这样洗完晒干也不用叠 随手一抓就是一双 永远不会... ### 在五月的最后一天，看落日. ### 记录一下和朋友去越南旅游的穿搭. 本人155cm45kg 梨形身材 朋友158cm 50kg 微梨 我们出去玩的穿搭会很重视【舒适度】！；还想写一些提升生活幸福感的小物，比如杯垫，睡眠眼罩，香氛等。；友邻们如果有推荐的家居好物也请评... ### 很爱做饭，每天都想冲回家做饭. ### 你为啥老不喂我. ### 江浙沪打零工，低成本生活：月开销两千，平淡的幸福。；. 我在南京，租房生活，物欲不高，知足常乐。；. 保持舒适甚至高品质生活是对我自己来说的，包括且不局限于：每年出国旅行一次、国内旅行一次、购买想要的电子产品等 一、利用刚毕业的优势 1、大学生就业补贴 建议到小红书上搜索工作所在... 我是个纯正工科生，本科研究生都是学的工科，虽然小时候对“艺术”类的东西很喜欢，但是没有经历过系统培训加上小时候互联网不像现在这么发达，导致一直没有发展出什么兴趣爱好特长之类的... 作为一个： 1.口味刁钻 2.不想吃外卖，因为外卖重油重盐。</x:v>
+        <x:v>房屋质量/户型线索：公开渠道无该公寓明确的房龄、户型、隔音、装修、物业的专属评价信息；；周边同区域类似公寓多为精装修，1室1厅30平米左右户型为主，安保24小时值班，有免费物业管理维修，该公寓地址标注显示靠近地铁线路，部分临近轨道/快速路的周边小区存在低频噪音震动干扰问题。；生活便利线索：公开渠道未查询到该公寓官方公布的明确月租价格，周边同类型海淀西北旺冷泉区域精装1室1厅公寓月租约2200元起，押一付一，无中介费，民水民电。；周边同区域类似公寓多为精装修，1室1厅30平米左右户型为主，安保24小时值班，有免费物业管理维修，该公寓地址标注显示靠近地铁线路，部分临近轨道/快速路的周边小区存在低频噪音震动干扰问题。；该公寓位于海淀区中关村外国语学校海淀校区东侧，周边冷泉区域有餐饮超市配套，距离最近地铁约463米，标注有停车场可免费停车，通勤到西北旺商圈较便利，具体公共交通接驳信息未明确公开。；风险线索：周边同区域类似公寓多为精装修，1室1厅30平米左右户型为主，安保24小时值班，有免费物业管理维修，该公寓地址标注显示靠近地铁线路，部分临近轨道/快速路的周边小区存在低频噪音震动干扰问题。</x:v>
       </x:c>
       <x:c r="O145" t="str">
-        <x:v>1. 海淀公寓出租_北京海淀酒店式公寓房屋出租价格，海淀商住两用租房 https://bj.zu.anjuke.com/gongyu-zufang/haidian
-2. 北京海淀租房小组 - 豆瓣 https://m.douban.com/group/haidianzufang
-3. 北京精装公寓出租信息 https://ifeng-m.lianjia.com/chuzu/bj/apartment/haidianqu/amp5amp3ama0
-4. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu/rmp3amp5amp4ama0
-5. 北京租房攻略｜租房价格｜朝阳｜海淀｜东城｜昌平｜合租｜整租 ... https://www.wellcee.com/beijing/m/rent-apartment</x:v>
+        <x:v>1. 【北京完美风暴公寓(冷泉东路分店)】地址，电话，路线，周边设施 https://map.360.cn/shenghuo/detail?pguid=de56f31cb9413057&amp;src=pc_shenbian
+2. 整租|近地铁 通勤方便 环境优美 物业 无中介费 拎包住 http://m.anjuke.com/bj/rent/4547535411764233-3/
+3. 离地铁463米的房子，真能隔绝轨道震动声？ https://m.fang.com/note/bj_2443051.html
+4. 2025 北京租房不踩坑！长租公寓实测科普，应届生 / 白领选房指南 https://m.sohu.com/a/962799449_122498610/
+5. 窗户漏风，多次要求维修敷衍了事 http://liuyan.people.com.cn/threads/content?tid=24479771
+6. “戴耳塞都没有用，因为你的心脏也会跟着震” http://news.qq.com/rain/a/20260521A04G9X00</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -7403,41 +7794,43 @@
         <x:v>北京市海淀区冷泉路冷泉村</x:v>
       </x:c>
       <x:c r="E146" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F146" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G146" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H146" t="n">
-        <x:v>2.5</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="I146" t="str">
-        <x:v>位于朝阳小红门，距网易大厦极远，通勤压力巨大，且证据多为泛化信息，不予推荐。</x:v>
+        <x:v>租金极低且配置全，但位于冷泉区域距网易较远，且信息多为区域泛化，建议谨慎。</x:v>
       </x:c>
       <x:c r="J146" t="str">
-        <x:v>² 朝阳-小红门 鸿博家园(二期D区) 1400元/月；【北京小户型公寓出租10003元/月</x:v>
+        <x:v>域类似整租公寓月租价格范围为1900元-2500元/月</x:v>
       </x:c>
       <x:c r="K146" t="str">
-        <x:v>为您找到以下"高品质小区" 租房房源 - 58同城。；独卫一居邻地铁配套齐全精装修南北通透有阳台首次出租随时看房 · 近塔湾街站短期租月付可谈温馨小房可议价. 1100元2室1厅·93.04㎡. 邻地铁押一付一配套齐全精装修南北通。；【北京小户型公寓出租10003元/月以下租房信息_房屋出租】- 房天下。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。</x:v>
+        <x:v>北京市海淀区冷泉路冷泉村区域类似整租公寓月租价格范围为1900元-2500元/月，户型多为1室1厅1卫，面积多在24-35平米之间，支持押一付一，无中介费，年付可享优惠，价格根据面积、楼层、采光有所浮动；；户型以独门独户1室1厅1卫为主，独立厨卫，部分为实墙设计；；装修多为精装修，部分配备智能控制面板、品牌家电，入住前深度保洁；；隔音方面实墙房源隔音效果较好；；物业自持，24小时安保值班，提供免费维修服务，车位充足可免费停车；</x:v>
       </x:c>
       <x:c r="L146" t="str">
-        <x:v>朝阳-小红门 鸿博家园(二期D区)出租房 鸿博次卧可月付可O押小红门地铁紧邻宋家庄十里河旧宫国贸 3室1厅 10m² 朝阳-小红门 鸿博家园(二期D区) 1400元/月. 距亦庄线-小红门站。；独卫一居邻地铁配套齐全精装修南北通透有阳台首次出租随时看房 · 近塔湾街站短期租月付可谈温馨小房可议价. 1100元2室1厅·93.04㎡. 邻地铁押一付一配套齐全精装修南北通。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。</x:v>
+        <x:v>通勤临近公交，临近地铁沿线，出行较为便利；；周边餐饮、超市、菜店齐全，配套健身房、咖啡厅等设施，生活购物较为方便；；未查询到明确距离大型商超、医院的公开信息；；未查询到公开的差评信息，也未找到该公寓明确的房龄信息，周边地铁具体距离未明确标注。；未查询到公开的差评信息，也未找到该公寓明确的房龄信息，周边地铁具体距离未明确标注</x:v>
       </x:c>
       <x:c r="M146" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未查询到公开的差评信息，也未找到该公寓明确的房龄信息，周边地铁具体距离未明确标注。；未查询到公开的差评信息，也未找到该公寓明确的房龄信息，周边地铁具体距离未明确标注</x:v>
       </x:c>
       <x:c r="N146" t="str">
-        <x:v>价格线索：² 朝阳-小红门 鸿博家园(二期D区) 1400元/月；【北京小户型公寓出租10003元/月；房屋质量/户型线索：为您找到以下"高品质小区" 租房房源 - 58同城。；独卫一居邻地铁配套齐全精装修南北通透有阳台首次出租随时看房 · 近塔湾街站短期租月付可谈温馨小房可议价. 1100元2室1厅·93.04㎡. 邻地铁押一付一配套齐全精装修南北通。；【北京小户型公寓出租10003元/月以下租房信息_房屋出租】- 房天下。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；生活便利线索：朝阳-小红门 鸿博家园(二期D区)出租房 鸿博次卧可月付可O押小红门地铁紧邻宋家庄十里河旧宫国贸 3室1厅 10m² 朝阳-小红门 鸿博家园(二期D区) 1400元/月. 距亦庄线-小红门站。；独卫一居邻地铁配套齐全精装修南北通透有阳台首次出租随时看房 · 近塔湾街站短期租月付可谈温馨小房可议价. 1100元2室1厅·93.04㎡. 邻地铁押一付一配套齐全精装修南北通。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；其中金融大街的租金最高，因为周边有儿童医院、协和医院这样的知名医院，又有高收入群体聚集的金融企业，这里的一居室月平均租金普遍在10000元以上，. 以金融大街板块为例，租金较便宜的丰汇园小区为1999年的板塔结合结构，包括回迁楼、员工宿舍楼、商品楼、办公楼，距离地铁4号线灵境胡同站大约1公里。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：域类似整租公寓月租价格范围为1900元-2500元/月；房屋质量/户型线索：北京市海淀区冷泉路冷泉村区域类似整租公寓月租价格范围为1900元-2500元/月，户型多为1室1厅1卫，面积多在24-35平米之间，支持押一付一，无中介费，年付可享优惠，价格根据面积、楼层、采光有所浮动；；户型以独门独户1室1厅1卫为主，独立厨卫，部分为实墙设计；；装修多为精装修，部分配备智能控制面板、品牌家电，入住前深度保洁；；隔音方面实墙房源隔音效果较好；；物业自持，24小时安保值班，提供免费维修服务，车位充足可免费停车；；生活便利线索：通勤临近公交，临近地铁沿线，出行较为便利；；周边餐饮、超市、菜店齐全，配套健身房、咖啡厅等设施，生活购物较为方便；；未查询到明确距离大型商超、医院的公开信息；；未查询到公开的差评信息，也未找到该公寓明确的房龄信息，周边地铁具体距离未明确标注。；未查询到公开的差评信息，也未找到该公寓明确的房龄信息，周边地铁具体距离未明确标注；风险线索：未查询到公开的差评信息，也未找到该公寓明确的房龄信息，周边地铁具体距离未明确标注。；未查询到公开的差评信息，也未找到该公寓明确的房龄信息，周边地铁具体距离未明确标注</x:v>
       </x:c>
       <x:c r="O146" t="str">
-        <x:v>1. 朝阳小红门租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/chaoyang-q-xiaohongmen
-2. 为您找到以下"高品质小区" 租房房源 - 58同城 https://mob.58.com/zf/sy/ssc-63/xiaohongmen
-3. 【北京小户型公寓出租10003元/月以下租房信息_房屋出租】- 房天下 https://www.fang.com/houses/zf_252973bj/c20-d210003,1,4,2
-4. 在北京租房到底要花多少钱？我们整理了一份5000字的攻略（附100 ... https://m.36kr.com/p/1721780568065
-5. 北京海淀区青年公寓多少钱一个月?租金标准- 北京本地宝 http://bj.bendibao.com/zffw/202566/373172.shtm</x:v>
+        <x:v>1. 整租 小红门公寓 月付 押一付一 近地铁 采光好交通便利 http://m.anjuke.com/bj/rent/3475766568394759-3/
+2. 采光超好 周边配套齐全 公共交通方便快捷 小区内管理规范 http://m.anjuke.com/bj/rent/4467916239660042-3/
+3. 整租|近地铁 通勤方便 环境优美 物业 无中介费 拎包住 http://m.anjuke.com/bj/rent/4547535411764233-3/
+4. 【多图】冷泉村住房，西北旺租房，整租公寓 无中介 押一付一 家电齐全 采光好 隔音好，海淀租房 https://bj.zu.anjuke.com/fangyuan/4157755741019142
+5. 整租精装公寓 物业直签 无中介 可月付 家电齐全 随时看房 http://m.anjuke.com/bj/rent/4518075252317189-3/
+6. 小红门地铁 300m 三户合租朝南卧室带阳台 可短签可长签 http://m.anjuke.com/bj/rent/4554354172402698-3/
+7. 整租丨近地铁丨采光充足丨可月付丨南北通透丨实拍 http://m.anjuke.com/bj/rent/4477858781555722-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -7454,7 +7847,7 @@
         <x:v>北京市海淀区上地柳浪家园南里25号楼</x:v>
       </x:c>
       <x:c r="E147" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F147" t="n">
         <x:v>8</x:v>
@@ -7463,32 +7856,35 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H147" t="n">
-        <x:v>6.2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I147" t="str">
-        <x:v>位于海淀温泉，配套设施较全，虽距软件园有一定距离，但属于海淀区，适合青年群体。</x:v>
+        <x:v>2014年电梯房，环境安静且配套完善，虽距地铁约1.9公里，仍是品质之选。</x:v>
       </x:c>
       <x:c r="J147" t="str">
-        <x:v>; 海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；海淀租金最高的小区 · 1.中间建筑50000元/月；租 1-3个月 4-6个月. 1300-2300元/月；m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月</x:v>
+        <x:v>整租一居室约5200元/月；-5800元/月；，整租两居室约7300元/月；-7500元/月；，合租次卧约2300元/月</x:v>
       </x:c>
       <x:c r="K147" t="str">
-        <x:v>2025-06-06 11:40 来源：北京海淀区人民政府 【我要纠错】. 【导语】：项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；. 项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准. 为落实《北京市关于加快发展保障性租赁住房的实施方案》（京政办发〔2022〕9 号），保障性租赁住房主要用于缓解在本市无房的新市民、青年人等群体住房问题，重点保障新毕业大学生等群体。；海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅 82m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月. 整租南北. 海淀。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。</x:v>
+        <x:v>柳浪家园南里小区建成于2014年，为电梯房；；美锦公寓房源多为精装修，家具家电齐全，采光通风较好；；小区容积率低，绿化面积大，环境安静舒适，24小时有保安；；未查询到明确隔音相关评价，少量反馈夜晚楼梯灯少、楼梯偏陡。</x:v>
       </x:c>
       <x:c r="L147" t="str">
-        <x:v>项目配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间。；这家公寓式酒店的客人可在住宿内部玩桌球，或在周边地区体验骑行。；酒店也靠近东直门交通枢纽，提供了一个游览城市的简易方法。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。</x:v>
+        <x:v>距离16号线农大南路地铁站步行约1.9公里，小区门口有公交车站，通勤出行较为便利；；紧邻南里超市、世纪华联超市，步行可达北京华联BHG Mall，购物方便；；附近有北京市上地医院，周边餐饮设施齐全，还有厢黄旗公园、乡土树木园等休闲绿地，生活配套完善。</x:v>
       </x:c>
       <x:c r="M147" t="str">
-        <x:v>也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>未查询到该公寓集中差评风险信息。</x:v>
       </x:c>
       <x:c r="N147" t="str">
-        <x:v>价格线索：; 海淀租金最高的小区 · 1.中间建筑50000元/月；海淀租金最低的小区 · 1.白水洼村住房1150元/月；淀租金上涨最多的小区 · 1.钓鱼台山庄7200元/月；海淀租金最高的小区 · 1.中间建筑50000元/月；租 1-3个月 4-6个月. 1300-2300元/月；m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月；房屋质量/户型线索：2025-06-06 11:40 来源：北京海淀区人民政府 【我要纠错】. 【导语】：项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；. 项目备案租金均价为109.5元/建筑平米•月(不含物业费)，并实行动态调整。；选房前，如有腾退等原因产生的房源可一并纳入上述配租房源,实际配租房源及相应户型信息以选房现场提供的展板为准. 为落实《北京市关于加快发展保障性租赁住房的实施方案》（京政办发〔2022〕9 号），保障性租赁住房主要用于缓解在本市无房的新市民、青年人等群体住房问题，重点保障新毕业大学生等群体。；海淀-温泉 温泉凯盛家园(二区)出租房源图片 电梯房家具家电齐全精装修南北通透 2室1厅 82m² 海淀-温泉 温泉凯盛家园(二区) 4600元/月. 整租南北. 海淀。；. ### 西城区. 根据北京清华同衡规划设计研究院技术创新中心去年2月份的调查报告显示，西城区重点学区建筑年代在1990年以前的占53%，1990年至今的占47%。；生活便利线索：项目配备智能家电和木质环保家具，配套健身房、社区食堂、会客厅、咖啡书屋等公共空间。；这家公寓式酒店的客人可在住宿内部玩桌球，或在周边地区体验骑行。；酒店也靠近东直门交通枢纽，提供了一个游览城市的简易方法。；不可否认的是，对于每一个在北京生活的人来说，租房都是一堂残酷现实的必修课。；这几个板块也是写字楼、商业、学校最为集中的区域。；风险线索：也就是说，如果你在西城想租学区房，遇见老旧小区的几率是非常大的。；. 新裕家园距离崇文门商圈步行十五分钟，一居、二居月均租金为5869元和9933元，不足处是有些户型朝北临街，噪音大，有些客厅朝北，白天没有阳光。</x:v>
+        <x:v>价格线索：整租一居室约5200元/月；-5800元/月；，整租两居室约7300元/月；-7500元/月；，合租次卧约2300元/月；房屋质量/户型线索：柳浪家园南里小区建成于2014年，为电梯房；；美锦公寓房源多为精装修，家具家电齐全，采光通风较好；；小区容积率低，绿化面积大，环境安静舒适，24小时有保安；；未查询到明确隔音相关评价，少量反馈夜晚楼梯灯少、楼梯偏陡。；生活便利线索：距离16号线农大南路地铁站步行约1.9公里，小区门口有公交车站，通勤出行较为便利；；紧邻南里超市、世纪华联超市，步行可达北京华联BHG Mall，购物方便；；附近有北京市上地医院，周边餐饮设施齐全，还有厢黄旗公园、乡土树木园等休闲绿地，生活配套完善。；风险线索：未查询到该公寓集中差评风险信息。</x:v>
       </x:c>
       <x:c r="O147" t="str">
-        <x:v>1. 北京海淀区租房攻略（附租金费用） https://zhuanlan.zhihu.com/p/625328501
-2. 北京海淀租房信息 http://mob.58.com/zf/cd-haidian
-3. 北京精装公寓出租信息 - 贝壳 https://m.ke.com/chuzu/bj/apartment/haidianqu
-4. 北京海淀区青年公寓多少钱一个月?租金标准 http://bj.bendibao.com/zffw/202566/373172.shtm
-5. 海淀租房租金_价格_房价 https://bj.zu.anjuke.com/fangyuan/haidian</x:v>
+        <x:v>1. ["价格可聊！上地 柳浪家园南里 精装两居 配套齐全 与业主直签","http://m.anjuke.com/bj/rent/4604136062376962-3/"]
+2. ["柳浪家园精装大次卧 临嘉华大厦硅谷亮城 中关村软件园农大西","http://m.anjuke.com/bj/rent/4295465759416326-3/"]
+3. ["上地 柳浪家园南里 精装一居室 价格便宜可谈 配施齐 可长租","http://m.anjuke.com/bj/rent/4135479190088717-3/"]
+4. ["柳浪家园(南里)点评,海淀 马连洼 厢黄旗东路19号,北京马连洼柳浪家园(南里)评价、业主点评、测评信息","https://m.xflapp.com/owner-comment/6580943715689300232/7043696027697709572"]
+5. 价格可聊！上地 柳浪家园南里 精装两居 配套齐全 与业主直签 http://m.anjuke.com/bj/rent/4604136062376962-3/
+6. 柳浪家园精装大次卧 临嘉华大厦硅谷亮城 中关村软件园农大西 http://m.anjuke.com/bj/rent/4295465759416326-3/
+7. 上地 柳浪家园 南北通透两居室 好户型 可长租 价格可聊 http://m.anjuke.com/bj/rent/4568741745449987-3/
+8. 上地 柳浪家园南里 精装一居室 价格便宜可谈 配施齐 可长租 http://m.anjuke.com/bj/rent/4135479190088717-3/</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -7505,39 +7901,44 @@
         <x:v>北京市昌平区回龙观新村龙域北街1号楼2层</x:v>
       </x:c>
       <x:c r="E148" t="str">
-        <x:v>成功(Tavily)</x:v>
+        <x:v>成功(火山)</x:v>
       </x:c>
       <x:c r="F148" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G148" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H148" t="n">
-        <x:v>7.5</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="I148" t="str">
-        <x:v>位于昌平回龙观，通勤距离相对合理，租金性价比高，是网易大厦周边较成熟的租住方案。</x:v>
+        <x:v>地处西二旗核心圈，通勤与医疗极其便利，性价比高，但需警惕房源信息匹配风险。</x:v>
       </x:c>
       <x:c r="J148" t="str">
-        <x:v>... 昌平-回龙观 流星花园三区 1500元/月</x:v>
+        <x:v>同户型价格不同：整租2室1厅约5300-5800元/月；（面积约62-73平米），合租次卧约1550元/月</x:v>
       </x:c>
       <x:c r="K148" t="str">
-        <x:v>品质租住生活新选择. ### 东方豪庭公寓. * [!；. 租金单价中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；. 密云区2026年第三批公租房配租涉及5个项目共74套房源，租金标准20-21元/㎡·月，租金含物业费。</x:v>
+        <x:v>不同户型价格不同：整租2室1厅约5300-5800元/月（面积约62-73平米），合租次卧约1550元/月（面积约15平米），部分房源支持押一付一、0中介费，部分房源收取每月租金9%的服务费。；多为精装修，户型格局规整，采光较好；；未提及明确房龄；；现有公开房源未标注隔音相关评价，物业相关信息较少，部分房源包物业取暖费用，提供家电免费维修服务。；未找到针对该公寓本身的隔音、物业的负面口碑，公开信息中存在北京其他公寓租赁的租客破坏卫生事件，但与该公寓无关，不明确是否有其他隐藏租赁风险。</x:v>
       </x:c>
       <x:c r="L148" t="str">
-        <x:v>: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；... 昌平-回龙观 流星花园三区 1500元/月. 距8号线-平西府站917m. 昌平-回龙观 流星花园三区出租房源图片 8号线平西府流星花园三区南向主卧带卫生间配套全采光佳 3室1厅 20m²。；品质租住生活新选择. ### 东方豪庭公寓. * [!；. * 北京望悦国际社区一键解锁国际菁英健康生活 悦运动 邀加入动型社区健康生活共同体，一键解锁国际菁英健康生活 清晨，跑步者的身影穿梭于社区林荫跑道；</x:v>
-      </x:c>
-      <x:c r="M148" t="str"/>
+        <x:v>通勤：距离18号线龙泽西地铁站约1.4-1.6公里，距离昌平线/13号线西二旗站约1.8公里，周边有公交车站，多条公交线路覆盖；；商超：周边有生鲜超市，步行可达，附近有昌发展万科广场、西二旗益民商城，满足日常购物休闲需求；；医疗：距离北京积水潭医院（新龙泽院区）约750米，就医方便；；餐饮：未找到该公寓周边餐饮的明确口碑评价，小区配套可满足基本做饭需求。</x:v>
+      </x:c>
+      <x:c r="M148" t="str">
+        <x:v>搜索结果未找到该公寓（地址：北京市昌平区回龙观新村龙域北街1号楼2层）的直接专属差评，搜索结果中房源多属于回龙观新村普通住宅，存在同名或地址误匹配的可能性；</x:v>
+      </x:c>
       <x:c r="N148" t="str">
-        <x:v>价格线索：... 昌平-回龙观 流星花园三区 1500元/月；房屋质量/户型线索：品质租住生活新选择. ### 东方豪庭公寓. * [!；. 租金单价中包含物业费，不包含供暖费、水费、电费、燃气费、电话费、上网费、有线电视初装及收视费等。；. 密云区2026年第三批公租房配租涉及5个项目共74套房源，租金标准20-21元/㎡·月，租金含物业费。；生活便利线索：: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|。；: 不限1000元以下1000-2000元2000-3000元3000-5000元5000-8000元8000-10000元-. : 相寓 天通苑·天通苑东三区·高楼层·2居室. : 相寓 天通苑·天通苑东三区·中楼层·4居室·小次卧2. : 相寓 天通苑·天通公园里·高楼层·1居室. : 相寓 天通苑·天通苑北二区·中楼层·3居室·主卧. : 整租·天通苑·天通苑北二区·2室·1厅. : 琥珀郡 交通便利 拎包入住 首次出租 干净整洁 家电. : 龙凤山语 精装一室 电梯中层 家电齐全 好停车 业主. : 石坊院 昌平地铁 干净整洁 家电齐全 随时入住 看房. : 相寓 天通苑·天通苑本四区·高楼层·7居室·次卧5. : 相寓 天通苑·公园两栋·高楼层·1房间. : 国惠村 电梯高层 干净整洁 家电家具齐全 业主双包. : 蓝郡国际花园 电梯一居 干净整洁 家具家电齐全 看房. : 路劲世界城 电梯两居 干净整洁 家电家具齐全 看房方. : 石坊院一居 干净整洁 家电齐全 交通便利 配套齐全. : 西三旗 西小口 育新 三旗百汇 霍营地铁口 瑞旗家园. 关于我们|网站合作|联系我们|招聘信息|各地租房|网站地图|意见反馈|手机房天下|开放平台|服务声明|加盟房天下. | **B** | 北京租房 | **D** | 东莞租房 | | 海南租房 | | 南宁租房 | | 沈阳租房 |. | **C** | 成都租房 | | 大连租房 | | 合肥租房 | **Q** | 青岛租房 | **T** | 天津租房 |. | | 重庆租房 | **F** | 福州租房 | **J** | 济南租房 | **S** | 上海租房 | **W** | 武汉租房 |. | | 长沙租房 | **G** | 广州租房 | **N** | 南京租房 | | 深圳租房 | | 无锡租房 |. | | 长春租房 | | 贵阳租房 | | 南昌租房 | | 苏州租房 | **X** | 西安租房 |.。；... 昌平-回龙观 流星花园三区 1500元/月. 距8号线-平西府站917m. 昌平-回龙观 流星花园三区出租房源图片 8号线平西府流星花园三区南向主卧带卫生间配套全采光佳 3室1厅 20m²。；品质租住生活新选择. ### 东方豪庭公寓. * [!；. * 北京望悦国际社区一键解锁国际菁英健康生活 悦运动 邀加入动型社区健康生活共同体，一键解锁国际菁英健康生活 清晨，跑步者的身影穿梭于社区林荫跑道；</x:v>
+        <x:v>价格线索：同户型价格不同：整租2室1厅约5300-5800元/月；（面积约62-73平米），合租次卧约1550元/月；房屋质量/户型线索：不同户型价格不同：整租2室1厅约5300-5800元/月（面积约62-73平米），合租次卧约1550元/月（面积约15平米），部分房源支持押一付一、0中介费，部分房源收取每月租金9%的服务费。；多为精装修，户型格局规整，采光较好；；未提及明确房龄；；现有公开房源未标注隔音相关评价，物业相关信息较少，部分房源包物业取暖费用，提供家电免费维修服务。；未找到针对该公寓本身的隔音、物业的负面口碑，公开信息中存在北京其他公寓租赁的租客破坏卫生事件，但与该公寓无关，不明确是否有其他隐藏租赁风险。；生活便利线索：通勤：距离18号线龙泽西地铁站约1.4-1.6公里，距离昌平线/13号线西二旗站约1.8公里，周边有公交车站，多条公交线路覆盖；；商超：周边有生鲜超市，步行可达，附近有昌发展万科广场、西二旗益民商城，满足日常购物休闲需求；；医疗：距离北京积水潭医院（新龙泽院区）约750米，就医方便；；餐饮：未找到该公寓周边餐饮的明确口碑评价，小区配套可满足基本做饭需求。；风险线索：搜索结果未找到该公寓（地址：北京市昌平区回龙观新村龙域北街1号楼2层）的直接专属差评，搜索结果中房源多属于回龙观新村普通住宅，存在同名或地址误匹配的可能性；</x:v>
       </x:c>
       <x:c r="O148" t="str">
-        <x:v>1. 北京昌平租房信息 - 58同城 http://mob.58.com/zf/hk-changping
-2. 北京酒店式公寓-出租（长租、短租、月租）-北京服务式公寓预订网 https://www.yudinggongyu.com
-3. 北京市昌平区租房 - 房天下 http://www.fang.com/houses/zf_253758bj
-4. 昌平租房租金_价格_房价|房产网-安居客北京租房网 https://bj.zu.anjuke.com/fangyuan/changping
-5. 北京酒店式公寓租房网: 北京酒店式公寓出租-北京服务式租房价格 https://www.gongyuzufang.com</x:v>
+        <x:v>1. ["回龙观新村，西二旗，小米快手元中心，昌发展，0押月付，全南向","http://m.anjuke.com/bj/rent/4522991498470414-3/"]
+2. ["回龙观新村全南两居室 看房随时 价格可聊","http://m.anjuke.com/bj/rent/4594150206270464-3/"]
+3. ["回龙观新村 直签 主次卧 积水潭 昌发展 西二旗 软件园","http://m.anjuke.com/bj/rent/4495086221812737-3/"]
+4. 回龙观新村，西二旗，小米快手元中心，昌发展，0押月付，全南向 http://m.anjuke.com/bj/rent/4522991498470414-3/
+5. 公寓租客恶行：满地垃圾与恶臭马桶让房东崩溃 https://m.sohu.com/a/1001466089_121956424/
+6. 回龙观新村全南两居室 看房随时 价格可聊 http://m.anjuke.com/bj/rent/4594150206270464-3/
+7. 公寓被租客弄得满地垃圾难下脚，马桶满是排泄物！房东：头一回遇到这种事 https://finance.sina.com.cn/jjxw/2026-03-26/doc-inhsicus0251238.shtml
+8. 回龙观新村 直签 主次卧 积水潭 昌发展 西二旗 软件园 http://m.anjuke.com/bj/rent/4495086221812737-3/</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
